--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,14 +416,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E543"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,10 +445,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>price_00:30</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -466,10 +472,13 @@
         <v>71663.39999999999</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>71323.7</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>71818.39999999999</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>71663.39999999999</v>
+      <c r="F2" s="1" t="n">
+        <v>71323.7</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +494,13 @@
         <v>2126.71</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>2118.6</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>2127.37</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>2126.71</v>
+      <c r="F3" s="1" t="n">
+        <v>2118.6</v>
       </c>
     </row>
     <row r="4">
@@ -504,10 +516,13 @@
         <v>89.59</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>89.59</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>89.45</v>
+      <c r="F4" s="1" t="n">
+        <v>89.23</v>
       </c>
     </row>
     <row r="5">
@@ -523,9 +538,12 @@
         <v>3.861</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>3.861</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -542,10 +560,13 @@
         <v>1.4085</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>1.4035</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>1.4085</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>1.4082</v>
+      <c r="F6" s="1" t="n">
+        <v>1.4035</v>
       </c>
     </row>
     <row r="7">
@@ -561,10 +582,13 @@
         <v>0.09828000000000001</v>
       </c>
       <c r="D7" s="1" t="n">
+        <v>0.09765</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>0.09796000000000001</v>
+      <c r="F7" s="1" t="n">
+        <v>0.09765</v>
       </c>
     </row>
     <row r="8">
@@ -580,10 +604,13 @@
         <v>0.014478</v>
       </c>
       <c r="D8" s="1" t="n">
+        <v>0.014158</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>0.014478</v>
+      <c r="F8" s="1" t="n">
+        <v>0.014158</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +626,13 @@
         <v>660.9299999999999</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>659.95</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>662.61</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>660.9299999999999</v>
+      <c r="F9" s="1" t="n">
+        <v>659.95</v>
       </c>
     </row>
     <row r="10">
@@ -618,9 +648,12 @@
         <v>19.415</v>
       </c>
       <c r="D10" s="1" t="n">
+        <v>19.149</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>19.415</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -637,10 +670,13 @@
         <v>0.0034747</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>0.0034668</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>0.0034782</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>0.0034747</v>
+      <c r="F11" s="1" t="n">
+        <v>0.0034668</v>
       </c>
     </row>
     <row r="12">
@@ -656,10 +692,13 @@
         <v>36.304</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>36.163</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>36.304</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>36.244</v>
+      <c r="F12" s="1" t="n">
+        <v>36.163</v>
       </c>
     </row>
     <row r="13">
@@ -675,9 +714,12 @@
         <v>213.55</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>213.55</v>
+        <v>213.78</v>
       </c>
       <c r="E13" s="1" t="n">
+        <v>213.78</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>213.2</v>
       </c>
     </row>
@@ -694,10 +736,13 @@
         <v>0.0011346</v>
       </c>
       <c r="D14" s="1" t="n">
+        <v>0.0011277</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>0.0011346</v>
+      <c r="F14" s="1" t="n">
+        <v>0.0011277</v>
       </c>
     </row>
     <row r="15">
@@ -713,9 +758,12 @@
         <v>0.28578</v>
       </c>
       <c r="D15" s="1" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="F15" s="1" t="n">
         <v>0.28578</v>
       </c>
     </row>
@@ -732,9 +780,12 @@
         <v>234.41</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>233.01</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>234.41</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="F16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -751,10 +802,13 @@
         <v>1.0133</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>1.0137</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>1.0133</v>
+      <c r="F17" s="1" t="n">
+        <v>1.012</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +824,13 @@
         <v>0.2717</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>0.2717</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>0.2714</v>
+      <c r="F18" s="1" t="n">
+        <v>0.2713</v>
       </c>
     </row>
     <row r="19">
@@ -789,10 +846,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>9.859</v>
+      </c>
+      <c r="E19" s="1" t="n">
         <v>9.893000000000001</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>9.890000000000001</v>
+      <c r="F19" s="1" t="n">
+        <v>9.859</v>
       </c>
     </row>
     <row r="20">
@@ -808,9 +868,12 @@
         <v>5033.31</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>5035.65</v>
+        <v>5042.6</v>
       </c>
       <c r="E20" s="1" t="n">
+        <v>5042.6</v>
+      </c>
+      <c r="F20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -827,9 +890,12 @@
         <v>462.57</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>462.95</v>
+      </c>
+      <c r="E21" s="1" t="n">
         <v>463.29</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>462.57</v>
       </c>
     </row>
@@ -846,9 +912,12 @@
         <v>1.4248</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>1.4248</v>
+        <v>1.4336</v>
       </c>
       <c r="E22" s="1" t="n">
+        <v>1.4336</v>
+      </c>
+      <c r="F22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -865,9 +934,12 @@
         <v>1.1445</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="F23" s="1" t="n">
         <v>1.1298</v>
       </c>
     </row>
@@ -884,9 +956,12 @@
         <v>1.36</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>1.36</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="F24" s="1" t="n">
         <v>1.351</v>
       </c>
     </row>
@@ -903,10 +978,13 @@
         <v>9.257</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>9.246</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>9.260999999999999</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>9.257</v>
+      <c r="F25" s="1" t="n">
+        <v>9.246</v>
       </c>
     </row>
     <row r="26">
@@ -922,10 +1000,13 @@
         <v>0.3714</v>
       </c>
       <c r="D26" s="1" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>0.3749</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>0.3714</v>
+      <c r="F26" s="1" t="n">
+        <v>0.368</v>
       </c>
     </row>
     <row r="27">
@@ -941,9 +1022,12 @@
         <v>0.887</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.887</v>
+        <v>0.889</v>
       </c>
       <c r="E27" s="1" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>0.887</v>
       </c>
     </row>
@@ -960,10 +1044,13 @@
         <v>1.803</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>1.787</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>1.803</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>1.798</v>
+      <c r="F28" s="1" t="n">
+        <v>1.787</v>
       </c>
     </row>
     <row r="29">
@@ -979,9 +1066,12 @@
         <v>0.1115</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>0.112</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="F29" s="1" t="n">
         <v>0.1115</v>
       </c>
     </row>
@@ -998,10 +1088,13 @@
         <v>0.002059</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>0.002054</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>0.002059</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>0.002058</v>
+      <c r="F30" s="1" t="n">
+        <v>0.002054</v>
       </c>
     </row>
     <row r="31">
@@ -1017,10 +1110,13 @@
         <v>1.504</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>1.506</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>1.504</v>
+      <c r="F31" s="1" t="n">
+        <v>1.499</v>
       </c>
     </row>
     <row r="32">
@@ -1036,10 +1132,13 @@
         <v>0.178</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>0.178</v>
+      <c r="F32" s="1" t="n">
+        <v>0.177</v>
       </c>
     </row>
     <row r="33">
@@ -1055,10 +1154,13 @@
         <v>0.1049</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>0.1048</v>
+      <c r="F33" s="1" t="n">
+        <v>0.1045</v>
       </c>
     </row>
     <row r="34">
@@ -1074,10 +1176,13 @@
         <v>113.94</v>
       </c>
       <c r="D34" s="1" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="E34" s="1" t="n">
         <v>113.97</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>113.94</v>
+      <c r="F34" s="1" t="n">
+        <v>113.65</v>
       </c>
     </row>
     <row r="35">
@@ -1093,10 +1198,13 @@
         <v>6.776</v>
       </c>
       <c r="D35" s="1" t="n">
+        <v>6.772</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>6.893</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>6.776</v>
+      <c r="F35" s="1" t="n">
+        <v>6.772</v>
       </c>
     </row>
     <row r="36">
@@ -1112,9 +1220,12 @@
         <v>0.017384</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.017384</v>
+        <v>0.017415</v>
       </c>
       <c r="E36" s="1" t="n">
+        <v>0.017415</v>
+      </c>
+      <c r="F36" s="1" t="n">
         <v>0.017313</v>
       </c>
     </row>
@@ -1131,10 +1242,13 @@
         <v>0.3667</v>
       </c>
       <c r="D37" s="1" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>0.3667</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>0.3666</v>
+      <c r="F37" s="1" t="n">
+        <v>0.3656</v>
       </c>
     </row>
     <row r="38">
@@ -1150,9 +1264,12 @@
         <v>55.42</v>
       </c>
       <c r="D38" s="1" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>55.42</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="F38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1169,9 +1286,12 @@
         <v>0.58131</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.58963</v>
+        <v>0.5914700000000001</v>
       </c>
       <c r="E39" s="1" t="n">
+        <v>0.5914700000000001</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1188,10 +1308,13 @@
         <v>4.057</v>
       </c>
       <c r="D40" s="1" t="n">
+        <v>4.051</v>
+      </c>
+      <c r="E40" s="1" t="n">
         <v>4.064</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>4.057</v>
+      <c r="F40" s="1" t="n">
+        <v>4.051</v>
       </c>
     </row>
     <row r="41">
@@ -1207,9 +1330,12 @@
         <v>0.04927</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.04938</v>
+        <v>0.04957</v>
       </c>
       <c r="E41" s="1" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="F41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -1226,10 +1352,13 @@
         <v>0.7034</v>
       </c>
       <c r="D42" s="1" t="n">
+        <v>0.7017</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>0.7056</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>0.7034</v>
+      <c r="F42" s="1" t="n">
+        <v>0.7017</v>
       </c>
     </row>
     <row r="43">
@@ -1245,9 +1374,12 @@
         <v>0.23341</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.23341</v>
+        <v>0.23491</v>
       </c>
       <c r="E43" s="1" t="n">
+        <v>0.23491</v>
+      </c>
+      <c r="F43" s="1" t="n">
         <v>0.23323</v>
       </c>
     </row>
@@ -1264,10 +1396,13 @@
         <v>0.35392</v>
       </c>
       <c r="D44" s="1" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>0.35392</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>0.35391</v>
+      <c r="F44" s="1" t="n">
+        <v>0.35261</v>
       </c>
     </row>
     <row r="45">
@@ -1283,9 +1418,12 @@
         <v>0.1714</v>
       </c>
       <c r="D45" s="1" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>0.1731</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="F45" s="1" t="n">
         <v>0.1714</v>
       </c>
     </row>
@@ -1302,9 +1440,12 @@
         <v>0.0264</v>
       </c>
       <c r="D46" s="1" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="E46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="F46" s="1" t="n">
         <v>0.0264</v>
       </c>
     </row>
@@ -1321,10 +1462,13 @@
         <v>0.006043</v>
       </c>
       <c r="D47" s="1" t="n">
+        <v>0.006032</v>
+      </c>
+      <c r="E47" s="1" t="n">
         <v>0.00605</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>0.006043</v>
+      <c r="F47" s="1" t="n">
+        <v>0.006032</v>
       </c>
     </row>
     <row r="48">
@@ -1340,10 +1484,13 @@
         <v>0.007513</v>
       </c>
       <c r="D48" s="1" t="n">
+        <v>0.007479</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>0.007515</v>
       </c>
-      <c r="E48" s="1" t="n">
-        <v>0.007513</v>
+      <c r="F48" s="1" t="n">
+        <v>0.007479</v>
       </c>
     </row>
     <row r="49">
@@ -1359,10 +1506,13 @@
         <v>0.1108</v>
       </c>
       <c r="D49" s="1" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>0.1111</v>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>0.1108</v>
+      <c r="F49" s="1" t="n">
+        <v>0.1105</v>
       </c>
     </row>
     <row r="50">
@@ -1378,10 +1528,13 @@
         <v>0.04033</v>
       </c>
       <c r="D50" s="1" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>0.04046</v>
       </c>
-      <c r="E50" s="1" t="n">
-        <v>0.04033</v>
+      <c r="F50" s="1" t="n">
+        <v>0.04017</v>
       </c>
     </row>
     <row r="51">
@@ -1397,10 +1550,13 @@
         <v>0.1659</v>
       </c>
       <c r="D51" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="E51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="E51" s="1" t="n">
-        <v>0.1659</v>
+      <c r="F51" s="1" t="n">
+        <v>0.1658</v>
       </c>
     </row>
     <row r="52">
@@ -1416,9 +1572,12 @@
         <v>0.00355</v>
       </c>
       <c r="D52" s="1" t="n">
+        <v>0.00354</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>0.00355</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="F52" s="1" t="n">
         <v>0.00354</v>
       </c>
     </row>
@@ -1435,10 +1594,13 @@
         <v>2.662</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="E53" s="1" t="n">
-        <v>2.662</v>
+      <c r="F53" s="1" t="n">
+        <v>2.645</v>
       </c>
     </row>
     <row r="54">
@@ -1454,10 +1616,13 @@
         <v>0.006277</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>0.006263</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>0.006298</v>
       </c>
-      <c r="E54" s="1" t="n">
-        <v>0.006277</v>
+      <c r="F54" s="1" t="n">
+        <v>0.006263</v>
       </c>
     </row>
     <row r="55">
@@ -1473,10 +1638,13 @@
         <v>0.02989</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>0.02927</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="E55" s="1" t="n">
-        <v>0.02989</v>
+      <c r="F55" s="1" t="n">
+        <v>0.02927</v>
       </c>
     </row>
     <row r="56">
@@ -1492,10 +1660,13 @@
         <v>0.7443</v>
       </c>
       <c r="D56" s="1" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+      <c r="E56" s="1" t="n">
         <v>0.7463</v>
       </c>
-      <c r="E56" s="1" t="n">
-        <v>0.7443</v>
+      <c r="F56" s="1" t="n">
+        <v>0.7433999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1511,10 +1682,13 @@
         <v>0.1048</v>
       </c>
       <c r="D57" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="E57" s="1" t="n">
-        <v>0.1048</v>
+      <c r="F57" s="1" t="n">
+        <v>0.104</v>
       </c>
     </row>
     <row r="58">
@@ -1530,10 +1704,13 @@
         <v>0.9523</v>
       </c>
       <c r="D58" s="1" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>0.9523</v>
+      <c r="F58" s="1" t="n">
+        <v>0.9505</v>
       </c>
     </row>
     <row r="59">
@@ -1549,9 +1726,12 @@
         <v>0.08391</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>0.08391</v>
+        <v>0.08542</v>
       </c>
       <c r="E59" s="1" t="n">
+        <v>0.08542</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -1568,10 +1748,13 @@
         <v>0.06947</v>
       </c>
       <c r="D60" s="1" t="n">
+        <v>0.06924</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>0.07001</v>
       </c>
-      <c r="E60" s="1" t="n">
-        <v>0.06947</v>
+      <c r="F60" s="1" t="n">
+        <v>0.06924</v>
       </c>
     </row>
     <row r="61">
@@ -1587,9 +1770,12 @@
         <v>0.05482</v>
       </c>
       <c r="D61" s="1" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>0.05482</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="F61" s="1" t="n">
         <v>0.05469</v>
       </c>
     </row>
@@ -1606,9 +1792,12 @@
         <v>0.009571</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>0.009571</v>
+        <v>0.009769</v>
       </c>
       <c r="E62" s="1" t="n">
+        <v>0.009769</v>
+      </c>
+      <c r="F62" s="1" t="n">
         <v>0.009535999999999999</v>
       </c>
     </row>
@@ -1625,9 +1814,12 @@
         <v>0.28956</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>0.28956</v>
+        <v>0.2896</v>
       </c>
       <c r="E63" s="1" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="F63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -1644,9 +1836,12 @@
         <v>0.07034</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0.07034</v>
+        <v>0.07234</v>
       </c>
       <c r="E64" s="1" t="n">
+        <v>0.07234</v>
+      </c>
+      <c r="F64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -1663,9 +1858,12 @@
         <v>0.3068</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>0.3073</v>
+        <v>0.31</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -1682,10 +1880,13 @@
         <v>0.1636</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>0.16337</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>0.1636</v>
       </c>
-      <c r="E66" s="1" t="n">
-        <v>0.16346</v>
+      <c r="F66" s="1" t="n">
+        <v>0.16337</v>
       </c>
     </row>
     <row r="67">
@@ -1701,9 +1902,12 @@
         <v>0.11988</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>0.11988</v>
+        <v>0.11997</v>
       </c>
       <c r="E67" s="1" t="n">
+        <v>0.11997</v>
+      </c>
+      <c r="F67" s="1" t="n">
         <v>0.11934</v>
       </c>
     </row>
@@ -1720,10 +1924,13 @@
         <v>0.09712</v>
       </c>
       <c r="D68" s="1" t="n">
+        <v>0.09666</v>
+      </c>
+      <c r="E68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="E68" s="1" t="n">
-        <v>0.09712</v>
+      <c r="F68" s="1" t="n">
+        <v>0.09666</v>
       </c>
     </row>
     <row r="69">
@@ -1739,10 +1946,13 @@
         <v>0.1254</v>
       </c>
       <c r="D69" s="1" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="E69" s="1" t="n">
         <v>0.1259</v>
       </c>
-      <c r="E69" s="1" t="n">
-        <v>0.1254</v>
+      <c r="F69" s="1" t="n">
+        <v>0.1247</v>
       </c>
     </row>
     <row r="70">
@@ -1758,10 +1968,13 @@
         <v>8.582000000000001</v>
       </c>
       <c r="D70" s="1" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>8.582000000000001</v>
       </c>
-      <c r="E70" s="1" t="n">
-        <v>8.567</v>
+      <c r="F70" s="1" t="n">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -1777,11 +1990,14 @@
         <v>0.24</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>0.24</v>
+        <v>0.239</v>
       </c>
       <c r="E71" s="1" t="n">
         <v>0.24</v>
       </c>
+      <c r="F71" s="1" t="n">
+        <v>0.239</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1796,9 +2012,12 @@
         <v>0.05163</v>
       </c>
       <c r="D72" s="1" t="n">
+        <v>0.05164</v>
+      </c>
+      <c r="E72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="F72" s="1" t="n">
         <v>0.05163</v>
       </c>
     </row>
@@ -1815,10 +2034,13 @@
         <v>0.05059</v>
       </c>
       <c r="D73" s="1" t="n">
+        <v>0.05013</v>
+      </c>
+      <c r="E73" s="1" t="n">
         <v>0.05059</v>
       </c>
-      <c r="E73" s="1" t="n">
-        <v>0.05039</v>
+      <c r="F73" s="1" t="n">
+        <v>0.05013</v>
       </c>
     </row>
     <row r="74">
@@ -1834,9 +2056,12 @@
         <v>0.1252</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>0.1253</v>
+        <v>0.1257</v>
       </c>
       <c r="E74" s="1" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="F74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -1853,9 +2078,12 @@
         <v>0.04688</v>
       </c>
       <c r="D75" s="1" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="E75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="F75" s="1" t="n">
         <v>0.04688</v>
       </c>
     </row>
@@ -1872,10 +2100,13 @@
         <v>0.06786</v>
       </c>
       <c r="D76" s="1" t="n">
+        <v>0.06743</v>
+      </c>
+      <c r="E76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="E76" s="1" t="n">
-        <v>0.06758</v>
+      <c r="F76" s="1" t="n">
+        <v>0.06743</v>
       </c>
     </row>
     <row r="77">
@@ -1891,9 +2122,12 @@
         <v>0.12881</v>
       </c>
       <c r="D77" s="1" t="n">
+        <v>0.12796</v>
+      </c>
+      <c r="E77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="E77" s="1" t="n">
+      <c r="F77" s="1" t="n">
         <v>0.12685</v>
       </c>
     </row>
@@ -1910,10 +2144,13 @@
         <v>0.1646</v>
       </c>
       <c r="D78" s="1" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="E78" s="1" t="n">
-        <v>0.1646</v>
+      <c r="F78" s="1" t="n">
+        <v>0.1624</v>
       </c>
     </row>
     <row r="79">
@@ -1929,9 +2166,12 @@
         <v>0.0272</v>
       </c>
       <c r="D79" s="1" t="n">
+        <v>0.02725</v>
+      </c>
+      <c r="E79" s="1" t="n">
         <v>0.02738</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="F79" s="1" t="n">
         <v>0.0272</v>
       </c>
     </row>
@@ -1948,10 +2188,13 @@
         <v>354.29</v>
       </c>
       <c r="D80" s="1" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="E80" s="1" t="n">
         <v>354.5</v>
       </c>
-      <c r="E80" s="1" t="n">
-        <v>354.29</v>
+      <c r="F80" s="1" t="n">
+        <v>354.1</v>
       </c>
     </row>
     <row r="81">
@@ -1967,10 +2210,13 @@
         <v>7.211999999999999e-05</v>
       </c>
       <c r="D81" s="1" t="n">
+        <v>7.196e-05</v>
+      </c>
+      <c r="E81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="E81" s="1" t="n">
-        <v>7.211999999999999e-05</v>
+      <c r="F81" s="1" t="n">
+        <v>7.196e-05</v>
       </c>
     </row>
     <row r="82">
@@ -1986,10 +2232,13 @@
         <v>0.2676</v>
       </c>
       <c r="D82" s="1" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="E82" s="1" t="n">
         <v>0.2681</v>
       </c>
-      <c r="E82" s="1" t="n">
-        <v>0.2676</v>
+      <c r="F82" s="1" t="n">
+        <v>0.2672</v>
       </c>
     </row>
     <row r="83">
@@ -2005,9 +2254,12 @@
         <v>1.1408</v>
       </c>
       <c r="D83" s="1" t="n">
+        <v>1.1418</v>
+      </c>
+      <c r="E83" s="1" t="n">
         <v>1.1447</v>
       </c>
-      <c r="E83" s="1" t="n">
+      <c r="F83" s="1" t="n">
         <v>1.1408</v>
       </c>
     </row>
@@ -2024,10 +2276,13 @@
         <v>0.3591</v>
       </c>
       <c r="D84" s="1" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="E84" s="1" t="n">
         <v>0.3592</v>
       </c>
-      <c r="E84" s="1" t="n">
-        <v>0.3591</v>
+      <c r="F84" s="1" t="n">
+        <v>0.3569</v>
       </c>
     </row>
     <row r="85">
@@ -2043,9 +2298,12 @@
         <v>2.0067</v>
       </c>
       <c r="D85" s="1" t="n">
+        <v>2.0118</v>
+      </c>
+      <c r="E85" s="1" t="n">
         <v>2.0181</v>
       </c>
-      <c r="E85" s="1" t="n">
+      <c r="F85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -2062,10 +2320,13 @@
         <v>1.3126</v>
       </c>
       <c r="D86" s="1" t="n">
+        <v>1.3103</v>
+      </c>
+      <c r="E86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="E86" s="1" t="n">
-        <v>1.3126</v>
+      <c r="F86" s="1" t="n">
+        <v>1.3103</v>
       </c>
     </row>
     <row r="87">
@@ -2084,6 +2345,9 @@
         <v>33.01</v>
       </c>
       <c r="E87" s="1" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="F87" s="1" t="n">
         <v>32.97</v>
       </c>
     </row>
@@ -2100,9 +2364,12 @@
         <v>0.01071</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>0.01071</v>
+        <v>0.01074</v>
       </c>
       <c r="E88" s="1" t="n">
+        <v>0.01074</v>
+      </c>
+      <c r="F88" s="1" t="n">
         <v>0.01046</v>
       </c>
     </row>
@@ -2119,10 +2386,13 @@
         <v>0.01832</v>
       </c>
       <c r="D89" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="E89" s="1" t="n">
-        <v>0.01832</v>
+      <c r="F89" s="1" t="n">
+        <v>0.01828</v>
       </c>
     </row>
     <row r="90">
@@ -2138,9 +2408,12 @@
         <v>0.03619</v>
       </c>
       <c r="D90" s="1" t="n">
+        <v>0.03586</v>
+      </c>
+      <c r="E90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="E90" s="1" t="n">
+      <c r="F90" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -2157,10 +2430,13 @@
         <v>0.01194</v>
       </c>
       <c r="D91" s="1" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="E91" s="1" t="n">
         <v>0.01202</v>
       </c>
-      <c r="E91" s="1" t="n">
-        <v>0.01194</v>
+      <c r="F91" s="1" t="n">
+        <v>0.01192</v>
       </c>
     </row>
     <row r="92">
@@ -2176,10 +2452,13 @@
         <v>3.118</v>
       </c>
       <c r="D92" s="1" t="n">
+        <v>3.111</v>
+      </c>
+      <c r="E92" s="1" t="n">
         <v>3.12</v>
       </c>
-      <c r="E92" s="1" t="n">
-        <v>3.118</v>
+      <c r="F92" s="1" t="n">
+        <v>3.111</v>
       </c>
     </row>
     <row r="93">
@@ -2195,10 +2474,13 @@
         <v>0.00564</v>
       </c>
       <c r="D93" s="1" t="n">
+        <v>0.005635</v>
+      </c>
+      <c r="E93" s="1" t="n">
         <v>0.00564</v>
       </c>
-      <c r="E93" s="1" t="n">
-        <v>0.005638</v>
+      <c r="F93" s="1" t="n">
+        <v>0.005635</v>
       </c>
     </row>
     <row r="94">
@@ -2214,9 +2496,12 @@
         <v>0.0945</v>
       </c>
       <c r="D94" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="E94" s="1" t="n">
         <v>0.0945</v>
       </c>
-      <c r="E94" s="1" t="n">
+      <c r="F94" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -2233,9 +2518,12 @@
         <v>0.6028</v>
       </c>
       <c r="D95" s="1" t="n">
+        <v>0.6025</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>0.6028</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="F95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -2252,10 +2540,13 @@
         <v>1.29e-05</v>
       </c>
       <c r="D96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="E96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="E96" s="1" t="n">
-        <v>1.29e-05</v>
+      <c r="F96" s="1" t="n">
+        <v>1.28e-05</v>
       </c>
     </row>
     <row r="97">
@@ -2271,9 +2562,12 @@
         <v>1.143</v>
       </c>
       <c r="D97" s="1" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>1.143</v>
       </c>
-      <c r="E97" s="1" t="n">
+      <c r="F97" s="1" t="n">
         <v>1.136</v>
       </c>
     </row>
@@ -2290,10 +2584,13 @@
         <v>0.25933</v>
       </c>
       <c r="D98" s="1" t="n">
+        <v>0.25703</v>
+      </c>
+      <c r="E98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="E98" s="1" t="n">
-        <v>0.25933</v>
+      <c r="F98" s="1" t="n">
+        <v>0.25703</v>
       </c>
     </row>
     <row r="99">
@@ -2309,10 +2606,13 @@
         <v>1.15</v>
       </c>
       <c r="D99" s="1" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="E99" s="1" t="n">
         <v>1.151</v>
       </c>
-      <c r="E99" s="1" t="n">
-        <v>1.15</v>
+      <c r="F99" s="1" t="n">
+        <v>1.146</v>
       </c>
     </row>
     <row r="100">
@@ -2328,10 +2628,13 @@
         <v>1.864</v>
       </c>
       <c r="D100" s="1" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>1.866</v>
       </c>
-      <c r="E100" s="1" t="n">
-        <v>1.864</v>
+      <c r="F100" s="1" t="n">
+        <v>1.862</v>
       </c>
     </row>
     <row r="101">
@@ -2347,9 +2650,12 @@
         <v>0.01599</v>
       </c>
       <c r="D101" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="E101" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="E101" s="1" t="n">
+      <c r="F101" s="1" t="n">
         <v>0.01597</v>
       </c>
     </row>
@@ -2366,10 +2672,13 @@
         <v>0.10377</v>
       </c>
       <c r="D102" s="1" t="n">
+        <v>0.10353</v>
+      </c>
+      <c r="E102" s="1" t="n">
         <v>0.10417</v>
       </c>
-      <c r="E102" s="1" t="n">
-        <v>0.10377</v>
+      <c r="F102" s="1" t="n">
+        <v>0.10353</v>
       </c>
     </row>
     <row r="103">
@@ -2385,10 +2694,13 @@
         <v>0.0006053</v>
       </c>
       <c r="D103" s="1" t="n">
+        <v>0.000605</v>
+      </c>
+      <c r="E103" s="1" t="n">
         <v>0.0006065000000000001</v>
       </c>
-      <c r="E103" s="1" t="n">
-        <v>0.0006053</v>
+      <c r="F103" s="1" t="n">
+        <v>0.000605</v>
       </c>
     </row>
     <row r="104">
@@ -2404,9 +2716,12 @@
         <v>0.0005566</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>0.0005594</v>
+        <v>0.00056</v>
       </c>
       <c r="E104" s="1" t="n">
+        <v>0.00056</v>
+      </c>
+      <c r="F104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -2423,11 +2738,14 @@
         <v>0.003257</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>0.003257</v>
+        <v>0.003244</v>
       </c>
       <c r="E105" s="1" t="n">
         <v>0.003257</v>
       </c>
+      <c r="F105" s="1" t="n">
+        <v>0.003244</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2442,10 +2760,13 @@
         <v>2.623</v>
       </c>
       <c r="D106" s="1" t="n">
+        <v>2.617</v>
+      </c>
+      <c r="E106" s="1" t="n">
         <v>2.638</v>
       </c>
-      <c r="E106" s="1" t="n">
-        <v>2.623</v>
+      <c r="F106" s="1" t="n">
+        <v>2.617</v>
       </c>
     </row>
     <row r="107">
@@ -2461,10 +2782,13 @@
         <v>0.1674</v>
       </c>
       <c r="D107" s="1" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E107" s="1" t="n">
         <v>0.1674</v>
       </c>
-      <c r="E107" s="1" t="n">
-        <v>0.1671</v>
+      <c r="F107" s="1" t="n">
+        <v>0.167</v>
       </c>
     </row>
     <row r="108">
@@ -2480,9 +2804,12 @@
         <v>0.09742000000000001</v>
       </c>
       <c r="D108" s="1" t="n">
+        <v>0.09744</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="F108" s="1" t="n">
         <v>0.09742000000000001</v>
       </c>
     </row>
@@ -2499,10 +2826,13 @@
         <v>0.02242</v>
       </c>
       <c r="D109" s="1" t="n">
+        <v>0.02229</v>
+      </c>
+      <c r="E109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="E109" s="1" t="n">
-        <v>0.02236</v>
+      <c r="F109" s="1" t="n">
+        <v>0.02229</v>
       </c>
     </row>
     <row r="110">
@@ -2518,9 +2848,12 @@
         <v>0.292</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>0.292</v>
+        <v>0.2937</v>
       </c>
       <c r="E110" s="1" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="F110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -2537,9 +2870,12 @@
         <v>0.05697</v>
       </c>
       <c r="D111" s="1" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="E111" s="1" t="n">
         <v>0.05697</v>
       </c>
-      <c r="E111" s="1" t="n">
+      <c r="F111" s="1" t="n">
         <v>0.05684</v>
       </c>
     </row>
@@ -2556,10 +2892,13 @@
         <v>0.3047</v>
       </c>
       <c r="D112" s="1" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="E112" s="1" t="n">
         <v>0.3057</v>
       </c>
-      <c r="E112" s="1" t="n">
-        <v>0.3047</v>
+      <c r="F112" s="1" t="n">
+        <v>0.3039</v>
       </c>
     </row>
     <row r="113">
@@ -2575,9 +2914,12 @@
         <v>18.67</v>
       </c>
       <c r="D113" s="1" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>18.67</v>
       </c>
-      <c r="E113" s="1" t="n">
+      <c r="F113" s="1" t="n">
         <v>18.62</v>
       </c>
     </row>
@@ -2594,9 +2936,12 @@
         <v>0.13225</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>0.13365</v>
+        <v>0.13373</v>
       </c>
       <c r="E114" s="1" t="n">
+        <v>0.13373</v>
+      </c>
+      <c r="F114" s="1" t="n">
         <v>0.13225</v>
       </c>
     </row>
@@ -2613,9 +2958,12 @@
         <v>0.01538</v>
       </c>
       <c r="D115" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="E115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="E115" s="1" t="n">
+      <c r="F115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -2632,10 +2980,13 @@
         <v>0.08545999999999999</v>
       </c>
       <c r="D116" s="1" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="E116" s="1" t="n">
         <v>0.08558</v>
       </c>
-      <c r="E116" s="1" t="n">
-        <v>0.08545999999999999</v>
+      <c r="F116" s="1" t="n">
+        <v>0.08527</v>
       </c>
     </row>
     <row r="117">
@@ -2651,10 +3002,13 @@
         <v>0.04921</v>
       </c>
       <c r="D117" s="1" t="n">
+        <v>0.049196</v>
+      </c>
+      <c r="E117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="E117" s="1" t="n">
-        <v>0.04921</v>
+      <c r="F117" s="1" t="n">
+        <v>0.049196</v>
       </c>
     </row>
     <row r="118">
@@ -2670,10 +3024,13 @@
         <v>0.04824</v>
       </c>
       <c r="D118" s="1" t="n">
+        <v>0.04807</v>
+      </c>
+      <c r="E118" s="1" t="n">
         <v>0.04844</v>
       </c>
-      <c r="E118" s="1" t="n">
-        <v>0.04824</v>
+      <c r="F118" s="1" t="n">
+        <v>0.04807</v>
       </c>
     </row>
     <row r="119">
@@ -2689,9 +3046,12 @@
         <v>0.04116</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>0.04116</v>
+        <v>0.04167</v>
       </c>
       <c r="E119" s="1" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="F119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -2708,9 +3068,12 @@
         <v>0.14654</v>
       </c>
       <c r="D120" s="1" t="n">
-        <v>0.14654</v>
+        <v>0.14662</v>
       </c>
       <c r="E120" s="1" t="n">
+        <v>0.14662</v>
+      </c>
+      <c r="F120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -2727,9 +3090,12 @@
         <v>0.1272</v>
       </c>
       <c r="D121" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="E121" s="1" t="n">
         <v>0.1279</v>
       </c>
-      <c r="E121" s="1" t="n">
+      <c r="F121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -2746,9 +3112,12 @@
         <v>1.887</v>
       </c>
       <c r="D122" s="1" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="E122" s="1" t="n">
         <v>1.893</v>
       </c>
-      <c r="E122" s="1" t="n">
+      <c r="F122" s="1" t="n">
         <v>1.887</v>
       </c>
     </row>
@@ -2765,10 +3134,13 @@
         <v>0.03048</v>
       </c>
       <c r="D123" s="1" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="E123" s="1" t="n">
         <v>0.03049</v>
       </c>
-      <c r="E123" s="1" t="n">
-        <v>0.03048</v>
+      <c r="F123" s="1" t="n">
+        <v>0.03041</v>
       </c>
     </row>
     <row r="124">
@@ -2784,9 +3156,12 @@
         <v>0.13288</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>0.13309</v>
+        <v>0.13346</v>
       </c>
       <c r="E124" s="1" t="n">
+        <v>0.13346</v>
+      </c>
+      <c r="F124" s="1" t="n">
         <v>0.13288</v>
       </c>
     </row>
@@ -2803,10 +3178,13 @@
         <v>0.04143</v>
       </c>
       <c r="D125" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="E125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="E125" s="1" t="n">
-        <v>0.04143</v>
+      <c r="F125" s="1" t="n">
+        <v>0.04139</v>
       </c>
     </row>
     <row r="126">
@@ -2822,9 +3200,12 @@
         <v>0.1154</v>
       </c>
       <c r="D126" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="E126" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="E126" s="1" t="n">
+      <c r="F126" s="1" t="n">
         <v>0.1154</v>
       </c>
     </row>
@@ -2841,9 +3222,12 @@
         <v>0.497</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>0.497</v>
+        <v>0.4979</v>
       </c>
       <c r="E127" s="1" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="F127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -2860,10 +3244,13 @@
         <v>0.03795</v>
       </c>
       <c r="D128" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="E128" s="1" t="n">
         <v>0.03797</v>
       </c>
-      <c r="E128" s="1" t="n">
-        <v>0.03795</v>
+      <c r="F128" s="1" t="n">
+        <v>0.03787</v>
       </c>
     </row>
     <row r="129">
@@ -2879,9 +3266,12 @@
         <v>0.796</v>
       </c>
       <c r="D129" s="1" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="E129" s="1" t="n">
         <v>0.797</v>
       </c>
-      <c r="E129" s="1" t="n">
+      <c r="F129" s="1" t="n">
         <v>0.796</v>
       </c>
     </row>
@@ -2898,9 +3288,12 @@
         <v>0.03458</v>
       </c>
       <c r="D130" s="1" t="n">
+        <v>0.03452</v>
+      </c>
+      <c r="E130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="E130" s="1" t="n">
+      <c r="F130" s="1" t="n">
         <v>0.03439</v>
       </c>
     </row>
@@ -2917,9 +3310,12 @@
         <v>0.4183</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>0.4183</v>
+        <v>0.4279</v>
       </c>
       <c r="E131" s="1" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="F131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -2936,10 +3332,13 @@
         <v>0.04405</v>
       </c>
       <c r="D132" s="1" t="n">
+        <v>0.04375</v>
+      </c>
+      <c r="E132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="E132" s="1" t="n">
-        <v>0.04405</v>
+      <c r="F132" s="1" t="n">
+        <v>0.04375</v>
       </c>
     </row>
     <row r="133">
@@ -2955,9 +3354,12 @@
         <v>1.2941</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>1.2946</v>
+        <v>1.2958</v>
       </c>
       <c r="E133" s="1" t="n">
+        <v>1.2958</v>
+      </c>
+      <c r="F133" s="1" t="n">
         <v>1.2941</v>
       </c>
     </row>
@@ -2974,9 +3376,12 @@
         <v>0.02215</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>0.02215</v>
+        <v>0.0222</v>
       </c>
       <c r="E134" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F134" s="1" t="n">
         <v>0.02208</v>
       </c>
     </row>
@@ -2993,9 +3398,12 @@
         <v>0.0004699</v>
       </c>
       <c r="D135" s="1" t="n">
+        <v>0.0004706</v>
+      </c>
+      <c r="E135" s="1" t="n">
         <v>0.0004716</v>
       </c>
-      <c r="E135" s="1" t="n">
+      <c r="F135" s="1" t="n">
         <v>0.0004699</v>
       </c>
     </row>
@@ -3012,9 +3420,12 @@
         <v>0.001913</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>0.001918</v>
+        <v>0.00195</v>
       </c>
       <c r="E136" s="1" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="F136" s="1" t="n">
         <v>0.001913</v>
       </c>
     </row>
@@ -3031,10 +3442,13 @@
         <v>0.3221</v>
       </c>
       <c r="D137" s="1" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <v>0.3227</v>
       </c>
-      <c r="E137" s="1" t="n">
-        <v>0.3221</v>
+      <c r="F137" s="1" t="n">
+        <v>0.3204</v>
       </c>
     </row>
     <row r="138">
@@ -3050,9 +3464,12 @@
         <v>0.5705</v>
       </c>
       <c r="D138" s="1" t="n">
+        <v>0.5713</v>
+      </c>
+      <c r="E138" s="1" t="n">
         <v>0.5717</v>
       </c>
-      <c r="E138" s="1" t="n">
+      <c r="F138" s="1" t="n">
         <v>0.5705</v>
       </c>
     </row>
@@ -3069,9 +3486,12 @@
         <v>0.02148</v>
       </c>
       <c r="D139" s="1" t="n">
-        <v>0.02148</v>
+        <v>0.0215</v>
       </c>
       <c r="E139" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="F139" s="1" t="n">
         <v>0.02145</v>
       </c>
     </row>
@@ -3088,9 +3508,12 @@
         <v>0.08081000000000001</v>
       </c>
       <c r="D140" s="1" t="n">
+        <v>0.08082</v>
+      </c>
+      <c r="E140" s="1" t="n">
         <v>0.08092000000000001</v>
       </c>
-      <c r="E140" s="1" t="n">
+      <c r="F140" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -3107,9 +3530,12 @@
         <v>0.00163</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>0.00163</v>
+        <v>0.001632</v>
       </c>
       <c r="E141" s="1" t="n">
+        <v>0.001632</v>
+      </c>
+      <c r="F141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -3126,9 +3552,12 @@
         <v>0.4256</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>0.4256</v>
+        <v>0.4269</v>
       </c>
       <c r="E142" s="1" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="F142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -3145,9 +3574,12 @@
         <v>0.030655</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>0.030655</v>
+        <v>0.030681</v>
       </c>
       <c r="E143" s="1" t="n">
+        <v>0.030681</v>
+      </c>
+      <c r="F143" s="1" t="n">
         <v>0.030377</v>
       </c>
     </row>
@@ -3164,9 +3596,12 @@
         <v>0.000225</v>
       </c>
       <c r="D144" s="1" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.000225</v>
       </c>
-      <c r="E144" s="1" t="n">
+      <c r="F144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -3183,9 +3618,12 @@
         <v>0.03197</v>
       </c>
       <c r="D145" s="1" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="E145" s="1" t="n">
         <v>0.03197</v>
       </c>
-      <c r="E145" s="1" t="n">
+      <c r="F145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -3202,9 +3640,12 @@
         <v>0.11584</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>0.11584</v>
+        <v>0.11596</v>
       </c>
       <c r="E146" s="1" t="n">
+        <v>0.11596</v>
+      </c>
+      <c r="F146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -3221,9 +3662,12 @@
         <v>0.02185</v>
       </c>
       <c r="D147" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="E147" s="1" t="n">
         <v>0.02185</v>
       </c>
-      <c r="E147" s="1" t="n">
+      <c r="F147" s="1" t="n">
         <v>0.02171</v>
       </c>
     </row>
@@ -3240,10 +3684,13 @@
         <v>1.4191</v>
       </c>
       <c r="D148" s="1" t="n">
+        <v>1.4154</v>
+      </c>
+      <c r="E148" s="1" t="n">
         <v>1.4234</v>
       </c>
-      <c r="E148" s="1" t="n">
-        <v>1.4191</v>
+      <c r="F148" s="1" t="n">
+        <v>1.4154</v>
       </c>
     </row>
     <row r="149">
@@ -3259,9 +3706,12 @@
         <v>1.8715</v>
       </c>
       <c r="D149" s="1" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="E149" s="1" t="n">
         <v>1.8715</v>
       </c>
-      <c r="E149" s="1" t="n">
+      <c r="F149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -3278,9 +3728,12 @@
         <v>0.1</v>
       </c>
       <c r="D150" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="E150" s="1" t="n">
+      <c r="F150" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3297,9 +3750,12 @@
         <v>4.521</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>4.521</v>
+        <v>4.553</v>
       </c>
       <c r="E151" s="1" t="n">
+        <v>4.553</v>
+      </c>
+      <c r="F151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -3316,9 +3772,12 @@
         <v>5.55</v>
       </c>
       <c r="D152" s="1" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="E152" s="1" t="n">
         <v>5.561</v>
       </c>
-      <c r="E152" s="1" t="n">
+      <c r="F152" s="1" t="n">
         <v>5.55</v>
       </c>
     </row>
@@ -3335,9 +3794,12 @@
         <v>0.3205</v>
       </c>
       <c r="D153" s="1" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="E153" s="1" t="n">
         <v>0.3205</v>
       </c>
-      <c r="E153" s="1" t="n">
+      <c r="F153" s="1" t="n">
         <v>0.3178</v>
       </c>
     </row>
@@ -3354,10 +3816,13 @@
         <v>0.5901</v>
       </c>
       <c r="D154" s="1" t="n">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="E154" s="1" t="n">
         <v>0.5901999999999999</v>
       </c>
-      <c r="E154" s="1" t="n">
-        <v>0.5901</v>
+      <c r="F154" s="1" t="n">
+        <v>0.5891999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -3373,9 +3838,12 @@
         <v>0.01267</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>0.01267</v>
+        <v>0.01269</v>
       </c>
       <c r="E155" s="1" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="F155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -3392,10 +3860,13 @@
         <v>0.1001</v>
       </c>
       <c r="D156" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="E156" s="1" t="n">
         <v>0.1002</v>
       </c>
-      <c r="E156" s="1" t="n">
-        <v>0.1001</v>
+      <c r="F156" s="1" t="n">
+        <v>0.0997</v>
       </c>
     </row>
     <row r="157">
@@ -3411,10 +3882,13 @@
         <v>16.588</v>
       </c>
       <c r="D157" s="1" t="n">
+        <v>16.563</v>
+      </c>
+      <c r="E157" s="1" t="n">
         <v>16.596</v>
       </c>
-      <c r="E157" s="1" t="n">
-        <v>16.588</v>
+      <c r="F157" s="1" t="n">
+        <v>16.563</v>
       </c>
     </row>
     <row r="158">
@@ -3430,9 +3904,12 @@
         <v>0.05548</v>
       </c>
       <c r="D158" s="1" t="n">
+        <v>0.05539</v>
+      </c>
+      <c r="E158" s="1" t="n">
         <v>0.05548</v>
       </c>
-      <c r="E158" s="1" t="n">
+      <c r="F158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -3449,10 +3926,13 @@
         <v>28.92</v>
       </c>
       <c r="D159" s="1" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="E159" s="1" t="n">
         <v>29.04</v>
       </c>
-      <c r="E159" s="1" t="n">
-        <v>28.92</v>
+      <c r="F159" s="1" t="n">
+        <v>28.87</v>
       </c>
     </row>
     <row r="160">
@@ -3468,10 +3948,13 @@
         <v>0.02124</v>
       </c>
       <c r="D160" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="E160" s="1" t="n">
         <v>0.02132</v>
       </c>
-      <c r="E160" s="1" t="n">
-        <v>0.02124</v>
+      <c r="F160" s="1" t="n">
+        <v>0.02121</v>
       </c>
     </row>
     <row r="161">
@@ -3487,10 +3970,13 @@
         <v>0.0006608</v>
       </c>
       <c r="D161" s="1" t="n">
+        <v>0.0006601000000000001</v>
+      </c>
+      <c r="E161" s="1" t="n">
         <v>0.0006619</v>
       </c>
-      <c r="E161" s="1" t="n">
-        <v>0.0006608</v>
+      <c r="F161" s="1" t="n">
+        <v>0.0006601000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -3506,9 +3992,12 @@
         <v>0.3968</v>
       </c>
       <c r="D162" s="1" t="n">
-        <v>0.3968</v>
+        <v>0.4016</v>
       </c>
       <c r="E162" s="1" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="F162" s="1" t="n">
         <v>0.3936</v>
       </c>
     </row>
@@ -3525,10 +4014,13 @@
         <v>0.1934</v>
       </c>
       <c r="D163" s="1" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="E163" s="1" t="n">
         <v>0.1939</v>
       </c>
-      <c r="E163" s="1" t="n">
-        <v>0.1934</v>
+      <c r="F163" s="1" t="n">
+        <v>0.1931</v>
       </c>
     </row>
     <row r="164">
@@ -3544,9 +4036,12 @@
         <v>0.32</v>
       </c>
       <c r="D164" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E164" s="1" t="n">
         <v>0.321</v>
       </c>
-      <c r="E164" s="1" t="n">
+      <c r="F164" s="1" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -3563,10 +4058,13 @@
         <v>0.376</v>
       </c>
       <c r="D165" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="E165" s="1" t="n">
-        <v>0.376</v>
+      <c r="F165" s="1" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="166">
@@ -3582,10 +4080,13 @@
         <v>0.02274</v>
       </c>
       <c r="D166" s="1" t="n">
+        <v>0.02271</v>
+      </c>
+      <c r="E166" s="1" t="n">
         <v>0.02276</v>
       </c>
-      <c r="E166" s="1" t="n">
-        <v>0.02274</v>
+      <c r="F166" s="1" t="n">
+        <v>0.02271</v>
       </c>
     </row>
     <row r="167">
@@ -3601,10 +4102,13 @@
         <v>0.007366</v>
       </c>
       <c r="D167" s="1" t="n">
+        <v>0.007348</v>
+      </c>
+      <c r="E167" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="E167" s="1" t="n">
-        <v>0.007366</v>
+      <c r="F167" s="1" t="n">
+        <v>0.007348</v>
       </c>
     </row>
     <row r="168">
@@ -3620,11 +4124,14 @@
         <v>0.01397</v>
       </c>
       <c r="D168" s="1" t="n">
-        <v>0.01397</v>
+        <v>0.01395</v>
       </c>
       <c r="E168" s="1" t="n">
         <v>0.01397</v>
       </c>
+      <c r="F168" s="1" t="n">
+        <v>0.01395</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3639,10 +4146,13 @@
         <v>0.25715</v>
       </c>
       <c r="D169" s="1" t="n">
+        <v>0.25376</v>
+      </c>
+      <c r="E169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="E169" s="1" t="n">
-        <v>0.25715</v>
+      <c r="F169" s="1" t="n">
+        <v>0.25376</v>
       </c>
     </row>
     <row r="170">
@@ -3658,9 +4168,12 @@
         <v>0.02143</v>
       </c>
       <c r="D170" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="E170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="E170" s="1" t="n">
+      <c r="F170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -3677,9 +4190,12 @@
         <v>0.1741</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>0.1741</v>
+        <v>0.1748</v>
       </c>
       <c r="E171" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="F171" s="1" t="n">
         <v>0.1733</v>
       </c>
     </row>
@@ -3696,11 +4212,14 @@
         <v>0.09</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E172" s="1" t="n">
         <v>0.09</v>
       </c>
+      <c r="F172" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3715,10 +4234,13 @@
         <v>0.004722</v>
       </c>
       <c r="D173" s="1" t="n">
+        <v>0.004719</v>
+      </c>
+      <c r="E173" s="1" t="n">
         <v>0.004729</v>
       </c>
-      <c r="E173" s="1" t="n">
-        <v>0.004722</v>
+      <c r="F173" s="1" t="n">
+        <v>0.004719</v>
       </c>
     </row>
     <row r="174">
@@ -3734,10 +4256,13 @@
         <v>0.4382</v>
       </c>
       <c r="D174" s="1" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="E174" s="1" t="n">
         <v>0.4382</v>
       </c>
-      <c r="E174" s="1" t="n">
-        <v>0.4373</v>
+      <c r="F174" s="1" t="n">
+        <v>0.4368</v>
       </c>
     </row>
     <row r="175">
@@ -3753,10 +4278,13 @@
         <v>0.09001000000000001</v>
       </c>
       <c r="D175" s="1" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="E175" s="1" t="n">
         <v>0.09001000000000001</v>
       </c>
-      <c r="E175" s="1" t="n">
-        <v>0.08966</v>
+      <c r="F175" s="1" t="n">
+        <v>0.0895</v>
       </c>
     </row>
     <row r="176">
@@ -3772,9 +4300,12 @@
         <v>0.2453</v>
       </c>
       <c r="D176" s="1" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="E176" s="1" t="n">
         <v>0.2475</v>
       </c>
-      <c r="E176" s="1" t="n">
+      <c r="F176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -3791,10 +4322,13 @@
         <v>0.01918</v>
       </c>
       <c r="D177" s="1" t="n">
+        <v>0.01917</v>
+      </c>
+      <c r="E177" s="1" t="n">
         <v>0.01925</v>
       </c>
-      <c r="E177" s="1" t="n">
-        <v>0.01918</v>
+      <c r="F177" s="1" t="n">
+        <v>0.01917</v>
       </c>
     </row>
     <row r="178">
@@ -3810,10 +4344,13 @@
         <v>6.196</v>
       </c>
       <c r="D178" s="1" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="E178" s="1" t="n">
         <v>6.196</v>
       </c>
-      <c r="E178" s="1" t="n">
-        <v>6.195</v>
+      <c r="F178" s="1" t="n">
+        <v>6.18</v>
       </c>
     </row>
     <row r="179">
@@ -3829,9 +4366,12 @@
         <v>0.1364</v>
       </c>
       <c r="D179" s="1" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="E179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="E179" s="1" t="n">
+      <c r="F179" s="1" t="n">
         <v>0.1364</v>
       </c>
     </row>
@@ -3848,9 +4388,12 @@
         <v>0.004848</v>
       </c>
       <c r="D180" s="1" t="n">
-        <v>0.004923</v>
+        <v>0.004943</v>
       </c>
       <c r="E180" s="1" t="n">
+        <v>0.004943</v>
+      </c>
+      <c r="F180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -3867,11 +4410,14 @@
         <v>0.01191</v>
       </c>
       <c r="D181" s="1" t="n">
-        <v>0.01191</v>
+        <v>0.01189</v>
       </c>
       <c r="E181" s="1" t="n">
         <v>0.01191</v>
       </c>
+      <c r="F181" s="1" t="n">
+        <v>0.01189</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3886,9 +4432,12 @@
         <v>0.007524</v>
       </c>
       <c r="D182" s="1" t="n">
-        <v>0.007524</v>
+        <v>0.007538</v>
       </c>
       <c r="E182" s="1" t="n">
+        <v>0.007538</v>
+      </c>
+      <c r="F182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -3905,10 +4454,13 @@
         <v>0.13206</v>
       </c>
       <c r="D183" s="1" t="n">
+        <v>0.13155</v>
+      </c>
+      <c r="E183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="E183" s="1" t="n">
-        <v>0.13194</v>
+      <c r="F183" s="1" t="n">
+        <v>0.13155</v>
       </c>
     </row>
     <row r="184">
@@ -3924,9 +4476,12 @@
         <v>0.09626</v>
       </c>
       <c r="D184" s="1" t="n">
-        <v>0.09626</v>
+        <v>0.09635000000000001</v>
       </c>
       <c r="E184" s="1" t="n">
+        <v>0.09635000000000001</v>
+      </c>
+      <c r="F184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -3943,9 +4498,12 @@
         <v>0.00758</v>
       </c>
       <c r="D185" s="1" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="E185" s="1" t="n">
         <v>0.00761</v>
       </c>
-      <c r="E185" s="1" t="n">
+      <c r="F185" s="1" t="n">
         <v>0.00758</v>
       </c>
     </row>
@@ -3962,9 +4520,12 @@
         <v>0.04914</v>
       </c>
       <c r="D186" s="1" t="n">
+        <v>0.04915</v>
+      </c>
+      <c r="E186" s="1" t="n">
         <v>0.04933</v>
       </c>
-      <c r="E186" s="1" t="n">
+      <c r="F186" s="1" t="n">
         <v>0.04914</v>
       </c>
     </row>
@@ -3981,9 +4542,12 @@
         <v>0.02695</v>
       </c>
       <c r="D187" s="1" t="n">
-        <v>0.02695</v>
+        <v>0.02699</v>
       </c>
       <c r="E187" s="1" t="n">
+        <v>0.02699</v>
+      </c>
+      <c r="F187" s="1" t="n">
         <v>0.02686</v>
       </c>
     </row>
@@ -4000,10 +4564,13 @@
         <v>0.003333</v>
       </c>
       <c r="D188" s="1" t="n">
+        <v>0.003323</v>
+      </c>
+      <c r="E188" s="1" t="n">
         <v>0.00334</v>
       </c>
-      <c r="E188" s="1" t="n">
-        <v>0.003333</v>
+      <c r="F188" s="1" t="n">
+        <v>0.003323</v>
       </c>
     </row>
     <row r="189">
@@ -4019,9 +4586,12 @@
         <v>0.2888</v>
       </c>
       <c r="D189" s="1" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="E189" s="1" t="n">
         <v>0.2888</v>
       </c>
-      <c r="E189" s="1" t="n">
+      <c r="F189" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -4038,10 +4608,13 @@
         <v>0.01821</v>
       </c>
       <c r="D190" s="1" t="n">
+        <v>0.01819</v>
+      </c>
+      <c r="E190" s="1" t="n">
         <v>0.01822</v>
       </c>
-      <c r="E190" s="1" t="n">
-        <v>0.01821</v>
+      <c r="F190" s="1" t="n">
+        <v>0.01819</v>
       </c>
     </row>
     <row r="191">
@@ -4057,11 +4630,14 @@
         <v>0.2617</v>
       </c>
       <c r="D191" s="1" t="n">
-        <v>0.2617</v>
+        <v>0.2606</v>
       </c>
       <c r="E191" s="1" t="n">
         <v>0.2617</v>
       </c>
+      <c r="F191" s="1" t="n">
+        <v>0.2606</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4076,10 +4652,13 @@
         <v>0.03946</v>
       </c>
       <c r="D192" s="1" t="n">
+        <v>0.03914</v>
+      </c>
+      <c r="E192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="E192" s="1" t="n">
-        <v>0.03946</v>
+      <c r="F192" s="1" t="n">
+        <v>0.03914</v>
       </c>
     </row>
     <row r="193">
@@ -4095,9 +4674,12 @@
         <v>0.0002205</v>
       </c>
       <c r="D193" s="1" t="n">
+        <v>0.0002208</v>
+      </c>
+      <c r="E193" s="1" t="n">
         <v>0.000221</v>
       </c>
-      <c r="E193" s="1" t="n">
+      <c r="F193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -4114,10 +4696,13 @@
         <v>4.169</v>
       </c>
       <c r="D194" s="1" t="n">
+        <v>4.154</v>
+      </c>
+      <c r="E194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="E194" s="1" t="n">
-        <v>4.169</v>
+      <c r="F194" s="1" t="n">
+        <v>4.154</v>
       </c>
     </row>
     <row r="195">
@@ -4133,9 +4718,12 @@
         <v>0.99934</v>
       </c>
       <c r="D195" s="1" t="n">
+        <v>0.99934</v>
+      </c>
+      <c r="E195" s="1" t="n">
         <v>0.999341</v>
       </c>
-      <c r="E195" s="1" t="n">
+      <c r="F195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -4152,9 +4740,12 @@
         <v>4.302</v>
       </c>
       <c r="D196" s="1" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="E196" s="1" t="n">
         <v>4.316</v>
       </c>
-      <c r="E196" s="1" t="n">
+      <c r="F196" s="1" t="n">
         <v>4.302</v>
       </c>
     </row>
@@ -4171,10 +4762,13 @@
         <v>0.15006</v>
       </c>
       <c r="D197" s="1" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="E197" s="1" t="n">
         <v>0.15012</v>
       </c>
-      <c r="E197" s="1" t="n">
-        <v>0.15006</v>
+      <c r="F197" s="1" t="n">
+        <v>0.14981</v>
       </c>
     </row>
     <row r="198">
@@ -4190,9 +4784,12 @@
         <v>0.007586</v>
       </c>
       <c r="D198" s="1" t="n">
+        <v>0.007485</v>
+      </c>
+      <c r="E198" s="1" t="n">
         <v>0.007586</v>
       </c>
-      <c r="E198" s="1" t="n">
+      <c r="F198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -4209,10 +4806,13 @@
         <v>0.4502</v>
       </c>
       <c r="D199" s="1" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="E199" s="1" t="n">
         <v>0.4503</v>
       </c>
-      <c r="E199" s="1" t="n">
-        <v>0.4502</v>
+      <c r="F199" s="1" t="n">
+        <v>0.4483</v>
       </c>
     </row>
     <row r="200">
@@ -4228,9 +4828,12 @@
         <v>0.5715</v>
       </c>
       <c r="D200" s="1" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5777</v>
       </c>
       <c r="E200" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="F200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -4247,10 +4850,13 @@
         <v>0.094</v>
       </c>
       <c r="D201" s="1" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="E201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="E201" s="1" t="n">
-        <v>0.094</v>
+      <c r="F201" s="1" t="n">
+        <v>0.09379999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -4266,9 +4872,12 @@
         <v>0.06063</v>
       </c>
       <c r="D202" s="1" t="n">
-        <v>0.06068</v>
+        <v>0.06069</v>
       </c>
       <c r="E202" s="1" t="n">
+        <v>0.06069</v>
+      </c>
+      <c r="F202" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -4285,9 +4894,12 @@
         <v>0.00847</v>
       </c>
       <c r="D203" s="1" t="n">
-        <v>0.00847</v>
+        <v>0.00851</v>
       </c>
       <c r="E203" s="1" t="n">
+        <v>0.00851</v>
+      </c>
+      <c r="F203" s="1" t="n">
         <v>0.008359999999999999</v>
       </c>
     </row>
@@ -4304,11 +4916,14 @@
         <v>0.00422</v>
       </c>
       <c r="D204" s="1" t="n">
-        <v>0.00422</v>
+        <v>0.00421</v>
       </c>
       <c r="E204" s="1" t="n">
         <v>0.00422</v>
       </c>
+      <c r="F204" s="1" t="n">
+        <v>0.00421</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4323,9 +4938,12 @@
         <v>0.009318</v>
       </c>
       <c r="D205" s="1" t="n">
+        <v>0.009283</v>
+      </c>
+      <c r="E205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="E205" s="1" t="n">
+      <c r="F205" s="1" t="n">
         <v>0.009239000000000001</v>
       </c>
     </row>
@@ -4342,9 +4960,12 @@
         <v>0.2356</v>
       </c>
       <c r="D206" s="1" t="n">
-        <v>0.2362</v>
+        <v>0.2366</v>
       </c>
       <c r="E206" s="1" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="F206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -4361,9 +4982,12 @@
         <v>0.02163</v>
       </c>
       <c r="D207" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="E207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="E207" s="1" t="n">
+      <c r="F207" s="1" t="n">
         <v>0.02128</v>
       </c>
     </row>
@@ -4380,10 +5004,13 @@
         <v>0.2376</v>
       </c>
       <c r="D208" s="1" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="E208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="E208" s="1" t="n">
-        <v>0.2376</v>
+      <c r="F208" s="1" t="n">
+        <v>0.2366</v>
       </c>
     </row>
     <row r="209">
@@ -4399,9 +5026,12 @@
         <v>0.3616</v>
       </c>
       <c r="D209" s="1" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="E209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="E209" s="1" t="n">
+      <c r="F209" s="1" t="n">
         <v>0.3616</v>
       </c>
     </row>
@@ -4418,10 +5048,13 @@
         <v>0.04302</v>
       </c>
       <c r="D210" s="1" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="E210" s="1" t="n">
         <v>0.04311</v>
       </c>
-      <c r="E210" s="1" t="n">
-        <v>0.04302</v>
+      <c r="F210" s="1" t="n">
+        <v>0.04286</v>
       </c>
     </row>
     <row r="211">
@@ -4437,10 +5070,13 @@
         <v>0.0004303</v>
       </c>
       <c r="D211" s="1" t="n">
+        <v>0.0004282</v>
+      </c>
+      <c r="E211" s="1" t="n">
         <v>0.0004307</v>
       </c>
-      <c r="E211" s="1" t="n">
-        <v>0.0004303</v>
+      <c r="F211" s="1" t="n">
+        <v>0.0004282</v>
       </c>
     </row>
     <row r="212">
@@ -4456,10 +5092,13 @@
         <v>0.02171</v>
       </c>
       <c r="D212" s="1" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="E212" s="1" t="n">
         <v>0.02171</v>
       </c>
-      <c r="E212" s="1" t="n">
-        <v>0.0217</v>
+      <c r="F212" s="1" t="n">
+        <v>0.0216</v>
       </c>
     </row>
     <row r="213">
@@ -4475,9 +5114,12 @@
         <v>0.1151</v>
       </c>
       <c r="D213" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="E213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="E213" s="1" t="n">
+      <c r="F213" s="1" t="n">
         <v>0.1151</v>
       </c>
     </row>
@@ -4494,10 +5136,13 @@
         <v>0.04199</v>
       </c>
       <c r="D214" s="1" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="E214" s="1" t="n">
         <v>0.04204</v>
       </c>
-      <c r="E214" s="1" t="n">
-        <v>0.04199</v>
+      <c r="F214" s="1" t="n">
+        <v>0.04188</v>
       </c>
     </row>
     <row r="215">
@@ -4513,9 +5158,12 @@
         <v>0.010028</v>
       </c>
       <c r="D215" s="1" t="n">
-        <v>0.010028</v>
+        <v>0.010039</v>
       </c>
       <c r="E215" s="1" t="n">
+        <v>0.010039</v>
+      </c>
+      <c r="F215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -4532,11 +5180,14 @@
         <v>0.064</v>
       </c>
       <c r="D216" s="1" t="n">
-        <v>0.064</v>
+        <v>0.0634</v>
       </c>
       <c r="E216" s="1" t="n">
         <v>0.064</v>
       </c>
+      <c r="F216" s="1" t="n">
+        <v>0.0634</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4551,10 +5202,13 @@
         <v>0.004184</v>
       </c>
       <c r="D217" s="1" t="n">
+        <v>0.004177</v>
+      </c>
+      <c r="E217" s="1" t="n">
         <v>0.004186</v>
       </c>
-      <c r="E217" s="1" t="n">
-        <v>0.004184</v>
+      <c r="F217" s="1" t="n">
+        <v>0.004177</v>
       </c>
     </row>
     <row r="218">
@@ -4570,9 +5224,12 @@
         <v>0.01062</v>
       </c>
       <c r="D218" s="1" t="n">
+        <v>0.01065</v>
+      </c>
+      <c r="E218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="E218" s="1" t="n">
+      <c r="F218" s="1" t="n">
         <v>0.01062</v>
       </c>
     </row>
@@ -4589,10 +5246,13 @@
         <v>0.03134</v>
       </c>
       <c r="D219" s="1" t="n">
+        <v>0.03054</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="E219" s="1" t="n">
-        <v>0.03127</v>
+      <c r="F219" s="1" t="n">
+        <v>0.03054</v>
       </c>
     </row>
     <row r="220">
@@ -4608,10 +5268,13 @@
         <v>2.305</v>
       </c>
       <c r="D220" s="1" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="E220" s="1" t="n">
         <v>2.306</v>
       </c>
-      <c r="E220" s="1" t="n">
-        <v>2.305</v>
+      <c r="F220" s="1" t="n">
+        <v>2.296</v>
       </c>
     </row>
     <row r="221">
@@ -4627,10 +5290,13 @@
         <v>0.023068</v>
       </c>
       <c r="D221" s="1" t="n">
+        <v>0.023027</v>
+      </c>
+      <c r="E221" s="1" t="n">
         <v>0.023068</v>
       </c>
-      <c r="E221" s="1" t="n">
-        <v>0.023052</v>
+      <c r="F221" s="1" t="n">
+        <v>0.023027</v>
       </c>
     </row>
     <row r="222">
@@ -4646,10 +5312,13 @@
         <v>0.0371</v>
       </c>
       <c r="D222" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="E222" s="1" t="n">
-        <v>0.0371</v>
+      <c r="F222" s="1" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="223">
@@ -4665,10 +5334,13 @@
         <v>0.2946</v>
       </c>
       <c r="D223" s="1" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="E223" s="1" t="n">
         <v>0.2946</v>
       </c>
-      <c r="E223" s="1" t="n">
-        <v>0.2943</v>
+      <c r="F223" s="1" t="n">
+        <v>0.294</v>
       </c>
     </row>
     <row r="224">
@@ -4684,9 +5356,12 @@
         <v>0.01537</v>
       </c>
       <c r="D224" s="1" t="n">
+        <v>0.01537</v>
+      </c>
+      <c r="E224" s="1" t="n">
         <v>0.01549</v>
       </c>
-      <c r="E224" s="1" t="n">
+      <c r="F224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -4703,10 +5378,13 @@
         <v>0.0004125</v>
       </c>
       <c r="D225" s="1" t="n">
+        <v>0.0004112</v>
+      </c>
+      <c r="E225" s="1" t="n">
         <v>0.0004135</v>
       </c>
-      <c r="E225" s="1" t="n">
-        <v>0.0004125</v>
+      <c r="F225" s="1" t="n">
+        <v>0.0004112</v>
       </c>
     </row>
     <row r="226">
@@ -4722,9 +5400,12 @@
         <v>0.08731999999999999</v>
       </c>
       <c r="D226" s="1" t="n">
+        <v>0.08765000000000001</v>
+      </c>
+      <c r="E226" s="1" t="n">
         <v>0.08766</v>
       </c>
-      <c r="E226" s="1" t="n">
+      <c r="F226" s="1" t="n">
         <v>0.08731999999999999</v>
       </c>
     </row>
@@ -4741,9 +5422,12 @@
         <v>0.945</v>
       </c>
       <c r="D227" s="1" t="n">
-        <v>0.945</v>
+        <v>0.949</v>
       </c>
       <c r="E227" s="1" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="F227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -4760,9 +5444,12 @@
         <v>0.0558</v>
       </c>
       <c r="D228" s="1" t="n">
-        <v>0.05614</v>
+        <v>0.0563</v>
       </c>
       <c r="E228" s="1" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="F228" s="1" t="n">
         <v>0.0558</v>
       </c>
     </row>
@@ -4779,10 +5466,13 @@
         <v>0.002022</v>
       </c>
       <c r="D229" s="1" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="E229" s="1" t="n">
         <v>0.002026</v>
       </c>
-      <c r="E229" s="1" t="n">
-        <v>0.002022</v>
+      <c r="F229" s="1" t="n">
+        <v>0.002017</v>
       </c>
     </row>
     <row r="230">
@@ -4798,9 +5488,12 @@
         <v>0.022734</v>
       </c>
       <c r="D230" s="1" t="n">
+        <v>0.022714</v>
+      </c>
+      <c r="E230" s="1" t="n">
         <v>0.022734</v>
       </c>
-      <c r="E230" s="1" t="n">
+      <c r="F230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -4817,9 +5510,12 @@
         <v>0.05499</v>
       </c>
       <c r="D231" s="1" t="n">
+        <v>0.05471</v>
+      </c>
+      <c r="E231" s="1" t="n">
         <v>0.05499</v>
       </c>
-      <c r="E231" s="1" t="n">
+      <c r="F231" s="1" t="n">
         <v>0.05471</v>
       </c>
     </row>
@@ -4836,10 +5532,13 @@
         <v>0.0594</v>
       </c>
       <c r="D232" s="1" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="E232" s="1" t="n">
         <v>0.0595</v>
       </c>
-      <c r="E232" s="1" t="n">
-        <v>0.0594</v>
+      <c r="F232" s="1" t="n">
+        <v>0.0591</v>
       </c>
     </row>
     <row r="233">
@@ -4855,10 +5554,13 @@
         <v>0.001687</v>
       </c>
       <c r="D233" s="1" t="n">
+        <v>0.001678</v>
+      </c>
+      <c r="E233" s="1" t="n">
         <v>0.001689</v>
       </c>
-      <c r="E233" s="1" t="n">
-        <v>0.001687</v>
+      <c r="F233" s="1" t="n">
+        <v>0.001678</v>
       </c>
     </row>
     <row r="234">
@@ -4874,9 +5576,12 @@
         <v>0.005788</v>
       </c>
       <c r="D234" s="1" t="n">
-        <v>0.005788</v>
+        <v>0.005796</v>
       </c>
       <c r="E234" s="1" t="n">
+        <v>0.005796</v>
+      </c>
+      <c r="F234" s="1" t="n">
         <v>0.005784</v>
       </c>
     </row>
@@ -4893,9 +5598,12 @@
         <v>0.1256</v>
       </c>
       <c r="D235" s="1" t="n">
-        <v>0.1256</v>
+        <v>0.12568</v>
       </c>
       <c r="E235" s="1" t="n">
+        <v>0.12568</v>
+      </c>
+      <c r="F235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -4912,10 +5620,13 @@
         <v>64.86</v>
       </c>
       <c r="D236" s="1" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="E236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="E236" s="1" t="n">
-        <v>64.86</v>
+      <c r="F236" s="1" t="n">
+        <v>64.78</v>
       </c>
     </row>
     <row r="237">
@@ -4931,10 +5642,13 @@
         <v>0.1024</v>
       </c>
       <c r="D237" s="1" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="E237" s="1" t="n">
         <v>0.1028</v>
       </c>
-      <c r="E237" s="1" t="n">
-        <v>0.1024</v>
+      <c r="F237" s="1" t="n">
+        <v>0.1021</v>
       </c>
     </row>
     <row r="238">
@@ -4950,10 +5664,13 @@
         <v>0.003944</v>
       </c>
       <c r="D238" s="1" t="n">
+        <v>0.003925</v>
+      </c>
+      <c r="E238" s="1" t="n">
         <v>0.003951</v>
       </c>
-      <c r="E238" s="1" t="n">
-        <v>0.003944</v>
+      <c r="F238" s="1" t="n">
+        <v>0.003925</v>
       </c>
     </row>
     <row r="239">
@@ -4969,10 +5686,13 @@
         <v>0.01541</v>
       </c>
       <c r="D239" s="1" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="E239" s="1" t="n">
         <v>0.01541</v>
       </c>
-      <c r="E239" s="1" t="n">
-        <v>0.01533</v>
+      <c r="F239" s="1" t="n">
+        <v>0.01532</v>
       </c>
     </row>
     <row r="240">
@@ -4988,9 +5708,12 @@
         <v>0.05621</v>
       </c>
       <c r="D240" s="1" t="n">
+        <v>0.05624</v>
+      </c>
+      <c r="E240" s="1" t="n">
         <v>0.05631</v>
       </c>
-      <c r="E240" s="1" t="n">
+      <c r="F240" s="1" t="n">
         <v>0.05621</v>
       </c>
     </row>
@@ -5007,10 +5730,13 @@
         <v>0.0115</v>
       </c>
       <c r="D241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="E241" s="1" t="n">
-        <v>0.0115</v>
+      <c r="F241" s="1" t="n">
+        <v>0.0114</v>
       </c>
     </row>
     <row r="242">
@@ -5026,10 +5752,13 @@
         <v>0.3368</v>
       </c>
       <c r="D242" s="1" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E242" s="1" t="n">
         <v>0.3372</v>
       </c>
-      <c r="E242" s="1" t="n">
-        <v>0.3368</v>
+      <c r="F242" s="1" t="n">
+        <v>0.336</v>
       </c>
     </row>
     <row r="243">
@@ -5045,10 +5774,13 @@
         <v>0.01243</v>
       </c>
       <c r="D243" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="E243" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="E243" s="1" t="n">
-        <v>0.01243</v>
+      <c r="F243" s="1" t="n">
+        <v>0.01241</v>
       </c>
     </row>
     <row r="244">
@@ -5064,10 +5796,13 @@
         <v>0.08032</v>
       </c>
       <c r="D244" s="1" t="n">
+        <v>0.07997</v>
+      </c>
+      <c r="E244" s="1" t="n">
         <v>0.08051999999999999</v>
       </c>
-      <c r="E244" s="1" t="n">
-        <v>0.08032</v>
+      <c r="F244" s="1" t="n">
+        <v>0.07997</v>
       </c>
     </row>
     <row r="245">
@@ -5083,9 +5818,12 @@
         <v>0.008052</v>
       </c>
       <c r="D245" s="1" t="n">
+        <v>0.008022</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="E245" s="1" t="n">
+      <c r="F245" s="1" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -5105,6 +5843,9 @@
         <v>0.03059</v>
       </c>
       <c r="E246" s="1" t="n">
+        <v>0.03059</v>
+      </c>
+      <c r="F246" s="1" t="n">
         <v>0.03056</v>
       </c>
     </row>
@@ -5121,9 +5862,12 @@
         <v>0.1808</v>
       </c>
       <c r="D247" s="1" t="n">
+        <v>0.1808</v>
+      </c>
+      <c r="E247" s="1" t="n">
         <v>0.1813</v>
       </c>
-      <c r="E247" s="1" t="n">
+      <c r="F247" s="1" t="n">
         <v>0.1808</v>
       </c>
     </row>
@@ -5140,10 +5884,13 @@
         <v>0.05929</v>
       </c>
       <c r="D248" s="1" t="n">
+        <v>0.05915</v>
+      </c>
+      <c r="E248" s="1" t="n">
         <v>0.05929</v>
       </c>
-      <c r="E248" s="1" t="n">
-        <v>0.05925</v>
+      <c r="F248" s="1" t="n">
+        <v>0.05915</v>
       </c>
     </row>
     <row r="249">
@@ -5159,10 +5906,13 @@
         <v>0.1669</v>
       </c>
       <c r="D249" s="1" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="E249" s="1" t="n">
         <v>0.1676</v>
       </c>
-      <c r="E249" s="1" t="n">
-        <v>0.1669</v>
+      <c r="F249" s="1" t="n">
+        <v>0.1664</v>
       </c>
     </row>
     <row r="250">
@@ -5178,10 +5928,13 @@
         <v>0.01946</v>
       </c>
       <c r="D250" s="1" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="E250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="E250" s="1" t="n">
-        <v>0.01946</v>
+      <c r="F250" s="1" t="n">
+        <v>0.01938</v>
       </c>
     </row>
     <row r="251">
@@ -5197,9 +5950,12 @@
         <v>0.02312</v>
       </c>
       <c r="D251" s="1" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="E251" s="1" t="n">
         <v>0.02312</v>
       </c>
-      <c r="E251" s="1" t="n">
+      <c r="F251" s="1" t="n">
         <v>0.02304</v>
       </c>
     </row>
@@ -5216,9 +5972,12 @@
         <v>0.30027</v>
       </c>
       <c r="D252" s="1" t="n">
-        <v>0.30027</v>
+        <v>0.30199</v>
       </c>
       <c r="E252" s="1" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="F252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -5235,10 +5994,13 @@
         <v>0.006074</v>
       </c>
       <c r="D253" s="1" t="n">
+        <v>0.00607</v>
+      </c>
+      <c r="E253" s="1" t="n">
         <v>0.006106</v>
       </c>
-      <c r="E253" s="1" t="n">
-        <v>0.006074</v>
+      <c r="F253" s="1" t="n">
+        <v>0.00607</v>
       </c>
     </row>
     <row r="254">
@@ -5254,10 +6016,13 @@
         <v>0.6163999999999999</v>
       </c>
       <c r="D254" s="1" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="E254" s="1" t="n">
         <v>0.6167</v>
       </c>
-      <c r="E254" s="1" t="n">
-        <v>0.6163999999999999</v>
+      <c r="F254" s="1" t="n">
+        <v>0.6141</v>
       </c>
     </row>
     <row r="255">
@@ -5273,10 +6038,13 @@
         <v>0.10811</v>
       </c>
       <c r="D255" s="1" t="n">
+        <v>0.10785</v>
+      </c>
+      <c r="E255" s="1" t="n">
         <v>0.10811</v>
       </c>
-      <c r="E255" s="1" t="n">
-        <v>0.10807</v>
+      <c r="F255" s="1" t="n">
+        <v>0.10785</v>
       </c>
     </row>
     <row r="256">
@@ -5292,9 +6060,12 @@
         <v>0.0907</v>
       </c>
       <c r="D256" s="1" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="E256" s="1" t="n">
         <v>0.0907</v>
       </c>
-      <c r="E256" s="1" t="n">
+      <c r="F256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -5311,10 +6082,13 @@
         <v>0.01421</v>
       </c>
       <c r="D257" s="1" t="n">
+        <v>0.01417</v>
+      </c>
+      <c r="E257" s="1" t="n">
         <v>0.01433</v>
       </c>
-      <c r="E257" s="1" t="n">
-        <v>0.01421</v>
+      <c r="F257" s="1" t="n">
+        <v>0.01417</v>
       </c>
     </row>
     <row r="258">
@@ -5330,9 +6104,12 @@
         <v>0.0511</v>
       </c>
       <c r="D258" s="1" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="E258" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="E258" s="1" t="n">
+      <c r="F258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -5349,10 +6126,13 @@
         <v>0.00827</v>
       </c>
       <c r="D259" s="1" t="n">
+        <v>0.008240000000000001</v>
+      </c>
+      <c r="E259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="E259" s="1" t="n">
-        <v>0.00827</v>
+      <c r="F259" s="1" t="n">
+        <v>0.008240000000000001</v>
       </c>
     </row>
     <row r="260">
@@ -5368,10 +6148,13 @@
         <v>0.1907</v>
       </c>
       <c r="D260" s="1" t="n">
+        <v>0.1902</v>
+      </c>
+      <c r="E260" s="1" t="n">
         <v>0.1907</v>
       </c>
-      <c r="E260" s="1" t="n">
-        <v>0.1904</v>
+      <c r="F260" s="1" t="n">
+        <v>0.1902</v>
       </c>
     </row>
     <row r="261">
@@ -5387,10 +6170,13 @@
         <v>0.0989</v>
       </c>
       <c r="D261" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="E261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="E261" s="1" t="n">
-        <v>0.0989</v>
+      <c r="F261" s="1" t="n">
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -5406,10 +6192,13 @@
         <v>0.2129</v>
       </c>
       <c r="D262" s="1" t="n">
+        <v>0.2128</v>
+      </c>
+      <c r="E262" s="1" t="n">
         <v>0.2138</v>
       </c>
-      <c r="E262" s="1" t="n">
-        <v>0.2129</v>
+      <c r="F262" s="1" t="n">
+        <v>0.2128</v>
       </c>
     </row>
     <row r="263">
@@ -5425,9 +6214,12 @@
         <v>0.008384000000000001</v>
       </c>
       <c r="D263" s="1" t="n">
-        <v>0.008384000000000001</v>
+        <v>0.008394</v>
       </c>
       <c r="E263" s="1" t="n">
+        <v>0.008394</v>
+      </c>
+      <c r="F263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -5444,10 +6236,13 @@
         <v>2.648</v>
       </c>
       <c r="D264" s="1" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="E264" s="1" t="n">
         <v>2.651</v>
       </c>
-      <c r="E264" s="1" t="n">
-        <v>2.648</v>
+      <c r="F264" s="1" t="n">
+        <v>2.647</v>
       </c>
     </row>
     <row r="265">
@@ -5463,10 +6258,13 @@
         <v>0.01889</v>
       </c>
       <c r="D265" s="1" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="E265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="E265" s="1" t="n">
-        <v>0.01889</v>
+      <c r="F265" s="1" t="n">
+        <v>0.01847</v>
       </c>
     </row>
     <row r="266">
@@ -5482,9 +6280,12 @@
         <v>0.3595</v>
       </c>
       <c r="D266" s="1" t="n">
-        <v>0.3602</v>
+        <v>0.3604</v>
       </c>
       <c r="E266" s="1" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="F266" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -5501,10 +6302,13 @@
         <v>0.03441</v>
       </c>
       <c r="D267" s="1" t="n">
+        <v>0.03429</v>
+      </c>
+      <c r="E267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="E267" s="1" t="n">
-        <v>0.03441</v>
+      <c r="F267" s="1" t="n">
+        <v>0.03429</v>
       </c>
     </row>
     <row r="268">
@@ -5520,9 +6324,12 @@
         <v>0.12</v>
       </c>
       <c r="D268" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="E268" s="1" t="n">
+      <c r="F268" s="1" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -5539,10 +6346,13 @@
         <v>0.0809</v>
       </c>
       <c r="D269" s="1" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="E269" s="1" t="n">
         <v>0.0809</v>
       </c>
-      <c r="E269" s="1" t="n">
-        <v>0.08082</v>
+      <c r="F269" s="1" t="n">
+        <v>0.08053</v>
       </c>
     </row>
     <row r="270">
@@ -5558,10 +6368,13 @@
         <v>0.01398</v>
       </c>
       <c r="D270" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="E270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="E270" s="1" t="n">
-        <v>0.01398</v>
+      <c r="F270" s="1" t="n">
+        <v>0.01397</v>
       </c>
     </row>
     <row r="271">
@@ -5577,11 +6390,14 @@
         <v>0.007659</v>
       </c>
       <c r="D271" s="1" t="n">
-        <v>0.007659</v>
+        <v>0.007654</v>
       </c>
       <c r="E271" s="1" t="n">
         <v>0.007659</v>
       </c>
+      <c r="F271" s="1" t="n">
+        <v>0.007654</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5596,10 +6412,13 @@
         <v>0.07432999999999999</v>
       </c>
       <c r="D272" s="1" t="n">
+        <v>0.07425</v>
+      </c>
+      <c r="E272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="E272" s="1" t="n">
-        <v>0.07432999999999999</v>
+      <c r="F272" s="1" t="n">
+        <v>0.07425</v>
       </c>
     </row>
     <row r="273">
@@ -5615,11 +6434,14 @@
         <v>3.13e-05</v>
       </c>
       <c r="D273" s="1" t="n">
-        <v>3.13e-05</v>
+        <v>3.11e-05</v>
       </c>
       <c r="E273" s="1" t="n">
         <v>3.13e-05</v>
       </c>
+      <c r="F273" s="1" t="n">
+        <v>3.11e-05</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5634,10 +6456,13 @@
         <v>0.00559</v>
       </c>
       <c r="D274" s="1" t="n">
+        <v>0.005586</v>
+      </c>
+      <c r="E274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="E274" s="1" t="n">
-        <v>0.00559</v>
+      <c r="F274" s="1" t="n">
+        <v>0.005586</v>
       </c>
     </row>
     <row r="275">
@@ -5653,11 +6478,14 @@
         <v>0.1804</v>
       </c>
       <c r="D275" s="1" t="n">
-        <v>0.1804</v>
+        <v>0.1802</v>
       </c>
       <c r="E275" s="1" t="n">
         <v>0.1804</v>
       </c>
+      <c r="F275" s="1" t="n">
+        <v>0.1802</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5672,9 +6500,12 @@
         <v>0.006876</v>
       </c>
       <c r="D276" s="1" t="n">
+        <v>0.006878</v>
+      </c>
+      <c r="E276" s="1" t="n">
         <v>0.006919</v>
       </c>
-      <c r="E276" s="1" t="n">
+      <c r="F276" s="1" t="n">
         <v>0.006876</v>
       </c>
     </row>
@@ -5691,10 +6522,13 @@
         <v>0.1317</v>
       </c>
       <c r="D277" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="E277" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="E277" s="1" t="n">
-        <v>0.1317</v>
+      <c r="F277" s="1" t="n">
+        <v>0.1316</v>
       </c>
     </row>
     <row r="278">
@@ -5710,10 +6544,13 @@
         <v>0.02354</v>
       </c>
       <c r="D278" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="E278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="E278" s="1" t="n">
-        <v>0.02354</v>
+      <c r="F278" s="1" t="n">
+        <v>0.02335</v>
       </c>
     </row>
     <row r="279">
@@ -5729,11 +6566,14 @@
         <v>0.01818</v>
       </c>
       <c r="D279" s="1" t="n">
-        <v>0.01818</v>
+        <v>0.01817</v>
       </c>
       <c r="E279" s="1" t="n">
         <v>0.01818</v>
       </c>
+      <c r="F279" s="1" t="n">
+        <v>0.01817</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5748,10 +6588,13 @@
         <v>0.03761</v>
       </c>
       <c r="D280" s="1" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="E280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="E280" s="1" t="n">
-        <v>0.03761</v>
+      <c r="F280" s="1" t="n">
+        <v>0.03755</v>
       </c>
     </row>
     <row r="281">
@@ -5767,10 +6610,13 @@
         <v>0.03988</v>
       </c>
       <c r="D281" s="1" t="n">
+        <v>0.03981</v>
+      </c>
+      <c r="E281" s="1" t="n">
         <v>0.03994</v>
       </c>
-      <c r="E281" s="1" t="n">
-        <v>0.03988</v>
+      <c r="F281" s="1" t="n">
+        <v>0.03981</v>
       </c>
     </row>
     <row r="282">
@@ -5786,10 +6632,13 @@
         <v>0.3045</v>
       </c>
       <c r="D282" s="1" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="E282" s="1" t="n">
         <v>0.3053</v>
       </c>
-      <c r="E282" s="1" t="n">
-        <v>0.3045</v>
+      <c r="F282" s="1" t="n">
+        <v>0.3025</v>
       </c>
     </row>
     <row r="283">
@@ -5805,10 +6654,13 @@
         <v>0.01127</v>
       </c>
       <c r="D283" s="1" t="n">
+        <v>0.01124</v>
+      </c>
+      <c r="E283" s="1" t="n">
         <v>0.01131</v>
       </c>
-      <c r="E283" s="1" t="n">
-        <v>0.01127</v>
+      <c r="F283" s="1" t="n">
+        <v>0.01124</v>
       </c>
     </row>
     <row r="284">
@@ -5824,9 +6676,12 @@
         <v>9.7e-06</v>
       </c>
       <c r="D284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="E284" s="1" t="n">
         <v>9.7e-06</v>
       </c>
-      <c r="E284" s="1" t="n">
+      <c r="F284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -5843,10 +6698,13 @@
         <v>0.1154</v>
       </c>
       <c r="D285" s="1" t="n">
+        <v>0.1153</v>
+      </c>
+      <c r="E285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="E285" s="1" t="n">
-        <v>0.1154</v>
+      <c r="F285" s="1" t="n">
+        <v>0.1153</v>
       </c>
     </row>
     <row r="286">
@@ -5862,10 +6720,13 @@
         <v>0.00345</v>
       </c>
       <c r="D286" s="1" t="n">
+        <v>0.003442</v>
+      </c>
+      <c r="E286" s="1" t="n">
         <v>0.003453</v>
       </c>
-      <c r="E286" s="1" t="n">
-        <v>0.00345</v>
+      <c r="F286" s="1" t="n">
+        <v>0.003442</v>
       </c>
     </row>
     <row r="287">
@@ -5881,10 +6742,13 @@
         <v>0.08563999999999999</v>
       </c>
       <c r="D287" s="1" t="n">
+        <v>0.08545999999999999</v>
+      </c>
+      <c r="E287" s="1" t="n">
         <v>0.08563999999999999</v>
       </c>
-      <c r="E287" s="1" t="n">
-        <v>0.08558</v>
+      <c r="F287" s="1" t="n">
+        <v>0.08545999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -5900,9 +6764,12 @@
         <v>0.09889000000000001</v>
       </c>
       <c r="D288" s="1" t="n">
+        <v>0.09962</v>
+      </c>
+      <c r="E288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="E288" s="1" t="n">
+      <c r="F288" s="1" t="n">
         <v>0.09889000000000001</v>
       </c>
     </row>
@@ -5919,10 +6786,13 @@
         <v>0.4308</v>
       </c>
       <c r="D289" s="1" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="E289" s="1" t="n">
         <v>0.4327</v>
       </c>
-      <c r="E289" s="1" t="n">
-        <v>0.4308</v>
+      <c r="F289" s="1" t="n">
+        <v>0.4307</v>
       </c>
     </row>
     <row r="290">
@@ -5938,10 +6808,13 @@
         <v>0.03928</v>
       </c>
       <c r="D290" s="1" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="E290" s="1" t="n">
         <v>0.03958</v>
       </c>
-      <c r="E290" s="1" t="n">
-        <v>0.03928</v>
+      <c r="F290" s="1" t="n">
+        <v>0.03921</v>
       </c>
     </row>
     <row r="291">
@@ -5957,10 +6830,13 @@
         <v>0.2433</v>
       </c>
       <c r="D291" s="1" t="n">
+        <v>0.2416</v>
+      </c>
+      <c r="E291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="E291" s="1" t="n">
-        <v>0.2433</v>
+      <c r="F291" s="1" t="n">
+        <v>0.2416</v>
       </c>
     </row>
     <row r="292">
@@ -5976,10 +6852,13 @@
         <v>0.28533</v>
       </c>
       <c r="D292" s="1" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="E292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="E292" s="1" t="n">
-        <v>0.28496</v>
+      <c r="F292" s="1" t="n">
+        <v>0.28375</v>
       </c>
     </row>
     <row r="293">
@@ -5995,10 +6874,13 @@
         <v>0.1512</v>
       </c>
       <c r="D293" s="1" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="E293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="E293" s="1" t="n">
-        <v>0.1512</v>
+      <c r="F293" s="1" t="n">
+        <v>0.1498</v>
       </c>
     </row>
     <row r="294">
@@ -6014,9 +6896,12 @@
         <v>4.238</v>
       </c>
       <c r="D294" s="1" t="n">
+        <v>4.243</v>
+      </c>
+      <c r="E294" s="1" t="n">
         <v>4.254</v>
       </c>
-      <c r="E294" s="1" t="n">
+      <c r="F294" s="1" t="n">
         <v>4.238</v>
       </c>
     </row>
@@ -6033,9 +6918,12 @@
         <v>0.03219</v>
       </c>
       <c r="D295" s="1" t="n">
-        <v>0.03219</v>
+        <v>0.03223</v>
       </c>
       <c r="E295" s="1" t="n">
+        <v>0.03223</v>
+      </c>
+      <c r="F295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -6052,9 +6940,12 @@
         <v>0.0009890000000000001</v>
       </c>
       <c r="D296" s="1" t="n">
+        <v>0.0009829999999999999</v>
+      </c>
+      <c r="E296" s="1" t="n">
         <v>0.0009890000000000001</v>
       </c>
-      <c r="E296" s="1" t="n">
+      <c r="F296" s="1" t="n">
         <v>0.00098</v>
       </c>
     </row>
@@ -6071,10 +6962,13 @@
         <v>0.08252</v>
       </c>
       <c r="D297" s="1" t="n">
+        <v>0.08209</v>
+      </c>
+      <c r="E297" s="1" t="n">
         <v>0.08255999999999999</v>
       </c>
-      <c r="E297" s="1" t="n">
-        <v>0.08252</v>
+      <c r="F297" s="1" t="n">
+        <v>0.08209</v>
       </c>
     </row>
     <row r="298">
@@ -6090,9 +6984,12 @@
         <v>0.05763</v>
       </c>
       <c r="D298" s="1" t="n">
+        <v>0.05771</v>
+      </c>
+      <c r="E298" s="1" t="n">
         <v>0.05792</v>
       </c>
-      <c r="E298" s="1" t="n">
+      <c r="F298" s="1" t="n">
         <v>0.05763</v>
       </c>
     </row>
@@ -6109,10 +7006,13 @@
         <v>0.09082</v>
       </c>
       <c r="D299" s="1" t="n">
+        <v>0.09066</v>
+      </c>
+      <c r="E299" s="1" t="n">
         <v>0.09109</v>
       </c>
-      <c r="E299" s="1" t="n">
-        <v>0.09082</v>
+      <c r="F299" s="1" t="n">
+        <v>0.09066</v>
       </c>
     </row>
     <row r="300">
@@ -6128,10 +7028,13 @@
         <v>0.02774</v>
       </c>
       <c r="D300" s="1" t="n">
+        <v>0.02764</v>
+      </c>
+      <c r="E300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="E300" s="1" t="n">
-        <v>0.02774</v>
+      <c r="F300" s="1" t="n">
+        <v>0.02764</v>
       </c>
     </row>
     <row r="301">
@@ -6147,10 +7050,13 @@
         <v>0.06605999999999999</v>
       </c>
       <c r="D301" s="1" t="n">
+        <v>0.06603000000000001</v>
+      </c>
+      <c r="E301" s="1" t="n">
         <v>0.06623999999999999</v>
       </c>
-      <c r="E301" s="1" t="n">
-        <v>0.06605999999999999</v>
+      <c r="F301" s="1" t="n">
+        <v>0.06603000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -6166,9 +7072,12 @@
         <v>0.052263</v>
       </c>
       <c r="D302" s="1" t="n">
-        <v>0.052263</v>
+        <v>0.052337</v>
       </c>
       <c r="E302" s="1" t="n">
+        <v>0.052337</v>
+      </c>
+      <c r="F302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -6185,10 +7094,13 @@
         <v>5163.3</v>
       </c>
       <c r="D303" s="1" t="n">
+        <v>5156.4</v>
+      </c>
+      <c r="E303" s="1" t="n">
         <v>5172.3</v>
       </c>
-      <c r="E303" s="1" t="n">
-        <v>5163.3</v>
+      <c r="F303" s="1" t="n">
+        <v>5156.4</v>
       </c>
     </row>
     <row r="304">
@@ -6204,10 +7116,13 @@
         <v>15.02</v>
       </c>
       <c r="D304" s="1" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E304" s="1" t="n">
         <v>15.02</v>
       </c>
-      <c r="E304" s="1" t="n">
-        <v>15.01</v>
+      <c r="F304" s="1" t="n">
+        <v>14.99</v>
       </c>
     </row>
     <row r="305">
@@ -6223,10 +7138,13 @@
         <v>0.003771</v>
       </c>
       <c r="D305" s="1" t="n">
+        <v>0.003722</v>
+      </c>
+      <c r="E305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="E305" s="1" t="n">
-        <v>0.003771</v>
+      <c r="F305" s="1" t="n">
+        <v>0.003722</v>
       </c>
     </row>
     <row r="306">
@@ -6242,9 +7160,12 @@
         <v>0.4573</v>
       </c>
       <c r="D306" s="1" t="n">
+        <v>0.4574</v>
+      </c>
+      <c r="E306" s="1" t="n">
         <v>0.4602</v>
       </c>
-      <c r="E306" s="1" t="n">
+      <c r="F306" s="1" t="n">
         <v>0.4573</v>
       </c>
     </row>
@@ -6261,9 +7182,12 @@
         <v>0.04732</v>
       </c>
       <c r="D307" s="1" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="E307" s="1" t="n">
         <v>0.04745</v>
       </c>
-      <c r="E307" s="1" t="n">
+      <c r="F307" s="1" t="n">
         <v>0.04732</v>
       </c>
     </row>
@@ -6280,9 +7204,12 @@
         <v>1.4627</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>1.4627</v>
+        <v>1.4784</v>
       </c>
       <c r="E308" s="1" t="n">
+        <v>1.4784</v>
+      </c>
+      <c r="F308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -6299,9 +7226,12 @@
         <v>0.0008068</v>
       </c>
       <c r="D309" s="1" t="n">
+        <v>0.000807</v>
+      </c>
+      <c r="E309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="E309" s="1" t="n">
+      <c r="F309" s="1" t="n">
         <v>0.0008068</v>
       </c>
     </row>
@@ -6318,11 +7248,14 @@
         <v>4.699</v>
       </c>
       <c r="D310" s="1" t="n">
-        <v>4.699</v>
+        <v>4.692</v>
       </c>
       <c r="E310" s="1" t="n">
         <v>4.699</v>
       </c>
+      <c r="F310" s="1" t="n">
+        <v>4.692</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6337,10 +7270,13 @@
         <v>4.778</v>
       </c>
       <c r="D311" s="1" t="n">
+        <v>4.765</v>
+      </c>
+      <c r="E311" s="1" t="n">
         <v>4.784</v>
       </c>
-      <c r="E311" s="1" t="n">
-        <v>4.778</v>
+      <c r="F311" s="1" t="n">
+        <v>4.765</v>
       </c>
     </row>
     <row r="312">
@@ -6356,9 +7292,12 @@
         <v>0.08121</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>0.08121</v>
+        <v>0.08133</v>
       </c>
       <c r="E312" s="1" t="n">
+        <v>0.08133</v>
+      </c>
+      <c r="F312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -6375,10 +7314,13 @@
         <v>2.048</v>
       </c>
       <c r="D313" s="1" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="E313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="E313" s="1" t="n">
-        <v>2.048</v>
+      <c r="F313" s="1" t="n">
+        <v>2.037</v>
       </c>
     </row>
     <row r="314">
@@ -6394,9 +7336,12 @@
         <v>0.06839000000000001</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>0.06839000000000001</v>
+        <v>0.06886</v>
       </c>
       <c r="E314" s="1" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="F314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -6413,9 +7358,12 @@
         <v>0.959</v>
       </c>
       <c r="D315" s="1" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="E315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="E315" s="1" t="n">
+      <c r="F315" s="1" t="n">
         <v>0.959</v>
       </c>
     </row>
@@ -6432,10 +7380,13 @@
         <v>0.1307</v>
       </c>
       <c r="D316" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="E316" s="1" t="n">
         <v>0.1308</v>
       </c>
-      <c r="E316" s="1" t="n">
-        <v>0.1307</v>
+      <c r="F316" s="1" t="n">
+        <v>0.1305</v>
       </c>
     </row>
     <row r="317">
@@ -6451,9 +7402,12 @@
         <v>0.18</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>0.18</v>
+        <v>0.1814</v>
       </c>
       <c r="E317" s="1" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="F317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -6473,6 +7427,9 @@
         <v>0.01666</v>
       </c>
       <c r="E318" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="F318" s="1" t="n">
         <v>0.01661</v>
       </c>
     </row>
@@ -6489,9 +7446,12 @@
         <v>0.08395</v>
       </c>
       <c r="D319" s="1" t="n">
+        <v>0.08399</v>
+      </c>
+      <c r="E319" s="1" t="n">
         <v>0.08409</v>
       </c>
-      <c r="E319" s="1" t="n">
+      <c r="F319" s="1" t="n">
         <v>0.08395</v>
       </c>
     </row>
@@ -6508,10 +7468,13 @@
         <v>0.007618</v>
       </c>
       <c r="D320" s="1" t="n">
+        <v>0.007597</v>
+      </c>
+      <c r="E320" s="1" t="n">
         <v>0.007659</v>
       </c>
-      <c r="E320" s="1" t="n">
-        <v>0.007618</v>
+      <c r="F320" s="1" t="n">
+        <v>0.007597</v>
       </c>
     </row>
     <row r="321">
@@ -6527,9 +7490,12 @@
         <v>0.05452</v>
       </c>
       <c r="D321" s="1" t="n">
+        <v>0.05453</v>
+      </c>
+      <c r="E321" s="1" t="n">
         <v>0.05463</v>
       </c>
-      <c r="E321" s="1" t="n">
+      <c r="F321" s="1" t="n">
         <v>0.05452</v>
       </c>
     </row>
@@ -6546,10 +7512,13 @@
         <v>0.5489000000000001</v>
       </c>
       <c r="D322" s="1" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="E322" s="1" t="n">
         <v>0.5513</v>
       </c>
-      <c r="E322" s="1" t="n">
-        <v>0.5489000000000001</v>
+      <c r="F322" s="1" t="n">
+        <v>0.5483</v>
       </c>
     </row>
     <row r="323">
@@ -6565,9 +7534,12 @@
         <v>0.07525</v>
       </c>
       <c r="D323" s="1" t="n">
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="E323" s="1" t="n">
         <v>0.07593</v>
       </c>
-      <c r="E323" s="1" t="n">
+      <c r="F323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -6584,9 +7556,12 @@
         <v>0.012753</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>0.012753</v>
+        <v>0.012807</v>
       </c>
       <c r="E324" s="1" t="n">
+        <v>0.012807</v>
+      </c>
+      <c r="F324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -6603,10 +7578,13 @@
         <v>0.09950000000000001</v>
       </c>
       <c r="D325" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="E325" s="1" t="n">
         <v>0.0998</v>
       </c>
-      <c r="E325" s="1" t="n">
-        <v>0.09950000000000001</v>
+      <c r="F325" s="1" t="n">
+        <v>0.0993</v>
       </c>
     </row>
     <row r="326">
@@ -6622,10 +7600,13 @@
         <v>0.01753</v>
       </c>
       <c r="D326" s="1" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="E326" s="1" t="n">
         <v>0.01756</v>
       </c>
-      <c r="E326" s="1" t="n">
-        <v>0.01753</v>
+      <c r="F326" s="1" t="n">
+        <v>0.01752</v>
       </c>
     </row>
     <row r="327">
@@ -6641,10 +7622,13 @@
         <v>0.06393</v>
       </c>
       <c r="D327" s="1" t="n">
+        <v>0.06392</v>
+      </c>
+      <c r="E327" s="1" t="n">
         <v>0.06401999999999999</v>
       </c>
-      <c r="E327" s="1" t="n">
-        <v>0.06393</v>
+      <c r="F327" s="1" t="n">
+        <v>0.06392</v>
       </c>
     </row>
     <row r="328">
@@ -6660,10 +7644,13 @@
         <v>0.2681</v>
       </c>
       <c r="D328" s="1" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="E328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="E328" s="1" t="n">
-        <v>0.2681</v>
+      <c r="F328" s="1" t="n">
+        <v>0.2675</v>
       </c>
     </row>
     <row r="329">
@@ -6679,9 +7666,12 @@
         <v>0.17224</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>0.17224</v>
+        <v>0.17286</v>
       </c>
       <c r="E329" s="1" t="n">
+        <v>0.17286</v>
+      </c>
+      <c r="F329" s="1" t="n">
         <v>0.17172</v>
       </c>
     </row>
@@ -6698,9 +7688,12 @@
         <v>2.064</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>2.064</v>
+        <v>2.071</v>
       </c>
       <c r="E330" s="1" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="F330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -6717,9 +7710,12 @@
         <v>0.0278</v>
       </c>
       <c r="D331" s="1" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="E331" s="1" t="n">
         <v>0.028</v>
       </c>
-      <c r="E331" s="1" t="n">
+      <c r="F331" s="1" t="n">
         <v>0.0278</v>
       </c>
     </row>
@@ -6736,9 +7732,12 @@
         <v>0.005932</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>0.005932</v>
+        <v>0.005981</v>
       </c>
       <c r="E332" s="1" t="n">
+        <v>0.005981</v>
+      </c>
+      <c r="F332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -6755,9 +7754,12 @@
         <v>0.003531</v>
       </c>
       <c r="D333" s="1" t="n">
+        <v>0.003548</v>
+      </c>
+      <c r="E333" s="1" t="n">
         <v>0.00355</v>
       </c>
-      <c r="E333" s="1" t="n">
+      <c r="F333" s="1" t="n">
         <v>0.003531</v>
       </c>
     </row>
@@ -6774,10 +7776,13 @@
         <v>0.01409</v>
       </c>
       <c r="D334" s="1" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="E334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="E334" s="1" t="n">
-        <v>0.01409</v>
+      <c r="F334" s="1" t="n">
+        <v>0.01399</v>
       </c>
     </row>
     <row r="335">
@@ -6793,9 +7798,12 @@
         <v>1.12</v>
       </c>
       <c r="D335" s="1" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E335" s="1" t="n">
         <v>1.125</v>
       </c>
-      <c r="E335" s="1" t="n">
+      <c r="F335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -6812,10 +7820,13 @@
         <v>0.011273</v>
       </c>
       <c r="D336" s="1" t="n">
+        <v>0.011253</v>
+      </c>
+      <c r="E336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="E336" s="1" t="n">
-        <v>0.011273</v>
+      <c r="F336" s="1" t="n">
+        <v>0.011253</v>
       </c>
     </row>
     <row r="337">
@@ -6831,9 +7842,12 @@
         <v>2.914</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>2.914</v>
+        <v>2.918</v>
       </c>
       <c r="E337" s="1" t="n">
+        <v>2.918</v>
+      </c>
+      <c r="F337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -6850,10 +7864,13 @@
         <v>0.01874</v>
       </c>
       <c r="D338" s="1" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="E338" s="1" t="n">
         <v>0.01884</v>
       </c>
-      <c r="E338" s="1" t="n">
-        <v>0.01874</v>
+      <c r="F338" s="1" t="n">
+        <v>0.01861</v>
       </c>
     </row>
     <row r="339">
@@ -6872,6 +7889,9 @@
         <v>0.07691000000000001</v>
       </c>
       <c r="E339" s="1" t="n">
+        <v>0.07691000000000001</v>
+      </c>
+      <c r="F339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -6888,11 +7908,14 @@
         <v>0.077</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="E340" s="1" t="n">
         <v>0.077</v>
       </c>
+      <c r="F340" s="1" t="n">
+        <v>0.076</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6907,9 +7930,12 @@
         <v>0.03628</v>
       </c>
       <c r="D341" s="1" t="n">
+        <v>0.03623</v>
+      </c>
+      <c r="E341" s="1" t="n">
         <v>0.03628</v>
       </c>
-      <c r="E341" s="1" t="n">
+      <c r="F341" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -6926,10 +7952,13 @@
         <v>2635</v>
       </c>
       <c r="D342" s="1" t="n">
+        <v>2620</v>
+      </c>
+      <c r="E342" s="1" t="n">
         <v>2635</v>
       </c>
-      <c r="E342" s="1" t="n">
-        <v>2623</v>
+      <c r="F342" s="1" t="n">
+        <v>2620</v>
       </c>
     </row>
     <row r="343">
@@ -6945,10 +7974,13 @@
         <v>0.0001965</v>
       </c>
       <c r="D343" s="1" t="n">
+        <v>0.0001959</v>
+      </c>
+      <c r="E343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="E343" s="1" t="n">
-        <v>0.0001965</v>
+      <c r="F343" s="1" t="n">
+        <v>0.0001959</v>
       </c>
     </row>
     <row r="344">
@@ -6964,10 +7996,13 @@
         <v>0.07989</v>
       </c>
       <c r="D344" s="1" t="n">
+        <v>0.07987</v>
+      </c>
+      <c r="E344" s="1" t="n">
         <v>0.07993</v>
       </c>
-      <c r="E344" s="1" t="n">
-        <v>0.07989</v>
+      <c r="F344" s="1" t="n">
+        <v>0.07987</v>
       </c>
     </row>
     <row r="345">
@@ -6983,10 +8018,13 @@
         <v>0.0164</v>
       </c>
       <c r="D345" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="E345" s="1" t="n">
         <v>0.01645</v>
       </c>
-      <c r="E345" s="1" t="n">
-        <v>0.0164</v>
+      <c r="F345" s="1" t="n">
+        <v>0.01632</v>
       </c>
     </row>
     <row r="346">
@@ -7002,9 +8040,12 @@
         <v>2.773</v>
       </c>
       <c r="D346" s="1" t="n">
+        <v>2.773</v>
+      </c>
+      <c r="E346" s="1" t="n">
         <v>2.794</v>
       </c>
-      <c r="E346" s="1" t="n">
+      <c r="F346" s="1" t="n">
         <v>2.773</v>
       </c>
     </row>
@@ -7021,10 +8062,13 @@
         <v>0.01643</v>
       </c>
       <c r="D347" s="1" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="E347" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="E347" s="1" t="n">
-        <v>0.01643</v>
+      <c r="F347" s="1" t="n">
+        <v>0.01639</v>
       </c>
     </row>
     <row r="348">
@@ -7040,9 +8084,12 @@
         <v>0.03829</v>
       </c>
       <c r="D348" s="1" t="n">
-        <v>0.03829</v>
+        <v>0.03877</v>
       </c>
       <c r="E348" s="1" t="n">
+        <v>0.03877</v>
+      </c>
+      <c r="F348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -7059,10 +8106,13 @@
         <v>0.305</v>
       </c>
       <c r="D349" s="1" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="E349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="E349" s="1" t="n">
-        <v>0.305</v>
+      <c r="F349" s="1" t="n">
+        <v>0.3037</v>
       </c>
     </row>
     <row r="350">
@@ -7078,10 +8128,13 @@
         <v>0.005095</v>
       </c>
       <c r="D350" s="1" t="n">
+        <v>0.005039</v>
+      </c>
+      <c r="E350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="E350" s="1" t="n">
-        <v>0.005095</v>
+      <c r="F350" s="1" t="n">
+        <v>0.005039</v>
       </c>
     </row>
     <row r="351">
@@ -7097,10 +8150,13 @@
         <v>0.005145</v>
       </c>
       <c r="D351" s="1" t="n">
+        <v>0.00512</v>
+      </c>
+      <c r="E351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="E351" s="1" t="n">
-        <v>0.005145</v>
+      <c r="F351" s="1" t="n">
+        <v>0.00512</v>
       </c>
     </row>
     <row r="352">
@@ -7116,10 +8172,13 @@
         <v>0.004394</v>
       </c>
       <c r="D352" s="1" t="n">
+        <v>0.004387</v>
+      </c>
+      <c r="E352" s="1" t="n">
         <v>0.004397</v>
       </c>
-      <c r="E352" s="1" t="n">
-        <v>0.004394</v>
+      <c r="F352" s="1" t="n">
+        <v>0.004387</v>
       </c>
     </row>
     <row r="353">
@@ -7135,10 +8194,13 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="D353" s="1" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="E353" s="1" t="n">
         <v>0.08211</v>
       </c>
-      <c r="E353" s="1" t="n">
-        <v>0.08210000000000001</v>
+      <c r="F353" s="1" t="n">
+        <v>0.08172</v>
       </c>
     </row>
     <row r="354">
@@ -7154,9 +8216,12 @@
         <v>1.291</v>
       </c>
       <c r="D354" s="1" t="n">
-        <v>1.291</v>
+        <v>1.292</v>
       </c>
       <c r="E354" s="1" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="F354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -7173,9 +8238,12 @@
         <v>7.744</v>
       </c>
       <c r="D355" s="1" t="n">
+        <v>7.745</v>
+      </c>
+      <c r="E355" s="1" t="n">
         <v>7.771</v>
       </c>
-      <c r="E355" s="1" t="n">
+      <c r="F355" s="1" t="n">
         <v>7.744</v>
       </c>
     </row>
@@ -7192,10 +8260,13 @@
         <v>0.007889999999999999</v>
       </c>
       <c r="D356" s="1" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="E356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="E356" s="1" t="n">
-        <v>0.007889999999999999</v>
+      <c r="F356" s="1" t="n">
+        <v>0.007849999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -7211,10 +8282,13 @@
         <v>0.00573</v>
       </c>
       <c r="D357" s="1" t="n">
+        <v>0.005696</v>
+      </c>
+      <c r="E357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="E357" s="1" t="n">
-        <v>0.00573</v>
+      <c r="F357" s="1" t="n">
+        <v>0.005696</v>
       </c>
     </row>
     <row r="358">
@@ -7230,10 +8304,13 @@
         <v>0.01577</v>
       </c>
       <c r="D358" s="1" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="E358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="E358" s="1" t="n">
-        <v>0.01577</v>
+      <c r="F358" s="1" t="n">
+        <v>0.01567</v>
       </c>
     </row>
     <row r="359">
@@ -7249,10 +8326,13 @@
         <v>3.654</v>
       </c>
       <c r="D359" s="1" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E359" s="1" t="n">
         <v>3.655</v>
       </c>
-      <c r="E359" s="1" t="n">
-        <v>3.654</v>
+      <c r="F359" s="1" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="360">
@@ -7268,9 +8348,12 @@
         <v>0.1499</v>
       </c>
       <c r="D360" s="1" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>0.1503</v>
       </c>
-      <c r="E360" s="1" t="n">
+      <c r="F360" s="1" t="n">
         <v>0.1499</v>
       </c>
     </row>
@@ -7287,9 +8370,12 @@
         <v>0.07069</v>
       </c>
       <c r="D361" s="1" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="E361" s="1" t="n">
         <v>0.07093000000000001</v>
       </c>
-      <c r="E361" s="1" t="n">
+      <c r="F361" s="1" t="n">
         <v>0.07069</v>
       </c>
     </row>
@@ -7306,10 +8392,13 @@
         <v>0.01795</v>
       </c>
       <c r="D362" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="E362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="E362" s="1" t="n">
-        <v>0.01795</v>
+      <c r="F362" s="1" t="n">
+        <v>0.01786</v>
       </c>
     </row>
     <row r="363">
@@ -7325,9 +8414,12 @@
         <v>0.02262</v>
       </c>
       <c r="D363" s="1" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="E363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="E363" s="1" t="n">
+      <c r="F363" s="1" t="n">
         <v>0.02262</v>
       </c>
     </row>
@@ -7344,10 +8436,13 @@
         <v>0.01277</v>
       </c>
       <c r="D364" s="1" t="n">
+        <v>0.01271</v>
+      </c>
+      <c r="E364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="E364" s="1" t="n">
-        <v>0.01277</v>
+      <c r="F364" s="1" t="n">
+        <v>0.01271</v>
       </c>
     </row>
     <row r="365">
@@ -7368,6 +8463,9 @@
       <c r="E365" s="1" t="n">
         <v>0.0919</v>
       </c>
+      <c r="F365" s="1" t="n">
+        <v>0.0919</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7382,10 +8480,13 @@
         <v>0.04245</v>
       </c>
       <c r="D366" s="1" t="n">
+        <v>0.04244</v>
+      </c>
+      <c r="E366" s="1" t="n">
         <v>0.04257</v>
       </c>
-      <c r="E366" s="1" t="n">
-        <v>0.04245</v>
+      <c r="F366" s="1" t="n">
+        <v>0.04244</v>
       </c>
     </row>
     <row r="367">
@@ -7401,10 +8502,13 @@
         <v>0.03154</v>
       </c>
       <c r="D367" s="1" t="n">
+        <v>0.03145</v>
+      </c>
+      <c r="E367" s="1" t="n">
         <v>0.03163</v>
       </c>
-      <c r="E367" s="1" t="n">
-        <v>0.03154</v>
+      <c r="F367" s="1" t="n">
+        <v>0.03145</v>
       </c>
     </row>
     <row r="368">
@@ -7420,9 +8524,12 @@
         <v>0.0236</v>
       </c>
       <c r="D368" s="1" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="E368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="E368" s="1" t="n">
+      <c r="F368" s="1" t="n">
         <v>0.0236</v>
       </c>
     </row>
@@ -7439,9 +8546,12 @@
         <v>0.03113</v>
       </c>
       <c r="D369" s="1" t="n">
+        <v>0.03114</v>
+      </c>
+      <c r="E369" s="1" t="n">
         <v>0.03128</v>
       </c>
-      <c r="E369" s="1" t="n">
+      <c r="F369" s="1" t="n">
         <v>0.03113</v>
       </c>
     </row>
@@ -7458,9 +8568,12 @@
         <v>0.07741000000000001</v>
       </c>
       <c r="D370" s="1" t="n">
+        <v>0.07751</v>
+      </c>
+      <c r="E370" s="1" t="n">
         <v>0.07784000000000001</v>
       </c>
-      <c r="E370" s="1" t="n">
+      <c r="F370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -7477,9 +8590,12 @@
         <v>0.1078</v>
       </c>
       <c r="D371" s="1" t="n">
-        <v>0.1078</v>
+        <v>0.1085</v>
       </c>
       <c r="E371" s="1" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="F371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -7496,9 +8612,12 @@
         <v>0.007108</v>
       </c>
       <c r="D372" s="1" t="n">
+        <v>0.007084</v>
+      </c>
+      <c r="E372" s="1" t="n">
         <v>0.007108</v>
       </c>
-      <c r="E372" s="1" t="n">
+      <c r="F372" s="1" t="n">
         <v>0.007057</v>
       </c>
     </row>
@@ -7515,10 +8634,13 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="D373" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="E373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="E373" s="1" t="n">
-        <v>0.09710000000000001</v>
+      <c r="F373" s="1" t="n">
+        <v>0.0965</v>
       </c>
     </row>
     <row r="374">
@@ -7534,9 +8656,12 @@
         <v>0.0583</v>
       </c>
       <c r="D374" s="1" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="E374" s="1" t="n">
         <v>0.05852</v>
       </c>
-      <c r="E374" s="1" t="n">
+      <c r="F374" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -7553,10 +8678,13 @@
         <v>0.3207</v>
       </c>
       <c r="D375" s="1" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="E375" s="1" t="n">
         <v>0.3207</v>
       </c>
-      <c r="E375" s="1" t="n">
-        <v>0.3197</v>
+      <c r="F375" s="1" t="n">
+        <v>0.3193</v>
       </c>
     </row>
     <row r="376">
@@ -7572,10 +8700,13 @@
         <v>0.01996</v>
       </c>
       <c r="D376" s="1" t="n">
+        <v>0.01988</v>
+      </c>
+      <c r="E376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="E376" s="1" t="n">
-        <v>0.01996</v>
+      <c r="F376" s="1" t="n">
+        <v>0.01988</v>
       </c>
     </row>
     <row r="377">
@@ -7591,10 +8722,13 @@
         <v>0.06888</v>
       </c>
       <c r="D377" s="1" t="n">
+        <v>0.06877</v>
+      </c>
+      <c r="E377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="E377" s="1" t="n">
-        <v>0.06888</v>
+      <c r="F377" s="1" t="n">
+        <v>0.06877</v>
       </c>
     </row>
     <row r="378">
@@ -7610,9 +8744,12 @@
         <v>0.15347</v>
       </c>
       <c r="D378" s="1" t="n">
-        <v>0.15365</v>
+        <v>0.15387</v>
       </c>
       <c r="E378" s="1" t="n">
+        <v>0.15387</v>
+      </c>
+      <c r="F378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -7629,10 +8766,13 @@
         <v>0.0006049</v>
       </c>
       <c r="D379" s="1" t="n">
+        <v>0.0006028</v>
+      </c>
+      <c r="E379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="E379" s="1" t="n">
-        <v>0.0006049</v>
+      <c r="F379" s="1" t="n">
+        <v>0.0006028</v>
       </c>
     </row>
     <row r="380">
@@ -7648,9 +8788,12 @@
         <v>0.01016</v>
       </c>
       <c r="D380" s="1" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="E380" s="1" t="n">
         <v>0.01019</v>
       </c>
-      <c r="E380" s="1" t="n">
+      <c r="F380" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -7667,9 +8810,12 @@
         <v>0.02553</v>
       </c>
       <c r="D381" s="1" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="E381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="E381" s="1" t="n">
+      <c r="F381" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -7686,9 +8832,12 @@
         <v>0.19064</v>
       </c>
       <c r="D382" s="1" t="n">
-        <v>0.19064</v>
+        <v>0.19096</v>
       </c>
       <c r="E382" s="1" t="n">
+        <v>0.19096</v>
+      </c>
+      <c r="F382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -7705,9 +8854,12 @@
         <v>0.09406</v>
       </c>
       <c r="D383" s="1" t="n">
-        <v>0.09406</v>
+        <v>0.09433</v>
       </c>
       <c r="E383" s="1" t="n">
+        <v>0.09433</v>
+      </c>
+      <c r="F383" s="1" t="n">
         <v>0.09372999999999999</v>
       </c>
     </row>
@@ -7724,9 +8876,12 @@
         <v>0.03206</v>
       </c>
       <c r="D384" s="1" t="n">
-        <v>0.03206</v>
+        <v>0.03208</v>
       </c>
       <c r="E384" s="1" t="n">
+        <v>0.03208</v>
+      </c>
+      <c r="F384" s="1" t="n">
         <v>0.03194</v>
       </c>
     </row>
@@ -7743,10 +8898,13 @@
         <v>0.0112</v>
       </c>
       <c r="D385" s="1" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="E385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="E385" s="1" t="n">
-        <v>0.0112</v>
+      <c r="F385" s="1" t="n">
+        <v>0.01115</v>
       </c>
     </row>
     <row r="386">
@@ -7762,10 +8920,13 @@
         <v>0.051</v>
       </c>
       <c r="D386" s="1" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="E386" s="1" t="n">
         <v>0.05101</v>
       </c>
-      <c r="E386" s="1" t="n">
-        <v>0.051</v>
+      <c r="F386" s="1" t="n">
+        <v>0.05087</v>
       </c>
     </row>
     <row r="387">
@@ -7781,10 +8942,13 @@
         <v>0.02494</v>
       </c>
       <c r="D387" s="1" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="E387" s="1" t="n">
         <v>0.02504</v>
       </c>
-      <c r="E387" s="1" t="n">
-        <v>0.02494</v>
+      <c r="F387" s="1" t="n">
+        <v>0.02483</v>
       </c>
     </row>
     <row r="388">
@@ -7800,9 +8964,12 @@
         <v>0.007365</v>
       </c>
       <c r="D388" s="1" t="n">
-        <v>0.007365</v>
+        <v>0.007381</v>
       </c>
       <c r="E388" s="1" t="n">
+        <v>0.007381</v>
+      </c>
+      <c r="F388" s="1" t="n">
         <v>0.007344</v>
       </c>
     </row>
@@ -7819,9 +8986,12 @@
         <v>0.01016</v>
       </c>
       <c r="D389" s="1" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="E389" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="E389" s="1" t="n">
+      <c r="F389" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -7838,9 +9008,12 @@
         <v>0.0833</v>
       </c>
       <c r="D390" s="1" t="n">
+        <v>0.08312</v>
+      </c>
+      <c r="E390" s="1" t="n">
         <v>0.0833</v>
       </c>
-      <c r="E390" s="1" t="n">
+      <c r="F390" s="1" t="n">
         <v>0.08304</v>
       </c>
     </row>
@@ -7857,10 +9030,13 @@
         <v>0.5019</v>
       </c>
       <c r="D391" s="1" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="E391" s="1" t="n">
         <v>0.5027</v>
       </c>
-      <c r="E391" s="1" t="n">
-        <v>0.5019</v>
+      <c r="F391" s="1" t="n">
+        <v>0.5017</v>
       </c>
     </row>
     <row r="392">
@@ -7876,10 +9052,13 @@
         <v>0.1172</v>
       </c>
       <c r="D392" s="1" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="E392" s="1" t="n">
         <v>0.1174</v>
       </c>
-      <c r="E392" s="1" t="n">
-        <v>0.1172</v>
+      <c r="F392" s="1" t="n">
+        <v>0.1171</v>
       </c>
     </row>
     <row r="393">
@@ -7895,10 +9074,13 @@
         <v>0.00251</v>
       </c>
       <c r="D393" s="1" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="E393" s="1" t="n">
-        <v>0.00251</v>
+      <c r="F393" s="1" t="n">
+        <v>0.0025</v>
       </c>
     </row>
     <row r="394">
@@ -7914,11 +9096,14 @@
         <v>0.02163</v>
       </c>
       <c r="D394" s="1" t="n">
-        <v>0.02163</v>
+        <v>0.02146</v>
       </c>
       <c r="E394" s="1" t="n">
         <v>0.02163</v>
       </c>
+      <c r="F394" s="1" t="n">
+        <v>0.02146</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7933,9 +9118,12 @@
         <v>0.0163</v>
       </c>
       <c r="D395" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="E395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="E395" s="1" t="n">
+      <c r="F395" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -7952,9 +9140,12 @@
         <v>0.1362</v>
       </c>
       <c r="D396" s="1" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="E396" s="1" t="n">
         <v>0.1362</v>
       </c>
-      <c r="E396" s="1" t="n">
+      <c r="F396" s="1" t="n">
         <v>0.1358</v>
       </c>
     </row>
@@ -7971,10 +9162,13 @@
         <v>0.01482</v>
       </c>
       <c r="D397" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="E397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="E397" s="1" t="n">
-        <v>0.01482</v>
+      <c r="F397" s="1" t="n">
+        <v>0.01475</v>
       </c>
     </row>
     <row r="398">
@@ -7990,9 +9184,12 @@
         <v>6.725</v>
       </c>
       <c r="D398" s="1" t="n">
+        <v>6.725</v>
+      </c>
+      <c r="E398" s="1" t="n">
         <v>6.755</v>
       </c>
-      <c r="E398" s="1" t="n">
+      <c r="F398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -8009,10 +9206,13 @@
         <v>0.009506000000000001</v>
       </c>
       <c r="D399" s="1" t="n">
+        <v>0.009473000000000001</v>
+      </c>
+      <c r="E399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="E399" s="1" t="n">
-        <v>0.009506000000000001</v>
+      <c r="F399" s="1" t="n">
+        <v>0.009473000000000001</v>
       </c>
     </row>
     <row r="400">
@@ -8028,10 +9228,13 @@
         <v>0.001291</v>
       </c>
       <c r="D400" s="1" t="n">
+        <v>0.001269</v>
+      </c>
+      <c r="E400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="E400" s="1" t="n">
-        <v>0.001287</v>
+      <c r="F400" s="1" t="n">
+        <v>0.001269</v>
       </c>
     </row>
     <row r="401">
@@ -8047,10 +9250,13 @@
         <v>0.01849</v>
       </c>
       <c r="D401" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="E401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="E401" s="1" t="n">
-        <v>0.01849</v>
+      <c r="F401" s="1" t="n">
+        <v>0.01841</v>
       </c>
     </row>
     <row r="402">
@@ -8066,9 +9272,12 @@
         <v>0.08577</v>
       </c>
       <c r="D402" s="1" t="n">
-        <v>0.08577</v>
+        <v>0.08587</v>
       </c>
       <c r="E402" s="1" t="n">
+        <v>0.08587</v>
+      </c>
+      <c r="F402" s="1" t="n">
         <v>0.08563999999999999</v>
       </c>
     </row>
@@ -8090,6 +9299,9 @@
       <c r="E403" s="1" t="n">
         <v>0.00553</v>
       </c>
+      <c r="F403" s="1" t="n">
+        <v>0.00553</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8104,10 +9316,13 @@
         <v>0.04381</v>
       </c>
       <c r="D404" s="1" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="E404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="E404" s="1" t="n">
-        <v>0.0437</v>
+      <c r="F404" s="1" t="n">
+        <v>0.04369</v>
       </c>
     </row>
     <row r="405">
@@ -8123,9 +9338,12 @@
         <v>0.05871</v>
       </c>
       <c r="D405" s="1" t="n">
+        <v>0.05873</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>0.05876</v>
       </c>
-      <c r="E405" s="1" t="n">
+      <c r="F405" s="1" t="n">
         <v>0.05871</v>
       </c>
     </row>
@@ -8142,10 +9360,13 @@
         <v>0.01659</v>
       </c>
       <c r="D406" s="1" t="n">
+        <v>0.01658</v>
+      </c>
+      <c r="E406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="E406" s="1" t="n">
-        <v>0.01659</v>
+      <c r="F406" s="1" t="n">
+        <v>0.01658</v>
       </c>
     </row>
     <row r="407">
@@ -8161,10 +9382,13 @@
         <v>0.0426</v>
       </c>
       <c r="D407" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="E407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="E407" s="1" t="n">
-        <v>0.0426</v>
+      <c r="F407" s="1" t="n">
+        <v>0.0425</v>
       </c>
     </row>
     <row r="408">
@@ -8180,10 +9404,13 @@
         <v>0.01945</v>
       </c>
       <c r="D408" s="1" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="E408" s="1" t="n">
         <v>0.0195</v>
       </c>
-      <c r="E408" s="1" t="n">
-        <v>0.01945</v>
+      <c r="F408" s="1" t="n">
+        <v>0.01938</v>
       </c>
     </row>
     <row r="409">
@@ -8199,9 +9426,12 @@
         <v>0.4439</v>
       </c>
       <c r="D409" s="1" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="E409" s="1" t="n">
         <v>0.4439</v>
       </c>
-      <c r="E409" s="1" t="n">
+      <c r="F409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -8218,10 +9448,13 @@
         <v>0.04433</v>
       </c>
       <c r="D410" s="1" t="n">
+        <v>0.04418</v>
+      </c>
+      <c r="E410" s="1" t="n">
         <v>0.04437</v>
       </c>
-      <c r="E410" s="1" t="n">
-        <v>0.04433</v>
+      <c r="F410" s="1" t="n">
+        <v>0.04418</v>
       </c>
     </row>
     <row r="411">
@@ -8237,10 +9470,13 @@
         <v>26.8</v>
       </c>
       <c r="D411" s="1" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="E411" s="1" t="n">
         <v>26.84</v>
       </c>
-      <c r="E411" s="1" t="n">
-        <v>26.8</v>
+      <c r="F411" s="1" t="n">
+        <v>26.78</v>
       </c>
     </row>
     <row r="412">
@@ -8256,10 +9492,13 @@
         <v>0.03527</v>
       </c>
       <c r="D412" s="1" t="n">
+        <v>0.03515</v>
+      </c>
+      <c r="E412" s="1" t="n">
         <v>0.03561</v>
       </c>
-      <c r="E412" s="1" t="n">
-        <v>0.03527</v>
+      <c r="F412" s="1" t="n">
+        <v>0.03515</v>
       </c>
     </row>
     <row r="413">
@@ -8275,10 +9514,13 @@
         <v>0.003425</v>
       </c>
       <c r="D413" s="1" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="E413" s="1" t="n">
         <v>0.003429</v>
       </c>
-      <c r="E413" s="1" t="n">
-        <v>0.003425</v>
+      <c r="F413" s="1" t="n">
+        <v>0.00341</v>
       </c>
     </row>
     <row r="414">
@@ -8294,9 +9536,12 @@
         <v>0.1527</v>
       </c>
       <c r="D414" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="E414" s="1" t="n">
         <v>0.1531</v>
       </c>
-      <c r="E414" s="1" t="n">
+      <c r="F414" s="1" t="n">
         <v>0.1527</v>
       </c>
     </row>
@@ -8313,9 +9558,12 @@
         <v>0.05258</v>
       </c>
       <c r="D415" s="1" t="n">
-        <v>0.05263</v>
+        <v>0.05267</v>
       </c>
       <c r="E415" s="1" t="n">
+        <v>0.05267</v>
+      </c>
+      <c r="F415" s="1" t="n">
         <v>0.05258</v>
       </c>
     </row>
@@ -8332,9 +9580,12 @@
         <v>0.00664</v>
       </c>
       <c r="D416" s="1" t="n">
+        <v>0.00664</v>
+      </c>
+      <c r="E416" s="1" t="n">
         <v>0.00668</v>
       </c>
-      <c r="E416" s="1" t="n">
+      <c r="F416" s="1" t="n">
         <v>0.00664</v>
       </c>
     </row>
@@ -8351,10 +9602,13 @@
         <v>0.06091</v>
       </c>
       <c r="D417" s="1" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="E417" s="1" t="n">
         <v>0.06091</v>
       </c>
-      <c r="E417" s="1" t="n">
-        <v>0.06086</v>
+      <c r="F417" s="1" t="n">
+        <v>0.0608</v>
       </c>
     </row>
     <row r="418">
@@ -8370,10 +9624,13 @@
         <v>0.008199</v>
       </c>
       <c r="D418" s="1" t="n">
+        <v>0.008156</v>
+      </c>
+      <c r="E418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="E418" s="1" t="n">
-        <v>0.008199</v>
+      <c r="F418" s="1" t="n">
+        <v>0.008156</v>
       </c>
     </row>
     <row r="419">
@@ -8389,9 +9646,12 @@
         <v>0.07459</v>
       </c>
       <c r="D419" s="1" t="n">
-        <v>0.07466</v>
+        <v>0.07471</v>
       </c>
       <c r="E419" s="1" t="n">
+        <v>0.07471</v>
+      </c>
+      <c r="F419" s="1" t="n">
         <v>0.07459</v>
       </c>
     </row>
@@ -8408,10 +9668,13 @@
         <v>0.02135</v>
       </c>
       <c r="D420" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="E420" s="1" t="n">
         <v>0.02145</v>
       </c>
-      <c r="E420" s="1" t="n">
-        <v>0.02135</v>
+      <c r="F420" s="1" t="n">
+        <v>0.0213</v>
       </c>
     </row>
     <row r="421">
@@ -8427,9 +9690,12 @@
         <v>0.06938999999999999</v>
       </c>
       <c r="D421" s="1" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="E421" s="1" t="n">
         <v>0.06984</v>
       </c>
-      <c r="E421" s="1" t="n">
+      <c r="F421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -8446,9 +9712,12 @@
         <v>0.01524</v>
       </c>
       <c r="D422" s="1" t="n">
-        <v>0.01527</v>
+        <v>0.01528</v>
       </c>
       <c r="E422" s="1" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="F422" s="1" t="n">
         <v>0.01524</v>
       </c>
     </row>
@@ -8465,10 +9734,13 @@
         <v>0.006689</v>
       </c>
       <c r="D423" s="1" t="n">
+        <v>0.006677</v>
+      </c>
+      <c r="E423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="E423" s="1" t="n">
-        <v>0.006689</v>
+      <c r="F423" s="1" t="n">
+        <v>0.006677</v>
       </c>
     </row>
     <row r="424">
@@ -8484,10 +9756,13 @@
         <v>0.919</v>
       </c>
       <c r="D424" s="1" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E424" s="1" t="n">
         <v>0.92</v>
       </c>
-      <c r="E424" s="1" t="n">
-        <v>0.919</v>
+      <c r="F424" s="1" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="425">
@@ -8503,9 +9778,12 @@
         <v>0.03555</v>
       </c>
       <c r="D425" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="E425" s="1" t="n">
         <v>0.03561</v>
       </c>
-      <c r="E425" s="1" t="n">
+      <c r="F425" s="1" t="n">
         <v>0.03555</v>
       </c>
     </row>
@@ -8522,9 +9800,12 @@
         <v>1.778</v>
       </c>
       <c r="D426" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E426" s="1" t="n">
         <v>1.781</v>
       </c>
-      <c r="E426" s="1" t="n">
+      <c r="F426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -8541,10 +9822,13 @@
         <v>0.12781</v>
       </c>
       <c r="D427" s="1" t="n">
+        <v>0.12771</v>
+      </c>
+      <c r="E427" s="1" t="n">
         <v>0.12793</v>
       </c>
-      <c r="E427" s="1" t="n">
-        <v>0.12781</v>
+      <c r="F427" s="1" t="n">
+        <v>0.12771</v>
       </c>
     </row>
     <row r="428">
@@ -8560,10 +9844,13 @@
         <v>0.05359</v>
       </c>
       <c r="D428" s="1" t="n">
+        <v>0.05339</v>
+      </c>
+      <c r="E428" s="1" t="n">
         <v>0.05359</v>
       </c>
-      <c r="E428" s="1" t="n">
-        <v>0.05354</v>
+      <c r="F428" s="1" t="n">
+        <v>0.05339</v>
       </c>
     </row>
     <row r="429">
@@ -8579,10 +9866,13 @@
         <v>1.317</v>
       </c>
       <c r="D429" s="1" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="E429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="E429" s="1" t="n">
-        <v>1.317</v>
+      <c r="F429" s="1" t="n">
+        <v>1.309</v>
       </c>
     </row>
     <row r="430">
@@ -8598,10 +9888,13 @@
         <v>0.07566000000000001</v>
       </c>
       <c r="D430" s="1" t="n">
+        <v>0.07547</v>
+      </c>
+      <c r="E430" s="1" t="n">
         <v>0.07566000000000001</v>
       </c>
-      <c r="E430" s="1" t="n">
-        <v>0.07563</v>
+      <c r="F430" s="1" t="n">
+        <v>0.07547</v>
       </c>
     </row>
     <row r="431">
@@ -8617,10 +9910,13 @@
         <v>0.1641</v>
       </c>
       <c r="D431" s="1" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="E431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="E431" s="1" t="n">
-        <v>0.1641</v>
+      <c r="F431" s="1" t="n">
+        <v>0.1636</v>
       </c>
     </row>
     <row r="432">
@@ -8636,9 +9932,12 @@
         <v>1.456</v>
       </c>
       <c r="D432" s="1" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="E432" s="1" t="n">
         <v>1.457</v>
       </c>
-      <c r="E432" s="1" t="n">
+      <c r="F432" s="1" t="n">
         <v>1.456</v>
       </c>
     </row>
@@ -8655,9 +9954,12 @@
         <v>3.306</v>
       </c>
       <c r="D433" s="1" t="n">
+        <v>3.306</v>
+      </c>
+      <c r="E433" s="1" t="n">
         <v>3.316</v>
       </c>
-      <c r="E433" s="1" t="n">
+      <c r="F433" s="1" t="n">
         <v>3.306</v>
       </c>
     </row>
@@ -8674,10 +9976,13 @@
         <v>0.1796</v>
       </c>
       <c r="D434" s="1" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="E434" s="1" t="n">
         <v>0.1802</v>
       </c>
-      <c r="E434" s="1" t="n">
-        <v>0.1796</v>
+      <c r="F434" s="1" t="n">
+        <v>0.1792</v>
       </c>
     </row>
     <row r="435">
@@ -8693,10 +9998,13 @@
         <v>0.008688</v>
       </c>
       <c r="D435" s="1" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="E435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="E435" s="1" t="n">
-        <v>0.008688</v>
+      <c r="F435" s="1" t="n">
+        <v>0.00864</v>
       </c>
     </row>
     <row r="436">
@@ -8712,9 +10020,12 @@
         <v>0.2841</v>
       </c>
       <c r="D436" s="1" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="E436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="E436" s="1" t="n">
+      <c r="F436" s="1" t="n">
         <v>0.2841</v>
       </c>
     </row>
@@ -8731,9 +10042,12 @@
         <v>0.03814</v>
       </c>
       <c r="D437" s="1" t="n">
-        <v>0.03814</v>
+        <v>0.03824</v>
       </c>
       <c r="E437" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="F437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -8750,9 +10064,12 @@
         <v>0.02452</v>
       </c>
       <c r="D438" s="1" t="n">
+        <v>0.02455</v>
+      </c>
+      <c r="E438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="E438" s="1" t="n">
+      <c r="F438" s="1" t="n">
         <v>0.02452</v>
       </c>
     </row>
@@ -8769,10 +10086,13 @@
         <v>0.0441</v>
       </c>
       <c r="D439" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="E439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="E439" s="1" t="n">
-        <v>0.0441</v>
+      <c r="F439" s="1" t="n">
+        <v>0.04406</v>
       </c>
     </row>
     <row r="440">
@@ -8788,10 +10108,13 @@
         <v>0.0005232</v>
       </c>
       <c r="D440" s="1" t="n">
+        <v>0.0005221</v>
+      </c>
+      <c r="E440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="E440" s="1" t="n">
-        <v>0.0005232</v>
+      <c r="F440" s="1" t="n">
+        <v>0.0005221</v>
       </c>
     </row>
     <row r="441">
@@ -8807,10 +10130,13 @@
         <v>0.04406</v>
       </c>
       <c r="D441" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="E441" s="1" t="n">
         <v>0.04428</v>
       </c>
-      <c r="E441" s="1" t="n">
-        <v>0.04406</v>
+      <c r="F441" s="1" t="n">
+        <v>0.04394</v>
       </c>
     </row>
     <row r="442">
@@ -8826,10 +10152,13 @@
         <v>0.000415</v>
       </c>
       <c r="D442" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="E442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="E442" s="1" t="n">
-        <v>0.000415</v>
+      <c r="F442" s="1" t="n">
+        <v>0.000413</v>
       </c>
     </row>
     <row r="443">
@@ -8845,10 +10174,13 @@
         <v>0.09789</v>
       </c>
       <c r="D443" s="1" t="n">
+        <v>0.09672</v>
+      </c>
+      <c r="E443" s="1" t="n">
         <v>0.09789</v>
       </c>
-      <c r="E443" s="1" t="n">
-        <v>0.09737</v>
+      <c r="F443" s="1" t="n">
+        <v>0.09672</v>
       </c>
     </row>
     <row r="444">
@@ -8864,10 +10196,13 @@
         <v>2.298</v>
       </c>
       <c r="D444" s="1" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="E444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="E444" s="1" t="n">
-        <v>2.298</v>
+      <c r="F444" s="1" t="n">
+        <v>2.289</v>
       </c>
     </row>
     <row r="445">
@@ -8883,9 +10218,12 @@
         <v>0.2671</v>
       </c>
       <c r="D445" s="1" t="n">
-        <v>0.2671</v>
+        <v>0.268</v>
       </c>
       <c r="E445" s="1" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="F445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -8902,10 +10240,13 @@
         <v>0.0007548</v>
       </c>
       <c r="D446" s="1" t="n">
+        <v>0.0007521</v>
+      </c>
+      <c r="E446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="E446" s="1" t="n">
-        <v>0.0007548</v>
+      <c r="F446" s="1" t="n">
+        <v>0.0007521</v>
       </c>
     </row>
     <row r="447">
@@ -8921,10 +10262,13 @@
         <v>0.03901</v>
       </c>
       <c r="D447" s="1" t="n">
+        <v>0.03873</v>
+      </c>
+      <c r="E447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="E447" s="1" t="n">
-        <v>0.03901</v>
+      <c r="F447" s="1" t="n">
+        <v>0.03873</v>
       </c>
     </row>
     <row r="448">
@@ -8940,9 +10284,12 @@
         <v>0.1755</v>
       </c>
       <c r="D448" s="1" t="n">
-        <v>0.1756</v>
+        <v>0.1763</v>
       </c>
       <c r="E448" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="F448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -8959,10 +10306,13 @@
         <v>0.04287</v>
       </c>
       <c r="D449" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="E449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="E449" s="1" t="n">
-        <v>0.04287</v>
+      <c r="F449" s="1" t="n">
+        <v>0.0427</v>
       </c>
     </row>
     <row r="450">
@@ -8978,10 +10328,13 @@
         <v>0.0001643</v>
       </c>
       <c r="D450" s="1" t="n">
+        <v>0.0001641</v>
+      </c>
+      <c r="E450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="E450" s="1" t="n">
-        <v>0.0001643</v>
+      <c r="F450" s="1" t="n">
+        <v>0.0001641</v>
       </c>
     </row>
     <row r="451">
@@ -8997,10 +10350,13 @@
         <v>0.03779</v>
       </c>
       <c r="D451" s="1" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="E451" s="1" t="n">
-        <v>0.03779</v>
+      <c r="F451" s="1" t="n">
+        <v>0.0376</v>
       </c>
     </row>
     <row r="452">
@@ -9016,10 +10372,13 @@
         <v>0.01</v>
       </c>
       <c r="D452" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="E452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="E452" s="1" t="n">
-        <v>0.00996</v>
+      <c r="F452" s="1" t="n">
+        <v>0.009939999999999999</v>
       </c>
     </row>
     <row r="453">
@@ -9035,10 +10394,13 @@
         <v>0.06796000000000001</v>
       </c>
       <c r="D453" s="1" t="n">
+        <v>0.06793</v>
+      </c>
+      <c r="E453" s="1" t="n">
         <v>0.06798999999999999</v>
       </c>
-      <c r="E453" s="1" t="n">
-        <v>0.06796000000000001</v>
+      <c r="F453" s="1" t="n">
+        <v>0.06793</v>
       </c>
     </row>
     <row r="454">
@@ -9054,10 +10416,13 @@
         <v>0.007554</v>
       </c>
       <c r="D454" s="1" t="n">
+        <v>0.007541</v>
+      </c>
+      <c r="E454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="E454" s="1" t="n">
-        <v>0.007554</v>
+      <c r="F454" s="1" t="n">
+        <v>0.007541</v>
       </c>
     </row>
     <row r="455">
@@ -9073,10 +10438,13 @@
         <v>0.003377</v>
       </c>
       <c r="D455" s="1" t="n">
+        <v>0.003362</v>
+      </c>
+      <c r="E455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="E455" s="1" t="n">
-        <v>0.00337</v>
+      <c r="F455" s="1" t="n">
+        <v>0.003362</v>
       </c>
     </row>
     <row r="456">
@@ -9092,10 +10460,13 @@
         <v>0.001859</v>
       </c>
       <c r="D456" s="1" t="n">
+        <v>0.001854</v>
+      </c>
+      <c r="E456" s="1" t="n">
         <v>0.001864</v>
       </c>
-      <c r="E456" s="1" t="n">
-        <v>0.001859</v>
+      <c r="F456" s="1" t="n">
+        <v>0.001854</v>
       </c>
     </row>
     <row r="457">
@@ -9111,10 +10482,13 @@
         <v>0.0001763</v>
       </c>
       <c r="D457" s="1" t="n">
+        <v>0.0001758</v>
+      </c>
+      <c r="E457" s="1" t="n">
         <v>0.0001763</v>
       </c>
-      <c r="E457" s="1" t="n">
-        <v>0.0001762</v>
+      <c r="F457" s="1" t="n">
+        <v>0.0001758</v>
       </c>
     </row>
     <row r="458">
@@ -9130,9 +10504,12 @@
         <v>0.0003873</v>
       </c>
       <c r="D458" s="1" t="n">
+        <v>0.0003874</v>
+      </c>
+      <c r="E458" s="1" t="n">
         <v>0.0003878</v>
       </c>
-      <c r="E458" s="1" t="n">
+      <c r="F458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -9149,10 +10526,13 @@
         <v>0.01404</v>
       </c>
       <c r="D459" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="E459" s="1" t="n">
         <v>0.01406</v>
       </c>
-      <c r="E459" s="1" t="n">
-        <v>0.01404</v>
+      <c r="F459" s="1" t="n">
+        <v>0.01391</v>
       </c>
     </row>
     <row r="460">
@@ -9168,9 +10548,12 @@
         <v>0.04532</v>
       </c>
       <c r="D460" s="1" t="n">
-        <v>0.04532</v>
+        <v>0.04533</v>
       </c>
       <c r="E460" s="1" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="F460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -9187,10 +10570,13 @@
         <v>0.2823</v>
       </c>
       <c r="D461" s="1" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="E461" s="1" t="n">
         <v>0.283</v>
       </c>
-      <c r="E461" s="1" t="n">
-        <v>0.2823</v>
+      <c r="F461" s="1" t="n">
+        <v>0.2822</v>
       </c>
     </row>
     <row r="462">
@@ -9206,9 +10592,12 @@
         <v>0.00622</v>
       </c>
       <c r="D462" s="1" t="n">
+        <v>0.006244</v>
+      </c>
+      <c r="E462" s="1" t="n">
         <v>0.006279</v>
       </c>
-      <c r="E462" s="1" t="n">
+      <c r="F462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -9225,10 +10614,13 @@
         <v>0.007052</v>
       </c>
       <c r="D463" s="1" t="n">
+        <v>0.00704</v>
+      </c>
+      <c r="E463" s="1" t="n">
         <v>0.007056</v>
       </c>
-      <c r="E463" s="1" t="n">
-        <v>0.007052</v>
+      <c r="F463" s="1" t="n">
+        <v>0.00704</v>
       </c>
     </row>
     <row r="464">
@@ -9244,9 +10636,12 @@
         <v>0.2864</v>
       </c>
       <c r="D464" s="1" t="n">
-        <v>0.2864</v>
+        <v>0.2878</v>
       </c>
       <c r="E464" s="1" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="F464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -9263,10 +10658,13 @@
         <v>0.08082</v>
       </c>
       <c r="D465" s="1" t="n">
+        <v>0.08078</v>
+      </c>
+      <c r="E465" s="1" t="n">
         <v>0.08134</v>
       </c>
-      <c r="E465" s="1" t="n">
-        <v>0.08082</v>
+      <c r="F465" s="1" t="n">
+        <v>0.08078</v>
       </c>
     </row>
     <row r="466">
@@ -9282,10 +10680,13 @@
         <v>0.6338</v>
       </c>
       <c r="D466" s="1" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="E466" s="1" t="n">
         <v>0.6343</v>
       </c>
-      <c r="E466" s="1" t="n">
-        <v>0.6338</v>
+      <c r="F466" s="1" t="n">
+        <v>0.6327</v>
       </c>
     </row>
     <row r="467">
@@ -9301,9 +10702,12 @@
         <v>0.01471</v>
       </c>
       <c r="D467" s="1" t="n">
-        <v>0.01471</v>
+        <v>0.01477</v>
       </c>
       <c r="E467" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="F467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -9320,10 +10724,13 @@
         <v>0.03458</v>
       </c>
       <c r="D468" s="1" t="n">
+        <v>0.03448</v>
+      </c>
+      <c r="E468" s="1" t="n">
         <v>0.03462</v>
       </c>
-      <c r="E468" s="1" t="n">
-        <v>0.03458</v>
+      <c r="F468" s="1" t="n">
+        <v>0.03448</v>
       </c>
     </row>
     <row r="469">
@@ -9339,10 +10746,13 @@
         <v>0.1645</v>
       </c>
       <c r="D469" s="1" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="E469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="E469" s="1" t="n">
-        <v>0.1645</v>
+      <c r="F469" s="1" t="n">
+        <v>0.1644</v>
       </c>
     </row>
     <row r="470">
@@ -9358,10 +10768,13 @@
         <v>0.4139</v>
       </c>
       <c r="D470" s="1" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="E470" s="1" t="n">
         <v>0.4139</v>
       </c>
-      <c r="E470" s="1" t="n">
-        <v>0.4137</v>
+      <c r="F470" s="1" t="n">
+        <v>0.4123</v>
       </c>
     </row>
     <row r="471">
@@ -9377,10 +10790,13 @@
         <v>0.06988</v>
       </c>
       <c r="D471" s="1" t="n">
+        <v>0.06975000000000001</v>
+      </c>
+      <c r="E471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="E471" s="1" t="n">
-        <v>0.06988</v>
+      <c r="F471" s="1" t="n">
+        <v>0.06975000000000001</v>
       </c>
     </row>
     <row r="472">
@@ -9396,10 +10812,13 @@
         <v>0.06701</v>
       </c>
       <c r="D472" s="1" t="n">
+        <v>0.06688</v>
+      </c>
+      <c r="E472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="E472" s="1" t="n">
-        <v>0.06701</v>
+      <c r="F472" s="1" t="n">
+        <v>0.06688</v>
       </c>
     </row>
     <row r="473">
@@ -9415,10 +10834,13 @@
         <v>0.01643</v>
       </c>
       <c r="D473" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="E473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="E473" s="1" t="n">
-        <v>0.01643</v>
+      <c r="F473" s="1" t="n">
+        <v>0.0164</v>
       </c>
     </row>
     <row r="474">
@@ -9434,10 +10856,13 @@
         <v>0.2108</v>
       </c>
       <c r="D474" s="1" t="n">
+        <v>0.2101</v>
+      </c>
+      <c r="E474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="E474" s="1" t="n">
-        <v>0.2108</v>
+      <c r="F474" s="1" t="n">
+        <v>0.2101</v>
       </c>
     </row>
     <row r="475">
@@ -9453,10 +10878,13 @@
         <v>0.04219</v>
       </c>
       <c r="D475" s="1" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="E475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="E475" s="1" t="n">
-        <v>0.04219</v>
+      <c r="F475" s="1" t="n">
+        <v>0.04202</v>
       </c>
     </row>
     <row r="476">
@@ -9472,10 +10900,13 @@
         <v>1.572</v>
       </c>
       <c r="D476" s="1" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E476" s="1" t="n">
         <v>1.572</v>
       </c>
-      <c r="E476" s="1" t="n">
-        <v>1.571</v>
+      <c r="F476" s="1" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="477">
@@ -9491,10 +10922,13 @@
         <v>0.1015</v>
       </c>
       <c r="D477" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="E477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="E477" s="1" t="n">
-        <v>0.1015</v>
+      <c r="F477" s="1" t="n">
+        <v>0.1012</v>
       </c>
     </row>
     <row r="478">
@@ -9510,10 +10944,13 @@
         <v>0.001159</v>
       </c>
       <c r="D478" s="1" t="n">
+        <v>0.001155</v>
+      </c>
+      <c r="E478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="E478" s="1" t="n">
-        <v>0.001159</v>
+      <c r="F478" s="1" t="n">
+        <v>0.001155</v>
       </c>
     </row>
     <row r="479">
@@ -9529,10 +10966,13 @@
         <v>0.1466</v>
       </c>
       <c r="D479" s="1" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="E479" s="1" t="n">
         <v>0.1473</v>
       </c>
-      <c r="E479" s="1" t="n">
-        <v>0.1466</v>
+      <c r="F479" s="1" t="n">
+        <v>0.1462</v>
       </c>
     </row>
     <row r="480">
@@ -9548,10 +10988,13 @@
         <v>0.001728</v>
       </c>
       <c r="D480" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="E480" s="1" t="n">
         <v>0.00173</v>
       </c>
-      <c r="E480" s="1" t="n">
-        <v>0.001728</v>
+      <c r="F480" s="1" t="n">
+        <v>0.001722</v>
       </c>
     </row>
     <row r="481">
@@ -9567,10 +11010,13 @@
         <v>0.923</v>
       </c>
       <c r="D481" s="1" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="E481" s="1" t="n">
-        <v>0.923</v>
+      <c r="F481" s="1" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="482">
@@ -9586,9 +11032,12 @@
         <v>0.13437</v>
       </c>
       <c r="D482" s="1" t="n">
+        <v>0.13463</v>
+      </c>
+      <c r="E482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="E482" s="1" t="n">
+      <c r="F482" s="1" t="n">
         <v>0.13437</v>
       </c>
     </row>
@@ -9605,9 +11054,12 @@
         <v>0.04056</v>
       </c>
       <c r="D483" s="1" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="E483" s="1" t="n">
         <v>0.04056</v>
       </c>
-      <c r="E483" s="1" t="n">
+      <c r="F483" s="1" t="n">
         <v>0.04048</v>
       </c>
     </row>
@@ -9624,9 +11076,12 @@
         <v>0.3137</v>
       </c>
       <c r="D484" s="1" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="E484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="E484" s="1" t="n">
+      <c r="F484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -9643,9 +11098,12 @@
         <v>0.05671</v>
       </c>
       <c r="D485" s="1" t="n">
+        <v>0.0566</v>
+      </c>
+      <c r="E485" s="1" t="n">
         <v>0.05671</v>
       </c>
-      <c r="E485" s="1" t="n">
+      <c r="F485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -9662,11 +11120,14 @@
         <v>0.001572</v>
       </c>
       <c r="D486" s="1" t="n">
-        <v>0.001572</v>
+        <v>0.001569</v>
       </c>
       <c r="E486" s="1" t="n">
         <v>0.001572</v>
       </c>
+      <c r="F486" s="1" t="n">
+        <v>0.001569</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -9681,10 +11142,13 @@
         <v>0.06722</v>
       </c>
       <c r="D487" s="1" t="n">
+        <v>0.06716</v>
+      </c>
+      <c r="E487" s="1" t="n">
         <v>0.06738</v>
       </c>
-      <c r="E487" s="1" t="n">
-        <v>0.06722</v>
+      <c r="F487" s="1" t="n">
+        <v>0.06716</v>
       </c>
     </row>
     <row r="488">
@@ -9700,10 +11164,13 @@
         <v>0.194</v>
       </c>
       <c r="D488" s="1" t="n">
+        <v>0.1936</v>
+      </c>
+      <c r="E488" s="1" t="n">
         <v>0.1942</v>
       </c>
-      <c r="E488" s="1" t="n">
-        <v>0.194</v>
+      <c r="F488" s="1" t="n">
+        <v>0.1936</v>
       </c>
     </row>
     <row r="489">
@@ -9719,10 +11186,13 @@
         <v>0.04817</v>
       </c>
       <c r="D489" s="1" t="n">
+        <v>0.04804</v>
+      </c>
+      <c r="E489" s="1" t="n">
         <v>0.04817</v>
       </c>
-      <c r="E489" s="1" t="n">
-        <v>0.04815</v>
+      <c r="F489" s="1" t="n">
+        <v>0.04804</v>
       </c>
     </row>
     <row r="490">
@@ -9738,11 +11208,14 @@
         <v>0.1395</v>
       </c>
       <c r="D490" s="1" t="n">
-        <v>0.1395</v>
+        <v>0.139</v>
       </c>
       <c r="E490" s="1" t="n">
         <v>0.1395</v>
       </c>
+      <c r="F490" s="1" t="n">
+        <v>0.139</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -9757,9 +11230,12 @@
         <v>0.02243</v>
       </c>
       <c r="D491" s="1" t="n">
+        <v>0.02243</v>
+      </c>
+      <c r="E491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="E491" s="1" t="n">
+      <c r="F491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -9776,10 +11252,13 @@
         <v>0.007856</v>
       </c>
       <c r="D492" s="1" t="n">
+        <v>0.007825</v>
+      </c>
+      <c r="E492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="E492" s="1" t="n">
-        <v>0.007856</v>
+      <c r="F492" s="1" t="n">
+        <v>0.007825</v>
       </c>
     </row>
     <row r="493">
@@ -9795,10 +11274,13 @@
         <v>0.0005966</v>
       </c>
       <c r="D493" s="1" t="n">
+        <v>0.0005952</v>
+      </c>
+      <c r="E493" s="1" t="n">
         <v>0.0005967</v>
       </c>
-      <c r="E493" s="1" t="n">
-        <v>0.0005966</v>
+      <c r="F493" s="1" t="n">
+        <v>0.0005952</v>
       </c>
     </row>
     <row r="494">
@@ -9814,10 +11296,13 @@
         <v>3.029</v>
       </c>
       <c r="D494" s="1" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="E494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="E494" s="1" t="n">
-        <v>3.029</v>
+      <c r="F494" s="1" t="n">
+        <v>2.999</v>
       </c>
     </row>
     <row r="495">
@@ -9833,10 +11318,13 @@
         <v>0.05103</v>
       </c>
       <c r="D495" s="1" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="E495" s="1" t="n">
         <v>0.05103</v>
       </c>
-      <c r="E495" s="1" t="n">
-        <v>0.05102</v>
+      <c r="F495" s="1" t="n">
+        <v>0.05085</v>
       </c>
     </row>
     <row r="496">
@@ -9852,11 +11340,14 @@
         <v>0.006886</v>
       </c>
       <c r="D496" s="1" t="n">
-        <v>0.006886</v>
+        <v>0.006839</v>
       </c>
       <c r="E496" s="1" t="n">
         <v>0.006886</v>
       </c>
+      <c r="F496" s="1" t="n">
+        <v>0.006839</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -9871,10 +11362,13 @@
         <v>1.302</v>
       </c>
       <c r="D497" s="1" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="E497" s="1" t="n">
         <v>1.302</v>
       </c>
-      <c r="E497" s="1" t="n">
-        <v>1.3</v>
+      <c r="F497" s="1" t="n">
+        <v>1.299</v>
       </c>
     </row>
     <row r="498">
@@ -9890,10 +11384,13 @@
         <v>0.04015</v>
       </c>
       <c r="D498" s="1" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="E498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="E498" s="1" t="n">
-        <v>0.04015</v>
+      <c r="F498" s="1" t="n">
+        <v>0.03999</v>
       </c>
     </row>
     <row r="499">
@@ -9909,10 +11406,13 @@
         <v>0.04204</v>
       </c>
       <c r="D499" s="1" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="E499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="E499" s="1" t="n">
-        <v>0.04204</v>
+      <c r="F499" s="1" t="n">
+        <v>0.04186</v>
       </c>
     </row>
     <row r="500">
@@ -9928,10 +11428,13 @@
         <v>0.00538</v>
       </c>
       <c r="D500" s="1" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="E500" s="1" t="n">
         <v>0.0054</v>
       </c>
-      <c r="E500" s="1" t="n">
-        <v>0.00538</v>
+      <c r="F500" s="1" t="n">
+        <v>0.00536</v>
       </c>
     </row>
     <row r="501">
@@ -9947,10 +11450,13 @@
         <v>0.03638</v>
       </c>
       <c r="D501" s="1" t="n">
+        <v>0.03625</v>
+      </c>
+      <c r="E501" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="E501" s="1" t="n">
-        <v>0.03628</v>
+      <c r="F501" s="1" t="n">
+        <v>0.03625</v>
       </c>
     </row>
     <row r="502">
@@ -9966,9 +11472,12 @@
         <v>0.07321</v>
       </c>
       <c r="D502" s="1" t="n">
+        <v>0.07324</v>
+      </c>
+      <c r="E502" s="1" t="n">
         <v>0.07335999999999999</v>
       </c>
-      <c r="E502" s="1" t="n">
+      <c r="F502" s="1" t="n">
         <v>0.07321</v>
       </c>
     </row>
@@ -9985,10 +11494,13 @@
         <v>0.0007531</v>
       </c>
       <c r="D503" s="1" t="n">
+        <v>0.0007499</v>
+      </c>
+      <c r="E503" s="1" t="n">
         <v>0.0007543</v>
       </c>
-      <c r="E503" s="1" t="n">
-        <v>0.0007531</v>
+      <c r="F503" s="1" t="n">
+        <v>0.0007499</v>
       </c>
     </row>
     <row r="504">
@@ -10004,10 +11516,13 @@
         <v>0.015946</v>
       </c>
       <c r="D504" s="1" t="n">
+        <v>0.015945</v>
+      </c>
+      <c r="E504" s="1" t="n">
         <v>0.015956</v>
       </c>
-      <c r="E504" s="1" t="n">
-        <v>0.015946</v>
+      <c r="F504" s="1" t="n">
+        <v>0.015945</v>
       </c>
     </row>
     <row r="505">
@@ -10028,6 +11543,9 @@
       <c r="E505" s="1" t="n">
         <v>0.00709</v>
       </c>
+      <c r="F505" s="1" t="n">
+        <v>0.00709</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -10047,6 +11565,9 @@
       <c r="E506" s="1" t="n">
         <v>0.0257</v>
       </c>
+      <c r="F506" s="1" t="n">
+        <v>0.0257</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -10061,10 +11582,13 @@
         <v>0.001351</v>
       </c>
       <c r="D507" s="1" t="n">
+        <v>0.001343</v>
+      </c>
+      <c r="E507" s="1" t="n">
         <v>0.001351</v>
       </c>
-      <c r="E507" s="1" t="n">
-        <v>0.00135</v>
+      <c r="F507" s="1" t="n">
+        <v>0.001343</v>
       </c>
     </row>
     <row r="508">
@@ -10080,10 +11604,13 @@
         <v>0.2831</v>
       </c>
       <c r="D508" s="1" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="E508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="E508" s="1" t="n">
-        <v>0.2831</v>
+      <c r="F508" s="1" t="n">
+        <v>0.2821</v>
       </c>
     </row>
     <row r="509">
@@ -10099,9 +11626,12 @@
         <v>0.1323</v>
       </c>
       <c r="D509" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="E509" s="1" t="n">
         <v>0.1324</v>
       </c>
-      <c r="E509" s="1" t="n">
+      <c r="F509" s="1" t="n">
         <v>0.1323</v>
       </c>
     </row>
@@ -10118,9 +11648,12 @@
         <v>0.04932</v>
       </c>
       <c r="D510" s="1" t="n">
+        <v>0.04934</v>
+      </c>
+      <c r="E510" s="1" t="n">
         <v>0.04949</v>
       </c>
-      <c r="E510" s="1" t="n">
+      <c r="F510" s="1" t="n">
         <v>0.04932</v>
       </c>
     </row>
@@ -10137,10 +11670,13 @@
         <v>0.00276</v>
       </c>
       <c r="D511" s="1" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="E511" s="1" t="n">
         <v>0.00277</v>
       </c>
-      <c r="E511" s="1" t="n">
-        <v>0.00276</v>
+      <c r="F511" s="1" t="n">
+        <v>0.00275</v>
       </c>
     </row>
     <row r="512">
@@ -10156,10 +11692,13 @@
         <v>0.015402</v>
       </c>
       <c r="D512" s="1" t="n">
+        <v>0.015351</v>
+      </c>
+      <c r="E512" s="1" t="n">
         <v>0.015434</v>
       </c>
-      <c r="E512" s="1" t="n">
-        <v>0.015402</v>
+      <c r="F512" s="1" t="n">
+        <v>0.015351</v>
       </c>
     </row>
     <row r="513">
@@ -10175,10 +11714,13 @@
         <v>0.6948</v>
       </c>
       <c r="D513" s="1" t="n">
+        <v>0.6933</v>
+      </c>
+      <c r="E513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="E513" s="1" t="n">
-        <v>0.6938</v>
+      <c r="F513" s="1" t="n">
+        <v>0.6933</v>
       </c>
     </row>
     <row r="514">
@@ -10194,9 +11736,12 @@
         <v>0.004534</v>
       </c>
       <c r="D514" s="1" t="n">
+        <v>0.004545</v>
+      </c>
+      <c r="E514" s="1" t="n">
         <v>0.004561</v>
       </c>
-      <c r="E514" s="1" t="n">
+      <c r="F514" s="1" t="n">
         <v>0.004534</v>
       </c>
     </row>
@@ -10213,11 +11758,14 @@
         <v>0.005048</v>
       </c>
       <c r="D515" s="1" t="n">
-        <v>0.005048</v>
+        <v>0.005037</v>
       </c>
       <c r="E515" s="1" t="n">
         <v>0.005048</v>
       </c>
+      <c r="F515" s="1" t="n">
+        <v>0.005037</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -10232,10 +11780,13 @@
         <v>0.06372999999999999</v>
       </c>
       <c r="D516" s="1" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="E516" s="1" t="n">
         <v>0.06385</v>
       </c>
-      <c r="E516" s="1" t="n">
-        <v>0.06372999999999999</v>
+      <c r="F516" s="1" t="n">
+        <v>0.06353</v>
       </c>
     </row>
     <row r="517">
@@ -10251,9 +11802,12 @@
         <v>0.06401</v>
       </c>
       <c r="D517" s="1" t="n">
-        <v>0.06401999999999999</v>
+        <v>0.06438000000000001</v>
       </c>
       <c r="E517" s="1" t="n">
+        <v>0.06438000000000001</v>
+      </c>
+      <c r="F517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -10270,10 +11824,13 @@
         <v>0.01214</v>
       </c>
       <c r="D518" s="1" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="E518" s="1" t="n">
         <v>0.01216</v>
       </c>
-      <c r="E518" s="1" t="n">
-        <v>0.01214</v>
+      <c r="F518" s="1" t="n">
+        <v>0.0121</v>
       </c>
     </row>
     <row r="519">
@@ -10289,10 +11846,13 @@
         <v>0.04768</v>
       </c>
       <c r="D519" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="E519" s="1" t="n">
         <v>0.04794</v>
       </c>
-      <c r="E519" s="1" t="n">
-        <v>0.04768</v>
+      <c r="F519" s="1" t="n">
+        <v>0.04743</v>
       </c>
     </row>
     <row r="520">
@@ -10308,10 +11868,13 @@
         <v>0.04394</v>
       </c>
       <c r="D520" s="1" t="n">
+        <v>0.04384</v>
+      </c>
+      <c r="E520" s="1" t="n">
         <v>0.04396</v>
       </c>
-      <c r="E520" s="1" t="n">
-        <v>0.04394</v>
+      <c r="F520" s="1" t="n">
+        <v>0.04384</v>
       </c>
     </row>
     <row r="521">
@@ -10327,10 +11890,13 @@
         <v>0.008560999999999999</v>
       </c>
       <c r="D521" s="1" t="n">
+        <v>0.008552000000000001</v>
+      </c>
+      <c r="E521" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="E521" s="1" t="n">
-        <v>0.008557</v>
+      <c r="F521" s="1" t="n">
+        <v>0.008552000000000001</v>
       </c>
     </row>
     <row r="522">
@@ -10346,10 +11912,13 @@
         <v>0.08969000000000001</v>
       </c>
       <c r="D522" s="1" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="E522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="E522" s="1" t="n">
-        <v>0.08969000000000001</v>
+      <c r="F522" s="1" t="n">
+        <v>0.0893</v>
       </c>
     </row>
     <row r="523">
@@ -10365,9 +11934,12 @@
         <v>0.006466</v>
       </c>
       <c r="D523" s="1" t="n">
+        <v>0.006462</v>
+      </c>
+      <c r="E523" s="1" t="n">
         <v>0.006466</v>
       </c>
-      <c r="E523" s="1" t="n">
+      <c r="F523" s="1" t="n">
         <v>0.00646</v>
       </c>
     </row>
@@ -10384,10 +11956,13 @@
         <v>0.01663</v>
       </c>
       <c r="D524" s="1" t="n">
+        <v>0.01662</v>
+      </c>
+      <c r="E524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="E524" s="1" t="n">
-        <v>0.01663</v>
+      <c r="F524" s="1" t="n">
+        <v>0.01662</v>
       </c>
     </row>
     <row r="525">
@@ -10403,9 +11978,12 @@
         <v>0.01808</v>
       </c>
       <c r="D525" s="1" t="n">
-        <v>0.01808</v>
+        <v>0.0181</v>
       </c>
       <c r="E525" s="1" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="F525" s="1" t="n">
         <v>0.01808</v>
       </c>
     </row>
@@ -10422,9 +12000,12 @@
         <v>0.07917</v>
       </c>
       <c r="D526" s="1" t="n">
+        <v>0.07918</v>
+      </c>
+      <c r="E526" s="1" t="n">
         <v>0.07938000000000001</v>
       </c>
-      <c r="E526" s="1" t="n">
+      <c r="F526" s="1" t="n">
         <v>0.07917</v>
       </c>
     </row>
@@ -10441,10 +12022,13 @@
         <v>0.01641</v>
       </c>
       <c r="D527" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="E527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="E527" s="1" t="n">
-        <v>0.01641</v>
+      <c r="F527" s="1" t="n">
+        <v>0.01634</v>
       </c>
     </row>
     <row r="528">
@@ -10460,10 +12044,13 @@
         <v>0.004183</v>
       </c>
       <c r="D528" s="1" t="n">
+        <v>0.004164</v>
+      </c>
+      <c r="E528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="E528" s="1" t="n">
-        <v>0.004183</v>
+      <c r="F528" s="1" t="n">
+        <v>0.004164</v>
       </c>
     </row>
     <row r="529">
@@ -10479,9 +12066,12 @@
         <v>0.003713</v>
       </c>
       <c r="D529" s="1" t="n">
+        <v>0.003698</v>
+      </c>
+      <c r="E529" s="1" t="n">
         <v>0.003713</v>
       </c>
-      <c r="E529" s="1" t="n">
+      <c r="F529" s="1" t="n">
         <v>0.003698</v>
       </c>
     </row>
@@ -10498,10 +12088,13 @@
         <v>1.328</v>
       </c>
       <c r="D530" s="1" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="E530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="E530" s="1" t="n">
-        <v>1.328</v>
+      <c r="F530" s="1" t="n">
+        <v>1.316</v>
       </c>
     </row>
     <row r="531">
@@ -10517,10 +12110,13 @@
         <v>0.4922</v>
       </c>
       <c r="D531" s="1" t="n">
+        <v>0.4912</v>
+      </c>
+      <c r="E531" s="1" t="n">
         <v>0.4922</v>
       </c>
-      <c r="E531" s="1" t="n">
-        <v>0.4919</v>
+      <c r="F531" s="1" t="n">
+        <v>0.4912</v>
       </c>
     </row>
     <row r="532">
@@ -10536,9 +12132,12 @@
         <v>0.03061</v>
       </c>
       <c r="D532" s="1" t="n">
-        <v>0.03061</v>
+        <v>0.03071</v>
       </c>
       <c r="E532" s="1" t="n">
+        <v>0.03071</v>
+      </c>
+      <c r="F532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -10555,10 +12154,13 @@
         <v>0.1535</v>
       </c>
       <c r="D533" s="1" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="E533" s="1" t="n">
         <v>0.1535</v>
       </c>
-      <c r="E533" s="1" t="n">
-        <v>0.1533</v>
+      <c r="F533" s="1" t="n">
+        <v>0.1532</v>
       </c>
     </row>
     <row r="534">
@@ -10574,10 +12176,13 @@
         <v>0.05404</v>
       </c>
       <c r="D534" s="1" t="n">
+        <v>0.05388</v>
+      </c>
+      <c r="E534" s="1" t="n">
         <v>0.05421</v>
       </c>
-      <c r="E534" s="1" t="n">
-        <v>0.05404</v>
+      <c r="F534" s="1" t="n">
+        <v>0.05388</v>
       </c>
     </row>
     <row r="535">
@@ -10593,10 +12198,13 @@
         <v>0.01507</v>
       </c>
       <c r="D535" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="E535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="E535" s="1" t="n">
-        <v>0.01507</v>
+      <c r="F535" s="1" t="n">
+        <v>0.01501</v>
       </c>
     </row>
     <row r="536">
@@ -10612,9 +12220,12 @@
         <v>0.05833</v>
       </c>
       <c r="D536" s="1" t="n">
-        <v>0.05833</v>
+        <v>0.0585</v>
       </c>
       <c r="E536" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="F536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -10631,10 +12242,13 @@
         <v>0.05508</v>
       </c>
       <c r="D537" s="1" t="n">
+        <v>0.05497</v>
+      </c>
+      <c r="E537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="E537" s="1" t="n">
-        <v>0.05499</v>
+      <c r="F537" s="1" t="n">
+        <v>0.05497</v>
       </c>
     </row>
     <row r="538">
@@ -10650,9 +12264,12 @@
         <v>0.1065</v>
       </c>
       <c r="D538" s="1" t="n">
-        <v>0.1065</v>
+        <v>0.1067</v>
       </c>
       <c r="E538" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="F538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -10669,10 +12286,13 @@
         <v>0.0129</v>
       </c>
       <c r="D539" s="1" t="n">
+        <v>0.01284</v>
+      </c>
+      <c r="E539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="E539" s="1" t="n">
-        <v>0.0129</v>
+      <c r="F539" s="1" t="n">
+        <v>0.01284</v>
       </c>
     </row>
     <row r="540">
@@ -10688,10 +12308,13 @@
         <v>0.1751</v>
       </c>
       <c r="D540" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E540" s="1" t="n">
         <v>0.1753</v>
       </c>
-      <c r="E540" s="1" t="n">
-        <v>0.1751</v>
+      <c r="F540" s="1" t="n">
+        <v>0.175</v>
       </c>
     </row>
     <row r="541">
@@ -10707,9 +12330,12 @@
         <v>0.1235</v>
       </c>
       <c r="D541" s="1" t="n">
-        <v>0.1235</v>
+        <v>0.1236</v>
       </c>
       <c r="E541" s="1" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="F541" s="1" t="n">
         <v>0.1231</v>
       </c>
     </row>
@@ -10726,10 +12352,13 @@
         <v>0.02496</v>
       </c>
       <c r="D542" s="1" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="E542" s="1" t="n">
         <v>0.02509</v>
       </c>
-      <c r="E542" s="1" t="n">
-        <v>0.02496</v>
+      <c r="F542" s="1" t="n">
+        <v>0.02489</v>
       </c>
     </row>
     <row r="543">
@@ -10745,9 +12374,12 @@
         <v>0.05891</v>
       </c>
       <c r="D543" s="1" t="n">
+        <v>0.05861</v>
+      </c>
+      <c r="E543" s="1" t="n">
         <v>0.05891</v>
       </c>
-      <c r="E543" s="1" t="n">
+      <c r="F543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I543"/>
+  <dimension ref="A1:J543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,9 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,10 +469,15 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>price_01:30</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -502,9 +508,12 @@
         <v>72052.5</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>71637.3</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>71323.7</v>
       </c>
     </row>
@@ -533,9 +542,12 @@
         <v>2135.64</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>2119.57</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>2118.6</v>
       </c>
     </row>
@@ -564,9 +576,12 @@
         <v>89.84</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>89.23</v>
       </c>
     </row>
@@ -595,9 +610,12 @@
         <v>3.888</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>3.851</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -626,10 +644,13 @@
         <v>1.4087</v>
       </c>
       <c r="H6" s="1" t="n">
+        <v>1.402</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>1.4035</v>
+      <c r="J6" s="1" t="n">
+        <v>1.402</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +678,13 @@
         <v>0.09744999999999999</v>
       </c>
       <c r="H7" s="1" t="n">
+        <v>0.09683</v>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>0.09744999999999999</v>
+      <c r="J7" s="1" t="n">
+        <v>0.09683</v>
       </c>
     </row>
     <row r="8">
@@ -688,10 +712,13 @@
         <v>0.014219</v>
       </c>
       <c r="H8" s="1" t="n">
+        <v>0.014064</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>0.014158</v>
+      <c r="J8" s="1" t="n">
+        <v>0.014064</v>
       </c>
     </row>
     <row r="9">
@@ -719,9 +746,12 @@
         <v>662.78</v>
       </c>
       <c r="H9" s="1" t="n">
+        <v>660.08</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>659.95</v>
       </c>
     </row>
@@ -750,9 +780,12 @@
         <v>19.312</v>
       </c>
       <c r="H10" s="1" t="n">
+        <v>19.203</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>19.415</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -781,10 +814,13 @@
         <v>0.0034688</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>0.003438</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>0.0034668</v>
+      <c r="J11" s="1" t="n">
+        <v>0.003438</v>
       </c>
     </row>
     <row r="12">
@@ -812,9 +848,12 @@
         <v>36.34</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>36.352</v>
+        <v>36.524</v>
       </c>
       <c r="I12" s="1" t="n">
+        <v>36.524</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -843,9 +882,12 @@
         <v>213.63</v>
       </c>
       <c r="H13" s="1" t="n">
+        <v>213.29</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>212.79</v>
       </c>
     </row>
@@ -874,10 +916,13 @@
         <v>0.0011325</v>
       </c>
       <c r="H14" s="1" t="n">
+        <v>0.0011193</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="I14" s="1" t="n">
-        <v>0.0011277</v>
+      <c r="J14" s="1" t="n">
+        <v>0.0011193</v>
       </c>
     </row>
     <row r="15">
@@ -905,10 +950,13 @@
         <v>0.28505</v>
       </c>
       <c r="H15" s="1" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="I15" s="1" t="n">
-        <v>0.28505</v>
+      <c r="J15" s="1" t="n">
+        <v>0.28497</v>
       </c>
     </row>
     <row r="16">
@@ -936,9 +984,12 @@
         <v>237.1</v>
       </c>
       <c r="H16" s="1" t="n">
+        <v>234.49</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="J16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -967,10 +1018,13 @@
         <v>1.0093</v>
       </c>
       <c r="H17" s="1" t="n">
+        <v>1.0027</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="I17" s="1" t="n">
-        <v>1.0093</v>
+      <c r="J17" s="1" t="n">
+        <v>1.0027</v>
       </c>
     </row>
     <row r="18">
@@ -998,10 +1052,13 @@
         <v>0.2717</v>
       </c>
       <c r="H18" s="1" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="I18" s="1" t="n">
-        <v>0.2713</v>
+      <c r="J18" s="1" t="n">
+        <v>0.2697</v>
       </c>
     </row>
     <row r="19">
@@ -1029,10 +1086,13 @@
         <v>9.891</v>
       </c>
       <c r="H19" s="1" t="n">
+        <v>9.834</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="I19" s="1" t="n">
-        <v>9.859</v>
+      <c r="J19" s="1" t="n">
+        <v>9.834</v>
       </c>
     </row>
     <row r="20">
@@ -1060,9 +1120,12 @@
         <v>5056.54</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>5056.54</v>
+        <v>5059.14</v>
       </c>
       <c r="I20" s="1" t="n">
+        <v>5059.14</v>
+      </c>
+      <c r="J20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1091,9 +1154,12 @@
         <v>464.66</v>
       </c>
       <c r="H21" s="1" t="n">
+        <v>463.47</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="I21" s="1" t="n">
+      <c r="J21" s="1" t="n">
         <v>462.57</v>
       </c>
     </row>
@@ -1122,9 +1188,12 @@
         <v>1.4336</v>
       </c>
       <c r="H22" s="1" t="n">
+        <v>1.4444</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="J22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1153,10 +1222,13 @@
         <v>1.0926</v>
       </c>
       <c r="H23" s="1" t="n">
+        <v>1.0691</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="I23" s="1" t="n">
-        <v>1.0926</v>
+      <c r="J23" s="1" t="n">
+        <v>1.0691</v>
       </c>
     </row>
     <row r="24">
@@ -1184,9 +1256,12 @@
         <v>1.37</v>
       </c>
       <c r="H24" s="1" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="J24" s="1" t="n">
         <v>1.351</v>
       </c>
     </row>
@@ -1215,10 +1290,13 @@
         <v>9.282</v>
       </c>
       <c r="H25" s="1" t="n">
+        <v>9.223000000000001</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="I25" s="1" t="n">
-        <v>9.246</v>
+      <c r="J25" s="1" t="n">
+        <v>9.223000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1246,9 +1324,12 @@
         <v>0.3776</v>
       </c>
       <c r="H26" s="1" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="J26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1277,9 +1358,12 @@
         <v>0.896</v>
       </c>
       <c r="H27" s="1" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="J27" s="1" t="n">
         <v>0.887</v>
       </c>
     </row>
@@ -1308,9 +1392,12 @@
         <v>1.814</v>
       </c>
       <c r="H28" s="1" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>1.823</v>
       </c>
-      <c r="I28" s="1" t="n">
+      <c r="J28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1339,10 +1426,13 @@
         <v>0.112</v>
       </c>
       <c r="H29" s="1" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="I29" s="1" t="n">
-        <v>0.1115</v>
+      <c r="J29" s="1" t="n">
+        <v>0.1111</v>
       </c>
     </row>
     <row r="30">
@@ -1370,10 +1460,13 @@
         <v>0.002065</v>
       </c>
       <c r="H30" s="1" t="n">
+        <v>0.002052</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>0.002054</v>
+      <c r="J30" s="1" t="n">
+        <v>0.002052</v>
       </c>
     </row>
     <row r="31">
@@ -1401,10 +1494,13 @@
         <v>1.504</v>
       </c>
       <c r="H31" s="1" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="I31" s="1" t="n">
-        <v>1.499</v>
+      <c r="J31" s="1" t="n">
+        <v>1.493</v>
       </c>
     </row>
     <row r="32">
@@ -1432,10 +1528,13 @@
         <v>0.1762</v>
       </c>
       <c r="H32" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="I32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="I32" s="1" t="n">
-        <v>0.1762</v>
+      <c r="J32" s="1" t="n">
+        <v>0.175</v>
       </c>
     </row>
     <row r="33">
@@ -1463,9 +1562,12 @@
         <v>0.1058</v>
       </c>
       <c r="H33" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="J33" s="1" t="n">
         <v>0.1045</v>
       </c>
     </row>
@@ -1494,9 +1596,12 @@
         <v>114.6</v>
       </c>
       <c r="H34" s="1" t="n">
+        <v>113.73</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="I34" s="1" t="n">
+      <c r="J34" s="1" t="n">
         <v>113.65</v>
       </c>
     </row>
@@ -1525,10 +1630,13 @@
         <v>6.898</v>
       </c>
       <c r="H35" s="1" t="n">
+        <v>6.766</v>
+      </c>
+      <c r="I35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="I35" s="1" t="n">
-        <v>6.772</v>
+      <c r="J35" s="1" t="n">
+        <v>6.766</v>
       </c>
     </row>
     <row r="36">
@@ -1556,10 +1664,13 @@
         <v>0.017369</v>
       </c>
       <c r="H36" s="1" t="n">
+        <v>0.016866</v>
+      </c>
+      <c r="I36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="I36" s="1" t="n">
-        <v>0.017313</v>
+      <c r="J36" s="1" t="n">
+        <v>0.016866</v>
       </c>
     </row>
     <row r="37">
@@ -1587,10 +1698,13 @@
         <v>0.3676</v>
       </c>
       <c r="H37" s="1" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="I37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="I37" s="1" t="n">
-        <v>0.3656</v>
+      <c r="J37" s="1" t="n">
+        <v>0.3638</v>
       </c>
     </row>
     <row r="38">
@@ -1618,9 +1732,12 @@
         <v>55.79</v>
       </c>
       <c r="H38" s="1" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="I38" s="1" t="n">
+      <c r="J38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1649,9 +1766,12 @@
         <v>0.59815</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>0.59182</v>
+      </c>
+      <c r="I39" s="1" t="n">
         <v>0.59815</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="J39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1680,9 +1800,12 @@
         <v>4.092</v>
       </c>
       <c r="H40" s="1" t="n">
+        <v>4.064</v>
+      </c>
+      <c r="I40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="I40" s="1" t="n">
+      <c r="J40" s="1" t="n">
         <v>4.051</v>
       </c>
     </row>
@@ -1711,9 +1834,12 @@
         <v>0.04979</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.04979</v>
+        <v>0.0499</v>
       </c>
       <c r="I41" s="1" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="J41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -1742,10 +1868,13 @@
         <v>0.7042</v>
       </c>
       <c r="H42" s="1" t="n">
+        <v>0.7014</v>
+      </c>
+      <c r="I42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="I42" s="1" t="n">
-        <v>0.7017</v>
+      <c r="J42" s="1" t="n">
+        <v>0.7014</v>
       </c>
     </row>
     <row r="43">
@@ -1773,9 +1902,12 @@
         <v>0.23597</v>
       </c>
       <c r="H43" s="1" t="n">
+        <v>0.23357</v>
+      </c>
+      <c r="I43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="I43" s="1" t="n">
+      <c r="J43" s="1" t="n">
         <v>0.23323</v>
       </c>
     </row>
@@ -1804,9 +1936,12 @@
         <v>0.35263</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.35392</v>
+        <v>0.35416</v>
       </c>
       <c r="I44" s="1" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="J44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -1835,10 +1970,13 @@
         <v>0.1728</v>
       </c>
       <c r="H45" s="1" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="I45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="I45" s="1" t="n">
-        <v>0.1714</v>
+      <c r="J45" s="1" t="n">
+        <v>0.1713</v>
       </c>
     </row>
     <row r="46">
@@ -1866,10 +2004,13 @@
         <v>0.0265</v>
       </c>
       <c r="H46" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="I46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="I46" s="1" t="n">
-        <v>0.0264</v>
+      <c r="J46" s="1" t="n">
+        <v>0.0262</v>
       </c>
     </row>
     <row r="47">
@@ -1897,10 +2038,13 @@
         <v>0.006026</v>
       </c>
       <c r="H47" s="1" t="n">
+        <v>0.005998</v>
+      </c>
+      <c r="I47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="I47" s="1" t="n">
-        <v>0.006026</v>
+      <c r="J47" s="1" t="n">
+        <v>0.005998</v>
       </c>
     </row>
     <row r="48">
@@ -1928,10 +2072,13 @@
         <v>0.007499</v>
       </c>
       <c r="H48" s="1" t="n">
+        <v>0.007417</v>
+      </c>
+      <c r="I48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="I48" s="1" t="n">
-        <v>0.007479</v>
+      <c r="J48" s="1" t="n">
+        <v>0.007417</v>
       </c>
     </row>
     <row r="49">
@@ -1959,10 +2106,13 @@
         <v>0.111</v>
       </c>
       <c r="H49" s="1" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="I49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="I49" s="1" t="n">
-        <v>0.1105</v>
+      <c r="J49" s="1" t="n">
+        <v>0.1087</v>
       </c>
     </row>
     <row r="50">
@@ -1990,9 +2140,12 @@
         <v>0.04038</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>0.04046</v>
+        <v>0.04048</v>
       </c>
       <c r="I50" s="1" t="n">
+        <v>0.04048</v>
+      </c>
+      <c r="J50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2021,10 +2174,13 @@
         <v>0.1656</v>
       </c>
       <c r="H51" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="I51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="I51" s="1" t="n">
-        <v>0.1655</v>
+      <c r="J51" s="1" t="n">
+        <v>0.1633</v>
       </c>
     </row>
     <row r="52">
@@ -2052,10 +2208,13 @@
         <v>0.00356</v>
       </c>
       <c r="H52" s="1" t="n">
+        <v>0.00353</v>
+      </c>
+      <c r="I52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="I52" s="1" t="n">
-        <v>0.00354</v>
+      <c r="J52" s="1" t="n">
+        <v>0.00353</v>
       </c>
     </row>
     <row r="53">
@@ -2083,10 +2242,13 @@
         <v>2.657</v>
       </c>
       <c r="H53" s="1" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="I53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="I53" s="1" t="n">
-        <v>2.645</v>
+      <c r="J53" s="1" t="n">
+        <v>2.631</v>
       </c>
     </row>
     <row r="54">
@@ -2114,10 +2276,13 @@
         <v>0.006295</v>
       </c>
       <c r="H54" s="1" t="n">
+        <v>0.006242</v>
+      </c>
+      <c r="I54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="I54" s="1" t="n">
-        <v>0.006263</v>
+      <c r="J54" s="1" t="n">
+        <v>0.006242</v>
       </c>
     </row>
     <row r="55">
@@ -2145,10 +2310,13 @@
         <v>0.02882</v>
       </c>
       <c r="H55" s="1" t="n">
+        <v>0.02879</v>
+      </c>
+      <c r="I55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="I55" s="1" t="n">
-        <v>0.02882</v>
+      <c r="J55" s="1" t="n">
+        <v>0.02879</v>
       </c>
     </row>
     <row r="56">
@@ -2176,10 +2344,13 @@
         <v>0.7495000000000001</v>
       </c>
       <c r="H56" s="1" t="n">
+        <v>0.7415</v>
+      </c>
+      <c r="I56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="I56" s="1" t="n">
-        <v>0.7433999999999999</v>
+      <c r="J56" s="1" t="n">
+        <v>0.7415</v>
       </c>
     </row>
     <row r="57">
@@ -2207,9 +2378,12 @@
         <v>0.105</v>
       </c>
       <c r="H57" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="I57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="I57" s="1" t="n">
+      <c r="J57" s="1" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -2238,10 +2412,13 @@
         <v>0.9574</v>
       </c>
       <c r="H58" s="1" t="n">
+        <v>0.9476</v>
+      </c>
+      <c r="I58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="I58" s="1" t="n">
-        <v>0.9505</v>
+      <c r="J58" s="1" t="n">
+        <v>0.9476</v>
       </c>
     </row>
     <row r="59">
@@ -2269,9 +2446,12 @@
         <v>0.08508</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>0.08542</v>
+        <v>0.08704000000000001</v>
       </c>
       <c r="I59" s="1" t="n">
+        <v>0.08704000000000001</v>
+      </c>
+      <c r="J59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -2300,9 +2480,12 @@
         <v>0.06995999999999999</v>
       </c>
       <c r="H60" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I60" s="1" t="n">
         <v>0.07001</v>
       </c>
-      <c r="I60" s="1" t="n">
+      <c r="J60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -2331,9 +2514,12 @@
         <v>0.05502</v>
       </c>
       <c r="H61" s="1" t="n">
+        <v>0.05482</v>
+      </c>
+      <c r="I61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="I61" s="1" t="n">
+      <c r="J61" s="1" t="n">
         <v>0.05469</v>
       </c>
     </row>
@@ -2362,10 +2548,13 @@
         <v>0.009735000000000001</v>
       </c>
       <c r="H62" s="1" t="n">
+        <v>0.009387</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="I62" s="1" t="n">
-        <v>0.009535999999999999</v>
+      <c r="J62" s="1" t="n">
+        <v>0.009387</v>
       </c>
     </row>
     <row r="63">
@@ -2393,9 +2582,12 @@
         <v>0.29028</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>0.29028</v>
+        <v>0.29032</v>
       </c>
       <c r="I63" s="1" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="J63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -2424,9 +2616,12 @@
         <v>0.07378999999999999</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>0.0742</v>
+        <v>0.07489</v>
       </c>
       <c r="I64" s="1" t="n">
+        <v>0.07489</v>
+      </c>
+      <c r="J64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -2455,9 +2650,12 @@
         <v>0.3154</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>0.3154</v>
+        <v>0.3155</v>
       </c>
       <c r="I65" s="1" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="J65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -2486,10 +2684,13 @@
         <v>0.16416</v>
       </c>
       <c r="H66" s="1" t="n">
+        <v>0.16324</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="I66" s="1" t="n">
-        <v>0.16337</v>
+      <c r="J66" s="1" t="n">
+        <v>0.16324</v>
       </c>
     </row>
     <row r="67">
@@ -2517,10 +2718,13 @@
         <v>0.11935</v>
       </c>
       <c r="H67" s="1" t="n">
+        <v>0.11919</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>0.11997</v>
       </c>
-      <c r="I67" s="1" t="n">
-        <v>0.11926</v>
+      <c r="J67" s="1" t="n">
+        <v>0.11919</v>
       </c>
     </row>
     <row r="68">
@@ -2548,10 +2752,13 @@
         <v>0.09715</v>
       </c>
       <c r="H68" s="1" t="n">
+        <v>0.09637999999999999</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="I68" s="1" t="n">
-        <v>0.09666</v>
+      <c r="J68" s="1" t="n">
+        <v>0.09637999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2579,9 +2786,12 @@
         <v>0.1261</v>
       </c>
       <c r="H69" s="1" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="I69" s="1" t="n">
+      <c r="J69" s="1" t="n">
         <v>0.1247</v>
       </c>
     </row>
@@ -2610,9 +2820,12 @@
         <v>8.602</v>
       </c>
       <c r="H70" s="1" t="n">
+        <v>8.564</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="I70" s="1" t="n">
+      <c r="J70" s="1" t="n">
         <v>8.550000000000001</v>
       </c>
     </row>
@@ -2641,10 +2854,13 @@
         <v>0.241</v>
       </c>
       <c r="H71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="I71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="I71" s="1" t="n">
-        <v>0.239</v>
+      <c r="J71" s="1" t="n">
+        <v>0.238</v>
       </c>
     </row>
     <row r="72">
@@ -2672,10 +2888,13 @@
         <v>0.05078</v>
       </c>
       <c r="H72" s="1" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="I72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="I72" s="1" t="n">
-        <v>0.05078</v>
+      <c r="J72" s="1" t="n">
+        <v>0.05056</v>
       </c>
     </row>
     <row r="73">
@@ -2703,9 +2922,12 @@
         <v>0.05101</v>
       </c>
       <c r="H73" s="1" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="I73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="I73" s="1" t="n">
+      <c r="J73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -2734,9 +2956,12 @@
         <v>0.1257</v>
       </c>
       <c r="H74" s="1" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="I74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="I74" s="1" t="n">
+      <c r="J74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -2765,10 +2990,13 @@
         <v>0.04695</v>
       </c>
       <c r="H75" s="1" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="I75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="I75" s="1" t="n">
-        <v>0.04688</v>
+      <c r="J75" s="1" t="n">
+        <v>0.0465</v>
       </c>
     </row>
     <row r="76">
@@ -2796,9 +3024,12 @@
         <v>0.06781</v>
       </c>
       <c r="H76" s="1" t="n">
+        <v>0.06743</v>
+      </c>
+      <c r="I76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="I76" s="1" t="n">
+      <c r="J76" s="1" t="n">
         <v>0.06743</v>
       </c>
     </row>
@@ -2827,9 +3058,12 @@
         <v>0.12753</v>
       </c>
       <c r="H77" s="1" t="n">
+        <v>0.12766</v>
+      </c>
+      <c r="I77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="I77" s="1" t="n">
+      <c r="J77" s="1" t="n">
         <v>0.12685</v>
       </c>
     </row>
@@ -2858,9 +3092,12 @@
         <v>0.1648</v>
       </c>
       <c r="H78" s="1" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="I78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="I78" s="1" t="n">
+      <c r="J78" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -2889,9 +3126,12 @@
         <v>0.0275</v>
       </c>
       <c r="H79" s="1" t="n">
+        <v>0.02738</v>
+      </c>
+      <c r="I79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="I79" s="1" t="n">
+      <c r="J79" s="1" t="n">
         <v>0.0272</v>
       </c>
     </row>
@@ -2920,9 +3160,12 @@
         <v>355.97</v>
       </c>
       <c r="H80" s="1" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="I80" s="1" t="n">
         <v>356.25</v>
       </c>
-      <c r="I80" s="1" t="n">
+      <c r="J80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -2951,10 +3194,13 @@
         <v>7.216e-05</v>
       </c>
       <c r="H81" s="1" t="n">
+        <v>7.142e-05</v>
+      </c>
+      <c r="I81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="I81" s="1" t="n">
-        <v>7.196e-05</v>
+      <c r="J81" s="1" t="n">
+        <v>7.142e-05</v>
       </c>
     </row>
     <row r="82">
@@ -2982,10 +3228,13 @@
         <v>0.2685</v>
       </c>
       <c r="H82" s="1" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="I82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="I82" s="1" t="n">
-        <v>0.2672</v>
+      <c r="J82" s="1" t="n">
+        <v>0.2668</v>
       </c>
     </row>
     <row r="83">
@@ -3013,9 +3262,12 @@
         <v>1.1483</v>
       </c>
       <c r="H83" s="1" t="n">
+        <v>1.1435</v>
+      </c>
+      <c r="I83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="I83" s="1" t="n">
+      <c r="J83" s="1" t="n">
         <v>1.1408</v>
       </c>
     </row>
@@ -3044,9 +3296,12 @@
         <v>0.363</v>
       </c>
       <c r="H84" s="1" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="I84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="I84" s="1" t="n">
+      <c r="J84" s="1" t="n">
         <v>0.3569</v>
       </c>
     </row>
@@ -3075,9 +3330,12 @@
         <v>2.0327</v>
       </c>
       <c r="H85" s="1" t="n">
+        <v>2.0252</v>
+      </c>
+      <c r="I85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="I85" s="1" t="n">
+      <c r="J85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -3106,9 +3364,12 @@
         <v>1.3125</v>
       </c>
       <c r="H86" s="1" t="n">
+        <v>1.3132</v>
+      </c>
+      <c r="I86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="I86" s="1" t="n">
+      <c r="J86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -3137,10 +3398,13 @@
         <v>33.15</v>
       </c>
       <c r="H87" s="1" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="I87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="I87" s="1" t="n">
-        <v>32.97</v>
+      <c r="J87" s="1" t="n">
+        <v>32.88</v>
       </c>
     </row>
     <row r="88">
@@ -3168,10 +3432,13 @@
         <v>0.01037</v>
       </c>
       <c r="H88" s="1" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="I88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="I88" s="1" t="n">
-        <v>0.01037</v>
+      <c r="J88" s="1" t="n">
+        <v>0.01002</v>
       </c>
     </row>
     <row r="89">
@@ -3199,9 +3466,12 @@
         <v>0.01843</v>
       </c>
       <c r="H89" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="I89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="I89" s="1" t="n">
+      <c r="J89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -3230,9 +3500,12 @@
         <v>0.03566</v>
       </c>
       <c r="H90" s="1" t="n">
+        <v>0.03577</v>
+      </c>
+      <c r="I90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="I90" s="1" t="n">
+      <c r="J90" s="1" t="n">
         <v>0.03566</v>
       </c>
     </row>
@@ -3261,10 +3534,13 @@
         <v>0.01196</v>
       </c>
       <c r="H91" s="1" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="I91" s="1" t="n">
         <v>0.01202</v>
       </c>
-      <c r="I91" s="1" t="n">
-        <v>0.01192</v>
+      <c r="J91" s="1" t="n">
+        <v>0.01191</v>
       </c>
     </row>
     <row r="92">
@@ -3292,9 +3568,12 @@
         <v>3.136</v>
       </c>
       <c r="H92" s="1" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="I92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="I92" s="1" t="n">
+      <c r="J92" s="1" t="n">
         <v>3.111</v>
       </c>
     </row>
@@ -3323,9 +3602,12 @@
         <v>0.005654</v>
       </c>
       <c r="H93" s="1" t="n">
+        <v>0.005635</v>
+      </c>
+      <c r="I93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="I93" s="1" t="n">
+      <c r="J93" s="1" t="n">
         <v>0.005635</v>
       </c>
     </row>
@@ -3354,10 +3636,13 @@
         <v>0.0941</v>
       </c>
       <c r="H94" s="1" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="I94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="I94" s="1" t="n">
-        <v>0.094</v>
+      <c r="J94" s="1" t="n">
+        <v>0.0936</v>
       </c>
     </row>
     <row r="95">
@@ -3385,9 +3670,12 @@
         <v>0.6032</v>
       </c>
       <c r="H95" s="1" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="I95" s="1" t="n">
         <v>0.6058</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="J95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -3416,9 +3704,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="H96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="I96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="I96" s="1" t="n">
+      <c r="J96" s="1" t="n">
         <v>1.28e-05</v>
       </c>
     </row>
@@ -3447,9 +3738,12 @@
         <v>1.142</v>
       </c>
       <c r="H97" s="1" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="I97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="I97" s="1" t="n">
+      <c r="J97" s="1" t="n">
         <v>1.136</v>
       </c>
     </row>
@@ -3478,10 +3772,13 @@
         <v>0.25472</v>
       </c>
       <c r="H98" s="1" t="n">
+        <v>0.25366</v>
+      </c>
+      <c r="I98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="I98" s="1" t="n">
-        <v>0.25472</v>
+      <c r="J98" s="1" t="n">
+        <v>0.25366</v>
       </c>
     </row>
     <row r="99">
@@ -3509,9 +3806,12 @@
         <v>1.156</v>
       </c>
       <c r="H99" s="1" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="I99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="I99" s="1" t="n">
+      <c r="J99" s="1" t="n">
         <v>1.146</v>
       </c>
     </row>
@@ -3540,9 +3840,12 @@
         <v>1.87</v>
       </c>
       <c r="H100" s="1" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="I100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="J100" s="1" t="n">
         <v>1.862</v>
       </c>
     </row>
@@ -3571,10 +3874,13 @@
         <v>0.01601</v>
       </c>
       <c r="H101" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="I101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="I101" s="1" t="n">
-        <v>0.01595</v>
+      <c r="J101" s="1" t="n">
+        <v>0.01593</v>
       </c>
     </row>
     <row r="102">
@@ -3602,9 +3908,12 @@
         <v>0.10431</v>
       </c>
       <c r="H102" s="1" t="n">
+        <v>0.10398</v>
+      </c>
+      <c r="I102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="J102" s="1" t="n">
         <v>0.10353</v>
       </c>
     </row>
@@ -3633,10 +3942,13 @@
         <v>0.0006039</v>
       </c>
       <c r="H103" s="1" t="n">
+        <v>0.000602</v>
+      </c>
+      <c r="I103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="I103" s="1" t="n">
-        <v>0.0006039</v>
+      <c r="J103" s="1" t="n">
+        <v>0.000602</v>
       </c>
     </row>
     <row r="104">
@@ -3664,9 +3976,12 @@
         <v>0.0005776000000000001</v>
       </c>
       <c r="H104" s="1" t="n">
+        <v>0.0005743</v>
+      </c>
+      <c r="I104" s="1" t="n">
         <v>0.0005776000000000001</v>
       </c>
-      <c r="I104" s="1" t="n">
+      <c r="J104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -3695,9 +4010,12 @@
         <v>0.003253</v>
       </c>
       <c r="H105" s="1" t="n">
+        <v>0.003239</v>
+      </c>
+      <c r="I105" s="1" t="n">
         <v>0.003257</v>
       </c>
-      <c r="I105" s="1" t="n">
+      <c r="J105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -3726,10 +4044,13 @@
         <v>2.637</v>
       </c>
       <c r="H106" s="1" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="I106" s="1" t="n">
-        <v>2.617</v>
+      <c r="J106" s="1" t="n">
+        <v>2.61</v>
       </c>
     </row>
     <row r="107">
@@ -3757,10 +4078,13 @@
         <v>0.1678</v>
       </c>
       <c r="H107" s="1" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="I107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="I107" s="1" t="n">
-        <v>0.167</v>
+      <c r="J107" s="1" t="n">
+        <v>0.1667</v>
       </c>
     </row>
     <row r="108">
@@ -3788,10 +4112,13 @@
         <v>0.09683</v>
       </c>
       <c r="H108" s="1" t="n">
+        <v>0.09607</v>
+      </c>
+      <c r="I108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="I108" s="1" t="n">
-        <v>0.09683</v>
+      <c r="J108" s="1" t="n">
+        <v>0.09607</v>
       </c>
     </row>
     <row r="109">
@@ -3819,10 +4146,13 @@
         <v>0.0223</v>
       </c>
       <c r="H109" s="1" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="I109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="I109" s="1" t="n">
-        <v>0.02228</v>
+      <c r="J109" s="1" t="n">
+        <v>0.02216</v>
       </c>
     </row>
     <row r="110">
@@ -3850,9 +4180,12 @@
         <v>0.2971</v>
       </c>
       <c r="H110" s="1" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="I110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="I110" s="1" t="n">
+      <c r="J110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -3881,9 +4214,12 @@
         <v>0.05736</v>
       </c>
       <c r="H111" s="1" t="n">
+        <v>0.05729</v>
+      </c>
+      <c r="I111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="I111" s="1" t="n">
+      <c r="J111" s="1" t="n">
         <v>0.05684</v>
       </c>
     </row>
@@ -3912,10 +4248,13 @@
         <v>0.3054</v>
       </c>
       <c r="H112" s="1" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="I112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="I112" s="1" t="n">
-        <v>0.3039</v>
+      <c r="J112" s="1" t="n">
+        <v>0.3026</v>
       </c>
     </row>
     <row r="113">
@@ -3943,9 +4282,12 @@
         <v>18.73</v>
       </c>
       <c r="H113" s="1" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="I113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="I113" s="1" t="n">
+      <c r="J113" s="1" t="n">
         <v>18.62</v>
       </c>
     </row>
@@ -3974,9 +4316,12 @@
         <v>0.13294</v>
       </c>
       <c r="H114" s="1" t="n">
+        <v>0.13302</v>
+      </c>
+      <c r="I114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="I114" s="1" t="n">
+      <c r="J114" s="1" t="n">
         <v>0.13225</v>
       </c>
     </row>
@@ -4005,9 +4350,12 @@
         <v>0.01552</v>
       </c>
       <c r="H115" s="1" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="I115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="I115" s="1" t="n">
+      <c r="J115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -4036,9 +4384,12 @@
         <v>0.08597</v>
       </c>
       <c r="H116" s="1" t="n">
+        <v>0.08529</v>
+      </c>
+      <c r="I116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="I116" s="1" t="n">
+      <c r="J116" s="1" t="n">
         <v>0.08527</v>
       </c>
     </row>
@@ -4067,10 +4418,13 @@
         <v>0.047967</v>
       </c>
       <c r="H117" s="1" t="n">
+        <v>0.047711</v>
+      </c>
+      <c r="I117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="I117" s="1" t="n">
-        <v>0.047967</v>
+      <c r="J117" s="1" t="n">
+        <v>0.047711</v>
       </c>
     </row>
     <row r="118">
@@ -4098,10 +4452,13 @@
         <v>0.04813</v>
       </c>
       <c r="H118" s="1" t="n">
+        <v>0.04771</v>
+      </c>
+      <c r="I118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="I118" s="1" t="n">
-        <v>0.04807</v>
+      <c r="J118" s="1" t="n">
+        <v>0.04771</v>
       </c>
     </row>
     <row r="119">
@@ -4129,9 +4486,12 @@
         <v>0.04216</v>
       </c>
       <c r="H119" s="1" t="n">
+        <v>0.04153</v>
+      </c>
+      <c r="I119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="I119" s="1" t="n">
+      <c r="J119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -4160,9 +4520,12 @@
         <v>0.14562</v>
       </c>
       <c r="H120" s="1" t="n">
+        <v>0.14658</v>
+      </c>
+      <c r="I120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="I120" s="1" t="n">
+      <c r="J120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -4191,9 +4554,12 @@
         <v>0.1287</v>
       </c>
       <c r="H121" s="1" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="I121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="I121" s="1" t="n">
+      <c r="J121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -4222,10 +4588,13 @@
         <v>1.894</v>
       </c>
       <c r="H122" s="1" t="n">
+        <v>1.883</v>
+      </c>
+      <c r="I122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="I122" s="1" t="n">
-        <v>1.887</v>
+      <c r="J122" s="1" t="n">
+        <v>1.883</v>
       </c>
     </row>
     <row r="123">
@@ -4253,10 +4622,13 @@
         <v>0.03049</v>
       </c>
       <c r="H123" s="1" t="n">
+        <v>0.03028</v>
+      </c>
+      <c r="I123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="I123" s="1" t="n">
-        <v>0.03041</v>
+      <c r="J123" s="1" t="n">
+        <v>0.03028</v>
       </c>
     </row>
     <row r="124">
@@ -4284,10 +4656,13 @@
         <v>0.13304</v>
       </c>
       <c r="H124" s="1" t="n">
+        <v>0.13279</v>
+      </c>
+      <c r="I124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="I124" s="1" t="n">
-        <v>0.13288</v>
+      <c r="J124" s="1" t="n">
+        <v>0.13279</v>
       </c>
     </row>
     <row r="125">
@@ -4315,10 +4690,13 @@
         <v>0.04144</v>
       </c>
       <c r="H125" s="1" t="n">
+        <v>0.04121</v>
+      </c>
+      <c r="I125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="I125" s="1" t="n">
-        <v>0.04139</v>
+      <c r="J125" s="1" t="n">
+        <v>0.04121</v>
       </c>
     </row>
     <row r="126">
@@ -4346,9 +4724,12 @@
         <v>0.1165</v>
       </c>
       <c r="H126" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="I126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="I126" s="1" t="n">
+      <c r="J126" s="1" t="n">
         <v>0.1154</v>
       </c>
     </row>
@@ -4377,9 +4758,12 @@
         <v>0.5046</v>
       </c>
       <c r="H127" s="1" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="I127" s="1" t="n">
         <v>0.5046</v>
       </c>
-      <c r="I127" s="1" t="n">
+      <c r="J127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -4408,9 +4792,12 @@
         <v>0.03819</v>
       </c>
       <c r="H128" s="1" t="n">
+        <v>0.03804</v>
+      </c>
+      <c r="I128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="I128" s="1" t="n">
+      <c r="J128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -4439,10 +4826,13 @@
         <v>0.798</v>
       </c>
       <c r="H129" s="1" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="I129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="I129" s="1" t="n">
-        <v>0.796</v>
+      <c r="J129" s="1" t="n">
+        <v>0.795</v>
       </c>
     </row>
     <row r="130">
@@ -4470,10 +4860,13 @@
         <v>0.03447</v>
       </c>
       <c r="H130" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="I130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="I130" s="1" t="n">
-        <v>0.03439</v>
+      <c r="J130" s="1" t="n">
+        <v>0.03422</v>
       </c>
     </row>
     <row r="131">
@@ -4501,9 +4894,12 @@
         <v>0.427</v>
       </c>
       <c r="H131" s="1" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="I131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="I131" s="1" t="n">
+      <c r="J131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4532,9 +4928,12 @@
         <v>0.04381</v>
       </c>
       <c r="H132" s="1" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="I132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="I132" s="1" t="n">
+      <c r="J132" s="1" t="n">
         <v>0.04361</v>
       </c>
     </row>
@@ -4563,9 +4962,12 @@
         <v>1.2987</v>
       </c>
       <c r="H133" s="1" t="n">
+        <v>1.2942</v>
+      </c>
+      <c r="I133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="I133" s="1" t="n">
+      <c r="J133" s="1" t="n">
         <v>1.2941</v>
       </c>
     </row>
@@ -4594,10 +4996,13 @@
         <v>0.02211</v>
       </c>
       <c r="H134" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="I134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="I134" s="1" t="n">
-        <v>0.02208</v>
+      <c r="J134" s="1" t="n">
+        <v>0.02197</v>
       </c>
     </row>
     <row r="135">
@@ -4625,10 +5030,13 @@
         <v>0.0004675</v>
       </c>
       <c r="H135" s="1" t="n">
+        <v>0.0004626</v>
+      </c>
+      <c r="I135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="I135" s="1" t="n">
-        <v>0.0004675</v>
+      <c r="J135" s="1" t="n">
+        <v>0.0004626</v>
       </c>
     </row>
     <row r="136">
@@ -4656,9 +5064,12 @@
         <v>0.001957</v>
       </c>
       <c r="H136" s="1" t="n">
+        <v>0.001915</v>
+      </c>
+      <c r="I136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="I136" s="1" t="n">
+      <c r="J136" s="1" t="n">
         <v>0.001913</v>
       </c>
     </row>
@@ -4687,9 +5098,12 @@
         <v>0.3231</v>
       </c>
       <c r="H137" s="1" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="I137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="I137" s="1" t="n">
+      <c r="J137" s="1" t="n">
         <v>0.3204</v>
       </c>
     </row>
@@ -4718,9 +5132,12 @@
         <v>0.5747</v>
       </c>
       <c r="H138" s="1" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="I138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="I138" s="1" t="n">
+      <c r="J138" s="1" t="n">
         <v>0.5705</v>
       </c>
     </row>
@@ -4749,10 +5166,13 @@
         <v>0.0215</v>
       </c>
       <c r="H139" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="I139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="I139" s="1" t="n">
-        <v>0.02145</v>
+      <c r="J139" s="1" t="n">
+        <v>0.02142</v>
       </c>
     </row>
     <row r="140">
@@ -4780,10 +5200,13 @@
         <v>0.08071</v>
       </c>
       <c r="H140" s="1" t="n">
+        <v>0.08058</v>
+      </c>
+      <c r="I140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="I140" s="1" t="n">
-        <v>0.08071</v>
+      <c r="J140" s="1" t="n">
+        <v>0.08058</v>
       </c>
     </row>
     <row r="141">
@@ -4814,6 +5237,9 @@
         <v>0.001656</v>
       </c>
       <c r="I141" s="1" t="n">
+        <v>0.001656</v>
+      </c>
+      <c r="J141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -4842,9 +5268,12 @@
         <v>0.4276</v>
       </c>
       <c r="H142" s="1" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="I142" s="1" t="n">
         <v>0.4276</v>
       </c>
-      <c r="I142" s="1" t="n">
+      <c r="J142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -4873,9 +5302,12 @@
         <v>0.030021</v>
       </c>
       <c r="H143" s="1" t="n">
+        <v>0.030184</v>
+      </c>
+      <c r="I143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="I143" s="1" t="n">
+      <c r="J143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -4904,9 +5336,12 @@
         <v>0.000225</v>
       </c>
       <c r="H144" s="1" t="n">
+        <v>0.000224</v>
+      </c>
+      <c r="I144" s="1" t="n">
         <v>0.000226</v>
       </c>
-      <c r="I144" s="1" t="n">
+      <c r="J144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -4935,9 +5370,12 @@
         <v>0.03529</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>0.03529</v>
+        <v>0.03675</v>
       </c>
       <c r="I145" s="1" t="n">
+        <v>0.03675</v>
+      </c>
+      <c r="J145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -4966,9 +5404,12 @@
         <v>0.11546</v>
       </c>
       <c r="H146" s="1" t="n">
+        <v>0.11567</v>
+      </c>
+      <c r="I146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="I146" s="1" t="n">
+      <c r="J146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -4997,9 +5438,12 @@
         <v>0.02198</v>
       </c>
       <c r="H147" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="I147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="I147" s="1" t="n">
+      <c r="J147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -5028,9 +5472,12 @@
         <v>1.4234</v>
       </c>
       <c r="H148" s="1" t="n">
+        <v>1.4166</v>
+      </c>
+      <c r="I148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="I148" s="1" t="n">
+      <c r="J148" s="1" t="n">
         <v>1.4154</v>
       </c>
     </row>
@@ -5059,9 +5506,12 @@
         <v>1.8868</v>
       </c>
       <c r="H149" s="1" t="n">
+        <v>1.8738</v>
+      </c>
+      <c r="I149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="I149" s="1" t="n">
+      <c r="J149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -5090,10 +5540,13 @@
         <v>0.1</v>
       </c>
       <c r="H150" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="I150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="I150" s="1" t="n">
-        <v>0.1</v>
+      <c r="J150" s="1" t="n">
+        <v>0.099</v>
       </c>
     </row>
     <row r="151">
@@ -5121,9 +5574,12 @@
         <v>4.593</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>4.609</v>
+        <v>4.623</v>
       </c>
       <c r="I151" s="1" t="n">
+        <v>4.623</v>
+      </c>
+      <c r="J151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -5152,9 +5608,12 @@
         <v>5.587</v>
       </c>
       <c r="H152" s="1" t="n">
+        <v>5.553</v>
+      </c>
+      <c r="I152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="I152" s="1" t="n">
+      <c r="J152" s="1" t="n">
         <v>5.55</v>
       </c>
     </row>
@@ -5183,9 +5642,12 @@
         <v>0.3235</v>
       </c>
       <c r="H153" s="1" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="I153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="I153" s="1" t="n">
+      <c r="J153" s="1" t="n">
         <v>0.3178</v>
       </c>
     </row>
@@ -5214,9 +5676,12 @@
         <v>0.5911999999999999</v>
       </c>
       <c r="H154" s="1" t="n">
+        <v>0.5908</v>
+      </c>
+      <c r="I154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="I154" s="1" t="n">
+      <c r="J154" s="1" t="n">
         <v>0.5891999999999999</v>
       </c>
     </row>
@@ -5245,9 +5710,12 @@
         <v>0.01279</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>0.01279</v>
+        <v>0.01292</v>
       </c>
       <c r="I155" s="1" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="J155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -5276,10 +5744,13 @@
         <v>0.1002</v>
       </c>
       <c r="H156" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="I156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="I156" s="1" t="n">
-        <v>0.0997</v>
+      <c r="J156" s="1" t="n">
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -5307,9 +5778,12 @@
         <v>16.741</v>
       </c>
       <c r="H157" s="1" t="n">
+        <v>16.698</v>
+      </c>
+      <c r="I157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="I157" s="1" t="n">
+      <c r="J157" s="1" t="n">
         <v>16.563</v>
       </c>
     </row>
@@ -5338,9 +5812,12 @@
         <v>0.05615</v>
       </c>
       <c r="H158" s="1" t="n">
+        <v>0.05592</v>
+      </c>
+      <c r="I158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="I158" s="1" t="n">
+      <c r="J158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -5369,9 +5846,12 @@
         <v>29.22</v>
       </c>
       <c r="H159" s="1" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="I159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="I159" s="1" t="n">
+      <c r="J159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -5400,9 +5880,12 @@
         <v>0.02138</v>
       </c>
       <c r="H160" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="I160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="I160" s="1" t="n">
+      <c r="J160" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -5431,10 +5914,13 @@
         <v>0.0006636</v>
       </c>
       <c r="H161" s="1" t="n">
+        <v>0.000659</v>
+      </c>
+      <c r="I161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="I161" s="1" t="n">
-        <v>0.0006601000000000001</v>
+      <c r="J161" s="1" t="n">
+        <v>0.000659</v>
       </c>
     </row>
     <row r="162">
@@ -5462,9 +5948,12 @@
         <v>0.3995</v>
       </c>
       <c r="H162" s="1" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="I162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="I162" s="1" t="n">
+      <c r="J162" s="1" t="n">
         <v>0.3936</v>
       </c>
     </row>
@@ -5493,9 +5982,12 @@
         <v>0.1951</v>
       </c>
       <c r="H163" s="1" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="I163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="I163" s="1" t="n">
+      <c r="J163" s="1" t="n">
         <v>0.1931</v>
       </c>
     </row>
@@ -5524,10 +6016,13 @@
         <v>0.32</v>
       </c>
       <c r="H164" s="1" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="I164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="I164" s="1" t="n">
-        <v>0.32</v>
+      <c r="J164" s="1" t="n">
+        <v>0.319</v>
       </c>
     </row>
     <row r="165">
@@ -5555,9 +6050,12 @@
         <v>0.377</v>
       </c>
       <c r="H165" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="I165" s="1" t="n">
+      <c r="J165" s="1" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -5586,10 +6084,13 @@
         <v>0.02276</v>
       </c>
       <c r="H166" s="1" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="I166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="I166" s="1" t="n">
-        <v>0.02271</v>
+      <c r="J166" s="1" t="n">
+        <v>0.02263</v>
       </c>
     </row>
     <row r="167">
@@ -5617,10 +6118,13 @@
         <v>0.007389</v>
       </c>
       <c r="H167" s="1" t="n">
+        <v>0.007343</v>
+      </c>
+      <c r="I167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="I167" s="1" t="n">
-        <v>0.007348</v>
+      <c r="J167" s="1" t="n">
+        <v>0.007343</v>
       </c>
     </row>
     <row r="168">
@@ -5648,10 +6152,13 @@
         <v>0.01391</v>
       </c>
       <c r="H168" s="1" t="n">
+        <v>0.01372</v>
+      </c>
+      <c r="I168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="I168" s="1" t="n">
-        <v>0.01391</v>
+      <c r="J168" s="1" t="n">
+        <v>0.01372</v>
       </c>
     </row>
     <row r="169">
@@ -5679,9 +6186,12 @@
         <v>0.25715</v>
       </c>
       <c r="H169" s="1" t="n">
+        <v>0.25531</v>
+      </c>
+      <c r="I169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="I169" s="1" t="n">
+      <c r="J169" s="1" t="n">
         <v>0.25376</v>
       </c>
     </row>
@@ -5710,9 +6220,12 @@
         <v>0.02174</v>
       </c>
       <c r="H170" s="1" t="n">
+        <v>0.02169</v>
+      </c>
+      <c r="I170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="I170" s="1" t="n">
+      <c r="J170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -5741,9 +6254,12 @@
         <v>0.177</v>
       </c>
       <c r="H171" s="1" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="I171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="I171" s="1" t="n">
+      <c r="J171" s="1" t="n">
         <v>0.1733</v>
       </c>
     </row>
@@ -5772,9 +6288,12 @@
         <v>0.09</v>
       </c>
       <c r="H172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="I172" s="1" t="n">
+      <c r="J172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -5803,10 +6322,13 @@
         <v>0.004729</v>
       </c>
       <c r="H173" s="1" t="n">
+        <v>0.004706</v>
+      </c>
+      <c r="I173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="I173" s="1" t="n">
-        <v>0.004719</v>
+      <c r="J173" s="1" t="n">
+        <v>0.004706</v>
       </c>
     </row>
     <row r="174">
@@ -5834,9 +6356,12 @@
         <v>0.4423</v>
       </c>
       <c r="H174" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="I174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="I174" s="1" t="n">
+      <c r="J174" s="1" t="n">
         <v>0.4368</v>
       </c>
     </row>
@@ -5865,9 +6390,12 @@
         <v>0.09021999999999999</v>
       </c>
       <c r="H175" s="1" t="n">
+        <v>0.08978</v>
+      </c>
+      <c r="I175" s="1" t="n">
         <v>0.09021999999999999</v>
       </c>
-      <c r="I175" s="1" t="n">
+      <c r="J175" s="1" t="n">
         <v>0.0895</v>
       </c>
     </row>
@@ -5896,9 +6424,12 @@
         <v>0.2475</v>
       </c>
       <c r="H176" s="1" t="n">
+        <v>0.2464</v>
+      </c>
+      <c r="I176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="I176" s="1" t="n">
+      <c r="J176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -5927,9 +6458,12 @@
         <v>0.01931</v>
       </c>
       <c r="H177" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="I177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="I177" s="1" t="n">
+      <c r="J177" s="1" t="n">
         <v>0.01917</v>
       </c>
     </row>
@@ -5958,9 +6492,12 @@
         <v>6.216</v>
       </c>
       <c r="H178" s="1" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="I178" s="1" t="n">
+      <c r="J178" s="1" t="n">
         <v>6.18</v>
       </c>
     </row>
@@ -5989,10 +6526,13 @@
         <v>0.1371</v>
       </c>
       <c r="H179" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="I179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="I179" s="1" t="n">
-        <v>0.1362</v>
+      <c r="J179" s="1" t="n">
+        <v>0.136</v>
       </c>
     </row>
     <row r="180">
@@ -6020,9 +6560,12 @@
         <v>0.005091</v>
       </c>
       <c r="H180" s="1" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="I180" s="1" t="n">
         <v>0.005093</v>
       </c>
-      <c r="I180" s="1" t="n">
+      <c r="J180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -6051,9 +6594,12 @@
         <v>0.01196</v>
       </c>
       <c r="H181" s="1" t="n">
+        <v>0.01194</v>
+      </c>
+      <c r="I181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="I181" s="1" t="n">
+      <c r="J181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -6082,9 +6628,12 @@
         <v>0.007408</v>
       </c>
       <c r="H182" s="1" t="n">
+        <v>0.00733</v>
+      </c>
+      <c r="I182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="I182" s="1" t="n">
+      <c r="J182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -6113,9 +6662,12 @@
         <v>0.13142</v>
       </c>
       <c r="H183" s="1" t="n">
+        <v>0.12988</v>
+      </c>
+      <c r="I183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="I183" s="1" t="n">
+      <c r="J183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -6144,9 +6696,12 @@
         <v>0.09733</v>
       </c>
       <c r="H184" s="1" t="n">
+        <v>0.09682</v>
+      </c>
+      <c r="I184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="I184" s="1" t="n">
+      <c r="J184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -6175,9 +6730,12 @@
         <v>0.00764</v>
       </c>
       <c r="H185" s="1" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="I185" s="1" t="n">
+      <c r="J185" s="1" t="n">
         <v>0.00758</v>
       </c>
     </row>
@@ -6206,10 +6764,13 @@
         <v>0.04928</v>
       </c>
       <c r="H186" s="1" t="n">
+        <v>0.04894</v>
+      </c>
+      <c r="I186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="I186" s="1" t="n">
-        <v>0.04914</v>
+      <c r="J186" s="1" t="n">
+        <v>0.04894</v>
       </c>
     </row>
     <row r="187">
@@ -6237,9 +6798,12 @@
         <v>0.02725</v>
       </c>
       <c r="H187" s="1" t="n">
+        <v>0.02694</v>
+      </c>
+      <c r="I187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="I187" s="1" t="n">
+      <c r="J187" s="1" t="n">
         <v>0.02686</v>
       </c>
     </row>
@@ -6268,10 +6832,13 @@
         <v>0.003351</v>
       </c>
       <c r="H188" s="1" t="n">
+        <v>0.00332</v>
+      </c>
+      <c r="I188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="I188" s="1" t="n">
-        <v>0.003323</v>
+      <c r="J188" s="1" t="n">
+        <v>0.00332</v>
       </c>
     </row>
     <row r="189">
@@ -6299,10 +6866,13 @@
         <v>0.2893</v>
       </c>
       <c r="H189" s="1" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="I189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="I189" s="1" t="n">
-        <v>0.2875</v>
+      <c r="J189" s="1" t="n">
+        <v>0.2869</v>
       </c>
     </row>
     <row r="190">
@@ -6330,10 +6900,13 @@
         <v>0.01833</v>
       </c>
       <c r="H190" s="1" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="I190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="I190" s="1" t="n">
-        <v>0.01819</v>
+      <c r="J190" s="1" t="n">
+        <v>0.01817</v>
       </c>
     </row>
     <row r="191">
@@ -6361,10 +6934,13 @@
         <v>0.2604</v>
       </c>
       <c r="H191" s="1" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="I191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="I191" s="1" t="n">
-        <v>0.2604</v>
+      <c r="J191" s="1" t="n">
+        <v>0.259</v>
       </c>
     </row>
     <row r="192">
@@ -6392,10 +6968,13 @@
         <v>0.03969</v>
       </c>
       <c r="H192" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="I192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="I192" s="1" t="n">
-        <v>0.03914</v>
+      <c r="J192" s="1" t="n">
+        <v>0.0387</v>
       </c>
     </row>
     <row r="193">
@@ -6423,9 +7002,12 @@
         <v>0.0002232</v>
       </c>
       <c r="H193" s="1" t="n">
-        <v>0.0002232</v>
+        <v>0.0002234</v>
       </c>
       <c r="I193" s="1" t="n">
+        <v>0.0002234</v>
+      </c>
+      <c r="J193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -6454,10 +7036,13 @@
         <v>4.17</v>
       </c>
       <c r="H194" s="1" t="n">
+        <v>4.144</v>
+      </c>
+      <c r="I194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="I194" s="1" t="n">
-        <v>4.154</v>
+      <c r="J194" s="1" t="n">
+        <v>4.144</v>
       </c>
     </row>
     <row r="195">
@@ -6485,9 +7070,12 @@
         <v>0.999341</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>0.999341</v>
+        <v>0.999401</v>
       </c>
       <c r="I195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="J195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -6516,10 +7104,13 @@
         <v>4.327</v>
       </c>
       <c r="H196" s="1" t="n">
+        <v>4.298</v>
+      </c>
+      <c r="I196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="I196" s="1" t="n">
-        <v>4.302</v>
+      <c r="J196" s="1" t="n">
+        <v>4.298</v>
       </c>
     </row>
     <row r="197">
@@ -6547,9 +7138,12 @@
         <v>0.15105</v>
       </c>
       <c r="H197" s="1" t="n">
-        <v>0.15105</v>
+        <v>0.15118</v>
       </c>
       <c r="I197" s="1" t="n">
+        <v>0.15118</v>
+      </c>
+      <c r="J197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -6578,9 +7172,12 @@
         <v>0.0077</v>
       </c>
       <c r="H198" s="1" t="n">
+        <v>0.007648</v>
+      </c>
+      <c r="I198" s="1" t="n">
         <v>0.0077</v>
       </c>
-      <c r="I198" s="1" t="n">
+      <c r="J198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -6609,9 +7206,12 @@
         <v>0.4533</v>
       </c>
       <c r="H199" s="1" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="I199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="I199" s="1" t="n">
+      <c r="J199" s="1" t="n">
         <v>0.4483</v>
       </c>
     </row>
@@ -6640,9 +7240,12 @@
         <v>0.5857</v>
       </c>
       <c r="H200" s="1" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="I200" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="I200" s="1" t="n">
+      <c r="J200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -6671,10 +7274,13 @@
         <v>0.0941</v>
       </c>
       <c r="H201" s="1" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="I201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="I201" s="1" t="n">
-        <v>0.09379999999999999</v>
+      <c r="J201" s="1" t="n">
+        <v>0.0936</v>
       </c>
     </row>
     <row r="202">
@@ -6702,9 +7308,12 @@
         <v>0.06103</v>
       </c>
       <c r="H202" s="1" t="n">
+        <v>0.06086</v>
+      </c>
+      <c r="I202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="I202" s="1" t="n">
+      <c r="J202" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -6733,10 +7342,13 @@
         <v>0.00821</v>
       </c>
       <c r="H203" s="1" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="I203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="I203" s="1" t="n">
-        <v>0.00821</v>
+      <c r="J203" s="1" t="n">
+        <v>0.00804</v>
       </c>
     </row>
     <row r="204">
@@ -6764,10 +7376,13 @@
         <v>0.00421</v>
       </c>
       <c r="H204" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="I204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="I204" s="1" t="n">
-        <v>0.00421</v>
+      <c r="J204" s="1" t="n">
+        <v>0.0042</v>
       </c>
     </row>
     <row r="205">
@@ -6795,9 +7410,12 @@
         <v>0.009284000000000001</v>
       </c>
       <c r="H205" s="1" t="n">
+        <v>0.009169</v>
+      </c>
+      <c r="I205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="I205" s="1" t="n">
+      <c r="J205" s="1" t="n">
         <v>0.009154000000000001</v>
       </c>
     </row>
@@ -6826,9 +7444,12 @@
         <v>0.2384</v>
       </c>
       <c r="H206" s="1" t="n">
-        <v>0.2399</v>
+        <v>0.2413</v>
       </c>
       <c r="I206" s="1" t="n">
+        <v>0.2413</v>
+      </c>
+      <c r="J206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -6857,10 +7478,13 @@
         <v>0.02112</v>
       </c>
       <c r="H207" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="I207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="I207" s="1" t="n">
-        <v>0.02112</v>
+      <c r="J207" s="1" t="n">
+        <v>0.02111</v>
       </c>
     </row>
     <row r="208">
@@ -6888,9 +7512,12 @@
         <v>0.2387</v>
       </c>
       <c r="H208" s="1" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="I208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="I208" s="1" t="n">
+      <c r="J208" s="1" t="n">
         <v>0.2366</v>
       </c>
     </row>
@@ -6919,10 +7546,13 @@
         <v>0.3622</v>
       </c>
       <c r="H209" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="I209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="I209" s="1" t="n">
-        <v>0.3613</v>
+      <c r="J209" s="1" t="n">
+        <v>0.3601</v>
       </c>
     </row>
     <row r="210">
@@ -6950,10 +7580,13 @@
         <v>0.04308</v>
       </c>
       <c r="H210" s="1" t="n">
+        <v>0.04259</v>
+      </c>
+      <c r="I210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="I210" s="1" t="n">
-        <v>0.04286</v>
+      <c r="J210" s="1" t="n">
+        <v>0.04259</v>
       </c>
     </row>
     <row r="211">
@@ -6981,9 +7614,12 @@
         <v>0.0004329</v>
       </c>
       <c r="H211" s="1" t="n">
+        <v>0.0004289</v>
+      </c>
+      <c r="I211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="I211" s="1" t="n">
+      <c r="J211" s="1" t="n">
         <v>0.0004282</v>
       </c>
     </row>
@@ -7012,9 +7648,12 @@
         <v>0.02179</v>
       </c>
       <c r="H212" s="1" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="I212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="I212" s="1" t="n">
+      <c r="J212" s="1" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -7043,10 +7682,13 @@
         <v>0.1154</v>
       </c>
       <c r="H213" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="I213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="I213" s="1" t="n">
-        <v>0.1151</v>
+      <c r="J213" s="1" t="n">
+        <v>0.1149</v>
       </c>
     </row>
     <row r="214">
@@ -7074,9 +7716,12 @@
         <v>0.04202</v>
       </c>
       <c r="H214" s="1" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="I214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="I214" s="1" t="n">
+      <c r="J214" s="1" t="n">
         <v>0.04188</v>
       </c>
     </row>
@@ -7105,9 +7750,12 @@
         <v>0.010043</v>
       </c>
       <c r="H215" s="1" t="n">
+        <v>0.010036</v>
+      </c>
+      <c r="I215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="I215" s="1" t="n">
+      <c r="J215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -7136,9 +7784,12 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="H216" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="I216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="I216" s="1" t="n">
+      <c r="J216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -7167,9 +7818,12 @@
         <v>0.004231</v>
       </c>
       <c r="H217" s="1" t="n">
+        <v>0.004209</v>
+      </c>
+      <c r="I217" s="1" t="n">
         <v>0.004231</v>
       </c>
-      <c r="I217" s="1" t="n">
+      <c r="J217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -7198,10 +7852,13 @@
         <v>0.01024</v>
       </c>
       <c r="H218" s="1" t="n">
+        <v>0.009820000000000001</v>
+      </c>
+      <c r="I218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="I218" s="1" t="n">
-        <v>0.01024</v>
+      <c r="J218" s="1" t="n">
+        <v>0.009820000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -7229,9 +7886,12 @@
         <v>0.02958</v>
       </c>
       <c r="H219" s="1" t="n">
+        <v>0.02983</v>
+      </c>
+      <c r="I219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="I219" s="1" t="n">
+      <c r="J219" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -7260,10 +7920,13 @@
         <v>2.312</v>
       </c>
       <c r="H220" s="1" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="I220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="I220" s="1" t="n">
-        <v>2.296</v>
+      <c r="J220" s="1" t="n">
+        <v>2.295</v>
       </c>
     </row>
     <row r="221">
@@ -7291,10 +7954,13 @@
         <v>0.023038</v>
       </c>
       <c r="H221" s="1" t="n">
+        <v>0.022908</v>
+      </c>
+      <c r="I221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="I221" s="1" t="n">
-        <v>0.023027</v>
+      <c r="J221" s="1" t="n">
+        <v>0.022908</v>
       </c>
     </row>
     <row r="222">
@@ -7322,10 +7988,13 @@
         <v>0.0372</v>
       </c>
       <c r="H222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="I222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="I222" s="1" t="n">
-        <v>0.037</v>
+      <c r="J222" s="1" t="n">
+        <v>0.0369</v>
       </c>
     </row>
     <row r="223">
@@ -7353,10 +8022,13 @@
         <v>0.2945</v>
       </c>
       <c r="H223" s="1" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="I223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="I223" s="1" t="n">
-        <v>0.294</v>
+      <c r="J223" s="1" t="n">
+        <v>0.2938</v>
       </c>
     </row>
     <row r="224">
@@ -7384,9 +8056,12 @@
         <v>0.01582</v>
       </c>
       <c r="H224" s="1" t="n">
+        <v>0.01564</v>
+      </c>
+      <c r="I224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="I224" s="1" t="n">
+      <c r="J224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -7415,10 +8090,13 @@
         <v>0.0004136</v>
       </c>
       <c r="H225" s="1" t="n">
+        <v>0.0004105</v>
+      </c>
+      <c r="I225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="I225" s="1" t="n">
-        <v>0.0004112</v>
+      <c r="J225" s="1" t="n">
+        <v>0.0004105</v>
       </c>
     </row>
     <row r="226">
@@ -7446,9 +8124,12 @@
         <v>0.08815000000000001</v>
       </c>
       <c r="H226" s="1" t="n">
+        <v>0.08735999999999999</v>
+      </c>
+      <c r="I226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="I226" s="1" t="n">
+      <c r="J226" s="1" t="n">
         <v>0.08731999999999999</v>
       </c>
     </row>
@@ -7477,9 +8158,12 @@
         <v>0.959</v>
       </c>
       <c r="H227" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="I227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="I227" s="1" t="n">
+      <c r="J227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -7508,9 +8192,12 @@
         <v>0.05622</v>
       </c>
       <c r="H228" s="1" t="n">
+        <v>0.05603</v>
+      </c>
+      <c r="I228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="I228" s="1" t="n">
+      <c r="J228" s="1" t="n">
         <v>0.0558</v>
       </c>
     </row>
@@ -7539,9 +8226,12 @@
         <v>0.002032</v>
       </c>
       <c r="H229" s="1" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="I229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="I229" s="1" t="n">
+      <c r="J229" s="1" t="n">
         <v>0.002017</v>
       </c>
     </row>
@@ -7570,9 +8260,12 @@
         <v>0.022893</v>
       </c>
       <c r="H230" s="1" t="n">
-        <v>0.022893</v>
+        <v>0.022963</v>
       </c>
       <c r="I230" s="1" t="n">
+        <v>0.022963</v>
+      </c>
+      <c r="J230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -7601,10 +8294,13 @@
         <v>0.05442</v>
       </c>
       <c r="H231" s="1" t="n">
+        <v>0.05407</v>
+      </c>
+      <c r="I231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="I231" s="1" t="n">
-        <v>0.05442</v>
+      <c r="J231" s="1" t="n">
+        <v>0.05407</v>
       </c>
     </row>
     <row r="232">
@@ -7632,9 +8328,12 @@
         <v>0.0596</v>
       </c>
       <c r="H232" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="I232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="I232" s="1" t="n">
+      <c r="J232" s="1" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -7663,9 +8362,12 @@
         <v>0.001698</v>
       </c>
       <c r="H233" s="1" t="n">
+        <v>0.001688</v>
+      </c>
+      <c r="I233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="I233" s="1" t="n">
+      <c r="J233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -7694,9 +8396,12 @@
         <v>0.005854</v>
       </c>
       <c r="H234" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="I234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="I234" s="1" t="n">
+      <c r="J234" s="1" t="n">
         <v>0.005784</v>
       </c>
     </row>
@@ -7725,9 +8430,12 @@
         <v>0.12578</v>
       </c>
       <c r="H235" s="1" t="n">
+        <v>0.12575</v>
+      </c>
+      <c r="I235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="I235" s="1" t="n">
+      <c r="J235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -7756,10 +8464,13 @@
         <v>65.15000000000001</v>
       </c>
       <c r="H236" s="1" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="I236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="I236" s="1" t="n">
-        <v>64.78</v>
+      <c r="J236" s="1" t="n">
+        <v>64.73999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -7787,9 +8498,12 @@
         <v>0.1028</v>
       </c>
       <c r="H237" s="1" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="I237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="I237" s="1" t="n">
+      <c r="J237" s="1" t="n">
         <v>0.1021</v>
       </c>
     </row>
@@ -7818,9 +8532,12 @@
         <v>0.003993</v>
       </c>
       <c r="H238" s="1" t="n">
+        <v>0.003969</v>
+      </c>
+      <c r="I238" s="1" t="n">
         <v>0.003993</v>
       </c>
-      <c r="I238" s="1" t="n">
+      <c r="J238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -7849,9 +8566,12 @@
         <v>0.01562</v>
       </c>
       <c r="H239" s="1" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="I239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="I239" s="1" t="n">
+      <c r="J239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -7880,9 +8600,12 @@
         <v>0.0568</v>
       </c>
       <c r="H240" s="1" t="n">
+        <v>0.05635</v>
+      </c>
+      <c r="I240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="I240" s="1" t="n">
+      <c r="J240" s="1" t="n">
         <v>0.05621</v>
       </c>
     </row>
@@ -7911,9 +8634,12 @@
         <v>0.0114</v>
       </c>
       <c r="H241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="I241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="I241" s="1" t="n">
+      <c r="J241" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -7942,9 +8668,12 @@
         <v>0.3388</v>
       </c>
       <c r="H242" s="1" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="I242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="I242" s="1" t="n">
+      <c r="J242" s="1" t="n">
         <v>0.336</v>
       </c>
     </row>
@@ -7973,10 +8702,13 @@
         <v>0.01242</v>
       </c>
       <c r="H243" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="I243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="I243" s="1" t="n">
-        <v>0.01241</v>
+      <c r="J243" s="1" t="n">
+        <v>0.01235</v>
       </c>
     </row>
     <row r="244">
@@ -8004,9 +8736,12 @@
         <v>0.08067000000000001</v>
       </c>
       <c r="H244" s="1" t="n">
+        <v>0.08041</v>
+      </c>
+      <c r="I244" s="1" t="n">
         <v>0.08067000000000001</v>
       </c>
-      <c r="I244" s="1" t="n">
+      <c r="J244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -8035,10 +8770,13 @@
         <v>0.007969</v>
       </c>
       <c r="H245" s="1" t="n">
+        <v>0.007848000000000001</v>
+      </c>
+      <c r="I245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="I245" s="1" t="n">
-        <v>0.007967999999999999</v>
+      <c r="J245" s="1" t="n">
+        <v>0.007848000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -8066,10 +8804,13 @@
         <v>0.03067</v>
       </c>
       <c r="H246" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="I246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="I246" s="1" t="n">
-        <v>0.03056</v>
+      <c r="J246" s="1" t="n">
+        <v>0.0305</v>
       </c>
     </row>
     <row r="247">
@@ -8097,9 +8838,12 @@
         <v>0.1827</v>
       </c>
       <c r="H247" s="1" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="I247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="I247" s="1" t="n">
+      <c r="J247" s="1" t="n">
         <v>0.1808</v>
       </c>
     </row>
@@ -8128,10 +8872,13 @@
         <v>0.0594</v>
       </c>
       <c r="H248" s="1" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="I248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="I248" s="1" t="n">
-        <v>0.05915</v>
+      <c r="J248" s="1" t="n">
+        <v>0.0591</v>
       </c>
     </row>
     <row r="249">
@@ -8159,9 +8906,12 @@
         <v>0.1684</v>
       </c>
       <c r="H249" s="1" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="I249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="I249" s="1" t="n">
+      <c r="J249" s="1" t="n">
         <v>0.1664</v>
       </c>
     </row>
@@ -8190,10 +8940,13 @@
         <v>0.01945</v>
       </c>
       <c r="H250" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="I250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="I250" s="1" t="n">
-        <v>0.01938</v>
+      <c r="J250" s="1" t="n">
+        <v>0.01931</v>
       </c>
     </row>
     <row r="251">
@@ -8221,9 +8974,12 @@
         <v>0.02304</v>
       </c>
       <c r="H251" s="1" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="I251" s="1" t="n">
         <v>0.02318</v>
       </c>
-      <c r="I251" s="1" t="n">
+      <c r="J251" s="1" t="n">
         <v>0.02304</v>
       </c>
     </row>
@@ -8252,9 +9008,12 @@
         <v>0.31227</v>
       </c>
       <c r="H252" s="1" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="I252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="I252" s="1" t="n">
+      <c r="J252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -8283,10 +9042,13 @@
         <v>0.006083</v>
       </c>
       <c r="H253" s="1" t="n">
+        <v>0.006037</v>
+      </c>
+      <c r="I253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="I253" s="1" t="n">
-        <v>0.006063</v>
+      <c r="J253" s="1" t="n">
+        <v>0.006037</v>
       </c>
     </row>
     <row r="254">
@@ -8314,9 +9076,12 @@
         <v>0.6186</v>
       </c>
       <c r="H254" s="1" t="n">
+        <v>0.6142</v>
+      </c>
+      <c r="I254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="I254" s="1" t="n">
+      <c r="J254" s="1" t="n">
         <v>0.6141</v>
       </c>
     </row>
@@ -8345,9 +9110,12 @@
         <v>0.10751</v>
       </c>
       <c r="H255" s="1" t="n">
+        <v>0.10727</v>
+      </c>
+      <c r="I255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="I255" s="1" t="n">
+      <c r="J255" s="1" t="n">
         <v>0.10726</v>
       </c>
     </row>
@@ -8376,9 +9144,12 @@
         <v>0.091</v>
       </c>
       <c r="H256" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="I256" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="I256" s="1" t="n">
+      <c r="J256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -8407,9 +9178,12 @@
         <v>0.01451</v>
       </c>
       <c r="H257" s="1" t="n">
+        <v>0.01433</v>
+      </c>
+      <c r="I257" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="I257" s="1" t="n">
+      <c r="J257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -8438,9 +9212,12 @@
         <v>0.05131</v>
       </c>
       <c r="H258" s="1" t="n">
+        <v>0.05137</v>
+      </c>
+      <c r="I258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="I258" s="1" t="n">
+      <c r="J258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -8469,9 +9246,12 @@
         <v>0.008279999999999999</v>
       </c>
       <c r="H259" s="1" t="n">
+        <v>0.008240000000000001</v>
+      </c>
+      <c r="I259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="I259" s="1" t="n">
+      <c r="J259" s="1" t="n">
         <v>0.008240000000000001</v>
       </c>
     </row>
@@ -8500,9 +9280,12 @@
         <v>0.1914</v>
       </c>
       <c r="H260" s="1" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="I260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="I260" s="1" t="n">
+      <c r="J260" s="1" t="n">
         <v>0.1902</v>
       </c>
     </row>
@@ -8531,9 +9314,12 @@
         <v>0.0992</v>
       </c>
       <c r="H261" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="I261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="I261" s="1" t="n">
+      <c r="J261" s="1" t="n">
         <v>0.09859999999999999</v>
       </c>
     </row>
@@ -8562,10 +9348,13 @@
         <v>0.2142</v>
       </c>
       <c r="H262" s="1" t="n">
+        <v>0.2127</v>
+      </c>
+      <c r="I262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="I262" s="1" t="n">
-        <v>0.2128</v>
+      <c r="J262" s="1" t="n">
+        <v>0.2127</v>
       </c>
     </row>
     <row r="263">
@@ -8593,9 +9382,12 @@
         <v>0.008522999999999999</v>
       </c>
       <c r="H263" s="1" t="n">
+        <v>0.008495000000000001</v>
+      </c>
+      <c r="I263" s="1" t="n">
         <v>0.008522999999999999</v>
       </c>
-      <c r="I263" s="1" t="n">
+      <c r="J263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -8624,10 +9416,13 @@
         <v>2.659</v>
       </c>
       <c r="H264" s="1" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="I264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="I264" s="1" t="n">
-        <v>2.647</v>
+      <c r="J264" s="1" t="n">
+        <v>2.645</v>
       </c>
     </row>
     <row r="265">
@@ -8655,9 +9450,12 @@
         <v>0.01878</v>
       </c>
       <c r="H265" s="1" t="n">
+        <v>0.01871</v>
+      </c>
+      <c r="I265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="I265" s="1" t="n">
+      <c r="J265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -8686,9 +9484,12 @@
         <v>0.3595</v>
       </c>
       <c r="H266" s="1" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="I266" s="1" t="n">
         <v>0.3604</v>
       </c>
-      <c r="I266" s="1" t="n">
+      <c r="J266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -8717,9 +9518,12 @@
         <v>0.0346</v>
       </c>
       <c r="H267" s="1" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="I267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="I267" s="1" t="n">
+      <c r="J267" s="1" t="n">
         <v>0.03429</v>
       </c>
     </row>
@@ -8748,10 +9552,13 @@
         <v>0.12</v>
       </c>
       <c r="H268" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="I268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="I268" s="1" t="n">
-        <v>0.119</v>
+      <c r="J268" s="1" t="n">
+        <v>0.118</v>
       </c>
     </row>
     <row r="269">
@@ -8779,10 +9586,13 @@
         <v>0.08091</v>
       </c>
       <c r="H269" s="1" t="n">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="I269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="I269" s="1" t="n">
-        <v>0.08053</v>
+      <c r="J269" s="1" t="n">
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -8810,10 +9620,13 @@
         <v>0.01397</v>
       </c>
       <c r="H270" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="I270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="I270" s="1" t="n">
-        <v>0.01397</v>
+      <c r="J270" s="1" t="n">
+        <v>0.01388</v>
       </c>
     </row>
     <row r="271">
@@ -8841,10 +9654,13 @@
         <v>0.007685</v>
       </c>
       <c r="H271" s="1" t="n">
+        <v>0.007625</v>
+      </c>
+      <c r="I271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="I271" s="1" t="n">
-        <v>0.007654</v>
+      <c r="J271" s="1" t="n">
+        <v>0.007625</v>
       </c>
     </row>
     <row r="272">
@@ -8872,9 +9688,12 @@
         <v>0.07428</v>
       </c>
       <c r="H272" s="1" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="I272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="I272" s="1" t="n">
+      <c r="J272" s="1" t="n">
         <v>0.07414</v>
       </c>
     </row>
@@ -8906,6 +9725,9 @@
         <v>3.16e-05</v>
       </c>
       <c r="I273" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="J273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -8934,10 +9756,13 @@
         <v>0.005553</v>
       </c>
       <c r="H274" s="1" t="n">
+        <v>0.005484</v>
+      </c>
+      <c r="I274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="I274" s="1" t="n">
-        <v>0.005553</v>
+      <c r="J274" s="1" t="n">
+        <v>0.005484</v>
       </c>
     </row>
     <row r="275">
@@ -8965,9 +9790,12 @@
         <v>0.1821</v>
       </c>
       <c r="H275" s="1" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="I275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="I275" s="1" t="n">
+      <c r="J275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -8996,9 +9824,12 @@
         <v>0.006922</v>
       </c>
       <c r="H276" s="1" t="n">
+        <v>0.006891</v>
+      </c>
+      <c r="I276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="I276" s="1" t="n">
+      <c r="J276" s="1" t="n">
         <v>0.006876</v>
       </c>
     </row>
@@ -9027,10 +9858,13 @@
         <v>0.132</v>
       </c>
       <c r="H277" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="I277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="I277" s="1" t="n">
-        <v>0.1316</v>
+      <c r="J277" s="1" t="n">
+        <v>0.1309</v>
       </c>
     </row>
     <row r="278">
@@ -9058,10 +9892,13 @@
         <v>0.02344</v>
       </c>
       <c r="H278" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="I278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="I278" s="1" t="n">
-        <v>0.02335</v>
+      <c r="J278" s="1" t="n">
+        <v>0.02323</v>
       </c>
     </row>
     <row r="279">
@@ -9089,10 +9926,13 @@
         <v>0.01827</v>
       </c>
       <c r="H279" s="1" t="n">
+        <v>0.01815</v>
+      </c>
+      <c r="I279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="I279" s="1" t="n">
-        <v>0.01817</v>
+      <c r="J279" s="1" t="n">
+        <v>0.01815</v>
       </c>
     </row>
     <row r="280">
@@ -9120,9 +9960,12 @@
         <v>0.03783</v>
       </c>
       <c r="H280" s="1" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="I280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="I280" s="1" t="n">
+      <c r="J280" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -9151,10 +9994,13 @@
         <v>0.04005</v>
       </c>
       <c r="H281" s="1" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="I281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="I281" s="1" t="n">
-        <v>0.03981</v>
+      <c r="J281" s="1" t="n">
+        <v>0.03979</v>
       </c>
     </row>
     <row r="282">
@@ -9182,10 +10028,13 @@
         <v>0.3048</v>
       </c>
       <c r="H282" s="1" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="I282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="I282" s="1" t="n">
-        <v>0.3025</v>
+      <c r="J282" s="1" t="n">
+        <v>0.3021</v>
       </c>
     </row>
     <row r="283">
@@ -9213,9 +10062,12 @@
         <v>0.0113</v>
       </c>
       <c r="H283" s="1" t="n">
+        <v>0.01124</v>
+      </c>
+      <c r="I283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="I283" s="1" t="n">
+      <c r="J283" s="1" t="n">
         <v>0.01124</v>
       </c>
     </row>
@@ -9244,9 +10096,12 @@
         <v>9.7e-06</v>
       </c>
       <c r="H284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="I284" s="1" t="n">
         <v>9.7e-06</v>
       </c>
-      <c r="I284" s="1" t="n">
+      <c r="J284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -9275,10 +10130,13 @@
         <v>0.1157</v>
       </c>
       <c r="H285" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="I285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="I285" s="1" t="n">
-        <v>0.1153</v>
+      <c r="J285" s="1" t="n">
+        <v>0.1151</v>
       </c>
     </row>
     <row r="286">
@@ -9306,9 +10164,12 @@
         <v>0.003485</v>
       </c>
       <c r="H286" s="1" t="n">
+        <v>0.00348</v>
+      </c>
+      <c r="I286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="I286" s="1" t="n">
+      <c r="J286" s="1" t="n">
         <v>0.003442</v>
       </c>
     </row>
@@ -9337,10 +10198,13 @@
         <v>0.08570999999999999</v>
       </c>
       <c r="H287" s="1" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="I287" s="1" t="n">
         <v>0.08573</v>
       </c>
-      <c r="I287" s="1" t="n">
-        <v>0.08545999999999999</v>
+      <c r="J287" s="1" t="n">
+        <v>0.08522</v>
       </c>
     </row>
     <row r="288">
@@ -9368,9 +10232,12 @@
         <v>0.09926</v>
       </c>
       <c r="H288" s="1" t="n">
+        <v>0.09921000000000001</v>
+      </c>
+      <c r="I288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="I288" s="1" t="n">
+      <c r="J288" s="1" t="n">
         <v>0.09889000000000001</v>
       </c>
     </row>
@@ -9399,9 +10266,12 @@
         <v>0.4358</v>
       </c>
       <c r="H289" s="1" t="n">
-        <v>0.4358</v>
+        <v>0.4359</v>
       </c>
       <c r="I289" s="1" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="J289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -9430,10 +10300,13 @@
         <v>0.03928</v>
       </c>
       <c r="H290" s="1" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="I290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="I290" s="1" t="n">
-        <v>0.03921</v>
+      <c r="J290" s="1" t="n">
+        <v>0.03897</v>
       </c>
     </row>
     <row r="291">
@@ -9461,10 +10334,13 @@
         <v>0.2409</v>
       </c>
       <c r="H291" s="1" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="I291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="I291" s="1" t="n">
-        <v>0.2409</v>
+      <c r="J291" s="1" t="n">
+        <v>0.2394</v>
       </c>
     </row>
     <row r="292">
@@ -9492,9 +10368,12 @@
         <v>0.28296</v>
       </c>
       <c r="H292" s="1" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="I292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="I292" s="1" t="n">
+      <c r="J292" s="1" t="n">
         <v>0.28275</v>
       </c>
     </row>
@@ -9523,10 +10402,13 @@
         <v>0.1503</v>
       </c>
       <c r="H293" s="1" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="I293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="I293" s="1" t="n">
-        <v>0.1498</v>
+      <c r="J293" s="1" t="n">
+        <v>0.1494</v>
       </c>
     </row>
     <row r="294">
@@ -9554,10 +10436,13 @@
         <v>4.262</v>
       </c>
       <c r="H294" s="1" t="n">
+        <v>4.232</v>
+      </c>
+      <c r="I294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="I294" s="1" t="n">
-        <v>4.238</v>
+      <c r="J294" s="1" t="n">
+        <v>4.232</v>
       </c>
     </row>
     <row r="295">
@@ -9585,9 +10470,12 @@
         <v>0.03318</v>
       </c>
       <c r="H295" s="1" t="n">
+        <v>0.03271</v>
+      </c>
+      <c r="I295" s="1" t="n">
         <v>0.03318</v>
       </c>
-      <c r="I295" s="1" t="n">
+      <c r="J295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -9616,9 +10504,12 @@
         <v>0.0009790000000000001</v>
       </c>
       <c r="H296" s="1" t="n">
+        <v>0.000985</v>
+      </c>
+      <c r="I296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="I296" s="1" t="n">
+      <c r="J296" s="1" t="n">
         <v>0.0009790000000000001</v>
       </c>
     </row>
@@ -9647,10 +10538,13 @@
         <v>0.08244</v>
       </c>
       <c r="H297" s="1" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="I297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="I297" s="1" t="n">
-        <v>0.08209</v>
+      <c r="J297" s="1" t="n">
+        <v>0.0818</v>
       </c>
     </row>
     <row r="298">
@@ -9678,9 +10572,12 @@
         <v>0.05821</v>
       </c>
       <c r="H298" s="1" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="I298" s="1" t="n">
         <v>0.05821</v>
       </c>
-      <c r="I298" s="1" t="n">
+      <c r="J298" s="1" t="n">
         <v>0.05763</v>
       </c>
     </row>
@@ -9709,9 +10606,12 @@
         <v>0.0917</v>
       </c>
       <c r="H299" s="1" t="n">
+        <v>0.09132999999999999</v>
+      </c>
+      <c r="I299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="I299" s="1" t="n">
+      <c r="J299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -9740,10 +10640,13 @@
         <v>0.02783</v>
       </c>
       <c r="H300" s="1" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="I300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="I300" s="1" t="n">
-        <v>0.02764</v>
+      <c r="J300" s="1" t="n">
+        <v>0.0276</v>
       </c>
     </row>
     <row r="301">
@@ -9771,10 +10674,13 @@
         <v>0.06612999999999999</v>
       </c>
       <c r="H301" s="1" t="n">
+        <v>0.06576</v>
+      </c>
+      <c r="I301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="I301" s="1" t="n">
-        <v>0.06603000000000001</v>
+      <c r="J301" s="1" t="n">
+        <v>0.06576</v>
       </c>
     </row>
     <row r="302">
@@ -9802,9 +10708,12 @@
         <v>0.052828</v>
       </c>
       <c r="H302" s="1" t="n">
+        <v>0.052777</v>
+      </c>
+      <c r="I302" s="1" t="n">
         <v>0.052828</v>
       </c>
-      <c r="I302" s="1" t="n">
+      <c r="J302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -9833,9 +10742,12 @@
         <v>5177.6</v>
       </c>
       <c r="H303" s="1" t="n">
+        <v>5175.3</v>
+      </c>
+      <c r="I303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="I303" s="1" t="n">
+      <c r="J303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -9864,9 +10776,12 @@
         <v>15.1</v>
       </c>
       <c r="H304" s="1" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="I304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="I304" s="1" t="n">
+      <c r="J304" s="1" t="n">
         <v>14.99</v>
       </c>
     </row>
@@ -9895,10 +10810,13 @@
         <v>0.003737</v>
       </c>
       <c r="H305" s="1" t="n">
+        <v>0.003721</v>
+      </c>
+      <c r="I305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="I305" s="1" t="n">
-        <v>0.003722</v>
+      <c r="J305" s="1" t="n">
+        <v>0.003721</v>
       </c>
     </row>
     <row r="306">
@@ -9926,9 +10844,12 @@
         <v>0.4608</v>
       </c>
       <c r="H306" s="1" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="I306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="I306" s="1" t="n">
+      <c r="J306" s="1" t="n">
         <v>0.4573</v>
       </c>
     </row>
@@ -9957,10 +10878,13 @@
         <v>0.04734</v>
       </c>
       <c r="H307" s="1" t="n">
+        <v>0.04718</v>
+      </c>
+      <c r="I307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="I307" s="1" t="n">
-        <v>0.04732</v>
+      <c r="J307" s="1" t="n">
+        <v>0.04718</v>
       </c>
     </row>
     <row r="308">
@@ -9988,9 +10912,12 @@
         <v>1.4853</v>
       </c>
       <c r="H308" s="1" t="n">
+        <v>1.4883</v>
+      </c>
+      <c r="I308" s="1" t="n">
         <v>1.4891</v>
       </c>
-      <c r="I308" s="1" t="n">
+      <c r="J308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -10019,10 +10946,13 @@
         <v>0.0008073000000000001</v>
       </c>
       <c r="H309" s="1" t="n">
+        <v>0.0007948</v>
+      </c>
+      <c r="I309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="I309" s="1" t="n">
-        <v>0.0008068</v>
+      <c r="J309" s="1" t="n">
+        <v>0.0007948</v>
       </c>
     </row>
     <row r="310">
@@ -10050,10 +10980,13 @@
         <v>4.687</v>
       </c>
       <c r="H310" s="1" t="n">
+        <v>4.657</v>
+      </c>
+      <c r="I310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="I310" s="1" t="n">
-        <v>4.687</v>
+      <c r="J310" s="1" t="n">
+        <v>4.657</v>
       </c>
     </row>
     <row r="311">
@@ -10081,9 +11014,12 @@
         <v>4.801</v>
       </c>
       <c r="H311" s="1" t="n">
+        <v>4.775</v>
+      </c>
+      <c r="I311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="I311" s="1" t="n">
+      <c r="J311" s="1" t="n">
         <v>4.765</v>
       </c>
     </row>
@@ -10112,9 +11048,12 @@
         <v>0.08212</v>
       </c>
       <c r="H312" s="1" t="n">
+        <v>0.08134</v>
+      </c>
+      <c r="I312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="I312" s="1" t="n">
+      <c r="J312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -10143,10 +11082,13 @@
         <v>2.041</v>
       </c>
       <c r="H313" s="1" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="I313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="I313" s="1" t="n">
-        <v>2.037</v>
+      <c r="J313" s="1" t="n">
+        <v>2.029</v>
       </c>
     </row>
     <row r="314">
@@ -10174,9 +11116,12 @@
         <v>0.07104000000000001</v>
       </c>
       <c r="H314" s="1" t="n">
-        <v>0.07104000000000001</v>
+        <v>0.07123</v>
       </c>
       <c r="I314" s="1" t="n">
+        <v>0.07123</v>
+      </c>
+      <c r="J314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -10205,10 +11150,13 @@
         <v>0.966</v>
       </c>
       <c r="H315" s="1" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="I315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="I315" s="1" t="n">
-        <v>0.957</v>
+      <c r="J315" s="1" t="n">
+        <v>0.955</v>
       </c>
     </row>
     <row r="316">
@@ -10236,9 +11184,12 @@
         <v>0.1313</v>
       </c>
       <c r="H316" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="I316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="I316" s="1" t="n">
+      <c r="J316" s="1" t="n">
         <v>0.1305</v>
       </c>
     </row>
@@ -10267,9 +11218,12 @@
         <v>0.186</v>
       </c>
       <c r="H317" s="1" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="I317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="I317" s="1" t="n">
+      <c r="J317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -10298,9 +11252,12 @@
         <v>0.01644</v>
       </c>
       <c r="H318" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="I318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="I318" s="1" t="n">
+      <c r="J318" s="1" t="n">
         <v>0.01634</v>
       </c>
     </row>
@@ -10329,9 +11286,12 @@
         <v>0.0843</v>
       </c>
       <c r="H319" s="1" t="n">
+        <v>0.08404</v>
+      </c>
+      <c r="I319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="I319" s="1" t="n">
+      <c r="J319" s="1" t="n">
         <v>0.08395</v>
       </c>
     </row>
@@ -10360,9 +11320,12 @@
         <v>0.007667</v>
       </c>
       <c r="H320" s="1" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="I320" s="1" t="n">
+      <c r="J320" s="1" t="n">
         <v>0.007597</v>
       </c>
     </row>
@@ -10391,10 +11354,13 @@
         <v>0.05501</v>
       </c>
       <c r="H321" s="1" t="n">
+        <v>0.05442</v>
+      </c>
+      <c r="I321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="I321" s="1" t="n">
-        <v>0.05452</v>
+      <c r="J321" s="1" t="n">
+        <v>0.05442</v>
       </c>
     </row>
     <row r="322">
@@ -10422,9 +11388,12 @@
         <v>0.5514</v>
       </c>
       <c r="H322" s="1" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="I322" s="1" t="n">
         <v>0.5514</v>
       </c>
-      <c r="I322" s="1" t="n">
+      <c r="J322" s="1" t="n">
         <v>0.5483</v>
       </c>
     </row>
@@ -10453,9 +11422,12 @@
         <v>0.07611999999999999</v>
       </c>
       <c r="H323" s="1" t="n">
+        <v>0.07568</v>
+      </c>
+      <c r="I323" s="1" t="n">
         <v>0.07611999999999999</v>
       </c>
-      <c r="I323" s="1" t="n">
+      <c r="J323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -10484,9 +11456,12 @@
         <v>0.012933</v>
       </c>
       <c r="H324" s="1" t="n">
-        <v>0.012933</v>
+        <v>0.013001</v>
       </c>
       <c r="I324" s="1" t="n">
+        <v>0.013001</v>
+      </c>
+      <c r="J324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -10515,9 +11490,12 @@
         <v>0.0997</v>
       </c>
       <c r="H325" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="I325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="I325" s="1" t="n">
+      <c r="J325" s="1" t="n">
         <v>0.0993</v>
       </c>
     </row>
@@ -10546,10 +11524,13 @@
         <v>0.01765</v>
       </c>
       <c r="H326" s="1" t="n">
+        <v>0.01748</v>
+      </c>
+      <c r="I326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="I326" s="1" t="n">
-        <v>0.01752</v>
+      <c r="J326" s="1" t="n">
+        <v>0.01748</v>
       </c>
     </row>
     <row r="327">
@@ -10577,9 +11558,12 @@
         <v>0.06432</v>
       </c>
       <c r="H327" s="1" t="n">
+        <v>0.06406000000000001</v>
+      </c>
+      <c r="I327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="I327" s="1" t="n">
+      <c r="J327" s="1" t="n">
         <v>0.06392</v>
       </c>
     </row>
@@ -10608,10 +11592,13 @@
         <v>0.2673</v>
       </c>
       <c r="H328" s="1" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="I328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="I328" s="1" t="n">
-        <v>0.2671</v>
+      <c r="J328" s="1" t="n">
+        <v>0.2647</v>
       </c>
     </row>
     <row r="329">
@@ -10639,10 +11626,13 @@
         <v>0.17297</v>
       </c>
       <c r="H329" s="1" t="n">
+        <v>0.17145</v>
+      </c>
+      <c r="I329" s="1" t="n">
         <v>0.17297</v>
       </c>
-      <c r="I329" s="1" t="n">
-        <v>0.17172</v>
+      <c r="J329" s="1" t="n">
+        <v>0.17145</v>
       </c>
     </row>
     <row r="330">
@@ -10670,9 +11660,12 @@
         <v>2.088</v>
       </c>
       <c r="H330" s="1" t="n">
+        <v>2.069</v>
+      </c>
+      <c r="I330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="I330" s="1" t="n">
+      <c r="J330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -10701,9 +11694,12 @@
         <v>0.0277</v>
       </c>
       <c r="H331" s="1" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="I331" s="1" t="n">
         <v>0.028</v>
       </c>
-      <c r="I331" s="1" t="n">
+      <c r="J331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -10732,9 +11728,12 @@
         <v>0.006031</v>
       </c>
       <c r="H332" s="1" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="I332" s="1" t="n">
         <v>0.006031</v>
       </c>
-      <c r="I332" s="1" t="n">
+      <c r="J332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -10763,10 +11762,13 @@
         <v>0.003578</v>
       </c>
       <c r="H333" s="1" t="n">
+        <v>0.003503</v>
+      </c>
+      <c r="I333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="I333" s="1" t="n">
-        <v>0.003531</v>
+      <c r="J333" s="1" t="n">
+        <v>0.003503</v>
       </c>
     </row>
     <row r="334">
@@ -10794,10 +11796,13 @@
         <v>0.01408</v>
       </c>
       <c r="H334" s="1" t="n">
+        <v>0.01398</v>
+      </c>
+      <c r="I334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="I334" s="1" t="n">
-        <v>0.01399</v>
+      <c r="J334" s="1" t="n">
+        <v>0.01398</v>
       </c>
     </row>
     <row r="335">
@@ -10825,9 +11830,12 @@
         <v>1.13</v>
       </c>
       <c r="H335" s="1" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="I335" s="1" t="n">
         <v>1.13</v>
       </c>
-      <c r="I335" s="1" t="n">
+      <c r="J335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -10856,9 +11864,12 @@
         <v>0.011298</v>
       </c>
       <c r="H336" s="1" t="n">
+        <v>0.011316</v>
+      </c>
+      <c r="I336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="I336" s="1" t="n">
+      <c r="J336" s="1" t="n">
         <v>0.011253</v>
       </c>
     </row>
@@ -10887,9 +11898,12 @@
         <v>2.964</v>
       </c>
       <c r="H337" s="1" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="I337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="I337" s="1" t="n">
+      <c r="J337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -10918,9 +11932,12 @@
         <v>0.01885</v>
       </c>
       <c r="H338" s="1" t="n">
+        <v>0.01871</v>
+      </c>
+      <c r="I338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="I338" s="1" t="n">
+      <c r="J338" s="1" t="n">
         <v>0.01861</v>
       </c>
     </row>
@@ -10949,9 +11966,12 @@
         <v>0.07790999999999999</v>
       </c>
       <c r="H339" s="1" t="n">
+        <v>0.07758</v>
+      </c>
+      <c r="I339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="I339" s="1" t="n">
+      <c r="J339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -10980,9 +12000,12 @@
         <v>0.076</v>
       </c>
       <c r="H340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="I340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="I340" s="1" t="n">
+      <c r="J340" s="1" t="n">
         <v>0.076</v>
       </c>
     </row>
@@ -11011,10 +12034,13 @@
         <v>0.03637</v>
       </c>
       <c r="H341" s="1" t="n">
+        <v>0.03618</v>
+      </c>
+      <c r="I341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="I341" s="1" t="n">
-        <v>0.0362</v>
+      <c r="J341" s="1" t="n">
+        <v>0.03618</v>
       </c>
     </row>
     <row r="342">
@@ -11042,9 +12068,12 @@
         <v>2647</v>
       </c>
       <c r="H342" s="1" t="n">
+        <v>2630</v>
+      </c>
+      <c r="I342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="I342" s="1" t="n">
+      <c r="J342" s="1" t="n">
         <v>2620</v>
       </c>
     </row>
@@ -11073,9 +12102,12 @@
         <v>0.0001972</v>
       </c>
       <c r="H343" s="1" t="n">
+        <v>0.0001968</v>
+      </c>
+      <c r="I343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="I343" s="1" t="n">
+      <c r="J343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -11104,10 +12136,13 @@
         <v>0.08008999999999999</v>
       </c>
       <c r="H344" s="1" t="n">
+        <v>0.07947</v>
+      </c>
+      <c r="I344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="I344" s="1" t="n">
-        <v>0.07987</v>
+      <c r="J344" s="1" t="n">
+        <v>0.07947</v>
       </c>
     </row>
     <row r="345">
@@ -11135,9 +12170,12 @@
         <v>0.01651</v>
       </c>
       <c r="H345" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="I345" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="I345" s="1" t="n">
+      <c r="J345" s="1" t="n">
         <v>0.01632</v>
       </c>
     </row>
@@ -11166,9 +12204,12 @@
         <v>2.799</v>
       </c>
       <c r="H346" s="1" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="I346" s="1" t="n">
+      <c r="J346" s="1" t="n">
         <v>2.773</v>
       </c>
     </row>
@@ -11197,9 +12238,12 @@
         <v>0.0165</v>
       </c>
       <c r="H347" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="I347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="I347" s="1" t="n">
+      <c r="J347" s="1" t="n">
         <v>0.01639</v>
       </c>
     </row>
@@ -11228,9 +12272,12 @@
         <v>0.0388</v>
       </c>
       <c r="H348" s="1" t="n">
+        <v>0.03867</v>
+      </c>
+      <c r="I348" s="1" t="n">
         <v>0.03897</v>
       </c>
-      <c r="I348" s="1" t="n">
+      <c r="J348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -11259,9 +12306,12 @@
         <v>0.3054</v>
       </c>
       <c r="H349" s="1" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="I349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="I349" s="1" t="n">
+      <c r="J349" s="1" t="n">
         <v>0.3037</v>
       </c>
     </row>
@@ -11290,9 +12340,12 @@
         <v>0.005081</v>
       </c>
       <c r="H350" s="1" t="n">
+        <v>0.005094</v>
+      </c>
+      <c r="I350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="I350" s="1" t="n">
+      <c r="J350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -11321,10 +12374,13 @@
         <v>0.005135</v>
       </c>
       <c r="H351" s="1" t="n">
+        <v>0.005096</v>
+      </c>
+      <c r="I351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="I351" s="1" t="n">
-        <v>0.00512</v>
+      <c r="J351" s="1" t="n">
+        <v>0.005096</v>
       </c>
     </row>
     <row r="352">
@@ -11352,9 +12408,12 @@
         <v>0.004419</v>
       </c>
       <c r="H352" s="1" t="n">
+        <v>0.004397</v>
+      </c>
+      <c r="I352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="I352" s="1" t="n">
+      <c r="J352" s="1" t="n">
         <v>0.004387</v>
       </c>
     </row>
@@ -11383,10 +12442,13 @@
         <v>0.08172</v>
       </c>
       <c r="H353" s="1" t="n">
+        <v>0.08129</v>
+      </c>
+      <c r="I353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="I353" s="1" t="n">
-        <v>0.08171</v>
+      <c r="J353" s="1" t="n">
+        <v>0.08129</v>
       </c>
     </row>
     <row r="354">
@@ -11414,9 +12476,12 @@
         <v>1.307</v>
       </c>
       <c r="H354" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="I354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="I354" s="1" t="n">
+      <c r="J354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -11445,10 +12510,13 @@
         <v>7.774</v>
       </c>
       <c r="H355" s="1" t="n">
+        <v>7.739</v>
+      </c>
+      <c r="I355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="I355" s="1" t="n">
-        <v>7.744</v>
+      <c r="J355" s="1" t="n">
+        <v>7.739</v>
       </c>
     </row>
     <row r="356">
@@ -11476,10 +12544,13 @@
         <v>0.007900000000000001</v>
       </c>
       <c r="H356" s="1" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="I356" s="1" t="n">
-        <v>0.007849999999999999</v>
+      <c r="J356" s="1" t="n">
+        <v>0.00781</v>
       </c>
     </row>
     <row r="357">
@@ -11507,9 +12578,12 @@
         <v>0.005728</v>
       </c>
       <c r="H357" s="1" t="n">
+        <v>0.005722</v>
+      </c>
+      <c r="I357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="I357" s="1" t="n">
+      <c r="J357" s="1" t="n">
         <v>0.005696</v>
       </c>
     </row>
@@ -11538,10 +12612,13 @@
         <v>0.01574</v>
       </c>
       <c r="H358" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="I358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="I358" s="1" t="n">
-        <v>0.01567</v>
+      <c r="J358" s="1" t="n">
+        <v>0.01554</v>
       </c>
     </row>
     <row r="359">
@@ -11569,9 +12646,12 @@
         <v>3.666</v>
       </c>
       <c r="H359" s="1" t="n">
+        <v>3.652</v>
+      </c>
+      <c r="I359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="I359" s="1" t="n">
+      <c r="J359" s="1" t="n">
         <v>3.65</v>
       </c>
     </row>
@@ -11600,9 +12680,12 @@
         <v>0.1515</v>
       </c>
       <c r="H360" s="1" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="I360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="I360" s="1" t="n">
+      <c r="J360" s="1" t="n">
         <v>0.1499</v>
       </c>
     </row>
@@ -11631,9 +12714,12 @@
         <v>0.07104000000000001</v>
       </c>
       <c r="H361" s="1" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="I361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="I361" s="1" t="n">
+      <c r="J361" s="1" t="n">
         <v>0.07069</v>
       </c>
     </row>
@@ -11662,10 +12748,13 @@
         <v>0.01795</v>
       </c>
       <c r="H362" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="I362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="I362" s="1" t="n">
-        <v>0.01786</v>
+      <c r="J362" s="1" t="n">
+        <v>0.01776</v>
       </c>
     </row>
     <row r="363">
@@ -11693,10 +12782,13 @@
         <v>0.02254</v>
       </c>
       <c r="H363" s="1" t="n">
+        <v>0.02243</v>
+      </c>
+      <c r="I363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="I363" s="1" t="n">
-        <v>0.02254</v>
+      <c r="J363" s="1" t="n">
+        <v>0.02243</v>
       </c>
     </row>
     <row r="364">
@@ -11724,10 +12816,13 @@
         <v>0.0127</v>
       </c>
       <c r="H364" s="1" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="I364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="I364" s="1" t="n">
-        <v>0.0127</v>
+      <c r="J364" s="1" t="n">
+        <v>0.01262</v>
       </c>
     </row>
     <row r="365">
@@ -11755,9 +12850,12 @@
         <v>0.0926</v>
       </c>
       <c r="H365" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="I365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="I365" s="1" t="n">
+      <c r="J365" s="1" t="n">
         <v>0.0919</v>
       </c>
     </row>
@@ -11786,10 +12884,13 @@
         <v>0.04255</v>
       </c>
       <c r="H366" s="1" t="n">
+        <v>0.04236</v>
+      </c>
+      <c r="I366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="I366" s="1" t="n">
-        <v>0.04244</v>
+      <c r="J366" s="1" t="n">
+        <v>0.04236</v>
       </c>
     </row>
     <row r="367">
@@ -11817,9 +12918,12 @@
         <v>0.03157</v>
       </c>
       <c r="H367" s="1" t="n">
+        <v>0.03148</v>
+      </c>
+      <c r="I367" s="1" t="n">
         <v>0.03164</v>
       </c>
-      <c r="I367" s="1" t="n">
+      <c r="J367" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -11848,10 +12952,13 @@
         <v>0.02358</v>
       </c>
       <c r="H368" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="I368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="I368" s="1" t="n">
-        <v>0.02358</v>
+      <c r="J368" s="1" t="n">
+        <v>0.02342</v>
       </c>
     </row>
     <row r="369">
@@ -11879,10 +12986,13 @@
         <v>0.03118</v>
       </c>
       <c r="H369" s="1" t="n">
+        <v>0.03102</v>
+      </c>
+      <c r="I369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="I369" s="1" t="n">
-        <v>0.03113</v>
+      <c r="J369" s="1" t="n">
+        <v>0.03102</v>
       </c>
     </row>
     <row r="370">
@@ -11910,9 +13020,12 @@
         <v>0.07890999999999999</v>
       </c>
       <c r="H370" s="1" t="n">
-        <v>0.07890999999999999</v>
+        <v>0.07932</v>
       </c>
       <c r="I370" s="1" t="n">
+        <v>0.07932</v>
+      </c>
+      <c r="J370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -11941,9 +13054,12 @@
         <v>0.1089</v>
       </c>
       <c r="H371" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="I371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="I371" s="1" t="n">
+      <c r="J371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -11972,9 +13088,12 @@
         <v>0.007156</v>
       </c>
       <c r="H372" s="1" t="n">
+        <v>0.007105</v>
+      </c>
+      <c r="I372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="I372" s="1" t="n">
+      <c r="J372" s="1" t="n">
         <v>0.007057</v>
       </c>
     </row>
@@ -12003,10 +13122,13 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="H373" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="I373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="I373" s="1" t="n">
-        <v>0.0965</v>
+      <c r="J373" s="1" t="n">
+        <v>0.0963</v>
       </c>
     </row>
     <row r="374">
@@ -12034,9 +13156,12 @@
         <v>0.05881</v>
       </c>
       <c r="H374" s="1" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="I374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="I374" s="1" t="n">
+      <c r="J374" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -12065,9 +13190,12 @@
         <v>0.3238</v>
       </c>
       <c r="H375" s="1" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="I375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="I375" s="1" t="n">
+      <c r="J375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -12096,10 +13224,13 @@
         <v>0.01994</v>
       </c>
       <c r="H376" s="1" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="I376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="I376" s="1" t="n">
-        <v>0.01988</v>
+      <c r="J376" s="1" t="n">
+        <v>0.01971</v>
       </c>
     </row>
     <row r="377">
@@ -12127,10 +13258,13 @@
         <v>0.06915</v>
       </c>
       <c r="H377" s="1" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="I377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="I377" s="1" t="n">
-        <v>0.06877</v>
+      <c r="J377" s="1" t="n">
+        <v>0.06872</v>
       </c>
     </row>
     <row r="378">
@@ -12158,9 +13292,12 @@
         <v>0.15493</v>
       </c>
       <c r="H378" s="1" t="n">
-        <v>0.15583</v>
+        <v>0.15637</v>
       </c>
       <c r="I378" s="1" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="J378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -12189,10 +13326,13 @@
         <v>0.0006057</v>
       </c>
       <c r="H379" s="1" t="n">
+        <v>0.0006015</v>
+      </c>
+      <c r="I379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="I379" s="1" t="n">
-        <v>0.0006028</v>
+      <c r="J379" s="1" t="n">
+        <v>0.0006015</v>
       </c>
     </row>
     <row r="380">
@@ -12220,9 +13360,12 @@
         <v>0.01024</v>
       </c>
       <c r="H380" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="I380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="I380" s="1" t="n">
+      <c r="J380" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -12251,10 +13394,13 @@
         <v>0.02561</v>
       </c>
       <c r="H381" s="1" t="n">
+        <v>0.02551</v>
+      </c>
+      <c r="I381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="I381" s="1" t="n">
-        <v>0.02553</v>
+      <c r="J381" s="1" t="n">
+        <v>0.02551</v>
       </c>
     </row>
     <row r="382">
@@ -12282,9 +13428,12 @@
         <v>0.19193</v>
       </c>
       <c r="H382" s="1" t="n">
+        <v>0.19145</v>
+      </c>
+      <c r="I382" s="1" t="n">
         <v>0.19263</v>
       </c>
-      <c r="I382" s="1" t="n">
+      <c r="J382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -12313,10 +13462,13 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="H383" s="1" t="n">
+        <v>0.09325</v>
+      </c>
+      <c r="I383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="I383" s="1" t="n">
-        <v>0.09329999999999999</v>
+      <c r="J383" s="1" t="n">
+        <v>0.09325</v>
       </c>
     </row>
     <row r="384">
@@ -12344,10 +13496,13 @@
         <v>0.03182</v>
       </c>
       <c r="H384" s="1" t="n">
+        <v>0.03176</v>
+      </c>
+      <c r="I384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="I384" s="1" t="n">
-        <v>0.03182</v>
+      <c r="J384" s="1" t="n">
+        <v>0.03176</v>
       </c>
     </row>
     <row r="385">
@@ -12375,10 +13530,13 @@
         <v>0.01118</v>
       </c>
       <c r="H385" s="1" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="I385" s="1" t="n">
-        <v>0.01115</v>
+      <c r="J385" s="1" t="n">
+        <v>0.0111</v>
       </c>
     </row>
     <row r="386">
@@ -12406,9 +13564,12 @@
         <v>0.05156</v>
       </c>
       <c r="H386" s="1" t="n">
-        <v>0.05156</v>
+        <v>0.05218</v>
       </c>
       <c r="I386" s="1" t="n">
+        <v>0.05218</v>
+      </c>
+      <c r="J386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -12437,9 +13598,12 @@
         <v>0.02524</v>
       </c>
       <c r="H387" s="1" t="n">
-        <v>0.02524</v>
+        <v>0.02541</v>
       </c>
       <c r="I387" s="1" t="n">
+        <v>0.02541</v>
+      </c>
+      <c r="J387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -12468,10 +13632,13 @@
         <v>0.007355</v>
       </c>
       <c r="H388" s="1" t="n">
+        <v>0.007291</v>
+      </c>
+      <c r="I388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="I388" s="1" t="n">
-        <v>0.007344</v>
+      <c r="J388" s="1" t="n">
+        <v>0.007291</v>
       </c>
     </row>
     <row r="389">
@@ -12499,10 +13666,13 @@
         <v>0.0102</v>
       </c>
       <c r="H389" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="I389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="I389" s="1" t="n">
-        <v>0.01016</v>
+      <c r="J389" s="1" t="n">
+        <v>0.01015</v>
       </c>
     </row>
     <row r="390">
@@ -12530,10 +13700,13 @@
         <v>0.0839</v>
       </c>
       <c r="H390" s="1" t="n">
+        <v>0.08295</v>
+      </c>
+      <c r="I390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="I390" s="1" t="n">
-        <v>0.08304</v>
+      <c r="J390" s="1" t="n">
+        <v>0.08295</v>
       </c>
     </row>
     <row r="391">
@@ -12561,9 +13734,12 @@
         <v>0.5061</v>
       </c>
       <c r="H391" s="1" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="I391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="I391" s="1" t="n">
+      <c r="J391" s="1" t="n">
         <v>0.5017</v>
       </c>
     </row>
@@ -12592,9 +13768,12 @@
         <v>0.1179</v>
       </c>
       <c r="H392" s="1" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="I392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="I392" s="1" t="n">
+      <c r="J392" s="1" t="n">
         <v>0.1171</v>
       </c>
     </row>
@@ -12623,10 +13802,13 @@
         <v>0.00251</v>
       </c>
       <c r="H393" s="1" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="I393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="I393" s="1" t="n">
-        <v>0.0025</v>
+      <c r="J393" s="1" t="n">
+        <v>0.00248</v>
       </c>
     </row>
     <row r="394">
@@ -12654,10 +13836,13 @@
         <v>0.02135</v>
       </c>
       <c r="H394" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="I394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="I394" s="1" t="n">
-        <v>0.02135</v>
+      <c r="J394" s="1" t="n">
+        <v>0.02121</v>
       </c>
     </row>
     <row r="395">
@@ -12685,10 +13870,13 @@
         <v>0.0163</v>
       </c>
       <c r="H395" s="1" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="I395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="I395" s="1" t="n">
-        <v>0.0162</v>
+      <c r="J395" s="1" t="n">
+        <v>0.0161</v>
       </c>
     </row>
     <row r="396">
@@ -12716,10 +13904,13 @@
         <v>0.1363</v>
       </c>
       <c r="H396" s="1" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="I396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="I396" s="1" t="n">
-        <v>0.1358</v>
+      <c r="J396" s="1" t="n">
+        <v>0.1357</v>
       </c>
     </row>
     <row r="397">
@@ -12747,10 +13938,13 @@
         <v>0.01476</v>
       </c>
       <c r="H397" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="I397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="I397" s="1" t="n">
-        <v>0.01473</v>
+      <c r="J397" s="1" t="n">
+        <v>0.01468</v>
       </c>
     </row>
     <row r="398">
@@ -12778,9 +13972,12 @@
         <v>6.955</v>
       </c>
       <c r="H398" s="1" t="n">
+        <v>6.901</v>
+      </c>
+      <c r="I398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="I398" s="1" t="n">
+      <c r="J398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -12809,9 +14006,12 @@
         <v>0.009448</v>
       </c>
       <c r="H399" s="1" t="n">
+        <v>0.009476</v>
+      </c>
+      <c r="I399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="I399" s="1" t="n">
+      <c r="J399" s="1" t="n">
         <v>0.009448</v>
       </c>
     </row>
@@ -12840,9 +14040,12 @@
         <v>0.001284</v>
       </c>
       <c r="H400" s="1" t="n">
+        <v>0.001277</v>
+      </c>
+      <c r="I400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="I400" s="1" t="n">
+      <c r="J400" s="1" t="n">
         <v>0.001264</v>
       </c>
     </row>
@@ -12871,9 +14074,12 @@
         <v>0.01859</v>
       </c>
       <c r="H401" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="I401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="I401" s="1" t="n">
+      <c r="J401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -12902,10 +14108,13 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="H402" s="1" t="n">
+        <v>0.08538999999999999</v>
+      </c>
+      <c r="I402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="I402" s="1" t="n">
-        <v>0.08563999999999999</v>
+      <c r="J402" s="1" t="n">
+        <v>0.08538999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -12933,9 +14142,12 @@
         <v>0.00556</v>
       </c>
       <c r="H403" s="1" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="I403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="I403" s="1" t="n">
+      <c r="J403" s="1" t="n">
         <v>0.00553</v>
       </c>
     </row>
@@ -12964,10 +14176,13 @@
         <v>0.04379</v>
       </c>
       <c r="H404" s="1" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="I404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="I404" s="1" t="n">
-        <v>0.04362</v>
+      <c r="J404" s="1" t="n">
+        <v>0.0434</v>
       </c>
     </row>
     <row r="405">
@@ -12995,10 +14210,13 @@
         <v>0.05906</v>
       </c>
       <c r="H405" s="1" t="n">
+        <v>0.05857</v>
+      </c>
+      <c r="I405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="I405" s="1" t="n">
-        <v>0.05871</v>
+      <c r="J405" s="1" t="n">
+        <v>0.05857</v>
       </c>
     </row>
     <row r="406">
@@ -13026,10 +14244,13 @@
         <v>0.01663</v>
       </c>
       <c r="H406" s="1" t="n">
+        <v>0.01651</v>
+      </c>
+      <c r="I406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="I406" s="1" t="n">
-        <v>0.01658</v>
+      <c r="J406" s="1" t="n">
+        <v>0.01651</v>
       </c>
     </row>
     <row r="407">
@@ -13057,9 +14278,12 @@
         <v>0.0428</v>
       </c>
       <c r="H407" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="I407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="I407" s="1" t="n">
+      <c r="J407" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -13088,10 +14312,13 @@
         <v>0.01947</v>
       </c>
       <c r="H408" s="1" t="n">
+        <v>0.01937</v>
+      </c>
+      <c r="I408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="I408" s="1" t="n">
-        <v>0.01938</v>
+      <c r="J408" s="1" t="n">
+        <v>0.01937</v>
       </c>
     </row>
     <row r="409">
@@ -13119,9 +14346,12 @@
         <v>0.4484</v>
       </c>
       <c r="H409" s="1" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="I409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="I409" s="1" t="n">
+      <c r="J409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -13150,9 +14380,12 @@
         <v>0.0445</v>
       </c>
       <c r="H410" s="1" t="n">
+        <v>0.04433</v>
+      </c>
+      <c r="I410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="I410" s="1" t="n">
+      <c r="J410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -13181,9 +14414,12 @@
         <v>28</v>
       </c>
       <c r="H411" s="1" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="I411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I411" s="1" t="n">
+      <c r="J411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -13212,9 +14448,12 @@
         <v>0.03564</v>
       </c>
       <c r="H412" s="1" t="n">
+        <v>0.03535</v>
+      </c>
+      <c r="I412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="I412" s="1" t="n">
+      <c r="J412" s="1" t="n">
         <v>0.03515</v>
       </c>
     </row>
@@ -13243,9 +14482,12 @@
         <v>0.003432</v>
       </c>
       <c r="H413" s="1" t="n">
+        <v>0.003414</v>
+      </c>
+      <c r="I413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="I413" s="1" t="n">
+      <c r="J413" s="1" t="n">
         <v>0.00341</v>
       </c>
     </row>
@@ -13274,9 +14516,12 @@
         <v>0.1538</v>
       </c>
       <c r="H414" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="I414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="I414" s="1" t="n">
+      <c r="J414" s="1" t="n">
         <v>0.1527</v>
       </c>
     </row>
@@ -13305,9 +14550,12 @@
         <v>0.05288</v>
       </c>
       <c r="H415" s="1" t="n">
+        <v>0.05265</v>
+      </c>
+      <c r="I415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="I415" s="1" t="n">
+      <c r="J415" s="1" t="n">
         <v>0.05258</v>
       </c>
     </row>
@@ -13336,10 +14584,13 @@
         <v>0.00666</v>
       </c>
       <c r="H416" s="1" t="n">
+        <v>0.00663</v>
+      </c>
+      <c r="I416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="I416" s="1" t="n">
-        <v>0.00664</v>
+      <c r="J416" s="1" t="n">
+        <v>0.00663</v>
       </c>
     </row>
     <row r="417">
@@ -13367,10 +14618,13 @@
         <v>0.06094</v>
       </c>
       <c r="H417" s="1" t="n">
+        <v>0.06065</v>
+      </c>
+      <c r="I417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="I417" s="1" t="n">
-        <v>0.0608</v>
+      <c r="J417" s="1" t="n">
+        <v>0.06065</v>
       </c>
     </row>
     <row r="418">
@@ -13398,10 +14652,13 @@
         <v>0.008203999999999999</v>
       </c>
       <c r="H418" s="1" t="n">
+        <v>0.008127000000000001</v>
+      </c>
+      <c r="I418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="I418" s="1" t="n">
-        <v>0.008156</v>
+      <c r="J418" s="1" t="n">
+        <v>0.008127000000000001</v>
       </c>
     </row>
     <row r="419">
@@ -13429,9 +14686,12 @@
         <v>0.07524</v>
       </c>
       <c r="H419" s="1" t="n">
+        <v>0.07516</v>
+      </c>
+      <c r="I419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="I419" s="1" t="n">
+      <c r="J419" s="1" t="n">
         <v>0.07459</v>
       </c>
     </row>
@@ -13460,9 +14720,12 @@
         <v>0.02146</v>
       </c>
       <c r="H420" s="1" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="I420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="I420" s="1" t="n">
+      <c r="J420" s="1" t="n">
         <v>0.0213</v>
       </c>
     </row>
@@ -13491,9 +14754,12 @@
         <v>0.07038999999999999</v>
       </c>
       <c r="H421" s="1" t="n">
+        <v>0.06983</v>
+      </c>
+      <c r="I421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="I421" s="1" t="n">
+      <c r="J421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -13522,10 +14788,13 @@
         <v>0.01514</v>
       </c>
       <c r="H422" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="I422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="I422" s="1" t="n">
-        <v>0.01514</v>
+      <c r="J422" s="1" t="n">
+        <v>0.01501</v>
       </c>
     </row>
     <row r="423">
@@ -13553,10 +14822,13 @@
         <v>0.006694</v>
       </c>
       <c r="H423" s="1" t="n">
+        <v>0.006662</v>
+      </c>
+      <c r="I423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="I423" s="1" t="n">
-        <v>0.006677</v>
+      <c r="J423" s="1" t="n">
+        <v>0.006662</v>
       </c>
     </row>
     <row r="424">
@@ -13584,10 +14856,13 @@
         <v>0.92</v>
       </c>
       <c r="H424" s="1" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="I424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="I424" s="1" t="n">
-        <v>0.915</v>
+      <c r="J424" s="1" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="425">
@@ -13615,9 +14890,12 @@
         <v>0.03567</v>
       </c>
       <c r="H425" s="1" t="n">
+        <v>0.03558</v>
+      </c>
+      <c r="I425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="I425" s="1" t="n">
+      <c r="J425" s="1" t="n">
         <v>0.03555</v>
       </c>
     </row>
@@ -13646,9 +14924,12 @@
         <v>1.81</v>
       </c>
       <c r="H426" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="I426" s="1" t="n">
+      <c r="J426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -13677,9 +14958,12 @@
         <v>0.12829</v>
       </c>
       <c r="H427" s="1" t="n">
+        <v>0.12776</v>
+      </c>
+      <c r="I427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="I427" s="1" t="n">
+      <c r="J427" s="1" t="n">
         <v>0.12771</v>
       </c>
     </row>
@@ -13708,9 +14992,12 @@
         <v>0.05362</v>
       </c>
       <c r="H428" s="1" t="n">
+        <v>0.05345</v>
+      </c>
+      <c r="I428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="I428" s="1" t="n">
+      <c r="J428" s="1" t="n">
         <v>0.05325</v>
       </c>
     </row>
@@ -13739,10 +15026,13 @@
         <v>1.314</v>
       </c>
       <c r="H429" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="I429" s="1" t="n">
-        <v>1.309</v>
+      <c r="J429" s="1" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="430">
@@ -13770,10 +15060,13 @@
         <v>0.07597</v>
       </c>
       <c r="H430" s="1" t="n">
+        <v>0.07527</v>
+      </c>
+      <c r="I430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="I430" s="1" t="n">
-        <v>0.07547</v>
+      <c r="J430" s="1" t="n">
+        <v>0.07527</v>
       </c>
     </row>
     <row r="431">
@@ -13801,10 +15094,13 @@
         <v>0.1637</v>
       </c>
       <c r="H431" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="I431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="I431" s="1" t="n">
-        <v>0.1636</v>
+      <c r="J431" s="1" t="n">
+        <v>0.1614</v>
       </c>
     </row>
     <row r="432">
@@ -13832,10 +15128,13 @@
         <v>1.461</v>
       </c>
       <c r="H432" s="1" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="I432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="I432" s="1" t="n">
-        <v>1.456</v>
+      <c r="J432" s="1" t="n">
+        <v>1.453</v>
       </c>
     </row>
     <row r="433">
@@ -13863,10 +15162,13 @@
         <v>3.311</v>
       </c>
       <c r="H433" s="1" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="I433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="I433" s="1" t="n">
-        <v>3.306</v>
+      <c r="J433" s="1" t="n">
+        <v>3.291</v>
       </c>
     </row>
     <row r="434">
@@ -13894,9 +15196,12 @@
         <v>0.1802</v>
       </c>
       <c r="H434" s="1" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="I434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="I434" s="1" t="n">
+      <c r="J434" s="1" t="n">
         <v>0.1792</v>
       </c>
     </row>
@@ -13925,10 +15230,13 @@
         <v>0.008663000000000001</v>
       </c>
       <c r="H435" s="1" t="n">
+        <v>0.008616</v>
+      </c>
+      <c r="I435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="I435" s="1" t="n">
-        <v>0.00864</v>
+      <c r="J435" s="1" t="n">
+        <v>0.008616</v>
       </c>
     </row>
     <row r="436">
@@ -13956,9 +15264,12 @@
         <v>0.2861</v>
       </c>
       <c r="H436" s="1" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="I436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="I436" s="1" t="n">
+      <c r="J436" s="1" t="n">
         <v>0.2841</v>
       </c>
     </row>
@@ -13987,9 +15298,12 @@
         <v>0.03873</v>
       </c>
       <c r="H437" s="1" t="n">
-        <v>0.03873</v>
+        <v>0.03905</v>
       </c>
       <c r="I437" s="1" t="n">
+        <v>0.03905</v>
+      </c>
+      <c r="J437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -14018,10 +15332,13 @@
         <v>0.02464</v>
       </c>
       <c r="H438" s="1" t="n">
+        <v>0.02438</v>
+      </c>
+      <c r="I438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="I438" s="1" t="n">
-        <v>0.02444</v>
+      <c r="J438" s="1" t="n">
+        <v>0.02438</v>
       </c>
     </row>
     <row r="439">
@@ -14049,9 +15366,12 @@
         <v>0.04412</v>
       </c>
       <c r="H439" s="1" t="n">
+        <v>0.04409</v>
+      </c>
+      <c r="I439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="I439" s="1" t="n">
+      <c r="J439" s="1" t="n">
         <v>0.04405</v>
       </c>
     </row>
@@ -14080,9 +15400,12 @@
         <v>0.0005231</v>
       </c>
       <c r="H440" s="1" t="n">
+        <v>0.0005233</v>
+      </c>
+      <c r="I440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="I440" s="1" t="n">
+      <c r="J440" s="1" t="n">
         <v>0.0005212</v>
       </c>
     </row>
@@ -14111,9 +15434,12 @@
         <v>0.04403</v>
       </c>
       <c r="H441" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="I441" s="1" t="n">
         <v>0.04428</v>
       </c>
-      <c r="I441" s="1" t="n">
+      <c r="J441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -14142,10 +15468,13 @@
         <v>0.000413</v>
       </c>
       <c r="H442" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="I442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="I442" s="1" t="n">
-        <v>0.000413</v>
+      <c r="J442" s="1" t="n">
+        <v>0.000412</v>
       </c>
     </row>
     <row r="443">
@@ -14173,10 +15502,13 @@
         <v>0.09689</v>
       </c>
       <c r="H443" s="1" t="n">
+        <v>0.09604</v>
+      </c>
+      <c r="I443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="I443" s="1" t="n">
-        <v>0.0961</v>
+      <c r="J443" s="1" t="n">
+        <v>0.09604</v>
       </c>
     </row>
     <row r="444">
@@ -14204,9 +15536,12 @@
         <v>2.305</v>
       </c>
       <c r="H444" s="1" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="I444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="I444" s="1" t="n">
+      <c r="J444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -14235,9 +15570,12 @@
         <v>0.2741</v>
       </c>
       <c r="H445" s="1" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="I445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="I445" s="1" t="n">
+      <c r="J445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -14266,10 +15604,13 @@
         <v>0.0007526</v>
       </c>
       <c r="H446" s="1" t="n">
+        <v>0.000748</v>
+      </c>
+      <c r="I446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="I446" s="1" t="n">
-        <v>0.0007521</v>
+      <c r="J446" s="1" t="n">
+        <v>0.000748</v>
       </c>
     </row>
     <row r="447">
@@ -14297,10 +15638,13 @@
         <v>0.03838</v>
       </c>
       <c r="H447" s="1" t="n">
+        <v>0.03835</v>
+      </c>
+      <c r="I447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="I447" s="1" t="n">
-        <v>0.03838</v>
+      <c r="J447" s="1" t="n">
+        <v>0.03835</v>
       </c>
     </row>
     <row r="448">
@@ -14328,9 +15672,12 @@
         <v>0.1772</v>
       </c>
       <c r="H448" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="I448" s="1" t="n">
         <v>0.1773</v>
       </c>
-      <c r="I448" s="1" t="n">
+      <c r="J448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -14359,9 +15706,12 @@
         <v>0.04299</v>
       </c>
       <c r="H449" s="1" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="I449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="I449" s="1" t="n">
+      <c r="J449" s="1" t="n">
         <v>0.0427</v>
       </c>
     </row>
@@ -14390,10 +15740,13 @@
         <v>0.000165</v>
       </c>
       <c r="H450" s="1" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="I450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="I450" s="1" t="n">
-        <v>0.0001641</v>
+      <c r="J450" s="1" t="n">
+        <v>0.000164</v>
       </c>
     </row>
     <row r="451">
@@ -14421,10 +15774,13 @@
         <v>0.03753</v>
       </c>
       <c r="H451" s="1" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="I451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="I451" s="1" t="n">
-        <v>0.03751</v>
+      <c r="J451" s="1" t="n">
+        <v>0.0375</v>
       </c>
     </row>
     <row r="452">
@@ -14452,10 +15808,13 @@
         <v>0.00996</v>
       </c>
       <c r="H452" s="1" t="n">
+        <v>0.009860000000000001</v>
+      </c>
+      <c r="I452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="I452" s="1" t="n">
-        <v>0.009939999999999999</v>
+      <c r="J452" s="1" t="n">
+        <v>0.009860000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -14483,9 +15842,12 @@
         <v>0.06816</v>
       </c>
       <c r="H453" s="1" t="n">
+        <v>0.06793</v>
+      </c>
+      <c r="I453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="I453" s="1" t="n">
+      <c r="J453" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -14514,10 +15876,13 @@
         <v>0.007586</v>
       </c>
       <c r="H454" s="1" t="n">
+        <v>0.007524</v>
+      </c>
+      <c r="I454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="I454" s="1" t="n">
-        <v>0.007541</v>
+      <c r="J454" s="1" t="n">
+        <v>0.007524</v>
       </c>
     </row>
     <row r="455">
@@ -14545,10 +15910,13 @@
         <v>0.00337</v>
       </c>
       <c r="H455" s="1" t="n">
+        <v>0.003337</v>
+      </c>
+      <c r="I455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="I455" s="1" t="n">
-        <v>0.003362</v>
+      <c r="J455" s="1" t="n">
+        <v>0.003337</v>
       </c>
     </row>
     <row r="456">
@@ -14576,9 +15944,12 @@
         <v>0.001875</v>
       </c>
       <c r="H456" s="1" t="n">
+        <v>0.001858</v>
+      </c>
+      <c r="I456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="I456" s="1" t="n">
+      <c r="J456" s="1" t="n">
         <v>0.001854</v>
       </c>
     </row>
@@ -14607,10 +15978,13 @@
         <v>0.0001765</v>
       </c>
       <c r="H457" s="1" t="n">
+        <v>0.0001756</v>
+      </c>
+      <c r="I457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="I457" s="1" t="n">
-        <v>0.0001758</v>
+      <c r="J457" s="1" t="n">
+        <v>0.0001756</v>
       </c>
     </row>
     <row r="458">
@@ -14638,9 +16012,12 @@
         <v>0.0003916</v>
       </c>
       <c r="H458" s="1" t="n">
+        <v>0.0003915</v>
+      </c>
+      <c r="I458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="I458" s="1" t="n">
+      <c r="J458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -14669,9 +16046,12 @@
         <v>0.01413</v>
       </c>
       <c r="H459" s="1" t="n">
+        <v>0.01406</v>
+      </c>
+      <c r="I459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="I459" s="1" t="n">
+      <c r="J459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -14700,9 +16080,12 @@
         <v>0.04553</v>
       </c>
       <c r="H460" s="1" t="n">
+        <v>0.04546</v>
+      </c>
+      <c r="I460" s="1" t="n">
         <v>0.04559</v>
       </c>
-      <c r="I460" s="1" t="n">
+      <c r="J460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -14731,9 +16114,12 @@
         <v>0.2839</v>
       </c>
       <c r="H461" s="1" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="I461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="I461" s="1" t="n">
+      <c r="J461" s="1" t="n">
         <v>0.2822</v>
       </c>
     </row>
@@ -14762,9 +16148,12 @@
         <v>0.006312</v>
       </c>
       <c r="H462" s="1" t="n">
+        <v>0.006273</v>
+      </c>
+      <c r="I462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="I462" s="1" t="n">
+      <c r="J462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -14793,9 +16182,12 @@
         <v>0.007086</v>
       </c>
       <c r="H463" s="1" t="n">
+        <v>0.007047</v>
+      </c>
+      <c r="I463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="I463" s="1" t="n">
+      <c r="J463" s="1" t="n">
         <v>0.00704</v>
       </c>
     </row>
@@ -14824,9 +16216,12 @@
         <v>0.288</v>
       </c>
       <c r="H464" s="1" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="I464" s="1" t="n">
         <v>0.288</v>
       </c>
-      <c r="I464" s="1" t="n">
+      <c r="J464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -14855,9 +16250,12 @@
         <v>0.08183</v>
       </c>
       <c r="H465" s="1" t="n">
+        <v>0.08109</v>
+      </c>
+      <c r="I465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="I465" s="1" t="n">
+      <c r="J465" s="1" t="n">
         <v>0.08078</v>
       </c>
     </row>
@@ -14886,9 +16284,12 @@
         <v>0.6368</v>
       </c>
       <c r="H466" s="1" t="n">
+        <v>0.6335</v>
+      </c>
+      <c r="I466" s="1" t="n">
         <v>0.6368</v>
       </c>
-      <c r="I466" s="1" t="n">
+      <c r="J466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -14917,9 +16318,12 @@
         <v>0.01499</v>
       </c>
       <c r="H467" s="1" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="I467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="I467" s="1" t="n">
+      <c r="J467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -14948,10 +16352,13 @@
         <v>0.03458</v>
       </c>
       <c r="H468" s="1" t="n">
+        <v>0.03439</v>
+      </c>
+      <c r="I468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="I468" s="1" t="n">
-        <v>0.03448</v>
+      <c r="J468" s="1" t="n">
+        <v>0.03439</v>
       </c>
     </row>
     <row r="469">
@@ -14979,10 +16386,13 @@
         <v>0.165</v>
       </c>
       <c r="H469" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="I469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="I469" s="1" t="n">
-        <v>0.1644</v>
+      <c r="J469" s="1" t="n">
+        <v>0.1637</v>
       </c>
     </row>
     <row r="470">
@@ -15010,10 +16420,13 @@
         <v>0.415</v>
       </c>
       <c r="H470" s="1" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="I470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="I470" s="1" t="n">
-        <v>0.4123</v>
+      <c r="J470" s="1" t="n">
+        <v>0.4121</v>
       </c>
     </row>
     <row r="471">
@@ -15041,10 +16454,13 @@
         <v>0.07004000000000001</v>
       </c>
       <c r="H471" s="1" t="n">
+        <v>0.06965</v>
+      </c>
+      <c r="I471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="I471" s="1" t="n">
-        <v>0.06975000000000001</v>
+      <c r="J471" s="1" t="n">
+        <v>0.06965</v>
       </c>
     </row>
     <row r="472">
@@ -15072,9 +16488,12 @@
         <v>0.06713</v>
       </c>
       <c r="H472" s="1" t="n">
+        <v>0.06721000000000001</v>
+      </c>
+      <c r="I472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="I472" s="1" t="n">
+      <c r="J472" s="1" t="n">
         <v>0.06688</v>
       </c>
     </row>
@@ -15103,10 +16522,13 @@
         <v>0.01645</v>
       </c>
       <c r="H473" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="I473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="I473" s="1" t="n">
-        <v>0.0164</v>
+      <c r="J473" s="1" t="n">
+        <v>0.01632</v>
       </c>
     </row>
     <row r="474">
@@ -15134,10 +16556,13 @@
         <v>0.2091</v>
       </c>
       <c r="H474" s="1" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="I474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="I474" s="1" t="n">
-        <v>0.2091</v>
+      <c r="J474" s="1" t="n">
+        <v>0.2075</v>
       </c>
     </row>
     <row r="475">
@@ -15165,9 +16590,12 @@
         <v>0.04241</v>
       </c>
       <c r="H475" s="1" t="n">
+        <v>0.04229</v>
+      </c>
+      <c r="I475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="I475" s="1" t="n">
+      <c r="J475" s="1" t="n">
         <v>0.04202</v>
       </c>
     </row>
@@ -15196,10 +16624,13 @@
         <v>1.577</v>
       </c>
       <c r="H476" s="1" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="I476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="I476" s="1" t="n">
-        <v>1.57</v>
+      <c r="J476" s="1" t="n">
+        <v>1.568</v>
       </c>
     </row>
     <row r="477">
@@ -15227,9 +16658,12 @@
         <v>0.1008</v>
       </c>
       <c r="H477" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="I477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="I477" s="1" t="n">
+      <c r="J477" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -15258,10 +16692,13 @@
         <v>0.00116</v>
       </c>
       <c r="H478" s="1" t="n">
+        <v>0.001154</v>
+      </c>
+      <c r="I478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="I478" s="1" t="n">
-        <v>0.001155</v>
+      <c r="J478" s="1" t="n">
+        <v>0.001154</v>
       </c>
     </row>
     <row r="479">
@@ -15289,9 +16726,12 @@
         <v>0.1473</v>
       </c>
       <c r="H479" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="I479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="I479" s="1" t="n">
+      <c r="J479" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -15320,9 +16760,12 @@
         <v>0.001733</v>
       </c>
       <c r="H480" s="1" t="n">
+        <v>0.001725</v>
+      </c>
+      <c r="I480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="I480" s="1" t="n">
+      <c r="J480" s="1" t="n">
         <v>0.001722</v>
       </c>
     </row>
@@ -15351,10 +16794,13 @@
         <v>0.921</v>
       </c>
       <c r="H481" s="1" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="I481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="I481" s="1" t="n">
-        <v>0.915</v>
+      <c r="J481" s="1" t="n">
+        <v>0.913</v>
       </c>
     </row>
     <row r="482">
@@ -15382,10 +16828,13 @@
         <v>0.13419</v>
       </c>
       <c r="H482" s="1" t="n">
+        <v>0.13367</v>
+      </c>
+      <c r="I482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="I482" s="1" t="n">
-        <v>0.13419</v>
+      <c r="J482" s="1" t="n">
+        <v>0.13367</v>
       </c>
     </row>
     <row r="483">
@@ -15413,10 +16862,13 @@
         <v>0.04063</v>
       </c>
       <c r="H483" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="I483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="I483" s="1" t="n">
-        <v>0.04048</v>
+      <c r="J483" s="1" t="n">
+        <v>0.04035</v>
       </c>
     </row>
     <row r="484">
@@ -15444,9 +16896,12 @@
         <v>0.3072</v>
       </c>
       <c r="H484" s="1" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="I484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="I484" s="1" t="n">
+      <c r="J484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -15475,9 +16930,12 @@
         <v>0.05709</v>
       </c>
       <c r="H485" s="1" t="n">
+        <v>0.05692</v>
+      </c>
+      <c r="I485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="I485" s="1" t="n">
+      <c r="J485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -15506,9 +16964,12 @@
         <v>0.001579</v>
       </c>
       <c r="H486" s="1" t="n">
+        <v>0.001569</v>
+      </c>
+      <c r="I486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="I486" s="1" t="n">
+      <c r="J486" s="1" t="n">
         <v>0.001569</v>
       </c>
     </row>
@@ -15537,9 +16998,12 @@
         <v>0.06766999999999999</v>
       </c>
       <c r="H487" s="1" t="n">
+        <v>0.06741</v>
+      </c>
+      <c r="I487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="I487" s="1" t="n">
+      <c r="J487" s="1" t="n">
         <v>0.06716</v>
       </c>
     </row>
@@ -15568,10 +17032,13 @@
         <v>0.1947</v>
       </c>
       <c r="H488" s="1" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="I488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="I488" s="1" t="n">
-        <v>0.1936</v>
+      <c r="J488" s="1" t="n">
+        <v>0.1935</v>
       </c>
     </row>
     <row r="489">
@@ -15599,10 +17066,13 @@
         <v>0.04826</v>
       </c>
       <c r="H489" s="1" t="n">
+        <v>0.04792</v>
+      </c>
+      <c r="I489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="I489" s="1" t="n">
-        <v>0.04804</v>
+      <c r="J489" s="1" t="n">
+        <v>0.04792</v>
       </c>
     </row>
     <row r="490">
@@ -15630,9 +17100,12 @@
         <v>0.1401</v>
       </c>
       <c r="H490" s="1" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="I490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="I490" s="1" t="n">
+      <c r="J490" s="1" t="n">
         <v>0.139</v>
       </c>
     </row>
@@ -15661,9 +17134,12 @@
         <v>0.02261</v>
       </c>
       <c r="H491" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="I491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="I491" s="1" t="n">
+      <c r="J491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -15692,9 +17168,12 @@
         <v>0.007901999999999999</v>
       </c>
       <c r="H492" s="1" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="I492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="I492" s="1" t="n">
+      <c r="J492" s="1" t="n">
         <v>0.007825</v>
       </c>
     </row>
@@ -15723,10 +17202,13 @@
         <v>0.0005992</v>
       </c>
       <c r="H493" s="1" t="n">
+        <v>0.0005949</v>
+      </c>
+      <c r="I493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="I493" s="1" t="n">
-        <v>0.0005952</v>
+      <c r="J493" s="1" t="n">
+        <v>0.0005949</v>
       </c>
     </row>
     <row r="494">
@@ -15754,9 +17236,12 @@
         <v>3.037</v>
       </c>
       <c r="H494" s="1" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="I494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="I494" s="1" t="n">
+      <c r="J494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -15785,10 +17270,13 @@
         <v>0.05123</v>
       </c>
       <c r="H495" s="1" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="I495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="I495" s="1" t="n">
-        <v>0.05085</v>
+      <c r="J495" s="1" t="n">
+        <v>0.05082</v>
       </c>
     </row>
     <row r="496">
@@ -15816,10 +17304,13 @@
         <v>0.006854</v>
       </c>
       <c r="H496" s="1" t="n">
+        <v>0.006802</v>
+      </c>
+      <c r="I496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="I496" s="1" t="n">
-        <v>0.006839</v>
+      <c r="J496" s="1" t="n">
+        <v>0.006802</v>
       </c>
     </row>
     <row r="497">
@@ -15847,9 +17338,12 @@
         <v>1.308</v>
       </c>
       <c r="H497" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="I497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="I497" s="1" t="n">
+      <c r="J497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -15878,10 +17372,13 @@
         <v>0.03984</v>
       </c>
       <c r="H498" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="I498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="I498" s="1" t="n">
-        <v>0.03984</v>
+      <c r="J498" s="1" t="n">
+        <v>0.03964</v>
       </c>
     </row>
     <row r="499">
@@ -15909,10 +17406,13 @@
         <v>0.04196</v>
       </c>
       <c r="H499" s="1" t="n">
+        <v>0.04166</v>
+      </c>
+      <c r="I499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="I499" s="1" t="n">
-        <v>0.04186</v>
+      <c r="J499" s="1" t="n">
+        <v>0.04166</v>
       </c>
     </row>
     <row r="500">
@@ -15940,9 +17440,12 @@
         <v>0.00549</v>
       </c>
       <c r="H500" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="I500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="I500" s="1" t="n">
+      <c r="J500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -15971,10 +17474,13 @@
         <v>0.0364</v>
       </c>
       <c r="H501" s="1" t="n">
+        <v>0.03617</v>
+      </c>
+      <c r="I501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="I501" s="1" t="n">
-        <v>0.03625</v>
+      <c r="J501" s="1" t="n">
+        <v>0.03617</v>
       </c>
     </row>
     <row r="502">
@@ -16002,9 +17508,12 @@
         <v>0.07342</v>
       </c>
       <c r="H502" s="1" t="n">
+        <v>0.07321999999999999</v>
+      </c>
+      <c r="I502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="I502" s="1" t="n">
+      <c r="J502" s="1" t="n">
         <v>0.07321</v>
       </c>
     </row>
@@ -16033,10 +17542,13 @@
         <v>0.0007548</v>
       </c>
       <c r="H503" s="1" t="n">
+        <v>0.0007497</v>
+      </c>
+      <c r="I503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="I503" s="1" t="n">
-        <v>0.0007499</v>
+      <c r="J503" s="1" t="n">
+        <v>0.0007497</v>
       </c>
     </row>
     <row r="504">
@@ -16064,9 +17576,12 @@
         <v>0.015976</v>
       </c>
       <c r="H504" s="1" t="n">
+        <v>0.015977</v>
+      </c>
+      <c r="I504" s="1" t="n">
         <v>0.016003</v>
       </c>
-      <c r="I504" s="1" t="n">
+      <c r="J504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -16095,10 +17610,13 @@
         <v>0.00712</v>
       </c>
       <c r="H505" s="1" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="I505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="I505" s="1" t="n">
-        <v>0.00709</v>
+      <c r="J505" s="1" t="n">
+        <v>0.00707</v>
       </c>
     </row>
     <row r="506">
@@ -16126,9 +17644,12 @@
         <v>0.0255</v>
       </c>
       <c r="H506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="I506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="I506" s="1" t="n">
+      <c r="J506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -16157,9 +17678,12 @@
         <v>0.001358</v>
       </c>
       <c r="H507" s="1" t="n">
+        <v>0.001357</v>
+      </c>
+      <c r="I507" s="1" t="n">
         <v>0.001358</v>
       </c>
-      <c r="I507" s="1" t="n">
+      <c r="J507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -16188,10 +17712,13 @@
         <v>0.2834</v>
       </c>
       <c r="H508" s="1" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="I508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="I508" s="1" t="n">
-        <v>0.2821</v>
+      <c r="J508" s="1" t="n">
+        <v>0.2816</v>
       </c>
     </row>
     <row r="509">
@@ -16219,10 +17746,13 @@
         <v>0.1329</v>
       </c>
       <c r="H509" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="I509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="I509" s="1" t="n">
-        <v>0.1323</v>
+      <c r="J509" s="1" t="n">
+        <v>0.132</v>
       </c>
     </row>
     <row r="510">
@@ -16250,9 +17780,12 @@
         <v>0.04972</v>
       </c>
       <c r="H510" s="1" t="n">
+        <v>0.04934</v>
+      </c>
+      <c r="I510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="I510" s="1" t="n">
+      <c r="J510" s="1" t="n">
         <v>0.04932</v>
       </c>
     </row>
@@ -16281,9 +17814,12 @@
         <v>0.00278</v>
       </c>
       <c r="H511" s="1" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="I511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="I511" s="1" t="n">
+      <c r="J511" s="1" t="n">
         <v>0.00275</v>
       </c>
     </row>
@@ -16312,9 +17848,12 @@
         <v>0.015426</v>
       </c>
       <c r="H512" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="I512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="I512" s="1" t="n">
+      <c r="J512" s="1" t="n">
         <v>0.015351</v>
       </c>
     </row>
@@ -16343,10 +17882,13 @@
         <v>0.6948</v>
       </c>
       <c r="H513" s="1" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="I513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="I513" s="1" t="n">
-        <v>0.6933</v>
+      <c r="J513" s="1" t="n">
+        <v>0.6925</v>
       </c>
     </row>
     <row r="514">
@@ -16374,9 +17916,12 @@
         <v>0.004578</v>
       </c>
       <c r="H514" s="1" t="n">
+        <v>0.00456</v>
+      </c>
+      <c r="I514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="I514" s="1" t="n">
+      <c r="J514" s="1" t="n">
         <v>0.004534</v>
       </c>
     </row>
@@ -16405,9 +17950,12 @@
         <v>0.005057</v>
       </c>
       <c r="H515" s="1" t="n">
+        <v>0.005037</v>
+      </c>
+      <c r="I515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="I515" s="1" t="n">
+      <c r="J515" s="1" t="n">
         <v>0.005037</v>
       </c>
     </row>
@@ -16436,10 +17984,13 @@
         <v>0.06356000000000001</v>
       </c>
       <c r="H516" s="1" t="n">
+        <v>0.06340999999999999</v>
+      </c>
+      <c r="I516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="I516" s="1" t="n">
-        <v>0.06353</v>
+      <c r="J516" s="1" t="n">
+        <v>0.06340999999999999</v>
       </c>
     </row>
     <row r="517">
@@ -16467,9 +18018,12 @@
         <v>0.06504</v>
       </c>
       <c r="H517" s="1" t="n">
+        <v>0.06476999999999999</v>
+      </c>
+      <c r="I517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="I517" s="1" t="n">
+      <c r="J517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -16498,10 +18052,13 @@
         <v>0.01216</v>
       </c>
       <c r="H518" s="1" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="I518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="I518" s="1" t="n">
-        <v>0.0121</v>
+      <c r="J518" s="1" t="n">
+        <v>0.01206</v>
       </c>
     </row>
     <row r="519">
@@ -16529,9 +18086,12 @@
         <v>0.04781</v>
       </c>
       <c r="H519" s="1" t="n">
+        <v>0.04772</v>
+      </c>
+      <c r="I519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="I519" s="1" t="n">
+      <c r="J519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -16560,9 +18120,12 @@
         <v>0.04411</v>
       </c>
       <c r="H520" s="1" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="I520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="I520" s="1" t="n">
+      <c r="J520" s="1" t="n">
         <v>0.04384</v>
       </c>
     </row>
@@ -16591,10 +18154,13 @@
         <v>0.008598</v>
       </c>
       <c r="H521" s="1" t="n">
+        <v>0.00851</v>
+      </c>
+      <c r="I521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="I521" s="1" t="n">
-        <v>0.008552000000000001</v>
+      <c r="J521" s="1" t="n">
+        <v>0.00851</v>
       </c>
     </row>
     <row r="522">
@@ -16622,10 +18188,13 @@
         <v>0.08910999999999999</v>
       </c>
       <c r="H522" s="1" t="n">
+        <v>0.08906</v>
+      </c>
+      <c r="I522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="I522" s="1" t="n">
-        <v>0.08910999999999999</v>
+      <c r="J522" s="1" t="n">
+        <v>0.08906</v>
       </c>
     </row>
     <row r="523">
@@ -16653,10 +18222,13 @@
         <v>0.006492</v>
       </c>
       <c r="H523" s="1" t="n">
+        <v>0.006453</v>
+      </c>
+      <c r="I523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="I523" s="1" t="n">
-        <v>0.00646</v>
+      <c r="J523" s="1" t="n">
+        <v>0.006453</v>
       </c>
     </row>
     <row r="524">
@@ -16684,10 +18256,13 @@
         <v>0.01667</v>
       </c>
       <c r="H524" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="I524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="I524" s="1" t="n">
-        <v>0.01662</v>
+      <c r="J524" s="1" t="n">
+        <v>0.01656</v>
       </c>
     </row>
     <row r="525">
@@ -16715,10 +18290,13 @@
         <v>0.01801</v>
       </c>
       <c r="H525" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="I525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="I525" s="1" t="n">
-        <v>0.01801</v>
+      <c r="J525" s="1" t="n">
+        <v>0.01787</v>
       </c>
     </row>
     <row r="526">
@@ -16746,10 +18324,13 @@
         <v>0.07951999999999999</v>
       </c>
       <c r="H526" s="1" t="n">
+        <v>0.07913000000000001</v>
+      </c>
+      <c r="I526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="I526" s="1" t="n">
-        <v>0.07917</v>
+      <c r="J526" s="1" t="n">
+        <v>0.07913000000000001</v>
       </c>
     </row>
     <row r="527">
@@ -16777,10 +18358,13 @@
         <v>0.01636</v>
       </c>
       <c r="H527" s="1" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="I527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="I527" s="1" t="n">
-        <v>0.01634</v>
+      <c r="J527" s="1" t="n">
+        <v>0.01618</v>
       </c>
     </row>
     <row r="528">
@@ -16808,9 +18392,12 @@
         <v>0.004191</v>
       </c>
       <c r="H528" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="I528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="I528" s="1" t="n">
+      <c r="J528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -16839,9 +18426,12 @@
         <v>0.003739</v>
       </c>
       <c r="H529" s="1" t="n">
+        <v>0.003705</v>
+      </c>
+      <c r="I529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="I529" s="1" t="n">
+      <c r="J529" s="1" t="n">
         <v>0.003698</v>
       </c>
     </row>
@@ -16870,9 +18460,12 @@
         <v>1.32</v>
       </c>
       <c r="H530" s="1" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="I530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="I530" s="1" t="n">
+      <c r="J530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -16901,9 +18494,12 @@
         <v>0.494</v>
       </c>
       <c r="H531" s="1" t="n">
+        <v>0.4917</v>
+      </c>
+      <c r="I531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="I531" s="1" t="n">
+      <c r="J531" s="1" t="n">
         <v>0.4912</v>
       </c>
     </row>
@@ -16932,9 +18528,12 @@
         <v>0.03091</v>
       </c>
       <c r="H532" s="1" t="n">
+        <v>0.03074</v>
+      </c>
+      <c r="I532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="I532" s="1" t="n">
+      <c r="J532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -16963,10 +18562,13 @@
         <v>0.1536</v>
       </c>
       <c r="H533" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="I533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="I533" s="1" t="n">
-        <v>0.1532</v>
+      <c r="J533" s="1" t="n">
+        <v>0.153</v>
       </c>
     </row>
     <row r="534">
@@ -16994,9 +18596,12 @@
         <v>0.05423</v>
       </c>
       <c r="H534" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="I534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="I534" s="1" t="n">
+      <c r="J534" s="1" t="n">
         <v>0.05388</v>
       </c>
     </row>
@@ -17025,9 +18630,12 @@
         <v>0.01509</v>
       </c>
       <c r="H535" s="1" t="n">
+        <v>0.01503</v>
+      </c>
+      <c r="I535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="I535" s="1" t="n">
+      <c r="J535" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -17056,9 +18664,12 @@
         <v>0.05879</v>
       </c>
       <c r="H536" s="1" t="n">
+        <v>0.05865</v>
+      </c>
+      <c r="I536" s="1" t="n">
         <v>0.05879</v>
       </c>
-      <c r="I536" s="1" t="n">
+      <c r="J536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -17087,10 +18698,13 @@
         <v>0.055</v>
       </c>
       <c r="H537" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="I537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="I537" s="1" t="n">
-        <v>0.05495</v>
+      <c r="J537" s="1" t="n">
+        <v>0.05488</v>
       </c>
     </row>
     <row r="538">
@@ -17118,9 +18732,12 @@
         <v>0.1076</v>
       </c>
       <c r="H538" s="1" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="I538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="I538" s="1" t="n">
+      <c r="J538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -17149,10 +18766,13 @@
         <v>0.01294</v>
       </c>
       <c r="H539" s="1" t="n">
+        <v>0.01281</v>
+      </c>
+      <c r="I539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="I539" s="1" t="n">
-        <v>0.01284</v>
+      <c r="J539" s="1" t="n">
+        <v>0.01281</v>
       </c>
     </row>
     <row r="540">
@@ -17180,10 +18800,13 @@
         <v>0.1763</v>
       </c>
       <c r="H540" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="I540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="I540" s="1" t="n">
-        <v>0.175</v>
+      <c r="J540" s="1" t="n">
+        <v>0.1749</v>
       </c>
     </row>
     <row r="541">
@@ -17211,10 +18834,13 @@
         <v>0.1237</v>
       </c>
       <c r="H541" s="1" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="I541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="I541" s="1" t="n">
-        <v>0.1231</v>
+      <c r="J541" s="1" t="n">
+        <v>0.1227</v>
       </c>
     </row>
     <row r="542">
@@ -17242,9 +18868,12 @@
         <v>0.02507</v>
       </c>
       <c r="H542" s="1" t="n">
+        <v>0.02493</v>
+      </c>
+      <c r="I542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="I542" s="1" t="n">
+      <c r="J542" s="1" t="n">
         <v>0.02489</v>
       </c>
     </row>
@@ -17273,9 +18902,12 @@
         <v>0.059</v>
       </c>
       <c r="H543" s="1" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="I543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="I543" s="1" t="n">
+      <c r="J543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N543"/>
+  <dimension ref="A1:O543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -431,8 +431,9 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,10 +499,15 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>price_02:45</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -547,9 +553,12 @@
         <v>71177.5</v>
       </c>
       <c r="M2" s="1" t="n">
+        <v>71212.7</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="O2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -593,9 +602,12 @@
         <v>2104.28</v>
       </c>
       <c r="M3" s="1" t="n">
+        <v>2104.83</v>
+      </c>
+      <c r="N3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="O3" s="1" t="n">
         <v>2102.04</v>
       </c>
     </row>
@@ -639,9 +651,12 @@
         <v>88.86</v>
       </c>
       <c r="M4" s="1" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>88.81999999999999</v>
       </c>
     </row>
@@ -685,9 +700,12 @@
         <v>3.792</v>
       </c>
       <c r="M5" s="1" t="n">
+        <v>3.818</v>
+      </c>
+      <c r="N5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -731,9 +749,12 @@
         <v>1.3962</v>
       </c>
       <c r="M6" s="1" t="n">
+        <v>1.3996</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -777,9 +798,12 @@
         <v>0.09623</v>
       </c>
       <c r="M7" s="1" t="n">
+        <v>0.09612</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.09601</v>
       </c>
     </row>
@@ -823,9 +847,12 @@
         <v>0.014636</v>
       </c>
       <c r="M8" s="1" t="n">
+        <v>0.014471</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="O8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -869,9 +896,12 @@
         <v>657.14</v>
       </c>
       <c r="M9" s="1" t="n">
+        <v>657.99</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -915,9 +945,12 @@
         <v>20.23</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>20.091</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>20.23</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="O10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -961,9 +994,12 @@
         <v>0.0034139</v>
       </c>
       <c r="M11" s="1" t="n">
+        <v>0.0034123</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="O11" s="1" t="n">
         <v>0.0034117</v>
       </c>
     </row>
@@ -1007,9 +1043,12 @@
         <v>36.704</v>
       </c>
       <c r="M12" s="1" t="n">
+        <v>36.596</v>
+      </c>
+      <c r="N12" s="1" t="n">
         <v>36.704</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="O12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1053,9 +1092,12 @@
         <v>213.8</v>
       </c>
       <c r="M13" s="1" t="n">
+        <v>214.65</v>
+      </c>
+      <c r="N13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="O13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1099,9 +1141,12 @@
         <v>0.0011147</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>0.0011238</v>
+      </c>
+      <c r="N14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="O14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1145,9 +1190,12 @@
         <v>0.30062</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.30062</v>
+        <v>0.30332</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1191,9 +1239,12 @@
         <v>232.27</v>
       </c>
       <c r="M16" s="1" t="n">
+        <v>231.81</v>
+      </c>
+      <c r="N16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="O16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1237,9 +1288,12 @@
         <v>1.0014</v>
       </c>
       <c r="M17" s="1" t="n">
+        <v>1.0032</v>
+      </c>
+      <c r="N17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="O17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1283,9 +1337,12 @@
         <v>0.2673</v>
       </c>
       <c r="M18" s="1" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="N18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="O18" s="1" t="n">
         <v>0.2671</v>
       </c>
     </row>
@@ -1329,9 +1386,12 @@
         <v>9.776</v>
       </c>
       <c r="M19" s="1" t="n">
+        <v>9.802</v>
+      </c>
+      <c r="N19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="N19" s="1" t="n">
+      <c r="O19" s="1" t="n">
         <v>9.755000000000001</v>
       </c>
     </row>
@@ -1375,9 +1435,12 @@
         <v>5041.65</v>
       </c>
       <c r="M20" s="1" t="n">
+        <v>5044.51</v>
+      </c>
+      <c r="N20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="N20" s="1" t="n">
+      <c r="O20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1421,9 +1484,12 @@
         <v>463.92</v>
       </c>
       <c r="M21" s="1" t="n">
+        <v>464.45</v>
+      </c>
+      <c r="N21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="O21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1467,10 +1533,13 @@
         <v>1.4211</v>
       </c>
       <c r="M22" s="1" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="N22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="N22" s="1" t="n">
-        <v>1.4185</v>
+      <c r="O22" s="1" t="n">
+        <v>1.404</v>
       </c>
     </row>
     <row r="23">
@@ -1513,10 +1582,13 @@
         <v>1.0303</v>
       </c>
       <c r="M23" s="1" t="n">
+        <v>1.0136</v>
+      </c>
+      <c r="N23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="N23" s="1" t="n">
-        <v>1.0303</v>
+      <c r="O23" s="1" t="n">
+        <v>1.0136</v>
       </c>
     </row>
     <row r="24">
@@ -1559,9 +1631,12 @@
         <v>1.344</v>
       </c>
       <c r="M24" s="1" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="N24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="N24" s="1" t="n">
+      <c r="O24" s="1" t="n">
         <v>1.344</v>
       </c>
     </row>
@@ -1605,9 +1680,12 @@
         <v>9.153</v>
       </c>
       <c r="M25" s="1" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="N25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="N25" s="1" t="n">
+      <c r="O25" s="1" t="n">
         <v>9.140000000000001</v>
       </c>
     </row>
@@ -1651,9 +1729,12 @@
         <v>0.3735</v>
       </c>
       <c r="M26" s="1" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="N26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="N26" s="1" t="n">
+      <c r="O26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1697,9 +1778,12 @@
         <v>0.88</v>
       </c>
       <c r="M27" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="N27" s="1" t="n">
+      <c r="O27" s="1" t="n">
         <v>0.876</v>
       </c>
     </row>
@@ -1743,9 +1827,12 @@
         <v>1.826</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>1.826</v>
+        <v>1.844</v>
       </c>
       <c r="N28" s="1" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1789,9 +1876,12 @@
         <v>0.1097</v>
       </c>
       <c r="M29" s="1" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="N29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="N29" s="1" t="n">
+      <c r="O29" s="1" t="n">
         <v>0.1096</v>
       </c>
     </row>
@@ -1835,9 +1925,12 @@
         <v>0.002047</v>
       </c>
       <c r="M30" s="1" t="n">
+        <v>0.002045</v>
+      </c>
+      <c r="N30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="N30" s="1" t="n">
+      <c r="O30" s="1" t="n">
         <v>0.002045</v>
       </c>
     </row>
@@ -1881,9 +1974,12 @@
         <v>1.475</v>
       </c>
       <c r="M31" s="1" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="N31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="N31" s="1" t="n">
+      <c r="O31" s="1" t="n">
         <v>1.475</v>
       </c>
     </row>
@@ -1927,9 +2023,12 @@
         <v>0.176</v>
       </c>
       <c r="M32" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="N32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="N32" s="1" t="n">
+      <c r="O32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -1973,10 +2072,13 @@
         <v>0.1038</v>
       </c>
       <c r="M33" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="N33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="N33" s="1" t="n">
-        <v>0.1038</v>
+      <c r="O33" s="1" t="n">
+        <v>0.1037</v>
       </c>
     </row>
     <row r="34">
@@ -2019,9 +2121,12 @@
         <v>112.91</v>
       </c>
       <c r="M34" s="1" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="N34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="N34" s="1" t="n">
+      <c r="O34" s="1" t="n">
         <v>112.91</v>
       </c>
     </row>
@@ -2065,10 +2170,13 @@
         <v>6.715</v>
       </c>
       <c r="M35" s="1" t="n">
+        <v>6.652</v>
+      </c>
+      <c r="N35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="N35" s="1" t="n">
-        <v>6.659</v>
+      <c r="O35" s="1" t="n">
+        <v>6.652</v>
       </c>
     </row>
     <row r="36">
@@ -2111,9 +2219,12 @@
         <v>0.017135</v>
       </c>
       <c r="M36" s="1" t="n">
+        <v>0.017343</v>
+      </c>
+      <c r="N36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="N36" s="1" t="n">
+      <c r="O36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2157,9 +2268,12 @@
         <v>0.3606</v>
       </c>
       <c r="M37" s="1" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="N37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="N37" s="1" t="n">
+      <c r="O37" s="1" t="n">
         <v>0.3606</v>
       </c>
     </row>
@@ -2203,9 +2317,12 @@
         <v>55.41</v>
       </c>
       <c r="M38" s="1" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="N38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="N38" s="1" t="n">
+      <c r="O38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2249,9 +2366,12 @@
         <v>0.59628</v>
       </c>
       <c r="M39" s="1" t="n">
+        <v>0.59515</v>
+      </c>
+      <c r="N39" s="1" t="n">
         <v>0.60089</v>
       </c>
-      <c r="N39" s="1" t="n">
+      <c r="O39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2295,9 +2415,12 @@
         <v>4.028</v>
       </c>
       <c r="M40" s="1" t="n">
+        <v>4.037</v>
+      </c>
+      <c r="N40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="N40" s="1" t="n">
+      <c r="O40" s="1" t="n">
         <v>4.028</v>
       </c>
     </row>
@@ -2341,9 +2464,12 @@
         <v>0.0513</v>
       </c>
       <c r="M41" s="1" t="n">
+        <v>0.05077</v>
+      </c>
+      <c r="N41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="N41" s="1" t="n">
+      <c r="O41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2387,9 +2513,12 @@
         <v>0.7033</v>
       </c>
       <c r="M42" s="1" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="N42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="N42" s="1" t="n">
+      <c r="O42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2433,10 +2562,13 @@
         <v>0.22842</v>
       </c>
       <c r="M43" s="1" t="n">
+        <v>0.22831</v>
+      </c>
+      <c r="N43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="N43" s="1" t="n">
-        <v>0.22842</v>
+      <c r="O43" s="1" t="n">
+        <v>0.22831</v>
       </c>
     </row>
     <row r="44">
@@ -2479,9 +2611,12 @@
         <v>0.35655</v>
       </c>
       <c r="M44" s="1" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="N44" s="1" t="n">
         <v>0.35655</v>
       </c>
-      <c r="N44" s="1" t="n">
+      <c r="O44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2525,9 +2660,12 @@
         <v>0.17</v>
       </c>
       <c r="M45" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="N45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="N45" s="1" t="n">
+      <c r="O45" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -2571,10 +2709,13 @@
         <v>0.026</v>
       </c>
       <c r="M46" s="1" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="N46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="N46" s="1" t="n">
-        <v>0.026</v>
+      <c r="O46" s="1" t="n">
+        <v>0.0259</v>
       </c>
     </row>
     <row r="47">
@@ -2617,9 +2758,12 @@
         <v>0.005958</v>
       </c>
       <c r="M47" s="1" t="n">
+        <v>0.005964</v>
+      </c>
+      <c r="N47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="N47" s="1" t="n">
+      <c r="O47" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -2663,9 +2807,12 @@
         <v>0.007379</v>
       </c>
       <c r="M48" s="1" t="n">
+        <v>0.007394</v>
+      </c>
+      <c r="N48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="N48" s="1" t="n">
+      <c r="O48" s="1" t="n">
         <v>0.007349</v>
       </c>
     </row>
@@ -2709,9 +2856,12 @@
         <v>0.1083</v>
       </c>
       <c r="M49" s="1" t="n">
+        <v>0.1084</v>
+      </c>
+      <c r="N49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="N49" s="1" t="n">
+      <c r="O49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -2755,9 +2905,12 @@
         <v>0.0411</v>
       </c>
       <c r="M50" s="1" t="n">
-        <v>0.04119</v>
+        <v>0.04153</v>
       </c>
       <c r="N50" s="1" t="n">
+        <v>0.04153</v>
+      </c>
+      <c r="O50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2801,9 +2954,12 @@
         <v>0.163</v>
       </c>
       <c r="M51" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="N51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="N51" s="1" t="n">
+      <c r="O51" s="1" t="n">
         <v>0.1617</v>
       </c>
     </row>
@@ -2847,9 +3003,12 @@
         <v>0.00351</v>
       </c>
       <c r="M52" s="1" t="n">
+        <v>0.00352</v>
+      </c>
+      <c r="N52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="N52" s="1" t="n">
+      <c r="O52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -2893,9 +3052,12 @@
         <v>2.634</v>
       </c>
       <c r="M53" s="1" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="N53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="N53" s="1" t="n">
+      <c r="O53" s="1" t="n">
         <v>2.622</v>
       </c>
     </row>
@@ -2939,9 +3101,12 @@
         <v>0.0062</v>
       </c>
       <c r="M54" s="1" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="N54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="N54" s="1" t="n">
+      <c r="O54" s="1" t="n">
         <v>0.006188</v>
       </c>
     </row>
@@ -2985,9 +3150,12 @@
         <v>0.02967</v>
       </c>
       <c r="M55" s="1" t="n">
+        <v>0.02948</v>
+      </c>
+      <c r="N55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="N55" s="1" t="n">
+      <c r="O55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -3031,9 +3199,12 @@
         <v>0.7363</v>
       </c>
       <c r="M56" s="1" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="N56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="N56" s="1" t="n">
+      <c r="O56" s="1" t="n">
         <v>0.7352</v>
       </c>
     </row>
@@ -3077,9 +3248,12 @@
         <v>0.1035</v>
       </c>
       <c r="M57" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="N57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="N57" s="1" t="n">
+      <c r="O57" s="1" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -3123,9 +3297,12 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M58" s="1" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="N58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="N58" s="1" t="n">
+      <c r="O58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -3169,9 +3346,12 @@
         <v>0.08744</v>
       </c>
       <c r="M59" s="1" t="n">
+        <v>0.08729000000000001</v>
+      </c>
+      <c r="N59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="N59" s="1" t="n">
+      <c r="O59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -3215,9 +3395,12 @@
         <v>0.07003</v>
       </c>
       <c r="M60" s="1" t="n">
+        <v>0.06969</v>
+      </c>
+      <c r="N60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="N60" s="1" t="n">
+      <c r="O60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -3261,9 +3444,12 @@
         <v>0.05466</v>
       </c>
       <c r="M61" s="1" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="N61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="N61" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>0.05445</v>
       </c>
     </row>
@@ -3307,9 +3493,12 @@
         <v>0.009974999999999999</v>
       </c>
       <c r="M62" s="1" t="n">
+        <v>0.010081</v>
+      </c>
+      <c r="N62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="N62" s="1" t="n">
+      <c r="O62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -3353,9 +3542,12 @@
         <v>0.2912</v>
       </c>
       <c r="M63" s="1" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="N63" s="1" t="n">
         <v>0.2912</v>
       </c>
-      <c r="N63" s="1" t="n">
+      <c r="O63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -3399,9 +3591,12 @@
         <v>0.07591000000000001</v>
       </c>
       <c r="M64" s="1" t="n">
+        <v>0.07581</v>
+      </c>
+      <c r="N64" s="1" t="n">
         <v>0.07591000000000001</v>
       </c>
-      <c r="N64" s="1" t="n">
+      <c r="O64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -3445,9 +3640,12 @@
         <v>0.3158</v>
       </c>
       <c r="M65" s="1" t="n">
-        <v>0.3169</v>
+        <v>0.3184</v>
       </c>
       <c r="N65" s="1" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="O65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -3491,9 +3689,12 @@
         <v>0.16271</v>
       </c>
       <c r="M66" s="1" t="n">
+        <v>0.16279</v>
+      </c>
+      <c r="N66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="N66" s="1" t="n">
+      <c r="O66" s="1" t="n">
         <v>0.16235</v>
       </c>
     </row>
@@ -3537,9 +3738,12 @@
         <v>0.11957</v>
       </c>
       <c r="M67" s="1" t="n">
+        <v>0.11957</v>
+      </c>
+      <c r="N67" s="1" t="n">
         <v>0.11999</v>
       </c>
-      <c r="N67" s="1" t="n">
+      <c r="O67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -3583,9 +3787,12 @@
         <v>0.0956</v>
       </c>
       <c r="M68" s="1" t="n">
+        <v>0.09568</v>
+      </c>
+      <c r="N68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="N68" s="1" t="n">
+      <c r="O68" s="1" t="n">
         <v>0.09548</v>
       </c>
     </row>
@@ -3629,9 +3836,12 @@
         <v>0.1242</v>
       </c>
       <c r="M69" s="1" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="N69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="N69" s="1" t="n">
+      <c r="O69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -3675,9 +3885,12 @@
         <v>8.523999999999999</v>
       </c>
       <c r="M70" s="1" t="n">
+        <v>8.532</v>
+      </c>
+      <c r="N70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="N70" s="1" t="n">
+      <c r="O70" s="1" t="n">
         <v>8.494</v>
       </c>
     </row>
@@ -3721,9 +3934,12 @@
         <v>0.238</v>
       </c>
       <c r="M71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="N71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="N71" s="1" t="n">
+      <c r="O71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -3767,9 +3983,12 @@
         <v>0.04992</v>
       </c>
       <c r="M72" s="1" t="n">
+        <v>0.05005</v>
+      </c>
+      <c r="N72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="N72" s="1" t="n">
+      <c r="O72" s="1" t="n">
         <v>0.04992</v>
       </c>
     </row>
@@ -3813,9 +4032,12 @@
         <v>0.05038</v>
       </c>
       <c r="M73" s="1" t="n">
+        <v>0.05044</v>
+      </c>
+      <c r="N73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="N73" s="1" t="n">
+      <c r="O73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -3859,9 +4081,12 @@
         <v>0.1255</v>
       </c>
       <c r="M74" s="1" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="N74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="N74" s="1" t="n">
+      <c r="O74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -3905,9 +4130,12 @@
         <v>0.04621</v>
       </c>
       <c r="M75" s="1" t="n">
+        <v>0.04666</v>
+      </c>
+      <c r="N75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="N75" s="1" t="n">
+      <c r="O75" s="1" t="n">
         <v>0.04621</v>
       </c>
     </row>
@@ -3951,9 +4179,12 @@
         <v>0.06698</v>
       </c>
       <c r="M76" s="1" t="n">
+        <v>0.06703000000000001</v>
+      </c>
+      <c r="N76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="N76" s="1" t="n">
+      <c r="O76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -3997,10 +4228,13 @@
         <v>0.12696</v>
       </c>
       <c r="M77" s="1" t="n">
+        <v>0.12584</v>
+      </c>
+      <c r="N77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="N77" s="1" t="n">
-        <v>0.12654</v>
+      <c r="O77" s="1" t="n">
+        <v>0.12584</v>
       </c>
     </row>
     <row r="78">
@@ -4043,9 +4277,12 @@
         <v>0.1621</v>
       </c>
       <c r="M78" s="1" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="N78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="N78" s="1" t="n">
+      <c r="O78" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -4089,9 +4326,12 @@
         <v>0.02705</v>
       </c>
       <c r="M79" s="1" t="n">
+        <v>0.02714</v>
+      </c>
+      <c r="N79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="N79" s="1" t="n">
+      <c r="O79" s="1" t="n">
         <v>0.02705</v>
       </c>
     </row>
@@ -4135,9 +4375,12 @@
         <v>358.61</v>
       </c>
       <c r="M80" s="1" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="N80" s="1" t="n">
         <v>358.61</v>
       </c>
-      <c r="N80" s="1" t="n">
+      <c r="O80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -4181,9 +4424,12 @@
         <v>7.103e-05</v>
       </c>
       <c r="M81" s="1" t="n">
+        <v>7.103e-05</v>
+      </c>
+      <c r="N81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="N81" s="1" t="n">
+      <c r="O81" s="1" t="n">
         <v>7.080999999999999e-05</v>
       </c>
     </row>
@@ -4227,9 +4473,12 @@
         <v>0.265</v>
       </c>
       <c r="M82" s="1" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="N82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="N82" s="1" t="n">
+      <c r="O82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -4273,10 +4522,13 @@
         <v>1.1341</v>
       </c>
       <c r="M83" s="1" t="n">
+        <v>1.1314</v>
+      </c>
+      <c r="N83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="N83" s="1" t="n">
-        <v>1.1341</v>
+      <c r="O83" s="1" t="n">
+        <v>1.1314</v>
       </c>
     </row>
     <row r="84">
@@ -4319,9 +4571,12 @@
         <v>0.3539</v>
       </c>
       <c r="M84" s="1" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="N84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="N84" s="1" t="n">
+      <c r="O84" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -4365,9 +4620,12 @@
         <v>2.0174</v>
       </c>
       <c r="M85" s="1" t="n">
+        <v>2.0207</v>
+      </c>
+      <c r="N85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="N85" s="1" t="n">
+      <c r="O85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -4411,9 +4669,12 @@
         <v>1.3205</v>
       </c>
       <c r="M86" s="1" t="n">
+        <v>1.3195</v>
+      </c>
+      <c r="N86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="N86" s="1" t="n">
+      <c r="O86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -4457,9 +4718,12 @@
         <v>32.68</v>
       </c>
       <c r="M87" s="1" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="N87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="N87" s="1" t="n">
+      <c r="O87" s="1" t="n">
         <v>32.68</v>
       </c>
     </row>
@@ -4503,9 +4767,12 @@
         <v>0.00941</v>
       </c>
       <c r="M88" s="1" t="n">
+        <v>0.009549999999999999</v>
+      </c>
+      <c r="N88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="N88" s="1" t="n">
+      <c r="O88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -4549,9 +4816,12 @@
         <v>0.01823</v>
       </c>
       <c r="M89" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="N89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="N89" s="1" t="n">
+      <c r="O89" s="1" t="n">
         <v>0.01823</v>
       </c>
     </row>
@@ -4595,9 +4865,12 @@
         <v>0.03497</v>
       </c>
       <c r="M90" s="1" t="n">
+        <v>0.03505</v>
+      </c>
+      <c r="N90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="N90" s="1" t="n">
+      <c r="O90" s="1" t="n">
         <v>0.03497</v>
       </c>
     </row>
@@ -4641,9 +4914,12 @@
         <v>0.012</v>
       </c>
       <c r="M91" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="N91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="N91" s="1" t="n">
+      <c r="O91" s="1" t="n">
         <v>0.0118</v>
       </c>
     </row>
@@ -4687,9 +4963,12 @@
         <v>3.098</v>
       </c>
       <c r="M92" s="1" t="n">
+        <v>3.101</v>
+      </c>
+      <c r="N92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="N92" s="1" t="n">
+      <c r="O92" s="1" t="n">
         <v>3.095</v>
       </c>
     </row>
@@ -4733,9 +5012,12 @@
         <v>0.005614</v>
       </c>
       <c r="M93" s="1" t="n">
+        <v>0.005611</v>
+      </c>
+      <c r="N93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="N93" s="1" t="n">
+      <c r="O93" s="1" t="n">
         <v>0.005596</v>
       </c>
     </row>
@@ -4779,9 +5061,12 @@
         <v>0.093</v>
       </c>
       <c r="M94" s="1" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="N94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="N94" s="1" t="n">
+      <c r="O94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -4825,9 +5110,12 @@
         <v>0.6064000000000001</v>
       </c>
       <c r="M95" s="1" t="n">
+        <v>0.6095</v>
+      </c>
+      <c r="N95" s="1" t="n">
         <v>0.6098</v>
       </c>
-      <c r="N95" s="1" t="n">
+      <c r="O95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -4871,9 +5159,12 @@
         <v>1.27e-05</v>
       </c>
       <c r="M96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="N96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="N96" s="1" t="n">
+      <c r="O96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -4917,10 +5208,13 @@
         <v>1.125</v>
       </c>
       <c r="M97" s="1" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="N97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="N97" s="1" t="n">
-        <v>1.125</v>
+      <c r="O97" s="1" t="n">
+        <v>1.121</v>
       </c>
     </row>
     <row r="98">
@@ -4963,9 +5257,12 @@
         <v>0.25558</v>
       </c>
       <c r="M98" s="1" t="n">
+        <v>0.25473</v>
+      </c>
+      <c r="N98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="N98" s="1" t="n">
+      <c r="O98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -5009,9 +5306,12 @@
         <v>1.145</v>
       </c>
       <c r="M99" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="N99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="N99" s="1" t="n">
+      <c r="O99" s="1" t="n">
         <v>1.144</v>
       </c>
     </row>
@@ -5055,9 +5355,12 @@
         <v>1.859</v>
       </c>
       <c r="M100" s="1" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="N100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="N100" s="1" t="n">
+      <c r="O100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -5101,9 +5404,12 @@
         <v>0.01585</v>
       </c>
       <c r="M101" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="N101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="N101" s="1" t="n">
+      <c r="O101" s="1" t="n">
         <v>0.01579</v>
       </c>
     </row>
@@ -5147,10 +5453,13 @@
         <v>0.10332</v>
       </c>
       <c r="M102" s="1" t="n">
+        <v>0.10279</v>
+      </c>
+      <c r="N102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="N102" s="1" t="n">
-        <v>0.10316</v>
+      <c r="O102" s="1" t="n">
+        <v>0.10279</v>
       </c>
     </row>
     <row r="103">
@@ -5193,9 +5502,12 @@
         <v>0.0005974</v>
       </c>
       <c r="M103" s="1" t="n">
+        <v>0.0005981</v>
+      </c>
+      <c r="N103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="N103" s="1" t="n">
+      <c r="O103" s="1" t="n">
         <v>0.0005967</v>
       </c>
     </row>
@@ -5239,9 +5551,12 @@
         <v>0.0005773</v>
       </c>
       <c r="M104" s="1" t="n">
-        <v>0.0005776000000000001</v>
+        <v>0.0005856</v>
       </c>
       <c r="N104" s="1" t="n">
+        <v>0.0005856</v>
+      </c>
+      <c r="O104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -5285,9 +5600,12 @@
         <v>0.003266</v>
       </c>
       <c r="M105" s="1" t="n">
-        <v>0.003266</v>
+        <v>0.003269</v>
       </c>
       <c r="N105" s="1" t="n">
+        <v>0.003269</v>
+      </c>
+      <c r="O105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -5331,9 +5649,12 @@
         <v>2.591</v>
       </c>
       <c r="M106" s="1" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="N106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="N106" s="1" t="n">
+      <c r="O106" s="1" t="n">
         <v>2.587</v>
       </c>
     </row>
@@ -5377,9 +5698,12 @@
         <v>0.1653</v>
       </c>
       <c r="M107" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="N107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="N107" s="1" t="n">
+      <c r="O107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -5423,9 +5747,12 @@
         <v>0.09614</v>
       </c>
       <c r="M108" s="1" t="n">
+        <v>0.09647</v>
+      </c>
+      <c r="N108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="N108" s="1" t="n">
+      <c r="O108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -5469,9 +5796,12 @@
         <v>0.02217</v>
       </c>
       <c r="M109" s="1" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="N109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="N109" s="1" t="n">
+      <c r="O109" s="1" t="n">
         <v>0.02204</v>
       </c>
     </row>
@@ -5515,9 +5845,12 @@
         <v>0.2921</v>
       </c>
       <c r="M110" s="1" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="N110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="N110" s="1" t="n">
+      <c r="O110" s="1" t="n">
         <v>0.2912</v>
       </c>
     </row>
@@ -5561,9 +5894,12 @@
         <v>0.05659</v>
       </c>
       <c r="M111" s="1" t="n">
+        <v>0.05692</v>
+      </c>
+      <c r="N111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="N111" s="1" t="n">
+      <c r="O111" s="1" t="n">
         <v>0.05659</v>
       </c>
     </row>
@@ -5607,9 +5943,12 @@
         <v>0.3011</v>
       </c>
       <c r="M112" s="1" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="N112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="N112" s="1" t="n">
+      <c r="O112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -5653,9 +5992,12 @@
         <v>18.66</v>
       </c>
       <c r="M113" s="1" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="N113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="N113" s="1" t="n">
+      <c r="O113" s="1" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -5699,9 +6041,12 @@
         <v>0.12876</v>
       </c>
       <c r="M114" s="1" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="N114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="N114" s="1" t="n">
+      <c r="O114" s="1" t="n">
         <v>0.12837</v>
       </c>
     </row>
@@ -5745,9 +6090,12 @@
         <v>0.01572</v>
       </c>
       <c r="M115" s="1" t="n">
-        <v>0.01583</v>
+        <v>0.01584</v>
       </c>
       <c r="N115" s="1" t="n">
+        <v>0.01584</v>
+      </c>
+      <c r="O115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -5791,9 +6139,12 @@
         <v>0.08473</v>
       </c>
       <c r="M116" s="1" t="n">
+        <v>0.08497</v>
+      </c>
+      <c r="N116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="N116" s="1" t="n">
+      <c r="O116" s="1" t="n">
         <v>0.08470999999999999</v>
       </c>
     </row>
@@ -5837,9 +6188,12 @@
         <v>0.047288</v>
       </c>
       <c r="M117" s="1" t="n">
+        <v>0.047386</v>
+      </c>
+      <c r="N117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="N117" s="1" t="n">
+      <c r="O117" s="1" t="n">
         <v>0.047288</v>
       </c>
     </row>
@@ -5883,9 +6237,12 @@
         <v>0.04732</v>
       </c>
       <c r="M118" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="N118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="N118" s="1" t="n">
+      <c r="O118" s="1" t="n">
         <v>0.04732</v>
       </c>
     </row>
@@ -5929,9 +6286,12 @@
         <v>0.03999</v>
       </c>
       <c r="M119" s="1" t="n">
+        <v>0.04054</v>
+      </c>
+      <c r="N119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="N119" s="1" t="n">
+      <c r="O119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -5975,10 +6335,13 @@
         <v>0.14471</v>
       </c>
       <c r="M120" s="1" t="n">
+        <v>0.14387</v>
+      </c>
+      <c r="N120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="N120" s="1" t="n">
-        <v>0.14463</v>
+      <c r="O120" s="1" t="n">
+        <v>0.14387</v>
       </c>
     </row>
     <row r="121">
@@ -6021,9 +6384,12 @@
         <v>0.1275</v>
       </c>
       <c r="M121" s="1" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="N121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="N121" s="1" t="n">
+      <c r="O121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -6067,10 +6433,13 @@
         <v>1.868</v>
       </c>
       <c r="M122" s="1" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="N122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="N122" s="1" t="n">
-        <v>1.867</v>
+      <c r="O122" s="1" t="n">
+        <v>1.864</v>
       </c>
     </row>
     <row r="123">
@@ -6113,9 +6482,12 @@
         <v>0.0302</v>
       </c>
       <c r="M123" s="1" t="n">
+        <v>0.03026</v>
+      </c>
+      <c r="N123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="N123" s="1" t="n">
+      <c r="O123" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -6159,10 +6531,13 @@
         <v>0.13161</v>
       </c>
       <c r="M124" s="1" t="n">
+        <v>0.13153</v>
+      </c>
+      <c r="N124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="N124" s="1" t="n">
-        <v>0.13159</v>
+      <c r="O124" s="1" t="n">
+        <v>0.13153</v>
       </c>
     </row>
     <row r="125">
@@ -6205,9 +6580,12 @@
         <v>0.04104</v>
       </c>
       <c r="M125" s="1" t="n">
+        <v>0.04103</v>
+      </c>
+      <c r="N125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="N125" s="1" t="n">
+      <c r="O125" s="1" t="n">
         <v>0.04095</v>
       </c>
     </row>
@@ -6251,9 +6629,12 @@
         <v>0.1147</v>
       </c>
       <c r="M126" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="N126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="N126" s="1" t="n">
+      <c r="O126" s="1" t="n">
         <v>0.1147</v>
       </c>
     </row>
@@ -6297,9 +6678,12 @@
         <v>0.5108</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>0.5108</v>
+        <v>0.5164</v>
       </c>
       <c r="N127" s="1" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="O127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -6343,9 +6727,12 @@
         <v>0.03802</v>
       </c>
       <c r="M128" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="N128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="N128" s="1" t="n">
+      <c r="O128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -6389,9 +6776,12 @@
         <v>0.791</v>
       </c>
       <c r="M129" s="1" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="N129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="N129" s="1" t="n">
+      <c r="O129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -6435,9 +6825,12 @@
         <v>0.03441</v>
       </c>
       <c r="M130" s="1" t="n">
+        <v>0.03449</v>
+      </c>
+      <c r="N130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="N130" s="1" t="n">
+      <c r="O130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -6481,9 +6874,12 @@
         <v>0.4251</v>
       </c>
       <c r="M131" s="1" t="n">
+        <v>0.4246</v>
+      </c>
+      <c r="N131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="N131" s="1" t="n">
+      <c r="O131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6527,9 +6923,12 @@
         <v>0.04376</v>
       </c>
       <c r="M132" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="N132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="N132" s="1" t="n">
+      <c r="O132" s="1" t="n">
         <v>0.04354</v>
       </c>
     </row>
@@ -6573,9 +6972,12 @@
         <v>1.2878</v>
       </c>
       <c r="M133" s="1" t="n">
+        <v>1.2899</v>
+      </c>
+      <c r="N133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="N133" s="1" t="n">
+      <c r="O133" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -6619,9 +7021,12 @@
         <v>0.02191</v>
       </c>
       <c r="M134" s="1" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="N134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="N134" s="1" t="n">
+      <c r="O134" s="1" t="n">
         <v>0.02184</v>
       </c>
     </row>
@@ -6665,9 +7070,12 @@
         <v>0.0004597</v>
       </c>
       <c r="M135" s="1" t="n">
+        <v>0.0004608</v>
+      </c>
+      <c r="N135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="N135" s="1" t="n">
+      <c r="O135" s="1" t="n">
         <v>0.0004592</v>
       </c>
     </row>
@@ -6711,9 +7119,12 @@
         <v>0.001899</v>
       </c>
       <c r="M136" s="1" t="n">
+        <v>0.001904</v>
+      </c>
+      <c r="N136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="N136" s="1" t="n">
+      <c r="O136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -6757,9 +7168,12 @@
         <v>0.3164</v>
       </c>
       <c r="M137" s="1" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="N137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="N137" s="1" t="n">
+      <c r="O137" s="1" t="n">
         <v>0.3164</v>
       </c>
     </row>
@@ -6803,9 +7217,12 @@
         <v>0.5705</v>
       </c>
       <c r="M138" s="1" t="n">
+        <v>0.5706</v>
+      </c>
+      <c r="N138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="N138" s="1" t="n">
+      <c r="O138" s="1" t="n">
         <v>0.5698</v>
       </c>
     </row>
@@ -6849,9 +7266,12 @@
         <v>0.0213</v>
       </c>
       <c r="M139" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="N139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="N139" s="1" t="n">
+      <c r="O139" s="1" t="n">
         <v>0.02125</v>
       </c>
     </row>
@@ -6895,9 +7315,12 @@
         <v>0.08039</v>
       </c>
       <c r="M140" s="1" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="N140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="N140" s="1" t="n">
+      <c r="O140" s="1" t="n">
         <v>0.08036</v>
       </c>
     </row>
@@ -6941,10 +7364,13 @@
         <v>0.001523</v>
       </c>
       <c r="M141" s="1" t="n">
+        <v>0.001502</v>
+      </c>
+      <c r="N141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="N141" s="1" t="n">
-        <v>0.001523</v>
+      <c r="O141" s="1" t="n">
+        <v>0.001502</v>
       </c>
     </row>
     <row r="142">
@@ -6987,9 +7413,12 @@
         <v>0.4375</v>
       </c>
       <c r="M142" s="1" t="n">
-        <v>0.4387</v>
+        <v>0.4447</v>
       </c>
       <c r="N142" s="1" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="O142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -7033,9 +7462,12 @@
         <v>0.030859</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>0.030859</v>
+        <v>0.031368</v>
       </c>
       <c r="N143" s="1" t="n">
+        <v>0.031368</v>
+      </c>
+      <c r="O143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -7079,9 +7511,12 @@
         <v>0.000226</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>0.000226</v>
+        <v>0.000227</v>
       </c>
       <c r="N144" s="1" t="n">
+        <v>0.000227</v>
+      </c>
+      <c r="O144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -7125,9 +7560,12 @@
         <v>0.03487</v>
       </c>
       <c r="M145" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="N145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="N145" s="1" t="n">
+      <c r="O145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -7171,9 +7609,12 @@
         <v>0.11554</v>
       </c>
       <c r="M146" s="1" t="n">
+        <v>0.11548</v>
+      </c>
+      <c r="N146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="N146" s="1" t="n">
+      <c r="O146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -7217,9 +7658,12 @@
         <v>0.02197</v>
       </c>
       <c r="M147" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="N147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="N147" s="1" t="n">
+      <c r="O147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -7263,9 +7707,12 @@
         <v>1.4122</v>
       </c>
       <c r="M148" s="1" t="n">
+        <v>1.4145</v>
+      </c>
+      <c r="N148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="N148" s="1" t="n">
+      <c r="O148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -7309,9 +7756,12 @@
         <v>1.8741</v>
       </c>
       <c r="M149" s="1" t="n">
+        <v>1.8787</v>
+      </c>
+      <c r="N149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="N149" s="1" t="n">
+      <c r="O149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -7355,9 +7805,12 @@
         <v>0.096</v>
       </c>
       <c r="M150" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="N150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="N150" s="1" t="n">
+      <c r="O150" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -7401,9 +7854,12 @@
         <v>4.607</v>
       </c>
       <c r="M151" s="1" t="n">
+        <v>4.614</v>
+      </c>
+      <c r="N151" s="1" t="n">
         <v>4.64</v>
       </c>
-      <c r="N151" s="1" t="n">
+      <c r="O151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -7447,9 +7903,12 @@
         <v>5.534</v>
       </c>
       <c r="M152" s="1" t="n">
+        <v>5.564</v>
+      </c>
+      <c r="N152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="N152" s="1" t="n">
+      <c r="O152" s="1" t="n">
         <v>5.522</v>
       </c>
     </row>
@@ -7493,10 +7952,13 @@
         <v>0.3187</v>
       </c>
       <c r="M153" s="1" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="N153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="N153" s="1" t="n">
-        <v>0.3175</v>
+      <c r="O153" s="1" t="n">
+        <v>0.3172</v>
       </c>
     </row>
     <row r="154">
@@ -7539,10 +8001,13 @@
         <v>0.5869</v>
       </c>
       <c r="M154" s="1" t="n">
+        <v>0.5862000000000001</v>
+      </c>
+      <c r="N154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="N154" s="1" t="n">
-        <v>0.5867</v>
+      <c r="O154" s="1" t="n">
+        <v>0.5862000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -7585,9 +8050,12 @@
         <v>0.01299</v>
       </c>
       <c r="M155" s="1" t="n">
+        <v>0.01292</v>
+      </c>
+      <c r="N155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="N155" s="1" t="n">
+      <c r="O155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -7631,9 +8099,12 @@
         <v>0.0985</v>
       </c>
       <c r="M156" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="N156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="N156" s="1" t="n">
+      <c r="O156" s="1" t="n">
         <v>0.0985</v>
       </c>
     </row>
@@ -7677,9 +8148,12 @@
         <v>16.553</v>
       </c>
       <c r="M157" s="1" t="n">
+        <v>16.578</v>
+      </c>
+      <c r="N157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="N157" s="1" t="n">
+      <c r="O157" s="1" t="n">
         <v>16.525</v>
       </c>
     </row>
@@ -7723,9 +8197,12 @@
         <v>0.05564</v>
       </c>
       <c r="M158" s="1" t="n">
+        <v>0.05572</v>
+      </c>
+      <c r="N158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="N158" s="1" t="n">
+      <c r="O158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -7769,9 +8246,12 @@
         <v>29</v>
       </c>
       <c r="M159" s="1" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="N159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="N159" s="1" t="n">
+      <c r="O159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -7815,9 +8295,12 @@
         <v>0.02107</v>
       </c>
       <c r="M160" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="N160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="N160" s="1" t="n">
+      <c r="O160" s="1" t="n">
         <v>0.02107</v>
       </c>
     </row>
@@ -7861,9 +8344,12 @@
         <v>0.0006543</v>
       </c>
       <c r="M161" s="1" t="n">
+        <v>0.0006555</v>
+      </c>
+      <c r="N161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="N161" s="1" t="n">
+      <c r="O161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -7907,9 +8393,12 @@
         <v>0.3808</v>
       </c>
       <c r="M162" s="1" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="N162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="N162" s="1" t="n">
+      <c r="O162" s="1" t="n">
         <v>0.3808</v>
       </c>
     </row>
@@ -7953,9 +8442,12 @@
         <v>0.1922</v>
       </c>
       <c r="M163" s="1" t="n">
+        <v>0.1924</v>
+      </c>
+      <c r="N163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="N163" s="1" t="n">
+      <c r="O163" s="1" t="n">
         <v>0.1922</v>
       </c>
     </row>
@@ -7999,9 +8491,12 @@
         <v>0.316</v>
       </c>
       <c r="M164" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="N164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="N164" s="1" t="n">
+      <c r="O164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -8045,9 +8540,12 @@
         <v>0.372</v>
       </c>
       <c r="M165" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="N165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="N165" s="1" t="n">
+      <c r="O165" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -8091,10 +8589,13 @@
         <v>0.02259</v>
       </c>
       <c r="M166" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="N166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="N166" s="1" t="n">
-        <v>0.02258</v>
+      <c r="O166" s="1" t="n">
+        <v>0.02256</v>
       </c>
     </row>
     <row r="167">
@@ -8137,9 +8638,12 @@
         <v>0.007284</v>
       </c>
       <c r="M167" s="1" t="n">
+        <v>0.007291</v>
+      </c>
+      <c r="N167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="N167" s="1" t="n">
+      <c r="O167" s="1" t="n">
         <v>0.007284</v>
       </c>
     </row>
@@ -8183,9 +8687,12 @@
         <v>0.01355</v>
       </c>
       <c r="M168" s="1" t="n">
+        <v>0.01357</v>
+      </c>
+      <c r="N168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="N168" s="1" t="n">
+      <c r="O168" s="1" t="n">
         <v>0.01355</v>
       </c>
     </row>
@@ -8229,9 +8736,12 @@
         <v>0.25206</v>
       </c>
       <c r="M169" s="1" t="n">
+        <v>0.25348</v>
+      </c>
+      <c r="N169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="N169" s="1" t="n">
+      <c r="O169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -8275,9 +8785,12 @@
         <v>0.02172</v>
       </c>
       <c r="M170" s="1" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="N170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="N170" s="1" t="n">
+      <c r="O170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -8321,10 +8834,13 @@
         <v>0.1713</v>
       </c>
       <c r="M171" s="1" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="N171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="N171" s="1" t="n">
-        <v>0.1713</v>
+      <c r="O171" s="1" t="n">
+        <v>0.1711</v>
       </c>
     </row>
     <row r="172">
@@ -8367,9 +8883,12 @@
         <v>0.089</v>
       </c>
       <c r="M172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="N172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="N172" s="1" t="n">
+      <c r="O172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -8413,9 +8932,12 @@
         <v>0.004676</v>
       </c>
       <c r="M173" s="1" t="n">
+        <v>0.004679</v>
+      </c>
+      <c r="N173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="N173" s="1" t="n">
+      <c r="O173" s="1" t="n">
         <v>0.004676</v>
       </c>
     </row>
@@ -8459,9 +8981,12 @@
         <v>0.438</v>
       </c>
       <c r="M174" s="1" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="N174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="N174" s="1" t="n">
+      <c r="O174" s="1" t="n">
         <v>0.4364</v>
       </c>
     </row>
@@ -8505,9 +9030,12 @@
         <v>0.09032999999999999</v>
       </c>
       <c r="M175" s="1" t="n">
+        <v>0.09016</v>
+      </c>
+      <c r="N175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="N175" s="1" t="n">
+      <c r="O175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -8551,9 +9079,12 @@
         <v>0.2471</v>
       </c>
       <c r="M176" s="1" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="N176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="N176" s="1" t="n">
+      <c r="O176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -8597,9 +9128,12 @@
         <v>0.01921</v>
       </c>
       <c r="M177" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="N177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="N177" s="1" t="n">
+      <c r="O177" s="1" t="n">
         <v>0.01909</v>
       </c>
     </row>
@@ -8643,9 +9177,12 @@
         <v>6.138</v>
       </c>
       <c r="M178" s="1" t="n">
+        <v>6.149</v>
+      </c>
+      <c r="N178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="N178" s="1" t="n">
+      <c r="O178" s="1" t="n">
         <v>6.138</v>
       </c>
     </row>
@@ -8689,9 +9226,12 @@
         <v>0.1363</v>
       </c>
       <c r="M179" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="N179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="N179" s="1" t="n">
+      <c r="O179" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -8735,9 +9275,12 @@
         <v>0.005054</v>
       </c>
       <c r="M180" s="1" t="n">
+        <v>0.005062</v>
+      </c>
+      <c r="N180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="N180" s="1" t="n">
+      <c r="O180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -8781,9 +9324,12 @@
         <v>0.01198</v>
       </c>
       <c r="M181" s="1" t="n">
+        <v>0.01197</v>
+      </c>
+      <c r="N181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="N181" s="1" t="n">
+      <c r="O181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -8827,9 +9373,12 @@
         <v>0.007389</v>
       </c>
       <c r="M182" s="1" t="n">
+        <v>0.007314</v>
+      </c>
+      <c r="N182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="N182" s="1" t="n">
+      <c r="O182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -8873,9 +9422,12 @@
         <v>0.1305</v>
       </c>
       <c r="M183" s="1" t="n">
+        <v>0.13152</v>
+      </c>
+      <c r="N183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="N183" s="1" t="n">
+      <c r="O183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -8919,9 +9471,12 @@
         <v>0.09696</v>
       </c>
       <c r="M184" s="1" t="n">
+        <v>0.09686</v>
+      </c>
+      <c r="N184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="N184" s="1" t="n">
+      <c r="O184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -8965,9 +9520,12 @@
         <v>0.00753</v>
       </c>
       <c r="M185" s="1" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="N185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="N185" s="1" t="n">
+      <c r="O185" s="1" t="n">
         <v>0.00753</v>
       </c>
     </row>
@@ -9011,9 +9569,12 @@
         <v>0.04874</v>
       </c>
       <c r="M186" s="1" t="n">
+        <v>0.04879</v>
+      </c>
+      <c r="N186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="N186" s="1" t="n">
+      <c r="O186" s="1" t="n">
         <v>0.0486</v>
       </c>
     </row>
@@ -9057,9 +9618,12 @@
         <v>0.02679</v>
       </c>
       <c r="M187" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="N187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="N187" s="1" t="n">
+      <c r="O187" s="1" t="n">
         <v>0.02674</v>
       </c>
     </row>
@@ -9103,9 +9667,12 @@
         <v>0.003308</v>
       </c>
       <c r="M188" s="1" t="n">
+        <v>0.003315</v>
+      </c>
+      <c r="N188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="N188" s="1" t="n">
+      <c r="O188" s="1" t="n">
         <v>0.003303</v>
       </c>
     </row>
@@ -9149,9 +9716,12 @@
         <v>0.2859</v>
       </c>
       <c r="M189" s="1" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="N189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="N189" s="1" t="n">
+      <c r="O189" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -9195,9 +9765,12 @@
         <v>0.0179</v>
       </c>
       <c r="M190" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="N190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="N190" s="1" t="n">
+      <c r="O190" s="1" t="n">
         <v>0.0179</v>
       </c>
     </row>
@@ -9241,9 +9814,12 @@
         <v>0.2576</v>
       </c>
       <c r="M191" s="1" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="N191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="N191" s="1" t="n">
+      <c r="O191" s="1" t="n">
         <v>0.2574</v>
       </c>
     </row>
@@ -9287,9 +9863,12 @@
         <v>0.03766</v>
       </c>
       <c r="M192" s="1" t="n">
+        <v>0.03791</v>
+      </c>
+      <c r="N192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="N192" s="1" t="n">
+      <c r="O192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -9333,9 +9912,12 @@
         <v>0.0002243</v>
       </c>
       <c r="M193" s="1" t="n">
+        <v>0.0002237</v>
+      </c>
+      <c r="N193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="N193" s="1" t="n">
+      <c r="O193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -9379,9 +9961,12 @@
         <v>4.106</v>
       </c>
       <c r="M194" s="1" t="n">
+        <v>4.101</v>
+      </c>
+      <c r="N194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="N194" s="1" t="n">
+      <c r="O194" s="1" t="n">
         <v>4.091</v>
       </c>
     </row>
@@ -9425,9 +10010,12 @@
         <v>0.999401</v>
       </c>
       <c r="M195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="N195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="N195" s="1" t="n">
+      <c r="O195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -9471,9 +10059,12 @@
         <v>4.295</v>
       </c>
       <c r="M196" s="1" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="N196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="N196" s="1" t="n">
+      <c r="O196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -9517,9 +10108,12 @@
         <v>0.15185</v>
       </c>
       <c r="M197" s="1" t="n">
+        <v>0.15143</v>
+      </c>
+      <c r="N197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="N197" s="1" t="n">
+      <c r="O197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -9563,9 +10157,12 @@
         <v>0.007766</v>
       </c>
       <c r="M198" s="1" t="n">
+        <v>0.007704</v>
+      </c>
+      <c r="N198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="N198" s="1" t="n">
+      <c r="O198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -9609,9 +10206,12 @@
         <v>0.4492</v>
       </c>
       <c r="M199" s="1" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="N199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="N199" s="1" t="n">
+      <c r="O199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -9655,9 +10255,12 @@
         <v>0.5895</v>
       </c>
       <c r="M200" s="1" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="N200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="N200" s="1" t="n">
+      <c r="O200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -9701,9 +10304,12 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="M201" s="1" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="N201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="N201" s="1" t="n">
+      <c r="O201" s="1" t="n">
         <v>0.0931</v>
       </c>
     </row>
@@ -9747,10 +10353,13 @@
         <v>0.06041</v>
       </c>
       <c r="M202" s="1" t="n">
+        <v>0.06025</v>
+      </c>
+      <c r="N202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="N202" s="1" t="n">
-        <v>0.06041</v>
+      <c r="O202" s="1" t="n">
+        <v>0.06025</v>
       </c>
     </row>
     <row r="203">
@@ -9793,9 +10402,12 @@
         <v>0.00843</v>
       </c>
       <c r="M203" s="1" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="N203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="N203" s="1" t="n">
+      <c r="O203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -9839,9 +10451,12 @@
         <v>0.00418</v>
       </c>
       <c r="M204" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="N204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="N204" s="1" t="n">
+      <c r="O204" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -9885,9 +10500,12 @@
         <v>0.009070999999999999</v>
       </c>
       <c r="M205" s="1" t="n">
+        <v>0.009128000000000001</v>
+      </c>
+      <c r="N205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="N205" s="1" t="n">
+      <c r="O205" s="1" t="n">
         <v>0.009070999999999999</v>
       </c>
     </row>
@@ -9931,9 +10549,12 @@
         <v>0.2395</v>
       </c>
       <c r="M206" s="1" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="N206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="N206" s="1" t="n">
+      <c r="O206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -9977,9 +10598,12 @@
         <v>0.02053</v>
       </c>
       <c r="M207" s="1" t="n">
+        <v>0.02065</v>
+      </c>
+      <c r="N207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="N207" s="1" t="n">
+      <c r="O207" s="1" t="n">
         <v>0.02053</v>
       </c>
     </row>
@@ -10023,9 +10647,12 @@
         <v>0.2365</v>
       </c>
       <c r="M208" s="1" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="N208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="N208" s="1" t="n">
+      <c r="O208" s="1" t="n">
         <v>0.2364</v>
       </c>
     </row>
@@ -10069,9 +10696,12 @@
         <v>0.3596</v>
       </c>
       <c r="M209" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="N209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="N209" s="1" t="n">
+      <c r="O209" s="1" t="n">
         <v>0.3586</v>
       </c>
     </row>
@@ -10115,9 +10745,12 @@
         <v>0.04241</v>
       </c>
       <c r="M210" s="1" t="n">
+        <v>0.04253</v>
+      </c>
+      <c r="N210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="N210" s="1" t="n">
+      <c r="O210" s="1" t="n">
         <v>0.04236</v>
       </c>
     </row>
@@ -10161,9 +10794,12 @@
         <v>0.0004274</v>
       </c>
       <c r="M211" s="1" t="n">
+        <v>0.0004285</v>
+      </c>
+      <c r="N211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="N211" s="1" t="n">
+      <c r="O211" s="1" t="n">
         <v>0.0004256</v>
       </c>
     </row>
@@ -10207,10 +10843,13 @@
         <v>0.0215</v>
       </c>
       <c r="M212" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="N212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="N212" s="1" t="n">
-        <v>0.0215</v>
+      <c r="O212" s="1" t="n">
+        <v>0.02148</v>
       </c>
     </row>
     <row r="213">
@@ -10253,9 +10892,12 @@
         <v>0.1143</v>
       </c>
       <c r="M213" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="N213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="N213" s="1" t="n">
+      <c r="O213" s="1" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -10299,9 +10941,12 @@
         <v>0.04187</v>
       </c>
       <c r="M214" s="1" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="N214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="N214" s="1" t="n">
+      <c r="O214" s="1" t="n">
         <v>0.04174</v>
       </c>
     </row>
@@ -10345,10 +10990,13 @@
         <v>0.009887</v>
       </c>
       <c r="M215" s="1" t="n">
+        <v>0.009875999999999999</v>
+      </c>
+      <c r="N215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="N215" s="1" t="n">
-        <v>0.009887</v>
+      <c r="O215" s="1" t="n">
+        <v>0.009875999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10391,9 +11039,12 @@
         <v>0.064</v>
       </c>
       <c r="M216" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="N216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="N216" s="1" t="n">
+      <c r="O216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -10437,9 +11088,12 @@
         <v>0.004258</v>
       </c>
       <c r="M217" s="1" t="n">
-        <v>0.004258</v>
+        <v>0.004266</v>
       </c>
       <c r="N217" s="1" t="n">
+        <v>0.004266</v>
+      </c>
+      <c r="O217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -10483,9 +11137,12 @@
         <v>0.01003</v>
       </c>
       <c r="M218" s="1" t="n">
+        <v>0.01005</v>
+      </c>
+      <c r="N218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="N218" s="1" t="n">
+      <c r="O218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -10529,9 +11186,12 @@
         <v>0.03011</v>
       </c>
       <c r="M219" s="1" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="N219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="N219" s="1" t="n">
+      <c r="O219" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -10575,9 +11235,12 @@
         <v>2.292</v>
       </c>
       <c r="M220" s="1" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="N220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="N220" s="1" t="n">
+      <c r="O220" s="1" t="n">
         <v>2.291</v>
       </c>
     </row>
@@ -10621,10 +11284,13 @@
         <v>0.022886</v>
       </c>
       <c r="M221" s="1" t="n">
+        <v>0.022819</v>
+      </c>
+      <c r="N221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="N221" s="1" t="n">
-        <v>0.022861</v>
+      <c r="O221" s="1" t="n">
+        <v>0.022819</v>
       </c>
     </row>
     <row r="222">
@@ -10667,9 +11333,12 @@
         <v>0.0369</v>
       </c>
       <c r="M222" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="N222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="N222" s="1" t="n">
+      <c r="O222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -10713,9 +11382,12 @@
         <v>0.2928</v>
       </c>
       <c r="M223" s="1" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="N223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="N223" s="1" t="n">
+      <c r="O223" s="1" t="n">
         <v>0.2918</v>
       </c>
     </row>
@@ -10759,9 +11431,12 @@
         <v>0.01558</v>
       </c>
       <c r="M224" s="1" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="N224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="N224" s="1" t="n">
+      <c r="O224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -10805,9 +11480,12 @@
         <v>0.0004074</v>
       </c>
       <c r="M225" s="1" t="n">
+        <v>0.0004076</v>
+      </c>
+      <c r="N225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="N225" s="1" t="n">
+      <c r="O225" s="1" t="n">
         <v>0.0004069</v>
       </c>
     </row>
@@ -10851,9 +11529,12 @@
         <v>0.08623</v>
       </c>
       <c r="M226" s="1" t="n">
+        <v>0.08659</v>
+      </c>
+      <c r="N226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="N226" s="1" t="n">
+      <c r="O226" s="1" t="n">
         <v>0.08623</v>
       </c>
     </row>
@@ -10897,9 +11578,12 @@
         <v>0.949</v>
       </c>
       <c r="M227" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="N227" s="1" t="n">
+      <c r="O227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -10943,10 +11627,13 @@
         <v>0.0557</v>
       </c>
       <c r="M228" s="1" t="n">
+        <v>0.05534</v>
+      </c>
+      <c r="N228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="N228" s="1" t="n">
-        <v>0.05546</v>
+      <c r="O228" s="1" t="n">
+        <v>0.05534</v>
       </c>
     </row>
     <row r="229">
@@ -10989,9 +11676,12 @@
         <v>0.002009</v>
       </c>
       <c r="M229" s="1" t="n">
+        <v>0.002008</v>
+      </c>
+      <c r="N229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="N229" s="1" t="n">
+      <c r="O229" s="1" t="n">
         <v>0.002003</v>
       </c>
     </row>
@@ -11035,9 +11725,12 @@
         <v>0.02285</v>
       </c>
       <c r="M230" s="1" t="n">
+        <v>0.022782</v>
+      </c>
+      <c r="N230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="N230" s="1" t="n">
+      <c r="O230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -11081,9 +11774,12 @@
         <v>0.05358</v>
       </c>
       <c r="M231" s="1" t="n">
+        <v>0.05373</v>
+      </c>
+      <c r="N231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="N231" s="1" t="n">
+      <c r="O231" s="1" t="n">
         <v>0.0535</v>
       </c>
     </row>
@@ -11127,9 +11823,12 @@
         <v>0.059</v>
       </c>
       <c r="M232" s="1" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="N232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="N232" s="1" t="n">
+      <c r="O232" s="1" t="n">
         <v>0.0587</v>
       </c>
     </row>
@@ -11173,9 +11872,12 @@
         <v>0.001681</v>
       </c>
       <c r="M233" s="1" t="n">
+        <v>0.001684</v>
+      </c>
+      <c r="N233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="N233" s="1" t="n">
+      <c r="O233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -11219,9 +11921,12 @@
         <v>0.005728</v>
       </c>
       <c r="M234" s="1" t="n">
+        <v>0.00576</v>
+      </c>
+      <c r="N234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="N234" s="1" t="n">
+      <c r="O234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -11265,10 +11970,13 @@
         <v>0.12449</v>
       </c>
       <c r="M235" s="1" t="n">
+        <v>0.12437</v>
+      </c>
+      <c r="N235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="N235" s="1" t="n">
-        <v>0.12449</v>
+      <c r="O235" s="1" t="n">
+        <v>0.12437</v>
       </c>
     </row>
     <row r="236">
@@ -11311,10 +12019,13 @@
         <v>64.77</v>
       </c>
       <c r="M236" s="1" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="N236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="N236" s="1" t="n">
-        <v>64.73</v>
+      <c r="O236" s="1" t="n">
+        <v>64.5</v>
       </c>
     </row>
     <row r="237">
@@ -11357,9 +12068,12 @@
         <v>0.1015</v>
       </c>
       <c r="M237" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="N237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="N237" s="1" t="n">
+      <c r="O237" s="1" t="n">
         <v>0.1015</v>
       </c>
     </row>
@@ -11403,9 +12117,12 @@
         <v>0.004035</v>
       </c>
       <c r="M238" s="1" t="n">
-        <v>0.004035</v>
+        <v>0.004053</v>
       </c>
       <c r="N238" s="1" t="n">
+        <v>0.004053</v>
+      </c>
+      <c r="O238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -11449,9 +12166,12 @@
         <v>0.01555</v>
       </c>
       <c r="M239" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="N239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="N239" s="1" t="n">
+      <c r="O239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -11495,9 +12215,12 @@
         <v>0.05604</v>
       </c>
       <c r="M240" s="1" t="n">
+        <v>0.05605</v>
+      </c>
+      <c r="N240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="N240" s="1" t="n">
+      <c r="O240" s="1" t="n">
         <v>0.05598</v>
       </c>
     </row>
@@ -11541,9 +12264,12 @@
         <v>0.0113</v>
       </c>
       <c r="M241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="N241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="N241" s="1" t="n">
+      <c r="O241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -11587,9 +12313,12 @@
         <v>0.3333</v>
       </c>
       <c r="M242" s="1" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="N242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="N242" s="1" t="n">
+      <c r="O242" s="1" t="n">
         <v>0.3333</v>
       </c>
     </row>
@@ -11633,9 +12362,12 @@
         <v>0.01227</v>
       </c>
       <c r="M243" s="1" t="n">
+        <v>0.01228</v>
+      </c>
+      <c r="N243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="N243" s="1" t="n">
+      <c r="O243" s="1" t="n">
         <v>0.01227</v>
       </c>
     </row>
@@ -11679,9 +12411,12 @@
         <v>0.08087</v>
       </c>
       <c r="M244" s="1" t="n">
-        <v>0.08087</v>
+        <v>0.08121</v>
       </c>
       <c r="N244" s="1" t="n">
+        <v>0.08121</v>
+      </c>
+      <c r="O244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -11725,9 +12460,12 @@
         <v>0.007815000000000001</v>
       </c>
       <c r="M245" s="1" t="n">
+        <v>0.007835</v>
+      </c>
+      <c r="N245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="N245" s="1" t="n">
+      <c r="O245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -11771,9 +12509,12 @@
         <v>0.03033</v>
       </c>
       <c r="M246" s="1" t="n">
+        <v>0.03036</v>
+      </c>
+      <c r="N246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="N246" s="1" t="n">
+      <c r="O246" s="1" t="n">
         <v>0.03025</v>
       </c>
     </row>
@@ -11817,9 +12558,12 @@
         <v>0.18</v>
       </c>
       <c r="M247" s="1" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="N247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="N247" s="1" t="n">
+      <c r="O247" s="1" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11863,9 +12607,12 @@
         <v>0.05875</v>
       </c>
       <c r="M248" s="1" t="n">
+        <v>0.05876</v>
+      </c>
+      <c r="N248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="N248" s="1" t="n">
+      <c r="O248" s="1" t="n">
         <v>0.05875</v>
       </c>
     </row>
@@ -11909,9 +12656,12 @@
         <v>0.166</v>
       </c>
       <c r="M249" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="N249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="N249" s="1" t="n">
+      <c r="O249" s="1" t="n">
         <v>0.166</v>
       </c>
     </row>
@@ -11955,9 +12705,12 @@
         <v>0.01913</v>
       </c>
       <c r="M250" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="N250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="N250" s="1" t="n">
+      <c r="O250" s="1" t="n">
         <v>0.01906</v>
       </c>
     </row>
@@ -12001,9 +12754,12 @@
         <v>0.02322</v>
       </c>
       <c r="M251" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="N251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="N251" s="1" t="n">
+      <c r="O251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -12047,9 +12803,12 @@
         <v>0.30554</v>
       </c>
       <c r="M252" s="1" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="N252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="N252" s="1" t="n">
+      <c r="O252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -12093,9 +12852,12 @@
         <v>0.006041</v>
       </c>
       <c r="M253" s="1" t="n">
+        <v>0.006013</v>
+      </c>
+      <c r="N253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="N253" s="1" t="n">
+      <c r="O253" s="1" t="n">
         <v>0.005971</v>
       </c>
     </row>
@@ -12139,9 +12901,12 @@
         <v>0.6133999999999999</v>
       </c>
       <c r="M254" s="1" t="n">
+        <v>0.6139</v>
+      </c>
+      <c r="N254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="N254" s="1" t="n">
+      <c r="O254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -12185,9 +12950,12 @@
         <v>0.10643</v>
       </c>
       <c r="M255" s="1" t="n">
+        <v>0.10635</v>
+      </c>
+      <c r="N255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="N255" s="1" t="n">
+      <c r="O255" s="1" t="n">
         <v>0.10612</v>
       </c>
     </row>
@@ -12231,9 +12999,12 @@
         <v>0.0916</v>
       </c>
       <c r="M256" s="1" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="N256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="N256" s="1" t="n">
+      <c r="O256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -12277,9 +13048,12 @@
         <v>0.01446</v>
       </c>
       <c r="M257" s="1" t="n">
+        <v>0.01444</v>
+      </c>
+      <c r="N257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="N257" s="1" t="n">
+      <c r="O257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -12323,10 +13097,13 @@
         <v>0.05051</v>
       </c>
       <c r="M258" s="1" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="N258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="N258" s="1" t="n">
-        <v>0.05051</v>
+      <c r="O258" s="1" t="n">
+        <v>0.05025</v>
       </c>
     </row>
     <row r="259">
@@ -12369,9 +13146,12 @@
         <v>0.00809</v>
       </c>
       <c r="M259" s="1" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="N259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="N259" s="1" t="n">
+      <c r="O259" s="1" t="n">
         <v>0.00809</v>
       </c>
     </row>
@@ -12415,9 +13195,12 @@
         <v>0.1903</v>
       </c>
       <c r="M260" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="N260" s="1" t="n">
+      <c r="O260" s="1" t="n">
         <v>0.1894</v>
       </c>
     </row>
@@ -12461,9 +13244,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="M261" s="1" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="N261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="N261" s="1" t="n">
+      <c r="O261" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
     </row>
@@ -12507,9 +13293,12 @@
         <v>0.2113</v>
       </c>
       <c r="M262" s="1" t="n">
+        <v>0.2116</v>
+      </c>
+      <c r="N262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="N262" s="1" t="n">
+      <c r="O262" s="1" t="n">
         <v>0.2113</v>
       </c>
     </row>
@@ -12553,9 +13342,12 @@
         <v>0.008525</v>
       </c>
       <c r="M263" s="1" t="n">
+        <v>0.008503999999999999</v>
+      </c>
+      <c r="N263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="N263" s="1" t="n">
+      <c r="O263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -12599,9 +13391,12 @@
         <v>2.634</v>
       </c>
       <c r="M264" s="1" t="n">
+        <v>2.637</v>
+      </c>
+      <c r="N264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="N264" s="1" t="n">
+      <c r="O264" s="1" t="n">
         <v>2.632</v>
       </c>
     </row>
@@ -12645,9 +13440,12 @@
         <v>0.01862</v>
       </c>
       <c r="M265" s="1" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="N265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="N265" s="1" t="n">
+      <c r="O265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -12691,9 +13489,12 @@
         <v>0.3607</v>
       </c>
       <c r="M266" s="1" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="N266" s="1" t="n">
         <v>0.3607</v>
       </c>
-      <c r="N266" s="1" t="n">
+      <c r="O266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -12737,9 +13538,12 @@
         <v>0.03434</v>
       </c>
       <c r="M267" s="1" t="n">
+        <v>0.03427</v>
+      </c>
+      <c r="N267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="N267" s="1" t="n">
+      <c r="O267" s="1" t="n">
         <v>0.03408</v>
       </c>
     </row>
@@ -12783,10 +13587,13 @@
         <v>0.118</v>
       </c>
       <c r="M268" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="N268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="N268" s="1" t="n">
-        <v>0.118</v>
+      <c r="O268" s="1" t="n">
+        <v>0.117</v>
       </c>
     </row>
     <row r="269">
@@ -12829,9 +13636,12 @@
         <v>0.07996</v>
       </c>
       <c r="M269" s="1" t="n">
+        <v>0.08024000000000001</v>
+      </c>
+      <c r="N269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="N269" s="1" t="n">
+      <c r="O269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -12875,9 +13685,12 @@
         <v>0.01382</v>
       </c>
       <c r="M270" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="N270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="N270" s="1" t="n">
+      <c r="O270" s="1" t="n">
         <v>0.01382</v>
       </c>
     </row>
@@ -12921,9 +13734,12 @@
         <v>0.007568</v>
       </c>
       <c r="M271" s="1" t="n">
+        <v>0.007578</v>
+      </c>
+      <c r="N271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="N271" s="1" t="n">
+      <c r="O271" s="1" t="n">
         <v>0.007558</v>
       </c>
     </row>
@@ -12967,9 +13783,12 @@
         <v>0.07423</v>
       </c>
       <c r="M272" s="1" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="N272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="N272" s="1" t="n">
+      <c r="O272" s="1" t="n">
         <v>0.0741</v>
       </c>
     </row>
@@ -13013,9 +13832,12 @@
         <v>3.15e-05</v>
       </c>
       <c r="M273" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="N273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="N273" s="1" t="n">
+      <c r="O273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -13059,10 +13881,13 @@
         <v>0.00548</v>
       </c>
       <c r="M274" s="1" t="n">
+        <v>0.005445</v>
+      </c>
+      <c r="N274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="N274" s="1" t="n">
-        <v>0.005469</v>
+      <c r="O274" s="1" t="n">
+        <v>0.005445</v>
       </c>
     </row>
     <row r="275">
@@ -13105,9 +13930,12 @@
         <v>0.1812</v>
       </c>
       <c r="M275" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="N275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="N275" s="1" t="n">
+      <c r="O275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -13151,9 +13979,12 @@
         <v>0.006827</v>
       </c>
       <c r="M276" s="1" t="n">
+        <v>0.006836</v>
+      </c>
+      <c r="N276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="N276" s="1" t="n">
+      <c r="O276" s="1" t="n">
         <v>0.006827</v>
       </c>
     </row>
@@ -13197,9 +14028,12 @@
         <v>0.1309</v>
       </c>
       <c r="M277" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="N277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="N277" s="1" t="n">
+      <c r="O277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -13243,9 +14077,12 @@
         <v>0.02327</v>
       </c>
       <c r="M278" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="N278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="N278" s="1" t="n">
+      <c r="O278" s="1" t="n">
         <v>0.02308</v>
       </c>
     </row>
@@ -13289,9 +14126,12 @@
         <v>0.01822</v>
       </c>
       <c r="M279" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="N279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="N279" s="1" t="n">
+      <c r="O279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -13335,9 +14175,12 @@
         <v>0.03704</v>
       </c>
       <c r="M280" s="1" t="n">
+        <v>0.03717</v>
+      </c>
+      <c r="N280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="N280" s="1" t="n">
+      <c r="O280" s="1" t="n">
         <v>0.03704</v>
       </c>
     </row>
@@ -13381,9 +14224,12 @@
         <v>0.03984</v>
       </c>
       <c r="M281" s="1" t="n">
+        <v>0.03985</v>
+      </c>
+      <c r="N281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="N281" s="1" t="n">
+      <c r="O281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -13427,9 +14273,12 @@
         <v>0.301</v>
       </c>
       <c r="M282" s="1" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="N282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="N282" s="1" t="n">
+      <c r="O282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -13473,9 +14322,12 @@
         <v>0.01121</v>
       </c>
       <c r="M283" s="1" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="N283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="N283" s="1" t="n">
+      <c r="O283" s="1" t="n">
         <v>0.01119</v>
       </c>
     </row>
@@ -13522,6 +14374,9 @@
         <v>9.799999999999999e-06</v>
       </c>
       <c r="N284" s="1" t="n">
+        <v>9.799999999999999e-06</v>
+      </c>
+      <c r="O284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -13565,9 +14420,12 @@
         <v>0.1147</v>
       </c>
       <c r="M285" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="N285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="N285" s="1" t="n">
+      <c r="O285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -13611,9 +14469,12 @@
         <v>0.00343</v>
       </c>
       <c r="M286" s="1" t="n">
+        <v>0.003439</v>
+      </c>
+      <c r="N286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="N286" s="1" t="n">
+      <c r="O286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -13657,9 +14518,12 @@
         <v>0.08562</v>
       </c>
       <c r="M287" s="1" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="N287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="N287" s="1" t="n">
+      <c r="O287" s="1" t="n">
         <v>0.08486</v>
       </c>
     </row>
@@ -13703,9 +14567,12 @@
         <v>0.10076</v>
       </c>
       <c r="M288" s="1" t="n">
+        <v>0.10055</v>
+      </c>
+      <c r="N288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="N288" s="1" t="n">
+      <c r="O288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -13749,9 +14616,12 @@
         <v>0.4326</v>
       </c>
       <c r="M289" s="1" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="N289" s="1" t="n">
         <v>0.4359</v>
       </c>
-      <c r="N289" s="1" t="n">
+      <c r="O289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -13795,9 +14665,12 @@
         <v>0.03915</v>
       </c>
       <c r="M290" s="1" t="n">
+        <v>0.03898</v>
+      </c>
+      <c r="N290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="N290" s="1" t="n">
+      <c r="O290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -13841,10 +14714,13 @@
         <v>0.2374</v>
       </c>
       <c r="M291" s="1" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="N291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="N291" s="1" t="n">
-        <v>0.2374</v>
+      <c r="O291" s="1" t="n">
+        <v>0.2373</v>
       </c>
     </row>
     <row r="292">
@@ -13887,10 +14763,13 @@
         <v>0.28254</v>
       </c>
       <c r="M292" s="1" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="N292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="N292" s="1" t="n">
-        <v>0.28254</v>
+      <c r="O292" s="1" t="n">
+        <v>0.28126</v>
       </c>
     </row>
     <row r="293">
@@ -13933,9 +14812,12 @@
         <v>0.1498</v>
       </c>
       <c r="M293" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="N293" s="1" t="n">
+      <c r="O293" s="1" t="n">
         <v>0.1489</v>
       </c>
     </row>
@@ -13979,10 +14861,13 @@
         <v>4.204</v>
       </c>
       <c r="M294" s="1" t="n">
+        <v>4.203</v>
+      </c>
+      <c r="N294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="N294" s="1" t="n">
-        <v>4.204</v>
+      <c r="O294" s="1" t="n">
+        <v>4.203</v>
       </c>
     </row>
     <row r="295">
@@ -14025,9 +14910,12 @@
         <v>0.03302</v>
       </c>
       <c r="M295" s="1" t="n">
-        <v>0.03339</v>
+        <v>0.03341</v>
       </c>
       <c r="N295" s="1" t="n">
+        <v>0.03341</v>
+      </c>
+      <c r="O295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -14071,9 +14959,12 @@
         <v>0.000965</v>
       </c>
       <c r="M296" s="1" t="n">
+        <v>0.000972</v>
+      </c>
+      <c r="N296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="N296" s="1" t="n">
+      <c r="O296" s="1" t="n">
         <v>0.000965</v>
       </c>
     </row>
@@ -14117,9 +15008,12 @@
         <v>0.08172</v>
       </c>
       <c r="M297" s="1" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="N297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="N297" s="1" t="n">
+      <c r="O297" s="1" t="n">
         <v>0.08154</v>
       </c>
     </row>
@@ -14163,9 +15057,12 @@
         <v>0.05812</v>
       </c>
       <c r="M298" s="1" t="n">
-        <v>0.05821</v>
+        <v>0.05845</v>
       </c>
       <c r="N298" s="1" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="O298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -14209,9 +15106,12 @@
         <v>0.0914</v>
       </c>
       <c r="M299" s="1" t="n">
+        <v>0.09096</v>
+      </c>
+      <c r="N299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="N299" s="1" t="n">
+      <c r="O299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -14255,9 +15155,12 @@
         <v>0.02752</v>
       </c>
       <c r="M300" s="1" t="n">
+        <v>0.02744</v>
+      </c>
+      <c r="N300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="N300" s="1" t="n">
+      <c r="O300" s="1" t="n">
         <v>0.0274</v>
       </c>
     </row>
@@ -14301,9 +15204,12 @@
         <v>0.06568</v>
       </c>
       <c r="M301" s="1" t="n">
+        <v>0.06568</v>
+      </c>
+      <c r="N301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="N301" s="1" t="n">
+      <c r="O301" s="1" t="n">
         <v>0.06557</v>
       </c>
     </row>
@@ -14347,9 +15253,12 @@
         <v>0.0535</v>
       </c>
       <c r="M302" s="1" t="n">
-        <v>0.0535</v>
+        <v>0.053585</v>
       </c>
       <c r="N302" s="1" t="n">
+        <v>0.053585</v>
+      </c>
+      <c r="O302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -14393,9 +15302,12 @@
         <v>5171.5</v>
       </c>
       <c r="M303" s="1" t="n">
+        <v>5170</v>
+      </c>
+      <c r="N303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="N303" s="1" t="n">
+      <c r="O303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -14439,9 +15351,12 @@
         <v>14.88</v>
       </c>
       <c r="M304" s="1" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="N304" s="1" t="n">
+      <c r="O304" s="1" t="n">
         <v>14.88</v>
       </c>
     </row>
@@ -14485,9 +15400,12 @@
         <v>0.003711</v>
       </c>
       <c r="M305" s="1" t="n">
+        <v>0.003713</v>
+      </c>
+      <c r="N305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="N305" s="1" t="n">
+      <c r="O305" s="1" t="n">
         <v>0.003695</v>
       </c>
     </row>
@@ -14531,9 +15449,12 @@
         <v>0.4562</v>
       </c>
       <c r="M306" s="1" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="N306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="N306" s="1" t="n">
+      <c r="O306" s="1" t="n">
         <v>0.4558</v>
       </c>
     </row>
@@ -14577,10 +15498,13 @@
         <v>0.04698</v>
       </c>
       <c r="M307" s="1" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="N307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="N307" s="1" t="n">
-        <v>0.04696</v>
+      <c r="O307" s="1" t="n">
+        <v>0.04682</v>
       </c>
     </row>
     <row r="308">
@@ -14623,9 +15547,12 @@
         <v>1.4918</v>
       </c>
       <c r="M308" s="1" t="n">
-        <v>1.4918</v>
+        <v>1.4939</v>
       </c>
       <c r="N308" s="1" t="n">
+        <v>1.4939</v>
+      </c>
+      <c r="O308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -14669,9 +15596,12 @@
         <v>0.0007892</v>
       </c>
       <c r="M309" s="1" t="n">
+        <v>0.0008085</v>
+      </c>
+      <c r="N309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="N309" s="1" t="n">
+      <c r="O309" s="1" t="n">
         <v>0.0007892</v>
       </c>
     </row>
@@ -14715,9 +15645,12 @@
         <v>4.579</v>
       </c>
       <c r="M310" s="1" t="n">
+        <v>4.596</v>
+      </c>
+      <c r="N310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="N310" s="1" t="n">
+      <c r="O310" s="1" t="n">
         <v>4.579</v>
       </c>
     </row>
@@ -14761,9 +15694,12 @@
         <v>4.756</v>
       </c>
       <c r="M311" s="1" t="n">
+        <v>4.771</v>
+      </c>
+      <c r="N311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="N311" s="1" t="n">
+      <c r="O311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -14807,9 +15743,12 @@
         <v>0.08141</v>
       </c>
       <c r="M312" s="1" t="n">
+        <v>0.08159</v>
+      </c>
+      <c r="N312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="N312" s="1" t="n">
+      <c r="O312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -14853,9 +15792,12 @@
         <v>2.012</v>
       </c>
       <c r="M313" s="1" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="N313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="N313" s="1" t="n">
+      <c r="O313" s="1" t="n">
         <v>2.012</v>
       </c>
     </row>
@@ -14899,9 +15841,12 @@
         <v>0.07260999999999999</v>
       </c>
       <c r="M314" s="1" t="n">
-        <v>0.07260999999999999</v>
+        <v>0.07482999999999999</v>
       </c>
       <c r="N314" s="1" t="n">
+        <v>0.07482999999999999</v>
+      </c>
+      <c r="O314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -14945,10 +15890,13 @@
         <v>0.945</v>
       </c>
       <c r="M315" s="1" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="N315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="N315" s="1" t="n">
-        <v>0.945</v>
+      <c r="O315" s="1" t="n">
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="316">
@@ -14991,9 +15939,12 @@
         <v>0.1309</v>
       </c>
       <c r="M316" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="N316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="N316" s="1" t="n">
+      <c r="O316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -15037,9 +15988,12 @@
         <v>0.1828</v>
       </c>
       <c r="M317" s="1" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="N317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="N317" s="1" t="n">
+      <c r="O317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -15083,9 +16037,12 @@
         <v>0.01622</v>
       </c>
       <c r="M318" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="N318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="N318" s="1" t="n">
+      <c r="O318" s="1" t="n">
         <v>0.01615</v>
       </c>
     </row>
@@ -15129,9 +16086,12 @@
         <v>0.08343</v>
       </c>
       <c r="M319" s="1" t="n">
+        <v>0.08357000000000001</v>
+      </c>
+      <c r="N319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="N319" s="1" t="n">
+      <c r="O319" s="1" t="n">
         <v>0.08343</v>
       </c>
     </row>
@@ -15175,9 +16135,12 @@
         <v>0.00763</v>
       </c>
       <c r="M320" s="1" t="n">
+        <v>0.007617</v>
+      </c>
+      <c r="N320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="N320" s="1" t="n">
+      <c r="O320" s="1" t="n">
         <v>0.007571</v>
       </c>
     </row>
@@ -15221,9 +16184,12 @@
         <v>0.0544</v>
       </c>
       <c r="M321" s="1" t="n">
+        <v>0.05432</v>
+      </c>
+      <c r="N321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="N321" s="1" t="n">
+      <c r="O321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -15267,9 +16233,12 @@
         <v>0.5505</v>
       </c>
       <c r="M322" s="1" t="n">
+        <v>0.5507</v>
+      </c>
+      <c r="N322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="N322" s="1" t="n">
+      <c r="O322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -15313,9 +16282,12 @@
         <v>0.07636999999999999</v>
       </c>
       <c r="M323" s="1" t="n">
+        <v>0.07609</v>
+      </c>
+      <c r="N323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="N323" s="1" t="n">
+      <c r="O323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -15359,9 +16331,12 @@
         <v>0.012936</v>
       </c>
       <c r="M324" s="1" t="n">
+        <v>0.012985</v>
+      </c>
+      <c r="N324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="N324" s="1" t="n">
+      <c r="O324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -15405,9 +16380,12 @@
         <v>0.0989</v>
       </c>
       <c r="M325" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="N325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="N325" s="1" t="n">
+      <c r="O325" s="1" t="n">
         <v>0.0989</v>
       </c>
     </row>
@@ -15451,9 +16429,12 @@
         <v>0.01739</v>
       </c>
       <c r="M326" s="1" t="n">
+        <v>0.01741</v>
+      </c>
+      <c r="N326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="N326" s="1" t="n">
+      <c r="O326" s="1" t="n">
         <v>0.01731</v>
       </c>
     </row>
@@ -15497,9 +16478,12 @@
         <v>0.06394</v>
       </c>
       <c r="M327" s="1" t="n">
+        <v>0.06401999999999999</v>
+      </c>
+      <c r="N327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="N327" s="1" t="n">
+      <c r="O327" s="1" t="n">
         <v>0.06382</v>
       </c>
     </row>
@@ -15543,9 +16527,12 @@
         <v>0.2622</v>
       </c>
       <c r="M328" s="1" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="N328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="N328" s="1" t="n">
+      <c r="O328" s="1" t="n">
         <v>0.2622</v>
       </c>
     </row>
@@ -15589,9 +16576,12 @@
         <v>0.17341</v>
       </c>
       <c r="M329" s="1" t="n">
+        <v>0.17301</v>
+      </c>
+      <c r="N329" s="1" t="n">
         <v>0.17341</v>
       </c>
-      <c r="N329" s="1" t="n">
+      <c r="O329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -15635,9 +16625,12 @@
         <v>2.047</v>
       </c>
       <c r="M330" s="1" t="n">
+        <v>2.063</v>
+      </c>
+      <c r="N330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="N330" s="1" t="n">
+      <c r="O330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -15681,9 +16674,12 @@
         <v>0.0288</v>
       </c>
       <c r="M331" s="1" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="N331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="N331" s="1" t="n">
+      <c r="O331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -15727,9 +16723,12 @@
         <v>0.006032</v>
       </c>
       <c r="M332" s="1" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="N332" s="1" t="n">
         <v>0.006032</v>
       </c>
-      <c r="N332" s="1" t="n">
+      <c r="O332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -15773,9 +16772,12 @@
         <v>0.003534</v>
       </c>
       <c r="M333" s="1" t="n">
+        <v>0.003532</v>
+      </c>
+      <c r="N333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="N333" s="1" t="n">
+      <c r="O333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -15819,9 +16821,12 @@
         <v>0.014</v>
       </c>
       <c r="M334" s="1" t="n">
+        <v>0.01403</v>
+      </c>
+      <c r="N334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="N334" s="1" t="n">
+      <c r="O334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -15868,6 +16873,9 @@
         <v>1.136</v>
       </c>
       <c r="N335" s="1" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="O335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -15911,9 +16919,12 @@
         <v>0.011259</v>
       </c>
       <c r="M336" s="1" t="n">
+        <v>0.011312</v>
+      </c>
+      <c r="N336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="N336" s="1" t="n">
+      <c r="O336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -15957,9 +16968,12 @@
         <v>2.975</v>
       </c>
       <c r="M337" s="1" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="N337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="N337" s="1" t="n">
+      <c r="O337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -16003,9 +17017,12 @@
         <v>0.01862</v>
       </c>
       <c r="M338" s="1" t="n">
+        <v>0.01863</v>
+      </c>
+      <c r="N338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="N338" s="1" t="n">
+      <c r="O338" s="1" t="n">
         <v>0.01858</v>
       </c>
     </row>
@@ -16049,9 +17066,12 @@
         <v>0.07731</v>
       </c>
       <c r="M339" s="1" t="n">
+        <v>0.07756</v>
+      </c>
+      <c r="N339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="N339" s="1" t="n">
+      <c r="O339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -16095,9 +17115,12 @@
         <v>0.075</v>
       </c>
       <c r="M340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="N340" s="1" t="n">
+      <c r="O340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -16141,9 +17164,12 @@
         <v>0.03585</v>
       </c>
       <c r="M341" s="1" t="n">
+        <v>0.03592</v>
+      </c>
+      <c r="N341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="N341" s="1" t="n">
+      <c r="O341" s="1" t="n">
         <v>0.03585</v>
       </c>
     </row>
@@ -16187,9 +17213,12 @@
         <v>2610</v>
       </c>
       <c r="M342" s="1" t="n">
+        <v>2607</v>
+      </c>
+      <c r="N342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="N342" s="1" t="n">
+      <c r="O342" s="1" t="n">
         <v>2606</v>
       </c>
     </row>
@@ -16233,9 +17262,12 @@
         <v>0.0001974</v>
       </c>
       <c r="M343" s="1" t="n">
-        <v>0.000198</v>
+        <v>0.0002003</v>
       </c>
       <c r="N343" s="1" t="n">
+        <v>0.0002003</v>
+      </c>
+      <c r="O343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -16279,9 +17311,12 @@
         <v>0.07944</v>
       </c>
       <c r="M344" s="1" t="n">
+        <v>0.07961</v>
+      </c>
+      <c r="N344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="N344" s="1" t="n">
+      <c r="O344" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -16325,9 +17360,12 @@
         <v>0.01669</v>
       </c>
       <c r="M345" s="1" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="N345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="N345" s="1" t="n">
+      <c r="O345" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -16371,9 +17409,12 @@
         <v>2.752</v>
       </c>
       <c r="M346" s="1" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="N346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="N346" s="1" t="n">
+      <c r="O346" s="1" t="n">
         <v>2.746</v>
       </c>
     </row>
@@ -16417,9 +17458,12 @@
         <v>0.01634</v>
       </c>
       <c r="M347" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="N347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="N347" s="1" t="n">
+      <c r="O347" s="1" t="n">
         <v>0.01631</v>
       </c>
     </row>
@@ -16463,9 +17507,12 @@
         <v>0.03929</v>
       </c>
       <c r="M348" s="1" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="N348" s="1" t="n">
         <v>0.03929</v>
       </c>
-      <c r="N348" s="1" t="n">
+      <c r="O348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -16509,9 +17556,12 @@
         <v>0.3028</v>
       </c>
       <c r="M349" s="1" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="N349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="N349" s="1" t="n">
+      <c r="O349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -16555,9 +17605,12 @@
         <v>0.005105</v>
       </c>
       <c r="M350" s="1" t="n">
+        <v>0.005113</v>
+      </c>
+      <c r="N350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="N350" s="1" t="n">
+      <c r="O350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -16601,9 +17654,12 @@
         <v>0.005104</v>
       </c>
       <c r="M351" s="1" t="n">
+        <v>0.005093</v>
+      </c>
+      <c r="N351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="N351" s="1" t="n">
+      <c r="O351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -16647,9 +17703,12 @@
         <v>0.004397</v>
       </c>
       <c r="M352" s="1" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="N352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="N352" s="1" t="n">
+      <c r="O352" s="1" t="n">
         <v>0.004384</v>
       </c>
     </row>
@@ -16693,9 +17752,12 @@
         <v>0.08093</v>
       </c>
       <c r="M353" s="1" t="n">
+        <v>0.08083</v>
+      </c>
+      <c r="N353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="N353" s="1" t="n">
+      <c r="O353" s="1" t="n">
         <v>0.08062999999999999</v>
       </c>
     </row>
@@ -16739,9 +17801,12 @@
         <v>1.279</v>
       </c>
       <c r="M354" s="1" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="N354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="N354" s="1" t="n">
+      <c r="O354" s="1" t="n">
         <v>1.277</v>
       </c>
     </row>
@@ -16785,10 +17850,13 @@
         <v>7.705</v>
       </c>
       <c r="M355" s="1" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="N355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="N355" s="1" t="n">
-        <v>7.705</v>
+      <c r="O355" s="1" t="n">
+        <v>7.7</v>
       </c>
     </row>
     <row r="356">
@@ -16831,9 +17899,12 @@
         <v>0.007820000000000001</v>
       </c>
       <c r="M356" s="1" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="N356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="N356" s="1" t="n">
+      <c r="O356" s="1" t="n">
         <v>0.00778</v>
       </c>
     </row>
@@ -16877,10 +17948,13 @@
         <v>0.005637</v>
       </c>
       <c r="M357" s="1" t="n">
+        <v>0.00563</v>
+      </c>
+      <c r="N357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="N357" s="1" t="n">
-        <v>0.005632</v>
+      <c r="O357" s="1" t="n">
+        <v>0.00563</v>
       </c>
     </row>
     <row r="358">
@@ -16923,10 +17997,13 @@
         <v>0.01555</v>
       </c>
       <c r="M358" s="1" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="N358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="N358" s="1" t="n">
-        <v>0.01551</v>
+      <c r="O358" s="1" t="n">
+        <v>0.01549</v>
       </c>
     </row>
     <row r="359">
@@ -16969,9 +18046,12 @@
         <v>3.635</v>
       </c>
       <c r="M359" s="1" t="n">
+        <v>3.636</v>
+      </c>
+      <c r="N359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="N359" s="1" t="n">
+      <c r="O359" s="1" t="n">
         <v>3.635</v>
       </c>
     </row>
@@ -17015,9 +18095,12 @@
         <v>0.15</v>
       </c>
       <c r="M360" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="N360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="N360" s="1" t="n">
+      <c r="O360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -17061,9 +18144,12 @@
         <v>0.07047</v>
       </c>
       <c r="M361" s="1" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="N361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="N361" s="1" t="n">
+      <c r="O361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -17107,9 +18193,12 @@
         <v>0.01765</v>
       </c>
       <c r="M362" s="1" t="n">
+        <v>0.01766</v>
+      </c>
+      <c r="N362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="N362" s="1" t="n">
+      <c r="O362" s="1" t="n">
         <v>0.01761</v>
       </c>
     </row>
@@ -17153,9 +18242,12 @@
         <v>0.02241</v>
       </c>
       <c r="M363" s="1" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="N363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="N363" s="1" t="n">
+      <c r="O363" s="1" t="n">
         <v>0.02234</v>
       </c>
     </row>
@@ -17199,9 +18291,12 @@
         <v>0.01259</v>
       </c>
       <c r="M364" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="N364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="N364" s="1" t="n">
+      <c r="O364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -17245,9 +18340,12 @@
         <v>0.0914</v>
       </c>
       <c r="M365" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="N365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="N365" s="1" t="n">
+      <c r="O365" s="1" t="n">
         <v>0.0914</v>
       </c>
     </row>
@@ -17291,9 +18389,12 @@
         <v>0.04232</v>
       </c>
       <c r="M366" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="N366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="N366" s="1" t="n">
+      <c r="O366" s="1" t="n">
         <v>0.04224</v>
       </c>
     </row>
@@ -17337,9 +18438,12 @@
         <v>0.03188</v>
       </c>
       <c r="M367" s="1" t="n">
+        <v>0.03151</v>
+      </c>
+      <c r="N367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="N367" s="1" t="n">
+      <c r="O367" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -17383,9 +18487,12 @@
         <v>0.02331</v>
       </c>
       <c r="M368" s="1" t="n">
+        <v>0.02345</v>
+      </c>
+      <c r="N368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="N368" s="1" t="n">
+      <c r="O368" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -17429,9 +18536,12 @@
         <v>0.03099</v>
       </c>
       <c r="M369" s="1" t="n">
+        <v>0.03096</v>
+      </c>
+      <c r="N369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="N369" s="1" t="n">
+      <c r="O369" s="1" t="n">
         <v>0.03089</v>
       </c>
     </row>
@@ -17475,9 +18585,12 @@
         <v>0.0794</v>
       </c>
       <c r="M370" s="1" t="n">
-        <v>0.0794</v>
+        <v>0.07990999999999999</v>
       </c>
       <c r="N370" s="1" t="n">
+        <v>0.07990999999999999</v>
+      </c>
+      <c r="O370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -17521,9 +18634,12 @@
         <v>0.1076</v>
       </c>
       <c r="M371" s="1" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="N371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="N371" s="1" t="n">
+      <c r="O371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -17567,9 +18683,12 @@
         <v>0.007024</v>
       </c>
       <c r="M372" s="1" t="n">
+        <v>0.007051</v>
+      </c>
+      <c r="N372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="N372" s="1" t="n">
+      <c r="O372" s="1" t="n">
         <v>0.007024</v>
       </c>
     </row>
@@ -17613,9 +18732,12 @@
         <v>0.096</v>
       </c>
       <c r="M373" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="N373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="N373" s="1" t="n">
+      <c r="O373" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -17659,9 +18781,12 @@
         <v>0.05771</v>
       </c>
       <c r="M374" s="1" t="n">
+        <v>0.05778</v>
+      </c>
+      <c r="N374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="N374" s="1" t="n">
+      <c r="O374" s="1" t="n">
         <v>0.05771</v>
       </c>
     </row>
@@ -17705,9 +18830,12 @@
         <v>0.3213</v>
       </c>
       <c r="M375" s="1" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="N375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="N375" s="1" t="n">
+      <c r="O375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -17751,9 +18879,12 @@
         <v>0.0195</v>
       </c>
       <c r="M376" s="1" t="n">
+        <v>0.01953</v>
+      </c>
+      <c r="N376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="N376" s="1" t="n">
+      <c r="O376" s="1" t="n">
         <v>0.0195</v>
       </c>
     </row>
@@ -17797,9 +18928,12 @@
         <v>0.0684</v>
       </c>
       <c r="M377" s="1" t="n">
+        <v>0.06854</v>
+      </c>
+      <c r="N377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="N377" s="1" t="n">
+      <c r="O377" s="1" t="n">
         <v>0.0684</v>
       </c>
     </row>
@@ -17843,9 +18977,12 @@
         <v>0.15577</v>
       </c>
       <c r="M378" s="1" t="n">
+        <v>0.15664</v>
+      </c>
+      <c r="N378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="N378" s="1" t="n">
+      <c r="O378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -17889,9 +19026,12 @@
         <v>0.0005982</v>
       </c>
       <c r="M379" s="1" t="n">
+        <v>0.0005977000000000001</v>
+      </c>
+      <c r="N379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="N379" s="1" t="n">
+      <c r="O379" s="1" t="n">
         <v>0.0005965</v>
       </c>
     </row>
@@ -17935,9 +19075,12 @@
         <v>0.01015</v>
       </c>
       <c r="M380" s="1" t="n">
+        <v>0.01018</v>
+      </c>
+      <c r="N380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="N380" s="1" t="n">
+      <c r="O380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -17981,9 +19124,12 @@
         <v>0.02553</v>
       </c>
       <c r="M381" s="1" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="N381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="N381" s="1" t="n">
+      <c r="O381" s="1" t="n">
         <v>0.02547</v>
       </c>
     </row>
@@ -18027,9 +19173,12 @@
         <v>0.19163</v>
       </c>
       <c r="M382" s="1" t="n">
+        <v>0.19134</v>
+      </c>
+      <c r="N382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="N382" s="1" t="n">
+      <c r="O382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -18073,9 +19222,12 @@
         <v>0.09242</v>
       </c>
       <c r="M383" s="1" t="n">
+        <v>0.09329</v>
+      </c>
+      <c r="N383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="N383" s="1" t="n">
+      <c r="O383" s="1" t="n">
         <v>0.09236</v>
       </c>
     </row>
@@ -18119,9 +19271,12 @@
         <v>0.03166</v>
       </c>
       <c r="M384" s="1" t="n">
+        <v>0.03167</v>
+      </c>
+      <c r="N384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="N384" s="1" t="n">
+      <c r="O384" s="1" t="n">
         <v>0.03166</v>
       </c>
     </row>
@@ -18165,9 +19320,12 @@
         <v>0.01093</v>
       </c>
       <c r="M385" s="1" t="n">
+        <v>0.01098</v>
+      </c>
+      <c r="N385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="N385" s="1" t="n">
+      <c r="O385" s="1" t="n">
         <v>0.01093</v>
       </c>
     </row>
@@ -18211,9 +19369,12 @@
         <v>0.05123</v>
       </c>
       <c r="M386" s="1" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="N386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="N386" s="1" t="n">
+      <c r="O386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -18257,9 +19418,12 @@
         <v>0.02513</v>
       </c>
       <c r="M387" s="1" t="n">
+        <v>0.02514</v>
+      </c>
+      <c r="N387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="N387" s="1" t="n">
+      <c r="O387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -18303,9 +19467,12 @@
         <v>0.007302</v>
       </c>
       <c r="M388" s="1" t="n">
+        <v>0.00728</v>
+      </c>
+      <c r="N388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="N388" s="1" t="n">
+      <c r="O388" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -18349,9 +19516,12 @@
         <v>0.0101</v>
       </c>
       <c r="M389" s="1" t="n">
+        <v>0.01014</v>
+      </c>
+      <c r="N389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="N389" s="1" t="n">
+      <c r="O389" s="1" t="n">
         <v>0.0101</v>
       </c>
     </row>
@@ -18395,9 +19565,12 @@
         <v>0.08260000000000001</v>
       </c>
       <c r="M390" s="1" t="n">
+        <v>0.08266</v>
+      </c>
+      <c r="N390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="N390" s="1" t="n">
+      <c r="O390" s="1" t="n">
         <v>0.08233</v>
       </c>
     </row>
@@ -18441,9 +19614,12 @@
         <v>0.5047</v>
       </c>
       <c r="M391" s="1" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="N391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="N391" s="1" t="n">
+      <c r="O391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -18487,9 +19663,12 @@
         <v>0.1165</v>
       </c>
       <c r="M392" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="N392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="N392" s="1" t="n">
+      <c r="O392" s="1" t="n">
         <v>0.1165</v>
       </c>
     </row>
@@ -18533,9 +19712,12 @@
         <v>0.00245</v>
       </c>
       <c r="M393" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="N393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="N393" s="1" t="n">
+      <c r="O393" s="1" t="n">
         <v>0.00245</v>
       </c>
     </row>
@@ -18579,9 +19761,12 @@
         <v>0.02126</v>
       </c>
       <c r="M394" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="N394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="N394" s="1" t="n">
+      <c r="O394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -18625,9 +19810,12 @@
         <v>0.016</v>
       </c>
       <c r="M395" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="N395" s="1" t="n">
+      <c r="O395" s="1" t="n">
         <v>0.0159</v>
       </c>
     </row>
@@ -18671,10 +19859,13 @@
         <v>0.1354</v>
       </c>
       <c r="M396" s="1" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="N396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="N396" s="1" t="n">
-        <v>0.1354</v>
+      <c r="O396" s="1" t="n">
+        <v>0.1353</v>
       </c>
     </row>
     <row r="397">
@@ -18717,9 +19908,12 @@
         <v>0.01458</v>
       </c>
       <c r="M397" s="1" t="n">
+        <v>0.01453</v>
+      </c>
+      <c r="N397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="N397" s="1" t="n">
+      <c r="O397" s="1" t="n">
         <v>0.01452</v>
       </c>
     </row>
@@ -18763,9 +19957,12 @@
         <v>6.708</v>
       </c>
       <c r="M398" s="1" t="n">
+        <v>6.797</v>
+      </c>
+      <c r="N398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="N398" s="1" t="n">
+      <c r="O398" s="1" t="n">
         <v>6.708</v>
       </c>
     </row>
@@ -18809,10 +20006,13 @@
         <v>0.009414</v>
       </c>
       <c r="M399" s="1" t="n">
+        <v>0.009396</v>
+      </c>
+      <c r="N399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="N399" s="1" t="n">
-        <v>0.009414</v>
+      <c r="O399" s="1" t="n">
+        <v>0.009396</v>
       </c>
     </row>
     <row r="400">
@@ -18855,9 +20055,12 @@
         <v>0.001265</v>
       </c>
       <c r="M400" s="1" t="n">
+        <v>0.00127</v>
+      </c>
+      <c r="N400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="N400" s="1" t="n">
+      <c r="O400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -18901,9 +20104,12 @@
         <v>0.01849</v>
       </c>
       <c r="M401" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="N401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="N401" s="1" t="n">
+      <c r="O401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -18947,9 +20153,12 @@
         <v>0.08498</v>
       </c>
       <c r="M402" s="1" t="n">
+        <v>0.08507000000000001</v>
+      </c>
+      <c r="N402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="N402" s="1" t="n">
+      <c r="O402" s="1" t="n">
         <v>0.08488999999999999</v>
       </c>
     </row>
@@ -18993,9 +20202,12 @@
         <v>0.00551</v>
       </c>
       <c r="M403" s="1" t="n">
+        <v>0.00553</v>
+      </c>
+      <c r="N403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="N403" s="1" t="n">
+      <c r="O403" s="1" t="n">
         <v>0.00551</v>
       </c>
     </row>
@@ -19039,9 +20251,12 @@
         <v>0.04271</v>
       </c>
       <c r="M404" s="1" t="n">
+        <v>0.04272</v>
+      </c>
+      <c r="N404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="N404" s="1" t="n">
+      <c r="O404" s="1" t="n">
         <v>0.04271</v>
       </c>
     </row>
@@ -19085,10 +20300,13 @@
         <v>0.05842</v>
       </c>
       <c r="M405" s="1" t="n">
+        <v>0.05836</v>
+      </c>
+      <c r="N405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="N405" s="1" t="n">
-        <v>0.05838</v>
+      <c r="O405" s="1" t="n">
+        <v>0.05836</v>
       </c>
     </row>
     <row r="406">
@@ -19131,9 +20349,12 @@
         <v>0.01658</v>
       </c>
       <c r="M406" s="1" t="n">
+        <v>0.01663</v>
+      </c>
+      <c r="N406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="N406" s="1" t="n">
+      <c r="O406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -19177,9 +20398,12 @@
         <v>0.0424</v>
       </c>
       <c r="M407" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="N407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="N407" s="1" t="n">
+      <c r="O407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -19223,9 +20447,12 @@
         <v>0.01928</v>
       </c>
       <c r="M408" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="N408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="N408" s="1" t="n">
+      <c r="O408" s="1" t="n">
         <v>0.01927</v>
       </c>
     </row>
@@ -19269,9 +20496,12 @@
         <v>0.4458</v>
       </c>
       <c r="M409" s="1" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="N409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="N409" s="1" t="n">
+      <c r="O409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -19315,9 +20545,12 @@
         <v>0.04408</v>
       </c>
       <c r="M410" s="1" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="N410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="N410" s="1" t="n">
+      <c r="O410" s="1" t="n">
         <v>0.04408</v>
       </c>
     </row>
@@ -19361,9 +20594,12 @@
         <v>27.42</v>
       </c>
       <c r="M411" s="1" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="N411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="N411" s="1" t="n">
+      <c r="O411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -19407,9 +20643,12 @@
         <v>0.03508</v>
       </c>
       <c r="M412" s="1" t="n">
+        <v>0.03522</v>
+      </c>
+      <c r="N412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="N412" s="1" t="n">
+      <c r="O412" s="1" t="n">
         <v>0.03508</v>
       </c>
     </row>
@@ -19453,9 +20692,12 @@
         <v>0.003397</v>
       </c>
       <c r="M413" s="1" t="n">
+        <v>0.003401</v>
+      </c>
+      <c r="N413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="N413" s="1" t="n">
+      <c r="O413" s="1" t="n">
         <v>0.003397</v>
       </c>
     </row>
@@ -19499,9 +20741,12 @@
         <v>0.1531</v>
       </c>
       <c r="M414" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="N414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="N414" s="1" t="n">
+      <c r="O414" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -19545,9 +20790,12 @@
         <v>0.05272</v>
       </c>
       <c r="M415" s="1" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="N415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="N415" s="1" t="n">
+      <c r="O415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -19591,9 +20839,12 @@
         <v>0.00659</v>
       </c>
       <c r="M416" s="1" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="N416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="N416" s="1" t="n">
+      <c r="O416" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -19637,9 +20888,12 @@
         <v>0.06045</v>
       </c>
       <c r="M417" s="1" t="n">
+        <v>0.06052</v>
+      </c>
+      <c r="N417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="N417" s="1" t="n">
+      <c r="O417" s="1" t="n">
         <v>0.06045</v>
       </c>
     </row>
@@ -19683,9 +20937,12 @@
         <v>0.007979</v>
       </c>
       <c r="M418" s="1" t="n">
+        <v>0.008036</v>
+      </c>
+      <c r="N418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="N418" s="1" t="n">
+      <c r="O418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -19729,9 +20986,12 @@
         <v>0.07444000000000001</v>
       </c>
       <c r="M419" s="1" t="n">
+        <v>0.07464999999999999</v>
+      </c>
+      <c r="N419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="N419" s="1" t="n">
+      <c r="O419" s="1" t="n">
         <v>0.07435</v>
       </c>
     </row>
@@ -19775,9 +21035,12 @@
         <v>0.02117</v>
       </c>
       <c r="M420" s="1" t="n">
+        <v>0.02128</v>
+      </c>
+      <c r="N420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="N420" s="1" t="n">
+      <c r="O420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -19821,9 +21084,12 @@
         <v>0.06959</v>
       </c>
       <c r="M421" s="1" t="n">
+        <v>0.06962</v>
+      </c>
+      <c r="N421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="N421" s="1" t="n">
+      <c r="O421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -19867,9 +21133,12 @@
         <v>0.01487</v>
       </c>
       <c r="M422" s="1" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="N422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="N422" s="1" t="n">
+      <c r="O422" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -19913,10 +21182,13 @@
         <v>0.006652</v>
       </c>
       <c r="M423" s="1" t="n">
+        <v>0.006638</v>
+      </c>
+      <c r="N423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="N423" s="1" t="n">
-        <v>0.006648</v>
+      <c r="O423" s="1" t="n">
+        <v>0.006638</v>
       </c>
     </row>
     <row r="424">
@@ -19959,9 +21231,12 @@
         <v>0.909</v>
       </c>
       <c r="M424" s="1" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="N424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="N424" s="1" t="n">
+      <c r="O424" s="1" t="n">
         <v>0.909</v>
       </c>
     </row>
@@ -20005,9 +21280,12 @@
         <v>0.03572</v>
       </c>
       <c r="M425" s="1" t="n">
+        <v>0.03567</v>
+      </c>
+      <c r="N425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="N425" s="1" t="n">
+      <c r="O425" s="1" t="n">
         <v>0.03546</v>
       </c>
     </row>
@@ -20051,9 +21329,12 @@
         <v>1.778</v>
       </c>
       <c r="M426" s="1" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="N426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="N426" s="1" t="n">
+      <c r="O426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -20097,9 +21378,12 @@
         <v>0.12805</v>
       </c>
       <c r="M427" s="1" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="N427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="N427" s="1" t="n">
+      <c r="O427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -20143,9 +21427,12 @@
         <v>0.05319</v>
       </c>
       <c r="M428" s="1" t="n">
+        <v>0.05307</v>
+      </c>
+      <c r="N428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="N428" s="1" t="n">
+      <c r="O428" s="1" t="n">
         <v>0.05297</v>
       </c>
     </row>
@@ -20189,9 +21476,12 @@
         <v>1.289</v>
       </c>
       <c r="M429" s="1" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="N429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="N429" s="1" t="n">
+      <c r="O429" s="1" t="n">
         <v>1.289</v>
       </c>
     </row>
@@ -20235,9 +21525,12 @@
         <v>0.07492</v>
       </c>
       <c r="M430" s="1" t="n">
+        <v>0.07488</v>
+      </c>
+      <c r="N430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="N430" s="1" t="n">
+      <c r="O430" s="1" t="n">
         <v>0.07482</v>
       </c>
     </row>
@@ -20281,9 +21574,12 @@
         <v>0.157</v>
       </c>
       <c r="M431" s="1" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="N431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="N431" s="1" t="n">
+      <c r="O431" s="1" t="n">
         <v>0.157</v>
       </c>
     </row>
@@ -20327,9 +21623,12 @@
         <v>1.45</v>
       </c>
       <c r="M432" s="1" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="N432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="N432" s="1" t="n">
+      <c r="O432" s="1" t="n">
         <v>1.445</v>
       </c>
     </row>
@@ -20373,9 +21672,12 @@
         <v>3.27</v>
       </c>
       <c r="M433" s="1" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="N433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="N433" s="1" t="n">
+      <c r="O433" s="1" t="n">
         <v>3.266</v>
       </c>
     </row>
@@ -20419,9 +21721,12 @@
         <v>0.179</v>
       </c>
       <c r="M434" s="1" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="N434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="N434" s="1" t="n">
+      <c r="O434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -20465,9 +21770,12 @@
         <v>0.00859</v>
       </c>
       <c r="M435" s="1" t="n">
+        <v>0.008598</v>
+      </c>
+      <c r="N435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="N435" s="1" t="n">
+      <c r="O435" s="1" t="n">
         <v>0.008580000000000001</v>
       </c>
     </row>
@@ -20511,9 +21819,12 @@
         <v>0.2828</v>
       </c>
       <c r="M436" s="1" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="N436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="N436" s="1" t="n">
+      <c r="O436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -20557,9 +21868,12 @@
         <v>0.03896</v>
       </c>
       <c r="M437" s="1" t="n">
+        <v>0.03898</v>
+      </c>
+      <c r="N437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="N437" s="1" t="n">
+      <c r="O437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -20603,9 +21917,12 @@
         <v>0.02436</v>
       </c>
       <c r="M438" s="1" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="N438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="N438" s="1" t="n">
+      <c r="O438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -20649,9 +21966,12 @@
         <v>0.04403</v>
       </c>
       <c r="M439" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="N439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="N439" s="1" t="n">
+      <c r="O439" s="1" t="n">
         <v>0.04403</v>
       </c>
     </row>
@@ -20695,9 +22015,12 @@
         <v>0.0005192</v>
       </c>
       <c r="M440" s="1" t="n">
+        <v>0.0005195</v>
+      </c>
+      <c r="N440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="N440" s="1" t="n">
+      <c r="O440" s="1" t="n">
         <v>0.0005188</v>
       </c>
     </row>
@@ -20741,9 +22064,12 @@
         <v>0.04428</v>
       </c>
       <c r="M441" s="1" t="n">
+        <v>0.04467</v>
+      </c>
+      <c r="N441" s="1" t="n">
         <v>0.04489</v>
       </c>
-      <c r="N441" s="1" t="n">
+      <c r="O441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -20787,9 +22113,12 @@
         <v>0.000412</v>
       </c>
       <c r="M442" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="N442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="N442" s="1" t="n">
+      <c r="O442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -20833,10 +22162,13 @@
         <v>0.09505</v>
       </c>
       <c r="M443" s="1" t="n">
+        <v>0.09467</v>
+      </c>
+      <c r="N443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="N443" s="1" t="n">
-        <v>0.0949</v>
+      <c r="O443" s="1" t="n">
+        <v>0.09467</v>
       </c>
     </row>
     <row r="444">
@@ -20879,9 +22211,12 @@
         <v>2.307</v>
       </c>
       <c r="M444" s="1" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="N444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="N444" s="1" t="n">
+      <c r="O444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -20925,9 +22260,12 @@
         <v>0.2684</v>
       </c>
       <c r="M445" s="1" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="N445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="N445" s="1" t="n">
+      <c r="O445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -20971,9 +22309,12 @@
         <v>0.0007415</v>
       </c>
       <c r="M446" s="1" t="n">
+        <v>0.0007434</v>
+      </c>
+      <c r="N446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="N446" s="1" t="n">
+      <c r="O446" s="1" t="n">
         <v>0.0007415</v>
       </c>
     </row>
@@ -21017,10 +22358,13 @@
         <v>0.03833</v>
       </c>
       <c r="M447" s="1" t="n">
+        <v>0.03812</v>
+      </c>
+      <c r="N447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="N447" s="1" t="n">
-        <v>0.03821</v>
+      <c r="O447" s="1" t="n">
+        <v>0.03812</v>
       </c>
     </row>
     <row r="448">
@@ -21063,9 +22407,12 @@
         <v>0.1783</v>
       </c>
       <c r="M448" s="1" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="N448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="N448" s="1" t="n">
+      <c r="O448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -21109,9 +22456,12 @@
         <v>0.0427</v>
       </c>
       <c r="M449" s="1" t="n">
+        <v>0.04288</v>
+      </c>
+      <c r="N449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="N449" s="1" t="n">
+      <c r="O449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -21155,9 +22505,12 @@
         <v>0.000164</v>
       </c>
       <c r="M450" s="1" t="n">
+        <v>0.0001643</v>
+      </c>
+      <c r="N450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="N450" s="1" t="n">
+      <c r="O450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -21201,10 +22554,13 @@
         <v>0.03745</v>
       </c>
       <c r="M451" s="1" t="n">
+        <v>0.03734</v>
+      </c>
+      <c r="N451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="N451" s="1" t="n">
-        <v>0.03745</v>
+      <c r="O451" s="1" t="n">
+        <v>0.03734</v>
       </c>
     </row>
     <row r="452">
@@ -21247,9 +22603,12 @@
         <v>0.00976</v>
       </c>
       <c r="M452" s="1" t="n">
+        <v>0.00976</v>
+      </c>
+      <c r="N452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="N452" s="1" t="n">
+      <c r="O452" s="1" t="n">
         <v>0.00976</v>
       </c>
     </row>
@@ -21293,9 +22652,12 @@
         <v>0.06791999999999999</v>
       </c>
       <c r="M453" s="1" t="n">
+        <v>0.06789000000000001</v>
+      </c>
+      <c r="N453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="N453" s="1" t="n">
+      <c r="O453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -21339,9 +22701,12 @@
         <v>0.007517</v>
       </c>
       <c r="M454" s="1" t="n">
+        <v>0.007524</v>
+      </c>
+      <c r="N454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="N454" s="1" t="n">
+      <c r="O454" s="1" t="n">
         <v>0.007494</v>
       </c>
     </row>
@@ -21385,10 +22750,13 @@
         <v>0.003303</v>
       </c>
       <c r="M455" s="1" t="n">
+        <v>0.003298</v>
+      </c>
+      <c r="N455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="N455" s="1" t="n">
-        <v>0.003302</v>
+      <c r="O455" s="1" t="n">
+        <v>0.003298</v>
       </c>
     </row>
     <row r="456">
@@ -21431,9 +22799,12 @@
         <v>0.00185</v>
       </c>
       <c r="M456" s="1" t="n">
+        <v>0.001848</v>
+      </c>
+      <c r="N456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="N456" s="1" t="n">
+      <c r="O456" s="1" t="n">
         <v>0.001842</v>
       </c>
     </row>
@@ -21477,9 +22848,12 @@
         <v>0.0001752</v>
       </c>
       <c r="M457" s="1" t="n">
+        <v>0.0001752</v>
+      </c>
+      <c r="N457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="N457" s="1" t="n">
+      <c r="O457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -21523,9 +22897,12 @@
         <v>0.00039</v>
       </c>
       <c r="M458" s="1" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="N458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="N458" s="1" t="n">
+      <c r="O458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -21569,9 +22946,12 @@
         <v>0.01394</v>
       </c>
       <c r="M459" s="1" t="n">
+        <v>0.01398</v>
+      </c>
+      <c r="N459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="N459" s="1" t="n">
+      <c r="O459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -21615,9 +22995,12 @@
         <v>0.04579</v>
       </c>
       <c r="M460" s="1" t="n">
-        <v>0.04579</v>
+        <v>0.04586</v>
       </c>
       <c r="N460" s="1" t="n">
+        <v>0.04586</v>
+      </c>
+      <c r="O460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -21661,9 +23044,12 @@
         <v>0.2818</v>
       </c>
       <c r="M461" s="1" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="N461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="N461" s="1" t="n">
+      <c r="O461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -21707,9 +23093,12 @@
         <v>0.006284</v>
       </c>
       <c r="M462" s="1" t="n">
+        <v>0.006261</v>
+      </c>
+      <c r="N462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="N462" s="1" t="n">
+      <c r="O462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -21753,9 +23142,12 @@
         <v>0.007043</v>
       </c>
       <c r="M463" s="1" t="n">
+        <v>0.007045</v>
+      </c>
+      <c r="N463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="N463" s="1" t="n">
+      <c r="O463" s="1" t="n">
         <v>0.007032</v>
       </c>
     </row>
@@ -21799,9 +23191,12 @@
         <v>0.2888</v>
       </c>
       <c r="M464" s="1" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="N464" s="1" t="n">
         <v>0.2888</v>
       </c>
-      <c r="N464" s="1" t="n">
+      <c r="O464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -21845,10 +23240,13 @@
         <v>0.08061</v>
       </c>
       <c r="M465" s="1" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="N465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="N465" s="1" t="n">
-        <v>0.08061</v>
+      <c r="O465" s="1" t="n">
+        <v>0.08053</v>
       </c>
     </row>
     <row r="466">
@@ -21891,9 +23289,12 @@
         <v>0.6369</v>
       </c>
       <c r="M466" s="1" t="n">
+        <v>0.6368</v>
+      </c>
+      <c r="N466" s="1" t="n">
         <v>0.6369</v>
       </c>
-      <c r="N466" s="1" t="n">
+      <c r="O466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -21937,9 +23338,12 @@
         <v>0.0148</v>
       </c>
       <c r="M467" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="N467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="N467" s="1" t="n">
+      <c r="O467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -21983,9 +23387,12 @@
         <v>0.03451</v>
       </c>
       <c r="M468" s="1" t="n">
+        <v>0.03458</v>
+      </c>
+      <c r="N468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="N468" s="1" t="n">
+      <c r="O468" s="1" t="n">
         <v>0.03434</v>
       </c>
     </row>
@@ -22029,9 +23436,12 @@
         <v>0.1625</v>
       </c>
       <c r="M469" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="N469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="N469" s="1" t="n">
+      <c r="O469" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -22075,9 +23485,12 @@
         <v>0.4099</v>
       </c>
       <c r="M470" s="1" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="N470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="N470" s="1" t="n">
+      <c r="O470" s="1" t="n">
         <v>0.4085</v>
       </c>
     </row>
@@ -22121,10 +23534,13 @@
         <v>0.06943000000000001</v>
       </c>
       <c r="M471" s="1" t="n">
+        <v>0.06884</v>
+      </c>
+      <c r="N471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="N471" s="1" t="n">
-        <v>0.06934999999999999</v>
+      <c r="O471" s="1" t="n">
+        <v>0.06884</v>
       </c>
     </row>
     <row r="472">
@@ -22167,9 +23583,12 @@
         <v>0.06619</v>
       </c>
       <c r="M472" s="1" t="n">
+        <v>0.06643</v>
+      </c>
+      <c r="N472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="N472" s="1" t="n">
+      <c r="O472" s="1" t="n">
         <v>0.06619</v>
       </c>
     </row>
@@ -22213,9 +23632,12 @@
         <v>0.01624</v>
       </c>
       <c r="M473" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="N473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="N473" s="1" t="n">
+      <c r="O473" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -22259,9 +23681,12 @@
         <v>0.2062</v>
       </c>
       <c r="M474" s="1" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="N474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="N474" s="1" t="n">
+      <c r="O474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -22305,9 +23730,12 @@
         <v>0.04251</v>
       </c>
       <c r="M475" s="1" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="N475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="N475" s="1" t="n">
+      <c r="O475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -22351,9 +23779,12 @@
         <v>1.561</v>
       </c>
       <c r="M476" s="1" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="N476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="N476" s="1" t="n">
+      <c r="O476" s="1" t="n">
         <v>1.561</v>
       </c>
     </row>
@@ -22397,9 +23828,12 @@
         <v>0.1008</v>
       </c>
       <c r="M477" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="N477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="N477" s="1" t="n">
+      <c r="O477" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -22443,9 +23877,12 @@
         <v>0.001152</v>
       </c>
       <c r="M478" s="1" t="n">
+        <v>0.001155</v>
+      </c>
+      <c r="N478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="N478" s="1" t="n">
+      <c r="O478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -22489,9 +23926,12 @@
         <v>0.1442</v>
       </c>
       <c r="M479" s="1" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="N479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="N479" s="1" t="n">
+      <c r="O479" s="1" t="n">
         <v>0.1442</v>
       </c>
     </row>
@@ -22535,9 +23975,12 @@
         <v>0.001723</v>
       </c>
       <c r="M480" s="1" t="n">
+        <v>0.001724</v>
+      </c>
+      <c r="N480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="N480" s="1" t="n">
+      <c r="O480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -22581,9 +24024,12 @@
         <v>0.909</v>
       </c>
       <c r="M481" s="1" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="N481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="N481" s="1" t="n">
+      <c r="O481" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -22627,9 +24073,12 @@
         <v>0.13375</v>
       </c>
       <c r="M482" s="1" t="n">
+        <v>0.13375</v>
+      </c>
+      <c r="N482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="N482" s="1" t="n">
+      <c r="O482" s="1" t="n">
         <v>0.13336</v>
       </c>
     </row>
@@ -22673,9 +24122,12 @@
         <v>0.04027</v>
       </c>
       <c r="M483" s="1" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="N483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="N483" s="1" t="n">
+      <c r="O483" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -22719,9 +24171,12 @@
         <v>0.3007</v>
       </c>
       <c r="M484" s="1" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="N484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="N484" s="1" t="n">
+      <c r="O484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -22765,9 +24220,12 @@
         <v>0.05646</v>
       </c>
       <c r="M485" s="1" t="n">
+        <v>0.05658</v>
+      </c>
+      <c r="N485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="N485" s="1" t="n">
+      <c r="O485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -22811,9 +24269,12 @@
         <v>0.001563</v>
       </c>
       <c r="M486" s="1" t="n">
+        <v>0.001566</v>
+      </c>
+      <c r="N486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="N486" s="1" t="n">
+      <c r="O486" s="1" t="n">
         <v>0.001563</v>
       </c>
     </row>
@@ -22857,9 +24318,12 @@
         <v>0.06708</v>
       </c>
       <c r="M487" s="1" t="n">
+        <v>0.06705999999999999</v>
+      </c>
+      <c r="N487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="N487" s="1" t="n">
+      <c r="O487" s="1" t="n">
         <v>0.06702</v>
       </c>
     </row>
@@ -22903,10 +24367,13 @@
         <v>0.1929</v>
       </c>
       <c r="M488" s="1" t="n">
+        <v>0.1924</v>
+      </c>
+      <c r="N488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="N488" s="1" t="n">
-        <v>0.1929</v>
+      <c r="O488" s="1" t="n">
+        <v>0.1924</v>
       </c>
     </row>
     <row r="489">
@@ -22949,9 +24416,12 @@
         <v>0.04797</v>
       </c>
       <c r="M489" s="1" t="n">
+        <v>0.04798</v>
+      </c>
+      <c r="N489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="N489" s="1" t="n">
+      <c r="O489" s="1" t="n">
         <v>0.04779</v>
       </c>
     </row>
@@ -22995,9 +24465,12 @@
         <v>0.1393</v>
       </c>
       <c r="M490" s="1" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="N490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="N490" s="1" t="n">
+      <c r="O490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -23041,9 +24514,12 @@
         <v>0.02244</v>
       </c>
       <c r="M491" s="1" t="n">
+        <v>0.02245</v>
+      </c>
+      <c r="N491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="N491" s="1" t="n">
+      <c r="O491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -23087,9 +24563,12 @@
         <v>0.007781</v>
       </c>
       <c r="M492" s="1" t="n">
+        <v>0.007795</v>
+      </c>
+      <c r="N492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="N492" s="1" t="n">
+      <c r="O492" s="1" t="n">
         <v>0.007746</v>
       </c>
     </row>
@@ -23133,9 +24612,12 @@
         <v>0.0005926</v>
       </c>
       <c r="M493" s="1" t="n">
+        <v>0.0005938</v>
+      </c>
+      <c r="N493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="N493" s="1" t="n">
+      <c r="O493" s="1" t="n">
         <v>0.0005926</v>
       </c>
     </row>
@@ -23179,9 +24661,12 @@
         <v>3.021</v>
       </c>
       <c r="M494" s="1" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="N494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="N494" s="1" t="n">
+      <c r="O494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -23225,9 +24710,12 @@
         <v>0.05063</v>
       </c>
       <c r="M495" s="1" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="N495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="N495" s="1" t="n">
+      <c r="O495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -23271,9 +24759,12 @@
         <v>0.006775</v>
       </c>
       <c r="M496" s="1" t="n">
+        <v>0.006824</v>
+      </c>
+      <c r="N496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="N496" s="1" t="n">
+      <c r="O496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -23317,9 +24808,12 @@
         <v>1.302</v>
       </c>
       <c r="M497" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="N497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="N497" s="1" t="n">
+      <c r="O497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -23363,9 +24857,12 @@
         <v>0.03941</v>
       </c>
       <c r="M498" s="1" t="n">
+        <v>0.03949</v>
+      </c>
+      <c r="N498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="N498" s="1" t="n">
+      <c r="O498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -23409,9 +24906,12 @@
         <v>0.04128</v>
       </c>
       <c r="M499" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="N499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="N499" s="1" t="n">
+      <c r="O499" s="1" t="n">
         <v>0.04101</v>
       </c>
     </row>
@@ -23455,9 +24955,12 @@
         <v>0.00545</v>
       </c>
       <c r="M500" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="N500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="N500" s="1" t="n">
+      <c r="O500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -23501,9 +25004,12 @@
         <v>0.03576</v>
       </c>
       <c r="M501" s="1" t="n">
+        <v>0.03579</v>
+      </c>
+      <c r="N501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="N501" s="1" t="n">
+      <c r="O501" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -23547,10 +25053,13 @@
         <v>0.07232</v>
       </c>
       <c r="M502" s="1" t="n">
+        <v>0.07227</v>
+      </c>
+      <c r="N502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="N502" s="1" t="n">
-        <v>0.07232</v>
+      <c r="O502" s="1" t="n">
+        <v>0.07227</v>
       </c>
     </row>
     <row r="503">
@@ -23593,9 +25102,12 @@
         <v>0.0007467</v>
       </c>
       <c r="M503" s="1" t="n">
+        <v>0.0007439</v>
+      </c>
+      <c r="N503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="N503" s="1" t="n">
+      <c r="O503" s="1" t="n">
         <v>0.0007422</v>
       </c>
     </row>
@@ -23639,9 +25151,12 @@
         <v>0.016016</v>
       </c>
       <c r="M504" s="1" t="n">
+        <v>0.016002</v>
+      </c>
+      <c r="N504" s="1" t="n">
         <v>0.016016</v>
       </c>
-      <c r="N504" s="1" t="n">
+      <c r="O504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -23685,9 +25200,12 @@
         <v>0.00703</v>
       </c>
       <c r="M505" s="1" t="n">
+        <v>0.00704</v>
+      </c>
+      <c r="N505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="N505" s="1" t="n">
+      <c r="O505" s="1" t="n">
         <v>0.00703</v>
       </c>
     </row>
@@ -23731,9 +25249,12 @@
         <v>0.0255</v>
       </c>
       <c r="M506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="N506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="N506" s="1" t="n">
+      <c r="O506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -23777,9 +25298,12 @@
         <v>0.001355</v>
       </c>
       <c r="M507" s="1" t="n">
+        <v>0.001354</v>
+      </c>
+      <c r="N507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="N507" s="1" t="n">
+      <c r="O507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -23823,9 +25347,12 @@
         <v>0.2812</v>
       </c>
       <c r="M508" s="1" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="N508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="N508" s="1" t="n">
+      <c r="O508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -23869,9 +25396,12 @@
         <v>0.1319</v>
       </c>
       <c r="M509" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="N509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="N509" s="1" t="n">
+      <c r="O509" s="1" t="n">
         <v>0.1317</v>
       </c>
     </row>
@@ -23915,9 +25445,12 @@
         <v>0.04927</v>
       </c>
       <c r="M510" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="N510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="N510" s="1" t="n">
+      <c r="O510" s="1" t="n">
         <v>0.04896</v>
       </c>
     </row>
@@ -23961,9 +25494,12 @@
         <v>0.00272</v>
       </c>
       <c r="M511" s="1" t="n">
+        <v>0.00273</v>
+      </c>
+      <c r="N511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="N511" s="1" t="n">
+      <c r="O511" s="1" t="n">
         <v>0.00272</v>
       </c>
     </row>
@@ -24007,9 +25543,12 @@
         <v>0.015017</v>
       </c>
       <c r="M512" s="1" t="n">
+        <v>0.015206</v>
+      </c>
+      <c r="N512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="N512" s="1" t="n">
+      <c r="O512" s="1" t="n">
         <v>0.015017</v>
       </c>
     </row>
@@ -24053,9 +25592,12 @@
         <v>0.6916</v>
       </c>
       <c r="M513" s="1" t="n">
+        <v>0.6918</v>
+      </c>
+      <c r="N513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="N513" s="1" t="n">
+      <c r="O513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -24099,9 +25641,12 @@
         <v>0.004535</v>
       </c>
       <c r="M514" s="1" t="n">
+        <v>0.004528</v>
+      </c>
+      <c r="N514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="N514" s="1" t="n">
+      <c r="O514" s="1" t="n">
         <v>0.004517</v>
       </c>
     </row>
@@ -24145,9 +25690,12 @@
         <v>0.005018</v>
       </c>
       <c r="M515" s="1" t="n">
+        <v>0.005019</v>
+      </c>
+      <c r="N515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="N515" s="1" t="n">
+      <c r="O515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -24191,9 +25739,12 @@
         <v>0.06331000000000001</v>
       </c>
       <c r="M516" s="1" t="n">
+        <v>0.06343</v>
+      </c>
+      <c r="N516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="N516" s="1" t="n">
+      <c r="O516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -24237,9 +25788,12 @@
         <v>0.06514</v>
       </c>
       <c r="M517" s="1" t="n">
+        <v>0.06489</v>
+      </c>
+      <c r="N517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="N517" s="1" t="n">
+      <c r="O517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -24283,9 +25837,12 @@
         <v>0.01204</v>
       </c>
       <c r="M518" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="N518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="N518" s="1" t="n">
+      <c r="O518" s="1" t="n">
         <v>0.01199</v>
       </c>
     </row>
@@ -24329,9 +25886,12 @@
         <v>0.04763</v>
       </c>
       <c r="M519" s="1" t="n">
+        <v>0.04767</v>
+      </c>
+      <c r="N519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="N519" s="1" t="n">
+      <c r="O519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -24375,9 +25935,12 @@
         <v>0.04371</v>
       </c>
       <c r="M520" s="1" t="n">
+        <v>0.04381</v>
+      </c>
+      <c r="N520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="N520" s="1" t="n">
+      <c r="O520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -24421,9 +25984,12 @@
         <v>0.00844</v>
       </c>
       <c r="M521" s="1" t="n">
+        <v>0.008469000000000001</v>
+      </c>
+      <c r="N521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="N521" s="1" t="n">
+      <c r="O521" s="1" t="n">
         <v>0.008411999999999999</v>
       </c>
     </row>
@@ -24467,9 +26033,12 @@
         <v>0.08787</v>
       </c>
       <c r="M522" s="1" t="n">
+        <v>0.08817</v>
+      </c>
+      <c r="N522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="N522" s="1" t="n">
+      <c r="O522" s="1" t="n">
         <v>0.08787</v>
       </c>
     </row>
@@ -24513,9 +26082,12 @@
         <v>0.006443</v>
       </c>
       <c r="M523" s="1" t="n">
+        <v>0.006451</v>
+      </c>
+      <c r="N523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="N523" s="1" t="n">
+      <c r="O523" s="1" t="n">
         <v>0.006433</v>
       </c>
     </row>
@@ -24559,9 +26131,12 @@
         <v>0.01641</v>
       </c>
       <c r="M524" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="N524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="N524" s="1" t="n">
+      <c r="O524" s="1" t="n">
         <v>0.01641</v>
       </c>
     </row>
@@ -24605,9 +26180,12 @@
         <v>0.01784</v>
       </c>
       <c r="M525" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="N525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="N525" s="1" t="n">
+      <c r="O525" s="1" t="n">
         <v>0.01779</v>
       </c>
     </row>
@@ -24651,9 +26229,12 @@
         <v>0.0793</v>
       </c>
       <c r="M526" s="1" t="n">
+        <v>0.07922</v>
+      </c>
+      <c r="N526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="N526" s="1" t="n">
+      <c r="O526" s="1" t="n">
         <v>0.07883</v>
       </c>
     </row>
@@ -24697,9 +26278,12 @@
         <v>0.01603</v>
       </c>
       <c r="M527" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="N527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="N527" s="1" t="n">
+      <c r="O527" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -24743,9 +26327,12 @@
         <v>0.004192</v>
       </c>
       <c r="M528" s="1" t="n">
+        <v>0.004182</v>
+      </c>
+      <c r="N528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="N528" s="1" t="n">
+      <c r="O528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -24789,9 +26376,12 @@
         <v>0.003699</v>
       </c>
       <c r="M529" s="1" t="n">
+        <v>0.003712</v>
+      </c>
+      <c r="N529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="N529" s="1" t="n">
+      <c r="O529" s="1" t="n">
         <v>0.00369</v>
       </c>
     </row>
@@ -24835,9 +26425,12 @@
         <v>1.324</v>
       </c>
       <c r="M530" s="1" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="N530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="N530" s="1" t="n">
+      <c r="O530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -24881,9 +26474,12 @@
         <v>0.4898</v>
       </c>
       <c r="M531" s="1" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="N531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="N531" s="1" t="n">
+      <c r="O531" s="1" t="n">
         <v>0.4893</v>
       </c>
     </row>
@@ -24927,9 +26523,12 @@
         <v>0.0306</v>
       </c>
       <c r="M532" s="1" t="n">
+        <v>0.03064</v>
+      </c>
+      <c r="N532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="N532" s="1" t="n">
+      <c r="O532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -24973,9 +26572,12 @@
         <v>0.153</v>
       </c>
       <c r="M533" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="N533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="N533" s="1" t="n">
+      <c r="O533" s="1" t="n">
         <v>0.153</v>
       </c>
     </row>
@@ -25019,9 +26621,12 @@
         <v>0.05382</v>
       </c>
       <c r="M534" s="1" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="N534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="N534" s="1" t="n">
+      <c r="O534" s="1" t="n">
         <v>0.0536</v>
       </c>
     </row>
@@ -25065,9 +26670,12 @@
         <v>0.0149</v>
       </c>
       <c r="M535" s="1" t="n">
+        <v>0.01494</v>
+      </c>
+      <c r="N535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="N535" s="1" t="n">
+      <c r="O535" s="1" t="n">
         <v>0.0149</v>
       </c>
     </row>
@@ -25111,9 +26719,12 @@
         <v>0.05909</v>
       </c>
       <c r="M536" s="1" t="n">
+        <v>0.05899</v>
+      </c>
+      <c r="N536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="N536" s="1" t="n">
+      <c r="O536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -25157,9 +26768,12 @@
         <v>0.05498</v>
       </c>
       <c r="M537" s="1" t="n">
+        <v>0.05487</v>
+      </c>
+      <c r="N537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="N537" s="1" t="n">
+      <c r="O537" s="1" t="n">
         <v>0.05481</v>
       </c>
     </row>
@@ -25203,9 +26817,12 @@
         <v>0.1061</v>
       </c>
       <c r="M538" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="N538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="N538" s="1" t="n">
+      <c r="O538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -25249,9 +26866,12 @@
         <v>0.01273</v>
       </c>
       <c r="M539" s="1" t="n">
+        <v>0.01278</v>
+      </c>
+      <c r="N539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="N539" s="1" t="n">
+      <c r="O539" s="1" t="n">
         <v>0.01273</v>
       </c>
     </row>
@@ -25295,9 +26915,12 @@
         <v>0.174</v>
       </c>
       <c r="M540" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="N540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="N540" s="1" t="n">
+      <c r="O540" s="1" t="n">
         <v>0.174</v>
       </c>
     </row>
@@ -25341,9 +26964,12 @@
         <v>0.1228</v>
       </c>
       <c r="M541" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="N541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="N541" s="1" t="n">
+      <c r="O541" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -25387,9 +27013,12 @@
         <v>0.02488</v>
       </c>
       <c r="M542" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="N542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="N542" s="1" t="n">
+      <c r="O542" s="1" t="n">
         <v>0.02481</v>
       </c>
     </row>
@@ -25433,9 +27062,12 @@
         <v>0.05868</v>
       </c>
       <c r="M543" s="1" t="n">
+        <v>0.05872</v>
+      </c>
+      <c r="N543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="N543" s="1" t="n">
+      <c r="O543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q543"/>
+  <dimension ref="A1:R543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -434,8 +434,9 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,10 +517,15 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>price_03:30</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -574,9 +580,12 @@
         <v>71187.10000000001</v>
       </c>
       <c r="P2" s="1" t="n">
+        <v>71072</v>
+      </c>
+      <c r="Q2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="R2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -629,10 +638,13 @@
         <v>2103.06</v>
       </c>
       <c r="P3" s="1" t="n">
+        <v>2098.64</v>
+      </c>
+      <c r="Q3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="Q3" s="1" t="n">
-        <v>2099.88</v>
+      <c r="R3" s="1" t="n">
+        <v>2098.64</v>
       </c>
     </row>
     <row r="4">
@@ -684,10 +696,13 @@
         <v>88.70999999999999</v>
       </c>
       <c r="P4" s="1" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Q4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="Q4" s="1" t="n">
-        <v>88.70999999999999</v>
+      <c r="R4" s="1" t="n">
+        <v>88.7</v>
       </c>
     </row>
     <row r="5">
@@ -739,9 +754,12 @@
         <v>3.803</v>
       </c>
       <c r="P5" s="1" t="n">
+        <v>3.791</v>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="R5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -794,9 +812,12 @@
         <v>1.3989</v>
       </c>
       <c r="P6" s="1" t="n">
+        <v>1.3993</v>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="R6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -849,10 +870,13 @@
         <v>0.09588000000000001</v>
       </c>
       <c r="P7" s="1" t="n">
+        <v>0.09572</v>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="Q7" s="1" t="n">
-        <v>0.0958</v>
+      <c r="R7" s="1" t="n">
+        <v>0.09572</v>
       </c>
     </row>
     <row r="8">
@@ -904,9 +928,12 @@
         <v>0.014259</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>0.014297</v>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="R8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -959,9 +986,12 @@
         <v>657.67</v>
       </c>
       <c r="P9" s="1" t="n">
+        <v>656.9299999999999</v>
+      </c>
+      <c r="Q9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="R9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1014,9 +1044,12 @@
         <v>20.288</v>
       </c>
       <c r="P10" s="1" t="n">
+        <v>20.129</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>20.288</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="R10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1069,10 +1102,13 @@
         <v>0.003395</v>
       </c>
       <c r="P11" s="1" t="n">
+        <v>0.0033816</v>
+      </c>
+      <c r="Q11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="Q11" s="1" t="n">
-        <v>0.003395</v>
+      <c r="R11" s="1" t="n">
+        <v>0.0033816</v>
       </c>
     </row>
     <row r="12">
@@ -1124,9 +1160,12 @@
         <v>36.46</v>
       </c>
       <c r="P12" s="1" t="n">
+        <v>36.478</v>
+      </c>
+      <c r="Q12" s="1" t="n">
         <v>36.704</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="R12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1179,9 +1218,12 @@
         <v>214</v>
       </c>
       <c r="P13" s="1" t="n">
+        <v>213.23</v>
+      </c>
+      <c r="Q13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="R13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1234,9 +1276,12 @@
         <v>0.0011196</v>
       </c>
       <c r="P14" s="1" t="n">
+        <v>0.0011172</v>
+      </c>
+      <c r="Q14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="R14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1289,9 +1334,12 @@
         <v>0.30053</v>
       </c>
       <c r="P15" s="1" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>0.30332</v>
       </c>
-      <c r="Q15" s="1" t="n">
+      <c r="R15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1344,9 +1392,12 @@
         <v>231.75</v>
       </c>
       <c r="P16" s="1" t="n">
+        <v>231.16</v>
+      </c>
+      <c r="Q16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="R16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1399,9 +1450,12 @@
         <v>0.9995000000000001</v>
       </c>
       <c r="P17" s="1" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="R17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1454,9 +1508,12 @@
         <v>0.2669</v>
       </c>
       <c r="P18" s="1" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="Q18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="R18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1509,10 +1566,13 @@
         <v>9.766999999999999</v>
       </c>
       <c r="P19" s="1" t="n">
+        <v>9.747999999999999</v>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="Q19" s="1" t="n">
-        <v>9.755000000000001</v>
+      <c r="R19" s="1" t="n">
+        <v>9.747999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1564,9 +1624,12 @@
         <v>5040.86</v>
       </c>
       <c r="P20" s="1" t="n">
+        <v>5037.16</v>
+      </c>
+      <c r="Q20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="R20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1619,9 +1682,12 @@
         <v>464.29</v>
       </c>
       <c r="P21" s="1" t="n">
+        <v>463.16</v>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="Q21" s="1" t="n">
+      <c r="R21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1674,9 +1740,12 @@
         <v>1.3736</v>
       </c>
       <c r="P22" s="1" t="n">
+        <v>1.3787</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="R22" s="1" t="n">
         <v>1.3736</v>
       </c>
     </row>
@@ -1729,9 +1798,12 @@
         <v>1.0347</v>
       </c>
       <c r="P23" s="1" t="n">
+        <v>1.0591</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="Q23" s="1" t="n">
+      <c r="R23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -1784,10 +1856,13 @@
         <v>1.348</v>
       </c>
       <c r="P24" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="Q24" s="1" t="n">
-        <v>1.344</v>
+      <c r="R24" s="1" t="n">
+        <v>1.343</v>
       </c>
     </row>
     <row r="25">
@@ -1839,10 +1914,13 @@
         <v>9.128</v>
       </c>
       <c r="P25" s="1" t="n">
+        <v>9.113</v>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="Q25" s="1" t="n">
-        <v>9.124000000000001</v>
+      <c r="R25" s="1" t="n">
+        <v>9.113</v>
       </c>
     </row>
     <row r="26">
@@ -1894,9 +1972,12 @@
         <v>0.3695</v>
       </c>
       <c r="P26" s="1" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="Q26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="R26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1949,10 +2030,13 @@
         <v>0.876</v>
       </c>
       <c r="P27" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>0.876</v>
+      <c r="R27" s="1" t="n">
+        <v>0.874</v>
       </c>
     </row>
     <row r="28">
@@ -2004,9 +2088,12 @@
         <v>1.84</v>
       </c>
       <c r="P28" s="1" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="Q28" s="1" t="n">
+      <c r="R28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2059,10 +2146,13 @@
         <v>0.1092</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="Q29" s="1" t="n">
-        <v>0.1092</v>
+      <c r="R29" s="1" t="n">
+        <v>0.1089</v>
       </c>
     </row>
     <row r="30">
@@ -2114,10 +2204,13 @@
         <v>0.002036</v>
       </c>
       <c r="P30" s="1" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="Q30" s="1" t="n">
-        <v>0.002034</v>
+      <c r="R30" s="1" t="n">
+        <v>0.002011</v>
       </c>
     </row>
     <row r="31">
@@ -2169,10 +2262,13 @@
         <v>1.474</v>
       </c>
       <c r="P31" s="1" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="Q31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="Q31" s="1" t="n">
-        <v>1.472</v>
+      <c r="R31" s="1" t="n">
+        <v>1.467</v>
       </c>
     </row>
     <row r="32">
@@ -2224,9 +2320,12 @@
         <v>0.1768</v>
       </c>
       <c r="P32" s="1" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="Q32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="Q32" s="1" t="n">
+      <c r="R32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2279,10 +2378,13 @@
         <v>0.1036</v>
       </c>
       <c r="P33" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="Q33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="Q33" s="1" t="n">
-        <v>0.1036</v>
+      <c r="R33" s="1" t="n">
+        <v>0.1035</v>
       </c>
     </row>
     <row r="34">
@@ -2334,10 +2436,13 @@
         <v>112.8</v>
       </c>
       <c r="P34" s="1" t="n">
+        <v>112.49</v>
+      </c>
+      <c r="Q34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="Q34" s="1" t="n">
-        <v>112.61</v>
+      <c r="R34" s="1" t="n">
+        <v>112.49</v>
       </c>
     </row>
     <row r="35">
@@ -2389,9 +2494,12 @@
         <v>6.59</v>
       </c>
       <c r="P35" s="1" t="n">
+        <v>6.619</v>
+      </c>
+      <c r="Q35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="Q35" s="1" t="n">
+      <c r="R35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2444,9 +2552,12 @@
         <v>0.017561</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>0.017561</v>
+        <v>0.017656</v>
       </c>
       <c r="Q36" s="1" t="n">
+        <v>0.017656</v>
+      </c>
+      <c r="R36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2499,10 +2610,13 @@
         <v>0.3603</v>
       </c>
       <c r="P37" s="1" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="Q37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="Q37" s="1" t="n">
-        <v>0.36</v>
+      <c r="R37" s="1" t="n">
+        <v>0.3595</v>
       </c>
     </row>
     <row r="38">
@@ -2554,9 +2668,12 @@
         <v>55.48</v>
       </c>
       <c r="P38" s="1" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="Q38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="Q38" s="1" t="n">
+      <c r="R38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2609,9 +2726,12 @@
         <v>0.61761</v>
       </c>
       <c r="P39" s="1" t="n">
+        <v>0.6167899999999999</v>
+      </c>
+      <c r="Q39" s="1" t="n">
         <v>0.61761</v>
       </c>
-      <c r="Q39" s="1" t="n">
+      <c r="R39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2664,10 +2784,13 @@
         <v>4.027</v>
       </c>
       <c r="P40" s="1" t="n">
+        <v>4.017</v>
+      </c>
+      <c r="Q40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="Q40" s="1" t="n">
-        <v>4.024</v>
+      <c r="R40" s="1" t="n">
+        <v>4.017</v>
       </c>
     </row>
     <row r="41">
@@ -2719,9 +2842,12 @@
         <v>0.04978</v>
       </c>
       <c r="P41" s="1" t="n">
+        <v>0.04981</v>
+      </c>
+      <c r="Q41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="Q41" s="1" t="n">
+      <c r="R41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2774,9 +2900,12 @@
         <v>0.7009</v>
       </c>
       <c r="P42" s="1" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="Q42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="Q42" s="1" t="n">
+      <c r="R42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2829,10 +2958,13 @@
         <v>0.2284</v>
       </c>
       <c r="P43" s="1" t="n">
+        <v>0.22785</v>
+      </c>
+      <c r="Q43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="Q43" s="1" t="n">
-        <v>0.22812</v>
+      <c r="R43" s="1" t="n">
+        <v>0.22785</v>
       </c>
     </row>
     <row r="44">
@@ -2884,9 +3016,12 @@
         <v>0.3581</v>
       </c>
       <c r="P44" s="1" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="Q44" s="1" t="n">
         <v>0.3581</v>
       </c>
-      <c r="Q44" s="1" t="n">
+      <c r="R44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2939,10 +3074,13 @@
         <v>0.1694</v>
       </c>
       <c r="P45" s="1" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="Q45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="Q45" s="1" t="n">
-        <v>0.1694</v>
+      <c r="R45" s="1" t="n">
+        <v>0.1687</v>
       </c>
     </row>
     <row r="46">
@@ -2994,9 +3132,12 @@
         <v>0.0261</v>
       </c>
       <c r="P46" s="1" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="Q46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="Q46" s="1" t="n">
+      <c r="R46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -3049,10 +3190,13 @@
         <v>0.005949</v>
       </c>
       <c r="P47" s="1" t="n">
+        <v>0.00594</v>
+      </c>
+      <c r="Q47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="Q47" s="1" t="n">
-        <v>0.005942</v>
+      <c r="R47" s="1" t="n">
+        <v>0.00594</v>
       </c>
     </row>
     <row r="48">
@@ -3104,10 +3248,13 @@
         <v>0.00736</v>
       </c>
       <c r="P48" s="1" t="n">
+        <v>0.007343</v>
+      </c>
+      <c r="Q48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="Q48" s="1" t="n">
-        <v>0.007349</v>
+      <c r="R48" s="1" t="n">
+        <v>0.007343</v>
       </c>
     </row>
     <row r="49">
@@ -3159,9 +3306,12 @@
         <v>0.1088</v>
       </c>
       <c r="P49" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="Q49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="Q49" s="1" t="n">
+      <c r="R49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3214,9 +3364,12 @@
         <v>0.04182</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>0.04182</v>
+        <v>0.04183</v>
       </c>
       <c r="Q50" s="1" t="n">
+        <v>0.04183</v>
+      </c>
+      <c r="R50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -3269,10 +3422,13 @@
         <v>0.1616</v>
       </c>
       <c r="P51" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="Q51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="Q51" s="1" t="n">
-        <v>0.1616</v>
+      <c r="R51" s="1" t="n">
+        <v>0.1614</v>
       </c>
     </row>
     <row r="52">
@@ -3324,9 +3480,12 @@
         <v>0.00351</v>
       </c>
       <c r="P52" s="1" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="Q52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="Q52" s="1" t="n">
+      <c r="R52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -3379,10 +3538,13 @@
         <v>2.62</v>
       </c>
       <c r="P53" s="1" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="Q53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="Q53" s="1" t="n">
-        <v>2.62</v>
+      <c r="R53" s="1" t="n">
+        <v>2.619</v>
       </c>
     </row>
     <row r="54">
@@ -3434,10 +3596,13 @@
         <v>0.006174</v>
       </c>
       <c r="P54" s="1" t="n">
+        <v>0.006157</v>
+      </c>
+      <c r="Q54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="Q54" s="1" t="n">
-        <v>0.006174</v>
+      <c r="R54" s="1" t="n">
+        <v>0.006157</v>
       </c>
     </row>
     <row r="55">
@@ -3489,9 +3654,12 @@
         <v>0.02927</v>
       </c>
       <c r="P55" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="Q55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="Q55" s="1" t="n">
+      <c r="R55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -3544,10 +3712,13 @@
         <v>0.7352</v>
       </c>
       <c r="P56" s="1" t="n">
+        <v>0.7322</v>
+      </c>
+      <c r="Q56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="Q56" s="1" t="n">
-        <v>0.7351</v>
+      <c r="R56" s="1" t="n">
+        <v>0.7322</v>
       </c>
     </row>
     <row r="57">
@@ -3599,10 +3770,13 @@
         <v>0.1035</v>
       </c>
       <c r="P57" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="Q57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="Q57" s="1" t="n">
-        <v>0.1034</v>
+      <c r="R57" s="1" t="n">
+        <v>0.103</v>
       </c>
     </row>
     <row r="58">
@@ -3654,9 +3828,12 @@
         <v>0.9388</v>
       </c>
       <c r="P58" s="1" t="n">
+        <v>0.9365</v>
+      </c>
+      <c r="Q58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="Q58" s="1" t="n">
+      <c r="R58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -3709,9 +3886,12 @@
         <v>0.0873</v>
       </c>
       <c r="P59" s="1" t="n">
+        <v>0.08717</v>
+      </c>
+      <c r="Q59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="Q59" s="1" t="n">
+      <c r="R59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -3764,10 +3944,13 @@
         <v>0.06936</v>
       </c>
       <c r="P60" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Q60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="Q60" s="1" t="n">
-        <v>0.06918000000000001</v>
+      <c r="R60" s="1" t="n">
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -3819,9 +4002,12 @@
         <v>0.05446</v>
       </c>
       <c r="P61" s="1" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="Q61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="Q61" s="1" t="n">
+      <c r="R61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -3874,9 +4060,12 @@
         <v>0.010259</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>0.010259</v>
+        <v>0.01036</v>
       </c>
       <c r="Q62" s="1" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="R62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -3929,9 +4118,12 @@
         <v>0.29156</v>
       </c>
       <c r="P63" s="1" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="Q63" s="1" t="n">
         <v>0.29156</v>
       </c>
-      <c r="Q63" s="1" t="n">
+      <c r="R63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -3984,9 +4176,12 @@
         <v>0.07549</v>
       </c>
       <c r="P64" s="1" t="n">
+        <v>0.07346</v>
+      </c>
+      <c r="Q64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="Q64" s="1" t="n">
+      <c r="R64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -4039,9 +4234,12 @@
         <v>0.3186</v>
       </c>
       <c r="P65" s="1" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="Q65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="Q65" s="1" t="n">
+      <c r="R65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -4094,9 +4292,12 @@
         <v>0.16253</v>
       </c>
       <c r="P66" s="1" t="n">
+        <v>0.16242</v>
+      </c>
+      <c r="Q66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="Q66" s="1" t="n">
+      <c r="R66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -4149,9 +4350,12 @@
         <v>0.12012</v>
       </c>
       <c r="P67" s="1" t="n">
+        <v>0.11998</v>
+      </c>
+      <c r="Q67" s="1" t="n">
         <v>0.12014</v>
       </c>
-      <c r="Q67" s="1" t="n">
+      <c r="R67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -4204,10 +4408,13 @@
         <v>0.09512</v>
       </c>
       <c r="P68" s="1" t="n">
+        <v>0.09494</v>
+      </c>
+      <c r="Q68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="Q68" s="1" t="n">
-        <v>0.09512</v>
+      <c r="R68" s="1" t="n">
+        <v>0.09494</v>
       </c>
     </row>
     <row r="69">
@@ -4259,9 +4466,12 @@
         <v>0.1243</v>
       </c>
       <c r="P69" s="1" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="Q69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="Q69" s="1" t="n">
+      <c r="R69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -4314,10 +4524,13 @@
         <v>8.510999999999999</v>
       </c>
       <c r="P70" s="1" t="n">
+        <v>8.491</v>
+      </c>
+      <c r="Q70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="Q70" s="1" t="n">
-        <v>8.494</v>
+      <c r="R70" s="1" t="n">
+        <v>8.491</v>
       </c>
     </row>
     <row r="71">
@@ -4369,9 +4582,12 @@
         <v>0.238</v>
       </c>
       <c r="P71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="Q71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="Q71" s="1" t="n">
+      <c r="R71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -4424,9 +4640,12 @@
         <v>0.04999</v>
       </c>
       <c r="P72" s="1" t="n">
+        <v>0.04996</v>
+      </c>
+      <c r="Q72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="Q72" s="1" t="n">
+      <c r="R72" s="1" t="n">
         <v>0.04992</v>
       </c>
     </row>
@@ -4479,9 +4698,12 @@
         <v>0.05037</v>
       </c>
       <c r="P73" s="1" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="Q73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="Q73" s="1" t="n">
+      <c r="R73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -4534,9 +4756,12 @@
         <v>0.1252</v>
       </c>
       <c r="P74" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="Q74" s="1" t="n">
+      <c r="R74" s="1" t="n">
         <v>0.1246</v>
       </c>
     </row>
@@ -4589,9 +4814,12 @@
         <v>0.04619</v>
       </c>
       <c r="P75" s="1" t="n">
+        <v>0.04642</v>
+      </c>
+      <c r="Q75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="Q75" s="1" t="n">
+      <c r="R75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -4644,9 +4872,12 @@
         <v>0.06725</v>
       </c>
       <c r="P76" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="Q76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="Q76" s="1" t="n">
+      <c r="R76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -4699,9 +4930,12 @@
         <v>0.12835</v>
       </c>
       <c r="P77" s="1" t="n">
+        <v>0.12842</v>
+      </c>
+      <c r="Q77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="Q77" s="1" t="n">
+      <c r="R77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -4754,10 +4988,13 @@
         <v>0.1611</v>
       </c>
       <c r="P78" s="1" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="Q78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="Q78" s="1" t="n">
-        <v>0.1611</v>
+      <c r="R78" s="1" t="n">
+        <v>0.1608</v>
       </c>
     </row>
     <row r="79">
@@ -4809,10 +5046,13 @@
         <v>0.02696</v>
       </c>
       <c r="P79" s="1" t="n">
+        <v>0.02693</v>
+      </c>
+      <c r="Q79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="Q79" s="1" t="n">
-        <v>0.02696</v>
+      <c r="R79" s="1" t="n">
+        <v>0.02693</v>
       </c>
     </row>
     <row r="80">
@@ -4864,9 +5104,12 @@
         <v>358.62</v>
       </c>
       <c r="P80" s="1" t="n">
+        <v>358.23</v>
+      </c>
+      <c r="Q80" s="1" t="n">
         <v>358.62</v>
       </c>
-      <c r="Q80" s="1" t="n">
+      <c r="R80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -4919,10 +5162,13 @@
         <v>7.053e-05</v>
       </c>
       <c r="P81" s="1" t="n">
+        <v>7.029000000000001e-05</v>
+      </c>
+      <c r="Q81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="Q81" s="1" t="n">
-        <v>7.053e-05</v>
+      <c r="R81" s="1" t="n">
+        <v>7.029000000000001e-05</v>
       </c>
     </row>
     <row r="82">
@@ -4974,9 +5220,12 @@
         <v>0.2655</v>
       </c>
       <c r="P82" s="1" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="Q82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="Q82" s="1" t="n">
+      <c r="R82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -5029,10 +5278,13 @@
         <v>1.1222</v>
       </c>
       <c r="P83" s="1" t="n">
+        <v>1.1167</v>
+      </c>
+      <c r="Q83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="Q83" s="1" t="n">
-        <v>1.1222</v>
+      <c r="R83" s="1" t="n">
+        <v>1.1167</v>
       </c>
     </row>
     <row r="84">
@@ -5084,10 +5336,13 @@
         <v>0.3547</v>
       </c>
       <c r="P84" s="1" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="Q84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="Q84" s="1" t="n">
-        <v>0.3535</v>
+      <c r="R84" s="1" t="n">
+        <v>0.3496</v>
       </c>
     </row>
     <row r="85">
@@ -5139,10 +5394,13 @@
         <v>2.0058</v>
       </c>
       <c r="P85" s="1" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="Q85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="Q85" s="1" t="n">
-        <v>2.0058</v>
+      <c r="R85" s="1" t="n">
+        <v>1.986</v>
       </c>
     </row>
     <row r="86">
@@ -5194,9 +5452,12 @@
         <v>1.317</v>
       </c>
       <c r="P86" s="1" t="n">
+        <v>1.3195</v>
+      </c>
+      <c r="Q86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="Q86" s="1" t="n">
+      <c r="R86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -5249,10 +5510,13 @@
         <v>32.64</v>
       </c>
       <c r="P87" s="1" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="Q87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="Q87" s="1" t="n">
-        <v>32.64</v>
+      <c r="R87" s="1" t="n">
+        <v>32.55</v>
       </c>
     </row>
     <row r="88">
@@ -5304,9 +5568,12 @@
         <v>0.00957</v>
       </c>
       <c r="P88" s="1" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="Q88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="Q88" s="1" t="n">
+      <c r="R88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -5359,10 +5626,13 @@
         <v>0.0181</v>
       </c>
       <c r="P89" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="Q89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="Q89" s="1" t="n">
-        <v>0.01808</v>
+      <c r="R89" s="1" t="n">
+        <v>0.01807</v>
       </c>
     </row>
     <row r="90">
@@ -5414,9 +5684,12 @@
         <v>0.03483</v>
       </c>
       <c r="P90" s="1" t="n">
+        <v>0.03485</v>
+      </c>
+      <c r="Q90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="Q90" s="1" t="n">
+      <c r="R90" s="1" t="n">
         <v>0.03479</v>
       </c>
     </row>
@@ -5469,9 +5742,12 @@
         <v>0.01179</v>
       </c>
       <c r="P91" s="1" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="Q91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="Q91" s="1" t="n">
+      <c r="R91" s="1" t="n">
         <v>0.01179</v>
       </c>
     </row>
@@ -5524,9 +5800,12 @@
         <v>3.098</v>
       </c>
       <c r="P92" s="1" t="n">
+        <v>3.091</v>
+      </c>
+      <c r="Q92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="Q92" s="1" t="n">
+      <c r="R92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -5579,10 +5858,13 @@
         <v>0.005585</v>
       </c>
       <c r="P93" s="1" t="n">
+        <v>0.005572</v>
+      </c>
+      <c r="Q93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="Q93" s="1" t="n">
-        <v>0.005585</v>
+      <c r="R93" s="1" t="n">
+        <v>0.005572</v>
       </c>
     </row>
     <row r="94">
@@ -5634,9 +5916,12 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="P94" s="1" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="Q94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="Q94" s="1" t="n">
+      <c r="R94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -5689,9 +5974,12 @@
         <v>0.6063</v>
       </c>
       <c r="P95" s="1" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="Q95" s="1" t="n">
         <v>0.6098</v>
       </c>
-      <c r="Q95" s="1" t="n">
+      <c r="R95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -5744,9 +6032,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="P96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="Q96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="Q96" s="1" t="n">
+      <c r="R96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -5799,9 +6090,12 @@
         <v>1.103</v>
       </c>
       <c r="P97" s="1" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="Q97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="Q97" s="1" t="n">
+      <c r="R97" s="1" t="n">
         <v>1.103</v>
       </c>
     </row>
@@ -5854,9 +6148,12 @@
         <v>0.25615</v>
       </c>
       <c r="P98" s="1" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="Q98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="Q98" s="1" t="n">
+      <c r="R98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -5909,10 +6206,13 @@
         <v>1.142</v>
       </c>
       <c r="P99" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="Q99" s="1" t="n">
-        <v>1.142</v>
+      <c r="R99" s="1" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="100">
@@ -5964,9 +6264,12 @@
         <v>1.858</v>
       </c>
       <c r="P100" s="1" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="Q100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="Q100" s="1" t="n">
+      <c r="R100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -6019,9 +6322,12 @@
         <v>0.01575</v>
       </c>
       <c r="P101" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="Q101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="Q101" s="1" t="n">
+      <c r="R101" s="1" t="n">
         <v>0.01575</v>
       </c>
     </row>
@@ -6074,10 +6380,13 @@
         <v>0.10225</v>
       </c>
       <c r="P102" s="1" t="n">
+        <v>0.10187</v>
+      </c>
+      <c r="Q102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="Q102" s="1" t="n">
-        <v>0.10225</v>
+      <c r="R102" s="1" t="n">
+        <v>0.10187</v>
       </c>
     </row>
     <row r="103">
@@ -6129,9 +6438,12 @@
         <v>0.0005941</v>
       </c>
       <c r="P103" s="1" t="n">
+        <v>0.0005941</v>
+      </c>
+      <c r="Q103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="Q103" s="1" t="n">
+      <c r="R103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -6184,9 +6496,12 @@
         <v>0.0005917</v>
       </c>
       <c r="P104" s="1" t="n">
+        <v>0.0005885</v>
+      </c>
+      <c r="Q104" s="1" t="n">
         <v>0.0005917</v>
       </c>
-      <c r="Q104" s="1" t="n">
+      <c r="R104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -6239,9 +6554,12 @@
         <v>0.003268</v>
       </c>
       <c r="P105" s="1" t="n">
+        <v>0.003257</v>
+      </c>
+      <c r="Q105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="Q105" s="1" t="n">
+      <c r="R105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -6294,10 +6612,13 @@
         <v>2.582</v>
       </c>
       <c r="P106" s="1" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="Q106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="Q106" s="1" t="n">
-        <v>2.582</v>
+      <c r="R106" s="1" t="n">
+        <v>2.572</v>
       </c>
     </row>
     <row r="107">
@@ -6349,9 +6670,12 @@
         <v>0.1653</v>
       </c>
       <c r="P107" s="1" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="Q107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="Q107" s="1" t="n">
+      <c r="R107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -6404,9 +6728,12 @@
         <v>0.09623</v>
       </c>
       <c r="P108" s="1" t="n">
+        <v>0.09633</v>
+      </c>
+      <c r="Q108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="Q108" s="1" t="n">
+      <c r="R108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -6459,10 +6786,13 @@
         <v>0.02209</v>
       </c>
       <c r="P109" s="1" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="Q109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="Q109" s="1" t="n">
-        <v>0.02204</v>
+      <c r="R109" s="1" t="n">
+        <v>0.02202</v>
       </c>
     </row>
     <row r="110">
@@ -6514,10 +6844,13 @@
         <v>0.2901</v>
       </c>
       <c r="P110" s="1" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="Q110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="Q110" s="1" t="n">
-        <v>0.2901</v>
+      <c r="R110" s="1" t="n">
+        <v>0.2894</v>
       </c>
     </row>
     <row r="111">
@@ -6569,10 +6902,13 @@
         <v>0.05675</v>
       </c>
       <c r="P111" s="1" t="n">
+        <v>0.05651</v>
+      </c>
+      <c r="Q111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="Q111" s="1" t="n">
-        <v>0.05659</v>
+      <c r="R111" s="1" t="n">
+        <v>0.05651</v>
       </c>
     </row>
     <row r="112">
@@ -6624,9 +6960,12 @@
         <v>0.3012</v>
       </c>
       <c r="P112" s="1" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="Q112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="Q112" s="1" t="n">
+      <c r="R112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -6679,10 +7018,13 @@
         <v>18.58</v>
       </c>
       <c r="P113" s="1" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="Q113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="Q113" s="1" t="n">
-        <v>18.58</v>
+      <c r="R113" s="1" t="n">
+        <v>18.53</v>
       </c>
     </row>
     <row r="114">
@@ -6734,10 +7076,13 @@
         <v>0.12729</v>
       </c>
       <c r="P114" s="1" t="n">
+        <v>0.12566</v>
+      </c>
+      <c r="Q114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="Q114" s="1" t="n">
-        <v>0.12729</v>
+      <c r="R114" s="1" t="n">
+        <v>0.12566</v>
       </c>
     </row>
     <row r="115">
@@ -6789,9 +7134,12 @@
         <v>0.01661</v>
       </c>
       <c r="P115" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="Q115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="Q115" s="1" t="n">
+      <c r="R115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -6844,10 +7192,13 @@
         <v>0.08465</v>
       </c>
       <c r="P116" s="1" t="n">
+        <v>0.08442</v>
+      </c>
+      <c r="Q116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="Q116" s="1" t="n">
-        <v>0.08454</v>
+      <c r="R116" s="1" t="n">
+        <v>0.08442</v>
       </c>
     </row>
     <row r="117">
@@ -6899,10 +7250,13 @@
         <v>0.04726</v>
       </c>
       <c r="P117" s="1" t="n">
+        <v>0.046846</v>
+      </c>
+      <c r="Q117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="Q117" s="1" t="n">
-        <v>0.04726</v>
+      <c r="R117" s="1" t="n">
+        <v>0.046846</v>
       </c>
     </row>
     <row r="118">
@@ -6954,10 +7308,13 @@
         <v>0.04717</v>
       </c>
       <c r="P118" s="1" t="n">
+        <v>0.04701</v>
+      </c>
+      <c r="Q118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="Q118" s="1" t="n">
-        <v>0.04717</v>
+      <c r="R118" s="1" t="n">
+        <v>0.04701</v>
       </c>
     </row>
     <row r="119">
@@ -7009,9 +7366,12 @@
         <v>0.04046</v>
       </c>
       <c r="P119" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="Q119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="Q119" s="1" t="n">
+      <c r="R119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -7064,9 +7424,12 @@
         <v>0.14508</v>
       </c>
       <c r="P120" s="1" t="n">
+        <v>0.14473</v>
+      </c>
+      <c r="Q120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="Q120" s="1" t="n">
+      <c r="R120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -7119,10 +7482,13 @@
         <v>0.1266</v>
       </c>
       <c r="P121" s="1" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="Q121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="Q121" s="1" t="n">
-        <v>0.1266</v>
+      <c r="R121" s="1" t="n">
+        <v>0.1264</v>
       </c>
     </row>
     <row r="122">
@@ -7174,10 +7540,13 @@
         <v>1.854</v>
       </c>
       <c r="P122" s="1" t="n">
+        <v>1.851</v>
+      </c>
+      <c r="Q122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="Q122" s="1" t="n">
-        <v>1.854</v>
+      <c r="R122" s="1" t="n">
+        <v>1.851</v>
       </c>
     </row>
     <row r="123">
@@ -7229,10 +7598,13 @@
         <v>0.0301</v>
       </c>
       <c r="P123" s="1" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="Q123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="Q123" s="1" t="n">
-        <v>0.03009</v>
+      <c r="R123" s="1" t="n">
+        <v>0.03001</v>
       </c>
     </row>
     <row r="124">
@@ -7284,9 +7656,12 @@
         <v>0.13218</v>
       </c>
       <c r="P124" s="1" t="n">
+        <v>0.13252</v>
+      </c>
+      <c r="Q124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="Q124" s="1" t="n">
+      <c r="R124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -7339,10 +7714,13 @@
         <v>0.04084</v>
       </c>
       <c r="P125" s="1" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="Q125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="Q125" s="1" t="n">
-        <v>0.04084</v>
+      <c r="R125" s="1" t="n">
+        <v>0.0408</v>
       </c>
     </row>
     <row r="126">
@@ -7394,10 +7772,13 @@
         <v>0.1144</v>
       </c>
       <c r="P126" s="1" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="Q126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="Q126" s="1" t="n">
-        <v>0.1144</v>
+      <c r="R126" s="1" t="n">
+        <v>0.1141</v>
       </c>
     </row>
     <row r="127">
@@ -7449,9 +7830,12 @@
         <v>0.5213</v>
       </c>
       <c r="P127" s="1" t="n">
-        <v>0.5213</v>
+        <v>0.5214</v>
       </c>
       <c r="Q127" s="1" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="R127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -7504,9 +7888,12 @@
         <v>0.0378</v>
       </c>
       <c r="P128" s="1" t="n">
+        <v>0.03781</v>
+      </c>
+      <c r="Q128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="Q128" s="1" t="n">
+      <c r="R128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -7559,9 +7946,12 @@
         <v>0.795</v>
       </c>
       <c r="P129" s="1" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="Q129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="Q129" s="1" t="n">
+      <c r="R129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -7614,9 +8004,12 @@
         <v>0.03437</v>
       </c>
       <c r="P130" s="1" t="n">
+        <v>0.03434</v>
+      </c>
+      <c r="Q130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="Q130" s="1" t="n">
+      <c r="R130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -7669,9 +8062,12 @@
         <v>0.4259</v>
       </c>
       <c r="P131" s="1" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="Q131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="Q131" s="1" t="n">
+      <c r="R131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -7724,9 +8120,12 @@
         <v>0.04319</v>
       </c>
       <c r="P132" s="1" t="n">
+        <v>0.04329</v>
+      </c>
+      <c r="Q132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="Q132" s="1" t="n">
+      <c r="R132" s="1" t="n">
         <v>0.04309</v>
       </c>
     </row>
@@ -7779,10 +8178,13 @@
         <v>1.2835</v>
       </c>
       <c r="P133" s="1" t="n">
+        <v>1.2805</v>
+      </c>
+      <c r="Q133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="Q133" s="1" t="n">
-        <v>1.282</v>
+      <c r="R133" s="1" t="n">
+        <v>1.2805</v>
       </c>
     </row>
     <row r="134">
@@ -7834,10 +8236,13 @@
         <v>0.02188</v>
       </c>
       <c r="P134" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="Q134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="Q134" s="1" t="n">
-        <v>0.02184</v>
+      <c r="R134" s="1" t="n">
+        <v>0.02178</v>
       </c>
     </row>
     <row r="135">
@@ -7889,10 +8294,13 @@
         <v>0.0004575</v>
       </c>
       <c r="P135" s="1" t="n">
+        <v>0.0004561</v>
+      </c>
+      <c r="Q135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="Q135" s="1" t="n">
-        <v>0.0004575</v>
+      <c r="R135" s="1" t="n">
+        <v>0.0004561</v>
       </c>
     </row>
     <row r="136">
@@ -7944,9 +8352,12 @@
         <v>0.001907</v>
       </c>
       <c r="P136" s="1" t="n">
+        <v>0.001904</v>
+      </c>
+      <c r="Q136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="Q136" s="1" t="n">
+      <c r="R136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -7999,10 +8410,13 @@
         <v>0.3145</v>
       </c>
       <c r="P137" s="1" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="Q137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="Q137" s="1" t="n">
-        <v>0.3143</v>
+      <c r="R137" s="1" t="n">
+        <v>0.3136</v>
       </c>
     </row>
     <row r="138">
@@ -8054,10 +8468,13 @@
         <v>0.5645</v>
       </c>
       <c r="P138" s="1" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="Q138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="Q138" s="1" t="n">
-        <v>0.5645</v>
+      <c r="R138" s="1" t="n">
+        <v>0.5633</v>
       </c>
     </row>
     <row r="139">
@@ -8109,9 +8526,12 @@
         <v>0.02121</v>
       </c>
       <c r="P139" s="1" t="n">
+        <v>0.02123</v>
+      </c>
+      <c r="Q139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="Q139" s="1" t="n">
+      <c r="R139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -8164,10 +8584,13 @@
         <v>0.08007</v>
       </c>
       <c r="P140" s="1" t="n">
+        <v>0.07979</v>
+      </c>
+      <c r="Q140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="Q140" s="1" t="n">
-        <v>0.08007</v>
+      <c r="R140" s="1" t="n">
+        <v>0.07979</v>
       </c>
     </row>
     <row r="141">
@@ -8219,9 +8642,12 @@
         <v>0.001525</v>
       </c>
       <c r="P141" s="1" t="n">
+        <v>0.001526</v>
+      </c>
+      <c r="Q141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="Q141" s="1" t="n">
+      <c r="R141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -8274,9 +8700,12 @@
         <v>0.4489</v>
       </c>
       <c r="P142" s="1" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="Q142" s="1" t="n">
         <v>0.4489</v>
       </c>
-      <c r="Q142" s="1" t="n">
+      <c r="R142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -8329,10 +8758,13 @@
         <v>0.030318</v>
       </c>
       <c r="P143" s="1" t="n">
+        <v>0.029913</v>
+      </c>
+      <c r="Q143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="Q143" s="1" t="n">
-        <v>0.030021</v>
+      <c r="R143" s="1" t="n">
+        <v>0.029913</v>
       </c>
     </row>
     <row r="144">
@@ -8384,9 +8816,12 @@
         <v>0.000227</v>
       </c>
       <c r="P144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="Q144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="Q144" s="1" t="n">
+      <c r="R144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -8439,9 +8874,12 @@
         <v>0.0356</v>
       </c>
       <c r="P145" s="1" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="Q145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="Q145" s="1" t="n">
+      <c r="R145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -8494,9 +8932,12 @@
         <v>0.11554</v>
       </c>
       <c r="P146" s="1" t="n">
-        <v>0.116</v>
+        <v>0.11649</v>
       </c>
       <c r="Q146" s="1" t="n">
+        <v>0.11649</v>
+      </c>
+      <c r="R146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -8549,9 +8990,12 @@
         <v>0.02188</v>
       </c>
       <c r="P147" s="1" t="n">
-        <v>0.02198</v>
+        <v>0.02218</v>
       </c>
       <c r="Q147" s="1" t="n">
+        <v>0.02218</v>
+      </c>
+      <c r="R147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -8604,9 +9048,12 @@
         <v>1.4116</v>
       </c>
       <c r="P148" s="1" t="n">
+        <v>1.4093</v>
+      </c>
+      <c r="Q148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="Q148" s="1" t="n">
+      <c r="R148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -8659,9 +9106,12 @@
         <v>1.8671</v>
       </c>
       <c r="P149" s="1" t="n">
+        <v>1.8688</v>
+      </c>
+      <c r="Q149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="Q149" s="1" t="n">
+      <c r="R149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -8714,9 +9164,12 @@
         <v>0.095</v>
       </c>
       <c r="P150" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="Q150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="Q150" s="1" t="n">
+      <c r="R150" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -8769,9 +9222,12 @@
         <v>4.614</v>
       </c>
       <c r="P151" s="1" t="n">
-        <v>4.64</v>
+        <v>4.647</v>
       </c>
       <c r="Q151" s="1" t="n">
+        <v>4.647</v>
+      </c>
+      <c r="R151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -8824,10 +9280,13 @@
         <v>5.528</v>
       </c>
       <c r="P152" s="1" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="Q152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="Q152" s="1" t="n">
-        <v>5.522</v>
+      <c r="R152" s="1" t="n">
+        <v>5.515</v>
       </c>
     </row>
     <row r="153">
@@ -8879,9 +9338,12 @@
         <v>0.3174</v>
       </c>
       <c r="P153" s="1" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="Q153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="Q153" s="1" t="n">
+      <c r="R153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -8934,10 +9396,13 @@
         <v>0.5838</v>
       </c>
       <c r="P154" s="1" t="n">
+        <v>0.5826</v>
+      </c>
+      <c r="Q154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="Q154" s="1" t="n">
-        <v>0.5838</v>
+      <c r="R154" s="1" t="n">
+        <v>0.5826</v>
       </c>
     </row>
     <row r="155">
@@ -8989,9 +9454,12 @@
         <v>0.01283</v>
       </c>
       <c r="P155" s="1" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="Q155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="Q155" s="1" t="n">
+      <c r="R155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -9044,10 +9512,13 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="P156" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="Q156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="Q156" s="1" t="n">
-        <v>0.09810000000000001</v>
+      <c r="R156" s="1" t="n">
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -9099,10 +9570,13 @@
         <v>16.386</v>
       </c>
       <c r="P157" s="1" t="n">
+        <v>16.341</v>
+      </c>
+      <c r="Q157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="Q157" s="1" t="n">
-        <v>16.386</v>
+      <c r="R157" s="1" t="n">
+        <v>16.341</v>
       </c>
     </row>
     <row r="158">
@@ -9154,9 +9628,12 @@
         <v>0.05516</v>
       </c>
       <c r="P158" s="1" t="n">
+        <v>0.05526</v>
+      </c>
+      <c r="Q158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="Q158" s="1" t="n">
+      <c r="R158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -9209,10 +9686,13 @@
         <v>28.76</v>
       </c>
       <c r="P159" s="1" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="Q159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="Q159" s="1" t="n">
-        <v>28.76</v>
+      <c r="R159" s="1" t="n">
+        <v>28.71</v>
       </c>
     </row>
     <row r="160">
@@ -9264,9 +9744,12 @@
         <v>0.02087</v>
       </c>
       <c r="P160" s="1" t="n">
+        <v>0.02088</v>
+      </c>
+      <c r="Q160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="Q160" s="1" t="n">
+      <c r="R160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -9319,9 +9802,12 @@
         <v>0.0006546</v>
       </c>
       <c r="P161" s="1" t="n">
+        <v>0.0006511000000000001</v>
+      </c>
+      <c r="Q161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="Q161" s="1" t="n">
+      <c r="R161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -9374,10 +9860,13 @@
         <v>0.3809</v>
       </c>
       <c r="P162" s="1" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="Q162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="Q162" s="1" t="n">
-        <v>0.3808</v>
+      <c r="R162" s="1" t="n">
+        <v>0.3805</v>
       </c>
     </row>
     <row r="163">
@@ -9429,10 +9918,13 @@
         <v>0.1917</v>
       </c>
       <c r="P163" s="1" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="Q163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="Q163" s="1" t="n">
-        <v>0.1915</v>
+      <c r="R163" s="1" t="n">
+        <v>0.1908</v>
       </c>
     </row>
     <row r="164">
@@ -9484,9 +9976,12 @@
         <v>0.317</v>
       </c>
       <c r="P164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Q164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="Q164" s="1" t="n">
+      <c r="R164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -9539,10 +10034,13 @@
         <v>0.372</v>
       </c>
       <c r="P165" s="1" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="Q165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="Q165" s="1" t="n">
-        <v>0.372</v>
+      <c r="R165" s="1" t="n">
+        <v>0.371</v>
       </c>
     </row>
     <row r="166">
@@ -9594,10 +10092,13 @@
         <v>0.02239</v>
       </c>
       <c r="P166" s="1" t="n">
+        <v>0.02233</v>
+      </c>
+      <c r="Q166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="Q166" s="1" t="n">
-        <v>0.02238</v>
+      <c r="R166" s="1" t="n">
+        <v>0.02233</v>
       </c>
     </row>
     <row r="167">
@@ -9649,10 +10150,13 @@
         <v>0.007278</v>
       </c>
       <c r="P167" s="1" t="n">
+        <v>0.007256</v>
+      </c>
+      <c r="Q167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="Q167" s="1" t="n">
-        <v>0.007269</v>
+      <c r="R167" s="1" t="n">
+        <v>0.007256</v>
       </c>
     </row>
     <row r="168">
@@ -9704,9 +10208,12 @@
         <v>0.01341</v>
       </c>
       <c r="P168" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="Q168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="Q168" s="1" t="n">
+      <c r="R168" s="1" t="n">
         <v>0.01341</v>
       </c>
     </row>
@@ -9759,9 +10266,12 @@
         <v>0.25338</v>
       </c>
       <c r="P169" s="1" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="Q169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="Q169" s="1" t="n">
+      <c r="R169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -9814,9 +10324,12 @@
         <v>0.02151</v>
       </c>
       <c r="P170" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="Q170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="Q170" s="1" t="n">
+      <c r="R170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -9869,9 +10382,12 @@
         <v>0.1714</v>
       </c>
       <c r="P171" s="1" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="Q171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="Q171" s="1" t="n">
+      <c r="R171" s="1" t="n">
         <v>0.1711</v>
       </c>
     </row>
@@ -9924,9 +10440,12 @@
         <v>0.089</v>
       </c>
       <c r="P172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="Q172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="Q172" s="1" t="n">
+      <c r="R172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -9979,10 +10498,13 @@
         <v>0.00467</v>
       </c>
       <c r="P173" s="1" t="n">
+        <v>0.004662</v>
+      </c>
+      <c r="Q173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="Q173" s="1" t="n">
-        <v>0.004669</v>
+      <c r="R173" s="1" t="n">
+        <v>0.004662</v>
       </c>
     </row>
     <row r="174">
@@ -10034,10 +10556,13 @@
         <v>0.4365</v>
       </c>
       <c r="P174" s="1" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="Q174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="Q174" s="1" t="n">
-        <v>0.4361</v>
+      <c r="R174" s="1" t="n">
+        <v>0.4343</v>
       </c>
     </row>
     <row r="175">
@@ -10089,9 +10614,12 @@
         <v>0.09029</v>
       </c>
       <c r="P175" s="1" t="n">
+        <v>0.09013</v>
+      </c>
+      <c r="Q175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="Q175" s="1" t="n">
+      <c r="R175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -10144,9 +10672,12 @@
         <v>0.2464</v>
       </c>
       <c r="P176" s="1" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="Q176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="Q176" s="1" t="n">
+      <c r="R176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -10199,10 +10730,13 @@
         <v>0.01916</v>
       </c>
       <c r="P177" s="1" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="Q177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="Q177" s="1" t="n">
-        <v>0.01909</v>
+      <c r="R177" s="1" t="n">
+        <v>0.01908</v>
       </c>
     </row>
     <row r="178">
@@ -10254,10 +10788,13 @@
         <v>6.126</v>
       </c>
       <c r="P178" s="1" t="n">
+        <v>6.108</v>
+      </c>
+      <c r="Q178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="Q178" s="1" t="n">
-        <v>6.122</v>
+      <c r="R178" s="1" t="n">
+        <v>6.108</v>
       </c>
     </row>
     <row r="179">
@@ -10309,9 +10846,12 @@
         <v>0.1349</v>
       </c>
       <c r="P179" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="Q179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="Q179" s="1" t="n">
+      <c r="R179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -10364,9 +10904,12 @@
         <v>0.005031</v>
       </c>
       <c r="P180" s="1" t="n">
+        <v>0.005039</v>
+      </c>
+      <c r="Q180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="Q180" s="1" t="n">
+      <c r="R180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -10419,10 +10962,13 @@
         <v>0.01183</v>
       </c>
       <c r="P181" s="1" t="n">
+        <v>0.01182</v>
+      </c>
+      <c r="Q181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="Q181" s="1" t="n">
-        <v>0.01183</v>
+      <c r="R181" s="1" t="n">
+        <v>0.01182</v>
       </c>
     </row>
     <row r="182">
@@ -10474,9 +11020,12 @@
         <v>0.007285</v>
       </c>
       <c r="P182" s="1" t="n">
+        <v>0.007314</v>
+      </c>
+      <c r="Q182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="Q182" s="1" t="n">
+      <c r="R182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -10529,9 +11078,12 @@
         <v>0.13152</v>
       </c>
       <c r="P183" s="1" t="n">
+        <v>0.13168</v>
+      </c>
+      <c r="Q183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="Q183" s="1" t="n">
+      <c r="R183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -10584,10 +11136,13 @@
         <v>0.09587</v>
       </c>
       <c r="P184" s="1" t="n">
+        <v>0.09555</v>
+      </c>
+      <c r="Q184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="Q184" s="1" t="n">
-        <v>0.09587</v>
+      <c r="R184" s="1" t="n">
+        <v>0.09555</v>
       </c>
     </row>
     <row r="185">
@@ -10639,10 +11194,13 @@
         <v>0.00752</v>
       </c>
       <c r="P185" s="1" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="Q185" s="1" t="n">
-        <v>0.00752</v>
+      <c r="R185" s="1" t="n">
+        <v>0.0075</v>
       </c>
     </row>
     <row r="186">
@@ -10694,10 +11252,13 @@
         <v>0.04869</v>
       </c>
       <c r="P186" s="1" t="n">
+        <v>0.04851</v>
+      </c>
+      <c r="Q186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="Q186" s="1" t="n">
-        <v>0.0486</v>
+      <c r="R186" s="1" t="n">
+        <v>0.04851</v>
       </c>
     </row>
     <row r="187">
@@ -10749,10 +11310,13 @@
         <v>0.02666</v>
       </c>
       <c r="P187" s="1" t="n">
+        <v>0.02652</v>
+      </c>
+      <c r="Q187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="Q187" s="1" t="n">
-        <v>0.02666</v>
+      <c r="R187" s="1" t="n">
+        <v>0.02652</v>
       </c>
     </row>
     <row r="188">
@@ -10804,10 +11368,13 @@
         <v>0.0033</v>
       </c>
       <c r="P188" s="1" t="n">
+        <v>0.003291</v>
+      </c>
+      <c r="Q188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="Q188" s="1" t="n">
-        <v>0.0033</v>
+      <c r="R188" s="1" t="n">
+        <v>0.003291</v>
       </c>
     </row>
     <row r="189">
@@ -10859,10 +11426,13 @@
         <v>0.2862</v>
       </c>
       <c r="P189" s="1" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="Q189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="Q189" s="1" t="n">
-        <v>0.2854</v>
+      <c r="R189" s="1" t="n">
+        <v>0.2847</v>
       </c>
     </row>
     <row r="190">
@@ -10914,10 +11484,13 @@
         <v>0.01787</v>
       </c>
       <c r="P190" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="Q190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="Q190" s="1" t="n">
-        <v>0.01785</v>
+      <c r="R190" s="1" t="n">
+        <v>0.01783</v>
       </c>
     </row>
     <row r="191">
@@ -10969,10 +11542,13 @@
         <v>0.2568</v>
       </c>
       <c r="P191" s="1" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="Q191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="Q191" s="1" t="n">
-        <v>0.2568</v>
+      <c r="R191" s="1" t="n">
+        <v>0.2562</v>
       </c>
     </row>
     <row r="192">
@@ -11024,9 +11600,12 @@
         <v>0.03817</v>
       </c>
       <c r="P192" s="1" t="n">
+        <v>0.03785</v>
+      </c>
+      <c r="Q192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="Q192" s="1" t="n">
+      <c r="R192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -11079,9 +11658,12 @@
         <v>0.0002214</v>
       </c>
       <c r="P193" s="1" t="n">
+        <v>0.0002209</v>
+      </c>
+      <c r="Q193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="Q193" s="1" t="n">
+      <c r="R193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -11134,9 +11716,12 @@
         <v>4.056</v>
       </c>
       <c r="P194" s="1" t="n">
+        <v>4.068</v>
+      </c>
+      <c r="Q194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="Q194" s="1" t="n">
+      <c r="R194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -11189,9 +11774,12 @@
         <v>0.999401</v>
       </c>
       <c r="P195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="Q195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="Q195" s="1" t="n">
+      <c r="R195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -11244,9 +11832,12 @@
         <v>4.287</v>
       </c>
       <c r="P196" s="1" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="Q196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="Q196" s="1" t="n">
+      <c r="R196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -11299,9 +11890,12 @@
         <v>0.15208</v>
       </c>
       <c r="P197" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="Q197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="Q197" s="1" t="n">
+      <c r="R197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -11354,9 +11948,12 @@
         <v>0.007702</v>
       </c>
       <c r="P198" s="1" t="n">
+        <v>0.007696</v>
+      </c>
+      <c r="Q198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="Q198" s="1" t="n">
+      <c r="R198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -11409,9 +12006,12 @@
         <v>0.4489</v>
       </c>
       <c r="P199" s="1" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="Q199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="Q199" s="1" t="n">
+      <c r="R199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -11464,9 +12064,12 @@
         <v>0.5841</v>
       </c>
       <c r="P200" s="1" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="Q200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="Q200" s="1" t="n">
+      <c r="R200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -11519,10 +12122,13 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="P201" s="1" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="Q201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="Q201" s="1" t="n">
-        <v>0.09279999999999999</v>
+      <c r="R201" s="1" t="n">
+        <v>0.0926</v>
       </c>
     </row>
     <row r="202">
@@ -11574,10 +12180,13 @@
         <v>0.05999</v>
       </c>
       <c r="P202" s="1" t="n">
+        <v>0.05994</v>
+      </c>
+      <c r="Q202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="Q202" s="1" t="n">
-        <v>0.05999</v>
+      <c r="R202" s="1" t="n">
+        <v>0.05994</v>
       </c>
     </row>
     <row r="203">
@@ -11629,9 +12238,12 @@
         <v>0.0083</v>
       </c>
       <c r="P203" s="1" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="Q203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="Q203" s="1" t="n">
+      <c r="R203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -11684,10 +12296,13 @@
         <v>0.00415</v>
       </c>
       <c r="P204" s="1" t="n">
+        <v>0.00413</v>
+      </c>
+      <c r="Q204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="Q204" s="1" t="n">
-        <v>0.00415</v>
+      <c r="R204" s="1" t="n">
+        <v>0.00413</v>
       </c>
     </row>
     <row r="205">
@@ -11739,9 +12354,12 @@
         <v>0.009131</v>
       </c>
       <c r="P205" s="1" t="n">
+        <v>0.009089</v>
+      </c>
+      <c r="Q205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="Q205" s="1" t="n">
+      <c r="R205" s="1" t="n">
         <v>0.009070999999999999</v>
       </c>
     </row>
@@ -11794,9 +12412,12 @@
         <v>0.2382</v>
       </c>
       <c r="P206" s="1" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="Q206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="Q206" s="1" t="n">
+      <c r="R206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -11849,10 +12470,13 @@
         <v>0.02057</v>
       </c>
       <c r="P207" s="1" t="n">
+        <v>0.02052</v>
+      </c>
+      <c r="Q207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="Q207" s="1" t="n">
-        <v>0.02053</v>
+      <c r="R207" s="1" t="n">
+        <v>0.02052</v>
       </c>
     </row>
     <row r="208">
@@ -11904,10 +12528,13 @@
         <v>0.2363</v>
       </c>
       <c r="P208" s="1" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="Q208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="Q208" s="1" t="n">
-        <v>0.2363</v>
+      <c r="R208" s="1" t="n">
+        <v>0.2357</v>
       </c>
     </row>
     <row r="209">
@@ -11959,10 +12586,13 @@
         <v>0.3598</v>
       </c>
       <c r="P209" s="1" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="Q209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="Q209" s="1" t="n">
-        <v>0.3586</v>
+      <c r="R209" s="1" t="n">
+        <v>0.3585</v>
       </c>
     </row>
     <row r="210">
@@ -12014,9 +12644,12 @@
         <v>0.04248</v>
       </c>
       <c r="P210" s="1" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="Q210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="Q210" s="1" t="n">
+      <c r="R210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -12069,10 +12702,13 @@
         <v>0.000425</v>
       </c>
       <c r="P211" s="1" t="n">
+        <v>0.0004237</v>
+      </c>
+      <c r="Q211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="Q211" s="1" t="n">
-        <v>0.000425</v>
+      <c r="R211" s="1" t="n">
+        <v>0.0004237</v>
       </c>
     </row>
     <row r="212">
@@ -12124,10 +12760,13 @@
         <v>0.02135</v>
       </c>
       <c r="P212" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="Q212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="Q212" s="1" t="n">
-        <v>0.02135</v>
+      <c r="R212" s="1" t="n">
+        <v>0.02129</v>
       </c>
     </row>
     <row r="213">
@@ -12179,10 +12818,13 @@
         <v>0.1139</v>
       </c>
       <c r="P213" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="Q213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="Q213" s="1" t="n">
-        <v>0.1137</v>
+      <c r="R213" s="1" t="n">
+        <v>0.1135</v>
       </c>
     </row>
     <row r="214">
@@ -12234,10 +12876,13 @@
         <v>0.04179</v>
       </c>
       <c r="P214" s="1" t="n">
+        <v>0.04173</v>
+      </c>
+      <c r="Q214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="Q214" s="1" t="n">
-        <v>0.04174</v>
+      <c r="R214" s="1" t="n">
+        <v>0.04173</v>
       </c>
     </row>
     <row r="215">
@@ -12289,9 +12934,12 @@
         <v>0.009839000000000001</v>
       </c>
       <c r="P215" s="1" t="n">
+        <v>0.009886000000000001</v>
+      </c>
+      <c r="Q215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="Q215" s="1" t="n">
+      <c r="R215" s="1" t="n">
         <v>0.009839000000000001</v>
       </c>
     </row>
@@ -12344,9 +12992,12 @@
         <v>0.0638</v>
       </c>
       <c r="P216" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="Q216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="Q216" s="1" t="n">
+      <c r="R216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -12399,9 +13050,12 @@
         <v>0.004207</v>
       </c>
       <c r="P217" s="1" t="n">
+        <v>0.004249</v>
+      </c>
+      <c r="Q217" s="1" t="n">
         <v>0.004266</v>
       </c>
-      <c r="Q217" s="1" t="n">
+      <c r="R217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -12454,9 +13108,12 @@
         <v>0.00996</v>
       </c>
       <c r="P218" s="1" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="Q218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="Q218" s="1" t="n">
+      <c r="R218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -12509,9 +13166,12 @@
         <v>0.02962</v>
       </c>
       <c r="P219" s="1" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="Q219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="Q219" s="1" t="n">
+      <c r="R219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -12564,10 +13224,13 @@
         <v>2.288</v>
       </c>
       <c r="P220" s="1" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="Q220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="Q220" s="1" t="n">
-        <v>2.288</v>
+      <c r="R220" s="1" t="n">
+        <v>2.281</v>
       </c>
     </row>
     <row r="221">
@@ -12619,10 +13282,13 @@
         <v>0.02276</v>
       </c>
       <c r="P221" s="1" t="n">
+        <v>0.022653</v>
+      </c>
+      <c r="Q221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="Q221" s="1" t="n">
-        <v>0.022737</v>
+      <c r="R221" s="1" t="n">
+        <v>0.022653</v>
       </c>
     </row>
     <row r="222">
@@ -12674,10 +13340,13 @@
         <v>0.0369</v>
       </c>
       <c r="P222" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="Q222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="Q222" s="1" t="n">
-        <v>0.0369</v>
+      <c r="R222" s="1" t="n">
+        <v>0.0368</v>
       </c>
     </row>
     <row r="223">
@@ -12729,9 +13398,12 @@
         <v>0.2915</v>
       </c>
       <c r="P223" s="1" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="Q223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="Q223" s="1" t="n">
+      <c r="R223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -12784,9 +13456,12 @@
         <v>0.01548</v>
       </c>
       <c r="P224" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="Q224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="Q224" s="1" t="n">
+      <c r="R224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -12839,10 +13514,13 @@
         <v>0.0004046</v>
       </c>
       <c r="P225" s="1" t="n">
+        <v>0.0004032</v>
+      </c>
+      <c r="Q225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="Q225" s="1" t="n">
-        <v>0.0004046</v>
+      <c r="R225" s="1" t="n">
+        <v>0.0004032</v>
       </c>
     </row>
     <row r="226">
@@ -12894,10 +13572,13 @@
         <v>0.08595</v>
       </c>
       <c r="P226" s="1" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="Q226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="Q226" s="1" t="n">
-        <v>0.08595</v>
+      <c r="R226" s="1" t="n">
+        <v>0.0857</v>
       </c>
     </row>
     <row r="227">
@@ -12949,9 +13630,12 @@
         <v>0.947</v>
       </c>
       <c r="P227" s="1" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="Q227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="Q227" s="1" t="n">
+      <c r="R227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -13004,10 +13688,13 @@
         <v>0.055</v>
       </c>
       <c r="P228" s="1" t="n">
+        <v>0.05487</v>
+      </c>
+      <c r="Q228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="Q228" s="1" t="n">
-        <v>0.055</v>
+      <c r="R228" s="1" t="n">
+        <v>0.05487</v>
       </c>
     </row>
     <row r="229">
@@ -13059,10 +13746,13 @@
         <v>0.001999</v>
       </c>
       <c r="P229" s="1" t="n">
+        <v>0.001997</v>
+      </c>
+      <c r="Q229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="Q229" s="1" t="n">
-        <v>0.001999</v>
+      <c r="R229" s="1" t="n">
+        <v>0.001997</v>
       </c>
     </row>
     <row r="230">
@@ -13114,9 +13804,12 @@
         <v>0.022824</v>
       </c>
       <c r="P230" s="1" t="n">
+        <v>0.022784</v>
+      </c>
+      <c r="Q230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="Q230" s="1" t="n">
+      <c r="R230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -13169,10 +13862,13 @@
         <v>0.05342</v>
       </c>
       <c r="P231" s="1" t="n">
+        <v>0.05338</v>
+      </c>
+      <c r="Q231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="Q231" s="1" t="n">
-        <v>0.05342</v>
+      <c r="R231" s="1" t="n">
+        <v>0.05338</v>
       </c>
     </row>
     <row r="232">
@@ -13224,10 +13920,13 @@
         <v>0.0586</v>
       </c>
       <c r="P232" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="Q232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="Q232" s="1" t="n">
-        <v>0.0586</v>
+      <c r="R232" s="1" t="n">
+        <v>0.0584</v>
       </c>
     </row>
     <row r="233">
@@ -13279,9 +13978,12 @@
         <v>0.001676</v>
       </c>
       <c r="P233" s="1" t="n">
+        <v>0.001677</v>
+      </c>
+      <c r="Q233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="Q233" s="1" t="n">
+      <c r="R233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -13334,9 +14036,12 @@
         <v>0.005748</v>
       </c>
       <c r="P234" s="1" t="n">
+        <v>0.005743</v>
+      </c>
+      <c r="Q234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="Q234" s="1" t="n">
+      <c r="R234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -13389,9 +14094,12 @@
         <v>0.12267</v>
       </c>
       <c r="P235" s="1" t="n">
+        <v>0.12298</v>
+      </c>
+      <c r="Q235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="Q235" s="1" t="n">
+      <c r="R235" s="1" t="n">
         <v>0.12267</v>
       </c>
     </row>
@@ -13444,9 +14152,12 @@
         <v>64.36</v>
       </c>
       <c r="P236" s="1" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="Q236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="Q236" s="1" t="n">
+      <c r="R236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -13499,10 +14210,13 @@
         <v>0.1012</v>
       </c>
       <c r="P237" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="Q237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="Q237" s="1" t="n">
-        <v>0.1012</v>
+      <c r="R237" s="1" t="n">
+        <v>0.1008</v>
       </c>
     </row>
     <row r="238">
@@ -13554,9 +14268,12 @@
         <v>0.004066</v>
       </c>
       <c r="P238" s="1" t="n">
+        <v>0.004023</v>
+      </c>
+      <c r="Q238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="Q238" s="1" t="n">
+      <c r="R238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -13609,10 +14326,13 @@
         <v>0.01538</v>
       </c>
       <c r="P239" s="1" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="Q239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="Q239" s="1" t="n">
-        <v>0.01532</v>
+      <c r="R239" s="1" t="n">
+        <v>0.01528</v>
       </c>
     </row>
     <row r="240">
@@ -13664,10 +14384,13 @@
         <v>0.05584</v>
       </c>
       <c r="P240" s="1" t="n">
+        <v>0.05575</v>
+      </c>
+      <c r="Q240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="Q240" s="1" t="n">
-        <v>0.05584</v>
+      <c r="R240" s="1" t="n">
+        <v>0.05575</v>
       </c>
     </row>
     <row r="241">
@@ -13719,9 +14442,12 @@
         <v>0.0113</v>
       </c>
       <c r="P241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="Q241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="Q241" s="1" t="n">
+      <c r="R241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -13774,9 +14500,12 @@
         <v>0.3338</v>
       </c>
       <c r="P242" s="1" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="Q242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="Q242" s="1" t="n">
+      <c r="R242" s="1" t="n">
         <v>0.3332</v>
       </c>
     </row>
@@ -13829,9 +14558,12 @@
         <v>0.01226</v>
       </c>
       <c r="P243" s="1" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="Q243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="Q243" s="1" t="n">
+      <c r="R243" s="1" t="n">
         <v>0.01223</v>
       </c>
     </row>
@@ -13884,9 +14616,12 @@
         <v>0.08044</v>
       </c>
       <c r="P244" s="1" t="n">
+        <v>0.08004</v>
+      </c>
+      <c r="Q244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="Q244" s="1" t="n">
+      <c r="R244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -13939,9 +14674,12 @@
         <v>0.007808</v>
       </c>
       <c r="P245" s="1" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="Q245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="Q245" s="1" t="n">
+      <c r="R245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -13994,10 +14732,13 @@
         <v>0.03027</v>
       </c>
       <c r="P246" s="1" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="Q246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="Q246" s="1" t="n">
-        <v>0.03025</v>
+      <c r="R246" s="1" t="n">
+        <v>0.0302</v>
       </c>
     </row>
     <row r="247">
@@ -14049,10 +14790,13 @@
         <v>0.1803</v>
       </c>
       <c r="P247" s="1" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="Q247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="Q247" s="1" t="n">
-        <v>0.18</v>
+      <c r="R247" s="1" t="n">
+        <v>0.1796</v>
       </c>
     </row>
     <row r="248">
@@ -14104,10 +14848,13 @@
         <v>0.0586</v>
       </c>
       <c r="P248" s="1" t="n">
+        <v>0.05856</v>
+      </c>
+      <c r="Q248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="Q248" s="1" t="n">
-        <v>0.0586</v>
+      <c r="R248" s="1" t="n">
+        <v>0.05856</v>
       </c>
     </row>
     <row r="249">
@@ -14159,9 +14906,12 @@
         <v>0.1663</v>
       </c>
       <c r="P249" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="Q249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="Q249" s="1" t="n">
+      <c r="R249" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -14214,10 +14964,13 @@
         <v>0.019</v>
       </c>
       <c r="P250" s="1" t="n">
+        <v>0.01898</v>
+      </c>
+      <c r="Q250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="Q250" s="1" t="n">
-        <v>0.019</v>
+      <c r="R250" s="1" t="n">
+        <v>0.01898</v>
       </c>
     </row>
     <row r="251">
@@ -14269,9 +15022,12 @@
         <v>0.02308</v>
       </c>
       <c r="P251" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="Q251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="Q251" s="1" t="n">
+      <c r="R251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -14324,9 +15080,12 @@
         <v>0.30624</v>
       </c>
       <c r="P252" s="1" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="Q252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="Q252" s="1" t="n">
+      <c r="R252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -14379,10 +15138,13 @@
         <v>0.005979</v>
       </c>
       <c r="P253" s="1" t="n">
+        <v>0.005956</v>
+      </c>
+      <c r="Q253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="Q253" s="1" t="n">
-        <v>0.005971</v>
+      <c r="R253" s="1" t="n">
+        <v>0.005956</v>
       </c>
     </row>
     <row r="254">
@@ -14434,9 +15196,12 @@
         <v>0.6123</v>
       </c>
       <c r="P254" s="1" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="Q254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="Q254" s="1" t="n">
+      <c r="R254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -14489,9 +15254,12 @@
         <v>0.10619</v>
       </c>
       <c r="P255" s="1" t="n">
+        <v>0.10611</v>
+      </c>
+      <c r="Q255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="Q255" s="1" t="n">
+      <c r="R255" s="1" t="n">
         <v>0.10601</v>
       </c>
     </row>
@@ -14544,9 +15312,12 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="P256" s="1" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="Q256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="Q256" s="1" t="n">
+      <c r="R256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -14599,9 +15370,12 @@
         <v>0.01456</v>
       </c>
       <c r="P257" s="1" t="n">
+        <v>0.01457</v>
+      </c>
+      <c r="Q257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="Q257" s="1" t="n">
+      <c r="R257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -14654,10 +15428,13 @@
         <v>0.0499</v>
       </c>
       <c r="P258" s="1" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="Q258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="Q258" s="1" t="n">
-        <v>0.0499</v>
+      <c r="R258" s="1" t="n">
+        <v>0.04965</v>
       </c>
     </row>
     <row r="259">
@@ -14709,9 +15486,12 @@
         <v>0.00804</v>
       </c>
       <c r="P259" s="1" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="Q259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="Q259" s="1" t="n">
+      <c r="R259" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -14764,10 +15544,13 @@
         <v>0.1897</v>
       </c>
       <c r="P260" s="1" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="Q260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="Q260" s="1" t="n">
-        <v>0.1894</v>
+      <c r="R260" s="1" t="n">
+        <v>0.1892</v>
       </c>
     </row>
     <row r="261">
@@ -14819,10 +15602,13 @@
         <v>0.0979</v>
       </c>
       <c r="P261" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="Q261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="Q261" s="1" t="n">
-        <v>0.0979</v>
+      <c r="R261" s="1" t="n">
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -14874,10 +15660,13 @@
         <v>0.2109</v>
       </c>
       <c r="P262" s="1" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="Q262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="Q262" s="1" t="n">
-        <v>0.2107</v>
+      <c r="R262" s="1" t="n">
+        <v>0.2103</v>
       </c>
     </row>
     <row r="263">
@@ -14929,9 +15718,12 @@
         <v>0.008489</v>
       </c>
       <c r="P263" s="1" t="n">
+        <v>0.008475</v>
+      </c>
+      <c r="Q263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="Q263" s="1" t="n">
+      <c r="R263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -14984,9 +15776,12 @@
         <v>2.636</v>
       </c>
       <c r="P264" s="1" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="Q264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="Q264" s="1" t="n">
+      <c r="R264" s="1" t="n">
         <v>2.629</v>
       </c>
     </row>
@@ -15039,9 +15834,12 @@
         <v>0.0186</v>
       </c>
       <c r="P265" s="1" t="n">
+        <v>0.01853</v>
+      </c>
+      <c r="Q265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="Q265" s="1" t="n">
+      <c r="R265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -15094,9 +15892,12 @@
         <v>0.3612</v>
       </c>
       <c r="P266" s="1" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Q266" s="1" t="n">
         <v>0.3612</v>
       </c>
-      <c r="Q266" s="1" t="n">
+      <c r="R266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -15149,9 +15950,12 @@
         <v>0.03408</v>
       </c>
       <c r="P267" s="1" t="n">
+        <v>0.03413</v>
+      </c>
+      <c r="Q267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="Q267" s="1" t="n">
+      <c r="R267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -15204,9 +16008,12 @@
         <v>0.118</v>
       </c>
       <c r="P268" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="Q268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="Q268" s="1" t="n">
+      <c r="R268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -15259,9 +16066,12 @@
         <v>0.08014</v>
       </c>
       <c r="P269" s="1" t="n">
+        <v>0.07976999999999999</v>
+      </c>
+      <c r="Q269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="Q269" s="1" t="n">
+      <c r="R269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -15314,10 +16124,13 @@
         <v>0.01377</v>
       </c>
       <c r="P270" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="Q270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="Q270" s="1" t="n">
-        <v>0.01377</v>
+      <c r="R270" s="1" t="n">
+        <v>0.01374</v>
       </c>
     </row>
     <row r="271">
@@ -15369,10 +16182,13 @@
         <v>0.007526</v>
       </c>
       <c r="P271" s="1" t="n">
+        <v>0.007504</v>
+      </c>
+      <c r="Q271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="Q271" s="1" t="n">
-        <v>0.007526</v>
+      <c r="R271" s="1" t="n">
+        <v>0.007504</v>
       </c>
     </row>
     <row r="272">
@@ -15424,10 +16240,13 @@
         <v>0.07413</v>
       </c>
       <c r="P272" s="1" t="n">
+        <v>0.07396</v>
+      </c>
+      <c r="Q272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="Q272" s="1" t="n">
-        <v>0.07405</v>
+      <c r="R272" s="1" t="n">
+        <v>0.07396</v>
       </c>
     </row>
     <row r="273">
@@ -15479,9 +16298,12 @@
         <v>3.14e-05</v>
       </c>
       <c r="P273" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="Q273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="Q273" s="1" t="n">
+      <c r="R273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -15534,10 +16356,13 @@
         <v>0.005414</v>
       </c>
       <c r="P274" s="1" t="n">
+        <v>0.005409</v>
+      </c>
+      <c r="Q274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="Q274" s="1" t="n">
-        <v>0.005414</v>
+      <c r="R274" s="1" t="n">
+        <v>0.005409</v>
       </c>
     </row>
     <row r="275">
@@ -15589,10 +16414,13 @@
         <v>0.1801</v>
       </c>
       <c r="P275" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="Q275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="Q275" s="1" t="n">
-        <v>0.1801</v>
+      <c r="R275" s="1" t="n">
+        <v>0.179</v>
       </c>
     </row>
     <row r="276">
@@ -15644,10 +16472,13 @@
         <v>0.00683</v>
       </c>
       <c r="P276" s="1" t="n">
+        <v>0.006819</v>
+      </c>
+      <c r="Q276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="Q276" s="1" t="n">
-        <v>0.00682</v>
+      <c r="R276" s="1" t="n">
+        <v>0.006819</v>
       </c>
     </row>
     <row r="277">
@@ -15699,9 +16530,12 @@
         <v>0.1306</v>
       </c>
       <c r="P277" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="Q277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="Q277" s="1" t="n">
+      <c r="R277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -15754,10 +16588,13 @@
         <v>0.02313</v>
       </c>
       <c r="P278" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="Q278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="Q278" s="1" t="n">
-        <v>0.02308</v>
+      <c r="R278" s="1" t="n">
+        <v>0.02306</v>
       </c>
     </row>
     <row r="279">
@@ -15809,9 +16646,12 @@
         <v>0.01815</v>
       </c>
       <c r="P279" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="Q279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="Q279" s="1" t="n">
+      <c r="R279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -15864,10 +16704,13 @@
         <v>0.03681</v>
       </c>
       <c r="P280" s="1" t="n">
+        <v>0.03666</v>
+      </c>
+      <c r="Q280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="Q280" s="1" t="n">
-        <v>0.03681</v>
+      <c r="R280" s="1" t="n">
+        <v>0.03666</v>
       </c>
     </row>
     <row r="281">
@@ -15919,9 +16762,12 @@
         <v>0.0396</v>
       </c>
       <c r="P281" s="1" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="Q281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="Q281" s="1" t="n">
+      <c r="R281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -15974,9 +16820,12 @@
         <v>0.3019</v>
       </c>
       <c r="P282" s="1" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="Q282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="Q282" s="1" t="n">
+      <c r="R282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -16029,10 +16878,13 @@
         <v>0.01119</v>
       </c>
       <c r="P283" s="1" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="Q283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="Q283" s="1" t="n">
-        <v>0.01119</v>
+      <c r="R283" s="1" t="n">
+        <v>0.01117</v>
       </c>
     </row>
     <row r="284">
@@ -16084,9 +16936,12 @@
         <v>9.7e-06</v>
       </c>
       <c r="P284" s="1" t="n">
+        <v>9.7e-06</v>
+      </c>
+      <c r="Q284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="Q284" s="1" t="n">
+      <c r="R284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -16139,9 +16994,12 @@
         <v>0.1145</v>
       </c>
       <c r="P285" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="Q285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="Q285" s="1" t="n">
+      <c r="R285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -16194,9 +17052,12 @@
         <v>0.003428</v>
       </c>
       <c r="P286" s="1" t="n">
+        <v>0.003425</v>
+      </c>
+      <c r="Q286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="Q286" s="1" t="n">
+      <c r="R286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -16249,10 +17110,13 @@
         <v>0.08497</v>
       </c>
       <c r="P287" s="1" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="Q287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="Q287" s="1" t="n">
-        <v>0.08486</v>
+      <c r="R287" s="1" t="n">
+        <v>0.08465</v>
       </c>
     </row>
     <row r="288">
@@ -16304,9 +17168,12 @@
         <v>0.09934</v>
       </c>
       <c r="P288" s="1" t="n">
+        <v>0.09958</v>
+      </c>
+      <c r="Q288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="Q288" s="1" t="n">
+      <c r="R288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -16359,9 +17226,12 @@
         <v>0.4338</v>
       </c>
       <c r="P289" s="1" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="Q289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="Q289" s="1" t="n">
+      <c r="R289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -16414,9 +17284,12 @@
         <v>0.03914</v>
       </c>
       <c r="P290" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="Q290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="Q290" s="1" t="n">
+      <c r="R290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -16469,10 +17342,13 @@
         <v>0.235</v>
       </c>
       <c r="P291" s="1" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="Q291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="Q291" s="1" t="n">
-        <v>0.235</v>
+      <c r="R291" s="1" t="n">
+        <v>0.2344</v>
       </c>
     </row>
     <row r="292">
@@ -16524,9 +17400,12 @@
         <v>0.28304</v>
       </c>
       <c r="P292" s="1" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="Q292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="Q292" s="1" t="n">
+      <c r="R292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -16579,10 +17458,13 @@
         <v>0.1494</v>
       </c>
       <c r="P293" s="1" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="Q293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="Q293" s="1" t="n">
-        <v>0.1489</v>
+      <c r="R293" s="1" t="n">
+        <v>0.1487</v>
       </c>
     </row>
     <row r="294">
@@ -16634,10 +17516,13 @@
         <v>4.181</v>
       </c>
       <c r="P294" s="1" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="Q294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="Q294" s="1" t="n">
-        <v>4.181</v>
+      <c r="R294" s="1" t="n">
+        <v>4.171</v>
       </c>
     </row>
     <row r="295">
@@ -16689,9 +17574,12 @@
         <v>0.03406</v>
       </c>
       <c r="P295" s="1" t="n">
-        <v>0.03406</v>
+        <v>0.03436</v>
       </c>
       <c r="Q295" s="1" t="n">
+        <v>0.03436</v>
+      </c>
+      <c r="R295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -16744,10 +17632,13 @@
         <v>0.000966</v>
       </c>
       <c r="P296" s="1" t="n">
+        <v>0.000964</v>
+      </c>
+      <c r="Q296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="Q296" s="1" t="n">
-        <v>0.000965</v>
+      <c r="R296" s="1" t="n">
+        <v>0.000964</v>
       </c>
     </row>
     <row r="297">
@@ -16799,10 +17690,13 @@
         <v>0.08161</v>
       </c>
       <c r="P297" s="1" t="n">
+        <v>0.08135000000000001</v>
+      </c>
+      <c r="Q297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="Q297" s="1" t="n">
-        <v>0.08154</v>
+      <c r="R297" s="1" t="n">
+        <v>0.08135000000000001</v>
       </c>
     </row>
     <row r="298">
@@ -16854,9 +17748,12 @@
         <v>0.05789</v>
       </c>
       <c r="P298" s="1" t="n">
+        <v>0.05781</v>
+      </c>
+      <c r="Q298" s="1" t="n">
         <v>0.05845</v>
       </c>
-      <c r="Q298" s="1" t="n">
+      <c r="R298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -16909,10 +17806,13 @@
         <v>0.09039</v>
       </c>
       <c r="P299" s="1" t="n">
+        <v>0.09028</v>
+      </c>
+      <c r="Q299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="Q299" s="1" t="n">
-        <v>0.09039</v>
+      <c r="R299" s="1" t="n">
+        <v>0.09028</v>
       </c>
     </row>
     <row r="300">
@@ -16964,9 +17864,12 @@
         <v>0.02724</v>
       </c>
       <c r="P300" s="1" t="n">
+        <v>0.02724</v>
+      </c>
+      <c r="Q300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="Q300" s="1" t="n">
+      <c r="R300" s="1" t="n">
         <v>0.02724</v>
       </c>
     </row>
@@ -17019,10 +17922,13 @@
         <v>0.06526999999999999</v>
       </c>
       <c r="P301" s="1" t="n">
+        <v>0.06525</v>
+      </c>
+      <c r="Q301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="Q301" s="1" t="n">
-        <v>0.06526999999999999</v>
+      <c r="R301" s="1" t="n">
+        <v>0.06525</v>
       </c>
     </row>
     <row r="302">
@@ -17074,9 +17980,12 @@
         <v>0.053559</v>
       </c>
       <c r="P302" s="1" t="n">
+        <v>0.053465</v>
+      </c>
+      <c r="Q302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="Q302" s="1" t="n">
+      <c r="R302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -17129,9 +18038,12 @@
         <v>5173.5</v>
       </c>
       <c r="P303" s="1" t="n">
+        <v>5172.5</v>
+      </c>
+      <c r="Q303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="Q303" s="1" t="n">
+      <c r="R303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -17184,10 +18096,13 @@
         <v>14.82</v>
       </c>
       <c r="P304" s="1" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Q304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="Q304" s="1" t="n">
-        <v>14.82</v>
+      <c r="R304" s="1" t="n">
+        <v>14.8</v>
       </c>
     </row>
     <row r="305">
@@ -17239,10 +18154,13 @@
         <v>0.003698</v>
       </c>
       <c r="P305" s="1" t="n">
+        <v>0.003688</v>
+      </c>
+      <c r="Q305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="Q305" s="1" t="n">
-        <v>0.003695</v>
+      <c r="R305" s="1" t="n">
+        <v>0.003688</v>
       </c>
     </row>
     <row r="306">
@@ -17294,9 +18212,12 @@
         <v>0.454</v>
       </c>
       <c r="P306" s="1" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="Q306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="Q306" s="1" t="n">
+      <c r="R306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -17349,10 +18270,13 @@
         <v>0.04666</v>
       </c>
       <c r="P307" s="1" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="Q307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="Q307" s="1" t="n">
-        <v>0.04666</v>
+      <c r="R307" s="1" t="n">
+        <v>0.04656</v>
       </c>
     </row>
     <row r="308">
@@ -17404,9 +18328,12 @@
         <v>1.4997</v>
       </c>
       <c r="P308" s="1" t="n">
-        <v>1.4997</v>
+        <v>1.5096</v>
       </c>
       <c r="Q308" s="1" t="n">
+        <v>1.5096</v>
+      </c>
+      <c r="R308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -17459,9 +18386,12 @@
         <v>0.0007989</v>
       </c>
       <c r="P309" s="1" t="n">
+        <v>0.0007994</v>
+      </c>
+      <c r="Q309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="Q309" s="1" t="n">
+      <c r="R309" s="1" t="n">
         <v>0.0007892</v>
       </c>
     </row>
@@ -17514,10 +18444,13 @@
         <v>4.553</v>
       </c>
       <c r="P310" s="1" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="Q310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="Q310" s="1" t="n">
-        <v>4.553</v>
+      <c r="R310" s="1" t="n">
+        <v>4.549</v>
       </c>
     </row>
     <row r="311">
@@ -17569,9 +18502,12 @@
         <v>4.768</v>
       </c>
       <c r="P311" s="1" t="n">
+        <v>4.772</v>
+      </c>
+      <c r="Q311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="Q311" s="1" t="n">
+      <c r="R311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -17624,9 +18560,12 @@
         <v>0.08173</v>
       </c>
       <c r="P312" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="Q312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="Q312" s="1" t="n">
+      <c r="R312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -17679,10 +18618,13 @@
         <v>2.01</v>
       </c>
       <c r="P313" s="1" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="Q313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q313" s="1" t="n">
-        <v>2.01</v>
+      <c r="R313" s="1" t="n">
+        <v>2.005</v>
       </c>
     </row>
     <row r="314">
@@ -17734,9 +18676,12 @@
         <v>0.07239</v>
       </c>
       <c r="P314" s="1" t="n">
+        <v>0.07418</v>
+      </c>
+      <c r="Q314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="Q314" s="1" t="n">
+      <c r="R314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -17789,9 +18734,12 @@
         <v>0.9360000000000001</v>
       </c>
       <c r="P315" s="1" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="Q315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="Q315" s="1" t="n">
+      <c r="R315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -17844,9 +18792,12 @@
         <v>0.1304</v>
       </c>
       <c r="P316" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="Q316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="Q316" s="1" t="n">
+      <c r="R316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -17899,9 +18850,12 @@
         <v>0.184</v>
       </c>
       <c r="P317" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="Q317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="Q317" s="1" t="n">
+      <c r="R317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -17954,9 +18908,12 @@
         <v>0.01607</v>
       </c>
       <c r="P318" s="1" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="Q318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="Q318" s="1" t="n">
+      <c r="R318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -18009,10 +18966,13 @@
         <v>0.08327</v>
       </c>
       <c r="P319" s="1" t="n">
+        <v>0.08318</v>
+      </c>
+      <c r="Q319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="Q319" s="1" t="n">
-        <v>0.08325</v>
+      <c r="R319" s="1" t="n">
+        <v>0.08318</v>
       </c>
     </row>
     <row r="320">
@@ -18064,10 +19024,13 @@
         <v>0.007514</v>
       </c>
       <c r="P320" s="1" t="n">
+        <v>0.007463</v>
+      </c>
+      <c r="Q320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="Q320" s="1" t="n">
-        <v>0.007514</v>
+      <c r="R320" s="1" t="n">
+        <v>0.007463</v>
       </c>
     </row>
     <row r="321">
@@ -18119,9 +19082,12 @@
         <v>0.05425</v>
       </c>
       <c r="P321" s="1" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="Q321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="Q321" s="1" t="n">
+      <c r="R321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -18174,9 +19140,12 @@
         <v>0.5495</v>
       </c>
       <c r="P322" s="1" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="Q322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="Q322" s="1" t="n">
+      <c r="R322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -18229,9 +19198,12 @@
         <v>0.07584</v>
       </c>
       <c r="P323" s="1" t="n">
+        <v>0.07568</v>
+      </c>
+      <c r="Q323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="Q323" s="1" t="n">
+      <c r="R323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -18284,9 +19256,12 @@
         <v>0.012989</v>
       </c>
       <c r="P324" s="1" t="n">
+        <v>0.012915</v>
+      </c>
+      <c r="Q324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="Q324" s="1" t="n">
+      <c r="R324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -18339,10 +19314,13 @@
         <v>0.0988</v>
       </c>
       <c r="P325" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="Q325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="Q325" s="1" t="n">
-        <v>0.0988</v>
+      <c r="R325" s="1" t="n">
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="326">
@@ -18394,10 +19372,13 @@
         <v>0.01734</v>
       </c>
       <c r="P326" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="Q326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="Q326" s="1" t="n">
-        <v>0.01731</v>
+      <c r="R326" s="1" t="n">
+        <v>0.01729</v>
       </c>
     </row>
     <row r="327">
@@ -18449,10 +19430,13 @@
         <v>0.0638</v>
       </c>
       <c r="P327" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="Q327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="Q327" s="1" t="n">
-        <v>0.0638</v>
+      <c r="R327" s="1" t="n">
+        <v>0.06370000000000001</v>
       </c>
     </row>
     <row r="328">
@@ -18504,10 +19488,13 @@
         <v>0.2614</v>
       </c>
       <c r="P328" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="Q328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="Q328" s="1" t="n">
-        <v>0.2614</v>
+      <c r="R328" s="1" t="n">
+        <v>0.2612</v>
       </c>
     </row>
     <row r="329">
@@ -18559,9 +19546,12 @@
         <v>0.17406</v>
       </c>
       <c r="P329" s="1" t="n">
+        <v>0.17393</v>
+      </c>
+      <c r="Q329" s="1" t="n">
         <v>0.17406</v>
       </c>
-      <c r="Q329" s="1" t="n">
+      <c r="R329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -18614,9 +19604,12 @@
         <v>2.046</v>
       </c>
       <c r="P330" s="1" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="Q330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="Q330" s="1" t="n">
+      <c r="R330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -18669,9 +19662,12 @@
         <v>0.0284</v>
       </c>
       <c r="P331" s="1" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="Q331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="Q331" s="1" t="n">
+      <c r="R331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -18724,9 +19720,12 @@
         <v>0.006006</v>
       </c>
       <c r="P332" s="1" t="n">
+        <v>0.00602</v>
+      </c>
+      <c r="Q332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="Q332" s="1" t="n">
+      <c r="R332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -18779,9 +19778,12 @@
         <v>0.003513</v>
       </c>
       <c r="P333" s="1" t="n">
+        <v>0.003527</v>
+      </c>
+      <c r="Q333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="Q333" s="1" t="n">
+      <c r="R333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -18834,9 +19836,12 @@
         <v>0.01401</v>
       </c>
       <c r="P334" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="Q334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="Q334" s="1" t="n">
+      <c r="R334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -18889,9 +19894,12 @@
         <v>1.14</v>
       </c>
       <c r="P335" s="1" t="n">
-        <v>1.14</v>
+        <v>1.141</v>
       </c>
       <c r="Q335" s="1" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="R335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -18944,9 +19952,12 @@
         <v>0.011289</v>
       </c>
       <c r="P336" s="1" t="n">
+        <v>0.011316</v>
+      </c>
+      <c r="Q336" s="1" t="n">
         <v>0.011344</v>
       </c>
-      <c r="Q336" s="1" t="n">
+      <c r="R336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -18999,9 +20010,12 @@
         <v>2.952</v>
       </c>
       <c r="P337" s="1" t="n">
+        <v>2.948</v>
+      </c>
+      <c r="Q337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="Q337" s="1" t="n">
+      <c r="R337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -19054,10 +20068,13 @@
         <v>0.01851</v>
       </c>
       <c r="P338" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="Q338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="Q338" s="1" t="n">
-        <v>0.01851</v>
+      <c r="R338" s="1" t="n">
+        <v>0.01844</v>
       </c>
     </row>
     <row r="339">
@@ -19109,9 +20126,12 @@
         <v>0.07725</v>
       </c>
       <c r="P339" s="1" t="n">
+        <v>0.07693999999999999</v>
+      </c>
+      <c r="Q339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="Q339" s="1" t="n">
+      <c r="R339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -19164,9 +20184,12 @@
         <v>0.076</v>
       </c>
       <c r="P340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="Q340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="Q340" s="1" t="n">
+      <c r="R340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -19219,10 +20242,13 @@
         <v>0.03585</v>
       </c>
       <c r="P341" s="1" t="n">
+        <v>0.03578</v>
+      </c>
+      <c r="Q341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="Q341" s="1" t="n">
-        <v>0.03581</v>
+      <c r="R341" s="1" t="n">
+        <v>0.03578</v>
       </c>
     </row>
     <row r="342">
@@ -19274,10 +20300,13 @@
         <v>2602</v>
       </c>
       <c r="P342" s="1" t="n">
+        <v>2592</v>
+      </c>
+      <c r="Q342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="Q342" s="1" t="n">
-        <v>2599</v>
+      <c r="R342" s="1" t="n">
+        <v>2592</v>
       </c>
     </row>
     <row r="343">
@@ -19329,9 +20358,12 @@
         <v>0.0001995</v>
       </c>
       <c r="P343" s="1" t="n">
+        <v>0.0001999</v>
+      </c>
+      <c r="Q343" s="1" t="n">
         <v>0.0002003</v>
       </c>
-      <c r="Q343" s="1" t="n">
+      <c r="R343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -19384,10 +20416,13 @@
         <v>0.07929</v>
       </c>
       <c r="P344" s="1" t="n">
+        <v>0.07915</v>
+      </c>
+      <c r="Q344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="Q344" s="1" t="n">
-        <v>0.07925</v>
+      <c r="R344" s="1" t="n">
+        <v>0.07915</v>
       </c>
     </row>
     <row r="345">
@@ -19439,10 +20474,13 @@
         <v>0.0163</v>
       </c>
       <c r="P345" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="Q345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="Q345" s="1" t="n">
-        <v>0.0163</v>
+      <c r="R345" s="1" t="n">
+        <v>0.01626</v>
       </c>
     </row>
     <row r="346">
@@ -19494,10 +20532,13 @@
         <v>2.734</v>
       </c>
       <c r="P346" s="1" t="n">
+        <v>2.731</v>
+      </c>
+      <c r="Q346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="Q346" s="1" t="n">
-        <v>2.734</v>
+      <c r="R346" s="1" t="n">
+        <v>2.731</v>
       </c>
     </row>
     <row r="347">
@@ -19549,10 +20590,13 @@
         <v>0.01626</v>
       </c>
       <c r="P347" s="1" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="Q347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="Q347" s="1" t="n">
-        <v>0.01626</v>
+      <c r="R347" s="1" t="n">
+        <v>0.01625</v>
       </c>
     </row>
     <row r="348">
@@ -19604,9 +20648,12 @@
         <v>0.03951</v>
       </c>
       <c r="P348" s="1" t="n">
-        <v>0.03968</v>
+        <v>0.03971</v>
       </c>
       <c r="Q348" s="1" t="n">
+        <v>0.03971</v>
+      </c>
+      <c r="R348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -19659,9 +20706,12 @@
         <v>0.3035</v>
       </c>
       <c r="P349" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Q349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="Q349" s="1" t="n">
+      <c r="R349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -19714,9 +20764,12 @@
         <v>0.005096</v>
       </c>
       <c r="P350" s="1" t="n">
+        <v>0.005084</v>
+      </c>
+      <c r="Q350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="Q350" s="1" t="n">
+      <c r="R350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -19769,9 +20822,12 @@
         <v>0.005072</v>
       </c>
       <c r="P351" s="1" t="n">
+        <v>0.005066</v>
+      </c>
+      <c r="Q351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="Q351" s="1" t="n">
+      <c r="R351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -19824,9 +20880,12 @@
         <v>0.004379</v>
       </c>
       <c r="P352" s="1" t="n">
+        <v>0.00438</v>
+      </c>
+      <c r="Q352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="Q352" s="1" t="n">
+      <c r="R352" s="1" t="n">
         <v>0.004379</v>
       </c>
     </row>
@@ -19879,9 +20938,12 @@
         <v>0.08041</v>
       </c>
       <c r="P353" s="1" t="n">
+        <v>0.08033</v>
+      </c>
+      <c r="Q353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="Q353" s="1" t="n">
+      <c r="R353" s="1" t="n">
         <v>0.0803</v>
       </c>
     </row>
@@ -19934,10 +20996,13 @@
         <v>1.265</v>
       </c>
       <c r="P354" s="1" t="n">
+        <v>1.258</v>
+      </c>
+      <c r="Q354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="Q354" s="1" t="n">
-        <v>1.265</v>
+      <c r="R354" s="1" t="n">
+        <v>1.258</v>
       </c>
     </row>
     <row r="355">
@@ -19989,10 +21054,13 @@
         <v>7.68</v>
       </c>
       <c r="P355" s="1" t="n">
+        <v>7.651</v>
+      </c>
+      <c r="Q355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="Q355" s="1" t="n">
-        <v>7.68</v>
+      <c r="R355" s="1" t="n">
+        <v>7.651</v>
       </c>
     </row>
     <row r="356">
@@ -20044,9 +21112,12 @@
         <v>0.00777</v>
       </c>
       <c r="P356" s="1" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="Q356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="Q356" s="1" t="n">
+      <c r="R356" s="1" t="n">
         <v>0.00777</v>
       </c>
     </row>
@@ -20099,9 +21170,12 @@
         <v>0.005643</v>
       </c>
       <c r="P357" s="1" t="n">
+        <v>0.00563</v>
+      </c>
+      <c r="Q357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="Q357" s="1" t="n">
+      <c r="R357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -20154,10 +21228,13 @@
         <v>0.01543</v>
       </c>
       <c r="P358" s="1" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="Q358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="Q358" s="1" t="n">
-        <v>0.01543</v>
+      <c r="R358" s="1" t="n">
+        <v>0.01533</v>
       </c>
     </row>
     <row r="359">
@@ -20209,10 +21286,13 @@
         <v>3.615</v>
       </c>
       <c r="P359" s="1" t="n">
+        <v>3.612</v>
+      </c>
+      <c r="Q359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="Q359" s="1" t="n">
-        <v>3.615</v>
+      <c r="R359" s="1" t="n">
+        <v>3.612</v>
       </c>
     </row>
     <row r="360">
@@ -20264,9 +21344,12 @@
         <v>0.1503</v>
       </c>
       <c r="P360" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="Q360" s="1" t="n">
+      <c r="R360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -20319,9 +21402,12 @@
         <v>0.07038999999999999</v>
       </c>
       <c r="P361" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="Q361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="Q361" s="1" t="n">
+      <c r="R361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -20374,9 +21460,12 @@
         <v>0.01761</v>
       </c>
       <c r="P362" s="1" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="Q362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="Q362" s="1" t="n">
+      <c r="R362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -20429,10 +21518,13 @@
         <v>0.02235</v>
       </c>
       <c r="P363" s="1" t="n">
+        <v>0.02229</v>
+      </c>
+      <c r="Q363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="Q363" s="1" t="n">
-        <v>0.02234</v>
+      <c r="R363" s="1" t="n">
+        <v>0.02229</v>
       </c>
     </row>
     <row r="364">
@@ -20484,9 +21576,12 @@
         <v>0.01251</v>
       </c>
       <c r="P364" s="1" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="Q364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="Q364" s="1" t="n">
+      <c r="R364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -20539,10 +21634,13 @@
         <v>0.091</v>
       </c>
       <c r="P365" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="Q365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="Q365" s="1" t="n">
-        <v>0.091</v>
+      <c r="R365" s="1" t="n">
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="366">
@@ -20594,10 +21692,13 @@
         <v>0.04223</v>
       </c>
       <c r="P366" s="1" t="n">
+        <v>0.04214</v>
+      </c>
+      <c r="Q366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="Q366" s="1" t="n">
-        <v>0.04223</v>
+      <c r="R366" s="1" t="n">
+        <v>0.04214</v>
       </c>
     </row>
     <row r="367">
@@ -20649,10 +21750,13 @@
         <v>0.03128</v>
       </c>
       <c r="P367" s="1" t="n">
+        <v>0.03124</v>
+      </c>
+      <c r="Q367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="Q367" s="1" t="n">
-        <v>0.03128</v>
+      <c r="R367" s="1" t="n">
+        <v>0.03124</v>
       </c>
     </row>
     <row r="368">
@@ -20704,10 +21808,13 @@
         <v>0.02336</v>
       </c>
       <c r="P368" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="Q368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="Q368" s="1" t="n">
-        <v>0.02331</v>
+      <c r="R368" s="1" t="n">
+        <v>0.0233</v>
       </c>
     </row>
     <row r="369">
@@ -20759,10 +21866,13 @@
         <v>0.03087</v>
       </c>
       <c r="P369" s="1" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="Q369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="Q369" s="1" t="n">
-        <v>0.03087</v>
+      <c r="R369" s="1" t="n">
+        <v>0.0308</v>
       </c>
     </row>
     <row r="370">
@@ -20814,9 +21924,12 @@
         <v>0.07935</v>
       </c>
       <c r="P370" s="1" t="n">
+        <v>0.07973</v>
+      </c>
+      <c r="Q370" s="1" t="n">
         <v>0.07990999999999999</v>
       </c>
-      <c r="Q370" s="1" t="n">
+      <c r="R370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -20869,10 +21982,13 @@
         <v>0.1073</v>
       </c>
       <c r="P371" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="Q371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="Q371" s="1" t="n">
-        <v>0.1073</v>
+      <c r="R371" s="1" t="n">
+        <v>0.1072</v>
       </c>
     </row>
     <row r="372">
@@ -20924,10 +22040,13 @@
         <v>0.006965</v>
       </c>
       <c r="P372" s="1" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="Q372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="Q372" s="1" t="n">
-        <v>0.006965</v>
+      <c r="R372" s="1" t="n">
+        <v>0.00694</v>
       </c>
     </row>
     <row r="373">
@@ -20979,9 +22098,12 @@
         <v>0.0959</v>
       </c>
       <c r="P373" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="Q373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="Q373" s="1" t="n">
+      <c r="R373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -21034,9 +22156,12 @@
         <v>0.0573</v>
       </c>
       <c r="P374" s="1" t="n">
+        <v>0.05739</v>
+      </c>
+      <c r="Q374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="Q374" s="1" t="n">
+      <c r="R374" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -21089,9 +22214,12 @@
         <v>0.3175</v>
       </c>
       <c r="P375" s="1" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="Q375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="Q375" s="1" t="n">
+      <c r="R375" s="1" t="n">
         <v>0.3175</v>
       </c>
     </row>
@@ -21144,10 +22272,13 @@
         <v>0.01942</v>
       </c>
       <c r="P376" s="1" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="Q376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="Q376" s="1" t="n">
-        <v>0.01942</v>
+      <c r="R376" s="1" t="n">
+        <v>0.01938</v>
       </c>
     </row>
     <row r="377">
@@ -21199,10 +22330,13 @@
         <v>0.0683</v>
       </c>
       <c r="P377" s="1" t="n">
+        <v>0.06818</v>
+      </c>
+      <c r="Q377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="Q377" s="1" t="n">
-        <v>0.06827999999999999</v>
+      <c r="R377" s="1" t="n">
+        <v>0.06818</v>
       </c>
     </row>
     <row r="378">
@@ -21254,9 +22388,12 @@
         <v>0.15781</v>
       </c>
       <c r="P378" s="1" t="n">
+        <v>0.15808</v>
+      </c>
+      <c r="Q378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="Q378" s="1" t="n">
+      <c r="R378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -21309,10 +22446,13 @@
         <v>0.0005941</v>
       </c>
       <c r="P379" s="1" t="n">
+        <v>0.0005929</v>
+      </c>
+      <c r="Q379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="Q379" s="1" t="n">
-        <v>0.0005941</v>
+      <c r="R379" s="1" t="n">
+        <v>0.0005929</v>
       </c>
     </row>
     <row r="380">
@@ -21364,9 +22504,12 @@
         <v>0.01015</v>
       </c>
       <c r="P380" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="Q380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="Q380" s="1" t="n">
+      <c r="R380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -21419,9 +22562,12 @@
         <v>0.02548</v>
       </c>
       <c r="P381" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="Q381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="Q381" s="1" t="n">
+      <c r="R381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -21474,9 +22620,12 @@
         <v>0.19005</v>
       </c>
       <c r="P382" s="1" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="Q382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="Q382" s="1" t="n">
+      <c r="R382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -21529,10 +22678,13 @@
         <v>0.09253</v>
       </c>
       <c r="P383" s="1" t="n">
+        <v>0.09214</v>
+      </c>
+      <c r="Q383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="Q383" s="1" t="n">
-        <v>0.09236</v>
+      <c r="R383" s="1" t="n">
+        <v>0.09214</v>
       </c>
     </row>
     <row r="384">
@@ -21584,9 +22736,12 @@
         <v>0.03167</v>
       </c>
       <c r="P384" s="1" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="Q384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="Q384" s="1" t="n">
+      <c r="R384" s="1" t="n">
         <v>0.03163</v>
       </c>
     </row>
@@ -21639,10 +22794,13 @@
         <v>0.0109</v>
       </c>
       <c r="P385" s="1" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="Q385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="Q385" s="1" t="n">
-        <v>0.0109</v>
+      <c r="R385" s="1" t="n">
+        <v>0.01086</v>
       </c>
     </row>
     <row r="386">
@@ -21694,10 +22852,13 @@
         <v>0.05073</v>
       </c>
       <c r="P386" s="1" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="Q386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="Q386" s="1" t="n">
-        <v>0.05073</v>
+      <c r="R386" s="1" t="n">
+        <v>0.05059</v>
       </c>
     </row>
     <row r="387">
@@ -21749,10 +22910,13 @@
         <v>0.02501</v>
       </c>
       <c r="P387" s="1" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="Q387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="Q387" s="1" t="n">
-        <v>0.02483</v>
+      <c r="R387" s="1" t="n">
+        <v>0.02405</v>
       </c>
     </row>
     <row r="388">
@@ -21804,10 +22968,13 @@
         <v>0.007258</v>
       </c>
       <c r="P388" s="1" t="n">
+        <v>0.007214</v>
+      </c>
+      <c r="Q388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="Q388" s="1" t="n">
-        <v>0.007258</v>
+      <c r="R388" s="1" t="n">
+        <v>0.007214</v>
       </c>
     </row>
     <row r="389">
@@ -21859,9 +23026,12 @@
         <v>0.01013</v>
       </c>
       <c r="P389" s="1" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="Q389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="Q389" s="1" t="n">
+      <c r="R389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -21914,10 +23084,13 @@
         <v>0.08237999999999999</v>
       </c>
       <c r="P390" s="1" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="Q390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="Q390" s="1" t="n">
-        <v>0.0823</v>
+      <c r="R390" s="1" t="n">
+        <v>0.08214</v>
       </c>
     </row>
     <row r="391">
@@ -21969,9 +23142,12 @@
         <v>0.5039</v>
       </c>
       <c r="P391" s="1" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="Q391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="Q391" s="1" t="n">
+      <c r="R391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -22024,10 +23200,13 @@
         <v>0.1162</v>
       </c>
       <c r="P392" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="Q392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="Q392" s="1" t="n">
-        <v>0.1162</v>
+      <c r="R392" s="1" t="n">
+        <v>0.1157</v>
       </c>
     </row>
     <row r="393">
@@ -22079,9 +23258,12 @@
         <v>0.00244</v>
       </c>
       <c r="P393" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="Q393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="Q393" s="1" t="n">
+      <c r="R393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -22134,10 +23316,13 @@
         <v>0.02127</v>
       </c>
       <c r="P394" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="Q394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="Q394" s="1" t="n">
-        <v>0.02121</v>
+      <c r="R394" s="1" t="n">
+        <v>0.02108</v>
       </c>
     </row>
     <row r="395">
@@ -22189,9 +23374,12 @@
         <v>0.0159</v>
       </c>
       <c r="P395" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="Q395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="Q395" s="1" t="n">
+      <c r="R395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -22244,9 +23432,12 @@
         <v>0.1352</v>
       </c>
       <c r="P396" s="1" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="Q396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="Q396" s="1" t="n">
+      <c r="R396" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -22299,9 +23490,12 @@
         <v>0.01442</v>
       </c>
       <c r="P397" s="1" t="n">
+        <v>0.01442</v>
+      </c>
+      <c r="Q397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="Q397" s="1" t="n">
+      <c r="R397" s="1" t="n">
         <v>0.01442</v>
       </c>
     </row>
@@ -22354,10 +23548,13 @@
         <v>6.731</v>
       </c>
       <c r="P398" s="1" t="n">
+        <v>6.679</v>
+      </c>
+      <c r="Q398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="Q398" s="1" t="n">
-        <v>6.701</v>
+      <c r="R398" s="1" t="n">
+        <v>6.679</v>
       </c>
     </row>
     <row r="399">
@@ -22409,10 +23606,13 @@
         <v>0.009391</v>
       </c>
       <c r="P399" s="1" t="n">
+        <v>0.00937</v>
+      </c>
+      <c r="Q399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="Q399" s="1" t="n">
-        <v>0.009384999999999999</v>
+      <c r="R399" s="1" t="n">
+        <v>0.00937</v>
       </c>
     </row>
     <row r="400">
@@ -22464,9 +23664,12 @@
         <v>0.001259</v>
       </c>
       <c r="P400" s="1" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="Q400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="Q400" s="1" t="n">
+      <c r="R400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -22519,10 +23722,13 @@
         <v>0.01849</v>
       </c>
       <c r="P401" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="Q401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="Q401" s="1" t="n">
-        <v>0.01841</v>
+      <c r="R401" s="1" t="n">
+        <v>0.0184</v>
       </c>
     </row>
     <row r="402">
@@ -22574,10 +23780,13 @@
         <v>0.08470999999999999</v>
       </c>
       <c r="P402" s="1" t="n">
+        <v>0.08447</v>
+      </c>
+      <c r="Q402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="Q402" s="1" t="n">
-        <v>0.08470999999999999</v>
+      <c r="R402" s="1" t="n">
+        <v>0.08447</v>
       </c>
     </row>
     <row r="403">
@@ -22629,10 +23838,13 @@
         <v>0.00552</v>
       </c>
       <c r="P403" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="Q403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="Q403" s="1" t="n">
-        <v>0.0055</v>
+      <c r="R403" s="1" t="n">
+        <v>0.00548</v>
       </c>
     </row>
     <row r="404">
@@ -22684,9 +23896,12 @@
         <v>0.0427</v>
       </c>
       <c r="P404" s="1" t="n">
+        <v>0.04261</v>
+      </c>
+      <c r="Q404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="Q404" s="1" t="n">
+      <c r="R404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -22739,10 +23954,13 @@
         <v>0.05831</v>
       </c>
       <c r="P405" s="1" t="n">
+        <v>0.05827</v>
+      </c>
+      <c r="Q405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="Q405" s="1" t="n">
-        <v>0.05831</v>
+      <c r="R405" s="1" t="n">
+        <v>0.05827</v>
       </c>
     </row>
     <row r="406">
@@ -22794,9 +24012,12 @@
         <v>0.01652</v>
       </c>
       <c r="P406" s="1" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="Q406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="Q406" s="1" t="n">
+      <c r="R406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -22849,9 +24070,12 @@
         <v>0.0424</v>
       </c>
       <c r="P407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="Q407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="Q407" s="1" t="n">
+      <c r="R407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -22904,10 +24128,13 @@
         <v>0.01924</v>
       </c>
       <c r="P408" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="Q408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="Q408" s="1" t="n">
-        <v>0.01922</v>
+      <c r="R408" s="1" t="n">
+        <v>0.01921</v>
       </c>
     </row>
     <row r="409">
@@ -22959,9 +24186,12 @@
         <v>0.4443</v>
       </c>
       <c r="P409" s="1" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="Q409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="Q409" s="1" t="n">
+      <c r="R409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -23014,10 +24244,13 @@
         <v>0.04394</v>
       </c>
       <c r="P410" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="Q410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="Q410" s="1" t="n">
-        <v>0.04394</v>
+      <c r="R410" s="1" t="n">
+        <v>0.04382</v>
       </c>
     </row>
     <row r="411">
@@ -23069,9 +24302,12 @@
         <v>27.25</v>
       </c>
       <c r="P411" s="1" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="Q411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="Q411" s="1" t="n">
+      <c r="R411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -23124,10 +24360,13 @@
         <v>0.03498</v>
       </c>
       <c r="P412" s="1" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="Q412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="Q412" s="1" t="n">
-        <v>0.03498</v>
+      <c r="R412" s="1" t="n">
+        <v>0.03493</v>
       </c>
     </row>
     <row r="413">
@@ -23179,10 +24418,13 @@
         <v>0.003392</v>
       </c>
       <c r="P413" s="1" t="n">
+        <v>0.003388</v>
+      </c>
+      <c r="Q413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="Q413" s="1" t="n">
-        <v>0.003392</v>
+      <c r="R413" s="1" t="n">
+        <v>0.003388</v>
       </c>
     </row>
     <row r="414">
@@ -23234,10 +24476,13 @@
         <v>0.1528</v>
       </c>
       <c r="P414" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="Q414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="Q414" s="1" t="n">
-        <v>0.1526</v>
+      <c r="R414" s="1" t="n">
+        <v>0.1525</v>
       </c>
     </row>
     <row r="415">
@@ -23289,9 +24534,12 @@
         <v>0.05258</v>
       </c>
       <c r="P415" s="1" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="Q415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="Q415" s="1" t="n">
+      <c r="R415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -23344,9 +24592,12 @@
         <v>0.00654</v>
       </c>
       <c r="P416" s="1" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="Q416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="Q416" s="1" t="n">
+      <c r="R416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -23399,9 +24650,12 @@
         <v>0.06026</v>
       </c>
       <c r="P417" s="1" t="n">
+        <v>0.06027</v>
+      </c>
+      <c r="Q417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="Q417" s="1" t="n">
+      <c r="R417" s="1" t="n">
         <v>0.06026</v>
       </c>
     </row>
@@ -23454,9 +24708,12 @@
         <v>0.008004000000000001</v>
       </c>
       <c r="P418" s="1" t="n">
+        <v>0.007992000000000001</v>
+      </c>
+      <c r="Q418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="Q418" s="1" t="n">
+      <c r="R418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -23509,9 +24766,12 @@
         <v>0.07425</v>
       </c>
       <c r="P419" s="1" t="n">
+        <v>0.07426000000000001</v>
+      </c>
+      <c r="Q419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="Q419" s="1" t="n">
+      <c r="R419" s="1" t="n">
         <v>0.07425</v>
       </c>
     </row>
@@ -23564,9 +24824,12 @@
         <v>0.02116</v>
       </c>
       <c r="P420" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="Q420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="Q420" s="1" t="n">
+      <c r="R420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -23619,10 +24882,13 @@
         <v>0.06909</v>
       </c>
       <c r="P421" s="1" t="n">
+        <v>0.06898</v>
+      </c>
+      <c r="Q421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="Q421" s="1" t="n">
-        <v>0.06909</v>
+      <c r="R421" s="1" t="n">
+        <v>0.06898</v>
       </c>
     </row>
     <row r="422">
@@ -23674,9 +24940,12 @@
         <v>0.01473</v>
       </c>
       <c r="P422" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="Q422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="Q422" s="1" t="n">
+      <c r="R422" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -23729,10 +24998,13 @@
         <v>0.006603</v>
       </c>
       <c r="P423" s="1" t="n">
+        <v>0.00658</v>
+      </c>
+      <c r="Q423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="Q423" s="1" t="n">
-        <v>0.006603</v>
+      <c r="R423" s="1" t="n">
+        <v>0.00658</v>
       </c>
     </row>
     <row r="424">
@@ -23784,9 +25056,12 @@
         <v>0.909</v>
       </c>
       <c r="P424" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="Q424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="Q424" s="1" t="n">
+      <c r="R424" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -23839,10 +25114,13 @@
         <v>0.03524</v>
       </c>
       <c r="P425" s="1" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="Q425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="Q425" s="1" t="n">
-        <v>0.03524</v>
+      <c r="R425" s="1" t="n">
+        <v>0.03519</v>
       </c>
     </row>
     <row r="426">
@@ -23894,9 +25172,12 @@
         <v>1.802</v>
       </c>
       <c r="P426" s="1" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="Q426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q426" s="1" t="n">
+      <c r="R426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -23949,9 +25230,12 @@
         <v>0.12821</v>
       </c>
       <c r="P427" s="1" t="n">
+        <v>0.12797</v>
+      </c>
+      <c r="Q427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="Q427" s="1" t="n">
+      <c r="R427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -24004,9 +25288,12 @@
         <v>0.05269</v>
       </c>
       <c r="P428" s="1" t="n">
+        <v>0.05277</v>
+      </c>
+      <c r="Q428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="Q428" s="1" t="n">
+      <c r="R428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -24059,10 +25346,13 @@
         <v>1.284</v>
       </c>
       <c r="P429" s="1" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="Q429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="Q429" s="1" t="n">
-        <v>1.284</v>
+      <c r="R429" s="1" t="n">
+        <v>1.282</v>
       </c>
     </row>
     <row r="430">
@@ -24114,10 +25404,13 @@
         <v>0.07474</v>
       </c>
       <c r="P430" s="1" t="n">
+        <v>0.07456</v>
+      </c>
+      <c r="Q430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="Q430" s="1" t="n">
-        <v>0.07463</v>
+      <c r="R430" s="1" t="n">
+        <v>0.07456</v>
       </c>
     </row>
     <row r="431">
@@ -24169,10 +25462,13 @@
         <v>0.1567</v>
       </c>
       <c r="P431" s="1" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="Q431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="Q431" s="1" t="n">
-        <v>0.1567</v>
+      <c r="R431" s="1" t="n">
+        <v>0.1564</v>
       </c>
     </row>
     <row r="432">
@@ -24224,9 +25520,12 @@
         <v>1.441</v>
       </c>
       <c r="P432" s="1" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="Q432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="Q432" s="1" t="n">
+      <c r="R432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -24279,10 +25578,13 @@
         <v>3.248</v>
       </c>
       <c r="P433" s="1" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="Q433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="Q433" s="1" t="n">
-        <v>3.248</v>
+      <c r="R433" s="1" t="n">
+        <v>3.239</v>
       </c>
     </row>
     <row r="434">
@@ -24334,9 +25636,12 @@
         <v>0.1788</v>
       </c>
       <c r="P434" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="Q434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="Q434" s="1" t="n">
+      <c r="R434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -24389,10 +25694,13 @@
         <v>0.008562</v>
       </c>
       <c r="P435" s="1" t="n">
+        <v>0.008548</v>
+      </c>
+      <c r="Q435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="Q435" s="1" t="n">
-        <v>0.008562</v>
+      <c r="R435" s="1" t="n">
+        <v>0.008548</v>
       </c>
     </row>
     <row r="436">
@@ -24444,9 +25752,12 @@
         <v>0.2823</v>
       </c>
       <c r="P436" s="1" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="Q436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="Q436" s="1" t="n">
+      <c r="R436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -24499,9 +25810,12 @@
         <v>0.03876</v>
       </c>
       <c r="P437" s="1" t="n">
+        <v>0.03876</v>
+      </c>
+      <c r="Q437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="Q437" s="1" t="n">
+      <c r="R437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -24554,9 +25868,12 @@
         <v>0.02434</v>
       </c>
       <c r="P438" s="1" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="Q438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="Q438" s="1" t="n">
+      <c r="R438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -24609,9 +25926,12 @@
         <v>0.04405</v>
       </c>
       <c r="P439" s="1" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="Q439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="Q439" s="1" t="n">
+      <c r="R439" s="1" t="n">
         <v>0.04401</v>
       </c>
     </row>
@@ -24664,10 +25984,13 @@
         <v>0.0005174999999999999</v>
       </c>
       <c r="P440" s="1" t="n">
+        <v>0.0005171</v>
+      </c>
+      <c r="Q440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="Q440" s="1" t="n">
-        <v>0.0005174999999999999</v>
+      <c r="R440" s="1" t="n">
+        <v>0.0005171</v>
       </c>
     </row>
     <row r="441">
@@ -24719,9 +26042,12 @@
         <v>0.04439</v>
       </c>
       <c r="P441" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="Q441" s="1" t="n">
         <v>0.04546</v>
       </c>
-      <c r="Q441" s="1" t="n">
+      <c r="R441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -24774,9 +26100,12 @@
         <v>0.000412</v>
       </c>
       <c r="P442" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="Q442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="Q442" s="1" t="n">
+      <c r="R442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -24829,9 +26158,12 @@
         <v>0.09426</v>
       </c>
       <c r="P443" s="1" t="n">
+        <v>0.09421</v>
+      </c>
+      <c r="Q443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="Q443" s="1" t="n">
+      <c r="R443" s="1" t="n">
         <v>0.09419</v>
       </c>
     </row>
@@ -24884,9 +26216,12 @@
         <v>2.299</v>
       </c>
       <c r="P444" s="1" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="Q444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="Q444" s="1" t="n">
+      <c r="R444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -24939,9 +26274,12 @@
         <v>0.2678</v>
       </c>
       <c r="P445" s="1" t="n">
+        <v>0.2676</v>
+      </c>
+      <c r="Q445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="Q445" s="1" t="n">
+      <c r="R445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -24994,10 +26332,13 @@
         <v>0.0007412</v>
       </c>
       <c r="P446" s="1" t="n">
+        <v>0.0007377</v>
+      </c>
+      <c r="Q446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="Q446" s="1" t="n">
-        <v>0.000741</v>
+      <c r="R446" s="1" t="n">
+        <v>0.0007377</v>
       </c>
     </row>
     <row r="447">
@@ -25049,9 +26390,12 @@
         <v>0.03867</v>
       </c>
       <c r="P447" s="1" t="n">
+        <v>0.03841</v>
+      </c>
+      <c r="Q447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="Q447" s="1" t="n">
+      <c r="R447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -25104,9 +26448,12 @@
         <v>0.1765</v>
       </c>
       <c r="P448" s="1" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="Q448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="Q448" s="1" t="n">
+      <c r="R448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -25159,9 +26506,12 @@
         <v>0.04275</v>
       </c>
       <c r="P449" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="Q449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="Q449" s="1" t="n">
+      <c r="R449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -25214,9 +26564,12 @@
         <v>0.0001642</v>
       </c>
       <c r="P450" s="1" t="n">
+        <v>0.0001638</v>
+      </c>
+      <c r="Q450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="Q450" s="1" t="n">
+      <c r="R450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -25269,10 +26622,13 @@
         <v>0.03712</v>
       </c>
       <c r="P451" s="1" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="Q451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="Q451" s="1" t="n">
-        <v>0.03708</v>
+      <c r="R451" s="1" t="n">
+        <v>0.03697</v>
       </c>
     </row>
     <row r="452">
@@ -25324,10 +26680,13 @@
         <v>0.0097</v>
       </c>
       <c r="P452" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="Q452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="Q452" s="1" t="n">
-        <v>0.0097</v>
+      <c r="R452" s="1" t="n">
+        <v>0.00966</v>
       </c>
     </row>
     <row r="453">
@@ -25379,9 +26738,12 @@
         <v>0.06794</v>
       </c>
       <c r="P453" s="1" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="Q453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="Q453" s="1" t="n">
+      <c r="R453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -25434,10 +26796,13 @@
         <v>0.007496</v>
       </c>
       <c r="P454" s="1" t="n">
+        <v>0.007478</v>
+      </c>
+      <c r="Q454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="Q454" s="1" t="n">
-        <v>0.00749</v>
+      <c r="R454" s="1" t="n">
+        <v>0.007478</v>
       </c>
     </row>
     <row r="455">
@@ -25489,10 +26854,13 @@
         <v>0.003282</v>
       </c>
       <c r="P455" s="1" t="n">
+        <v>0.003269</v>
+      </c>
+      <c r="Q455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="Q455" s="1" t="n">
-        <v>0.003278</v>
+      <c r="R455" s="1" t="n">
+        <v>0.003269</v>
       </c>
     </row>
     <row r="456">
@@ -25544,9 +26912,12 @@
         <v>0.00184</v>
       </c>
       <c r="P456" s="1" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="Q456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="Q456" s="1" t="n">
+      <c r="R456" s="1" t="n">
         <v>0.00184</v>
       </c>
     </row>
@@ -25599,9 +26970,12 @@
         <v>0.0001749</v>
       </c>
       <c r="P457" s="1" t="n">
+        <v>0.0001745</v>
+      </c>
+      <c r="Q457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="Q457" s="1" t="n">
+      <c r="R457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -25654,9 +27028,12 @@
         <v>0.0003895</v>
       </c>
       <c r="P458" s="1" t="n">
+        <v>0.0003897</v>
+      </c>
+      <c r="Q458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="Q458" s="1" t="n">
+      <c r="R458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -25709,9 +27086,12 @@
         <v>0.01393</v>
       </c>
       <c r="P459" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="Q459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="Q459" s="1" t="n">
+      <c r="R459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -25764,9 +27144,12 @@
         <v>0.04568</v>
       </c>
       <c r="P460" s="1" t="n">
+        <v>0.04564</v>
+      </c>
+      <c r="Q460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="Q460" s="1" t="n">
+      <c r="R460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -25819,9 +27202,12 @@
         <v>0.2819</v>
       </c>
       <c r="P461" s="1" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="Q461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="Q461" s="1" t="n">
+      <c r="R461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -25874,9 +27260,12 @@
         <v>0.006255</v>
       </c>
       <c r="P462" s="1" t="n">
+        <v>0.006221</v>
+      </c>
+      <c r="Q462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="Q462" s="1" t="n">
+      <c r="R462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -25929,9 +27318,12 @@
         <v>0.006999</v>
       </c>
       <c r="P463" s="1" t="n">
+        <v>0.007011</v>
+      </c>
+      <c r="Q463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="Q463" s="1" t="n">
+      <c r="R463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -25984,9 +27376,12 @@
         <v>0.2878</v>
       </c>
       <c r="P464" s="1" t="n">
-        <v>0.2888</v>
+        <v>0.289</v>
       </c>
       <c r="Q464" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="R464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -26039,9 +27434,12 @@
         <v>0.08047</v>
       </c>
       <c r="P465" s="1" t="n">
+        <v>0.08051</v>
+      </c>
+      <c r="Q465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="Q465" s="1" t="n">
+      <c r="R465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -26094,9 +27492,12 @@
         <v>0.6392</v>
       </c>
       <c r="P466" s="1" t="n">
+        <v>0.6391</v>
+      </c>
+      <c r="Q466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="Q466" s="1" t="n">
+      <c r="R466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -26149,9 +27550,12 @@
         <v>0.01471</v>
       </c>
       <c r="P467" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="Q467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="Q467" s="1" t="n">
+      <c r="R467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -26204,10 +27608,13 @@
         <v>0.03426</v>
       </c>
       <c r="P468" s="1" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="Q468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="Q468" s="1" t="n">
-        <v>0.03426</v>
+      <c r="R468" s="1" t="n">
+        <v>0.0342</v>
       </c>
     </row>
     <row r="469">
@@ -26259,10 +27666,13 @@
         <v>0.1617</v>
       </c>
       <c r="P469" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="Q469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="Q469" s="1" t="n">
-        <v>0.1617</v>
+      <c r="R469" s="1" t="n">
+        <v>0.1613</v>
       </c>
     </row>
     <row r="470">
@@ -26314,9 +27724,12 @@
         <v>0.408</v>
       </c>
       <c r="P470" s="1" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="Q470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="Q470" s="1" t="n">
+      <c r="R470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -26369,10 +27782,13 @@
         <v>0.06866</v>
       </c>
       <c r="P471" s="1" t="n">
+        <v>0.06859</v>
+      </c>
+      <c r="Q471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="Q471" s="1" t="n">
-        <v>0.06866</v>
+      <c r="R471" s="1" t="n">
+        <v>0.06859</v>
       </c>
     </row>
     <row r="472">
@@ -26424,10 +27840,13 @@
         <v>0.06605999999999999</v>
       </c>
       <c r="P472" s="1" t="n">
+        <v>0.06549000000000001</v>
+      </c>
+      <c r="Q472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="Q472" s="1" t="n">
-        <v>0.06605999999999999</v>
+      <c r="R472" s="1" t="n">
+        <v>0.06549000000000001</v>
       </c>
     </row>
     <row r="473">
@@ -26479,9 +27898,12 @@
         <v>0.0162</v>
       </c>
       <c r="P473" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="Q473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="Q473" s="1" t="n">
+      <c r="R473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -26534,9 +27956,12 @@
         <v>0.2067</v>
       </c>
       <c r="P474" s="1" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="Q474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="Q474" s="1" t="n">
+      <c r="R474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -26589,9 +28014,12 @@
         <v>0.0424</v>
       </c>
       <c r="P475" s="1" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="Q475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="Q475" s="1" t="n">
+      <c r="R475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -26644,9 +28072,12 @@
         <v>1.557</v>
       </c>
       <c r="P476" s="1" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="Q476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="Q476" s="1" t="n">
+      <c r="R476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -26699,9 +28130,12 @@
         <v>0.1005</v>
       </c>
       <c r="P477" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="Q477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="Q477" s="1" t="n">
+      <c r="R477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -26754,9 +28188,12 @@
         <v>0.001154</v>
       </c>
       <c r="P478" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="Q478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="Q478" s="1" t="n">
+      <c r="R478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -26809,10 +28246,13 @@
         <v>0.1435</v>
       </c>
       <c r="P479" s="1" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="Q479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="Q479" s="1" t="n">
-        <v>0.1435</v>
+      <c r="R479" s="1" t="n">
+        <v>0.1433</v>
       </c>
     </row>
     <row r="480">
@@ -26864,9 +28304,12 @@
         <v>0.001722</v>
       </c>
       <c r="P480" s="1" t="n">
+        <v>0.001726</v>
+      </c>
+      <c r="Q480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="Q480" s="1" t="n">
+      <c r="R480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -26919,10 +28362,13 @@
         <v>0.908</v>
       </c>
       <c r="P481" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="Q481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="Q481" s="1" t="n">
-        <v>0.908</v>
+      <c r="R481" s="1" t="n">
+        <v>0.905</v>
       </c>
     </row>
     <row r="482">
@@ -26974,10 +28420,13 @@
         <v>0.13303</v>
       </c>
       <c r="P482" s="1" t="n">
+        <v>0.13288</v>
+      </c>
+      <c r="Q482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="Q482" s="1" t="n">
-        <v>0.13303</v>
+      <c r="R482" s="1" t="n">
+        <v>0.13288</v>
       </c>
     </row>
     <row r="483">
@@ -27029,10 +28478,13 @@
         <v>0.04011</v>
       </c>
       <c r="P483" s="1" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="Q483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="Q483" s="1" t="n">
-        <v>0.04011</v>
+      <c r="R483" s="1" t="n">
+        <v>0.04005</v>
       </c>
     </row>
     <row r="484">
@@ -27084,10 +28536,13 @@
         <v>0.3014</v>
       </c>
       <c r="P484" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="Q484" s="1" t="n">
-        <v>0.3001</v>
+      <c r="R484" s="1" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="485">
@@ -27139,9 +28594,12 @@
         <v>0.05667</v>
       </c>
       <c r="P485" s="1" t="n">
+        <v>0.05657</v>
+      </c>
+      <c r="Q485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="Q485" s="1" t="n">
+      <c r="R485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -27194,9 +28652,12 @@
         <v>0.001559</v>
       </c>
       <c r="P486" s="1" t="n">
+        <v>0.001559</v>
+      </c>
+      <c r="Q486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="Q486" s="1" t="n">
+      <c r="R486" s="1" t="n">
         <v>0.001559</v>
       </c>
     </row>
@@ -27249,10 +28710,13 @@
         <v>0.06676</v>
       </c>
       <c r="P487" s="1" t="n">
+        <v>0.06665</v>
+      </c>
+      <c r="Q487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="Q487" s="1" t="n">
-        <v>0.06676</v>
+      <c r="R487" s="1" t="n">
+        <v>0.06665</v>
       </c>
     </row>
     <row r="488">
@@ -27304,10 +28768,13 @@
         <v>0.1913</v>
       </c>
       <c r="P488" s="1" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="Q488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="Q488" s="1" t="n">
-        <v>0.1913</v>
+      <c r="R488" s="1" t="n">
+        <v>0.1911</v>
       </c>
     </row>
     <row r="489">
@@ -27359,10 +28826,13 @@
         <v>0.04776</v>
       </c>
       <c r="P489" s="1" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="Q489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="Q489" s="1" t="n">
-        <v>0.04776</v>
+      <c r="R489" s="1" t="n">
+        <v>0.04768</v>
       </c>
     </row>
     <row r="490">
@@ -27414,9 +28884,12 @@
         <v>0.1394</v>
       </c>
       <c r="P490" s="1" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="Q490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="Q490" s="1" t="n">
+      <c r="R490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -27469,10 +28942,13 @@
         <v>0.02235</v>
       </c>
       <c r="P491" s="1" t="n">
+        <v>0.02227</v>
+      </c>
+      <c r="Q491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="Q491" s="1" t="n">
-        <v>0.02235</v>
+      <c r="R491" s="1" t="n">
+        <v>0.02227</v>
       </c>
     </row>
     <row r="492">
@@ -27524,10 +29000,13 @@
         <v>0.007735</v>
       </c>
       <c r="P492" s="1" t="n">
+        <v>0.007706</v>
+      </c>
+      <c r="Q492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="Q492" s="1" t="n">
-        <v>0.007735</v>
+      <c r="R492" s="1" t="n">
+        <v>0.007706</v>
       </c>
     </row>
     <row r="493">
@@ -27579,9 +29058,12 @@
         <v>0.0005919</v>
       </c>
       <c r="P493" s="1" t="n">
+        <v>0.0005919</v>
+      </c>
+      <c r="Q493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="Q493" s="1" t="n">
+      <c r="R493" s="1" t="n">
         <v>0.0005918</v>
       </c>
     </row>
@@ -27634,9 +29116,12 @@
         <v>3.027</v>
       </c>
       <c r="P494" s="1" t="n">
+        <v>3.014</v>
+      </c>
+      <c r="Q494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="Q494" s="1" t="n">
+      <c r="R494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -27689,9 +29174,12 @@
         <v>0.05064</v>
       </c>
       <c r="P495" s="1" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="Q495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="Q495" s="1" t="n">
+      <c r="R495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -27744,9 +29232,12 @@
         <v>0.0068</v>
       </c>
       <c r="P496" s="1" t="n">
+        <v>0.006806</v>
+      </c>
+      <c r="Q496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="Q496" s="1" t="n">
+      <c r="R496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -27799,9 +29290,12 @@
         <v>1.301</v>
       </c>
       <c r="P497" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="Q497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="Q497" s="1" t="n">
+      <c r="R497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -27854,9 +29348,12 @@
         <v>0.03926</v>
       </c>
       <c r="P498" s="1" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="Q498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="Q498" s="1" t="n">
+      <c r="R498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -27909,10 +29406,13 @@
         <v>0.04092</v>
       </c>
       <c r="P499" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="Q499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="Q499" s="1" t="n">
-        <v>0.04092</v>
+      <c r="R499" s="1" t="n">
+        <v>0.04085</v>
       </c>
     </row>
     <row r="500">
@@ -27964,9 +29464,12 @@
         <v>0.00546</v>
       </c>
       <c r="P500" s="1" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="Q500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="Q500" s="1" t="n">
+      <c r="R500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -28019,10 +29522,13 @@
         <v>0.03565</v>
       </c>
       <c r="P501" s="1" t="n">
+        <v>0.03552</v>
+      </c>
+      <c r="Q501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="Q501" s="1" t="n">
-        <v>0.03565</v>
+      <c r="R501" s="1" t="n">
+        <v>0.03552</v>
       </c>
     </row>
     <row r="502">
@@ -28074,10 +29580,13 @@
         <v>0.07209</v>
       </c>
       <c r="P502" s="1" t="n">
+        <v>0.07205</v>
+      </c>
+      <c r="Q502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="Q502" s="1" t="n">
-        <v>0.07209</v>
+      <c r="R502" s="1" t="n">
+        <v>0.07205</v>
       </c>
     </row>
     <row r="503">
@@ -28129,9 +29638,12 @@
         <v>0.0007418</v>
       </c>
       <c r="P503" s="1" t="n">
+        <v>0.000742</v>
+      </c>
+      <c r="Q503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="Q503" s="1" t="n">
+      <c r="R503" s="1" t="n">
         <v>0.0007412</v>
       </c>
     </row>
@@ -28184,9 +29696,12 @@
         <v>0.016034</v>
       </c>
       <c r="P504" s="1" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="Q504" s="1" t="n">
         <v>0.016034</v>
       </c>
-      <c r="Q504" s="1" t="n">
+      <c r="R504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -28239,10 +29754,13 @@
         <v>0.00703</v>
       </c>
       <c r="P505" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="Q505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="Q505" s="1" t="n">
-        <v>0.00703</v>
+      <c r="R505" s="1" t="n">
+        <v>0.00702</v>
       </c>
     </row>
     <row r="506">
@@ -28294,9 +29812,12 @@
         <v>0.0253</v>
       </c>
       <c r="P506" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="Q506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="Q506" s="1" t="n">
+      <c r="R506" s="1" t="n">
         <v>0.0253</v>
       </c>
     </row>
@@ -28349,9 +29870,12 @@
         <v>0.001348</v>
       </c>
       <c r="P507" s="1" t="n">
+        <v>0.001343</v>
+      </c>
+      <c r="Q507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="Q507" s="1" t="n">
+      <c r="R507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -28404,9 +29928,12 @@
         <v>0.281</v>
       </c>
       <c r="P508" s="1" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="Q508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="Q508" s="1" t="n">
+      <c r="R508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -28459,9 +29986,12 @@
         <v>0.1316</v>
       </c>
       <c r="P509" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="Q509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="Q509" s="1" t="n">
+      <c r="R509" s="1" t="n">
         <v>0.1314</v>
       </c>
     </row>
@@ -28514,10 +30044,13 @@
         <v>0.04897</v>
       </c>
       <c r="P510" s="1" t="n">
+        <v>0.04883</v>
+      </c>
+      <c r="Q510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="Q510" s="1" t="n">
-        <v>0.04896</v>
+      <c r="R510" s="1" t="n">
+        <v>0.04883</v>
       </c>
     </row>
     <row r="511">
@@ -28569,9 +30102,12 @@
         <v>0.00271</v>
       </c>
       <c r="P511" s="1" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="Q511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="Q511" s="1" t="n">
+      <c r="R511" s="1" t="n">
         <v>0.00271</v>
       </c>
     </row>
@@ -28624,10 +30160,13 @@
         <v>0.015066</v>
       </c>
       <c r="P512" s="1" t="n">
+        <v>0.014989</v>
+      </c>
+      <c r="Q512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="Q512" s="1" t="n">
-        <v>0.015017</v>
+      <c r="R512" s="1" t="n">
+        <v>0.014989</v>
       </c>
     </row>
     <row r="513">
@@ -28679,9 +30218,12 @@
         <v>0.6918</v>
       </c>
       <c r="P513" s="1" t="n">
+        <v>0.6906</v>
+      </c>
+      <c r="Q513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="Q513" s="1" t="n">
+      <c r="R513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -28734,10 +30276,13 @@
         <v>0.004508</v>
       </c>
       <c r="P514" s="1" t="n">
+        <v>0.004471</v>
+      </c>
+      <c r="Q514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="Q514" s="1" t="n">
-        <v>0.004508</v>
+      <c r="R514" s="1" t="n">
+        <v>0.004471</v>
       </c>
     </row>
     <row r="515">
@@ -28789,9 +30334,12 @@
         <v>0.005012</v>
       </c>
       <c r="P515" s="1" t="n">
+        <v>0.005016</v>
+      </c>
+      <c r="Q515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="Q515" s="1" t="n">
+      <c r="R515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -28844,9 +30392,12 @@
         <v>0.0633</v>
       </c>
       <c r="P516" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="Q516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="Q516" s="1" t="n">
+      <c r="R516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -28899,9 +30450,12 @@
         <v>0.06536</v>
       </c>
       <c r="P517" s="1" t="n">
+        <v>0.06515</v>
+      </c>
+      <c r="Q517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="Q517" s="1" t="n">
+      <c r="R517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -28954,10 +30508,13 @@
         <v>0.01201</v>
       </c>
       <c r="P518" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="Q518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="Q518" s="1" t="n">
-        <v>0.01199</v>
+      <c r="R518" s="1" t="n">
+        <v>0.01198</v>
       </c>
     </row>
     <row r="519">
@@ -29009,10 +30566,13 @@
         <v>0.04741</v>
       </c>
       <c r="P519" s="1" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="Q519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="Q519" s="1" t="n">
-        <v>0.04741</v>
+      <c r="R519" s="1" t="n">
+        <v>0.04733</v>
       </c>
     </row>
     <row r="520">
@@ -29064,9 +30624,12 @@
         <v>0.04362</v>
       </c>
       <c r="P520" s="1" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="Q520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="Q520" s="1" t="n">
+      <c r="R520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -29119,10 +30682,13 @@
         <v>0.008448000000000001</v>
       </c>
       <c r="P521" s="1" t="n">
+        <v>0.008402</v>
+      </c>
+      <c r="Q521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="Q521" s="1" t="n">
-        <v>0.008411999999999999</v>
+      <c r="R521" s="1" t="n">
+        <v>0.008402</v>
       </c>
     </row>
     <row r="522">
@@ -29174,10 +30740,13 @@
         <v>0.08801</v>
       </c>
       <c r="P522" s="1" t="n">
+        <v>0.08773</v>
+      </c>
+      <c r="Q522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="Q522" s="1" t="n">
-        <v>0.08787</v>
+      <c r="R522" s="1" t="n">
+        <v>0.08773</v>
       </c>
     </row>
     <row r="523">
@@ -29229,10 +30798,13 @@
         <v>0.006424</v>
       </c>
       <c r="P523" s="1" t="n">
+        <v>0.006407</v>
+      </c>
+      <c r="Q523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="Q523" s="1" t="n">
-        <v>0.006424</v>
+      <c r="R523" s="1" t="n">
+        <v>0.006407</v>
       </c>
     </row>
     <row r="524">
@@ -29284,10 +30856,13 @@
         <v>0.01637</v>
       </c>
       <c r="P524" s="1" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="Q524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="Q524" s="1" t="n">
-        <v>0.01635</v>
+      <c r="R524" s="1" t="n">
+        <v>0.01628</v>
       </c>
     </row>
     <row r="525">
@@ -29339,10 +30914,13 @@
         <v>0.01777</v>
       </c>
       <c r="P525" s="1" t="n">
+        <v>0.01772</v>
+      </c>
+      <c r="Q525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="Q525" s="1" t="n">
-        <v>0.01777</v>
+      <c r="R525" s="1" t="n">
+        <v>0.01772</v>
       </c>
     </row>
     <row r="526">
@@ -29394,10 +30972,13 @@
         <v>0.07865999999999999</v>
       </c>
       <c r="P526" s="1" t="n">
+        <v>0.07862</v>
+      </c>
+      <c r="Q526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="Q526" s="1" t="n">
-        <v>0.07865999999999999</v>
+      <c r="R526" s="1" t="n">
+        <v>0.07862</v>
       </c>
     </row>
     <row r="527">
@@ -29449,9 +31030,12 @@
         <v>0.01599</v>
       </c>
       <c r="P527" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="Q527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="Q527" s="1" t="n">
+      <c r="R527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -29504,10 +31088,13 @@
         <v>0.004175</v>
       </c>
       <c r="P528" s="1" t="n">
+        <v>0.004159</v>
+      </c>
+      <c r="Q528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="Q528" s="1" t="n">
-        <v>0.004164</v>
+      <c r="R528" s="1" t="n">
+        <v>0.004159</v>
       </c>
     </row>
     <row r="529">
@@ -29559,10 +31146,13 @@
         <v>0.0037</v>
       </c>
       <c r="P529" s="1" t="n">
+        <v>0.003672</v>
+      </c>
+      <c r="Q529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="Q529" s="1" t="n">
-        <v>0.00369</v>
+      <c r="R529" s="1" t="n">
+        <v>0.003672</v>
       </c>
     </row>
     <row r="530">
@@ -29614,9 +31204,12 @@
         <v>1.326</v>
       </c>
       <c r="P530" s="1" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="Q530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="Q530" s="1" t="n">
+      <c r="R530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -29669,10 +31262,13 @@
         <v>0.4885</v>
       </c>
       <c r="P531" s="1" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="Q531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="Q531" s="1" t="n">
-        <v>0.4882</v>
+      <c r="R531" s="1" t="n">
+        <v>0.487</v>
       </c>
     </row>
     <row r="532">
@@ -29724,9 +31320,12 @@
         <v>0.03062</v>
       </c>
       <c r="P532" s="1" t="n">
+        <v>0.03059</v>
+      </c>
+      <c r="Q532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="Q532" s="1" t="n">
+      <c r="R532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -29779,9 +31378,12 @@
         <v>0.1525</v>
       </c>
       <c r="P533" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="Q533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="Q533" s="1" t="n">
+      <c r="R533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -29834,9 +31436,12 @@
         <v>0.05344</v>
       </c>
       <c r="P534" s="1" t="n">
+        <v>0.05344</v>
+      </c>
+      <c r="Q534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="Q534" s="1" t="n">
+      <c r="R534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -29889,10 +31494,13 @@
         <v>0.01479</v>
       </c>
       <c r="P535" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="Q535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="Q535" s="1" t="n">
-        <v>0.01479</v>
+      <c r="R535" s="1" t="n">
+        <v>0.01476</v>
       </c>
     </row>
     <row r="536">
@@ -29944,9 +31552,12 @@
         <v>0.05866</v>
       </c>
       <c r="P536" s="1" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="Q536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="Q536" s="1" t="n">
+      <c r="R536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -29999,10 +31610,13 @@
         <v>0.0548</v>
       </c>
       <c r="P537" s="1" t="n">
+        <v>0.05476</v>
+      </c>
+      <c r="Q537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="Q537" s="1" t="n">
-        <v>0.0548</v>
+      <c r="R537" s="1" t="n">
+        <v>0.05476</v>
       </c>
     </row>
     <row r="538">
@@ -30054,10 +31668,13 @@
         <v>0.1059</v>
       </c>
       <c r="P538" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="Q538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="Q538" s="1" t="n">
-        <v>0.1058</v>
+      <c r="R538" s="1" t="n">
+        <v>0.1057</v>
       </c>
     </row>
     <row r="539">
@@ -30109,10 +31726,13 @@
         <v>0.01273</v>
       </c>
       <c r="P539" s="1" t="n">
+        <v>0.01266</v>
+      </c>
+      <c r="Q539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="Q539" s="1" t="n">
-        <v>0.01273</v>
+      <c r="R539" s="1" t="n">
+        <v>0.01266</v>
       </c>
     </row>
     <row r="540">
@@ -30164,10 +31784,13 @@
         <v>0.1728</v>
       </c>
       <c r="P540" s="1" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="Q540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="Q540" s="1" t="n">
-        <v>0.1728</v>
+      <c r="R540" s="1" t="n">
+        <v>0.1725</v>
       </c>
     </row>
     <row r="541">
@@ -30219,9 +31842,12 @@
         <v>0.1228</v>
       </c>
       <c r="P541" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="Q541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="Q541" s="1" t="n">
+      <c r="R541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -30274,9 +31900,12 @@
         <v>0.02478</v>
       </c>
       <c r="P542" s="1" t="n">
+        <v>0.02478</v>
+      </c>
+      <c r="Q542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="Q542" s="1" t="n">
+      <c r="R542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -30329,9 +31958,12 @@
         <v>0.0588</v>
       </c>
       <c r="P543" s="1" t="n">
+        <v>0.05858</v>
+      </c>
+      <c r="Q543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="Q543" s="1" t="n">
+      <c r="R543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R543"/>
+  <dimension ref="A1:S543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -435,8 +435,9 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,10 +523,15 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>price_03:45</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -583,9 +589,12 @@
         <v>71072</v>
       </c>
       <c r="Q2" s="1" t="n">
+        <v>71123.2</v>
+      </c>
+      <c r="R2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="S2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -641,9 +650,12 @@
         <v>2098.64</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>2102.99</v>
+      </c>
+      <c r="R3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="S3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -699,9 +711,12 @@
         <v>88.7</v>
       </c>
       <c r="Q4" s="1" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="R4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="S4" s="1" t="n">
         <v>88.7</v>
       </c>
     </row>
@@ -757,9 +772,12 @@
         <v>3.791</v>
       </c>
       <c r="Q5" s="1" t="n">
+        <v>3.849</v>
+      </c>
+      <c r="R5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="S5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -815,9 +833,12 @@
         <v>1.3993</v>
       </c>
       <c r="Q6" s="1" t="n">
+        <v>1.4009</v>
+      </c>
+      <c r="R6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="S6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -873,9 +894,12 @@
         <v>0.09572</v>
       </c>
       <c r="Q7" s="1" t="n">
+        <v>0.09592000000000001</v>
+      </c>
+      <c r="R7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -931,9 +955,12 @@
         <v>0.014297</v>
       </c>
       <c r="Q8" s="1" t="n">
+        <v>0.014506</v>
+      </c>
+      <c r="R8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="S8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -989,9 +1016,12 @@
         <v>656.9299999999999</v>
       </c>
       <c r="Q9" s="1" t="n">
+        <v>657.46</v>
+      </c>
+      <c r="R9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="S9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1047,9 +1077,12 @@
         <v>20.129</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>20.209</v>
+      </c>
+      <c r="R10" s="1" t="n">
         <v>20.288</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="S10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1105,9 +1138,12 @@
         <v>0.0033816</v>
       </c>
       <c r="Q11" s="1" t="n">
+        <v>0.0033857</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="S11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1163,9 +1199,12 @@
         <v>36.478</v>
       </c>
       <c r="Q12" s="1" t="n">
+        <v>36.576</v>
+      </c>
+      <c r="R12" s="1" t="n">
         <v>36.704</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="S12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1221,9 +1260,12 @@
         <v>213.23</v>
       </c>
       <c r="Q13" s="1" t="n">
+        <v>213.03</v>
+      </c>
+      <c r="R13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="S13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1279,9 +1321,12 @@
         <v>0.0011172</v>
       </c>
       <c r="Q14" s="1" t="n">
+        <v>0.0011178</v>
+      </c>
+      <c r="R14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="S14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1337,9 +1382,12 @@
         <v>0.30252</v>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>0.30332</v>
+        <v>0.31126</v>
       </c>
       <c r="R15" s="1" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1395,10 +1443,13 @@
         <v>231.16</v>
       </c>
       <c r="Q16" s="1" t="n">
+        <v>230.07</v>
+      </c>
+      <c r="R16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="R16" s="1" t="n">
-        <v>230.3</v>
+      <c r="S16" s="1" t="n">
+        <v>230.07</v>
       </c>
     </row>
     <row r="17">
@@ -1453,9 +1504,12 @@
         <v>0.9996</v>
       </c>
       <c r="Q17" s="1" t="n">
+        <v>1.0003</v>
+      </c>
+      <c r="R17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="S17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1511,9 +1565,12 @@
         <v>0.2669</v>
       </c>
       <c r="Q18" s="1" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="R18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="S18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1569,9 +1626,12 @@
         <v>9.747999999999999</v>
       </c>
       <c r="Q19" s="1" t="n">
+        <v>9.765000000000001</v>
+      </c>
+      <c r="R19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="S19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -1627,10 +1687,13 @@
         <v>5037.16</v>
       </c>
       <c r="Q20" s="1" t="n">
+        <v>5026.79</v>
+      </c>
+      <c r="R20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="R20" s="1" t="n">
-        <v>5033.31</v>
+      <c r="S20" s="1" t="n">
+        <v>5026.79</v>
       </c>
     </row>
     <row r="21">
@@ -1685,9 +1748,12 @@
         <v>463.16</v>
       </c>
       <c r="Q21" s="1" t="n">
+        <v>463.2</v>
+      </c>
+      <c r="R21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="S21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1743,9 +1809,12 @@
         <v>1.3787</v>
       </c>
       <c r="Q22" s="1" t="n">
+        <v>1.3836</v>
+      </c>
+      <c r="R22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="S22" s="1" t="n">
         <v>1.3736</v>
       </c>
     </row>
@@ -1801,9 +1870,12 @@
         <v>1.0591</v>
       </c>
       <c r="Q23" s="1" t="n">
+        <v>1.0617</v>
+      </c>
+      <c r="R23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="S23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -1859,9 +1931,12 @@
         <v>1.343</v>
       </c>
       <c r="Q24" s="1" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="S24" s="1" t="n">
         <v>1.343</v>
       </c>
     </row>
@@ -1917,9 +1992,12 @@
         <v>9.113</v>
       </c>
       <c r="Q25" s="1" t="n">
+        <v>9.125999999999999</v>
+      </c>
+      <c r="R25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="S25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -1975,9 +2053,12 @@
         <v>0.3689</v>
       </c>
       <c r="Q26" s="1" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="R26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="R26" s="1" t="n">
+      <c r="S26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -2033,9 +2114,12 @@
         <v>0.874</v>
       </c>
       <c r="Q27" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="R27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="S27" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -2091,9 +2175,12 @@
         <v>1.833</v>
       </c>
       <c r="Q28" s="1" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="R28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="S28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2149,9 +2236,12 @@
         <v>0.1089</v>
       </c>
       <c r="Q29" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="R29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="R29" s="1" t="n">
+      <c r="S29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -2207,9 +2297,12 @@
         <v>0.002011</v>
       </c>
       <c r="Q30" s="1" t="n">
+        <v>0.002015</v>
+      </c>
+      <c r="R30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="R30" s="1" t="n">
+      <c r="S30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -2265,10 +2358,13 @@
         <v>1.467</v>
       </c>
       <c r="Q31" s="1" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="R31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="R31" s="1" t="n">
-        <v>1.467</v>
+      <c r="S31" s="1" t="n">
+        <v>1.466</v>
       </c>
     </row>
     <row r="32">
@@ -2323,9 +2419,12 @@
         <v>0.1769</v>
       </c>
       <c r="Q32" s="1" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="R32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="R32" s="1" t="n">
+      <c r="S32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2381,9 +2480,12 @@
         <v>0.1035</v>
       </c>
       <c r="Q33" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="R33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="R33" s="1" t="n">
+      <c r="S33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -2439,9 +2541,12 @@
         <v>112.49</v>
       </c>
       <c r="Q34" s="1" t="n">
+        <v>112.67</v>
+      </c>
+      <c r="R34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="R34" s="1" t="n">
+      <c r="S34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -2497,9 +2602,12 @@
         <v>6.619</v>
       </c>
       <c r="Q35" s="1" t="n">
+        <v>6.683</v>
+      </c>
+      <c r="R35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="R35" s="1" t="n">
+      <c r="S35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2555,9 +2663,12 @@
         <v>0.017656</v>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>0.017656</v>
+        <v>0.017668</v>
       </c>
       <c r="R36" s="1" t="n">
+        <v>0.017668</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2613,9 +2724,12 @@
         <v>0.3595</v>
       </c>
       <c r="Q37" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="R37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="R37" s="1" t="n">
+      <c r="S37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -2671,9 +2785,12 @@
         <v>55.35</v>
       </c>
       <c r="Q38" s="1" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="R38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="R38" s="1" t="n">
+      <c r="S38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2729,9 +2846,12 @@
         <v>0.6167899999999999</v>
       </c>
       <c r="Q39" s="1" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="R39" s="1" t="n">
         <v>0.61761</v>
       </c>
-      <c r="R39" s="1" t="n">
+      <c r="S39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2787,9 +2907,12 @@
         <v>4.017</v>
       </c>
       <c r="Q40" s="1" t="n">
+        <v>4.028</v>
+      </c>
+      <c r="R40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="R40" s="1" t="n">
+      <c r="S40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -2845,9 +2968,12 @@
         <v>0.04981</v>
       </c>
       <c r="Q41" s="1" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="R41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="R41" s="1" t="n">
+      <c r="S41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2903,10 +3029,13 @@
         <v>0.701</v>
       </c>
       <c r="Q42" s="1" t="n">
+        <v>0.7000999999999999</v>
+      </c>
+      <c r="R42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="R42" s="1" t="n">
-        <v>0.7006</v>
+      <c r="S42" s="1" t="n">
+        <v>0.7000999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2961,10 +3090,13 @@
         <v>0.22785</v>
       </c>
       <c r="Q43" s="1" t="n">
+        <v>0.22771</v>
+      </c>
+      <c r="R43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="R43" s="1" t="n">
-        <v>0.22785</v>
+      <c r="S43" s="1" t="n">
+        <v>0.22771</v>
       </c>
     </row>
     <row r="44">
@@ -3019,9 +3151,12 @@
         <v>0.35629</v>
       </c>
       <c r="Q44" s="1" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="R44" s="1" t="n">
         <v>0.3581</v>
       </c>
-      <c r="R44" s="1" t="n">
+      <c r="S44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -3077,10 +3212,13 @@
         <v>0.1687</v>
       </c>
       <c r="Q45" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="R45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="R45" s="1" t="n">
-        <v>0.1687</v>
+      <c r="S45" s="1" t="n">
+        <v>0.1682</v>
       </c>
     </row>
     <row r="46">
@@ -3135,9 +3273,12 @@
         <v>0.0264</v>
       </c>
       <c r="Q46" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="R46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="R46" s="1" t="n">
+      <c r="S46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -3193,9 +3334,12 @@
         <v>0.00594</v>
       </c>
       <c r="Q47" s="1" t="n">
+        <v>0.005945</v>
+      </c>
+      <c r="R47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="R47" s="1" t="n">
+      <c r="S47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -3251,9 +3395,12 @@
         <v>0.007343</v>
       </c>
       <c r="Q48" s="1" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="R48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="R48" s="1" t="n">
+      <c r="S48" s="1" t="n">
         <v>0.007343</v>
       </c>
     </row>
@@ -3309,9 +3456,12 @@
         <v>0.1088</v>
       </c>
       <c r="Q49" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="R49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="R49" s="1" t="n">
+      <c r="S49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3367,9 +3517,12 @@
         <v>0.04183</v>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>0.04183</v>
+        <v>0.0421</v>
       </c>
       <c r="R50" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="S50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -3425,9 +3578,12 @@
         <v>0.1614</v>
       </c>
       <c r="Q51" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="R51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="R51" s="1" t="n">
+      <c r="S51" s="1" t="n">
         <v>0.1614</v>
       </c>
     </row>
@@ -3483,9 +3639,12 @@
         <v>0.0035</v>
       </c>
       <c r="Q52" s="1" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="R52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="R52" s="1" t="n">
+      <c r="S52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -3541,10 +3700,13 @@
         <v>2.619</v>
       </c>
       <c r="Q53" s="1" t="n">
+        <v>2.613</v>
+      </c>
+      <c r="R53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="R53" s="1" t="n">
-        <v>2.619</v>
+      <c r="S53" s="1" t="n">
+        <v>2.613</v>
       </c>
     </row>
     <row r="54">
@@ -3599,9 +3761,12 @@
         <v>0.006157</v>
       </c>
       <c r="Q54" s="1" t="n">
+        <v>0.006174</v>
+      </c>
+      <c r="R54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="R54" s="1" t="n">
+      <c r="S54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -3657,9 +3822,12 @@
         <v>0.029</v>
       </c>
       <c r="Q55" s="1" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="R55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="R55" s="1" t="n">
+      <c r="S55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -3715,9 +3883,12 @@
         <v>0.7322</v>
       </c>
       <c r="Q56" s="1" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="R56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="R56" s="1" t="n">
+      <c r="S56" s="1" t="n">
         <v>0.7322</v>
       </c>
     </row>
@@ -3773,9 +3944,12 @@
         <v>0.103</v>
       </c>
       <c r="Q57" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="R57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="R57" s="1" t="n">
+      <c r="S57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -3831,9 +4005,12 @@
         <v>0.9365</v>
       </c>
       <c r="Q58" s="1" t="n">
+        <v>0.9372</v>
+      </c>
+      <c r="R58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="R58" s="1" t="n">
+      <c r="S58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -3889,9 +4066,12 @@
         <v>0.08717</v>
       </c>
       <c r="Q59" s="1" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="R59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="R59" s="1" t="n">
+      <c r="S59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -3947,9 +4127,12 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="Q60" s="1" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="R60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="R60" s="1" t="n">
+      <c r="S60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -4005,9 +4188,12 @@
         <v>0.0544</v>
       </c>
       <c r="Q61" s="1" t="n">
+        <v>0.05453</v>
+      </c>
+      <c r="R61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="R61" s="1" t="n">
+      <c r="S61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -4063,9 +4249,12 @@
         <v>0.01036</v>
       </c>
       <c r="Q62" s="1" t="n">
+        <v>0.01035</v>
+      </c>
+      <c r="R62" s="1" t="n">
         <v>0.01036</v>
       </c>
-      <c r="R62" s="1" t="n">
+      <c r="S62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -4121,9 +4310,12 @@
         <v>0.29126</v>
       </c>
       <c r="Q63" s="1" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="R63" s="1" t="n">
         <v>0.29156</v>
       </c>
-      <c r="R63" s="1" t="n">
+      <c r="S63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -4179,9 +4371,12 @@
         <v>0.07346</v>
       </c>
       <c r="Q64" s="1" t="n">
+        <v>0.07475999999999999</v>
+      </c>
+      <c r="R64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="R64" s="1" t="n">
+      <c r="S64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -4237,9 +4432,12 @@
         <v>0.3172</v>
       </c>
       <c r="Q65" s="1" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="R65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="R65" s="1" t="n">
+      <c r="S65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -4295,9 +4493,12 @@
         <v>0.16242</v>
       </c>
       <c r="Q66" s="1" t="n">
+        <v>0.16238</v>
+      </c>
+      <c r="R66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="R66" s="1" t="n">
+      <c r="S66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -4353,9 +4554,12 @@
         <v>0.11998</v>
       </c>
       <c r="Q67" s="1" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="R67" s="1" t="n">
         <v>0.12014</v>
       </c>
-      <c r="R67" s="1" t="n">
+      <c r="S67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -4411,10 +4615,13 @@
         <v>0.09494</v>
       </c>
       <c r="Q68" s="1" t="n">
+        <v>0.09487</v>
+      </c>
+      <c r="R68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="R68" s="1" t="n">
-        <v>0.09494</v>
+      <c r="S68" s="1" t="n">
+        <v>0.09487</v>
       </c>
     </row>
     <row r="69">
@@ -4469,9 +4676,12 @@
         <v>0.1239</v>
       </c>
       <c r="Q69" s="1" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="R69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="R69" s="1" t="n">
+      <c r="S69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -4527,9 +4737,12 @@
         <v>8.491</v>
       </c>
       <c r="Q70" s="1" t="n">
+        <v>8.499000000000001</v>
+      </c>
+      <c r="R70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="R70" s="1" t="n">
+      <c r="S70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -4585,9 +4798,12 @@
         <v>0.239</v>
       </c>
       <c r="Q71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="R71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="R71" s="1" t="n">
+      <c r="S71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -4643,10 +4859,13 @@
         <v>0.04996</v>
       </c>
       <c r="Q72" s="1" t="n">
+        <v>0.04983</v>
+      </c>
+      <c r="R72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="R72" s="1" t="n">
-        <v>0.04992</v>
+      <c r="S72" s="1" t="n">
+        <v>0.04983</v>
       </c>
     </row>
     <row r="73">
@@ -4701,9 +4920,12 @@
         <v>0.05042</v>
       </c>
       <c r="Q73" s="1" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="R73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="R73" s="1" t="n">
+      <c r="S73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -4759,9 +4981,12 @@
         <v>0.125</v>
       </c>
       <c r="Q74" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="R74" s="1" t="n">
+      <c r="S74" s="1" t="n">
         <v>0.1246</v>
       </c>
     </row>
@@ -4817,9 +5042,12 @@
         <v>0.04642</v>
       </c>
       <c r="Q75" s="1" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="R75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="R75" s="1" t="n">
+      <c r="S75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -4875,9 +5103,12 @@
         <v>0.06697</v>
       </c>
       <c r="Q76" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="R76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="R76" s="1" t="n">
+      <c r="S76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -4933,9 +5164,12 @@
         <v>0.12842</v>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>0.12881</v>
+        <v>0.12959</v>
       </c>
       <c r="R77" s="1" t="n">
+        <v>0.12959</v>
+      </c>
+      <c r="S77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -4991,10 +5225,13 @@
         <v>0.1608</v>
       </c>
       <c r="Q78" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="R78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="R78" s="1" t="n">
-        <v>0.1608</v>
+      <c r="S78" s="1" t="n">
+        <v>0.1607</v>
       </c>
     </row>
     <row r="79">
@@ -5049,9 +5286,12 @@
         <v>0.02693</v>
       </c>
       <c r="Q79" s="1" t="n">
+        <v>0.02694</v>
+      </c>
+      <c r="R79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="R79" s="1" t="n">
+      <c r="S79" s="1" t="n">
         <v>0.02693</v>
       </c>
     </row>
@@ -5107,9 +5347,12 @@
         <v>358.23</v>
       </c>
       <c r="Q80" s="1" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="R80" s="1" t="n">
         <v>358.62</v>
       </c>
-      <c r="R80" s="1" t="n">
+      <c r="S80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -5165,9 +5408,12 @@
         <v>7.029000000000001e-05</v>
       </c>
       <c r="Q81" s="1" t="n">
+        <v>7.04e-05</v>
+      </c>
+      <c r="R81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="R81" s="1" t="n">
+      <c r="S81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -5223,9 +5469,12 @@
         <v>0.2649</v>
       </c>
       <c r="Q82" s="1" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="R82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="R82" s="1" t="n">
+      <c r="S82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -5281,10 +5530,13 @@
         <v>1.1167</v>
       </c>
       <c r="Q83" s="1" t="n">
+        <v>1.1054</v>
+      </c>
+      <c r="R83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="R83" s="1" t="n">
-        <v>1.1167</v>
+      <c r="S83" s="1" t="n">
+        <v>1.1054</v>
       </c>
     </row>
     <row r="84">
@@ -5339,9 +5591,12 @@
         <v>0.3496</v>
       </c>
       <c r="Q84" s="1" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="R84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="R84" s="1" t="n">
+      <c r="S84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -5397,10 +5652,13 @@
         <v>1.986</v>
       </c>
       <c r="Q85" s="1" t="n">
+        <v>1.9784</v>
+      </c>
+      <c r="R85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="R85" s="1" t="n">
-        <v>1.986</v>
+      <c r="S85" s="1" t="n">
+        <v>1.9784</v>
       </c>
     </row>
     <row r="86">
@@ -5455,9 +5713,12 @@
         <v>1.3195</v>
       </c>
       <c r="Q86" s="1" t="n">
+        <v>1.3184</v>
+      </c>
+      <c r="R86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="R86" s="1" t="n">
+      <c r="S86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -5513,10 +5774,13 @@
         <v>32.55</v>
       </c>
       <c r="Q87" s="1" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="R87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="R87" s="1" t="n">
-        <v>32.55</v>
+      <c r="S87" s="1" t="n">
+        <v>32.52</v>
       </c>
     </row>
     <row r="88">
@@ -5571,9 +5835,12 @@
         <v>0.009429999999999999</v>
       </c>
       <c r="Q88" s="1" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="R88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="R88" s="1" t="n">
+      <c r="S88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -5629,10 +5896,13 @@
         <v>0.01807</v>
       </c>
       <c r="Q89" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="R89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="R89" s="1" t="n">
-        <v>0.01807</v>
+      <c r="S89" s="1" t="n">
+        <v>0.01805</v>
       </c>
     </row>
     <row r="90">
@@ -5687,10 +5957,13 @@
         <v>0.03485</v>
       </c>
       <c r="Q90" s="1" t="n">
+        <v>0.03477</v>
+      </c>
+      <c r="R90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="R90" s="1" t="n">
-        <v>0.03479</v>
+      <c r="S90" s="1" t="n">
+        <v>0.03477</v>
       </c>
     </row>
     <row r="91">
@@ -5745,9 +6018,12 @@
         <v>0.01185</v>
       </c>
       <c r="Q91" s="1" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="R91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="R91" s="1" t="n">
+      <c r="S91" s="1" t="n">
         <v>0.01179</v>
       </c>
     </row>
@@ -5803,9 +6079,12 @@
         <v>3.091</v>
       </c>
       <c r="Q92" s="1" t="n">
+        <v>3.094</v>
+      </c>
+      <c r="R92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="R92" s="1" t="n">
+      <c r="S92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -5861,10 +6140,13 @@
         <v>0.005572</v>
       </c>
       <c r="Q93" s="1" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="R93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="R93" s="1" t="n">
-        <v>0.005572</v>
+      <c r="S93" s="1" t="n">
+        <v>0.00557</v>
       </c>
     </row>
     <row r="94">
@@ -5919,9 +6201,12 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="Q94" s="1" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="R94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="R94" s="1" t="n">
+      <c r="S94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -5977,9 +6262,12 @@
         <v>0.6052999999999999</v>
       </c>
       <c r="Q95" s="1" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="R95" s="1" t="n">
         <v>0.6098</v>
       </c>
-      <c r="R95" s="1" t="n">
+      <c r="S95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -6035,9 +6323,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="Q96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="R96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="R96" s="1" t="n">
+      <c r="S96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -6093,9 +6384,12 @@
         <v>1.104</v>
       </c>
       <c r="Q97" s="1" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="R97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="R97" s="1" t="n">
+      <c r="S97" s="1" t="n">
         <v>1.103</v>
       </c>
     </row>
@@ -6151,9 +6445,12 @@
         <v>0.25635</v>
       </c>
       <c r="Q98" s="1" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="R98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="R98" s="1" t="n">
+      <c r="S98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -6209,9 +6506,12 @@
         <v>1.14</v>
       </c>
       <c r="Q99" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="R99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="R99" s="1" t="n">
+      <c r="S99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -6267,9 +6567,12 @@
         <v>1.852</v>
       </c>
       <c r="Q100" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="R100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="R100" s="1" t="n">
+      <c r="S100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -6325,9 +6628,12 @@
         <v>0.01576</v>
       </c>
       <c r="Q101" s="1" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="R101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="R101" s="1" t="n">
+      <c r="S101" s="1" t="n">
         <v>0.01575</v>
       </c>
     </row>
@@ -6383,10 +6689,13 @@
         <v>0.10187</v>
       </c>
       <c r="Q102" s="1" t="n">
+        <v>0.10155</v>
+      </c>
+      <c r="R102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="R102" s="1" t="n">
-        <v>0.10187</v>
+      <c r="S102" s="1" t="n">
+        <v>0.10155</v>
       </c>
     </row>
     <row r="103">
@@ -6441,9 +6750,12 @@
         <v>0.0005941</v>
       </c>
       <c r="Q103" s="1" t="n">
+        <v>0.0005953</v>
+      </c>
+      <c r="R103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="R103" s="1" t="n">
+      <c r="S103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -6499,9 +6811,12 @@
         <v>0.0005885</v>
       </c>
       <c r="Q104" s="1" t="n">
+        <v>0.0005876</v>
+      </c>
+      <c r="R104" s="1" t="n">
         <v>0.0005917</v>
       </c>
-      <c r="R104" s="1" t="n">
+      <c r="S104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -6557,9 +6872,12 @@
         <v>0.003257</v>
       </c>
       <c r="Q105" s="1" t="n">
+        <v>0.003229</v>
+      </c>
+      <c r="R105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="R105" s="1" t="n">
+      <c r="S105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -6615,9 +6933,12 @@
         <v>2.572</v>
       </c>
       <c r="Q106" s="1" t="n">
+        <v>2.573</v>
+      </c>
+      <c r="R106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="R106" s="1" t="n">
+      <c r="S106" s="1" t="n">
         <v>2.572</v>
       </c>
     </row>
@@ -6673,9 +6994,12 @@
         <v>0.1651</v>
       </c>
       <c r="Q107" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="R107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="R107" s="1" t="n">
+      <c r="S107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -6731,9 +7055,12 @@
         <v>0.09633</v>
       </c>
       <c r="Q108" s="1" t="n">
+        <v>0.09629</v>
+      </c>
+      <c r="R108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="R108" s="1" t="n">
+      <c r="S108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -6789,9 +7116,12 @@
         <v>0.02202</v>
       </c>
       <c r="Q109" s="1" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="R109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="R109" s="1" t="n">
+      <c r="S109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -6847,9 +7177,12 @@
         <v>0.2894</v>
       </c>
       <c r="Q110" s="1" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="R110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="R110" s="1" t="n">
+      <c r="S110" s="1" t="n">
         <v>0.2894</v>
       </c>
     </row>
@@ -6905,9 +7238,12 @@
         <v>0.05651</v>
       </c>
       <c r="Q111" s="1" t="n">
+        <v>0.05665</v>
+      </c>
+      <c r="R111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="R111" s="1" t="n">
+      <c r="S111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -6963,9 +7299,12 @@
         <v>0.3005</v>
       </c>
       <c r="Q112" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="R112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="R112" s="1" t="n">
+      <c r="S112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -7021,9 +7360,12 @@
         <v>18.53</v>
       </c>
       <c r="Q113" s="1" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="R113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="R113" s="1" t="n">
+      <c r="S113" s="1" t="n">
         <v>18.53</v>
       </c>
     </row>
@@ -7079,9 +7421,12 @@
         <v>0.12566</v>
       </c>
       <c r="Q114" s="1" t="n">
+        <v>0.12686</v>
+      </c>
+      <c r="R114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="R114" s="1" t="n">
+      <c r="S114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -7137,9 +7482,12 @@
         <v>0.01634</v>
       </c>
       <c r="Q115" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="R115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="R115" s="1" t="n">
+      <c r="S115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -7195,9 +7543,12 @@
         <v>0.08442</v>
       </c>
       <c r="Q116" s="1" t="n">
+        <v>0.08445999999999999</v>
+      </c>
+      <c r="R116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="R116" s="1" t="n">
+      <c r="S116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -7253,9 +7604,12 @@
         <v>0.046846</v>
       </c>
       <c r="Q117" s="1" t="n">
+        <v>0.046928</v>
+      </c>
+      <c r="R117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="R117" s="1" t="n">
+      <c r="S117" s="1" t="n">
         <v>0.046846</v>
       </c>
     </row>
@@ -7311,9 +7665,12 @@
         <v>0.04701</v>
       </c>
       <c r="Q118" s="1" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="R118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="R118" s="1" t="n">
+      <c r="S118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -7369,9 +7726,12 @@
         <v>0.0404</v>
       </c>
       <c r="Q119" s="1" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="R119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="R119" s="1" t="n">
+      <c r="S119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -7427,9 +7787,12 @@
         <v>0.14473</v>
       </c>
       <c r="Q120" s="1" t="n">
+        <v>0.14441</v>
+      </c>
+      <c r="R120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="R120" s="1" t="n">
+      <c r="S120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -7485,10 +7848,13 @@
         <v>0.1264</v>
       </c>
       <c r="Q121" s="1" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="R121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="R121" s="1" t="n">
-        <v>0.1264</v>
+      <c r="S121" s="1" t="n">
+        <v>0.1252</v>
       </c>
     </row>
     <row r="122">
@@ -7543,9 +7909,12 @@
         <v>1.851</v>
       </c>
       <c r="Q122" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="R122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="R122" s="1" t="n">
+      <c r="S122" s="1" t="n">
         <v>1.851</v>
       </c>
     </row>
@@ -7601,9 +7970,12 @@
         <v>0.03001</v>
       </c>
       <c r="Q123" s="1" t="n">
+        <v>0.03006</v>
+      </c>
+      <c r="R123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="R123" s="1" t="n">
+      <c r="S123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -7659,9 +8031,12 @@
         <v>0.13252</v>
       </c>
       <c r="Q124" s="1" t="n">
+        <v>0.13267</v>
+      </c>
+      <c r="R124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="R124" s="1" t="n">
+      <c r="S124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -7717,9 +8092,12 @@
         <v>0.0408</v>
       </c>
       <c r="Q125" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="R125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="R125" s="1" t="n">
+      <c r="S125" s="1" t="n">
         <v>0.0408</v>
       </c>
     </row>
@@ -7775,9 +8153,12 @@
         <v>0.1141</v>
       </c>
       <c r="Q126" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="R126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="R126" s="1" t="n">
+      <c r="S126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -7833,9 +8214,12 @@
         <v>0.5214</v>
       </c>
       <c r="Q127" s="1" t="n">
-        <v>0.5214</v>
+        <v>0.5216</v>
       </c>
       <c r="R127" s="1" t="n">
+        <v>0.5216</v>
+      </c>
+      <c r="S127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -7891,9 +8275,12 @@
         <v>0.03781</v>
       </c>
       <c r="Q128" s="1" t="n">
+        <v>0.03794</v>
+      </c>
+      <c r="R128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="R128" s="1" t="n">
+      <c r="S128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -7949,9 +8336,12 @@
         <v>0.793</v>
       </c>
       <c r="Q129" s="1" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="R129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="R129" s="1" t="n">
+      <c r="S129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -8007,9 +8397,12 @@
         <v>0.03434</v>
       </c>
       <c r="Q130" s="1" t="n">
+        <v>0.03444</v>
+      </c>
+      <c r="R130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="R130" s="1" t="n">
+      <c r="S130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -8065,9 +8458,12 @@
         <v>0.4259</v>
       </c>
       <c r="Q131" s="1" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="R131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="R131" s="1" t="n">
+      <c r="S131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -8123,9 +8519,12 @@
         <v>0.04329</v>
       </c>
       <c r="Q132" s="1" t="n">
+        <v>0.04326</v>
+      </c>
+      <c r="R132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="R132" s="1" t="n">
+      <c r="S132" s="1" t="n">
         <v>0.04309</v>
       </c>
     </row>
@@ -8181,9 +8580,12 @@
         <v>1.2805</v>
       </c>
       <c r="Q133" s="1" t="n">
+        <v>1.2814</v>
+      </c>
+      <c r="R133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="R133" s="1" t="n">
+      <c r="S133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -8239,9 +8641,12 @@
         <v>0.02178</v>
       </c>
       <c r="Q134" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="R134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="R134" s="1" t="n">
+      <c r="S134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -8297,9 +8702,12 @@
         <v>0.0004561</v>
       </c>
       <c r="Q135" s="1" t="n">
+        <v>0.000457</v>
+      </c>
+      <c r="R135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="R135" s="1" t="n">
+      <c r="S135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -8355,9 +8763,12 @@
         <v>0.001904</v>
       </c>
       <c r="Q136" s="1" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="R136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="R136" s="1" t="n">
+      <c r="S136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -8413,9 +8824,12 @@
         <v>0.3136</v>
       </c>
       <c r="Q137" s="1" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="R137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="R137" s="1" t="n">
+      <c r="S137" s="1" t="n">
         <v>0.3136</v>
       </c>
     </row>
@@ -8471,10 +8885,13 @@
         <v>0.5633</v>
       </c>
       <c r="Q138" s="1" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="R138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="R138" s="1" t="n">
-        <v>0.5633</v>
+      <c r="S138" s="1" t="n">
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -8529,9 +8946,12 @@
         <v>0.02123</v>
       </c>
       <c r="Q139" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="R139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="R139" s="1" t="n">
+      <c r="S139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -8587,9 +9007,12 @@
         <v>0.07979</v>
       </c>
       <c r="Q140" s="1" t="n">
+        <v>0.07986</v>
+      </c>
+      <c r="R140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="R140" s="1" t="n">
+      <c r="S140" s="1" t="n">
         <v>0.07979</v>
       </c>
     </row>
@@ -8645,9 +9068,12 @@
         <v>0.001526</v>
       </c>
       <c r="Q141" s="1" t="n">
+        <v>0.001505</v>
+      </c>
+      <c r="R141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="R141" s="1" t="n">
+      <c r="S141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -8703,9 +9129,12 @@
         <v>0.446</v>
       </c>
       <c r="Q142" s="1" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="R142" s="1" t="n">
         <v>0.4489</v>
       </c>
-      <c r="R142" s="1" t="n">
+      <c r="S142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -8761,9 +9190,12 @@
         <v>0.029913</v>
       </c>
       <c r="Q143" s="1" t="n">
+        <v>0.030027</v>
+      </c>
+      <c r="R143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="R143" s="1" t="n">
+      <c r="S143" s="1" t="n">
         <v>0.029913</v>
       </c>
     </row>
@@ -8819,9 +9251,12 @@
         <v>0.000226</v>
       </c>
       <c r="Q144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="R144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="R144" s="1" t="n">
+      <c r="S144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -8877,9 +9312,12 @@
         <v>0.0355</v>
       </c>
       <c r="Q145" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="R145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="R145" s="1" t="n">
+      <c r="S145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -8935,9 +9373,12 @@
         <v>0.11649</v>
       </c>
       <c r="Q146" s="1" t="n">
+        <v>0.11645</v>
+      </c>
+      <c r="R146" s="1" t="n">
         <v>0.11649</v>
       </c>
-      <c r="R146" s="1" t="n">
+      <c r="S146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -8993,9 +9434,12 @@
         <v>0.02218</v>
       </c>
       <c r="Q147" s="1" t="n">
-        <v>0.02218</v>
+        <v>0.02231</v>
       </c>
       <c r="R147" s="1" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="S147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -9051,9 +9495,12 @@
         <v>1.4093</v>
       </c>
       <c r="Q148" s="1" t="n">
+        <v>1.4116</v>
+      </c>
+      <c r="R148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="R148" s="1" t="n">
+      <c r="S148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -9109,9 +9556,12 @@
         <v>1.8688</v>
       </c>
       <c r="Q149" s="1" t="n">
+        <v>1.8688</v>
+      </c>
+      <c r="R149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="R149" s="1" t="n">
+      <c r="S149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -9167,9 +9617,12 @@
         <v>0.096</v>
       </c>
       <c r="Q150" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="R150" s="1" t="n">
+      <c r="S150" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -9225,9 +9678,12 @@
         <v>4.647</v>
       </c>
       <c r="Q151" s="1" t="n">
+        <v>4.632</v>
+      </c>
+      <c r="R151" s="1" t="n">
         <v>4.647</v>
       </c>
-      <c r="R151" s="1" t="n">
+      <c r="S151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -9283,10 +9739,13 @@
         <v>5.515</v>
       </c>
       <c r="Q152" s="1" t="n">
+        <v>5.511</v>
+      </c>
+      <c r="R152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="R152" s="1" t="n">
-        <v>5.515</v>
+      <c r="S152" s="1" t="n">
+        <v>5.511</v>
       </c>
     </row>
     <row r="153">
@@ -9341,9 +9800,12 @@
         <v>0.3163</v>
       </c>
       <c r="Q153" s="1" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="R153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="R153" s="1" t="n">
+      <c r="S153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -9399,10 +9861,13 @@
         <v>0.5826</v>
       </c>
       <c r="Q154" s="1" t="n">
+        <v>0.5825</v>
+      </c>
+      <c r="R154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="R154" s="1" t="n">
-        <v>0.5826</v>
+      <c r="S154" s="1" t="n">
+        <v>0.5825</v>
       </c>
     </row>
     <row r="155">
@@ -9457,9 +9922,12 @@
         <v>0.01275</v>
       </c>
       <c r="Q155" s="1" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="R155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="R155" s="1" t="n">
+      <c r="S155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -9515,10 +9983,13 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="Q156" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="R156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="R156" s="1" t="n">
-        <v>0.09760000000000001</v>
+      <c r="S156" s="1" t="n">
+        <v>0.0974</v>
       </c>
     </row>
     <row r="157">
@@ -9573,9 +10044,12 @@
         <v>16.341</v>
       </c>
       <c r="Q157" s="1" t="n">
+        <v>16.372</v>
+      </c>
+      <c r="R157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="R157" s="1" t="n">
+      <c r="S157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -9631,9 +10105,12 @@
         <v>0.05526</v>
       </c>
       <c r="Q158" s="1" t="n">
+        <v>0.05538</v>
+      </c>
+      <c r="R158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="R158" s="1" t="n">
+      <c r="S158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -9689,10 +10166,13 @@
         <v>28.71</v>
       </c>
       <c r="Q159" s="1" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="R159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="R159" s="1" t="n">
-        <v>28.71</v>
+      <c r="S159" s="1" t="n">
+        <v>28.65</v>
       </c>
     </row>
     <row r="160">
@@ -9747,9 +10227,12 @@
         <v>0.02088</v>
       </c>
       <c r="Q160" s="1" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="R160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="R160" s="1" t="n">
+      <c r="S160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -9805,10 +10288,13 @@
         <v>0.0006511000000000001</v>
       </c>
       <c r="Q161" s="1" t="n">
+        <v>0.0006503</v>
+      </c>
+      <c r="R161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="R161" s="1" t="n">
-        <v>0.0006507</v>
+      <c r="S161" s="1" t="n">
+        <v>0.0006503</v>
       </c>
     </row>
     <row r="162">
@@ -9863,10 +10349,13 @@
         <v>0.3805</v>
       </c>
       <c r="Q162" s="1" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="R162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="R162" s="1" t="n">
-        <v>0.3805</v>
+      <c r="S162" s="1" t="n">
+        <v>0.3785</v>
       </c>
     </row>
     <row r="163">
@@ -9921,9 +10410,12 @@
         <v>0.1908</v>
       </c>
       <c r="Q163" s="1" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="R163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="R163" s="1" t="n">
+      <c r="S163" s="1" t="n">
         <v>0.1908</v>
       </c>
     </row>
@@ -9979,9 +10471,12 @@
         <v>0.316</v>
       </c>
       <c r="Q164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="R164" s="1" t="n">
+      <c r="S164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -10037,9 +10532,12 @@
         <v>0.371</v>
       </c>
       <c r="Q165" s="1" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="R165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="R165" s="1" t="n">
+      <c r="S165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -10095,9 +10593,12 @@
         <v>0.02233</v>
       </c>
       <c r="Q166" s="1" t="n">
+        <v>0.02236</v>
+      </c>
+      <c r="R166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="R166" s="1" t="n">
+      <c r="S166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -10153,9 +10654,12 @@
         <v>0.007256</v>
       </c>
       <c r="Q167" s="1" t="n">
+        <v>0.007264</v>
+      </c>
+      <c r="R167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="R167" s="1" t="n">
+      <c r="S167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -10211,10 +10715,13 @@
         <v>0.01341</v>
       </c>
       <c r="Q168" s="1" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="R168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="R168" s="1" t="n">
-        <v>0.01341</v>
+      <c r="S168" s="1" t="n">
+        <v>0.01337</v>
       </c>
     </row>
     <row r="169">
@@ -10269,9 +10776,12 @@
         <v>0.25295</v>
       </c>
       <c r="Q169" s="1" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="R169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="R169" s="1" t="n">
+      <c r="S169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -10327,9 +10837,12 @@
         <v>0.02145</v>
       </c>
       <c r="Q170" s="1" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="R170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="R170" s="1" t="n">
+      <c r="S170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -10385,10 +10898,13 @@
         <v>0.1712</v>
       </c>
       <c r="Q171" s="1" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="R171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="R171" s="1" t="n">
-        <v>0.1711</v>
+      <c r="S171" s="1" t="n">
+        <v>0.171</v>
       </c>
     </row>
     <row r="172">
@@ -10443,9 +10959,12 @@
         <v>0.089</v>
       </c>
       <c r="Q172" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="R172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="R172" s="1" t="n">
+      <c r="S172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -10501,9 +11020,12 @@
         <v>0.004662</v>
       </c>
       <c r="Q173" s="1" t="n">
+        <v>0.00467</v>
+      </c>
+      <c r="R173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="R173" s="1" t="n">
+      <c r="S173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -10559,9 +11081,12 @@
         <v>0.4343</v>
       </c>
       <c r="Q174" s="1" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="R174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="R174" s="1" t="n">
+      <c r="S174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -10617,9 +11142,12 @@
         <v>0.09013</v>
       </c>
       <c r="Q175" s="1" t="n">
+        <v>0.08995</v>
+      </c>
+      <c r="R175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="R175" s="1" t="n">
+      <c r="S175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -10675,9 +11203,12 @@
         <v>0.2459</v>
       </c>
       <c r="Q176" s="1" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="R176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="R176" s="1" t="n">
+      <c r="S176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -10733,9 +11264,12 @@
         <v>0.01908</v>
       </c>
       <c r="Q177" s="1" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="R177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="R177" s="1" t="n">
+      <c r="S177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -10791,9 +11325,12 @@
         <v>6.108</v>
       </c>
       <c r="Q178" s="1" t="n">
+        <v>6.116</v>
+      </c>
+      <c r="R178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="R178" s="1" t="n">
+      <c r="S178" s="1" t="n">
         <v>6.108</v>
       </c>
     </row>
@@ -10849,9 +11386,12 @@
         <v>0.1362</v>
       </c>
       <c r="Q179" s="1" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="R179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="R179" s="1" t="n">
+      <c r="S179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -10907,9 +11447,12 @@
         <v>0.005039</v>
       </c>
       <c r="Q180" s="1" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="R180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="R180" s="1" t="n">
+      <c r="S180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -10965,9 +11508,12 @@
         <v>0.01182</v>
       </c>
       <c r="Q181" s="1" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="R181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="R181" s="1" t="n">
+      <c r="S181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -11023,9 +11569,12 @@
         <v>0.007314</v>
       </c>
       <c r="Q182" s="1" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="R182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="R182" s="1" t="n">
+      <c r="S182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -11081,9 +11630,12 @@
         <v>0.13168</v>
       </c>
       <c r="Q183" s="1" t="n">
+        <v>0.13061</v>
+      </c>
+      <c r="R183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="R183" s="1" t="n">
+      <c r="S183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -11139,10 +11691,13 @@
         <v>0.09555</v>
       </c>
       <c r="Q184" s="1" t="n">
+        <v>0.09513000000000001</v>
+      </c>
+      <c r="R184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="R184" s="1" t="n">
-        <v>0.09555</v>
+      <c r="S184" s="1" t="n">
+        <v>0.09513000000000001</v>
       </c>
     </row>
     <row r="185">
@@ -11197,9 +11752,12 @@
         <v>0.0075</v>
       </c>
       <c r="Q185" s="1" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="R185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="R185" s="1" t="n">
+      <c r="S185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -11255,9 +11813,12 @@
         <v>0.04851</v>
       </c>
       <c r="Q186" s="1" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="R186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="R186" s="1" t="n">
+      <c r="S186" s="1" t="n">
         <v>0.04851</v>
       </c>
     </row>
@@ -11313,9 +11874,12 @@
         <v>0.02652</v>
       </c>
       <c r="Q187" s="1" t="n">
+        <v>0.02663</v>
+      </c>
+      <c r="R187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="R187" s="1" t="n">
+      <c r="S187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -11371,10 +11935,13 @@
         <v>0.003291</v>
       </c>
       <c r="Q188" s="1" t="n">
+        <v>0.003282</v>
+      </c>
+      <c r="R188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="R188" s="1" t="n">
-        <v>0.003291</v>
+      <c r="S188" s="1" t="n">
+        <v>0.003282</v>
       </c>
     </row>
     <row r="189">
@@ -11429,9 +11996,12 @@
         <v>0.2847</v>
       </c>
       <c r="Q189" s="1" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="R189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="R189" s="1" t="n">
+      <c r="S189" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -11487,9 +12057,12 @@
         <v>0.01783</v>
       </c>
       <c r="Q190" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="R190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="R190" s="1" t="n">
+      <c r="S190" s="1" t="n">
         <v>0.01783</v>
       </c>
     </row>
@@ -11545,9 +12118,12 @@
         <v>0.2562</v>
       </c>
       <c r="Q191" s="1" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="R191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="R191" s="1" t="n">
+      <c r="S191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -11603,9 +12179,12 @@
         <v>0.03785</v>
       </c>
       <c r="Q192" s="1" t="n">
+        <v>0.03802</v>
+      </c>
+      <c r="R192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="R192" s="1" t="n">
+      <c r="S192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -11661,9 +12240,12 @@
         <v>0.0002209</v>
       </c>
       <c r="Q193" s="1" t="n">
+        <v>0.0002207</v>
+      </c>
+      <c r="R193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="R193" s="1" t="n">
+      <c r="S193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -11719,9 +12301,12 @@
         <v>4.068</v>
       </c>
       <c r="Q194" s="1" t="n">
+        <v>4.086</v>
+      </c>
+      <c r="R194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="R194" s="1" t="n">
+      <c r="S194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -11777,9 +12362,12 @@
         <v>0.9994</v>
       </c>
       <c r="Q195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="R195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="R195" s="1" t="n">
+      <c r="S195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -11835,9 +12423,12 @@
         <v>4.276</v>
       </c>
       <c r="Q196" s="1" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="R196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="R196" s="1" t="n">
+      <c r="S196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -11893,9 +12484,12 @@
         <v>0.1519</v>
       </c>
       <c r="Q197" s="1" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="R197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="R197" s="1" t="n">
+      <c r="S197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -11951,9 +12545,12 @@
         <v>0.007696</v>
       </c>
       <c r="Q198" s="1" t="n">
+        <v>0.007723</v>
+      </c>
+      <c r="R198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="R198" s="1" t="n">
+      <c r="S198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -12009,9 +12606,12 @@
         <v>0.4486</v>
       </c>
       <c r="Q199" s="1" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="R199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="R199" s="1" t="n">
+      <c r="S199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -12067,9 +12667,12 @@
         <v>0.5837</v>
       </c>
       <c r="Q200" s="1" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="R200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="R200" s="1" t="n">
+      <c r="S200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -12125,10 +12728,13 @@
         <v>0.0926</v>
       </c>
       <c r="Q201" s="1" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="R201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="R201" s="1" t="n">
-        <v>0.0926</v>
+      <c r="S201" s="1" t="n">
+        <v>0.0925</v>
       </c>
     </row>
     <row r="202">
@@ -12183,9 +12789,12 @@
         <v>0.05994</v>
       </c>
       <c r="Q202" s="1" t="n">
+        <v>0.06004</v>
+      </c>
+      <c r="R202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="R202" s="1" t="n">
+      <c r="S202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -12241,9 +12850,12 @@
         <v>0.00827</v>
       </c>
       <c r="Q203" s="1" t="n">
+        <v>0.008240000000000001</v>
+      </c>
+      <c r="R203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="R203" s="1" t="n">
+      <c r="S203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -12299,10 +12911,13 @@
         <v>0.00413</v>
       </c>
       <c r="Q204" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="R204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="R204" s="1" t="n">
-        <v>0.00413</v>
+      <c r="S204" s="1" t="n">
+        <v>0.00412</v>
       </c>
     </row>
     <row r="205">
@@ -12357,9 +12972,12 @@
         <v>0.009089</v>
       </c>
       <c r="Q205" s="1" t="n">
+        <v>0.009083000000000001</v>
+      </c>
+      <c r="R205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="R205" s="1" t="n">
+      <c r="S205" s="1" t="n">
         <v>0.009070999999999999</v>
       </c>
     </row>
@@ -12415,9 +13033,12 @@
         <v>0.2381</v>
       </c>
       <c r="Q206" s="1" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="R206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="R206" s="1" t="n">
+      <c r="S206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -12473,9 +13094,12 @@
         <v>0.02052</v>
       </c>
       <c r="Q207" s="1" t="n">
+        <v>0.02065</v>
+      </c>
+      <c r="R207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="R207" s="1" t="n">
+      <c r="S207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -12531,9 +13155,12 @@
         <v>0.2357</v>
       </c>
       <c r="Q208" s="1" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="R208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="R208" s="1" t="n">
+      <c r="S208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -12589,10 +13216,13 @@
         <v>0.3585</v>
       </c>
       <c r="Q209" s="1" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="R209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="R209" s="1" t="n">
-        <v>0.3585</v>
+      <c r="S209" s="1" t="n">
+        <v>0.3584</v>
       </c>
     </row>
     <row r="210">
@@ -12647,9 +13277,12 @@
         <v>0.04245</v>
       </c>
       <c r="Q210" s="1" t="n">
+        <v>0.04257</v>
+      </c>
+      <c r="R210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="R210" s="1" t="n">
+      <c r="S210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -12705,9 +13338,12 @@
         <v>0.0004237</v>
       </c>
       <c r="Q211" s="1" t="n">
+        <v>0.0004241</v>
+      </c>
+      <c r="R211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="R211" s="1" t="n">
+      <c r="S211" s="1" t="n">
         <v>0.0004237</v>
       </c>
     </row>
@@ -12763,10 +13399,13 @@
         <v>0.02129</v>
       </c>
       <c r="Q212" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="R212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="R212" s="1" t="n">
-        <v>0.02129</v>
+      <c r="S212" s="1" t="n">
+        <v>0.02126</v>
       </c>
     </row>
     <row r="213">
@@ -12821,9 +13460,12 @@
         <v>0.1135</v>
       </c>
       <c r="Q213" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="R213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="R213" s="1" t="n">
+      <c r="S213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -12879,9 +13521,12 @@
         <v>0.04173</v>
       </c>
       <c r="Q214" s="1" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="R214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="R214" s="1" t="n">
+      <c r="S214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -12937,9 +13582,12 @@
         <v>0.009886000000000001</v>
       </c>
       <c r="Q215" s="1" t="n">
+        <v>0.009844</v>
+      </c>
+      <c r="R215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="R215" s="1" t="n">
+      <c r="S215" s="1" t="n">
         <v>0.009839000000000001</v>
       </c>
     </row>
@@ -12995,9 +13643,12 @@
         <v>0.0636</v>
       </c>
       <c r="Q216" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="R216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="R216" s="1" t="n">
+      <c r="S216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -13053,9 +13704,12 @@
         <v>0.004249</v>
       </c>
       <c r="Q217" s="1" t="n">
+        <v>0.004259</v>
+      </c>
+      <c r="R217" s="1" t="n">
         <v>0.004266</v>
       </c>
-      <c r="R217" s="1" t="n">
+      <c r="S217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -13111,9 +13765,12 @@
         <v>0.00997</v>
       </c>
       <c r="Q218" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="R218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="R218" s="1" t="n">
+      <c r="S218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -13169,9 +13826,12 @@
         <v>0.02979</v>
       </c>
       <c r="Q219" s="1" t="n">
+        <v>0.02975</v>
+      </c>
+      <c r="R219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="R219" s="1" t="n">
+      <c r="S219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -13227,9 +13887,12 @@
         <v>2.281</v>
       </c>
       <c r="Q220" s="1" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="R220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="R220" s="1" t="n">
+      <c r="S220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -13285,10 +13948,13 @@
         <v>0.022653</v>
       </c>
       <c r="Q221" s="1" t="n">
+        <v>0.022529</v>
+      </c>
+      <c r="R221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="R221" s="1" t="n">
-        <v>0.022653</v>
+      <c r="S221" s="1" t="n">
+        <v>0.022529</v>
       </c>
     </row>
     <row r="222">
@@ -13343,9 +14009,12 @@
         <v>0.0368</v>
       </c>
       <c r="Q222" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="R222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="R222" s="1" t="n">
+      <c r="S222" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -13401,9 +14070,12 @@
         <v>0.292</v>
       </c>
       <c r="Q223" s="1" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="R223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="R223" s="1" t="n">
+      <c r="S223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -13459,9 +14131,12 @@
         <v>0.01542</v>
       </c>
       <c r="Q224" s="1" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="R224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="R224" s="1" t="n">
+      <c r="S224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -13517,9 +14192,12 @@
         <v>0.0004032</v>
       </c>
       <c r="Q225" s="1" t="n">
+        <v>0.0004037</v>
+      </c>
+      <c r="R225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="R225" s="1" t="n">
+      <c r="S225" s="1" t="n">
         <v>0.0004032</v>
       </c>
     </row>
@@ -13575,10 +14253,13 @@
         <v>0.0857</v>
       </c>
       <c r="Q226" s="1" t="n">
+        <v>0.08522</v>
+      </c>
+      <c r="R226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="R226" s="1" t="n">
-        <v>0.0857</v>
+      <c r="S226" s="1" t="n">
+        <v>0.08522</v>
       </c>
     </row>
     <row r="227">
@@ -13633,9 +14314,12 @@
         <v>0.945</v>
       </c>
       <c r="Q227" s="1" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="R227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="R227" s="1" t="n">
+      <c r="S227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -13691,10 +14375,13 @@
         <v>0.05487</v>
       </c>
       <c r="Q228" s="1" t="n">
+        <v>0.05439</v>
+      </c>
+      <c r="R228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="R228" s="1" t="n">
-        <v>0.05487</v>
+      <c r="S228" s="1" t="n">
+        <v>0.05439</v>
       </c>
     </row>
     <row r="229">
@@ -13749,9 +14436,12 @@
         <v>0.001997</v>
       </c>
       <c r="Q229" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="R229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="R229" s="1" t="n">
+      <c r="S229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -13807,9 +14497,12 @@
         <v>0.022784</v>
       </c>
       <c r="Q230" s="1" t="n">
+        <v>0.022774</v>
+      </c>
+      <c r="R230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="R230" s="1" t="n">
+      <c r="S230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -13865,9 +14558,12 @@
         <v>0.05338</v>
       </c>
       <c r="Q231" s="1" t="n">
+        <v>0.05344</v>
+      </c>
+      <c r="R231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="R231" s="1" t="n">
+      <c r="S231" s="1" t="n">
         <v>0.05338</v>
       </c>
     </row>
@@ -13923,10 +14619,13 @@
         <v>0.0584</v>
       </c>
       <c r="Q232" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="R232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="R232" s="1" t="n">
-        <v>0.0584</v>
+      <c r="S232" s="1" t="n">
+        <v>0.0583</v>
       </c>
     </row>
     <row r="233">
@@ -13981,9 +14680,12 @@
         <v>0.001677</v>
       </c>
       <c r="Q233" s="1" t="n">
+        <v>0.001684</v>
+      </c>
+      <c r="R233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="R233" s="1" t="n">
+      <c r="S233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -14039,9 +14741,12 @@
         <v>0.005743</v>
       </c>
       <c r="Q234" s="1" t="n">
+        <v>0.005749</v>
+      </c>
+      <c r="R234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="R234" s="1" t="n">
+      <c r="S234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -14097,10 +14802,13 @@
         <v>0.12298</v>
       </c>
       <c r="Q235" s="1" t="n">
+        <v>0.12245</v>
+      </c>
+      <c r="R235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="R235" s="1" t="n">
-        <v>0.12267</v>
+      <c r="S235" s="1" t="n">
+        <v>0.12245</v>
       </c>
     </row>
     <row r="236">
@@ -14155,9 +14863,12 @@
         <v>64.34</v>
       </c>
       <c r="Q236" s="1" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="R236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="R236" s="1" t="n">
+      <c r="S236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -14213,9 +14924,12 @@
         <v>0.1008</v>
       </c>
       <c r="Q237" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="R237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="R237" s="1" t="n">
+      <c r="S237" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -14271,9 +14985,12 @@
         <v>0.004023</v>
       </c>
       <c r="Q238" s="1" t="n">
+        <v>0.004014</v>
+      </c>
+      <c r="R238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="R238" s="1" t="n">
+      <c r="S238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -14329,10 +15046,13 @@
         <v>0.01528</v>
       </c>
       <c r="Q239" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="R239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="R239" s="1" t="n">
-        <v>0.01528</v>
+      <c r="S239" s="1" t="n">
+        <v>0.01512</v>
       </c>
     </row>
     <row r="240">
@@ -14387,9 +15107,12 @@
         <v>0.05575</v>
       </c>
       <c r="Q240" s="1" t="n">
+        <v>0.05584</v>
+      </c>
+      <c r="R240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="R240" s="1" t="n">
+      <c r="S240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -14445,9 +15168,12 @@
         <v>0.0113</v>
       </c>
       <c r="Q241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="R241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="R241" s="1" t="n">
+      <c r="S241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -14503,9 +15229,12 @@
         <v>0.3334</v>
       </c>
       <c r="Q242" s="1" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="R242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="R242" s="1" t="n">
+      <c r="S242" s="1" t="n">
         <v>0.3332</v>
       </c>
     </row>
@@ -14561,10 +15290,13 @@
         <v>0.01223</v>
       </c>
       <c r="Q243" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="R243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="R243" s="1" t="n">
-        <v>0.01223</v>
+      <c r="S243" s="1" t="n">
+        <v>0.01222</v>
       </c>
     </row>
     <row r="244">
@@ -14619,10 +15351,13 @@
         <v>0.08004</v>
       </c>
       <c r="Q244" s="1" t="n">
+        <v>0.07973</v>
+      </c>
+      <c r="R244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="R244" s="1" t="n">
-        <v>0.07997</v>
+      <c r="S244" s="1" t="n">
+        <v>0.07973</v>
       </c>
     </row>
     <row r="245">
@@ -14677,9 +15412,12 @@
         <v>0.00778</v>
       </c>
       <c r="Q245" s="1" t="n">
+        <v>0.007812</v>
+      </c>
+      <c r="R245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="R245" s="1" t="n">
+      <c r="S245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -14735,9 +15473,12 @@
         <v>0.0302</v>
       </c>
       <c r="Q246" s="1" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="R246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="R246" s="1" t="n">
+      <c r="S246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -14793,9 +15534,12 @@
         <v>0.1796</v>
       </c>
       <c r="Q247" s="1" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="R247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="R247" s="1" t="n">
+      <c r="S247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -14851,9 +15595,12 @@
         <v>0.05856</v>
       </c>
       <c r="Q248" s="1" t="n">
+        <v>0.05866</v>
+      </c>
+      <c r="R248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="R248" s="1" t="n">
+      <c r="S248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -14909,9 +15656,12 @@
         <v>0.1658</v>
       </c>
       <c r="Q249" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="R249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="R249" s="1" t="n">
+      <c r="S249" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -14967,9 +15717,12 @@
         <v>0.01898</v>
       </c>
       <c r="Q250" s="1" t="n">
+        <v>0.01902</v>
+      </c>
+      <c r="R250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="R250" s="1" t="n">
+      <c r="S250" s="1" t="n">
         <v>0.01898</v>
       </c>
     </row>
@@ -15025,9 +15778,12 @@
         <v>0.02304</v>
       </c>
       <c r="Q251" s="1" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="R251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="R251" s="1" t="n">
+      <c r="S251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -15083,9 +15839,12 @@
         <v>0.30644</v>
       </c>
       <c r="Q252" s="1" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="R252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="R252" s="1" t="n">
+      <c r="S252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -15141,9 +15900,12 @@
         <v>0.005956</v>
       </c>
       <c r="Q253" s="1" t="n">
+        <v>0.005971</v>
+      </c>
+      <c r="R253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="R253" s="1" t="n">
+      <c r="S253" s="1" t="n">
         <v>0.005956</v>
       </c>
     </row>
@@ -15199,9 +15961,12 @@
         <v>0.6118</v>
       </c>
       <c r="Q254" s="1" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="R254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="R254" s="1" t="n">
+      <c r="S254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -15257,10 +16022,13 @@
         <v>0.10611</v>
       </c>
       <c r="Q255" s="1" t="n">
+        <v>0.10593</v>
+      </c>
+      <c r="R255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="R255" s="1" t="n">
-        <v>0.10601</v>
+      <c r="S255" s="1" t="n">
+        <v>0.10593</v>
       </c>
     </row>
     <row r="256">
@@ -15315,10 +16083,13 @@
         <v>0.0902</v>
       </c>
       <c r="Q256" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="R256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="R256" s="1" t="n">
-        <v>0.0901</v>
+      <c r="S256" s="1" t="n">
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -15373,9 +16144,12 @@
         <v>0.01457</v>
       </c>
       <c r="Q257" s="1" t="n">
+        <v>0.01449</v>
+      </c>
+      <c r="R257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="R257" s="1" t="n">
+      <c r="S257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -15431,9 +16205,12 @@
         <v>0.04965</v>
       </c>
       <c r="Q258" s="1" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="R258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="R258" s="1" t="n">
+      <c r="S258" s="1" t="n">
         <v>0.04965</v>
       </c>
     </row>
@@ -15489,9 +16266,12 @@
         <v>0.008070000000000001</v>
       </c>
       <c r="Q259" s="1" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="R259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="R259" s="1" t="n">
+      <c r="S259" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -15547,9 +16327,12 @@
         <v>0.1892</v>
       </c>
       <c r="Q260" s="1" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="R260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="R260" s="1" t="n">
+      <c r="S260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -15605,9 +16388,12 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="Q261" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="R261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="R261" s="1" t="n">
+      <c r="S261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -15663,9 +16449,12 @@
         <v>0.2103</v>
       </c>
       <c r="Q262" s="1" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="R262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="R262" s="1" t="n">
+      <c r="S262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -15721,9 +16510,12 @@
         <v>0.008475</v>
       </c>
       <c r="Q263" s="1" t="n">
+        <v>0.008467000000000001</v>
+      </c>
+      <c r="R263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="R263" s="1" t="n">
+      <c r="S263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -15779,9 +16571,12 @@
         <v>2.631</v>
       </c>
       <c r="Q264" s="1" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="R264" s="1" t="n">
+      <c r="S264" s="1" t="n">
         <v>2.629</v>
       </c>
     </row>
@@ -15837,9 +16632,12 @@
         <v>0.01853</v>
       </c>
       <c r="Q265" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="R265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="R265" s="1" t="n">
+      <c r="S265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -15895,9 +16693,12 @@
         <v>0.3602</v>
       </c>
       <c r="Q266" s="1" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="R266" s="1" t="n">
         <v>0.3612</v>
       </c>
-      <c r="R266" s="1" t="n">
+      <c r="S266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -15953,9 +16754,12 @@
         <v>0.03413</v>
       </c>
       <c r="Q267" s="1" t="n">
+        <v>0.03424</v>
+      </c>
+      <c r="R267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="R267" s="1" t="n">
+      <c r="S267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -16011,9 +16815,12 @@
         <v>0.117</v>
       </c>
       <c r="Q268" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="R268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="R268" s="1" t="n">
+      <c r="S268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -16069,9 +16876,12 @@
         <v>0.07976999999999999</v>
       </c>
       <c r="Q269" s="1" t="n">
+        <v>0.07974000000000001</v>
+      </c>
+      <c r="R269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="R269" s="1" t="n">
+      <c r="S269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -16127,9 +16937,12 @@
         <v>0.01374</v>
       </c>
       <c r="Q270" s="1" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="R270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="R270" s="1" t="n">
+      <c r="S270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -16185,9 +16998,12 @@
         <v>0.007504</v>
       </c>
       <c r="Q271" s="1" t="n">
+        <v>0.007516</v>
+      </c>
+      <c r="R271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="R271" s="1" t="n">
+      <c r="S271" s="1" t="n">
         <v>0.007504</v>
       </c>
     </row>
@@ -16243,9 +17059,12 @@
         <v>0.07396</v>
       </c>
       <c r="Q272" s="1" t="n">
+        <v>0.07418</v>
+      </c>
+      <c r="R272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="R272" s="1" t="n">
+      <c r="S272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -16301,9 +17120,12 @@
         <v>3.14e-05</v>
       </c>
       <c r="Q273" s="1" t="n">
+        <v>3.13e-05</v>
+      </c>
+      <c r="R273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="R273" s="1" t="n">
+      <c r="S273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -16359,9 +17181,12 @@
         <v>0.005409</v>
       </c>
       <c r="Q274" s="1" t="n">
+        <v>0.00542</v>
+      </c>
+      <c r="R274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="R274" s="1" t="n">
+      <c r="S274" s="1" t="n">
         <v>0.005409</v>
       </c>
     </row>
@@ -16417,10 +17242,13 @@
         <v>0.179</v>
       </c>
       <c r="Q275" s="1" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="R275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="R275" s="1" t="n">
-        <v>0.179</v>
+      <c r="S275" s="1" t="n">
+        <v>0.1784</v>
       </c>
     </row>
     <row r="276">
@@ -16475,10 +17303,13 @@
         <v>0.006819</v>
       </c>
       <c r="Q276" s="1" t="n">
+        <v>0.006809</v>
+      </c>
+      <c r="R276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="R276" s="1" t="n">
-        <v>0.006819</v>
+      <c r="S276" s="1" t="n">
+        <v>0.006809</v>
       </c>
     </row>
     <row r="277">
@@ -16533,9 +17364,12 @@
         <v>0.1303</v>
       </c>
       <c r="Q277" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="R277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="R277" s="1" t="n">
+      <c r="S277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -16591,9 +17425,12 @@
         <v>0.02306</v>
       </c>
       <c r="Q278" s="1" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="R278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="R278" s="1" t="n">
+      <c r="S278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -16649,9 +17486,12 @@
         <v>0.01812</v>
       </c>
       <c r="Q279" s="1" t="n">
+        <v>0.01813</v>
+      </c>
+      <c r="R279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="R279" s="1" t="n">
+      <c r="S279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -16707,9 +17547,12 @@
         <v>0.03666</v>
       </c>
       <c r="Q280" s="1" t="n">
+        <v>0.03681</v>
+      </c>
+      <c r="R280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="R280" s="1" t="n">
+      <c r="S280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -16765,9 +17608,12 @@
         <v>0.03957</v>
       </c>
       <c r="Q281" s="1" t="n">
+        <v>0.03963</v>
+      </c>
+      <c r="R281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="R281" s="1" t="n">
+      <c r="S281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -16823,9 +17669,12 @@
         <v>0.3021</v>
       </c>
       <c r="Q282" s="1" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="R282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="R282" s="1" t="n">
+      <c r="S282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -16881,10 +17730,13 @@
         <v>0.01117</v>
       </c>
       <c r="Q283" s="1" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="R283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="R283" s="1" t="n">
-        <v>0.01117</v>
+      <c r="S283" s="1" t="n">
+        <v>0.01115</v>
       </c>
     </row>
     <row r="284">
@@ -16939,9 +17791,12 @@
         <v>9.7e-06</v>
       </c>
       <c r="Q284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="R284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="R284" s="1" t="n">
+      <c r="S284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -16997,9 +17852,12 @@
         <v>0.1143</v>
       </c>
       <c r="Q285" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="R285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="R285" s="1" t="n">
+      <c r="S285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -17055,9 +17913,12 @@
         <v>0.003425</v>
       </c>
       <c r="Q286" s="1" t="n">
+        <v>0.003425</v>
+      </c>
+      <c r="R286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="R286" s="1" t="n">
+      <c r="S286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -17113,9 +17974,12 @@
         <v>0.08465</v>
       </c>
       <c r="Q287" s="1" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="R287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="R287" s="1" t="n">
+      <c r="S287" s="1" t="n">
         <v>0.08465</v>
       </c>
     </row>
@@ -17171,9 +18035,12 @@
         <v>0.09958</v>
       </c>
       <c r="Q288" s="1" t="n">
+        <v>0.09970999999999999</v>
+      </c>
+      <c r="R288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="R288" s="1" t="n">
+      <c r="S288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -17229,9 +18096,12 @@
         <v>0.4341</v>
       </c>
       <c r="Q289" s="1" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="R289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="R289" s="1" t="n">
+      <c r="S289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -17287,9 +18157,12 @@
         <v>0.0392</v>
       </c>
       <c r="Q290" s="1" t="n">
+        <v>0.03943</v>
+      </c>
+      <c r="R290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="R290" s="1" t="n">
+      <c r="S290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -17345,9 +18218,12 @@
         <v>0.2344</v>
       </c>
       <c r="Q291" s="1" t="n">
+        <v>0.2349</v>
+      </c>
+      <c r="R291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="R291" s="1" t="n">
+      <c r="S291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -17403,9 +18279,12 @@
         <v>0.2833</v>
       </c>
       <c r="Q292" s="1" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="R292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="R292" s="1" t="n">
+      <c r="S292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -17461,9 +18340,12 @@
         <v>0.1487</v>
       </c>
       <c r="Q293" s="1" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="R293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="R293" s="1" t="n">
+      <c r="S293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -17519,9 +18401,12 @@
         <v>4.171</v>
       </c>
       <c r="Q294" s="1" t="n">
+        <v>4.171</v>
+      </c>
+      <c r="R294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="R294" s="1" t="n">
+      <c r="S294" s="1" t="n">
         <v>4.171</v>
       </c>
     </row>
@@ -17577,9 +18462,12 @@
         <v>0.03436</v>
       </c>
       <c r="Q295" s="1" t="n">
-        <v>0.03436</v>
+        <v>0.03509</v>
       </c>
       <c r="R295" s="1" t="n">
+        <v>0.03509</v>
+      </c>
+      <c r="S295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -17635,9 +18523,12 @@
         <v>0.000964</v>
       </c>
       <c r="Q296" s="1" t="n">
+        <v>0.000967</v>
+      </c>
+      <c r="R296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="R296" s="1" t="n">
+      <c r="S296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -17693,9 +18584,12 @@
         <v>0.08135000000000001</v>
       </c>
       <c r="Q297" s="1" t="n">
+        <v>0.08148</v>
+      </c>
+      <c r="R297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="R297" s="1" t="n">
+      <c r="S297" s="1" t="n">
         <v>0.08135000000000001</v>
       </c>
     </row>
@@ -17751,9 +18645,12 @@
         <v>0.05781</v>
       </c>
       <c r="Q298" s="1" t="n">
+        <v>0.05784</v>
+      </c>
+      <c r="R298" s="1" t="n">
         <v>0.05845</v>
       </c>
-      <c r="R298" s="1" t="n">
+      <c r="S298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -17809,9 +18706,12 @@
         <v>0.09028</v>
       </c>
       <c r="Q299" s="1" t="n">
+        <v>0.09054</v>
+      </c>
+      <c r="R299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="R299" s="1" t="n">
+      <c r="S299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -17867,9 +18767,12 @@
         <v>0.02724</v>
       </c>
       <c r="Q300" s="1" t="n">
+        <v>0.02725</v>
+      </c>
+      <c r="R300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="R300" s="1" t="n">
+      <c r="S300" s="1" t="n">
         <v>0.02724</v>
       </c>
     </row>
@@ -17925,9 +18828,12 @@
         <v>0.06525</v>
       </c>
       <c r="Q301" s="1" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="R301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="R301" s="1" t="n">
+      <c r="S301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -17983,9 +18889,12 @@
         <v>0.053465</v>
       </c>
       <c r="Q302" s="1" t="n">
+        <v>0.053562</v>
+      </c>
+      <c r="R302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="R302" s="1" t="n">
+      <c r="S302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -18041,9 +18950,12 @@
         <v>5172.5</v>
       </c>
       <c r="Q303" s="1" t="n">
+        <v>5168.2</v>
+      </c>
+      <c r="R303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="R303" s="1" t="n">
+      <c r="S303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -18099,9 +19011,12 @@
         <v>14.8</v>
       </c>
       <c r="Q304" s="1" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="R304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="R304" s="1" t="n">
+      <c r="S304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -18157,9 +19072,12 @@
         <v>0.003688</v>
       </c>
       <c r="Q305" s="1" t="n">
+        <v>0.003696</v>
+      </c>
+      <c r="R305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="R305" s="1" t="n">
+      <c r="S305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -18215,9 +19133,12 @@
         <v>0.4532</v>
       </c>
       <c r="Q306" s="1" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="R306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="R306" s="1" t="n">
+      <c r="S306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -18273,10 +19194,13 @@
         <v>0.04656</v>
       </c>
       <c r="Q307" s="1" t="n">
+        <v>0.04651</v>
+      </c>
+      <c r="R307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="R307" s="1" t="n">
-        <v>0.04656</v>
+      <c r="S307" s="1" t="n">
+        <v>0.04651</v>
       </c>
     </row>
     <row r="308">
@@ -18331,9 +19255,12 @@
         <v>1.5096</v>
       </c>
       <c r="Q308" s="1" t="n">
+        <v>1.5049</v>
+      </c>
+      <c r="R308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="R308" s="1" t="n">
+      <c r="S308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -18389,10 +19316,13 @@
         <v>0.0007994</v>
       </c>
       <c r="Q309" s="1" t="n">
+        <v>0.0007861</v>
+      </c>
+      <c r="R309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="R309" s="1" t="n">
-        <v>0.0007892</v>
+      <c r="S309" s="1" t="n">
+        <v>0.0007861</v>
       </c>
     </row>
     <row r="310">
@@ -18447,9 +19377,12 @@
         <v>4.549</v>
       </c>
       <c r="Q310" s="1" t="n">
+        <v>4.552</v>
+      </c>
+      <c r="R310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="R310" s="1" t="n">
+      <c r="S310" s="1" t="n">
         <v>4.549</v>
       </c>
     </row>
@@ -18505,9 +19438,12 @@
         <v>4.772</v>
       </c>
       <c r="Q311" s="1" t="n">
+        <v>4.766</v>
+      </c>
+      <c r="R311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="R311" s="1" t="n">
+      <c r="S311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -18563,10 +19499,13 @@
         <v>0.08125</v>
       </c>
       <c r="Q312" s="1" t="n">
+        <v>0.08057</v>
+      </c>
+      <c r="R312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="R312" s="1" t="n">
-        <v>0.08098</v>
+      <c r="S312" s="1" t="n">
+        <v>0.08057</v>
       </c>
     </row>
     <row r="313">
@@ -18621,9 +19560,12 @@
         <v>2.005</v>
       </c>
       <c r="Q313" s="1" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="R313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="R313" s="1" t="n">
+      <c r="S313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -18679,9 +19621,12 @@
         <v>0.07418</v>
       </c>
       <c r="Q314" s="1" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="R314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="R314" s="1" t="n">
+      <c r="S314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -18737,9 +19682,12 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="Q315" s="1" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="R315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="R315" s="1" t="n">
+      <c r="S315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -18795,9 +19743,12 @@
         <v>0.1303</v>
       </c>
       <c r="Q316" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="R316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="R316" s="1" t="n">
+      <c r="S316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -18853,9 +19804,12 @@
         <v>0.184</v>
       </c>
       <c r="Q317" s="1" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="R317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="R317" s="1" t="n">
+      <c r="S317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -18911,9 +19865,12 @@
         <v>0.01608</v>
       </c>
       <c r="Q318" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="R318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="R318" s="1" t="n">
+      <c r="S318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -18969,9 +19926,12 @@
         <v>0.08318</v>
       </c>
       <c r="Q319" s="1" t="n">
+        <v>0.08323999999999999</v>
+      </c>
+      <c r="R319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="R319" s="1" t="n">
+      <c r="S319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -19027,9 +19987,12 @@
         <v>0.007463</v>
       </c>
       <c r="Q320" s="1" t="n">
+        <v>0.007481</v>
+      </c>
+      <c r="R320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="R320" s="1" t="n">
+      <c r="S320" s="1" t="n">
         <v>0.007463</v>
       </c>
     </row>
@@ -19085,9 +20048,12 @@
         <v>0.05422</v>
       </c>
       <c r="Q321" s="1" t="n">
+        <v>0.05427</v>
+      </c>
+      <c r="R321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="R321" s="1" t="n">
+      <c r="S321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -19143,9 +20109,12 @@
         <v>0.5483</v>
       </c>
       <c r="Q322" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="R322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="R322" s="1" t="n">
+      <c r="S322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -19201,9 +20170,12 @@
         <v>0.07568</v>
       </c>
       <c r="Q323" s="1" t="n">
+        <v>0.07566000000000001</v>
+      </c>
+      <c r="R323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="R323" s="1" t="n">
+      <c r="S323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -19259,9 +20231,12 @@
         <v>0.012915</v>
       </c>
       <c r="Q324" s="1" t="n">
+        <v>0.012973</v>
+      </c>
+      <c r="R324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="R324" s="1" t="n">
+      <c r="S324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -19317,10 +20292,13 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="Q325" s="1" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="R325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="R325" s="1" t="n">
-        <v>0.09859999999999999</v>
+      <c r="S325" s="1" t="n">
+        <v>0.0985</v>
       </c>
     </row>
     <row r="326">
@@ -19375,9 +20353,12 @@
         <v>0.01729</v>
       </c>
       <c r="Q326" s="1" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="R326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="R326" s="1" t="n">
+      <c r="S326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -19433,9 +20414,12 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="Q327" s="1" t="n">
+        <v>0.06372999999999999</v>
+      </c>
+      <c r="R327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="R327" s="1" t="n">
+      <c r="S327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -19491,9 +20475,12 @@
         <v>0.2612</v>
       </c>
       <c r="Q328" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="R328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="R328" s="1" t="n">
+      <c r="S328" s="1" t="n">
         <v>0.2612</v>
       </c>
     </row>
@@ -19549,9 +20536,12 @@
         <v>0.17393</v>
       </c>
       <c r="Q329" s="1" t="n">
-        <v>0.17406</v>
+        <v>0.17476</v>
       </c>
       <c r="R329" s="1" t="n">
+        <v>0.17476</v>
+      </c>
+      <c r="S329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -19607,10 +20597,13 @@
         <v>2.046</v>
       </c>
       <c r="Q330" s="1" t="n">
+        <v>2.037</v>
+      </c>
+      <c r="R330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="R330" s="1" t="n">
-        <v>2.043</v>
+      <c r="S330" s="1" t="n">
+        <v>2.037</v>
       </c>
     </row>
     <row r="331">
@@ -19665,9 +20658,12 @@
         <v>0.0286</v>
       </c>
       <c r="Q331" s="1" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="R331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="R331" s="1" t="n">
+      <c r="S331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -19723,9 +20719,12 @@
         <v>0.00602</v>
       </c>
       <c r="Q332" s="1" t="n">
+        <v>0.00599</v>
+      </c>
+      <c r="R332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="R332" s="1" t="n">
+      <c r="S332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -19781,9 +20780,12 @@
         <v>0.003527</v>
       </c>
       <c r="Q333" s="1" t="n">
+        <v>0.003531</v>
+      </c>
+      <c r="R333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="R333" s="1" t="n">
+      <c r="S333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -19839,9 +20841,12 @@
         <v>0.01397</v>
       </c>
       <c r="Q334" s="1" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="R334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="R334" s="1" t="n">
+      <c r="S334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -19897,9 +20902,12 @@
         <v>1.141</v>
       </c>
       <c r="Q335" s="1" t="n">
-        <v>1.141</v>
+        <v>1.143</v>
       </c>
       <c r="R335" s="1" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="S335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -19955,9 +20963,12 @@
         <v>0.011316</v>
       </c>
       <c r="Q336" s="1" t="n">
+        <v>0.011326</v>
+      </c>
+      <c r="R336" s="1" t="n">
         <v>0.011344</v>
       </c>
-      <c r="R336" s="1" t="n">
+      <c r="S336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -20013,9 +21024,12 @@
         <v>2.948</v>
       </c>
       <c r="Q337" s="1" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="R337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="R337" s="1" t="n">
+      <c r="S337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -20071,9 +21085,12 @@
         <v>0.01844</v>
       </c>
       <c r="Q338" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="R338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="R338" s="1" t="n">
+      <c r="S338" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -20129,9 +21146,12 @@
         <v>0.07693999999999999</v>
       </c>
       <c r="Q339" s="1" t="n">
+        <v>0.07693</v>
+      </c>
+      <c r="R339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="R339" s="1" t="n">
+      <c r="S339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -20187,9 +21207,12 @@
         <v>0.075</v>
       </c>
       <c r="Q340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="R340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="R340" s="1" t="n">
+      <c r="S340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -20245,9 +21268,12 @@
         <v>0.03578</v>
       </c>
       <c r="Q341" s="1" t="n">
+        <v>0.03578</v>
+      </c>
+      <c r="R341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="R341" s="1" t="n">
+      <c r="S341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -20303,9 +21329,12 @@
         <v>2592</v>
       </c>
       <c r="Q342" s="1" t="n">
+        <v>2596</v>
+      </c>
+      <c r="R342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="R342" s="1" t="n">
+      <c r="S342" s="1" t="n">
         <v>2592</v>
       </c>
     </row>
@@ -20361,9 +21390,12 @@
         <v>0.0001999</v>
       </c>
       <c r="Q343" s="1" t="n">
-        <v>0.0002003</v>
+        <v>0.0002007</v>
       </c>
       <c r="R343" s="1" t="n">
+        <v>0.0002007</v>
+      </c>
+      <c r="S343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -20419,9 +21451,12 @@
         <v>0.07915</v>
       </c>
       <c r="Q344" s="1" t="n">
+        <v>0.07931000000000001</v>
+      </c>
+      <c r="R344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="R344" s="1" t="n">
+      <c r="S344" s="1" t="n">
         <v>0.07915</v>
       </c>
     </row>
@@ -20477,10 +21512,13 @@
         <v>0.01626</v>
       </c>
       <c r="Q345" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="R345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="R345" s="1" t="n">
-        <v>0.01626</v>
+      <c r="S345" s="1" t="n">
+        <v>0.01622</v>
       </c>
     </row>
     <row r="346">
@@ -20535,9 +21573,12 @@
         <v>2.731</v>
       </c>
       <c r="Q346" s="1" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="R346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="R346" s="1" t="n">
+      <c r="S346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -20593,9 +21634,12 @@
         <v>0.01625</v>
       </c>
       <c r="Q347" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="R347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="R347" s="1" t="n">
+      <c r="S347" s="1" t="n">
         <v>0.01625</v>
       </c>
     </row>
@@ -20651,9 +21695,12 @@
         <v>0.03971</v>
       </c>
       <c r="Q348" s="1" t="n">
-        <v>0.03971</v>
+        <v>0.04</v>
       </c>
       <c r="R348" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -20709,9 +21756,12 @@
         <v>0.304</v>
       </c>
       <c r="Q349" s="1" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="R349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="R349" s="1" t="n">
+      <c r="S349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -20767,9 +21817,12 @@
         <v>0.005084</v>
       </c>
       <c r="Q350" s="1" t="n">
+        <v>0.005081</v>
+      </c>
+      <c r="R350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="R350" s="1" t="n">
+      <c r="S350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -20825,10 +21878,13 @@
         <v>0.005066</v>
       </c>
       <c r="Q351" s="1" t="n">
+        <v>0.005054</v>
+      </c>
+      <c r="R351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="R351" s="1" t="n">
-        <v>0.005065</v>
+      <c r="S351" s="1" t="n">
+        <v>0.005054</v>
       </c>
     </row>
     <row r="352">
@@ -20883,9 +21939,12 @@
         <v>0.00438</v>
       </c>
       <c r="Q352" s="1" t="n">
+        <v>0.004383</v>
+      </c>
+      <c r="R352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="R352" s="1" t="n">
+      <c r="S352" s="1" t="n">
         <v>0.004379</v>
       </c>
     </row>
@@ -20941,10 +22000,13 @@
         <v>0.08033</v>
       </c>
       <c r="Q353" s="1" t="n">
+        <v>0.08008</v>
+      </c>
+      <c r="R353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="R353" s="1" t="n">
-        <v>0.0803</v>
+      <c r="S353" s="1" t="n">
+        <v>0.08008</v>
       </c>
     </row>
     <row r="354">
@@ -20999,9 +22061,12 @@
         <v>1.258</v>
       </c>
       <c r="Q354" s="1" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="R354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="R354" s="1" t="n">
+      <c r="S354" s="1" t="n">
         <v>1.258</v>
       </c>
     </row>
@@ -21057,9 +22122,12 @@
         <v>7.651</v>
       </c>
       <c r="Q355" s="1" t="n">
+        <v>7.663</v>
+      </c>
+      <c r="R355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="R355" s="1" t="n">
+      <c r="S355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -21115,9 +22183,12 @@
         <v>0.0078</v>
       </c>
       <c r="Q356" s="1" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="R356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="R356" s="1" t="n">
+      <c r="S356" s="1" t="n">
         <v>0.00777</v>
       </c>
     </row>
@@ -21173,9 +22244,12 @@
         <v>0.00563</v>
       </c>
       <c r="Q357" s="1" t="n">
+        <v>0.005623</v>
+      </c>
+      <c r="R357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="R357" s="1" t="n">
+      <c r="S357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -21231,9 +22305,12 @@
         <v>0.01533</v>
       </c>
       <c r="Q358" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="R358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="R358" s="1" t="n">
+      <c r="S358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -21289,10 +22366,13 @@
         <v>3.612</v>
       </c>
       <c r="Q359" s="1" t="n">
+        <v>3.605</v>
+      </c>
+      <c r="R359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="R359" s="1" t="n">
-        <v>3.612</v>
+      <c r="S359" s="1" t="n">
+        <v>3.605</v>
       </c>
     </row>
     <row r="360">
@@ -21347,9 +22427,12 @@
         <v>0.15</v>
       </c>
       <c r="Q360" s="1" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="R360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="R360" s="1" t="n">
+      <c r="S360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -21405,9 +22488,12 @@
         <v>0.07033</v>
       </c>
       <c r="Q361" s="1" t="n">
+        <v>0.07041</v>
+      </c>
+      <c r="R361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="R361" s="1" t="n">
+      <c r="S361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -21463,9 +22549,12 @@
         <v>0.0176</v>
       </c>
       <c r="Q362" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="R362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="R362" s="1" t="n">
+      <c r="S362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -21521,9 +22610,12 @@
         <v>0.02229</v>
       </c>
       <c r="Q363" s="1" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="R363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="R363" s="1" t="n">
+      <c r="S363" s="1" t="n">
         <v>0.02229</v>
       </c>
     </row>
@@ -21579,9 +22671,12 @@
         <v>0.0125</v>
       </c>
       <c r="Q364" s="1" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="R364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="R364" s="1" t="n">
+      <c r="S364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -21637,9 +22732,12 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="Q365" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="R365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="R365" s="1" t="n">
+      <c r="S365" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -21695,9 +22793,12 @@
         <v>0.04214</v>
       </c>
       <c r="Q366" s="1" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="R366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="R366" s="1" t="n">
+      <c r="S366" s="1" t="n">
         <v>0.04214</v>
       </c>
     </row>
@@ -21753,9 +22854,12 @@
         <v>0.03124</v>
       </c>
       <c r="Q367" s="1" t="n">
+        <v>0.03136</v>
+      </c>
+      <c r="R367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="R367" s="1" t="n">
+      <c r="S367" s="1" t="n">
         <v>0.03124</v>
       </c>
     </row>
@@ -21811,9 +22915,12 @@
         <v>0.0233</v>
       </c>
       <c r="Q368" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="R368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="R368" s="1" t="n">
+      <c r="S368" s="1" t="n">
         <v>0.0233</v>
       </c>
     </row>
@@ -21869,9 +22976,12 @@
         <v>0.0308</v>
       </c>
       <c r="Q369" s="1" t="n">
+        <v>0.03087</v>
+      </c>
+      <c r="R369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="R369" s="1" t="n">
+      <c r="S369" s="1" t="n">
         <v>0.0308</v>
       </c>
     </row>
@@ -21927,9 +23037,12 @@
         <v>0.07973</v>
       </c>
       <c r="Q370" s="1" t="n">
-        <v>0.07990999999999999</v>
+        <v>0.07998</v>
       </c>
       <c r="R370" s="1" t="n">
+        <v>0.07998</v>
+      </c>
+      <c r="S370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -21985,9 +23098,12 @@
         <v>0.1072</v>
       </c>
       <c r="Q371" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="R371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="R371" s="1" t="n">
+      <c r="S371" s="1" t="n">
         <v>0.1072</v>
       </c>
     </row>
@@ -22043,9 +23159,12 @@
         <v>0.00694</v>
       </c>
       <c r="Q372" s="1" t="n">
+        <v>0.006968</v>
+      </c>
+      <c r="R372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="R372" s="1" t="n">
+      <c r="S372" s="1" t="n">
         <v>0.00694</v>
       </c>
     </row>
@@ -22101,9 +23220,12 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="Q373" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="R373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="R373" s="1" t="n">
+      <c r="S373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -22159,9 +23281,12 @@
         <v>0.05739</v>
       </c>
       <c r="Q374" s="1" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="R374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="R374" s="1" t="n">
+      <c r="S374" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -22217,9 +23342,12 @@
         <v>0.3177</v>
       </c>
       <c r="Q375" s="1" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="R375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="R375" s="1" t="n">
+      <c r="S375" s="1" t="n">
         <v>0.3175</v>
       </c>
     </row>
@@ -22275,9 +23403,12 @@
         <v>0.01938</v>
       </c>
       <c r="Q376" s="1" t="n">
+        <v>0.01943</v>
+      </c>
+      <c r="R376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="R376" s="1" t="n">
+      <c r="S376" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -22333,9 +23464,12 @@
         <v>0.06818</v>
       </c>
       <c r="Q377" s="1" t="n">
+        <v>0.06829</v>
+      </c>
+      <c r="R377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="R377" s="1" t="n">
+      <c r="S377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -22391,9 +23525,12 @@
         <v>0.15808</v>
       </c>
       <c r="Q378" s="1" t="n">
+        <v>0.15797</v>
+      </c>
+      <c r="R378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="R378" s="1" t="n">
+      <c r="S378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -22449,10 +23586,13 @@
         <v>0.0005929</v>
       </c>
       <c r="Q379" s="1" t="n">
+        <v>0.0005922</v>
+      </c>
+      <c r="R379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="R379" s="1" t="n">
-        <v>0.0005929</v>
+      <c r="S379" s="1" t="n">
+        <v>0.0005922</v>
       </c>
     </row>
     <row r="380">
@@ -22507,9 +23647,12 @@
         <v>0.01015</v>
       </c>
       <c r="Q380" s="1" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="R380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="R380" s="1" t="n">
+      <c r="S380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -22565,9 +23708,12 @@
         <v>0.0254</v>
       </c>
       <c r="Q381" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="R381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="R381" s="1" t="n">
+      <c r="S381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -22623,9 +23769,12 @@
         <v>0.1903</v>
       </c>
       <c r="Q382" s="1" t="n">
+        <v>0.18967</v>
+      </c>
+      <c r="R382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="R382" s="1" t="n">
+      <c r="S382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -22681,9 +23830,12 @@
         <v>0.09214</v>
       </c>
       <c r="Q383" s="1" t="n">
+        <v>0.09224</v>
+      </c>
+      <c r="R383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="R383" s="1" t="n">
+      <c r="S383" s="1" t="n">
         <v>0.09214</v>
       </c>
     </row>
@@ -22739,9 +23891,12 @@
         <v>0.03166</v>
       </c>
       <c r="Q384" s="1" t="n">
+        <v>0.03163</v>
+      </c>
+      <c r="R384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="R384" s="1" t="n">
+      <c r="S384" s="1" t="n">
         <v>0.03163</v>
       </c>
     </row>
@@ -22797,9 +23952,12 @@
         <v>0.01086</v>
       </c>
       <c r="Q385" s="1" t="n">
+        <v>0.01087</v>
+      </c>
+      <c r="R385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="R385" s="1" t="n">
+      <c r="S385" s="1" t="n">
         <v>0.01086</v>
       </c>
     </row>
@@ -22855,9 +24013,12 @@
         <v>0.05059</v>
       </c>
       <c r="Q386" s="1" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="R386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="R386" s="1" t="n">
+      <c r="S386" s="1" t="n">
         <v>0.05059</v>
       </c>
     </row>
@@ -22913,9 +24074,12 @@
         <v>0.02405</v>
       </c>
       <c r="Q387" s="1" t="n">
+        <v>0.02425</v>
+      </c>
+      <c r="R387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="R387" s="1" t="n">
+      <c r="S387" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -22971,9 +24135,12 @@
         <v>0.007214</v>
       </c>
       <c r="Q388" s="1" t="n">
+        <v>0.007224</v>
+      </c>
+      <c r="R388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="R388" s="1" t="n">
+      <c r="S388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -23029,9 +24196,12 @@
         <v>0.0101</v>
       </c>
       <c r="Q389" s="1" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="R389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="R389" s="1" t="n">
+      <c r="S389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -23087,9 +24257,12 @@
         <v>0.08214</v>
       </c>
       <c r="Q390" s="1" t="n">
+        <v>0.08218</v>
+      </c>
+      <c r="R390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="R390" s="1" t="n">
+      <c r="S390" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -23145,9 +24318,12 @@
         <v>0.5042</v>
       </c>
       <c r="Q391" s="1" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="R391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="R391" s="1" t="n">
+      <c r="S391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -23203,9 +24379,12 @@
         <v>0.1157</v>
       </c>
       <c r="Q392" s="1" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="R392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="R392" s="1" t="n">
+      <c r="S392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -23261,9 +24440,12 @@
         <v>0.00244</v>
       </c>
       <c r="Q393" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="R393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="R393" s="1" t="n">
+      <c r="S393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -23319,9 +24501,12 @@
         <v>0.02108</v>
       </c>
       <c r="Q394" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="R394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="R394" s="1" t="n">
+      <c r="S394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -23377,9 +24562,12 @@
         <v>0.0159</v>
       </c>
       <c r="Q395" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="R395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="R395" s="1" t="n">
+      <c r="S395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -23435,9 +24623,12 @@
         <v>0.1349</v>
       </c>
       <c r="Q396" s="1" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="R396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="R396" s="1" t="n">
+      <c r="S396" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -23493,10 +24684,13 @@
         <v>0.01442</v>
       </c>
       <c r="Q397" s="1" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="R397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="R397" s="1" t="n">
-        <v>0.01442</v>
+      <c r="S397" s="1" t="n">
+        <v>0.0144</v>
       </c>
     </row>
     <row r="398">
@@ -23551,9 +24745,12 @@
         <v>6.679</v>
       </c>
       <c r="Q398" s="1" t="n">
+        <v>6.698</v>
+      </c>
+      <c r="R398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="R398" s="1" t="n">
+      <c r="S398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -23609,10 +24806,13 @@
         <v>0.00937</v>
       </c>
       <c r="Q399" s="1" t="n">
+        <v>0.009363</v>
+      </c>
+      <c r="R399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="R399" s="1" t="n">
-        <v>0.00937</v>
+      <c r="S399" s="1" t="n">
+        <v>0.009363</v>
       </c>
     </row>
     <row r="400">
@@ -23667,9 +24867,12 @@
         <v>0.00126</v>
       </c>
       <c r="Q400" s="1" t="n">
+        <v>0.001256</v>
+      </c>
+      <c r="R400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="R400" s="1" t="n">
+      <c r="S400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -23725,9 +24928,12 @@
         <v>0.0184</v>
       </c>
       <c r="Q401" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="R401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="R401" s="1" t="n">
+      <c r="S401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -23783,9 +24989,12 @@
         <v>0.08447</v>
       </c>
       <c r="Q402" s="1" t="n">
+        <v>0.08454</v>
+      </c>
+      <c r="R402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="R402" s="1" t="n">
+      <c r="S402" s="1" t="n">
         <v>0.08447</v>
       </c>
     </row>
@@ -23841,9 +25050,12 @@
         <v>0.00548</v>
       </c>
       <c r="Q403" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="R403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="R403" s="1" t="n">
+      <c r="S403" s="1" t="n">
         <v>0.00548</v>
       </c>
     </row>
@@ -23899,9 +25111,12 @@
         <v>0.04261</v>
       </c>
       <c r="Q404" s="1" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="R404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="R404" s="1" t="n">
+      <c r="S404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -23957,9 +25172,12 @@
         <v>0.05827</v>
       </c>
       <c r="Q405" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="R405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="R405" s="1" t="n">
+      <c r="S405" s="1" t="n">
         <v>0.05827</v>
       </c>
     </row>
@@ -24015,9 +25233,12 @@
         <v>0.01655</v>
       </c>
       <c r="Q406" s="1" t="n">
+        <v>0.01658</v>
+      </c>
+      <c r="R406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="R406" s="1" t="n">
+      <c r="S406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -24073,9 +25294,12 @@
         <v>0.0424</v>
       </c>
       <c r="Q407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="R407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="R407" s="1" t="n">
+      <c r="S407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -24131,9 +25355,12 @@
         <v>0.01921</v>
       </c>
       <c r="Q408" s="1" t="n">
+        <v>0.01923</v>
+      </c>
+      <c r="R408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="R408" s="1" t="n">
+      <c r="S408" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -24189,9 +25416,12 @@
         <v>0.4435</v>
       </c>
       <c r="Q409" s="1" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="R409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="R409" s="1" t="n">
+      <c r="S409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -24247,9 +25477,12 @@
         <v>0.04382</v>
       </c>
       <c r="Q410" s="1" t="n">
+        <v>0.04384</v>
+      </c>
+      <c r="R410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="R410" s="1" t="n">
+      <c r="S410" s="1" t="n">
         <v>0.04382</v>
       </c>
     </row>
@@ -24305,9 +25538,12 @@
         <v>27.11</v>
       </c>
       <c r="Q411" s="1" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="R411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="R411" s="1" t="n">
+      <c r="S411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -24363,9 +25599,12 @@
         <v>0.03493</v>
       </c>
       <c r="Q412" s="1" t="n">
+        <v>0.03508</v>
+      </c>
+      <c r="R412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="R412" s="1" t="n">
+      <c r="S412" s="1" t="n">
         <v>0.03493</v>
       </c>
     </row>
@@ -24421,9 +25660,12 @@
         <v>0.003388</v>
       </c>
       <c r="Q413" s="1" t="n">
+        <v>0.003389</v>
+      </c>
+      <c r="R413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="R413" s="1" t="n">
+      <c r="S413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -24479,10 +25721,13 @@
         <v>0.1525</v>
       </c>
       <c r="Q414" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="R414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="R414" s="1" t="n">
-        <v>0.1525</v>
+      <c r="S414" s="1" t="n">
+        <v>0.1523</v>
       </c>
     </row>
     <row r="415">
@@ -24537,10 +25782,13 @@
         <v>0.05251</v>
       </c>
       <c r="Q415" s="1" t="n">
+        <v>0.05229</v>
+      </c>
+      <c r="R415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="R415" s="1" t="n">
-        <v>0.0525</v>
+      <c r="S415" s="1" t="n">
+        <v>0.05229</v>
       </c>
     </row>
     <row r="416">
@@ -24595,9 +25843,12 @@
         <v>0.00654</v>
       </c>
       <c r="Q416" s="1" t="n">
+        <v>0.00655</v>
+      </c>
+      <c r="R416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="R416" s="1" t="n">
+      <c r="S416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -24653,10 +25904,13 @@
         <v>0.06027</v>
       </c>
       <c r="Q417" s="1" t="n">
+        <v>0.06025</v>
+      </c>
+      <c r="R417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="R417" s="1" t="n">
-        <v>0.06026</v>
+      <c r="S417" s="1" t="n">
+        <v>0.06025</v>
       </c>
     </row>
     <row r="418">
@@ -24711,9 +25965,12 @@
         <v>0.007992000000000001</v>
       </c>
       <c r="Q418" s="1" t="n">
+        <v>0.008003</v>
+      </c>
+      <c r="R418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="R418" s="1" t="n">
+      <c r="S418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -24769,10 +26026,13 @@
         <v>0.07426000000000001</v>
       </c>
       <c r="Q419" s="1" t="n">
+        <v>0.07414999999999999</v>
+      </c>
+      <c r="R419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="R419" s="1" t="n">
-        <v>0.07425</v>
+      <c r="S419" s="1" t="n">
+        <v>0.07414999999999999</v>
       </c>
     </row>
     <row r="420">
@@ -24827,9 +26087,12 @@
         <v>0.02112</v>
       </c>
       <c r="Q420" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="R420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="R420" s="1" t="n">
+      <c r="S420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -24885,10 +26148,13 @@
         <v>0.06898</v>
       </c>
       <c r="Q421" s="1" t="n">
+        <v>0.06897</v>
+      </c>
+      <c r="R421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="R421" s="1" t="n">
-        <v>0.06898</v>
+      <c r="S421" s="1" t="n">
+        <v>0.06897</v>
       </c>
     </row>
     <row r="422">
@@ -24943,9 +26209,12 @@
         <v>0.01474</v>
       </c>
       <c r="Q422" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="R422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="R422" s="1" t="n">
+      <c r="S422" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -25001,9 +26270,12 @@
         <v>0.00658</v>
       </c>
       <c r="Q423" s="1" t="n">
+        <v>0.006589</v>
+      </c>
+      <c r="R423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="R423" s="1" t="n">
+      <c r="S423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -25059,10 +26331,13 @@
         <v>0.908</v>
       </c>
       <c r="Q424" s="1" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="R424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="R424" s="1" t="n">
-        <v>0.908</v>
+      <c r="S424" s="1" t="n">
+        <v>0.907</v>
       </c>
     </row>
     <row r="425">
@@ -25117,9 +26392,12 @@
         <v>0.03519</v>
       </c>
       <c r="Q425" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="R425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="R425" s="1" t="n">
+      <c r="S425" s="1" t="n">
         <v>0.03519</v>
       </c>
     </row>
@@ -25175,9 +26453,12 @@
         <v>1.794</v>
       </c>
       <c r="Q426" s="1" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="R426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="R426" s="1" t="n">
+      <c r="S426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -25233,9 +26514,12 @@
         <v>0.12797</v>
       </c>
       <c r="Q427" s="1" t="n">
+        <v>0.12809</v>
+      </c>
+      <c r="R427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="R427" s="1" t="n">
+      <c r="S427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -25291,9 +26575,12 @@
         <v>0.05277</v>
       </c>
       <c r="Q428" s="1" t="n">
+        <v>0.05326</v>
+      </c>
+      <c r="R428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="R428" s="1" t="n">
+      <c r="S428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -25349,9 +26636,12 @@
         <v>1.282</v>
       </c>
       <c r="Q429" s="1" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="R429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="R429" s="1" t="n">
+      <c r="S429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -25407,9 +26697,12 @@
         <v>0.07456</v>
       </c>
       <c r="Q430" s="1" t="n">
+        <v>0.07462000000000001</v>
+      </c>
+      <c r="R430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="R430" s="1" t="n">
+      <c r="S430" s="1" t="n">
         <v>0.07456</v>
       </c>
     </row>
@@ -25465,10 +26758,13 @@
         <v>0.1564</v>
       </c>
       <c r="Q431" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="R431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="R431" s="1" t="n">
-        <v>0.1564</v>
+      <c r="S431" s="1" t="n">
+        <v>0.156</v>
       </c>
     </row>
     <row r="432">
@@ -25523,9 +26819,12 @@
         <v>1.439</v>
       </c>
       <c r="Q432" s="1" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="R432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="R432" s="1" t="n">
+      <c r="S432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -25581,9 +26880,12 @@
         <v>3.239</v>
       </c>
       <c r="Q433" s="1" t="n">
+        <v>3.259</v>
+      </c>
+      <c r="R433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="R433" s="1" t="n">
+      <c r="S433" s="1" t="n">
         <v>3.239</v>
       </c>
     </row>
@@ -25639,9 +26941,12 @@
         <v>0.1783</v>
       </c>
       <c r="Q434" s="1" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="R434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="R434" s="1" t="n">
+      <c r="S434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -25697,9 +27002,12 @@
         <v>0.008548</v>
       </c>
       <c r="Q435" s="1" t="n">
+        <v>0.008553</v>
+      </c>
+      <c r="R435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="R435" s="1" t="n">
+      <c r="S435" s="1" t="n">
         <v>0.008548</v>
       </c>
     </row>
@@ -25755,9 +27063,12 @@
         <v>0.2824</v>
       </c>
       <c r="Q436" s="1" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="R436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="R436" s="1" t="n">
+      <c r="S436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -25813,9 +27124,12 @@
         <v>0.03876</v>
       </c>
       <c r="Q437" s="1" t="n">
+        <v>0.03893</v>
+      </c>
+      <c r="R437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="R437" s="1" t="n">
+      <c r="S437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -25871,9 +27185,12 @@
         <v>0.0243</v>
       </c>
       <c r="Q438" s="1" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="R438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="R438" s="1" t="n">
+      <c r="S438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -25929,9 +27246,12 @@
         <v>0.04403</v>
       </c>
       <c r="Q439" s="1" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="R439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="R439" s="1" t="n">
+      <c r="S439" s="1" t="n">
         <v>0.04401</v>
       </c>
     </row>
@@ -25987,9 +27307,12 @@
         <v>0.0005171</v>
       </c>
       <c r="Q440" s="1" t="n">
+        <v>0.0005188</v>
+      </c>
+      <c r="R440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="R440" s="1" t="n">
+      <c r="S440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -26045,9 +27368,12 @@
         <v>0.04413</v>
       </c>
       <c r="Q441" s="1" t="n">
+        <v>0.04461</v>
+      </c>
+      <c r="R441" s="1" t="n">
         <v>0.04546</v>
       </c>
-      <c r="R441" s="1" t="n">
+      <c r="S441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -26103,9 +27429,12 @@
         <v>0.000413</v>
       </c>
       <c r="Q442" s="1" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="R442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="R442" s="1" t="n">
+      <c r="S442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -26161,10 +27490,13 @@
         <v>0.09421</v>
       </c>
       <c r="Q443" s="1" t="n">
+        <v>0.09397</v>
+      </c>
+      <c r="R443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="R443" s="1" t="n">
-        <v>0.09419</v>
+      <c r="S443" s="1" t="n">
+        <v>0.09397</v>
       </c>
     </row>
     <row r="444">
@@ -26219,9 +27551,12 @@
         <v>2.289</v>
       </c>
       <c r="Q444" s="1" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="R444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="R444" s="1" t="n">
+      <c r="S444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -26277,9 +27612,12 @@
         <v>0.2676</v>
       </c>
       <c r="Q445" s="1" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="R445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="R445" s="1" t="n">
+      <c r="S445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -26335,10 +27673,13 @@
         <v>0.0007377</v>
       </c>
       <c r="Q446" s="1" t="n">
+        <v>0.0007376</v>
+      </c>
+      <c r="R446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="R446" s="1" t="n">
-        <v>0.0007377</v>
+      <c r="S446" s="1" t="n">
+        <v>0.0007376</v>
       </c>
     </row>
     <row r="447">
@@ -26393,9 +27734,12 @@
         <v>0.03841</v>
       </c>
       <c r="Q447" s="1" t="n">
+        <v>0.03818</v>
+      </c>
+      <c r="R447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="R447" s="1" t="n">
+      <c r="S447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -26451,9 +27795,12 @@
         <v>0.1769</v>
       </c>
       <c r="Q448" s="1" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="R448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="R448" s="1" t="n">
+      <c r="S448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -26509,9 +27856,12 @@
         <v>0.0427</v>
       </c>
       <c r="Q449" s="1" t="n">
+        <v>0.04285</v>
+      </c>
+      <c r="R449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="R449" s="1" t="n">
+      <c r="S449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -26567,9 +27917,12 @@
         <v>0.0001638</v>
       </c>
       <c r="Q450" s="1" t="n">
+        <v>0.0001641</v>
+      </c>
+      <c r="R450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="R450" s="1" t="n">
+      <c r="S450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -26625,9 +27978,12 @@
         <v>0.03697</v>
       </c>
       <c r="Q451" s="1" t="n">
+        <v>0.03698</v>
+      </c>
+      <c r="R451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="R451" s="1" t="n">
+      <c r="S451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -26683,9 +28039,12 @@
         <v>0.00966</v>
       </c>
       <c r="Q452" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="R452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="R452" s="1" t="n">
+      <c r="S452" s="1" t="n">
         <v>0.00966</v>
       </c>
     </row>
@@ -26741,9 +28100,12 @@
         <v>0.0679</v>
       </c>
       <c r="Q453" s="1" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="R453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="R453" s="1" t="n">
+      <c r="S453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -26799,9 +28161,12 @@
         <v>0.007478</v>
       </c>
       <c r="Q454" s="1" t="n">
+        <v>0.007489</v>
+      </c>
+      <c r="R454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="R454" s="1" t="n">
+      <c r="S454" s="1" t="n">
         <v>0.007478</v>
       </c>
     </row>
@@ -26857,9 +28222,12 @@
         <v>0.003269</v>
       </c>
       <c r="Q455" s="1" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="R455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="R455" s="1" t="n">
+      <c r="S455" s="1" t="n">
         <v>0.003269</v>
       </c>
     </row>
@@ -26915,9 +28283,12 @@
         <v>0.00184</v>
       </c>
       <c r="Q456" s="1" t="n">
+        <v>0.001845</v>
+      </c>
+      <c r="R456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="R456" s="1" t="n">
+      <c r="S456" s="1" t="n">
         <v>0.00184</v>
       </c>
     </row>
@@ -26973,9 +28344,12 @@
         <v>0.0001745</v>
       </c>
       <c r="Q457" s="1" t="n">
+        <v>0.0001749</v>
+      </c>
+      <c r="R457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="R457" s="1" t="n">
+      <c r="S457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -27031,9 +28405,12 @@
         <v>0.0003897</v>
       </c>
       <c r="Q458" s="1" t="n">
+        <v>0.0003889</v>
+      </c>
+      <c r="R458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="R458" s="1" t="n">
+      <c r="S458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -27089,9 +28466,12 @@
         <v>0.01391</v>
       </c>
       <c r="Q459" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="R459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="R459" s="1" t="n">
+      <c r="S459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -27147,9 +28527,12 @@
         <v>0.04564</v>
       </c>
       <c r="Q460" s="1" t="n">
+        <v>0.04566</v>
+      </c>
+      <c r="R460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="R460" s="1" t="n">
+      <c r="S460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -27205,9 +28588,12 @@
         <v>0.2828</v>
       </c>
       <c r="Q461" s="1" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="R461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="R461" s="1" t="n">
+      <c r="S461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -27263,9 +28649,12 @@
         <v>0.006221</v>
       </c>
       <c r="Q462" s="1" t="n">
+        <v>0.006233</v>
+      </c>
+      <c r="R462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="R462" s="1" t="n">
+      <c r="S462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -27321,9 +28710,12 @@
         <v>0.007011</v>
       </c>
       <c r="Q463" s="1" t="n">
+        <v>0.007033</v>
+      </c>
+      <c r="R463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="R463" s="1" t="n">
+      <c r="S463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -27379,9 +28771,12 @@
         <v>0.289</v>
       </c>
       <c r="Q464" s="1" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="R464" s="1" t="n">
         <v>0.289</v>
       </c>
-      <c r="R464" s="1" t="n">
+      <c r="S464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -27437,9 +28832,12 @@
         <v>0.08051</v>
       </c>
       <c r="Q465" s="1" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="R465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="R465" s="1" t="n">
+      <c r="S465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -27495,9 +28893,12 @@
         <v>0.6391</v>
       </c>
       <c r="Q466" s="1" t="n">
+        <v>0.6387</v>
+      </c>
+      <c r="R466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="R466" s="1" t="n">
+      <c r="S466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -27553,9 +28954,12 @@
         <v>0.01471</v>
       </c>
       <c r="Q467" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="R467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="R467" s="1" t="n">
+      <c r="S467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -27611,10 +29015,13 @@
         <v>0.0342</v>
       </c>
       <c r="Q468" s="1" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="R468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="R468" s="1" t="n">
-        <v>0.0342</v>
+      <c r="S468" s="1" t="n">
+        <v>0.03404</v>
       </c>
     </row>
     <row r="469">
@@ -27669,9 +29076,12 @@
         <v>0.1613</v>
       </c>
       <c r="Q469" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="R469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="R469" s="1" t="n">
+      <c r="S469" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -27727,9 +29137,12 @@
         <v>0.408</v>
       </c>
       <c r="Q470" s="1" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="R470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="R470" s="1" t="n">
+      <c r="S470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -27785,10 +29198,13 @@
         <v>0.06859</v>
       </c>
       <c r="Q471" s="1" t="n">
+        <v>0.06854</v>
+      </c>
+      <c r="R471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="R471" s="1" t="n">
-        <v>0.06859</v>
+      <c r="S471" s="1" t="n">
+        <v>0.06854</v>
       </c>
     </row>
     <row r="472">
@@ -27843,10 +29259,13 @@
         <v>0.06549000000000001</v>
       </c>
       <c r="Q472" s="1" t="n">
+        <v>0.06541</v>
+      </c>
+      <c r="R472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="R472" s="1" t="n">
-        <v>0.06549000000000001</v>
+      <c r="S472" s="1" t="n">
+        <v>0.06541</v>
       </c>
     </row>
     <row r="473">
@@ -27901,9 +29320,12 @@
         <v>0.0162</v>
       </c>
       <c r="Q473" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="R473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="R473" s="1" t="n">
+      <c r="S473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -27959,9 +29381,12 @@
         <v>0.2066</v>
       </c>
       <c r="Q474" s="1" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="R474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="R474" s="1" t="n">
+      <c r="S474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -28017,9 +29442,12 @@
         <v>0.0422</v>
       </c>
       <c r="Q475" s="1" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="R475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="R475" s="1" t="n">
+      <c r="S475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -28075,9 +29503,12 @@
         <v>1.567</v>
       </c>
       <c r="Q476" s="1" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="R476" s="1" t="n">
+      <c r="S476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -28133,9 +29564,12 @@
         <v>0.1002</v>
       </c>
       <c r="Q477" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="R477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="R477" s="1" t="n">
+      <c r="S477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -28191,9 +29625,12 @@
         <v>0.001152</v>
       </c>
       <c r="Q478" s="1" t="n">
+        <v>0.001155</v>
+      </c>
+      <c r="R478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="R478" s="1" t="n">
+      <c r="S478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -28249,9 +29686,12 @@
         <v>0.1433</v>
       </c>
       <c r="Q479" s="1" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="R479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="R479" s="1" t="n">
+      <c r="S479" s="1" t="n">
         <v>0.1433</v>
       </c>
     </row>
@@ -28307,9 +29747,12 @@
         <v>0.001726</v>
       </c>
       <c r="Q480" s="1" t="n">
-        <v>0.001734</v>
+        <v>0.001794</v>
       </c>
       <c r="R480" s="1" t="n">
+        <v>0.001794</v>
+      </c>
+      <c r="S480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -28365,10 +29808,13 @@
         <v>0.905</v>
       </c>
       <c r="Q481" s="1" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="R481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="R481" s="1" t="n">
-        <v>0.905</v>
+      <c r="S481" s="1" t="n">
+        <v>0.904</v>
       </c>
     </row>
     <row r="482">
@@ -28423,10 +29869,13 @@
         <v>0.13288</v>
       </c>
       <c r="Q482" s="1" t="n">
+        <v>0.13262</v>
+      </c>
+      <c r="R482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="R482" s="1" t="n">
-        <v>0.13288</v>
+      <c r="S482" s="1" t="n">
+        <v>0.13262</v>
       </c>
     </row>
     <row r="483">
@@ -28481,9 +29930,12 @@
         <v>0.04005</v>
       </c>
       <c r="Q483" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="R483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="R483" s="1" t="n">
+      <c r="S483" s="1" t="n">
         <v>0.04005</v>
       </c>
     </row>
@@ -28539,10 +29991,13 @@
         <v>0.3</v>
       </c>
       <c r="Q484" s="1" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="R484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="R484" s="1" t="n">
-        <v>0.3</v>
+      <c r="S484" s="1" t="n">
+        <v>0.2999</v>
       </c>
     </row>
     <row r="485">
@@ -28597,9 +30052,12 @@
         <v>0.05657</v>
       </c>
       <c r="Q485" s="1" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="R485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="R485" s="1" t="n">
+      <c r="S485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -28655,10 +30113,13 @@
         <v>0.001559</v>
       </c>
       <c r="Q486" s="1" t="n">
+        <v>0.001558</v>
+      </c>
+      <c r="R486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="R486" s="1" t="n">
-        <v>0.001559</v>
+      <c r="S486" s="1" t="n">
+        <v>0.001558</v>
       </c>
     </row>
     <row r="487">
@@ -28713,10 +30174,13 @@
         <v>0.06665</v>
       </c>
       <c r="Q487" s="1" t="n">
+        <v>0.06662</v>
+      </c>
+      <c r="R487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="R487" s="1" t="n">
-        <v>0.06665</v>
+      <c r="S487" s="1" t="n">
+        <v>0.06662</v>
       </c>
     </row>
     <row r="488">
@@ -28771,9 +30235,12 @@
         <v>0.1911</v>
       </c>
       <c r="Q488" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="R488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="R488" s="1" t="n">
+      <c r="S488" s="1" t="n">
         <v>0.1911</v>
       </c>
     </row>
@@ -28829,9 +30296,12 @@
         <v>0.04768</v>
       </c>
       <c r="Q489" s="1" t="n">
+        <v>0.04771</v>
+      </c>
+      <c r="R489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="R489" s="1" t="n">
+      <c r="S489" s="1" t="n">
         <v>0.04768</v>
       </c>
     </row>
@@ -28887,9 +30357,12 @@
         <v>0.139</v>
       </c>
       <c r="Q490" s="1" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="R490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="R490" s="1" t="n">
+      <c r="S490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -28945,9 +30418,12 @@
         <v>0.02227</v>
       </c>
       <c r="Q491" s="1" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="R491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="R491" s="1" t="n">
+      <c r="S491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -29003,9 +30479,12 @@
         <v>0.007706</v>
       </c>
       <c r="Q492" s="1" t="n">
+        <v>0.007711</v>
+      </c>
+      <c r="R492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="R492" s="1" t="n">
+      <c r="S492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -29061,9 +30540,12 @@
         <v>0.0005919</v>
       </c>
       <c r="Q493" s="1" t="n">
+        <v>0.0005927</v>
+      </c>
+      <c r="R493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="R493" s="1" t="n">
+      <c r="S493" s="1" t="n">
         <v>0.0005918</v>
       </c>
     </row>
@@ -29119,9 +30601,12 @@
         <v>3.014</v>
       </c>
       <c r="Q494" s="1" t="n">
+        <v>3.024</v>
+      </c>
+      <c r="R494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="R494" s="1" t="n">
+      <c r="S494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -29177,9 +30662,12 @@
         <v>0.05046</v>
       </c>
       <c r="Q495" s="1" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="R495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="R495" s="1" t="n">
+      <c r="S495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -29235,9 +30723,12 @@
         <v>0.006806</v>
       </c>
       <c r="Q496" s="1" t="n">
+        <v>0.006802</v>
+      </c>
+      <c r="R496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="R496" s="1" t="n">
+      <c r="S496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -29293,9 +30784,12 @@
         <v>1.301</v>
       </c>
       <c r="Q497" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="R497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="R497" s="1" t="n">
+      <c r="S497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -29351,9 +30845,12 @@
         <v>0.03911</v>
       </c>
       <c r="Q498" s="1" t="n">
+        <v>0.03914</v>
+      </c>
+      <c r="R498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="R498" s="1" t="n">
+      <c r="S498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -29409,9 +30906,12 @@
         <v>0.04085</v>
       </c>
       <c r="Q499" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="R499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="R499" s="1" t="n">
+      <c r="S499" s="1" t="n">
         <v>0.04085</v>
       </c>
     </row>
@@ -29467,9 +30967,12 @@
         <v>0.00541</v>
       </c>
       <c r="Q500" s="1" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="R500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="R500" s="1" t="n">
+      <c r="S500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -29525,10 +31028,13 @@
         <v>0.03552</v>
       </c>
       <c r="Q501" s="1" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="R501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="R501" s="1" t="n">
-        <v>0.03552</v>
+      <c r="S501" s="1" t="n">
+        <v>0.03548</v>
       </c>
     </row>
     <row r="502">
@@ -29583,9 +31089,12 @@
         <v>0.07205</v>
       </c>
       <c r="Q502" s="1" t="n">
+        <v>0.07206</v>
+      </c>
+      <c r="R502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="R502" s="1" t="n">
+      <c r="S502" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -29641,9 +31150,12 @@
         <v>0.000742</v>
       </c>
       <c r="Q503" s="1" t="n">
+        <v>0.0007433</v>
+      </c>
+      <c r="R503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="R503" s="1" t="n">
+      <c r="S503" s="1" t="n">
         <v>0.0007412</v>
       </c>
     </row>
@@ -29699,9 +31211,12 @@
         <v>0.01601</v>
       </c>
       <c r="Q504" s="1" t="n">
+        <v>0.016014</v>
+      </c>
+      <c r="R504" s="1" t="n">
         <v>0.016034</v>
       </c>
-      <c r="R504" s="1" t="n">
+      <c r="S504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -29757,9 +31272,12 @@
         <v>0.00702</v>
       </c>
       <c r="Q505" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="R505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="R505" s="1" t="n">
+      <c r="S505" s="1" t="n">
         <v>0.00702</v>
       </c>
     </row>
@@ -29815,10 +31333,13 @@
         <v>0.0253</v>
       </c>
       <c r="Q506" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="R506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="R506" s="1" t="n">
-        <v>0.0253</v>
+      <c r="S506" s="1" t="n">
+        <v>0.0252</v>
       </c>
     </row>
     <row r="507">
@@ -29873,9 +31394,12 @@
         <v>0.001343</v>
       </c>
       <c r="Q507" s="1" t="n">
+        <v>0.001346</v>
+      </c>
+      <c r="R507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="R507" s="1" t="n">
+      <c r="S507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -29931,9 +31455,12 @@
         <v>0.2806</v>
       </c>
       <c r="Q508" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="R508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="R508" s="1" t="n">
+      <c r="S508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -29989,9 +31516,12 @@
         <v>0.1315</v>
       </c>
       <c r="Q509" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="R509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="R509" s="1" t="n">
+      <c r="S509" s="1" t="n">
         <v>0.1314</v>
       </c>
     </row>
@@ -30047,9 +31577,12 @@
         <v>0.04883</v>
       </c>
       <c r="Q510" s="1" t="n">
+        <v>0.04884</v>
+      </c>
+      <c r="R510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="R510" s="1" t="n">
+      <c r="S510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -30105,9 +31638,12 @@
         <v>0.00271</v>
       </c>
       <c r="Q511" s="1" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="R511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="R511" s="1" t="n">
+      <c r="S511" s="1" t="n">
         <v>0.00271</v>
       </c>
     </row>
@@ -30163,9 +31699,12 @@
         <v>0.014989</v>
       </c>
       <c r="Q512" s="1" t="n">
+        <v>0.015044</v>
+      </c>
+      <c r="R512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="R512" s="1" t="n">
+      <c r="S512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -30221,9 +31760,12 @@
         <v>0.6906</v>
       </c>
       <c r="Q513" s="1" t="n">
+        <v>0.6914</v>
+      </c>
+      <c r="R513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="R513" s="1" t="n">
+      <c r="S513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -30279,9 +31821,12 @@
         <v>0.004471</v>
       </c>
       <c r="Q514" s="1" t="n">
+        <v>0.004476</v>
+      </c>
+      <c r="R514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="R514" s="1" t="n">
+      <c r="S514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -30337,9 +31882,12 @@
         <v>0.005016</v>
       </c>
       <c r="Q515" s="1" t="n">
+        <v>0.005019</v>
+      </c>
+      <c r="R515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="R515" s="1" t="n">
+      <c r="S515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -30395,9 +31943,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="Q516" s="1" t="n">
+        <v>0.06327000000000001</v>
+      </c>
+      <c r="R516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="R516" s="1" t="n">
+      <c r="S516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -30453,9 +32004,12 @@
         <v>0.06515</v>
       </c>
       <c r="Q517" s="1" t="n">
+        <v>0.06525</v>
+      </c>
+      <c r="R517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="R517" s="1" t="n">
+      <c r="S517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -30511,9 +32065,12 @@
         <v>0.01198</v>
       </c>
       <c r="Q518" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="R518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="R518" s="1" t="n">
+      <c r="S518" s="1" t="n">
         <v>0.01198</v>
       </c>
     </row>
@@ -30569,9 +32126,12 @@
         <v>0.04733</v>
       </c>
       <c r="Q519" s="1" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="R519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="R519" s="1" t="n">
+      <c r="S519" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -30627,9 +32187,12 @@
         <v>0.04356</v>
       </c>
       <c r="Q520" s="1" t="n">
+        <v>0.04358</v>
+      </c>
+      <c r="R520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="R520" s="1" t="n">
+      <c r="S520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -30685,9 +32248,12 @@
         <v>0.008402</v>
       </c>
       <c r="Q521" s="1" t="n">
+        <v>0.008418999999999999</v>
+      </c>
+      <c r="R521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="R521" s="1" t="n">
+      <c r="S521" s="1" t="n">
         <v>0.008402</v>
       </c>
     </row>
@@ -30743,10 +32309,13 @@
         <v>0.08773</v>
       </c>
       <c r="Q522" s="1" t="n">
+        <v>0.08762</v>
+      </c>
+      <c r="R522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="R522" s="1" t="n">
-        <v>0.08773</v>
+      <c r="S522" s="1" t="n">
+        <v>0.08762</v>
       </c>
     </row>
     <row r="523">
@@ -30801,9 +32370,12 @@
         <v>0.006407</v>
       </c>
       <c r="Q523" s="1" t="n">
+        <v>0.00643</v>
+      </c>
+      <c r="R523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="R523" s="1" t="n">
+      <c r="S523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -30859,9 +32431,12 @@
         <v>0.01628</v>
       </c>
       <c r="Q524" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="R524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="R524" s="1" t="n">
+      <c r="S524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -30917,10 +32492,13 @@
         <v>0.01772</v>
       </c>
       <c r="Q525" s="1" t="n">
+        <v>0.01762</v>
+      </c>
+      <c r="R525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="R525" s="1" t="n">
-        <v>0.01772</v>
+      <c r="S525" s="1" t="n">
+        <v>0.01762</v>
       </c>
     </row>
     <row r="526">
@@ -30975,9 +32553,12 @@
         <v>0.07862</v>
       </c>
       <c r="Q526" s="1" t="n">
+        <v>0.07865</v>
+      </c>
+      <c r="R526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="R526" s="1" t="n">
+      <c r="S526" s="1" t="n">
         <v>0.07862</v>
       </c>
     </row>
@@ -31033,9 +32614,12 @@
         <v>0.01597</v>
       </c>
       <c r="Q527" s="1" t="n">
+        <v>0.01605</v>
+      </c>
+      <c r="R527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="R527" s="1" t="n">
+      <c r="S527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -31091,9 +32675,12 @@
         <v>0.004159</v>
       </c>
       <c r="Q528" s="1" t="n">
+        <v>0.004168</v>
+      </c>
+      <c r="R528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="R528" s="1" t="n">
+      <c r="S528" s="1" t="n">
         <v>0.004159</v>
       </c>
     </row>
@@ -31149,9 +32736,12 @@
         <v>0.003672</v>
       </c>
       <c r="Q529" s="1" t="n">
+        <v>0.003678</v>
+      </c>
+      <c r="R529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="R529" s="1" t="n">
+      <c r="S529" s="1" t="n">
         <v>0.003672</v>
       </c>
     </row>
@@ -31207,9 +32797,12 @@
         <v>1.325</v>
       </c>
       <c r="Q530" s="1" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="R530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="R530" s="1" t="n">
+      <c r="S530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -31265,9 +32858,12 @@
         <v>0.487</v>
       </c>
       <c r="Q531" s="1" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="R531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="R531" s="1" t="n">
+      <c r="S531" s="1" t="n">
         <v>0.487</v>
       </c>
     </row>
@@ -31323,9 +32919,12 @@
         <v>0.03059</v>
       </c>
       <c r="Q532" s="1" t="n">
+        <v>0.03063</v>
+      </c>
+      <c r="R532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="R532" s="1" t="n">
+      <c r="S532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -31381,9 +32980,12 @@
         <v>0.1526</v>
       </c>
       <c r="Q533" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="R533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="R533" s="1" t="n">
+      <c r="S533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -31439,9 +33041,12 @@
         <v>0.05344</v>
       </c>
       <c r="Q534" s="1" t="n">
+        <v>0.05352</v>
+      </c>
+      <c r="R534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="R534" s="1" t="n">
+      <c r="S534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -31497,9 +33102,12 @@
         <v>0.01476</v>
       </c>
       <c r="Q535" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="R535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="R535" s="1" t="n">
+      <c r="S535" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -31555,9 +33163,12 @@
         <v>0.05903</v>
       </c>
       <c r="Q536" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="R536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="R536" s="1" t="n">
+      <c r="S536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -31613,9 +33224,12 @@
         <v>0.05476</v>
       </c>
       <c r="Q537" s="1" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="R537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="R537" s="1" t="n">
+      <c r="S537" s="1" t="n">
         <v>0.05476</v>
       </c>
     </row>
@@ -31671,9 +33285,12 @@
         <v>0.1057</v>
       </c>
       <c r="Q538" s="1" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="R538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="R538" s="1" t="n">
+      <c r="S538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -31729,9 +33346,12 @@
         <v>0.01266</v>
       </c>
       <c r="Q539" s="1" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="R539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="R539" s="1" t="n">
+      <c r="S539" s="1" t="n">
         <v>0.01266</v>
       </c>
     </row>
@@ -31787,9 +33407,12 @@
         <v>0.1725</v>
       </c>
       <c r="Q540" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="R540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="R540" s="1" t="n">
+      <c r="S540" s="1" t="n">
         <v>0.1725</v>
       </c>
     </row>
@@ -31845,9 +33468,12 @@
         <v>0.1228</v>
       </c>
       <c r="Q541" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="R541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="R541" s="1" t="n">
+      <c r="S541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -31903,9 +33529,12 @@
         <v>0.02478</v>
       </c>
       <c r="Q542" s="1" t="n">
+        <v>0.02479</v>
+      </c>
+      <c r="R542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="R542" s="1" t="n">
+      <c r="S542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -31961,9 +33590,12 @@
         <v>0.05858</v>
       </c>
       <c r="Q543" s="1" t="n">
+        <v>0.05852</v>
+      </c>
+      <c r="R543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="R543" s="1" t="n">
+      <c r="S543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S543"/>
+  <dimension ref="A1:T543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -436,8 +436,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,10 +529,15 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>price_04:00</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -592,9 +598,12 @@
         <v>71123.2</v>
       </c>
       <c r="R2" s="1" t="n">
+        <v>71128.7</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -653,9 +662,12 @@
         <v>2102.99</v>
       </c>
       <c r="R3" s="1" t="n">
+        <v>2101</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="T3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -714,9 +726,12 @@
         <v>88.8</v>
       </c>
       <c r="R4" s="1" t="n">
+        <v>88.84</v>
+      </c>
+      <c r="S4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>88.7</v>
       </c>
     </row>
@@ -775,9 +790,12 @@
         <v>3.849</v>
       </c>
       <c r="R5" s="1" t="n">
+        <v>3.834</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="T5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -836,9 +854,12 @@
         <v>1.4009</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="T6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -897,9 +918,12 @@
         <v>0.09592000000000001</v>
       </c>
       <c r="R7" s="1" t="n">
+        <v>0.09596</v>
+      </c>
+      <c r="S7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="T7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -958,9 +982,12 @@
         <v>0.014506</v>
       </c>
       <c r="R8" s="1" t="n">
+        <v>0.014425</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="S8" s="1" t="n">
+      <c r="T8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -1019,9 +1046,12 @@
         <v>657.46</v>
       </c>
       <c r="R9" s="1" t="n">
+        <v>657.2</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="T9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1080,9 +1110,12 @@
         <v>20.209</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>20.288</v>
+        <v>20.308</v>
       </c>
       <c r="S10" s="1" t="n">
+        <v>20.308</v>
+      </c>
+      <c r="T10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1141,9 +1174,12 @@
         <v>0.0033857</v>
       </c>
       <c r="R11" s="1" t="n">
+        <v>0.0033886</v>
+      </c>
+      <c r="S11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="S11" s="1" t="n">
+      <c r="T11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1202,9 +1238,12 @@
         <v>36.576</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>36.704</v>
+        <v>36.735</v>
       </c>
       <c r="S12" s="1" t="n">
+        <v>36.735</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1263,9 +1302,12 @@
         <v>213.03</v>
       </c>
       <c r="R13" s="1" t="n">
+        <v>212.45</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="S13" s="1" t="n">
+      <c r="T13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1324,9 +1366,12 @@
         <v>0.0011178</v>
       </c>
       <c r="R14" s="1" t="n">
+        <v>0.0011213</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="S14" s="1" t="n">
+      <c r="T14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1385,9 +1430,12 @@
         <v>0.31126</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.31126</v>
+        <v>0.31973</v>
       </c>
       <c r="S15" s="1" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="T15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1446,10 +1494,13 @@
         <v>230.07</v>
       </c>
       <c r="R16" s="1" t="n">
+        <v>229.42</v>
+      </c>
+      <c r="S16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="S16" s="1" t="n">
-        <v>230.07</v>
+      <c r="T16" s="1" t="n">
+        <v>229.42</v>
       </c>
     </row>
     <row r="17">
@@ -1507,9 +1558,12 @@
         <v>1.0003</v>
       </c>
       <c r="R17" s="1" t="n">
+        <v>1.0008</v>
+      </c>
+      <c r="S17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="S17" s="1" t="n">
+      <c r="T17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1568,9 +1622,12 @@
         <v>0.267</v>
       </c>
       <c r="R18" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="S18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="S18" s="1" t="n">
+      <c r="T18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1629,9 +1686,12 @@
         <v>9.765000000000001</v>
       </c>
       <c r="R19" s="1" t="n">
+        <v>9.766999999999999</v>
+      </c>
+      <c r="S19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="S19" s="1" t="n">
+      <c r="T19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -1690,10 +1750,13 @@
         <v>5026.79</v>
       </c>
       <c r="R20" s="1" t="n">
+        <v>5019.17</v>
+      </c>
+      <c r="S20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="S20" s="1" t="n">
-        <v>5026.79</v>
+      <c r="T20" s="1" t="n">
+        <v>5019.17</v>
       </c>
     </row>
     <row r="21">
@@ -1751,9 +1814,12 @@
         <v>463.2</v>
       </c>
       <c r="R21" s="1" t="n">
+        <v>462.96</v>
+      </c>
+      <c r="S21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="S21" s="1" t="n">
+      <c r="T21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1812,9 +1878,12 @@
         <v>1.3836</v>
       </c>
       <c r="R22" s="1" t="n">
+        <v>1.3823</v>
+      </c>
+      <c r="S22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="S22" s="1" t="n">
+      <c r="T22" s="1" t="n">
         <v>1.3736</v>
       </c>
     </row>
@@ -1873,9 +1942,12 @@
         <v>1.0617</v>
       </c>
       <c r="R23" s="1" t="n">
+        <v>1.0666</v>
+      </c>
+      <c r="S23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="S23" s="1" t="n">
+      <c r="T23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -1934,9 +2006,12 @@
         <v>1.345</v>
       </c>
       <c r="R24" s="1" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="S24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="S24" s="1" t="n">
+      <c r="T24" s="1" t="n">
         <v>1.343</v>
       </c>
     </row>
@@ -1995,9 +2070,12 @@
         <v>9.125999999999999</v>
       </c>
       <c r="R25" s="1" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="S25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="S25" s="1" t="n">
+      <c r="T25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -2056,9 +2134,12 @@
         <v>0.3702</v>
       </c>
       <c r="R26" s="1" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="S26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="S26" s="1" t="n">
+      <c r="T26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -2117,10 +2198,13 @@
         <v>0.874</v>
       </c>
       <c r="R27" s="1" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="S27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="S27" s="1" t="n">
-        <v>0.874</v>
+      <c r="T27" s="1" t="n">
+        <v>0.872</v>
       </c>
     </row>
     <row r="28">
@@ -2178,9 +2262,12 @@
         <v>1.832</v>
       </c>
       <c r="R28" s="1" t="n">
+        <v>1.835</v>
+      </c>
+      <c r="S28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="S28" s="1" t="n">
+      <c r="T28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2239,9 +2326,12 @@
         <v>0.109</v>
       </c>
       <c r="R29" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="S29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="S29" s="1" t="n">
+      <c r="T29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -2300,9 +2390,12 @@
         <v>0.002015</v>
       </c>
       <c r="R30" s="1" t="n">
+        <v>0.002015</v>
+      </c>
+      <c r="S30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="S30" s="1" t="n">
+      <c r="T30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -2361,9 +2454,12 @@
         <v>1.466</v>
       </c>
       <c r="R31" s="1" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="S31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="S31" s="1" t="n">
+      <c r="T31" s="1" t="n">
         <v>1.466</v>
       </c>
     </row>
@@ -2422,9 +2518,12 @@
         <v>0.1772</v>
       </c>
       <c r="R32" s="1" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="S32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="S32" s="1" t="n">
+      <c r="T32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2483,9 +2582,12 @@
         <v>0.1035</v>
       </c>
       <c r="R33" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="S33" s="1" t="n">
+      <c r="T33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -2544,9 +2646,12 @@
         <v>112.67</v>
       </c>
       <c r="R34" s="1" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="S34" s="1" t="n">
+      <c r="T34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -2605,9 +2710,12 @@
         <v>6.683</v>
       </c>
       <c r="R35" s="1" t="n">
+        <v>6.645</v>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="S35" s="1" t="n">
+      <c r="T35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2666,9 +2774,12 @@
         <v>0.017668</v>
       </c>
       <c r="R36" s="1" t="n">
+        <v>0.017641</v>
+      </c>
+      <c r="S36" s="1" t="n">
         <v>0.017668</v>
       </c>
-      <c r="S36" s="1" t="n">
+      <c r="T36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2727,9 +2838,12 @@
         <v>0.3601</v>
       </c>
       <c r="R37" s="1" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="S37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="S37" s="1" t="n">
+      <c r="T37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -2788,9 +2902,12 @@
         <v>55.45</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="S38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="S38" s="1" t="n">
+      <c r="T38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2849,9 +2966,12 @@
         <v>0.60942</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.61761</v>
+        <v>0.61856</v>
       </c>
       <c r="S39" s="1" t="n">
+        <v>0.61856</v>
+      </c>
+      <c r="T39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2910,9 +3030,12 @@
         <v>4.028</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>4.027</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="S40" s="1" t="n">
+      <c r="T40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -2971,10 +3094,13 @@
         <v>0.04928</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="S41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="S41" s="1" t="n">
-        <v>0.04927</v>
+      <c r="T41" s="1" t="n">
+        <v>0.04921</v>
       </c>
     </row>
     <row r="42">
@@ -3032,10 +3158,13 @@
         <v>0.7000999999999999</v>
       </c>
       <c r="R42" s="1" t="n">
+        <v>0.6995</v>
+      </c>
+      <c r="S42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="S42" s="1" t="n">
-        <v>0.7000999999999999</v>
+      <c r="T42" s="1" t="n">
+        <v>0.6995</v>
       </c>
     </row>
     <row r="43">
@@ -3093,9 +3222,12 @@
         <v>0.22771</v>
       </c>
       <c r="R43" s="1" t="n">
+        <v>0.22809</v>
+      </c>
+      <c r="S43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="S43" s="1" t="n">
+      <c r="T43" s="1" t="n">
         <v>0.22771</v>
       </c>
     </row>
@@ -3154,9 +3286,12 @@
         <v>0.35772</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.3581</v>
+        <v>0.35918</v>
       </c>
       <c r="S44" s="1" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="T44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -3215,9 +3350,12 @@
         <v>0.1682</v>
       </c>
       <c r="R45" s="1" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="S45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="S45" s="1" t="n">
+      <c r="T45" s="1" t="n">
         <v>0.1682</v>
       </c>
     </row>
@@ -3276,9 +3414,12 @@
         <v>0.0262</v>
       </c>
       <c r="R46" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="S46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="S46" s="1" t="n">
+      <c r="T46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -3337,9 +3478,12 @@
         <v>0.005945</v>
       </c>
       <c r="R47" s="1" t="n">
+        <v>0.005953</v>
+      </c>
+      <c r="S47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="S47" s="1" t="n">
+      <c r="T47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -3398,9 +3542,12 @@
         <v>0.00736</v>
       </c>
       <c r="R48" s="1" t="n">
+        <v>0.007372</v>
+      </c>
+      <c r="S48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="S48" s="1" t="n">
+      <c r="T48" s="1" t="n">
         <v>0.007343</v>
       </c>
     </row>
@@ -3459,9 +3606,12 @@
         <v>0.109</v>
       </c>
       <c r="R49" s="1" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="S49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="S49" s="1" t="n">
+      <c r="T49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3520,9 +3670,12 @@
         <v>0.0421</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.0421</v>
+        <v>0.04215</v>
       </c>
       <c r="S50" s="1" t="n">
+        <v>0.04215</v>
+      </c>
+      <c r="T50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -3581,9 +3734,12 @@
         <v>0.1616</v>
       </c>
       <c r="R51" s="1" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="S51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="S51" s="1" t="n">
+      <c r="T51" s="1" t="n">
         <v>0.1614</v>
       </c>
     </row>
@@ -3642,9 +3798,12 @@
         <v>0.00351</v>
       </c>
       <c r="R52" s="1" t="n">
+        <v>0.00353</v>
+      </c>
+      <c r="S52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="S52" s="1" t="n">
+      <c r="T52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -3703,9 +3862,12 @@
         <v>2.613</v>
       </c>
       <c r="R53" s="1" t="n">
+        <v>2.613</v>
+      </c>
+      <c r="S53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="S53" s="1" t="n">
+      <c r="T53" s="1" t="n">
         <v>2.613</v>
       </c>
     </row>
@@ -3764,9 +3926,12 @@
         <v>0.006174</v>
       </c>
       <c r="R54" s="1" t="n">
+        <v>0.006187</v>
+      </c>
+      <c r="S54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="S54" s="1" t="n">
+      <c r="T54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -3825,10 +3990,13 @@
         <v>0.02883</v>
       </c>
       <c r="R55" s="1" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="S55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="S55" s="1" t="n">
-        <v>0.02879</v>
+      <c r="T55" s="1" t="n">
+        <v>0.02875</v>
       </c>
     </row>
     <row r="56">
@@ -3886,9 +4054,12 @@
         <v>0.7335</v>
       </c>
       <c r="R56" s="1" t="n">
+        <v>0.7344000000000001</v>
+      </c>
+      <c r="S56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="S56" s="1" t="n">
+      <c r="T56" s="1" t="n">
         <v>0.7322</v>
       </c>
     </row>
@@ -3947,9 +4118,12 @@
         <v>0.1031</v>
       </c>
       <c r="R57" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="S57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="S57" s="1" t="n">
+      <c r="T57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -4008,9 +4182,12 @@
         <v>0.9372</v>
       </c>
       <c r="R58" s="1" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="S58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="S58" s="1" t="n">
+      <c r="T58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -4069,9 +4246,12 @@
         <v>0.0872</v>
       </c>
       <c r="R59" s="1" t="n">
+        <v>0.08767</v>
+      </c>
+      <c r="S59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="S59" s="1" t="n">
+      <c r="T59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -4130,9 +4310,12 @@
         <v>0.06936</v>
       </c>
       <c r="R60" s="1" t="n">
+        <v>0.06909</v>
+      </c>
+      <c r="S60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="S60" s="1" t="n">
+      <c r="T60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -4191,9 +4374,12 @@
         <v>0.05453</v>
       </c>
       <c r="R61" s="1" t="n">
+        <v>0.05457</v>
+      </c>
+      <c r="S61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="S61" s="1" t="n">
+      <c r="T61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -4252,9 +4438,12 @@
         <v>0.01035</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>0.01036</v>
+        <v>0.010478</v>
       </c>
       <c r="S62" s="1" t="n">
+        <v>0.010478</v>
+      </c>
+      <c r="T62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -4313,9 +4502,12 @@
         <v>0.29147</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>0.29156</v>
+        <v>0.29164</v>
       </c>
       <c r="S63" s="1" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="T63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -4374,9 +4566,12 @@
         <v>0.07475999999999999</v>
       </c>
       <c r="R64" s="1" t="n">
+        <v>0.07548000000000001</v>
+      </c>
+      <c r="S64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="S64" s="1" t="n">
+      <c r="T64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -4435,9 +4630,12 @@
         <v>0.318</v>
       </c>
       <c r="R65" s="1" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="S65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="S65" s="1" t="n">
+      <c r="T65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -4496,9 +4694,12 @@
         <v>0.16238</v>
       </c>
       <c r="R66" s="1" t="n">
+        <v>0.16269</v>
+      </c>
+      <c r="S66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="S66" s="1" t="n">
+      <c r="T66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -4557,9 +4758,12 @@
         <v>0.1199</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>0.12014</v>
+        <v>0.1203</v>
       </c>
       <c r="S67" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="T67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -4618,9 +4822,12 @@
         <v>0.09487</v>
       </c>
       <c r="R68" s="1" t="n">
+        <v>0.09501999999999999</v>
+      </c>
+      <c r="S68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="S68" s="1" t="n">
+      <c r="T68" s="1" t="n">
         <v>0.09487</v>
       </c>
     </row>
@@ -4679,9 +4886,12 @@
         <v>0.1241</v>
       </c>
       <c r="R69" s="1" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="S69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="S69" s="1" t="n">
+      <c r="T69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -4740,9 +4950,12 @@
         <v>8.499000000000001</v>
       </c>
       <c r="R70" s="1" t="n">
+        <v>8.509</v>
+      </c>
+      <c r="S70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="S70" s="1" t="n">
+      <c r="T70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -4801,9 +5014,12 @@
         <v>0.239</v>
       </c>
       <c r="R71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="S71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="S71" s="1" t="n">
+      <c r="T71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -4862,9 +5078,12 @@
         <v>0.04983</v>
       </c>
       <c r="R72" s="1" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="S72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="S72" s="1" t="n">
+      <c r="T72" s="1" t="n">
         <v>0.04983</v>
       </c>
     </row>
@@ -4923,9 +5142,12 @@
         <v>0.05043</v>
       </c>
       <c r="R73" s="1" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="S73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="S73" s="1" t="n">
+      <c r="T73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -4984,10 +5206,13 @@
         <v>0.125</v>
       </c>
       <c r="R74" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="S74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="S74" s="1" t="n">
-        <v>0.1246</v>
+      <c r="T74" s="1" t="n">
+        <v>0.124</v>
       </c>
     </row>
     <row r="75">
@@ -5045,9 +5270,12 @@
         <v>0.04644</v>
       </c>
       <c r="R75" s="1" t="n">
+        <v>0.04669</v>
+      </c>
+      <c r="S75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="S75" s="1" t="n">
+      <c r="T75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -5106,10 +5334,13 @@
         <v>0.06697</v>
       </c>
       <c r="R76" s="1" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="S76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="S76" s="1" t="n">
-        <v>0.06691</v>
+      <c r="T76" s="1" t="n">
+        <v>0.06679</v>
       </c>
     </row>
     <row r="77">
@@ -5167,9 +5398,12 @@
         <v>0.12959</v>
       </c>
       <c r="R77" s="1" t="n">
-        <v>0.12959</v>
+        <v>0.13048</v>
       </c>
       <c r="S77" s="1" t="n">
+        <v>0.13048</v>
+      </c>
+      <c r="T77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -5228,9 +5462,12 @@
         <v>0.1607</v>
       </c>
       <c r="R78" s="1" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="S78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="S78" s="1" t="n">
+      <c r="T78" s="1" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -5289,9 +5526,12 @@
         <v>0.02694</v>
       </c>
       <c r="R79" s="1" t="n">
+        <v>0.02699</v>
+      </c>
+      <c r="S79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="S79" s="1" t="n">
+      <c r="T79" s="1" t="n">
         <v>0.02693</v>
       </c>
     </row>
@@ -5350,9 +5590,12 @@
         <v>358.29</v>
       </c>
       <c r="R80" s="1" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="S80" s="1" t="n">
         <v>358.62</v>
       </c>
-      <c r="S80" s="1" t="n">
+      <c r="T80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -5411,9 +5654,12 @@
         <v>7.04e-05</v>
       </c>
       <c r="R81" s="1" t="n">
+        <v>7.054999999999999e-05</v>
+      </c>
+      <c r="S81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="S81" s="1" t="n">
+      <c r="T81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -5472,9 +5718,12 @@
         <v>0.2657</v>
       </c>
       <c r="R82" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="S82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="S82" s="1" t="n">
+      <c r="T82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -5533,9 +5782,12 @@
         <v>1.1054</v>
       </c>
       <c r="R83" s="1" t="n">
+        <v>1.1056</v>
+      </c>
+      <c r="S83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="S83" s="1" t="n">
+      <c r="T83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -5594,9 +5846,12 @@
         <v>0.3509</v>
       </c>
       <c r="R84" s="1" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="S84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="S84" s="1" t="n">
+      <c r="T84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -5655,9 +5910,12 @@
         <v>1.9784</v>
       </c>
       <c r="R85" s="1" t="n">
+        <v>1.9854</v>
+      </c>
+      <c r="S85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="S85" s="1" t="n">
+      <c r="T85" s="1" t="n">
         <v>1.9784</v>
       </c>
     </row>
@@ -5716,9 +5974,12 @@
         <v>1.3184</v>
       </c>
       <c r="R86" s="1" t="n">
+        <v>1.3189</v>
+      </c>
+      <c r="S86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="S86" s="1" t="n">
+      <c r="T86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -5777,9 +6038,12 @@
         <v>32.52</v>
       </c>
       <c r="R87" s="1" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="S87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="S87" s="1" t="n">
+      <c r="T87" s="1" t="n">
         <v>32.52</v>
       </c>
     </row>
@@ -5838,9 +6102,12 @@
         <v>0.009429999999999999</v>
       </c>
       <c r="R88" s="1" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="S88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="S88" s="1" t="n">
+      <c r="T88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -5899,10 +6166,13 @@
         <v>0.01805</v>
       </c>
       <c r="R89" s="1" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="S89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="S89" s="1" t="n">
-        <v>0.01805</v>
+      <c r="T89" s="1" t="n">
+        <v>0.01798</v>
       </c>
     </row>
     <row r="90">
@@ -5960,10 +6230,13 @@
         <v>0.03477</v>
       </c>
       <c r="R90" s="1" t="n">
+        <v>0.03468</v>
+      </c>
+      <c r="S90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="S90" s="1" t="n">
-        <v>0.03477</v>
+      <c r="T90" s="1" t="n">
+        <v>0.03468</v>
       </c>
     </row>
     <row r="91">
@@ -6021,10 +6294,13 @@
         <v>0.0118</v>
       </c>
       <c r="R91" s="1" t="n">
+        <v>0.01178</v>
+      </c>
+      <c r="S91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="S91" s="1" t="n">
-        <v>0.01179</v>
+      <c r="T91" s="1" t="n">
+        <v>0.01178</v>
       </c>
     </row>
     <row r="92">
@@ -6082,9 +6358,12 @@
         <v>3.094</v>
       </c>
       <c r="R92" s="1" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="S92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="S92" s="1" t="n">
+      <c r="T92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -6143,9 +6422,12 @@
         <v>0.00557</v>
       </c>
       <c r="R93" s="1" t="n">
+        <v>0.005571</v>
+      </c>
+      <c r="S93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="S93" s="1" t="n">
+      <c r="T93" s="1" t="n">
         <v>0.00557</v>
       </c>
     </row>
@@ -6204,9 +6486,12 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="R94" s="1" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="S94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="S94" s="1" t="n">
+      <c r="T94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -6268,6 +6553,9 @@
         <v>0.6098</v>
       </c>
       <c r="S95" s="1" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="T95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -6326,9 +6614,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="R96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="S96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="S96" s="1" t="n">
+      <c r="T96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -6387,10 +6678,13 @@
         <v>1.103</v>
       </c>
       <c r="R97" s="1" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="S97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="S97" s="1" t="n">
-        <v>1.103</v>
+      <c r="T97" s="1" t="n">
+        <v>1.102</v>
       </c>
     </row>
     <row r="98">
@@ -6448,9 +6742,12 @@
         <v>0.25409</v>
       </c>
       <c r="R98" s="1" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="S98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="S98" s="1" t="n">
+      <c r="T98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -6509,9 +6806,12 @@
         <v>1.142</v>
       </c>
       <c r="R99" s="1" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="S99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="S99" s="1" t="n">
+      <c r="T99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -6570,9 +6870,12 @@
         <v>1.853</v>
       </c>
       <c r="R100" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="S100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="S100" s="1" t="n">
+      <c r="T100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -6631,9 +6934,12 @@
         <v>0.01582</v>
       </c>
       <c r="R101" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="S101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="S101" s="1" t="n">
+      <c r="T101" s="1" t="n">
         <v>0.01575</v>
       </c>
     </row>
@@ -6692,9 +6998,12 @@
         <v>0.10155</v>
       </c>
       <c r="R102" s="1" t="n">
+        <v>0.10155</v>
+      </c>
+      <c r="S102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="S102" s="1" t="n">
+      <c r="T102" s="1" t="n">
         <v>0.10155</v>
       </c>
     </row>
@@ -6753,9 +7062,12 @@
         <v>0.0005953</v>
       </c>
       <c r="R103" s="1" t="n">
+        <v>0.0005957</v>
+      </c>
+      <c r="S103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="S103" s="1" t="n">
+      <c r="T103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -6814,9 +7126,12 @@
         <v>0.0005876</v>
       </c>
       <c r="R104" s="1" t="n">
-        <v>0.0005917</v>
+        <v>0.0005932</v>
       </c>
       <c r="S104" s="1" t="n">
+        <v>0.0005932</v>
+      </c>
+      <c r="T104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -6875,10 +7190,13 @@
         <v>0.003229</v>
       </c>
       <c r="R105" s="1" t="n">
+        <v>0.003216</v>
+      </c>
+      <c r="S105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="S105" s="1" t="n">
-        <v>0.003229</v>
+      <c r="T105" s="1" t="n">
+        <v>0.003216</v>
       </c>
     </row>
     <row r="106">
@@ -6936,9 +7254,12 @@
         <v>2.573</v>
       </c>
       <c r="R106" s="1" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="S106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="S106" s="1" t="n">
+      <c r="T106" s="1" t="n">
         <v>2.572</v>
       </c>
     </row>
@@ -6997,9 +7318,12 @@
         <v>0.1656</v>
       </c>
       <c r="R107" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="S107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="S107" s="1" t="n">
+      <c r="T107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -7058,9 +7382,12 @@
         <v>0.09629</v>
       </c>
       <c r="R108" s="1" t="n">
+        <v>0.09617000000000001</v>
+      </c>
+      <c r="S108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="S108" s="1" t="n">
+      <c r="T108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -7119,9 +7446,12 @@
         <v>0.02206</v>
       </c>
       <c r="R109" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="S109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="S109" s="1" t="n">
+      <c r="T109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -7180,9 +7510,12 @@
         <v>0.2894</v>
       </c>
       <c r="R110" s="1" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="S110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="S110" s="1" t="n">
+      <c r="T110" s="1" t="n">
         <v>0.2894</v>
       </c>
     </row>
@@ -7241,9 +7574,12 @@
         <v>0.05665</v>
       </c>
       <c r="R111" s="1" t="n">
+        <v>0.05688</v>
+      </c>
+      <c r="S111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="S111" s="1" t="n">
+      <c r="T111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -7302,9 +7638,12 @@
         <v>0.3009</v>
       </c>
       <c r="R112" s="1" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="S112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="S112" s="1" t="n">
+      <c r="T112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -7363,9 +7702,12 @@
         <v>18.58</v>
       </c>
       <c r="R113" s="1" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="S113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="S113" s="1" t="n">
+      <c r="T113" s="1" t="n">
         <v>18.53</v>
       </c>
     </row>
@@ -7424,9 +7766,12 @@
         <v>0.12686</v>
       </c>
       <c r="R114" s="1" t="n">
+        <v>0.12665</v>
+      </c>
+      <c r="S114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="S114" s="1" t="n">
+      <c r="T114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -7485,9 +7830,12 @@
         <v>0.01577</v>
       </c>
       <c r="R115" s="1" t="n">
+        <v>0.01569</v>
+      </c>
+      <c r="S115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="S115" s="1" t="n">
+      <c r="T115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -7546,9 +7894,12 @@
         <v>0.08445999999999999</v>
       </c>
       <c r="R116" s="1" t="n">
+        <v>0.08461</v>
+      </c>
+      <c r="S116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="S116" s="1" t="n">
+      <c r="T116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -7607,9 +7958,12 @@
         <v>0.046928</v>
       </c>
       <c r="R117" s="1" t="n">
+        <v>0.046858</v>
+      </c>
+      <c r="S117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="S117" s="1" t="n">
+      <c r="T117" s="1" t="n">
         <v>0.046846</v>
       </c>
     </row>
@@ -7668,9 +8022,12 @@
         <v>0.0471</v>
       </c>
       <c r="R118" s="1" t="n">
+        <v>0.04711</v>
+      </c>
+      <c r="S118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="S118" s="1" t="n">
+      <c r="T118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -7729,9 +8086,12 @@
         <v>0.04028</v>
       </c>
       <c r="R119" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="S119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="S119" s="1" t="n">
+      <c r="T119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -7790,9 +8150,12 @@
         <v>0.14441</v>
       </c>
       <c r="R120" s="1" t="n">
+        <v>0.14435</v>
+      </c>
+      <c r="S120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="S120" s="1" t="n">
+      <c r="T120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -7851,9 +8214,12 @@
         <v>0.1252</v>
       </c>
       <c r="R121" s="1" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="S121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="S121" s="1" t="n">
+      <c r="T121" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -7912,9 +8278,12 @@
         <v>1.853</v>
       </c>
       <c r="R122" s="1" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="S122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="S122" s="1" t="n">
+      <c r="T122" s="1" t="n">
         <v>1.851</v>
       </c>
     </row>
@@ -7973,9 +8342,12 @@
         <v>0.03006</v>
       </c>
       <c r="R123" s="1" t="n">
+        <v>0.03006</v>
+      </c>
+      <c r="S123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="S123" s="1" t="n">
+      <c r="T123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -8034,9 +8406,12 @@
         <v>0.13267</v>
       </c>
       <c r="R124" s="1" t="n">
+        <v>0.13289</v>
+      </c>
+      <c r="S124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="S124" s="1" t="n">
+      <c r="T124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -8095,10 +8470,13 @@
         <v>0.04085</v>
       </c>
       <c r="R125" s="1" t="n">
+        <v>0.04075</v>
+      </c>
+      <c r="S125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="S125" s="1" t="n">
-        <v>0.0408</v>
+      <c r="T125" s="1" t="n">
+        <v>0.04075</v>
       </c>
     </row>
     <row r="126">
@@ -8156,9 +8534,12 @@
         <v>0.1144</v>
       </c>
       <c r="R126" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="S126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="S126" s="1" t="n">
+      <c r="T126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -8217,9 +8598,12 @@
         <v>0.5216</v>
       </c>
       <c r="R127" s="1" t="n">
-        <v>0.5216</v>
+        <v>0.5286</v>
       </c>
       <c r="S127" s="1" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="T127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -8278,9 +8662,12 @@
         <v>0.03794</v>
       </c>
       <c r="R128" s="1" t="n">
+        <v>0.03796</v>
+      </c>
+      <c r="S128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="S128" s="1" t="n">
+      <c r="T128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -8339,9 +8726,12 @@
         <v>0.795</v>
       </c>
       <c r="R129" s="1" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="S129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="S129" s="1" t="n">
+      <c r="T129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -8400,9 +8790,12 @@
         <v>0.03444</v>
       </c>
       <c r="R130" s="1" t="n">
+        <v>0.03453</v>
+      </c>
+      <c r="S130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="S130" s="1" t="n">
+      <c r="T130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -8461,9 +8854,12 @@
         <v>0.4235</v>
       </c>
       <c r="R131" s="1" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="S131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="S131" s="1" t="n">
+      <c r="T131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -8522,9 +8918,12 @@
         <v>0.04326</v>
       </c>
       <c r="R132" s="1" t="n">
+        <v>0.04328</v>
+      </c>
+      <c r="S132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="S132" s="1" t="n">
+      <c r="T132" s="1" t="n">
         <v>0.04309</v>
       </c>
     </row>
@@ -8583,9 +8982,12 @@
         <v>1.2814</v>
       </c>
       <c r="R133" s="1" t="n">
+        <v>1.2805</v>
+      </c>
+      <c r="S133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="S133" s="1" t="n">
+      <c r="T133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -8644,9 +9046,12 @@
         <v>0.02178</v>
       </c>
       <c r="R134" s="1" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="S134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="S134" s="1" t="n">
+      <c r="T134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -8705,9 +9110,12 @@
         <v>0.000457</v>
       </c>
       <c r="R135" s="1" t="n">
+        <v>0.0004567</v>
+      </c>
+      <c r="S135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="S135" s="1" t="n">
+      <c r="T135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -8766,9 +9174,12 @@
         <v>0.0019</v>
       </c>
       <c r="R136" s="1" t="n">
+        <v>0.001899</v>
+      </c>
+      <c r="S136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="S136" s="1" t="n">
+      <c r="T136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -8827,9 +9238,12 @@
         <v>0.3141</v>
       </c>
       <c r="R137" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="S137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="S137" s="1" t="n">
+      <c r="T137" s="1" t="n">
         <v>0.3136</v>
       </c>
     </row>
@@ -8888,9 +9302,12 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="R138" s="1" t="n">
+        <v>0.5632</v>
+      </c>
+      <c r="S138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="S138" s="1" t="n">
+      <c r="T138" s="1" t="n">
         <v>0.5629999999999999</v>
       </c>
     </row>
@@ -8949,9 +9366,12 @@
         <v>0.02121</v>
       </c>
       <c r="R139" s="1" t="n">
+        <v>0.02132</v>
+      </c>
+      <c r="S139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="S139" s="1" t="n">
+      <c r="T139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -9010,10 +9430,13 @@
         <v>0.07986</v>
       </c>
       <c r="R140" s="1" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="S140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="S140" s="1" t="n">
-        <v>0.07979</v>
+      <c r="T140" s="1" t="n">
+        <v>0.0796</v>
       </c>
     </row>
     <row r="141">
@@ -9071,9 +9494,12 @@
         <v>0.001505</v>
       </c>
       <c r="R141" s="1" t="n">
+        <v>0.001516</v>
+      </c>
+      <c r="S141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="S141" s="1" t="n">
+      <c r="T141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -9132,9 +9558,12 @@
         <v>0.4478</v>
       </c>
       <c r="R142" s="1" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="S142" s="1" t="n">
         <v>0.4489</v>
       </c>
-      <c r="S142" s="1" t="n">
+      <c r="T142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -9193,9 +9622,12 @@
         <v>0.030027</v>
       </c>
       <c r="R143" s="1" t="n">
+        <v>0.029994</v>
+      </c>
+      <c r="S143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="S143" s="1" t="n">
+      <c r="T143" s="1" t="n">
         <v>0.029913</v>
       </c>
     </row>
@@ -9254,9 +9686,12 @@
         <v>0.000225</v>
       </c>
       <c r="R144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="S144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="S144" s="1" t="n">
+      <c r="T144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -9315,9 +9750,12 @@
         <v>0.03575</v>
       </c>
       <c r="R145" s="1" t="n">
+        <v>0.03541</v>
+      </c>
+      <c r="S145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="S145" s="1" t="n">
+      <c r="T145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -9376,9 +9814,12 @@
         <v>0.11645</v>
       </c>
       <c r="R146" s="1" t="n">
+        <v>0.11631</v>
+      </c>
+      <c r="S146" s="1" t="n">
         <v>0.11649</v>
       </c>
-      <c r="S146" s="1" t="n">
+      <c r="T146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -9440,6 +9881,9 @@
         <v>0.02231</v>
       </c>
       <c r="S147" s="1" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="T147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -9498,9 +9942,12 @@
         <v>1.4116</v>
       </c>
       <c r="R148" s="1" t="n">
+        <v>1.4122</v>
+      </c>
+      <c r="S148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="S148" s="1" t="n">
+      <c r="T148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -9559,9 +10006,12 @@
         <v>1.8688</v>
       </c>
       <c r="R149" s="1" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="S149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="S149" s="1" t="n">
+      <c r="T149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -9620,10 +10070,13 @@
         <v>0.095</v>
       </c>
       <c r="R150" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="S150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="S150" s="1" t="n">
-        <v>0.095</v>
+      <c r="T150" s="1" t="n">
+        <v>0.094</v>
       </c>
     </row>
     <row r="151">
@@ -9681,9 +10134,12 @@
         <v>4.632</v>
       </c>
       <c r="R151" s="1" t="n">
-        <v>4.647</v>
+        <v>4.653</v>
       </c>
       <c r="S151" s="1" t="n">
+        <v>4.653</v>
+      </c>
+      <c r="T151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -9742,9 +10198,12 @@
         <v>5.511</v>
       </c>
       <c r="R152" s="1" t="n">
+        <v>5.516</v>
+      </c>
+      <c r="S152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="S152" s="1" t="n">
+      <c r="T152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -9803,9 +10262,12 @@
         <v>0.3184</v>
       </c>
       <c r="R153" s="1" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="S153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="S153" s="1" t="n">
+      <c r="T153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -9864,9 +10326,12 @@
         <v>0.5825</v>
       </c>
       <c r="R154" s="1" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="S154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="S154" s="1" t="n">
+      <c r="T154" s="1" t="n">
         <v>0.5825</v>
       </c>
     </row>
@@ -9925,9 +10390,12 @@
         <v>0.01274</v>
       </c>
       <c r="R155" s="1" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="S155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="S155" s="1" t="n">
+      <c r="T155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -9986,9 +10454,12 @@
         <v>0.0974</v>
       </c>
       <c r="R156" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="S156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="S156" s="1" t="n">
+      <c r="T156" s="1" t="n">
         <v>0.0974</v>
       </c>
     </row>
@@ -10047,9 +10518,12 @@
         <v>16.372</v>
       </c>
       <c r="R157" s="1" t="n">
+        <v>16.409</v>
+      </c>
+      <c r="S157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="S157" s="1" t="n">
+      <c r="T157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -10108,9 +10582,12 @@
         <v>0.05538</v>
       </c>
       <c r="R158" s="1" t="n">
+        <v>0.05552</v>
+      </c>
+      <c r="S158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="S158" s="1" t="n">
+      <c r="T158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -10169,9 +10646,12 @@
         <v>28.65</v>
       </c>
       <c r="R159" s="1" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="S159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="S159" s="1" t="n">
+      <c r="T159" s="1" t="n">
         <v>28.65</v>
       </c>
     </row>
@@ -10230,9 +10710,12 @@
         <v>0.02122</v>
       </c>
       <c r="R160" s="1" t="n">
+        <v>0.02123</v>
+      </c>
+      <c r="S160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="S160" s="1" t="n">
+      <c r="T160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -10291,9 +10774,12 @@
         <v>0.0006503</v>
       </c>
       <c r="R161" s="1" t="n">
+        <v>0.0006511000000000001</v>
+      </c>
+      <c r="S161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="S161" s="1" t="n">
+      <c r="T161" s="1" t="n">
         <v>0.0006503</v>
       </c>
     </row>
@@ -10352,9 +10838,12 @@
         <v>0.3785</v>
       </c>
       <c r="R162" s="1" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="S162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="S162" s="1" t="n">
+      <c r="T162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -10413,9 +10902,12 @@
         <v>0.191</v>
       </c>
       <c r="R163" s="1" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="S163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="S163" s="1" t="n">
+      <c r="T163" s="1" t="n">
         <v>0.1908</v>
       </c>
     </row>
@@ -10474,9 +10966,12 @@
         <v>0.316</v>
       </c>
       <c r="R164" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="S164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="S164" s="1" t="n">
+      <c r="T164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -10535,9 +11030,12 @@
         <v>0.371</v>
       </c>
       <c r="R165" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="S165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="S165" s="1" t="n">
+      <c r="T165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -10596,9 +11094,12 @@
         <v>0.02236</v>
       </c>
       <c r="R166" s="1" t="n">
+        <v>0.02238</v>
+      </c>
+      <c r="S166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="S166" s="1" t="n">
+      <c r="T166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -10657,9 +11158,12 @@
         <v>0.007264</v>
       </c>
       <c r="R167" s="1" t="n">
+        <v>0.007267</v>
+      </c>
+      <c r="S167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="S167" s="1" t="n">
+      <c r="T167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -10718,10 +11222,13 @@
         <v>0.01337</v>
       </c>
       <c r="R168" s="1" t="n">
+        <v>0.01332</v>
+      </c>
+      <c r="S168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="S168" s="1" t="n">
-        <v>0.01337</v>
+      <c r="T168" s="1" t="n">
+        <v>0.01332</v>
       </c>
     </row>
     <row r="169">
@@ -10779,9 +11286,12 @@
         <v>0.253</v>
       </c>
       <c r="R169" s="1" t="n">
+        <v>0.25398</v>
+      </c>
+      <c r="S169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="S169" s="1" t="n">
+      <c r="T169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -10840,9 +11350,12 @@
         <v>0.02156</v>
       </c>
       <c r="R170" s="1" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="S170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="S170" s="1" t="n">
+      <c r="T170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -10901,9 +11414,12 @@
         <v>0.171</v>
       </c>
       <c r="R171" s="1" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="S171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="S171" s="1" t="n">
+      <c r="T171" s="1" t="n">
         <v>0.171</v>
       </c>
     </row>
@@ -10962,9 +11478,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="R172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="S172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="S172" s="1" t="n">
+      <c r="T172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -11023,9 +11542,12 @@
         <v>0.00467</v>
       </c>
       <c r="R173" s="1" t="n">
+        <v>0.00467</v>
+      </c>
+      <c r="S173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="S173" s="1" t="n">
+      <c r="T173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -11084,9 +11606,12 @@
         <v>0.4363</v>
       </c>
       <c r="R174" s="1" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="S174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="S174" s="1" t="n">
+      <c r="T174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -11145,9 +11670,12 @@
         <v>0.08995</v>
       </c>
       <c r="R175" s="1" t="n">
+        <v>0.09013</v>
+      </c>
+      <c r="S175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="S175" s="1" t="n">
+      <c r="T175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -11206,9 +11734,12 @@
         <v>0.2459</v>
       </c>
       <c r="R176" s="1" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="S176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="S176" s="1" t="n">
+      <c r="T176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -11267,9 +11798,12 @@
         <v>0.0191</v>
       </c>
       <c r="R177" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="S177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="S177" s="1" t="n">
+      <c r="T177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -11328,9 +11862,12 @@
         <v>6.116</v>
       </c>
       <c r="R178" s="1" t="n">
+        <v>6.114</v>
+      </c>
+      <c r="S178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="S178" s="1" t="n">
+      <c r="T178" s="1" t="n">
         <v>6.108</v>
       </c>
     </row>
@@ -11389,9 +11926,12 @@
         <v>0.137</v>
       </c>
       <c r="R179" s="1" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="S179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="S179" s="1" t="n">
+      <c r="T179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -11450,9 +11990,12 @@
         <v>0.00497</v>
       </c>
       <c r="R180" s="1" t="n">
+        <v>0.004989</v>
+      </c>
+      <c r="S180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="S180" s="1" t="n">
+      <c r="T180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -11511,9 +12054,12 @@
         <v>0.01185</v>
       </c>
       <c r="R181" s="1" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="S181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="S181" s="1" t="n">
+      <c r="T181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -11572,9 +12118,12 @@
         <v>0.00736</v>
       </c>
       <c r="R182" s="1" t="n">
+        <v>0.007376</v>
+      </c>
+      <c r="S182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="S182" s="1" t="n">
+      <c r="T182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -11633,9 +12182,12 @@
         <v>0.13061</v>
       </c>
       <c r="R183" s="1" t="n">
+        <v>0.13039</v>
+      </c>
+      <c r="S183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="S183" s="1" t="n">
+      <c r="T183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -11694,9 +12246,12 @@
         <v>0.09513000000000001</v>
       </c>
       <c r="R184" s="1" t="n">
+        <v>0.09585</v>
+      </c>
+      <c r="S184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="S184" s="1" t="n">
+      <c r="T184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -11755,9 +12310,12 @@
         <v>0.00751</v>
       </c>
       <c r="R185" s="1" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="S185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="S185" s="1" t="n">
+      <c r="T185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -11816,9 +12374,12 @@
         <v>0.04859</v>
       </c>
       <c r="R186" s="1" t="n">
+        <v>0.04864</v>
+      </c>
+      <c r="S186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="S186" s="1" t="n">
+      <c r="T186" s="1" t="n">
         <v>0.04851</v>
       </c>
     </row>
@@ -11877,9 +12438,12 @@
         <v>0.02663</v>
       </c>
       <c r="R187" s="1" t="n">
+        <v>0.02673</v>
+      </c>
+      <c r="S187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="S187" s="1" t="n">
+      <c r="T187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -11938,9 +12502,12 @@
         <v>0.003282</v>
       </c>
       <c r="R188" s="1" t="n">
+        <v>0.003283</v>
+      </c>
+      <c r="S188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="S188" s="1" t="n">
+      <c r="T188" s="1" t="n">
         <v>0.003282</v>
       </c>
     </row>
@@ -11999,9 +12566,12 @@
         <v>0.2853</v>
       </c>
       <c r="R189" s="1" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="S189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="S189" s="1" t="n">
+      <c r="T189" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -12060,9 +12630,12 @@
         <v>0.01784</v>
       </c>
       <c r="R190" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="S190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="S190" s="1" t="n">
+      <c r="T190" s="1" t="n">
         <v>0.01783</v>
       </c>
     </row>
@@ -12121,9 +12694,12 @@
         <v>0.2565</v>
       </c>
       <c r="R191" s="1" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="S191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="S191" s="1" t="n">
+      <c r="T191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -12182,9 +12758,12 @@
         <v>0.03802</v>
       </c>
       <c r="R192" s="1" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="S192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="S192" s="1" t="n">
+      <c r="T192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -12243,9 +12822,12 @@
         <v>0.0002207</v>
       </c>
       <c r="R193" s="1" t="n">
+        <v>0.0002207</v>
+      </c>
+      <c r="S193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="S193" s="1" t="n">
+      <c r="T193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -12304,9 +12886,12 @@
         <v>4.086</v>
       </c>
       <c r="R194" s="1" t="n">
+        <v>4.081</v>
+      </c>
+      <c r="S194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="S194" s="1" t="n">
+      <c r="T194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -12365,9 +12950,12 @@
         <v>0.9994</v>
       </c>
       <c r="R195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="S195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="S195" s="1" t="n">
+      <c r="T195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -12426,9 +13014,12 @@
         <v>4.288</v>
       </c>
       <c r="R196" s="1" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="S196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="S196" s="1" t="n">
+      <c r="T196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -12487,9 +13078,12 @@
         <v>0.15125</v>
       </c>
       <c r="R197" s="1" t="n">
+        <v>0.15078</v>
+      </c>
+      <c r="S197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="S197" s="1" t="n">
+      <c r="T197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -12548,9 +13142,12 @@
         <v>0.007723</v>
       </c>
       <c r="R198" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="S198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="S198" s="1" t="n">
+      <c r="T198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -12609,9 +13206,12 @@
         <v>0.4492</v>
       </c>
       <c r="R199" s="1" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="S199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="S199" s="1" t="n">
+      <c r="T199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -12670,9 +13270,12 @@
         <v>0.5857</v>
       </c>
       <c r="R200" s="1" t="n">
+        <v>0.5851</v>
+      </c>
+      <c r="S200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="S200" s="1" t="n">
+      <c r="T200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -12731,9 +13334,12 @@
         <v>0.0925</v>
       </c>
       <c r="R201" s="1" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="S201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="S201" s="1" t="n">
+      <c r="T201" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -12792,9 +13398,12 @@
         <v>0.06004</v>
       </c>
       <c r="R202" s="1" t="n">
+        <v>0.06008</v>
+      </c>
+      <c r="S202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="S202" s="1" t="n">
+      <c r="T202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -12853,9 +13462,12 @@
         <v>0.008240000000000001</v>
       </c>
       <c r="R203" s="1" t="n">
+        <v>0.008240000000000001</v>
+      </c>
+      <c r="S203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="S203" s="1" t="n">
+      <c r="T203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -12914,9 +13526,12 @@
         <v>0.00412</v>
       </c>
       <c r="R204" s="1" t="n">
+        <v>0.00413</v>
+      </c>
+      <c r="S204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="S204" s="1" t="n">
+      <c r="T204" s="1" t="n">
         <v>0.00412</v>
       </c>
     </row>
@@ -12975,9 +13590,12 @@
         <v>0.009083000000000001</v>
       </c>
       <c r="R205" s="1" t="n">
+        <v>0.009122</v>
+      </c>
+      <c r="S205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="S205" s="1" t="n">
+      <c r="T205" s="1" t="n">
         <v>0.009070999999999999</v>
       </c>
     </row>
@@ -13036,9 +13654,12 @@
         <v>0.2375</v>
       </c>
       <c r="R206" s="1" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="S206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="S206" s="1" t="n">
+      <c r="T206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -13097,9 +13718,12 @@
         <v>0.02065</v>
       </c>
       <c r="R207" s="1" t="n">
+        <v>0.02066</v>
+      </c>
+      <c r="S207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="S207" s="1" t="n">
+      <c r="T207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -13158,9 +13782,12 @@
         <v>0.2361</v>
       </c>
       <c r="R208" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="S208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="S208" s="1" t="n">
+      <c r="T208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -13219,9 +13846,12 @@
         <v>0.3584</v>
       </c>
       <c r="R209" s="1" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="S209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="S209" s="1" t="n">
+      <c r="T209" s="1" t="n">
         <v>0.3584</v>
       </c>
     </row>
@@ -13280,9 +13910,12 @@
         <v>0.04257</v>
       </c>
       <c r="R210" s="1" t="n">
+        <v>0.04254</v>
+      </c>
+      <c r="S210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="S210" s="1" t="n">
+      <c r="T210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -13341,9 +13974,12 @@
         <v>0.0004241</v>
       </c>
       <c r="R211" s="1" t="n">
+        <v>0.0004241</v>
+      </c>
+      <c r="S211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="S211" s="1" t="n">
+      <c r="T211" s="1" t="n">
         <v>0.0004237</v>
       </c>
     </row>
@@ -13402,10 +14038,13 @@
         <v>0.02126</v>
       </c>
       <c r="R212" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="S212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="S212" s="1" t="n">
-        <v>0.02126</v>
+      <c r="T212" s="1" t="n">
+        <v>0.02125</v>
       </c>
     </row>
     <row r="213">
@@ -13463,9 +14102,12 @@
         <v>0.1136</v>
       </c>
       <c r="R213" s="1" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="S213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="S213" s="1" t="n">
+      <c r="T213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -13524,9 +14166,12 @@
         <v>0.04188</v>
       </c>
       <c r="R214" s="1" t="n">
+        <v>0.04186</v>
+      </c>
+      <c r="S214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="S214" s="1" t="n">
+      <c r="T214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -13585,9 +14230,12 @@
         <v>0.009844</v>
       </c>
       <c r="R215" s="1" t="n">
+        <v>0.009846000000000001</v>
+      </c>
+      <c r="S215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="S215" s="1" t="n">
+      <c r="T215" s="1" t="n">
         <v>0.009839000000000001</v>
       </c>
     </row>
@@ -13646,9 +14294,12 @@
         <v>0.0636</v>
       </c>
       <c r="R216" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="S216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="S216" s="1" t="n">
+      <c r="T216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -13707,9 +14358,12 @@
         <v>0.004259</v>
       </c>
       <c r="R217" s="1" t="n">
-        <v>0.004266</v>
+        <v>0.004287</v>
       </c>
       <c r="S217" s="1" t="n">
+        <v>0.004287</v>
+      </c>
+      <c r="T217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -13768,9 +14422,12 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="R218" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="S218" s="1" t="n">
+      <c r="T218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -13829,9 +14486,12 @@
         <v>0.02975</v>
       </c>
       <c r="R219" s="1" t="n">
+        <v>0.02954</v>
+      </c>
+      <c r="S219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="S219" s="1" t="n">
+      <c r="T219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -13890,9 +14550,12 @@
         <v>2.284</v>
       </c>
       <c r="R220" s="1" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="S220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="S220" s="1" t="n">
+      <c r="T220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -13951,9 +14614,12 @@
         <v>0.022529</v>
       </c>
       <c r="R221" s="1" t="n">
+        <v>0.022618</v>
+      </c>
+      <c r="S221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="S221" s="1" t="n">
+      <c r="T221" s="1" t="n">
         <v>0.022529</v>
       </c>
     </row>
@@ -14012,9 +14678,12 @@
         <v>0.0368</v>
       </c>
       <c r="R222" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="S222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="S222" s="1" t="n">
+      <c r="T222" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -14073,9 +14742,12 @@
         <v>0.292</v>
       </c>
       <c r="R223" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="S223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="S223" s="1" t="n">
+      <c r="T223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -14134,9 +14806,12 @@
         <v>0.0155</v>
       </c>
       <c r="R224" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="S224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="S224" s="1" t="n">
+      <c r="T224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -14195,9 +14870,12 @@
         <v>0.0004037</v>
       </c>
       <c r="R225" s="1" t="n">
+        <v>0.0004035</v>
+      </c>
+      <c r="S225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="S225" s="1" t="n">
+      <c r="T225" s="1" t="n">
         <v>0.0004032</v>
       </c>
     </row>
@@ -14256,9 +14934,12 @@
         <v>0.08522</v>
       </c>
       <c r="R226" s="1" t="n">
+        <v>0.08535</v>
+      </c>
+      <c r="S226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="S226" s="1" t="n">
+      <c r="T226" s="1" t="n">
         <v>0.08522</v>
       </c>
     </row>
@@ -14317,9 +14998,12 @@
         <v>0.947</v>
       </c>
       <c r="R227" s="1" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="S227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="S227" s="1" t="n">
+      <c r="T227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -14378,9 +15062,12 @@
         <v>0.05439</v>
       </c>
       <c r="R228" s="1" t="n">
+        <v>0.05463</v>
+      </c>
+      <c r="S228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="S228" s="1" t="n">
+      <c r="T228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -14439,9 +15126,12 @@
         <v>0.002</v>
       </c>
       <c r="R229" s="1" t="n">
+        <v>0.002003</v>
+      </c>
+      <c r="S229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="S229" s="1" t="n">
+      <c r="T229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -14500,9 +15190,12 @@
         <v>0.022774</v>
       </c>
       <c r="R230" s="1" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="S230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="S230" s="1" t="n">
+      <c r="T230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -14561,9 +15254,12 @@
         <v>0.05344</v>
       </c>
       <c r="R231" s="1" t="n">
+        <v>0.05348</v>
+      </c>
+      <c r="S231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="S231" s="1" t="n">
+      <c r="T231" s="1" t="n">
         <v>0.05338</v>
       </c>
     </row>
@@ -14622,9 +15318,12 @@
         <v>0.0583</v>
       </c>
       <c r="R232" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="S232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="S232" s="1" t="n">
+      <c r="T232" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -14683,9 +15382,12 @@
         <v>0.001684</v>
       </c>
       <c r="R233" s="1" t="n">
+        <v>0.001686</v>
+      </c>
+      <c r="S233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="S233" s="1" t="n">
+      <c r="T233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -14744,9 +15446,12 @@
         <v>0.005749</v>
       </c>
       <c r="R234" s="1" t="n">
+        <v>0.005737</v>
+      </c>
+      <c r="S234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="S234" s="1" t="n">
+      <c r="T234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -14805,9 +15510,12 @@
         <v>0.12245</v>
       </c>
       <c r="R235" s="1" t="n">
+        <v>0.12265</v>
+      </c>
+      <c r="S235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="S235" s="1" t="n">
+      <c r="T235" s="1" t="n">
         <v>0.12245</v>
       </c>
     </row>
@@ -14866,9 +15574,12 @@
         <v>64.59</v>
       </c>
       <c r="R236" s="1" t="n">
+        <v>64.58</v>
+      </c>
+      <c r="S236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="S236" s="1" t="n">
+      <c r="T236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -14927,9 +15638,12 @@
         <v>0.1008</v>
       </c>
       <c r="R237" s="1" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="S237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="S237" s="1" t="n">
+      <c r="T237" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -14988,9 +15702,12 @@
         <v>0.004014</v>
       </c>
       <c r="R238" s="1" t="n">
+        <v>0.004011</v>
+      </c>
+      <c r="S238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="S238" s="1" t="n">
+      <c r="T238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -15049,10 +15766,13 @@
         <v>0.01512</v>
       </c>
       <c r="R239" s="1" t="n">
+        <v>0.01492</v>
+      </c>
+      <c r="S239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="S239" s="1" t="n">
-        <v>0.01512</v>
+      <c r="T239" s="1" t="n">
+        <v>0.01492</v>
       </c>
     </row>
     <row r="240">
@@ -15110,9 +15830,12 @@
         <v>0.05584</v>
       </c>
       <c r="R240" s="1" t="n">
+        <v>0.05586</v>
+      </c>
+      <c r="S240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="S240" s="1" t="n">
+      <c r="T240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -15171,9 +15894,12 @@
         <v>0.0114</v>
       </c>
       <c r="R241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="S241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="S241" s="1" t="n">
+      <c r="T241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -15232,10 +15958,13 @@
         <v>0.3339</v>
       </c>
       <c r="R242" s="1" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="S242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="S242" s="1" t="n">
-        <v>0.3332</v>
+      <c r="T242" s="1" t="n">
+        <v>0.3321</v>
       </c>
     </row>
     <row r="243">
@@ -15293,9 +16022,12 @@
         <v>0.01222</v>
       </c>
       <c r="R243" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="S243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="S243" s="1" t="n">
+      <c r="T243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -15354,9 +16086,12 @@
         <v>0.07973</v>
       </c>
       <c r="R244" s="1" t="n">
+        <v>0.08006000000000001</v>
+      </c>
+      <c r="S244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="S244" s="1" t="n">
+      <c r="T244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -15415,9 +16150,12 @@
         <v>0.007812</v>
       </c>
       <c r="R245" s="1" t="n">
+        <v>0.007861</v>
+      </c>
+      <c r="S245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="S245" s="1" t="n">
+      <c r="T245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -15476,9 +16214,12 @@
         <v>0.0302</v>
       </c>
       <c r="R246" s="1" t="n">
+        <v>0.03024</v>
+      </c>
+      <c r="S246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="S246" s="1" t="n">
+      <c r="T246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -15537,9 +16278,12 @@
         <v>0.1796</v>
       </c>
       <c r="R247" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="S247" s="1" t="n">
+      <c r="T247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -15598,9 +16342,12 @@
         <v>0.05866</v>
       </c>
       <c r="R248" s="1" t="n">
+        <v>0.05873</v>
+      </c>
+      <c r="S248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="S248" s="1" t="n">
+      <c r="T248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -15659,9 +16406,12 @@
         <v>0.1657</v>
       </c>
       <c r="R249" s="1" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="S249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="S249" s="1" t="n">
+      <c r="T249" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -15720,9 +16470,12 @@
         <v>0.01902</v>
       </c>
       <c r="R250" s="1" t="n">
+        <v>0.01903</v>
+      </c>
+      <c r="S250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="S250" s="1" t="n">
+      <c r="T250" s="1" t="n">
         <v>0.01898</v>
       </c>
     </row>
@@ -15781,9 +16534,12 @@
         <v>0.02303</v>
       </c>
       <c r="R251" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="S251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="S251" s="1" t="n">
+      <c r="T251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -15842,9 +16598,12 @@
         <v>0.30589</v>
       </c>
       <c r="R252" s="1" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="S252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="S252" s="1" t="n">
+      <c r="T252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -15903,9 +16662,12 @@
         <v>0.005971</v>
       </c>
       <c r="R253" s="1" t="n">
+        <v>0.00598</v>
+      </c>
+      <c r="S253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="S253" s="1" t="n">
+      <c r="T253" s="1" t="n">
         <v>0.005956</v>
       </c>
     </row>
@@ -15964,9 +16726,12 @@
         <v>0.6124000000000001</v>
       </c>
       <c r="R254" s="1" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="S254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="S254" s="1" t="n">
+      <c r="T254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -16025,10 +16790,13 @@
         <v>0.10593</v>
       </c>
       <c r="R255" s="1" t="n">
+        <v>0.10579</v>
+      </c>
+      <c r="S255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="S255" s="1" t="n">
-        <v>0.10593</v>
+      <c r="T255" s="1" t="n">
+        <v>0.10579</v>
       </c>
     </row>
     <row r="256">
@@ -16086,9 +16854,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="R256" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="S256" s="1" t="n">
+      <c r="T256" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
     </row>
@@ -16147,9 +16918,12 @@
         <v>0.01449</v>
       </c>
       <c r="R257" s="1" t="n">
+        <v>0.01448</v>
+      </c>
+      <c r="S257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="S257" s="1" t="n">
+      <c r="T257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -16208,9 +16982,12 @@
         <v>0.0497</v>
       </c>
       <c r="R258" s="1" t="n">
+        <v>0.04998</v>
+      </c>
+      <c r="S258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="S258" s="1" t="n">
+      <c r="T258" s="1" t="n">
         <v>0.04965</v>
       </c>
     </row>
@@ -16269,9 +17046,12 @@
         <v>0.00804</v>
       </c>
       <c r="R259" s="1" t="n">
+        <v>0.008059999999999999</v>
+      </c>
+      <c r="S259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="S259" s="1" t="n">
+      <c r="T259" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -16330,9 +17110,12 @@
         <v>0.1896</v>
       </c>
       <c r="R260" s="1" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="S260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="S260" s="1" t="n">
+      <c r="T260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -16391,9 +17174,12 @@
         <v>0.0977</v>
       </c>
       <c r="R261" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="S261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="S261" s="1" t="n">
+      <c r="T261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -16452,9 +17238,12 @@
         <v>0.2108</v>
       </c>
       <c r="R262" s="1" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="S262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="S262" s="1" t="n">
+      <c r="T262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -16513,9 +17302,12 @@
         <v>0.008467000000000001</v>
       </c>
       <c r="R263" s="1" t="n">
+        <v>0.008499</v>
+      </c>
+      <c r="S263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="S263" s="1" t="n">
+      <c r="T263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -16574,9 +17366,12 @@
         <v>2.63</v>
       </c>
       <c r="R264" s="1" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="S264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="S264" s="1" t="n">
+      <c r="T264" s="1" t="n">
         <v>2.629</v>
       </c>
     </row>
@@ -16635,9 +17430,12 @@
         <v>0.01859</v>
       </c>
       <c r="R265" s="1" t="n">
+        <v>0.01867</v>
+      </c>
+      <c r="S265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="S265" s="1" t="n">
+      <c r="T265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -16696,9 +17494,12 @@
         <v>0.3604</v>
       </c>
       <c r="R266" s="1" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="S266" s="1" t="n">
         <v>0.3612</v>
       </c>
-      <c r="S266" s="1" t="n">
+      <c r="T266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -16757,9 +17558,12 @@
         <v>0.03424</v>
       </c>
       <c r="R267" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="S267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="S267" s="1" t="n">
+      <c r="T267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -16818,9 +17622,12 @@
         <v>0.118</v>
       </c>
       <c r="R268" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="S268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="S268" s="1" t="n">
+      <c r="T268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -16879,10 +17686,13 @@
         <v>0.07974000000000001</v>
       </c>
       <c r="R269" s="1" t="n">
+        <v>0.07937</v>
+      </c>
+      <c r="S269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="S269" s="1" t="n">
-        <v>0.07973</v>
+      <c r="T269" s="1" t="n">
+        <v>0.07937</v>
       </c>
     </row>
     <row r="270">
@@ -16940,9 +17750,12 @@
         <v>0.01376</v>
       </c>
       <c r="R270" s="1" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="S270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="S270" s="1" t="n">
+      <c r="T270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -17001,9 +17814,12 @@
         <v>0.007516</v>
       </c>
       <c r="R271" s="1" t="n">
+        <v>0.007508</v>
+      </c>
+      <c r="S271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="S271" s="1" t="n">
+      <c r="T271" s="1" t="n">
         <v>0.007504</v>
       </c>
     </row>
@@ -17062,9 +17878,12 @@
         <v>0.07418</v>
       </c>
       <c r="R272" s="1" t="n">
+        <v>0.07417</v>
+      </c>
+      <c r="S272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="S272" s="1" t="n">
+      <c r="T272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -17123,9 +17942,12 @@
         <v>3.13e-05</v>
       </c>
       <c r="R273" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="S273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="S273" s="1" t="n">
+      <c r="T273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -17184,9 +18006,12 @@
         <v>0.00542</v>
       </c>
       <c r="R274" s="1" t="n">
+        <v>0.005422</v>
+      </c>
+      <c r="S274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="S274" s="1" t="n">
+      <c r="T274" s="1" t="n">
         <v>0.005409</v>
       </c>
     </row>
@@ -17245,9 +18070,12 @@
         <v>0.1784</v>
       </c>
       <c r="R275" s="1" t="n">
+        <v>0.1791</v>
+      </c>
+      <c r="S275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="S275" s="1" t="n">
+      <c r="T275" s="1" t="n">
         <v>0.1784</v>
       </c>
     </row>
@@ -17306,9 +18134,12 @@
         <v>0.006809</v>
       </c>
       <c r="R276" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+      <c r="S276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="S276" s="1" t="n">
+      <c r="T276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -17367,10 +18198,13 @@
         <v>0.1305</v>
       </c>
       <c r="R277" s="1" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="S277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="S277" s="1" t="n">
-        <v>0.1303</v>
+      <c r="T277" s="1" t="n">
+        <v>0.1302</v>
       </c>
     </row>
     <row r="278">
@@ -17428,9 +18262,12 @@
         <v>0.0231</v>
       </c>
       <c r="R278" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="S278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="S278" s="1" t="n">
+      <c r="T278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -17489,9 +18326,12 @@
         <v>0.01813</v>
       </c>
       <c r="R279" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="S279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="S279" s="1" t="n">
+      <c r="T279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -17550,9 +18390,12 @@
         <v>0.03681</v>
       </c>
       <c r="R280" s="1" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="S280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="S280" s="1" t="n">
+      <c r="T280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -17611,9 +18454,12 @@
         <v>0.03963</v>
       </c>
       <c r="R281" s="1" t="n">
+        <v>0.03968</v>
+      </c>
+      <c r="S281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="S281" s="1" t="n">
+      <c r="T281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -17672,9 +18518,12 @@
         <v>0.3036</v>
       </c>
       <c r="R282" s="1" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="S282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="S282" s="1" t="n">
+      <c r="T282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -17733,9 +18582,12 @@
         <v>0.01115</v>
       </c>
       <c r="R283" s="1" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="S283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="S283" s="1" t="n">
+      <c r="T283" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -17794,9 +18646,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="R284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="S284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="S284" s="1" t="n">
+      <c r="T284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -17855,9 +18710,12 @@
         <v>0.1143</v>
       </c>
       <c r="R285" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="S285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="S285" s="1" t="n">
+      <c r="T285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -17916,9 +18774,12 @@
         <v>0.003425</v>
       </c>
       <c r="R286" s="1" t="n">
+        <v>0.003425</v>
+      </c>
+      <c r="S286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="S286" s="1" t="n">
+      <c r="T286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -17977,9 +18838,12 @@
         <v>0.08473</v>
       </c>
       <c r="R287" s="1" t="n">
+        <v>0.08477</v>
+      </c>
+      <c r="S287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="S287" s="1" t="n">
+      <c r="T287" s="1" t="n">
         <v>0.08465</v>
       </c>
     </row>
@@ -18038,9 +18902,12 @@
         <v>0.09970999999999999</v>
       </c>
       <c r="R288" s="1" t="n">
+        <v>0.09970999999999999</v>
+      </c>
+      <c r="S288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="S288" s="1" t="n">
+      <c r="T288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -18099,9 +18966,12 @@
         <v>0.433</v>
       </c>
       <c r="R289" s="1" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="S289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="S289" s="1" t="n">
+      <c r="T289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -18160,9 +19030,12 @@
         <v>0.03943</v>
       </c>
       <c r="R290" s="1" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="S290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="S290" s="1" t="n">
+      <c r="T290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -18221,9 +19094,12 @@
         <v>0.2349</v>
       </c>
       <c r="R291" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="S291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="S291" s="1" t="n">
+      <c r="T291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -18282,9 +19158,12 @@
         <v>0.28318</v>
       </c>
       <c r="R292" s="1" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="S292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="S292" s="1" t="n">
+      <c r="T292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -18343,9 +19222,12 @@
         <v>0.1489</v>
       </c>
       <c r="R293" s="1" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="S293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="S293" s="1" t="n">
+      <c r="T293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -18404,9 +19286,12 @@
         <v>4.171</v>
       </c>
       <c r="R294" s="1" t="n">
+        <v>4.172</v>
+      </c>
+      <c r="S294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="S294" s="1" t="n">
+      <c r="T294" s="1" t="n">
         <v>4.171</v>
       </c>
     </row>
@@ -18465,9 +19350,12 @@
         <v>0.03509</v>
       </c>
       <c r="R295" s="1" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="S295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="S295" s="1" t="n">
+      <c r="T295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -18526,9 +19414,12 @@
         <v>0.000967</v>
       </c>
       <c r="R296" s="1" t="n">
+        <v>0.000967</v>
+      </c>
+      <c r="S296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="S296" s="1" t="n">
+      <c r="T296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -18587,9 +19478,12 @@
         <v>0.08148</v>
       </c>
       <c r="R297" s="1" t="n">
+        <v>0.08143</v>
+      </c>
+      <c r="S297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="S297" s="1" t="n">
+      <c r="T297" s="1" t="n">
         <v>0.08135000000000001</v>
       </c>
     </row>
@@ -18648,9 +19542,12 @@
         <v>0.05784</v>
       </c>
       <c r="R298" s="1" t="n">
+        <v>0.05813</v>
+      </c>
+      <c r="S298" s="1" t="n">
         <v>0.05845</v>
       </c>
-      <c r="S298" s="1" t="n">
+      <c r="T298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -18709,9 +19606,12 @@
         <v>0.09054</v>
       </c>
       <c r="R299" s="1" t="n">
+        <v>0.09079</v>
+      </c>
+      <c r="S299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="S299" s="1" t="n">
+      <c r="T299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -18770,10 +19670,13 @@
         <v>0.02725</v>
       </c>
       <c r="R300" s="1" t="n">
+        <v>0.02723</v>
+      </c>
+      <c r="S300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="S300" s="1" t="n">
-        <v>0.02724</v>
+      <c r="T300" s="1" t="n">
+        <v>0.02723</v>
       </c>
     </row>
     <row r="301">
@@ -18831,9 +19734,12 @@
         <v>0.0653</v>
       </c>
       <c r="R301" s="1" t="n">
+        <v>0.06539</v>
+      </c>
+      <c r="S301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="S301" s="1" t="n">
+      <c r="T301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -18892,9 +19798,12 @@
         <v>0.053562</v>
       </c>
       <c r="R302" s="1" t="n">
+        <v>0.053376</v>
+      </c>
+      <c r="S302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="S302" s="1" t="n">
+      <c r="T302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -18953,9 +19862,12 @@
         <v>5168.2</v>
       </c>
       <c r="R303" s="1" t="n">
+        <v>5171.3</v>
+      </c>
+      <c r="S303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="S303" s="1" t="n">
+      <c r="T303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -19014,9 +19926,12 @@
         <v>14.85</v>
       </c>
       <c r="R304" s="1" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="S304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="S304" s="1" t="n">
+      <c r="T304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -19075,9 +19990,12 @@
         <v>0.003696</v>
       </c>
       <c r="R305" s="1" t="n">
+        <v>0.003706</v>
+      </c>
+      <c r="S305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="S305" s="1" t="n">
+      <c r="T305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -19136,9 +20054,12 @@
         <v>0.4543</v>
       </c>
       <c r="R306" s="1" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="S306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="S306" s="1" t="n">
+      <c r="T306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -19197,9 +20118,12 @@
         <v>0.04651</v>
       </c>
       <c r="R307" s="1" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="S307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="S307" s="1" t="n">
+      <c r="T307" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -19258,9 +20182,12 @@
         <v>1.5049</v>
       </c>
       <c r="R308" s="1" t="n">
+        <v>1.5053</v>
+      </c>
+      <c r="S308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="S308" s="1" t="n">
+      <c r="T308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -19319,9 +20246,12 @@
         <v>0.0007861</v>
       </c>
       <c r="R309" s="1" t="n">
+        <v>0.0007881</v>
+      </c>
+      <c r="S309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="S309" s="1" t="n">
+      <c r="T309" s="1" t="n">
         <v>0.0007861</v>
       </c>
     </row>
@@ -19380,9 +20310,12 @@
         <v>4.552</v>
       </c>
       <c r="R310" s="1" t="n">
+        <v>4.551</v>
+      </c>
+      <c r="S310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="S310" s="1" t="n">
+      <c r="T310" s="1" t="n">
         <v>4.549</v>
       </c>
     </row>
@@ -19441,9 +20374,12 @@
         <v>4.766</v>
       </c>
       <c r="R311" s="1" t="n">
+        <v>4.759</v>
+      </c>
+      <c r="S311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="S311" s="1" t="n">
+      <c r="T311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -19502,9 +20438,12 @@
         <v>0.08057</v>
       </c>
       <c r="R312" s="1" t="n">
+        <v>0.08058999999999999</v>
+      </c>
+      <c r="S312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="S312" s="1" t="n">
+      <c r="T312" s="1" t="n">
         <v>0.08057</v>
       </c>
     </row>
@@ -19563,9 +20502,12 @@
         <v>2.005</v>
       </c>
       <c r="R313" s="1" t="n">
+        <v>2.014</v>
+      </c>
+      <c r="S313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="S313" s="1" t="n">
+      <c r="T313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -19624,9 +20566,12 @@
         <v>0.0725</v>
       </c>
       <c r="R314" s="1" t="n">
+        <v>0.07189</v>
+      </c>
+      <c r="S314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="S314" s="1" t="n">
+      <c r="T314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -19685,9 +20630,12 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="R315" s="1" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="S315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="S315" s="1" t="n">
+      <c r="T315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -19746,9 +20694,12 @@
         <v>0.1303</v>
       </c>
       <c r="R316" s="1" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="S316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="S316" s="1" t="n">
+      <c r="T316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -19807,9 +20758,12 @@
         <v>0.1845</v>
       </c>
       <c r="R317" s="1" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="S317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="S317" s="1" t="n">
+      <c r="T317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -19868,9 +20822,12 @@
         <v>0.01612</v>
       </c>
       <c r="R318" s="1" t="n">
+        <v>0.01609</v>
+      </c>
+      <c r="S318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="S318" s="1" t="n">
+      <c r="T318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -19929,9 +20886,12 @@
         <v>0.08323999999999999</v>
       </c>
       <c r="R319" s="1" t="n">
+        <v>0.08326</v>
+      </c>
+      <c r="S319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="S319" s="1" t="n">
+      <c r="T319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -19990,9 +20950,12 @@
         <v>0.007481</v>
       </c>
       <c r="R320" s="1" t="n">
+        <v>0.007516</v>
+      </c>
+      <c r="S320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="S320" s="1" t="n">
+      <c r="T320" s="1" t="n">
         <v>0.007463</v>
       </c>
     </row>
@@ -20051,9 +21014,12 @@
         <v>0.05427</v>
       </c>
       <c r="R321" s="1" t="n">
+        <v>0.05432</v>
+      </c>
+      <c r="S321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="S321" s="1" t="n">
+      <c r="T321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -20112,9 +21078,12 @@
         <v>0.5501</v>
       </c>
       <c r="R322" s="1" t="n">
+        <v>0.5499000000000001</v>
+      </c>
+      <c r="S322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="S322" s="1" t="n">
+      <c r="T322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -20173,9 +21142,12 @@
         <v>0.07566000000000001</v>
       </c>
       <c r="R323" s="1" t="n">
+        <v>0.07564</v>
+      </c>
+      <c r="S323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="S323" s="1" t="n">
+      <c r="T323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -20234,9 +21206,12 @@
         <v>0.012973</v>
       </c>
       <c r="R324" s="1" t="n">
-        <v>0.013001</v>
+        <v>0.013004</v>
       </c>
       <c r="S324" s="1" t="n">
+        <v>0.013004</v>
+      </c>
+      <c r="T324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -20295,9 +21270,12 @@
         <v>0.0985</v>
       </c>
       <c r="R325" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="S325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="S325" s="1" t="n">
+      <c r="T325" s="1" t="n">
         <v>0.0985</v>
       </c>
     </row>
@@ -20356,9 +21334,12 @@
         <v>0.0173</v>
       </c>
       <c r="R326" s="1" t="n">
+        <v>0.01733</v>
+      </c>
+      <c r="S326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="S326" s="1" t="n">
+      <c r="T326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -20417,9 +21398,12 @@
         <v>0.06372999999999999</v>
       </c>
       <c r="R327" s="1" t="n">
+        <v>0.06395000000000001</v>
+      </c>
+      <c r="S327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="S327" s="1" t="n">
+      <c r="T327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -20478,9 +21462,12 @@
         <v>0.2644</v>
       </c>
       <c r="R328" s="1" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="S328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="S328" s="1" t="n">
+      <c r="T328" s="1" t="n">
         <v>0.2612</v>
       </c>
     </row>
@@ -20539,9 +21526,12 @@
         <v>0.17476</v>
       </c>
       <c r="R329" s="1" t="n">
+        <v>0.17356</v>
+      </c>
+      <c r="S329" s="1" t="n">
         <v>0.17476</v>
       </c>
-      <c r="S329" s="1" t="n">
+      <c r="T329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -20600,10 +21590,13 @@
         <v>2.037</v>
       </c>
       <c r="R330" s="1" t="n">
+        <v>2.035</v>
+      </c>
+      <c r="S330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="S330" s="1" t="n">
-        <v>2.037</v>
+      <c r="T330" s="1" t="n">
+        <v>2.035</v>
       </c>
     </row>
     <row r="331">
@@ -20661,9 +21654,12 @@
         <v>0.0287</v>
       </c>
       <c r="R331" s="1" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="S331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="S331" s="1" t="n">
+      <c r="T331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -20722,9 +21718,12 @@
         <v>0.00599</v>
       </c>
       <c r="R332" s="1" t="n">
+        <v>0.006015</v>
+      </c>
+      <c r="S332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="S332" s="1" t="n">
+      <c r="T332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -20783,9 +21782,12 @@
         <v>0.003531</v>
       </c>
       <c r="R333" s="1" t="n">
+        <v>0.003534</v>
+      </c>
+      <c r="S333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="S333" s="1" t="n">
+      <c r="T333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -20844,9 +21846,12 @@
         <v>0.01399</v>
       </c>
       <c r="R334" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="S334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="S334" s="1" t="n">
+      <c r="T334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -20905,9 +21910,12 @@
         <v>1.143</v>
       </c>
       <c r="R335" s="1" t="n">
-        <v>1.143</v>
+        <v>1.145</v>
       </c>
       <c r="S335" s="1" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="T335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -20966,9 +21974,12 @@
         <v>0.011326</v>
       </c>
       <c r="R336" s="1" t="n">
+        <v>0.011332</v>
+      </c>
+      <c r="S336" s="1" t="n">
         <v>0.011344</v>
       </c>
-      <c r="S336" s="1" t="n">
+      <c r="T336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -21027,9 +22038,12 @@
         <v>2.949</v>
       </c>
       <c r="R337" s="1" t="n">
+        <v>2.959</v>
+      </c>
+      <c r="S337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="S337" s="1" t="n">
+      <c r="T337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -21088,9 +22102,12 @@
         <v>0.01846</v>
       </c>
       <c r="R338" s="1" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="S338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="S338" s="1" t="n">
+      <c r="T338" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -21149,9 +22166,12 @@
         <v>0.07693</v>
       </c>
       <c r="R339" s="1" t="n">
+        <v>0.07704</v>
+      </c>
+      <c r="S339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="S339" s="1" t="n">
+      <c r="T339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -21210,9 +22230,12 @@
         <v>0.075</v>
       </c>
       <c r="R340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="S340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="S340" s="1" t="n">
+      <c r="T340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -21271,9 +22294,12 @@
         <v>0.03578</v>
       </c>
       <c r="R341" s="1" t="n">
+        <v>0.03585</v>
+      </c>
+      <c r="S341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="S341" s="1" t="n">
+      <c r="T341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -21332,10 +22358,13 @@
         <v>2596</v>
       </c>
       <c r="R342" s="1" t="n">
+        <v>2581</v>
+      </c>
+      <c r="S342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="S342" s="1" t="n">
-        <v>2592</v>
+      <c r="T342" s="1" t="n">
+        <v>2581</v>
       </c>
     </row>
     <row r="343">
@@ -21393,9 +22422,12 @@
         <v>0.0002007</v>
       </c>
       <c r="R343" s="1" t="n">
-        <v>0.0002007</v>
+        <v>0.0002046</v>
       </c>
       <c r="S343" s="1" t="n">
+        <v>0.0002046</v>
+      </c>
+      <c r="T343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -21454,9 +22486,12 @@
         <v>0.07931000000000001</v>
       </c>
       <c r="R344" s="1" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="S344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="S344" s="1" t="n">
+      <c r="T344" s="1" t="n">
         <v>0.07915</v>
       </c>
     </row>
@@ -21515,9 +22550,12 @@
         <v>0.01622</v>
       </c>
       <c r="R345" s="1" t="n">
+        <v>0.01628</v>
+      </c>
+      <c r="S345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="S345" s="1" t="n">
+      <c r="T345" s="1" t="n">
         <v>0.01622</v>
       </c>
     </row>
@@ -21576,9 +22614,12 @@
         <v>2.735</v>
       </c>
       <c r="R346" s="1" t="n">
+        <v>2.736</v>
+      </c>
+      <c r="S346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="S346" s="1" t="n">
+      <c r="T346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -21637,9 +22678,12 @@
         <v>0.01632</v>
       </c>
       <c r="R347" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="S347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="S347" s="1" t="n">
+      <c r="T347" s="1" t="n">
         <v>0.01625</v>
       </c>
     </row>
@@ -21698,9 +22742,12 @@
         <v>0.04</v>
       </c>
       <c r="R348" s="1" t="n">
+        <v>0.03972</v>
+      </c>
+      <c r="S348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="S348" s="1" t="n">
+      <c r="T348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -21759,9 +22806,12 @@
         <v>0.3046</v>
       </c>
       <c r="R349" s="1" t="n">
-        <v>0.3065</v>
+        <v>0.3076</v>
       </c>
       <c r="S349" s="1" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="T349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -21820,9 +22870,12 @@
         <v>0.005081</v>
       </c>
       <c r="R350" s="1" t="n">
+        <v>0.005077</v>
+      </c>
+      <c r="S350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="S350" s="1" t="n">
+      <c r="T350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -21881,9 +22934,12 @@
         <v>0.005054</v>
       </c>
       <c r="R351" s="1" t="n">
+        <v>0.005084</v>
+      </c>
+      <c r="S351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="S351" s="1" t="n">
+      <c r="T351" s="1" t="n">
         <v>0.005054</v>
       </c>
     </row>
@@ -21942,9 +22998,12 @@
         <v>0.004383</v>
       </c>
       <c r="R352" s="1" t="n">
+        <v>0.00439</v>
+      </c>
+      <c r="S352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="S352" s="1" t="n">
+      <c r="T352" s="1" t="n">
         <v>0.004379</v>
       </c>
     </row>
@@ -22003,9 +23062,12 @@
         <v>0.08008</v>
       </c>
       <c r="R353" s="1" t="n">
+        <v>0.08031000000000001</v>
+      </c>
+      <c r="S353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="S353" s="1" t="n">
+      <c r="T353" s="1" t="n">
         <v>0.08008</v>
       </c>
     </row>
@@ -22064,9 +23126,12 @@
         <v>1.261</v>
       </c>
       <c r="R354" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="S354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="S354" s="1" t="n">
+      <c r="T354" s="1" t="n">
         <v>1.258</v>
       </c>
     </row>
@@ -22125,9 +23190,12 @@
         <v>7.663</v>
       </c>
       <c r="R355" s="1" t="n">
+        <v>7.668</v>
+      </c>
+      <c r="S355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="S355" s="1" t="n">
+      <c r="T355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -22186,9 +23254,12 @@
         <v>0.007820000000000001</v>
       </c>
       <c r="R356" s="1" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="S356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="S356" s="1" t="n">
+      <c r="T356" s="1" t="n">
         <v>0.00777</v>
       </c>
     </row>
@@ -22247,9 +23318,12 @@
         <v>0.005623</v>
       </c>
       <c r="R357" s="1" t="n">
+        <v>0.005637</v>
+      </c>
+      <c r="S357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="S357" s="1" t="n">
+      <c r="T357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -22308,9 +23382,12 @@
         <v>0.01542</v>
       </c>
       <c r="R358" s="1" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="S358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="S358" s="1" t="n">
+      <c r="T358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -22369,9 +23446,12 @@
         <v>3.605</v>
       </c>
       <c r="R359" s="1" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="S359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="S359" s="1" t="n">
+      <c r="T359" s="1" t="n">
         <v>3.605</v>
       </c>
     </row>
@@ -22430,9 +23510,12 @@
         <v>0.1502</v>
       </c>
       <c r="R360" s="1" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="S360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="S360" s="1" t="n">
+      <c r="T360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -22491,9 +23574,12 @@
         <v>0.07041</v>
       </c>
       <c r="R361" s="1" t="n">
+        <v>0.07044</v>
+      </c>
+      <c r="S361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="S361" s="1" t="n">
+      <c r="T361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -22552,9 +23638,12 @@
         <v>0.01765</v>
       </c>
       <c r="R362" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+      <c r="S362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="S362" s="1" t="n">
+      <c r="T362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -22613,9 +23702,12 @@
         <v>0.02231</v>
       </c>
       <c r="R363" s="1" t="n">
+        <v>0.02232</v>
+      </c>
+      <c r="S363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="S363" s="1" t="n">
+      <c r="T363" s="1" t="n">
         <v>0.02229</v>
       </c>
     </row>
@@ -22674,9 +23766,12 @@
         <v>0.01252</v>
       </c>
       <c r="R364" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="S364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="S364" s="1" t="n">
+      <c r="T364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -22735,9 +23830,12 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="R365" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="S365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="S365" s="1" t="n">
+      <c r="T365" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -22796,9 +23894,12 @@
         <v>0.04219</v>
       </c>
       <c r="R366" s="1" t="n">
+        <v>0.04227</v>
+      </c>
+      <c r="S366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="S366" s="1" t="n">
+      <c r="T366" s="1" t="n">
         <v>0.04214</v>
       </c>
     </row>
@@ -22857,9 +23958,12 @@
         <v>0.03136</v>
       </c>
       <c r="R367" s="1" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="S367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="S367" s="1" t="n">
+      <c r="T367" s="1" t="n">
         <v>0.03124</v>
       </c>
     </row>
@@ -22918,9 +24022,12 @@
         <v>0.02332</v>
       </c>
       <c r="R368" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="S368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="S368" s="1" t="n">
+      <c r="T368" s="1" t="n">
         <v>0.0233</v>
       </c>
     </row>
@@ -22979,9 +24086,12 @@
         <v>0.03087</v>
       </c>
       <c r="R369" s="1" t="n">
+        <v>0.03095</v>
+      </c>
+      <c r="S369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="S369" s="1" t="n">
+      <c r="T369" s="1" t="n">
         <v>0.0308</v>
       </c>
     </row>
@@ -23040,9 +24150,12 @@
         <v>0.07998</v>
       </c>
       <c r="R370" s="1" t="n">
+        <v>0.07963000000000001</v>
+      </c>
+      <c r="S370" s="1" t="n">
         <v>0.07998</v>
       </c>
-      <c r="S370" s="1" t="n">
+      <c r="T370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -23101,9 +24214,12 @@
         <v>0.1075</v>
       </c>
       <c r="R371" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="S371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="S371" s="1" t="n">
+      <c r="T371" s="1" t="n">
         <v>0.1072</v>
       </c>
     </row>
@@ -23162,9 +24278,12 @@
         <v>0.006968</v>
       </c>
       <c r="R372" s="1" t="n">
+        <v>0.006964</v>
+      </c>
+      <c r="S372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="S372" s="1" t="n">
+      <c r="T372" s="1" t="n">
         <v>0.00694</v>
       </c>
     </row>
@@ -23223,9 +24342,12 @@
         <v>0.0958</v>
       </c>
       <c r="R373" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="S373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="S373" s="1" t="n">
+      <c r="T373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -23284,9 +24406,12 @@
         <v>0.0575</v>
       </c>
       <c r="R374" s="1" t="n">
+        <v>0.05776</v>
+      </c>
+      <c r="S374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="S374" s="1" t="n">
+      <c r="T374" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -23345,10 +24470,13 @@
         <v>0.3177</v>
       </c>
       <c r="R375" s="1" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="S375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="S375" s="1" t="n">
-        <v>0.3175</v>
+      <c r="T375" s="1" t="n">
+        <v>0.3169</v>
       </c>
     </row>
     <row r="376">
@@ -23406,9 +24534,12 @@
         <v>0.01943</v>
       </c>
       <c r="R376" s="1" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="S376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="S376" s="1" t="n">
+      <c r="T376" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -23467,9 +24598,12 @@
         <v>0.06829</v>
       </c>
       <c r="R377" s="1" t="n">
+        <v>0.06834999999999999</v>
+      </c>
+      <c r="S377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="S377" s="1" t="n">
+      <c r="T377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -23528,9 +24662,12 @@
         <v>0.15797</v>
       </c>
       <c r="R378" s="1" t="n">
-        <v>0.1581</v>
+        <v>0.15872</v>
       </c>
       <c r="S378" s="1" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="T378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -23589,9 +24726,12 @@
         <v>0.0005922</v>
       </c>
       <c r="R379" s="1" t="n">
+        <v>0.0005932999999999999</v>
+      </c>
+      <c r="S379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="S379" s="1" t="n">
+      <c r="T379" s="1" t="n">
         <v>0.0005922</v>
       </c>
     </row>
@@ -23650,10 +24790,13 @@
         <v>0.01016</v>
       </c>
       <c r="R380" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="S380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="S380" s="1" t="n">
-        <v>0.01015</v>
+      <c r="T380" s="1" t="n">
+        <v>0.01012</v>
       </c>
     </row>
     <row r="381">
@@ -23711,9 +24854,12 @@
         <v>0.0256</v>
       </c>
       <c r="R381" s="1" t="n">
+        <v>0.02562</v>
+      </c>
+      <c r="S381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="S381" s="1" t="n">
+      <c r="T381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -23772,9 +24918,12 @@
         <v>0.18967</v>
       </c>
       <c r="R382" s="1" t="n">
+        <v>0.18964</v>
+      </c>
+      <c r="S382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="S382" s="1" t="n">
+      <c r="T382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -23833,9 +24982,12 @@
         <v>0.09224</v>
       </c>
       <c r="R383" s="1" t="n">
+        <v>0.09222</v>
+      </c>
+      <c r="S383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="S383" s="1" t="n">
+      <c r="T383" s="1" t="n">
         <v>0.09214</v>
       </c>
     </row>
@@ -23894,10 +25046,13 @@
         <v>0.03163</v>
       </c>
       <c r="R384" s="1" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="S384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="S384" s="1" t="n">
-        <v>0.03163</v>
+      <c r="T384" s="1" t="n">
+        <v>0.0316</v>
       </c>
     </row>
     <row r="385">
@@ -23955,9 +25110,12 @@
         <v>0.01087</v>
       </c>
       <c r="R385" s="1" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="S385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="S385" s="1" t="n">
+      <c r="T385" s="1" t="n">
         <v>0.01086</v>
       </c>
     </row>
@@ -24016,10 +25174,13 @@
         <v>0.05063</v>
       </c>
       <c r="R386" s="1" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="S386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="S386" s="1" t="n">
-        <v>0.05059</v>
+      <c r="T386" s="1" t="n">
+        <v>0.05043</v>
       </c>
     </row>
     <row r="387">
@@ -24077,9 +25238,12 @@
         <v>0.02425</v>
       </c>
       <c r="R387" s="1" t="n">
+        <v>0.02431</v>
+      </c>
+      <c r="S387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="S387" s="1" t="n">
+      <c r="T387" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -24138,9 +25302,12 @@
         <v>0.007224</v>
       </c>
       <c r="R388" s="1" t="n">
+        <v>0.007267</v>
+      </c>
+      <c r="S388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="S388" s="1" t="n">
+      <c r="T388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -24199,9 +25366,12 @@
         <v>0.01011</v>
       </c>
       <c r="R389" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="S389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="S389" s="1" t="n">
+      <c r="T389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -24260,9 +25430,12 @@
         <v>0.08218</v>
       </c>
       <c r="R390" s="1" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="S390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="S390" s="1" t="n">
+      <c r="T390" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -24321,9 +25494,12 @@
         <v>0.5051</v>
       </c>
       <c r="R391" s="1" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="S391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="S391" s="1" t="n">
+      <c r="T391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -24382,9 +25558,12 @@
         <v>0.1161</v>
       </c>
       <c r="R392" s="1" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="S392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="S392" s="1" t="n">
+      <c r="T392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -24443,9 +25622,12 @@
         <v>0.00245</v>
       </c>
       <c r="R393" s="1" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="S393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="S393" s="1" t="n">
+      <c r="T393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -24504,9 +25686,12 @@
         <v>0.02121</v>
       </c>
       <c r="R394" s="1" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="S394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="S394" s="1" t="n">
+      <c r="T394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -24565,9 +25750,12 @@
         <v>0.0159</v>
       </c>
       <c r="R395" s="1" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="S395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="S395" s="1" t="n">
+      <c r="T395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -24626,9 +25814,12 @@
         <v>0.1349</v>
       </c>
       <c r="R396" s="1" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="S396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="S396" s="1" t="n">
+      <c r="T396" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -24687,9 +25878,12 @@
         <v>0.0144</v>
       </c>
       <c r="R397" s="1" t="n">
+        <v>0.01443</v>
+      </c>
+      <c r="S397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="S397" s="1" t="n">
+      <c r="T397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -24748,9 +25942,12 @@
         <v>6.698</v>
       </c>
       <c r="R398" s="1" t="n">
+        <v>6.718</v>
+      </c>
+      <c r="S398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="S398" s="1" t="n">
+      <c r="T398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -24809,9 +26006,12 @@
         <v>0.009363</v>
       </c>
       <c r="R399" s="1" t="n">
+        <v>0.009379</v>
+      </c>
+      <c r="S399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="S399" s="1" t="n">
+      <c r="T399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -24870,10 +26070,13 @@
         <v>0.001256</v>
       </c>
       <c r="R400" s="1" t="n">
+        <v>0.001241</v>
+      </c>
+      <c r="S400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="S400" s="1" t="n">
-        <v>0.001256</v>
+      <c r="T400" s="1" t="n">
+        <v>0.001241</v>
       </c>
     </row>
     <row r="401">
@@ -24931,9 +26134,12 @@
         <v>0.01846</v>
       </c>
       <c r="R401" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="S401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="S401" s="1" t="n">
+      <c r="T401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -24992,9 +26198,12 @@
         <v>0.08454</v>
       </c>
       <c r="R402" s="1" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="S402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="S402" s="1" t="n">
+      <c r="T402" s="1" t="n">
         <v>0.08447</v>
       </c>
     </row>
@@ -25053,9 +26262,12 @@
         <v>0.00548</v>
       </c>
       <c r="R403" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="S403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="S403" s="1" t="n">
+      <c r="T403" s="1" t="n">
         <v>0.00548</v>
       </c>
     </row>
@@ -25114,9 +26326,12 @@
         <v>0.04263</v>
       </c>
       <c r="R404" s="1" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="S404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="S404" s="1" t="n">
+      <c r="T404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -25175,9 +26390,12 @@
         <v>0.0583</v>
       </c>
       <c r="R405" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="S405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="S405" s="1" t="n">
+      <c r="T405" s="1" t="n">
         <v>0.05827</v>
       </c>
     </row>
@@ -25239,6 +26457,9 @@
         <v>0.01689</v>
       </c>
       <c r="S406" s="1" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="T406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -25297,9 +26518,12 @@
         <v>0.0424</v>
       </c>
       <c r="R407" s="1" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="S407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="S407" s="1" t="n">
+      <c r="T407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -25358,9 +26582,12 @@
         <v>0.01923</v>
       </c>
       <c r="R408" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="S408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="S408" s="1" t="n">
+      <c r="T408" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -25419,9 +26646,12 @@
         <v>0.4435</v>
       </c>
       <c r="R409" s="1" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="S409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="S409" s="1" t="n">
+      <c r="T409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -25480,10 +26710,13 @@
         <v>0.04384</v>
       </c>
       <c r="R410" s="1" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="S410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="S410" s="1" t="n">
-        <v>0.04382</v>
+      <c r="T410" s="1" t="n">
+        <v>0.04379</v>
       </c>
     </row>
     <row r="411">
@@ -25541,9 +26774,12 @@
         <v>27.11</v>
       </c>
       <c r="R411" s="1" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="S411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="S411" s="1" t="n">
+      <c r="T411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -25602,9 +26838,12 @@
         <v>0.03508</v>
       </c>
       <c r="R412" s="1" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="S412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="S412" s="1" t="n">
+      <c r="T412" s="1" t="n">
         <v>0.03493</v>
       </c>
     </row>
@@ -25663,9 +26902,12 @@
         <v>0.003389</v>
       </c>
       <c r="R413" s="1" t="n">
+        <v>0.003398</v>
+      </c>
+      <c r="S413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="S413" s="1" t="n">
+      <c r="T413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -25724,9 +26966,12 @@
         <v>0.1523</v>
       </c>
       <c r="R414" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="S414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="S414" s="1" t="n">
+      <c r="T414" s="1" t="n">
         <v>0.1523</v>
       </c>
     </row>
@@ -25785,10 +27030,13 @@
         <v>0.05229</v>
       </c>
       <c r="R415" s="1" t="n">
+        <v>0.05228</v>
+      </c>
+      <c r="S415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="S415" s="1" t="n">
-        <v>0.05229</v>
+      <c r="T415" s="1" t="n">
+        <v>0.05228</v>
       </c>
     </row>
     <row r="416">
@@ -25846,9 +27094,12 @@
         <v>0.00655</v>
       </c>
       <c r="R416" s="1" t="n">
+        <v>0.00655</v>
+      </c>
+      <c r="S416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="S416" s="1" t="n">
+      <c r="T416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -25907,9 +27158,12 @@
         <v>0.06025</v>
       </c>
       <c r="R417" s="1" t="n">
+        <v>0.06027</v>
+      </c>
+      <c r="S417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="S417" s="1" t="n">
+      <c r="T417" s="1" t="n">
         <v>0.06025</v>
       </c>
     </row>
@@ -25968,9 +27222,12 @@
         <v>0.008003</v>
       </c>
       <c r="R418" s="1" t="n">
+        <v>0.008036</v>
+      </c>
+      <c r="S418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="S418" s="1" t="n">
+      <c r="T418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -26029,9 +27286,12 @@
         <v>0.07414999999999999</v>
       </c>
       <c r="R419" s="1" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="S419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="S419" s="1" t="n">
+      <c r="T419" s="1" t="n">
         <v>0.07414999999999999</v>
       </c>
     </row>
@@ -26090,9 +27350,12 @@
         <v>0.02116</v>
       </c>
       <c r="R420" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="S420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="S420" s="1" t="n">
+      <c r="T420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -26151,10 +27414,13 @@
         <v>0.06897</v>
       </c>
       <c r="R421" s="1" t="n">
+        <v>0.06894</v>
+      </c>
+      <c r="S421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="S421" s="1" t="n">
-        <v>0.06897</v>
+      <c r="T421" s="1" t="n">
+        <v>0.06894</v>
       </c>
     </row>
     <row r="422">
@@ -26212,9 +27478,12 @@
         <v>0.01475</v>
       </c>
       <c r="R422" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="S422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="S422" s="1" t="n">
+      <c r="T422" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -26273,9 +27542,12 @@
         <v>0.006589</v>
       </c>
       <c r="R423" s="1" t="n">
+        <v>0.006581</v>
+      </c>
+      <c r="S423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="S423" s="1" t="n">
+      <c r="T423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -26334,9 +27606,12 @@
         <v>0.907</v>
       </c>
       <c r="R424" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="S424" s="1" t="n">
+      <c r="T424" s="1" t="n">
         <v>0.907</v>
       </c>
     </row>
@@ -26395,9 +27670,12 @@
         <v>0.0354</v>
       </c>
       <c r="R425" s="1" t="n">
+        <v>0.03546</v>
+      </c>
+      <c r="S425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="S425" s="1" t="n">
+      <c r="T425" s="1" t="n">
         <v>0.03519</v>
       </c>
     </row>
@@ -26456,9 +27734,12 @@
         <v>1.803</v>
       </c>
       <c r="R426" s="1" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="S426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="S426" s="1" t="n">
+      <c r="T426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -26517,9 +27798,12 @@
         <v>0.12809</v>
       </c>
       <c r="R427" s="1" t="n">
-        <v>0.12835</v>
+        <v>0.12837</v>
       </c>
       <c r="S427" s="1" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="T427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -26578,9 +27862,12 @@
         <v>0.05326</v>
       </c>
       <c r="R428" s="1" t="n">
+        <v>0.05292</v>
+      </c>
+      <c r="S428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="S428" s="1" t="n">
+      <c r="T428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -26639,9 +27926,12 @@
         <v>1.286</v>
       </c>
       <c r="R429" s="1" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="S429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="S429" s="1" t="n">
+      <c r="T429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -26700,9 +27990,12 @@
         <v>0.07462000000000001</v>
       </c>
       <c r="R430" s="1" t="n">
+        <v>0.07461</v>
+      </c>
+      <c r="S430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="S430" s="1" t="n">
+      <c r="T430" s="1" t="n">
         <v>0.07456</v>
       </c>
     </row>
@@ -26761,9 +28054,12 @@
         <v>0.156</v>
       </c>
       <c r="R431" s="1" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="S431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="S431" s="1" t="n">
+      <c r="T431" s="1" t="n">
         <v>0.156</v>
       </c>
     </row>
@@ -26822,9 +28118,12 @@
         <v>1.438</v>
       </c>
       <c r="R432" s="1" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="S432" s="1" t="n">
+      <c r="T432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -26883,9 +28182,12 @@
         <v>3.259</v>
       </c>
       <c r="R433" s="1" t="n">
+        <v>3.255</v>
+      </c>
+      <c r="S433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="S433" s="1" t="n">
+      <c r="T433" s="1" t="n">
         <v>3.239</v>
       </c>
     </row>
@@ -26944,9 +28246,12 @@
         <v>0.1784</v>
       </c>
       <c r="R434" s="1" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="S434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="S434" s="1" t="n">
+      <c r="T434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -27005,9 +28310,12 @@
         <v>0.008553</v>
       </c>
       <c r="R435" s="1" t="n">
+        <v>0.008557</v>
+      </c>
+      <c r="S435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="S435" s="1" t="n">
+      <c r="T435" s="1" t="n">
         <v>0.008548</v>
       </c>
     </row>
@@ -27066,9 +28374,12 @@
         <v>0.2828</v>
       </c>
       <c r="R436" s="1" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="S436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="S436" s="1" t="n">
+      <c r="T436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -27127,9 +28438,12 @@
         <v>0.03893</v>
       </c>
       <c r="R437" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="S437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="S437" s="1" t="n">
+      <c r="T437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -27188,10 +28502,13 @@
         <v>0.0242</v>
       </c>
       <c r="R438" s="1" t="n">
+        <v>0.02405</v>
+      </c>
+      <c r="S438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="S438" s="1" t="n">
-        <v>0.0242</v>
+      <c r="T438" s="1" t="n">
+        <v>0.02405</v>
       </c>
     </row>
     <row r="439">
@@ -27249,9 +28566,12 @@
         <v>0.04401</v>
       </c>
       <c r="R439" s="1" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="S439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="S439" s="1" t="n">
+      <c r="T439" s="1" t="n">
         <v>0.04401</v>
       </c>
     </row>
@@ -27310,9 +28630,12 @@
         <v>0.0005188</v>
       </c>
       <c r="R440" s="1" t="n">
+        <v>0.0005207</v>
+      </c>
+      <c r="S440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="S440" s="1" t="n">
+      <c r="T440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -27371,9 +28694,12 @@
         <v>0.04461</v>
       </c>
       <c r="R441" s="1" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="S441" s="1" t="n">
         <v>0.04546</v>
       </c>
-      <c r="S441" s="1" t="n">
+      <c r="T441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -27432,9 +28758,12 @@
         <v>0.000414</v>
       </c>
       <c r="R442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="S442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="S442" s="1" t="n">
+      <c r="T442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -27493,10 +28822,13 @@
         <v>0.09397</v>
       </c>
       <c r="R443" s="1" t="n">
+        <v>0.09392</v>
+      </c>
+      <c r="S443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="S443" s="1" t="n">
-        <v>0.09397</v>
+      <c r="T443" s="1" t="n">
+        <v>0.09392</v>
       </c>
     </row>
     <row r="444">
@@ -27554,10 +28886,13 @@
         <v>2.291</v>
       </c>
       <c r="R444" s="1" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="S444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="S444" s="1" t="n">
-        <v>2.289</v>
+      <c r="T444" s="1" t="n">
+        <v>2.286</v>
       </c>
     </row>
     <row r="445">
@@ -27615,9 +28950,12 @@
         <v>0.2692</v>
       </c>
       <c r="R445" s="1" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="S445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="S445" s="1" t="n">
+      <c r="T445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -27676,9 +29014,12 @@
         <v>0.0007376</v>
       </c>
       <c r="R446" s="1" t="n">
+        <v>0.0007378</v>
+      </c>
+      <c r="S446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="S446" s="1" t="n">
+      <c r="T446" s="1" t="n">
         <v>0.0007376</v>
       </c>
     </row>
@@ -27737,9 +29078,12 @@
         <v>0.03818</v>
       </c>
       <c r="R447" s="1" t="n">
+        <v>0.03861</v>
+      </c>
+      <c r="S447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="S447" s="1" t="n">
+      <c r="T447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -27798,9 +29142,12 @@
         <v>0.1771</v>
       </c>
       <c r="R448" s="1" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="S448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="S448" s="1" t="n">
+      <c r="T448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -27859,9 +29206,12 @@
         <v>0.04285</v>
       </c>
       <c r="R449" s="1" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="S449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="S449" s="1" t="n">
+      <c r="T449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -27920,9 +29270,12 @@
         <v>0.0001641</v>
       </c>
       <c r="R450" s="1" t="n">
+        <v>0.0001649</v>
+      </c>
+      <c r="S450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="S450" s="1" t="n">
+      <c r="T450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -27981,9 +29334,12 @@
         <v>0.03698</v>
       </c>
       <c r="R451" s="1" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="S451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="S451" s="1" t="n">
+      <c r="T451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -28042,9 +29398,12 @@
         <v>0.00967</v>
       </c>
       <c r="R452" s="1" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="S452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="S452" s="1" t="n">
+      <c r="T452" s="1" t="n">
         <v>0.00966</v>
       </c>
     </row>
@@ -28103,9 +29462,12 @@
         <v>0.06798</v>
       </c>
       <c r="R453" s="1" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="S453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="S453" s="1" t="n">
+      <c r="T453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -28164,9 +29526,12 @@
         <v>0.007489</v>
       </c>
       <c r="R454" s="1" t="n">
+        <v>0.007494</v>
+      </c>
+      <c r="S454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="S454" s="1" t="n">
+      <c r="T454" s="1" t="n">
         <v>0.007478</v>
       </c>
     </row>
@@ -28225,9 +29590,12 @@
         <v>0.00327</v>
       </c>
       <c r="R455" s="1" t="n">
+        <v>0.003273</v>
+      </c>
+      <c r="S455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="S455" s="1" t="n">
+      <c r="T455" s="1" t="n">
         <v>0.003269</v>
       </c>
     </row>
@@ -28286,9 +29654,12 @@
         <v>0.001845</v>
       </c>
       <c r="R456" s="1" t="n">
+        <v>0.001846</v>
+      </c>
+      <c r="S456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="S456" s="1" t="n">
+      <c r="T456" s="1" t="n">
         <v>0.00184</v>
       </c>
     </row>
@@ -28347,9 +29718,12 @@
         <v>0.0001749</v>
       </c>
       <c r="R457" s="1" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="S457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="S457" s="1" t="n">
+      <c r="T457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -28408,9 +29782,12 @@
         <v>0.0003889</v>
       </c>
       <c r="R458" s="1" t="n">
+        <v>0.0003889</v>
+      </c>
+      <c r="S458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="S458" s="1" t="n">
+      <c r="T458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -28469,9 +29846,12 @@
         <v>0.01397</v>
       </c>
       <c r="R459" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="S459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="S459" s="1" t="n">
+      <c r="T459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -28530,9 +29910,12 @@
         <v>0.04566</v>
       </c>
       <c r="R460" s="1" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="S460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="S460" s="1" t="n">
+      <c r="T460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -28591,9 +29974,12 @@
         <v>0.2831</v>
       </c>
       <c r="R461" s="1" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="S461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="S461" s="1" t="n">
+      <c r="T461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -28652,9 +30038,12 @@
         <v>0.006233</v>
       </c>
       <c r="R462" s="1" t="n">
+        <v>0.006224</v>
+      </c>
+      <c r="S462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="S462" s="1" t="n">
+      <c r="T462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -28713,9 +30102,12 @@
         <v>0.007033</v>
       </c>
       <c r="R463" s="1" t="n">
+        <v>0.007075</v>
+      </c>
+      <c r="S463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="S463" s="1" t="n">
+      <c r="T463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -28774,9 +30166,12 @@
         <v>0.2881</v>
       </c>
       <c r="R464" s="1" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="S464" s="1" t="n">
         <v>0.289</v>
       </c>
-      <c r="S464" s="1" t="n">
+      <c r="T464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -28835,9 +30230,12 @@
         <v>0.08051999999999999</v>
       </c>
       <c r="R465" s="1" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="S465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="S465" s="1" t="n">
+      <c r="T465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -28896,9 +30294,12 @@
         <v>0.6387</v>
       </c>
       <c r="R466" s="1" t="n">
+        <v>0.6362</v>
+      </c>
+      <c r="S466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="S466" s="1" t="n">
+      <c r="T466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -28957,9 +30358,12 @@
         <v>0.0147</v>
       </c>
       <c r="R467" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="S467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="S467" s="1" t="n">
+      <c r="T467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -29018,10 +30422,13 @@
         <v>0.03404</v>
       </c>
       <c r="R468" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="S468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="S468" s="1" t="n">
-        <v>0.03404</v>
+      <c r="T468" s="1" t="n">
+        <v>0.034</v>
       </c>
     </row>
     <row r="469">
@@ -29079,9 +30486,12 @@
         <v>0.1614</v>
       </c>
       <c r="R469" s="1" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="S469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="S469" s="1" t="n">
+      <c r="T469" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -29140,9 +30550,12 @@
         <v>0.4084</v>
       </c>
       <c r="R470" s="1" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="S470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="S470" s="1" t="n">
+      <c r="T470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -29201,9 +30614,12 @@
         <v>0.06854</v>
       </c>
       <c r="R471" s="1" t="n">
+        <v>0.06876</v>
+      </c>
+      <c r="S471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="S471" s="1" t="n">
+      <c r="T471" s="1" t="n">
         <v>0.06854</v>
       </c>
     </row>
@@ -29262,9 +30678,12 @@
         <v>0.06541</v>
       </c>
       <c r="R472" s="1" t="n">
+        <v>0.06549000000000001</v>
+      </c>
+      <c r="S472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="S472" s="1" t="n">
+      <c r="T472" s="1" t="n">
         <v>0.06541</v>
       </c>
     </row>
@@ -29323,9 +30742,12 @@
         <v>0.01621</v>
       </c>
       <c r="R473" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="S473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="S473" s="1" t="n">
+      <c r="T473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -29384,9 +30806,12 @@
         <v>0.2068</v>
       </c>
       <c r="R474" s="1" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="S474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="S474" s="1" t="n">
+      <c r="T474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -29445,10 +30870,13 @@
         <v>0.04202</v>
       </c>
       <c r="R475" s="1" t="n">
+        <v>0.04183</v>
+      </c>
+      <c r="S475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="S475" s="1" t="n">
-        <v>0.042</v>
+      <c r="T475" s="1" t="n">
+        <v>0.04183</v>
       </c>
     </row>
     <row r="476">
@@ -29506,9 +30934,12 @@
         <v>1.56</v>
       </c>
       <c r="R476" s="1" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="S476" s="1" t="n">
+      <c r="T476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -29567,9 +30998,12 @@
         <v>0.1002</v>
       </c>
       <c r="R477" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="S477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="S477" s="1" t="n">
+      <c r="T477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -29628,9 +31062,12 @@
         <v>0.001155</v>
       </c>
       <c r="R478" s="1" t="n">
+        <v>0.001155</v>
+      </c>
+      <c r="S478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="S478" s="1" t="n">
+      <c r="T478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -29689,9 +31126,12 @@
         <v>0.1436</v>
       </c>
       <c r="R479" s="1" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="S479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="S479" s="1" t="n">
+      <c r="T479" s="1" t="n">
         <v>0.1433</v>
       </c>
     </row>
@@ -29750,9 +31190,12 @@
         <v>0.001794</v>
       </c>
       <c r="R480" s="1" t="n">
-        <v>0.001794</v>
+        <v>0.001842</v>
       </c>
       <c r="S480" s="1" t="n">
+        <v>0.001842</v>
+      </c>
+      <c r="T480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -29811,9 +31254,12 @@
         <v>0.904</v>
       </c>
       <c r="R481" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="S481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="S481" s="1" t="n">
+      <c r="T481" s="1" t="n">
         <v>0.904</v>
       </c>
     </row>
@@ -29872,10 +31318,13 @@
         <v>0.13262</v>
       </c>
       <c r="R482" s="1" t="n">
+        <v>0.13233</v>
+      </c>
+      <c r="S482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="S482" s="1" t="n">
-        <v>0.13262</v>
+      <c r="T482" s="1" t="n">
+        <v>0.13233</v>
       </c>
     </row>
     <row r="483">
@@ -29933,9 +31382,12 @@
         <v>0.04015</v>
       </c>
       <c r="R483" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="S483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="S483" s="1" t="n">
+      <c r="T483" s="1" t="n">
         <v>0.04005</v>
       </c>
     </row>
@@ -29994,9 +31446,12 @@
         <v>0.2999</v>
       </c>
       <c r="R484" s="1" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="S484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="S484" s="1" t="n">
+      <c r="T484" s="1" t="n">
         <v>0.2999</v>
       </c>
     </row>
@@ -30055,9 +31510,12 @@
         <v>0.05653</v>
       </c>
       <c r="R485" s="1" t="n">
+        <v>0.05654</v>
+      </c>
+      <c r="S485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="S485" s="1" t="n">
+      <c r="T485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -30116,9 +31574,12 @@
         <v>0.001558</v>
       </c>
       <c r="R486" s="1" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="S486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="S486" s="1" t="n">
+      <c r="T486" s="1" t="n">
         <v>0.001558</v>
       </c>
     </row>
@@ -30177,9 +31638,12 @@
         <v>0.06662</v>
       </c>
       <c r="R487" s="1" t="n">
+        <v>0.06676</v>
+      </c>
+      <c r="S487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="S487" s="1" t="n">
+      <c r="T487" s="1" t="n">
         <v>0.06662</v>
       </c>
     </row>
@@ -30238,9 +31702,12 @@
         <v>0.1914</v>
       </c>
       <c r="R488" s="1" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="S488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="S488" s="1" t="n">
+      <c r="T488" s="1" t="n">
         <v>0.1911</v>
       </c>
     </row>
@@ -30299,9 +31766,12 @@
         <v>0.04771</v>
       </c>
       <c r="R489" s="1" t="n">
+        <v>0.04772</v>
+      </c>
+      <c r="S489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="S489" s="1" t="n">
+      <c r="T489" s="1" t="n">
         <v>0.04768</v>
       </c>
     </row>
@@ -30360,9 +31830,12 @@
         <v>0.1393</v>
       </c>
       <c r="R490" s="1" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="S490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="S490" s="1" t="n">
+      <c r="T490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -30421,9 +31894,12 @@
         <v>0.02234</v>
       </c>
       <c r="R491" s="1" t="n">
+        <v>0.02236</v>
+      </c>
+      <c r="S491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="S491" s="1" t="n">
+      <c r="T491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -30482,9 +31958,12 @@
         <v>0.007711</v>
       </c>
       <c r="R492" s="1" t="n">
+        <v>0.007734</v>
+      </c>
+      <c r="S492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="S492" s="1" t="n">
+      <c r="T492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -30543,9 +32022,12 @@
         <v>0.0005927</v>
       </c>
       <c r="R493" s="1" t="n">
+        <v>0.0005932</v>
+      </c>
+      <c r="S493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="S493" s="1" t="n">
+      <c r="T493" s="1" t="n">
         <v>0.0005918</v>
       </c>
     </row>
@@ -30604,9 +32086,12 @@
         <v>3.024</v>
       </c>
       <c r="R494" s="1" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="S494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="S494" s="1" t="n">
+      <c r="T494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -30665,9 +32150,12 @@
         <v>0.05043</v>
       </c>
       <c r="R495" s="1" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="S495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="S495" s="1" t="n">
+      <c r="T495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -30726,9 +32214,12 @@
         <v>0.006802</v>
       </c>
       <c r="R496" s="1" t="n">
+        <v>0.006847</v>
+      </c>
+      <c r="S496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="S496" s="1" t="n">
+      <c r="T496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -30787,9 +32278,12 @@
         <v>1.303</v>
       </c>
       <c r="R497" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="S497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="S497" s="1" t="n">
+      <c r="T497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -30848,9 +32342,12 @@
         <v>0.03914</v>
       </c>
       <c r="R498" s="1" t="n">
+        <v>0.03912</v>
+      </c>
+      <c r="S498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="S498" s="1" t="n">
+      <c r="T498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -30909,9 +32406,12 @@
         <v>0.0409</v>
       </c>
       <c r="R499" s="1" t="n">
+        <v>0.04096</v>
+      </c>
+      <c r="S499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="S499" s="1" t="n">
+      <c r="T499" s="1" t="n">
         <v>0.04085</v>
       </c>
     </row>
@@ -30970,9 +32470,12 @@
         <v>0.00543</v>
       </c>
       <c r="R500" s="1" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="S500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="S500" s="1" t="n">
+      <c r="T500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -31031,9 +32534,12 @@
         <v>0.03548</v>
       </c>
       <c r="R501" s="1" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="S501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="S501" s="1" t="n">
+      <c r="T501" s="1" t="n">
         <v>0.03548</v>
       </c>
     </row>
@@ -31092,9 +32598,12 @@
         <v>0.07206</v>
       </c>
       <c r="R502" s="1" t="n">
+        <v>0.07216</v>
+      </c>
+      <c r="S502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="S502" s="1" t="n">
+      <c r="T502" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -31153,9 +32662,12 @@
         <v>0.0007433</v>
       </c>
       <c r="R503" s="1" t="n">
+        <v>0.0007427999999999999</v>
+      </c>
+      <c r="S503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="S503" s="1" t="n">
+      <c r="T503" s="1" t="n">
         <v>0.0007412</v>
       </c>
     </row>
@@ -31214,9 +32726,12 @@
         <v>0.016014</v>
       </c>
       <c r="R504" s="1" t="n">
+        <v>0.01602</v>
+      </c>
+      <c r="S504" s="1" t="n">
         <v>0.016034</v>
       </c>
-      <c r="S504" s="1" t="n">
+      <c r="T504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -31275,9 +32790,12 @@
         <v>0.00702</v>
       </c>
       <c r="R505" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="S505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="S505" s="1" t="n">
+      <c r="T505" s="1" t="n">
         <v>0.00702</v>
       </c>
     </row>
@@ -31336,9 +32854,12 @@
         <v>0.0252</v>
       </c>
       <c r="R506" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="S506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="S506" s="1" t="n">
+      <c r="T506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -31397,9 +32918,12 @@
         <v>0.001346</v>
       </c>
       <c r="R507" s="1" t="n">
+        <v>0.001346</v>
+      </c>
+      <c r="S507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="S507" s="1" t="n">
+      <c r="T507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -31458,9 +32982,12 @@
         <v>0.2811</v>
       </c>
       <c r="R508" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="S508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="S508" s="1" t="n">
+      <c r="T508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -31519,9 +33046,12 @@
         <v>0.1316</v>
       </c>
       <c r="R509" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="S509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="S509" s="1" t="n">
+      <c r="T509" s="1" t="n">
         <v>0.1314</v>
       </c>
     </row>
@@ -31580,9 +33110,12 @@
         <v>0.04884</v>
       </c>
       <c r="R510" s="1" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="S510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="S510" s="1" t="n">
+      <c r="T510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -31641,9 +33174,12 @@
         <v>0.00271</v>
       </c>
       <c r="R511" s="1" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="S511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="S511" s="1" t="n">
+      <c r="T511" s="1" t="n">
         <v>0.00271</v>
       </c>
     </row>
@@ -31702,9 +33238,12 @@
         <v>0.015044</v>
       </c>
       <c r="R512" s="1" t="n">
+        <v>0.015051</v>
+      </c>
+      <c r="S512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="S512" s="1" t="n">
+      <c r="T512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -31763,9 +33302,12 @@
         <v>0.6914</v>
       </c>
       <c r="R513" s="1" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="S513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="S513" s="1" t="n">
+      <c r="T513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -31824,9 +33366,12 @@
         <v>0.004476</v>
       </c>
       <c r="R514" s="1" t="n">
+        <v>0.004496</v>
+      </c>
+      <c r="S514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="S514" s="1" t="n">
+      <c r="T514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -31885,9 +33430,12 @@
         <v>0.005019</v>
       </c>
       <c r="R515" s="1" t="n">
+        <v>0.005026</v>
+      </c>
+      <c r="S515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="S515" s="1" t="n">
+      <c r="T515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -31946,9 +33494,12 @@
         <v>0.06327000000000001</v>
       </c>
       <c r="R516" s="1" t="n">
+        <v>0.06335</v>
+      </c>
+      <c r="S516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="S516" s="1" t="n">
+      <c r="T516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -32007,9 +33558,12 @@
         <v>0.06525</v>
       </c>
       <c r="R517" s="1" t="n">
+        <v>0.06551999999999999</v>
+      </c>
+      <c r="S517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="S517" s="1" t="n">
+      <c r="T517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -32068,9 +33622,12 @@
         <v>0.01198</v>
       </c>
       <c r="R518" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="S518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="S518" s="1" t="n">
+      <c r="T518" s="1" t="n">
         <v>0.01198</v>
       </c>
     </row>
@@ -32129,9 +33686,12 @@
         <v>0.0474</v>
       </c>
       <c r="R519" s="1" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="S519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="S519" s="1" t="n">
+      <c r="T519" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -32190,9 +33750,12 @@
         <v>0.04358</v>
       </c>
       <c r="R520" s="1" t="n">
+        <v>0.04364</v>
+      </c>
+      <c r="S520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="S520" s="1" t="n">
+      <c r="T520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -32251,9 +33814,12 @@
         <v>0.008418999999999999</v>
       </c>
       <c r="R521" s="1" t="n">
+        <v>0.008425999999999999</v>
+      </c>
+      <c r="S521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="S521" s="1" t="n">
+      <c r="T521" s="1" t="n">
         <v>0.008402</v>
       </c>
     </row>
@@ -32312,9 +33878,12 @@
         <v>0.08762</v>
       </c>
       <c r="R522" s="1" t="n">
+        <v>0.08772000000000001</v>
+      </c>
+      <c r="S522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="S522" s="1" t="n">
+      <c r="T522" s="1" t="n">
         <v>0.08762</v>
       </c>
     </row>
@@ -32373,9 +33942,12 @@
         <v>0.00643</v>
       </c>
       <c r="R523" s="1" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="S523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="S523" s="1" t="n">
+      <c r="T523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -32434,9 +34006,12 @@
         <v>0.01632</v>
       </c>
       <c r="R524" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="S524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="S524" s="1" t="n">
+      <c r="T524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -32495,9 +34070,12 @@
         <v>0.01762</v>
       </c>
       <c r="R525" s="1" t="n">
+        <v>0.01773</v>
+      </c>
+      <c r="S525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="S525" s="1" t="n">
+      <c r="T525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -32556,9 +34134,12 @@
         <v>0.07865</v>
       </c>
       <c r="R526" s="1" t="n">
+        <v>0.07897999999999999</v>
+      </c>
+      <c r="S526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="S526" s="1" t="n">
+      <c r="T526" s="1" t="n">
         <v>0.07862</v>
       </c>
     </row>
@@ -32617,9 +34198,12 @@
         <v>0.01605</v>
       </c>
       <c r="R527" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="S527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="S527" s="1" t="n">
+      <c r="T527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -32678,10 +34262,13 @@
         <v>0.004168</v>
       </c>
       <c r="R528" s="1" t="n">
+        <v>0.004151</v>
+      </c>
+      <c r="S528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="S528" s="1" t="n">
-        <v>0.004159</v>
+      <c r="T528" s="1" t="n">
+        <v>0.004151</v>
       </c>
     </row>
     <row r="529">
@@ -32739,9 +34326,12 @@
         <v>0.003678</v>
       </c>
       <c r="R529" s="1" t="n">
+        <v>0.003678</v>
+      </c>
+      <c r="S529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="S529" s="1" t="n">
+      <c r="T529" s="1" t="n">
         <v>0.003672</v>
       </c>
     </row>
@@ -32800,9 +34390,12 @@
         <v>1.328</v>
       </c>
       <c r="R530" s="1" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="S530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="S530" s="1" t="n">
+      <c r="T530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -32861,9 +34454,12 @@
         <v>0.4874</v>
       </c>
       <c r="R531" s="1" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="S531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="S531" s="1" t="n">
+      <c r="T531" s="1" t="n">
         <v>0.487</v>
       </c>
     </row>
@@ -32922,9 +34518,12 @@
         <v>0.03063</v>
       </c>
       <c r="R532" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="S532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="S532" s="1" t="n">
+      <c r="T532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -32983,9 +34582,12 @@
         <v>0.1526</v>
       </c>
       <c r="R533" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="S533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="S533" s="1" t="n">
+      <c r="T533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -33044,9 +34646,12 @@
         <v>0.05352</v>
       </c>
       <c r="R534" s="1" t="n">
+        <v>0.05359</v>
+      </c>
+      <c r="S534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="S534" s="1" t="n">
+      <c r="T534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -33105,9 +34710,12 @@
         <v>0.01483</v>
       </c>
       <c r="R535" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="S535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="S535" s="1" t="n">
+      <c r="T535" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -33166,9 +34774,12 @@
         <v>0.059</v>
       </c>
       <c r="R536" s="1" t="n">
+        <v>0.05863</v>
+      </c>
+      <c r="S536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="S536" s="1" t="n">
+      <c r="T536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -33227,9 +34838,12 @@
         <v>0.05481</v>
       </c>
       <c r="R537" s="1" t="n">
+        <v>0.05484</v>
+      </c>
+      <c r="S537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="S537" s="1" t="n">
+      <c r="T537" s="1" t="n">
         <v>0.05476</v>
       </c>
     </row>
@@ -33288,9 +34902,12 @@
         <v>0.106</v>
       </c>
       <c r="R538" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="S538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="S538" s="1" t="n">
+      <c r="T538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -33349,10 +34966,13 @@
         <v>0.01268</v>
       </c>
       <c r="R539" s="1" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="S539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="S539" s="1" t="n">
-        <v>0.01266</v>
+      <c r="T539" s="1" t="n">
+        <v>0.01265</v>
       </c>
     </row>
     <row r="540">
@@ -33410,10 +35030,13 @@
         <v>0.1728</v>
       </c>
       <c r="R540" s="1" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="S540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="S540" s="1" t="n">
-        <v>0.1725</v>
+      <c r="T540" s="1" t="n">
+        <v>0.1723</v>
       </c>
     </row>
     <row r="541">
@@ -33471,9 +35094,12 @@
         <v>0.123</v>
       </c>
       <c r="R541" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="S541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="S541" s="1" t="n">
+      <c r="T541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -33532,9 +35158,12 @@
         <v>0.02479</v>
       </c>
       <c r="R542" s="1" t="n">
+        <v>0.02484</v>
+      </c>
+      <c r="S542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="S542" s="1" t="n">
+      <c r="T542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -33593,9 +35222,12 @@
         <v>0.05852</v>
       </c>
       <c r="R543" s="1" t="n">
+        <v>0.05858</v>
+      </c>
+      <c r="S543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="S543" s="1" t="n">
+      <c r="T543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V543"/>
+  <dimension ref="A1:W543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -439,8 +439,9 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,10 +547,15 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>price_04:45</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -619,9 +625,12 @@
         <v>71260.7</v>
       </c>
       <c r="U2" s="1" t="n">
+        <v>71264.89999999999</v>
+      </c>
+      <c r="V2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="V2" s="1" t="n">
+      <c r="W2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -689,9 +698,12 @@
         <v>2109.27</v>
       </c>
       <c r="U3" s="1" t="n">
+        <v>2109.57</v>
+      </c>
+      <c r="V3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="V3" s="1" t="n">
+      <c r="W3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -759,9 +771,12 @@
         <v>88.84999999999999</v>
       </c>
       <c r="U4" s="1" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="V4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="W4" s="1" t="n">
         <v>88.7</v>
       </c>
     </row>
@@ -829,9 +844,12 @@
         <v>3.877</v>
       </c>
       <c r="U5" s="1" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="V5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="W5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -899,9 +917,12 @@
         <v>1.403</v>
       </c>
       <c r="U6" s="1" t="n">
+        <v>1.4026</v>
+      </c>
+      <c r="V6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="W6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -969,9 +990,12 @@
         <v>0.09626999999999999</v>
       </c>
       <c r="U7" s="1" t="n">
+        <v>0.09637</v>
+      </c>
+      <c r="V7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -1039,9 +1063,12 @@
         <v>0.014167</v>
       </c>
       <c r="U8" s="1" t="n">
+        <v>0.014199</v>
+      </c>
+      <c r="V8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="V8" s="1" t="n">
+      <c r="W8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -1109,9 +1136,12 @@
         <v>657.42</v>
       </c>
       <c r="U9" s="1" t="n">
+        <v>656.91</v>
+      </c>
+      <c r="V9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="V9" s="1" t="n">
+      <c r="W9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1179,9 +1209,12 @@
         <v>20.464</v>
       </c>
       <c r="U10" s="1" t="n">
+        <v>20.216</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>20.464</v>
       </c>
-      <c r="V10" s="1" t="n">
+      <c r="W10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1249,9 +1282,12 @@
         <v>0.0033968</v>
       </c>
       <c r="U11" s="1" t="n">
+        <v>0.0033964</v>
+      </c>
+      <c r="V11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="V11" s="1" t="n">
+      <c r="W11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1319,9 +1355,12 @@
         <v>36.869</v>
       </c>
       <c r="U12" s="1" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>36.869</v>
       </c>
-      <c r="V12" s="1" t="n">
+      <c r="W12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1389,10 +1428,13 @@
         <v>211.7</v>
       </c>
       <c r="U13" s="1" t="n">
+        <v>211.58</v>
+      </c>
+      <c r="V13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="V13" s="1" t="n">
-        <v>211.7</v>
+      <c r="W13" s="1" t="n">
+        <v>211.58</v>
       </c>
     </row>
     <row r="14">
@@ -1459,9 +1501,12 @@
         <v>0.0011316</v>
       </c>
       <c r="U14" s="1" t="n">
+        <v>0.0011298</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="V14" s="1" t="n">
+      <c r="W14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1529,9 +1574,12 @@
         <v>0.33108</v>
       </c>
       <c r="U15" s="1" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="V15" s="1" t="n">
+      <c r="W15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1599,9 +1647,12 @@
         <v>231.42</v>
       </c>
       <c r="U16" s="1" t="n">
+        <v>232.09</v>
+      </c>
+      <c r="V16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="V16" s="1" t="n">
+      <c r="W16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -1669,9 +1720,12 @@
         <v>1.0017</v>
       </c>
       <c r="U17" s="1" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="V17" s="1" t="n">
+      <c r="W17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1739,9 +1793,12 @@
         <v>0.2671</v>
       </c>
       <c r="U18" s="1" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="V18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="V18" s="1" t="n">
+      <c r="W18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1809,9 +1866,12 @@
         <v>9.776</v>
       </c>
       <c r="U19" s="1" t="n">
+        <v>9.772</v>
+      </c>
+      <c r="V19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="V19" s="1" t="n">
+      <c r="W19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -1879,9 +1939,12 @@
         <v>5015.33</v>
       </c>
       <c r="U20" s="1" t="n">
+        <v>5024.45</v>
+      </c>
+      <c r="V20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="V20" s="1" t="n">
+      <c r="W20" s="1" t="n">
         <v>5015.33</v>
       </c>
     </row>
@@ -1949,9 +2012,12 @@
         <v>463.07</v>
       </c>
       <c r="U21" s="1" t="n">
+        <v>463.14</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="V21" s="1" t="n">
+      <c r="W21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -2019,9 +2085,12 @@
         <v>1.3686</v>
       </c>
       <c r="U22" s="1" t="n">
+        <v>1.3854</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="V22" s="1" t="n">
+      <c r="W22" s="1" t="n">
         <v>1.3686</v>
       </c>
     </row>
@@ -2089,9 +2158,12 @@
         <v>1.0649</v>
       </c>
       <c r="U23" s="1" t="n">
+        <v>1.0364</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="V23" s="1" t="n">
+      <c r="W23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2159,9 +2231,12 @@
         <v>1.342</v>
       </c>
       <c r="U24" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="V24" s="1" t="n">
+      <c r="W24" s="1" t="n">
         <v>1.342</v>
       </c>
     </row>
@@ -2229,9 +2304,12 @@
         <v>9.159000000000001</v>
       </c>
       <c r="U25" s="1" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="V25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="V25" s="1" t="n">
+      <c r="W25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -2299,10 +2377,13 @@
         <v>0.3696</v>
       </c>
       <c r="U26" s="1" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="V26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="V26" s="1" t="n">
-        <v>0.368</v>
+      <c r="W26" s="1" t="n">
+        <v>0.367</v>
       </c>
     </row>
     <row r="27">
@@ -2369,9 +2450,12 @@
         <v>0.87</v>
       </c>
       <c r="U27" s="1" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="V27" s="1" t="n">
+      <c r="W27" s="1" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -2439,9 +2523,12 @@
         <v>1.833</v>
       </c>
       <c r="U28" s="1" t="n">
+        <v>1.835</v>
+      </c>
+      <c r="V28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="V28" s="1" t="n">
+      <c r="W28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2509,9 +2596,12 @@
         <v>0.1095</v>
       </c>
       <c r="U29" s="1" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="V29" s="1" t="n">
+      <c r="W29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -2579,9 +2669,12 @@
         <v>0.002022</v>
       </c>
       <c r="U30" s="1" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="V30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="V30" s="1" t="n">
+      <c r="W30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -2649,9 +2742,12 @@
         <v>1.46</v>
       </c>
       <c r="U31" s="1" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="V31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="V31" s="1" t="n">
+      <c r="W31" s="1" t="n">
         <v>1.46</v>
       </c>
     </row>
@@ -2719,9 +2815,12 @@
         <v>0.1774</v>
       </c>
       <c r="U32" s="1" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="V32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="V32" s="1" t="n">
+      <c r="W32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2789,9 +2888,12 @@
         <v>0.1038</v>
       </c>
       <c r="U33" s="1" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="V33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="V33" s="1" t="n">
+      <c r="W33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -2859,9 +2961,12 @@
         <v>113.28</v>
       </c>
       <c r="U34" s="1" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="V34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="V34" s="1" t="n">
+      <c r="W34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -2929,9 +3034,12 @@
         <v>6.812</v>
       </c>
       <c r="U35" s="1" t="n">
+        <v>6.867</v>
+      </c>
+      <c r="V35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="V35" s="1" t="n">
+      <c r="W35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2999,9 +3107,12 @@
         <v>0.017562</v>
       </c>
       <c r="U36" s="1" t="n">
+        <v>0.017605</v>
+      </c>
+      <c r="V36" s="1" t="n">
         <v>0.017668</v>
       </c>
-      <c r="V36" s="1" t="n">
+      <c r="W36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -3069,9 +3180,12 @@
         <v>0.3609</v>
       </c>
       <c r="U37" s="1" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="V37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="V37" s="1" t="n">
+      <c r="W37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -3139,9 +3253,12 @@
         <v>55.65</v>
       </c>
       <c r="U38" s="1" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="V38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="V38" s="1" t="n">
+      <c r="W38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -3209,9 +3326,12 @@
         <v>0.5717</v>
       </c>
       <c r="U39" s="1" t="n">
+        <v>0.57506</v>
+      </c>
+      <c r="V39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="V39" s="1" t="n">
+      <c r="W39" s="1" t="n">
         <v>0.5717</v>
       </c>
     </row>
@@ -3279,9 +3399,12 @@
         <v>4.023</v>
       </c>
       <c r="U40" s="1" t="n">
+        <v>4.026</v>
+      </c>
+      <c r="V40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="V40" s="1" t="n">
+      <c r="W40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -3349,9 +3472,12 @@
         <v>0.04892</v>
       </c>
       <c r="U41" s="1" t="n">
+        <v>0.04909</v>
+      </c>
+      <c r="V41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="V41" s="1" t="n">
+      <c r="W41" s="1" t="n">
         <v>0.04892</v>
       </c>
     </row>
@@ -3419,9 +3545,12 @@
         <v>0.7022</v>
       </c>
       <c r="U42" s="1" t="n">
+        <v>0.7027</v>
+      </c>
+      <c r="V42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="V42" s="1" t="n">
+      <c r="W42" s="1" t="n">
         <v>0.6995</v>
       </c>
     </row>
@@ -3489,9 +3618,12 @@
         <v>0.22713</v>
       </c>
       <c r="U43" s="1" t="n">
+        <v>0.22763</v>
+      </c>
+      <c r="V43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="V43" s="1" t="n">
+      <c r="W43" s="1" t="n">
         <v>0.22713</v>
       </c>
     </row>
@@ -3559,9 +3691,12 @@
         <v>0.35943</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>0.35992</v>
+        <v>0.3603</v>
       </c>
       <c r="V44" s="1" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="W44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -3629,9 +3764,12 @@
         <v>0.1688</v>
       </c>
       <c r="U45" s="1" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="V45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="V45" s="1" t="n">
+      <c r="W45" s="1" t="n">
         <v>0.1682</v>
       </c>
     </row>
@@ -3699,9 +3837,12 @@
         <v>0.026</v>
       </c>
       <c r="U46" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="V46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="V46" s="1" t="n">
+      <c r="W46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -3769,9 +3910,12 @@
         <v>0.005967</v>
       </c>
       <c r="U47" s="1" t="n">
+        <v>0.005965</v>
+      </c>
+      <c r="V47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="V47" s="1" t="n">
+      <c r="W47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -3839,9 +3983,12 @@
         <v>0.007391</v>
       </c>
       <c r="U48" s="1" t="n">
+        <v>0.007388</v>
+      </c>
+      <c r="V48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="V48" s="1" t="n">
+      <c r="W48" s="1" t="n">
         <v>0.007343</v>
       </c>
     </row>
@@ -3909,9 +4056,12 @@
         <v>0.1099</v>
       </c>
       <c r="U49" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="V49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="V49" s="1" t="n">
+      <c r="W49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3979,9 +4129,12 @@
         <v>0.04222</v>
       </c>
       <c r="U50" s="1" t="n">
+        <v>0.04213</v>
+      </c>
+      <c r="V50" s="1" t="n">
         <v>0.04222</v>
       </c>
-      <c r="V50" s="1" t="n">
+      <c r="W50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -4049,9 +4202,12 @@
         <v>0.1614</v>
       </c>
       <c r="U51" s="1" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="V51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="V51" s="1" t="n">
+      <c r="W51" s="1" t="n">
         <v>0.1614</v>
       </c>
     </row>
@@ -4119,9 +4275,12 @@
         <v>0.00354</v>
       </c>
       <c r="U52" s="1" t="n">
+        <v>0.00356</v>
+      </c>
+      <c r="V52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="V52" s="1" t="n">
+      <c r="W52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -4189,9 +4348,12 @@
         <v>2.63</v>
       </c>
       <c r="U53" s="1" t="n">
+        <v>2.623</v>
+      </c>
+      <c r="V53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="V53" s="1" t="n">
+      <c r="W53" s="1" t="n">
         <v>2.613</v>
       </c>
     </row>
@@ -4259,9 +4421,12 @@
         <v>0.006193</v>
       </c>
       <c r="U54" s="1" t="n">
+        <v>0.006192</v>
+      </c>
+      <c r="V54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="V54" s="1" t="n">
+      <c r="W54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -4329,10 +4494,13 @@
         <v>0.0283</v>
       </c>
       <c r="U55" s="1" t="n">
+        <v>0.02785</v>
+      </c>
+      <c r="V55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="V55" s="1" t="n">
-        <v>0.0283</v>
+      <c r="W55" s="1" t="n">
+        <v>0.02785</v>
       </c>
     </row>
     <row r="56">
@@ -4399,9 +4567,12 @@
         <v>0.7342</v>
       </c>
       <c r="U56" s="1" t="n">
+        <v>0.7341</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="V56" s="1" t="n">
+      <c r="W56" s="1" t="n">
         <v>0.7322</v>
       </c>
     </row>
@@ -4469,9 +4640,12 @@
         <v>0.1034</v>
       </c>
       <c r="U57" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="V57" s="1" t="n">
+      <c r="W57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -4539,9 +4713,12 @@
         <v>0.9369</v>
       </c>
       <c r="U58" s="1" t="n">
+        <v>0.9373</v>
+      </c>
+      <c r="V58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="V58" s="1" t="n">
+      <c r="W58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -4609,9 +4786,12 @@
         <v>0.08691</v>
       </c>
       <c r="U59" s="1" t="n">
+        <v>0.08452999999999999</v>
+      </c>
+      <c r="V59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="V59" s="1" t="n">
+      <c r="W59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -4679,9 +4859,12 @@
         <v>0.07027</v>
       </c>
       <c r="U60" s="1" t="n">
+        <v>0.06977999999999999</v>
+      </c>
+      <c r="V60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="V60" s="1" t="n">
+      <c r="W60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -4749,9 +4932,12 @@
         <v>0.05472</v>
       </c>
       <c r="U61" s="1" t="n">
+        <v>0.05448</v>
+      </c>
+      <c r="V61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="V61" s="1" t="n">
+      <c r="W61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -4819,9 +5005,12 @@
         <v>0.010598</v>
       </c>
       <c r="U62" s="1" t="n">
+        <v>0.010395</v>
+      </c>
+      <c r="V62" s="1" t="n">
         <v>0.010624</v>
       </c>
-      <c r="V62" s="1" t="n">
+      <c r="W62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -4889,9 +5078,12 @@
         <v>0.29207</v>
       </c>
       <c r="U63" s="1" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="V63" s="1" t="n">
         <v>0.29207</v>
       </c>
-      <c r="V63" s="1" t="n">
+      <c r="W63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -4959,9 +5151,12 @@
         <v>0.07452</v>
       </c>
       <c r="U64" s="1" t="n">
+        <v>0.07369000000000001</v>
+      </c>
+      <c r="V64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="V64" s="1" t="n">
+      <c r="W64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -5029,9 +5224,12 @@
         <v>0.3154</v>
       </c>
       <c r="U65" s="1" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="V65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="V65" s="1" t="n">
+      <c r="W65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -5099,9 +5297,12 @@
         <v>0.16283</v>
       </c>
       <c r="U66" s="1" t="n">
+        <v>0.16375</v>
+      </c>
+      <c r="V66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="V66" s="1" t="n">
+      <c r="W66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -5169,9 +5370,12 @@
         <v>0.12022</v>
       </c>
       <c r="U67" s="1" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="V67" s="1" t="n">
         <v>0.1203</v>
       </c>
-      <c r="V67" s="1" t="n">
+      <c r="W67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -5239,9 +5443,12 @@
         <v>0.09474</v>
       </c>
       <c r="U68" s="1" t="n">
+        <v>0.09490999999999999</v>
+      </c>
+      <c r="V68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="V68" s="1" t="n">
+      <c r="W68" s="1" t="n">
         <v>0.09474</v>
       </c>
     </row>
@@ -5309,9 +5516,12 @@
         <v>0.124</v>
       </c>
       <c r="U69" s="1" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="V69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="V69" s="1" t="n">
+      <c r="W69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -5379,9 +5589,12 @@
         <v>8.52</v>
       </c>
       <c r="U70" s="1" t="n">
+        <v>8.529</v>
+      </c>
+      <c r="V70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="V70" s="1" t="n">
+      <c r="W70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -5449,9 +5662,12 @@
         <v>0.239</v>
       </c>
       <c r="U71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="V71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="V71" s="1" t="n">
+      <c r="W71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -5519,10 +5735,13 @@
         <v>0.04984</v>
       </c>
       <c r="U72" s="1" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="V72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="V72" s="1" t="n">
-        <v>0.04969</v>
+      <c r="W72" s="1" t="n">
+        <v>0.04955</v>
       </c>
     </row>
     <row r="73">
@@ -5589,9 +5808,12 @@
         <v>0.05073</v>
       </c>
       <c r="U73" s="1" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="V73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="V73" s="1" t="n">
+      <c r="W73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -5659,10 +5881,13 @@
         <v>0.1253</v>
       </c>
       <c r="U74" s="1" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="V74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="V74" s="1" t="n">
-        <v>0.124</v>
+      <c r="W74" s="1" t="n">
+        <v>0.1234</v>
       </c>
     </row>
     <row r="75">
@@ -5729,9 +5954,12 @@
         <v>0.04668</v>
       </c>
       <c r="U75" s="1" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="V75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="V75" s="1" t="n">
+      <c r="W75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -5799,10 +6027,13 @@
         <v>0.06668</v>
       </c>
       <c r="U76" s="1" t="n">
+        <v>0.0664</v>
+      </c>
+      <c r="V76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="V76" s="1" t="n">
-        <v>0.06668</v>
+      <c r="W76" s="1" t="n">
+        <v>0.0664</v>
       </c>
     </row>
     <row r="77">
@@ -5869,9 +6100,12 @@
         <v>0.13299</v>
       </c>
       <c r="U77" s="1" t="n">
-        <v>0.13357</v>
+        <v>0.13509</v>
       </c>
       <c r="V77" s="1" t="n">
+        <v>0.13509</v>
+      </c>
+      <c r="W77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -5939,9 +6173,12 @@
         <v>0.1617</v>
       </c>
       <c r="U78" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="V78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="V78" s="1" t="n">
+      <c r="W78" s="1" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -6009,9 +6246,12 @@
         <v>0.02695</v>
       </c>
       <c r="U79" s="1" t="n">
+        <v>0.02699</v>
+      </c>
+      <c r="V79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="V79" s="1" t="n">
+      <c r="W79" s="1" t="n">
         <v>0.02693</v>
       </c>
     </row>
@@ -6079,9 +6319,12 @@
         <v>358.73</v>
       </c>
       <c r="U80" s="1" t="n">
-        <v>359.36</v>
+        <v>361.56</v>
       </c>
       <c r="V80" s="1" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="W80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -6149,9 +6392,12 @@
         <v>7.071000000000001e-05</v>
       </c>
       <c r="U81" s="1" t="n">
+        <v>7.064e-05</v>
+      </c>
+      <c r="V81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="V81" s="1" t="n">
+      <c r="W81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -6219,9 +6465,12 @@
         <v>0.2653</v>
       </c>
       <c r="U82" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="V82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="V82" s="1" t="n">
+      <c r="W82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -6289,9 +6538,12 @@
         <v>1.1147</v>
       </c>
       <c r="U83" s="1" t="n">
+        <v>1.1224</v>
+      </c>
+      <c r="V83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="V83" s="1" t="n">
+      <c r="W83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -6359,9 +6611,12 @@
         <v>0.352</v>
       </c>
       <c r="U84" s="1" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="V84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="V84" s="1" t="n">
+      <c r="W84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -6429,9 +6684,12 @@
         <v>1.9568</v>
       </c>
       <c r="U85" s="1" t="n">
+        <v>1.9669</v>
+      </c>
+      <c r="V85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="V85" s="1" t="n">
+      <c r="W85" s="1" t="n">
         <v>1.9568</v>
       </c>
     </row>
@@ -6499,9 +6757,12 @@
         <v>1.3164</v>
       </c>
       <c r="U86" s="1" t="n">
+        <v>1.3142</v>
+      </c>
+      <c r="V86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="V86" s="1" t="n">
+      <c r="W86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -6569,9 +6830,12 @@
         <v>32.56</v>
       </c>
       <c r="U87" s="1" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="V87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="V87" s="1" t="n">
+      <c r="W87" s="1" t="n">
         <v>32.52</v>
       </c>
     </row>
@@ -6639,9 +6903,12 @@
         <v>0.00949</v>
       </c>
       <c r="U88" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="V88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="V88" s="1" t="n">
+      <c r="W88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -6709,9 +6976,12 @@
         <v>0.01803</v>
       </c>
       <c r="U89" s="1" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="V89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="V89" s="1" t="n">
+      <c r="W89" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -6779,9 +7049,12 @@
         <v>0.03502</v>
       </c>
       <c r="U90" s="1" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="V90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="V90" s="1" t="n">
+      <c r="W90" s="1" t="n">
         <v>0.03468</v>
       </c>
     </row>
@@ -6849,9 +7122,12 @@
         <v>0.01174</v>
       </c>
       <c r="U91" s="1" t="n">
+        <v>0.01174</v>
+      </c>
+      <c r="V91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="V91" s="1" t="n">
+      <c r="W91" s="1" t="n">
         <v>0.01172</v>
       </c>
     </row>
@@ -6919,9 +7195,12 @@
         <v>3.095</v>
       </c>
       <c r="U92" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="V92" s="1" t="n">
+      <c r="W92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -6989,10 +7268,13 @@
         <v>0.005565</v>
       </c>
       <c r="U93" s="1" t="n">
+        <v>0.005559</v>
+      </c>
+      <c r="V93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="V93" s="1" t="n">
-        <v>0.005565</v>
+      <c r="W93" s="1" t="n">
+        <v>0.005559</v>
       </c>
     </row>
     <row r="94">
@@ -7059,9 +7341,12 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="U94" s="1" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="V94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="V94" s="1" t="n">
+      <c r="W94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -7129,9 +7414,12 @@
         <v>0.619</v>
       </c>
       <c r="U95" s="1" t="n">
-        <v>0.619</v>
+        <v>0.6234</v>
       </c>
       <c r="V95" s="1" t="n">
+        <v>0.6234</v>
+      </c>
+      <c r="W95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -7199,9 +7487,12 @@
         <v>1.27e-05</v>
       </c>
       <c r="U96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="V96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="V96" s="1" t="n">
+      <c r="W96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -7269,9 +7560,12 @@
         <v>1.1</v>
       </c>
       <c r="U97" s="1" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="V97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="V97" s="1" t="n">
+      <c r="W97" s="1" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -7339,9 +7633,12 @@
         <v>0.25252</v>
       </c>
       <c r="U98" s="1" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="V98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="V98" s="1" t="n">
+      <c r="W98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -7409,9 +7706,12 @@
         <v>1.15</v>
       </c>
       <c r="U99" s="1" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="V99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="V99" s="1" t="n">
+      <c r="W99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -7479,9 +7779,12 @@
         <v>1.855</v>
       </c>
       <c r="U100" s="1" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="V100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="V100" s="1" t="n">
+      <c r="W100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -7549,10 +7852,13 @@
         <v>0.01573</v>
       </c>
       <c r="U101" s="1" t="n">
+        <v>0.01563</v>
+      </c>
+      <c r="V101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="V101" s="1" t="n">
-        <v>0.01573</v>
+      <c r="W101" s="1" t="n">
+        <v>0.01563</v>
       </c>
     </row>
     <row r="102">
@@ -7619,9 +7925,12 @@
         <v>0.10062</v>
       </c>
       <c r="U102" s="1" t="n">
+        <v>0.10149</v>
+      </c>
+      <c r="V102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="V102" s="1" t="n">
+      <c r="W102" s="1" t="n">
         <v>0.10062</v>
       </c>
     </row>
@@ -7689,9 +7998,12 @@
         <v>0.0005965</v>
       </c>
       <c r="U103" s="1" t="n">
+        <v>0.0005967</v>
+      </c>
+      <c r="V103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="V103" s="1" t="n">
+      <c r="W103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -7759,9 +8071,12 @@
         <v>0.0005808</v>
       </c>
       <c r="U104" s="1" t="n">
+        <v>0.000576</v>
+      </c>
+      <c r="V104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="V104" s="1" t="n">
+      <c r="W104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -7829,9 +8144,12 @@
         <v>0.003231</v>
       </c>
       <c r="U105" s="1" t="n">
+        <v>0.003216</v>
+      </c>
+      <c r="V105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="V105" s="1" t="n">
+      <c r="W105" s="1" t="n">
         <v>0.003216</v>
       </c>
     </row>
@@ -7899,9 +8217,12 @@
         <v>2.572</v>
       </c>
       <c r="U106" s="1" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="V106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="V106" s="1" t="n">
+      <c r="W106" s="1" t="n">
         <v>2.572</v>
       </c>
     </row>
@@ -7969,9 +8290,12 @@
         <v>0.1658</v>
       </c>
       <c r="U107" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="V107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="V107" s="1" t="n">
+      <c r="W107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -8039,9 +8363,12 @@
         <v>0.09605</v>
       </c>
       <c r="U108" s="1" t="n">
+        <v>0.09582</v>
+      </c>
+      <c r="V108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="V108" s="1" t="n">
+      <c r="W108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -8109,9 +8436,12 @@
         <v>0.02207</v>
       </c>
       <c r="U109" s="1" t="n">
+        <v>0.02213</v>
+      </c>
+      <c r="V109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="V109" s="1" t="n">
+      <c r="W109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -8179,9 +8509,12 @@
         <v>0.2916</v>
       </c>
       <c r="U110" s="1" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="V110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="V110" s="1" t="n">
+      <c r="W110" s="1" t="n">
         <v>0.2894</v>
       </c>
     </row>
@@ -8249,9 +8582,12 @@
         <v>0.05712</v>
       </c>
       <c r="U111" s="1" t="n">
+        <v>0.05707</v>
+      </c>
+      <c r="V111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="V111" s="1" t="n">
+      <c r="W111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -8319,9 +8655,12 @@
         <v>0.301</v>
       </c>
       <c r="U112" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="V112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="V112" s="1" t="n">
+      <c r="W112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -8389,9 +8728,12 @@
         <v>18.55</v>
       </c>
       <c r="U113" s="1" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="V113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="V113" s="1" t="n">
+      <c r="W113" s="1" t="n">
         <v>18.53</v>
       </c>
     </row>
@@ -8459,9 +8801,12 @@
         <v>0.12753</v>
       </c>
       <c r="U114" s="1" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="V114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="V114" s="1" t="n">
+      <c r="W114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -8529,9 +8874,12 @@
         <v>0.01557</v>
       </c>
       <c r="U115" s="1" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="V115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="V115" s="1" t="n">
+      <c r="W115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -8599,9 +8947,12 @@
         <v>0.08451</v>
       </c>
       <c r="U116" s="1" t="n">
+        <v>0.08462</v>
+      </c>
+      <c r="V116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="V116" s="1" t="n">
+      <c r="W116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -8669,10 +9020,13 @@
         <v>0.04704</v>
       </c>
       <c r="U117" s="1" t="n">
+        <v>0.046737</v>
+      </c>
+      <c r="V117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="V117" s="1" t="n">
-        <v>0.046846</v>
+      <c r="W117" s="1" t="n">
+        <v>0.046737</v>
       </c>
     </row>
     <row r="118">
@@ -8739,9 +9093,12 @@
         <v>0.04713</v>
       </c>
       <c r="U118" s="1" t="n">
+        <v>0.04718</v>
+      </c>
+      <c r="V118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="V118" s="1" t="n">
+      <c r="W118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -8809,9 +9166,12 @@
         <v>0.04016</v>
       </c>
       <c r="U119" s="1" t="n">
+        <v>0.04021</v>
+      </c>
+      <c r="V119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="V119" s="1" t="n">
+      <c r="W119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -8879,9 +9239,12 @@
         <v>0.14451</v>
       </c>
       <c r="U120" s="1" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="V120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="V120" s="1" t="n">
+      <c r="W120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -8949,9 +9312,12 @@
         <v>0.1254</v>
       </c>
       <c r="U121" s="1" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="V121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="V121" s="1" t="n">
+      <c r="W121" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -9019,10 +9385,13 @@
         <v>1.842</v>
       </c>
       <c r="U122" s="1" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="V122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="V122" s="1" t="n">
-        <v>1.842</v>
+      <c r="W122" s="1" t="n">
+        <v>1.837</v>
       </c>
     </row>
     <row r="123">
@@ -9089,9 +9458,12 @@
         <v>0.03007</v>
       </c>
       <c r="U123" s="1" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="V123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="V123" s="1" t="n">
+      <c r="W123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -9159,9 +9531,12 @@
         <v>0.13454</v>
       </c>
       <c r="U124" s="1" t="n">
+        <v>0.13393</v>
+      </c>
+      <c r="V124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="V124" s="1" t="n">
+      <c r="W124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -9229,9 +9604,12 @@
         <v>0.04096</v>
       </c>
       <c r="U125" s="1" t="n">
+        <v>0.04102</v>
+      </c>
+      <c r="V125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="V125" s="1" t="n">
+      <c r="W125" s="1" t="n">
         <v>0.04075</v>
       </c>
     </row>
@@ -9299,9 +9677,12 @@
         <v>0.1145</v>
       </c>
       <c r="U126" s="1" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="V126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="V126" s="1" t="n">
+      <c r="W126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -9369,9 +9750,12 @@
         <v>0.5322</v>
       </c>
       <c r="U127" s="1" t="n">
-        <v>0.5322</v>
+        <v>0.535</v>
       </c>
       <c r="V127" s="1" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="W127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -9439,9 +9823,12 @@
         <v>0.03819</v>
       </c>
       <c r="U128" s="1" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="V128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="V128" s="1" t="n">
+      <c r="W128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -9509,9 +9896,12 @@
         <v>0.794</v>
       </c>
       <c r="U129" s="1" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="V129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="V129" s="1" t="n">
+      <c r="W129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -9579,9 +9969,12 @@
         <v>0.03428</v>
       </c>
       <c r="U130" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="V130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="V130" s="1" t="n">
+      <c r="W130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -9649,9 +10042,12 @@
         <v>0.4219</v>
       </c>
       <c r="U131" s="1" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="V131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="V131" s="1" t="n">
+      <c r="W131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -9719,9 +10115,12 @@
         <v>0.04303</v>
       </c>
       <c r="U132" s="1" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="V132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="V132" s="1" t="n">
+      <c r="W132" s="1" t="n">
         <v>0.04303</v>
       </c>
     </row>
@@ -9789,9 +10188,12 @@
         <v>1.2806</v>
       </c>
       <c r="U133" s="1" t="n">
+        <v>1.2813</v>
+      </c>
+      <c r="V133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="V133" s="1" t="n">
+      <c r="W133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -9859,9 +10261,12 @@
         <v>0.02191</v>
       </c>
       <c r="U134" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="V134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="V134" s="1" t="n">
+      <c r="W134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -9929,9 +10334,12 @@
         <v>0.0004565</v>
       </c>
       <c r="U135" s="1" t="n">
+        <v>0.0004573</v>
+      </c>
+      <c r="V135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="V135" s="1" t="n">
+      <c r="W135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -9999,9 +10407,12 @@
         <v>0.001928</v>
       </c>
       <c r="U136" s="1" t="n">
+        <v>0.001902</v>
+      </c>
+      <c r="V136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="V136" s="1" t="n">
+      <c r="W136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -10069,9 +10480,12 @@
         <v>0.3156</v>
       </c>
       <c r="U137" s="1" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="V137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="V137" s="1" t="n">
+      <c r="W137" s="1" t="n">
         <v>0.3136</v>
       </c>
     </row>
@@ -10139,9 +10553,12 @@
         <v>0.5603</v>
       </c>
       <c r="U138" s="1" t="n">
+        <v>0.5601</v>
+      </c>
+      <c r="V138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="V138" s="1" t="n">
+      <c r="W138" s="1" t="n">
         <v>0.5599</v>
       </c>
     </row>
@@ -10209,9 +10626,12 @@
         <v>0.02135</v>
       </c>
       <c r="U139" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="V139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="V139" s="1" t="n">
+      <c r="W139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -10279,9 +10699,12 @@
         <v>0.07994</v>
       </c>
       <c r="U140" s="1" t="n">
+        <v>0.08003</v>
+      </c>
+      <c r="V140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="V140" s="1" t="n">
+      <c r="W140" s="1" t="n">
         <v>0.0796</v>
       </c>
     </row>
@@ -10349,9 +10772,12 @@
         <v>0.00153</v>
       </c>
       <c r="U141" s="1" t="n">
+        <v>0.001527</v>
+      </c>
+      <c r="V141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="V141" s="1" t="n">
+      <c r="W141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -10419,9 +10845,12 @@
         <v>0.4489</v>
       </c>
       <c r="U142" s="1" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="V142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="V142" s="1" t="n">
+      <c r="W142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -10489,9 +10918,12 @@
         <v>0.030224</v>
       </c>
       <c r="U143" s="1" t="n">
+        <v>0.030158</v>
+      </c>
+      <c r="V143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="V143" s="1" t="n">
+      <c r="W143" s="1" t="n">
         <v>0.029881</v>
       </c>
     </row>
@@ -10559,9 +10991,12 @@
         <v>0.000225</v>
       </c>
       <c r="U144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="V144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="V144" s="1" t="n">
+      <c r="W144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -10629,9 +11064,12 @@
         <v>0.03498</v>
       </c>
       <c r="U145" s="1" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="V145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="V145" s="1" t="n">
+      <c r="W145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -10699,9 +11137,12 @@
         <v>0.11676</v>
       </c>
       <c r="U146" s="1" t="n">
-        <v>0.11676</v>
+        <v>0.11717</v>
       </c>
       <c r="V146" s="1" t="n">
+        <v>0.11717</v>
+      </c>
+      <c r="W146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -10769,9 +11210,12 @@
         <v>0.02254</v>
       </c>
       <c r="U147" s="1" t="n">
-        <v>0.02254</v>
+        <v>0.02258</v>
       </c>
       <c r="V147" s="1" t="n">
+        <v>0.02258</v>
+      </c>
+      <c r="W147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -10839,9 +11283,12 @@
         <v>1.4143</v>
       </c>
       <c r="U148" s="1" t="n">
+        <v>1.4126</v>
+      </c>
+      <c r="V148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="V148" s="1" t="n">
+      <c r="W148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -10909,9 +11356,12 @@
         <v>1.8691</v>
       </c>
       <c r="U149" s="1" t="n">
+        <v>1.8704</v>
+      </c>
+      <c r="V149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="V149" s="1" t="n">
+      <c r="W149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -10979,9 +11429,12 @@
         <v>0.095</v>
       </c>
       <c r="U150" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="V150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="V150" s="1" t="n">
+      <c r="W150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -11049,9 +11502,12 @@
         <v>4.697</v>
       </c>
       <c r="U151" s="1" t="n">
-        <v>4.697</v>
+        <v>4.708</v>
       </c>
       <c r="V151" s="1" t="n">
+        <v>4.708</v>
+      </c>
+      <c r="W151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -11119,9 +11575,12 @@
         <v>5.534</v>
       </c>
       <c r="U152" s="1" t="n">
+        <v>5.542</v>
+      </c>
+      <c r="V152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="V152" s="1" t="n">
+      <c r="W152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -11189,9 +11648,12 @@
         <v>0.3205</v>
       </c>
       <c r="U153" s="1" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="V153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="V153" s="1" t="n">
+      <c r="W153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -11259,9 +11721,12 @@
         <v>0.5838</v>
       </c>
       <c r="U154" s="1" t="n">
+        <v>0.5852000000000001</v>
+      </c>
+      <c r="V154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="V154" s="1" t="n">
+      <c r="W154" s="1" t="n">
         <v>0.5825</v>
       </c>
     </row>
@@ -11329,9 +11794,12 @@
         <v>0.01274</v>
       </c>
       <c r="U155" s="1" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="V155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="V155" s="1" t="n">
+      <c r="W155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -11399,9 +11867,12 @@
         <v>0.0973</v>
       </c>
       <c r="U156" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="V156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="V156" s="1" t="n">
+      <c r="W156" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
     </row>
@@ -11469,9 +11940,12 @@
         <v>16.395</v>
       </c>
       <c r="U157" s="1" t="n">
+        <v>16.411</v>
+      </c>
+      <c r="V157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="V157" s="1" t="n">
+      <c r="W157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -11539,9 +12013,12 @@
         <v>0.0555</v>
       </c>
       <c r="U158" s="1" t="n">
+        <v>0.05548</v>
+      </c>
+      <c r="V158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="V158" s="1" t="n">
+      <c r="W158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -11609,9 +12086,12 @@
         <v>28.77</v>
       </c>
       <c r="U159" s="1" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="V159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="V159" s="1" t="n">
+      <c r="W159" s="1" t="n">
         <v>28.65</v>
       </c>
     </row>
@@ -11682,6 +12162,9 @@
         <v>0.02141</v>
       </c>
       <c r="V160" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="W160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -11749,9 +12232,12 @@
         <v>0.0006539</v>
       </c>
       <c r="U161" s="1" t="n">
+        <v>0.0006528</v>
+      </c>
+      <c r="V161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="V161" s="1" t="n">
+      <c r="W161" s="1" t="n">
         <v>0.0006503</v>
       </c>
     </row>
@@ -11819,9 +12305,12 @@
         <v>0.3818</v>
       </c>
       <c r="U162" s="1" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="V162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="V162" s="1" t="n">
+      <c r="W162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -11889,9 +12378,12 @@
         <v>0.1911</v>
       </c>
       <c r="U163" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="V163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="V163" s="1" t="n">
+      <c r="W163" s="1" t="n">
         <v>0.1908</v>
       </c>
     </row>
@@ -11959,9 +12451,12 @@
         <v>0.316</v>
       </c>
       <c r="U164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="V164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="V164" s="1" t="n">
+      <c r="W164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -12029,9 +12524,12 @@
         <v>0.376</v>
       </c>
       <c r="U165" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="V165" s="1" t="n">
+      <c r="W165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -12099,9 +12597,12 @@
         <v>0.02245</v>
       </c>
       <c r="U166" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="V166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="V166" s="1" t="n">
+      <c r="W166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -12169,9 +12670,12 @@
         <v>0.007268</v>
       </c>
       <c r="U167" s="1" t="n">
+        <v>0.007271</v>
+      </c>
+      <c r="V167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="V167" s="1" t="n">
+      <c r="W167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -12239,9 +12743,12 @@
         <v>0.01341</v>
       </c>
       <c r="U168" s="1" t="n">
+        <v>0.01336</v>
+      </c>
+      <c r="V168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="V168" s="1" t="n">
+      <c r="W168" s="1" t="n">
         <v>0.01332</v>
       </c>
     </row>
@@ -12309,9 +12816,12 @@
         <v>0.25566</v>
       </c>
       <c r="U169" s="1" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="V169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="V169" s="1" t="n">
+      <c r="W169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -12379,9 +12889,12 @@
         <v>0.0218</v>
       </c>
       <c r="U170" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="V170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="V170" s="1" t="n">
+      <c r="W170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -12449,9 +12962,12 @@
         <v>0.1722</v>
       </c>
       <c r="U171" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="V171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="V171" s="1" t="n">
+      <c r="W171" s="1" t="n">
         <v>0.171</v>
       </c>
     </row>
@@ -12519,9 +13035,12 @@
         <v>0.09</v>
       </c>
       <c r="U172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="V172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="V172" s="1" t="n">
+      <c r="W172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -12589,9 +13108,12 @@
         <v>0.004673</v>
       </c>
       <c r="U173" s="1" t="n">
+        <v>0.004679</v>
+      </c>
+      <c r="V173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="V173" s="1" t="n">
+      <c r="W173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -12659,9 +13181,12 @@
         <v>0.4385</v>
       </c>
       <c r="U174" s="1" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="V174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="V174" s="1" t="n">
+      <c r="W174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -12729,9 +13254,12 @@
         <v>0.09053</v>
       </c>
       <c r="U175" s="1" t="n">
-        <v>0.09057</v>
+        <v>0.09096</v>
       </c>
       <c r="V175" s="1" t="n">
+        <v>0.09096</v>
+      </c>
+      <c r="W175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -12799,9 +13327,12 @@
         <v>0.2458</v>
       </c>
       <c r="U176" s="1" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="V176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="V176" s="1" t="n">
+      <c r="W176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -12869,9 +13400,12 @@
         <v>0.01919</v>
       </c>
       <c r="U177" s="1" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="V177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="V177" s="1" t="n">
+      <c r="W177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -12939,9 +13473,12 @@
         <v>6.106</v>
       </c>
       <c r="U178" s="1" t="n">
+        <v>6.108</v>
+      </c>
+      <c r="V178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="V178" s="1" t="n">
+      <c r="W178" s="1" t="n">
         <v>6.106</v>
       </c>
     </row>
@@ -13009,9 +13546,12 @@
         <v>0.1372</v>
       </c>
       <c r="U179" s="1" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="V179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="V179" s="1" t="n">
+      <c r="W179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -13079,9 +13619,12 @@
         <v>0.005006</v>
       </c>
       <c r="U180" s="1" t="n">
+        <v>0.004985</v>
+      </c>
+      <c r="V180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="V180" s="1" t="n">
+      <c r="W180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -13149,9 +13692,12 @@
         <v>0.01195</v>
       </c>
       <c r="U181" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="V181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="V181" s="1" t="n">
+      <c r="W181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -13219,9 +13765,12 @@
         <v>0.007395</v>
       </c>
       <c r="U182" s="1" t="n">
+        <v>0.007345</v>
+      </c>
+      <c r="V182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="V182" s="1" t="n">
+      <c r="W182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -13289,9 +13838,12 @@
         <v>0.13047</v>
       </c>
       <c r="U183" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="V183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="V183" s="1" t="n">
+      <c r="W183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -13359,9 +13911,12 @@
         <v>0.09587</v>
       </c>
       <c r="U184" s="1" t="n">
+        <v>0.09573</v>
+      </c>
+      <c r="V184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="V184" s="1" t="n">
+      <c r="W184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -13429,9 +13984,12 @@
         <v>0.00752</v>
       </c>
       <c r="U185" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="V185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="V185" s="1" t="n">
+      <c r="W185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -13499,9 +14057,12 @@
         <v>0.04862</v>
       </c>
       <c r="U186" s="1" t="n">
+        <v>0.04864</v>
+      </c>
+      <c r="V186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="V186" s="1" t="n">
+      <c r="W186" s="1" t="n">
         <v>0.04851</v>
       </c>
     </row>
@@ -13569,9 +14130,12 @@
         <v>0.02685</v>
       </c>
       <c r="U187" s="1" t="n">
+        <v>0.02683</v>
+      </c>
+      <c r="V187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="V187" s="1" t="n">
+      <c r="W187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -13639,10 +14203,13 @@
         <v>0.003283</v>
       </c>
       <c r="U188" s="1" t="n">
+        <v>0.003274</v>
+      </c>
+      <c r="V188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="V188" s="1" t="n">
-        <v>0.003282</v>
+      <c r="W188" s="1" t="n">
+        <v>0.003274</v>
       </c>
     </row>
     <row r="189">
@@ -13709,9 +14276,12 @@
         <v>0.2853</v>
       </c>
       <c r="U189" s="1" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="V189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="V189" s="1" t="n">
+      <c r="W189" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -13779,9 +14349,12 @@
         <v>0.01783</v>
       </c>
       <c r="U190" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="V190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="V190" s="1" t="n">
+      <c r="W190" s="1" t="n">
         <v>0.01783</v>
       </c>
     </row>
@@ -13849,9 +14422,12 @@
         <v>0.2566</v>
       </c>
       <c r="U191" s="1" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="V191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="V191" s="1" t="n">
+      <c r="W191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -13919,9 +14495,12 @@
         <v>0.03805</v>
       </c>
       <c r="U192" s="1" t="n">
+        <v>0.03803</v>
+      </c>
+      <c r="V192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="V192" s="1" t="n">
+      <c r="W192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -13989,9 +14568,12 @@
         <v>0.000221</v>
       </c>
       <c r="U193" s="1" t="n">
+        <v>0.0002208</v>
+      </c>
+      <c r="V193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="V193" s="1" t="n">
+      <c r="W193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -14059,9 +14641,12 @@
         <v>4.078</v>
       </c>
       <c r="U194" s="1" t="n">
+        <v>4.084</v>
+      </c>
+      <c r="V194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="V194" s="1" t="n">
+      <c r="W194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -14129,9 +14714,12 @@
         <v>0.9994</v>
       </c>
       <c r="U195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="V195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="V195" s="1" t="n">
+      <c r="W195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -14199,9 +14787,12 @@
         <v>4.324</v>
       </c>
       <c r="U196" s="1" t="n">
-        <v>4.347</v>
+        <v>4.354</v>
       </c>
       <c r="V196" s="1" t="n">
+        <v>4.354</v>
+      </c>
+      <c r="W196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -14269,9 +14860,12 @@
         <v>0.15195</v>
       </c>
       <c r="U197" s="1" t="n">
+        <v>0.15168</v>
+      </c>
+      <c r="V197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="V197" s="1" t="n">
+      <c r="W197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -14339,9 +14933,12 @@
         <v>0.00792</v>
       </c>
       <c r="U198" s="1" t="n">
-        <v>0.00792</v>
+        <v>0.007920999999999999</v>
       </c>
       <c r="V198" s="1" t="n">
+        <v>0.007920999999999999</v>
+      </c>
+      <c r="W198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -14409,9 +15006,12 @@
         <v>0.4501</v>
       </c>
       <c r="U199" s="1" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="V199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="V199" s="1" t="n">
+      <c r="W199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -14479,9 +15079,12 @@
         <v>0.5872000000000001</v>
       </c>
       <c r="U200" s="1" t="n">
+        <v>0.5874</v>
+      </c>
+      <c r="V200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="V200" s="1" t="n">
+      <c r="W200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -14549,9 +15152,12 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="U201" s="1" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="V201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="V201" s="1" t="n">
+      <c r="W201" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -14619,9 +15225,12 @@
         <v>0.06041</v>
       </c>
       <c r="U202" s="1" t="n">
+        <v>0.06048</v>
+      </c>
+      <c r="V202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="V202" s="1" t="n">
+      <c r="W202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -14689,9 +15298,12 @@
         <v>0.008319999999999999</v>
       </c>
       <c r="U203" s="1" t="n">
+        <v>0.008189999999999999</v>
+      </c>
+      <c r="V203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="V203" s="1" t="n">
+      <c r="W203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -14759,9 +15371,12 @@
         <v>0.00412</v>
       </c>
       <c r="U204" s="1" t="n">
+        <v>0.00414</v>
+      </c>
+      <c r="V204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="V204" s="1" t="n">
+      <c r="W204" s="1" t="n">
         <v>0.00412</v>
       </c>
     </row>
@@ -14829,9 +15444,12 @@
         <v>0.009067</v>
       </c>
       <c r="U205" s="1" t="n">
+        <v>0.009081000000000001</v>
+      </c>
+      <c r="V205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="V205" s="1" t="n">
+      <c r="W205" s="1" t="n">
         <v>0.009067</v>
       </c>
     </row>
@@ -14899,9 +15517,12 @@
         <v>0.2371</v>
       </c>
       <c r="U206" s="1" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="V206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="V206" s="1" t="n">
+      <c r="W206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -14969,9 +15590,12 @@
         <v>0.02109</v>
       </c>
       <c r="U207" s="1" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="V207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="V207" s="1" t="n">
+      <c r="W207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -15039,9 +15663,12 @@
         <v>0.2373</v>
       </c>
       <c r="U208" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="V208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="V208" s="1" t="n">
+      <c r="W208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -15109,9 +15736,12 @@
         <v>0.361</v>
       </c>
       <c r="U209" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="V209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="V209" s="1" t="n">
+      <c r="W209" s="1" t="n">
         <v>0.3584</v>
       </c>
     </row>
@@ -15179,9 +15809,12 @@
         <v>0.04294</v>
       </c>
       <c r="U210" s="1" t="n">
+        <v>0.04295</v>
+      </c>
+      <c r="V210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="V210" s="1" t="n">
+      <c r="W210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -15249,10 +15882,13 @@
         <v>0.0004235</v>
       </c>
       <c r="U211" s="1" t="n">
+        <v>0.0004234</v>
+      </c>
+      <c r="V211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="V211" s="1" t="n">
-        <v>0.0004235</v>
+      <c r="W211" s="1" t="n">
+        <v>0.0004234</v>
       </c>
     </row>
     <row r="212">
@@ -15319,9 +15955,12 @@
         <v>0.02123</v>
       </c>
       <c r="U212" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="V212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="V212" s="1" t="n">
+      <c r="W212" s="1" t="n">
         <v>0.02123</v>
       </c>
     </row>
@@ -15389,9 +16028,12 @@
         <v>0.1143</v>
       </c>
       <c r="U213" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="V213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="V213" s="1" t="n">
+      <c r="W213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -15459,9 +16101,12 @@
         <v>0.04193</v>
       </c>
       <c r="U214" s="1" t="n">
+        <v>0.04201</v>
+      </c>
+      <c r="V214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="V214" s="1" t="n">
+      <c r="W214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -15529,9 +16174,12 @@
         <v>0.009875999999999999</v>
       </c>
       <c r="U215" s="1" t="n">
+        <v>0.009841000000000001</v>
+      </c>
+      <c r="V215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="V215" s="1" t="n">
+      <c r="W215" s="1" t="n">
         <v>0.009839000000000001</v>
       </c>
     </row>
@@ -15599,9 +16247,12 @@
         <v>0.0636</v>
       </c>
       <c r="U216" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="V216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="V216" s="1" t="n">
+      <c r="W216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -15669,9 +16320,12 @@
         <v>0.004224</v>
       </c>
       <c r="U217" s="1" t="n">
+        <v>0.004223</v>
+      </c>
+      <c r="V217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="V217" s="1" t="n">
+      <c r="W217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -15739,9 +16393,12 @@
         <v>0.01002</v>
       </c>
       <c r="U218" s="1" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="V218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="V218" s="1" t="n">
+      <c r="W218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -15809,9 +16466,12 @@
         <v>0.02943</v>
       </c>
       <c r="U219" s="1" t="n">
+        <v>0.02968</v>
+      </c>
+      <c r="V219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="V219" s="1" t="n">
+      <c r="W219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -15879,9 +16539,12 @@
         <v>2.29</v>
       </c>
       <c r="U220" s="1" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="V220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="V220" s="1" t="n">
+      <c r="W220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -15949,9 +16612,12 @@
         <v>0.022707</v>
       </c>
       <c r="U221" s="1" t="n">
+        <v>0.022767</v>
+      </c>
+      <c r="V221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="V221" s="1" t="n">
+      <c r="W221" s="1" t="n">
         <v>0.022529</v>
       </c>
     </row>
@@ -16019,9 +16685,12 @@
         <v>0.0368</v>
       </c>
       <c r="U222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="V222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="V222" s="1" t="n">
+      <c r="W222" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -16089,9 +16758,12 @@
         <v>0.2928</v>
       </c>
       <c r="U223" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="V223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="V223" s="1" t="n">
+      <c r="W223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -16159,9 +16831,12 @@
         <v>0.01553</v>
       </c>
       <c r="U224" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="V224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="V224" s="1" t="n">
+      <c r="W224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -16229,9 +16904,12 @@
         <v>0.0004031</v>
       </c>
       <c r="U225" s="1" t="n">
+        <v>0.0004036</v>
+      </c>
+      <c r="V225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="V225" s="1" t="n">
+      <c r="W225" s="1" t="n">
         <v>0.0004031</v>
       </c>
     </row>
@@ -16299,9 +16977,12 @@
         <v>0.08519</v>
       </c>
       <c r="U226" s="1" t="n">
+        <v>0.0853</v>
+      </c>
+      <c r="V226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="V226" s="1" t="n">
+      <c r="W226" s="1" t="n">
         <v>0.08519</v>
       </c>
     </row>
@@ -16369,9 +17050,12 @@
         <v>0.948</v>
       </c>
       <c r="U227" s="1" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="V227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="V227" s="1" t="n">
+      <c r="W227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -16439,9 +17123,12 @@
         <v>0.05565</v>
       </c>
       <c r="U228" s="1" t="n">
+        <v>0.05552</v>
+      </c>
+      <c r="V228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="V228" s="1" t="n">
+      <c r="W228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -16509,9 +17196,12 @@
         <v>0.002018</v>
       </c>
       <c r="U229" s="1" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="V229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="V229" s="1" t="n">
+      <c r="W229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -16579,9 +17269,12 @@
         <v>0.022858</v>
       </c>
       <c r="U230" s="1" t="n">
+        <v>0.022834</v>
+      </c>
+      <c r="V230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="V230" s="1" t="n">
+      <c r="W230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -16649,9 +17342,12 @@
         <v>0.05344</v>
       </c>
       <c r="U231" s="1" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="V231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="V231" s="1" t="n">
+      <c r="W231" s="1" t="n">
         <v>0.05338</v>
       </c>
     </row>
@@ -16719,9 +17415,12 @@
         <v>0.0583</v>
       </c>
       <c r="U232" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="V232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="V232" s="1" t="n">
+      <c r="W232" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -16789,9 +17488,12 @@
         <v>0.001705</v>
       </c>
       <c r="U233" s="1" t="n">
-        <v>0.001705</v>
+        <v>0.001727</v>
       </c>
       <c r="V233" s="1" t="n">
+        <v>0.001727</v>
+      </c>
+      <c r="W233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -16859,10 +17561,13 @@
         <v>0.00573</v>
       </c>
       <c r="U234" s="1" t="n">
+        <v>0.005721</v>
+      </c>
+      <c r="V234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="V234" s="1" t="n">
-        <v>0.005728</v>
+      <c r="W234" s="1" t="n">
+        <v>0.005721</v>
       </c>
     </row>
     <row r="235">
@@ -16929,9 +17634,12 @@
         <v>0.12263</v>
       </c>
       <c r="U235" s="1" t="n">
+        <v>0.12335</v>
+      </c>
+      <c r="V235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="V235" s="1" t="n">
+      <c r="W235" s="1" t="n">
         <v>0.12245</v>
       </c>
     </row>
@@ -16999,9 +17707,12 @@
         <v>65</v>
       </c>
       <c r="U236" s="1" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="V236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="V236" s="1" t="n">
+      <c r="W236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -17069,9 +17780,12 @@
         <v>0.1015</v>
       </c>
       <c r="U237" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="V237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="V237" s="1" t="n">
+      <c r="W237" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -17139,9 +17853,12 @@
         <v>0.004039</v>
       </c>
       <c r="U238" s="1" t="n">
+        <v>0.004017</v>
+      </c>
+      <c r="V238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="V238" s="1" t="n">
+      <c r="W238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -17209,9 +17926,12 @@
         <v>0.01509</v>
       </c>
       <c r="U239" s="1" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="V239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="V239" s="1" t="n">
+      <c r="W239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -17279,9 +17999,12 @@
         <v>0.05591</v>
       </c>
       <c r="U240" s="1" t="n">
+        <v>0.05582</v>
+      </c>
+      <c r="V240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="V240" s="1" t="n">
+      <c r="W240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -17349,9 +18072,12 @@
         <v>0.0115</v>
       </c>
       <c r="U241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="V241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="V241" s="1" t="n">
+      <c r="W241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -17419,9 +18145,12 @@
         <v>0.3322</v>
       </c>
       <c r="U242" s="1" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="V242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="V242" s="1" t="n">
+      <c r="W242" s="1" t="n">
         <v>0.3321</v>
       </c>
     </row>
@@ -17489,9 +18218,12 @@
         <v>0.0123</v>
       </c>
       <c r="U243" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="V243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="V243" s="1" t="n">
+      <c r="W243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -17559,9 +18291,12 @@
         <v>0.08111</v>
       </c>
       <c r="U244" s="1" t="n">
+        <v>0.08117000000000001</v>
+      </c>
+      <c r="V244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="V244" s="1" t="n">
+      <c r="W244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -17629,9 +18364,12 @@
         <v>0.007812</v>
       </c>
       <c r="U245" s="1" t="n">
+        <v>0.007863</v>
+      </c>
+      <c r="V245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="V245" s="1" t="n">
+      <c r="W245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -17699,9 +18437,12 @@
         <v>0.03026</v>
       </c>
       <c r="U246" s="1" t="n">
+        <v>0.03029</v>
+      </c>
+      <c r="V246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="V246" s="1" t="n">
+      <c r="W246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -17769,9 +18510,12 @@
         <v>0.18</v>
       </c>
       <c r="U247" s="1" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="V247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="V247" s="1" t="n">
+      <c r="W247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -17839,9 +18583,12 @@
         <v>0.05867</v>
       </c>
       <c r="U248" s="1" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="V248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="V248" s="1" t="n">
+      <c r="W248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -17909,10 +18656,13 @@
         <v>0.1656</v>
       </c>
       <c r="U249" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="V249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="V249" s="1" t="n">
-        <v>0.1656</v>
+      <c r="W249" s="1" t="n">
+        <v>0.1653</v>
       </c>
     </row>
     <row r="250">
@@ -17979,9 +18729,12 @@
         <v>0.01896</v>
       </c>
       <c r="U250" s="1" t="n">
+        <v>0.01897</v>
+      </c>
+      <c r="V250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="V250" s="1" t="n">
+      <c r="W250" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -18049,9 +18802,12 @@
         <v>0.02301</v>
       </c>
       <c r="U251" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="V251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="V251" s="1" t="n">
+      <c r="W251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -18119,9 +18875,12 @@
         <v>0.30429</v>
       </c>
       <c r="U252" s="1" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="V252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="V252" s="1" t="n">
+      <c r="W252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -18189,9 +18948,12 @@
         <v>0.005981</v>
       </c>
       <c r="U253" s="1" t="n">
+        <v>0.005994</v>
+      </c>
+      <c r="V253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="V253" s="1" t="n">
+      <c r="W253" s="1" t="n">
         <v>0.005956</v>
       </c>
     </row>
@@ -18259,9 +19021,12 @@
         <v>0.6125</v>
       </c>
       <c r="U254" s="1" t="n">
+        <v>0.6131</v>
+      </c>
+      <c r="V254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="V254" s="1" t="n">
+      <c r="W254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -18329,9 +19094,12 @@
         <v>0.10577</v>
       </c>
       <c r="U255" s="1" t="n">
+        <v>0.10579</v>
+      </c>
+      <c r="V255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="V255" s="1" t="n">
+      <c r="W255" s="1" t="n">
         <v>0.10569</v>
       </c>
     </row>
@@ -18399,9 +19167,12 @@
         <v>0.0901</v>
       </c>
       <c r="U256" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="V256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="V256" s="1" t="n">
+      <c r="W256" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -18469,9 +19240,12 @@
         <v>0.0146</v>
       </c>
       <c r="U257" s="1" t="n">
-        <v>0.0147</v>
+        <v>0.01477</v>
       </c>
       <c r="V257" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="W257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -18539,9 +19313,12 @@
         <v>0.04988</v>
       </c>
       <c r="U258" s="1" t="n">
+        <v>0.04987</v>
+      </c>
+      <c r="V258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="V258" s="1" t="n">
+      <c r="W258" s="1" t="n">
         <v>0.04965</v>
       </c>
     </row>
@@ -18609,10 +19386,13 @@
         <v>0.008</v>
       </c>
       <c r="U259" s="1" t="n">
+        <v>0.00793</v>
+      </c>
+      <c r="V259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="V259" s="1" t="n">
-        <v>0.008</v>
+      <c r="W259" s="1" t="n">
+        <v>0.00793</v>
       </c>
     </row>
     <row r="260">
@@ -18679,9 +19459,12 @@
         <v>0.1895</v>
       </c>
       <c r="U260" s="1" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="V260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="V260" s="1" t="n">
+      <c r="W260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -18749,9 +19532,12 @@
         <v>0.0977</v>
       </c>
       <c r="U261" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="V261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="V261" s="1" t="n">
+      <c r="W261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -18819,9 +19605,12 @@
         <v>0.2105</v>
       </c>
       <c r="U262" s="1" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="V262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="V262" s="1" t="n">
+      <c r="W262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -18889,9 +19678,12 @@
         <v>0.008486</v>
       </c>
       <c r="U263" s="1" t="n">
+        <v>0.008543</v>
+      </c>
+      <c r="V263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="V263" s="1" t="n">
+      <c r="W263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -18959,10 +19751,13 @@
         <v>2.628</v>
       </c>
       <c r="U264" s="1" t="n">
+        <v>2.617</v>
+      </c>
+      <c r="V264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="V264" s="1" t="n">
-        <v>2.628</v>
+      <c r="W264" s="1" t="n">
+        <v>2.617</v>
       </c>
     </row>
     <row r="265">
@@ -19029,9 +19824,12 @@
         <v>0.01858</v>
       </c>
       <c r="U265" s="1" t="n">
+        <v>0.01867</v>
+      </c>
+      <c r="V265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="V265" s="1" t="n">
+      <c r="W265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -19099,9 +19897,12 @@
         <v>0.3599</v>
       </c>
       <c r="U266" s="1" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="V266" s="1" t="n">
         <v>0.3612</v>
       </c>
-      <c r="V266" s="1" t="n">
+      <c r="W266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -19169,9 +19970,12 @@
         <v>0.03438</v>
       </c>
       <c r="U267" s="1" t="n">
+        <v>0.03455</v>
+      </c>
+      <c r="V267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="V267" s="1" t="n">
+      <c r="W267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -19239,9 +20043,12 @@
         <v>0.122</v>
       </c>
       <c r="U268" s="1" t="n">
-        <v>0.123</v>
+        <v>0.127</v>
       </c>
       <c r="V268" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="W268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -19309,9 +20116,12 @@
         <v>0.07925</v>
       </c>
       <c r="U269" s="1" t="n">
+        <v>0.07928</v>
+      </c>
+      <c r="V269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="V269" s="1" t="n">
+      <c r="W269" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -19379,9 +20189,12 @@
         <v>0.01376</v>
       </c>
       <c r="U270" s="1" t="n">
+        <v>0.01378</v>
+      </c>
+      <c r="V270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="V270" s="1" t="n">
+      <c r="W270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -19449,9 +20262,12 @@
         <v>0.007513</v>
       </c>
       <c r="U271" s="1" t="n">
+        <v>0.007515</v>
+      </c>
+      <c r="V271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="V271" s="1" t="n">
+      <c r="W271" s="1" t="n">
         <v>0.007504</v>
       </c>
     </row>
@@ -19519,9 +20335,12 @@
         <v>0.07425</v>
       </c>
       <c r="U272" s="1" t="n">
+        <v>0.07416</v>
+      </c>
+      <c r="V272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="V272" s="1" t="n">
+      <c r="W272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -19592,6 +20411,9 @@
         <v>3.16e-05</v>
       </c>
       <c r="V273" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="W273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -19659,9 +20481,12 @@
         <v>0.005432</v>
       </c>
       <c r="U274" s="1" t="n">
+        <v>0.005433</v>
+      </c>
+      <c r="V274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="V274" s="1" t="n">
+      <c r="W274" s="1" t="n">
         <v>0.005409</v>
       </c>
     </row>
@@ -19729,9 +20554,12 @@
         <v>0.1766</v>
       </c>
       <c r="U275" s="1" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="V275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="V275" s="1" t="n">
+      <c r="W275" s="1" t="n">
         <v>0.1766</v>
       </c>
     </row>
@@ -19799,9 +20627,12 @@
         <v>0.006817</v>
       </c>
       <c r="U276" s="1" t="n">
+        <v>0.006831</v>
+      </c>
+      <c r="V276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="V276" s="1" t="n">
+      <c r="W276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -19869,9 +20700,12 @@
         <v>0.1308</v>
       </c>
       <c r="U277" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="V277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="V277" s="1" t="n">
+      <c r="W277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -19939,9 +20773,12 @@
         <v>0.02315</v>
       </c>
       <c r="U278" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="V278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="V278" s="1" t="n">
+      <c r="W278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -20009,9 +20846,12 @@
         <v>0.0181</v>
       </c>
       <c r="U279" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="V279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="V279" s="1" t="n">
+      <c r="W279" s="1" t="n">
         <v>0.0181</v>
       </c>
     </row>
@@ -20079,9 +20919,12 @@
         <v>0.03668</v>
       </c>
       <c r="U280" s="1" t="n">
+        <v>0.03679</v>
+      </c>
+      <c r="V280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="V280" s="1" t="n">
+      <c r="W280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -20149,9 +20992,12 @@
         <v>0.0397</v>
       </c>
       <c r="U281" s="1" t="n">
+        <v>0.03976</v>
+      </c>
+      <c r="V281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="V281" s="1" t="n">
+      <c r="W281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -20219,9 +21065,12 @@
         <v>0.3046</v>
       </c>
       <c r="U282" s="1" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="V282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="V282" s="1" t="n">
+      <c r="W282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -20289,9 +21138,12 @@
         <v>0.01119</v>
       </c>
       <c r="U283" s="1" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="V283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="V283" s="1" t="n">
+      <c r="W283" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -20359,9 +21211,12 @@
         <v>9.7e-06</v>
       </c>
       <c r="U284" s="1" t="n">
+        <v>9.500000000000001e-06</v>
+      </c>
+      <c r="V284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="V284" s="1" t="n">
+      <c r="W284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -20429,9 +21284,12 @@
         <v>0.1143</v>
       </c>
       <c r="U285" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="V285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="V285" s="1" t="n">
+      <c r="W285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -20499,9 +21357,12 @@
         <v>0.003439</v>
       </c>
       <c r="U286" s="1" t="n">
+        <v>0.003455</v>
+      </c>
+      <c r="V286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="V286" s="1" t="n">
+      <c r="W286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -20569,9 +21430,12 @@
         <v>0.08487</v>
       </c>
       <c r="U287" s="1" t="n">
+        <v>0.08477999999999999</v>
+      </c>
+      <c r="V287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="V287" s="1" t="n">
+      <c r="W287" s="1" t="n">
         <v>0.08465</v>
       </c>
     </row>
@@ -20639,9 +21503,12 @@
         <v>0.09943</v>
       </c>
       <c r="U288" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="V288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="V288" s="1" t="n">
+      <c r="W288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -20709,9 +21576,12 @@
         <v>0.4353</v>
       </c>
       <c r="U289" s="1" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="V289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="V289" s="1" t="n">
+      <c r="W289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -20779,9 +21649,12 @@
         <v>0.03951</v>
       </c>
       <c r="U290" s="1" t="n">
+        <v>0.03965</v>
+      </c>
+      <c r="V290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="V290" s="1" t="n">
+      <c r="W290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -20849,9 +21722,12 @@
         <v>0.2345</v>
       </c>
       <c r="U291" s="1" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="V291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="V291" s="1" t="n">
+      <c r="W291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -20919,9 +21795,12 @@
         <v>0.2832</v>
       </c>
       <c r="U292" s="1" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="V292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="V292" s="1" t="n">
+      <c r="W292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -20989,9 +21868,12 @@
         <v>0.152</v>
       </c>
       <c r="U293" s="1" t="n">
-        <v>0.152</v>
+        <v>0.1521</v>
       </c>
       <c r="V293" s="1" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="W293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -21059,9 +21941,12 @@
         <v>4.165</v>
       </c>
       <c r="U294" s="1" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="V294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="V294" s="1" t="n">
+      <c r="W294" s="1" t="n">
         <v>4.165</v>
       </c>
     </row>
@@ -21129,9 +22014,12 @@
         <v>0.03416</v>
       </c>
       <c r="U295" s="1" t="n">
+        <v>0.03385</v>
+      </c>
+      <c r="V295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="V295" s="1" t="n">
+      <c r="W295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -21199,9 +22087,12 @@
         <v>0.0009700000000000001</v>
       </c>
       <c r="U296" s="1" t="n">
+        <v>0.000972</v>
+      </c>
+      <c r="V296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="V296" s="1" t="n">
+      <c r="W296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -21269,9 +22160,12 @@
         <v>0.0815</v>
       </c>
       <c r="U297" s="1" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="V297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="V297" s="1" t="n">
+      <c r="W297" s="1" t="n">
         <v>0.08135000000000001</v>
       </c>
     </row>
@@ -21339,9 +22233,12 @@
         <v>0.05869</v>
       </c>
       <c r="U298" s="1" t="n">
-        <v>0.05869</v>
+        <v>0.05876</v>
       </c>
       <c r="V298" s="1" t="n">
+        <v>0.05876</v>
+      </c>
+      <c r="W298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -21409,9 +22306,12 @@
         <v>0.09103</v>
       </c>
       <c r="U299" s="1" t="n">
+        <v>0.09109</v>
+      </c>
+      <c r="V299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="V299" s="1" t="n">
+      <c r="W299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -21479,9 +22379,12 @@
         <v>0.02727</v>
       </c>
       <c r="U300" s="1" t="n">
+        <v>0.02733</v>
+      </c>
+      <c r="V300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="V300" s="1" t="n">
+      <c r="W300" s="1" t="n">
         <v>0.02723</v>
       </c>
     </row>
@@ -21549,9 +22452,12 @@
         <v>0.06562</v>
       </c>
       <c r="U301" s="1" t="n">
+        <v>0.06589</v>
+      </c>
+      <c r="V301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="V301" s="1" t="n">
+      <c r="W301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -21619,9 +22525,12 @@
         <v>0.053416</v>
       </c>
       <c r="U302" s="1" t="n">
+        <v>0.053584</v>
+      </c>
+      <c r="V302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="V302" s="1" t="n">
+      <c r="W302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -21689,9 +22598,12 @@
         <v>5167.1</v>
       </c>
       <c r="U303" s="1" t="n">
+        <v>5167.2</v>
+      </c>
+      <c r="V303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="V303" s="1" t="n">
+      <c r="W303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -21759,9 +22671,12 @@
         <v>14.87</v>
       </c>
       <c r="U304" s="1" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="V304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="V304" s="1" t="n">
+      <c r="W304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -21829,9 +22744,12 @@
         <v>0.003717</v>
       </c>
       <c r="U305" s="1" t="n">
+        <v>0.003715</v>
+      </c>
+      <c r="V305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="V305" s="1" t="n">
+      <c r="W305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -21899,9 +22817,12 @@
         <v>0.454</v>
       </c>
       <c r="U306" s="1" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="V306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="V306" s="1" t="n">
+      <c r="W306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -21969,9 +22890,12 @@
         <v>0.04673</v>
       </c>
       <c r="U307" s="1" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="V307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="V307" s="1" t="n">
+      <c r="W307" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -22039,9 +22963,12 @@
         <v>1.4885</v>
       </c>
       <c r="U308" s="1" t="n">
+        <v>1.4843</v>
+      </c>
+      <c r="V308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="V308" s="1" t="n">
+      <c r="W308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -22109,9 +23036,12 @@
         <v>0.0007911</v>
       </c>
       <c r="U309" s="1" t="n">
+        <v>0.0007876</v>
+      </c>
+      <c r="V309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="V309" s="1" t="n">
+      <c r="W309" s="1" t="n">
         <v>0.0007861</v>
       </c>
     </row>
@@ -22179,9 +23109,12 @@
         <v>4.55</v>
       </c>
       <c r="U310" s="1" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="V310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="V310" s="1" t="n">
+      <c r="W310" s="1" t="n">
         <v>4.549</v>
       </c>
     </row>
@@ -22249,9 +23182,12 @@
         <v>4.777</v>
       </c>
       <c r="U311" s="1" t="n">
+        <v>4.778</v>
+      </c>
+      <c r="V311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="V311" s="1" t="n">
+      <c r="W311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -22319,9 +23255,12 @@
         <v>0.08033999999999999</v>
       </c>
       <c r="U312" s="1" t="n">
+        <v>0.08035</v>
+      </c>
+      <c r="V312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="V312" s="1" t="n">
+      <c r="W312" s="1" t="n">
         <v>0.08033999999999999</v>
       </c>
     </row>
@@ -22389,9 +23328,12 @@
         <v>2.022</v>
       </c>
       <c r="U313" s="1" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="V313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="V313" s="1" t="n">
+      <c r="W313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -22459,9 +23401,12 @@
         <v>0.07196</v>
       </c>
       <c r="U314" s="1" t="n">
+        <v>0.07103</v>
+      </c>
+      <c r="V314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="V314" s="1" t="n">
+      <c r="W314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -22529,9 +23474,12 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="U315" s="1" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="V315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="V315" s="1" t="n">
+      <c r="W315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -22599,9 +23547,12 @@
         <v>0.1295</v>
       </c>
       <c r="U316" s="1" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="V316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="V316" s="1" t="n">
+      <c r="W316" s="1" t="n">
         <v>0.1295</v>
       </c>
     </row>
@@ -22669,9 +23620,12 @@
         <v>0.187</v>
       </c>
       <c r="U317" s="1" t="n">
-        <v>0.187</v>
+        <v>0.1877</v>
       </c>
       <c r="V317" s="1" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="W317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -22739,9 +23693,12 @@
         <v>0.01607</v>
       </c>
       <c r="U318" s="1" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="V318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="V318" s="1" t="n">
+      <c r="W318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -22809,9 +23766,12 @@
         <v>0.0834</v>
       </c>
       <c r="U319" s="1" t="n">
+        <v>0.08373999999999999</v>
+      </c>
+      <c r="V319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="V319" s="1" t="n">
+      <c r="W319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -22879,9 +23839,12 @@
         <v>0.007502</v>
       </c>
       <c r="U320" s="1" t="n">
+        <v>0.007506</v>
+      </c>
+      <c r="V320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="V320" s="1" t="n">
+      <c r="W320" s="1" t="n">
         <v>0.007463</v>
       </c>
     </row>
@@ -22949,9 +23912,12 @@
         <v>0.05435</v>
       </c>
       <c r="U321" s="1" t="n">
+        <v>0.05442</v>
+      </c>
+      <c r="V321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="V321" s="1" t="n">
+      <c r="W321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -23019,9 +23985,12 @@
         <v>0.5501</v>
       </c>
       <c r="U322" s="1" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="V322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="V322" s="1" t="n">
+      <c r="W322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -23089,9 +24058,12 @@
         <v>0.07571</v>
       </c>
       <c r="U323" s="1" t="n">
+        <v>0.07548000000000001</v>
+      </c>
+      <c r="V323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="V323" s="1" t="n">
+      <c r="W323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -23159,9 +24131,12 @@
         <v>0.013005</v>
       </c>
       <c r="U324" s="1" t="n">
-        <v>0.013005</v>
+        <v>0.013039</v>
       </c>
       <c r="V324" s="1" t="n">
+        <v>0.013039</v>
+      </c>
+      <c r="W324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -23229,9 +24204,12 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="U325" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="V325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="V325" s="1" t="n">
+      <c r="W325" s="1" t="n">
         <v>0.0985</v>
       </c>
     </row>
@@ -23299,9 +24277,12 @@
         <v>0.01738</v>
       </c>
       <c r="U326" s="1" t="n">
+        <v>0.01739</v>
+      </c>
+      <c r="V326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="V326" s="1" t="n">
+      <c r="W326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -23369,9 +24350,12 @@
         <v>0.06407</v>
       </c>
       <c r="U327" s="1" t="n">
+        <v>0.06406000000000001</v>
+      </c>
+      <c r="V327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="V327" s="1" t="n">
+      <c r="W327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -23439,9 +24423,12 @@
         <v>0.2628</v>
       </c>
       <c r="U328" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="V328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="V328" s="1" t="n">
+      <c r="W328" s="1" t="n">
         <v>0.2612</v>
       </c>
     </row>
@@ -23509,9 +24496,12 @@
         <v>0.17297</v>
       </c>
       <c r="U329" s="1" t="n">
+        <v>0.17282</v>
+      </c>
+      <c r="V329" s="1" t="n">
         <v>0.17476</v>
       </c>
-      <c r="V329" s="1" t="n">
+      <c r="W329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -23579,10 +24569,13 @@
         <v>2.032</v>
       </c>
       <c r="U330" s="1" t="n">
+        <v>2.028</v>
+      </c>
+      <c r="V330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="V330" s="1" t="n">
-        <v>2.032</v>
+      <c r="W330" s="1" t="n">
+        <v>2.028</v>
       </c>
     </row>
     <row r="331">
@@ -23649,9 +24642,12 @@
         <v>0.0288</v>
       </c>
       <c r="U331" s="1" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="V331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="V331" s="1" t="n">
+      <c r="W331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -23719,9 +24715,12 @@
         <v>0.006032</v>
       </c>
       <c r="U332" s="1" t="n">
+        <v>0.006049</v>
+      </c>
+      <c r="V332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="V332" s="1" t="n">
+      <c r="W332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -23789,9 +24788,12 @@
         <v>0.003458</v>
       </c>
       <c r="U333" s="1" t="n">
+        <v>0.003458</v>
+      </c>
+      <c r="V333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="V333" s="1" t="n">
+      <c r="W333" s="1" t="n">
         <v>0.003458</v>
       </c>
     </row>
@@ -23859,9 +24861,12 @@
         <v>0.01396</v>
       </c>
       <c r="U334" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="V334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="V334" s="1" t="n">
+      <c r="W334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -23929,9 +24934,12 @@
         <v>1.134</v>
       </c>
       <c r="U335" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V335" s="1" t="n">
         <v>1.158</v>
       </c>
-      <c r="V335" s="1" t="n">
+      <c r="W335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -23999,9 +25007,12 @@
         <v>0.01136</v>
       </c>
       <c r="U336" s="1" t="n">
+        <v>0.011349</v>
+      </c>
+      <c r="V336" s="1" t="n">
         <v>0.011365</v>
       </c>
-      <c r="V336" s="1" t="n">
+      <c r="W336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -24069,9 +25080,12 @@
         <v>2.968</v>
       </c>
       <c r="U337" s="1" t="n">
+        <v>2.991</v>
+      </c>
+      <c r="V337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="V337" s="1" t="n">
+      <c r="W337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -24139,9 +25153,12 @@
         <v>0.01851</v>
       </c>
       <c r="U338" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="V338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="V338" s="1" t="n">
+      <c r="W338" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -24209,9 +25226,12 @@
         <v>0.07729</v>
       </c>
       <c r="U339" s="1" t="n">
+        <v>0.07731</v>
+      </c>
+      <c r="V339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="V339" s="1" t="n">
+      <c r="W339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -24279,9 +25299,12 @@
         <v>0.075</v>
       </c>
       <c r="U340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="V340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="V340" s="1" t="n">
+      <c r="W340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -24349,9 +25372,12 @@
         <v>0.03586</v>
       </c>
       <c r="U341" s="1" t="n">
+        <v>0.03597</v>
+      </c>
+      <c r="V341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="V341" s="1" t="n">
+      <c r="W341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -24419,9 +25445,12 @@
         <v>2579</v>
       </c>
       <c r="U342" s="1" t="n">
+        <v>2587</v>
+      </c>
+      <c r="V342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="V342" s="1" t="n">
+      <c r="W342" s="1" t="n">
         <v>2579</v>
       </c>
     </row>
@@ -24489,9 +25518,12 @@
         <v>0.0002049</v>
       </c>
       <c r="U343" s="1" t="n">
+        <v>0.0002035</v>
+      </c>
+      <c r="V343" s="1" t="n">
         <v>0.0002049</v>
       </c>
-      <c r="V343" s="1" t="n">
+      <c r="W343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -24559,9 +25591,12 @@
         <v>0.07949000000000001</v>
       </c>
       <c r="U344" s="1" t="n">
+        <v>0.07945000000000001</v>
+      </c>
+      <c r="V344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="V344" s="1" t="n">
+      <c r="W344" s="1" t="n">
         <v>0.07915</v>
       </c>
     </row>
@@ -24629,9 +25664,12 @@
         <v>0.01623</v>
       </c>
       <c r="U345" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="V345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="V345" s="1" t="n">
+      <c r="W345" s="1" t="n">
         <v>0.01622</v>
       </c>
     </row>
@@ -24699,9 +25737,12 @@
         <v>2.744</v>
       </c>
       <c r="U346" s="1" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="V346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="V346" s="1" t="n">
+      <c r="W346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -24769,9 +25810,12 @@
         <v>0.01634</v>
       </c>
       <c r="U347" s="1" t="n">
+        <v>0.01649</v>
+      </c>
+      <c r="V347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="V347" s="1" t="n">
+      <c r="W347" s="1" t="n">
         <v>0.01625</v>
       </c>
     </row>
@@ -24839,9 +25883,12 @@
         <v>0.03889</v>
       </c>
       <c r="U348" s="1" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="V348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="V348" s="1" t="n">
+      <c r="W348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -24909,9 +25956,12 @@
         <v>0.3056</v>
       </c>
       <c r="U349" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="V349" s="1" t="n">
         <v>0.3076</v>
       </c>
-      <c r="V349" s="1" t="n">
+      <c r="W349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -24979,9 +26029,12 @@
         <v>0.005076</v>
       </c>
       <c r="U350" s="1" t="n">
+        <v>0.005086</v>
+      </c>
+      <c r="V350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="V350" s="1" t="n">
+      <c r="W350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -25049,9 +26102,12 @@
         <v>0.005083</v>
       </c>
       <c r="U351" s="1" t="n">
+        <v>0.005101</v>
+      </c>
+      <c r="V351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="V351" s="1" t="n">
+      <c r="W351" s="1" t="n">
         <v>0.005054</v>
       </c>
     </row>
@@ -25119,9 +26175,12 @@
         <v>0.004389</v>
       </c>
       <c r="U352" s="1" t="n">
+        <v>0.00439</v>
+      </c>
+      <c r="V352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="V352" s="1" t="n">
+      <c r="W352" s="1" t="n">
         <v>0.004379</v>
       </c>
     </row>
@@ -25189,9 +26248,12 @@
         <v>0.08044</v>
       </c>
       <c r="U353" s="1" t="n">
+        <v>0.08051999999999999</v>
+      </c>
+      <c r="V353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="V353" s="1" t="n">
+      <c r="W353" s="1" t="n">
         <v>0.08008</v>
       </c>
     </row>
@@ -25259,9 +26321,12 @@
         <v>1.264</v>
       </c>
       <c r="U354" s="1" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="V354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="V354" s="1" t="n">
+      <c r="W354" s="1" t="n">
         <v>1.258</v>
       </c>
     </row>
@@ -25329,9 +26394,12 @@
         <v>7.698</v>
       </c>
       <c r="U355" s="1" t="n">
+        <v>7.703</v>
+      </c>
+      <c r="V355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="V355" s="1" t="n">
+      <c r="W355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -25399,9 +26467,12 @@
         <v>0.00784</v>
       </c>
       <c r="U356" s="1" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="V356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="V356" s="1" t="n">
+      <c r="W356" s="1" t="n">
         <v>0.00777</v>
       </c>
     </row>
@@ -25469,9 +26540,12 @@
         <v>0.005658</v>
       </c>
       <c r="U357" s="1" t="n">
+        <v>0.005649</v>
+      </c>
+      <c r="V357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="V357" s="1" t="n">
+      <c r="W357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -25539,9 +26613,12 @@
         <v>0.01546</v>
       </c>
       <c r="U358" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="V358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="V358" s="1" t="n">
+      <c r="W358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -25609,10 +26686,13 @@
         <v>3.599</v>
       </c>
       <c r="U359" s="1" t="n">
+        <v>3.597</v>
+      </c>
+      <c r="V359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="V359" s="1" t="n">
-        <v>3.599</v>
+      <c r="W359" s="1" t="n">
+        <v>3.597</v>
       </c>
     </row>
     <row r="360">
@@ -25679,9 +26759,12 @@
         <v>0.1494</v>
       </c>
       <c r="U360" s="1" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="V360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="V360" s="1" t="n">
+      <c r="W360" s="1" t="n">
         <v>0.1494</v>
       </c>
     </row>
@@ -25749,10 +26832,13 @@
         <v>0.07026</v>
       </c>
       <c r="U361" s="1" t="n">
+        <v>0.07017</v>
+      </c>
+      <c r="V361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="V361" s="1" t="n">
-        <v>0.07019</v>
+      <c r="W361" s="1" t="n">
+        <v>0.07017</v>
       </c>
     </row>
     <row r="362">
@@ -25819,9 +26905,12 @@
         <v>0.01767</v>
       </c>
       <c r="U362" s="1" t="n">
+        <v>0.01769</v>
+      </c>
+      <c r="V362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="V362" s="1" t="n">
+      <c r="W362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -25889,10 +26978,13 @@
         <v>0.0223</v>
       </c>
       <c r="U363" s="1" t="n">
+        <v>0.02228</v>
+      </c>
+      <c r="V363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="V363" s="1" t="n">
-        <v>0.02229</v>
+      <c r="W363" s="1" t="n">
+        <v>0.02228</v>
       </c>
     </row>
     <row r="364">
@@ -25959,9 +27051,12 @@
         <v>0.01251</v>
       </c>
       <c r="U364" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="V364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="V364" s="1" t="n">
+      <c r="W364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -26029,9 +27124,12 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="U365" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="V365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="V365" s="1" t="n">
+      <c r="W365" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -26099,9 +27197,12 @@
         <v>0.04228</v>
       </c>
       <c r="U366" s="1" t="n">
+        <v>0.04227</v>
+      </c>
+      <c r="V366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="V366" s="1" t="n">
+      <c r="W366" s="1" t="n">
         <v>0.04214</v>
       </c>
     </row>
@@ -26169,9 +27270,12 @@
         <v>0.03163</v>
       </c>
       <c r="U367" s="1" t="n">
+        <v>0.03162</v>
+      </c>
+      <c r="V367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="V367" s="1" t="n">
+      <c r="W367" s="1" t="n">
         <v>0.03124</v>
       </c>
     </row>
@@ -26239,10 +27343,13 @@
         <v>0.02326</v>
       </c>
       <c r="U368" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="V368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="V368" s="1" t="n">
-        <v>0.02322</v>
+      <c r="W368" s="1" t="n">
+        <v>0.02318</v>
       </c>
     </row>
     <row r="369">
@@ -26309,9 +27416,12 @@
         <v>0.03089</v>
       </c>
       <c r="U369" s="1" t="n">
+        <v>0.03091</v>
+      </c>
+      <c r="V369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="V369" s="1" t="n">
+      <c r="W369" s="1" t="n">
         <v>0.0308</v>
       </c>
     </row>
@@ -26379,9 +27489,12 @@
         <v>0.0799</v>
       </c>
       <c r="U370" s="1" t="n">
+        <v>0.08001999999999999</v>
+      </c>
+      <c r="V370" s="1" t="n">
         <v>0.08017000000000001</v>
       </c>
-      <c r="V370" s="1" t="n">
+      <c r="W370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -26449,10 +27562,13 @@
         <v>0.1072</v>
       </c>
       <c r="U371" s="1" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="V371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="V371" s="1" t="n">
-        <v>0.1072</v>
+      <c r="W371" s="1" t="n">
+        <v>0.1069</v>
       </c>
     </row>
     <row r="372">
@@ -26519,9 +27635,12 @@
         <v>0.007012</v>
       </c>
       <c r="U372" s="1" t="n">
+        <v>0.007004</v>
+      </c>
+      <c r="V372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="V372" s="1" t="n">
+      <c r="W372" s="1" t="n">
         <v>0.00694</v>
       </c>
     </row>
@@ -26589,9 +27708,12 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="U373" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="V373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="V373" s="1" t="n">
+      <c r="W373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -26659,9 +27781,12 @@
         <v>0.05739</v>
       </c>
       <c r="U374" s="1" t="n">
+        <v>0.05745</v>
+      </c>
+      <c r="V374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="V374" s="1" t="n">
+      <c r="W374" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -26729,9 +27854,12 @@
         <v>0.3175</v>
       </c>
       <c r="U375" s="1" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="V375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="V375" s="1" t="n">
+      <c r="W375" s="1" t="n">
         <v>0.3169</v>
       </c>
     </row>
@@ -26799,9 +27927,12 @@
         <v>0.01946</v>
       </c>
       <c r="U376" s="1" t="n">
+        <v>0.01952</v>
+      </c>
+      <c r="V376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="V376" s="1" t="n">
+      <c r="W376" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -26869,9 +28000,12 @@
         <v>0.06845999999999999</v>
       </c>
       <c r="U377" s="1" t="n">
+        <v>0.06857000000000001</v>
+      </c>
+      <c r="V377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="V377" s="1" t="n">
+      <c r="W377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -26939,9 +28073,12 @@
         <v>0.15799</v>
       </c>
       <c r="U378" s="1" t="n">
+        <v>0.15764</v>
+      </c>
+      <c r="V378" s="1" t="n">
         <v>0.15872</v>
       </c>
-      <c r="V378" s="1" t="n">
+      <c r="W378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -27009,9 +28146,12 @@
         <v>0.0005941</v>
       </c>
       <c r="U379" s="1" t="n">
+        <v>0.0005968</v>
+      </c>
+      <c r="V379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="V379" s="1" t="n">
+      <c r="W379" s="1" t="n">
         <v>0.0005922</v>
       </c>
     </row>
@@ -27079,9 +28219,12 @@
         <v>0.01016</v>
       </c>
       <c r="U380" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="V380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="V380" s="1" t="n">
+      <c r="W380" s="1" t="n">
         <v>0.01012</v>
       </c>
     </row>
@@ -27149,9 +28292,12 @@
         <v>0.02558</v>
       </c>
       <c r="U381" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="V381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="V381" s="1" t="n">
+      <c r="W381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -27219,10 +28365,13 @@
         <v>0.18817</v>
       </c>
       <c r="U382" s="1" t="n">
+        <v>0.18764</v>
+      </c>
+      <c r="V382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="V382" s="1" t="n">
-        <v>0.18817</v>
+      <c r="W382" s="1" t="n">
+        <v>0.18764</v>
       </c>
     </row>
     <row r="383">
@@ -27289,9 +28438,12 @@
         <v>0.0921</v>
       </c>
       <c r="U383" s="1" t="n">
+        <v>0.09233</v>
+      </c>
+      <c r="V383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="V383" s="1" t="n">
+      <c r="W383" s="1" t="n">
         <v>0.0921</v>
       </c>
     </row>
@@ -27359,9 +28511,12 @@
         <v>0.03163</v>
       </c>
       <c r="U384" s="1" t="n">
+        <v>0.03162</v>
+      </c>
+      <c r="V384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="V384" s="1" t="n">
+      <c r="W384" s="1" t="n">
         <v>0.0316</v>
       </c>
     </row>
@@ -27429,9 +28584,12 @@
         <v>0.01088</v>
       </c>
       <c r="U385" s="1" t="n">
+        <v>0.01088</v>
+      </c>
+      <c r="V385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="V385" s="1" t="n">
+      <c r="W385" s="1" t="n">
         <v>0.01086</v>
       </c>
     </row>
@@ -27499,9 +28657,12 @@
         <v>0.05043</v>
       </c>
       <c r="U386" s="1" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="V386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="V386" s="1" t="n">
+      <c r="W386" s="1" t="n">
         <v>0.05043</v>
       </c>
     </row>
@@ -27569,9 +28730,12 @@
         <v>0.02419</v>
       </c>
       <c r="U387" s="1" t="n">
+        <v>0.02412</v>
+      </c>
+      <c r="V387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="V387" s="1" t="n">
+      <c r="W387" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -27639,9 +28803,12 @@
         <v>0.007264</v>
       </c>
       <c r="U388" s="1" t="n">
+        <v>0.007245</v>
+      </c>
+      <c r="V388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="V388" s="1" t="n">
+      <c r="W388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -27709,9 +28876,12 @@
         <v>0.01015</v>
       </c>
       <c r="U389" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="V389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="V389" s="1" t="n">
+      <c r="W389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -27779,9 +28949,12 @@
         <v>0.08223999999999999</v>
       </c>
       <c r="U390" s="1" t="n">
+        <v>0.08217000000000001</v>
+      </c>
+      <c r="V390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="V390" s="1" t="n">
+      <c r="W390" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -27849,9 +29022,12 @@
         <v>0.504</v>
       </c>
       <c r="U391" s="1" t="n">
+        <v>0.5034999999999999</v>
+      </c>
+      <c r="V391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="V391" s="1" t="n">
+      <c r="W391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -27919,9 +29095,12 @@
         <v>0.1165</v>
       </c>
       <c r="U392" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="V392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="V392" s="1" t="n">
+      <c r="W392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -27989,9 +29168,12 @@
         <v>0.00246</v>
       </c>
       <c r="U393" s="1" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="V393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="V393" s="1" t="n">
+      <c r="W393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -28059,9 +29241,12 @@
         <v>0.0218</v>
       </c>
       <c r="U394" s="1" t="n">
+        <v>0.02168</v>
+      </c>
+      <c r="V394" s="1" t="n">
         <v>0.0218</v>
       </c>
-      <c r="V394" s="1" t="n">
+      <c r="W394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -28129,9 +29314,12 @@
         <v>0.0158</v>
       </c>
       <c r="U395" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="V395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="V395" s="1" t="n">
+      <c r="W395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -28199,9 +29387,12 @@
         <v>0.1352</v>
       </c>
       <c r="U396" s="1" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="V396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="V396" s="1" t="n">
+      <c r="W396" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -28269,9 +29460,12 @@
         <v>0.01448</v>
       </c>
       <c r="U397" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="V397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="V397" s="1" t="n">
+      <c r="W397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -28339,9 +29533,12 @@
         <v>6.763</v>
       </c>
       <c r="U398" s="1" t="n">
+        <v>6.766</v>
+      </c>
+      <c r="V398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="V398" s="1" t="n">
+      <c r="W398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -28409,9 +29606,12 @@
         <v>0.009526</v>
       </c>
       <c r="U399" s="1" t="n">
+        <v>0.009486</v>
+      </c>
+      <c r="V399" s="1" t="n">
         <v>0.009526</v>
       </c>
-      <c r="V399" s="1" t="n">
+      <c r="W399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -28479,9 +29679,12 @@
         <v>0.001253</v>
       </c>
       <c r="U400" s="1" t="n">
+        <v>0.001257</v>
+      </c>
+      <c r="V400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="V400" s="1" t="n">
+      <c r="W400" s="1" t="n">
         <v>0.001241</v>
       </c>
     </row>
@@ -28549,9 +29752,12 @@
         <v>0.01852</v>
       </c>
       <c r="U401" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="V401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="V401" s="1" t="n">
+      <c r="W401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -28619,9 +29825,12 @@
         <v>0.08495</v>
       </c>
       <c r="U402" s="1" t="n">
+        <v>0.08481</v>
+      </c>
+      <c r="V402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="V402" s="1" t="n">
+      <c r="W402" s="1" t="n">
         <v>0.08447</v>
       </c>
     </row>
@@ -28689,9 +29898,12 @@
         <v>0.00549</v>
       </c>
       <c r="U403" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="V403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="V403" s="1" t="n">
+      <c r="W403" s="1" t="n">
         <v>0.00548</v>
       </c>
     </row>
@@ -28759,9 +29971,12 @@
         <v>0.04281</v>
       </c>
       <c r="U404" s="1" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="V404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="V404" s="1" t="n">
+      <c r="W404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -28829,9 +30044,12 @@
         <v>0.05829</v>
       </c>
       <c r="U405" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="V405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="V405" s="1" t="n">
+      <c r="W405" s="1" t="n">
         <v>0.05827</v>
       </c>
     </row>
@@ -28899,9 +30117,12 @@
         <v>0.01653</v>
       </c>
       <c r="U406" s="1" t="n">
+        <v>0.01677</v>
+      </c>
+      <c r="V406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="V406" s="1" t="n">
+      <c r="W406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -28969,9 +30190,12 @@
         <v>0.0423</v>
       </c>
       <c r="U407" s="1" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="V407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="V407" s="1" t="n">
+      <c r="W407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -29039,9 +30263,12 @@
         <v>0.01926</v>
       </c>
       <c r="U408" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="V408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="V408" s="1" t="n">
+      <c r="W408" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -29109,9 +30336,12 @@
         <v>0.4444</v>
       </c>
       <c r="U409" s="1" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="V409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="V409" s="1" t="n">
+      <c r="W409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -29179,10 +30409,13 @@
         <v>0.04379</v>
       </c>
       <c r="U410" s="1" t="n">
+        <v>0.04374</v>
+      </c>
+      <c r="V410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="V410" s="1" t="n">
-        <v>0.04379</v>
+      <c r="W410" s="1" t="n">
+        <v>0.04374</v>
       </c>
     </row>
     <row r="411">
@@ -29249,9 +30482,12 @@
         <v>27.3</v>
       </c>
       <c r="U411" s="1" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="V411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="V411" s="1" t="n">
+      <c r="W411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -29319,9 +30555,12 @@
         <v>0.03517</v>
       </c>
       <c r="U412" s="1" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="V412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="V412" s="1" t="n">
+      <c r="W412" s="1" t="n">
         <v>0.03493</v>
       </c>
     </row>
@@ -29389,9 +30628,12 @@
         <v>0.003409</v>
       </c>
       <c r="U413" s="1" t="n">
+        <v>0.003408</v>
+      </c>
+      <c r="V413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="V413" s="1" t="n">
+      <c r="W413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -29459,9 +30701,12 @@
         <v>0.1521</v>
       </c>
       <c r="U414" s="1" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="V414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="V414" s="1" t="n">
+      <c r="W414" s="1" t="n">
         <v>0.1521</v>
       </c>
     </row>
@@ -29529,9 +30774,12 @@
         <v>0.05232</v>
       </c>
       <c r="U415" s="1" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="V415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="V415" s="1" t="n">
+      <c r="W415" s="1" t="n">
         <v>0.05228</v>
       </c>
     </row>
@@ -29599,9 +30847,12 @@
         <v>0.00656</v>
       </c>
       <c r="U416" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="V416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="V416" s="1" t="n">
+      <c r="W416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -29669,9 +30920,12 @@
         <v>0.0603</v>
       </c>
       <c r="U417" s="1" t="n">
+        <v>0.06031</v>
+      </c>
+      <c r="V417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="V417" s="1" t="n">
+      <c r="W417" s="1" t="n">
         <v>0.06025</v>
       </c>
     </row>
@@ -29739,9 +30993,12 @@
         <v>0.008051000000000001</v>
       </c>
       <c r="U418" s="1" t="n">
+        <v>0.008035</v>
+      </c>
+      <c r="V418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="V418" s="1" t="n">
+      <c r="W418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -29809,9 +31066,12 @@
         <v>0.07421</v>
       </c>
       <c r="U419" s="1" t="n">
+        <v>0.07442</v>
+      </c>
+      <c r="V419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="V419" s="1" t="n">
+      <c r="W419" s="1" t="n">
         <v>0.07414999999999999</v>
       </c>
     </row>
@@ -29879,9 +31139,12 @@
         <v>0.02132</v>
       </c>
       <c r="U420" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="V420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="V420" s="1" t="n">
+      <c r="W420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -29949,9 +31212,12 @@
         <v>0.06906</v>
       </c>
       <c r="U421" s="1" t="n">
+        <v>0.06925000000000001</v>
+      </c>
+      <c r="V421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="V421" s="1" t="n">
+      <c r="W421" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -30019,9 +31285,12 @@
         <v>0.01482</v>
       </c>
       <c r="U422" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="V422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="V422" s="1" t="n">
+      <c r="W422" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -30089,9 +31358,12 @@
         <v>0.006596</v>
       </c>
       <c r="U423" s="1" t="n">
+        <v>0.006608</v>
+      </c>
+      <c r="V423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="V423" s="1" t="n">
+      <c r="W423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -30159,9 +31431,12 @@
         <v>0.908</v>
       </c>
       <c r="U424" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="V424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="V424" s="1" t="n">
+      <c r="W424" s="1" t="n">
         <v>0.907</v>
       </c>
     </row>
@@ -30229,9 +31504,12 @@
         <v>0.0354</v>
       </c>
       <c r="U425" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="V425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="V425" s="1" t="n">
+      <c r="W425" s="1" t="n">
         <v>0.03519</v>
       </c>
     </row>
@@ -30299,9 +31577,12 @@
         <v>1.802</v>
       </c>
       <c r="U426" s="1" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="V426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="V426" s="1" t="n">
+      <c r="W426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -30369,9 +31650,12 @@
         <v>0.12852</v>
       </c>
       <c r="U427" s="1" t="n">
-        <v>0.12875</v>
+        <v>0.12876</v>
       </c>
       <c r="V427" s="1" t="n">
+        <v>0.12876</v>
+      </c>
+      <c r="W427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -30439,9 +31723,12 @@
         <v>0.05306</v>
       </c>
       <c r="U428" s="1" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="V428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="V428" s="1" t="n">
+      <c r="W428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -30509,9 +31796,12 @@
         <v>1.292</v>
       </c>
       <c r="U429" s="1" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="V429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="V429" s="1" t="n">
+      <c r="W429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -30579,9 +31869,12 @@
         <v>0.07457999999999999</v>
       </c>
       <c r="U430" s="1" t="n">
+        <v>0.07467</v>
+      </c>
+      <c r="V430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="V430" s="1" t="n">
+      <c r="W430" s="1" t="n">
         <v>0.07456</v>
       </c>
     </row>
@@ -30649,9 +31942,12 @@
         <v>0.1567</v>
       </c>
       <c r="U431" s="1" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="V431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="V431" s="1" t="n">
+      <c r="W431" s="1" t="n">
         <v>0.156</v>
       </c>
     </row>
@@ -30719,9 +32015,12 @@
         <v>1.444</v>
       </c>
       <c r="U432" s="1" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="V432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="V432" s="1" t="n">
+      <c r="W432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -30789,9 +32088,12 @@
         <v>3.256</v>
       </c>
       <c r="U433" s="1" t="n">
+        <v>3.253</v>
+      </c>
+      <c r="V433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="V433" s="1" t="n">
+      <c r="W433" s="1" t="n">
         <v>3.239</v>
       </c>
     </row>
@@ -30859,9 +32161,12 @@
         <v>0.1784</v>
       </c>
       <c r="U434" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="V434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="V434" s="1" t="n">
+      <c r="W434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -30929,9 +32234,12 @@
         <v>0.008567</v>
       </c>
       <c r="U435" s="1" t="n">
+        <v>0.008567</v>
+      </c>
+      <c r="V435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="V435" s="1" t="n">
+      <c r="W435" s="1" t="n">
         <v>0.008548</v>
       </c>
     </row>
@@ -30999,9 +32307,12 @@
         <v>0.2805</v>
       </c>
       <c r="U436" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="V436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="V436" s="1" t="n">
+      <c r="W436" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -31069,9 +32380,12 @@
         <v>0.03875</v>
       </c>
       <c r="U437" s="1" t="n">
+        <v>0.03877</v>
+      </c>
+      <c r="V437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="V437" s="1" t="n">
+      <c r="W437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -31139,9 +32453,12 @@
         <v>0.02412</v>
       </c>
       <c r="U438" s="1" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="V438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="V438" s="1" t="n">
+      <c r="W438" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -31209,9 +32526,12 @@
         <v>0.04409</v>
       </c>
       <c r="U439" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="V439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="V439" s="1" t="n">
+      <c r="W439" s="1" t="n">
         <v>0.04401</v>
       </c>
     </row>
@@ -31279,9 +32599,12 @@
         <v>0.0005189</v>
       </c>
       <c r="U440" s="1" t="n">
+        <v>0.0005225</v>
+      </c>
+      <c r="V440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="V440" s="1" t="n">
+      <c r="W440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -31349,9 +32672,12 @@
         <v>0.04493</v>
       </c>
       <c r="U441" s="1" t="n">
+        <v>0.04486</v>
+      </c>
+      <c r="V441" s="1" t="n">
         <v>0.04581</v>
       </c>
-      <c r="V441" s="1" t="n">
+      <c r="W441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -31419,9 +32745,12 @@
         <v>0.000415</v>
       </c>
       <c r="U442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="V442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="V442" s="1" t="n">
+      <c r="W442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -31489,9 +32818,12 @@
         <v>0.09425</v>
       </c>
       <c r="U443" s="1" t="n">
+        <v>0.09415999999999999</v>
+      </c>
+      <c r="V443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="V443" s="1" t="n">
+      <c r="W443" s="1" t="n">
         <v>0.09392</v>
       </c>
     </row>
@@ -31559,9 +32891,12 @@
         <v>2.29</v>
       </c>
       <c r="U444" s="1" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="V444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="V444" s="1" t="n">
+      <c r="W444" s="1" t="n">
         <v>2.286</v>
       </c>
     </row>
@@ -31629,9 +32964,12 @@
         <v>0.2698</v>
       </c>
       <c r="U445" s="1" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="V445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="V445" s="1" t="n">
+      <c r="W445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -31699,9 +33037,12 @@
         <v>0.0007413</v>
       </c>
       <c r="U446" s="1" t="n">
+        <v>0.0007401</v>
+      </c>
+      <c r="V446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="V446" s="1" t="n">
+      <c r="W446" s="1" t="n">
         <v>0.0007376</v>
       </c>
     </row>
@@ -31769,9 +33110,12 @@
         <v>0.0387</v>
       </c>
       <c r="U447" s="1" t="n">
+        <v>0.03861</v>
+      </c>
+      <c r="V447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="V447" s="1" t="n">
+      <c r="W447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -31839,9 +33183,12 @@
         <v>0.1775</v>
       </c>
       <c r="U448" s="1" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="V448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="V448" s="1" t="n">
+      <c r="W448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -31909,9 +33256,12 @@
         <v>0.04273</v>
       </c>
       <c r="U449" s="1" t="n">
+        <v>0.04272</v>
+      </c>
+      <c r="V449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="V449" s="1" t="n">
+      <c r="W449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -31982,6 +33332,9 @@
         <v>0.0001654</v>
       </c>
       <c r="V450" s="1" t="n">
+        <v>0.0001654</v>
+      </c>
+      <c r="W450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -32049,9 +33402,12 @@
         <v>0.03715</v>
       </c>
       <c r="U451" s="1" t="n">
+        <v>0.03725</v>
+      </c>
+      <c r="V451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="V451" s="1" t="n">
+      <c r="W451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -32119,10 +33475,13 @@
         <v>0.00959</v>
       </c>
       <c r="U452" s="1" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="V452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="V452" s="1" t="n">
-        <v>0.00959</v>
+      <c r="W452" s="1" t="n">
+        <v>0.00957</v>
       </c>
     </row>
     <row r="453">
@@ -32189,9 +33548,12 @@
         <v>0.06777</v>
       </c>
       <c r="U453" s="1" t="n">
+        <v>0.06791999999999999</v>
+      </c>
+      <c r="V453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="V453" s="1" t="n">
+      <c r="W453" s="1" t="n">
         <v>0.06776</v>
       </c>
     </row>
@@ -32259,9 +33621,12 @@
         <v>0.00749</v>
       </c>
       <c r="U454" s="1" t="n">
+        <v>0.007495</v>
+      </c>
+      <c r="V454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="V454" s="1" t="n">
+      <c r="W454" s="1" t="n">
         <v>0.007478</v>
       </c>
     </row>
@@ -32329,9 +33694,12 @@
         <v>0.003271</v>
       </c>
       <c r="U455" s="1" t="n">
+        <v>0.003272</v>
+      </c>
+      <c r="V455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="V455" s="1" t="n">
+      <c r="W455" s="1" t="n">
         <v>0.003267</v>
       </c>
     </row>
@@ -32399,9 +33767,12 @@
         <v>0.001842</v>
       </c>
       <c r="U456" s="1" t="n">
+        <v>0.001847</v>
+      </c>
+      <c r="V456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="V456" s="1" t="n">
+      <c r="W456" s="1" t="n">
         <v>0.00184</v>
       </c>
     </row>
@@ -32469,9 +33840,12 @@
         <v>0.0001752</v>
       </c>
       <c r="U457" s="1" t="n">
+        <v>0.0001751</v>
+      </c>
+      <c r="V457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="V457" s="1" t="n">
+      <c r="W457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -32539,9 +33913,12 @@
         <v>0.0003883</v>
       </c>
       <c r="U458" s="1" t="n">
+        <v>0.0003896</v>
+      </c>
+      <c r="V458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="V458" s="1" t="n">
+      <c r="W458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -32609,9 +33986,12 @@
         <v>0.01402</v>
       </c>
       <c r="U459" s="1" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="V459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="V459" s="1" t="n">
+      <c r="W459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -32679,9 +34059,12 @@
         <v>0.0457</v>
       </c>
       <c r="U460" s="1" t="n">
+        <v>0.04565</v>
+      </c>
+      <c r="V460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="V460" s="1" t="n">
+      <c r="W460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -32749,9 +34132,12 @@
         <v>0.2843</v>
       </c>
       <c r="U461" s="1" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="V461" s="1" t="n">
         <v>0.2843</v>
       </c>
-      <c r="V461" s="1" t="n">
+      <c r="W461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -32819,9 +34205,12 @@
         <v>0.006248</v>
       </c>
       <c r="U462" s="1" t="n">
+        <v>0.006236</v>
+      </c>
+      <c r="V462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="V462" s="1" t="n">
+      <c r="W462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -32889,9 +34278,12 @@
         <v>0.00707</v>
       </c>
       <c r="U463" s="1" t="n">
-        <v>0.007088</v>
+        <v>0.007095</v>
       </c>
       <c r="V463" s="1" t="n">
+        <v>0.007095</v>
+      </c>
+      <c r="W463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -32962,6 +34354,9 @@
         <v>0.289</v>
       </c>
       <c r="V464" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="W464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -33029,9 +34424,12 @@
         <v>0.08155999999999999</v>
       </c>
       <c r="U465" s="1" t="n">
+        <v>0.08073</v>
+      </c>
+      <c r="V465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="V465" s="1" t="n">
+      <c r="W465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -33099,9 +34497,12 @@
         <v>0.6365</v>
       </c>
       <c r="U466" s="1" t="n">
+        <v>0.6352</v>
+      </c>
+      <c r="V466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="V466" s="1" t="n">
+      <c r="W466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -33169,9 +34570,12 @@
         <v>0.0147</v>
       </c>
       <c r="U467" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="V467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="V467" s="1" t="n">
+      <c r="W467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -33239,9 +34643,12 @@
         <v>0.03442</v>
       </c>
       <c r="U468" s="1" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="V468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="V468" s="1" t="n">
+      <c r="W468" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -33309,9 +34716,12 @@
         <v>0.1624</v>
       </c>
       <c r="U469" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="V469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="V469" s="1" t="n">
+      <c r="W469" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -33379,9 +34789,12 @@
         <v>0.4094</v>
       </c>
       <c r="U470" s="1" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="V470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="V470" s="1" t="n">
+      <c r="W470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -33449,9 +34862,12 @@
         <v>0.06875000000000001</v>
       </c>
       <c r="U471" s="1" t="n">
+        <v>0.06866999999999999</v>
+      </c>
+      <c r="V471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="V471" s="1" t="n">
+      <c r="W471" s="1" t="n">
         <v>0.06854</v>
       </c>
     </row>
@@ -33519,9 +34935,12 @@
         <v>0.06515</v>
       </c>
       <c r="U472" s="1" t="n">
+        <v>0.06534</v>
+      </c>
+      <c r="V472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="V472" s="1" t="n">
+      <c r="W472" s="1" t="n">
         <v>0.06515</v>
       </c>
     </row>
@@ -33589,9 +35008,12 @@
         <v>0.01624</v>
       </c>
       <c r="U473" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="V473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="V473" s="1" t="n">
+      <c r="W473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -33659,9 +35081,12 @@
         <v>0.2065</v>
       </c>
       <c r="U474" s="1" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="V474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="V474" s="1" t="n">
+      <c r="W474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -33729,9 +35154,12 @@
         <v>0.042</v>
       </c>
       <c r="U475" s="1" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="V475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="V475" s="1" t="n">
+      <c r="W475" s="1" t="n">
         <v>0.04183</v>
       </c>
     </row>
@@ -33799,9 +35227,12 @@
         <v>1.572</v>
       </c>
       <c r="U476" s="1" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="V476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="V476" s="1" t="n">
+      <c r="W476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -33869,9 +35300,12 @@
         <v>0.1005</v>
       </c>
       <c r="U477" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="V477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="V477" s="1" t="n">
+      <c r="W477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -33939,9 +35373,12 @@
         <v>0.001157</v>
       </c>
       <c r="U478" s="1" t="n">
+        <v>0.001158</v>
+      </c>
+      <c r="V478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="V478" s="1" t="n">
+      <c r="W478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -34009,10 +35446,13 @@
         <v>0.1437</v>
       </c>
       <c r="U479" s="1" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="V479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="V479" s="1" t="n">
-        <v>0.1433</v>
+      <c r="W479" s="1" t="n">
+        <v>0.1429</v>
       </c>
     </row>
     <row r="480">
@@ -34079,9 +35519,12 @@
         <v>0.001865</v>
       </c>
       <c r="U480" s="1" t="n">
-        <v>0.001865</v>
+        <v>0.001936</v>
       </c>
       <c r="V480" s="1" t="n">
+        <v>0.001936</v>
+      </c>
+      <c r="W480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -34149,9 +35592,12 @@
         <v>0.905</v>
       </c>
       <c r="U481" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="V481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="V481" s="1" t="n">
+      <c r="W481" s="1" t="n">
         <v>0.904</v>
       </c>
     </row>
@@ -34219,9 +35665,12 @@
         <v>0.13287</v>
       </c>
       <c r="U482" s="1" t="n">
+        <v>0.13335</v>
+      </c>
+      <c r="V482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="V482" s="1" t="n">
+      <c r="W482" s="1" t="n">
         <v>0.13233</v>
       </c>
     </row>
@@ -34289,9 +35738,12 @@
         <v>0.04015</v>
       </c>
       <c r="U483" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="V483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="V483" s="1" t="n">
+      <c r="W483" s="1" t="n">
         <v>0.04005</v>
       </c>
     </row>
@@ -34359,9 +35811,12 @@
         <v>0.3013</v>
       </c>
       <c r="U484" s="1" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="V484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="V484" s="1" t="n">
+      <c r="W484" s="1" t="n">
         <v>0.2999</v>
       </c>
     </row>
@@ -34429,9 +35884,12 @@
         <v>0.05651</v>
       </c>
       <c r="U485" s="1" t="n">
+        <v>0.05658</v>
+      </c>
+      <c r="V485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="V485" s="1" t="n">
+      <c r="W485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -34499,9 +35957,12 @@
         <v>0.00156</v>
       </c>
       <c r="U486" s="1" t="n">
+        <v>0.001561</v>
+      </c>
+      <c r="V486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="V486" s="1" t="n">
+      <c r="W486" s="1" t="n">
         <v>0.001558</v>
       </c>
     </row>
@@ -34569,9 +36030,12 @@
         <v>0.0668</v>
       </c>
       <c r="U487" s="1" t="n">
+        <v>0.06682</v>
+      </c>
+      <c r="V487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="V487" s="1" t="n">
+      <c r="W487" s="1" t="n">
         <v>0.06662</v>
       </c>
     </row>
@@ -34639,9 +36103,12 @@
         <v>0.1915</v>
       </c>
       <c r="U488" s="1" t="n">
+        <v>0.1918</v>
+      </c>
+      <c r="V488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="V488" s="1" t="n">
+      <c r="W488" s="1" t="n">
         <v>0.1911</v>
       </c>
     </row>
@@ -34709,9 +36176,12 @@
         <v>0.0477</v>
       </c>
       <c r="U489" s="1" t="n">
+        <v>0.04775</v>
+      </c>
+      <c r="V489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="V489" s="1" t="n">
+      <c r="W489" s="1" t="n">
         <v>0.04768</v>
       </c>
     </row>
@@ -34779,9 +36249,12 @@
         <v>0.1394</v>
       </c>
       <c r="U490" s="1" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="V490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="V490" s="1" t="n">
+      <c r="W490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -34849,9 +36322,12 @@
         <v>0.02241</v>
       </c>
       <c r="U491" s="1" t="n">
+        <v>0.02241</v>
+      </c>
+      <c r="V491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="V491" s="1" t="n">
+      <c r="W491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -34919,9 +36395,12 @@
         <v>0.007751</v>
       </c>
       <c r="U492" s="1" t="n">
+        <v>0.007798</v>
+      </c>
+      <c r="V492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="V492" s="1" t="n">
+      <c r="W492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -34989,9 +36468,12 @@
         <v>0.0005927</v>
       </c>
       <c r="U493" s="1" t="n">
+        <v>0.0005919</v>
+      </c>
+      <c r="V493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="V493" s="1" t="n">
+      <c r="W493" s="1" t="n">
         <v>0.0005918</v>
       </c>
     </row>
@@ -35059,9 +36541,12 @@
         <v>3.027</v>
       </c>
       <c r="U494" s="1" t="n">
+        <v>3.032</v>
+      </c>
+      <c r="V494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="V494" s="1" t="n">
+      <c r="W494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -35129,9 +36614,12 @@
         <v>0.05069</v>
       </c>
       <c r="U495" s="1" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="V495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="V495" s="1" t="n">
+      <c r="W495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -35199,9 +36687,12 @@
         <v>0.006837</v>
       </c>
       <c r="U496" s="1" t="n">
+        <v>0.006822</v>
+      </c>
+      <c r="V496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="V496" s="1" t="n">
+      <c r="W496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -35269,9 +36760,12 @@
         <v>1.305</v>
       </c>
       <c r="U497" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="V497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="V497" s="1" t="n">
+      <c r="W497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -35339,9 +36833,12 @@
         <v>0.0392</v>
       </c>
       <c r="U498" s="1" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="V498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="V498" s="1" t="n">
+      <c r="W498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -35409,9 +36906,12 @@
         <v>0.04093</v>
       </c>
       <c r="U499" s="1" t="n">
+        <v>0.04099</v>
+      </c>
+      <c r="V499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="V499" s="1" t="n">
+      <c r="W499" s="1" t="n">
         <v>0.04085</v>
       </c>
     </row>
@@ -35479,9 +36979,12 @@
         <v>0.00543</v>
       </c>
       <c r="U500" s="1" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="V500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="V500" s="1" t="n">
+      <c r="W500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -35549,9 +37052,12 @@
         <v>0.03551</v>
       </c>
       <c r="U501" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="V501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="V501" s="1" t="n">
+      <c r="W501" s="1" t="n">
         <v>0.03548</v>
       </c>
     </row>
@@ -35619,9 +37125,12 @@
         <v>0.07226</v>
       </c>
       <c r="U502" s="1" t="n">
+        <v>0.07209</v>
+      </c>
+      <c r="V502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="V502" s="1" t="n">
+      <c r="W502" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -35689,9 +37198,12 @@
         <v>0.0007441</v>
       </c>
       <c r="U503" s="1" t="n">
+        <v>0.0007444</v>
+      </c>
+      <c r="V503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="V503" s="1" t="n">
+      <c r="W503" s="1" t="n">
         <v>0.0007412</v>
       </c>
     </row>
@@ -35759,9 +37271,12 @@
         <v>0.016027</v>
       </c>
       <c r="U504" s="1" t="n">
+        <v>0.016031</v>
+      </c>
+      <c r="V504" s="1" t="n">
         <v>0.016034</v>
       </c>
-      <c r="V504" s="1" t="n">
+      <c r="W504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -35829,9 +37344,12 @@
         <v>0.00702</v>
       </c>
       <c r="U505" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="V505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="V505" s="1" t="n">
+      <c r="W505" s="1" t="n">
         <v>0.00701</v>
       </c>
     </row>
@@ -35899,9 +37417,12 @@
         <v>0.0254</v>
       </c>
       <c r="U506" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="V506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="V506" s="1" t="n">
+      <c r="W506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -35969,9 +37490,12 @@
         <v>0.001355</v>
       </c>
       <c r="U507" s="1" t="n">
+        <v>0.001356</v>
+      </c>
+      <c r="V507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="V507" s="1" t="n">
+      <c r="W507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -36039,9 +37563,12 @@
         <v>0.2808</v>
       </c>
       <c r="U508" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="V508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="V508" s="1" t="n">
+      <c r="W508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -36109,9 +37636,12 @@
         <v>0.1316</v>
       </c>
       <c r="U509" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="V509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="V509" s="1" t="n">
+      <c r="W509" s="1" t="n">
         <v>0.1314</v>
       </c>
     </row>
@@ -36179,9 +37709,12 @@
         <v>0.04916</v>
       </c>
       <c r="U510" s="1" t="n">
+        <v>0.04922</v>
+      </c>
+      <c r="V510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="V510" s="1" t="n">
+      <c r="W510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -36249,9 +37782,12 @@
         <v>0.0027</v>
       </c>
       <c r="U511" s="1" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="V511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="V511" s="1" t="n">
+      <c r="W511" s="1" t="n">
         <v>0.0027</v>
       </c>
     </row>
@@ -36319,9 +37855,12 @@
         <v>0.015038</v>
       </c>
       <c r="U512" s="1" t="n">
+        <v>0.015062</v>
+      </c>
+      <c r="V512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="V512" s="1" t="n">
+      <c r="W512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -36389,9 +37928,12 @@
         <v>0.6902</v>
       </c>
       <c r="U513" s="1" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="V513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="V513" s="1" t="n">
+      <c r="W513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -36459,9 +38001,12 @@
         <v>0.004499</v>
       </c>
       <c r="U514" s="1" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="V514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="V514" s="1" t="n">
+      <c r="W514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -36529,9 +38074,12 @@
         <v>0.005052</v>
       </c>
       <c r="U515" s="1" t="n">
+        <v>0.005043</v>
+      </c>
+      <c r="V515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="V515" s="1" t="n">
+      <c r="W515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -36599,9 +38147,12 @@
         <v>0.06319</v>
       </c>
       <c r="U516" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="V516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="V516" s="1" t="n">
+      <c r="W516" s="1" t="n">
         <v>0.06319</v>
       </c>
     </row>
@@ -36669,9 +38220,12 @@
         <v>0.06492000000000001</v>
       </c>
       <c r="U517" s="1" t="n">
+        <v>0.06517000000000001</v>
+      </c>
+      <c r="V517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="V517" s="1" t="n">
+      <c r="W517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -36739,9 +38293,12 @@
         <v>0.012</v>
       </c>
       <c r="U518" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="V518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="V518" s="1" t="n">
+      <c r="W518" s="1" t="n">
         <v>0.01198</v>
       </c>
     </row>
@@ -36809,9 +38366,12 @@
         <v>0.04754</v>
       </c>
       <c r="U519" s="1" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="V519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="V519" s="1" t="n">
+      <c r="W519" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -36879,9 +38439,12 @@
         <v>0.0438</v>
       </c>
       <c r="U520" s="1" t="n">
+        <v>0.04382</v>
+      </c>
+      <c r="V520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="V520" s="1" t="n">
+      <c r="W520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -36949,9 +38512,12 @@
         <v>0.008434000000000001</v>
       </c>
       <c r="U521" s="1" t="n">
+        <v>0.008421</v>
+      </c>
+      <c r="V521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="V521" s="1" t="n">
+      <c r="W521" s="1" t="n">
         <v>0.008402</v>
       </c>
     </row>
@@ -37019,9 +38585,12 @@
         <v>0.08788</v>
       </c>
       <c r="U522" s="1" t="n">
+        <v>0.08787</v>
+      </c>
+      <c r="V522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="V522" s="1" t="n">
+      <c r="W522" s="1" t="n">
         <v>0.08762</v>
       </c>
     </row>
@@ -37089,9 +38658,12 @@
         <v>0.006463</v>
       </c>
       <c r="U523" s="1" t="n">
+        <v>0.00649</v>
+      </c>
+      <c r="V523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="V523" s="1" t="n">
+      <c r="W523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -37159,9 +38731,12 @@
         <v>0.01631</v>
       </c>
       <c r="U524" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="V524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="V524" s="1" t="n">
+      <c r="W524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -37229,9 +38804,12 @@
         <v>0.01787</v>
       </c>
       <c r="U525" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="V525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="V525" s="1" t="n">
+      <c r="W525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -37299,10 +38877,13 @@
         <v>0.07872</v>
       </c>
       <c r="U526" s="1" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="V526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="V526" s="1" t="n">
-        <v>0.07862</v>
+      <c r="W526" s="1" t="n">
+        <v>0.0786</v>
       </c>
     </row>
     <row r="527">
@@ -37369,9 +38950,12 @@
         <v>0.01601</v>
       </c>
       <c r="U527" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="V527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="V527" s="1" t="n">
+      <c r="W527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -37439,9 +39023,12 @@
         <v>0.004113</v>
       </c>
       <c r="U528" s="1" t="n">
+        <v>0.004126</v>
+      </c>
+      <c r="V528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="V528" s="1" t="n">
+      <c r="W528" s="1" t="n">
         <v>0.004113</v>
       </c>
     </row>
@@ -37509,9 +39096,12 @@
         <v>0.003679</v>
       </c>
       <c r="U529" s="1" t="n">
+        <v>0.003683</v>
+      </c>
+      <c r="V529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="V529" s="1" t="n">
+      <c r="W529" s="1" t="n">
         <v>0.003672</v>
       </c>
     </row>
@@ -37579,9 +39169,12 @@
         <v>1.326</v>
       </c>
       <c r="U530" s="1" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="V530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="V530" s="1" t="n">
+      <c r="W530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -37649,9 +39242,12 @@
         <v>0.4881</v>
       </c>
       <c r="U531" s="1" t="n">
+        <v>0.4886</v>
+      </c>
+      <c r="V531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="V531" s="1" t="n">
+      <c r="W531" s="1" t="n">
         <v>0.487</v>
       </c>
     </row>
@@ -37719,9 +39315,12 @@
         <v>0.03053</v>
       </c>
       <c r="U532" s="1" t="n">
+        <v>0.03053</v>
+      </c>
+      <c r="V532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="V532" s="1" t="n">
+      <c r="W532" s="1" t="n">
         <v>0.03053</v>
       </c>
     </row>
@@ -37789,9 +39388,12 @@
         <v>0.1524</v>
       </c>
       <c r="U533" s="1" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="V533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="V533" s="1" t="n">
+      <c r="W533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -37859,9 +39461,12 @@
         <v>0.0535</v>
       </c>
       <c r="U534" s="1" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="V534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="V534" s="1" t="n">
+      <c r="W534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -37929,9 +39534,12 @@
         <v>0.01472</v>
       </c>
       <c r="U535" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="V535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="V535" s="1" t="n">
+      <c r="W535" s="1" t="n">
         <v>0.01472</v>
       </c>
     </row>
@@ -37999,9 +39607,12 @@
         <v>0.05868</v>
       </c>
       <c r="U536" s="1" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="V536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="V536" s="1" t="n">
+      <c r="W536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -38069,9 +39680,12 @@
         <v>0.05479</v>
       </c>
       <c r="U537" s="1" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="V537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="V537" s="1" t="n">
+      <c r="W537" s="1" t="n">
         <v>0.05476</v>
       </c>
     </row>
@@ -38139,9 +39753,12 @@
         <v>0.1058</v>
       </c>
       <c r="U538" s="1" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="V538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="V538" s="1" t="n">
+      <c r="W538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -38209,9 +39826,12 @@
         <v>0.01269</v>
       </c>
       <c r="U539" s="1" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="V539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="V539" s="1" t="n">
+      <c r="W539" s="1" t="n">
         <v>0.01265</v>
       </c>
     </row>
@@ -38279,9 +39899,12 @@
         <v>0.1727</v>
       </c>
       <c r="U540" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="V540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="V540" s="1" t="n">
+      <c r="W540" s="1" t="n">
         <v>0.1723</v>
       </c>
     </row>
@@ -38349,9 +39972,12 @@
         <v>0.123</v>
       </c>
       <c r="U541" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="V541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="V541" s="1" t="n">
+      <c r="W541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -38419,9 +40045,12 @@
         <v>0.02487</v>
       </c>
       <c r="U542" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="V542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="V542" s="1" t="n">
+      <c r="W542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -38489,9 +40118,12 @@
         <v>0.05851</v>
       </c>
       <c r="U543" s="1" t="n">
+        <v>0.05859</v>
+      </c>
+      <c r="V543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="V543" s="1" t="n">
+      <c r="W543" s="1" t="n">
         <v>0.05851</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y543"/>
+  <dimension ref="A1:Z543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -442,8 +442,9 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -564,10 +565,15 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>price_05:30</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -646,9 +652,12 @@
         <v>71367.60000000001</v>
       </c>
       <c r="X2" s="1" t="n">
+        <v>71123.89999999999</v>
+      </c>
+      <c r="Y2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="Y2" s="1" t="n">
+      <c r="Z2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -725,9 +734,12 @@
         <v>2112.06</v>
       </c>
       <c r="X3" s="1" t="n">
+        <v>2104.4</v>
+      </c>
+      <c r="Y3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="Y3" s="1" t="n">
+      <c r="Z3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -804,10 +816,13 @@
         <v>88.93000000000001</v>
       </c>
       <c r="X4" s="1" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="Y4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="Y4" s="1" t="n">
-        <v>88.7</v>
+      <c r="Z4" s="1" t="n">
+        <v>88.47</v>
       </c>
     </row>
     <row r="5">
@@ -883,9 +898,12 @@
         <v>3.852</v>
       </c>
       <c r="X5" s="1" t="n">
+        <v>3.828</v>
+      </c>
+      <c r="Y5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="Y5" s="1" t="n">
+      <c r="Z5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -962,9 +980,12 @@
         <v>1.4033</v>
       </c>
       <c r="X6" s="1" t="n">
+        <v>1.3979</v>
+      </c>
+      <c r="Y6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="Y6" s="1" t="n">
+      <c r="Z6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -1041,9 +1062,12 @@
         <v>0.09662</v>
       </c>
       <c r="X7" s="1" t="n">
+        <v>0.09617000000000001</v>
+      </c>
+      <c r="Y7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="Y7" s="1" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -1120,10 +1144,13 @@
         <v>0.013671</v>
       </c>
       <c r="X8" s="1" t="n">
+        <v>0.013551</v>
+      </c>
+      <c r="Y8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="Y8" s="1" t="n">
-        <v>0.013671</v>
+      <c r="Z8" s="1" t="n">
+        <v>0.013551</v>
       </c>
     </row>
     <row r="9">
@@ -1199,9 +1226,12 @@
         <v>658.35</v>
       </c>
       <c r="X9" s="1" t="n">
+        <v>656.61</v>
+      </c>
+      <c r="Y9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="Y9" s="1" t="n">
+      <c r="Z9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1278,9 +1308,12 @@
         <v>19.986</v>
       </c>
       <c r="X10" s="1" t="n">
+        <v>19.704</v>
+      </c>
+      <c r="Y10" s="1" t="n">
         <v>20.464</v>
       </c>
-      <c r="Y10" s="1" t="n">
+      <c r="Z10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1357,9 +1390,12 @@
         <v>0.0034186</v>
       </c>
       <c r="X11" s="1" t="n">
+        <v>0.0033994</v>
+      </c>
+      <c r="Y11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="Y11" s="1" t="n">
+      <c r="Z11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1436,9 +1472,12 @@
         <v>36.615</v>
       </c>
       <c r="X12" s="1" t="n">
+        <v>36.551</v>
+      </c>
+      <c r="Y12" s="1" t="n">
         <v>36.869</v>
       </c>
-      <c r="Y12" s="1" t="n">
+      <c r="Z12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1515,10 +1554,13 @@
         <v>212.32</v>
       </c>
       <c r="X13" s="1" t="n">
+        <v>210.47</v>
+      </c>
+      <c r="Y13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="Y13" s="1" t="n">
-        <v>211.48</v>
+      <c r="Z13" s="1" t="n">
+        <v>210.47</v>
       </c>
     </row>
     <row r="14">
@@ -1594,9 +1636,12 @@
         <v>0.0011307</v>
       </c>
       <c r="X14" s="1" t="n">
+        <v>0.0011332</v>
+      </c>
+      <c r="Y14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="Y14" s="1" t="n">
+      <c r="Z14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1673,9 +1718,12 @@
         <v>0.30305</v>
       </c>
       <c r="X15" s="1" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Y15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="Y15" s="1" t="n">
+      <c r="Z15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1752,9 +1800,12 @@
         <v>234.51</v>
       </c>
       <c r="X16" s="1" t="n">
+        <v>232.12</v>
+      </c>
+      <c r="Y16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="Y16" s="1" t="n">
+      <c r="Z16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -1831,9 +1882,12 @@
         <v>1.0071</v>
       </c>
       <c r="X17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="Y17" s="1" t="n">
+      <c r="Z17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1910,9 +1964,12 @@
         <v>0.2682</v>
       </c>
       <c r="X18" s="1" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="Y18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="Y18" s="1" t="n">
+      <c r="Z18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1989,9 +2046,12 @@
         <v>9.81</v>
       </c>
       <c r="X19" s="1" t="n">
+        <v>9.750999999999999</v>
+      </c>
+      <c r="Y19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="Y19" s="1" t="n">
+      <c r="Z19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -2068,10 +2128,13 @@
         <v>5014.48</v>
       </c>
       <c r="X20" s="1" t="n">
+        <v>5012.6</v>
+      </c>
+      <c r="Y20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="Y20" s="1" t="n">
-        <v>5014.48</v>
+      <c r="Z20" s="1" t="n">
+        <v>5012.6</v>
       </c>
     </row>
     <row r="21">
@@ -2147,9 +2210,12 @@
         <v>464.14</v>
       </c>
       <c r="X21" s="1" t="n">
+        <v>462.84</v>
+      </c>
+      <c r="Y21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="Y21" s="1" t="n">
+      <c r="Z21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -2226,9 +2292,12 @@
         <v>1.4047</v>
       </c>
       <c r="X22" s="1" t="n">
+        <v>1.4064</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="Y22" s="1" t="n">
+      <c r="Z22" s="1" t="n">
         <v>1.3686</v>
       </c>
     </row>
@@ -2305,9 +2374,12 @@
         <v>1.0556</v>
       </c>
       <c r="X23" s="1" t="n">
+        <v>1.0523</v>
+      </c>
+      <c r="Y23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="Y23" s="1" t="n">
+      <c r="Z23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2384,9 +2456,12 @@
         <v>1.353</v>
       </c>
       <c r="X24" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="Y24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="Y24" s="1" t="n">
+      <c r="Z24" s="1" t="n">
         <v>1.342</v>
       </c>
     </row>
@@ -2463,9 +2538,12 @@
         <v>9.183</v>
       </c>
       <c r="X25" s="1" t="n">
+        <v>9.125</v>
+      </c>
+      <c r="Y25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="Y25" s="1" t="n">
+      <c r="Z25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -2542,10 +2620,13 @@
         <v>0.363</v>
       </c>
       <c r="X26" s="1" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="Y26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="Y26" s="1" t="n">
-        <v>0.3619</v>
+      <c r="Z26" s="1" t="n">
+        <v>0.3613</v>
       </c>
     </row>
     <row r="27">
@@ -2621,9 +2702,12 @@
         <v>0.88</v>
       </c>
       <c r="X27" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Y27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="Y27" s="1" t="n">
+      <c r="Z27" s="1" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -2700,9 +2784,12 @@
         <v>1.863</v>
       </c>
       <c r="X28" s="1" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="Y28" s="1" t="n">
         <v>1.863</v>
       </c>
-      <c r="Y28" s="1" t="n">
+      <c r="Z28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2779,9 +2866,12 @@
         <v>0.11</v>
       </c>
       <c r="X29" s="1" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="Y29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="Y29" s="1" t="n">
+      <c r="Z29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -2858,9 +2948,12 @@
         <v>0.002025</v>
       </c>
       <c r="X30" s="1" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="Y30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="Y30" s="1" t="n">
+      <c r="Z30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -2937,9 +3030,12 @@
         <v>1.471</v>
       </c>
       <c r="X31" s="1" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="Y31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="Y31" s="1" t="n">
+      <c r="Z31" s="1" t="n">
         <v>1.46</v>
       </c>
     </row>
@@ -3016,9 +3112,12 @@
         <v>0.1771</v>
       </c>
       <c r="X32" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="Y32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="Y32" s="1" t="n">
+      <c r="Z32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -3095,9 +3194,12 @@
         <v>0.1043</v>
       </c>
       <c r="X33" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="Y33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="Y33" s="1" t="n">
+      <c r="Z33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -3174,9 +3276,12 @@
         <v>113.61</v>
       </c>
       <c r="X34" s="1" t="n">
+        <v>113.01</v>
+      </c>
+      <c r="Y34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="Y34" s="1" t="n">
+      <c r="Z34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -3253,9 +3358,12 @@
         <v>6.853</v>
       </c>
       <c r="X35" s="1" t="n">
+        <v>6.827</v>
+      </c>
+      <c r="Y35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="Y35" s="1" t="n">
+      <c r="Z35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -3332,9 +3440,12 @@
         <v>0.017894</v>
       </c>
       <c r="X36" s="1" t="n">
+        <v>0.017643</v>
+      </c>
+      <c r="Y36" s="1" t="n">
         <v>0.017894</v>
       </c>
-      <c r="Y36" s="1" t="n">
+      <c r="Z36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -3411,9 +3522,12 @@
         <v>0.3628</v>
       </c>
       <c r="X37" s="1" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="Y37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="Y37" s="1" t="n">
+      <c r="Z37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -3490,9 +3604,12 @@
         <v>55.92</v>
       </c>
       <c r="X38" s="1" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="Y38" s="1" t="n">
         <v>55.92</v>
       </c>
-      <c r="Y38" s="1" t="n">
+      <c r="Z38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -3569,9 +3686,12 @@
         <v>0.59278</v>
       </c>
       <c r="X39" s="1" t="n">
+        <v>0.5864</v>
+      </c>
+      <c r="Y39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="Y39" s="1" t="n">
+      <c r="Z39" s="1" t="n">
         <v>0.5717</v>
       </c>
     </row>
@@ -3648,9 +3768,12 @@
         <v>4.037</v>
       </c>
       <c r="X40" s="1" t="n">
+        <v>4.019</v>
+      </c>
+      <c r="Y40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="Y40" s="1" t="n">
+      <c r="Z40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -3727,10 +3850,13 @@
         <v>0.04831</v>
       </c>
       <c r="X41" s="1" t="n">
+        <v>0.04803</v>
+      </c>
+      <c r="Y41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="Y41" s="1" t="n">
-        <v>0.04831</v>
+      <c r="Z41" s="1" t="n">
+        <v>0.04803</v>
       </c>
     </row>
     <row r="42">
@@ -3806,9 +3932,12 @@
         <v>0.7018</v>
       </c>
       <c r="X42" s="1" t="n">
+        <v>0.6998</v>
+      </c>
+      <c r="Y42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="Y42" s="1" t="n">
+      <c r="Z42" s="1" t="n">
         <v>0.6995</v>
       </c>
     </row>
@@ -3885,10 +4014,13 @@
         <v>0.22684</v>
       </c>
       <c r="X43" s="1" t="n">
+        <v>0.22604</v>
+      </c>
+      <c r="Y43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="Y43" s="1" t="n">
-        <v>0.22684</v>
+      <c r="Z43" s="1" t="n">
+        <v>0.22604</v>
       </c>
     </row>
     <row r="44">
@@ -3964,9 +4096,12 @@
         <v>0.36093</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.36093</v>
+        <v>0.36189</v>
       </c>
       <c r="Y44" s="1" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="Z44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -4043,9 +4178,12 @@
         <v>0.17</v>
       </c>
       <c r="X45" s="1" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="Y45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="Y45" s="1" t="n">
+      <c r="Z45" s="1" t="n">
         <v>0.1682</v>
       </c>
     </row>
@@ -4122,10 +4260,13 @@
         <v>0.026</v>
       </c>
       <c r="X46" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="Y46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="Y46" s="1" t="n">
-        <v>0.0258</v>
+      <c r="Z46" s="1" t="n">
+        <v>0.0257</v>
       </c>
     </row>
     <row r="47">
@@ -4201,9 +4342,12 @@
         <v>0.005987</v>
       </c>
       <c r="X47" s="1" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="Y47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="Y47" s="1" t="n">
+      <c r="Z47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -4280,9 +4424,12 @@
         <v>0.007422</v>
       </c>
       <c r="X48" s="1" t="n">
+        <v>0.007362</v>
+      </c>
+      <c r="Y48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="Y48" s="1" t="n">
+      <c r="Z48" s="1" t="n">
         <v>0.007343</v>
       </c>
     </row>
@@ -4359,9 +4506,12 @@
         <v>0.1105</v>
       </c>
       <c r="X49" s="1" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="Y49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="Y49" s="1" t="n">
+      <c r="Z49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -4438,9 +4588,12 @@
         <v>0.04147</v>
       </c>
       <c r="X50" s="1" t="n">
+        <v>0.04123</v>
+      </c>
+      <c r="Y50" s="1" t="n">
         <v>0.04222</v>
       </c>
-      <c r="Y50" s="1" t="n">
+      <c r="Z50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -4517,10 +4670,13 @@
         <v>0.1625</v>
       </c>
       <c r="X51" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="Y51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="Y51" s="1" t="n">
-        <v>0.1614</v>
+      <c r="Z51" s="1" t="n">
+        <v>0.1604</v>
       </c>
     </row>
     <row r="52">
@@ -4596,9 +4752,12 @@
         <v>0.0036</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.0036</v>
+        <v>0.00361</v>
       </c>
       <c r="Y52" s="1" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="Z52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -4675,9 +4834,12 @@
         <v>2.622</v>
       </c>
       <c r="X53" s="1" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="Y53" s="1" t="n">
+      <c r="Z53" s="1" t="n">
         <v>2.613</v>
       </c>
     </row>
@@ -4754,9 +4916,12 @@
         <v>0.006224</v>
       </c>
       <c r="X54" s="1" t="n">
+        <v>0.006193</v>
+      </c>
+      <c r="Y54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="Y54" s="1" t="n">
+      <c r="Z54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -4833,10 +4998,13 @@
         <v>0.02785</v>
       </c>
       <c r="X55" s="1" t="n">
+        <v>0.02738</v>
+      </c>
+      <c r="Y55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="Y55" s="1" t="n">
-        <v>0.02767</v>
+      <c r="Z55" s="1" t="n">
+        <v>0.02738</v>
       </c>
     </row>
     <row r="56">
@@ -4912,10 +5080,13 @@
         <v>0.7368</v>
       </c>
       <c r="X56" s="1" t="n">
+        <v>0.7298</v>
+      </c>
+      <c r="Y56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="Y56" s="1" t="n">
-        <v>0.7322</v>
+      <c r="Z56" s="1" t="n">
+        <v>0.7298</v>
       </c>
     </row>
     <row r="57">
@@ -4991,9 +5162,12 @@
         <v>0.104</v>
       </c>
       <c r="X57" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="Y57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="Y57" s="1" t="n">
+      <c r="Z57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -5070,9 +5244,12 @@
         <v>0.9456</v>
       </c>
       <c r="X58" s="1" t="n">
+        <v>0.9389</v>
+      </c>
+      <c r="Y58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="Y58" s="1" t="n">
+      <c r="Z58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -5149,9 +5326,12 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="X59" s="1" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="Y59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="Y59" s="1" t="n">
+      <c r="Z59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -5228,9 +5408,12 @@
         <v>0.06986000000000001</v>
       </c>
       <c r="X60" s="1" t="n">
+        <v>0.06972</v>
+      </c>
+      <c r="Y60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="Y60" s="1" t="n">
+      <c r="Z60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -5307,9 +5490,12 @@
         <v>0.05539</v>
       </c>
       <c r="X61" s="1" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="Y61" s="1" t="n">
         <v>0.05539</v>
       </c>
-      <c r="Y61" s="1" t="n">
+      <c r="Z61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -5386,9 +5572,12 @@
         <v>0.01057</v>
       </c>
       <c r="X62" s="1" t="n">
-        <v>0.010624</v>
+        <v>0.010649</v>
       </c>
       <c r="Y62" s="1" t="n">
+        <v>0.010649</v>
+      </c>
+      <c r="Z62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -5465,9 +5654,12 @@
         <v>0.29206</v>
       </c>
       <c r="X63" s="1" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="Y63" s="1" t="n">
         <v>0.29207</v>
       </c>
-      <c r="Y63" s="1" t="n">
+      <c r="Z63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -5544,9 +5736,12 @@
         <v>0.07099</v>
       </c>
       <c r="X64" s="1" t="n">
+        <v>0.07074999999999999</v>
+      </c>
+      <c r="Y64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="Y64" s="1" t="n">
+      <c r="Z64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -5623,9 +5818,12 @@
         <v>0.3147</v>
       </c>
       <c r="X65" s="1" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="Y65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="Y65" s="1" t="n">
+      <c r="Z65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -5702,9 +5900,12 @@
         <v>0.16464</v>
       </c>
       <c r="X66" s="1" t="n">
-        <v>0.16464</v>
+        <v>0.16472</v>
       </c>
       <c r="Y66" s="1" t="n">
+        <v>0.16472</v>
+      </c>
+      <c r="Z66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -5781,10 +5982,13 @@
         <v>0.11935</v>
       </c>
       <c r="X67" s="1" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="Y67" s="1" t="n">
         <v>0.1203</v>
       </c>
-      <c r="Y67" s="1" t="n">
-        <v>0.11919</v>
+      <c r="Z67" s="1" t="n">
+        <v>0.1191</v>
       </c>
     </row>
     <row r="68">
@@ -5860,9 +6064,12 @@
         <v>0.09515999999999999</v>
       </c>
       <c r="X68" s="1" t="n">
+        <v>0.09487</v>
+      </c>
+      <c r="Y68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="Y68" s="1" t="n">
+      <c r="Z68" s="1" t="n">
         <v>0.09474</v>
       </c>
     </row>
@@ -5939,9 +6146,12 @@
         <v>0.1248</v>
       </c>
       <c r="X69" s="1" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="Y69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="Y69" s="1" t="n">
+      <c r="Z69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -6018,9 +6228,12 @@
         <v>8.558</v>
       </c>
       <c r="X70" s="1" t="n">
+        <v>8.525</v>
+      </c>
+      <c r="Y70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="Y70" s="1" t="n">
+      <c r="Z70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -6097,9 +6310,12 @@
         <v>0.238</v>
       </c>
       <c r="X71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Y71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="Y71" s="1" t="n">
+      <c r="Z71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -6176,9 +6392,12 @@
         <v>0.04962</v>
       </c>
       <c r="X72" s="1" t="n">
+        <v>0.04961</v>
+      </c>
+      <c r="Y72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="Y72" s="1" t="n">
+      <c r="Z72" s="1" t="n">
         <v>0.04955</v>
       </c>
     </row>
@@ -6255,9 +6474,12 @@
         <v>0.05064</v>
       </c>
       <c r="X73" s="1" t="n">
+        <v>0.05021</v>
+      </c>
+      <c r="Y73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="Y73" s="1" t="n">
+      <c r="Z73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -6334,10 +6556,13 @@
         <v>0.1232</v>
       </c>
       <c r="X74" s="1" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="Y74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="Y74" s="1" t="n">
-        <v>0.1232</v>
+      <c r="Z74" s="1" t="n">
+        <v>0.1222</v>
       </c>
     </row>
     <row r="75">
@@ -6413,9 +6638,12 @@
         <v>0.0466</v>
       </c>
       <c r="X75" s="1" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="Y75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="Y75" s="1" t="n">
+      <c r="Z75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -6492,9 +6720,12 @@
         <v>0.06691</v>
       </c>
       <c r="X76" s="1" t="n">
+        <v>0.06651</v>
+      </c>
+      <c r="Y76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="Y76" s="1" t="n">
+      <c r="Z76" s="1" t="n">
         <v>0.0664</v>
       </c>
     </row>
@@ -6571,9 +6802,12 @@
         <v>0.13727</v>
       </c>
       <c r="X77" s="1" t="n">
+        <v>0.13494</v>
+      </c>
+      <c r="Y77" s="1" t="n">
         <v>0.13727</v>
       </c>
-      <c r="Y77" s="1" t="n">
+      <c r="Z77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -6650,9 +6884,12 @@
         <v>0.1623</v>
       </c>
       <c r="X78" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="Y78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="Y78" s="1" t="n">
+      <c r="Z78" s="1" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -6729,10 +6966,13 @@
         <v>0.02707</v>
       </c>
       <c r="X79" s="1" t="n">
+        <v>0.02692</v>
+      </c>
+      <c r="Y79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="Y79" s="1" t="n">
-        <v>0.02693</v>
+      <c r="Z79" s="1" t="n">
+        <v>0.02692</v>
       </c>
     </row>
     <row r="80">
@@ -6808,9 +7048,12 @@
         <v>359.94</v>
       </c>
       <c r="X80" s="1" t="n">
+        <v>355.33</v>
+      </c>
+      <c r="Y80" s="1" t="n">
         <v>362.68</v>
       </c>
-      <c r="Y80" s="1" t="n">
+      <c r="Z80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -6887,9 +7130,12 @@
         <v>7.087e-05</v>
       </c>
       <c r="X81" s="1" t="n">
+        <v>7.056e-05</v>
+      </c>
+      <c r="Y81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="Y81" s="1" t="n">
+      <c r="Z81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -6966,9 +7212,12 @@
         <v>0.266</v>
       </c>
       <c r="X82" s="1" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="Y82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="Y82" s="1" t="n">
+      <c r="Z82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -7045,9 +7294,12 @@
         <v>1.1215</v>
       </c>
       <c r="X83" s="1" t="n">
+        <v>1.1199</v>
+      </c>
+      <c r="Y83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="Y83" s="1" t="n">
+      <c r="Z83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -7124,9 +7376,12 @@
         <v>0.3566</v>
       </c>
       <c r="X84" s="1" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="Y84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="Y84" s="1" t="n">
+      <c r="Z84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -7203,10 +7458,13 @@
         <v>1.956</v>
       </c>
       <c r="X85" s="1" t="n">
+        <v>1.9339</v>
+      </c>
+      <c r="Y85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="Y85" s="1" t="n">
-        <v>1.956</v>
+      <c r="Z85" s="1" t="n">
+        <v>1.9339</v>
       </c>
     </row>
     <row r="86">
@@ -7282,9 +7540,12 @@
         <v>1.3203</v>
       </c>
       <c r="X86" s="1" t="n">
+        <v>1.3184</v>
+      </c>
+      <c r="Y86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="Y86" s="1" t="n">
+      <c r="Z86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -7361,10 +7622,13 @@
         <v>32.7</v>
       </c>
       <c r="X87" s="1" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="Y87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="Y87" s="1" t="n">
-        <v>32.52</v>
+      <c r="Z87" s="1" t="n">
+        <v>32.5</v>
       </c>
     </row>
     <row r="88">
@@ -7440,9 +7704,12 @@
         <v>0.00958</v>
       </c>
       <c r="X88" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="Y88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="Y88" s="1" t="n">
+      <c r="Z88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -7519,10 +7786,13 @@
         <v>0.01782</v>
       </c>
       <c r="X89" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="Y89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="Y89" s="1" t="n">
-        <v>0.01782</v>
+      <c r="Z89" s="1" t="n">
+        <v>0.01781</v>
       </c>
     </row>
     <row r="90">
@@ -7598,10 +7868,13 @@
         <v>0.03504</v>
       </c>
       <c r="X90" s="1" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="Y90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="Y90" s="1" t="n">
-        <v>0.03468</v>
+      <c r="Z90" s="1" t="n">
+        <v>0.03445</v>
       </c>
     </row>
     <row r="91">
@@ -7677,10 +7950,13 @@
         <v>0.01171</v>
       </c>
       <c r="X91" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="Y91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="Y91" s="1" t="n">
-        <v>0.01169</v>
+      <c r="Z91" s="1" t="n">
+        <v>0.01154</v>
       </c>
     </row>
     <row r="92">
@@ -7756,9 +8032,12 @@
         <v>3.113</v>
       </c>
       <c r="X92" s="1" t="n">
+        <v>3.101</v>
+      </c>
+      <c r="Y92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="Y92" s="1" t="n">
+      <c r="Z92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -7835,9 +8114,12 @@
         <v>0.005585</v>
       </c>
       <c r="X93" s="1" t="n">
+        <v>0.005573</v>
+      </c>
+      <c r="Y93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="Y93" s="1" t="n">
+      <c r="Z93" s="1" t="n">
         <v>0.005559</v>
       </c>
     </row>
@@ -7914,9 +8196,12 @@
         <v>0.0944</v>
       </c>
       <c r="X94" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="Y94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="Y94" s="1" t="n">
+      <c r="Z94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -7993,9 +8278,12 @@
         <v>0.6318</v>
       </c>
       <c r="X95" s="1" t="n">
-        <v>0.6318</v>
+        <v>0.6363</v>
       </c>
       <c r="Y95" s="1" t="n">
+        <v>0.6363</v>
+      </c>
+      <c r="Z95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -8072,9 +8360,12 @@
         <v>1.27e-05</v>
       </c>
       <c r="X96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="Y96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="Y96" s="1" t="n">
+      <c r="Z96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -8151,9 +8442,12 @@
         <v>1.108</v>
       </c>
       <c r="X97" s="1" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="Y97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="Y97" s="1" t="n">
+      <c r="Z97" s="1" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -8230,10 +8524,13 @@
         <v>0.25251</v>
       </c>
       <c r="X98" s="1" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="Y98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="Y98" s="1" t="n">
-        <v>0.2523</v>
+      <c r="Z98" s="1" t="n">
+        <v>0.2508</v>
       </c>
     </row>
     <row r="99">
@@ -8309,9 +8606,12 @@
         <v>1.157</v>
       </c>
       <c r="X99" s="1" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="Y99" s="1" t="n">
         <v>1.157</v>
       </c>
-      <c r="Y99" s="1" t="n">
+      <c r="Z99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -8388,9 +8688,12 @@
         <v>1.863</v>
       </c>
       <c r="X100" s="1" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="Y100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="Y100" s="1" t="n">
+      <c r="Z100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -8467,9 +8770,12 @@
         <v>0.0157</v>
       </c>
       <c r="X101" s="1" t="n">
+        <v>0.01569</v>
+      </c>
+      <c r="Y101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="Y101" s="1" t="n">
+      <c r="Z101" s="1" t="n">
         <v>0.01563</v>
       </c>
     </row>
@@ -8546,9 +8852,12 @@
         <v>0.10174</v>
       </c>
       <c r="X102" s="1" t="n">
+        <v>0.10124</v>
+      </c>
+      <c r="Y102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="Y102" s="1" t="n">
+      <c r="Z102" s="1" t="n">
         <v>0.10062</v>
       </c>
     </row>
@@ -8625,9 +8934,12 @@
         <v>0.0005984</v>
       </c>
       <c r="X103" s="1" t="n">
+        <v>0.0005963</v>
+      </c>
+      <c r="Y103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="Y103" s="1" t="n">
+      <c r="Z103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -8704,9 +9016,12 @@
         <v>0.0005754999999999999</v>
       </c>
       <c r="X104" s="1" t="n">
+        <v>0.0005689</v>
+      </c>
+      <c r="Y104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="Y104" s="1" t="n">
+      <c r="Z104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -8783,9 +9098,12 @@
         <v>0.003252</v>
       </c>
       <c r="X105" s="1" t="n">
+        <v>0.003242</v>
+      </c>
+      <c r="Y105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="Y105" s="1" t="n">
+      <c r="Z105" s="1" t="n">
         <v>0.003216</v>
       </c>
     </row>
@@ -8862,10 +9180,13 @@
         <v>2.577</v>
       </c>
       <c r="X106" s="1" t="n">
+        <v>2.557</v>
+      </c>
+      <c r="Y106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="Y106" s="1" t="n">
-        <v>2.572</v>
+      <c r="Z106" s="1" t="n">
+        <v>2.557</v>
       </c>
     </row>
     <row r="107">
@@ -8941,9 +9262,12 @@
         <v>0.166</v>
       </c>
       <c r="X107" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="Y107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="Y107" s="1" t="n">
+      <c r="Z107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -9020,9 +9344,12 @@
         <v>0.09655</v>
       </c>
       <c r="X108" s="1" t="n">
+        <v>0.09597</v>
+      </c>
+      <c r="Y108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="Y108" s="1" t="n">
+      <c r="Z108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -9099,9 +9426,12 @@
         <v>0.02214</v>
       </c>
       <c r="X109" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="Y109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="Y109" s="1" t="n">
+      <c r="Z109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -9178,9 +9508,12 @@
         <v>0.2916</v>
       </c>
       <c r="X110" s="1" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="Y110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="Y110" s="1" t="n">
+      <c r="Z110" s="1" t="n">
         <v>0.2894</v>
       </c>
     </row>
@@ -9257,9 +9590,12 @@
         <v>0.05689</v>
       </c>
       <c r="X111" s="1" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="Y111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="Y111" s="1" t="n">
+      <c r="Z111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -9336,9 +9672,12 @@
         <v>0.3028</v>
       </c>
       <c r="X112" s="1" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="Y112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="Y112" s="1" t="n">
+      <c r="Z112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -9415,10 +9754,13 @@
         <v>18.59</v>
       </c>
       <c r="X113" s="1" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="Y113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="Y113" s="1" t="n">
-        <v>18.53</v>
+      <c r="Z113" s="1" t="n">
+        <v>18.52</v>
       </c>
     </row>
     <row r="114">
@@ -9494,9 +9836,12 @@
         <v>0.12711</v>
       </c>
       <c r="X114" s="1" t="n">
+        <v>0.12632</v>
+      </c>
+      <c r="Y114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="Y114" s="1" t="n">
+      <c r="Z114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -9573,9 +9918,12 @@
         <v>0.01595</v>
       </c>
       <c r="X115" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="Y115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="Y115" s="1" t="n">
+      <c r="Z115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -9652,9 +10000,12 @@
         <v>0.08511000000000001</v>
       </c>
       <c r="X116" s="1" t="n">
+        <v>0.08470999999999999</v>
+      </c>
+      <c r="Y116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="Y116" s="1" t="n">
+      <c r="Z116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -9731,10 +10082,13 @@
         <v>0.046747</v>
       </c>
       <c r="X117" s="1" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="Y117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="Y117" s="1" t="n">
-        <v>0.046552</v>
+      <c r="Z117" s="1" t="n">
+        <v>0.04654</v>
       </c>
     </row>
     <row r="118">
@@ -9810,9 +10164,12 @@
         <v>0.04745</v>
       </c>
       <c r="X118" s="1" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="Y118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="Y118" s="1" t="n">
+      <c r="Z118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -9889,9 +10246,12 @@
         <v>0.04003</v>
       </c>
       <c r="X119" s="1" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="Y119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="Y119" s="1" t="n">
+      <c r="Z119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -9968,9 +10328,12 @@
         <v>0.145</v>
       </c>
       <c r="X120" s="1" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="Y120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="Y120" s="1" t="n">
+      <c r="Z120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -10047,10 +10410,13 @@
         <v>0.1251</v>
       </c>
       <c r="X121" s="1" t="n">
+        <v>0.1246</v>
+      </c>
+      <c r="Y121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="Y121" s="1" t="n">
-        <v>0.1251</v>
+      <c r="Z121" s="1" t="n">
+        <v>0.1246</v>
       </c>
     </row>
     <row r="122">
@@ -10126,10 +10492,13 @@
         <v>1.844</v>
       </c>
       <c r="X122" s="1" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="Y122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="Y122" s="1" t="n">
-        <v>1.836</v>
+      <c r="Z122" s="1" t="n">
+        <v>1.831</v>
       </c>
     </row>
     <row r="123">
@@ -10205,9 +10574,12 @@
         <v>0.03022</v>
       </c>
       <c r="X123" s="1" t="n">
+        <v>0.03008</v>
+      </c>
+      <c r="Y123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="Y123" s="1" t="n">
+      <c r="Z123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -10284,9 +10656,12 @@
         <v>0.13338</v>
       </c>
       <c r="X124" s="1" t="n">
+        <v>0.13227</v>
+      </c>
+      <c r="Y124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="Y124" s="1" t="n">
+      <c r="Z124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -10363,9 +10738,12 @@
         <v>0.0411</v>
       </c>
       <c r="X125" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="Y125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="Y125" s="1" t="n">
+      <c r="Z125" s="1" t="n">
         <v>0.04075</v>
       </c>
     </row>
@@ -10442,9 +10820,12 @@
         <v>0.1151</v>
       </c>
       <c r="X126" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="Y126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="Y126" s="1" t="n">
+      <c r="Z126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -10521,9 +10902,12 @@
         <v>0.533</v>
       </c>
       <c r="X127" s="1" t="n">
-        <v>0.535</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="Y127" s="1" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="Z127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -10600,9 +10984,12 @@
         <v>0.03827</v>
       </c>
       <c r="X128" s="1" t="n">
+        <v>0.03816</v>
+      </c>
+      <c r="Y128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="Y128" s="1" t="n">
+      <c r="Z128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -10679,9 +11066,12 @@
         <v>0.797</v>
       </c>
       <c r="X129" s="1" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="Y129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="Y129" s="1" t="n">
+      <c r="Z129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -10758,9 +11148,12 @@
         <v>0.03463</v>
       </c>
       <c r="X130" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="Y130" s="1" t="n">
         <v>0.03463</v>
       </c>
-      <c r="Y130" s="1" t="n">
+      <c r="Z130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -10837,9 +11230,12 @@
         <v>0.4288</v>
       </c>
       <c r="X131" s="1" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="Y131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="Y131" s="1" t="n">
+      <c r="Z131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -10916,9 +11312,12 @@
         <v>0.04332</v>
       </c>
       <c r="X132" s="1" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="Y132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="Y132" s="1" t="n">
+      <c r="Z132" s="1" t="n">
         <v>0.04303</v>
       </c>
     </row>
@@ -10995,9 +11394,12 @@
         <v>1.2862</v>
       </c>
       <c r="X133" s="1" t="n">
+        <v>1.2806</v>
+      </c>
+      <c r="Y133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="Y133" s="1" t="n">
+      <c r="Z133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -11074,9 +11476,12 @@
         <v>0.02201</v>
       </c>
       <c r="X134" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="Y134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="Y134" s="1" t="n">
+      <c r="Z134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -11153,9 +11558,12 @@
         <v>0.0004596</v>
       </c>
       <c r="X135" s="1" t="n">
+        <v>0.0004568</v>
+      </c>
+      <c r="Y135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="Y135" s="1" t="n">
+      <c r="Z135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -11232,9 +11640,12 @@
         <v>0.001912</v>
       </c>
       <c r="X136" s="1" t="n">
+        <v>0.001892</v>
+      </c>
+      <c r="Y136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="Y136" s="1" t="n">
+      <c r="Z136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -11311,9 +11722,12 @@
         <v>0.3169</v>
       </c>
       <c r="X137" s="1" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="Y137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="Y137" s="1" t="n">
+      <c r="Z137" s="1" t="n">
         <v>0.3136</v>
       </c>
     </row>
@@ -11390,10 +11804,13 @@
         <v>0.5620000000000001</v>
       </c>
       <c r="X138" s="1" t="n">
+        <v>0.5582</v>
+      </c>
+      <c r="Y138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="Y138" s="1" t="n">
-        <v>0.5599</v>
+      <c r="Z138" s="1" t="n">
+        <v>0.5582</v>
       </c>
     </row>
     <row r="139">
@@ -11469,9 +11886,12 @@
         <v>0.02124</v>
       </c>
       <c r="X139" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="Y139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="Y139" s="1" t="n">
+      <c r="Z139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -11548,10 +11968,13 @@
         <v>0.07985</v>
       </c>
       <c r="X140" s="1" t="n">
+        <v>0.07947</v>
+      </c>
+      <c r="Y140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="Y140" s="1" t="n">
-        <v>0.0796</v>
+      <c r="Z140" s="1" t="n">
+        <v>0.07947</v>
       </c>
     </row>
     <row r="141">
@@ -11627,9 +12050,12 @@
         <v>0.001515</v>
       </c>
       <c r="X141" s="1" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="Y141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="Y141" s="1" t="n">
+      <c r="Z141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -11706,9 +12132,12 @@
         <v>0.4509</v>
       </c>
       <c r="X142" s="1" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="Y142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="Y142" s="1" t="n">
+      <c r="Z142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -11785,9 +12214,12 @@
         <v>0.030243</v>
       </c>
       <c r="X143" s="1" t="n">
+        <v>0.029959</v>
+      </c>
+      <c r="Y143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="Y143" s="1" t="n">
+      <c r="Z143" s="1" t="n">
         <v>0.029881</v>
       </c>
     </row>
@@ -11864,9 +12296,12 @@
         <v>0.000226</v>
       </c>
       <c r="X144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="Y144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="Y144" s="1" t="n">
+      <c r="Z144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -11943,9 +12378,12 @@
         <v>0.03448</v>
       </c>
       <c r="X145" s="1" t="n">
+        <v>0.03476</v>
+      </c>
+      <c r="Y145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="Y145" s="1" t="n">
+      <c r="Z145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -12022,9 +12460,12 @@
         <v>0.11682</v>
       </c>
       <c r="X146" s="1" t="n">
+        <v>0.11675</v>
+      </c>
+      <c r="Y146" s="1" t="n">
         <v>0.11718</v>
       </c>
-      <c r="Y146" s="1" t="n">
+      <c r="Z146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -12101,9 +12542,12 @@
         <v>0.02219</v>
       </c>
       <c r="X147" s="1" t="n">
+        <v>0.02223</v>
+      </c>
+      <c r="Y147" s="1" t="n">
         <v>0.02258</v>
       </c>
-      <c r="Y147" s="1" t="n">
+      <c r="Z147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -12180,9 +12624,12 @@
         <v>1.4165</v>
       </c>
       <c r="X148" s="1" t="n">
+        <v>1.4124</v>
+      </c>
+      <c r="Y148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="Y148" s="1" t="n">
+      <c r="Z148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -12259,10 +12706,13 @@
         <v>1.8666</v>
       </c>
       <c r="X149" s="1" t="n">
+        <v>1.8574</v>
+      </c>
+      <c r="Y149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="Y149" s="1" t="n">
-        <v>1.8594</v>
+      <c r="Z149" s="1" t="n">
+        <v>1.8574</v>
       </c>
     </row>
     <row r="150">
@@ -12338,9 +12788,12 @@
         <v>0.096</v>
       </c>
       <c r="X150" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Y150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="Y150" s="1" t="n">
+      <c r="Z150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -12417,9 +12870,12 @@
         <v>4.731</v>
       </c>
       <c r="X151" s="1" t="n">
+        <v>4.675</v>
+      </c>
+      <c r="Y151" s="1" t="n">
         <v>4.731</v>
       </c>
-      <c r="Y151" s="1" t="n">
+      <c r="Z151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -12496,9 +12952,12 @@
         <v>5.559</v>
       </c>
       <c r="X152" s="1" t="n">
+        <v>5.526</v>
+      </c>
+      <c r="Y152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="Y152" s="1" t="n">
+      <c r="Z152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -12575,9 +13034,12 @@
         <v>0.3248</v>
       </c>
       <c r="X153" s="1" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="Y153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="Y153" s="1" t="n">
+      <c r="Z153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -12654,9 +13116,12 @@
         <v>0.5861</v>
       </c>
       <c r="X154" s="1" t="n">
+        <v>0.5845</v>
+      </c>
+      <c r="Y154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="Y154" s="1" t="n">
+      <c r="Z154" s="1" t="n">
         <v>0.5825</v>
       </c>
     </row>
@@ -12733,9 +13198,12 @@
         <v>0.01284</v>
       </c>
       <c r="X155" s="1" t="n">
+        <v>0.01268</v>
+      </c>
+      <c r="Y155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="Y155" s="1" t="n">
+      <c r="Z155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -12812,9 +13280,12 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="X156" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="Y156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="Y156" s="1" t="n">
+      <c r="Z156" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
     </row>
@@ -12891,9 +13362,12 @@
         <v>16.477</v>
       </c>
       <c r="X157" s="1" t="n">
+        <v>16.373</v>
+      </c>
+      <c r="Y157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="Y157" s="1" t="n">
+      <c r="Z157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -12970,9 +13444,12 @@
         <v>0.0555</v>
       </c>
       <c r="X158" s="1" t="n">
+        <v>0.05527</v>
+      </c>
+      <c r="Y158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="Y158" s="1" t="n">
+      <c r="Z158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -13049,9 +13526,12 @@
         <v>28.86</v>
       </c>
       <c r="X159" s="1" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="Y159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="Y159" s="1" t="n">
+      <c r="Z159" s="1" t="n">
         <v>28.65</v>
       </c>
     </row>
@@ -13128,9 +13608,12 @@
         <v>0.02166</v>
       </c>
       <c r="X160" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="Y160" s="1" t="n">
         <v>0.02166</v>
       </c>
-      <c r="Y160" s="1" t="n">
+      <c r="Z160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -13207,9 +13690,12 @@
         <v>0.0006561</v>
       </c>
       <c r="X161" s="1" t="n">
+        <v>0.0006522</v>
+      </c>
+      <c r="Y161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="Y161" s="1" t="n">
+      <c r="Z161" s="1" t="n">
         <v>0.0006503</v>
       </c>
     </row>
@@ -13286,9 +13772,12 @@
         <v>0.3909</v>
       </c>
       <c r="X162" s="1" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Y162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="Y162" s="1" t="n">
+      <c r="Z162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -13365,10 +13854,13 @@
         <v>0.1916</v>
       </c>
       <c r="X163" s="1" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="Y163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="Y163" s="1" t="n">
-        <v>0.1908</v>
+      <c r="Z163" s="1" t="n">
+        <v>0.1905</v>
       </c>
     </row>
     <row r="164">
@@ -13444,9 +13936,12 @@
         <v>0.317</v>
       </c>
       <c r="X164" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="Y164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="Y164" s="1" t="n">
+      <c r="Z164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -13523,9 +14018,12 @@
         <v>0.378</v>
       </c>
       <c r="X165" s="1" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="Y165" s="1" t="n">
         <v>0.378</v>
       </c>
-      <c r="Y165" s="1" t="n">
+      <c r="Z165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -13602,9 +14100,12 @@
         <v>0.02263</v>
       </c>
       <c r="X166" s="1" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="Y166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="Y166" s="1" t="n">
+      <c r="Z166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -13681,9 +14182,12 @@
         <v>0.00729</v>
       </c>
       <c r="X167" s="1" t="n">
+        <v>0.007257</v>
+      </c>
+      <c r="Y167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="Y167" s="1" t="n">
+      <c r="Z167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -13760,10 +14264,13 @@
         <v>0.0134</v>
       </c>
       <c r="X168" s="1" t="n">
+        <v>0.01327</v>
+      </c>
+      <c r="Y168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="Y168" s="1" t="n">
-        <v>0.0133</v>
+      <c r="Z168" s="1" t="n">
+        <v>0.01327</v>
       </c>
     </row>
     <row r="169">
@@ -13839,9 +14346,12 @@
         <v>0.25751</v>
       </c>
       <c r="X169" s="1" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="Y169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="Y169" s="1" t="n">
+      <c r="Z169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -13918,9 +14428,12 @@
         <v>0.02188</v>
       </c>
       <c r="X170" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="Y170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="Y170" s="1" t="n">
+      <c r="Z170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -13997,10 +14510,13 @@
         <v>0.1725</v>
       </c>
       <c r="X171" s="1" t="n">
+        <v>0.1708</v>
+      </c>
+      <c r="Y171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="Y171" s="1" t="n">
-        <v>0.171</v>
+      <c r="Z171" s="1" t="n">
+        <v>0.1708</v>
       </c>
     </row>
     <row r="172">
@@ -14079,6 +14595,9 @@
         <v>0.09</v>
       </c>
       <c r="Y172" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -14155,9 +14674,12 @@
         <v>0.004691</v>
       </c>
       <c r="X173" s="1" t="n">
+        <v>0.004669</v>
+      </c>
+      <c r="Y173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="Y173" s="1" t="n">
+      <c r="Z173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -14234,9 +14756,12 @@
         <v>0.4397</v>
       </c>
       <c r="X174" s="1" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="Y174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="Y174" s="1" t="n">
+      <c r="Z174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -14313,9 +14838,12 @@
         <v>0.09276</v>
       </c>
       <c r="X175" s="1" t="n">
+        <v>0.09273000000000001</v>
+      </c>
+      <c r="Y175" s="1" t="n">
         <v>0.09276</v>
       </c>
-      <c r="Y175" s="1" t="n">
+      <c r="Z175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -14392,10 +14920,13 @@
         <v>0.245</v>
       </c>
       <c r="X176" s="1" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="Y176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="Y176" s="1" t="n">
-        <v>0.245</v>
+      <c r="Z176" s="1" t="n">
+        <v>0.2434</v>
       </c>
     </row>
     <row r="177">
@@ -14471,9 +15002,12 @@
         <v>0.01928</v>
       </c>
       <c r="X177" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="Y177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="Y177" s="1" t="n">
+      <c r="Z177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -14550,10 +15084,13 @@
         <v>6.134</v>
       </c>
       <c r="X178" s="1" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="Y178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="Y178" s="1" t="n">
-        <v>6.106</v>
+      <c r="Z178" s="1" t="n">
+        <v>6.09</v>
       </c>
     </row>
     <row r="179">
@@ -14629,9 +15166,12 @@
         <v>0.136</v>
       </c>
       <c r="X179" s="1" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="Y179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="Y179" s="1" t="n">
+      <c r="Z179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -14708,9 +15248,12 @@
         <v>0.004958</v>
       </c>
       <c r="X180" s="1" t="n">
+        <v>0.004954</v>
+      </c>
+      <c r="Y180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="Y180" s="1" t="n">
+      <c r="Z180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -14787,9 +15330,12 @@
         <v>0.012</v>
       </c>
       <c r="X181" s="1" t="n">
+        <v>0.01194</v>
+      </c>
+      <c r="Y181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="Y181" s="1" t="n">
+      <c r="Z181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -14866,10 +15412,13 @@
         <v>0.007285</v>
       </c>
       <c r="X182" s="1" t="n">
+        <v>0.007212</v>
+      </c>
+      <c r="Y182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="Y182" s="1" t="n">
-        <v>0.007224</v>
+      <c r="Z182" s="1" t="n">
+        <v>0.007212</v>
       </c>
     </row>
     <row r="183">
@@ -14945,9 +15494,12 @@
         <v>0.13069</v>
       </c>
       <c r="X183" s="1" t="n">
+        <v>0.13076</v>
+      </c>
+      <c r="Y183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="Y183" s="1" t="n">
+      <c r="Z183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -15024,9 +15576,12 @@
         <v>0.09601999999999999</v>
       </c>
       <c r="X184" s="1" t="n">
+        <v>0.09606000000000001</v>
+      </c>
+      <c r="Y184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="Y184" s="1" t="n">
+      <c r="Z184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -15103,9 +15658,12 @@
         <v>0.00756</v>
       </c>
       <c r="X185" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="Y185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="Y185" s="1" t="n">
+      <c r="Z185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -15182,10 +15740,13 @@
         <v>0.04877</v>
       </c>
       <c r="X186" s="1" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="Y186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="Y186" s="1" t="n">
-        <v>0.04851</v>
+      <c r="Z186" s="1" t="n">
+        <v>0.0485</v>
       </c>
     </row>
     <row r="187">
@@ -15261,9 +15822,12 @@
         <v>0.0268</v>
       </c>
       <c r="X187" s="1" t="n">
+        <v>0.02656</v>
+      </c>
+      <c r="Y187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="Y187" s="1" t="n">
+      <c r="Z187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -15340,10 +15904,13 @@
         <v>0.003282</v>
       </c>
       <c r="X188" s="1" t="n">
+        <v>0.00327</v>
+      </c>
+      <c r="Y188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="Y188" s="1" t="n">
-        <v>0.003274</v>
+      <c r="Z188" s="1" t="n">
+        <v>0.00327</v>
       </c>
     </row>
     <row r="189">
@@ -15419,9 +15986,12 @@
         <v>0.2861</v>
       </c>
       <c r="X189" s="1" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="Y189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="Y189" s="1" t="n">
+      <c r="Z189" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -15498,10 +16068,13 @@
         <v>0.01786</v>
       </c>
       <c r="X190" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="Y190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="Y190" s="1" t="n">
-        <v>0.01783</v>
+      <c r="Z190" s="1" t="n">
+        <v>0.01779</v>
       </c>
     </row>
     <row r="191">
@@ -15577,9 +16150,12 @@
         <v>0.2584</v>
       </c>
       <c r="X191" s="1" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="Y191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="Y191" s="1" t="n">
+      <c r="Z191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -15656,10 +16232,13 @@
         <v>0.03821</v>
       </c>
       <c r="X192" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="Y192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="Y192" s="1" t="n">
-        <v>0.03766</v>
+      <c r="Z192" s="1" t="n">
+        <v>0.037</v>
       </c>
     </row>
     <row r="193">
@@ -15735,9 +16314,12 @@
         <v>0.0002218</v>
       </c>
       <c r="X193" s="1" t="n">
+        <v>0.0002212</v>
+      </c>
+      <c r="Y193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="Y193" s="1" t="n">
+      <c r="Z193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -15814,9 +16396,12 @@
         <v>4.087</v>
       </c>
       <c r="X194" s="1" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="Y194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="Y194" s="1" t="n">
+      <c r="Z194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -15896,6 +16481,9 @@
         <v>0.999401</v>
       </c>
       <c r="Y195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="Z195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -15972,9 +16560,12 @@
         <v>4.349</v>
       </c>
       <c r="X196" s="1" t="n">
+        <v>4.354</v>
+      </c>
+      <c r="Y196" s="1" t="n">
         <v>4.368</v>
       </c>
-      <c r="Y196" s="1" t="n">
+      <c r="Z196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -16051,9 +16642,12 @@
         <v>0.15114</v>
       </c>
       <c r="X197" s="1" t="n">
+        <v>0.15134</v>
+      </c>
+      <c r="Y197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="Y197" s="1" t="n">
+      <c r="Z197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -16130,9 +16724,12 @@
         <v>0.007990000000000001</v>
       </c>
       <c r="X198" s="1" t="n">
+        <v>0.007986</v>
+      </c>
+      <c r="Y198" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="Y198" s="1" t="n">
+      <c r="Z198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -16209,9 +16806,12 @@
         <v>0.4531</v>
       </c>
       <c r="X199" s="1" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="Y199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="Y199" s="1" t="n">
+      <c r="Z199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -16288,9 +16888,12 @@
         <v>0.5878</v>
       </c>
       <c r="X200" s="1" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="Y200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="Y200" s="1" t="n">
+      <c r="Z200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -16367,9 +16970,12 @@
         <v>0.0927</v>
       </c>
       <c r="X201" s="1" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="Y201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="Y201" s="1" t="n">
+      <c r="Z201" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -16446,9 +17052,12 @@
         <v>0.06057</v>
       </c>
       <c r="X202" s="1" t="n">
+        <v>0.06024</v>
+      </c>
+      <c r="Y202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="Y202" s="1" t="n">
+      <c r="Z202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -16525,9 +17134,12 @@
         <v>0.00804</v>
       </c>
       <c r="X203" s="1" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="Y203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="Y203" s="1" t="n">
+      <c r="Z203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -16604,9 +17216,12 @@
         <v>0.00413</v>
       </c>
       <c r="X204" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="Y204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="Y204" s="1" t="n">
+      <c r="Z204" s="1" t="n">
         <v>0.00412</v>
       </c>
     </row>
@@ -16683,10 +17298,13 @@
         <v>0.009069000000000001</v>
       </c>
       <c r="X205" s="1" t="n">
+        <v>0.009036000000000001</v>
+      </c>
+      <c r="Y205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="Y205" s="1" t="n">
-        <v>0.009067</v>
+      <c r="Z205" s="1" t="n">
+        <v>0.009036000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -16762,9 +17380,12 @@
         <v>0.2388</v>
       </c>
       <c r="X206" s="1" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="Y206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="Y206" s="1" t="n">
+      <c r="Z206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -16841,9 +17462,12 @@
         <v>0.0214</v>
       </c>
       <c r="X207" s="1" t="n">
+        <v>0.02123</v>
+      </c>
+      <c r="Y207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="Y207" s="1" t="n">
+      <c r="Z207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -16920,9 +17544,12 @@
         <v>0.2386</v>
       </c>
       <c r="X208" s="1" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="Y208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="Y208" s="1" t="n">
+      <c r="Z208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -16999,10 +17626,13 @@
         <v>0.3596</v>
       </c>
       <c r="X209" s="1" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="Y209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="Y209" s="1" t="n">
-        <v>0.3584</v>
+      <c r="Z209" s="1" t="n">
+        <v>0.3576</v>
       </c>
     </row>
     <row r="210">
@@ -17078,9 +17708,12 @@
         <v>0.0429</v>
       </c>
       <c r="X210" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="Y210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="Y210" s="1" t="n">
+      <c r="Z210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -17157,10 +17790,13 @@
         <v>0.000425</v>
       </c>
       <c r="X211" s="1" t="n">
+        <v>0.0004225</v>
+      </c>
+      <c r="Y211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="Y211" s="1" t="n">
-        <v>0.0004234</v>
+      <c r="Z211" s="1" t="n">
+        <v>0.0004225</v>
       </c>
     </row>
     <row r="212">
@@ -17236,10 +17872,13 @@
         <v>0.02136</v>
       </c>
       <c r="X212" s="1" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="Y212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="Y212" s="1" t="n">
-        <v>0.02123</v>
+      <c r="Z212" s="1" t="n">
+        <v>0.02122</v>
       </c>
     </row>
     <row r="213">
@@ -17315,9 +17954,12 @@
         <v>0.1156</v>
       </c>
       <c r="X213" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="Y213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="Y213" s="1" t="n">
+      <c r="Z213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -17394,9 +18036,12 @@
         <v>0.04225</v>
       </c>
       <c r="X214" s="1" t="n">
-        <v>0.04225</v>
+        <v>0.04232</v>
       </c>
       <c r="Y214" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="Z214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -17473,10 +18118,13 @@
         <v>0.00976</v>
       </c>
       <c r="X215" s="1" t="n">
+        <v>0.00971</v>
+      </c>
+      <c r="Y215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="Y215" s="1" t="n">
-        <v>0.00976</v>
+      <c r="Z215" s="1" t="n">
+        <v>0.00971</v>
       </c>
     </row>
     <row r="216">
@@ -17552,9 +18200,12 @@
         <v>0.064</v>
       </c>
       <c r="X216" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="Y216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="Y216" s="1" t="n">
+      <c r="Z216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -17631,10 +18282,13 @@
         <v>0.004204</v>
       </c>
       <c r="X217" s="1" t="n">
+        <v>0.004169</v>
+      </c>
+      <c r="Y217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="Y217" s="1" t="n">
-        <v>0.004177</v>
+      <c r="Z217" s="1" t="n">
+        <v>0.004169</v>
       </c>
     </row>
     <row r="218">
@@ -17710,9 +18364,12 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="X218" s="1" t="n">
+        <v>0.00984</v>
+      </c>
+      <c r="Y218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="Y218" s="1" t="n">
+      <c r="Z218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -17789,9 +18446,12 @@
         <v>0.02971</v>
       </c>
       <c r="X219" s="1" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="Y219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="Y219" s="1" t="n">
+      <c r="Z219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -17868,9 +18528,12 @@
         <v>2.293</v>
       </c>
       <c r="X220" s="1" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="Y220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="Y220" s="1" t="n">
+      <c r="Z220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -17947,10 +18610,13 @@
         <v>0.022653</v>
       </c>
       <c r="X221" s="1" t="n">
+        <v>0.022502</v>
+      </c>
+      <c r="Y221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="Y221" s="1" t="n">
-        <v>0.022529</v>
+      <c r="Z221" s="1" t="n">
+        <v>0.022502</v>
       </c>
     </row>
     <row r="222">
@@ -18026,9 +18692,12 @@
         <v>0.037</v>
       </c>
       <c r="X222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="Y222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="Y222" s="1" t="n">
+      <c r="Z222" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -18105,9 +18774,12 @@
         <v>0.2931</v>
       </c>
       <c r="X223" s="1" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="Y223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="Y223" s="1" t="n">
+      <c r="Z223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -18184,9 +18856,12 @@
         <v>0.01561</v>
       </c>
       <c r="X224" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Y224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="Y224" s="1" t="n">
+      <c r="Z224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -18263,10 +18938,13 @@
         <v>0.0004045</v>
       </c>
       <c r="X225" s="1" t="n">
+        <v>0.0004028</v>
+      </c>
+      <c r="Y225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="Y225" s="1" t="n">
-        <v>0.0004031</v>
+      <c r="Z225" s="1" t="n">
+        <v>0.0004028</v>
       </c>
     </row>
     <row r="226">
@@ -18342,10 +19020,13 @@
         <v>0.08525000000000001</v>
       </c>
       <c r="X226" s="1" t="n">
+        <v>0.08487</v>
+      </c>
+      <c r="Y226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="Y226" s="1" t="n">
-        <v>0.08519</v>
+      <c r="Z226" s="1" t="n">
+        <v>0.08487</v>
       </c>
     </row>
     <row r="227">
@@ -18421,9 +19102,12 @@
         <v>0.948</v>
       </c>
       <c r="X227" s="1" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="Y227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="Y227" s="1" t="n">
+      <c r="Z227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -18500,9 +19184,12 @@
         <v>0.05576</v>
       </c>
       <c r="X228" s="1" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="Y228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="Y228" s="1" t="n">
+      <c r="Z228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -18579,9 +19266,12 @@
         <v>0.00202</v>
       </c>
       <c r="X229" s="1" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="Y229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="Y229" s="1" t="n">
+      <c r="Z229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -18658,9 +19348,12 @@
         <v>0.022963</v>
       </c>
       <c r="X230" s="1" t="n">
+        <v>0.022879</v>
+      </c>
+      <c r="Y230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="Y230" s="1" t="n">
+      <c r="Z230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -18737,9 +19430,12 @@
         <v>0.0537</v>
       </c>
       <c r="X231" s="1" t="n">
+        <v>0.05346</v>
+      </c>
+      <c r="Y231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="Y231" s="1" t="n">
+      <c r="Z231" s="1" t="n">
         <v>0.05338</v>
       </c>
     </row>
@@ -18816,9 +19512,12 @@
         <v>0.0584</v>
       </c>
       <c r="X232" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="Y232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="Y232" s="1" t="n">
+      <c r="Z232" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -18895,9 +19594,12 @@
         <v>0.001728</v>
       </c>
       <c r="X233" s="1" t="n">
+        <v>0.001713</v>
+      </c>
+      <c r="Y233" s="1" t="n">
         <v>0.001728</v>
       </c>
-      <c r="Y233" s="1" t="n">
+      <c r="Z233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -18974,9 +19676,12 @@
         <v>0.005748</v>
       </c>
       <c r="X234" s="1" t="n">
+        <v>0.005769</v>
+      </c>
+      <c r="Y234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="Y234" s="1" t="n">
+      <c r="Z234" s="1" t="n">
         <v>0.005718</v>
       </c>
     </row>
@@ -19053,9 +19758,12 @@
         <v>0.12298</v>
       </c>
       <c r="X235" s="1" t="n">
+        <v>0.12247</v>
+      </c>
+      <c r="Y235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="Y235" s="1" t="n">
+      <c r="Z235" s="1" t="n">
         <v>0.12245</v>
       </c>
     </row>
@@ -19132,9 +19840,12 @@
         <v>64.88</v>
       </c>
       <c r="X236" s="1" t="n">
+        <v>64.63</v>
+      </c>
+      <c r="Y236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="Y236" s="1" t="n">
+      <c r="Z236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -19211,9 +19922,12 @@
         <v>0.1019</v>
       </c>
       <c r="X237" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="Y237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="Y237" s="1" t="n">
+      <c r="Z237" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -19290,9 +20004,12 @@
         <v>0.003978</v>
       </c>
       <c r="X238" s="1" t="n">
+        <v>0.003959</v>
+      </c>
+      <c r="Y238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="Y238" s="1" t="n">
+      <c r="Z238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -19369,9 +20086,12 @@
         <v>0.015</v>
       </c>
       <c r="X239" s="1" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="Y239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="Y239" s="1" t="n">
+      <c r="Z239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -19448,9 +20168,12 @@
         <v>0.05601</v>
       </c>
       <c r="X240" s="1" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="Y240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="Y240" s="1" t="n">
+      <c r="Z240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -19527,9 +20250,12 @@
         <v>0.0115</v>
       </c>
       <c r="X241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="Y241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="Y241" s="1" t="n">
+      <c r="Z241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -19606,9 +20332,12 @@
         <v>0.3339</v>
       </c>
       <c r="X242" s="1" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="Y242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="Y242" s="1" t="n">
+      <c r="Z242" s="1" t="n">
         <v>0.3321</v>
       </c>
     </row>
@@ -19685,9 +20414,12 @@
         <v>0.01233</v>
       </c>
       <c r="X243" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="Y243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="Y243" s="1" t="n">
+      <c r="Z243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -19764,9 +20496,12 @@
         <v>0.08162999999999999</v>
       </c>
       <c r="X244" s="1" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="Y244" s="1" t="n">
         <v>0.08162999999999999</v>
       </c>
-      <c r="Y244" s="1" t="n">
+      <c r="Z244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -19843,9 +20578,12 @@
         <v>0.007842999999999999</v>
       </c>
       <c r="X245" s="1" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="Y245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="Y245" s="1" t="n">
+      <c r="Z245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -19922,9 +20660,12 @@
         <v>0.03033</v>
       </c>
       <c r="X246" s="1" t="n">
+        <v>0.03027</v>
+      </c>
+      <c r="Y246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="Y246" s="1" t="n">
+      <c r="Z246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -20001,9 +20742,12 @@
         <v>0.181</v>
       </c>
       <c r="X247" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Y247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="Y247" s="1" t="n">
+      <c r="Z247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -20080,9 +20824,12 @@
         <v>0.05893</v>
       </c>
       <c r="X248" s="1" t="n">
+        <v>0.05887</v>
+      </c>
+      <c r="Y248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="Y248" s="1" t="n">
+      <c r="Z248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -20159,10 +20906,13 @@
         <v>0.1662</v>
       </c>
       <c r="X249" s="1" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="Y249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="Y249" s="1" t="n">
-        <v>0.1653</v>
+      <c r="Z249" s="1" t="n">
+        <v>0.1651</v>
       </c>
     </row>
     <row r="250">
@@ -20238,9 +20988,12 @@
         <v>0.01899</v>
       </c>
       <c r="X250" s="1" t="n">
+        <v>0.01899</v>
+      </c>
+      <c r="Y250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="Y250" s="1" t="n">
+      <c r="Z250" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -20317,9 +21070,12 @@
         <v>0.02313</v>
       </c>
       <c r="X251" s="1" t="n">
+        <v>0.02309</v>
+      </c>
+      <c r="Y251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="Y251" s="1" t="n">
+      <c r="Z251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -20396,9 +21152,12 @@
         <v>0.30805</v>
       </c>
       <c r="X252" s="1" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="Y252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="Y252" s="1" t="n">
+      <c r="Z252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -20475,9 +21234,12 @@
         <v>0.00601</v>
       </c>
       <c r="X253" s="1" t="n">
+        <v>0.005977</v>
+      </c>
+      <c r="Y253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="Y253" s="1" t="n">
+      <c r="Z253" s="1" t="n">
         <v>0.005956</v>
       </c>
     </row>
@@ -20554,9 +21316,12 @@
         <v>0.615</v>
       </c>
       <c r="X254" s="1" t="n">
+        <v>0.6128</v>
+      </c>
+      <c r="Y254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="Y254" s="1" t="n">
+      <c r="Z254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -20633,9 +21398,12 @@
         <v>0.10629</v>
       </c>
       <c r="X255" s="1" t="n">
+        <v>0.10572</v>
+      </c>
+      <c r="Y255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="Y255" s="1" t="n">
+      <c r="Z255" s="1" t="n">
         <v>0.10569</v>
       </c>
     </row>
@@ -20712,9 +21480,12 @@
         <v>0.0898</v>
       </c>
       <c r="X256" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="Y256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="Y256" s="1" t="n">
+      <c r="Z256" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -20791,9 +21562,12 @@
         <v>0.01501</v>
       </c>
       <c r="X257" s="1" t="n">
-        <v>0.01501</v>
+        <v>0.01518</v>
       </c>
       <c r="Y257" s="1" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="Z257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -20870,10 +21644,13 @@
         <v>0.04978</v>
       </c>
       <c r="X258" s="1" t="n">
+        <v>0.04948</v>
+      </c>
+      <c r="Y258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="Y258" s="1" t="n">
-        <v>0.04965</v>
+      <c r="Z258" s="1" t="n">
+        <v>0.04948</v>
       </c>
     </row>
     <row r="259">
@@ -20949,9 +21726,12 @@
         <v>0.00793</v>
       </c>
       <c r="X259" s="1" t="n">
+        <v>0.00793</v>
+      </c>
+      <c r="Y259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="Y259" s="1" t="n">
+      <c r="Z259" s="1" t="n">
         <v>0.00793</v>
       </c>
     </row>
@@ -21028,9 +21808,12 @@
         <v>0.1902</v>
       </c>
       <c r="X260" s="1" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="Y260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="Y260" s="1" t="n">
+      <c r="Z260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -21107,9 +21890,12 @@
         <v>0.0979</v>
       </c>
       <c r="X261" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="Y261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="Y261" s="1" t="n">
+      <c r="Z261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -21186,9 +21972,12 @@
         <v>0.212</v>
       </c>
       <c r="X262" s="1" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="Y262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="Y262" s="1" t="n">
+      <c r="Z262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -21265,9 +22054,12 @@
         <v>0.008616</v>
       </c>
       <c r="X263" s="1" t="n">
+        <v>0.008602</v>
+      </c>
+      <c r="Y263" s="1" t="n">
         <v>0.008616</v>
       </c>
-      <c r="Y263" s="1" t="n">
+      <c r="Z263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -21344,10 +22136,13 @@
         <v>2.623</v>
       </c>
       <c r="X264" s="1" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="Y264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="Y264" s="1" t="n">
-        <v>2.617</v>
+      <c r="Z264" s="1" t="n">
+        <v>2.616</v>
       </c>
     </row>
     <row r="265">
@@ -21423,9 +22218,12 @@
         <v>0.01859</v>
       </c>
       <c r="X265" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="Y265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="Y265" s="1" t="n">
+      <c r="Z265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -21502,9 +22300,12 @@
         <v>0.3594</v>
       </c>
       <c r="X266" s="1" t="n">
-        <v>0.3612</v>
+        <v>0.3617</v>
       </c>
       <c r="Y266" s="1" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="Z266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -21581,9 +22382,12 @@
         <v>0.03458</v>
       </c>
       <c r="X267" s="1" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="Y267" s="1" t="n">
         <v>0.03471</v>
       </c>
-      <c r="Y267" s="1" t="n">
+      <c r="Z267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -21660,9 +22464,12 @@
         <v>0.133</v>
       </c>
       <c r="X268" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="Y268" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="Y268" s="1" t="n">
+      <c r="Z268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -21739,10 +22546,13 @@
         <v>0.07932</v>
       </c>
       <c r="X269" s="1" t="n">
+        <v>0.07896</v>
+      </c>
+      <c r="Y269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="Y269" s="1" t="n">
-        <v>0.07925</v>
+      <c r="Z269" s="1" t="n">
+        <v>0.07896</v>
       </c>
     </row>
     <row r="270">
@@ -21818,9 +22628,12 @@
         <v>0.01383</v>
       </c>
       <c r="X270" s="1" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="Y270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="Y270" s="1" t="n">
+      <c r="Z270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -21897,10 +22710,13 @@
         <v>0.007543</v>
       </c>
       <c r="X271" s="1" t="n">
+        <v>0.007498</v>
+      </c>
+      <c r="Y271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="Y271" s="1" t="n">
-        <v>0.007504</v>
+      <c r="Z271" s="1" t="n">
+        <v>0.007498</v>
       </c>
     </row>
     <row r="272">
@@ -21976,9 +22792,12 @@
         <v>0.07406</v>
       </c>
       <c r="X272" s="1" t="n">
+        <v>0.07405</v>
+      </c>
+      <c r="Y272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="Y272" s="1" t="n">
+      <c r="Z272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -22055,9 +22874,12 @@
         <v>3.15e-05</v>
       </c>
       <c r="X273" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="Y273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="Y273" s="1" t="n">
+      <c r="Z273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -22134,10 +22956,13 @@
         <v>0.005435</v>
       </c>
       <c r="X274" s="1" t="n">
+        <v>0.005404</v>
+      </c>
+      <c r="Y274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="Y274" s="1" t="n">
-        <v>0.005409</v>
+      <c r="Z274" s="1" t="n">
+        <v>0.005404</v>
       </c>
     </row>
     <row r="275">
@@ -22213,10 +23038,13 @@
         <v>0.1768</v>
       </c>
       <c r="X275" s="1" t="n">
+        <v>0.1749</v>
+      </c>
+      <c r="Y275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="Y275" s="1" t="n">
-        <v>0.1766</v>
+      <c r="Z275" s="1" t="n">
+        <v>0.1749</v>
       </c>
     </row>
     <row r="276">
@@ -22292,9 +23120,12 @@
         <v>0.006888</v>
       </c>
       <c r="X276" s="1" t="n">
+        <v>0.006863</v>
+      </c>
+      <c r="Y276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="Y276" s="1" t="n">
+      <c r="Z276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -22371,9 +23202,12 @@
         <v>0.1325</v>
       </c>
       <c r="X277" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="Y277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="Y277" s="1" t="n">
+      <c r="Z277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -22450,9 +23284,12 @@
         <v>0.02334</v>
       </c>
       <c r="X278" s="1" t="n">
+        <v>0.02313</v>
+      </c>
+      <c r="Y278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="Y278" s="1" t="n">
+      <c r="Z278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -22529,9 +23366,12 @@
         <v>0.01817</v>
       </c>
       <c r="X279" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="Y279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="Y279" s="1" t="n">
+      <c r="Z279" s="1" t="n">
         <v>0.0181</v>
       </c>
     </row>
@@ -22608,9 +23448,12 @@
         <v>0.03713</v>
       </c>
       <c r="X280" s="1" t="n">
+        <v>0.03696</v>
+      </c>
+      <c r="Y280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="Y280" s="1" t="n">
+      <c r="Z280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -22687,9 +23530,12 @@
         <v>0.03991</v>
       </c>
       <c r="X281" s="1" t="n">
+        <v>0.03975</v>
+      </c>
+      <c r="Y281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="Y281" s="1" t="n">
+      <c r="Z281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -22766,9 +23612,12 @@
         <v>0.3079</v>
       </c>
       <c r="X282" s="1" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="Y282" s="1" t="n">
         <v>0.3079</v>
       </c>
-      <c r="Y282" s="1" t="n">
+      <c r="Z282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -22845,9 +23694,12 @@
         <v>0.01126</v>
       </c>
       <c r="X283" s="1" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="Y283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="Y283" s="1" t="n">
+      <c r="Z283" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -22924,9 +23776,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="X284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="Y284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="Y284" s="1" t="n">
+      <c r="Z284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -23003,9 +23858,12 @@
         <v>0.1146</v>
       </c>
       <c r="X285" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="Y285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="Y285" s="1" t="n">
+      <c r="Z285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -23082,9 +23940,12 @@
         <v>0.003485</v>
       </c>
       <c r="X286" s="1" t="n">
+        <v>0.003443</v>
+      </c>
+      <c r="Y286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="Y286" s="1" t="n">
+      <c r="Z286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -23161,9 +24022,12 @@
         <v>0.08524</v>
       </c>
       <c r="X287" s="1" t="n">
+        <v>0.08484</v>
+      </c>
+      <c r="Y287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="Y287" s="1" t="n">
+      <c r="Z287" s="1" t="n">
         <v>0.08465</v>
       </c>
     </row>
@@ -23240,9 +24104,12 @@
         <v>0.09974</v>
       </c>
       <c r="X288" s="1" t="n">
+        <v>0.09933</v>
+      </c>
+      <c r="Y288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="Y288" s="1" t="n">
+      <c r="Z288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -23319,9 +24186,12 @@
         <v>0.435</v>
       </c>
       <c r="X289" s="1" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="Y289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="Y289" s="1" t="n">
+      <c r="Z289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -23398,9 +24268,12 @@
         <v>0.0399</v>
       </c>
       <c r="X290" s="1" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="Y290" s="1" t="n">
         <v>0.0399</v>
       </c>
-      <c r="Y290" s="1" t="n">
+      <c r="Z290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -23477,9 +24350,12 @@
         <v>0.2357</v>
       </c>
       <c r="X291" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="Y291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="Y291" s="1" t="n">
+      <c r="Z291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -23556,9 +24432,12 @@
         <v>0.28318</v>
       </c>
       <c r="X292" s="1" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="Y292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="Y292" s="1" t="n">
+      <c r="Z292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -23635,9 +24514,12 @@
         <v>0.1522</v>
       </c>
       <c r="X293" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="Y293" s="1" t="n">
         <v>0.1539</v>
       </c>
-      <c r="Y293" s="1" t="n">
+      <c r="Z293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -23714,10 +24596,13 @@
         <v>4.177</v>
       </c>
       <c r="X294" s="1" t="n">
+        <v>4.161</v>
+      </c>
+      <c r="Y294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="Y294" s="1" t="n">
-        <v>4.165</v>
+      <c r="Z294" s="1" t="n">
+        <v>4.161</v>
       </c>
     </row>
     <row r="295">
@@ -23793,9 +24678,12 @@
         <v>0.03382</v>
       </c>
       <c r="X295" s="1" t="n">
+        <v>0.03375</v>
+      </c>
+      <c r="Y295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="Y295" s="1" t="n">
+      <c r="Z295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -23872,9 +24760,12 @@
         <v>0.000972</v>
       </c>
       <c r="X296" s="1" t="n">
+        <v>0.000971</v>
+      </c>
+      <c r="Y296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="Y296" s="1" t="n">
+      <c r="Z296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -23951,9 +24842,12 @@
         <v>0.08176</v>
       </c>
       <c r="X297" s="1" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="Y297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="Y297" s="1" t="n">
+      <c r="Z297" s="1" t="n">
         <v>0.08135000000000001</v>
       </c>
     </row>
@@ -24030,9 +24924,12 @@
         <v>0.05863</v>
       </c>
       <c r="X298" s="1" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="Y298" s="1" t="n">
         <v>0.05876</v>
       </c>
-      <c r="Y298" s="1" t="n">
+      <c r="Z298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -24109,9 +25006,12 @@
         <v>0.09202</v>
       </c>
       <c r="X299" s="1" t="n">
+        <v>0.09157999999999999</v>
+      </c>
+      <c r="Y299" s="1" t="n">
         <v>0.09202</v>
       </c>
-      <c r="Y299" s="1" t="n">
+      <c r="Z299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -24188,9 +25088,12 @@
         <v>0.02733</v>
       </c>
       <c r="X300" s="1" t="n">
+        <v>0.02724</v>
+      </c>
+      <c r="Y300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="Y300" s="1" t="n">
+      <c r="Z300" s="1" t="n">
         <v>0.02723</v>
       </c>
     </row>
@@ -24267,9 +25170,12 @@
         <v>0.06587</v>
       </c>
       <c r="X301" s="1" t="n">
+        <v>0.06561</v>
+      </c>
+      <c r="Y301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="Y301" s="1" t="n">
+      <c r="Z301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -24346,9 +25252,12 @@
         <v>0.05338</v>
       </c>
       <c r="X302" s="1" t="n">
+        <v>0.053558</v>
+      </c>
+      <c r="Y302" s="1" t="n">
         <v>0.053599</v>
       </c>
-      <c r="Y302" s="1" t="n">
+      <c r="Z302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -24425,9 +25334,12 @@
         <v>5166.2</v>
       </c>
       <c r="X303" s="1" t="n">
+        <v>5167.3</v>
+      </c>
+      <c r="Y303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="Y303" s="1" t="n">
+      <c r="Z303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -24504,9 +25416,12 @@
         <v>14.91</v>
       </c>
       <c r="X304" s="1" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="Y304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="Y304" s="1" t="n">
+      <c r="Z304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -24583,9 +25498,12 @@
         <v>0.003736</v>
       </c>
       <c r="X305" s="1" t="n">
+        <v>0.003738</v>
+      </c>
+      <c r="Y305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="Y305" s="1" t="n">
+      <c r="Z305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -24662,9 +25580,12 @@
         <v>0.4579</v>
       </c>
       <c r="X306" s="1" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="Y306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="Y306" s="1" t="n">
+      <c r="Z306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -24741,10 +25662,13 @@
         <v>0.04671</v>
       </c>
       <c r="X307" s="1" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="Y307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="Y307" s="1" t="n">
-        <v>0.04651</v>
+      <c r="Z307" s="1" t="n">
+        <v>0.04649</v>
       </c>
     </row>
     <row r="308">
@@ -24820,9 +25744,12 @@
         <v>1.4916</v>
       </c>
       <c r="X308" s="1" t="n">
+        <v>1.4919</v>
+      </c>
+      <c r="Y308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="Y308" s="1" t="n">
+      <c r="Z308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -24899,9 +25826,12 @@
         <v>0.0007956</v>
       </c>
       <c r="X309" s="1" t="n">
+        <v>0.0007959</v>
+      </c>
+      <c r="Y309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="Y309" s="1" t="n">
+      <c r="Z309" s="1" t="n">
         <v>0.0007861</v>
       </c>
     </row>
@@ -24978,10 +25908,13 @@
         <v>4.542</v>
       </c>
       <c r="X310" s="1" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="Y310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="Y310" s="1" t="n">
-        <v>4.542</v>
+      <c r="Z310" s="1" t="n">
+        <v>4.526</v>
       </c>
     </row>
     <row r="311">
@@ -25057,9 +25990,12 @@
         <v>4.809</v>
       </c>
       <c r="X311" s="1" t="n">
+        <v>4.775</v>
+      </c>
+      <c r="Y311" s="1" t="n">
         <v>4.809</v>
       </c>
-      <c r="Y311" s="1" t="n">
+      <c r="Z311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -25136,9 +26072,12 @@
         <v>0.08099000000000001</v>
       </c>
       <c r="X312" s="1" t="n">
+        <v>0.08062999999999999</v>
+      </c>
+      <c r="Y312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="Y312" s="1" t="n">
+      <c r="Z312" s="1" t="n">
         <v>0.08033999999999999</v>
       </c>
     </row>
@@ -25215,9 +26154,12 @@
         <v>2.036</v>
       </c>
       <c r="X313" s="1" t="n">
+        <v>2.027</v>
+      </c>
+      <c r="Y313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="Y313" s="1" t="n">
+      <c r="Z313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -25294,9 +26236,12 @@
         <v>0.07128</v>
       </c>
       <c r="X314" s="1" t="n">
+        <v>0.07074999999999999</v>
+      </c>
+      <c r="Y314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="Y314" s="1" t="n">
+      <c r="Z314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -25373,9 +26318,12 @@
         <v>0.953</v>
       </c>
       <c r="X315" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="Y315" s="1" t="n">
+      <c r="Z315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -25452,9 +26400,12 @@
         <v>0.1303</v>
       </c>
       <c r="X316" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Y316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="Y316" s="1" t="n">
+      <c r="Z316" s="1" t="n">
         <v>0.1295</v>
       </c>
     </row>
@@ -25531,9 +26482,12 @@
         <v>0.1872</v>
       </c>
       <c r="X317" s="1" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="Y317" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="Y317" s="1" t="n">
+      <c r="Z317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -25610,10 +26564,13 @@
         <v>0.01606</v>
       </c>
       <c r="X318" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="Y318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="Y318" s="1" t="n">
-        <v>0.01606</v>
+      <c r="Z318" s="1" t="n">
+        <v>0.01604</v>
       </c>
     </row>
     <row r="319">
@@ -25689,9 +26646,12 @@
         <v>0.08377</v>
       </c>
       <c r="X319" s="1" t="n">
+        <v>0.08347</v>
+      </c>
+      <c r="Y319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="Y319" s="1" t="n">
+      <c r="Z319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -25768,9 +26728,12 @@
         <v>0.007525</v>
       </c>
       <c r="X320" s="1" t="n">
+        <v>0.007493</v>
+      </c>
+      <c r="Y320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="Y320" s="1" t="n">
+      <c r="Z320" s="1" t="n">
         <v>0.007463</v>
       </c>
     </row>
@@ -25847,9 +26810,12 @@
         <v>0.05453</v>
       </c>
       <c r="X321" s="1" t="n">
+        <v>0.05437</v>
+      </c>
+      <c r="Y321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="Y321" s="1" t="n">
+      <c r="Z321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -25926,9 +26892,12 @@
         <v>0.5508</v>
       </c>
       <c r="X322" s="1" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="Y322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="Y322" s="1" t="n">
+      <c r="Z322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -26005,10 +26974,13 @@
         <v>0.07492</v>
       </c>
       <c r="X323" s="1" t="n">
+        <v>0.07387000000000001</v>
+      </c>
+      <c r="Y323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="Y323" s="1" t="n">
-        <v>0.07492</v>
+      <c r="Z323" s="1" t="n">
+        <v>0.07387000000000001</v>
       </c>
     </row>
     <row r="324">
@@ -26084,9 +27056,12 @@
         <v>0.013031</v>
       </c>
       <c r="X324" s="1" t="n">
-        <v>0.013039</v>
+        <v>0.013045</v>
       </c>
       <c r="Y324" s="1" t="n">
+        <v>0.013045</v>
+      </c>
+      <c r="Z324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -26163,10 +27138,13 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="X325" s="1" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="Y325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="Y325" s="1" t="n">
-        <v>0.0985</v>
+      <c r="Z325" s="1" t="n">
+        <v>0.0984</v>
       </c>
     </row>
     <row r="326">
@@ -26242,9 +27220,12 @@
         <v>0.01742</v>
       </c>
       <c r="X326" s="1" t="n">
+        <v>0.01738</v>
+      </c>
+      <c r="Y326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="Y326" s="1" t="n">
+      <c r="Z326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -26321,9 +27302,12 @@
         <v>0.06435</v>
       </c>
       <c r="X327" s="1" t="n">
+        <v>0.06426999999999999</v>
+      </c>
+      <c r="Y327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="Y327" s="1" t="n">
+      <c r="Z327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -26400,9 +27384,12 @@
         <v>0.2641</v>
       </c>
       <c r="X328" s="1" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="Y328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="Y328" s="1" t="n">
+      <c r="Z328" s="1" t="n">
         <v>0.2612</v>
       </c>
     </row>
@@ -26479,9 +27466,12 @@
         <v>0.17362</v>
       </c>
       <c r="X329" s="1" t="n">
+        <v>0.17381</v>
+      </c>
+      <c r="Y329" s="1" t="n">
         <v>0.17476</v>
       </c>
-      <c r="Y329" s="1" t="n">
+      <c r="Z329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -26558,10 +27548,13 @@
         <v>2.033</v>
       </c>
       <c r="X330" s="1" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Y330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="Y330" s="1" t="n">
-        <v>2.028</v>
+      <c r="Z330" s="1" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="331">
@@ -26637,9 +27630,12 @@
         <v>0.0288</v>
       </c>
       <c r="X331" s="1" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="Y331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="Y331" s="1" t="n">
+      <c r="Z331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -26716,9 +27712,12 @@
         <v>0.006047</v>
       </c>
       <c r="X332" s="1" t="n">
+        <v>0.006009</v>
+      </c>
+      <c r="Y332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="Y332" s="1" t="n">
+      <c r="Z332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -26795,10 +27794,13 @@
         <v>0.003475</v>
       </c>
       <c r="X333" s="1" t="n">
+        <v>0.003452</v>
+      </c>
+      <c r="Y333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="Y333" s="1" t="n">
-        <v>0.003456</v>
+      <c r="Z333" s="1" t="n">
+        <v>0.003452</v>
       </c>
     </row>
     <row r="334">
@@ -26874,10 +27876,13 @@
         <v>0.01401</v>
       </c>
       <c r="X334" s="1" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="Y334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="Y334" s="1" t="n">
-        <v>0.01394</v>
+      <c r="Z334" s="1" t="n">
+        <v>0.0139</v>
       </c>
     </row>
     <row r="335">
@@ -26953,9 +27958,12 @@
         <v>1.138</v>
       </c>
       <c r="X335" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y335" s="1" t="n">
         <v>1.158</v>
       </c>
-      <c r="Y335" s="1" t="n">
+      <c r="Z335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -27032,9 +28040,12 @@
         <v>0.011352</v>
       </c>
       <c r="X336" s="1" t="n">
+        <v>0.011291</v>
+      </c>
+      <c r="Y336" s="1" t="n">
         <v>0.011377</v>
       </c>
-      <c r="Y336" s="1" t="n">
+      <c r="Z336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -27111,9 +28122,12 @@
         <v>2.97</v>
       </c>
       <c r="X337" s="1" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="Y337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="Y337" s="1" t="n">
+      <c r="Z337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -27190,9 +28204,12 @@
         <v>0.01854</v>
       </c>
       <c r="X338" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="Y338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="Y338" s="1" t="n">
+      <c r="Z338" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -27269,10 +28286,13 @@
         <v>0.07724</v>
       </c>
       <c r="X339" s="1" t="n">
+        <v>0.07685</v>
+      </c>
+      <c r="Y339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="Y339" s="1" t="n">
-        <v>0.07689</v>
+      <c r="Z339" s="1" t="n">
+        <v>0.07685</v>
       </c>
     </row>
     <row r="340">
@@ -27348,9 +28368,12 @@
         <v>0.076</v>
       </c>
       <c r="X340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="Y340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="Y340" s="1" t="n">
+      <c r="Z340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -27427,9 +28450,12 @@
         <v>0.03618</v>
       </c>
       <c r="X341" s="1" t="n">
+        <v>0.03596</v>
+      </c>
+      <c r="Y341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="Y341" s="1" t="n">
+      <c r="Z341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -27506,9 +28532,12 @@
         <v>2590</v>
       </c>
       <c r="X342" s="1" t="n">
+        <v>2585</v>
+      </c>
+      <c r="Y342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="Y342" s="1" t="n">
+      <c r="Z342" s="1" t="n">
         <v>2579</v>
       </c>
     </row>
@@ -27585,9 +28614,12 @@
         <v>0.0002028</v>
       </c>
       <c r="X343" s="1" t="n">
+        <v>0.0001959</v>
+      </c>
+      <c r="Y343" s="1" t="n">
         <v>0.0002049</v>
       </c>
-      <c r="Y343" s="1" t="n">
+      <c r="Z343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -27664,9 +28696,12 @@
         <v>0.07973</v>
       </c>
       <c r="X344" s="1" t="n">
+        <v>0.07939</v>
+      </c>
+      <c r="Y344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="Y344" s="1" t="n">
+      <c r="Z344" s="1" t="n">
         <v>0.07915</v>
       </c>
     </row>
@@ -27743,10 +28778,13 @@
         <v>0.01624</v>
       </c>
       <c r="X345" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="Y345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="Y345" s="1" t="n">
-        <v>0.01622</v>
+      <c r="Z345" s="1" t="n">
+        <v>0.01612</v>
       </c>
     </row>
     <row r="346">
@@ -27822,9 +28860,12 @@
         <v>2.764</v>
       </c>
       <c r="X346" s="1" t="n">
+        <v>2.749</v>
+      </c>
+      <c r="Y346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="Y346" s="1" t="n">
+      <c r="Z346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -27901,9 +28942,12 @@
         <v>0.01643</v>
       </c>
       <c r="X347" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="Y347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="Y347" s="1" t="n">
+      <c r="Z347" s="1" t="n">
         <v>0.01625</v>
       </c>
     </row>
@@ -27980,9 +29024,12 @@
         <v>0.03826</v>
       </c>
       <c r="X348" s="1" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="Y348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="Y348" s="1" t="n">
+      <c r="Z348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -28059,9 +29106,12 @@
         <v>0.3072</v>
       </c>
       <c r="X349" s="1" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="Y349" s="1" t="n">
         <v>0.3076</v>
       </c>
-      <c r="Y349" s="1" t="n">
+      <c r="Z349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -28138,9 +29188,12 @@
         <v>0.005107</v>
       </c>
       <c r="X350" s="1" t="n">
+        <v>0.005074</v>
+      </c>
+      <c r="Y350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="Y350" s="1" t="n">
+      <c r="Z350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -28217,9 +29270,12 @@
         <v>0.005136</v>
       </c>
       <c r="X351" s="1" t="n">
+        <v>0.005092</v>
+      </c>
+      <c r="Y351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="Y351" s="1" t="n">
+      <c r="Z351" s="1" t="n">
         <v>0.005054</v>
       </c>
     </row>
@@ -28296,9 +29352,12 @@
         <v>0.004389</v>
       </c>
       <c r="X352" s="1" t="n">
+        <v>0.004383</v>
+      </c>
+      <c r="Y352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="Y352" s="1" t="n">
+      <c r="Z352" s="1" t="n">
         <v>0.004379</v>
       </c>
     </row>
@@ -28375,9 +29434,12 @@
         <v>0.08051999999999999</v>
       </c>
       <c r="X353" s="1" t="n">
+        <v>0.08051</v>
+      </c>
+      <c r="Y353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="Y353" s="1" t="n">
+      <c r="Z353" s="1" t="n">
         <v>0.08008</v>
       </c>
     </row>
@@ -28454,9 +29516,12 @@
         <v>1.264</v>
       </c>
       <c r="X354" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="Y354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="Y354" s="1" t="n">
+      <c r="Z354" s="1" t="n">
         <v>1.258</v>
       </c>
     </row>
@@ -28533,9 +29598,12 @@
         <v>7.726</v>
       </c>
       <c r="X355" s="1" t="n">
+        <v>7.701</v>
+      </c>
+      <c r="Y355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="Y355" s="1" t="n">
+      <c r="Z355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -28612,9 +29680,12 @@
         <v>0.00778</v>
       </c>
       <c r="X356" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="Y356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="Y356" s="1" t="n">
+      <c r="Z356" s="1" t="n">
         <v>0.00774</v>
       </c>
     </row>
@@ -28691,9 +29762,12 @@
         <v>0.005671</v>
       </c>
       <c r="X357" s="1" t="n">
+        <v>0.005651</v>
+      </c>
+      <c r="Y357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="Y357" s="1" t="n">
+      <c r="Z357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -28770,9 +29844,12 @@
         <v>0.01554</v>
       </c>
       <c r="X358" s="1" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="Y358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="Y358" s="1" t="n">
+      <c r="Z358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -28849,9 +29926,12 @@
         <v>3.614</v>
       </c>
       <c r="X359" s="1" t="n">
+        <v>3.624</v>
+      </c>
+      <c r="Y359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="Y359" s="1" t="n">
+      <c r="Z359" s="1" t="n">
         <v>3.597</v>
       </c>
     </row>
@@ -28928,10 +30008,13 @@
         <v>0.1495</v>
       </c>
       <c r="X360" s="1" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="Y360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="Y360" s="1" t="n">
-        <v>0.1494</v>
+      <c r="Z360" s="1" t="n">
+        <v>0.1492</v>
       </c>
     </row>
     <row r="361">
@@ -29007,9 +30090,12 @@
         <v>0.07038</v>
       </c>
       <c r="X361" s="1" t="n">
+        <v>0.07045</v>
+      </c>
+      <c r="Y361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="Y361" s="1" t="n">
+      <c r="Z361" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -29086,9 +30172,12 @@
         <v>0.01774</v>
       </c>
       <c r="X362" s="1" t="n">
+        <v>0.01763</v>
+      </c>
+      <c r="Y362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="Y362" s="1" t="n">
+      <c r="Z362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -29165,10 +30254,13 @@
         <v>0.02231</v>
       </c>
       <c r="X363" s="1" t="n">
+        <v>0.02221</v>
+      </c>
+      <c r="Y363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="Y363" s="1" t="n">
-        <v>0.02228</v>
+      <c r="Z363" s="1" t="n">
+        <v>0.02221</v>
       </c>
     </row>
     <row r="364">
@@ -29244,9 +30336,12 @@
         <v>0.01251</v>
       </c>
       <c r="X364" s="1" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="Y364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="Y364" s="1" t="n">
+      <c r="Z364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -29323,10 +30418,13 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="X365" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="Y365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="Y365" s="1" t="n">
-        <v>0.09080000000000001</v>
+      <c r="Z365" s="1" t="n">
+        <v>0.0907</v>
       </c>
     </row>
     <row r="366">
@@ -29402,9 +30500,12 @@
         <v>0.04234</v>
       </c>
       <c r="X366" s="1" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="Y366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="Y366" s="1" t="n">
+      <c r="Z366" s="1" t="n">
         <v>0.04214</v>
       </c>
     </row>
@@ -29481,9 +30582,12 @@
         <v>0.03154</v>
       </c>
       <c r="X367" s="1" t="n">
+        <v>0.03154</v>
+      </c>
+      <c r="Y367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="Y367" s="1" t="n">
+      <c r="Z367" s="1" t="n">
         <v>0.03124</v>
       </c>
     </row>
@@ -29560,10 +30664,13 @@
         <v>0.0231</v>
       </c>
       <c r="X368" s="1" t="n">
+        <v>0.02302</v>
+      </c>
+      <c r="Y368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="Y368" s="1" t="n">
-        <v>0.0231</v>
+      <c r="Z368" s="1" t="n">
+        <v>0.02302</v>
       </c>
     </row>
     <row r="369">
@@ -29639,9 +30746,12 @@
         <v>0.03094</v>
       </c>
       <c r="X369" s="1" t="n">
+        <v>0.03092</v>
+      </c>
+      <c r="Y369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="Y369" s="1" t="n">
+      <c r="Z369" s="1" t="n">
         <v>0.0308</v>
       </c>
     </row>
@@ -29718,9 +30828,12 @@
         <v>0.07983999999999999</v>
       </c>
       <c r="X370" s="1" t="n">
+        <v>0.07971</v>
+      </c>
+      <c r="Y370" s="1" t="n">
         <v>0.08017000000000001</v>
       </c>
-      <c r="Y370" s="1" t="n">
+      <c r="Z370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -29797,9 +30910,12 @@
         <v>0.1072</v>
       </c>
       <c r="X371" s="1" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="Y371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="Y371" s="1" t="n">
+      <c r="Z371" s="1" t="n">
         <v>0.1069</v>
       </c>
     </row>
@@ -29876,9 +30992,12 @@
         <v>0.007037</v>
       </c>
       <c r="X372" s="1" t="n">
+        <v>0.006972</v>
+      </c>
+      <c r="Y372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="Y372" s="1" t="n">
+      <c r="Z372" s="1" t="n">
         <v>0.00694</v>
       </c>
     </row>
@@ -29955,9 +31074,12 @@
         <v>0.0968</v>
       </c>
       <c r="X373" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="Y373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="Y373" s="1" t="n">
+      <c r="Z373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -30034,9 +31156,12 @@
         <v>0.0575</v>
       </c>
       <c r="X374" s="1" t="n">
+        <v>0.05733</v>
+      </c>
+      <c r="Y374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="Y374" s="1" t="n">
+      <c r="Z374" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -30113,9 +31238,12 @@
         <v>0.3192</v>
       </c>
       <c r="X375" s="1" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="Y375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="Y375" s="1" t="n">
+      <c r="Z375" s="1" t="n">
         <v>0.3169</v>
       </c>
     </row>
@@ -30192,9 +31320,12 @@
         <v>0.01951</v>
       </c>
       <c r="X376" s="1" t="n">
+        <v>0.01948</v>
+      </c>
+      <c r="Y376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="Y376" s="1" t="n">
+      <c r="Z376" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -30271,9 +31402,12 @@
         <v>0.06856</v>
       </c>
       <c r="X377" s="1" t="n">
+        <v>0.06863</v>
+      </c>
+      <c r="Y377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="Y377" s="1" t="n">
+      <c r="Z377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -30350,9 +31484,12 @@
         <v>0.15726</v>
       </c>
       <c r="X378" s="1" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="Y378" s="1" t="n">
         <v>0.15872</v>
       </c>
-      <c r="Y378" s="1" t="n">
+      <c r="Z378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -30429,9 +31566,12 @@
         <v>0.0006016</v>
       </c>
       <c r="X379" s="1" t="n">
+        <v>0.0005985</v>
+      </c>
+      <c r="Y379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="Y379" s="1" t="n">
+      <c r="Z379" s="1" t="n">
         <v>0.0005922</v>
       </c>
     </row>
@@ -30508,9 +31648,12 @@
         <v>0.01017</v>
       </c>
       <c r="X380" s="1" t="n">
+        <v>0.01014</v>
+      </c>
+      <c r="Y380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="Y380" s="1" t="n">
+      <c r="Z380" s="1" t="n">
         <v>0.01012</v>
       </c>
     </row>
@@ -30587,9 +31730,12 @@
         <v>0.02558</v>
       </c>
       <c r="X381" s="1" t="n">
+        <v>0.02543</v>
+      </c>
+      <c r="Y381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="Y381" s="1" t="n">
+      <c r="Z381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -30666,10 +31812,13 @@
         <v>0.18706</v>
       </c>
       <c r="X382" s="1" t="n">
+        <v>0.18672</v>
+      </c>
+      <c r="Y382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="Y382" s="1" t="n">
-        <v>0.18706</v>
+      <c r="Z382" s="1" t="n">
+        <v>0.18672</v>
       </c>
     </row>
     <row r="383">
@@ -30745,10 +31894,13 @@
         <v>0.0926</v>
       </c>
       <c r="X383" s="1" t="n">
+        <v>0.09205000000000001</v>
+      </c>
+      <c r="Y383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="Y383" s="1" t="n">
-        <v>0.0921</v>
+      <c r="Z383" s="1" t="n">
+        <v>0.09205000000000001</v>
       </c>
     </row>
     <row r="384">
@@ -30824,9 +31976,12 @@
         <v>0.03171</v>
       </c>
       <c r="X384" s="1" t="n">
+        <v>0.03181</v>
+      </c>
+      <c r="Y384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="Y384" s="1" t="n">
+      <c r="Z384" s="1" t="n">
         <v>0.0316</v>
       </c>
     </row>
@@ -30903,10 +32058,13 @@
         <v>0.01086</v>
       </c>
       <c r="X385" s="1" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="Y385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="Y385" s="1" t="n">
-        <v>0.01086</v>
+      <c r="Z385" s="1" t="n">
+        <v>0.01082</v>
       </c>
     </row>
     <row r="386">
@@ -30982,9 +32140,12 @@
         <v>0.05087</v>
       </c>
       <c r="X386" s="1" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="Y386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="Y386" s="1" t="n">
+      <c r="Z386" s="1" t="n">
         <v>0.05043</v>
       </c>
     </row>
@@ -31061,10 +32222,13 @@
         <v>0.02385</v>
       </c>
       <c r="X387" s="1" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="Y387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="Y387" s="1" t="n">
-        <v>0.02384</v>
+      <c r="Z387" s="1" t="n">
+        <v>0.0236</v>
       </c>
     </row>
     <row r="388">
@@ -31140,9 +32304,12 @@
         <v>0.007255</v>
       </c>
       <c r="X388" s="1" t="n">
+        <v>0.00727</v>
+      </c>
+      <c r="Y388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="Y388" s="1" t="n">
+      <c r="Z388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -31219,9 +32386,12 @@
         <v>0.01014</v>
       </c>
       <c r="X389" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="Y389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="Y389" s="1" t="n">
+      <c r="Z389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -31298,10 +32468,13 @@
         <v>0.08236</v>
       </c>
       <c r="X390" s="1" t="n">
+        <v>0.08177</v>
+      </c>
+      <c r="Y390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="Y390" s="1" t="n">
-        <v>0.08214</v>
+      <c r="Z390" s="1" t="n">
+        <v>0.08177</v>
       </c>
     </row>
     <row r="391">
@@ -31377,10 +32550,13 @@
         <v>0.5044</v>
       </c>
       <c r="X391" s="1" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="Y391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="Y391" s="1" t="n">
-        <v>0.5014</v>
+      <c r="Z391" s="1" t="n">
+        <v>0.5009</v>
       </c>
     </row>
     <row r="392">
@@ -31456,9 +32632,12 @@
         <v>0.1168</v>
       </c>
       <c r="X392" s="1" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="Y392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="Y392" s="1" t="n">
+      <c r="Z392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -31535,9 +32714,12 @@
         <v>0.00247</v>
       </c>
       <c r="X393" s="1" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="Y393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="Y393" s="1" t="n">
+      <c r="Z393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -31614,9 +32796,12 @@
         <v>0.02184</v>
       </c>
       <c r="X394" s="1" t="n">
-        <v>0.02184</v>
+        <v>0.02188</v>
       </c>
       <c r="Y394" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="Z394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -31693,9 +32878,12 @@
         <v>0.0161</v>
       </c>
       <c r="X395" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="Y395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="Y395" s="1" t="n">
+      <c r="Z395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -31772,10 +32960,13 @@
         <v>0.1351</v>
       </c>
       <c r="X396" s="1" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="Y396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="Y396" s="1" t="n">
-        <v>0.1349</v>
+      <c r="Z396" s="1" t="n">
+        <v>0.1348</v>
       </c>
     </row>
     <row r="397">
@@ -31851,9 +33042,12 @@
         <v>0.01455</v>
       </c>
       <c r="X397" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="Y397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="Y397" s="1" t="n">
+      <c r="Z397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -31930,9 +33124,12 @@
         <v>6.785</v>
       </c>
       <c r="X398" s="1" t="n">
+        <v>6.762</v>
+      </c>
+      <c r="Y398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="Y398" s="1" t="n">
+      <c r="Z398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -32009,9 +33206,12 @@
         <v>0.009490999999999999</v>
       </c>
       <c r="X399" s="1" t="n">
+        <v>0.009509</v>
+      </c>
+      <c r="Y399" s="1" t="n">
         <v>0.009526</v>
       </c>
-      <c r="Y399" s="1" t="n">
+      <c r="Z399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -32088,9 +33288,12 @@
         <v>0.001252</v>
       </c>
       <c r="X400" s="1" t="n">
+        <v>0.001245</v>
+      </c>
+      <c r="Y400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="Y400" s="1" t="n">
+      <c r="Z400" s="1" t="n">
         <v>0.001241</v>
       </c>
     </row>
@@ -32167,9 +33370,12 @@
         <v>0.01854</v>
       </c>
       <c r="X401" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="Y401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="Y401" s="1" t="n">
+      <c r="Z401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -32246,9 +33452,12 @@
         <v>0.0851</v>
       </c>
       <c r="X402" s="1" t="n">
+        <v>0.08477999999999999</v>
+      </c>
+      <c r="Y402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="Y402" s="1" t="n">
+      <c r="Z402" s="1" t="n">
         <v>0.08447</v>
       </c>
     </row>
@@ -32325,9 +33534,12 @@
         <v>0.00549</v>
       </c>
       <c r="X403" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="Y403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="Y403" s="1" t="n">
+      <c r="Z403" s="1" t="n">
         <v>0.00548</v>
       </c>
     </row>
@@ -32404,9 +33616,12 @@
         <v>0.04305</v>
       </c>
       <c r="X404" s="1" t="n">
+        <v>0.04313</v>
+      </c>
+      <c r="Y404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="Y404" s="1" t="n">
+      <c r="Z404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -32483,9 +33698,12 @@
         <v>0.0586</v>
       </c>
       <c r="X405" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="Y405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="Y405" s="1" t="n">
+      <c r="Z405" s="1" t="n">
         <v>0.05827</v>
       </c>
     </row>
@@ -32562,9 +33780,12 @@
         <v>0.01679</v>
       </c>
       <c r="X406" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="Y406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="Y406" s="1" t="n">
+      <c r="Z406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -32641,9 +33862,12 @@
         <v>0.0425</v>
       </c>
       <c r="X407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="Y407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="Y407" s="1" t="n">
+      <c r="Z407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -32720,9 +33944,12 @@
         <v>0.01935</v>
       </c>
       <c r="X408" s="1" t="n">
+        <v>0.01927</v>
+      </c>
+      <c r="Y408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="Y408" s="1" t="n">
+      <c r="Z408" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -32799,9 +34026,12 @@
         <v>0.4465</v>
       </c>
       <c r="X409" s="1" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="Y409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="Y409" s="1" t="n">
+      <c r="Z409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -32878,10 +34108,13 @@
         <v>0.04376</v>
       </c>
       <c r="X410" s="1" t="n">
+        <v>0.04355</v>
+      </c>
+      <c r="Y410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="Y410" s="1" t="n">
-        <v>0.04374</v>
+      <c r="Z410" s="1" t="n">
+        <v>0.04355</v>
       </c>
     </row>
     <row r="411">
@@ -32957,9 +34190,12 @@
         <v>27.32</v>
       </c>
       <c r="X411" s="1" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="Y411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="Y411" s="1" t="n">
+      <c r="Z411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -33036,9 +34272,12 @@
         <v>0.03522</v>
       </c>
       <c r="X412" s="1" t="n">
+        <v>0.03497</v>
+      </c>
+      <c r="Y412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="Y412" s="1" t="n">
+      <c r="Z412" s="1" t="n">
         <v>0.03493</v>
       </c>
     </row>
@@ -33115,9 +34354,12 @@
         <v>0.003408</v>
       </c>
       <c r="X413" s="1" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="Y413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="Y413" s="1" t="n">
+      <c r="Z413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -33194,10 +34436,13 @@
         <v>0.1525</v>
       </c>
       <c r="X414" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="Y414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="Y414" s="1" t="n">
-        <v>0.1521</v>
+      <c r="Z414" s="1" t="n">
+        <v>0.152</v>
       </c>
     </row>
     <row r="415">
@@ -33273,9 +34518,12 @@
         <v>0.05265</v>
       </c>
       <c r="X415" s="1" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="Y415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="Y415" s="1" t="n">
+      <c r="Z415" s="1" t="n">
         <v>0.05228</v>
       </c>
     </row>
@@ -33352,9 +34600,12 @@
         <v>0.00663</v>
       </c>
       <c r="X416" s="1" t="n">
+        <v>0.00655</v>
+      </c>
+      <c r="Y416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="Y416" s="1" t="n">
+      <c r="Z416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -33431,9 +34682,12 @@
         <v>0.06046</v>
       </c>
       <c r="X417" s="1" t="n">
+        <v>0.06038</v>
+      </c>
+      <c r="Y417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="Y417" s="1" t="n">
+      <c r="Z417" s="1" t="n">
         <v>0.06025</v>
       </c>
     </row>
@@ -33510,9 +34764,12 @@
         <v>0.008092</v>
       </c>
       <c r="X418" s="1" t="n">
+        <v>0.008057</v>
+      </c>
+      <c r="Y418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="Y418" s="1" t="n">
+      <c r="Z418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -33589,10 +34846,13 @@
         <v>0.07454</v>
       </c>
       <c r="X419" s="1" t="n">
+        <v>0.07399</v>
+      </c>
+      <c r="Y419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="Y419" s="1" t="n">
-        <v>0.07414999999999999</v>
+      <c r="Z419" s="1" t="n">
+        <v>0.07399</v>
       </c>
     </row>
     <row r="420">
@@ -33668,9 +34928,12 @@
         <v>0.02135</v>
       </c>
       <c r="X420" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="Y420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="Y420" s="1" t="n">
+      <c r="Z420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -33747,9 +35010,12 @@
         <v>0.06934</v>
       </c>
       <c r="X421" s="1" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Y421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="Y421" s="1" t="n">
+      <c r="Z421" s="1" t="n">
         <v>0.0689</v>
       </c>
     </row>
@@ -33826,9 +35092,12 @@
         <v>0.01485</v>
       </c>
       <c r="X422" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="Y422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="Y422" s="1" t="n">
+      <c r="Z422" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -33905,9 +35174,12 @@
         <v>0.006626</v>
       </c>
       <c r="X423" s="1" t="n">
+        <v>0.006616</v>
+      </c>
+      <c r="Y423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="Y423" s="1" t="n">
+      <c r="Z423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -33984,10 +35256,13 @@
         <v>0.908</v>
       </c>
       <c r="X424" s="1" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="Y424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="Y424" s="1" t="n">
-        <v>0.907</v>
+      <c r="Z424" s="1" t="n">
+        <v>0.905</v>
       </c>
     </row>
     <row r="425">
@@ -34063,9 +35338,12 @@
         <v>0.03538</v>
       </c>
       <c r="X425" s="1" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="Y425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="Y425" s="1" t="n">
+      <c r="Z425" s="1" t="n">
         <v>0.03519</v>
       </c>
     </row>
@@ -34142,9 +35420,12 @@
         <v>1.784</v>
       </c>
       <c r="X426" s="1" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="Y426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="Y426" s="1" t="n">
+      <c r="Z426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -34221,9 +35502,12 @@
         <v>0.1291</v>
       </c>
       <c r="X427" s="1" t="n">
+        <v>0.12895</v>
+      </c>
+      <c r="Y427" s="1" t="n">
         <v>0.1291</v>
       </c>
-      <c r="Y427" s="1" t="n">
+      <c r="Z427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -34300,9 +35584,12 @@
         <v>0.05365</v>
       </c>
       <c r="X428" s="1" t="n">
+        <v>0.05361</v>
+      </c>
+      <c r="Y428" s="1" t="n">
         <v>0.05391</v>
       </c>
-      <c r="Y428" s="1" t="n">
+      <c r="Z428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -34379,9 +35666,12 @@
         <v>1.304</v>
       </c>
       <c r="X429" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="Y429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="Y429" s="1" t="n">
+      <c r="Z429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -34458,10 +35748,13 @@
         <v>0.07473</v>
       </c>
       <c r="X430" s="1" t="n">
+        <v>0.07444000000000001</v>
+      </c>
+      <c r="Y430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="Y430" s="1" t="n">
-        <v>0.07456</v>
+      <c r="Z430" s="1" t="n">
+        <v>0.07444000000000001</v>
       </c>
     </row>
     <row r="431">
@@ -34537,9 +35830,12 @@
         <v>0.1567</v>
       </c>
       <c r="X431" s="1" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="Y431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="Y431" s="1" t="n">
+      <c r="Z431" s="1" t="n">
         <v>0.156</v>
       </c>
     </row>
@@ -34616,9 +35912,12 @@
         <v>1.451</v>
       </c>
       <c r="X432" s="1" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="Y432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="Y432" s="1" t="n">
+      <c r="Z432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -34695,10 +35994,13 @@
         <v>3.255</v>
       </c>
       <c r="X433" s="1" t="n">
+        <v>3.236</v>
+      </c>
+      <c r="Y433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="Y433" s="1" t="n">
-        <v>3.239</v>
+      <c r="Z433" s="1" t="n">
+        <v>3.236</v>
       </c>
     </row>
     <row r="434">
@@ -34774,10 +36076,13 @@
         <v>0.1782</v>
       </c>
       <c r="X434" s="1" t="n">
+        <v>0.1779</v>
+      </c>
+      <c r="Y434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="Y434" s="1" t="n">
-        <v>0.1782</v>
+      <c r="Z434" s="1" t="n">
+        <v>0.1779</v>
       </c>
     </row>
     <row r="435">
@@ -34853,9 +36158,12 @@
         <v>0.008585000000000001</v>
       </c>
       <c r="X435" s="1" t="n">
+        <v>0.008567999999999999</v>
+      </c>
+      <c r="Y435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="Y435" s="1" t="n">
+      <c r="Z435" s="1" t="n">
         <v>0.008548</v>
       </c>
     </row>
@@ -34932,10 +36240,13 @@
         <v>0.2816</v>
       </c>
       <c r="X436" s="1" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="Y436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="Y436" s="1" t="n">
-        <v>0.2805</v>
+      <c r="Z436" s="1" t="n">
+        <v>0.2803</v>
       </c>
     </row>
     <row r="437">
@@ -35011,9 +36322,12 @@
         <v>0.03865</v>
       </c>
       <c r="X437" s="1" t="n">
+        <v>0.03877</v>
+      </c>
+      <c r="Y437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="Y437" s="1" t="n">
+      <c r="Z437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -35090,9 +36404,12 @@
         <v>0.02439</v>
       </c>
       <c r="X438" s="1" t="n">
+        <v>0.02442</v>
+      </c>
+      <c r="Y438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="Y438" s="1" t="n">
+      <c r="Z438" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -35169,10 +36486,13 @@
         <v>0.04401</v>
       </c>
       <c r="X439" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="Y439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="Y439" s="1" t="n">
-        <v>0.04401</v>
+      <c r="Z439" s="1" t="n">
+        <v>0.044</v>
       </c>
     </row>
     <row r="440">
@@ -35248,9 +36568,12 @@
         <v>0.0005312</v>
       </c>
       <c r="X440" s="1" t="n">
+        <v>0.0005222</v>
+      </c>
+      <c r="Y440" s="1" t="n">
         <v>0.0005312</v>
       </c>
-      <c r="Y440" s="1" t="n">
+      <c r="Z440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -35327,9 +36650,12 @@
         <v>0.04474</v>
       </c>
       <c r="X441" s="1" t="n">
+        <v>0.04486</v>
+      </c>
+      <c r="Y441" s="1" t="n">
         <v>0.04581</v>
       </c>
-      <c r="Y441" s="1" t="n">
+      <c r="Z441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -35406,9 +36732,12 @@
         <v>0.000419</v>
       </c>
       <c r="X442" s="1" t="n">
+        <v>0.000418</v>
+      </c>
+      <c r="Y442" s="1" t="n">
         <v>0.000419</v>
       </c>
-      <c r="Y442" s="1" t="n">
+      <c r="Z442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -35485,9 +36814,12 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="X443" s="1" t="n">
+        <v>0.09427000000000001</v>
+      </c>
+      <c r="Y443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="Y443" s="1" t="n">
+      <c r="Z443" s="1" t="n">
         <v>0.09392</v>
       </c>
     </row>
@@ -35564,10 +36896,13 @@
         <v>2.299</v>
       </c>
       <c r="X444" s="1" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="Y444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="Y444" s="1" t="n">
-        <v>2.286</v>
+      <c r="Z444" s="1" t="n">
+        <v>2.284</v>
       </c>
     </row>
     <row r="445">
@@ -35643,9 +36978,12 @@
         <v>0.2694</v>
       </c>
       <c r="X445" s="1" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="Y445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="Y445" s="1" t="n">
+      <c r="Z445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -35722,9 +37060,12 @@
         <v>0.0007437</v>
       </c>
       <c r="X446" s="1" t="n">
+        <v>0.0007413</v>
+      </c>
+      <c r="Y446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="Y446" s="1" t="n">
+      <c r="Z446" s="1" t="n">
         <v>0.0007376</v>
       </c>
     </row>
@@ -35801,9 +37142,12 @@
         <v>0.03864</v>
       </c>
       <c r="X447" s="1" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="Y447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="Y447" s="1" t="n">
+      <c r="Z447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -35880,9 +37224,12 @@
         <v>0.1769</v>
       </c>
       <c r="X448" s="1" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="Y448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="Y448" s="1" t="n">
+      <c r="Z448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -35959,9 +37306,12 @@
         <v>0.04312</v>
       </c>
       <c r="X449" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="Y449" s="1" t="n">
         <v>0.04312</v>
       </c>
-      <c r="Y449" s="1" t="n">
+      <c r="Z449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -36038,9 +37388,12 @@
         <v>0.0001651</v>
       </c>
       <c r="X450" s="1" t="n">
+        <v>0.0001644</v>
+      </c>
+      <c r="Y450" s="1" t="n">
         <v>0.0001657</v>
       </c>
-      <c r="Y450" s="1" t="n">
+      <c r="Z450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -36117,9 +37470,12 @@
         <v>0.0374</v>
       </c>
       <c r="X451" s="1" t="n">
+        <v>0.03747</v>
+      </c>
+      <c r="Y451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="Y451" s="1" t="n">
+      <c r="Z451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -36196,9 +37552,12 @@
         <v>0.009520000000000001</v>
       </c>
       <c r="X452" s="1" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="Y452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="Y452" s="1" t="n">
+      <c r="Z452" s="1" t="n">
         <v>0.009520000000000001</v>
       </c>
     </row>
@@ -36275,10 +37634,13 @@
         <v>0.06779</v>
       </c>
       <c r="X453" s="1" t="n">
+        <v>0.06766</v>
+      </c>
+      <c r="Y453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="Y453" s="1" t="n">
-        <v>0.06776</v>
+      <c r="Z453" s="1" t="n">
+        <v>0.06766</v>
       </c>
     </row>
     <row r="454">
@@ -36354,10 +37716,13 @@
         <v>0.00751</v>
       </c>
       <c r="X454" s="1" t="n">
+        <v>0.007472</v>
+      </c>
+      <c r="Y454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="Y454" s="1" t="n">
-        <v>0.007478</v>
+      <c r="Z454" s="1" t="n">
+        <v>0.007472</v>
       </c>
     </row>
     <row r="455">
@@ -36433,10 +37798,13 @@
         <v>0.003272</v>
       </c>
       <c r="X455" s="1" t="n">
+        <v>0.003259</v>
+      </c>
+      <c r="Y455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="Y455" s="1" t="n">
-        <v>0.003267</v>
+      <c r="Z455" s="1" t="n">
+        <v>0.003259</v>
       </c>
     </row>
     <row r="456">
@@ -36512,9 +37880,12 @@
         <v>0.001848</v>
       </c>
       <c r="X456" s="1" t="n">
+        <v>0.001841</v>
+      </c>
+      <c r="Y456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="Y456" s="1" t="n">
+      <c r="Z456" s="1" t="n">
         <v>0.00184</v>
       </c>
     </row>
@@ -36591,9 +37962,12 @@
         <v>0.0001752</v>
       </c>
       <c r="X457" s="1" t="n">
+        <v>0.0001749</v>
+      </c>
+      <c r="Y457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="Y457" s="1" t="n">
+      <c r="Z457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -36670,9 +38044,12 @@
         <v>0.0003899</v>
       </c>
       <c r="X458" s="1" t="n">
+        <v>0.000389</v>
+      </c>
+      <c r="Y458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="Y458" s="1" t="n">
+      <c r="Z458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -36749,9 +38126,12 @@
         <v>0.01403</v>
       </c>
       <c r="X459" s="1" t="n">
+        <v>0.01398</v>
+      </c>
+      <c r="Y459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="Y459" s="1" t="n">
+      <c r="Z459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -36828,9 +38208,12 @@
         <v>0.04553</v>
       </c>
       <c r="X460" s="1" t="n">
+        <v>0.04535</v>
+      </c>
+      <c r="Y460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="Y460" s="1" t="n">
+      <c r="Z460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -36907,9 +38290,12 @@
         <v>0.283</v>
       </c>
       <c r="X461" s="1" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="Y461" s="1" t="n">
         <v>0.2843</v>
       </c>
-      <c r="Y461" s="1" t="n">
+      <c r="Z461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -36986,9 +38372,12 @@
         <v>0.006234</v>
       </c>
       <c r="X462" s="1" t="n">
+        <v>0.006238</v>
+      </c>
+      <c r="Y462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="Y462" s="1" t="n">
+      <c r="Z462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -37065,9 +38454,12 @@
         <v>0.007119</v>
       </c>
       <c r="X463" s="1" t="n">
+        <v>0.007084</v>
+      </c>
+      <c r="Y463" s="1" t="n">
         <v>0.007153</v>
       </c>
-      <c r="Y463" s="1" t="n">
+      <c r="Z463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -37144,9 +38536,12 @@
         <v>0.2893</v>
       </c>
       <c r="X464" s="1" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="Y464" s="1" t="n">
         <v>0.2895</v>
       </c>
-      <c r="Y464" s="1" t="n">
+      <c r="Z464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -37223,9 +38618,12 @@
         <v>0.08087</v>
       </c>
       <c r="X465" s="1" t="n">
+        <v>0.08068</v>
+      </c>
+      <c r="Y465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="Y465" s="1" t="n">
+      <c r="Z465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -37302,9 +38700,12 @@
         <v>0.6378</v>
       </c>
       <c r="X466" s="1" t="n">
+        <v>0.6357</v>
+      </c>
+      <c r="Y466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="Y466" s="1" t="n">
+      <c r="Z466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -37381,10 +38782,13 @@
         <v>0.01477</v>
       </c>
       <c r="X467" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="Y467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="Y467" s="1" t="n">
-        <v>0.0147</v>
+      <c r="Z467" s="1" t="n">
+        <v>0.01469</v>
       </c>
     </row>
     <row r="468">
@@ -37460,9 +38864,12 @@
         <v>0.03432</v>
       </c>
       <c r="X468" s="1" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="Y468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="Y468" s="1" t="n">
+      <c r="Z468" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -37539,9 +38946,12 @@
         <v>0.1623</v>
       </c>
       <c r="X469" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="Y469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="Y469" s="1" t="n">
+      <c r="Z469" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -37618,9 +39028,12 @@
         <v>0.4107</v>
       </c>
       <c r="X470" s="1" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="Y470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="Y470" s="1" t="n">
+      <c r="Z470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -37697,9 +39110,12 @@
         <v>0.06899</v>
       </c>
       <c r="X471" s="1" t="n">
+        <v>0.06899</v>
+      </c>
+      <c r="Y471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="Y471" s="1" t="n">
+      <c r="Z471" s="1" t="n">
         <v>0.06854</v>
       </c>
     </row>
@@ -37776,9 +39192,12 @@
         <v>0.0659</v>
       </c>
       <c r="X472" s="1" t="n">
+        <v>0.06546</v>
+      </c>
+      <c r="Y472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="Y472" s="1" t="n">
+      <c r="Z472" s="1" t="n">
         <v>0.06515</v>
       </c>
     </row>
@@ -37855,9 +39274,12 @@
         <v>0.01628</v>
       </c>
       <c r="X473" s="1" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="Y473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="Y473" s="1" t="n">
+      <c r="Z473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -37934,10 +39356,13 @@
         <v>0.2064</v>
       </c>
       <c r="X474" s="1" t="n">
+        <v>0.2054</v>
+      </c>
+      <c r="Y474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="Y474" s="1" t="n">
-        <v>0.2061</v>
+      <c r="Z474" s="1" t="n">
+        <v>0.2054</v>
       </c>
     </row>
     <row r="475">
@@ -38013,9 +39438,12 @@
         <v>0.04192</v>
       </c>
       <c r="X475" s="1" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="Y475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="Y475" s="1" t="n">
+      <c r="Z475" s="1" t="n">
         <v>0.04183</v>
       </c>
     </row>
@@ -38092,9 +39520,12 @@
         <v>1.572</v>
       </c>
       <c r="X476" s="1" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="Y476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="Y476" s="1" t="n">
+      <c r="Z476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -38171,9 +39602,12 @@
         <v>0.1011</v>
       </c>
       <c r="X477" s="1" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="Y477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="Y477" s="1" t="n">
+      <c r="Z477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -38250,9 +39684,12 @@
         <v>0.001158</v>
       </c>
       <c r="X478" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="Y478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="Y478" s="1" t="n">
+      <c r="Z478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -38329,9 +39766,12 @@
         <v>0.1436</v>
       </c>
       <c r="X479" s="1" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="Y479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="Y479" s="1" t="n">
+      <c r="Z479" s="1" t="n">
         <v>0.1429</v>
       </c>
     </row>
@@ -38408,9 +39848,12 @@
         <v>0.001954</v>
       </c>
       <c r="X480" s="1" t="n">
-        <v>0.001954</v>
+        <v>0.001969</v>
       </c>
       <c r="Y480" s="1" t="n">
+        <v>0.001969</v>
+      </c>
+      <c r="Z480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -38487,10 +39930,13 @@
         <v>0.907</v>
       </c>
       <c r="X481" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="Y481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="Y481" s="1" t="n">
-        <v>0.904</v>
+      <c r="Z481" s="1" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="482">
@@ -38566,9 +40012,12 @@
         <v>0.1339</v>
       </c>
       <c r="X482" s="1" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="Y482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="Y482" s="1" t="n">
+      <c r="Z482" s="1" t="n">
         <v>0.13233</v>
       </c>
     </row>
@@ -38645,9 +40094,12 @@
         <v>0.04023</v>
       </c>
       <c r="X483" s="1" t="n">
+        <v>0.04013</v>
+      </c>
+      <c r="Y483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="Y483" s="1" t="n">
+      <c r="Z483" s="1" t="n">
         <v>0.04005</v>
       </c>
     </row>
@@ -38724,9 +40176,12 @@
         <v>0.3023</v>
       </c>
       <c r="X484" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="Y484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="Y484" s="1" t="n">
+      <c r="Z484" s="1" t="n">
         <v>0.2999</v>
       </c>
     </row>
@@ -38803,9 +40258,12 @@
         <v>0.05682</v>
       </c>
       <c r="X485" s="1" t="n">
+        <v>0.05645</v>
+      </c>
+      <c r="Y485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="Y485" s="1" t="n">
+      <c r="Z485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -38882,10 +40340,13 @@
         <v>0.001562</v>
       </c>
       <c r="X486" s="1" t="n">
+        <v>0.001555</v>
+      </c>
+      <c r="Y486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="Y486" s="1" t="n">
-        <v>0.001558</v>
+      <c r="Z486" s="1" t="n">
+        <v>0.001555</v>
       </c>
     </row>
     <row r="487">
@@ -38961,10 +40422,13 @@
         <v>0.06687</v>
       </c>
       <c r="X487" s="1" t="n">
+        <v>0.06655999999999999</v>
+      </c>
+      <c r="Y487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="Y487" s="1" t="n">
-        <v>0.06662</v>
+      <c r="Z487" s="1" t="n">
+        <v>0.06655999999999999</v>
       </c>
     </row>
     <row r="488">
@@ -39040,9 +40504,12 @@
         <v>0.1924</v>
       </c>
       <c r="X488" s="1" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="Y488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="Y488" s="1" t="n">
+      <c r="Z488" s="1" t="n">
         <v>0.1911</v>
       </c>
     </row>
@@ -39119,10 +40586,13 @@
         <v>0.04776</v>
       </c>
       <c r="X489" s="1" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="Y489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="Y489" s="1" t="n">
-        <v>0.04768</v>
+      <c r="Z489" s="1" t="n">
+        <v>0.04761</v>
       </c>
     </row>
     <row r="490">
@@ -39198,9 +40668,12 @@
         <v>0.14</v>
       </c>
       <c r="X490" s="1" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="Y490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="Y490" s="1" t="n">
+      <c r="Z490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -39277,9 +40750,12 @@
         <v>0.02252</v>
       </c>
       <c r="X491" s="1" t="n">
+        <v>0.02251</v>
+      </c>
+      <c r="Y491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="Y491" s="1" t="n">
+      <c r="Z491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -39356,9 +40832,12 @@
         <v>0.007802</v>
       </c>
       <c r="X492" s="1" t="n">
+        <v>0.007791</v>
+      </c>
+      <c r="Y492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="Y492" s="1" t="n">
+      <c r="Z492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -39435,10 +40914,13 @@
         <v>0.0005925</v>
       </c>
       <c r="X493" s="1" t="n">
+        <v>0.0005903</v>
+      </c>
+      <c r="Y493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="Y493" s="1" t="n">
-        <v>0.0005918</v>
+      <c r="Z493" s="1" t="n">
+        <v>0.0005903</v>
       </c>
     </row>
     <row r="494">
@@ -39514,9 +40996,12 @@
         <v>3.019</v>
       </c>
       <c r="X494" s="1" t="n">
+        <v>3.014</v>
+      </c>
+      <c r="Y494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="Y494" s="1" t="n">
+      <c r="Z494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -39593,9 +41078,12 @@
         <v>0.0509</v>
       </c>
       <c r="X495" s="1" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="Y495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="Y495" s="1" t="n">
+      <c r="Z495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -39672,9 +41160,12 @@
         <v>0.006827</v>
       </c>
       <c r="X496" s="1" t="n">
+        <v>0.006794</v>
+      </c>
+      <c r="Y496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="Y496" s="1" t="n">
+      <c r="Z496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -39751,9 +41242,12 @@
         <v>1.305</v>
       </c>
       <c r="X497" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="Y497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="Y497" s="1" t="n">
+      <c r="Z497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -39830,9 +41324,12 @@
         <v>0.03928</v>
       </c>
       <c r="X498" s="1" t="n">
+        <v>0.03909</v>
+      </c>
+      <c r="Y498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="Y498" s="1" t="n">
+      <c r="Z498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -39909,9 +41406,12 @@
         <v>0.04114</v>
       </c>
       <c r="X499" s="1" t="n">
+        <v>0.04105</v>
+      </c>
+      <c r="Y499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="Y499" s="1" t="n">
+      <c r="Z499" s="1" t="n">
         <v>0.04085</v>
       </c>
     </row>
@@ -39988,9 +41488,12 @@
         <v>0.00546</v>
       </c>
       <c r="X500" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="Y500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="Y500" s="1" t="n">
+      <c r="Z500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -40067,9 +41570,12 @@
         <v>0.03557</v>
       </c>
       <c r="X501" s="1" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="Y501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="Y501" s="1" t="n">
+      <c r="Z501" s="1" t="n">
         <v>0.03548</v>
       </c>
     </row>
@@ -40146,10 +41652,13 @@
         <v>0.07206</v>
       </c>
       <c r="X502" s="1" t="n">
+        <v>0.07191</v>
+      </c>
+      <c r="Y502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="Y502" s="1" t="n">
-        <v>0.07205</v>
+      <c r="Z502" s="1" t="n">
+        <v>0.07191</v>
       </c>
     </row>
     <row r="503">
@@ -40225,10 +41734,13 @@
         <v>0.0007435</v>
       </c>
       <c r="X503" s="1" t="n">
+        <v>0.0007403000000000001</v>
+      </c>
+      <c r="Y503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="Y503" s="1" t="n">
-        <v>0.0007412</v>
+      <c r="Z503" s="1" t="n">
+        <v>0.0007403000000000001</v>
       </c>
     </row>
     <row r="504">
@@ -40304,9 +41816,12 @@
         <v>0.016067</v>
       </c>
       <c r="X504" s="1" t="n">
+        <v>0.016038</v>
+      </c>
+      <c r="Y504" s="1" t="n">
         <v>0.016067</v>
       </c>
-      <c r="Y504" s="1" t="n">
+      <c r="Z504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -40383,9 +41898,12 @@
         <v>0.00704</v>
       </c>
       <c r="X505" s="1" t="n">
+        <v>0.00701</v>
+      </c>
+      <c r="Y505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="Y505" s="1" t="n">
+      <c r="Z505" s="1" t="n">
         <v>0.00701</v>
       </c>
     </row>
@@ -40462,9 +41980,12 @@
         <v>0.0256</v>
       </c>
       <c r="X506" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="Y506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="Y506" s="1" t="n">
+      <c r="Z506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -40544,6 +42065,9 @@
         <v>0.00136</v>
       </c>
       <c r="Y507" s="1" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="Z507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -40620,9 +42144,12 @@
         <v>0.2822</v>
       </c>
       <c r="X508" s="1" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="Y508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="Y508" s="1" t="n">
+      <c r="Z508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -40699,10 +42226,13 @@
         <v>0.1318</v>
       </c>
       <c r="X509" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="Y509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="Y509" s="1" t="n">
-        <v>0.1314</v>
+      <c r="Z509" s="1" t="n">
+        <v>0.1311</v>
       </c>
     </row>
     <row r="510">
@@ -40778,9 +42308,12 @@
         <v>0.04931</v>
       </c>
       <c r="X510" s="1" t="n">
+        <v>0.04926</v>
+      </c>
+      <c r="Y510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="Y510" s="1" t="n">
+      <c r="Z510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -40857,10 +42390,13 @@
         <v>0.00271</v>
       </c>
       <c r="X511" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="Y511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="Y511" s="1" t="n">
-        <v>0.0027</v>
+      <c r="Z511" s="1" t="n">
+        <v>0.00269</v>
       </c>
     </row>
     <row r="512">
@@ -40936,9 +42472,12 @@
         <v>0.015069</v>
       </c>
       <c r="X512" s="1" t="n">
+        <v>0.015026</v>
+      </c>
+      <c r="Y512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="Y512" s="1" t="n">
+      <c r="Z512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -41015,9 +42554,12 @@
         <v>0.6913</v>
       </c>
       <c r="X513" s="1" t="n">
+        <v>0.6901</v>
+      </c>
+      <c r="Y513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="Y513" s="1" t="n">
+      <c r="Z513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -41094,9 +42636,12 @@
         <v>0.004522</v>
       </c>
       <c r="X514" s="1" t="n">
+        <v>0.004521</v>
+      </c>
+      <c r="Y514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="Y514" s="1" t="n">
+      <c r="Z514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -41173,9 +42718,12 @@
         <v>0.005074</v>
       </c>
       <c r="X515" s="1" t="n">
+        <v>0.005058</v>
+      </c>
+      <c r="Y515" s="1" t="n">
         <v>0.005074</v>
       </c>
-      <c r="Y515" s="1" t="n">
+      <c r="Z515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -41252,10 +42800,13 @@
         <v>0.06324</v>
       </c>
       <c r="X516" s="1" t="n">
+        <v>0.06317</v>
+      </c>
+      <c r="Y516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="Y516" s="1" t="n">
-        <v>0.06319</v>
+      <c r="Z516" s="1" t="n">
+        <v>0.06317</v>
       </c>
     </row>
     <row r="517">
@@ -41331,9 +42882,12 @@
         <v>0.06522</v>
       </c>
       <c r="X517" s="1" t="n">
+        <v>0.06505</v>
+      </c>
+      <c r="Y517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="Y517" s="1" t="n">
+      <c r="Z517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -41410,9 +42964,12 @@
         <v>0.01201</v>
       </c>
       <c r="X518" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="Y518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="Y518" s="1" t="n">
+      <c r="Z518" s="1" t="n">
         <v>0.01198</v>
       </c>
     </row>
@@ -41489,9 +43046,12 @@
         <v>0.04757</v>
       </c>
       <c r="X519" s="1" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="Y519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="Y519" s="1" t="n">
+      <c r="Z519" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -41568,9 +43128,12 @@
         <v>0.04393</v>
       </c>
       <c r="X520" s="1" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="Y520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="Y520" s="1" t="n">
+      <c r="Z520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -41647,10 +43210,13 @@
         <v>0.008416999999999999</v>
       </c>
       <c r="X521" s="1" t="n">
+        <v>0.008332000000000001</v>
+      </c>
+      <c r="Y521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="Y521" s="1" t="n">
-        <v>0.008402</v>
+      <c r="Z521" s="1" t="n">
+        <v>0.008332000000000001</v>
       </c>
     </row>
     <row r="522">
@@ -41726,9 +43292,12 @@
         <v>0.08787</v>
       </c>
       <c r="X522" s="1" t="n">
+        <v>0.08767999999999999</v>
+      </c>
+      <c r="Y522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="Y522" s="1" t="n">
+      <c r="Z522" s="1" t="n">
         <v>0.08762</v>
       </c>
     </row>
@@ -41805,9 +43374,12 @@
         <v>0.006503</v>
       </c>
       <c r="X523" s="1" t="n">
+        <v>0.006486</v>
+      </c>
+      <c r="Y523" s="1" t="n">
         <v>0.006503</v>
       </c>
-      <c r="Y523" s="1" t="n">
+      <c r="Z523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -41884,9 +43456,12 @@
         <v>0.01638</v>
       </c>
       <c r="X524" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="Y524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="Y524" s="1" t="n">
+      <c r="Z524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -41963,9 +43538,12 @@
         <v>0.0179</v>
       </c>
       <c r="X525" s="1" t="n">
+        <v>0.01789</v>
+      </c>
+      <c r="Y525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="Y525" s="1" t="n">
+      <c r="Z525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -42042,9 +43620,12 @@
         <v>0.07897999999999999</v>
       </c>
       <c r="X526" s="1" t="n">
+        <v>0.07889</v>
+      </c>
+      <c r="Y526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="Y526" s="1" t="n">
+      <c r="Z526" s="1" t="n">
         <v>0.0786</v>
       </c>
     </row>
@@ -42121,9 +43702,12 @@
         <v>0.01608</v>
       </c>
       <c r="X527" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="Y527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="Y527" s="1" t="n">
+      <c r="Z527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -42200,9 +43784,12 @@
         <v>0.004131</v>
       </c>
       <c r="X528" s="1" t="n">
+        <v>0.004124</v>
+      </c>
+      <c r="Y528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="Y528" s="1" t="n">
+      <c r="Z528" s="1" t="n">
         <v>0.004113</v>
       </c>
     </row>
@@ -42279,9 +43866,12 @@
         <v>0.003688</v>
       </c>
       <c r="X529" s="1" t="n">
+        <v>0.003683</v>
+      </c>
+      <c r="Y529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="Y529" s="1" t="n">
+      <c r="Z529" s="1" t="n">
         <v>0.003672</v>
       </c>
     </row>
@@ -42358,9 +43948,12 @@
         <v>1.323</v>
       </c>
       <c r="X530" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Y530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="Y530" s="1" t="n">
+      <c r="Z530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -42437,9 +44030,12 @@
         <v>0.4893</v>
       </c>
       <c r="X531" s="1" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="Y531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="Y531" s="1" t="n">
+      <c r="Z531" s="1" t="n">
         <v>0.487</v>
       </c>
     </row>
@@ -42516,10 +44112,13 @@
         <v>0.03056</v>
       </c>
       <c r="X532" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="Y532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="Y532" s="1" t="n">
-        <v>0.03053</v>
+      <c r="Z532" s="1" t="n">
+        <v>0.0305</v>
       </c>
     </row>
     <row r="533">
@@ -42595,9 +44194,12 @@
         <v>0.1527</v>
       </c>
       <c r="X533" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="Y533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="Y533" s="1" t="n">
+      <c r="Z533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -42674,9 +44276,12 @@
         <v>0.05363</v>
       </c>
       <c r="X534" s="1" t="n">
+        <v>0.05351</v>
+      </c>
+      <c r="Y534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="Y534" s="1" t="n">
+      <c r="Z534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -42753,9 +44358,12 @@
         <v>0.01486</v>
       </c>
       <c r="X535" s="1" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="Y535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="Y535" s="1" t="n">
+      <c r="Z535" s="1" t="n">
         <v>0.01472</v>
       </c>
     </row>
@@ -42832,9 +44440,12 @@
         <v>0.05878</v>
       </c>
       <c r="X536" s="1" t="n">
+        <v>0.05885</v>
+      </c>
+      <c r="Y536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="Y536" s="1" t="n">
+      <c r="Z536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -42911,10 +44522,13 @@
         <v>0.05475</v>
       </c>
       <c r="X537" s="1" t="n">
+        <v>0.05472</v>
+      </c>
+      <c r="Y537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="Y537" s="1" t="n">
-        <v>0.05475</v>
+      <c r="Z537" s="1" t="n">
+        <v>0.05472</v>
       </c>
     </row>
     <row r="538">
@@ -42990,9 +44604,12 @@
         <v>0.1063</v>
       </c>
       <c r="X538" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="Y538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="Y538" s="1" t="n">
+      <c r="Z538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -43069,9 +44686,12 @@
         <v>0.01277</v>
       </c>
       <c r="X539" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="Y539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="Y539" s="1" t="n">
+      <c r="Z539" s="1" t="n">
         <v>0.01265</v>
       </c>
     </row>
@@ -43148,10 +44768,13 @@
         <v>0.1731</v>
       </c>
       <c r="X540" s="1" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="Y540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="Y540" s="1" t="n">
-        <v>0.1723</v>
+      <c r="Z540" s="1" t="n">
+        <v>0.1721</v>
       </c>
     </row>
     <row r="541">
@@ -43227,9 +44850,12 @@
         <v>0.1236</v>
       </c>
       <c r="X541" s="1" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="Y541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="Y541" s="1" t="n">
+      <c r="Z541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -43306,9 +44932,12 @@
         <v>0.02488</v>
       </c>
       <c r="X542" s="1" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="Y542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="Y542" s="1" t="n">
+      <c r="Z542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -43385,10 +45014,13 @@
         <v>0.05857</v>
       </c>
       <c r="X543" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="Y543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="Y543" s="1" t="n">
-        <v>0.05851</v>
+      <c r="Z543" s="1" t="n">
+        <v>0.05832</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA543"/>
+  <dimension ref="A1:AB543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -444,8 +444,9 @@
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,10 +577,15 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>price_06:00</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -664,9 +670,12 @@
         <v>71081.7</v>
       </c>
       <c r="Z2" s="1" t="n">
+        <v>71060.39999999999</v>
+      </c>
+      <c r="AA2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="AA2" s="1" t="n">
+      <c r="AB2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -749,9 +758,12 @@
         <v>2103.12</v>
       </c>
       <c r="Z3" s="1" t="n">
+        <v>2103.21</v>
+      </c>
+      <c r="AA3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="AA3" s="1" t="n">
+      <c r="AB3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -834,9 +846,12 @@
         <v>88.59999999999999</v>
       </c>
       <c r="Z4" s="1" t="n">
+        <v>88.58</v>
+      </c>
+      <c r="AA4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AB4" s="1" t="n">
         <v>88.47</v>
       </c>
     </row>
@@ -919,9 +934,12 @@
         <v>3.814</v>
       </c>
       <c r="Z5" s="1" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="AA5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AB5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -1004,9 +1022,12 @@
         <v>1.3985</v>
       </c>
       <c r="Z6" s="1" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="AA6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AB6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -1089,9 +1110,12 @@
         <v>0.09614</v>
       </c>
       <c r="Z7" s="1" t="n">
+        <v>0.09618</v>
+      </c>
+      <c r="AA7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -1174,10 +1198,13 @@
         <v>0.013419</v>
       </c>
       <c r="Z8" s="1" t="n">
+        <v>0.013414</v>
+      </c>
+      <c r="AA8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="AA8" s="1" t="n">
-        <v>0.013419</v>
+      <c r="AB8" s="1" t="n">
+        <v>0.013414</v>
       </c>
     </row>
     <row r="9">
@@ -1259,9 +1286,12 @@
         <v>657.05</v>
       </c>
       <c r="Z9" s="1" t="n">
+        <v>657.24</v>
+      </c>
+      <c r="AA9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="AA9" s="1" t="n">
+      <c r="AB9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1344,9 +1374,12 @@
         <v>19.782</v>
       </c>
       <c r="Z10" s="1" t="n">
+        <v>19.986</v>
+      </c>
+      <c r="AA10" s="1" t="n">
         <v>20.464</v>
       </c>
-      <c r="AA10" s="1" t="n">
+      <c r="AB10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1429,9 +1462,12 @@
         <v>0.0033941</v>
       </c>
       <c r="Z11" s="1" t="n">
+        <v>0.0033927</v>
+      </c>
+      <c r="AA11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="AA11" s="1" t="n">
+      <c r="AB11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1514,9 +1550,12 @@
         <v>36.541</v>
       </c>
       <c r="Z12" s="1" t="n">
+        <v>36.564</v>
+      </c>
+      <c r="AA12" s="1" t="n">
         <v>36.869</v>
       </c>
-      <c r="AA12" s="1" t="n">
+      <c r="AB12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1599,10 +1638,13 @@
         <v>209.94</v>
       </c>
       <c r="Z13" s="1" t="n">
+        <v>209.75</v>
+      </c>
+      <c r="AA13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="AA13" s="1" t="n">
-        <v>209.94</v>
+      <c r="AB13" s="1" t="n">
+        <v>209.75</v>
       </c>
     </row>
     <row r="14">
@@ -1684,9 +1726,12 @@
         <v>0.0011313</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>0.0011389</v>
+        <v>0.0011412</v>
       </c>
       <c r="AA14" s="1" t="n">
+        <v>0.0011412</v>
+      </c>
+      <c r="AB14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1769,9 +1814,12 @@
         <v>0.32663</v>
       </c>
       <c r="Z15" s="1" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AA15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="AA15" s="1" t="n">
+      <c r="AB15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1854,9 +1902,12 @@
         <v>231.9</v>
       </c>
       <c r="Z16" s="1" t="n">
+        <v>232.75</v>
+      </c>
+      <c r="AA16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="AA16" s="1" t="n">
+      <c r="AB16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -1939,9 +1990,12 @@
         <v>0.997</v>
       </c>
       <c r="Z17" s="1" t="n">
+        <v>0.9983</v>
+      </c>
+      <c r="AA17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="AA17" s="1" t="n">
+      <c r="AB17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -2024,9 +2078,12 @@
         <v>0.2668</v>
       </c>
       <c r="Z18" s="1" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AA18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="AA18" s="1" t="n">
+      <c r="AB18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -2109,9 +2166,12 @@
         <v>9.755000000000001</v>
       </c>
       <c r="Z19" s="1" t="n">
+        <v>9.757</v>
+      </c>
+      <c r="AA19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="AA19" s="1" t="n">
+      <c r="AB19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -2194,9 +2254,12 @@
         <v>5012.13</v>
       </c>
       <c r="Z20" s="1" t="n">
+        <v>5018.9</v>
+      </c>
+      <c r="AA20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="AA20" s="1" t="n">
+      <c r="AB20" s="1" t="n">
         <v>5012.13</v>
       </c>
     </row>
@@ -2279,9 +2342,12 @@
         <v>462.91</v>
       </c>
       <c r="Z21" s="1" t="n">
+        <v>462.75</v>
+      </c>
+      <c r="AA21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="AA21" s="1" t="n">
+      <c r="AB21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -2364,9 +2430,12 @@
         <v>1.3951</v>
       </c>
       <c r="Z22" s="1" t="n">
+        <v>1.3988</v>
+      </c>
+      <c r="AA22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="AA22" s="1" t="n">
+      <c r="AB22" s="1" t="n">
         <v>1.3686</v>
       </c>
     </row>
@@ -2449,9 +2518,12 @@
         <v>1.0462</v>
       </c>
       <c r="Z23" s="1" t="n">
+        <v>1.0485</v>
+      </c>
+      <c r="AA23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="AA23" s="1" t="n">
+      <c r="AB23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2534,10 +2606,13 @@
         <v>1.344</v>
       </c>
       <c r="Z24" s="1" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AA24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="AA24" s="1" t="n">
-        <v>1.342</v>
+      <c r="AB24" s="1" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="25">
@@ -2619,9 +2694,12 @@
         <v>9.129</v>
       </c>
       <c r="Z25" s="1" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AA25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="AA25" s="1" t="n">
+      <c r="AB25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -2704,9 +2782,12 @@
         <v>0.3578</v>
       </c>
       <c r="Z26" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AA26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="AA26" s="1" t="n">
+      <c r="AB26" s="1" t="n">
         <v>0.3578</v>
       </c>
     </row>
@@ -2789,9 +2870,12 @@
         <v>0.871</v>
       </c>
       <c r="Z27" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AA27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="AA27" s="1" t="n">
+      <c r="AB27" s="1" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -2874,9 +2958,12 @@
         <v>1.808</v>
       </c>
       <c r="Z28" s="1" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="AA28" s="1" t="n">
         <v>1.863</v>
       </c>
-      <c r="AA28" s="1" t="n">
+      <c r="AB28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2959,9 +3046,12 @@
         <v>0.1092</v>
       </c>
       <c r="Z29" s="1" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="AA29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="AA29" s="1" t="n">
+      <c r="AB29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -3044,9 +3134,12 @@
         <v>0.00202</v>
       </c>
       <c r="Z30" s="1" t="n">
+        <v>0.002013</v>
+      </c>
+      <c r="AA30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="AA30" s="1" t="n">
+      <c r="AB30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -3129,9 +3222,12 @@
         <v>1.461</v>
       </c>
       <c r="Z31" s="1" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="AA31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="AA31" s="1" t="n">
+      <c r="AB31" s="1" t="n">
         <v>1.46</v>
       </c>
     </row>
@@ -3214,9 +3310,12 @@
         <v>0.177</v>
       </c>
       <c r="Z32" s="1" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="AA32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="AA32" s="1" t="n">
+      <c r="AB32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -3299,9 +3398,12 @@
         <v>0.1039</v>
       </c>
       <c r="Z33" s="1" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="AA33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="AA33" s="1" t="n">
+      <c r="AB33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -3384,9 +3486,12 @@
         <v>112.87</v>
       </c>
       <c r="Z34" s="1" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="AA34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="AA34" s="1" t="n">
+      <c r="AB34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -3469,9 +3574,12 @@
         <v>6.711</v>
       </c>
       <c r="Z35" s="1" t="n">
+        <v>6.743</v>
+      </c>
+      <c r="AA35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="AA35" s="1" t="n">
+      <c r="AB35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -3554,9 +3662,12 @@
         <v>0.017709</v>
       </c>
       <c r="Z36" s="1" t="n">
-        <v>0.017894</v>
+        <v>0.018773</v>
       </c>
       <c r="AA36" s="1" t="n">
+        <v>0.018773</v>
+      </c>
+      <c r="AB36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -3639,9 +3750,12 @@
         <v>0.3601</v>
       </c>
       <c r="Z37" s="1" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AA37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="AA37" s="1" t="n">
+      <c r="AB37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -3724,9 +3838,12 @@
         <v>55.69</v>
       </c>
       <c r="Z38" s="1" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="AA38" s="1" t="n">
         <v>55.92</v>
       </c>
-      <c r="AA38" s="1" t="n">
+      <c r="AB38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -3809,9 +3926,12 @@
         <v>0.59048</v>
       </c>
       <c r="Z39" s="1" t="n">
+        <v>0.61153</v>
+      </c>
+      <c r="AA39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="AA39" s="1" t="n">
+      <c r="AB39" s="1" t="n">
         <v>0.5717</v>
       </c>
     </row>
@@ -3894,9 +4014,12 @@
         <v>4.023</v>
       </c>
       <c r="Z40" s="1" t="n">
+        <v>4.021</v>
+      </c>
+      <c r="AA40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="AA40" s="1" t="n">
+      <c r="AB40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -3979,9 +4102,12 @@
         <v>0.04766</v>
       </c>
       <c r="Z41" s="1" t="n">
+        <v>0.04791</v>
+      </c>
+      <c r="AA41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="AA41" s="1" t="n">
+      <c r="AB41" s="1" t="n">
         <v>0.04766</v>
       </c>
     </row>
@@ -4064,9 +4190,12 @@
         <v>0.7008</v>
       </c>
       <c r="Z42" s="1" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="AA42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="AA42" s="1" t="n">
+      <c r="AB42" s="1" t="n">
         <v>0.6995</v>
       </c>
     </row>
@@ -4149,9 +4278,12 @@
         <v>0.2269</v>
       </c>
       <c r="Z43" s="1" t="n">
+        <v>0.22704</v>
+      </c>
+      <c r="AA43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="AA43" s="1" t="n">
+      <c r="AB43" s="1" t="n">
         <v>0.22604</v>
       </c>
     </row>
@@ -4234,9 +4366,12 @@
         <v>0.36291</v>
       </c>
       <c r="Z44" s="1" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="AA44" s="1" t="n">
         <v>0.36291</v>
       </c>
-      <c r="AA44" s="1" t="n">
+      <c r="AB44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -4319,9 +4454,12 @@
         <v>0.1688</v>
       </c>
       <c r="Z45" s="1" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="AA45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="AA45" s="1" t="n">
+      <c r="AB45" s="1" t="n">
         <v>0.1682</v>
       </c>
     </row>
@@ -4404,9 +4542,12 @@
         <v>0.0257</v>
       </c>
       <c r="Z46" s="1" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="AA46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="AA46" s="1" t="n">
+      <c r="AB46" s="1" t="n">
         <v>0.0257</v>
       </c>
     </row>
@@ -4489,9 +4630,12 @@
         <v>0.00594</v>
       </c>
       <c r="Z47" s="1" t="n">
+        <v>0.005946</v>
+      </c>
+      <c r="AA47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="AA47" s="1" t="n">
+      <c r="AB47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -4574,10 +4718,13 @@
         <v>0.007343</v>
       </c>
       <c r="Z48" s="1" t="n">
+        <v>0.007331</v>
+      </c>
+      <c r="AA48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="AA48" s="1" t="n">
-        <v>0.007343</v>
+      <c r="AB48" s="1" t="n">
+        <v>0.007331</v>
       </c>
     </row>
     <row r="49">
@@ -4659,9 +4806,12 @@
         <v>0.1094</v>
       </c>
       <c r="Z49" s="1" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="AA49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="AA49" s="1" t="n">
+      <c r="AB49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -4744,9 +4894,12 @@
         <v>0.04119</v>
       </c>
       <c r="Z50" s="1" t="n">
+        <v>0.04115</v>
+      </c>
+      <c r="AA50" s="1" t="n">
         <v>0.04222</v>
       </c>
-      <c r="AA50" s="1" t="n">
+      <c r="AB50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -4829,10 +4982,13 @@
         <v>0.1603</v>
       </c>
       <c r="Z51" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="AA51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="AA51" s="1" t="n">
-        <v>0.1603</v>
+      <c r="AB51" s="1" t="n">
+        <v>0.1599</v>
       </c>
     </row>
     <row r="52">
@@ -4914,9 +5070,12 @@
         <v>0.00357</v>
       </c>
       <c r="Z52" s="1" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="AA52" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="AA52" s="1" t="n">
+      <c r="AB52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -4999,9 +5158,12 @@
         <v>2.619</v>
       </c>
       <c r="Z53" s="1" t="n">
+        <v>2.616</v>
+      </c>
+      <c r="AA53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="AA53" s="1" t="n">
+      <c r="AB53" s="1" t="n">
         <v>2.613</v>
       </c>
     </row>
@@ -5084,9 +5246,12 @@
         <v>0.006189</v>
       </c>
       <c r="Z54" s="1" t="n">
+        <v>0.00618</v>
+      </c>
+      <c r="AA54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="AA54" s="1" t="n">
+      <c r="AB54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -5169,9 +5334,12 @@
         <v>0.02746</v>
       </c>
       <c r="Z55" s="1" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="AA55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="AA55" s="1" t="n">
+      <c r="AB55" s="1" t="n">
         <v>0.02738</v>
       </c>
     </row>
@@ -5254,10 +5422,13 @@
         <v>0.7292999999999999</v>
       </c>
       <c r="Z56" s="1" t="n">
+        <v>0.7284</v>
+      </c>
+      <c r="AA56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="AA56" s="1" t="n">
-        <v>0.7292999999999999</v>
+      <c r="AB56" s="1" t="n">
+        <v>0.7284</v>
       </c>
     </row>
     <row r="57">
@@ -5339,9 +5510,12 @@
         <v>0.1031</v>
       </c>
       <c r="Z57" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="AA57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="AA57" s="1" t="n">
+      <c r="AB57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -5424,9 +5598,12 @@
         <v>0.9366</v>
       </c>
       <c r="Z58" s="1" t="n">
+        <v>0.9377</v>
+      </c>
+      <c r="AA58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="AA58" s="1" t="n">
+      <c r="AB58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -5509,10 +5686,13 @@
         <v>0.08348999999999999</v>
       </c>
       <c r="Z59" s="1" t="n">
+        <v>0.08294</v>
+      </c>
+      <c r="AA59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="AA59" s="1" t="n">
-        <v>0.08348999999999999</v>
+      <c r="AB59" s="1" t="n">
+        <v>0.08294</v>
       </c>
     </row>
     <row r="60">
@@ -5594,9 +5774,12 @@
         <v>0.07033</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.07033</v>
+        <v>0.07701</v>
       </c>
       <c r="AA60" s="1" t="n">
+        <v>0.07701</v>
+      </c>
+      <c r="AB60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -5679,9 +5862,12 @@
         <v>0.05476</v>
       </c>
       <c r="Z61" s="1" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="AA61" s="1" t="n">
         <v>0.05539</v>
       </c>
-      <c r="AA61" s="1" t="n">
+      <c r="AB61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -5764,9 +5950,12 @@
         <v>0.010492</v>
       </c>
       <c r="Z62" s="1" t="n">
+        <v>0.010507</v>
+      </c>
+      <c r="AA62" s="1" t="n">
         <v>0.010649</v>
       </c>
-      <c r="AA62" s="1" t="n">
+      <c r="AB62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -5849,9 +6038,12 @@
         <v>0.2919</v>
       </c>
       <c r="Z63" s="1" t="n">
-        <v>0.29207</v>
+        <v>0.29231</v>
       </c>
       <c r="AA63" s="1" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AB63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -5934,10 +6126,13 @@
         <v>0.06902</v>
       </c>
       <c r="Z64" s="1" t="n">
+        <v>0.06756</v>
+      </c>
+      <c r="AA64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="AA64" s="1" t="n">
-        <v>0.06894</v>
+      <c r="AB64" s="1" t="n">
+        <v>0.06756</v>
       </c>
     </row>
     <row r="65">
@@ -6019,9 +6214,12 @@
         <v>0.3129</v>
       </c>
       <c r="Z65" s="1" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AA65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="AA65" s="1" t="n">
+      <c r="AB65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -6104,9 +6302,12 @@
         <v>0.16484</v>
       </c>
       <c r="Z66" s="1" t="n">
-        <v>0.16484</v>
+        <v>0.16587</v>
       </c>
       <c r="AA66" s="1" t="n">
+        <v>0.16587</v>
+      </c>
+      <c r="AB66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -6189,9 +6390,12 @@
         <v>0.12026</v>
       </c>
       <c r="Z67" s="1" t="n">
-        <v>0.1203</v>
+        <v>0.12035</v>
       </c>
       <c r="AA67" s="1" t="n">
+        <v>0.12035</v>
+      </c>
+      <c r="AB67" s="1" t="n">
         <v>0.1191</v>
       </c>
     </row>
@@ -6274,9 +6478,12 @@
         <v>0.09501999999999999</v>
       </c>
       <c r="Z68" s="1" t="n">
+        <v>0.09517</v>
+      </c>
+      <c r="AA68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="AA68" s="1" t="n">
+      <c r="AB68" s="1" t="n">
         <v>0.09474</v>
       </c>
     </row>
@@ -6359,9 +6566,12 @@
         <v>0.1243</v>
       </c>
       <c r="Z69" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AA69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="AA69" s="1" t="n">
+      <c r="AB69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -6444,9 +6654,12 @@
         <v>8.516999999999999</v>
       </c>
       <c r="Z70" s="1" t="n">
+        <v>8.523999999999999</v>
+      </c>
+      <c r="AA70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="AA70" s="1" t="n">
+      <c r="AB70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -6529,9 +6742,12 @@
         <v>0.238</v>
       </c>
       <c r="Z71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="AA71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="AA71" s="1" t="n">
+      <c r="AB71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -6614,9 +6830,12 @@
         <v>0.04961</v>
       </c>
       <c r="Z72" s="1" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="AA72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="AA72" s="1" t="n">
+      <c r="AB72" s="1" t="n">
         <v>0.04955</v>
       </c>
     </row>
@@ -6699,9 +6918,12 @@
         <v>0.05019</v>
       </c>
       <c r="Z73" s="1" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="AA73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="AA73" s="1" t="n">
+      <c r="AB73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -6784,9 +7006,12 @@
         <v>0.1221</v>
       </c>
       <c r="Z74" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AA74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="AA74" s="1" t="n">
+      <c r="AB74" s="1" t="n">
         <v>0.1221</v>
       </c>
     </row>
@@ -6869,9 +7094,12 @@
         <v>0.04652</v>
       </c>
       <c r="Z75" s="1" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="AA75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="AA75" s="1" t="n">
+      <c r="AB75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -6954,9 +7182,12 @@
         <v>0.06630999999999999</v>
       </c>
       <c r="Z76" s="1" t="n">
+        <v>0.06637999999999999</v>
+      </c>
+      <c r="AA76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="AA76" s="1" t="n">
+      <c r="AB76" s="1" t="n">
         <v>0.06630999999999999</v>
       </c>
     </row>
@@ -7039,9 +7270,12 @@
         <v>0.13191</v>
       </c>
       <c r="Z77" s="1" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="AA77" s="1" t="n">
         <v>0.13727</v>
       </c>
-      <c r="AA77" s="1" t="n">
+      <c r="AB77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -7124,9 +7358,12 @@
         <v>0.1608</v>
       </c>
       <c r="Z78" s="1" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="AA78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="AA78" s="1" t="n">
+      <c r="AB78" s="1" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -7209,9 +7446,12 @@
         <v>0.02692</v>
       </c>
       <c r="Z79" s="1" t="n">
+        <v>0.02694</v>
+      </c>
+      <c r="AA79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="AA79" s="1" t="n">
+      <c r="AB79" s="1" t="n">
         <v>0.02692</v>
       </c>
     </row>
@@ -7294,9 +7534,12 @@
         <v>354.72</v>
       </c>
       <c r="Z80" s="1" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="AA80" s="1" t="n">
         <v>362.68</v>
       </c>
-      <c r="AA80" s="1" t="n">
+      <c r="AB80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -7379,9 +7622,12 @@
         <v>7.038e-05</v>
       </c>
       <c r="Z81" s="1" t="n">
+        <v>7.032e-05</v>
+      </c>
+      <c r="AA81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="AA81" s="1" t="n">
+      <c r="AB81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -7464,9 +7710,12 @@
         <v>0.2648</v>
       </c>
       <c r="Z82" s="1" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="AA82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="AA82" s="1" t="n">
+      <c r="AB82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -7549,9 +7798,12 @@
         <v>1.1115</v>
       </c>
       <c r="Z83" s="1" t="n">
+        <v>1.1204</v>
+      </c>
+      <c r="AA83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="AA83" s="1" t="n">
+      <c r="AB83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -7634,9 +7886,12 @@
         <v>0.3517</v>
       </c>
       <c r="Z84" s="1" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AA84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="AA84" s="1" t="n">
+      <c r="AB84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -7719,9 +7974,12 @@
         <v>1.936</v>
       </c>
       <c r="Z85" s="1" t="n">
+        <v>1.9378</v>
+      </c>
+      <c r="AA85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="AA85" s="1" t="n">
+      <c r="AB85" s="1" t="n">
         <v>1.9339</v>
       </c>
     </row>
@@ -7804,9 +8062,12 @@
         <v>1.3195</v>
       </c>
       <c r="Z86" s="1" t="n">
-        <v>1.3205</v>
+        <v>1.3218</v>
       </c>
       <c r="AA86" s="1" t="n">
+        <v>1.3218</v>
+      </c>
+      <c r="AB86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -7889,9 +8150,12 @@
         <v>32.4</v>
       </c>
       <c r="Z87" s="1" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="AA87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="AA87" s="1" t="n">
+      <c r="AB87" s="1" t="n">
         <v>32.4</v>
       </c>
     </row>
@@ -7974,9 +8238,12 @@
         <v>0.00961</v>
       </c>
       <c r="Z88" s="1" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="AA88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="AA88" s="1" t="n">
+      <c r="AB88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -8059,10 +8326,13 @@
         <v>0.01772</v>
       </c>
       <c r="Z89" s="1" t="n">
+        <v>0.01769</v>
+      </c>
+      <c r="AA89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="AA89" s="1" t="n">
-        <v>0.01772</v>
+      <c r="AB89" s="1" t="n">
+        <v>0.01769</v>
       </c>
     </row>
     <row r="90">
@@ -8144,10 +8414,13 @@
         <v>0.03446</v>
       </c>
       <c r="Z90" s="1" t="n">
+        <v>0.03423</v>
+      </c>
+      <c r="AA90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="AA90" s="1" t="n">
-        <v>0.03445</v>
+      <c r="AB90" s="1" t="n">
+        <v>0.03423</v>
       </c>
     </row>
     <row r="91">
@@ -8229,9 +8502,12 @@
         <v>0.01156</v>
       </c>
       <c r="Z91" s="1" t="n">
+        <v>0.01159</v>
+      </c>
+      <c r="AA91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AA91" s="1" t="n">
+      <c r="AB91" s="1" t="n">
         <v>0.01154</v>
       </c>
     </row>
@@ -8314,9 +8590,12 @@
         <v>3.098</v>
       </c>
       <c r="Z92" s="1" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="AA92" s="1" t="n">
+      <c r="AB92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -8399,9 +8678,12 @@
         <v>0.005572</v>
       </c>
       <c r="Z93" s="1" t="n">
+        <v>0.005591</v>
+      </c>
+      <c r="AA93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="AA93" s="1" t="n">
+      <c r="AB93" s="1" t="n">
         <v>0.005559</v>
       </c>
     </row>
@@ -8484,9 +8766,12 @@
         <v>0.094</v>
       </c>
       <c r="Z94" s="1" t="n">
+        <v>0.0939</v>
+      </c>
+      <c r="AA94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="AA94" s="1" t="n">
+      <c r="AB94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -8569,9 +8854,12 @@
         <v>0.6405999999999999</v>
       </c>
       <c r="Z95" s="1" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="AA95" s="1" t="n">
         <v>0.6405999999999999</v>
       </c>
-      <c r="AA95" s="1" t="n">
+      <c r="AB95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -8654,9 +8942,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="Z96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="AA96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="AA96" s="1" t="n">
+      <c r="AB96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -8739,9 +9030,12 @@
         <v>1.105</v>
       </c>
       <c r="Z97" s="1" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="AA97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="AA97" s="1" t="n">
+      <c r="AB97" s="1" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -8824,9 +9118,12 @@
         <v>0.24996</v>
       </c>
       <c r="Z98" s="1" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AA98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="AA98" s="1" t="n">
+      <c r="AB98" s="1" t="n">
         <v>0.24996</v>
       </c>
     </row>
@@ -8909,9 +9206,12 @@
         <v>1.153</v>
       </c>
       <c r="Z99" s="1" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="AA99" s="1" t="n">
         <v>1.157</v>
       </c>
-      <c r="AA99" s="1" t="n">
+      <c r="AB99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -8994,9 +9294,12 @@
         <v>1.86</v>
       </c>
       <c r="Z100" s="1" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="AA100" s="1" t="n">
+      <c r="AB100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -9079,9 +9382,12 @@
         <v>0.01568</v>
       </c>
       <c r="Z101" s="1" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="AA101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="AA101" s="1" t="n">
+      <c r="AB101" s="1" t="n">
         <v>0.01563</v>
       </c>
     </row>
@@ -9164,9 +9470,12 @@
         <v>0.10132</v>
       </c>
       <c r="Z102" s="1" t="n">
+        <v>0.10151</v>
+      </c>
+      <c r="AA102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="AA102" s="1" t="n">
+      <c r="AB102" s="1" t="n">
         <v>0.10062</v>
       </c>
     </row>
@@ -9249,9 +9558,12 @@
         <v>0.0005954000000000001</v>
       </c>
       <c r="Z103" s="1" t="n">
+        <v>0.0005969</v>
+      </c>
+      <c r="AA103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="AA103" s="1" t="n">
+      <c r="AB103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -9334,9 +9646,12 @@
         <v>0.0005717</v>
       </c>
       <c r="Z104" s="1" t="n">
+        <v>0.000572</v>
+      </c>
+      <c r="AA104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="AA104" s="1" t="n">
+      <c r="AB104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -9419,9 +9734,12 @@
         <v>0.003213</v>
       </c>
       <c r="Z105" s="1" t="n">
+        <v>0.003223</v>
+      </c>
+      <c r="AA105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="AA105" s="1" t="n">
+      <c r="AB105" s="1" t="n">
         <v>0.003213</v>
       </c>
     </row>
@@ -9504,9 +9822,12 @@
         <v>2.551</v>
       </c>
       <c r="Z106" s="1" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="AA106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="AA106" s="1" t="n">
+      <c r="AB106" s="1" t="n">
         <v>2.551</v>
       </c>
     </row>
@@ -9589,9 +9910,12 @@
         <v>0.1657</v>
       </c>
       <c r="Z107" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="AA107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="AA107" s="1" t="n">
+      <c r="AB107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -9674,9 +9998,12 @@
         <v>0.09594</v>
       </c>
       <c r="Z108" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="AA108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="AA108" s="1" t="n">
+      <c r="AB108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -9759,9 +10086,12 @@
         <v>0.02208</v>
       </c>
       <c r="Z109" s="1" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="AA109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="AA109" s="1" t="n">
+      <c r="AB109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -9844,9 +10174,12 @@
         <v>0.2859</v>
       </c>
       <c r="Z110" s="1" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AA110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="AA110" s="1" t="n">
+      <c r="AB110" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -9929,9 +10262,12 @@
         <v>0.05701</v>
       </c>
       <c r="Z111" s="1" t="n">
+        <v>0.05698</v>
+      </c>
+      <c r="AA111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="AA111" s="1" t="n">
+      <c r="AB111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -10014,9 +10350,12 @@
         <v>0.3008</v>
       </c>
       <c r="Z112" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AA112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="AA112" s="1" t="n">
+      <c r="AB112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -10099,9 +10438,12 @@
         <v>18.56</v>
       </c>
       <c r="Z113" s="1" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="AA113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="AA113" s="1" t="n">
+      <c r="AB113" s="1" t="n">
         <v>18.52</v>
       </c>
     </row>
@@ -10184,9 +10526,12 @@
         <v>0.12724</v>
       </c>
       <c r="Z114" s="1" t="n">
+        <v>0.12724</v>
+      </c>
+      <c r="AA114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="AA114" s="1" t="n">
+      <c r="AB114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -10269,9 +10614,12 @@
         <v>0.01591</v>
       </c>
       <c r="Z115" s="1" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="AA115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="AA115" s="1" t="n">
+      <c r="AB115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -10354,9 +10702,12 @@
         <v>0.08466</v>
       </c>
       <c r="Z116" s="1" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="AA116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="AA116" s="1" t="n">
+      <c r="AB116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -10439,10 +10790,13 @@
         <v>0.046288</v>
       </c>
       <c r="Z117" s="1" t="n">
+        <v>0.046106</v>
+      </c>
+      <c r="AA117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="AA117" s="1" t="n">
-        <v>0.046288</v>
+      <c r="AB117" s="1" t="n">
+        <v>0.046106</v>
       </c>
     </row>
     <row r="118">
@@ -10524,9 +10878,12 @@
         <v>0.04708</v>
       </c>
       <c r="Z118" s="1" t="n">
+        <v>0.04716</v>
+      </c>
+      <c r="AA118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="AA118" s="1" t="n">
+      <c r="AB118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -10609,9 +10966,12 @@
         <v>0.03993</v>
       </c>
       <c r="Z119" s="1" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AA119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="AA119" s="1" t="n">
+      <c r="AB119" s="1" t="n">
         <v>0.03993</v>
       </c>
     </row>
@@ -10694,9 +11054,12 @@
         <v>0.14519</v>
       </c>
       <c r="Z120" s="1" t="n">
+        <v>0.14525</v>
+      </c>
+      <c r="AA120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="AA120" s="1" t="n">
+      <c r="AB120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -10779,9 +11142,12 @@
         <v>0.1243</v>
       </c>
       <c r="Z121" s="1" t="n">
+        <v>0.1243</v>
+      </c>
+      <c r="AA121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="AA121" s="1" t="n">
+      <c r="AB121" s="1" t="n">
         <v>0.1243</v>
       </c>
     </row>
@@ -10864,9 +11230,12 @@
         <v>1.834</v>
       </c>
       <c r="Z122" s="1" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="AA122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="AA122" s="1" t="n">
+      <c r="AB122" s="1" t="n">
         <v>1.831</v>
       </c>
     </row>
@@ -10949,9 +11318,12 @@
         <v>0.03006</v>
       </c>
       <c r="Z123" s="1" t="n">
+        <v>0.03003</v>
+      </c>
+      <c r="AA123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="AA123" s="1" t="n">
+      <c r="AB123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -11034,9 +11406,12 @@
         <v>0.13176</v>
       </c>
       <c r="Z124" s="1" t="n">
+        <v>0.13192</v>
+      </c>
+      <c r="AA124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="AA124" s="1" t="n">
+      <c r="AB124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -11119,9 +11494,12 @@
         <v>0.04091</v>
       </c>
       <c r="Z125" s="1" t="n">
+        <v>0.04081</v>
+      </c>
+      <c r="AA125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="AA125" s="1" t="n">
+      <c r="AB125" s="1" t="n">
         <v>0.04075</v>
       </c>
     </row>
@@ -11204,9 +11582,12 @@
         <v>0.1143</v>
       </c>
       <c r="Z126" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AA126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="AA126" s="1" t="n">
+      <c r="AB126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -11289,9 +11670,12 @@
         <v>0.5426</v>
       </c>
       <c r="Z127" s="1" t="n">
-        <v>0.5426</v>
+        <v>0.5446</v>
       </c>
       <c r="AA127" s="1" t="n">
+        <v>0.5446</v>
+      </c>
+      <c r="AB127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -11374,9 +11758,12 @@
         <v>0.03823</v>
       </c>
       <c r="Z128" s="1" t="n">
+        <v>0.03811</v>
+      </c>
+      <c r="AA128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="AA128" s="1" t="n">
+      <c r="AB128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -11459,9 +11846,12 @@
         <v>0.794</v>
       </c>
       <c r="Z129" s="1" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="AA129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="AA129" s="1" t="n">
+      <c r="AB129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -11544,9 +11934,12 @@
         <v>0.03426</v>
       </c>
       <c r="Z130" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="AA130" s="1" t="n">
         <v>0.03463</v>
       </c>
-      <c r="AA130" s="1" t="n">
+      <c r="AB130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -11629,9 +12022,12 @@
         <v>0.4266</v>
       </c>
       <c r="Z131" s="1" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="AA131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="AA131" s="1" t="n">
+      <c r="AB131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -11714,9 +12110,12 @@
         <v>0.04296</v>
       </c>
       <c r="Z132" s="1" t="n">
+        <v>0.04309</v>
+      </c>
+      <c r="AA132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="AA132" s="1" t="n">
+      <c r="AB132" s="1" t="n">
         <v>0.04296</v>
       </c>
     </row>
@@ -11799,9 +12198,12 @@
         <v>1.2827</v>
       </c>
       <c r="Z133" s="1" t="n">
+        <v>1.2826</v>
+      </c>
+      <c r="AA133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="AA133" s="1" t="n">
+      <c r="AB133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -11884,9 +12286,12 @@
         <v>0.02179</v>
       </c>
       <c r="Z134" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="AA134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="AA134" s="1" t="n">
+      <c r="AB134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -11969,9 +12374,12 @@
         <v>0.0004569</v>
       </c>
       <c r="Z135" s="1" t="n">
+        <v>0.0004562</v>
+      </c>
+      <c r="AA135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="AA135" s="1" t="n">
+      <c r="AB135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -12054,9 +12462,12 @@
         <v>0.001897</v>
       </c>
       <c r="Z136" s="1" t="n">
+        <v>0.001886</v>
+      </c>
+      <c r="AA136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="AA136" s="1" t="n">
+      <c r="AB136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -12139,10 +12550,13 @@
         <v>0.314</v>
       </c>
       <c r="Z137" s="1" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AA137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="AA137" s="1" t="n">
-        <v>0.3136</v>
+      <c r="AB137" s="1" t="n">
+        <v>0.3132</v>
       </c>
     </row>
     <row r="138">
@@ -12224,10 +12638,13 @@
         <v>0.5581</v>
       </c>
       <c r="Z138" s="1" t="n">
+        <v>0.5578</v>
+      </c>
+      <c r="AA138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="AA138" s="1" t="n">
-        <v>0.5581</v>
+      <c r="AB138" s="1" t="n">
+        <v>0.5578</v>
       </c>
     </row>
     <row r="139">
@@ -12309,9 +12726,12 @@
         <v>0.02115</v>
       </c>
       <c r="Z139" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="AA139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="AA139" s="1" t="n">
+      <c r="AB139" s="1" t="n">
         <v>0.02115</v>
       </c>
     </row>
@@ -12394,9 +12814,12 @@
         <v>0.07929</v>
       </c>
       <c r="Z140" s="1" t="n">
+        <v>0.07931000000000001</v>
+      </c>
+      <c r="AA140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="AA140" s="1" t="n">
+      <c r="AB140" s="1" t="n">
         <v>0.07929</v>
       </c>
     </row>
@@ -12479,9 +12902,12 @@
         <v>0.001523</v>
       </c>
       <c r="Z141" s="1" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="AA141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="AA141" s="1" t="n">
+      <c r="AB141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -12564,9 +12990,12 @@
         <v>0.4444</v>
       </c>
       <c r="Z142" s="1" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="AA142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="AA142" s="1" t="n">
+      <c r="AB142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -12649,10 +13078,13 @@
         <v>0.029951</v>
       </c>
       <c r="Z143" s="1" t="n">
+        <v>0.029754</v>
+      </c>
+      <c r="AA143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="AA143" s="1" t="n">
-        <v>0.029881</v>
+      <c r="AB143" s="1" t="n">
+        <v>0.029754</v>
       </c>
     </row>
     <row r="144">
@@ -12734,9 +13166,12 @@
         <v>0.000226</v>
       </c>
       <c r="Z144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="AA144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="AA144" s="1" t="n">
+      <c r="AB144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -12819,9 +13254,12 @@
         <v>0.03514</v>
       </c>
       <c r="Z145" s="1" t="n">
+        <v>0.03481</v>
+      </c>
+      <c r="AA145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="AA145" s="1" t="n">
+      <c r="AB145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -12904,9 +13342,12 @@
         <v>0.11682</v>
       </c>
       <c r="Z146" s="1" t="n">
-        <v>0.11718</v>
+        <v>0.11778</v>
       </c>
       <c r="AA146" s="1" t="n">
+        <v>0.11778</v>
+      </c>
+      <c r="AB146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -12989,9 +13430,12 @@
         <v>0.02214</v>
       </c>
       <c r="Z147" s="1" t="n">
+        <v>0.02216</v>
+      </c>
+      <c r="AA147" s="1" t="n">
         <v>0.02258</v>
       </c>
-      <c r="AA147" s="1" t="n">
+      <c r="AB147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -13074,9 +13518,12 @@
         <v>1.4118</v>
       </c>
       <c r="Z148" s="1" t="n">
+        <v>1.4123</v>
+      </c>
+      <c r="AA148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="AA148" s="1" t="n">
+      <c r="AB148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -13159,10 +13606,13 @@
         <v>1.8541</v>
       </c>
       <c r="Z149" s="1" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="AA149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="AA149" s="1" t="n">
-        <v>1.8541</v>
+      <c r="AB149" s="1" t="n">
+        <v>1.854</v>
       </c>
     </row>
     <row r="150">
@@ -13244,9 +13694,12 @@
         <v>0.096</v>
       </c>
       <c r="Z150" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AA150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="AA150" s="1" t="n">
+      <c r="AB150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -13329,9 +13782,12 @@
         <v>4.623</v>
       </c>
       <c r="Z151" s="1" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA151" s="1" t="n">
         <v>4.731</v>
       </c>
-      <c r="AA151" s="1" t="n">
+      <c r="AB151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -13414,9 +13870,12 @@
         <v>5.53</v>
       </c>
       <c r="Z152" s="1" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="AA152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="AA152" s="1" t="n">
+      <c r="AB152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -13499,9 +13958,12 @@
         <v>0.3216</v>
       </c>
       <c r="Z153" s="1" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AA153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="AA153" s="1" t="n">
+      <c r="AB153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -13584,9 +14046,12 @@
         <v>0.5833</v>
       </c>
       <c r="Z154" s="1" t="n">
+        <v>0.5845</v>
+      </c>
+      <c r="AA154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="AA154" s="1" t="n">
+      <c r="AB154" s="1" t="n">
         <v>0.5825</v>
       </c>
     </row>
@@ -13669,9 +14134,12 @@
         <v>0.01266</v>
       </c>
       <c r="Z155" s="1" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="AA155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="AA155" s="1" t="n">
+      <c r="AB155" s="1" t="n">
         <v>0.01266</v>
       </c>
     </row>
@@ -13754,10 +14222,13 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="Z156" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AA156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="AA156" s="1" t="n">
-        <v>0.09710000000000001</v>
+      <c r="AB156" s="1" t="n">
+        <v>0.097</v>
       </c>
     </row>
     <row r="157">
@@ -13839,9 +14310,12 @@
         <v>16.35</v>
       </c>
       <c r="Z157" s="1" t="n">
+        <v>16.345</v>
+      </c>
+      <c r="AA157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="AA157" s="1" t="n">
+      <c r="AB157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -13924,9 +14398,12 @@
         <v>0.0551</v>
       </c>
       <c r="Z158" s="1" t="n">
+        <v>0.05532</v>
+      </c>
+      <c r="AA158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="AA158" s="1" t="n">
+      <c r="AB158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -14009,9 +14486,12 @@
         <v>28.57</v>
       </c>
       <c r="Z159" s="1" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="AA159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="AA159" s="1" t="n">
+      <c r="AB159" s="1" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -14094,9 +14574,12 @@
         <v>0.02162</v>
       </c>
       <c r="Z160" s="1" t="n">
-        <v>0.02166</v>
+        <v>0.0218</v>
       </c>
       <c r="AA160" s="1" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="AB160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -14179,9 +14662,12 @@
         <v>0.0006505</v>
       </c>
       <c r="Z161" s="1" t="n">
+        <v>0.0006522</v>
+      </c>
+      <c r="AA161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="AA161" s="1" t="n">
+      <c r="AB161" s="1" t="n">
         <v>0.0006503</v>
       </c>
     </row>
@@ -14264,9 +14750,12 @@
         <v>0.3898</v>
       </c>
       <c r="Z162" s="1" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AA162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="AA162" s="1" t="n">
+      <c r="AB162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -14349,9 +14838,12 @@
         <v>0.1903</v>
       </c>
       <c r="Z163" s="1" t="n">
+        <v>0.1904</v>
+      </c>
+      <c r="AA163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="AA163" s="1" t="n">
+      <c r="AB163" s="1" t="n">
         <v>0.1903</v>
       </c>
     </row>
@@ -14434,9 +14926,12 @@
         <v>0.314</v>
       </c>
       <c r="Z164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AA164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="AA164" s="1" t="n">
+      <c r="AB164" s="1" t="n">
         <v>0.314</v>
       </c>
     </row>
@@ -14519,9 +15014,12 @@
         <v>0.376</v>
       </c>
       <c r="Z165" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AA165" s="1" t="n">
         <v>0.378</v>
       </c>
-      <c r="AA165" s="1" t="n">
+      <c r="AB165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -14604,9 +15102,12 @@
         <v>0.02249</v>
       </c>
       <c r="Z166" s="1" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="AA166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="AA166" s="1" t="n">
+      <c r="AB166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -14689,9 +15190,12 @@
         <v>0.007258</v>
       </c>
       <c r="Z167" s="1" t="n">
+        <v>0.00726</v>
+      </c>
+      <c r="AA167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="AA167" s="1" t="n">
+      <c r="AB167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -14774,9 +15278,12 @@
         <v>0.01324</v>
       </c>
       <c r="Z168" s="1" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AA168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="AA168" s="1" t="n">
+      <c r="AB168" s="1" t="n">
         <v>0.01324</v>
       </c>
     </row>
@@ -14859,9 +15366,12 @@
         <v>0.25576</v>
       </c>
       <c r="Z169" s="1" t="n">
+        <v>0.25558</v>
+      </c>
+      <c r="AA169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="AA169" s="1" t="n">
+      <c r="AB169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -14944,9 +15454,12 @@
         <v>0.02201</v>
       </c>
       <c r="Z170" s="1" t="n">
-        <v>0.02201</v>
+        <v>0.0221</v>
       </c>
       <c r="AA170" s="1" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="AB170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -15029,9 +15542,12 @@
         <v>0.1709</v>
       </c>
       <c r="Z171" s="1" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="AA171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="AA171" s="1" t="n">
+      <c r="AB171" s="1" t="n">
         <v>0.1708</v>
       </c>
     </row>
@@ -15114,9 +15630,12 @@
         <v>0.09</v>
       </c>
       <c r="Z172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AA172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="AA172" s="1" t="n">
+      <c r="AB172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -15199,9 +15718,12 @@
         <v>0.004665</v>
       </c>
       <c r="Z173" s="1" t="n">
+        <v>0.004681</v>
+      </c>
+      <c r="AA173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="AA173" s="1" t="n">
+      <c r="AB173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -15284,9 +15806,12 @@
         <v>0.4419</v>
       </c>
       <c r="Z174" s="1" t="n">
-        <v>0.4423</v>
+        <v>0.4428</v>
       </c>
       <c r="AA174" s="1" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="AB174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -15369,9 +15894,12 @@
         <v>0.09165</v>
       </c>
       <c r="Z175" s="1" t="n">
+        <v>0.09235</v>
+      </c>
+      <c r="AA175" s="1" t="n">
         <v>0.09276</v>
       </c>
-      <c r="AA175" s="1" t="n">
+      <c r="AB175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -15454,9 +15982,12 @@
         <v>0.2425</v>
       </c>
       <c r="Z176" s="1" t="n">
+        <v>0.2427</v>
+      </c>
+      <c r="AA176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="AA176" s="1" t="n">
+      <c r="AB176" s="1" t="n">
         <v>0.2425</v>
       </c>
     </row>
@@ -15539,9 +16070,12 @@
         <v>0.01922</v>
       </c>
       <c r="Z177" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AA177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="AA177" s="1" t="n">
+      <c r="AB177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -15624,9 +16158,12 @@
         <v>6.09</v>
       </c>
       <c r="Z178" s="1" t="n">
+        <v>6.095</v>
+      </c>
+      <c r="AA178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="AA178" s="1" t="n">
+      <c r="AB178" s="1" t="n">
         <v>6.09</v>
       </c>
     </row>
@@ -15709,9 +16246,12 @@
         <v>0.1361</v>
       </c>
       <c r="Z179" s="1" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="AA179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="AA179" s="1" t="n">
+      <c r="AB179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -15794,9 +16334,12 @@
         <v>0.004959</v>
       </c>
       <c r="Z180" s="1" t="n">
+        <v>0.004973</v>
+      </c>
+      <c r="AA180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="AA180" s="1" t="n">
+      <c r="AB180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -15879,9 +16422,12 @@
         <v>0.01187</v>
       </c>
       <c r="Z181" s="1" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="AA181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AA181" s="1" t="n">
+      <c r="AB181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -15964,9 +16510,12 @@
         <v>0.007212</v>
       </c>
       <c r="Z182" s="1" t="n">
+        <v>0.007244</v>
+      </c>
+      <c r="AA182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="AA182" s="1" t="n">
+      <c r="AB182" s="1" t="n">
         <v>0.007212</v>
       </c>
     </row>
@@ -16049,9 +16598,12 @@
         <v>0.13145</v>
       </c>
       <c r="Z183" s="1" t="n">
+        <v>0.13141</v>
+      </c>
+      <c r="AA183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="AA183" s="1" t="n">
+      <c r="AB183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -16134,9 +16686,12 @@
         <v>0.09562</v>
       </c>
       <c r="Z184" s="1" t="n">
+        <v>0.09626</v>
+      </c>
+      <c r="AA184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="AA184" s="1" t="n">
+      <c r="AB184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -16219,9 +16774,12 @@
         <v>0.00754</v>
       </c>
       <c r="Z185" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="AA185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="AA185" s="1" t="n">
+      <c r="AB185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -16304,9 +16862,12 @@
         <v>0.04848</v>
       </c>
       <c r="Z186" s="1" t="n">
+        <v>0.04851</v>
+      </c>
+      <c r="AA186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="AA186" s="1" t="n">
+      <c r="AB186" s="1" t="n">
         <v>0.04848</v>
       </c>
     </row>
@@ -16389,9 +16950,12 @@
         <v>0.02663</v>
       </c>
       <c r="Z187" s="1" t="n">
+        <v>0.02661</v>
+      </c>
+      <c r="AA187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="AA187" s="1" t="n">
+      <c r="AB187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -16474,9 +17038,12 @@
         <v>0.003262</v>
       </c>
       <c r="Z188" s="1" t="n">
+        <v>0.003269</v>
+      </c>
+      <c r="AA188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="AA188" s="1" t="n">
+      <c r="AB188" s="1" t="n">
         <v>0.003262</v>
       </c>
     </row>
@@ -16559,9 +17126,12 @@
         <v>0.2842</v>
       </c>
       <c r="Z189" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AA189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="AA189" s="1" t="n">
+      <c r="AB189" s="1" t="n">
         <v>0.2842</v>
       </c>
     </row>
@@ -16644,9 +17214,12 @@
         <v>0.01763</v>
       </c>
       <c r="Z190" s="1" t="n">
+        <v>0.01766</v>
+      </c>
+      <c r="AA190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AA190" s="1" t="n">
+      <c r="AB190" s="1" t="n">
         <v>0.01763</v>
       </c>
     </row>
@@ -16729,9 +17302,12 @@
         <v>0.2569</v>
       </c>
       <c r="Z191" s="1" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="AA191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="AA191" s="1" t="n">
+      <c r="AB191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -16814,9 +17390,12 @@
         <v>0.03707</v>
       </c>
       <c r="Z192" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="AA192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="AA192" s="1" t="n">
+      <c r="AB192" s="1" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -16899,9 +17478,12 @@
         <v>0.0002207</v>
       </c>
       <c r="Z193" s="1" t="n">
+        <v>0.000221</v>
+      </c>
+      <c r="AA193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="AA193" s="1" t="n">
+      <c r="AB193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -16984,9 +17566,12 @@
         <v>4.066</v>
       </c>
       <c r="Z194" s="1" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="AA194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="AA194" s="1" t="n">
+      <c r="AB194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -17072,6 +17657,9 @@
         <v>0.999401</v>
       </c>
       <c r="AA195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="AB195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -17154,9 +17742,12 @@
         <v>4.323</v>
       </c>
       <c r="Z196" s="1" t="n">
+        <v>4.336</v>
+      </c>
+      <c r="AA196" s="1" t="n">
         <v>4.368</v>
       </c>
-      <c r="AA196" s="1" t="n">
+      <c r="AB196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -17239,9 +17830,12 @@
         <v>0.15127</v>
       </c>
       <c r="Z197" s="1" t="n">
+        <v>0.15141</v>
+      </c>
+      <c r="AA197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="AA197" s="1" t="n">
+      <c r="AB197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -17324,9 +17918,12 @@
         <v>0.007998999999999999</v>
       </c>
       <c r="Z198" s="1" t="n">
+        <v>0.007884</v>
+      </c>
+      <c r="AA198" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="AA198" s="1" t="n">
+      <c r="AB198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -17409,9 +18006,12 @@
         <v>0.4512</v>
       </c>
       <c r="Z199" s="1" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="AA199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="AA199" s="1" t="n">
+      <c r="AB199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -17494,9 +18094,12 @@
         <v>0.5724</v>
       </c>
       <c r="Z200" s="1" t="n">
+        <v>0.5786</v>
+      </c>
+      <c r="AA200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="AA200" s="1" t="n">
+      <c r="AB200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -17579,9 +18182,12 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="Z201" s="1" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="AA201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="AA201" s="1" t="n">
+      <c r="AB201" s="1" t="n">
         <v>0.09229999999999999</v>
       </c>
     </row>
@@ -17664,9 +18270,12 @@
         <v>0.06022</v>
       </c>
       <c r="Z202" s="1" t="n">
+        <v>0.06021</v>
+      </c>
+      <c r="AA202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="AA202" s="1" t="n">
+      <c r="AB202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -17749,9 +18358,12 @@
         <v>0.00822</v>
       </c>
       <c r="Z203" s="1" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="AA203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="AA203" s="1" t="n">
+      <c r="AB203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -17834,9 +18446,12 @@
         <v>0.00411</v>
       </c>
       <c r="Z204" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="AA204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="AA204" s="1" t="n">
+      <c r="AB204" s="1" t="n">
         <v>0.00411</v>
       </c>
     </row>
@@ -17919,9 +18534,12 @@
         <v>0.009008</v>
       </c>
       <c r="Z205" s="1" t="n">
+        <v>0.009037</v>
+      </c>
+      <c r="AA205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="AA205" s="1" t="n">
+      <c r="AB205" s="1" t="n">
         <v>0.009008</v>
       </c>
     </row>
@@ -18004,9 +18622,12 @@
         <v>0.2402</v>
       </c>
       <c r="Z206" s="1" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="AA206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="AA206" s="1" t="n">
+      <c r="AB206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -18089,9 +18710,12 @@
         <v>0.02102</v>
       </c>
       <c r="Z207" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="AA207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="AA207" s="1" t="n">
+      <c r="AB207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -18174,9 +18798,12 @@
         <v>0.237</v>
       </c>
       <c r="Z208" s="1" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="AA208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="AA208" s="1" t="n">
+      <c r="AB208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -18259,10 +18886,13 @@
         <v>0.3568</v>
       </c>
       <c r="Z209" s="1" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AA209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="AA209" s="1" t="n">
-        <v>0.3568</v>
+      <c r="AB209" s="1" t="n">
+        <v>0.3566</v>
       </c>
     </row>
     <row r="210">
@@ -18344,9 +18974,12 @@
         <v>0.04278</v>
       </c>
       <c r="Z210" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="AA210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="AA210" s="1" t="n">
+      <c r="AB210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -18429,10 +19062,13 @@
         <v>0.0004217</v>
       </c>
       <c r="Z211" s="1" t="n">
+        <v>0.0004215</v>
+      </c>
+      <c r="AA211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="AA211" s="1" t="n">
-        <v>0.0004217</v>
+      <c r="AB211" s="1" t="n">
+        <v>0.0004215</v>
       </c>
     </row>
     <row r="212">
@@ -18514,9 +19150,12 @@
         <v>0.02126</v>
       </c>
       <c r="Z212" s="1" t="n">
+        <v>0.02132</v>
+      </c>
+      <c r="AA212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="AA212" s="1" t="n">
+      <c r="AB212" s="1" t="n">
         <v>0.02122</v>
       </c>
     </row>
@@ -18599,9 +19238,12 @@
         <v>0.1144</v>
       </c>
       <c r="Z213" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="AA213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="AA213" s="1" t="n">
+      <c r="AB213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -18684,9 +19326,12 @@
         <v>0.0423</v>
       </c>
       <c r="Z214" s="1" t="n">
-        <v>0.04232</v>
+        <v>0.04242</v>
       </c>
       <c r="AA214" s="1" t="n">
+        <v>0.04242</v>
+      </c>
+      <c r="AB214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -18769,9 +19414,12 @@
         <v>0.009677</v>
       </c>
       <c r="Z215" s="1" t="n">
+        <v>0.009689</v>
+      </c>
+      <c r="AA215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="AA215" s="1" t="n">
+      <c r="AB215" s="1" t="n">
         <v>0.009677</v>
       </c>
     </row>
@@ -18854,9 +19502,12 @@
         <v>0.0638</v>
       </c>
       <c r="Z216" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AA216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="AA216" s="1" t="n">
+      <c r="AB216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -18939,9 +19590,12 @@
         <v>0.004138</v>
       </c>
       <c r="Z217" s="1" t="n">
+        <v>0.004144</v>
+      </c>
+      <c r="AA217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="AA217" s="1" t="n">
+      <c r="AB217" s="1" t="n">
         <v>0.004138</v>
       </c>
     </row>
@@ -19024,9 +19678,12 @@
         <v>0.00979</v>
       </c>
       <c r="Z218" s="1" t="n">
+        <v>0.00979</v>
+      </c>
+      <c r="AA218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="AA218" s="1" t="n">
+      <c r="AB218" s="1" t="n">
         <v>0.00979</v>
       </c>
     </row>
@@ -19109,10 +19766,13 @@
         <v>0.02917</v>
       </c>
       <c r="Z219" s="1" t="n">
+        <v>0.02916</v>
+      </c>
+      <c r="AA219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="AA219" s="1" t="n">
-        <v>0.02917</v>
+      <c r="AB219" s="1" t="n">
+        <v>0.02916</v>
       </c>
     </row>
     <row r="220">
@@ -19194,9 +19854,12 @@
         <v>2.284</v>
       </c>
       <c r="Z220" s="1" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="AA220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="AA220" s="1" t="n">
+      <c r="AB220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -19279,9 +19942,12 @@
         <v>0.022427</v>
       </c>
       <c r="Z221" s="1" t="n">
+        <v>0.022493</v>
+      </c>
+      <c r="AA221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="AA221" s="1" t="n">
+      <c r="AB221" s="1" t="n">
         <v>0.022427</v>
       </c>
     </row>
@@ -19364,9 +20030,12 @@
         <v>0.0367</v>
       </c>
       <c r="Z222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="AA222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="AA222" s="1" t="n">
+      <c r="AB222" s="1" t="n">
         <v>0.0367</v>
       </c>
     </row>
@@ -19449,9 +20118,12 @@
         <v>0.2918</v>
       </c>
       <c r="Z223" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AA223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="AA223" s="1" t="n">
+      <c r="AB223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -19534,9 +20206,12 @@
         <v>0.01575</v>
       </c>
       <c r="Z224" s="1" t="n">
-        <v>0.01582</v>
+        <v>0.01583</v>
       </c>
       <c r="AA224" s="1" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="AB224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -19619,9 +20294,12 @@
         <v>0.0004017</v>
       </c>
       <c r="Z225" s="1" t="n">
+        <v>0.0004018</v>
+      </c>
+      <c r="AA225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="AA225" s="1" t="n">
+      <c r="AB225" s="1" t="n">
         <v>0.0004017</v>
       </c>
     </row>
@@ -19704,9 +20382,12 @@
         <v>0.08468000000000001</v>
       </c>
       <c r="Z226" s="1" t="n">
+        <v>0.08492</v>
+      </c>
+      <c r="AA226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="AA226" s="1" t="n">
+      <c r="AB226" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
     </row>
@@ -19789,9 +20470,12 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="Z227" s="1" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AA227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="AA227" s="1" t="n">
+      <c r="AB227" s="1" t="n">
         <v>0.9429999999999999</v>
       </c>
     </row>
@@ -19874,9 +20558,12 @@
         <v>0.0553</v>
       </c>
       <c r="Z228" s="1" t="n">
+        <v>0.05555</v>
+      </c>
+      <c r="AA228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="AA228" s="1" t="n">
+      <c r="AB228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -19959,9 +20646,12 @@
         <v>0.002001</v>
       </c>
       <c r="Z229" s="1" t="n">
+        <v>0.002001</v>
+      </c>
+      <c r="AA229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="AA229" s="1" t="n">
+      <c r="AB229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -20044,10 +20734,13 @@
         <v>0.0227</v>
       </c>
       <c r="Z230" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="AA230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="AA230" s="1" t="n">
-        <v>0.022659</v>
+      <c r="AB230" s="1" t="n">
+        <v>0.02265</v>
       </c>
     </row>
     <row r="231">
@@ -20129,10 +20822,13 @@
         <v>0.0532</v>
       </c>
       <c r="Z231" s="1" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="AA231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="AA231" s="1" t="n">
-        <v>0.0532</v>
+      <c r="AB231" s="1" t="n">
+        <v>0.05316</v>
       </c>
     </row>
     <row r="232">
@@ -20214,9 +20910,12 @@
         <v>0.0582</v>
       </c>
       <c r="Z232" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="AA232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="AA232" s="1" t="n">
+      <c r="AB232" s="1" t="n">
         <v>0.0582</v>
       </c>
     </row>
@@ -20299,9 +20998,12 @@
         <v>0.00171</v>
       </c>
       <c r="Z233" s="1" t="n">
+        <v>0.001714</v>
+      </c>
+      <c r="AA233" s="1" t="n">
         <v>0.001728</v>
       </c>
-      <c r="AA233" s="1" t="n">
+      <c r="AB233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -20384,9 +21086,12 @@
         <v>0.005749</v>
       </c>
       <c r="Z234" s="1" t="n">
+        <v>0.005741</v>
+      </c>
+      <c r="AA234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="AA234" s="1" t="n">
+      <c r="AB234" s="1" t="n">
         <v>0.005718</v>
       </c>
     </row>
@@ -20469,10 +21174,13 @@
         <v>0.122</v>
       </c>
       <c r="Z235" s="1" t="n">
+        <v>0.12179</v>
+      </c>
+      <c r="AA235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="AA235" s="1" t="n">
-        <v>0.122</v>
+      <c r="AB235" s="1" t="n">
+        <v>0.12179</v>
       </c>
     </row>
     <row r="236">
@@ -20554,9 +21262,12 @@
         <v>64.66</v>
       </c>
       <c r="Z236" s="1" t="n">
+        <v>64.76000000000001</v>
+      </c>
+      <c r="AA236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="AA236" s="1" t="n">
+      <c r="AB236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -20639,9 +21350,12 @@
         <v>0.0997</v>
       </c>
       <c r="Z237" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AA237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="AA237" s="1" t="n">
+      <c r="AB237" s="1" t="n">
         <v>0.0997</v>
       </c>
     </row>
@@ -20724,9 +21438,12 @@
         <v>0.003924</v>
       </c>
       <c r="Z238" s="1" t="n">
+        <v>0.003929</v>
+      </c>
+      <c r="AA238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="AA238" s="1" t="n">
+      <c r="AB238" s="1" t="n">
         <v>0.003924</v>
       </c>
     </row>
@@ -20809,9 +21526,12 @@
         <v>0.01506</v>
       </c>
       <c r="Z239" s="1" t="n">
+        <v>0.01511</v>
+      </c>
+      <c r="AA239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="AA239" s="1" t="n">
+      <c r="AB239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -20894,9 +21614,12 @@
         <v>0.0558</v>
       </c>
       <c r="Z240" s="1" t="n">
+        <v>0.05591</v>
+      </c>
+      <c r="AA240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="AA240" s="1" t="n">
+      <c r="AB240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -20979,9 +21702,12 @@
         <v>0.0115</v>
       </c>
       <c r="Z241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AA241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="AA241" s="1" t="n">
+      <c r="AB241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -21064,9 +21790,12 @@
         <v>0.333</v>
       </c>
       <c r="Z242" s="1" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AA242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="AA242" s="1" t="n">
+      <c r="AB242" s="1" t="n">
         <v>0.3321</v>
       </c>
     </row>
@@ -21149,9 +21878,12 @@
         <v>0.01227</v>
       </c>
       <c r="Z243" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="AA243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="AA243" s="1" t="n">
+      <c r="AB243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -21234,9 +21966,12 @@
         <v>0.08117000000000001</v>
       </c>
       <c r="Z244" s="1" t="n">
+        <v>0.08118</v>
+      </c>
+      <c r="AA244" s="1" t="n">
         <v>0.08162999999999999</v>
       </c>
-      <c r="AA244" s="1" t="n">
+      <c r="AB244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -21319,9 +22054,12 @@
         <v>0.007844</v>
       </c>
       <c r="Z245" s="1" t="n">
+        <v>0.007867000000000001</v>
+      </c>
+      <c r="AA245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="AA245" s="1" t="n">
+      <c r="AB245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -21404,9 +22142,12 @@
         <v>0.03031</v>
       </c>
       <c r="Z246" s="1" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="AA246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="AA246" s="1" t="n">
+      <c r="AB246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -21489,9 +22230,12 @@
         <v>0.1799</v>
       </c>
       <c r="Z247" s="1" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="AA247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="AA247" s="1" t="n">
+      <c r="AB247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -21574,9 +22318,12 @@
         <v>0.05895</v>
       </c>
       <c r="Z248" s="1" t="n">
+        <v>0.05879</v>
+      </c>
+      <c r="AA248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="AA248" s="1" t="n">
+      <c r="AB248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -21659,9 +22406,12 @@
         <v>0.1646</v>
       </c>
       <c r="Z249" s="1" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="AA249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="AA249" s="1" t="n">
+      <c r="AB249" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -21744,9 +22494,12 @@
         <v>0.01881</v>
       </c>
       <c r="Z250" s="1" t="n">
+        <v>0.01883</v>
+      </c>
+      <c r="AA250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="AA250" s="1" t="n">
+      <c r="AB250" s="1" t="n">
         <v>0.01881</v>
       </c>
     </row>
@@ -21829,9 +22582,12 @@
         <v>0.02313</v>
       </c>
       <c r="Z251" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="AA251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="AA251" s="1" t="n">
+      <c r="AB251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -21914,9 +22670,12 @@
         <v>0.30499</v>
       </c>
       <c r="Z252" s="1" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AA252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="AA252" s="1" t="n">
+      <c r="AB252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -21999,9 +22758,12 @@
         <v>0.005941</v>
       </c>
       <c r="Z253" s="1" t="n">
+        <v>0.005941</v>
+      </c>
+      <c r="AA253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="AA253" s="1" t="n">
+      <c r="AB253" s="1" t="n">
         <v>0.005941</v>
       </c>
     </row>
@@ -22084,9 +22846,12 @@
         <v>0.6128</v>
       </c>
       <c r="Z254" s="1" t="n">
+        <v>0.6126</v>
+      </c>
+      <c r="AA254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="AA254" s="1" t="n">
+      <c r="AB254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -22169,9 +22934,12 @@
         <v>0.10545</v>
       </c>
       <c r="Z255" s="1" t="n">
+        <v>0.10576</v>
+      </c>
+      <c r="AA255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="AA255" s="1" t="n">
+      <c r="AB255" s="1" t="n">
         <v>0.10545</v>
       </c>
     </row>
@@ -22254,9 +23022,12 @@
         <v>0.0898</v>
       </c>
       <c r="Z256" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AA256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="AA256" s="1" t="n">
+      <c r="AB256" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -22339,9 +23110,12 @@
         <v>0.01491</v>
       </c>
       <c r="Z257" s="1" t="n">
+        <v>0.01506</v>
+      </c>
+      <c r="AA257" s="1" t="n">
         <v>0.01518</v>
       </c>
-      <c r="AA257" s="1" t="n">
+      <c r="AB257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -22424,9 +23198,12 @@
         <v>0.04938</v>
       </c>
       <c r="Z258" s="1" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="AA258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="AA258" s="1" t="n">
+      <c r="AB258" s="1" t="n">
         <v>0.04938</v>
       </c>
     </row>
@@ -22509,10 +23286,13 @@
         <v>0.007860000000000001</v>
       </c>
       <c r="Z259" s="1" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="AA259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="AA259" s="1" t="n">
-        <v>0.007860000000000001</v>
+      <c r="AB259" s="1" t="n">
+        <v>0.00784</v>
       </c>
     </row>
     <row r="260">
@@ -22594,9 +23374,12 @@
         <v>0.1893</v>
       </c>
       <c r="Z260" s="1" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="AA260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="AA260" s="1" t="n">
+      <c r="AB260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -22679,9 +23462,12 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="Z261" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="AA261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="AA261" s="1" t="n">
+      <c r="AB261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -22764,9 +23550,12 @@
         <v>0.2108</v>
       </c>
       <c r="Z262" s="1" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="AA262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="AA262" s="1" t="n">
+      <c r="AB262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -22849,9 +23638,12 @@
         <v>0.008548999999999999</v>
       </c>
       <c r="Z263" s="1" t="n">
+        <v>0.008597</v>
+      </c>
+      <c r="AA263" s="1" t="n">
         <v>0.008616</v>
       </c>
-      <c r="AA263" s="1" t="n">
+      <c r="AB263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -22934,9 +23726,12 @@
         <v>2.617</v>
       </c>
       <c r="Z264" s="1" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="AA264" s="1" t="n">
+      <c r="AB264" s="1" t="n">
         <v>2.616</v>
       </c>
     </row>
@@ -23019,9 +23814,12 @@
         <v>0.01845</v>
       </c>
       <c r="Z265" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="AA265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="AA265" s="1" t="n">
+      <c r="AB265" s="1" t="n">
         <v>0.01845</v>
       </c>
     </row>
@@ -23104,9 +23902,12 @@
         <v>0.3613</v>
       </c>
       <c r="Z266" s="1" t="n">
-        <v>0.3617</v>
+        <v>0.3619</v>
       </c>
       <c r="AA266" s="1" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AB266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -23189,9 +23990,12 @@
         <v>0.03439</v>
       </c>
       <c r="Z267" s="1" t="n">
+        <v>0.03444</v>
+      </c>
+      <c r="AA267" s="1" t="n">
         <v>0.03471</v>
       </c>
-      <c r="AA267" s="1" t="n">
+      <c r="AB267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -23274,9 +24078,12 @@
         <v>0.13</v>
       </c>
       <c r="Z268" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AA268" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="AA268" s="1" t="n">
+      <c r="AB268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -23359,9 +24166,12 @@
         <v>0.07901</v>
       </c>
       <c r="Z269" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AA269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="AA269" s="1" t="n">
+      <c r="AB269" s="1" t="n">
         <v>0.07896</v>
       </c>
     </row>
@@ -23444,9 +24254,12 @@
         <v>0.01377</v>
       </c>
       <c r="Z270" s="1" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="AA270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="AA270" s="1" t="n">
+      <c r="AB270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -23529,9 +24342,12 @@
         <v>0.007479</v>
       </c>
       <c r="Z271" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="AA271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="AA271" s="1" t="n">
+      <c r="AB271" s="1" t="n">
         <v>0.007479</v>
       </c>
     </row>
@@ -23614,9 +24430,12 @@
         <v>0.07396999999999999</v>
       </c>
       <c r="Z272" s="1" t="n">
+        <v>0.07414</v>
+      </c>
+      <c r="AA272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="AA272" s="1" t="n">
+      <c r="AB272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -23699,9 +24518,12 @@
         <v>3.12e-05</v>
       </c>
       <c r="Z273" s="1" t="n">
+        <v>3.12e-05</v>
+      </c>
+      <c r="AA273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="AA273" s="1" t="n">
+      <c r="AB273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -23784,9 +24606,12 @@
         <v>0.005413</v>
       </c>
       <c r="Z274" s="1" t="n">
+        <v>0.005412</v>
+      </c>
+      <c r="AA274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="AA274" s="1" t="n">
+      <c r="AB274" s="1" t="n">
         <v>0.005404</v>
       </c>
     </row>
@@ -23869,10 +24694,13 @@
         <v>0.1749</v>
       </c>
       <c r="Z275" s="1" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="AA275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="AA275" s="1" t="n">
-        <v>0.1749</v>
+      <c r="AB275" s="1" t="n">
+        <v>0.1744</v>
       </c>
     </row>
     <row r="276">
@@ -23954,9 +24782,12 @@
         <v>0.006877</v>
       </c>
       <c r="Z276" s="1" t="n">
+        <v>0.006868</v>
+      </c>
+      <c r="AA276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="AA276" s="1" t="n">
+      <c r="AB276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -24039,9 +24870,12 @@
         <v>0.1321</v>
       </c>
       <c r="Z277" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="AA277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="AA277" s="1" t="n">
+      <c r="AB277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -24124,9 +24958,12 @@
         <v>0.02313</v>
       </c>
       <c r="Z278" s="1" t="n">
+        <v>0.02313</v>
+      </c>
+      <c r="AA278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="AA278" s="1" t="n">
+      <c r="AB278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -24209,9 +25046,12 @@
         <v>0.01811</v>
       </c>
       <c r="Z279" s="1" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="AA279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AA279" s="1" t="n">
+      <c r="AB279" s="1" t="n">
         <v>0.0181</v>
       </c>
     </row>
@@ -24294,9 +25134,12 @@
         <v>0.0368</v>
       </c>
       <c r="Z280" s="1" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="AA280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="AA280" s="1" t="n">
+      <c r="AB280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -24379,9 +25222,12 @@
         <v>0.03979</v>
       </c>
       <c r="Z281" s="1" t="n">
+        <v>0.03973</v>
+      </c>
+      <c r="AA281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="AA281" s="1" t="n">
+      <c r="AB281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -24464,9 +25310,12 @@
         <v>0.303</v>
       </c>
       <c r="Z282" s="1" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AA282" s="1" t="n">
         <v>0.3079</v>
       </c>
-      <c r="AA282" s="1" t="n">
+      <c r="AB282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -24549,9 +25398,12 @@
         <v>0.01118</v>
       </c>
       <c r="Z283" s="1" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="AA283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="AA283" s="1" t="n">
+      <c r="AB283" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -24634,9 +25486,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="Z284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="AA284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="AA284" s="1" t="n">
+      <c r="AB284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -24719,9 +25574,12 @@
         <v>0.1142</v>
       </c>
       <c r="Z285" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="AA285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="AA285" s="1" t="n">
+      <c r="AB285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -24804,9 +25662,12 @@
         <v>0.003441</v>
       </c>
       <c r="Z286" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="AA286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="AA286" s="1" t="n">
+      <c r="AB286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -24889,9 +25750,12 @@
         <v>0.08462</v>
       </c>
       <c r="Z287" s="1" t="n">
+        <v>0.08474</v>
+      </c>
+      <c r="AA287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="AA287" s="1" t="n">
+      <c r="AB287" s="1" t="n">
         <v>0.08462</v>
       </c>
     </row>
@@ -24974,9 +25838,12 @@
         <v>0.0997</v>
       </c>
       <c r="Z288" s="1" t="n">
+        <v>0.10061</v>
+      </c>
+      <c r="AA288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="AA288" s="1" t="n">
+      <c r="AB288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -25059,9 +25926,12 @@
         <v>0.4311</v>
       </c>
       <c r="Z289" s="1" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="AA289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="AA289" s="1" t="n">
+      <c r="AB289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -25144,9 +26014,12 @@
         <v>0.04004</v>
       </c>
       <c r="Z290" s="1" t="n">
-        <v>0.04004</v>
+        <v>0.04037</v>
       </c>
       <c r="AA290" s="1" t="n">
+        <v>0.04037</v>
+      </c>
+      <c r="AB290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -25229,9 +26102,12 @@
         <v>0.2344</v>
       </c>
       <c r="Z291" s="1" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="AA291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="AA291" s="1" t="n">
+      <c r="AB291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -25314,9 +26190,12 @@
         <v>0.2844</v>
       </c>
       <c r="Z292" s="1" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="AA292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="AA292" s="1" t="n">
+      <c r="AB292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -25399,9 +26278,12 @@
         <v>0.1512</v>
       </c>
       <c r="Z293" s="1" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="AA293" s="1" t="n">
         <v>0.1539</v>
       </c>
-      <c r="AA293" s="1" t="n">
+      <c r="AB293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -25484,9 +26366,12 @@
         <v>4.163</v>
       </c>
       <c r="Z294" s="1" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="AA294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="AA294" s="1" t="n">
+      <c r="AB294" s="1" t="n">
         <v>4.161</v>
       </c>
     </row>
@@ -25569,9 +26454,12 @@
         <v>0.03321</v>
       </c>
       <c r="Z295" s="1" t="n">
+        <v>0.03331</v>
+      </c>
+      <c r="AA295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="AA295" s="1" t="n">
+      <c r="AB295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -25654,9 +26542,12 @@
         <v>0.000969</v>
       </c>
       <c r="Z296" s="1" t="n">
+        <v>0.000969</v>
+      </c>
+      <c r="AA296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="AA296" s="1" t="n">
+      <c r="AB296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -25739,9 +26630,12 @@
         <v>0.08126</v>
       </c>
       <c r="Z297" s="1" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="AA297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="AA297" s="1" t="n">
+      <c r="AB297" s="1" t="n">
         <v>0.08126</v>
       </c>
     </row>
@@ -25824,9 +26718,12 @@
         <v>0.05827</v>
       </c>
       <c r="Z298" s="1" t="n">
+        <v>0.05863</v>
+      </c>
+      <c r="AA298" s="1" t="n">
         <v>0.05876</v>
       </c>
-      <c r="AA298" s="1" t="n">
+      <c r="AB298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -25909,9 +26806,12 @@
         <v>0.09156</v>
       </c>
       <c r="Z299" s="1" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="AA299" s="1" t="n">
         <v>0.09202</v>
       </c>
-      <c r="AA299" s="1" t="n">
+      <c r="AB299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -25994,9 +26894,12 @@
         <v>0.02718</v>
       </c>
       <c r="Z300" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="AA300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="AA300" s="1" t="n">
+      <c r="AB300" s="1" t="n">
         <v>0.02718</v>
       </c>
     </row>
@@ -26079,9 +26982,12 @@
         <v>0.06536</v>
       </c>
       <c r="Z301" s="1" t="n">
+        <v>0.06528</v>
+      </c>
+      <c r="AA301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="AA301" s="1" t="n">
+      <c r="AB301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -26164,9 +27070,12 @@
         <v>0.053371</v>
       </c>
       <c r="Z302" s="1" t="n">
+        <v>0.053551</v>
+      </c>
+      <c r="AA302" s="1" t="n">
         <v>0.053599</v>
       </c>
-      <c r="AA302" s="1" t="n">
+      <c r="AB302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -26249,9 +27158,12 @@
         <v>5166.6</v>
       </c>
       <c r="Z303" s="1" t="n">
+        <v>5166.2</v>
+      </c>
+      <c r="AA303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="AA303" s="1" t="n">
+      <c r="AB303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -26334,9 +27246,12 @@
         <v>14.85</v>
       </c>
       <c r="Z304" s="1" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="AA304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="AA304" s="1" t="n">
+      <c r="AB304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -26419,9 +27334,12 @@
         <v>0.003758</v>
       </c>
       <c r="Z305" s="1" t="n">
+        <v>0.003765</v>
+      </c>
+      <c r="AA305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="AA305" s="1" t="n">
+      <c r="AB305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -26504,9 +27422,12 @@
         <v>0.4548</v>
       </c>
       <c r="Z306" s="1" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="AA306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="AA306" s="1" t="n">
+      <c r="AB306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -26589,9 +27510,12 @@
         <v>0.04663</v>
       </c>
       <c r="Z307" s="1" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AA307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="AA307" s="1" t="n">
+      <c r="AB307" s="1" t="n">
         <v>0.04649</v>
       </c>
     </row>
@@ -26674,9 +27598,12 @@
         <v>1.4968</v>
       </c>
       <c r="Z308" s="1" t="n">
+        <v>1.5065</v>
+      </c>
+      <c r="AA308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="AA308" s="1" t="n">
+      <c r="AB308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -26759,9 +27686,12 @@
         <v>0.0007866</v>
       </c>
       <c r="Z309" s="1" t="n">
+        <v>0.0007893</v>
+      </c>
+      <c r="AA309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="AA309" s="1" t="n">
+      <c r="AB309" s="1" t="n">
         <v>0.0007861</v>
       </c>
     </row>
@@ -26844,10 +27774,13 @@
         <v>4.525</v>
       </c>
       <c r="Z310" s="1" t="n">
+        <v>4.519</v>
+      </c>
+      <c r="AA310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="AA310" s="1" t="n">
-        <v>4.525</v>
+      <c r="AB310" s="1" t="n">
+        <v>4.519</v>
       </c>
     </row>
     <row r="311">
@@ -26929,9 +27862,12 @@
         <v>4.76</v>
       </c>
       <c r="Z311" s="1" t="n">
+        <v>4.772</v>
+      </c>
+      <c r="AA311" s="1" t="n">
         <v>4.809</v>
       </c>
-      <c r="AA311" s="1" t="n">
+      <c r="AB311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -27014,9 +27950,12 @@
         <v>0.08058</v>
       </c>
       <c r="Z312" s="1" t="n">
+        <v>0.08064</v>
+      </c>
+      <c r="AA312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="AA312" s="1" t="n">
+      <c r="AB312" s="1" t="n">
         <v>0.08033999999999999</v>
       </c>
     </row>
@@ -27099,9 +28038,12 @@
         <v>2.021</v>
       </c>
       <c r="Z313" s="1" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="AA313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA313" s="1" t="n">
+      <c r="AB313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -27184,9 +28126,12 @@
         <v>0.0704</v>
       </c>
       <c r="Z314" s="1" t="n">
+        <v>0.07047</v>
+      </c>
+      <c r="AA314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="AA314" s="1" t="n">
+      <c r="AB314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -27269,9 +28214,12 @@
         <v>0.947</v>
       </c>
       <c r="Z315" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AA315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="AA315" s="1" t="n">
+      <c r="AB315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -27354,10 +28302,13 @@
         <v>0.1297</v>
       </c>
       <c r="Z316" s="1" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="AA316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="AA316" s="1" t="n">
-        <v>0.1295</v>
+      <c r="AB316" s="1" t="n">
+        <v>0.1294</v>
       </c>
     </row>
     <row r="317">
@@ -27439,9 +28390,12 @@
         <v>0.1847</v>
       </c>
       <c r="Z317" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="AA317" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="AA317" s="1" t="n">
+      <c r="AB317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -27524,9 +28478,12 @@
         <v>0.0159</v>
       </c>
       <c r="Z318" s="1" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="AA318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="AA318" s="1" t="n">
+      <c r="AB318" s="1" t="n">
         <v>0.0159</v>
       </c>
     </row>
@@ -27609,9 +28566,12 @@
         <v>0.08319</v>
       </c>
       <c r="Z319" s="1" t="n">
+        <v>0.08337</v>
+      </c>
+      <c r="AA319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="AA319" s="1" t="n">
+      <c r="AB319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -27694,9 +28654,12 @@
         <v>0.007462</v>
       </c>
       <c r="Z320" s="1" t="n">
+        <v>0.007467</v>
+      </c>
+      <c r="AA320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="AA320" s="1" t="n">
+      <c r="AB320" s="1" t="n">
         <v>0.007462</v>
       </c>
     </row>
@@ -27779,9 +28742,12 @@
         <v>0.05424</v>
       </c>
       <c r="Z321" s="1" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="AA321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="AA321" s="1" t="n">
+      <c r="AB321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -27864,9 +28830,12 @@
         <v>0.5479000000000001</v>
       </c>
       <c r="Z322" s="1" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="AA322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="AA322" s="1" t="n">
+      <c r="AB322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -27949,10 +28918,13 @@
         <v>0.07373</v>
       </c>
       <c r="Z323" s="1" t="n">
+        <v>0.07346</v>
+      </c>
+      <c r="AA323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="AA323" s="1" t="n">
-        <v>0.07373</v>
+      <c r="AB323" s="1" t="n">
+        <v>0.07346</v>
       </c>
     </row>
     <row r="324">
@@ -28034,9 +29006,12 @@
         <v>0.012967</v>
       </c>
       <c r="Z324" s="1" t="n">
+        <v>0.012956</v>
+      </c>
+      <c r="AA324" s="1" t="n">
         <v>0.013045</v>
       </c>
-      <c r="AA324" s="1" t="n">
+      <c r="AB324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -28119,9 +29094,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="Z325" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="AA325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="AA325" s="1" t="n">
+      <c r="AB325" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
     </row>
@@ -28204,9 +29182,12 @@
         <v>0.01736</v>
       </c>
       <c r="Z326" s="1" t="n">
+        <v>0.01738</v>
+      </c>
+      <c r="AA326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="AA326" s="1" t="n">
+      <c r="AB326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -28289,9 +29270,12 @@
         <v>0.0644</v>
       </c>
       <c r="Z327" s="1" t="n">
-        <v>0.0644</v>
+        <v>0.06455</v>
       </c>
       <c r="AA327" s="1" t="n">
+        <v>0.06455</v>
+      </c>
+      <c r="AB327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -28374,9 +29358,12 @@
         <v>0.2625</v>
       </c>
       <c r="Z328" s="1" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="AA328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="AA328" s="1" t="n">
+      <c r="AB328" s="1" t="n">
         <v>0.2612</v>
       </c>
     </row>
@@ -28459,9 +29446,12 @@
         <v>0.17435</v>
       </c>
       <c r="Z329" s="1" t="n">
-        <v>0.17476</v>
+        <v>0.17565</v>
       </c>
       <c r="AA329" s="1" t="n">
+        <v>0.17565</v>
+      </c>
+      <c r="AB329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -28544,9 +29534,12 @@
         <v>2.002</v>
       </c>
       <c r="Z330" s="1" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="AA330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="AA330" s="1" t="n">
+      <c r="AB330" s="1" t="n">
         <v>2.002</v>
       </c>
     </row>
@@ -28629,9 +29622,12 @@
         <v>0.0285</v>
       </c>
       <c r="Z331" s="1" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="AA331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="AA331" s="1" t="n">
+      <c r="AB331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -28714,9 +29710,12 @@
         <v>0.005968</v>
       </c>
       <c r="Z332" s="1" t="n">
+        <v>0.006013</v>
+      </c>
+      <c r="AA332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="AA332" s="1" t="n">
+      <c r="AB332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -28799,9 +29798,12 @@
         <v>0.003441</v>
       </c>
       <c r="Z333" s="1" t="n">
+        <v>0.003463</v>
+      </c>
+      <c r="AA333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="AA333" s="1" t="n">
+      <c r="AB333" s="1" t="n">
         <v>0.003441</v>
       </c>
     </row>
@@ -28884,9 +29886,12 @@
         <v>0.01387</v>
       </c>
       <c r="Z334" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AA334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="AA334" s="1" t="n">
+      <c r="AB334" s="1" t="n">
         <v>0.01387</v>
       </c>
     </row>
@@ -28969,9 +29974,12 @@
         <v>1.131</v>
       </c>
       <c r="Z335" s="1" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="AA335" s="1" t="n">
         <v>1.158</v>
       </c>
-      <c r="AA335" s="1" t="n">
+      <c r="AB335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -29054,9 +30062,12 @@
         <v>0.011221</v>
       </c>
       <c r="Z336" s="1" t="n">
+        <v>0.011225</v>
+      </c>
+      <c r="AA336" s="1" t="n">
         <v>0.011377</v>
       </c>
-      <c r="AA336" s="1" t="n">
+      <c r="AB336" s="1" t="n">
         <v>0.011221</v>
       </c>
     </row>
@@ -29139,9 +30150,12 @@
         <v>2.971</v>
       </c>
       <c r="Z337" s="1" t="n">
+        <v>2.958</v>
+      </c>
+      <c r="AA337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="AA337" s="1" t="n">
+      <c r="AB337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -29224,9 +30238,12 @@
         <v>0.0184</v>
       </c>
       <c r="Z338" s="1" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="AA338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="AA338" s="1" t="n">
+      <c r="AB338" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -29309,9 +30326,12 @@
         <v>0.07679</v>
       </c>
       <c r="Z339" s="1" t="n">
+        <v>0.07693</v>
+      </c>
+      <c r="AA339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="AA339" s="1" t="n">
+      <c r="AB339" s="1" t="n">
         <v>0.07679</v>
       </c>
     </row>
@@ -29394,9 +30414,12 @@
         <v>0.075</v>
       </c>
       <c r="Z340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AA340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="AA340" s="1" t="n">
+      <c r="AB340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -29479,9 +30502,12 @@
         <v>0.03614</v>
       </c>
       <c r="Z341" s="1" t="n">
+        <v>0.03614</v>
+      </c>
+      <c r="AA341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="AA341" s="1" t="n">
+      <c r="AB341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -29564,9 +30590,12 @@
         <v>2587</v>
       </c>
       <c r="Z342" s="1" t="n">
+        <v>2586</v>
+      </c>
+      <c r="AA342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="AA342" s="1" t="n">
+      <c r="AB342" s="1" t="n">
         <v>2579</v>
       </c>
     </row>
@@ -29649,9 +30678,12 @@
         <v>0.0001952</v>
       </c>
       <c r="Z343" s="1" t="n">
+        <v>0.0001971</v>
+      </c>
+      <c r="AA343" s="1" t="n">
         <v>0.0002049</v>
       </c>
-      <c r="AA343" s="1" t="n">
+      <c r="AB343" s="1" t="n">
         <v>0.0001952</v>
       </c>
     </row>
@@ -29734,9 +30766,12 @@
         <v>0.07933999999999999</v>
       </c>
       <c r="Z344" s="1" t="n">
+        <v>0.07929</v>
+      </c>
+      <c r="AA344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="AA344" s="1" t="n">
+      <c r="AB344" s="1" t="n">
         <v>0.07915</v>
       </c>
     </row>
@@ -29819,10 +30854,13 @@
         <v>0.01608</v>
       </c>
       <c r="Z345" s="1" t="n">
+        <v>0.01604</v>
+      </c>
+      <c r="AA345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="AA345" s="1" t="n">
-        <v>0.01608</v>
+      <c r="AB345" s="1" t="n">
+        <v>0.01604</v>
       </c>
     </row>
     <row r="346">
@@ -29904,9 +30942,12 @@
         <v>2.753</v>
       </c>
       <c r="Z346" s="1" t="n">
+        <v>2.754</v>
+      </c>
+      <c r="AA346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="AA346" s="1" t="n">
+      <c r="AB346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -29989,9 +31030,12 @@
         <v>0.01629</v>
       </c>
       <c r="Z347" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="AA347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="AA347" s="1" t="n">
+      <c r="AB347" s="1" t="n">
         <v>0.01625</v>
       </c>
     </row>
@@ -30074,9 +31118,12 @@
         <v>0.03817</v>
       </c>
       <c r="Z348" s="1" t="n">
+        <v>0.03817</v>
+      </c>
+      <c r="AA348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="AA348" s="1" t="n">
+      <c r="AB348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -30159,9 +31206,12 @@
         <v>0.3051</v>
       </c>
       <c r="Z349" s="1" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AA349" s="1" t="n">
         <v>0.3076</v>
       </c>
-      <c r="AA349" s="1" t="n">
+      <c r="AB349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -30244,9 +31294,12 @@
         <v>0.005066</v>
       </c>
       <c r="Z350" s="1" t="n">
+        <v>0.005079</v>
+      </c>
+      <c r="AA350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="AA350" s="1" t="n">
+      <c r="AB350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -30329,9 +31382,12 @@
         <v>0.005086</v>
       </c>
       <c r="Z351" s="1" t="n">
+        <v>0.005094</v>
+      </c>
+      <c r="AA351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="AA351" s="1" t="n">
+      <c r="AB351" s="1" t="n">
         <v>0.005054</v>
       </c>
     </row>
@@ -30414,10 +31470,13 @@
         <v>0.004372</v>
       </c>
       <c r="Z352" s="1" t="n">
+        <v>0.004371</v>
+      </c>
+      <c r="AA352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="AA352" s="1" t="n">
-        <v>0.004372</v>
+      <c r="AB352" s="1" t="n">
+        <v>0.004371</v>
       </c>
     </row>
     <row r="353">
@@ -30499,9 +31558,12 @@
         <v>0.08051999999999999</v>
       </c>
       <c r="Z353" s="1" t="n">
+        <v>0.08066</v>
+      </c>
+      <c r="AA353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="AA353" s="1" t="n">
+      <c r="AB353" s="1" t="n">
         <v>0.08008</v>
       </c>
     </row>
@@ -30584,9 +31646,12 @@
         <v>1.255</v>
       </c>
       <c r="Z354" s="1" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="AA354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="AA354" s="1" t="n">
+      <c r="AB354" s="1" t="n">
         <v>1.255</v>
       </c>
     </row>
@@ -30669,9 +31734,12 @@
         <v>7.71</v>
       </c>
       <c r="Z355" s="1" t="n">
+        <v>7.701</v>
+      </c>
+      <c r="AA355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="AA355" s="1" t="n">
+      <c r="AB355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -30754,9 +31822,12 @@
         <v>0.00775</v>
       </c>
       <c r="Z356" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="AA356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="AA356" s="1" t="n">
+      <c r="AB356" s="1" t="n">
         <v>0.00774</v>
       </c>
     </row>
@@ -30839,9 +31910,12 @@
         <v>0.005655</v>
       </c>
       <c r="Z357" s="1" t="n">
+        <v>0.005636</v>
+      </c>
+      <c r="AA357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="AA357" s="1" t="n">
+      <c r="AB357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -30924,9 +31998,12 @@
         <v>0.01546</v>
       </c>
       <c r="Z358" s="1" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="AA358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="AA358" s="1" t="n">
+      <c r="AB358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -31009,9 +32086,12 @@
         <v>3.617</v>
       </c>
       <c r="Z359" s="1" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AA359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="AA359" s="1" t="n">
+      <c r="AB359" s="1" t="n">
         <v>3.597</v>
       </c>
     </row>
@@ -31094,9 +32174,12 @@
         <v>0.1495</v>
       </c>
       <c r="Z360" s="1" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="AA360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="AA360" s="1" t="n">
+      <c r="AB360" s="1" t="n">
         <v>0.1492</v>
       </c>
     </row>
@@ -31179,9 +32262,12 @@
         <v>0.0704</v>
       </c>
       <c r="Z361" s="1" t="n">
+        <v>0.07034</v>
+      </c>
+      <c r="AA361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="AA361" s="1" t="n">
+      <c r="AB361" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -31264,9 +32350,12 @@
         <v>0.01762</v>
       </c>
       <c r="Z362" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="AA362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="AA362" s="1" t="n">
+      <c r="AB362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -31349,9 +32438,12 @@
         <v>0.0222</v>
       </c>
       <c r="Z363" s="1" t="n">
+        <v>0.02222</v>
+      </c>
+      <c r="AA363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="AA363" s="1" t="n">
+      <c r="AB363" s="1" t="n">
         <v>0.0222</v>
       </c>
     </row>
@@ -31434,9 +32526,12 @@
         <v>0.0125</v>
       </c>
       <c r="Z364" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="AA364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="AA364" s="1" t="n">
+      <c r="AB364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -31519,9 +32614,12 @@
         <v>0.0905</v>
       </c>
       <c r="Z365" s="1" t="n">
+        <v>0.0905</v>
+      </c>
+      <c r="AA365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="AA365" s="1" t="n">
+      <c r="AB365" s="1" t="n">
         <v>0.0905</v>
       </c>
     </row>
@@ -31604,9 +32702,12 @@
         <v>0.04217</v>
       </c>
       <c r="Z366" s="1" t="n">
+        <v>0.04222</v>
+      </c>
+      <c r="AA366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="AA366" s="1" t="n">
+      <c r="AB366" s="1" t="n">
         <v>0.04214</v>
       </c>
     </row>
@@ -31689,9 +32790,12 @@
         <v>0.0315</v>
       </c>
       <c r="Z367" s="1" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="AA367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="AA367" s="1" t="n">
+      <c r="AB367" s="1" t="n">
         <v>0.03124</v>
       </c>
     </row>
@@ -31774,9 +32878,12 @@
         <v>0.02302</v>
       </c>
       <c r="Z368" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="AA368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="AA368" s="1" t="n">
+      <c r="AB368" s="1" t="n">
         <v>0.02302</v>
       </c>
     </row>
@@ -31859,9 +32966,12 @@
         <v>0.03095</v>
       </c>
       <c r="Z369" s="1" t="n">
+        <v>0.03084</v>
+      </c>
+      <c r="AA369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="AA369" s="1" t="n">
+      <c r="AB369" s="1" t="n">
         <v>0.0308</v>
       </c>
     </row>
@@ -31944,9 +33054,12 @@
         <v>0.07978</v>
       </c>
       <c r="Z370" s="1" t="n">
+        <v>0.07972</v>
+      </c>
+      <c r="AA370" s="1" t="n">
         <v>0.08017000000000001</v>
       </c>
-      <c r="AA370" s="1" t="n">
+      <c r="AB370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -32029,9 +33142,12 @@
         <v>0.1069</v>
       </c>
       <c r="Z371" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="AA371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="AA371" s="1" t="n">
+      <c r="AB371" s="1" t="n">
         <v>0.1069</v>
       </c>
     </row>
@@ -32114,9 +33230,12 @@
         <v>0.006943</v>
       </c>
       <c r="Z372" s="1" t="n">
+        <v>0.006945</v>
+      </c>
+      <c r="AA372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="AA372" s="1" t="n">
+      <c r="AB372" s="1" t="n">
         <v>0.00694</v>
       </c>
     </row>
@@ -32199,9 +33318,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="Z373" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="AA373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="AA373" s="1" t="n">
+      <c r="AB373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -32284,9 +33406,12 @@
         <v>0.0571</v>
       </c>
       <c r="Z374" s="1" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="AA374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="AA374" s="1" t="n">
+      <c r="AB374" s="1" t="n">
         <v>0.0571</v>
       </c>
     </row>
@@ -32369,10 +33494,13 @@
         <v>0.3168</v>
       </c>
       <c r="Z375" s="1" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AA375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="AA375" s="1" t="n">
-        <v>0.3168</v>
+      <c r="AB375" s="1" t="n">
+        <v>0.3143</v>
       </c>
     </row>
     <row r="376">
@@ -32454,9 +33582,12 @@
         <v>0.01932</v>
       </c>
       <c r="Z376" s="1" t="n">
+        <v>0.01936</v>
+      </c>
+      <c r="AA376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="AA376" s="1" t="n">
+      <c r="AB376" s="1" t="n">
         <v>0.01932</v>
       </c>
     </row>
@@ -32539,9 +33670,12 @@
         <v>0.06865</v>
       </c>
       <c r="Z377" s="1" t="n">
+        <v>0.06883</v>
+      </c>
+      <c r="AA377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="AA377" s="1" t="n">
+      <c r="AB377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -32624,9 +33758,12 @@
         <v>0.15513</v>
       </c>
       <c r="Z378" s="1" t="n">
+        <v>0.15544</v>
+      </c>
+      <c r="AA378" s="1" t="n">
         <v>0.15872</v>
       </c>
-      <c r="AA378" s="1" t="n">
+      <c r="AB378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -32709,9 +33846,12 @@
         <v>0.0005949</v>
       </c>
       <c r="Z379" s="1" t="n">
+        <v>0.0005948</v>
+      </c>
+      <c r="AA379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="AA379" s="1" t="n">
+      <c r="AB379" s="1" t="n">
         <v>0.0005922</v>
       </c>
     </row>
@@ -32794,9 +33934,12 @@
         <v>0.01011</v>
       </c>
       <c r="Z380" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="AA380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="AA380" s="1" t="n">
+      <c r="AB380" s="1" t="n">
         <v>0.01011</v>
       </c>
     </row>
@@ -32879,9 +34022,12 @@
         <v>0.02545</v>
       </c>
       <c r="Z381" s="1" t="n">
+        <v>0.02543</v>
+      </c>
+      <c r="AA381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="AA381" s="1" t="n">
+      <c r="AB381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -32964,9 +34110,12 @@
         <v>0.18542</v>
       </c>
       <c r="Z382" s="1" t="n">
+        <v>0.18614</v>
+      </c>
+      <c r="AA382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="AA382" s="1" t="n">
+      <c r="AB382" s="1" t="n">
         <v>0.18542</v>
       </c>
     </row>
@@ -33049,9 +34198,12 @@
         <v>0.09205000000000001</v>
       </c>
       <c r="Z383" s="1" t="n">
+        <v>0.09223000000000001</v>
+      </c>
+      <c r="AA383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="AA383" s="1" t="n">
+      <c r="AB383" s="1" t="n">
         <v>0.09205000000000001</v>
       </c>
     </row>
@@ -33134,9 +34286,12 @@
         <v>0.03174</v>
       </c>
       <c r="Z384" s="1" t="n">
+        <v>0.03176</v>
+      </c>
+      <c r="AA384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="AA384" s="1" t="n">
+      <c r="AB384" s="1" t="n">
         <v>0.0316</v>
       </c>
     </row>
@@ -33219,10 +34374,13 @@
         <v>0.01081</v>
       </c>
       <c r="Z385" s="1" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="AA385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="AA385" s="1" t="n">
-        <v>0.01081</v>
+      <c r="AB385" s="1" t="n">
+        <v>0.0108</v>
       </c>
     </row>
     <row r="386">
@@ -33304,10 +34462,13 @@
         <v>0.05032</v>
       </c>
       <c r="Z386" s="1" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="AA386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="AA386" s="1" t="n">
-        <v>0.05032</v>
+      <c r="AB386" s="1" t="n">
+        <v>0.0503</v>
       </c>
     </row>
     <row r="387">
@@ -33389,10 +34550,13 @@
         <v>0.02355</v>
       </c>
       <c r="Z387" s="1" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="AA387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="AA387" s="1" t="n">
-        <v>0.02355</v>
+      <c r="AB387" s="1" t="n">
+        <v>0.0235</v>
       </c>
     </row>
     <row r="388">
@@ -33474,9 +34638,12 @@
         <v>0.007335</v>
       </c>
       <c r="Z388" s="1" t="n">
+        <v>0.007221</v>
+      </c>
+      <c r="AA388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="AA388" s="1" t="n">
+      <c r="AB388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -33559,9 +34726,12 @@
         <v>0.01011</v>
       </c>
       <c r="Z389" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="AA389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="AA389" s="1" t="n">
+      <c r="AB389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -33644,9 +34814,12 @@
         <v>0.08169</v>
       </c>
       <c r="Z390" s="1" t="n">
+        <v>0.08184</v>
+      </c>
+      <c r="AA390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="AA390" s="1" t="n">
+      <c r="AB390" s="1" t="n">
         <v>0.08169</v>
       </c>
     </row>
@@ -33729,9 +34902,12 @@
         <v>0.5006</v>
       </c>
       <c r="Z391" s="1" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="AA391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="AA391" s="1" t="n">
+      <c r="AB391" s="1" t="n">
         <v>0.5006</v>
       </c>
     </row>
@@ -33814,9 +34990,12 @@
         <v>0.1163</v>
       </c>
       <c r="Z392" s="1" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="AA392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="AA392" s="1" t="n">
+      <c r="AB392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -33899,9 +35078,12 @@
         <v>0.00246</v>
       </c>
       <c r="Z393" s="1" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="AA393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="AA393" s="1" t="n">
+      <c r="AB393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -33984,9 +35166,12 @@
         <v>0.02179</v>
       </c>
       <c r="Z394" s="1" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="AA394" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="AA394" s="1" t="n">
+      <c r="AB394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -34069,9 +35254,12 @@
         <v>0.0163</v>
       </c>
       <c r="Z395" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AA395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="AA395" s="1" t="n">
+      <c r="AB395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -34154,9 +35342,12 @@
         <v>0.1349</v>
       </c>
       <c r="Z396" s="1" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="AA396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="AA396" s="1" t="n">
+      <c r="AB396" s="1" t="n">
         <v>0.1348</v>
       </c>
     </row>
@@ -34239,9 +35430,12 @@
         <v>0.0145</v>
       </c>
       <c r="Z397" s="1" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="AA397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="AA397" s="1" t="n">
+      <c r="AB397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -34324,9 +35518,12 @@
         <v>6.793</v>
       </c>
       <c r="Z398" s="1" t="n">
+        <v>6.777</v>
+      </c>
+      <c r="AA398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="AA398" s="1" t="n">
+      <c r="AB398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -34409,9 +35606,12 @@
         <v>0.009542</v>
       </c>
       <c r="Z399" s="1" t="n">
+        <v>0.00953</v>
+      </c>
+      <c r="AA399" s="1" t="n">
         <v>0.009542</v>
       </c>
-      <c r="AA399" s="1" t="n">
+      <c r="AB399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -34494,9 +35694,12 @@
         <v>0.001242</v>
       </c>
       <c r="Z400" s="1" t="n">
+        <v>0.001255</v>
+      </c>
+      <c r="AA400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="AA400" s="1" t="n">
+      <c r="AB400" s="1" t="n">
         <v>0.001241</v>
       </c>
     </row>
@@ -34579,9 +35782,12 @@
         <v>0.01849</v>
       </c>
       <c r="Z401" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="AA401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="AA401" s="1" t="n">
+      <c r="AB401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -34664,9 +35870,12 @@
         <v>0.08451</v>
       </c>
       <c r="Z402" s="1" t="n">
+        <v>0.08459</v>
+      </c>
+      <c r="AA402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AA402" s="1" t="n">
+      <c r="AB402" s="1" t="n">
         <v>0.08447</v>
       </c>
     </row>
@@ -34749,10 +35958,13 @@
         <v>0.00546</v>
       </c>
       <c r="Z403" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="AA403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="AA403" s="1" t="n">
-        <v>0.00546</v>
+      <c r="AB403" s="1" t="n">
+        <v>0.00545</v>
       </c>
     </row>
     <row r="404">
@@ -34834,9 +36046,12 @@
         <v>0.04304</v>
       </c>
       <c r="Z404" s="1" t="n">
+        <v>0.04301</v>
+      </c>
+      <c r="AA404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="AA404" s="1" t="n">
+      <c r="AB404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -34919,9 +36134,12 @@
         <v>0.05851</v>
       </c>
       <c r="Z405" s="1" t="n">
+        <v>0.05854</v>
+      </c>
+      <c r="AA405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="AA405" s="1" t="n">
+      <c r="AB405" s="1" t="n">
         <v>0.05827</v>
       </c>
     </row>
@@ -35004,9 +36222,12 @@
         <v>0.01666</v>
       </c>
       <c r="Z406" s="1" t="n">
+        <v>0.01657</v>
+      </c>
+      <c r="AA406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="AA406" s="1" t="n">
+      <c r="AB406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -35089,10 +36310,13 @@
         <v>0.0423</v>
       </c>
       <c r="Z407" s="1" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="AA407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="AA407" s="1" t="n">
-        <v>0.0423</v>
+      <c r="AB407" s="1" t="n">
+        <v>0.0422</v>
       </c>
     </row>
     <row r="408">
@@ -35174,9 +36398,12 @@
         <v>0.01924</v>
       </c>
       <c r="Z408" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="AA408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="AA408" s="1" t="n">
+      <c r="AB408" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -35259,9 +36486,12 @@
         <v>0.4419</v>
       </c>
       <c r="Z409" s="1" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="AA409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="AA409" s="1" t="n">
+      <c r="AB409" s="1" t="n">
         <v>0.4419</v>
       </c>
     </row>
@@ -35344,9 +36574,12 @@
         <v>0.04337</v>
       </c>
       <c r="Z410" s="1" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AA410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="AA410" s="1" t="n">
+      <c r="AB410" s="1" t="n">
         <v>0.04337</v>
       </c>
     </row>
@@ -35429,9 +36662,12 @@
         <v>27.21</v>
       </c>
       <c r="Z411" s="1" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="AA411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="AA411" s="1" t="n">
+      <c r="AB411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -35514,9 +36750,12 @@
         <v>0.03486</v>
       </c>
       <c r="Z412" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AA412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="AA412" s="1" t="n">
+      <c r="AB412" s="1" t="n">
         <v>0.03486</v>
       </c>
     </row>
@@ -35599,9 +36838,12 @@
         <v>0.003405</v>
       </c>
       <c r="Z413" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="AA413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="AA413" s="1" t="n">
+      <c r="AB413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -35684,9 +36926,12 @@
         <v>0.1517</v>
       </c>
       <c r="Z414" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="AA414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="AA414" s="1" t="n">
+      <c r="AB414" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -35769,9 +37014,12 @@
         <v>0.05258</v>
       </c>
       <c r="Z415" s="1" t="n">
+        <v>0.05252</v>
+      </c>
+      <c r="AA415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="AA415" s="1" t="n">
+      <c r="AB415" s="1" t="n">
         <v>0.05228</v>
       </c>
     </row>
@@ -35854,9 +37102,12 @@
         <v>0.00656</v>
       </c>
       <c r="Z416" s="1" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="AA416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="AA416" s="1" t="n">
+      <c r="AB416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -35939,9 +37190,12 @@
         <v>0.06037</v>
       </c>
       <c r="Z417" s="1" t="n">
+        <v>0.06043</v>
+      </c>
+      <c r="AA417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="AA417" s="1" t="n">
+      <c r="AB417" s="1" t="n">
         <v>0.06025</v>
       </c>
     </row>
@@ -36024,9 +37278,12 @@
         <v>0.008012999999999999</v>
       </c>
       <c r="Z418" s="1" t="n">
+        <v>0.008045</v>
+      </c>
+      <c r="AA418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="AA418" s="1" t="n">
+      <c r="AB418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -36109,9 +37366,12 @@
         <v>0.07306</v>
       </c>
       <c r="Z419" s="1" t="n">
+        <v>0.07327</v>
+      </c>
+      <c r="AA419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="AA419" s="1" t="n">
+      <c r="AB419" s="1" t="n">
         <v>0.07306</v>
       </c>
     </row>
@@ -36194,9 +37454,12 @@
         <v>0.02134</v>
       </c>
       <c r="Z420" s="1" t="n">
+        <v>0.02124</v>
+      </c>
+      <c r="AA420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="AA420" s="1" t="n">
+      <c r="AB420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -36279,10 +37542,13 @@
         <v>0.06892</v>
       </c>
       <c r="Z421" s="1" t="n">
+        <v>0.06879</v>
+      </c>
+      <c r="AA421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="AA421" s="1" t="n">
-        <v>0.0689</v>
+      <c r="AB421" s="1" t="n">
+        <v>0.06879</v>
       </c>
     </row>
     <row r="422">
@@ -36364,9 +37630,12 @@
         <v>0.0147</v>
       </c>
       <c r="Z422" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="AA422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="AA422" s="1" t="n">
+      <c r="AB422" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -36449,9 +37718,12 @@
         <v>0.006616</v>
       </c>
       <c r="Z423" s="1" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="AA423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="AA423" s="1" t="n">
+      <c r="AB423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -36534,10 +37806,13 @@
         <v>0.903</v>
       </c>
       <c r="Z424" s="1" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="AA424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="AA424" s="1" t="n">
-        <v>0.903</v>
+      <c r="AB424" s="1" t="n">
+        <v>0.902</v>
       </c>
     </row>
     <row r="425">
@@ -36619,9 +37894,12 @@
         <v>0.03512</v>
       </c>
       <c r="Z425" s="1" t="n">
+        <v>0.03528</v>
+      </c>
+      <c r="AA425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="AA425" s="1" t="n">
+      <c r="AB425" s="1" t="n">
         <v>0.03512</v>
       </c>
     </row>
@@ -36704,9 +37982,12 @@
         <v>1.788</v>
       </c>
       <c r="Z426" s="1" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="AA426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="AA426" s="1" t="n">
+      <c r="AB426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -36789,9 +38070,12 @@
         <v>0.12916</v>
       </c>
       <c r="Z427" s="1" t="n">
-        <v>0.12916</v>
+        <v>0.12936</v>
       </c>
       <c r="AA427" s="1" t="n">
+        <v>0.12936</v>
+      </c>
+      <c r="AB427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -36874,9 +38158,12 @@
         <v>0.05332</v>
       </c>
       <c r="Z428" s="1" t="n">
+        <v>0.05285</v>
+      </c>
+      <c r="AA428" s="1" t="n">
         <v>0.05391</v>
       </c>
-      <c r="AA428" s="1" t="n">
+      <c r="AB428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -36959,9 +38246,12 @@
         <v>1.297</v>
       </c>
       <c r="Z429" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="AA429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="AA429" s="1" t="n">
+      <c r="AB429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -37044,9 +38334,12 @@
         <v>0.07446</v>
       </c>
       <c r="Z430" s="1" t="n">
+        <v>0.07451000000000001</v>
+      </c>
+      <c r="AA430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="AA430" s="1" t="n">
+      <c r="AB430" s="1" t="n">
         <v>0.07444000000000001</v>
       </c>
     </row>
@@ -37129,9 +38422,12 @@
         <v>0.1559</v>
       </c>
       <c r="Z431" s="1" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="AA431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="AA431" s="1" t="n">
+      <c r="AB431" s="1" t="n">
         <v>0.1559</v>
       </c>
     </row>
@@ -37214,9 +38510,12 @@
         <v>1.447</v>
       </c>
       <c r="Z432" s="1" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="AA432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="AA432" s="1" t="n">
+      <c r="AB432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -37299,9 +38598,12 @@
         <v>3.225</v>
       </c>
       <c r="Z433" s="1" t="n">
+        <v>3.236</v>
+      </c>
+      <c r="AA433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="AA433" s="1" t="n">
+      <c r="AB433" s="1" t="n">
         <v>3.225</v>
       </c>
     </row>
@@ -37384,9 +38686,12 @@
         <v>0.1775</v>
       </c>
       <c r="Z434" s="1" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="AA434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="AA434" s="1" t="n">
+      <c r="AB434" s="1" t="n">
         <v>0.1775</v>
       </c>
     </row>
@@ -37469,9 +38774,12 @@
         <v>0.008572</v>
       </c>
       <c r="Z435" s="1" t="n">
+        <v>0.008580000000000001</v>
+      </c>
+      <c r="AA435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="AA435" s="1" t="n">
+      <c r="AB435" s="1" t="n">
         <v>0.008548</v>
       </c>
     </row>
@@ -37554,9 +38862,12 @@
         <v>0.2808</v>
       </c>
       <c r="Z436" s="1" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AA436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="AA436" s="1" t="n">
+      <c r="AB436" s="1" t="n">
         <v>0.2803</v>
       </c>
     </row>
@@ -37639,9 +38950,12 @@
         <v>0.03802</v>
       </c>
       <c r="Z437" s="1" t="n">
+        <v>0.03818</v>
+      </c>
+      <c r="AA437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="AA437" s="1" t="n">
+      <c r="AB437" s="1" t="n">
         <v>0.03802</v>
       </c>
     </row>
@@ -37724,9 +39038,12 @@
         <v>0.02436</v>
       </c>
       <c r="Z438" s="1" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="AA438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="AA438" s="1" t="n">
+      <c r="AB438" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -37809,9 +39126,12 @@
         <v>0.04403</v>
       </c>
       <c r="Z439" s="1" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="AA439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="AA439" s="1" t="n">
+      <c r="AB439" s="1" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -37894,9 +39214,12 @@
         <v>0.0005202</v>
       </c>
       <c r="Z440" s="1" t="n">
+        <v>0.0005194</v>
+      </c>
+      <c r="AA440" s="1" t="n">
         <v>0.0005312</v>
       </c>
-      <c r="AA440" s="1" t="n">
+      <c r="AB440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -37979,9 +39302,12 @@
         <v>0.04483</v>
       </c>
       <c r="Z441" s="1" t="n">
+        <v>0.04488</v>
+      </c>
+      <c r="AA441" s="1" t="n">
         <v>0.04581</v>
       </c>
-      <c r="AA441" s="1" t="n">
+      <c r="AB441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -38064,9 +39390,12 @@
         <v>0.000418</v>
       </c>
       <c r="Z442" s="1" t="n">
+        <v>0.000417</v>
+      </c>
+      <c r="AA442" s="1" t="n">
         <v>0.000419</v>
       </c>
-      <c r="AA442" s="1" t="n">
+      <c r="AB442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -38149,9 +39478,12 @@
         <v>0.09468</v>
       </c>
       <c r="Z443" s="1" t="n">
+        <v>0.09453</v>
+      </c>
+      <c r="AA443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="AA443" s="1" t="n">
+      <c r="AB443" s="1" t="n">
         <v>0.09392</v>
       </c>
     </row>
@@ -38234,9 +39566,12 @@
         <v>2.279</v>
       </c>
       <c r="Z444" s="1" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="AA444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="AA444" s="1" t="n">
+      <c r="AB444" s="1" t="n">
         <v>2.279</v>
       </c>
     </row>
@@ -38319,9 +39654,12 @@
         <v>0.2671</v>
       </c>
       <c r="Z445" s="1" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="AA445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="AA445" s="1" t="n">
+      <c r="AB445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -38404,9 +39742,12 @@
         <v>0.0007455</v>
       </c>
       <c r="Z446" s="1" t="n">
+        <v>0.0007455</v>
+      </c>
+      <c r="AA446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="AA446" s="1" t="n">
+      <c r="AB446" s="1" t="n">
         <v>0.0007376</v>
       </c>
     </row>
@@ -38489,9 +39830,12 @@
         <v>0.03835</v>
       </c>
       <c r="Z447" s="1" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="AA447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="AA447" s="1" t="n">
+      <c r="AB447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -38574,9 +39918,12 @@
         <v>0.1762</v>
       </c>
       <c r="Z448" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="AA448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="AA448" s="1" t="n">
+      <c r="AB448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -38659,9 +40006,12 @@
         <v>0.04284</v>
       </c>
       <c r="Z449" s="1" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AA449" s="1" t="n">
         <v>0.04312</v>
       </c>
-      <c r="AA449" s="1" t="n">
+      <c r="AB449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -38744,9 +40094,12 @@
         <v>0.0001647</v>
       </c>
       <c r="Z450" s="1" t="n">
+        <v>0.000165</v>
+      </c>
+      <c r="AA450" s="1" t="n">
         <v>0.0001657</v>
       </c>
-      <c r="AA450" s="1" t="n">
+      <c r="AB450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -38829,9 +40182,12 @@
         <v>0.03735</v>
       </c>
       <c r="Z451" s="1" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AA451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="AA451" s="1" t="n">
+      <c r="AB451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -38914,10 +40270,13 @@
         <v>0.00941</v>
       </c>
       <c r="Z452" s="1" t="n">
+        <v>0.009390000000000001</v>
+      </c>
+      <c r="AA452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="AA452" s="1" t="n">
-        <v>0.00941</v>
+      <c r="AB452" s="1" t="n">
+        <v>0.009390000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -38999,10 +40358,13 @@
         <v>0.06748999999999999</v>
       </c>
       <c r="Z453" s="1" t="n">
+        <v>0.06733</v>
+      </c>
+      <c r="AA453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="AA453" s="1" t="n">
-        <v>0.06748999999999999</v>
+      <c r="AB453" s="1" t="n">
+        <v>0.06733</v>
       </c>
     </row>
     <row r="454">
@@ -39084,9 +40446,12 @@
         <v>0.007493</v>
       </c>
       <c r="Z454" s="1" t="n">
+        <v>0.007483</v>
+      </c>
+      <c r="AA454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="AA454" s="1" t="n">
+      <c r="AB454" s="1" t="n">
         <v>0.007472</v>
       </c>
     </row>
@@ -39169,9 +40534,12 @@
         <v>0.00324</v>
       </c>
       <c r="Z455" s="1" t="n">
+        <v>0.003242</v>
+      </c>
+      <c r="AA455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="AA455" s="1" t="n">
+      <c r="AB455" s="1" t="n">
         <v>0.00324</v>
       </c>
     </row>
@@ -39254,9 +40622,12 @@
         <v>0.001835</v>
       </c>
       <c r="Z456" s="1" t="n">
+        <v>0.001838</v>
+      </c>
+      <c r="AA456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="AA456" s="1" t="n">
+      <c r="AB456" s="1" t="n">
         <v>0.001835</v>
       </c>
     </row>
@@ -39339,9 +40710,12 @@
         <v>0.0001742</v>
       </c>
       <c r="Z457" s="1" t="n">
+        <v>0.0001744</v>
+      </c>
+      <c r="AA457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="AA457" s="1" t="n">
+      <c r="AB457" s="1" t="n">
         <v>0.0001742</v>
       </c>
     </row>
@@ -39424,9 +40798,12 @@
         <v>0.0003885</v>
       </c>
       <c r="Z458" s="1" t="n">
+        <v>0.0003889</v>
+      </c>
+      <c r="AA458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="AA458" s="1" t="n">
+      <c r="AB458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -39509,9 +40886,12 @@
         <v>0.01391</v>
       </c>
       <c r="Z459" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="AA459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="AA459" s="1" t="n">
+      <c r="AB459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -39594,9 +40974,12 @@
         <v>0.04531</v>
       </c>
       <c r="Z460" s="1" t="n">
+        <v>0.04537</v>
+      </c>
+      <c r="AA460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="AA460" s="1" t="n">
+      <c r="AB460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -39679,9 +41062,12 @@
         <v>0.2818</v>
       </c>
       <c r="Z461" s="1" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AA461" s="1" t="n">
         <v>0.2843</v>
       </c>
-      <c r="AA461" s="1" t="n">
+      <c r="AB461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -39764,9 +41150,12 @@
         <v>0.006203</v>
       </c>
       <c r="Z462" s="1" t="n">
+        <v>0.006224</v>
+      </c>
+      <c r="AA462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="AA462" s="1" t="n">
+      <c r="AB462" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -39849,9 +41238,12 @@
         <v>0.007063</v>
       </c>
       <c r="Z463" s="1" t="n">
+        <v>0.007074</v>
+      </c>
+      <c r="AA463" s="1" t="n">
         <v>0.007153</v>
       </c>
-      <c r="AA463" s="1" t="n">
+      <c r="AB463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -39934,9 +41326,12 @@
         <v>0.2865</v>
       </c>
       <c r="Z464" s="1" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="AA464" s="1" t="n">
         <v>0.2895</v>
       </c>
-      <c r="AA464" s="1" t="n">
+      <c r="AB464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -40019,9 +41414,12 @@
         <v>0.08065</v>
       </c>
       <c r="Z465" s="1" t="n">
+        <v>0.08061</v>
+      </c>
+      <c r="AA465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="AA465" s="1" t="n">
+      <c r="AB465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -40104,9 +41502,12 @@
         <v>0.6341</v>
       </c>
       <c r="Z466" s="1" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="AA466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="AA466" s="1" t="n">
+      <c r="AB466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -40189,9 +41590,12 @@
         <v>0.01464</v>
       </c>
       <c r="Z467" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="AA467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="AA467" s="1" t="n">
+      <c r="AB467" s="1" t="n">
         <v>0.01464</v>
       </c>
     </row>
@@ -40274,9 +41678,12 @@
         <v>0.03409</v>
       </c>
       <c r="Z468" s="1" t="n">
+        <v>0.03443</v>
+      </c>
+      <c r="AA468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="AA468" s="1" t="n">
+      <c r="AB468" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -40359,9 +41766,12 @@
         <v>0.1609</v>
       </c>
       <c r="Z469" s="1" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="AA469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="AA469" s="1" t="n">
+      <c r="AB469" s="1" t="n">
         <v>0.1609</v>
       </c>
     </row>
@@ -40444,9 +41854,12 @@
         <v>0.4083</v>
       </c>
       <c r="Z470" s="1" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="AA470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="AA470" s="1" t="n">
+      <c r="AB470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -40529,9 +41942,12 @@
         <v>0.06872</v>
       </c>
       <c r="Z471" s="1" t="n">
+        <v>0.06876</v>
+      </c>
+      <c r="AA471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="AA471" s="1" t="n">
+      <c r="AB471" s="1" t="n">
         <v>0.06854</v>
       </c>
     </row>
@@ -40614,9 +42030,12 @@
         <v>0.06517000000000001</v>
       </c>
       <c r="Z472" s="1" t="n">
+        <v>0.06539</v>
+      </c>
+      <c r="AA472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="AA472" s="1" t="n">
+      <c r="AB472" s="1" t="n">
         <v>0.06515</v>
       </c>
     </row>
@@ -40699,9 +42118,12 @@
         <v>0.01625</v>
       </c>
       <c r="Z473" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="AA473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="AA473" s="1" t="n">
+      <c r="AB473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -40784,9 +42206,12 @@
         <v>0.2047</v>
       </c>
       <c r="Z474" s="1" t="n">
+        <v>0.2049</v>
+      </c>
+      <c r="AA474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="AA474" s="1" t="n">
+      <c r="AB474" s="1" t="n">
         <v>0.2047</v>
       </c>
     </row>
@@ -40869,9 +42294,12 @@
         <v>0.04139</v>
       </c>
       <c r="Z475" s="1" t="n">
+        <v>0.04156</v>
+      </c>
+      <c r="AA475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="AA475" s="1" t="n">
+      <c r="AB475" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -40954,9 +42382,12 @@
         <v>1.563</v>
       </c>
       <c r="Z476" s="1" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="AA476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="AA476" s="1" t="n">
+      <c r="AB476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -41039,9 +42470,12 @@
         <v>0.1007</v>
       </c>
       <c r="Z477" s="1" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AA477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="AA477" s="1" t="n">
+      <c r="AB477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -41124,9 +42558,12 @@
         <v>0.001152</v>
       </c>
       <c r="Z478" s="1" t="n">
+        <v>0.001154</v>
+      </c>
+      <c r="AA478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="AA478" s="1" t="n">
+      <c r="AB478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -41209,9 +42646,12 @@
         <v>0.1425</v>
       </c>
       <c r="Z479" s="1" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="AA479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="AA479" s="1" t="n">
+      <c r="AB479" s="1" t="n">
         <v>0.1425</v>
       </c>
     </row>
@@ -41294,9 +42734,12 @@
         <v>0.001948</v>
       </c>
       <c r="Z480" s="1" t="n">
+        <v>0.001911</v>
+      </c>
+      <c r="AA480" s="1" t="n">
         <v>0.001969</v>
       </c>
-      <c r="AA480" s="1" t="n">
+      <c r="AB480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -41379,9 +42822,12 @@
         <v>0.902</v>
       </c>
       <c r="Z481" s="1" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="AA481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="AA481" s="1" t="n">
+      <c r="AB481" s="1" t="n">
         <v>0.902</v>
       </c>
     </row>
@@ -41464,9 +42910,12 @@
         <v>0.13321</v>
       </c>
       <c r="Z482" s="1" t="n">
+        <v>0.13306</v>
+      </c>
+      <c r="AA482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="AA482" s="1" t="n">
+      <c r="AB482" s="1" t="n">
         <v>0.13233</v>
       </c>
     </row>
@@ -41549,9 +42998,12 @@
         <v>0.0402</v>
       </c>
       <c r="Z483" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="AA483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="AA483" s="1" t="n">
+      <c r="AB483" s="1" t="n">
         <v>0.04005</v>
       </c>
     </row>
@@ -41634,9 +43086,12 @@
         <v>0.301</v>
       </c>
       <c r="Z484" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AA484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="AA484" s="1" t="n">
+      <c r="AB484" s="1" t="n">
         <v>0.2999</v>
       </c>
     </row>
@@ -41719,9 +43174,12 @@
         <v>0.05608</v>
       </c>
       <c r="Z485" s="1" t="n">
+        <v>0.05625</v>
+      </c>
+      <c r="AA485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="AA485" s="1" t="n">
+      <c r="AB485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -41804,9 +43262,12 @@
         <v>0.001558</v>
       </c>
       <c r="Z486" s="1" t="n">
+        <v>0.001559</v>
+      </c>
+      <c r="AA486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="AA486" s="1" t="n">
+      <c r="AB486" s="1" t="n">
         <v>0.001555</v>
       </c>
     </row>
@@ -41889,9 +43350,12 @@
         <v>0.0665</v>
       </c>
       <c r="Z487" s="1" t="n">
+        <v>0.06669</v>
+      </c>
+      <c r="AA487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="AA487" s="1" t="n">
+      <c r="AB487" s="1" t="n">
         <v>0.0665</v>
       </c>
     </row>
@@ -41974,9 +43438,12 @@
         <v>0.1915</v>
       </c>
       <c r="Z488" s="1" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="AA488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="AA488" s="1" t="n">
+      <c r="AB488" s="1" t="n">
         <v>0.1911</v>
       </c>
     </row>
@@ -42059,9 +43526,12 @@
         <v>0.04765</v>
       </c>
       <c r="Z489" s="1" t="n">
+        <v>0.04767</v>
+      </c>
+      <c r="AA489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="AA489" s="1" t="n">
+      <c r="AB489" s="1" t="n">
         <v>0.04761</v>
       </c>
     </row>
@@ -42144,9 +43614,12 @@
         <v>0.1384</v>
       </c>
       <c r="Z490" s="1" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="AA490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="AA490" s="1" t="n">
+      <c r="AB490" s="1" t="n">
         <v>0.1384</v>
       </c>
     </row>
@@ -42229,9 +43702,12 @@
         <v>0.0225</v>
       </c>
       <c r="Z491" s="1" t="n">
+        <v>0.02262</v>
+      </c>
+      <c r="AA491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="AA491" s="1" t="n">
+      <c r="AB491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -42314,9 +43790,12 @@
         <v>0.007753</v>
       </c>
       <c r="Z492" s="1" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="AA492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="AA492" s="1" t="n">
+      <c r="AB492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -42399,9 +43878,12 @@
         <v>0.0005904</v>
       </c>
       <c r="Z493" s="1" t="n">
+        <v>0.0005904</v>
+      </c>
+      <c r="AA493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="AA493" s="1" t="n">
+      <c r="AB493" s="1" t="n">
         <v>0.0005903</v>
       </c>
     </row>
@@ -42484,9 +43966,12 @@
         <v>3.005</v>
       </c>
       <c r="Z494" s="1" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="AA494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="AA494" s="1" t="n">
+      <c r="AB494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -42569,9 +44054,12 @@
         <v>0.05054</v>
       </c>
       <c r="Z495" s="1" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="AA495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="AA495" s="1" t="n">
+      <c r="AB495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -42654,9 +44142,12 @@
         <v>0.006761</v>
       </c>
       <c r="Z496" s="1" t="n">
+        <v>0.006793</v>
+      </c>
+      <c r="AA496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="AA496" s="1" t="n">
+      <c r="AB496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -42739,9 +44230,12 @@
         <v>1.298</v>
       </c>
       <c r="Z497" s="1" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="AA497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="AA497" s="1" t="n">
+      <c r="AB497" s="1" t="n">
         <v>1.298</v>
       </c>
     </row>
@@ -42824,9 +44318,12 @@
         <v>0.03896</v>
       </c>
       <c r="Z498" s="1" t="n">
+        <v>0.03905</v>
+      </c>
+      <c r="AA498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="AA498" s="1" t="n">
+      <c r="AB498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -42909,9 +44406,12 @@
         <v>0.04093</v>
       </c>
       <c r="Z499" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="AA499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="AA499" s="1" t="n">
+      <c r="AB499" s="1" t="n">
         <v>0.04085</v>
       </c>
     </row>
@@ -42994,9 +44494,12 @@
         <v>0.00541</v>
       </c>
       <c r="Z500" s="1" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="AA500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="AA500" s="1" t="n">
+      <c r="AB500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -43079,9 +44582,12 @@
         <v>0.0355</v>
       </c>
       <c r="Z501" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="AA501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="AA501" s="1" t="n">
+      <c r="AB501" s="1" t="n">
         <v>0.03548</v>
       </c>
     </row>
@@ -43164,9 +44670,12 @@
         <v>0.07195</v>
       </c>
       <c r="Z502" s="1" t="n">
+        <v>0.07207</v>
+      </c>
+      <c r="AA502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="AA502" s="1" t="n">
+      <c r="AB502" s="1" t="n">
         <v>0.07191</v>
       </c>
     </row>
@@ -43249,9 +44758,12 @@
         <v>0.0007389</v>
       </c>
       <c r="Z503" s="1" t="n">
+        <v>0.0007407</v>
+      </c>
+      <c r="AA503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="AA503" s="1" t="n">
+      <c r="AB503" s="1" t="n">
         <v>0.0007389</v>
       </c>
     </row>
@@ -43334,9 +44846,12 @@
         <v>0.016047</v>
       </c>
       <c r="Z504" s="1" t="n">
-        <v>0.016067</v>
+        <v>0.01607</v>
       </c>
       <c r="AA504" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="AB504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -43419,9 +44934,12 @@
         <v>0.00702</v>
       </c>
       <c r="Z505" s="1" t="n">
+        <v>0.00701</v>
+      </c>
+      <c r="AA505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="AA505" s="1" t="n">
+      <c r="AB505" s="1" t="n">
         <v>0.00701</v>
       </c>
     </row>
@@ -43507,6 +45025,9 @@
         <v>0.0257</v>
       </c>
       <c r="AA506" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="AB506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -43589,9 +45110,12 @@
         <v>0.00136</v>
       </c>
       <c r="Z507" s="1" t="n">
-        <v>0.00136</v>
+        <v>0.001362</v>
       </c>
       <c r="AA507" s="1" t="n">
+        <v>0.001362</v>
+      </c>
+      <c r="AB507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -43674,9 +45198,12 @@
         <v>0.281</v>
       </c>
       <c r="Z508" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AA508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="AA508" s="1" t="n">
+      <c r="AB508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -43759,9 +45286,12 @@
         <v>0.1311</v>
       </c>
       <c r="Z509" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="AA509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="AA509" s="1" t="n">
+      <c r="AB509" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -43844,9 +45374,12 @@
         <v>0.04906</v>
       </c>
       <c r="Z510" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="AA510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="AA510" s="1" t="n">
+      <c r="AB510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -43929,9 +45462,12 @@
         <v>0.00269</v>
       </c>
       <c r="Z511" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="AA511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="AA511" s="1" t="n">
+      <c r="AB511" s="1" t="n">
         <v>0.00269</v>
       </c>
     </row>
@@ -44014,9 +45550,12 @@
         <v>0.01501</v>
       </c>
       <c r="Z512" s="1" t="n">
+        <v>0.015037</v>
+      </c>
+      <c r="AA512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="AA512" s="1" t="n">
+      <c r="AB512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -44099,9 +45638,12 @@
         <v>0.6883</v>
       </c>
       <c r="Z513" s="1" t="n">
+        <v>0.6895</v>
+      </c>
+      <c r="AA513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="AA513" s="1" t="n">
+      <c r="AB513" s="1" t="n">
         <v>0.6883</v>
       </c>
     </row>
@@ -44184,9 +45726,12 @@
         <v>0.004529</v>
       </c>
       <c r="Z514" s="1" t="n">
+        <v>0.004549</v>
+      </c>
+      <c r="AA514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="AA514" s="1" t="n">
+      <c r="AB514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -44269,9 +45814,12 @@
         <v>0.005064</v>
       </c>
       <c r="Z515" s="1" t="n">
+        <v>0.005071</v>
+      </c>
+      <c r="AA515" s="1" t="n">
         <v>0.005074</v>
       </c>
-      <c r="AA515" s="1" t="n">
+      <c r="AB515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -44354,10 +45902,13 @@
         <v>0.06307</v>
       </c>
       <c r="Z516" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AA516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="AA516" s="1" t="n">
-        <v>0.06307</v>
+      <c r="AB516" s="1" t="n">
+        <v>0.063</v>
       </c>
     </row>
     <row r="517">
@@ -44439,9 +45990,12 @@
         <v>0.06466</v>
       </c>
       <c r="Z517" s="1" t="n">
+        <v>0.06462</v>
+      </c>
+      <c r="AA517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="AA517" s="1" t="n">
+      <c r="AB517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -44524,9 +46078,12 @@
         <v>0.01195</v>
       </c>
       <c r="Z518" s="1" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="AA518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="AA518" s="1" t="n">
+      <c r="AB518" s="1" t="n">
         <v>0.01195</v>
       </c>
     </row>
@@ -44609,9 +46166,12 @@
         <v>0.04742</v>
       </c>
       <c r="Z519" s="1" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="AA519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="AA519" s="1" t="n">
+      <c r="AB519" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -44694,9 +46254,12 @@
         <v>0.04379</v>
       </c>
       <c r="Z520" s="1" t="n">
+        <v>0.04375</v>
+      </c>
+      <c r="AA520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="AA520" s="1" t="n">
+      <c r="AB520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -44779,9 +46342,12 @@
         <v>0.008288</v>
       </c>
       <c r="Z521" s="1" t="n">
+        <v>0.008366</v>
+      </c>
+      <c r="AA521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="AA521" s="1" t="n">
+      <c r="AB521" s="1" t="n">
         <v>0.008288</v>
       </c>
     </row>
@@ -44864,9 +46430,12 @@
         <v>0.08785999999999999</v>
       </c>
       <c r="Z522" s="1" t="n">
+        <v>0.08776</v>
+      </c>
+      <c r="AA522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="AA522" s="1" t="n">
+      <c r="AB522" s="1" t="n">
         <v>0.08762</v>
       </c>
     </row>
@@ -44949,9 +46518,12 @@
         <v>0.006462</v>
       </c>
       <c r="Z523" s="1" t="n">
+        <v>0.006463</v>
+      </c>
+      <c r="AA523" s="1" t="n">
         <v>0.006503</v>
       </c>
-      <c r="AA523" s="1" t="n">
+      <c r="AB523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -45034,9 +46606,12 @@
         <v>0.0163</v>
       </c>
       <c r="Z524" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="AA524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="AA524" s="1" t="n">
+      <c r="AB524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -45119,9 +46694,12 @@
         <v>0.01784</v>
       </c>
       <c r="Z525" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="AA525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="AA525" s="1" t="n">
+      <c r="AB525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -45204,10 +46782,13 @@
         <v>0.07857</v>
       </c>
       <c r="Z526" s="1" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="AA526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="AA526" s="1" t="n">
-        <v>0.07857</v>
+      <c r="AB526" s="1" t="n">
+        <v>0.0785</v>
       </c>
     </row>
     <row r="527">
@@ -45289,9 +46870,12 @@
         <v>0.01602</v>
       </c>
       <c r="Z527" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AA527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="AA527" s="1" t="n">
+      <c r="AB527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -45374,9 +46958,12 @@
         <v>0.004132</v>
       </c>
       <c r="Z528" s="1" t="n">
+        <v>0.004125</v>
+      </c>
+      <c r="AA528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="AA528" s="1" t="n">
+      <c r="AB528" s="1" t="n">
         <v>0.004113</v>
       </c>
     </row>
@@ -45459,10 +47046,13 @@
         <v>0.003685</v>
       </c>
       <c r="Z529" s="1" t="n">
+        <v>0.003665</v>
+      </c>
+      <c r="AA529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="AA529" s="1" t="n">
-        <v>0.003672</v>
+      <c r="AB529" s="1" t="n">
+        <v>0.003665</v>
       </c>
     </row>
     <row r="530">
@@ -45544,9 +47134,12 @@
         <v>1.32</v>
       </c>
       <c r="Z530" s="1" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="AA530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="AA530" s="1" t="n">
+      <c r="AB530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -45629,9 +47222,12 @@
         <v>0.4866</v>
       </c>
       <c r="Z531" s="1" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="AA531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="AA531" s="1" t="n">
+      <c r="AB531" s="1" t="n">
         <v>0.4866</v>
       </c>
     </row>
@@ -45714,9 +47310,12 @@
         <v>0.03041</v>
       </c>
       <c r="Z532" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="AA532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="AA532" s="1" t="n">
+      <c r="AB532" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -45799,9 +47398,12 @@
         <v>0.1521</v>
       </c>
       <c r="Z533" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="AA533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="AA533" s="1" t="n">
+      <c r="AB533" s="1" t="n">
         <v>0.1521</v>
       </c>
     </row>
@@ -45884,9 +47486,12 @@
         <v>0.05354</v>
       </c>
       <c r="Z534" s="1" t="n">
+        <v>0.05363</v>
+      </c>
+      <c r="AA534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="AA534" s="1" t="n">
+      <c r="AB534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -45969,9 +47574,12 @@
         <v>0.01487</v>
       </c>
       <c r="Z535" s="1" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="AA535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="AA535" s="1" t="n">
+      <c r="AB535" s="1" t="n">
         <v>0.01472</v>
       </c>
     </row>
@@ -46054,9 +47662,12 @@
         <v>0.05843</v>
       </c>
       <c r="Z536" s="1" t="n">
+        <v>0.05829</v>
+      </c>
+      <c r="AA536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="AA536" s="1" t="n">
+      <c r="AB536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -46139,9 +47750,12 @@
         <v>0.0546</v>
       </c>
       <c r="Z537" s="1" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="AA537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="AA537" s="1" t="n">
+      <c r="AB537" s="1" t="n">
         <v>0.0546</v>
       </c>
     </row>
@@ -46224,9 +47838,12 @@
         <v>0.106</v>
       </c>
       <c r="Z538" s="1" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="AA538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="AA538" s="1" t="n">
+      <c r="AB538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -46309,9 +47926,12 @@
         <v>0.01267</v>
       </c>
       <c r="Z539" s="1" t="n">
+        <v>0.01267</v>
+      </c>
+      <c r="AA539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="AA539" s="1" t="n">
+      <c r="AB539" s="1" t="n">
         <v>0.01265</v>
       </c>
     </row>
@@ -46394,9 +48014,12 @@
         <v>0.1725</v>
       </c>
       <c r="Z540" s="1" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="AA540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="AA540" s="1" t="n">
+      <c r="AB540" s="1" t="n">
         <v>0.1721</v>
       </c>
     </row>
@@ -46479,9 +48102,12 @@
         <v>0.1228</v>
       </c>
       <c r="Z541" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="AA541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="AA541" s="1" t="n">
+      <c r="AB541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -46564,9 +48190,12 @@
         <v>0.02496</v>
       </c>
       <c r="Z542" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="AA542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="AA542" s="1" t="n">
+      <c r="AB542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -46649,9 +48278,12 @@
         <v>0.05843</v>
       </c>
       <c r="Z543" s="1" t="n">
+        <v>0.05836</v>
+      </c>
+      <c r="AA543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="AA543" s="1" t="n">
+      <c r="AB543" s="1" t="n">
         <v>0.05832</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB543"/>
+  <dimension ref="A1:AC543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -445,8 +445,9 @@
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -582,10 +583,15 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>price_06:15</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -673,10 +679,13 @@
         <v>71060.39999999999</v>
       </c>
       <c r="AA2" s="1" t="n">
+        <v>70810.60000000001</v>
+      </c>
+      <c r="AB2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="AB2" s="1" t="n">
-        <v>70995.10000000001</v>
+      <c r="AC2" s="1" t="n">
+        <v>70810.60000000001</v>
       </c>
     </row>
     <row r="3">
@@ -761,10 +770,13 @@
         <v>2103.21</v>
       </c>
       <c r="AA3" s="1" t="n">
+        <v>2090.89</v>
+      </c>
+      <c r="AB3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="AB3" s="1" t="n">
-        <v>2098.64</v>
+      <c r="AC3" s="1" t="n">
+        <v>2090.89</v>
       </c>
     </row>
     <row r="4">
@@ -849,10 +861,13 @@
         <v>88.58</v>
       </c>
       <c r="AA4" s="1" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="AB4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="AB4" s="1" t="n">
-        <v>88.47</v>
+      <c r="AC4" s="1" t="n">
+        <v>88.16</v>
       </c>
     </row>
     <row r="5">
@@ -937,9 +952,12 @@
         <v>3.853</v>
       </c>
       <c r="AA5" s="1" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="AB5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AC5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -1025,9 +1043,12 @@
         <v>1.4002</v>
       </c>
       <c r="AA6" s="1" t="n">
+        <v>1.3967</v>
+      </c>
+      <c r="AB6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AC6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -1113,9 +1134,12 @@
         <v>0.09618</v>
       </c>
       <c r="AA7" s="1" t="n">
+        <v>0.09593</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -1201,10 +1225,13 @@
         <v>0.013414</v>
       </c>
       <c r="AA8" s="1" t="n">
+        <v>0.013043</v>
+      </c>
+      <c r="AB8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="AB8" s="1" t="n">
-        <v>0.013414</v>
+      <c r="AC8" s="1" t="n">
+        <v>0.013043</v>
       </c>
     </row>
     <row r="9">
@@ -1289,9 +1316,12 @@
         <v>657.24</v>
       </c>
       <c r="AA9" s="1" t="n">
+        <v>656.16</v>
+      </c>
+      <c r="AB9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="AB9" s="1" t="n">
+      <c r="AC9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1377,9 +1407,12 @@
         <v>19.986</v>
       </c>
       <c r="AA10" s="1" t="n">
+        <v>19.982</v>
+      </c>
+      <c r="AB10" s="1" t="n">
         <v>20.464</v>
       </c>
-      <c r="AB10" s="1" t="n">
+      <c r="AC10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1465,10 +1498,13 @@
         <v>0.0033927</v>
       </c>
       <c r="AA11" s="1" t="n">
+        <v>0.0033745</v>
+      </c>
+      <c r="AB11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="AB11" s="1" t="n">
-        <v>0.0033816</v>
+      <c r="AC11" s="1" t="n">
+        <v>0.0033745</v>
       </c>
     </row>
     <row r="12">
@@ -1553,9 +1589,12 @@
         <v>36.564</v>
       </c>
       <c r="AA12" s="1" t="n">
+        <v>36.266</v>
+      </c>
+      <c r="AB12" s="1" t="n">
         <v>36.869</v>
       </c>
-      <c r="AB12" s="1" t="n">
+      <c r="AC12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1641,10 +1680,13 @@
         <v>209.75</v>
       </c>
       <c r="AA13" s="1" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="AB13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="AB13" s="1" t="n">
-        <v>209.75</v>
+      <c r="AC13" s="1" t="n">
+        <v>208.77</v>
       </c>
     </row>
     <row r="14">
@@ -1729,9 +1771,12 @@
         <v>0.0011412</v>
       </c>
       <c r="AA14" s="1" t="n">
+        <v>0.0011406</v>
+      </c>
+      <c r="AB14" s="1" t="n">
         <v>0.0011412</v>
       </c>
-      <c r="AB14" s="1" t="n">
+      <c r="AC14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1817,9 +1862,12 @@
         <v>0.32231</v>
       </c>
       <c r="AA15" s="1" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AB15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="AB15" s="1" t="n">
+      <c r="AC15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1905,9 +1953,12 @@
         <v>232.75</v>
       </c>
       <c r="AA16" s="1" t="n">
+        <v>232.26</v>
+      </c>
+      <c r="AB16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="AB16" s="1" t="n">
+      <c r="AC16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -1993,10 +2044,13 @@
         <v>0.9983</v>
       </c>
       <c r="AA17" s="1" t="n">
+        <v>0.9921</v>
+      </c>
+      <c r="AB17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="AB17" s="1" t="n">
-        <v>0.9963</v>
+      <c r="AC17" s="1" t="n">
+        <v>0.9921</v>
       </c>
     </row>
     <row r="18">
@@ -2081,10 +2135,13 @@
         <v>0.2667</v>
       </c>
       <c r="AA18" s="1" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AB18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="AB18" s="1" t="n">
-        <v>0.2664</v>
+      <c r="AC18" s="1" t="n">
+        <v>0.2654</v>
       </c>
     </row>
     <row r="19">
@@ -2169,10 +2226,13 @@
         <v>9.757</v>
       </c>
       <c r="AA19" s="1" t="n">
+        <v>9.721</v>
+      </c>
+      <c r="AB19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="AB19" s="1" t="n">
-        <v>9.747999999999999</v>
+      <c r="AC19" s="1" t="n">
+        <v>9.721</v>
       </c>
     </row>
     <row r="20">
@@ -2257,9 +2317,12 @@
         <v>5018.9</v>
       </c>
       <c r="AA20" s="1" t="n">
+        <v>5021.57</v>
+      </c>
+      <c r="AB20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="AB20" s="1" t="n">
+      <c r="AC20" s="1" t="n">
         <v>5012.13</v>
       </c>
     </row>
@@ -2345,10 +2408,13 @@
         <v>462.75</v>
       </c>
       <c r="AA21" s="1" t="n">
+        <v>461.09</v>
+      </c>
+      <c r="AB21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="AB21" s="1" t="n">
-        <v>462.36</v>
+      <c r="AC21" s="1" t="n">
+        <v>461.09</v>
       </c>
     </row>
     <row r="22">
@@ -2433,9 +2499,12 @@
         <v>1.3988</v>
       </c>
       <c r="AA22" s="1" t="n">
+        <v>1.3889</v>
+      </c>
+      <c r="AB22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="AB22" s="1" t="n">
+      <c r="AC22" s="1" t="n">
         <v>1.3686</v>
       </c>
     </row>
@@ -2521,9 +2590,12 @@
         <v>1.0485</v>
       </c>
       <c r="AA23" s="1" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AB23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="AB23" s="1" t="n">
+      <c r="AC23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2609,10 +2681,13 @@
         <v>1.34</v>
       </c>
       <c r="AA24" s="1" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="AB24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="AB24" s="1" t="n">
-        <v>1.34</v>
+      <c r="AC24" s="1" t="n">
+        <v>1.335</v>
       </c>
     </row>
     <row r="25">
@@ -2697,10 +2772,13 @@
         <v>9.130000000000001</v>
       </c>
       <c r="AA25" s="1" t="n">
+        <v>9.086</v>
+      </c>
+      <c r="AB25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="AB25" s="1" t="n">
-        <v>9.113</v>
+      <c r="AC25" s="1" t="n">
+        <v>9.086</v>
       </c>
     </row>
     <row r="26">
@@ -2785,9 +2863,12 @@
         <v>0.361</v>
       </c>
       <c r="AA26" s="1" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AB26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="AB26" s="1" t="n">
+      <c r="AC26" s="1" t="n">
         <v>0.3578</v>
       </c>
     </row>
@@ -2873,10 +2954,13 @@
         <v>0.87</v>
       </c>
       <c r="AA27" s="1" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="AB27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="AB27" s="1" t="n">
-        <v>0.87</v>
+      <c r="AC27" s="1" t="n">
+        <v>0.865</v>
       </c>
     </row>
     <row r="28">
@@ -2961,9 +3045,12 @@
         <v>1.815</v>
       </c>
       <c r="AA28" s="1" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="AB28" s="1" t="n">
         <v>1.863</v>
       </c>
-      <c r="AB28" s="1" t="n">
+      <c r="AC28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -3049,10 +3136,13 @@
         <v>0.1092</v>
       </c>
       <c r="AA29" s="1" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="AB29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="AB29" s="1" t="n">
-        <v>0.1089</v>
+      <c r="AC29" s="1" t="n">
+        <v>0.1086</v>
       </c>
     </row>
     <row r="30">
@@ -3137,10 +3227,13 @@
         <v>0.002013</v>
       </c>
       <c r="AA30" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AB30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="AB30" s="1" t="n">
-        <v>0.002011</v>
+      <c r="AC30" s="1" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
@@ -3225,10 +3318,13 @@
         <v>1.463</v>
       </c>
       <c r="AA31" s="1" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="AB31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="AB31" s="1" t="n">
-        <v>1.46</v>
+      <c r="AC31" s="1" t="n">
+        <v>1.453</v>
       </c>
     </row>
     <row r="32">
@@ -3313,9 +3409,12 @@
         <v>0.1775</v>
       </c>
       <c r="AA32" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="AB32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="AB32" s="1" t="n">
+      <c r="AC32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -3401,9 +3500,12 @@
         <v>0.1042</v>
       </c>
       <c r="AA33" s="1" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="AB33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="AB33" s="1" t="n">
+      <c r="AC33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -3489,10 +3591,13 @@
         <v>112.91</v>
       </c>
       <c r="AA34" s="1" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="AB34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="AB34" s="1" t="n">
-        <v>112.49</v>
+      <c r="AC34" s="1" t="n">
+        <v>112.25</v>
       </c>
     </row>
     <row r="35">
@@ -3577,9 +3682,12 @@
         <v>6.743</v>
       </c>
       <c r="AA35" s="1" t="n">
+        <v>6.614</v>
+      </c>
+      <c r="AB35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="AB35" s="1" t="n">
+      <c r="AC35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -3665,9 +3773,12 @@
         <v>0.018773</v>
       </c>
       <c r="AA36" s="1" t="n">
+        <v>0.018579</v>
+      </c>
+      <c r="AB36" s="1" t="n">
         <v>0.018773</v>
       </c>
-      <c r="AB36" s="1" t="n">
+      <c r="AC36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -3753,10 +3864,13 @@
         <v>0.3602</v>
       </c>
       <c r="AA37" s="1" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AB37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="AB37" s="1" t="n">
-        <v>0.3595</v>
+      <c r="AC37" s="1" t="n">
+        <v>0.3573</v>
       </c>
     </row>
     <row r="38">
@@ -3841,9 +3955,12 @@
         <v>55.63</v>
       </c>
       <c r="AA38" s="1" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="AB38" s="1" t="n">
         <v>55.92</v>
       </c>
-      <c r="AB38" s="1" t="n">
+      <c r="AC38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -3929,9 +4046,12 @@
         <v>0.61153</v>
       </c>
       <c r="AA39" s="1" t="n">
+        <v>0.60905</v>
+      </c>
+      <c r="AB39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="AB39" s="1" t="n">
+      <c r="AC39" s="1" t="n">
         <v>0.5717</v>
       </c>
     </row>
@@ -4017,10 +4137,13 @@
         <v>4.021</v>
       </c>
       <c r="AA40" s="1" t="n">
+        <v>4.006</v>
+      </c>
+      <c r="AB40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="AB40" s="1" t="n">
-        <v>4.017</v>
+      <c r="AC40" s="1" t="n">
+        <v>4.006</v>
       </c>
     </row>
     <row r="41">
@@ -4105,10 +4228,13 @@
         <v>0.04791</v>
       </c>
       <c r="AA41" s="1" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="AB41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="AB41" s="1" t="n">
-        <v>0.04766</v>
+      <c r="AC41" s="1" t="n">
+        <v>0.04741</v>
       </c>
     </row>
     <row r="42">
@@ -4193,10 +4319,13 @@
         <v>0.6997</v>
       </c>
       <c r="AA42" s="1" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="AB42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="AB42" s="1" t="n">
-        <v>0.6995</v>
+      <c r="AC42" s="1" t="n">
+        <v>0.6948</v>
       </c>
     </row>
     <row r="43">
@@ -4281,9 +4410,12 @@
         <v>0.22704</v>
       </c>
       <c r="AA43" s="1" t="n">
+        <v>0.22679</v>
+      </c>
+      <c r="AB43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="AB43" s="1" t="n">
+      <c r="AC43" s="1" t="n">
         <v>0.22604</v>
       </c>
     </row>
@@ -4369,9 +4501,12 @@
         <v>0.36183</v>
       </c>
       <c r="AA44" s="1" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AB44" s="1" t="n">
         <v>0.36291</v>
       </c>
-      <c r="AB44" s="1" t="n">
+      <c r="AC44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -4457,10 +4592,13 @@
         <v>0.1687</v>
       </c>
       <c r="AA45" s="1" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="AB45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="AB45" s="1" t="n">
-        <v>0.1682</v>
+      <c r="AC45" s="1" t="n">
+        <v>0.1673</v>
       </c>
     </row>
     <row r="46">
@@ -4545,9 +4683,12 @@
         <v>0.0259</v>
       </c>
       <c r="AA46" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="AB46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="AB46" s="1" t="n">
+      <c r="AC46" s="1" t="n">
         <v>0.0257</v>
       </c>
     </row>
@@ -4633,10 +4774,13 @@
         <v>0.005946</v>
       </c>
       <c r="AA47" s="1" t="n">
+        <v>0.005926</v>
+      </c>
+      <c r="AB47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="AB47" s="1" t="n">
-        <v>0.00594</v>
+      <c r="AC47" s="1" t="n">
+        <v>0.005926</v>
       </c>
     </row>
     <row r="48">
@@ -4721,10 +4865,13 @@
         <v>0.007331</v>
       </c>
       <c r="AA48" s="1" t="n">
+        <v>0.007288</v>
+      </c>
+      <c r="AB48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="AB48" s="1" t="n">
-        <v>0.007331</v>
+      <c r="AC48" s="1" t="n">
+        <v>0.007288</v>
       </c>
     </row>
     <row r="49">
@@ -4809,9 +4956,12 @@
         <v>0.1092</v>
       </c>
       <c r="AA49" s="1" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="AB49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="AB49" s="1" t="n">
+      <c r="AC49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -4897,9 +5047,12 @@
         <v>0.04115</v>
       </c>
       <c r="AA50" s="1" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="AB50" s="1" t="n">
         <v>0.04222</v>
       </c>
-      <c r="AB50" s="1" t="n">
+      <c r="AC50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -4985,10 +5138,13 @@
         <v>0.1599</v>
       </c>
       <c r="AA51" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="AB51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="AB51" s="1" t="n">
-        <v>0.1599</v>
+      <c r="AC51" s="1" t="n">
+        <v>0.1593</v>
       </c>
     </row>
     <row r="52">
@@ -5073,9 +5229,12 @@
         <v>0.00355</v>
       </c>
       <c r="AA52" s="1" t="n">
+        <v>0.00353</v>
+      </c>
+      <c r="AB52" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="AB52" s="1" t="n">
+      <c r="AC52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -5161,10 +5320,13 @@
         <v>2.616</v>
       </c>
       <c r="AA53" s="1" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="AB53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="AB53" s="1" t="n">
-        <v>2.613</v>
+      <c r="AC53" s="1" t="n">
+        <v>2.606</v>
       </c>
     </row>
     <row r="54">
@@ -5249,10 +5411,13 @@
         <v>0.00618</v>
       </c>
       <c r="AA54" s="1" t="n">
+        <v>0.006149</v>
+      </c>
+      <c r="AB54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="AB54" s="1" t="n">
-        <v>0.006157</v>
+      <c r="AC54" s="1" t="n">
+        <v>0.006149</v>
       </c>
     </row>
     <row r="55">
@@ -5337,9 +5502,12 @@
         <v>0.0275</v>
       </c>
       <c r="AA55" s="1" t="n">
+        <v>0.02805</v>
+      </c>
+      <c r="AB55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="AB55" s="1" t="n">
+      <c r="AC55" s="1" t="n">
         <v>0.02738</v>
       </c>
     </row>
@@ -5425,10 +5593,13 @@
         <v>0.7284</v>
       </c>
       <c r="AA56" s="1" t="n">
+        <v>0.7226</v>
+      </c>
+      <c r="AB56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="AB56" s="1" t="n">
-        <v>0.7284</v>
+      <c r="AC56" s="1" t="n">
+        <v>0.7226</v>
       </c>
     </row>
     <row r="57">
@@ -5513,10 +5684,13 @@
         <v>0.1031</v>
       </c>
       <c r="AA57" s="1" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AB57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="AB57" s="1" t="n">
-        <v>0.103</v>
+      <c r="AC57" s="1" t="n">
+        <v>0.1025</v>
       </c>
     </row>
     <row r="58">
@@ -5601,10 +5775,13 @@
         <v>0.9377</v>
       </c>
       <c r="AA58" s="1" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="AB58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="AB58" s="1" t="n">
-        <v>0.9355</v>
+      <c r="AC58" s="1" t="n">
+        <v>0.9294</v>
       </c>
     </row>
     <row r="59">
@@ -5689,9 +5866,12 @@
         <v>0.08294</v>
       </c>
       <c r="AA59" s="1" t="n">
+        <v>0.08356</v>
+      </c>
+      <c r="AB59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="AB59" s="1" t="n">
+      <c r="AC59" s="1" t="n">
         <v>0.08294</v>
       </c>
     </row>
@@ -5777,9 +5957,12 @@
         <v>0.07701</v>
       </c>
       <c r="AA60" s="1" t="n">
+        <v>0.07337</v>
+      </c>
+      <c r="AB60" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="AB60" s="1" t="n">
+      <c r="AC60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -5865,9 +6048,12 @@
         <v>0.05493</v>
       </c>
       <c r="AA61" s="1" t="n">
+        <v>0.05452</v>
+      </c>
+      <c r="AB61" s="1" t="n">
         <v>0.05539</v>
       </c>
-      <c r="AB61" s="1" t="n">
+      <c r="AC61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -5953,9 +6139,12 @@
         <v>0.010507</v>
       </c>
       <c r="AA62" s="1" t="n">
-        <v>0.010649</v>
+        <v>0.01067</v>
       </c>
       <c r="AB62" s="1" t="n">
+        <v>0.01067</v>
+      </c>
+      <c r="AC62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -6041,9 +6230,12 @@
         <v>0.29231</v>
       </c>
       <c r="AA63" s="1" t="n">
-        <v>0.29231</v>
+        <v>0.29275</v>
       </c>
       <c r="AB63" s="1" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="AC63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -6129,9 +6321,12 @@
         <v>0.06756</v>
       </c>
       <c r="AA64" s="1" t="n">
+        <v>0.06832000000000001</v>
+      </c>
+      <c r="AB64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="AB64" s="1" t="n">
+      <c r="AC64" s="1" t="n">
         <v>0.06756</v>
       </c>
     </row>
@@ -6217,10 +6412,13 @@
         <v>0.3145</v>
       </c>
       <c r="AA65" s="1" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="AB65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="AB65" s="1" t="n">
-        <v>0.3068</v>
+      <c r="AC65" s="1" t="n">
+        <v>0.3062</v>
       </c>
     </row>
     <row r="66">
@@ -6305,9 +6503,12 @@
         <v>0.16587</v>
       </c>
       <c r="AA66" s="1" t="n">
+        <v>0.16554</v>
+      </c>
+      <c r="AB66" s="1" t="n">
         <v>0.16587</v>
       </c>
-      <c r="AB66" s="1" t="n">
+      <c r="AC66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -6393,9 +6594,12 @@
         <v>0.12035</v>
       </c>
       <c r="AA67" s="1" t="n">
+        <v>0.12018</v>
+      </c>
+      <c r="AB67" s="1" t="n">
         <v>0.12035</v>
       </c>
-      <c r="AB67" s="1" t="n">
+      <c r="AC67" s="1" t="n">
         <v>0.1191</v>
       </c>
     </row>
@@ -6481,9 +6685,12 @@
         <v>0.09517</v>
       </c>
       <c r="AA68" s="1" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="AB68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="AB68" s="1" t="n">
+      <c r="AC68" s="1" t="n">
         <v>0.09474</v>
       </c>
     </row>
@@ -6569,10 +6776,13 @@
         <v>0.124</v>
       </c>
       <c r="AA69" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="AB69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="AB69" s="1" t="n">
-        <v>0.1239</v>
+      <c r="AC69" s="1" t="n">
+        <v>0.1231</v>
       </c>
     </row>
     <row r="70">
@@ -6657,10 +6867,13 @@
         <v>8.523999999999999</v>
       </c>
       <c r="AA70" s="1" t="n">
+        <v>8.478</v>
+      </c>
+      <c r="AB70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="AB70" s="1" t="n">
-        <v>8.491</v>
+      <c r="AC70" s="1" t="n">
+        <v>8.478</v>
       </c>
     </row>
     <row r="71">
@@ -6745,10 +6958,13 @@
         <v>0.239</v>
       </c>
       <c r="AA71" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AB71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="AB71" s="1" t="n">
-        <v>0.238</v>
+      <c r="AC71" s="1" t="n">
+        <v>0.236</v>
       </c>
     </row>
     <row r="72">
@@ -6833,10 +7049,13 @@
         <v>0.04999</v>
       </c>
       <c r="AA72" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="AB72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="AB72" s="1" t="n">
-        <v>0.04955</v>
+      <c r="AC72" s="1" t="n">
+        <v>0.04927</v>
       </c>
     </row>
     <row r="73">
@@ -6921,9 +7140,12 @@
         <v>0.05066</v>
       </c>
       <c r="AA73" s="1" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="AB73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="AB73" s="1" t="n">
+      <c r="AC73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -7009,9 +7231,12 @@
         <v>0.123</v>
       </c>
       <c r="AA74" s="1" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="AB74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="AB74" s="1" t="n">
+      <c r="AC74" s="1" t="n">
         <v>0.1221</v>
       </c>
     </row>
@@ -7097,9 +7322,12 @@
         <v>0.04665</v>
       </c>
       <c r="AA75" s="1" t="n">
+        <v>0.04675</v>
+      </c>
+      <c r="AB75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="AB75" s="1" t="n">
+      <c r="AC75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -7185,10 +7413,13 @@
         <v>0.06637999999999999</v>
       </c>
       <c r="AA76" s="1" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="AB76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="AB76" s="1" t="n">
-        <v>0.06630999999999999</v>
+      <c r="AC76" s="1" t="n">
+        <v>0.06610000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7273,9 +7504,12 @@
         <v>0.1331</v>
       </c>
       <c r="AA77" s="1" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="AB77" s="1" t="n">
         <v>0.13727</v>
       </c>
-      <c r="AB77" s="1" t="n">
+      <c r="AC77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -7361,10 +7595,13 @@
         <v>0.1607</v>
       </c>
       <c r="AA78" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="AB78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="AB78" s="1" t="n">
-        <v>0.1607</v>
+      <c r="AC78" s="1" t="n">
+        <v>0.1585</v>
       </c>
     </row>
     <row r="79">
@@ -7449,10 +7686,13 @@
         <v>0.02694</v>
       </c>
       <c r="AA79" s="1" t="n">
+        <v>0.02691</v>
+      </c>
+      <c r="AB79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="AB79" s="1" t="n">
-        <v>0.02692</v>
+      <c r="AC79" s="1" t="n">
+        <v>0.02691</v>
       </c>
     </row>
     <row r="80">
@@ -7537,9 +7777,12 @@
         <v>356.11</v>
       </c>
       <c r="AA80" s="1" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="AB80" s="1" t="n">
         <v>362.68</v>
       </c>
-      <c r="AB80" s="1" t="n">
+      <c r="AC80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -7625,10 +7868,13 @@
         <v>7.032e-05</v>
       </c>
       <c r="AA81" s="1" t="n">
+        <v>6.984e-05</v>
+      </c>
+      <c r="AB81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="AB81" s="1" t="n">
-        <v>7.029000000000001e-05</v>
+      <c r="AC81" s="1" t="n">
+        <v>6.984e-05</v>
       </c>
     </row>
     <row r="82">
@@ -7713,10 +7959,13 @@
         <v>0.2646</v>
       </c>
       <c r="AA82" s="1" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="AB82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="AB82" s="1" t="n">
-        <v>0.2645</v>
+      <c r="AC82" s="1" t="n">
+        <v>0.2629</v>
       </c>
     </row>
     <row r="83">
@@ -7801,9 +8050,12 @@
         <v>1.1204</v>
       </c>
       <c r="AA83" s="1" t="n">
+        <v>1.1078</v>
+      </c>
+      <c r="AB83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="AB83" s="1" t="n">
+      <c r="AC83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -7889,10 +8141,13 @@
         <v>0.3508</v>
       </c>
       <c r="AA84" s="1" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="AB84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="AB84" s="1" t="n">
-        <v>0.3496</v>
+      <c r="AC84" s="1" t="n">
+        <v>0.3468</v>
       </c>
     </row>
     <row r="85">
@@ -7977,10 +8232,13 @@
         <v>1.9378</v>
       </c>
       <c r="AA85" s="1" t="n">
+        <v>1.9329</v>
+      </c>
+      <c r="AB85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="AB85" s="1" t="n">
-        <v>1.9339</v>
+      <c r="AC85" s="1" t="n">
+        <v>1.9329</v>
       </c>
     </row>
     <row r="86">
@@ -8065,9 +8323,12 @@
         <v>1.3218</v>
       </c>
       <c r="AA86" s="1" t="n">
+        <v>1.3126</v>
+      </c>
+      <c r="AB86" s="1" t="n">
         <v>1.3218</v>
       </c>
-      <c r="AB86" s="1" t="n">
+      <c r="AC86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -8153,10 +8414,13 @@
         <v>32.41</v>
       </c>
       <c r="AA87" s="1" t="n">
+        <v>32.32</v>
+      </c>
+      <c r="AB87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="AB87" s="1" t="n">
-        <v>32.4</v>
+      <c r="AC87" s="1" t="n">
+        <v>32.32</v>
       </c>
     </row>
     <row r="88">
@@ -8241,9 +8505,12 @@
         <v>0.009520000000000001</v>
       </c>
       <c r="AA88" s="1" t="n">
+        <v>0.00944</v>
+      </c>
+      <c r="AB88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="AB88" s="1" t="n">
+      <c r="AC88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -8329,10 +8596,13 @@
         <v>0.01769</v>
       </c>
       <c r="AA89" s="1" t="n">
+        <v>0.01755</v>
+      </c>
+      <c r="AB89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="AB89" s="1" t="n">
-        <v>0.01769</v>
+      <c r="AC89" s="1" t="n">
+        <v>0.01755</v>
       </c>
     </row>
     <row r="90">
@@ -8417,10 +8687,13 @@
         <v>0.03423</v>
       </c>
       <c r="AA90" s="1" t="n">
+        <v>0.03388</v>
+      </c>
+      <c r="AB90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="AB90" s="1" t="n">
-        <v>0.03423</v>
+      <c r="AC90" s="1" t="n">
+        <v>0.03388</v>
       </c>
     </row>
     <row r="91">
@@ -8505,9 +8778,12 @@
         <v>0.01159</v>
       </c>
       <c r="AA91" s="1" t="n">
+        <v>0.01154</v>
+      </c>
+      <c r="AB91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AB91" s="1" t="n">
+      <c r="AC91" s="1" t="n">
         <v>0.01154</v>
       </c>
     </row>
@@ -8593,10 +8869,13 @@
         <v>3.1</v>
       </c>
       <c r="AA92" s="1" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="AB92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="AB92" s="1" t="n">
-        <v>3.09</v>
+      <c r="AC92" s="1" t="n">
+        <v>3.085</v>
       </c>
     </row>
     <row r="93">
@@ -8681,9 +8960,12 @@
         <v>0.005591</v>
       </c>
       <c r="AA93" s="1" t="n">
+        <v>0.005566</v>
+      </c>
+      <c r="AB93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="AB93" s="1" t="n">
+      <c r="AC93" s="1" t="n">
         <v>0.005559</v>
       </c>
     </row>
@@ -8769,9 +9051,12 @@
         <v>0.0939</v>
       </c>
       <c r="AA94" s="1" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="AB94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="AB94" s="1" t="n">
+      <c r="AC94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -8857,9 +9142,12 @@
         <v>0.6385999999999999</v>
       </c>
       <c r="AA95" s="1" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="AB95" s="1" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="AC95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -8945,9 +9233,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="AA96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="AB96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="AB96" s="1" t="n">
+      <c r="AC96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -9033,9 +9324,12 @@
         <v>1.104</v>
       </c>
       <c r="AA97" s="1" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="AB97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="AB97" s="1" t="n">
+      <c r="AC97" s="1" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -9121,10 +9415,13 @@
         <v>0.25007</v>
       </c>
       <c r="AA98" s="1" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="AB98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="AB98" s="1" t="n">
-        <v>0.24996</v>
+      <c r="AC98" s="1" t="n">
+        <v>0.2466</v>
       </c>
     </row>
     <row r="99">
@@ -9209,9 +9506,12 @@
         <v>1.155</v>
       </c>
       <c r="AA99" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="AB99" s="1" t="n">
         <v>1.157</v>
       </c>
-      <c r="AB99" s="1" t="n">
+      <c r="AC99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -9297,9 +9597,12 @@
         <v>1.86</v>
       </c>
       <c r="AA100" s="1" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="AB100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="AB100" s="1" t="n">
+      <c r="AC100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -9385,10 +9688,13 @@
         <v>0.01567</v>
       </c>
       <c r="AA101" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="AB101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="AB101" s="1" t="n">
-        <v>0.01563</v>
+      <c r="AC101" s="1" t="n">
+        <v>0.01557</v>
       </c>
     </row>
     <row r="102">
@@ -9473,9 +9779,12 @@
         <v>0.10151</v>
       </c>
       <c r="AA102" s="1" t="n">
+        <v>0.10142</v>
+      </c>
+      <c r="AB102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="AB102" s="1" t="n">
+      <c r="AC102" s="1" t="n">
         <v>0.10062</v>
       </c>
     </row>
@@ -9561,10 +9870,13 @@
         <v>0.0005969</v>
       </c>
       <c r="AA103" s="1" t="n">
+        <v>0.0005925</v>
+      </c>
+      <c r="AB103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="AB103" s="1" t="n">
-        <v>0.0005941</v>
+      <c r="AC103" s="1" t="n">
+        <v>0.0005925</v>
       </c>
     </row>
     <row r="104">
@@ -9649,9 +9961,12 @@
         <v>0.000572</v>
       </c>
       <c r="AA104" s="1" t="n">
+        <v>0.0005710999999999999</v>
+      </c>
+      <c r="AB104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="AB104" s="1" t="n">
+      <c r="AC104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -9737,10 +10052,13 @@
         <v>0.003223</v>
       </c>
       <c r="AA105" s="1" t="n">
+        <v>0.003191</v>
+      </c>
+      <c r="AB105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="AB105" s="1" t="n">
-        <v>0.003213</v>
+      <c r="AC105" s="1" t="n">
+        <v>0.003191</v>
       </c>
     </row>
     <row r="106">
@@ -9825,10 +10143,13 @@
         <v>2.555</v>
       </c>
       <c r="AA106" s="1" t="n">
+        <v>2.523</v>
+      </c>
+      <c r="AB106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="AB106" s="1" t="n">
-        <v>2.551</v>
+      <c r="AC106" s="1" t="n">
+        <v>2.523</v>
       </c>
     </row>
     <row r="107">
@@ -9913,9 +10234,12 @@
         <v>0.1658</v>
       </c>
       <c r="AA107" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="AB107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="AB107" s="1" t="n">
+      <c r="AC107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -10001,10 +10325,13 @@
         <v>0.0959</v>
       </c>
       <c r="AA108" s="1" t="n">
+        <v>0.09544999999999999</v>
+      </c>
+      <c r="AB108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="AB108" s="1" t="n">
-        <v>0.0955</v>
+      <c r="AC108" s="1" t="n">
+        <v>0.09544999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -10089,9 +10416,12 @@
         <v>0.02214</v>
       </c>
       <c r="AA109" s="1" t="n">
+        <v>0.02212</v>
+      </c>
+      <c r="AB109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="AB109" s="1" t="n">
+      <c r="AC109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -10177,10 +10507,13 @@
         <v>0.2871</v>
       </c>
       <c r="AA110" s="1" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AB110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="AB110" s="1" t="n">
-        <v>0.2859</v>
+      <c r="AC110" s="1" t="n">
+        <v>0.2851</v>
       </c>
     </row>
     <row r="111">
@@ -10265,9 +10598,12 @@
         <v>0.05698</v>
       </c>
       <c r="AA111" s="1" t="n">
+        <v>0.05664</v>
+      </c>
+      <c r="AB111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="AB111" s="1" t="n">
+      <c r="AC111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -10353,10 +10689,13 @@
         <v>0.301</v>
       </c>
       <c r="AA112" s="1" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="AB112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="AB112" s="1" t="n">
-        <v>0.3002</v>
+      <c r="AC112" s="1" t="n">
+        <v>0.2989</v>
       </c>
     </row>
     <row r="113">
@@ -10441,9 +10780,12 @@
         <v>18.54</v>
       </c>
       <c r="AA113" s="1" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AB113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="AB113" s="1" t="n">
+      <c r="AC113" s="1" t="n">
         <v>18.52</v>
       </c>
     </row>
@@ -10529,9 +10871,12 @@
         <v>0.12724</v>
       </c>
       <c r="AA114" s="1" t="n">
+        <v>0.12767</v>
+      </c>
+      <c r="AB114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="AB114" s="1" t="n">
+      <c r="AC114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -10617,9 +10962,12 @@
         <v>0.01589</v>
       </c>
       <c r="AA115" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="AB115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="AB115" s="1" t="n">
+      <c r="AC115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -10705,10 +11053,13 @@
         <v>0.0847</v>
       </c>
       <c r="AA116" s="1" t="n">
+        <v>0.08411</v>
+      </c>
+      <c r="AB116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="AB116" s="1" t="n">
-        <v>0.08442</v>
+      <c r="AC116" s="1" t="n">
+        <v>0.08411</v>
       </c>
     </row>
     <row r="117">
@@ -10793,9 +11144,12 @@
         <v>0.046106</v>
       </c>
       <c r="AA117" s="1" t="n">
+        <v>0.046473</v>
+      </c>
+      <c r="AB117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="AB117" s="1" t="n">
+      <c r="AC117" s="1" t="n">
         <v>0.046106</v>
       </c>
     </row>
@@ -10881,10 +11235,13 @@
         <v>0.04716</v>
       </c>
       <c r="AA118" s="1" t="n">
+        <v>0.04685</v>
+      </c>
+      <c r="AB118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="AB118" s="1" t="n">
-        <v>0.04701</v>
+      <c r="AC118" s="1" t="n">
+        <v>0.04685</v>
       </c>
     </row>
     <row r="119">
@@ -10969,9 +11326,12 @@
         <v>0.04002</v>
       </c>
       <c r="AA119" s="1" t="n">
+        <v>0.04013</v>
+      </c>
+      <c r="AB119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="AB119" s="1" t="n">
+      <c r="AC119" s="1" t="n">
         <v>0.03993</v>
       </c>
     </row>
@@ -11057,9 +11417,12 @@
         <v>0.14525</v>
       </c>
       <c r="AA120" s="1" t="n">
+        <v>0.14603</v>
+      </c>
+      <c r="AB120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="AB120" s="1" t="n">
+      <c r="AC120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -11145,10 +11508,13 @@
         <v>0.1243</v>
       </c>
       <c r="AA121" s="1" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="AB121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="AB121" s="1" t="n">
-        <v>0.1243</v>
+      <c r="AC121" s="1" t="n">
+        <v>0.1239</v>
       </c>
     </row>
     <row r="122">
@@ -11233,10 +11599,13 @@
         <v>1.833</v>
       </c>
       <c r="AA122" s="1" t="n">
+        <v>1.819</v>
+      </c>
+      <c r="AB122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="AB122" s="1" t="n">
-        <v>1.831</v>
+      <c r="AC122" s="1" t="n">
+        <v>1.819</v>
       </c>
     </row>
     <row r="123">
@@ -11321,10 +11690,13 @@
         <v>0.03003</v>
       </c>
       <c r="AA123" s="1" t="n">
+        <v>0.02985</v>
+      </c>
+      <c r="AB123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="AB123" s="1" t="n">
-        <v>0.03001</v>
+      <c r="AC123" s="1" t="n">
+        <v>0.02985</v>
       </c>
     </row>
     <row r="124">
@@ -11409,9 +11781,12 @@
         <v>0.13192</v>
       </c>
       <c r="AA124" s="1" t="n">
+        <v>0.13157</v>
+      </c>
+      <c r="AB124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="AB124" s="1" t="n">
+      <c r="AC124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -11497,10 +11872,13 @@
         <v>0.04081</v>
       </c>
       <c r="AA125" s="1" t="n">
+        <v>0.04068</v>
+      </c>
+      <c r="AB125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="AB125" s="1" t="n">
-        <v>0.04075</v>
+      <c r="AC125" s="1" t="n">
+        <v>0.04068</v>
       </c>
     </row>
     <row r="126">
@@ -11585,10 +11963,13 @@
         <v>0.115</v>
       </c>
       <c r="AA126" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="AB126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="AB126" s="1" t="n">
-        <v>0.1141</v>
+      <c r="AC126" s="1" t="n">
+        <v>0.1135</v>
       </c>
     </row>
     <row r="127">
@@ -11673,9 +12054,12 @@
         <v>0.5446</v>
       </c>
       <c r="AA127" s="1" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="AB127" s="1" t="n">
         <v>0.5446</v>
       </c>
-      <c r="AB127" s="1" t="n">
+      <c r="AC127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -11761,9 +12145,12 @@
         <v>0.03811</v>
       </c>
       <c r="AA128" s="1" t="n">
+        <v>0.03795</v>
+      </c>
+      <c r="AB128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="AB128" s="1" t="n">
+      <c r="AC128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -11849,9 +12236,12 @@
         <v>0.795</v>
       </c>
       <c r="AA129" s="1" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="AB129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="AB129" s="1" t="n">
+      <c r="AC129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -11937,9 +12327,12 @@
         <v>0.03446</v>
       </c>
       <c r="AA130" s="1" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="AB130" s="1" t="n">
         <v>0.03463</v>
       </c>
-      <c r="AB130" s="1" t="n">
+      <c r="AC130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -12025,9 +12418,12 @@
         <v>0.4252</v>
       </c>
       <c r="AA131" s="1" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="AB131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="AB131" s="1" t="n">
+      <c r="AC131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -12113,9 +12509,12 @@
         <v>0.04309</v>
       </c>
       <c r="AA132" s="1" t="n">
+        <v>0.04301</v>
+      </c>
+      <c r="AB132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="AB132" s="1" t="n">
+      <c r="AC132" s="1" t="n">
         <v>0.04296</v>
       </c>
     </row>
@@ -12201,10 +12600,13 @@
         <v>1.2826</v>
       </c>
       <c r="AA133" s="1" t="n">
+        <v>1.2782</v>
+      </c>
+      <c r="AB133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="AB133" s="1" t="n">
-        <v>1.2805</v>
+      <c r="AC133" s="1" t="n">
+        <v>1.2782</v>
       </c>
     </row>
     <row r="134">
@@ -12289,9 +12691,12 @@
         <v>0.02181</v>
       </c>
       <c r="AA134" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="AB134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="AB134" s="1" t="n">
+      <c r="AC134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -12377,10 +12782,13 @@
         <v>0.0004562</v>
       </c>
       <c r="AA135" s="1" t="n">
+        <v>0.0004514</v>
+      </c>
+      <c r="AB135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="AB135" s="1" t="n">
-        <v>0.0004561</v>
+      <c r="AC135" s="1" t="n">
+        <v>0.0004514</v>
       </c>
     </row>
     <row r="136">
@@ -12465,9 +12873,12 @@
         <v>0.001886</v>
       </c>
       <c r="AA136" s="1" t="n">
+        <v>0.001886</v>
+      </c>
+      <c r="AB136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="AB136" s="1" t="n">
+      <c r="AC136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -12553,10 +12964,13 @@
         <v>0.3132</v>
       </c>
       <c r="AA137" s="1" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AB137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="AB137" s="1" t="n">
-        <v>0.3132</v>
+      <c r="AC137" s="1" t="n">
+        <v>0.3086</v>
       </c>
     </row>
     <row r="138">
@@ -12641,10 +13055,13 @@
         <v>0.5578</v>
       </c>
       <c r="AA138" s="1" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="AB138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="AB138" s="1" t="n">
-        <v>0.5578</v>
+      <c r="AC138" s="1" t="n">
+        <v>0.5552</v>
       </c>
     </row>
     <row r="139">
@@ -12729,9 +13146,12 @@
         <v>0.02116</v>
       </c>
       <c r="AA139" s="1" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="AB139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="AB139" s="1" t="n">
+      <c r="AC139" s="1" t="n">
         <v>0.02115</v>
       </c>
     </row>
@@ -12817,10 +13237,13 @@
         <v>0.07931000000000001</v>
       </c>
       <c r="AA140" s="1" t="n">
+        <v>0.07879</v>
+      </c>
+      <c r="AB140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="AB140" s="1" t="n">
-        <v>0.07929</v>
+      <c r="AC140" s="1" t="n">
+        <v>0.07879</v>
       </c>
     </row>
     <row r="141">
@@ -12905,9 +13328,12 @@
         <v>0.001523</v>
       </c>
       <c r="AA141" s="1" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="AB141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="AB141" s="1" t="n">
+      <c r="AC141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -12993,9 +13419,12 @@
         <v>0.4453</v>
       </c>
       <c r="AA142" s="1" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="AB142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="AB142" s="1" t="n">
+      <c r="AC142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -13081,9 +13510,12 @@
         <v>0.029754</v>
       </c>
       <c r="AA143" s="1" t="n">
+        <v>0.029809</v>
+      </c>
+      <c r="AB143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="AB143" s="1" t="n">
+      <c r="AC143" s="1" t="n">
         <v>0.029754</v>
       </c>
     </row>
@@ -13169,9 +13601,12 @@
         <v>0.000226</v>
       </c>
       <c r="AA144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="AB144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="AB144" s="1" t="n">
+      <c r="AC144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -13257,9 +13692,12 @@
         <v>0.03481</v>
       </c>
       <c r="AA145" s="1" t="n">
+        <v>0.03368</v>
+      </c>
+      <c r="AB145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="AB145" s="1" t="n">
+      <c r="AC145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -13345,9 +13783,12 @@
         <v>0.11778</v>
       </c>
       <c r="AA146" s="1" t="n">
-        <v>0.11778</v>
+        <v>0.1178</v>
       </c>
       <c r="AB146" s="1" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="AC146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -13433,9 +13874,12 @@
         <v>0.02216</v>
       </c>
       <c r="AA147" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="AB147" s="1" t="n">
         <v>0.02258</v>
       </c>
-      <c r="AB147" s="1" t="n">
+      <c r="AC147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -13521,9 +13965,12 @@
         <v>1.4123</v>
       </c>
       <c r="AA148" s="1" t="n">
+        <v>1.4084</v>
+      </c>
+      <c r="AB148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="AB148" s="1" t="n">
+      <c r="AC148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -13609,10 +14056,13 @@
         <v>1.854</v>
       </c>
       <c r="AA149" s="1" t="n">
+        <v>1.8462</v>
+      </c>
+      <c r="AB149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="AB149" s="1" t="n">
-        <v>1.854</v>
+      <c r="AC149" s="1" t="n">
+        <v>1.8462</v>
       </c>
     </row>
     <row r="150">
@@ -13697,9 +14147,12 @@
         <v>0.095</v>
       </c>
       <c r="AA150" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AB150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="AB150" s="1" t="n">
+      <c r="AC150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -13785,9 +14238,12 @@
         <v>4.65</v>
       </c>
       <c r="AA151" s="1" t="n">
+        <v>4.639</v>
+      </c>
+      <c r="AB151" s="1" t="n">
         <v>4.731</v>
       </c>
-      <c r="AB151" s="1" t="n">
+      <c r="AC151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -13873,9 +14329,12 @@
         <v>5.578</v>
       </c>
       <c r="AA152" s="1" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AB152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="AB152" s="1" t="n">
+      <c r="AC152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -13961,9 +14420,12 @@
         <v>0.3196</v>
       </c>
       <c r="AA153" s="1" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AB153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="AB153" s="1" t="n">
+      <c r="AC153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -14049,10 +14511,13 @@
         <v>0.5845</v>
       </c>
       <c r="AA154" s="1" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="AB154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="AB154" s="1" t="n">
-        <v>0.5825</v>
+      <c r="AC154" s="1" t="n">
+        <v>0.5824</v>
       </c>
     </row>
     <row r="155">
@@ -14137,10 +14602,13 @@
         <v>0.01269</v>
       </c>
       <c r="AA155" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AB155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="AB155" s="1" t="n">
-        <v>0.01266</v>
+      <c r="AC155" s="1" t="n">
+        <v>0.0126</v>
       </c>
     </row>
     <row r="156">
@@ -14225,10 +14693,13 @@
         <v>0.097</v>
       </c>
       <c r="AA156" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="AB156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="AB156" s="1" t="n">
-        <v>0.097</v>
+      <c r="AC156" s="1" t="n">
+        <v>0.0963</v>
       </c>
     </row>
     <row r="157">
@@ -14313,10 +14784,13 @@
         <v>16.345</v>
       </c>
       <c r="AA157" s="1" t="n">
+        <v>16.215</v>
+      </c>
+      <c r="AB157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="AB157" s="1" t="n">
-        <v>16.341</v>
+      <c r="AC157" s="1" t="n">
+        <v>16.215</v>
       </c>
     </row>
     <row r="158">
@@ -14401,9 +14875,12 @@
         <v>0.05532</v>
       </c>
       <c r="AA158" s="1" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="AB158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="AB158" s="1" t="n">
+      <c r="AC158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -14489,10 +14966,13 @@
         <v>28.62</v>
       </c>
       <c r="AA159" s="1" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="AB159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="AB159" s="1" t="n">
-        <v>28.57</v>
+      <c r="AC159" s="1" t="n">
+        <v>28.38</v>
       </c>
     </row>
     <row r="160">
@@ -14577,9 +15057,12 @@
         <v>0.0218</v>
       </c>
       <c r="AA160" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="AB160" s="1" t="n">
         <v>0.0218</v>
       </c>
-      <c r="AB160" s="1" t="n">
+      <c r="AC160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -14665,10 +15148,13 @@
         <v>0.0006522</v>
       </c>
       <c r="AA161" s="1" t="n">
+        <v>0.0006465</v>
+      </c>
+      <c r="AB161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="AB161" s="1" t="n">
-        <v>0.0006503</v>
+      <c r="AC161" s="1" t="n">
+        <v>0.0006465</v>
       </c>
     </row>
     <row r="162">
@@ -14753,9 +15239,12 @@
         <v>0.393</v>
       </c>
       <c r="AA162" s="1" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AB162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="AB162" s="1" t="n">
+      <c r="AC162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -14841,10 +15330,13 @@
         <v>0.1904</v>
       </c>
       <c r="AA163" s="1" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="AB163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="AB163" s="1" t="n">
-        <v>0.1903</v>
+      <c r="AC163" s="1" t="n">
+        <v>0.1887</v>
       </c>
     </row>
     <row r="164">
@@ -14929,10 +15421,13 @@
         <v>0.316</v>
       </c>
       <c r="AA164" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AB164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="AB164" s="1" t="n">
-        <v>0.314</v>
+      <c r="AC164" s="1" t="n">
+        <v>0.313</v>
       </c>
     </row>
     <row r="165">
@@ -15017,9 +15512,12 @@
         <v>0.375</v>
       </c>
       <c r="AA165" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AB165" s="1" t="n">
         <v>0.378</v>
       </c>
-      <c r="AB165" s="1" t="n">
+      <c r="AC165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -15105,9 +15603,12 @@
         <v>0.0225</v>
       </c>
       <c r="AA166" s="1" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="AB166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="AB166" s="1" t="n">
+      <c r="AC166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -15193,10 +15694,13 @@
         <v>0.00726</v>
       </c>
       <c r="AA167" s="1" t="n">
+        <v>0.007227</v>
+      </c>
+      <c r="AB167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="AB167" s="1" t="n">
-        <v>0.007256</v>
+      <c r="AC167" s="1" t="n">
+        <v>0.007227</v>
       </c>
     </row>
     <row r="168">
@@ -15281,10 +15785,13 @@
         <v>0.0133</v>
       </c>
       <c r="AA168" s="1" t="n">
+        <v>0.01313</v>
+      </c>
+      <c r="AB168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="AB168" s="1" t="n">
-        <v>0.01324</v>
+      <c r="AC168" s="1" t="n">
+        <v>0.01313</v>
       </c>
     </row>
     <row r="169">
@@ -15369,9 +15876,12 @@
         <v>0.25558</v>
       </c>
       <c r="AA169" s="1" t="n">
+        <v>0.25381</v>
+      </c>
+      <c r="AB169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="AB169" s="1" t="n">
+      <c r="AC169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -15457,9 +15967,12 @@
         <v>0.0221</v>
       </c>
       <c r="AA170" s="1" t="n">
-        <v>0.0221</v>
+        <v>0.02218</v>
       </c>
       <c r="AB170" s="1" t="n">
+        <v>0.02218</v>
+      </c>
+      <c r="AC170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -15545,9 +16058,12 @@
         <v>0.1713</v>
       </c>
       <c r="AA171" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="AB171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="AB171" s="1" t="n">
+      <c r="AC171" s="1" t="n">
         <v>0.1708</v>
       </c>
     </row>
@@ -15633,9 +16149,12 @@
         <v>0.089</v>
       </c>
       <c r="AA172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AB172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="AB172" s="1" t="n">
+      <c r="AC172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -15721,10 +16240,13 @@
         <v>0.004681</v>
       </c>
       <c r="AA173" s="1" t="n">
+        <v>0.004656</v>
+      </c>
+      <c r="AB173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="AB173" s="1" t="n">
-        <v>0.004662</v>
+      <c r="AC173" s="1" t="n">
+        <v>0.004656</v>
       </c>
     </row>
     <row r="174">
@@ -15809,9 +16331,12 @@
         <v>0.4428</v>
       </c>
       <c r="AA174" s="1" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="AB174" s="1" t="n">
         <v>0.4428</v>
       </c>
-      <c r="AB174" s="1" t="n">
+      <c r="AC174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -15897,9 +16422,12 @@
         <v>0.09235</v>
       </c>
       <c r="AA175" s="1" t="n">
+        <v>0.09229</v>
+      </c>
+      <c r="AB175" s="1" t="n">
         <v>0.09276</v>
       </c>
-      <c r="AB175" s="1" t="n">
+      <c r="AC175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -15985,10 +16513,13 @@
         <v>0.2427</v>
       </c>
       <c r="AA176" s="1" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="AB176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="AB176" s="1" t="n">
-        <v>0.2425</v>
+      <c r="AC176" s="1" t="n">
+        <v>0.2417</v>
       </c>
     </row>
     <row r="177">
@@ -16073,10 +16604,13 @@
         <v>0.0192</v>
       </c>
       <c r="AA177" s="1" t="n">
+        <v>0.01907</v>
+      </c>
+      <c r="AB177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="AB177" s="1" t="n">
-        <v>0.01908</v>
+      <c r="AC177" s="1" t="n">
+        <v>0.01907</v>
       </c>
     </row>
     <row r="178">
@@ -16161,10 +16695,13 @@
         <v>6.095</v>
       </c>
       <c r="AA178" s="1" t="n">
+        <v>6.059</v>
+      </c>
+      <c r="AB178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="AB178" s="1" t="n">
-        <v>6.09</v>
+      <c r="AC178" s="1" t="n">
+        <v>6.059</v>
       </c>
     </row>
     <row r="179">
@@ -16249,10 +16786,13 @@
         <v>0.1356</v>
       </c>
       <c r="AA179" s="1" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="AB179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="AB179" s="1" t="n">
-        <v>0.1349</v>
+      <c r="AC179" s="1" t="n">
+        <v>0.1346</v>
       </c>
     </row>
     <row r="180">
@@ -16337,9 +16877,12 @@
         <v>0.004973</v>
       </c>
       <c r="AA180" s="1" t="n">
+        <v>0.00493</v>
+      </c>
+      <c r="AB180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="AB180" s="1" t="n">
+      <c r="AC180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -16425,9 +16968,12 @@
         <v>0.01191</v>
       </c>
       <c r="AA181" s="1" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="AB181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AB181" s="1" t="n">
+      <c r="AC181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -16513,10 +17059,13 @@
         <v>0.007244</v>
       </c>
       <c r="AA182" s="1" t="n">
+        <v>0.007168</v>
+      </c>
+      <c r="AB182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="AB182" s="1" t="n">
-        <v>0.007212</v>
+      <c r="AC182" s="1" t="n">
+        <v>0.007168</v>
       </c>
     </row>
     <row r="183">
@@ -16601,9 +17150,12 @@
         <v>0.13141</v>
       </c>
       <c r="AA183" s="1" t="n">
-        <v>0.13206</v>
+        <v>0.13233</v>
       </c>
       <c r="AB183" s="1" t="n">
+        <v>0.13233</v>
+      </c>
+      <c r="AC183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -16689,9 +17241,12 @@
         <v>0.09626</v>
       </c>
       <c r="AA184" s="1" t="n">
+        <v>0.09562</v>
+      </c>
+      <c r="AB184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="AB184" s="1" t="n">
+      <c r="AC184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -16777,10 +17332,13 @@
         <v>0.00752</v>
       </c>
       <c r="AA185" s="1" t="n">
+        <v>0.00743</v>
+      </c>
+      <c r="AB185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="AB185" s="1" t="n">
-        <v>0.0075</v>
+      <c r="AC185" s="1" t="n">
+        <v>0.00743</v>
       </c>
     </row>
     <row r="186">
@@ -16865,10 +17423,13 @@
         <v>0.04851</v>
       </c>
       <c r="AA186" s="1" t="n">
+        <v>0.04828</v>
+      </c>
+      <c r="AB186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="AB186" s="1" t="n">
-        <v>0.04848</v>
+      <c r="AC186" s="1" t="n">
+        <v>0.04828</v>
       </c>
     </row>
     <row r="187">
@@ -16953,10 +17514,13 @@
         <v>0.02661</v>
       </c>
       <c r="AA187" s="1" t="n">
+        <v>0.02644</v>
+      </c>
+      <c r="AB187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="AB187" s="1" t="n">
-        <v>0.02652</v>
+      <c r="AC187" s="1" t="n">
+        <v>0.02644</v>
       </c>
     </row>
     <row r="188">
@@ -17041,10 +17605,13 @@
         <v>0.003269</v>
       </c>
       <c r="AA188" s="1" t="n">
+        <v>0.003239</v>
+      </c>
+      <c r="AB188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="AB188" s="1" t="n">
-        <v>0.003262</v>
+      <c r="AC188" s="1" t="n">
+        <v>0.003239</v>
       </c>
     </row>
     <row r="189">
@@ -17129,10 +17696,13 @@
         <v>0.2844</v>
       </c>
       <c r="AA189" s="1" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="AB189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="AB189" s="1" t="n">
-        <v>0.2842</v>
+      <c r="AC189" s="1" t="n">
+        <v>0.2832</v>
       </c>
     </row>
     <row r="190">
@@ -17217,10 +17787,13 @@
         <v>0.01766</v>
       </c>
       <c r="AA190" s="1" t="n">
+        <v>0.01744</v>
+      </c>
+      <c r="AB190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AB190" s="1" t="n">
-        <v>0.01763</v>
+      <c r="AC190" s="1" t="n">
+        <v>0.01744</v>
       </c>
     </row>
     <row r="191">
@@ -17305,9 +17878,12 @@
         <v>0.2572</v>
       </c>
       <c r="AA191" s="1" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="AB191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="AB191" s="1" t="n">
+      <c r="AC191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -17393,9 +17969,12 @@
         <v>0.0372</v>
       </c>
       <c r="AA192" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AB192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="AB192" s="1" t="n">
+      <c r="AC192" s="1" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -17481,10 +18060,13 @@
         <v>0.000221</v>
       </c>
       <c r="AA193" s="1" t="n">
+        <v>0.0002194</v>
+      </c>
+      <c r="AB193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="AB193" s="1" t="n">
-        <v>0.0002205</v>
+      <c r="AC193" s="1" t="n">
+        <v>0.0002194</v>
       </c>
     </row>
     <row r="194">
@@ -17569,10 +18151,13 @@
         <v>4.072</v>
       </c>
       <c r="AA194" s="1" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="AB194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="AB194" s="1" t="n">
-        <v>4.056</v>
+      <c r="AC194" s="1" t="n">
+        <v>4.033</v>
       </c>
     </row>
     <row r="195">
@@ -17660,6 +18245,9 @@
         <v>0.999401</v>
       </c>
       <c r="AB195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="AC195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -17745,9 +18333,12 @@
         <v>4.336</v>
       </c>
       <c r="AA196" s="1" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AB196" s="1" t="n">
         <v>4.368</v>
       </c>
-      <c r="AB196" s="1" t="n">
+      <c r="AC196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -17833,9 +18424,12 @@
         <v>0.15141</v>
       </c>
       <c r="AA197" s="1" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="AB197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="AB197" s="1" t="n">
+      <c r="AC197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -17921,9 +18515,12 @@
         <v>0.007884</v>
       </c>
       <c r="AA198" s="1" t="n">
+        <v>0.007859</v>
+      </c>
+      <c r="AB198" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="AB198" s="1" t="n">
+      <c r="AC198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -18009,9 +18606,12 @@
         <v>0.4519</v>
       </c>
       <c r="AA199" s="1" t="n">
+        <v>0.4503</v>
+      </c>
+      <c r="AB199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="AB199" s="1" t="n">
+      <c r="AC199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -18097,9 +18697,12 @@
         <v>0.5786</v>
       </c>
       <c r="AA200" s="1" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="AB200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="AB200" s="1" t="n">
+      <c r="AC200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -18185,10 +18788,13 @@
         <v>0.0927</v>
       </c>
       <c r="AA201" s="1" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="AB201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="AB201" s="1" t="n">
-        <v>0.09229999999999999</v>
+      <c r="AC201" s="1" t="n">
+        <v>0.0921</v>
       </c>
     </row>
     <row r="202">
@@ -18273,9 +18879,12 @@
         <v>0.06021</v>
       </c>
       <c r="AA202" s="1" t="n">
+        <v>0.06006</v>
+      </c>
+      <c r="AB202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="AB202" s="1" t="n">
+      <c r="AC202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -18361,9 +18970,12 @@
         <v>0.008319999999999999</v>
       </c>
       <c r="AA203" s="1" t="n">
+        <v>0.00835</v>
+      </c>
+      <c r="AB203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="AB203" s="1" t="n">
+      <c r="AC203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -18449,9 +19061,12 @@
         <v>0.00412</v>
       </c>
       <c r="AA204" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="AB204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="AB204" s="1" t="n">
+      <c r="AC204" s="1" t="n">
         <v>0.00411</v>
       </c>
     </row>
@@ -18537,9 +19152,12 @@
         <v>0.009037</v>
       </c>
       <c r="AA205" s="1" t="n">
+        <v>0.009008</v>
+      </c>
+      <c r="AB205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="AB205" s="1" t="n">
+      <c r="AC205" s="1" t="n">
         <v>0.009008</v>
       </c>
     </row>
@@ -18625,9 +19243,12 @@
         <v>0.2407</v>
       </c>
       <c r="AA206" s="1" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="AB206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="AB206" s="1" t="n">
+      <c r="AC206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -18713,9 +19334,12 @@
         <v>0.0213</v>
       </c>
       <c r="AA207" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="AB207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="AB207" s="1" t="n">
+      <c r="AC207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -18801,9 +19425,12 @@
         <v>0.2372</v>
       </c>
       <c r="AA208" s="1" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AB208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="AB208" s="1" t="n">
+      <c r="AC208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -18889,10 +19516,13 @@
         <v>0.3566</v>
       </c>
       <c r="AA209" s="1" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AB209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="AB209" s="1" t="n">
-        <v>0.3566</v>
+      <c r="AC209" s="1" t="n">
+        <v>0.3547</v>
       </c>
     </row>
     <row r="210">
@@ -18977,9 +19607,12 @@
         <v>0.04279</v>
       </c>
       <c r="AA210" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="AB210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="AB210" s="1" t="n">
+      <c r="AC210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -19065,10 +19698,13 @@
         <v>0.0004215</v>
       </c>
       <c r="AA211" s="1" t="n">
+        <v>0.0004179</v>
+      </c>
+      <c r="AB211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="AB211" s="1" t="n">
-        <v>0.0004215</v>
+      <c r="AC211" s="1" t="n">
+        <v>0.0004179</v>
       </c>
     </row>
     <row r="212">
@@ -19153,10 +19789,13 @@
         <v>0.02132</v>
       </c>
       <c r="AA212" s="1" t="n">
+        <v>0.02117</v>
+      </c>
+      <c r="AB212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="AB212" s="1" t="n">
-        <v>0.02122</v>
+      <c r="AC212" s="1" t="n">
+        <v>0.02117</v>
       </c>
     </row>
     <row r="213">
@@ -19241,9 +19880,12 @@
         <v>0.1152</v>
       </c>
       <c r="AA213" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="AB213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="AB213" s="1" t="n">
+      <c r="AC213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -19329,9 +19971,12 @@
         <v>0.04242</v>
       </c>
       <c r="AA214" s="1" t="n">
+        <v>0.04231</v>
+      </c>
+      <c r="AB214" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="AB214" s="1" t="n">
+      <c r="AC214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -19417,9 +20062,12 @@
         <v>0.009689</v>
       </c>
       <c r="AA215" s="1" t="n">
+        <v>0.009684999999999999</v>
+      </c>
+      <c r="AB215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="AB215" s="1" t="n">
+      <c r="AC215" s="1" t="n">
         <v>0.009677</v>
       </c>
     </row>
@@ -19505,9 +20153,12 @@
         <v>0.064</v>
       </c>
       <c r="AA216" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="AB216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="AB216" s="1" t="n">
+      <c r="AC216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -19593,10 +20244,13 @@
         <v>0.004144</v>
       </c>
       <c r="AA217" s="1" t="n">
+        <v>0.004107</v>
+      </c>
+      <c r="AB217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="AB217" s="1" t="n">
-        <v>0.004138</v>
+      <c r="AC217" s="1" t="n">
+        <v>0.004107</v>
       </c>
     </row>
     <row r="218">
@@ -19681,10 +20335,13 @@
         <v>0.00979</v>
       </c>
       <c r="AA218" s="1" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="AB218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="AB218" s="1" t="n">
-        <v>0.00979</v>
+      <c r="AC218" s="1" t="n">
+        <v>0.009719999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -19769,10 +20426,13 @@
         <v>0.02916</v>
       </c>
       <c r="AA219" s="1" t="n">
+        <v>0.02871</v>
+      </c>
+      <c r="AB219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="AB219" s="1" t="n">
-        <v>0.02916</v>
+      <c r="AC219" s="1" t="n">
+        <v>0.02871</v>
       </c>
     </row>
     <row r="220">
@@ -19857,10 +20517,13 @@
         <v>2.281</v>
       </c>
       <c r="AA220" s="1" t="n">
+        <v>2.274</v>
+      </c>
+      <c r="AB220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="AB220" s="1" t="n">
-        <v>2.281</v>
+      <c r="AC220" s="1" t="n">
+        <v>2.274</v>
       </c>
     </row>
     <row r="221">
@@ -19945,10 +20608,13 @@
         <v>0.022493</v>
       </c>
       <c r="AA221" s="1" t="n">
+        <v>0.022357</v>
+      </c>
+      <c r="AB221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="AB221" s="1" t="n">
-        <v>0.022427</v>
+      <c r="AC221" s="1" t="n">
+        <v>0.022357</v>
       </c>
     </row>
     <row r="222">
@@ -20033,9 +20699,12 @@
         <v>0.0369</v>
       </c>
       <c r="AA222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="AB222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="AB222" s="1" t="n">
+      <c r="AC222" s="1" t="n">
         <v>0.0367</v>
       </c>
     </row>
@@ -20121,10 +20790,13 @@
         <v>0.2917</v>
       </c>
       <c r="AA223" s="1" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AB223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="AB223" s="1" t="n">
-        <v>0.2915</v>
+      <c r="AC223" s="1" t="n">
+        <v>0.2903</v>
       </c>
     </row>
     <row r="224">
@@ -20209,9 +20881,12 @@
         <v>0.01583</v>
       </c>
       <c r="AA224" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="AB224" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="AB224" s="1" t="n">
+      <c r="AC224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -20297,10 +20972,13 @@
         <v>0.0004018</v>
       </c>
       <c r="AA225" s="1" t="n">
+        <v>0.0003989</v>
+      </c>
+      <c r="AB225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="AB225" s="1" t="n">
-        <v>0.0004017</v>
+      <c r="AC225" s="1" t="n">
+        <v>0.0003989</v>
       </c>
     </row>
     <row r="226">
@@ -20385,10 +21063,13 @@
         <v>0.08492</v>
       </c>
       <c r="AA226" s="1" t="n">
+        <v>0.08416</v>
+      </c>
+      <c r="AB226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="AB226" s="1" t="n">
-        <v>0.08468000000000001</v>
+      <c r="AC226" s="1" t="n">
+        <v>0.08416</v>
       </c>
     </row>
     <row r="227">
@@ -20473,10 +21154,13 @@
         <v>0.944</v>
       </c>
       <c r="AA227" s="1" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AB227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="AB227" s="1" t="n">
-        <v>0.9429999999999999</v>
+      <c r="AC227" s="1" t="n">
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -20561,9 +21245,12 @@
         <v>0.05555</v>
       </c>
       <c r="AA228" s="1" t="n">
+        <v>0.05523</v>
+      </c>
+      <c r="AB228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="AB228" s="1" t="n">
+      <c r="AC228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -20649,10 +21336,13 @@
         <v>0.002001</v>
       </c>
       <c r="AA229" s="1" t="n">
+        <v>0.001986</v>
+      </c>
+      <c r="AB229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="AB229" s="1" t="n">
-        <v>0.001997</v>
+      <c r="AC229" s="1" t="n">
+        <v>0.001986</v>
       </c>
     </row>
     <row r="230">
@@ -20737,10 +21427,13 @@
         <v>0.02265</v>
       </c>
       <c r="AA230" s="1" t="n">
+        <v>0.022561</v>
+      </c>
+      <c r="AB230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="AB230" s="1" t="n">
-        <v>0.02265</v>
+      <c r="AC230" s="1" t="n">
+        <v>0.022561</v>
       </c>
     </row>
     <row r="231">
@@ -20825,10 +21518,13 @@
         <v>0.05316</v>
       </c>
       <c r="AA231" s="1" t="n">
+        <v>0.05279</v>
+      </c>
+      <c r="AB231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="AB231" s="1" t="n">
-        <v>0.05316</v>
+      <c r="AC231" s="1" t="n">
+        <v>0.05279</v>
       </c>
     </row>
     <row r="232">
@@ -20913,9 +21609,12 @@
         <v>0.0585</v>
       </c>
       <c r="AA232" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="AB232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="AB232" s="1" t="n">
+      <c r="AC232" s="1" t="n">
         <v>0.0582</v>
       </c>
     </row>
@@ -21001,9 +21700,12 @@
         <v>0.001714</v>
       </c>
       <c r="AA233" s="1" t="n">
+        <v>0.001717</v>
+      </c>
+      <c r="AB233" s="1" t="n">
         <v>0.001728</v>
       </c>
-      <c r="AB233" s="1" t="n">
+      <c r="AC233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -21089,9 +21791,12 @@
         <v>0.005741</v>
       </c>
       <c r="AA234" s="1" t="n">
+        <v>0.005733</v>
+      </c>
+      <c r="AB234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="AB234" s="1" t="n">
+      <c r="AC234" s="1" t="n">
         <v>0.005718</v>
       </c>
     </row>
@@ -21177,10 +21882,13 @@
         <v>0.12179</v>
       </c>
       <c r="AA235" s="1" t="n">
+        <v>0.12126</v>
+      </c>
+      <c r="AB235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="AB235" s="1" t="n">
-        <v>0.12179</v>
+      <c r="AC235" s="1" t="n">
+        <v>0.12126</v>
       </c>
     </row>
     <row r="236">
@@ -21265,9 +21973,12 @@
         <v>64.76000000000001</v>
       </c>
       <c r="AA236" s="1" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="AB236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="AB236" s="1" t="n">
+      <c r="AC236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -21353,10 +22064,13 @@
         <v>0.1</v>
       </c>
       <c r="AA237" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
+      <c r="AB237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="AB237" s="1" t="n">
-        <v>0.0997</v>
+      <c r="AC237" s="1" t="n">
+        <v>0.09950000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -21441,10 +22155,13 @@
         <v>0.003929</v>
       </c>
       <c r="AA238" s="1" t="n">
+        <v>0.003915</v>
+      </c>
+      <c r="AB238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="AB238" s="1" t="n">
-        <v>0.003924</v>
+      <c r="AC238" s="1" t="n">
+        <v>0.003915</v>
       </c>
     </row>
     <row r="239">
@@ -21529,9 +22246,12 @@
         <v>0.01511</v>
       </c>
       <c r="AA239" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AB239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="AB239" s="1" t="n">
+      <c r="AC239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -21617,10 +22337,13 @@
         <v>0.05591</v>
       </c>
       <c r="AA240" s="1" t="n">
+        <v>0.05562</v>
+      </c>
+      <c r="AB240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="AB240" s="1" t="n">
-        <v>0.05575</v>
+      <c r="AC240" s="1" t="n">
+        <v>0.05562</v>
       </c>
     </row>
     <row r="241">
@@ -21705,9 +22428,12 @@
         <v>0.0114</v>
       </c>
       <c r="AA241" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="AB241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="AB241" s="1" t="n">
+      <c r="AC241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -21793,10 +22519,13 @@
         <v>0.3335</v>
       </c>
       <c r="AA242" s="1" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AB242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="AB242" s="1" t="n">
-        <v>0.3321</v>
+      <c r="AC242" s="1" t="n">
+        <v>0.3315</v>
       </c>
     </row>
     <row r="243">
@@ -21881,9 +22610,12 @@
         <v>0.01229</v>
       </c>
       <c r="AA243" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="AB243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="AB243" s="1" t="n">
+      <c r="AC243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -21969,9 +22701,12 @@
         <v>0.08118</v>
       </c>
       <c r="AA244" s="1" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="AB244" s="1" t="n">
         <v>0.08162999999999999</v>
       </c>
-      <c r="AB244" s="1" t="n">
+      <c r="AC244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -22057,9 +22792,12 @@
         <v>0.007867000000000001</v>
       </c>
       <c r="AA245" s="1" t="n">
+        <v>0.007953999999999999</v>
+      </c>
+      <c r="AB245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="AB245" s="1" t="n">
+      <c r="AC245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -22145,9 +22883,12 @@
         <v>0.03033</v>
       </c>
       <c r="AA246" s="1" t="n">
+        <v>0.03022</v>
+      </c>
+      <c r="AB246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="AB246" s="1" t="n">
+      <c r="AC246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -22233,10 +22974,13 @@
         <v>0.1797</v>
       </c>
       <c r="AA247" s="1" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="AB247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="AB247" s="1" t="n">
-        <v>0.1796</v>
+      <c r="AC247" s="1" t="n">
+        <v>0.1792</v>
       </c>
     </row>
     <row r="248">
@@ -22321,9 +23065,12 @@
         <v>0.05879</v>
       </c>
       <c r="AA248" s="1" t="n">
+        <v>0.05873</v>
+      </c>
+      <c r="AB248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="AB248" s="1" t="n">
+      <c r="AC248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -22409,10 +23156,13 @@
         <v>0.1649</v>
       </c>
       <c r="AA249" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="AB249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="AB249" s="1" t="n">
-        <v>0.1646</v>
+      <c r="AC249" s="1" t="n">
+        <v>0.1637</v>
       </c>
     </row>
     <row r="250">
@@ -22497,10 +23247,13 @@
         <v>0.01883</v>
       </c>
       <c r="AA250" s="1" t="n">
+        <v>0.01878</v>
+      </c>
+      <c r="AB250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="AB250" s="1" t="n">
-        <v>0.01881</v>
+      <c r="AC250" s="1" t="n">
+        <v>0.01878</v>
       </c>
     </row>
     <row r="251">
@@ -22585,9 +23338,12 @@
         <v>0.02312</v>
       </c>
       <c r="AA251" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="AB251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="AB251" s="1" t="n">
+      <c r="AC251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -22673,9 +23429,12 @@
         <v>0.30499</v>
       </c>
       <c r="AA252" s="1" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AB252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="AB252" s="1" t="n">
+      <c r="AC252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -22761,10 +23520,13 @@
         <v>0.005941</v>
       </c>
       <c r="AA253" s="1" t="n">
+        <v>0.005924</v>
+      </c>
+      <c r="AB253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="AB253" s="1" t="n">
-        <v>0.005941</v>
+      <c r="AC253" s="1" t="n">
+        <v>0.005924</v>
       </c>
     </row>
     <row r="254">
@@ -22849,10 +23611,13 @@
         <v>0.6126</v>
       </c>
       <c r="AA254" s="1" t="n">
+        <v>0.6092</v>
+      </c>
+      <c r="AB254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="AB254" s="1" t="n">
-        <v>0.6116</v>
+      <c r="AC254" s="1" t="n">
+        <v>0.6092</v>
       </c>
     </row>
     <row r="255">
@@ -22937,9 +23702,12 @@
         <v>0.10576</v>
       </c>
       <c r="AA255" s="1" t="n">
+        <v>0.10575</v>
+      </c>
+      <c r="AB255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="AB255" s="1" t="n">
+      <c r="AC255" s="1" t="n">
         <v>0.10545</v>
       </c>
     </row>
@@ -23025,10 +23793,13 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="AA256" s="1" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="AB256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="AB256" s="1" t="n">
-        <v>0.0898</v>
+      <c r="AC256" s="1" t="n">
+        <v>0.0891</v>
       </c>
     </row>
     <row r="257">
@@ -23113,9 +23884,12 @@
         <v>0.01506</v>
       </c>
       <c r="AA257" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="AB257" s="1" t="n">
         <v>0.01518</v>
       </c>
-      <c r="AB257" s="1" t="n">
+      <c r="AC257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -23201,9 +23975,12 @@
         <v>0.04965</v>
       </c>
       <c r="AA258" s="1" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="AB258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="AB258" s="1" t="n">
+      <c r="AC258" s="1" t="n">
         <v>0.04938</v>
       </c>
     </row>
@@ -23289,10 +24066,13 @@
         <v>0.00784</v>
       </c>
       <c r="AA259" s="1" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="AB259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="AB259" s="1" t="n">
-        <v>0.00784</v>
+      <c r="AC259" s="1" t="n">
+        <v>0.00779</v>
       </c>
     </row>
     <row r="260">
@@ -23377,10 +24157,13 @@
         <v>0.1894</v>
       </c>
       <c r="AA260" s="1" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="AB260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="AB260" s="1" t="n">
-        <v>0.1892</v>
+      <c r="AC260" s="1" t="n">
+        <v>0.1883</v>
       </c>
     </row>
     <row r="261">
@@ -23465,10 +24248,13 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="AA261" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="AB261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="AB261" s="1" t="n">
-        <v>0.09760000000000001</v>
+      <c r="AC261" s="1" t="n">
+        <v>0.0975</v>
       </c>
     </row>
     <row r="262">
@@ -23553,10 +24339,13 @@
         <v>0.2106</v>
       </c>
       <c r="AA262" s="1" t="n">
+        <v>0.2094</v>
+      </c>
+      <c r="AB262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="AB262" s="1" t="n">
-        <v>0.2103</v>
+      <c r="AC262" s="1" t="n">
+        <v>0.2094</v>
       </c>
     </row>
     <row r="263">
@@ -23641,9 +24430,12 @@
         <v>0.008597</v>
       </c>
       <c r="AA263" s="1" t="n">
+        <v>0.008546</v>
+      </c>
+      <c r="AB263" s="1" t="n">
         <v>0.008616</v>
       </c>
-      <c r="AB263" s="1" t="n">
+      <c r="AC263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -23729,10 +24521,13 @@
         <v>2.62</v>
       </c>
       <c r="AA264" s="1" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="AB264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="AB264" s="1" t="n">
-        <v>2.616</v>
+      <c r="AC264" s="1" t="n">
+        <v>2.609</v>
       </c>
     </row>
     <row r="265">
@@ -23817,10 +24612,13 @@
         <v>0.01852</v>
       </c>
       <c r="AA265" s="1" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="AB265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="AB265" s="1" t="n">
-        <v>0.01845</v>
+      <c r="AC265" s="1" t="n">
+        <v>0.01839</v>
       </c>
     </row>
     <row r="266">
@@ -23905,9 +24703,12 @@
         <v>0.3619</v>
       </c>
       <c r="AA266" s="1" t="n">
-        <v>0.3619</v>
+        <v>0.3648</v>
       </c>
       <c r="AB266" s="1" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="AC266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -23993,9 +24794,12 @@
         <v>0.03444</v>
       </c>
       <c r="AA267" s="1" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="AB267" s="1" t="n">
         <v>0.03471</v>
       </c>
-      <c r="AB267" s="1" t="n">
+      <c r="AC267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -24081,9 +24885,12 @@
         <v>0.127</v>
       </c>
       <c r="AA268" s="1" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AB268" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="AB268" s="1" t="n">
+      <c r="AC268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -24169,10 +24976,13 @@
         <v>0.079</v>
       </c>
       <c r="AA269" s="1" t="n">
+        <v>0.07862</v>
+      </c>
+      <c r="AB269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="AB269" s="1" t="n">
-        <v>0.07896</v>
+      <c r="AC269" s="1" t="n">
+        <v>0.07862</v>
       </c>
     </row>
     <row r="270">
@@ -24257,10 +25067,13 @@
         <v>0.01379</v>
       </c>
       <c r="AA270" s="1" t="n">
+        <v>0.01373</v>
+      </c>
+      <c r="AB270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="AB270" s="1" t="n">
-        <v>0.01374</v>
+      <c r="AC270" s="1" t="n">
+        <v>0.01373</v>
       </c>
     </row>
     <row r="271">
@@ -24345,10 +25158,13 @@
         <v>0.007502</v>
       </c>
       <c r="AA271" s="1" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="AB271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="AB271" s="1" t="n">
-        <v>0.007479</v>
+      <c r="AC271" s="1" t="n">
+        <v>0.00745</v>
       </c>
     </row>
     <row r="272">
@@ -24433,9 +25249,12 @@
         <v>0.07414</v>
       </c>
       <c r="AA272" s="1" t="n">
+        <v>0.07403999999999999</v>
+      </c>
+      <c r="AB272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="AB272" s="1" t="n">
+      <c r="AC272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -24521,10 +25340,13 @@
         <v>3.12e-05</v>
       </c>
       <c r="AA273" s="1" t="n">
+        <v>3.09e-05</v>
+      </c>
+      <c r="AB273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="AB273" s="1" t="n">
-        <v>3.11e-05</v>
+      <c r="AC273" s="1" t="n">
+        <v>3.09e-05</v>
       </c>
     </row>
     <row r="274">
@@ -24609,10 +25431,13 @@
         <v>0.005412</v>
       </c>
       <c r="AA274" s="1" t="n">
+        <v>0.005382</v>
+      </c>
+      <c r="AB274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="AB274" s="1" t="n">
-        <v>0.005404</v>
+      <c r="AC274" s="1" t="n">
+        <v>0.005382</v>
       </c>
     </row>
     <row r="275">
@@ -24697,9 +25522,12 @@
         <v>0.1744</v>
       </c>
       <c r="AA275" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="AB275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="AB275" s="1" t="n">
+      <c r="AC275" s="1" t="n">
         <v>0.1744</v>
       </c>
     </row>
@@ -24785,9 +25613,12 @@
         <v>0.006868</v>
       </c>
       <c r="AA276" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+      <c r="AB276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="AB276" s="1" t="n">
+      <c r="AC276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -24873,9 +25704,12 @@
         <v>0.1323</v>
       </c>
       <c r="AA277" s="1" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="AB277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="AB277" s="1" t="n">
+      <c r="AC277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -24961,10 +25795,13 @@
         <v>0.02313</v>
       </c>
       <c r="AA278" s="1" t="n">
+        <v>0.02291</v>
+      </c>
+      <c r="AB278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="AB278" s="1" t="n">
-        <v>0.02306</v>
+      <c r="AC278" s="1" t="n">
+        <v>0.02291</v>
       </c>
     </row>
     <row r="279">
@@ -25049,10 +25886,13 @@
         <v>0.0181</v>
       </c>
       <c r="AA279" s="1" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="AB279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AB279" s="1" t="n">
-        <v>0.0181</v>
+      <c r="AC279" s="1" t="n">
+        <v>0.01796</v>
       </c>
     </row>
     <row r="280">
@@ -25137,10 +25977,13 @@
         <v>0.0367</v>
       </c>
       <c r="AA280" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AB280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="AB280" s="1" t="n">
-        <v>0.03666</v>
+      <c r="AC280" s="1" t="n">
+        <v>0.0363</v>
       </c>
     </row>
     <row r="281">
@@ -25225,9 +26068,12 @@
         <v>0.03973</v>
       </c>
       <c r="AA281" s="1" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="AB281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="AB281" s="1" t="n">
+      <c r="AC281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -25313,9 +26159,12 @@
         <v>0.3043</v>
       </c>
       <c r="AA282" s="1" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AB282" s="1" t="n">
         <v>0.3079</v>
       </c>
-      <c r="AB282" s="1" t="n">
+      <c r="AC282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -25401,10 +26250,13 @@
         <v>0.01119</v>
       </c>
       <c r="AA283" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="AB283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="AB283" s="1" t="n">
-        <v>0.01115</v>
+      <c r="AC283" s="1" t="n">
+        <v>0.01114</v>
       </c>
     </row>
     <row r="284">
@@ -25489,9 +26341,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="AA284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="AB284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="AB284" s="1" t="n">
+      <c r="AC284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -25577,10 +26432,13 @@
         <v>0.1145</v>
       </c>
       <c r="AA285" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="AB285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="AB285" s="1" t="n">
-        <v>0.1141</v>
+      <c r="AC285" s="1" t="n">
+        <v>0.1137</v>
       </c>
     </row>
     <row r="286">
@@ -25665,9 +26523,12 @@
         <v>0.00344</v>
       </c>
       <c r="AA286" s="1" t="n">
+        <v>0.003426</v>
+      </c>
+      <c r="AB286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="AB286" s="1" t="n">
+      <c r="AC286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -25753,10 +26614,13 @@
         <v>0.08474</v>
       </c>
       <c r="AA287" s="1" t="n">
+        <v>0.08451</v>
+      </c>
+      <c r="AB287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="AB287" s="1" t="n">
-        <v>0.08462</v>
+      <c r="AC287" s="1" t="n">
+        <v>0.08451</v>
       </c>
     </row>
     <row r="288">
@@ -25841,9 +26705,12 @@
         <v>0.10061</v>
       </c>
       <c r="AA288" s="1" t="n">
-        <v>0.10076</v>
+        <v>0.10125</v>
       </c>
       <c r="AB288" s="1" t="n">
+        <v>0.10125</v>
+      </c>
+      <c r="AC288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -25929,10 +26796,13 @@
         <v>0.4319</v>
       </c>
       <c r="AA289" s="1" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AB289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="AB289" s="1" t="n">
-        <v>0.4307</v>
+      <c r="AC289" s="1" t="n">
+        <v>0.428</v>
       </c>
     </row>
     <row r="290">
@@ -26017,9 +26887,12 @@
         <v>0.04037</v>
       </c>
       <c r="AA290" s="1" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="AB290" s="1" t="n">
         <v>0.04037</v>
       </c>
-      <c r="AB290" s="1" t="n">
+      <c r="AC290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -26105,10 +26978,13 @@
         <v>0.2345</v>
       </c>
       <c r="AA291" s="1" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AB291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="AB291" s="1" t="n">
-        <v>0.2344</v>
+      <c r="AC291" s="1" t="n">
+        <v>0.2327</v>
       </c>
     </row>
     <row r="292">
@@ -26193,9 +27069,12 @@
         <v>0.28495</v>
       </c>
       <c r="AA292" s="1" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="AB292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="AB292" s="1" t="n">
+      <c r="AC292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -26281,9 +27160,12 @@
         <v>0.1511</v>
       </c>
       <c r="AA293" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="AB293" s="1" t="n">
         <v>0.1539</v>
       </c>
-      <c r="AB293" s="1" t="n">
+      <c r="AC293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -26369,10 +27251,13 @@
         <v>4.174</v>
       </c>
       <c r="AA294" s="1" t="n">
+        <v>4.151</v>
+      </c>
+      <c r="AB294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="AB294" s="1" t="n">
-        <v>4.161</v>
+      <c r="AC294" s="1" t="n">
+        <v>4.151</v>
       </c>
     </row>
     <row r="295">
@@ -26457,9 +27342,12 @@
         <v>0.03331</v>
       </c>
       <c r="AA295" s="1" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="AB295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="AB295" s="1" t="n">
+      <c r="AC295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -26545,9 +27433,12 @@
         <v>0.000969</v>
       </c>
       <c r="AA296" s="1" t="n">
+        <v>0.000967</v>
+      </c>
+      <c r="AB296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="AB296" s="1" t="n">
+      <c r="AC296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -26633,10 +27524,13 @@
         <v>0.08173</v>
       </c>
       <c r="AA297" s="1" t="n">
+        <v>0.08101999999999999</v>
+      </c>
+      <c r="AB297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="AB297" s="1" t="n">
-        <v>0.08126</v>
+      <c r="AC297" s="1" t="n">
+        <v>0.08101999999999999</v>
       </c>
     </row>
     <row r="298">
@@ -26721,9 +27615,12 @@
         <v>0.05863</v>
       </c>
       <c r="AA298" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="AB298" s="1" t="n">
         <v>0.05876</v>
       </c>
-      <c r="AB298" s="1" t="n">
+      <c r="AC298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -26809,9 +27706,12 @@
         <v>0.09181</v>
       </c>
       <c r="AA299" s="1" t="n">
-        <v>0.09202</v>
+        <v>0.09214</v>
       </c>
       <c r="AB299" s="1" t="n">
+        <v>0.09214</v>
+      </c>
+      <c r="AC299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -26897,10 +27797,13 @@
         <v>0.0272</v>
       </c>
       <c r="AA300" s="1" t="n">
+        <v>0.02717</v>
+      </c>
+      <c r="AB300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="AB300" s="1" t="n">
-        <v>0.02718</v>
+      <c r="AC300" s="1" t="n">
+        <v>0.02717</v>
       </c>
     </row>
     <row r="301">
@@ -26985,10 +27888,13 @@
         <v>0.06528</v>
       </c>
       <c r="AA301" s="1" t="n">
+        <v>0.06475</v>
+      </c>
+      <c r="AB301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="AB301" s="1" t="n">
-        <v>0.06525</v>
+      <c r="AC301" s="1" t="n">
+        <v>0.06475</v>
       </c>
     </row>
     <row r="302">
@@ -27073,9 +27979,12 @@
         <v>0.053551</v>
       </c>
       <c r="AA302" s="1" t="n">
+        <v>0.053484</v>
+      </c>
+      <c r="AB302" s="1" t="n">
         <v>0.053599</v>
       </c>
-      <c r="AB302" s="1" t="n">
+      <c r="AC302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -27161,9 +28070,12 @@
         <v>5166.2</v>
       </c>
       <c r="AA303" s="1" t="n">
+        <v>5169</v>
+      </c>
+      <c r="AB303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="AB303" s="1" t="n">
+      <c r="AC303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -27249,9 +28161,12 @@
         <v>14.93</v>
       </c>
       <c r="AA304" s="1" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AB304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="AB304" s="1" t="n">
+      <c r="AC304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -27337,9 +28252,12 @@
         <v>0.003765</v>
       </c>
       <c r="AA305" s="1" t="n">
+        <v>0.003785</v>
+      </c>
+      <c r="AB305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="AB305" s="1" t="n">
+      <c r="AC305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -27425,9 +28343,12 @@
         <v>0.4562</v>
       </c>
       <c r="AA306" s="1" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="AB306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="AB306" s="1" t="n">
+      <c r="AC306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -27513,10 +28434,13 @@
         <v>0.04658</v>
       </c>
       <c r="AA307" s="1" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="AB307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="AB307" s="1" t="n">
-        <v>0.04649</v>
+      <c r="AC307" s="1" t="n">
+        <v>0.0463</v>
       </c>
     </row>
     <row r="308">
@@ -27601,9 +28525,12 @@
         <v>1.5065</v>
       </c>
       <c r="AA308" s="1" t="n">
-        <v>1.5096</v>
+        <v>1.5176</v>
       </c>
       <c r="AB308" s="1" t="n">
+        <v>1.5176</v>
+      </c>
+      <c r="AC308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -27689,10 +28616,13 @@
         <v>0.0007893</v>
       </c>
       <c r="AA309" s="1" t="n">
+        <v>0.0007850999999999999</v>
+      </c>
+      <c r="AB309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="AB309" s="1" t="n">
-        <v>0.0007861</v>
+      <c r="AC309" s="1" t="n">
+        <v>0.0007850999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -27777,10 +28707,13 @@
         <v>4.519</v>
       </c>
       <c r="AA310" s="1" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="AB310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="AB310" s="1" t="n">
-        <v>4.519</v>
+      <c r="AC310" s="1" t="n">
+        <v>4.498</v>
       </c>
     </row>
     <row r="311">
@@ -27865,9 +28798,12 @@
         <v>4.772</v>
       </c>
       <c r="AA311" s="1" t="n">
+        <v>4.762</v>
+      </c>
+      <c r="AB311" s="1" t="n">
         <v>4.809</v>
       </c>
-      <c r="AB311" s="1" t="n">
+      <c r="AC311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -27953,10 +28889,13 @@
         <v>0.08064</v>
       </c>
       <c r="AA312" s="1" t="n">
+        <v>0.08029</v>
+      </c>
+      <c r="AB312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="AB312" s="1" t="n">
-        <v>0.08033999999999999</v>
+      <c r="AC312" s="1" t="n">
+        <v>0.08029</v>
       </c>
     </row>
     <row r="313">
@@ -28041,9 +28980,12 @@
         <v>2.022</v>
       </c>
       <c r="AA313" s="1" t="n">
+        <v>2.018</v>
+      </c>
+      <c r="AB313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB313" s="1" t="n">
+      <c r="AC313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -28129,9 +29071,12 @@
         <v>0.07047</v>
       </c>
       <c r="AA314" s="1" t="n">
+        <v>0.07106999999999999</v>
+      </c>
+      <c r="AB314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="AB314" s="1" t="n">
+      <c r="AC314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -28217,9 +29162,12 @@
         <v>0.95</v>
       </c>
       <c r="AA315" s="1" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="AB315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="AB315" s="1" t="n">
+      <c r="AC315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -28305,10 +29253,13 @@
         <v>0.1294</v>
       </c>
       <c r="AA316" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AB316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="AB316" s="1" t="n">
-        <v>0.1294</v>
+      <c r="AC316" s="1" t="n">
+        <v>0.129</v>
       </c>
     </row>
     <row r="317">
@@ -28393,9 +29344,12 @@
         <v>0.1872</v>
       </c>
       <c r="AA317" s="1" t="n">
+        <v>0.1859</v>
+      </c>
+      <c r="AB317" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="AB317" s="1" t="n">
+      <c r="AC317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -28481,9 +29435,12 @@
         <v>0.01595</v>
       </c>
       <c r="AA318" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="AB318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="AB318" s="1" t="n">
+      <c r="AC318" s="1" t="n">
         <v>0.0159</v>
       </c>
     </row>
@@ -28569,10 +29526,13 @@
         <v>0.08337</v>
       </c>
       <c r="AA319" s="1" t="n">
+        <v>0.08298999999999999</v>
+      </c>
+      <c r="AB319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="AB319" s="1" t="n">
-        <v>0.08318</v>
+      <c r="AC319" s="1" t="n">
+        <v>0.08298999999999999</v>
       </c>
     </row>
     <row r="320">
@@ -28657,10 +29617,13 @@
         <v>0.007467</v>
       </c>
       <c r="AA320" s="1" t="n">
+        <v>0.007397</v>
+      </c>
+      <c r="AB320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="AB320" s="1" t="n">
-        <v>0.007462</v>
+      <c r="AC320" s="1" t="n">
+        <v>0.007397</v>
       </c>
     </row>
     <row r="321">
@@ -28745,10 +29708,13 @@
         <v>0.05408</v>
       </c>
       <c r="AA321" s="1" t="n">
+        <v>0.05382</v>
+      </c>
+      <c r="AB321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="AB321" s="1" t="n">
-        <v>0.05406</v>
+      <c r="AC321" s="1" t="n">
+        <v>0.05382</v>
       </c>
     </row>
     <row r="322">
@@ -28833,10 +29799,13 @@
         <v>0.5485</v>
       </c>
       <c r="AA322" s="1" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="AB322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="AB322" s="1" t="n">
-        <v>0.5476</v>
+      <c r="AC322" s="1" t="n">
+        <v>0.5468</v>
       </c>
     </row>
     <row r="323">
@@ -28921,10 +29890,13 @@
         <v>0.07346</v>
       </c>
       <c r="AA323" s="1" t="n">
+        <v>0.07285999999999999</v>
+      </c>
+      <c r="AB323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="AB323" s="1" t="n">
-        <v>0.07346</v>
+      <c r="AC323" s="1" t="n">
+        <v>0.07285999999999999</v>
       </c>
     </row>
     <row r="324">
@@ -29009,9 +29981,12 @@
         <v>0.012956</v>
       </c>
       <c r="AA324" s="1" t="n">
+        <v>0.012984</v>
+      </c>
+      <c r="AB324" s="1" t="n">
         <v>0.013045</v>
       </c>
-      <c r="AB324" s="1" t="n">
+      <c r="AC324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -29097,10 +30072,13 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="AA325" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="AB325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="AB325" s="1" t="n">
-        <v>0.09810000000000001</v>
+      <c r="AC325" s="1" t="n">
+        <v>0.0978</v>
       </c>
     </row>
     <row r="326">
@@ -29185,9 +30163,12 @@
         <v>0.01738</v>
       </c>
       <c r="AA326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="AB326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="AB326" s="1" t="n">
+      <c r="AC326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -29273,9 +30254,12 @@
         <v>0.06455</v>
       </c>
       <c r="AA327" s="1" t="n">
+        <v>0.06398</v>
+      </c>
+      <c r="AB327" s="1" t="n">
         <v>0.06455</v>
       </c>
-      <c r="AB327" s="1" t="n">
+      <c r="AC327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -29361,10 +30345,13 @@
         <v>0.2626</v>
       </c>
       <c r="AA328" s="1" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="AB328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="AB328" s="1" t="n">
-        <v>0.2612</v>
+      <c r="AC328" s="1" t="n">
+        <v>0.2604</v>
       </c>
     </row>
     <row r="329">
@@ -29449,9 +30436,12 @@
         <v>0.17565</v>
       </c>
       <c r="AA329" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="AB329" s="1" t="n">
         <v>0.17565</v>
       </c>
-      <c r="AB329" s="1" t="n">
+      <c r="AC329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -29537,10 +30527,13 @@
         <v>2.008</v>
       </c>
       <c r="AA330" s="1" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="AB330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="AB330" s="1" t="n">
-        <v>2.002</v>
+      <c r="AC330" s="1" t="n">
+        <v>1.995</v>
       </c>
     </row>
     <row r="331">
@@ -29625,9 +30618,12 @@
         <v>0.0286</v>
       </c>
       <c r="AA331" s="1" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="AB331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="AB331" s="1" t="n">
+      <c r="AC331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -29713,9 +30709,12 @@
         <v>0.006013</v>
       </c>
       <c r="AA332" s="1" t="n">
-        <v>0.006063</v>
+        <v>0.006122</v>
       </c>
       <c r="AB332" s="1" t="n">
+        <v>0.006122</v>
+      </c>
+      <c r="AC332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -29801,9 +30800,12 @@
         <v>0.003463</v>
       </c>
       <c r="AA333" s="1" t="n">
+        <v>0.00346</v>
+      </c>
+      <c r="AB333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="AB333" s="1" t="n">
+      <c r="AC333" s="1" t="n">
         <v>0.003441</v>
       </c>
     </row>
@@ -29889,10 +30891,13 @@
         <v>0.01389</v>
       </c>
       <c r="AA334" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AB334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="AB334" s="1" t="n">
-        <v>0.01387</v>
+      <c r="AC334" s="1" t="n">
+        <v>0.01384</v>
       </c>
     </row>
     <row r="335">
@@ -29977,9 +30982,12 @@
         <v>1.132</v>
       </c>
       <c r="AA335" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="AB335" s="1" t="n">
         <v>1.158</v>
       </c>
-      <c r="AB335" s="1" t="n">
+      <c r="AC335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -30065,10 +31073,13 @@
         <v>0.011225</v>
       </c>
       <c r="AA336" s="1" t="n">
+        <v>0.011205</v>
+      </c>
+      <c r="AB336" s="1" t="n">
         <v>0.011377</v>
       </c>
-      <c r="AB336" s="1" t="n">
-        <v>0.011221</v>
+      <c r="AC336" s="1" t="n">
+        <v>0.011205</v>
       </c>
     </row>
     <row r="337">
@@ -30153,9 +31164,12 @@
         <v>2.958</v>
       </c>
       <c r="AA337" s="1" t="n">
+        <v>2.954</v>
+      </c>
+      <c r="AB337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="AB337" s="1" t="n">
+      <c r="AC337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -30241,10 +31255,13 @@
         <v>0.01843</v>
       </c>
       <c r="AA338" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AB338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="AB338" s="1" t="n">
-        <v>0.0184</v>
+      <c r="AC338" s="1" t="n">
+        <v>0.01833</v>
       </c>
     </row>
     <row r="339">
@@ -30329,10 +31346,13 @@
         <v>0.07693</v>
       </c>
       <c r="AA339" s="1" t="n">
+        <v>0.07643999999999999</v>
+      </c>
+      <c r="AB339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="AB339" s="1" t="n">
-        <v>0.07679</v>
+      <c r="AC339" s="1" t="n">
+        <v>0.07643999999999999</v>
       </c>
     </row>
     <row r="340">
@@ -30417,9 +31437,12 @@
         <v>0.075</v>
       </c>
       <c r="AA340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AB340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="AB340" s="1" t="n">
+      <c r="AC340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -30505,9 +31528,12 @@
         <v>0.03614</v>
       </c>
       <c r="AA341" s="1" t="n">
+        <v>0.03604</v>
+      </c>
+      <c r="AB341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="AB341" s="1" t="n">
+      <c r="AC341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -30593,10 +31619,13 @@
         <v>2586</v>
       </c>
       <c r="AA342" s="1" t="n">
+        <v>2571</v>
+      </c>
+      <c r="AB342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="AB342" s="1" t="n">
-        <v>2579</v>
+      <c r="AC342" s="1" t="n">
+        <v>2571</v>
       </c>
     </row>
     <row r="343">
@@ -30681,9 +31710,12 @@
         <v>0.0001971</v>
       </c>
       <c r="AA343" s="1" t="n">
+        <v>0.0001971</v>
+      </c>
+      <c r="AB343" s="1" t="n">
         <v>0.0002049</v>
       </c>
-      <c r="AB343" s="1" t="n">
+      <c r="AC343" s="1" t="n">
         <v>0.0001952</v>
       </c>
     </row>
@@ -30769,10 +31801,13 @@
         <v>0.07929</v>
       </c>
       <c r="AA344" s="1" t="n">
+        <v>0.07890999999999999</v>
+      </c>
+      <c r="AB344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="AB344" s="1" t="n">
-        <v>0.07915</v>
+      <c r="AC344" s="1" t="n">
+        <v>0.07890999999999999</v>
       </c>
     </row>
     <row r="345">
@@ -30857,10 +31892,13 @@
         <v>0.01604</v>
       </c>
       <c r="AA345" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="AB345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="AB345" s="1" t="n">
-        <v>0.01604</v>
+      <c r="AC345" s="1" t="n">
+        <v>0.01597</v>
       </c>
     </row>
     <row r="346">
@@ -30945,9 +31983,12 @@
         <v>2.754</v>
       </c>
       <c r="AA346" s="1" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="AB346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="AB346" s="1" t="n">
+      <c r="AC346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -31033,10 +32074,13 @@
         <v>0.01629</v>
       </c>
       <c r="AA347" s="1" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="AB347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="AB347" s="1" t="n">
-        <v>0.01625</v>
+      <c r="AC347" s="1" t="n">
+        <v>0.01617</v>
       </c>
     </row>
     <row r="348">
@@ -31121,9 +32165,12 @@
         <v>0.03817</v>
       </c>
       <c r="AA348" s="1" t="n">
+        <v>0.03819</v>
+      </c>
+      <c r="AB348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="AB348" s="1" t="n">
+      <c r="AC348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -31209,9 +32256,12 @@
         <v>0.3049</v>
       </c>
       <c r="AA349" s="1" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AB349" s="1" t="n">
         <v>0.3076</v>
       </c>
-      <c r="AB349" s="1" t="n">
+      <c r="AC349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -31297,9 +32347,12 @@
         <v>0.005079</v>
       </c>
       <c r="AA350" s="1" t="n">
+        <v>0.005052</v>
+      </c>
+      <c r="AB350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="AB350" s="1" t="n">
+      <c r="AC350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -31385,9 +32438,12 @@
         <v>0.005094</v>
       </c>
       <c r="AA351" s="1" t="n">
+        <v>0.005063</v>
+      </c>
+      <c r="AB351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="AB351" s="1" t="n">
+      <c r="AC351" s="1" t="n">
         <v>0.005054</v>
       </c>
     </row>
@@ -31473,9 +32529,12 @@
         <v>0.004371</v>
       </c>
       <c r="AA352" s="1" t="n">
+        <v>0.004381</v>
+      </c>
+      <c r="AB352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="AB352" s="1" t="n">
+      <c r="AC352" s="1" t="n">
         <v>0.004371</v>
       </c>
     </row>
@@ -31561,9 +32620,12 @@
         <v>0.08066</v>
       </c>
       <c r="AA353" s="1" t="n">
+        <v>0.08042000000000001</v>
+      </c>
+      <c r="AB353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="AB353" s="1" t="n">
+      <c r="AC353" s="1" t="n">
         <v>0.08008</v>
       </c>
     </row>
@@ -31649,10 +32711,13 @@
         <v>1.266</v>
       </c>
       <c r="AA354" s="1" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="AB354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="AB354" s="1" t="n">
-        <v>1.255</v>
+      <c r="AC354" s="1" t="n">
+        <v>1.228</v>
       </c>
     </row>
     <row r="355">
@@ -31737,9 +32802,12 @@
         <v>7.701</v>
       </c>
       <c r="AA355" s="1" t="n">
+        <v>7.685</v>
+      </c>
+      <c r="AB355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="AB355" s="1" t="n">
+      <c r="AC355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -31825,10 +32893,13 @@
         <v>0.00776</v>
       </c>
       <c r="AA356" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="AB356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="AB356" s="1" t="n">
-        <v>0.00774</v>
+      <c r="AC356" s="1" t="n">
+        <v>0.00766</v>
       </c>
     </row>
     <row r="357">
@@ -31913,9 +32984,12 @@
         <v>0.005636</v>
       </c>
       <c r="AA357" s="1" t="n">
+        <v>0.005631</v>
+      </c>
+      <c r="AB357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="AB357" s="1" t="n">
+      <c r="AC357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -32001,9 +33075,12 @@
         <v>0.01547</v>
       </c>
       <c r="AA358" s="1" t="n">
+        <v>0.01535</v>
+      </c>
+      <c r="AB358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="AB358" s="1" t="n">
+      <c r="AC358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -32089,9 +33166,12 @@
         <v>3.625</v>
       </c>
       <c r="AA359" s="1" t="n">
+        <v>3.605</v>
+      </c>
+      <c r="AB359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="AB359" s="1" t="n">
+      <c r="AC359" s="1" t="n">
         <v>3.597</v>
       </c>
     </row>
@@ -32177,9 +33257,12 @@
         <v>0.1499</v>
       </c>
       <c r="AA360" s="1" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="AB360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="AB360" s="1" t="n">
+      <c r="AC360" s="1" t="n">
         <v>0.1492</v>
       </c>
     </row>
@@ -32265,10 +33348,13 @@
         <v>0.07034</v>
       </c>
       <c r="AA361" s="1" t="n">
+        <v>0.07009</v>
+      </c>
+      <c r="AB361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="AB361" s="1" t="n">
-        <v>0.07015</v>
+      <c r="AC361" s="1" t="n">
+        <v>0.07009</v>
       </c>
     </row>
     <row r="362">
@@ -32353,10 +33439,13 @@
         <v>0.01765</v>
       </c>
       <c r="AA362" s="1" t="n">
+        <v>0.01756</v>
+      </c>
+      <c r="AB362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="AB362" s="1" t="n">
-        <v>0.0176</v>
+      <c r="AC362" s="1" t="n">
+        <v>0.01756</v>
       </c>
     </row>
     <row r="363">
@@ -32441,10 +33530,13 @@
         <v>0.02222</v>
       </c>
       <c r="AA363" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="AB363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="AB363" s="1" t="n">
-        <v>0.0222</v>
+      <c r="AC363" s="1" t="n">
+        <v>0.02205</v>
       </c>
     </row>
     <row r="364">
@@ -32529,10 +33621,13 @@
         <v>0.01249</v>
       </c>
       <c r="AA364" s="1" t="n">
+        <v>0.01243</v>
+      </c>
+      <c r="AB364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="AB364" s="1" t="n">
-        <v>0.01249</v>
+      <c r="AC364" s="1" t="n">
+        <v>0.01243</v>
       </c>
     </row>
     <row r="365">
@@ -32617,10 +33712,13 @@
         <v>0.0905</v>
       </c>
       <c r="AA365" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="AB365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="AB365" s="1" t="n">
-        <v>0.0905</v>
+      <c r="AC365" s="1" t="n">
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="366">
@@ -32705,10 +33803,13 @@
         <v>0.04222</v>
       </c>
       <c r="AA366" s="1" t="n">
+        <v>0.04199</v>
+      </c>
+      <c r="AB366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="AB366" s="1" t="n">
-        <v>0.04214</v>
+      <c r="AC366" s="1" t="n">
+        <v>0.04199</v>
       </c>
     </row>
     <row r="367">
@@ -32793,10 +33894,13 @@
         <v>0.0315</v>
       </c>
       <c r="AA367" s="1" t="n">
+        <v>0.03081</v>
+      </c>
+      <c r="AB367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="AB367" s="1" t="n">
-        <v>0.03124</v>
+      <c r="AC367" s="1" t="n">
+        <v>0.03081</v>
       </c>
     </row>
     <row r="368">
@@ -32881,10 +33985,13 @@
         <v>0.02304</v>
       </c>
       <c r="AA368" s="1" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="AB368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="AB368" s="1" t="n">
-        <v>0.02302</v>
+      <c r="AC368" s="1" t="n">
+        <v>0.02289</v>
       </c>
     </row>
     <row r="369">
@@ -32969,10 +34076,13 @@
         <v>0.03084</v>
       </c>
       <c r="AA369" s="1" t="n">
+        <v>0.03066</v>
+      </c>
+      <c r="AB369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="AB369" s="1" t="n">
-        <v>0.0308</v>
+      <c r="AC369" s="1" t="n">
+        <v>0.03066</v>
       </c>
     </row>
     <row r="370">
@@ -33057,9 +34167,12 @@
         <v>0.07972</v>
       </c>
       <c r="AA370" s="1" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="AB370" s="1" t="n">
         <v>0.08017000000000001</v>
       </c>
-      <c r="AB370" s="1" t="n">
+      <c r="AC370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -33145,10 +34258,13 @@
         <v>0.1071</v>
       </c>
       <c r="AA371" s="1" t="n">
+        <v>0.1063</v>
+      </c>
+      <c r="AB371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="AB371" s="1" t="n">
-        <v>0.1069</v>
+      <c r="AC371" s="1" t="n">
+        <v>0.1063</v>
       </c>
     </row>
     <row r="372">
@@ -33233,10 +34349,13 @@
         <v>0.006945</v>
       </c>
       <c r="AA372" s="1" t="n">
+        <v>0.006926</v>
+      </c>
+      <c r="AB372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="AB372" s="1" t="n">
-        <v>0.00694</v>
+      <c r="AC372" s="1" t="n">
+        <v>0.006926</v>
       </c>
     </row>
     <row r="373">
@@ -33321,9 +34440,12 @@
         <v>0.0969</v>
       </c>
       <c r="AA373" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="AB373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="AB373" s="1" t="n">
+      <c r="AC373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -33409,10 +34531,13 @@
         <v>0.0572</v>
       </c>
       <c r="AA374" s="1" t="n">
+        <v>0.05683</v>
+      </c>
+      <c r="AB374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="AB374" s="1" t="n">
-        <v>0.0571</v>
+      <c r="AC374" s="1" t="n">
+        <v>0.05683</v>
       </c>
     </row>
     <row r="375">
@@ -33497,9 +34622,12 @@
         <v>0.3143</v>
       </c>
       <c r="AA375" s="1" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AB375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="AB375" s="1" t="n">
+      <c r="AC375" s="1" t="n">
         <v>0.3143</v>
       </c>
     </row>
@@ -33585,10 +34713,13 @@
         <v>0.01936</v>
       </c>
       <c r="AA376" s="1" t="n">
+        <v>0.01923</v>
+      </c>
+      <c r="AB376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="AB376" s="1" t="n">
-        <v>0.01932</v>
+      <c r="AC376" s="1" t="n">
+        <v>0.01923</v>
       </c>
     </row>
     <row r="377">
@@ -33673,9 +34804,12 @@
         <v>0.06883</v>
       </c>
       <c r="AA377" s="1" t="n">
+        <v>0.06841999999999999</v>
+      </c>
+      <c r="AB377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="AB377" s="1" t="n">
+      <c r="AC377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -33761,9 +34895,12 @@
         <v>0.15544</v>
       </c>
       <c r="AA378" s="1" t="n">
+        <v>0.15749</v>
+      </c>
+      <c r="AB378" s="1" t="n">
         <v>0.15872</v>
       </c>
-      <c r="AB378" s="1" t="n">
+      <c r="AC378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -33849,10 +34986,13 @@
         <v>0.0005948</v>
       </c>
       <c r="AA379" s="1" t="n">
+        <v>0.0005909</v>
+      </c>
+      <c r="AB379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="AB379" s="1" t="n">
-        <v>0.0005922</v>
+      <c r="AC379" s="1" t="n">
+        <v>0.0005909</v>
       </c>
     </row>
     <row r="380">
@@ -33937,10 +35077,13 @@
         <v>0.01012</v>
       </c>
       <c r="AA380" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="AB380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="AB380" s="1" t="n">
-        <v>0.01011</v>
+      <c r="AC380" s="1" t="n">
+        <v>0.01008</v>
       </c>
     </row>
     <row r="381">
@@ -34025,10 +35168,13 @@
         <v>0.02543</v>
       </c>
       <c r="AA381" s="1" t="n">
+        <v>0.02533</v>
+      </c>
+      <c r="AB381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="AB381" s="1" t="n">
-        <v>0.02538</v>
+      <c r="AC381" s="1" t="n">
+        <v>0.02533</v>
       </c>
     </row>
     <row r="382">
@@ -34113,10 +35259,13 @@
         <v>0.18614</v>
       </c>
       <c r="AA382" s="1" t="n">
+        <v>0.18387</v>
+      </c>
+      <c r="AB382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="AB382" s="1" t="n">
-        <v>0.18542</v>
+      <c r="AC382" s="1" t="n">
+        <v>0.18387</v>
       </c>
     </row>
     <row r="383">
@@ -34201,10 +35350,13 @@
         <v>0.09223000000000001</v>
       </c>
       <c r="AA383" s="1" t="n">
+        <v>0.09107999999999999</v>
+      </c>
+      <c r="AB383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="AB383" s="1" t="n">
-        <v>0.09205000000000001</v>
+      <c r="AC383" s="1" t="n">
+        <v>0.09107999999999999</v>
       </c>
     </row>
     <row r="384">
@@ -34289,9 +35441,12 @@
         <v>0.03176</v>
       </c>
       <c r="AA384" s="1" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="AB384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="AB384" s="1" t="n">
+      <c r="AC384" s="1" t="n">
         <v>0.0316</v>
       </c>
     </row>
@@ -34377,10 +35532,13 @@
         <v>0.0108</v>
       </c>
       <c r="AA385" s="1" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="AB385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="AB385" s="1" t="n">
-        <v>0.0108</v>
+      <c r="AC385" s="1" t="n">
+        <v>0.0107</v>
       </c>
     </row>
     <row r="386">
@@ -34465,10 +35623,13 @@
         <v>0.0503</v>
       </c>
       <c r="AA386" s="1" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="AB386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="AB386" s="1" t="n">
-        <v>0.0503</v>
+      <c r="AC386" s="1" t="n">
+        <v>0.05022</v>
       </c>
     </row>
     <row r="387">
@@ -34553,9 +35714,12 @@
         <v>0.0235</v>
       </c>
       <c r="AA387" s="1" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="AB387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="AB387" s="1" t="n">
+      <c r="AC387" s="1" t="n">
         <v>0.0235</v>
       </c>
     </row>
@@ -34641,9 +35805,12 @@
         <v>0.007221</v>
       </c>
       <c r="AA388" s="1" t="n">
+        <v>0.007297</v>
+      </c>
+      <c r="AB388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="AB388" s="1" t="n">
+      <c r="AC388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -34729,10 +35896,13 @@
         <v>0.01012</v>
       </c>
       <c r="AA389" s="1" t="n">
+        <v>0.01004</v>
+      </c>
+      <c r="AB389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="AB389" s="1" t="n">
-        <v>0.01009</v>
+      <c r="AC389" s="1" t="n">
+        <v>0.01004</v>
       </c>
     </row>
     <row r="390">
@@ -34817,10 +35987,13 @@
         <v>0.08184</v>
       </c>
       <c r="AA390" s="1" t="n">
+        <v>0.08146</v>
+      </c>
+      <c r="AB390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="AB390" s="1" t="n">
-        <v>0.08169</v>
+      <c r="AC390" s="1" t="n">
+        <v>0.08146</v>
       </c>
     </row>
     <row r="391">
@@ -34905,10 +36078,13 @@
         <v>0.501</v>
       </c>
       <c r="AA391" s="1" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="AB391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="AB391" s="1" t="n">
-        <v>0.5006</v>
+      <c r="AC391" s="1" t="n">
+        <v>0.4985</v>
       </c>
     </row>
     <row r="392">
@@ -34993,9 +36169,12 @@
         <v>0.1163</v>
       </c>
       <c r="AA392" s="1" t="n">
+        <v>0.1158</v>
+      </c>
+      <c r="AB392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="AB392" s="1" t="n">
+      <c r="AC392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -35081,9 +36260,12 @@
         <v>0.00247</v>
       </c>
       <c r="AA393" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="AB393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="AB393" s="1" t="n">
+      <c r="AC393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -35169,9 +36351,12 @@
         <v>0.02185</v>
       </c>
       <c r="AA394" s="1" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="AB394" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="AB394" s="1" t="n">
+      <c r="AC394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -35260,6 +36445,9 @@
         <v>0.0163</v>
       </c>
       <c r="AB395" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AC395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -35345,10 +36533,13 @@
         <v>0.1348</v>
       </c>
       <c r="AA396" s="1" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="AB396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="AB396" s="1" t="n">
-        <v>0.1348</v>
+      <c r="AC396" s="1" t="n">
+        <v>0.1345</v>
       </c>
     </row>
     <row r="397">
@@ -35433,9 +36624,12 @@
         <v>0.0145</v>
       </c>
       <c r="AA397" s="1" t="n">
+        <v>0.01443</v>
+      </c>
+      <c r="AB397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="AB397" s="1" t="n">
+      <c r="AC397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -35521,9 +36715,12 @@
         <v>6.777</v>
       </c>
       <c r="AA398" s="1" t="n">
+        <v>6.748</v>
+      </c>
+      <c r="AB398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="AB398" s="1" t="n">
+      <c r="AC398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -35609,9 +36806,12 @@
         <v>0.00953</v>
       </c>
       <c r="AA399" s="1" t="n">
+        <v>0.009539000000000001</v>
+      </c>
+      <c r="AB399" s="1" t="n">
         <v>0.009542</v>
       </c>
-      <c r="AB399" s="1" t="n">
+      <c r="AC399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -35697,9 +36897,12 @@
         <v>0.001255</v>
       </c>
       <c r="AA400" s="1" t="n">
+        <v>0.001252</v>
+      </c>
+      <c r="AB400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="AB400" s="1" t="n">
+      <c r="AC400" s="1" t="n">
         <v>0.001241</v>
       </c>
     </row>
@@ -35785,9 +36988,12 @@
         <v>0.01849</v>
       </c>
       <c r="AA401" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="AB401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="AB401" s="1" t="n">
+      <c r="AC401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -35873,10 +37079,13 @@
         <v>0.08459</v>
       </c>
       <c r="AA402" s="1" t="n">
+        <v>0.08427999999999999</v>
+      </c>
+      <c r="AB402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AB402" s="1" t="n">
-        <v>0.08447</v>
+      <c r="AC402" s="1" t="n">
+        <v>0.08427999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -35961,10 +37170,13 @@
         <v>0.00545</v>
       </c>
       <c r="AA403" s="1" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="AB403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="AB403" s="1" t="n">
-        <v>0.00545</v>
+      <c r="AC403" s="1" t="n">
+        <v>0.00543</v>
       </c>
     </row>
     <row r="404">
@@ -36049,9 +37261,12 @@
         <v>0.04301</v>
       </c>
       <c r="AA404" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="AB404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="AB404" s="1" t="n">
+      <c r="AC404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -36137,10 +37352,13 @@
         <v>0.05854</v>
       </c>
       <c r="AA405" s="1" t="n">
+        <v>0.05802</v>
+      </c>
+      <c r="AB405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="AB405" s="1" t="n">
-        <v>0.05827</v>
+      <c r="AC405" s="1" t="n">
+        <v>0.05802</v>
       </c>
     </row>
     <row r="406">
@@ -36225,9 +37443,12 @@
         <v>0.01657</v>
       </c>
       <c r="AA406" s="1" t="n">
+        <v>0.01648</v>
+      </c>
+      <c r="AB406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="AB406" s="1" t="n">
+      <c r="AC406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -36313,10 +37534,13 @@
         <v>0.0422</v>
       </c>
       <c r="AA407" s="1" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="AB407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="AB407" s="1" t="n">
-        <v>0.0422</v>
+      <c r="AC407" s="1" t="n">
+        <v>0.0421</v>
       </c>
     </row>
     <row r="408">
@@ -36401,10 +37625,13 @@
         <v>0.01929</v>
       </c>
       <c r="AA408" s="1" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="AB408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="AB408" s="1" t="n">
-        <v>0.01921</v>
+      <c r="AC408" s="1" t="n">
+        <v>0.01918</v>
       </c>
     </row>
     <row r="409">
@@ -36489,10 +37716,13 @@
         <v>0.4425</v>
       </c>
       <c r="AA409" s="1" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="AB409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="AB409" s="1" t="n">
-        <v>0.4419</v>
+      <c r="AC409" s="1" t="n">
+        <v>0.4406</v>
       </c>
     </row>
     <row r="410">
@@ -36577,10 +37807,13 @@
         <v>0.04341</v>
       </c>
       <c r="AA410" s="1" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="AB410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="AB410" s="1" t="n">
-        <v>0.04337</v>
+      <c r="AC410" s="1" t="n">
+        <v>0.04322</v>
       </c>
     </row>
     <row r="411">
@@ -36665,9 +37898,12 @@
         <v>27.17</v>
       </c>
       <c r="AA411" s="1" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="AB411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="AB411" s="1" t="n">
+      <c r="AC411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -36753,10 +37989,13 @@
         <v>0.035</v>
       </c>
       <c r="AA412" s="1" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="AB412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="AB412" s="1" t="n">
-        <v>0.03486</v>
+      <c r="AC412" s="1" t="n">
+        <v>0.0347</v>
       </c>
     </row>
     <row r="413">
@@ -36841,9 +38080,12 @@
         <v>0.003404</v>
       </c>
       <c r="AA413" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="AB413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="AB413" s="1" t="n">
+      <c r="AC413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -36929,10 +38171,13 @@
         <v>0.1519</v>
       </c>
       <c r="AA414" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="AB414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="AB414" s="1" t="n">
-        <v>0.1517</v>
+      <c r="AC414" s="1" t="n">
+        <v>0.1513</v>
       </c>
     </row>
     <row r="415">
@@ -37017,10 +38262,13 @@
         <v>0.05252</v>
       </c>
       <c r="AA415" s="1" t="n">
+        <v>0.05222</v>
+      </c>
+      <c r="AB415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="AB415" s="1" t="n">
-        <v>0.05228</v>
+      <c r="AC415" s="1" t="n">
+        <v>0.05222</v>
       </c>
     </row>
     <row r="416">
@@ -37105,9 +38353,12 @@
         <v>0.00661</v>
       </c>
       <c r="AA416" s="1" t="n">
+        <v>0.00655</v>
+      </c>
+      <c r="AB416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="AB416" s="1" t="n">
+      <c r="AC416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -37193,9 +38444,12 @@
         <v>0.06043</v>
       </c>
       <c r="AA417" s="1" t="n">
+        <v>0.06026</v>
+      </c>
+      <c r="AB417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="AB417" s="1" t="n">
+      <c r="AC417" s="1" t="n">
         <v>0.06025</v>
       </c>
     </row>
@@ -37281,9 +38535,12 @@
         <v>0.008045</v>
       </c>
       <c r="AA418" s="1" t="n">
+        <v>0.008000999999999999</v>
+      </c>
+      <c r="AB418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="AB418" s="1" t="n">
+      <c r="AC418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -37369,9 +38626,12 @@
         <v>0.07327</v>
       </c>
       <c r="AA419" s="1" t="n">
+        <v>0.07319000000000001</v>
+      </c>
+      <c r="AB419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="AB419" s="1" t="n">
+      <c r="AC419" s="1" t="n">
         <v>0.07306</v>
       </c>
     </row>
@@ -37457,9 +38717,12 @@
         <v>0.02124</v>
       </c>
       <c r="AA420" s="1" t="n">
+        <v>0.02113</v>
+      </c>
+      <c r="AB420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="AB420" s="1" t="n">
+      <c r="AC420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -37545,10 +38808,13 @@
         <v>0.06879</v>
       </c>
       <c r="AA421" s="1" t="n">
+        <v>0.06843</v>
+      </c>
+      <c r="AB421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="AB421" s="1" t="n">
-        <v>0.06879</v>
+      <c r="AC421" s="1" t="n">
+        <v>0.06843</v>
       </c>
     </row>
     <row r="422">
@@ -37633,10 +38899,13 @@
         <v>0.01471</v>
       </c>
       <c r="AA422" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="AB422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="AB422" s="1" t="n">
-        <v>0.0147</v>
+      <c r="AC422" s="1" t="n">
+        <v>0.01466</v>
       </c>
     </row>
     <row r="423">
@@ -37721,9 +38990,12 @@
         <v>0.00661</v>
       </c>
       <c r="AA423" s="1" t="n">
+        <v>0.006597</v>
+      </c>
+      <c r="AB423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="AB423" s="1" t="n">
+      <c r="AC423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -37809,10 +39081,13 @@
         <v>0.902</v>
       </c>
       <c r="AA424" s="1" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="AB424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="AB424" s="1" t="n">
-        <v>0.902</v>
+      <c r="AC424" s="1" t="n">
+        <v>0.901</v>
       </c>
     </row>
     <row r="425">
@@ -37897,10 +39172,13 @@
         <v>0.03528</v>
       </c>
       <c r="AA425" s="1" t="n">
+        <v>0.03507</v>
+      </c>
+      <c r="AB425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="AB425" s="1" t="n">
-        <v>0.03512</v>
+      <c r="AC425" s="1" t="n">
+        <v>0.03507</v>
       </c>
     </row>
     <row r="426">
@@ -37985,9 +39263,12 @@
         <v>1.791</v>
       </c>
       <c r="AA426" s="1" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="AB426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB426" s="1" t="n">
+      <c r="AC426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -38073,9 +39354,12 @@
         <v>0.12936</v>
       </c>
       <c r="AA427" s="1" t="n">
+        <v>0.12911</v>
+      </c>
+      <c r="AB427" s="1" t="n">
         <v>0.12936</v>
       </c>
-      <c r="AB427" s="1" t="n">
+      <c r="AC427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -38161,9 +39445,12 @@
         <v>0.05285</v>
       </c>
       <c r="AA428" s="1" t="n">
+        <v>0.05331</v>
+      </c>
+      <c r="AB428" s="1" t="n">
         <v>0.05391</v>
       </c>
-      <c r="AB428" s="1" t="n">
+      <c r="AC428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -38249,9 +39536,12 @@
         <v>1.303</v>
       </c>
       <c r="AA429" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="AB429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="AB429" s="1" t="n">
+      <c r="AC429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -38337,10 +39627,13 @@
         <v>0.07451000000000001</v>
       </c>
       <c r="AA430" s="1" t="n">
+        <v>0.07416</v>
+      </c>
+      <c r="AB430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="AB430" s="1" t="n">
-        <v>0.07444000000000001</v>
+      <c r="AC430" s="1" t="n">
+        <v>0.07416</v>
       </c>
     </row>
     <row r="431">
@@ -38425,10 +39718,13 @@
         <v>0.1559</v>
       </c>
       <c r="AA431" s="1" t="n">
+        <v>0.1547</v>
+      </c>
+      <c r="AB431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="AB431" s="1" t="n">
-        <v>0.1559</v>
+      <c r="AC431" s="1" t="n">
+        <v>0.1547</v>
       </c>
     </row>
     <row r="432">
@@ -38513,9 +39809,12 @@
         <v>1.444</v>
       </c>
       <c r="AA432" s="1" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="AB432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="AB432" s="1" t="n">
+      <c r="AC432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -38601,10 +39900,13 @@
         <v>3.236</v>
       </c>
       <c r="AA433" s="1" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AB433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="AB433" s="1" t="n">
-        <v>3.225</v>
+      <c r="AC433" s="1" t="n">
+        <v>3.22</v>
       </c>
     </row>
     <row r="434">
@@ -38689,10 +39991,13 @@
         <v>0.1776</v>
       </c>
       <c r="AA434" s="1" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="AB434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="AB434" s="1" t="n">
-        <v>0.1775</v>
+      <c r="AC434" s="1" t="n">
+        <v>0.1772</v>
       </c>
     </row>
     <row r="435">
@@ -38777,10 +40082,13 @@
         <v>0.008580000000000001</v>
       </c>
       <c r="AA435" s="1" t="n">
+        <v>0.008536999999999999</v>
+      </c>
+      <c r="AB435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="AB435" s="1" t="n">
-        <v>0.008548</v>
+      <c r="AC435" s="1" t="n">
+        <v>0.008536999999999999</v>
       </c>
     </row>
     <row r="436">
@@ -38865,9 +40173,12 @@
         <v>0.2813</v>
       </c>
       <c r="AA436" s="1" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AB436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="AB436" s="1" t="n">
+      <c r="AC436" s="1" t="n">
         <v>0.2803</v>
       </c>
     </row>
@@ -38953,9 +40264,12 @@
         <v>0.03818</v>
       </c>
       <c r="AA437" s="1" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="AB437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="AB437" s="1" t="n">
+      <c r="AC437" s="1" t="n">
         <v>0.03802</v>
       </c>
     </row>
@@ -39041,9 +40355,12 @@
         <v>0.02432</v>
       </c>
       <c r="AA438" s="1" t="n">
+        <v>0.02416</v>
+      </c>
+      <c r="AB438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="AB438" s="1" t="n">
+      <c r="AC438" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -39129,9 +40446,12 @@
         <v>0.04403</v>
       </c>
       <c r="AA439" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="AB439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="AB439" s="1" t="n">
+      <c r="AC439" s="1" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -39217,9 +40537,12 @@
         <v>0.0005194</v>
       </c>
       <c r="AA440" s="1" t="n">
+        <v>0.0005173000000000001</v>
+      </c>
+      <c r="AB440" s="1" t="n">
         <v>0.0005312</v>
       </c>
-      <c r="AB440" s="1" t="n">
+      <c r="AC440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -39305,9 +40628,12 @@
         <v>0.04488</v>
       </c>
       <c r="AA441" s="1" t="n">
+        <v>0.04544</v>
+      </c>
+      <c r="AB441" s="1" t="n">
         <v>0.04581</v>
       </c>
-      <c r="AB441" s="1" t="n">
+      <c r="AC441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -39393,9 +40719,12 @@
         <v>0.000417</v>
       </c>
       <c r="AA442" s="1" t="n">
+        <v>0.000416</v>
+      </c>
+      <c r="AB442" s="1" t="n">
         <v>0.000419</v>
       </c>
-      <c r="AB442" s="1" t="n">
+      <c r="AC442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -39481,9 +40810,12 @@
         <v>0.09453</v>
       </c>
       <c r="AA443" s="1" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="AB443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="AB443" s="1" t="n">
+      <c r="AC443" s="1" t="n">
         <v>0.09392</v>
       </c>
     </row>
@@ -39569,10 +40901,13 @@
         <v>2.281</v>
       </c>
       <c r="AA444" s="1" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AB444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="AB444" s="1" t="n">
-        <v>2.279</v>
+      <c r="AC444" s="1" t="n">
+        <v>2.268</v>
       </c>
     </row>
     <row r="445">
@@ -39657,10 +40992,13 @@
         <v>0.2665</v>
       </c>
       <c r="AA445" s="1" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="AB445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="AB445" s="1" t="n">
-        <v>0.2661</v>
+      <c r="AC445" s="1" t="n">
+        <v>0.2659</v>
       </c>
     </row>
     <row r="446">
@@ -39745,9 +41083,12 @@
         <v>0.0007455</v>
       </c>
       <c r="AA446" s="1" t="n">
+        <v>0.0007421</v>
+      </c>
+      <c r="AB446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="AB446" s="1" t="n">
+      <c r="AC446" s="1" t="n">
         <v>0.0007376</v>
       </c>
     </row>
@@ -39833,9 +41174,12 @@
         <v>0.03851</v>
       </c>
       <c r="AA447" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="AB447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="AB447" s="1" t="n">
+      <c r="AC447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -39921,9 +41265,12 @@
         <v>0.1763</v>
       </c>
       <c r="AA448" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="AB448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="AB448" s="1" t="n">
+      <c r="AC448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -40009,9 +41356,12 @@
         <v>0.0429</v>
       </c>
       <c r="AA449" s="1" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="AB449" s="1" t="n">
         <v>0.04312</v>
       </c>
-      <c r="AB449" s="1" t="n">
+      <c r="AC449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -40097,9 +41447,12 @@
         <v>0.000165</v>
       </c>
       <c r="AA450" s="1" t="n">
+        <v>0.0001639</v>
+      </c>
+      <c r="AB450" s="1" t="n">
         <v>0.0001657</v>
       </c>
-      <c r="AB450" s="1" t="n">
+      <c r="AC450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -40185,9 +41538,12 @@
         <v>0.03737</v>
       </c>
       <c r="AA451" s="1" t="n">
+        <v>0.03719</v>
+      </c>
+      <c r="AB451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="AB451" s="1" t="n">
+      <c r="AC451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -40273,10 +41629,13 @@
         <v>0.009390000000000001</v>
       </c>
       <c r="AA452" s="1" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="AB452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="AB452" s="1" t="n">
-        <v>0.009390000000000001</v>
+      <c r="AC452" s="1" t="n">
+        <v>0.009310000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -40361,10 +41720,13 @@
         <v>0.06733</v>
       </c>
       <c r="AA453" s="1" t="n">
+        <v>0.06713</v>
+      </c>
+      <c r="AB453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="AB453" s="1" t="n">
-        <v>0.06733</v>
+      <c r="AC453" s="1" t="n">
+        <v>0.06713</v>
       </c>
     </row>
     <row r="454">
@@ -40449,10 +41811,13 @@
         <v>0.007483</v>
       </c>
       <c r="AA454" s="1" t="n">
+        <v>0.007453</v>
+      </c>
+      <c r="AB454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="AB454" s="1" t="n">
-        <v>0.007472</v>
+      <c r="AC454" s="1" t="n">
+        <v>0.007453</v>
       </c>
     </row>
     <row r="455">
@@ -40537,10 +41902,13 @@
         <v>0.003242</v>
       </c>
       <c r="AA455" s="1" t="n">
+        <v>0.003234</v>
+      </c>
+      <c r="AB455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="AB455" s="1" t="n">
-        <v>0.00324</v>
+      <c r="AC455" s="1" t="n">
+        <v>0.003234</v>
       </c>
     </row>
     <row r="456">
@@ -40625,10 +41993,13 @@
         <v>0.001838</v>
       </c>
       <c r="AA456" s="1" t="n">
+        <v>0.001826</v>
+      </c>
+      <c r="AB456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="AB456" s="1" t="n">
-        <v>0.001835</v>
+      <c r="AC456" s="1" t="n">
+        <v>0.001826</v>
       </c>
     </row>
     <row r="457">
@@ -40713,10 +42084,13 @@
         <v>0.0001744</v>
       </c>
       <c r="AA457" s="1" t="n">
+        <v>0.0001737</v>
+      </c>
+      <c r="AB457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="AB457" s="1" t="n">
-        <v>0.0001742</v>
+      <c r="AC457" s="1" t="n">
+        <v>0.0001737</v>
       </c>
     </row>
     <row r="458">
@@ -40801,10 +42175,13 @@
         <v>0.0003889</v>
       </c>
       <c r="AA458" s="1" t="n">
+        <v>0.0003866</v>
+      </c>
+      <c r="AB458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="AB458" s="1" t="n">
-        <v>0.0003873</v>
+      <c r="AC458" s="1" t="n">
+        <v>0.0003866</v>
       </c>
     </row>
     <row r="459">
@@ -40889,10 +42266,13 @@
         <v>0.01392</v>
       </c>
       <c r="AA459" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="AB459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="AB459" s="1" t="n">
-        <v>0.01391</v>
+      <c r="AC459" s="1" t="n">
+        <v>0.01386</v>
       </c>
     </row>
     <row r="460">
@@ -40977,9 +42357,12 @@
         <v>0.04537</v>
       </c>
       <c r="AA460" s="1" t="n">
+        <v>0.04524</v>
+      </c>
+      <c r="AB460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="AB460" s="1" t="n">
+      <c r="AC460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -41065,10 +42448,13 @@
         <v>0.2815</v>
       </c>
       <c r="AA461" s="1" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="AB461" s="1" t="n">
         <v>0.2843</v>
       </c>
-      <c r="AB461" s="1" t="n">
-        <v>0.2809</v>
+      <c r="AC461" s="1" t="n">
+        <v>0.2807</v>
       </c>
     </row>
     <row r="462">
@@ -41153,10 +42539,13 @@
         <v>0.006224</v>
       </c>
       <c r="AA462" s="1" t="n">
+        <v>0.006184</v>
+      </c>
+      <c r="AB462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="AB462" s="1" t="n">
-        <v>0.006203</v>
+      <c r="AC462" s="1" t="n">
+        <v>0.006184</v>
       </c>
     </row>
     <row r="463">
@@ -41241,9 +42630,12 @@
         <v>0.007074</v>
       </c>
       <c r="AA463" s="1" t="n">
+        <v>0.00706</v>
+      </c>
+      <c r="AB463" s="1" t="n">
         <v>0.007153</v>
       </c>
-      <c r="AB463" s="1" t="n">
+      <c r="AC463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -41329,9 +42721,12 @@
         <v>0.2869</v>
       </c>
       <c r="AA464" s="1" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AB464" s="1" t="n">
         <v>0.2895</v>
       </c>
-      <c r="AB464" s="1" t="n">
+      <c r="AC464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -41417,9 +42812,12 @@
         <v>0.08061</v>
       </c>
       <c r="AA465" s="1" t="n">
+        <v>0.08084</v>
+      </c>
+      <c r="AB465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="AB465" s="1" t="n">
+      <c r="AC465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -41505,10 +42903,13 @@
         <v>0.6329</v>
       </c>
       <c r="AA466" s="1" t="n">
+        <v>0.6288</v>
+      </c>
+      <c r="AB466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="AB466" s="1" t="n">
-        <v>0.6318</v>
+      <c r="AC466" s="1" t="n">
+        <v>0.6288</v>
       </c>
     </row>
     <row r="467">
@@ -41593,10 +42994,13 @@
         <v>0.01466</v>
       </c>
       <c r="AA467" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="AB467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="AB467" s="1" t="n">
-        <v>0.01464</v>
+      <c r="AC467" s="1" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="468">
@@ -41681,9 +43085,12 @@
         <v>0.03443</v>
       </c>
       <c r="AA468" s="1" t="n">
+        <v>0.03457</v>
+      </c>
+      <c r="AB468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="AB468" s="1" t="n">
+      <c r="AC468" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -41769,10 +43176,13 @@
         <v>0.1615</v>
       </c>
       <c r="AA469" s="1" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="AB469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="AB469" s="1" t="n">
-        <v>0.1609</v>
+      <c r="AC469" s="1" t="n">
+        <v>0.1604</v>
       </c>
     </row>
     <row r="470">
@@ -41857,10 +43267,13 @@
         <v>0.4086</v>
       </c>
       <c r="AA470" s="1" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="AB470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="AB470" s="1" t="n">
-        <v>0.408</v>
+      <c r="AC470" s="1" t="n">
+        <v>0.4058</v>
       </c>
     </row>
     <row r="471">
@@ -41945,9 +43358,12 @@
         <v>0.06876</v>
       </c>
       <c r="AA471" s="1" t="n">
+        <v>0.06858</v>
+      </c>
+      <c r="AB471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="AB471" s="1" t="n">
+      <c r="AC471" s="1" t="n">
         <v>0.06854</v>
       </c>
     </row>
@@ -42033,10 +43449,13 @@
         <v>0.06539</v>
       </c>
       <c r="AA472" s="1" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="AB472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="AB472" s="1" t="n">
-        <v>0.06515</v>
+      <c r="AC472" s="1" t="n">
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="473">
@@ -42121,9 +43540,12 @@
         <v>0.01629</v>
       </c>
       <c r="AA473" s="1" t="n">
+        <v>0.01625</v>
+      </c>
+      <c r="AB473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="AB473" s="1" t="n">
+      <c r="AC473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -42209,10 +43631,13 @@
         <v>0.2049</v>
       </c>
       <c r="AA474" s="1" t="n">
+        <v>0.2037</v>
+      </c>
+      <c r="AB474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="AB474" s="1" t="n">
-        <v>0.2047</v>
+      <c r="AC474" s="1" t="n">
+        <v>0.2037</v>
       </c>
     </row>
     <row r="475">
@@ -42297,9 +43722,12 @@
         <v>0.04156</v>
       </c>
       <c r="AA475" s="1" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="AB475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="AB475" s="1" t="n">
+      <c r="AC475" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -42385,10 +43813,13 @@
         <v>1.562</v>
       </c>
       <c r="AA476" s="1" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="AB476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="AB476" s="1" t="n">
-        <v>1.557</v>
+      <c r="AC476" s="1" t="n">
+        <v>1.554</v>
       </c>
     </row>
     <row r="477">
@@ -42473,9 +43904,12 @@
         <v>0.101</v>
       </c>
       <c r="AA477" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="AB477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="AB477" s="1" t="n">
+      <c r="AC477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -42561,9 +43995,12 @@
         <v>0.001154</v>
       </c>
       <c r="AA478" s="1" t="n">
+        <v>0.001151</v>
+      </c>
+      <c r="AB478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="AB478" s="1" t="n">
+      <c r="AC478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -42649,10 +44086,13 @@
         <v>0.1427</v>
       </c>
       <c r="AA479" s="1" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="AB479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="AB479" s="1" t="n">
-        <v>0.1425</v>
+      <c r="AC479" s="1" t="n">
+        <v>0.1417</v>
       </c>
     </row>
     <row r="480">
@@ -42737,9 +44177,12 @@
         <v>0.001911</v>
       </c>
       <c r="AA480" s="1" t="n">
+        <v>0.001886</v>
+      </c>
+      <c r="AB480" s="1" t="n">
         <v>0.001969</v>
       </c>
-      <c r="AB480" s="1" t="n">
+      <c r="AC480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -42825,10 +44268,13 @@
         <v>0.903</v>
       </c>
       <c r="AA481" s="1" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AB481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="AB481" s="1" t="n">
-        <v>0.902</v>
+      <c r="AC481" s="1" t="n">
+        <v>0.899</v>
       </c>
     </row>
     <row r="482">
@@ -42913,9 +44359,12 @@
         <v>0.13306</v>
       </c>
       <c r="AA482" s="1" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="AB482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="AB482" s="1" t="n">
+      <c r="AC482" s="1" t="n">
         <v>0.13233</v>
       </c>
     </row>
@@ -43001,10 +44450,13 @@
         <v>0.04016</v>
       </c>
       <c r="AA483" s="1" t="n">
+        <v>0.04004</v>
+      </c>
+      <c r="AB483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="AB483" s="1" t="n">
-        <v>0.04005</v>
+      <c r="AC483" s="1" t="n">
+        <v>0.04004</v>
       </c>
     </row>
     <row r="484">
@@ -43089,9 +44541,12 @@
         <v>0.3009</v>
       </c>
       <c r="AA484" s="1" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AB484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="AB484" s="1" t="n">
+      <c r="AC484" s="1" t="n">
         <v>0.2999</v>
       </c>
     </row>
@@ -43177,10 +44632,13 @@
         <v>0.05625</v>
       </c>
       <c r="AA485" s="1" t="n">
+        <v>0.05601</v>
+      </c>
+      <c r="AB485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="AB485" s="1" t="n">
-        <v>0.05603</v>
+      <c r="AC485" s="1" t="n">
+        <v>0.05601</v>
       </c>
     </row>
     <row r="486">
@@ -43265,9 +44723,12 @@
         <v>0.001559</v>
       </c>
       <c r="AA486" s="1" t="n">
+        <v>0.001555</v>
+      </c>
+      <c r="AB486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="AB486" s="1" t="n">
+      <c r="AC486" s="1" t="n">
         <v>0.001555</v>
       </c>
     </row>
@@ -43353,10 +44814,13 @@
         <v>0.06669</v>
       </c>
       <c r="AA487" s="1" t="n">
+        <v>0.06635000000000001</v>
+      </c>
+      <c r="AB487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="AB487" s="1" t="n">
-        <v>0.0665</v>
+      <c r="AC487" s="1" t="n">
+        <v>0.06635000000000001</v>
       </c>
     </row>
     <row r="488">
@@ -43441,10 +44905,13 @@
         <v>0.1912</v>
       </c>
       <c r="AA488" s="1" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="AB488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="AB488" s="1" t="n">
-        <v>0.1911</v>
+      <c r="AC488" s="1" t="n">
+        <v>0.1906</v>
       </c>
     </row>
     <row r="489">
@@ -43529,10 +44996,13 @@
         <v>0.04767</v>
       </c>
       <c r="AA489" s="1" t="n">
+        <v>0.04745</v>
+      </c>
+      <c r="AB489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="AB489" s="1" t="n">
-        <v>0.04761</v>
+      <c r="AC489" s="1" t="n">
+        <v>0.04745</v>
       </c>
     </row>
     <row r="490">
@@ -43617,10 +45087,13 @@
         <v>0.1385</v>
       </c>
       <c r="AA490" s="1" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AB490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="AB490" s="1" t="n">
-        <v>0.1384</v>
+      <c r="AC490" s="1" t="n">
+        <v>0.138</v>
       </c>
     </row>
     <row r="491">
@@ -43705,9 +45178,12 @@
         <v>0.02262</v>
       </c>
       <c r="AA491" s="1" t="n">
+        <v>0.02252</v>
+      </c>
+      <c r="AB491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="AB491" s="1" t="n">
+      <c r="AC491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -43793,9 +45269,12 @@
         <v>0.00777</v>
       </c>
       <c r="AA492" s="1" t="n">
+        <v>0.007741</v>
+      </c>
+      <c r="AB492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="AB492" s="1" t="n">
+      <c r="AC492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -43881,10 +45360,13 @@
         <v>0.0005904</v>
       </c>
       <c r="AA493" s="1" t="n">
+        <v>0.0005879</v>
+      </c>
+      <c r="AB493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="AB493" s="1" t="n">
-        <v>0.0005903</v>
+      <c r="AC493" s="1" t="n">
+        <v>0.0005879</v>
       </c>
     </row>
     <row r="494">
@@ -43969,10 +45451,13 @@
         <v>3.003</v>
       </c>
       <c r="AA494" s="1" t="n">
+        <v>2.993</v>
+      </c>
+      <c r="AB494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="AB494" s="1" t="n">
-        <v>2.999</v>
+      <c r="AC494" s="1" t="n">
+        <v>2.993</v>
       </c>
     </row>
     <row r="495">
@@ -44057,10 +45542,13 @@
         <v>0.0508</v>
       </c>
       <c r="AA495" s="1" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="AB495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="AB495" s="1" t="n">
-        <v>0.05042</v>
+      <c r="AC495" s="1" t="n">
+        <v>0.0504</v>
       </c>
     </row>
     <row r="496">
@@ -44145,10 +45633,13 @@
         <v>0.006793</v>
       </c>
       <c r="AA496" s="1" t="n">
+        <v>0.006734</v>
+      </c>
+      <c r="AB496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="AB496" s="1" t="n">
-        <v>0.006742</v>
+      <c r="AC496" s="1" t="n">
+        <v>0.006734</v>
       </c>
     </row>
     <row r="497">
@@ -44233,9 +45724,12 @@
         <v>1.299</v>
       </c>
       <c r="AA497" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="AB497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="AB497" s="1" t="n">
+      <c r="AC497" s="1" t="n">
         <v>1.298</v>
       </c>
     </row>
@@ -44321,9 +45815,12 @@
         <v>0.03905</v>
       </c>
       <c r="AA498" s="1" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="AB498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="AB498" s="1" t="n">
+      <c r="AC498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -44409,10 +45906,13 @@
         <v>0.0409</v>
       </c>
       <c r="AA499" s="1" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="AB499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="AB499" s="1" t="n">
-        <v>0.04085</v>
+      <c r="AC499" s="1" t="n">
+        <v>0.04072</v>
       </c>
     </row>
     <row r="500">
@@ -44497,9 +45997,12 @@
         <v>0.00541</v>
       </c>
       <c r="AA500" s="1" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="AB500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="AB500" s="1" t="n">
+      <c r="AC500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -44585,10 +46088,13 @@
         <v>0.03554</v>
       </c>
       <c r="AA501" s="1" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="AB501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="AB501" s="1" t="n">
-        <v>0.03548</v>
+      <c r="AC501" s="1" t="n">
+        <v>0.03542</v>
       </c>
     </row>
     <row r="502">
@@ -44673,10 +46179,13 @@
         <v>0.07207</v>
       </c>
       <c r="AA502" s="1" t="n">
+        <v>0.07174999999999999</v>
+      </c>
+      <c r="AB502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="AB502" s="1" t="n">
-        <v>0.07191</v>
+      <c r="AC502" s="1" t="n">
+        <v>0.07174999999999999</v>
       </c>
     </row>
     <row r="503">
@@ -44761,10 +46270,13 @@
         <v>0.0007407</v>
       </c>
       <c r="AA503" s="1" t="n">
+        <v>0.000738</v>
+      </c>
+      <c r="AB503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="AB503" s="1" t="n">
-        <v>0.0007389</v>
+      <c r="AC503" s="1" t="n">
+        <v>0.000738</v>
       </c>
     </row>
     <row r="504">
@@ -44849,9 +46361,12 @@
         <v>0.01607</v>
       </c>
       <c r="AA504" s="1" t="n">
+        <v>0.016062</v>
+      </c>
+      <c r="AB504" s="1" t="n">
         <v>0.01607</v>
       </c>
-      <c r="AB504" s="1" t="n">
+      <c r="AC504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -44937,10 +46452,13 @@
         <v>0.00701</v>
       </c>
       <c r="AA505" s="1" t="n">
+        <v>0.00698</v>
+      </c>
+      <c r="AB505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="AB505" s="1" t="n">
-        <v>0.00701</v>
+      <c r="AC505" s="1" t="n">
+        <v>0.00698</v>
       </c>
     </row>
     <row r="506">
@@ -45025,9 +46543,12 @@
         <v>0.0257</v>
       </c>
       <c r="AA506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AB506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="AB506" s="1" t="n">
+      <c r="AC506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -45116,6 +46637,9 @@
         <v>0.001362</v>
       </c>
       <c r="AB507" s="1" t="n">
+        <v>0.001362</v>
+      </c>
+      <c r="AC507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -45201,10 +46725,13 @@
         <v>0.2811</v>
       </c>
       <c r="AA508" s="1" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="AB508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="AB508" s="1" t="n">
-        <v>0.2805</v>
+      <c r="AC508" s="1" t="n">
+        <v>0.2798</v>
       </c>
     </row>
     <row r="509">
@@ -45289,10 +46816,13 @@
         <v>0.1314</v>
       </c>
       <c r="AA509" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="AB509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="AB509" s="1" t="n">
-        <v>0.1311</v>
+      <c r="AC509" s="1" t="n">
+        <v>0.131</v>
       </c>
     </row>
     <row r="510">
@@ -45377,9 +46907,12 @@
         <v>0.04927</v>
       </c>
       <c r="AA510" s="1" t="n">
+        <v>0.04887</v>
+      </c>
+      <c r="AB510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="AB510" s="1" t="n">
+      <c r="AC510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -45465,10 +46998,13 @@
         <v>0.00269</v>
       </c>
       <c r="AA511" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="AB511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="AB511" s="1" t="n">
-        <v>0.00269</v>
+      <c r="AC511" s="1" t="n">
+        <v>0.00267</v>
       </c>
     </row>
     <row r="512">
@@ -45553,9 +47089,12 @@
         <v>0.015037</v>
       </c>
       <c r="AA512" s="1" t="n">
+        <v>0.014989</v>
+      </c>
+      <c r="AB512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="AB512" s="1" t="n">
+      <c r="AC512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -45641,9 +47180,12 @@
         <v>0.6895</v>
       </c>
       <c r="AA513" s="1" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="AB513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="AB513" s="1" t="n">
+      <c r="AC513" s="1" t="n">
         <v>0.6883</v>
       </c>
     </row>
@@ -45729,9 +47271,12 @@
         <v>0.004549</v>
       </c>
       <c r="AA514" s="1" t="n">
+        <v>0.004498</v>
+      </c>
+      <c r="AB514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="AB514" s="1" t="n">
+      <c r="AC514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -45817,9 +47362,12 @@
         <v>0.005071</v>
       </c>
       <c r="AA515" s="1" t="n">
+        <v>0.005064</v>
+      </c>
+      <c r="AB515" s="1" t="n">
         <v>0.005074</v>
       </c>
-      <c r="AB515" s="1" t="n">
+      <c r="AC515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -45905,10 +47453,13 @@
         <v>0.063</v>
       </c>
       <c r="AA516" s="1" t="n">
+        <v>0.06283999999999999</v>
+      </c>
+      <c r="AB516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="AB516" s="1" t="n">
-        <v>0.063</v>
+      <c r="AC516" s="1" t="n">
+        <v>0.06283999999999999</v>
       </c>
     </row>
     <row r="517">
@@ -45993,9 +47544,12 @@
         <v>0.06462</v>
       </c>
       <c r="AA517" s="1" t="n">
+        <v>0.06441</v>
+      </c>
+      <c r="AB517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="AB517" s="1" t="n">
+      <c r="AC517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -46081,10 +47635,13 @@
         <v>0.01196</v>
       </c>
       <c r="AA518" s="1" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="AB518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="AB518" s="1" t="n">
-        <v>0.01195</v>
+      <c r="AC518" s="1" t="n">
+        <v>0.0119</v>
       </c>
     </row>
     <row r="519">
@@ -46169,10 +47726,13 @@
         <v>0.04734</v>
       </c>
       <c r="AA519" s="1" t="n">
+        <v>0.0468</v>
+      </c>
+      <c r="AB519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="AB519" s="1" t="n">
-        <v>0.04733</v>
+      <c r="AC519" s="1" t="n">
+        <v>0.0468</v>
       </c>
     </row>
     <row r="520">
@@ -46257,9 +47817,12 @@
         <v>0.04375</v>
       </c>
       <c r="AA520" s="1" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AB520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="AB520" s="1" t="n">
+      <c r="AC520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -46345,9 +47908,12 @@
         <v>0.008366</v>
       </c>
       <c r="AA521" s="1" t="n">
+        <v>0.008373</v>
+      </c>
+      <c r="AB521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="AB521" s="1" t="n">
+      <c r="AC521" s="1" t="n">
         <v>0.008288</v>
       </c>
     </row>
@@ -46433,10 +47999,13 @@
         <v>0.08776</v>
       </c>
       <c r="AA522" s="1" t="n">
+        <v>0.08749</v>
+      </c>
+      <c r="AB522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="AB522" s="1" t="n">
-        <v>0.08762</v>
+      <c r="AC522" s="1" t="n">
+        <v>0.08749</v>
       </c>
     </row>
     <row r="523">
@@ -46521,9 +48090,12 @@
         <v>0.006463</v>
       </c>
       <c r="AA523" s="1" t="n">
+        <v>0.006436</v>
+      </c>
+      <c r="AB523" s="1" t="n">
         <v>0.006503</v>
       </c>
-      <c r="AB523" s="1" t="n">
+      <c r="AC523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -46609,9 +48181,12 @@
         <v>0.01631</v>
       </c>
       <c r="AA524" s="1" t="n">
+        <v>0.01629</v>
+      </c>
+      <c r="AB524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="AB524" s="1" t="n">
+      <c r="AC524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -46697,9 +48272,12 @@
         <v>0.01785</v>
       </c>
       <c r="AA525" s="1" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="AB525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="AB525" s="1" t="n">
+      <c r="AC525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -46785,10 +48363,13 @@
         <v>0.0785</v>
       </c>
       <c r="AA526" s="1" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="AB526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="AB526" s="1" t="n">
-        <v>0.0785</v>
+      <c r="AC526" s="1" t="n">
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="527">
@@ -46873,9 +48454,12 @@
         <v>0.016</v>
       </c>
       <c r="AA527" s="1" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="AB527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="AB527" s="1" t="n">
+      <c r="AC527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -46961,10 +48545,13 @@
         <v>0.004125</v>
       </c>
       <c r="AA528" s="1" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="AB528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="AB528" s="1" t="n">
-        <v>0.004113</v>
+      <c r="AC528" s="1" t="n">
+        <v>0.00409</v>
       </c>
     </row>
     <row r="529">
@@ -47049,9 +48636,12 @@
         <v>0.003665</v>
       </c>
       <c r="AA529" s="1" t="n">
+        <v>0.003682</v>
+      </c>
+      <c r="AB529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="AB529" s="1" t="n">
+      <c r="AC529" s="1" t="n">
         <v>0.003665</v>
       </c>
     </row>
@@ -47137,9 +48727,12 @@
         <v>1.322</v>
       </c>
       <c r="AA530" s="1" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="AB530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="AB530" s="1" t="n">
+      <c r="AC530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -47225,10 +48818,13 @@
         <v>0.4874</v>
       </c>
       <c r="AA531" s="1" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="AB531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="AB531" s="1" t="n">
-        <v>0.4866</v>
+      <c r="AC531" s="1" t="n">
+        <v>0.4858</v>
       </c>
     </row>
     <row r="532">
@@ -47313,9 +48909,12 @@
         <v>0.03049</v>
       </c>
       <c r="AA532" s="1" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="AB532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="AB532" s="1" t="n">
+      <c r="AC532" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -47401,10 +49000,13 @@
         <v>0.1523</v>
       </c>
       <c r="AA533" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AB533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="AB533" s="1" t="n">
-        <v>0.1521</v>
+      <c r="AC533" s="1" t="n">
+        <v>0.152</v>
       </c>
     </row>
     <row r="534">
@@ -47489,10 +49091,13 @@
         <v>0.05363</v>
       </c>
       <c r="AA534" s="1" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="AB534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="AB534" s="1" t="n">
-        <v>0.05344</v>
+      <c r="AC534" s="1" t="n">
+        <v>0.05314</v>
       </c>
     </row>
     <row r="535">
@@ -47577,10 +49182,13 @@
         <v>0.0149</v>
       </c>
       <c r="AA535" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="AB535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="AB535" s="1" t="n">
-        <v>0.01472</v>
+      <c r="AC535" s="1" t="n">
+        <v>0.01471</v>
       </c>
     </row>
     <row r="536">
@@ -47665,10 +49273,13 @@
         <v>0.05829</v>
       </c>
       <c r="AA536" s="1" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="AB536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="AB536" s="1" t="n">
-        <v>0.0581</v>
+      <c r="AC536" s="1" t="n">
+        <v>0.0576</v>
       </c>
     </row>
     <row r="537">
@@ -47753,10 +49364,13 @@
         <v>0.0547</v>
       </c>
       <c r="AA537" s="1" t="n">
+        <v>0.05459</v>
+      </c>
+      <c r="AB537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="AB537" s="1" t="n">
-        <v>0.0546</v>
+      <c r="AC537" s="1" t="n">
+        <v>0.05459</v>
       </c>
     </row>
     <row r="538">
@@ -47841,9 +49455,12 @@
         <v>0.1064</v>
       </c>
       <c r="AA538" s="1" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="AB538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="AB538" s="1" t="n">
+      <c r="AC538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -47929,9 +49546,12 @@
         <v>0.01267</v>
       </c>
       <c r="AA539" s="1" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="AB539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="AB539" s="1" t="n">
+      <c r="AC539" s="1" t="n">
         <v>0.01265</v>
       </c>
     </row>
@@ -48017,10 +49637,13 @@
         <v>0.1724</v>
       </c>
       <c r="AA540" s="1" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="AB540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="AB540" s="1" t="n">
-        <v>0.1721</v>
+      <c r="AC540" s="1" t="n">
+        <v>0.1719</v>
       </c>
     </row>
     <row r="541">
@@ -48105,9 +49728,12 @@
         <v>0.1231</v>
       </c>
       <c r="AA541" s="1" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="AB541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="AB541" s="1" t="n">
+      <c r="AC541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -48193,10 +49819,13 @@
         <v>0.0249</v>
       </c>
       <c r="AA542" s="1" t="n">
+        <v>0.02474</v>
+      </c>
+      <c r="AB542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="AB542" s="1" t="n">
-        <v>0.02478</v>
+      <c r="AC542" s="1" t="n">
+        <v>0.02474</v>
       </c>
     </row>
     <row r="543">
@@ -48281,10 +49910,13 @@
         <v>0.05836</v>
       </c>
       <c r="AA543" s="1" t="n">
+        <v>0.05813</v>
+      </c>
+      <c r="AB543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="AB543" s="1" t="n">
-        <v>0.05832</v>
+      <c r="AC543" s="1" t="n">
+        <v>0.05813</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC543"/>
+  <dimension ref="A1:AD543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -446,8 +446,9 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,10 +589,15 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>price_06:30</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -682,10 +688,13 @@
         <v>70810.60000000001</v>
       </c>
       <c r="AB2" s="1" t="n">
+        <v>70636.60000000001</v>
+      </c>
+      <c r="AC2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="AC2" s="1" t="n">
-        <v>70810.60000000001</v>
+      <c r="AD2" s="1" t="n">
+        <v>70636.60000000001</v>
       </c>
     </row>
     <row r="3">
@@ -773,10 +782,13 @@
         <v>2090.89</v>
       </c>
       <c r="AB3" s="1" t="n">
+        <v>2081.65</v>
+      </c>
+      <c r="AC3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="AC3" s="1" t="n">
-        <v>2090.89</v>
+      <c r="AD3" s="1" t="n">
+        <v>2081.65</v>
       </c>
     </row>
     <row r="4">
@@ -864,10 +876,13 @@
         <v>88.16</v>
       </c>
       <c r="AB4" s="1" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="AC4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="AC4" s="1" t="n">
-        <v>88.16</v>
+      <c r="AD4" s="1" t="n">
+        <v>87.84</v>
       </c>
     </row>
     <row r="5">
@@ -955,9 +970,12 @@
         <v>3.845</v>
       </c>
       <c r="AB5" s="1" t="n">
+        <v>3.791</v>
+      </c>
+      <c r="AC5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AD5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -1046,10 +1064,13 @@
         <v>1.3967</v>
       </c>
       <c r="AB6" s="1" t="n">
+        <v>1.3913</v>
+      </c>
+      <c r="AC6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="AC6" s="1" t="n">
-        <v>1.3931</v>
+      <c r="AD6" s="1" t="n">
+        <v>1.3913</v>
       </c>
     </row>
     <row r="7">
@@ -1137,10 +1158,13 @@
         <v>0.09593</v>
       </c>
       <c r="AB7" s="1" t="n">
+        <v>0.09563000000000001</v>
+      </c>
+      <c r="AC7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="AC7" s="1" t="n">
-        <v>0.09572</v>
+      <c r="AD7" s="1" t="n">
+        <v>0.09563000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1228,10 +1252,13 @@
         <v>0.013043</v>
       </c>
       <c r="AB8" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="AC8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="AC8" s="1" t="n">
-        <v>0.013043</v>
+      <c r="AD8" s="1" t="n">
+        <v>0.01259</v>
       </c>
     </row>
     <row r="9">
@@ -1319,10 +1346,13 @@
         <v>656.16</v>
       </c>
       <c r="AB9" s="1" t="n">
+        <v>654.74</v>
+      </c>
+      <c r="AC9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="AC9" s="1" t="n">
-        <v>655.72</v>
+      <c r="AD9" s="1" t="n">
+        <v>654.74</v>
       </c>
     </row>
     <row r="10">
@@ -1410,9 +1440,12 @@
         <v>19.982</v>
       </c>
       <c r="AB10" s="1" t="n">
+        <v>20.014</v>
+      </c>
+      <c r="AC10" s="1" t="n">
         <v>20.464</v>
       </c>
-      <c r="AC10" s="1" t="n">
+      <c r="AD10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1501,10 +1534,13 @@
         <v>0.0033745</v>
       </c>
       <c r="AB11" s="1" t="n">
+        <v>0.0033626</v>
+      </c>
+      <c r="AC11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="AC11" s="1" t="n">
-        <v>0.0033745</v>
+      <c r="AD11" s="1" t="n">
+        <v>0.0033626</v>
       </c>
     </row>
     <row r="12">
@@ -1592,10 +1628,13 @@
         <v>36.266</v>
       </c>
       <c r="AB12" s="1" t="n">
+        <v>36.098</v>
+      </c>
+      <c r="AC12" s="1" t="n">
         <v>36.869</v>
       </c>
-      <c r="AC12" s="1" t="n">
-        <v>36.163</v>
+      <c r="AD12" s="1" t="n">
+        <v>36.098</v>
       </c>
     </row>
     <row r="13">
@@ -1683,10 +1722,13 @@
         <v>208.77</v>
       </c>
       <c r="AB13" s="1" t="n">
+        <v>206.94</v>
+      </c>
+      <c r="AC13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="AC13" s="1" t="n">
-        <v>208.77</v>
+      <c r="AD13" s="1" t="n">
+        <v>206.94</v>
       </c>
     </row>
     <row r="14">
@@ -1774,9 +1816,12 @@
         <v>0.0011406</v>
       </c>
       <c r="AB14" s="1" t="n">
+        <v>0.0011368</v>
+      </c>
+      <c r="AC14" s="1" t="n">
         <v>0.0011412</v>
       </c>
-      <c r="AC14" s="1" t="n">
+      <c r="AD14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1865,9 +1910,12 @@
         <v>0.32493</v>
       </c>
       <c r="AB15" s="1" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AC15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="AC15" s="1" t="n">
+      <c r="AD15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1956,9 +2004,12 @@
         <v>232.26</v>
       </c>
       <c r="AB16" s="1" t="n">
+        <v>230.49</v>
+      </c>
+      <c r="AC16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="AC16" s="1" t="n">
+      <c r="AD16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -2047,10 +2098,13 @@
         <v>0.9921</v>
       </c>
       <c r="AB17" s="1" t="n">
+        <v>0.9883</v>
+      </c>
+      <c r="AC17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="AC17" s="1" t="n">
-        <v>0.9921</v>
+      <c r="AD17" s="1" t="n">
+        <v>0.9883</v>
       </c>
     </row>
     <row r="18">
@@ -2138,10 +2192,13 @@
         <v>0.2654</v>
       </c>
       <c r="AB18" s="1" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="AC18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="AC18" s="1" t="n">
-        <v>0.2654</v>
+      <c r="AD18" s="1" t="n">
+        <v>0.2641</v>
       </c>
     </row>
     <row r="19">
@@ -2229,10 +2286,13 @@
         <v>9.721</v>
       </c>
       <c r="AB19" s="1" t="n">
+        <v>9.683999999999999</v>
+      </c>
+      <c r="AC19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="AC19" s="1" t="n">
-        <v>9.721</v>
+      <c r="AD19" s="1" t="n">
+        <v>9.683999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2320,9 +2380,12 @@
         <v>5021.57</v>
       </c>
       <c r="AB20" s="1" t="n">
+        <v>5022.64</v>
+      </c>
+      <c r="AC20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="AC20" s="1" t="n">
+      <c r="AD20" s="1" t="n">
         <v>5012.13</v>
       </c>
     </row>
@@ -2411,10 +2474,13 @@
         <v>461.09</v>
       </c>
       <c r="AB21" s="1" t="n">
+        <v>460.07</v>
+      </c>
+      <c r="AC21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="AC21" s="1" t="n">
-        <v>461.09</v>
+      <c r="AD21" s="1" t="n">
+        <v>460.07</v>
       </c>
     </row>
     <row r="22">
@@ -2502,9 +2568,12 @@
         <v>1.3889</v>
       </c>
       <c r="AB22" s="1" t="n">
+        <v>1.3864</v>
+      </c>
+      <c r="AC22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="AC22" s="1" t="n">
+      <c r="AD22" s="1" t="n">
         <v>1.3686</v>
       </c>
     </row>
@@ -2593,9 +2662,12 @@
         <v>1.046</v>
       </c>
       <c r="AB23" s="1" t="n">
+        <v>1.0386</v>
+      </c>
+      <c r="AC23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="AC23" s="1" t="n">
+      <c r="AD23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2684,10 +2756,13 @@
         <v>1.335</v>
       </c>
       <c r="AB24" s="1" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AC24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="AC24" s="1" t="n">
-        <v>1.335</v>
+      <c r="AD24" s="1" t="n">
+        <v>1.328</v>
       </c>
     </row>
     <row r="25">
@@ -2775,10 +2850,13 @@
         <v>9.086</v>
       </c>
       <c r="AB25" s="1" t="n">
+        <v>9.044</v>
+      </c>
+      <c r="AC25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="AC25" s="1" t="n">
-        <v>9.086</v>
+      <c r="AD25" s="1" t="n">
+        <v>9.044</v>
       </c>
     </row>
     <row r="26">
@@ -2866,9 +2944,12 @@
         <v>0.358</v>
       </c>
       <c r="AB26" s="1" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AC26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="AC26" s="1" t="n">
+      <c r="AD26" s="1" t="n">
         <v>0.3578</v>
       </c>
     </row>
@@ -2957,10 +3038,13 @@
         <v>0.865</v>
       </c>
       <c r="AB27" s="1" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AC27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="AC27" s="1" t="n">
-        <v>0.865</v>
+      <c r="AD27" s="1" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="28">
@@ -3048,10 +3132,13 @@
         <v>1.797</v>
       </c>
       <c r="AB28" s="1" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="AC28" s="1" t="n">
         <v>1.863</v>
       </c>
-      <c r="AC28" s="1" t="n">
-        <v>1.787</v>
+      <c r="AD28" s="1" t="n">
+        <v>1.784</v>
       </c>
     </row>
     <row r="29">
@@ -3139,10 +3226,13 @@
         <v>0.1086</v>
       </c>
       <c r="AB29" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="AC29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="AC29" s="1" t="n">
-        <v>0.1086</v>
+      <c r="AD29" s="1" t="n">
+        <v>0.1078</v>
       </c>
     </row>
     <row r="30">
@@ -3230,10 +3320,13 @@
         <v>0.002</v>
       </c>
       <c r="AB30" s="1" t="n">
+        <v>0.001984</v>
+      </c>
+      <c r="AC30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="AC30" s="1" t="n">
-        <v>0.002</v>
+      <c r="AD30" s="1" t="n">
+        <v>0.001984</v>
       </c>
     </row>
     <row r="31">
@@ -3321,10 +3414,13 @@
         <v>1.453</v>
       </c>
       <c r="AB31" s="1" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="AC31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="AC31" s="1" t="n">
-        <v>1.453</v>
+      <c r="AD31" s="1" t="n">
+        <v>1.449</v>
       </c>
     </row>
     <row r="32">
@@ -3412,9 +3508,12 @@
         <v>0.1763</v>
       </c>
       <c r="AB32" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AC32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="AC32" s="1" t="n">
+      <c r="AD32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -3503,9 +3602,12 @@
         <v>0.1039</v>
       </c>
       <c r="AB33" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="AC33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="AC33" s="1" t="n">
+      <c r="AD33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -3594,10 +3696,13 @@
         <v>112.25</v>
       </c>
       <c r="AB34" s="1" t="n">
+        <v>111.56</v>
+      </c>
+      <c r="AC34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="AC34" s="1" t="n">
-        <v>112.25</v>
+      <c r="AD34" s="1" t="n">
+        <v>111.56</v>
       </c>
     </row>
     <row r="35">
@@ -3685,10 +3790,13 @@
         <v>6.614</v>
       </c>
       <c r="AB35" s="1" t="n">
+        <v>6.424</v>
+      </c>
+      <c r="AC35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="AC35" s="1" t="n">
-        <v>6.587</v>
+      <c r="AD35" s="1" t="n">
+        <v>6.424</v>
       </c>
     </row>
     <row r="36">
@@ -3776,9 +3884,12 @@
         <v>0.018579</v>
       </c>
       <c r="AB36" s="1" t="n">
+        <v>0.018764</v>
+      </c>
+      <c r="AC36" s="1" t="n">
         <v>0.018773</v>
       </c>
-      <c r="AC36" s="1" t="n">
+      <c r="AD36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -3867,10 +3978,13 @@
         <v>0.3573</v>
       </c>
       <c r="AB37" s="1" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AC37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="AC37" s="1" t="n">
-        <v>0.3573</v>
+      <c r="AD37" s="1" t="n">
+        <v>0.3551</v>
       </c>
     </row>
     <row r="38">
@@ -3958,10 +4072,13 @@
         <v>55.43</v>
       </c>
       <c r="AB38" s="1" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="AC38" s="1" t="n">
         <v>55.92</v>
       </c>
-      <c r="AC38" s="1" t="n">
-        <v>55.3</v>
+      <c r="AD38" s="1" t="n">
+        <v>55.17</v>
       </c>
     </row>
     <row r="39">
@@ -4049,9 +4166,12 @@
         <v>0.60905</v>
       </c>
       <c r="AB39" s="1" t="n">
+        <v>0.59502</v>
+      </c>
+      <c r="AC39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="AC39" s="1" t="n">
+      <c r="AD39" s="1" t="n">
         <v>0.5717</v>
       </c>
     </row>
@@ -4140,10 +4260,13 @@
         <v>4.006</v>
       </c>
       <c r="AB40" s="1" t="n">
+        <v>3.986</v>
+      </c>
+      <c r="AC40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="AC40" s="1" t="n">
-        <v>4.006</v>
+      <c r="AD40" s="1" t="n">
+        <v>3.986</v>
       </c>
     </row>
     <row r="41">
@@ -4231,10 +4354,13 @@
         <v>0.04741</v>
       </c>
       <c r="AB41" s="1" t="n">
+        <v>0.04676</v>
+      </c>
+      <c r="AC41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="AC41" s="1" t="n">
-        <v>0.04741</v>
+      <c r="AD41" s="1" t="n">
+        <v>0.04676</v>
       </c>
     </row>
     <row r="42">
@@ -4322,10 +4448,13 @@
         <v>0.6948</v>
       </c>
       <c r="AB42" s="1" t="n">
+        <v>0.6936</v>
+      </c>
+      <c r="AC42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="AC42" s="1" t="n">
-        <v>0.6948</v>
+      <c r="AD42" s="1" t="n">
+        <v>0.6936</v>
       </c>
     </row>
     <row r="43">
@@ -4413,10 +4542,13 @@
         <v>0.22679</v>
       </c>
       <c r="AB43" s="1" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="AC43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="AC43" s="1" t="n">
-        <v>0.22604</v>
+      <c r="AD43" s="1" t="n">
+        <v>0.22597</v>
       </c>
     </row>
     <row r="44">
@@ -4504,9 +4636,12 @@
         <v>0.36065</v>
       </c>
       <c r="AB44" s="1" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AC44" s="1" t="n">
         <v>0.36291</v>
       </c>
-      <c r="AC44" s="1" t="n">
+      <c r="AD44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -4595,10 +4730,13 @@
         <v>0.1673</v>
       </c>
       <c r="AB45" s="1" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="AC45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="AC45" s="1" t="n">
-        <v>0.1673</v>
+      <c r="AD45" s="1" t="n">
+        <v>0.1657</v>
       </c>
     </row>
     <row r="46">
@@ -4686,10 +4824,13 @@
         <v>0.0257</v>
       </c>
       <c r="AB46" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AC46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="AC46" s="1" t="n">
-        <v>0.0257</v>
+      <c r="AD46" s="1" t="n">
+        <v>0.0255</v>
       </c>
     </row>
     <row r="47">
@@ -4777,10 +4918,13 @@
         <v>0.005926</v>
       </c>
       <c r="AB47" s="1" t="n">
+        <v>0.005897</v>
+      </c>
+      <c r="AC47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="AC47" s="1" t="n">
-        <v>0.005926</v>
+      <c r="AD47" s="1" t="n">
+        <v>0.005897</v>
       </c>
     </row>
     <row r="48">
@@ -4868,10 +5012,13 @@
         <v>0.007288</v>
       </c>
       <c r="AB48" s="1" t="n">
+        <v>0.007228</v>
+      </c>
+      <c r="AC48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="AC48" s="1" t="n">
-        <v>0.007288</v>
+      <c r="AD48" s="1" t="n">
+        <v>0.007228</v>
       </c>
     </row>
     <row r="49">
@@ -4959,9 +5106,12 @@
         <v>0.1086</v>
       </c>
       <c r="AB49" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="AC49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="AC49" s="1" t="n">
+      <c r="AD49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -5050,9 +5200,12 @@
         <v>0.04073</v>
       </c>
       <c r="AB50" s="1" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="AC50" s="1" t="n">
         <v>0.04222</v>
       </c>
-      <c r="AC50" s="1" t="n">
+      <c r="AD50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -5141,10 +5294,13 @@
         <v>0.1593</v>
       </c>
       <c r="AB51" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="AC51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="AC51" s="1" t="n">
-        <v>0.1593</v>
+      <c r="AD51" s="1" t="n">
+        <v>0.1583</v>
       </c>
     </row>
     <row r="52">
@@ -5232,10 +5388,13 @@
         <v>0.00353</v>
       </c>
       <c r="AB52" s="1" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="AC52" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="AC52" s="1" t="n">
-        <v>0.0035</v>
+      <c r="AD52" s="1" t="n">
+        <v>0.00349</v>
       </c>
     </row>
     <row r="53">
@@ -5323,10 +5482,13 @@
         <v>2.606</v>
       </c>
       <c r="AB53" s="1" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="AC53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="AC53" s="1" t="n">
-        <v>2.606</v>
+      <c r="AD53" s="1" t="n">
+        <v>2.602</v>
       </c>
     </row>
     <row r="54">
@@ -5414,10 +5576,13 @@
         <v>0.006149</v>
       </c>
       <c r="AB54" s="1" t="n">
+        <v>0.006086</v>
+      </c>
+      <c r="AC54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="AC54" s="1" t="n">
-        <v>0.006149</v>
+      <c r="AD54" s="1" t="n">
+        <v>0.006086</v>
       </c>
     </row>
     <row r="55">
@@ -5505,9 +5670,12 @@
         <v>0.02805</v>
       </c>
       <c r="AB55" s="1" t="n">
+        <v>0.02764</v>
+      </c>
+      <c r="AC55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="AC55" s="1" t="n">
+      <c r="AD55" s="1" t="n">
         <v>0.02738</v>
       </c>
     </row>
@@ -5596,10 +5764,13 @@
         <v>0.7226</v>
       </c>
       <c r="AB56" s="1" t="n">
+        <v>0.7159</v>
+      </c>
+      <c r="AC56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="AC56" s="1" t="n">
-        <v>0.7226</v>
+      <c r="AD56" s="1" t="n">
+        <v>0.7159</v>
       </c>
     </row>
     <row r="57">
@@ -5687,10 +5858,13 @@
         <v>0.1025</v>
       </c>
       <c r="AB57" s="1" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="AC57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="AC57" s="1" t="n">
-        <v>0.1025</v>
+      <c r="AD57" s="1" t="n">
+        <v>0.1018</v>
       </c>
     </row>
     <row r="58">
@@ -5778,10 +5952,13 @@
         <v>0.9294</v>
       </c>
       <c r="AB58" s="1" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="AC58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="AC58" s="1" t="n">
-        <v>0.9294</v>
+      <c r="AD58" s="1" t="n">
+        <v>0.9211</v>
       </c>
     </row>
     <row r="59">
@@ -5869,9 +6046,12 @@
         <v>0.08356</v>
       </c>
       <c r="AB59" s="1" t="n">
+        <v>0.08397</v>
+      </c>
+      <c r="AC59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="AC59" s="1" t="n">
+      <c r="AD59" s="1" t="n">
         <v>0.08294</v>
       </c>
     </row>
@@ -5960,9 +6140,12 @@
         <v>0.07337</v>
       </c>
       <c r="AB60" s="1" t="n">
+        <v>0.07053</v>
+      </c>
+      <c r="AC60" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="AC60" s="1" t="n">
+      <c r="AD60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -6051,10 +6234,13 @@
         <v>0.05452</v>
       </c>
       <c r="AB61" s="1" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="AC61" s="1" t="n">
         <v>0.05539</v>
       </c>
-      <c r="AC61" s="1" t="n">
-        <v>0.05439</v>
+      <c r="AD61" s="1" t="n">
+        <v>0.05349</v>
       </c>
     </row>
     <row r="62">
@@ -6142,9 +6328,12 @@
         <v>0.01067</v>
       </c>
       <c r="AB62" s="1" t="n">
+        <v>0.01063</v>
+      </c>
+      <c r="AC62" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="AC62" s="1" t="n">
+      <c r="AD62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -6233,9 +6422,12 @@
         <v>0.29275</v>
       </c>
       <c r="AB63" s="1" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="AC63" s="1" t="n">
         <v>0.29275</v>
       </c>
-      <c r="AC63" s="1" t="n">
+      <c r="AD63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -6324,10 +6516,13 @@
         <v>0.06832000000000001</v>
       </c>
       <c r="AB64" s="1" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="AC64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="AC64" s="1" t="n">
-        <v>0.06756</v>
+      <c r="AD64" s="1" t="n">
+        <v>0.06677</v>
       </c>
     </row>
     <row r="65">
@@ -6415,10 +6610,13 @@
         <v>0.3062</v>
       </c>
       <c r="AB65" s="1" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AC65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="AC65" s="1" t="n">
-        <v>0.3062</v>
+      <c r="AD65" s="1" t="n">
+        <v>0.3022</v>
       </c>
     </row>
     <row r="66">
@@ -6506,9 +6704,12 @@
         <v>0.16554</v>
       </c>
       <c r="AB66" s="1" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AC66" s="1" t="n">
         <v>0.16587</v>
       </c>
-      <c r="AC66" s="1" t="n">
+      <c r="AD66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -6597,9 +6798,12 @@
         <v>0.12018</v>
       </c>
       <c r="AB67" s="1" t="n">
+        <v>0.12027</v>
+      </c>
+      <c r="AC67" s="1" t="n">
         <v>0.12035</v>
       </c>
-      <c r="AC67" s="1" t="n">
+      <c r="AD67" s="1" t="n">
         <v>0.1191</v>
       </c>
     </row>
@@ -6688,10 +6892,13 @@
         <v>0.09497</v>
       </c>
       <c r="AB68" s="1" t="n">
+        <v>0.09465</v>
+      </c>
+      <c r="AC68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="AC68" s="1" t="n">
-        <v>0.09474</v>
+      <c r="AD68" s="1" t="n">
+        <v>0.09465</v>
       </c>
     </row>
     <row r="69">
@@ -6779,10 +6986,13 @@
         <v>0.1231</v>
       </c>
       <c r="AB69" s="1" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="AC69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="AC69" s="1" t="n">
-        <v>0.1231</v>
+      <c r="AD69" s="1" t="n">
+        <v>0.1223</v>
       </c>
     </row>
     <row r="70">
@@ -6870,10 +7080,13 @@
         <v>8.478</v>
       </c>
       <c r="AB70" s="1" t="n">
+        <v>8.433</v>
+      </c>
+      <c r="AC70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="AC70" s="1" t="n">
-        <v>8.478</v>
+      <c r="AD70" s="1" t="n">
+        <v>8.433</v>
       </c>
     </row>
     <row r="71">
@@ -6961,10 +7174,13 @@
         <v>0.236</v>
       </c>
       <c r="AB71" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AC71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="AC71" s="1" t="n">
-        <v>0.236</v>
+      <c r="AD71" s="1" t="n">
+        <v>0.234</v>
       </c>
     </row>
     <row r="72">
@@ -7052,10 +7268,13 @@
         <v>0.04927</v>
       </c>
       <c r="AB72" s="1" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="AC72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="AC72" s="1" t="n">
-        <v>0.04927</v>
+      <c r="AD72" s="1" t="n">
+        <v>0.04904</v>
       </c>
     </row>
     <row r="73">
@@ -7143,9 +7362,12 @@
         <v>0.05016</v>
       </c>
       <c r="AB73" s="1" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="AC73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="AC73" s="1" t="n">
+      <c r="AD73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -7234,10 +7456,13 @@
         <v>0.1222</v>
       </c>
       <c r="AB74" s="1" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="AC74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="AC74" s="1" t="n">
-        <v>0.1221</v>
+      <c r="AD74" s="1" t="n">
+        <v>0.1212</v>
       </c>
     </row>
     <row r="75">
@@ -7325,9 +7550,12 @@
         <v>0.04675</v>
       </c>
       <c r="AB75" s="1" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AC75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="AC75" s="1" t="n">
+      <c r="AD75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -7416,10 +7644,13 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="AB76" s="1" t="n">
+        <v>0.06578000000000001</v>
+      </c>
+      <c r="AC76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="AC76" s="1" t="n">
-        <v>0.06610000000000001</v>
+      <c r="AD76" s="1" t="n">
+        <v>0.06578000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7507,9 +7738,12 @@
         <v>0.12851</v>
       </c>
       <c r="AB77" s="1" t="n">
+        <v>0.12686</v>
+      </c>
+      <c r="AC77" s="1" t="n">
         <v>0.13727</v>
       </c>
-      <c r="AC77" s="1" t="n">
+      <c r="AD77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -7598,9 +7832,12 @@
         <v>0.1585</v>
       </c>
       <c r="AB78" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="AC78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="AC78" s="1" t="n">
+      <c r="AD78" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -7689,10 +7926,13 @@
         <v>0.02691</v>
       </c>
       <c r="AB79" s="1" t="n">
+        <v>0.02678</v>
+      </c>
+      <c r="AC79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="AC79" s="1" t="n">
-        <v>0.02691</v>
+      <c r="AD79" s="1" t="n">
+        <v>0.02678</v>
       </c>
     </row>
     <row r="80">
@@ -7780,9 +8020,12 @@
         <v>356.05</v>
       </c>
       <c r="AB80" s="1" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="AC80" s="1" t="n">
         <v>362.68</v>
       </c>
-      <c r="AC80" s="1" t="n">
+      <c r="AD80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -7871,10 +8114,13 @@
         <v>6.984e-05</v>
       </c>
       <c r="AB81" s="1" t="n">
+        <v>6.949e-05</v>
+      </c>
+      <c r="AC81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="AC81" s="1" t="n">
-        <v>6.984e-05</v>
+      <c r="AD81" s="1" t="n">
+        <v>6.949e-05</v>
       </c>
     </row>
     <row r="82">
@@ -7962,10 +8208,13 @@
         <v>0.2629</v>
       </c>
       <c r="AB82" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="AC82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="AC82" s="1" t="n">
-        <v>0.2629</v>
+      <c r="AD82" s="1" t="n">
+        <v>0.2614</v>
       </c>
     </row>
     <row r="83">
@@ -8053,9 +8302,12 @@
         <v>1.1078</v>
       </c>
       <c r="AB83" s="1" t="n">
+        <v>1.1058</v>
+      </c>
+      <c r="AC83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="AC83" s="1" t="n">
+      <c r="AD83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -8144,10 +8396,13 @@
         <v>0.3468</v>
       </c>
       <c r="AB84" s="1" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AC84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="AC84" s="1" t="n">
-        <v>0.3468</v>
+      <c r="AD84" s="1" t="n">
+        <v>0.3449</v>
       </c>
     </row>
     <row r="85">
@@ -8235,10 +8490,13 @@
         <v>1.9329</v>
       </c>
       <c r="AB85" s="1" t="n">
+        <v>1.9239</v>
+      </c>
+      <c r="AC85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="AC85" s="1" t="n">
-        <v>1.9329</v>
+      <c r="AD85" s="1" t="n">
+        <v>1.9239</v>
       </c>
     </row>
     <row r="86">
@@ -8326,10 +8584,13 @@
         <v>1.3126</v>
       </c>
       <c r="AB86" s="1" t="n">
+        <v>1.3065</v>
+      </c>
+      <c r="AC86" s="1" t="n">
         <v>1.3218</v>
       </c>
-      <c r="AC86" s="1" t="n">
-        <v>1.3103</v>
+      <c r="AD86" s="1" t="n">
+        <v>1.3065</v>
       </c>
     </row>
     <row r="87">
@@ -8417,10 +8678,13 @@
         <v>32.32</v>
       </c>
       <c r="AB87" s="1" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="AC87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="AC87" s="1" t="n">
-        <v>32.32</v>
+      <c r="AD87" s="1" t="n">
+        <v>32.14</v>
       </c>
     </row>
     <row r="88">
@@ -8508,9 +8772,12 @@
         <v>0.00944</v>
       </c>
       <c r="AB88" s="1" t="n">
+        <v>0.009429999999999999</v>
+      </c>
+      <c r="AC88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="AC88" s="1" t="n">
+      <c r="AD88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -8599,10 +8866,13 @@
         <v>0.01755</v>
       </c>
       <c r="AB89" s="1" t="n">
+        <v>0.01748</v>
+      </c>
+      <c r="AC89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="AC89" s="1" t="n">
-        <v>0.01755</v>
+      <c r="AD89" s="1" t="n">
+        <v>0.01748</v>
       </c>
     </row>
     <row r="90">
@@ -8690,10 +8960,13 @@
         <v>0.03388</v>
       </c>
       <c r="AB90" s="1" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="AC90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="AC90" s="1" t="n">
-        <v>0.03388</v>
+      <c r="AD90" s="1" t="n">
+        <v>0.0333</v>
       </c>
     </row>
     <row r="91">
@@ -8781,10 +9054,13 @@
         <v>0.01154</v>
       </c>
       <c r="AB91" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="AC91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AC91" s="1" t="n">
-        <v>0.01154</v>
+      <c r="AD91" s="1" t="n">
+        <v>0.01144</v>
       </c>
     </row>
     <row r="92">
@@ -8872,10 +9148,13 @@
         <v>3.085</v>
       </c>
       <c r="AB92" s="1" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="AC92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="AC92" s="1" t="n">
-        <v>3.085</v>
+      <c r="AD92" s="1" t="n">
+        <v>3.069</v>
       </c>
     </row>
     <row r="93">
@@ -8963,10 +9242,13 @@
         <v>0.005566</v>
       </c>
       <c r="AB93" s="1" t="n">
+        <v>0.005523</v>
+      </c>
+      <c r="AC93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="AC93" s="1" t="n">
-        <v>0.005559</v>
+      <c r="AD93" s="1" t="n">
+        <v>0.005523</v>
       </c>
     </row>
     <row r="94">
@@ -9054,9 +9336,12 @@
         <v>0.09379999999999999</v>
       </c>
       <c r="AB94" s="1" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="AC94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="AC94" s="1" t="n">
+      <c r="AD94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -9145,9 +9430,12 @@
         <v>0.6475</v>
       </c>
       <c r="AB95" s="1" t="n">
-        <v>0.6475</v>
+        <v>0.6528</v>
       </c>
       <c r="AC95" s="1" t="n">
+        <v>0.6528</v>
+      </c>
+      <c r="AD95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -9236,10 +9524,13 @@
         <v>1.27e-05</v>
       </c>
       <c r="AB96" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="AC96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="AC96" s="1" t="n">
-        <v>1.27e-05</v>
+      <c r="AD96" s="1" t="n">
+        <v>1.22e-05</v>
       </c>
     </row>
     <row r="97">
@@ -9327,10 +9618,13 @@
         <v>1.102</v>
       </c>
       <c r="AB97" s="1" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="AC97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="AC97" s="1" t="n">
-        <v>1.1</v>
+      <c r="AD97" s="1" t="n">
+        <v>1.097</v>
       </c>
     </row>
     <row r="98">
@@ -9418,10 +9712,13 @@
         <v>0.2466</v>
       </c>
       <c r="AB98" s="1" t="n">
+        <v>0.24367</v>
+      </c>
+      <c r="AC98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="AC98" s="1" t="n">
-        <v>0.2466</v>
+      <c r="AD98" s="1" t="n">
+        <v>0.24367</v>
       </c>
     </row>
     <row r="99">
@@ -9509,9 +9806,12 @@
         <v>1.147</v>
       </c>
       <c r="AB99" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="AC99" s="1" t="n">
         <v>1.157</v>
       </c>
-      <c r="AC99" s="1" t="n">
+      <c r="AD99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -9600,10 +9900,13 @@
         <v>1.852</v>
       </c>
       <c r="AB100" s="1" t="n">
+        <v>1.843</v>
+      </c>
+      <c r="AC100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="AC100" s="1" t="n">
-        <v>1.852</v>
+      <c r="AD100" s="1" t="n">
+        <v>1.843</v>
       </c>
     </row>
     <row r="101">
@@ -9691,10 +9994,13 @@
         <v>0.01557</v>
       </c>
       <c r="AB101" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="AC101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="AC101" s="1" t="n">
-        <v>0.01557</v>
+      <c r="AD101" s="1" t="n">
+        <v>0.01551</v>
       </c>
     </row>
     <row r="102">
@@ -9782,9 +10088,12 @@
         <v>0.10142</v>
       </c>
       <c r="AB102" s="1" t="n">
+        <v>0.10088</v>
+      </c>
+      <c r="AC102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="AC102" s="1" t="n">
+      <c r="AD102" s="1" t="n">
         <v>0.10062</v>
       </c>
     </row>
@@ -9873,10 +10182,13 @@
         <v>0.0005925</v>
       </c>
       <c r="AB103" s="1" t="n">
+        <v>0.0005886</v>
+      </c>
+      <c r="AC103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="AC103" s="1" t="n">
-        <v>0.0005925</v>
+      <c r="AD103" s="1" t="n">
+        <v>0.0005886</v>
       </c>
     </row>
     <row r="104">
@@ -9964,9 +10276,12 @@
         <v>0.0005710999999999999</v>
       </c>
       <c r="AB104" s="1" t="n">
+        <v>0.0005729</v>
+      </c>
+      <c r="AC104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="AC104" s="1" t="n">
+      <c r="AD104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -10055,10 +10370,13 @@
         <v>0.003191</v>
       </c>
       <c r="AB105" s="1" t="n">
+        <v>0.003178</v>
+      </c>
+      <c r="AC105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="AC105" s="1" t="n">
-        <v>0.003191</v>
+      <c r="AD105" s="1" t="n">
+        <v>0.003178</v>
       </c>
     </row>
     <row r="106">
@@ -10146,10 +10464,13 @@
         <v>2.523</v>
       </c>
       <c r="AB106" s="1" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="AC106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="AC106" s="1" t="n">
-        <v>2.523</v>
+      <c r="AD106" s="1" t="n">
+        <v>2.509</v>
       </c>
     </row>
     <row r="107">
@@ -10237,10 +10558,13 @@
         <v>0.1652</v>
       </c>
       <c r="AB107" s="1" t="n">
+        <v>0.1643</v>
+      </c>
+      <c r="AC107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="AC107" s="1" t="n">
-        <v>0.165</v>
+      <c r="AD107" s="1" t="n">
+        <v>0.1643</v>
       </c>
     </row>
     <row r="108">
@@ -10328,10 +10652,13 @@
         <v>0.09544999999999999</v>
       </c>
       <c r="AB108" s="1" t="n">
+        <v>0.09492</v>
+      </c>
+      <c r="AC108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="AC108" s="1" t="n">
-        <v>0.09544999999999999</v>
+      <c r="AD108" s="1" t="n">
+        <v>0.09492</v>
       </c>
     </row>
     <row r="109">
@@ -10419,9 +10746,12 @@
         <v>0.02212</v>
       </c>
       <c r="AB109" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="AC109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="AC109" s="1" t="n">
+      <c r="AD109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -10510,10 +10840,13 @@
         <v>0.2851</v>
       </c>
       <c r="AB110" s="1" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="AC110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="AC110" s="1" t="n">
-        <v>0.2851</v>
+      <c r="AD110" s="1" t="n">
+        <v>0.2838</v>
       </c>
     </row>
     <row r="111">
@@ -10601,10 +10934,13 @@
         <v>0.05664</v>
       </c>
       <c r="AB111" s="1" t="n">
+        <v>0.05629</v>
+      </c>
+      <c r="AC111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="AC111" s="1" t="n">
-        <v>0.05651</v>
+      <c r="AD111" s="1" t="n">
+        <v>0.05629</v>
       </c>
     </row>
     <row r="112">
@@ -10692,10 +11028,13 @@
         <v>0.2989</v>
       </c>
       <c r="AB112" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AC112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="AC112" s="1" t="n">
-        <v>0.2989</v>
+      <c r="AD112" s="1" t="n">
+        <v>0.2968</v>
       </c>
     </row>
     <row r="113">
@@ -10783,10 +11122,13 @@
         <v>18.52</v>
       </c>
       <c r="AB113" s="1" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AC113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="AC113" s="1" t="n">
-        <v>18.52</v>
+      <c r="AD113" s="1" t="n">
+        <v>18.43</v>
       </c>
     </row>
     <row r="114">
@@ -10874,9 +11216,12 @@
         <v>0.12767</v>
       </c>
       <c r="AB114" s="1" t="n">
+        <v>0.12683</v>
+      </c>
+      <c r="AC114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="AC114" s="1" t="n">
+      <c r="AD114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -10965,9 +11310,12 @@
         <v>0.01597</v>
       </c>
       <c r="AB115" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="AC115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="AC115" s="1" t="n">
+      <c r="AD115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -11056,10 +11404,13 @@
         <v>0.08411</v>
       </c>
       <c r="AB116" s="1" t="n">
+        <v>0.08352999999999999</v>
+      </c>
+      <c r="AC116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="AC116" s="1" t="n">
-        <v>0.08411</v>
+      <c r="AD116" s="1" t="n">
+        <v>0.08352999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -11147,9 +11498,12 @@
         <v>0.046473</v>
       </c>
       <c r="AB117" s="1" t="n">
+        <v>0.046527</v>
+      </c>
+      <c r="AC117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="AC117" s="1" t="n">
+      <c r="AD117" s="1" t="n">
         <v>0.046106</v>
       </c>
     </row>
@@ -11238,10 +11592,13 @@
         <v>0.04685</v>
       </c>
       <c r="AB118" s="1" t="n">
+        <v>0.04651</v>
+      </c>
+      <c r="AC118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="AC118" s="1" t="n">
-        <v>0.04685</v>
+      <c r="AD118" s="1" t="n">
+        <v>0.04651</v>
       </c>
     </row>
     <row r="119">
@@ -11329,9 +11686,12 @@
         <v>0.04013</v>
       </c>
       <c r="AB119" s="1" t="n">
+        <v>0.04003</v>
+      </c>
+      <c r="AC119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="AC119" s="1" t="n">
+      <c r="AD119" s="1" t="n">
         <v>0.03993</v>
       </c>
     </row>
@@ -11420,9 +11780,12 @@
         <v>0.14603</v>
       </c>
       <c r="AB120" s="1" t="n">
+        <v>0.14564</v>
+      </c>
+      <c r="AC120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="AC120" s="1" t="n">
+      <c r="AD120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -11511,10 +11874,13 @@
         <v>0.1239</v>
       </c>
       <c r="AB121" s="1" t="n">
+        <v>0.1234</v>
+      </c>
+      <c r="AC121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="AC121" s="1" t="n">
-        <v>0.1239</v>
+      <c r="AD121" s="1" t="n">
+        <v>0.1234</v>
       </c>
     </row>
     <row r="122">
@@ -11602,10 +11968,13 @@
         <v>1.819</v>
       </c>
       <c r="AB122" s="1" t="n">
+        <v>1.809</v>
+      </c>
+      <c r="AC122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="AC122" s="1" t="n">
-        <v>1.819</v>
+      <c r="AD122" s="1" t="n">
+        <v>1.809</v>
       </c>
     </row>
     <row r="123">
@@ -11693,10 +12062,13 @@
         <v>0.02985</v>
       </c>
       <c r="AB123" s="1" t="n">
+        <v>0.02973</v>
+      </c>
+      <c r="AC123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="AC123" s="1" t="n">
-        <v>0.02985</v>
+      <c r="AD123" s="1" t="n">
+        <v>0.02973</v>
       </c>
     </row>
     <row r="124">
@@ -11784,10 +12156,13 @@
         <v>0.13157</v>
       </c>
       <c r="AB124" s="1" t="n">
+        <v>0.13125</v>
+      </c>
+      <c r="AC124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="AC124" s="1" t="n">
-        <v>0.13138</v>
+      <c r="AD124" s="1" t="n">
+        <v>0.13125</v>
       </c>
     </row>
     <row r="125">
@@ -11875,10 +12250,13 @@
         <v>0.04068</v>
       </c>
       <c r="AB125" s="1" t="n">
+        <v>0.04036</v>
+      </c>
+      <c r="AC125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="AC125" s="1" t="n">
-        <v>0.04068</v>
+      <c r="AD125" s="1" t="n">
+        <v>0.04036</v>
       </c>
     </row>
     <row r="126">
@@ -11966,10 +12344,13 @@
         <v>0.1135</v>
       </c>
       <c r="AB126" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="AC126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="AC126" s="1" t="n">
-        <v>0.1135</v>
+      <c r="AD126" s="1" t="n">
+        <v>0.1133</v>
       </c>
     </row>
     <row r="127">
@@ -12057,9 +12438,12 @@
         <v>0.5441</v>
       </c>
       <c r="AB127" s="1" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AC127" s="1" t="n">
         <v>0.5446</v>
       </c>
-      <c r="AC127" s="1" t="n">
+      <c r="AD127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -12148,9 +12532,12 @@
         <v>0.03795</v>
       </c>
       <c r="AB128" s="1" t="n">
+        <v>0.03789</v>
+      </c>
+      <c r="AC128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="AC128" s="1" t="n">
+      <c r="AD128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -12239,10 +12626,13 @@
         <v>0.793</v>
       </c>
       <c r="AB129" s="1" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="AC129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="AC129" s="1" t="n">
-        <v>0.791</v>
+      <c r="AD129" s="1" t="n">
+        <v>0.789</v>
       </c>
     </row>
     <row r="130">
@@ -12330,10 +12720,13 @@
         <v>0.03431</v>
       </c>
       <c r="AB130" s="1" t="n">
+        <v>0.03421</v>
+      </c>
+      <c r="AC130" s="1" t="n">
         <v>0.03463</v>
       </c>
-      <c r="AC130" s="1" t="n">
-        <v>0.03422</v>
+      <c r="AD130" s="1" t="n">
+        <v>0.03421</v>
       </c>
     </row>
     <row r="131">
@@ -12421,9 +12814,12 @@
         <v>0.4227</v>
       </c>
       <c r="AB131" s="1" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AC131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="AC131" s="1" t="n">
+      <c r="AD131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -12512,9 +12908,12 @@
         <v>0.04301</v>
       </c>
       <c r="AB132" s="1" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="AC132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="AC132" s="1" t="n">
+      <c r="AD132" s="1" t="n">
         <v>0.04296</v>
       </c>
     </row>
@@ -12603,10 +13002,13 @@
         <v>1.2782</v>
       </c>
       <c r="AB133" s="1" t="n">
+        <v>1.2712</v>
+      </c>
+      <c r="AC133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="AC133" s="1" t="n">
-        <v>1.2782</v>
+      <c r="AD133" s="1" t="n">
+        <v>1.2712</v>
       </c>
     </row>
     <row r="134">
@@ -12694,10 +13096,13 @@
         <v>0.02181</v>
       </c>
       <c r="AB134" s="1" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="AC134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="AC134" s="1" t="n">
-        <v>0.02178</v>
+      <c r="AD134" s="1" t="n">
+        <v>0.02171</v>
       </c>
     </row>
     <row r="135">
@@ -12785,10 +13190,13 @@
         <v>0.0004514</v>
       </c>
       <c r="AB135" s="1" t="n">
+        <v>0.0004482</v>
+      </c>
+      <c r="AC135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="AC135" s="1" t="n">
-        <v>0.0004514</v>
+      <c r="AD135" s="1" t="n">
+        <v>0.0004482</v>
       </c>
     </row>
     <row r="136">
@@ -12876,9 +13284,12 @@
         <v>0.001886</v>
       </c>
       <c r="AB136" s="1" t="n">
+        <v>0.001892</v>
+      </c>
+      <c r="AC136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="AC136" s="1" t="n">
+      <c r="AD136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -12967,10 +13378,13 @@
         <v>0.3086</v>
       </c>
       <c r="AB137" s="1" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AC137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="AC137" s="1" t="n">
-        <v>0.3086</v>
+      <c r="AD137" s="1" t="n">
+        <v>0.3071</v>
       </c>
     </row>
     <row r="138">
@@ -13058,10 +13472,13 @@
         <v>0.5552</v>
       </c>
       <c r="AB138" s="1" t="n">
+        <v>0.5508</v>
+      </c>
+      <c r="AC138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="AC138" s="1" t="n">
-        <v>0.5552</v>
+      <c r="AD138" s="1" t="n">
+        <v>0.5508</v>
       </c>
     </row>
     <row r="139">
@@ -13149,9 +13566,12 @@
         <v>0.0212</v>
       </c>
       <c r="AB139" s="1" t="n">
+        <v>0.02118</v>
+      </c>
+      <c r="AC139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="AC139" s="1" t="n">
+      <c r="AD139" s="1" t="n">
         <v>0.02115</v>
       </c>
     </row>
@@ -13240,10 +13660,13 @@
         <v>0.07879</v>
       </c>
       <c r="AB140" s="1" t="n">
+        <v>0.07858</v>
+      </c>
+      <c r="AC140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="AC140" s="1" t="n">
-        <v>0.07879</v>
+      <c r="AD140" s="1" t="n">
+        <v>0.07858</v>
       </c>
     </row>
     <row r="141">
@@ -13331,9 +13754,12 @@
         <v>0.00153</v>
       </c>
       <c r="AB141" s="1" t="n">
+        <v>0.001525</v>
+      </c>
+      <c r="AC141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="AC141" s="1" t="n">
+      <c r="AD141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -13422,9 +13848,12 @@
         <v>0.4473</v>
       </c>
       <c r="AB142" s="1" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="AC142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="AC142" s="1" t="n">
+      <c r="AD142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -13513,10 +13942,13 @@
         <v>0.029809</v>
       </c>
       <c r="AB143" s="1" t="n">
+        <v>0.029604</v>
+      </c>
+      <c r="AC143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="AC143" s="1" t="n">
-        <v>0.029754</v>
+      <c r="AD143" s="1" t="n">
+        <v>0.029604</v>
       </c>
     </row>
     <row r="144">
@@ -13604,9 +14036,12 @@
         <v>0.000226</v>
       </c>
       <c r="AB144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="AC144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="AC144" s="1" t="n">
+      <c r="AD144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -13695,9 +14130,12 @@
         <v>0.03368</v>
       </c>
       <c r="AB145" s="1" t="n">
+        <v>0.03386</v>
+      </c>
+      <c r="AC145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="AC145" s="1" t="n">
+      <c r="AD145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -13786,9 +14224,12 @@
         <v>0.1178</v>
       </c>
       <c r="AB146" s="1" t="n">
-        <v>0.1178</v>
+        <v>0.11787</v>
       </c>
       <c r="AC146" s="1" t="n">
+        <v>0.11787</v>
+      </c>
+      <c r="AD146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -13877,9 +14318,12 @@
         <v>0.02196</v>
       </c>
       <c r="AB147" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="AC147" s="1" t="n">
         <v>0.02258</v>
       </c>
-      <c r="AC147" s="1" t="n">
+      <c r="AD147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -13968,10 +14412,13 @@
         <v>1.4084</v>
       </c>
       <c r="AB148" s="1" t="n">
+        <v>1.4029</v>
+      </c>
+      <c r="AC148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="AC148" s="1" t="n">
-        <v>1.4084</v>
+      <c r="AD148" s="1" t="n">
+        <v>1.4029</v>
       </c>
     </row>
     <row r="149">
@@ -14059,10 +14506,13 @@
         <v>1.8462</v>
       </c>
       <c r="AB149" s="1" t="n">
+        <v>1.8417</v>
+      </c>
+      <c r="AC149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="AC149" s="1" t="n">
-        <v>1.8462</v>
+      <c r="AD149" s="1" t="n">
+        <v>1.8417</v>
       </c>
     </row>
     <row r="150">
@@ -14150,9 +14600,12 @@
         <v>0.097</v>
       </c>
       <c r="AB150" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AC150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="AC150" s="1" t="n">
+      <c r="AD150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -14241,9 +14694,12 @@
         <v>4.639</v>
       </c>
       <c r="AB151" s="1" t="n">
+        <v>4.642</v>
+      </c>
+      <c r="AC151" s="1" t="n">
         <v>4.731</v>
       </c>
-      <c r="AC151" s="1" t="n">
+      <c r="AD151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -14332,9 +14788,12 @@
         <v>5.53</v>
       </c>
       <c r="AB152" s="1" t="n">
+        <v>5.519</v>
+      </c>
+      <c r="AC152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="AC152" s="1" t="n">
+      <c r="AD152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -14423,9 +14882,12 @@
         <v>0.3177</v>
       </c>
       <c r="AB153" s="1" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AC153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="AC153" s="1" t="n">
+      <c r="AD153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -14514,10 +14976,13 @@
         <v>0.5824</v>
       </c>
       <c r="AB154" s="1" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="AC154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="AC154" s="1" t="n">
-        <v>0.5824</v>
+      <c r="AD154" s="1" t="n">
+        <v>0.5807</v>
       </c>
     </row>
     <row r="155">
@@ -14605,10 +15070,13 @@
         <v>0.0126</v>
       </c>
       <c r="AB155" s="1" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AC155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="AC155" s="1" t="n">
-        <v>0.0126</v>
+      <c r="AD155" s="1" t="n">
+        <v>0.0125</v>
       </c>
     </row>
     <row r="156">
@@ -14696,10 +15164,13 @@
         <v>0.0963</v>
       </c>
       <c r="AB156" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AC156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="AC156" s="1" t="n">
-        <v>0.0963</v>
+      <c r="AD156" s="1" t="n">
+        <v>0.0956</v>
       </c>
     </row>
     <row r="157">
@@ -14787,10 +15258,13 @@
         <v>16.215</v>
       </c>
       <c r="AB157" s="1" t="n">
+        <v>16.107</v>
+      </c>
+      <c r="AC157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="AC157" s="1" t="n">
-        <v>16.215</v>
+      <c r="AD157" s="1" t="n">
+        <v>16.107</v>
       </c>
     </row>
     <row r="158">
@@ -14878,9 +15352,12 @@
         <v>0.05547</v>
       </c>
       <c r="AB158" s="1" t="n">
+        <v>0.05493</v>
+      </c>
+      <c r="AC158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="AC158" s="1" t="n">
+      <c r="AD158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -14969,10 +15446,13 @@
         <v>28.38</v>
       </c>
       <c r="AB159" s="1" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="AC159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="AC159" s="1" t="n">
-        <v>28.38</v>
+      <c r="AD159" s="1" t="n">
+        <v>28.17</v>
       </c>
     </row>
     <row r="160">
@@ -15060,9 +15540,12 @@
         <v>0.0214</v>
       </c>
       <c r="AB160" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AC160" s="1" t="n">
         <v>0.0218</v>
       </c>
-      <c r="AC160" s="1" t="n">
+      <c r="AD160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -15151,10 +15634,13 @@
         <v>0.0006465</v>
       </c>
       <c r="AB161" s="1" t="n">
+        <v>0.0006434</v>
+      </c>
+      <c r="AC161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="AC161" s="1" t="n">
-        <v>0.0006465</v>
+      <c r="AD161" s="1" t="n">
+        <v>0.0006434</v>
       </c>
     </row>
     <row r="162">
@@ -15242,9 +15728,12 @@
         <v>0.3889</v>
       </c>
       <c r="AB162" s="1" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="AC162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="AC162" s="1" t="n">
+      <c r="AD162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -15333,10 +15822,13 @@
         <v>0.1887</v>
       </c>
       <c r="AB163" s="1" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="AC163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="AC163" s="1" t="n">
-        <v>0.1887</v>
+      <c r="AD163" s="1" t="n">
+        <v>0.1879</v>
       </c>
     </row>
     <row r="164">
@@ -15424,10 +15916,13 @@
         <v>0.313</v>
       </c>
       <c r="AB164" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AC164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="AC164" s="1" t="n">
-        <v>0.313</v>
+      <c r="AD164" s="1" t="n">
+        <v>0.312</v>
       </c>
     </row>
     <row r="165">
@@ -15515,9 +16010,12 @@
         <v>0.375</v>
       </c>
       <c r="AB165" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AC165" s="1" t="n">
         <v>0.378</v>
       </c>
-      <c r="AC165" s="1" t="n">
+      <c r="AD165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -15606,10 +16104,13 @@
         <v>0.02234</v>
       </c>
       <c r="AB166" s="1" t="n">
+        <v>0.02223</v>
+      </c>
+      <c r="AC166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="AC166" s="1" t="n">
-        <v>0.02233</v>
+      <c r="AD166" s="1" t="n">
+        <v>0.02223</v>
       </c>
     </row>
     <row r="167">
@@ -15697,10 +16198,13 @@
         <v>0.007227</v>
       </c>
       <c r="AB167" s="1" t="n">
+        <v>0.007187</v>
+      </c>
+      <c r="AC167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="AC167" s="1" t="n">
-        <v>0.007227</v>
+      <c r="AD167" s="1" t="n">
+        <v>0.007187</v>
       </c>
     </row>
     <row r="168">
@@ -15788,10 +16292,13 @@
         <v>0.01313</v>
       </c>
       <c r="AB168" s="1" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="AC168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="AC168" s="1" t="n">
-        <v>0.01313</v>
+      <c r="AD168" s="1" t="n">
+        <v>0.01312</v>
       </c>
     </row>
     <row r="169">
@@ -15879,10 +16386,13 @@
         <v>0.25381</v>
       </c>
       <c r="AB169" s="1" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="AC169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="AC169" s="1" t="n">
-        <v>0.25151</v>
+      <c r="AD169" s="1" t="n">
+        <v>0.2509</v>
       </c>
     </row>
     <row r="170">
@@ -15970,9 +16480,12 @@
         <v>0.02218</v>
       </c>
       <c r="AB170" s="1" t="n">
-        <v>0.02218</v>
+        <v>0.02219</v>
       </c>
       <c r="AC170" s="1" t="n">
+        <v>0.02219</v>
+      </c>
+      <c r="AD170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -16061,9 +16574,12 @@
         <v>0.1718</v>
       </c>
       <c r="AB171" s="1" t="n">
+        <v>0.1708</v>
+      </c>
+      <c r="AC171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="AC171" s="1" t="n">
+      <c r="AD171" s="1" t="n">
         <v>0.1708</v>
       </c>
     </row>
@@ -16152,9 +16668,12 @@
         <v>0.089</v>
       </c>
       <c r="AB172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AC172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC172" s="1" t="n">
+      <c r="AD172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -16243,10 +16762,13 @@
         <v>0.004656</v>
       </c>
       <c r="AB173" s="1" t="n">
+        <v>0.004642</v>
+      </c>
+      <c r="AC173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="AC173" s="1" t="n">
-        <v>0.004656</v>
+      <c r="AD173" s="1" t="n">
+        <v>0.004642</v>
       </c>
     </row>
     <row r="174">
@@ -16334,9 +16856,12 @@
         <v>0.4411</v>
       </c>
       <c r="AB174" s="1" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="AC174" s="1" t="n">
         <v>0.4428</v>
       </c>
-      <c r="AC174" s="1" t="n">
+      <c r="AD174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -16425,9 +16950,12 @@
         <v>0.09229</v>
       </c>
       <c r="AB175" s="1" t="n">
+        <v>0.09166000000000001</v>
+      </c>
+      <c r="AC175" s="1" t="n">
         <v>0.09276</v>
       </c>
-      <c r="AC175" s="1" t="n">
+      <c r="AD175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -16516,10 +17044,13 @@
         <v>0.2417</v>
       </c>
       <c r="AB176" s="1" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="AC176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="AC176" s="1" t="n">
-        <v>0.2417</v>
+      <c r="AD176" s="1" t="n">
+        <v>0.2401</v>
       </c>
     </row>
     <row r="177">
@@ -16607,10 +17138,13 @@
         <v>0.01907</v>
       </c>
       <c r="AB177" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="AC177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="AC177" s="1" t="n">
-        <v>0.01907</v>
+      <c r="AD177" s="1" t="n">
+        <v>0.01904</v>
       </c>
     </row>
     <row r="178">
@@ -16698,10 +17232,13 @@
         <v>6.059</v>
       </c>
       <c r="AB178" s="1" t="n">
+        <v>6.021</v>
+      </c>
+      <c r="AC178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="AC178" s="1" t="n">
-        <v>6.059</v>
+      <c r="AD178" s="1" t="n">
+        <v>6.021</v>
       </c>
     </row>
     <row r="179">
@@ -16789,10 +17326,13 @@
         <v>0.1346</v>
       </c>
       <c r="AB179" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AC179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="AC179" s="1" t="n">
-        <v>0.1346</v>
+      <c r="AD179" s="1" t="n">
+        <v>0.134</v>
       </c>
     </row>
     <row r="180">
@@ -16880,9 +17420,12 @@
         <v>0.00493</v>
       </c>
       <c r="AB180" s="1" t="n">
+        <v>0.004941</v>
+      </c>
+      <c r="AC180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="AC180" s="1" t="n">
+      <c r="AD180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -16971,10 +17514,13 @@
         <v>0.01186</v>
       </c>
       <c r="AB181" s="1" t="n">
+        <v>0.01179</v>
+      </c>
+      <c r="AC181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AC181" s="1" t="n">
-        <v>0.01182</v>
+      <c r="AD181" s="1" t="n">
+        <v>0.01179</v>
       </c>
     </row>
     <row r="182">
@@ -17062,9 +17608,12 @@
         <v>0.007168</v>
       </c>
       <c r="AB182" s="1" t="n">
+        <v>0.007189</v>
+      </c>
+      <c r="AC182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="AC182" s="1" t="n">
+      <c r="AD182" s="1" t="n">
         <v>0.007168</v>
       </c>
     </row>
@@ -17153,9 +17702,12 @@
         <v>0.13233</v>
       </c>
       <c r="AB183" s="1" t="n">
+        <v>0.13202</v>
+      </c>
+      <c r="AC183" s="1" t="n">
         <v>0.13233</v>
       </c>
-      <c r="AC183" s="1" t="n">
+      <c r="AD183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -17244,9 +17796,12 @@
         <v>0.09562</v>
       </c>
       <c r="AB184" s="1" t="n">
+        <v>0.09608</v>
+      </c>
+      <c r="AC184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="AC184" s="1" t="n">
+      <c r="AD184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -17335,10 +17890,13 @@
         <v>0.00743</v>
       </c>
       <c r="AB185" s="1" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="AC185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="AC185" s="1" t="n">
-        <v>0.00743</v>
+      <c r="AD185" s="1" t="n">
+        <v>0.00736</v>
       </c>
     </row>
     <row r="186">
@@ -17426,10 +17984,13 @@
         <v>0.04828</v>
       </c>
       <c r="AB186" s="1" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="AC186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="AC186" s="1" t="n">
-        <v>0.04828</v>
+      <c r="AD186" s="1" t="n">
+        <v>0.04797</v>
       </c>
     </row>
     <row r="187">
@@ -17517,10 +18078,13 @@
         <v>0.02644</v>
       </c>
       <c r="AB187" s="1" t="n">
+        <v>0.02622</v>
+      </c>
+      <c r="AC187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="AC187" s="1" t="n">
-        <v>0.02644</v>
+      <c r="AD187" s="1" t="n">
+        <v>0.02622</v>
       </c>
     </row>
     <row r="188">
@@ -17608,10 +18172,13 @@
         <v>0.003239</v>
       </c>
       <c r="AB188" s="1" t="n">
+        <v>0.00322</v>
+      </c>
+      <c r="AC188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="AC188" s="1" t="n">
-        <v>0.003239</v>
+      <c r="AD188" s="1" t="n">
+        <v>0.00322</v>
       </c>
     </row>
     <row r="189">
@@ -17699,10 +18266,13 @@
         <v>0.2832</v>
       </c>
       <c r="AB189" s="1" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AC189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="AC189" s="1" t="n">
-        <v>0.2832</v>
+      <c r="AD189" s="1" t="n">
+        <v>0.2815</v>
       </c>
     </row>
     <row r="190">
@@ -17790,10 +18360,13 @@
         <v>0.01744</v>
       </c>
       <c r="AB190" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="AC190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AC190" s="1" t="n">
-        <v>0.01744</v>
+      <c r="AD190" s="1" t="n">
+        <v>0.01729</v>
       </c>
     </row>
     <row r="191">
@@ -17881,10 +18454,13 @@
         <v>0.2563</v>
       </c>
       <c r="AB191" s="1" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AC191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="AC191" s="1" t="n">
-        <v>0.2562</v>
+      <c r="AD191" s="1" t="n">
+        <v>0.254</v>
       </c>
     </row>
     <row r="192">
@@ -17972,10 +18548,13 @@
         <v>0.0371</v>
       </c>
       <c r="AB192" s="1" t="n">
+        <v>0.03695</v>
+      </c>
+      <c r="AC192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="AC192" s="1" t="n">
-        <v>0.037</v>
+      <c r="AD192" s="1" t="n">
+        <v>0.03695</v>
       </c>
     </row>
     <row r="193">
@@ -18063,10 +18642,13 @@
         <v>0.0002194</v>
       </c>
       <c r="AB193" s="1" t="n">
+        <v>0.0002179</v>
+      </c>
+      <c r="AC193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="AC193" s="1" t="n">
-        <v>0.0002194</v>
+      <c r="AD193" s="1" t="n">
+        <v>0.0002179</v>
       </c>
     </row>
     <row r="194">
@@ -18154,10 +18736,13 @@
         <v>4.033</v>
       </c>
       <c r="AB194" s="1" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AC194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="AC194" s="1" t="n">
-        <v>4.033</v>
+      <c r="AD194" s="1" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="195">
@@ -18248,6 +18833,9 @@
         <v>0.999401</v>
       </c>
       <c r="AC195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="AD195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -18336,9 +18924,12 @@
         <v>4.335</v>
       </c>
       <c r="AB196" s="1" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="AC196" s="1" t="n">
         <v>4.368</v>
       </c>
-      <c r="AC196" s="1" t="n">
+      <c r="AD196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -18427,9 +19018,12 @@
         <v>0.15185</v>
       </c>
       <c r="AB197" s="1" t="n">
+        <v>0.15196</v>
+      </c>
+      <c r="AC197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="AC197" s="1" t="n">
+      <c r="AD197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -18518,9 +19112,12 @@
         <v>0.007859</v>
       </c>
       <c r="AB198" s="1" t="n">
+        <v>0.007744</v>
+      </c>
+      <c r="AC198" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="AC198" s="1" t="n">
+      <c r="AD198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -18609,9 +19206,12 @@
         <v>0.4503</v>
       </c>
       <c r="AB199" s="1" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="AC199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="AC199" s="1" t="n">
+      <c r="AD199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -18700,10 +19300,13 @@
         <v>0.5787</v>
       </c>
       <c r="AB200" s="1" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="AC200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="AC200" s="1" t="n">
-        <v>0.5715</v>
+      <c r="AD200" s="1" t="n">
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -18791,10 +19394,13 @@
         <v>0.0921</v>
       </c>
       <c r="AB201" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="AC201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="AC201" s="1" t="n">
-        <v>0.0921</v>
+      <c r="AD201" s="1" t="n">
+        <v>0.0915</v>
       </c>
     </row>
     <row r="202">
@@ -18882,10 +19488,13 @@
         <v>0.06006</v>
       </c>
       <c r="AB202" s="1" t="n">
+        <v>0.05966</v>
+      </c>
+      <c r="AC202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="AC202" s="1" t="n">
-        <v>0.05994</v>
+      <c r="AD202" s="1" t="n">
+        <v>0.05966</v>
       </c>
     </row>
     <row r="203">
@@ -18973,9 +19582,12 @@
         <v>0.00835</v>
       </c>
       <c r="AB203" s="1" t="n">
+        <v>0.008229999999999999</v>
+      </c>
+      <c r="AC203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="AC203" s="1" t="n">
+      <c r="AD203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -19064,10 +19676,13 @@
         <v>0.00412</v>
       </c>
       <c r="AB204" s="1" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="AC204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="AC204" s="1" t="n">
-        <v>0.00411</v>
+      <c r="AD204" s="1" t="n">
+        <v>0.00409</v>
       </c>
     </row>
     <row r="205">
@@ -19155,10 +19770,13 @@
         <v>0.009008</v>
       </c>
       <c r="AB205" s="1" t="n">
+        <v>0.008928</v>
+      </c>
+      <c r="AC205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="AC205" s="1" t="n">
-        <v>0.009008</v>
+      <c r="AD205" s="1" t="n">
+        <v>0.008928</v>
       </c>
     </row>
     <row r="206">
@@ -19249,6 +19867,9 @@
         <v>0.2418</v>
       </c>
       <c r="AC206" s="1" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="AD206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -19337,9 +19958,12 @@
         <v>0.0215</v>
       </c>
       <c r="AB207" s="1" t="n">
-        <v>0.02163</v>
+        <v>0.02169</v>
       </c>
       <c r="AC207" s="1" t="n">
+        <v>0.02169</v>
+      </c>
+      <c r="AD207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -19428,10 +20052,13 @@
         <v>0.236</v>
       </c>
       <c r="AB208" s="1" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="AC208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="AC208" s="1" t="n">
-        <v>0.2357</v>
+      <c r="AD208" s="1" t="n">
+        <v>0.2335</v>
       </c>
     </row>
     <row r="209">
@@ -19519,10 +20146,13 @@
         <v>0.3547</v>
       </c>
       <c r="AB209" s="1" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AC209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="AC209" s="1" t="n">
-        <v>0.3547</v>
+      <c r="AD209" s="1" t="n">
+        <v>0.3524</v>
       </c>
     </row>
     <row r="210">
@@ -19610,10 +20240,13 @@
         <v>0.0425</v>
       </c>
       <c r="AB210" s="1" t="n">
+        <v>0.04229</v>
+      </c>
+      <c r="AC210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="AC210" s="1" t="n">
-        <v>0.04232</v>
+      <c r="AD210" s="1" t="n">
+        <v>0.04229</v>
       </c>
     </row>
     <row r="211">
@@ -19701,10 +20334,13 @@
         <v>0.0004179</v>
       </c>
       <c r="AB211" s="1" t="n">
+        <v>0.0004153</v>
+      </c>
+      <c r="AC211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="AC211" s="1" t="n">
-        <v>0.0004179</v>
+      <c r="AD211" s="1" t="n">
+        <v>0.0004153</v>
       </c>
     </row>
     <row r="212">
@@ -19792,10 +20428,13 @@
         <v>0.02117</v>
       </c>
       <c r="AB212" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="AC212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="AC212" s="1" t="n">
-        <v>0.02117</v>
+      <c r="AD212" s="1" t="n">
+        <v>0.02103</v>
       </c>
     </row>
     <row r="213">
@@ -19883,9 +20522,12 @@
         <v>0.1146</v>
       </c>
       <c r="AB213" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="AC213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="AC213" s="1" t="n">
+      <c r="AD213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -19974,9 +20616,12 @@
         <v>0.04231</v>
       </c>
       <c r="AB214" s="1" t="n">
+        <v>0.04203</v>
+      </c>
+      <c r="AC214" s="1" t="n">
         <v>0.04242</v>
       </c>
-      <c r="AC214" s="1" t="n">
+      <c r="AD214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -20065,10 +20710,13 @@
         <v>0.009684999999999999</v>
       </c>
       <c r="AB215" s="1" t="n">
+        <v>0.009624000000000001</v>
+      </c>
+      <c r="AC215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="AC215" s="1" t="n">
-        <v>0.009677</v>
+      <c r="AD215" s="1" t="n">
+        <v>0.009624000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -20156,10 +20804,13 @@
         <v>0.0638</v>
       </c>
       <c r="AB216" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="AC216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="AC216" s="1" t="n">
-        <v>0.0634</v>
+      <c r="AD216" s="1" t="n">
+        <v>0.0633</v>
       </c>
     </row>
     <row r="217">
@@ -20247,10 +20898,13 @@
         <v>0.004107</v>
       </c>
       <c r="AB217" s="1" t="n">
+        <v>0.004092</v>
+      </c>
+      <c r="AC217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="AC217" s="1" t="n">
-        <v>0.004107</v>
+      <c r="AD217" s="1" t="n">
+        <v>0.004092</v>
       </c>
     </row>
     <row r="218">
@@ -20338,9 +20992,12 @@
         <v>0.009719999999999999</v>
       </c>
       <c r="AB218" s="1" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="AC218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="AC218" s="1" t="n">
+      <c r="AD218" s="1" t="n">
         <v>0.009719999999999999</v>
       </c>
     </row>
@@ -20429,10 +21086,13 @@
         <v>0.02871</v>
       </c>
       <c r="AB219" s="1" t="n">
+        <v>0.02853</v>
+      </c>
+      <c r="AC219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="AC219" s="1" t="n">
-        <v>0.02871</v>
+      <c r="AD219" s="1" t="n">
+        <v>0.02853</v>
       </c>
     </row>
     <row r="220">
@@ -20520,10 +21180,13 @@
         <v>2.274</v>
       </c>
       <c r="AB220" s="1" t="n">
+        <v>2.262</v>
+      </c>
+      <c r="AC220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="AC220" s="1" t="n">
-        <v>2.274</v>
+      <c r="AD220" s="1" t="n">
+        <v>2.262</v>
       </c>
     </row>
     <row r="221">
@@ -20611,10 +21274,13 @@
         <v>0.022357</v>
       </c>
       <c r="AB221" s="1" t="n">
+        <v>0.022168</v>
+      </c>
+      <c r="AC221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="AC221" s="1" t="n">
-        <v>0.022357</v>
+      <c r="AD221" s="1" t="n">
+        <v>0.022168</v>
       </c>
     </row>
     <row r="222">
@@ -20702,9 +21368,12 @@
         <v>0.0369</v>
       </c>
       <c r="AB222" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="AC222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="AC222" s="1" t="n">
+      <c r="AD222" s="1" t="n">
         <v>0.0367</v>
       </c>
     </row>
@@ -20793,10 +21462,13 @@
         <v>0.2903</v>
       </c>
       <c r="AB223" s="1" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="AC223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="AC223" s="1" t="n">
-        <v>0.2903</v>
+      <c r="AD223" s="1" t="n">
+        <v>0.2898</v>
       </c>
     </row>
     <row r="224">
@@ -20884,9 +21556,12 @@
         <v>0.01573</v>
       </c>
       <c r="AB224" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="AC224" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="AC224" s="1" t="n">
+      <c r="AD224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -20975,10 +21650,13 @@
         <v>0.0003989</v>
       </c>
       <c r="AB225" s="1" t="n">
+        <v>0.0003956</v>
+      </c>
+      <c r="AC225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="AC225" s="1" t="n">
-        <v>0.0003989</v>
+      <c r="AD225" s="1" t="n">
+        <v>0.0003956</v>
       </c>
     </row>
     <row r="226">
@@ -21066,10 +21744,13 @@
         <v>0.08416</v>
       </c>
       <c r="AB226" s="1" t="n">
+        <v>0.08369</v>
+      </c>
+      <c r="AC226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="AC226" s="1" t="n">
-        <v>0.08416</v>
+      <c r="AD226" s="1" t="n">
+        <v>0.08369</v>
       </c>
     </row>
     <row r="227">
@@ -21157,10 +21838,13 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="AB227" s="1" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="AC227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="AC227" s="1" t="n">
-        <v>0.9409999999999999</v>
+      <c r="AD227" s="1" t="n">
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="228">
@@ -21248,9 +21932,12 @@
         <v>0.05523</v>
       </c>
       <c r="AB228" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="AC228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="AC228" s="1" t="n">
+      <c r="AD228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -21339,10 +22026,13 @@
         <v>0.001986</v>
       </c>
       <c r="AB229" s="1" t="n">
+        <v>0.001977</v>
+      </c>
+      <c r="AC229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="AC229" s="1" t="n">
-        <v>0.001986</v>
+      <c r="AD229" s="1" t="n">
+        <v>0.001977</v>
       </c>
     </row>
     <row r="230">
@@ -21430,10 +22120,13 @@
         <v>0.022561</v>
       </c>
       <c r="AB230" s="1" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="AC230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="AC230" s="1" t="n">
-        <v>0.022561</v>
+      <c r="AD230" s="1" t="n">
+        <v>0.0225</v>
       </c>
     </row>
     <row r="231">
@@ -21521,10 +22214,13 @@
         <v>0.05279</v>
       </c>
       <c r="AB231" s="1" t="n">
+        <v>0.05237</v>
+      </c>
+      <c r="AC231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="AC231" s="1" t="n">
-        <v>0.05279</v>
+      <c r="AD231" s="1" t="n">
+        <v>0.05237</v>
       </c>
     </row>
     <row r="232">
@@ -21612,10 +22308,13 @@
         <v>0.0582</v>
       </c>
       <c r="AB232" s="1" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="AC232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="AC232" s="1" t="n">
-        <v>0.0582</v>
+      <c r="AD232" s="1" t="n">
+        <v>0.0581</v>
       </c>
     </row>
     <row r="233">
@@ -21703,9 +22402,12 @@
         <v>0.001717</v>
       </c>
       <c r="AB233" s="1" t="n">
+        <v>0.001707</v>
+      </c>
+      <c r="AC233" s="1" t="n">
         <v>0.001728</v>
       </c>
-      <c r="AC233" s="1" t="n">
+      <c r="AD233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -21794,10 +22496,13 @@
         <v>0.005733</v>
       </c>
       <c r="AB234" s="1" t="n">
+        <v>0.005701</v>
+      </c>
+      <c r="AC234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="AC234" s="1" t="n">
-        <v>0.005718</v>
+      <c r="AD234" s="1" t="n">
+        <v>0.005701</v>
       </c>
     </row>
     <row r="235">
@@ -21885,10 +22590,13 @@
         <v>0.12126</v>
       </c>
       <c r="AB235" s="1" t="n">
+        <v>0.12035</v>
+      </c>
+      <c r="AC235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="AC235" s="1" t="n">
-        <v>0.12126</v>
+      <c r="AD235" s="1" t="n">
+        <v>0.12035</v>
       </c>
     </row>
     <row r="236">
@@ -21976,10 +22684,13 @@
         <v>64.45</v>
       </c>
       <c r="AB236" s="1" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="AC236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="AC236" s="1" t="n">
-        <v>64.25</v>
+      <c r="AD236" s="1" t="n">
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -22067,10 +22778,13 @@
         <v>0.09950000000000001</v>
       </c>
       <c r="AB237" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="AC237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="AC237" s="1" t="n">
-        <v>0.09950000000000001</v>
+      <c r="AD237" s="1" t="n">
+        <v>0.0988</v>
       </c>
     </row>
     <row r="238">
@@ -22158,10 +22872,13 @@
         <v>0.003915</v>
       </c>
       <c r="AB238" s="1" t="n">
+        <v>0.003831</v>
+      </c>
+      <c r="AC238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="AC238" s="1" t="n">
-        <v>0.003915</v>
+      <c r="AD238" s="1" t="n">
+        <v>0.003831</v>
       </c>
     </row>
     <row r="239">
@@ -22249,9 +22966,12 @@
         <v>0.01508</v>
       </c>
       <c r="AB239" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AC239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="AC239" s="1" t="n">
+      <c r="AD239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -22340,10 +23060,13 @@
         <v>0.05562</v>
       </c>
       <c r="AB240" s="1" t="n">
+        <v>0.05532</v>
+      </c>
+      <c r="AC240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="AC240" s="1" t="n">
-        <v>0.05562</v>
+      <c r="AD240" s="1" t="n">
+        <v>0.05532</v>
       </c>
     </row>
     <row r="241">
@@ -22431,9 +23154,12 @@
         <v>0.0115</v>
       </c>
       <c r="AB241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AC241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="AC241" s="1" t="n">
+      <c r="AD241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -22522,10 +23248,13 @@
         <v>0.3315</v>
       </c>
       <c r="AB242" s="1" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AC242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="AC242" s="1" t="n">
-        <v>0.3315</v>
+      <c r="AD242" s="1" t="n">
+        <v>0.3283</v>
       </c>
     </row>
     <row r="243">
@@ -22613,10 +23342,13 @@
         <v>0.01222</v>
       </c>
       <c r="AB243" s="1" t="n">
+        <v>0.01208</v>
+      </c>
+      <c r="AC243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="AC243" s="1" t="n">
-        <v>0.01222</v>
+      <c r="AD243" s="1" t="n">
+        <v>0.01208</v>
       </c>
     </row>
     <row r="244">
@@ -22704,9 +23436,12 @@
         <v>0.08116</v>
       </c>
       <c r="AB244" s="1" t="n">
+        <v>0.08114</v>
+      </c>
+      <c r="AC244" s="1" t="n">
         <v>0.08162999999999999</v>
       </c>
-      <c r="AC244" s="1" t="n">
+      <c r="AD244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -22795,9 +23530,12 @@
         <v>0.007953999999999999</v>
       </c>
       <c r="AB245" s="1" t="n">
+        <v>0.007858</v>
+      </c>
+      <c r="AC245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="AC245" s="1" t="n">
+      <c r="AD245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -22886,9 +23624,12 @@
         <v>0.03022</v>
       </c>
       <c r="AB246" s="1" t="n">
+        <v>0.03022</v>
+      </c>
+      <c r="AC246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="AC246" s="1" t="n">
+      <c r="AD246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -22977,10 +23718,13 @@
         <v>0.1792</v>
       </c>
       <c r="AB247" s="1" t="n">
+        <v>0.1781</v>
+      </c>
+      <c r="AC247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="AC247" s="1" t="n">
-        <v>0.1792</v>
+      <c r="AD247" s="1" t="n">
+        <v>0.1781</v>
       </c>
     </row>
     <row r="248">
@@ -23068,9 +23812,12 @@
         <v>0.05873</v>
       </c>
       <c r="AB248" s="1" t="n">
+        <v>0.05863</v>
+      </c>
+      <c r="AC248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="AC248" s="1" t="n">
+      <c r="AD248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -23159,10 +23906,13 @@
         <v>0.1637</v>
       </c>
       <c r="AB249" s="1" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="AC249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="AC249" s="1" t="n">
-        <v>0.1637</v>
+      <c r="AD249" s="1" t="n">
+        <v>0.1629</v>
       </c>
     </row>
     <row r="250">
@@ -23250,10 +24000,13 @@
         <v>0.01878</v>
       </c>
       <c r="AB250" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="AC250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="AC250" s="1" t="n">
-        <v>0.01878</v>
+      <c r="AD250" s="1" t="n">
+        <v>0.01859</v>
       </c>
     </row>
     <row r="251">
@@ -23341,9 +24094,12 @@
         <v>0.02311</v>
       </c>
       <c r="AB251" s="1" t="n">
+        <v>0.02306</v>
+      </c>
+      <c r="AC251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="AC251" s="1" t="n">
+      <c r="AD251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -23432,9 +24188,12 @@
         <v>0.30767</v>
       </c>
       <c r="AB252" s="1" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AC252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="AC252" s="1" t="n">
+      <c r="AD252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -23523,10 +24282,13 @@
         <v>0.005924</v>
       </c>
       <c r="AB253" s="1" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AC253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="AC253" s="1" t="n">
-        <v>0.005924</v>
+      <c r="AD253" s="1" t="n">
+        <v>0.0059</v>
       </c>
     </row>
     <row r="254">
@@ -23614,10 +24376,13 @@
         <v>0.6092</v>
       </c>
       <c r="AB254" s="1" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="AC254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="AC254" s="1" t="n">
-        <v>0.6092</v>
+      <c r="AD254" s="1" t="n">
+        <v>0.6066</v>
       </c>
     </row>
     <row r="255">
@@ -23705,10 +24470,13 @@
         <v>0.10575</v>
       </c>
       <c r="AB255" s="1" t="n">
+        <v>0.10505</v>
+      </c>
+      <c r="AC255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="AC255" s="1" t="n">
-        <v>0.10545</v>
+      <c r="AD255" s="1" t="n">
+        <v>0.10505</v>
       </c>
     </row>
     <row r="256">
@@ -23796,10 +24564,13 @@
         <v>0.0891</v>
       </c>
       <c r="AB256" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AC256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="AC256" s="1" t="n">
-        <v>0.0891</v>
+      <c r="AD256" s="1" t="n">
+        <v>0.089</v>
       </c>
     </row>
     <row r="257">
@@ -23887,9 +24658,12 @@
         <v>0.01491</v>
       </c>
       <c r="AB257" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="AC257" s="1" t="n">
         <v>0.01518</v>
       </c>
-      <c r="AC257" s="1" t="n">
+      <c r="AD257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -23978,10 +24752,13 @@
         <v>0.04941</v>
       </c>
       <c r="AB258" s="1" t="n">
+        <v>0.04882</v>
+      </c>
+      <c r="AC258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="AC258" s="1" t="n">
-        <v>0.04938</v>
+      <c r="AD258" s="1" t="n">
+        <v>0.04882</v>
       </c>
     </row>
     <row r="259">
@@ -24069,10 +24846,13 @@
         <v>0.00779</v>
       </c>
       <c r="AB259" s="1" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="AC259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="AC259" s="1" t="n">
-        <v>0.00779</v>
+      <c r="AD259" s="1" t="n">
+        <v>0.00776</v>
       </c>
     </row>
     <row r="260">
@@ -24160,10 +24940,13 @@
         <v>0.1883</v>
       </c>
       <c r="AB260" s="1" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="AC260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="AC260" s="1" t="n">
-        <v>0.1883</v>
+      <c r="AD260" s="1" t="n">
+        <v>0.1873</v>
       </c>
     </row>
     <row r="261">
@@ -24251,10 +25034,13 @@
         <v>0.0975</v>
       </c>
       <c r="AB261" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="AC261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="AC261" s="1" t="n">
-        <v>0.0975</v>
+      <c r="AD261" s="1" t="n">
+        <v>0.0968</v>
       </c>
     </row>
     <row r="262">
@@ -24342,10 +25128,13 @@
         <v>0.2094</v>
       </c>
       <c r="AB262" s="1" t="n">
+        <v>0.2084</v>
+      </c>
+      <c r="AC262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="AC262" s="1" t="n">
-        <v>0.2094</v>
+      <c r="AD262" s="1" t="n">
+        <v>0.2084</v>
       </c>
     </row>
     <row r="263">
@@ -24433,9 +25222,12 @@
         <v>0.008546</v>
       </c>
       <c r="AB263" s="1" t="n">
+        <v>0.008486</v>
+      </c>
+      <c r="AC263" s="1" t="n">
         <v>0.008616</v>
       </c>
-      <c r="AC263" s="1" t="n">
+      <c r="AD263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -24524,10 +25316,13 @@
         <v>2.609</v>
       </c>
       <c r="AB264" s="1" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="AC264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="AC264" s="1" t="n">
-        <v>2.609</v>
+      <c r="AD264" s="1" t="n">
+        <v>2.599</v>
       </c>
     </row>
     <row r="265">
@@ -24615,10 +25410,13 @@
         <v>0.01839</v>
       </c>
       <c r="AB265" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="AC265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="AC265" s="1" t="n">
-        <v>0.01839</v>
+      <c r="AD265" s="1" t="n">
+        <v>0.01828</v>
       </c>
     </row>
     <row r="266">
@@ -24706,9 +25504,12 @@
         <v>0.3648</v>
       </c>
       <c r="AB266" s="1" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AC266" s="1" t="n">
         <v>0.3648</v>
       </c>
-      <c r="AC266" s="1" t="n">
+      <c r="AD266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -24797,10 +25598,13 @@
         <v>0.0342</v>
       </c>
       <c r="AB267" s="1" t="n">
+        <v>0.03387</v>
+      </c>
+      <c r="AC267" s="1" t="n">
         <v>0.03471</v>
       </c>
-      <c r="AC267" s="1" t="n">
-        <v>0.034</v>
+      <c r="AD267" s="1" t="n">
+        <v>0.03387</v>
       </c>
     </row>
     <row r="268">
@@ -24888,9 +25692,12 @@
         <v>0.127</v>
       </c>
       <c r="AB268" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AC268" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="AC268" s="1" t="n">
+      <c r="AD268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -24979,10 +25786,13 @@
         <v>0.07862</v>
       </c>
       <c r="AB269" s="1" t="n">
+        <v>0.07847999999999999</v>
+      </c>
+      <c r="AC269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="AC269" s="1" t="n">
-        <v>0.07862</v>
+      <c r="AD269" s="1" t="n">
+        <v>0.07847999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -25070,10 +25880,13 @@
         <v>0.01373</v>
       </c>
       <c r="AB270" s="1" t="n">
+        <v>0.01364</v>
+      </c>
+      <c r="AC270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="AC270" s="1" t="n">
-        <v>0.01373</v>
+      <c r="AD270" s="1" t="n">
+        <v>0.01364</v>
       </c>
     </row>
     <row r="271">
@@ -25161,10 +25974,13 @@
         <v>0.00745</v>
       </c>
       <c r="AB271" s="1" t="n">
+        <v>0.007375</v>
+      </c>
+      <c r="AC271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="AC271" s="1" t="n">
-        <v>0.00745</v>
+      <c r="AD271" s="1" t="n">
+        <v>0.007375</v>
       </c>
     </row>
     <row r="272">
@@ -25252,10 +26068,13 @@
         <v>0.07403999999999999</v>
       </c>
       <c r="AB272" s="1" t="n">
+        <v>0.07392</v>
+      </c>
+      <c r="AC272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="AC272" s="1" t="n">
-        <v>0.07396</v>
+      <c r="AD272" s="1" t="n">
+        <v>0.07392</v>
       </c>
     </row>
     <row r="273">
@@ -25343,10 +26162,13 @@
         <v>3.09e-05</v>
       </c>
       <c r="AB273" s="1" t="n">
+        <v>3.06e-05</v>
+      </c>
+      <c r="AC273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="AC273" s="1" t="n">
-        <v>3.09e-05</v>
+      <c r="AD273" s="1" t="n">
+        <v>3.06e-05</v>
       </c>
     </row>
     <row r="274">
@@ -25434,10 +26256,13 @@
         <v>0.005382</v>
       </c>
       <c r="AB274" s="1" t="n">
+        <v>0.005357</v>
+      </c>
+      <c r="AC274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="AC274" s="1" t="n">
-        <v>0.005382</v>
+      <c r="AD274" s="1" t="n">
+        <v>0.005357</v>
       </c>
     </row>
     <row r="275">
@@ -25525,10 +26350,13 @@
         <v>0.1747</v>
       </c>
       <c r="AB275" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="AC275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="AC275" s="1" t="n">
-        <v>0.1744</v>
+      <c r="AD275" s="1" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="276">
@@ -25616,10 +26444,13 @@
         <v>0.00682</v>
       </c>
       <c r="AB276" s="1" t="n">
+        <v>0.006801</v>
+      </c>
+      <c r="AC276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="AC276" s="1" t="n">
-        <v>0.006809</v>
+      <c r="AD276" s="1" t="n">
+        <v>0.006801</v>
       </c>
     </row>
     <row r="277">
@@ -25707,9 +26538,12 @@
         <v>0.1323</v>
       </c>
       <c r="AB277" s="1" t="n">
+        <v>0.1322</v>
+      </c>
+      <c r="AC277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="AC277" s="1" t="n">
+      <c r="AD277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -25798,10 +26632,13 @@
         <v>0.02291</v>
       </c>
       <c r="AB278" s="1" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="AC278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="AC278" s="1" t="n">
-        <v>0.02291</v>
+      <c r="AD278" s="1" t="n">
+        <v>0.0227</v>
       </c>
     </row>
     <row r="279">
@@ -25889,10 +26726,13 @@
         <v>0.01796</v>
       </c>
       <c r="AB279" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="AC279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AC279" s="1" t="n">
-        <v>0.01796</v>
+      <c r="AD279" s="1" t="n">
+        <v>0.01779</v>
       </c>
     </row>
     <row r="280">
@@ -25980,10 +26820,13 @@
         <v>0.0363</v>
       </c>
       <c r="AB280" s="1" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="AC280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="AC280" s="1" t="n">
-        <v>0.0363</v>
+      <c r="AD280" s="1" t="n">
+        <v>0.03628</v>
       </c>
     </row>
     <row r="281">
@@ -26071,10 +26914,13 @@
         <v>0.0396</v>
       </c>
       <c r="AB281" s="1" t="n">
+        <v>0.03933</v>
+      </c>
+      <c r="AC281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="AC281" s="1" t="n">
-        <v>0.03953</v>
+      <c r="AD281" s="1" t="n">
+        <v>0.03933</v>
       </c>
     </row>
     <row r="282">
@@ -26162,10 +27008,13 @@
         <v>0.3022</v>
       </c>
       <c r="AB282" s="1" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AC282" s="1" t="n">
         <v>0.3079</v>
       </c>
-      <c r="AC282" s="1" t="n">
-        <v>0.3001</v>
+      <c r="AD282" s="1" t="n">
+        <v>0.2995</v>
       </c>
     </row>
     <row r="283">
@@ -26253,10 +27102,13 @@
         <v>0.01114</v>
       </c>
       <c r="AB283" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="AC283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="AC283" s="1" t="n">
-        <v>0.01114</v>
+      <c r="AD283" s="1" t="n">
+        <v>0.01108</v>
       </c>
     </row>
     <row r="284">
@@ -26344,9 +27196,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="AB284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="AC284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="AC284" s="1" t="n">
+      <c r="AD284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -26435,10 +27290,13 @@
         <v>0.1137</v>
       </c>
       <c r="AB285" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="AC285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="AC285" s="1" t="n">
-        <v>0.1137</v>
+      <c r="AD285" s="1" t="n">
+        <v>0.1133</v>
       </c>
     </row>
     <row r="286">
@@ -26526,10 +27384,13 @@
         <v>0.003426</v>
       </c>
       <c r="AB286" s="1" t="n">
+        <v>0.003414</v>
+      </c>
+      <c r="AC286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="AC286" s="1" t="n">
-        <v>0.003422</v>
+      <c r="AD286" s="1" t="n">
+        <v>0.003414</v>
       </c>
     </row>
     <row r="287">
@@ -26617,10 +27478,13 @@
         <v>0.08451</v>
       </c>
       <c r="AB287" s="1" t="n">
+        <v>0.08409</v>
+      </c>
+      <c r="AC287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="AC287" s="1" t="n">
-        <v>0.08451</v>
+      <c r="AD287" s="1" t="n">
+        <v>0.08409</v>
       </c>
     </row>
     <row r="288">
@@ -26708,9 +27572,12 @@
         <v>0.10125</v>
       </c>
       <c r="AB288" s="1" t="n">
+        <v>0.10016</v>
+      </c>
+      <c r="AC288" s="1" t="n">
         <v>0.10125</v>
       </c>
-      <c r="AC288" s="1" t="n">
+      <c r="AD288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -26799,10 +27666,13 @@
         <v>0.428</v>
       </c>
       <c r="AB289" s="1" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="AC289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="AC289" s="1" t="n">
-        <v>0.428</v>
+      <c r="AD289" s="1" t="n">
+        <v>0.4258</v>
       </c>
     </row>
     <row r="290">
@@ -26890,9 +27760,12 @@
         <v>0.04027</v>
       </c>
       <c r="AB290" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="AC290" s="1" t="n">
         <v>0.04037</v>
       </c>
-      <c r="AC290" s="1" t="n">
+      <c r="AD290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -26981,10 +27854,13 @@
         <v>0.2327</v>
       </c>
       <c r="AB291" s="1" t="n">
+        <v>0.2316</v>
+      </c>
+      <c r="AC291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="AC291" s="1" t="n">
-        <v>0.2327</v>
+      <c r="AD291" s="1" t="n">
+        <v>0.2316</v>
       </c>
     </row>
     <row r="292">
@@ -27072,9 +27948,12 @@
         <v>0.28518</v>
       </c>
       <c r="AB292" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AC292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="AC292" s="1" t="n">
+      <c r="AD292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -27163,9 +28042,12 @@
         <v>0.1503</v>
       </c>
       <c r="AB293" s="1" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="AC293" s="1" t="n">
         <v>0.1539</v>
       </c>
-      <c r="AC293" s="1" t="n">
+      <c r="AD293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -27254,10 +28136,13 @@
         <v>4.151</v>
       </c>
       <c r="AB294" s="1" t="n">
+        <v>4.131</v>
+      </c>
+      <c r="AC294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="AC294" s="1" t="n">
-        <v>4.151</v>
+      <c r="AD294" s="1" t="n">
+        <v>4.131</v>
       </c>
     </row>
     <row r="295">
@@ -27345,9 +28230,12 @@
         <v>0.03318</v>
       </c>
       <c r="AB295" s="1" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="AC295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="AC295" s="1" t="n">
+      <c r="AD295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -27436,9 +28324,12 @@
         <v>0.000967</v>
       </c>
       <c r="AB296" s="1" t="n">
+        <v>0.000965</v>
+      </c>
+      <c r="AC296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="AC296" s="1" t="n">
+      <c r="AD296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -27527,10 +28418,13 @@
         <v>0.08101999999999999</v>
       </c>
       <c r="AB297" s="1" t="n">
+        <v>0.08037</v>
+      </c>
+      <c r="AC297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="AC297" s="1" t="n">
-        <v>0.08101999999999999</v>
+      <c r="AD297" s="1" t="n">
+        <v>0.08037</v>
       </c>
     </row>
     <row r="298">
@@ -27618,9 +28512,12 @@
         <v>0.05832</v>
       </c>
       <c r="AB298" s="1" t="n">
+        <v>0.05764</v>
+      </c>
+      <c r="AC298" s="1" t="n">
         <v>0.05876</v>
       </c>
-      <c r="AC298" s="1" t="n">
+      <c r="AD298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -27709,9 +28606,12 @@
         <v>0.09214</v>
       </c>
       <c r="AB299" s="1" t="n">
+        <v>0.09128</v>
+      </c>
+      <c r="AC299" s="1" t="n">
         <v>0.09214</v>
       </c>
-      <c r="AC299" s="1" t="n">
+      <c r="AD299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -27800,10 +28700,13 @@
         <v>0.02717</v>
       </c>
       <c r="AB300" s="1" t="n">
+        <v>0.0269</v>
+      </c>
+      <c r="AC300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="AC300" s="1" t="n">
-        <v>0.02717</v>
+      <c r="AD300" s="1" t="n">
+        <v>0.0269</v>
       </c>
     </row>
     <row r="301">
@@ -27891,10 +28794,13 @@
         <v>0.06475</v>
       </c>
       <c r="AB301" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="AC301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="AC301" s="1" t="n">
-        <v>0.06475</v>
+      <c r="AD301" s="1" t="n">
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -27982,9 +28888,12 @@
         <v>0.053484</v>
       </c>
       <c r="AB302" s="1" t="n">
+        <v>0.053511</v>
+      </c>
+      <c r="AC302" s="1" t="n">
         <v>0.053599</v>
       </c>
-      <c r="AC302" s="1" t="n">
+      <c r="AD302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -28073,9 +28982,12 @@
         <v>5169</v>
       </c>
       <c r="AB303" s="1" t="n">
+        <v>5172.7</v>
+      </c>
+      <c r="AC303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="AC303" s="1" t="n">
+      <c r="AD303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -28164,9 +29076,12 @@
         <v>14.87</v>
       </c>
       <c r="AB304" s="1" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AC304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="AC304" s="1" t="n">
+      <c r="AD304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -28255,9 +29170,12 @@
         <v>0.003785</v>
       </c>
       <c r="AB305" s="1" t="n">
+        <v>0.003775</v>
+      </c>
+      <c r="AC305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="AC305" s="1" t="n">
+      <c r="AD305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -28346,10 +29264,13 @@
         <v>0.4548</v>
       </c>
       <c r="AB306" s="1" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="AC306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="AC306" s="1" t="n">
-        <v>0.4531</v>
+      <c r="AD306" s="1" t="n">
+        <v>0.4523</v>
       </c>
     </row>
     <row r="307">
@@ -28437,10 +29358,13 @@
         <v>0.0463</v>
       </c>
       <c r="AB307" s="1" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="AC307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="AC307" s="1" t="n">
-        <v>0.0463</v>
+      <c r="AD307" s="1" t="n">
+        <v>0.04625</v>
       </c>
     </row>
     <row r="308">
@@ -28528,9 +29452,12 @@
         <v>1.5176</v>
       </c>
       <c r="AB308" s="1" t="n">
+        <v>1.5116</v>
+      </c>
+      <c r="AC308" s="1" t="n">
         <v>1.5176</v>
       </c>
-      <c r="AC308" s="1" t="n">
+      <c r="AD308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -28619,10 +29546,13 @@
         <v>0.0007850999999999999</v>
       </c>
       <c r="AB309" s="1" t="n">
+        <v>0.0007817</v>
+      </c>
+      <c r="AC309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="AC309" s="1" t="n">
-        <v>0.0007850999999999999</v>
+      <c r="AD309" s="1" t="n">
+        <v>0.0007817</v>
       </c>
     </row>
     <row r="310">
@@ -28710,10 +29640,13 @@
         <v>4.498</v>
       </c>
       <c r="AB310" s="1" t="n">
+        <v>4.476</v>
+      </c>
+      <c r="AC310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="AC310" s="1" t="n">
-        <v>4.498</v>
+      <c r="AD310" s="1" t="n">
+        <v>4.476</v>
       </c>
     </row>
     <row r="311">
@@ -28801,9 +29734,12 @@
         <v>4.762</v>
       </c>
       <c r="AB311" s="1" t="n">
+        <v>4.743</v>
+      </c>
+      <c r="AC311" s="1" t="n">
         <v>4.809</v>
       </c>
-      <c r="AC311" s="1" t="n">
+      <c r="AD311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -28892,10 +29828,13 @@
         <v>0.08029</v>
       </c>
       <c r="AB312" s="1" t="n">
+        <v>0.07983</v>
+      </c>
+      <c r="AC312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="AC312" s="1" t="n">
-        <v>0.08029</v>
+      <c r="AD312" s="1" t="n">
+        <v>0.07983</v>
       </c>
     </row>
     <row r="313">
@@ -28983,10 +29922,13 @@
         <v>2.018</v>
       </c>
       <c r="AB313" s="1" t="n">
+        <v>2.003</v>
+      </c>
+      <c r="AC313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC313" s="1" t="n">
-        <v>2.005</v>
+      <c r="AD313" s="1" t="n">
+        <v>2.003</v>
       </c>
     </row>
     <row r="314">
@@ -29074,9 +30016,12 @@
         <v>0.07106999999999999</v>
       </c>
       <c r="AB314" s="1" t="n">
+        <v>0.07095</v>
+      </c>
+      <c r="AC314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="AC314" s="1" t="n">
+      <c r="AD314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -29165,9 +30110,12 @@
         <v>0.948</v>
       </c>
       <c r="AB315" s="1" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AC315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="AC315" s="1" t="n">
+      <c r="AD315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -29256,10 +30204,13 @@
         <v>0.129</v>
       </c>
       <c r="AB316" s="1" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="AC316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="AC316" s="1" t="n">
-        <v>0.129</v>
+      <c r="AD316" s="1" t="n">
+        <v>0.1283</v>
       </c>
     </row>
     <row r="317">
@@ -29347,9 +30298,12 @@
         <v>0.1859</v>
       </c>
       <c r="AB317" s="1" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="AC317" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="AC317" s="1" t="n">
+      <c r="AD317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -29438,10 +30392,13 @@
         <v>0.01594</v>
       </c>
       <c r="AB318" s="1" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="AC318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="AC318" s="1" t="n">
-        <v>0.0159</v>
+      <c r="AD318" s="1" t="n">
+        <v>0.01585</v>
       </c>
     </row>
     <row r="319">
@@ -29529,10 +30486,13 @@
         <v>0.08298999999999999</v>
       </c>
       <c r="AB319" s="1" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="AC319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="AC319" s="1" t="n">
-        <v>0.08298999999999999</v>
+      <c r="AD319" s="1" t="n">
+        <v>0.08255</v>
       </c>
     </row>
     <row r="320">
@@ -29620,10 +30580,13 @@
         <v>0.007397</v>
       </c>
       <c r="AB320" s="1" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="AC320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="AC320" s="1" t="n">
-        <v>0.007397</v>
+      <c r="AD320" s="1" t="n">
+        <v>0.00736</v>
       </c>
     </row>
     <row r="321">
@@ -29711,10 +30674,13 @@
         <v>0.05382</v>
       </c>
       <c r="AB321" s="1" t="n">
+        <v>0.05371</v>
+      </c>
+      <c r="AC321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="AC321" s="1" t="n">
-        <v>0.05382</v>
+      <c r="AD321" s="1" t="n">
+        <v>0.05371</v>
       </c>
     </row>
     <row r="322">
@@ -29802,9 +30768,12 @@
         <v>0.5468</v>
       </c>
       <c r="AB322" s="1" t="n">
+        <v>0.5474</v>
+      </c>
+      <c r="AC322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="AC322" s="1" t="n">
+      <c r="AD322" s="1" t="n">
         <v>0.5468</v>
       </c>
     </row>
@@ -29893,10 +30862,13 @@
         <v>0.07285999999999999</v>
       </c>
       <c r="AB323" s="1" t="n">
+        <v>0.07242</v>
+      </c>
+      <c r="AC323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="AC323" s="1" t="n">
-        <v>0.07285999999999999</v>
+      <c r="AD323" s="1" t="n">
+        <v>0.07242</v>
       </c>
     </row>
     <row r="324">
@@ -29984,9 +30956,12 @@
         <v>0.012984</v>
       </c>
       <c r="AB324" s="1" t="n">
-        <v>0.013045</v>
+        <v>0.013071</v>
       </c>
       <c r="AC324" s="1" t="n">
+        <v>0.013071</v>
+      </c>
+      <c r="AD324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -30075,10 +31050,13 @@
         <v>0.0978</v>
       </c>
       <c r="AB325" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="AC325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="AC325" s="1" t="n">
-        <v>0.0978</v>
+      <c r="AD325" s="1" t="n">
+        <v>0.0974</v>
       </c>
     </row>
     <row r="326">
@@ -30166,10 +31144,13 @@
         <v>0.01732</v>
       </c>
       <c r="AB326" s="1" t="n">
+        <v>0.01722</v>
+      </c>
+      <c r="AC326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="AC326" s="1" t="n">
-        <v>0.01729</v>
+      <c r="AD326" s="1" t="n">
+        <v>0.01722</v>
       </c>
     </row>
     <row r="327">
@@ -30257,10 +31238,13 @@
         <v>0.06398</v>
       </c>
       <c r="AB327" s="1" t="n">
+        <v>0.06363000000000001</v>
+      </c>
+      <c r="AC327" s="1" t="n">
         <v>0.06455</v>
       </c>
-      <c r="AC327" s="1" t="n">
-        <v>0.06370000000000001</v>
+      <c r="AD327" s="1" t="n">
+        <v>0.06363000000000001</v>
       </c>
     </row>
     <row r="328">
@@ -30348,10 +31332,13 @@
         <v>0.2604</v>
       </c>
       <c r="AB328" s="1" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AC328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="AC328" s="1" t="n">
-        <v>0.2604</v>
+      <c r="AD328" s="1" t="n">
+        <v>0.259</v>
       </c>
     </row>
     <row r="329">
@@ -30439,9 +31426,12 @@
         <v>0.1748</v>
       </c>
       <c r="AB329" s="1" t="n">
+        <v>0.17216</v>
+      </c>
+      <c r="AC329" s="1" t="n">
         <v>0.17565</v>
       </c>
-      <c r="AC329" s="1" t="n">
+      <c r="AD329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -30530,10 +31520,13 @@
         <v>1.995</v>
       </c>
       <c r="AB330" s="1" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="AC330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="AC330" s="1" t="n">
-        <v>1.995</v>
+      <c r="AD330" s="1" t="n">
+        <v>1.977</v>
       </c>
     </row>
     <row r="331">
@@ -30621,9 +31614,12 @@
         <v>0.0287</v>
       </c>
       <c r="AB331" s="1" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="AC331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="AC331" s="1" t="n">
+      <c r="AD331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -30712,9 +31708,12 @@
         <v>0.006122</v>
       </c>
       <c r="AB332" s="1" t="n">
-        <v>0.006122</v>
+        <v>0.006198</v>
       </c>
       <c r="AC332" s="1" t="n">
+        <v>0.006198</v>
+      </c>
+      <c r="AD332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -30803,9 +31802,12 @@
         <v>0.00346</v>
       </c>
       <c r="AB333" s="1" t="n">
+        <v>0.003448</v>
+      </c>
+      <c r="AC333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="AC333" s="1" t="n">
+      <c r="AD333" s="1" t="n">
         <v>0.003441</v>
       </c>
     </row>
@@ -30894,10 +31896,13 @@
         <v>0.01384</v>
       </c>
       <c r="AB334" s="1" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="AC334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="AC334" s="1" t="n">
-        <v>0.01384</v>
+      <c r="AD334" s="1" t="n">
+        <v>0.01375</v>
       </c>
     </row>
     <row r="335">
@@ -30985,10 +31990,13 @@
         <v>1.126</v>
       </c>
       <c r="AB335" s="1" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="AC335" s="1" t="n">
         <v>1.158</v>
       </c>
-      <c r="AC335" s="1" t="n">
-        <v>1.12</v>
+      <c r="AD335" s="1" t="n">
+        <v>1.116</v>
       </c>
     </row>
     <row r="336">
@@ -31076,10 +32084,13 @@
         <v>0.011205</v>
       </c>
       <c r="AB336" s="1" t="n">
+        <v>0.011174</v>
+      </c>
+      <c r="AC336" s="1" t="n">
         <v>0.011377</v>
       </c>
-      <c r="AC336" s="1" t="n">
-        <v>0.011205</v>
+      <c r="AD336" s="1" t="n">
+        <v>0.011174</v>
       </c>
     </row>
     <row r="337">
@@ -31167,9 +32178,12 @@
         <v>2.954</v>
       </c>
       <c r="AB337" s="1" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="AC337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="AC337" s="1" t="n">
+      <c r="AD337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -31258,10 +32272,13 @@
         <v>0.01833</v>
       </c>
       <c r="AB338" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="AC338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="AC338" s="1" t="n">
-        <v>0.01833</v>
+      <c r="AD338" s="1" t="n">
+        <v>0.01822</v>
       </c>
     </row>
     <row r="339">
@@ -31349,10 +32366,13 @@
         <v>0.07643999999999999</v>
       </c>
       <c r="AB339" s="1" t="n">
+        <v>0.07595</v>
+      </c>
+      <c r="AC339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="AC339" s="1" t="n">
-        <v>0.07643999999999999</v>
+      <c r="AD339" s="1" t="n">
+        <v>0.07595</v>
       </c>
     </row>
     <row r="340">
@@ -31440,9 +32460,12 @@
         <v>0.075</v>
       </c>
       <c r="AB340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AC340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="AC340" s="1" t="n">
+      <c r="AD340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -31531,9 +32554,12 @@
         <v>0.03604</v>
       </c>
       <c r="AB341" s="1" t="n">
+        <v>0.03578</v>
+      </c>
+      <c r="AC341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="AC341" s="1" t="n">
+      <c r="AD341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -31622,10 +32648,13 @@
         <v>2571</v>
       </c>
       <c r="AB342" s="1" t="n">
+        <v>2557</v>
+      </c>
+      <c r="AC342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="AC342" s="1" t="n">
-        <v>2571</v>
+      <c r="AD342" s="1" t="n">
+        <v>2557</v>
       </c>
     </row>
     <row r="343">
@@ -31713,9 +32742,12 @@
         <v>0.0001971</v>
       </c>
       <c r="AB343" s="1" t="n">
+        <v>0.0001954</v>
+      </c>
+      <c r="AC343" s="1" t="n">
         <v>0.0002049</v>
       </c>
-      <c r="AC343" s="1" t="n">
+      <c r="AD343" s="1" t="n">
         <v>0.0001952</v>
       </c>
     </row>
@@ -31804,9 +32836,12 @@
         <v>0.07890999999999999</v>
       </c>
       <c r="AB344" s="1" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="AC344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="AC344" s="1" t="n">
+      <c r="AD344" s="1" t="n">
         <v>0.07890999999999999</v>
       </c>
     </row>
@@ -31895,10 +32930,13 @@
         <v>0.01597</v>
       </c>
       <c r="AB345" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="AC345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="AC345" s="1" t="n">
-        <v>0.01597</v>
+      <c r="AD345" s="1" t="n">
+        <v>0.0159</v>
       </c>
     </row>
     <row r="346">
@@ -31986,10 +33024,13 @@
         <v>2.734</v>
       </c>
       <c r="AB346" s="1" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="AC346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="AC346" s="1" t="n">
-        <v>2.731</v>
+      <c r="AD346" s="1" t="n">
+        <v>2.717</v>
       </c>
     </row>
     <row r="347">
@@ -32077,10 +33118,13 @@
         <v>0.01617</v>
       </c>
       <c r="AB347" s="1" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="AC347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="AC347" s="1" t="n">
-        <v>0.01617</v>
+      <c r="AD347" s="1" t="n">
+        <v>0.01608</v>
       </c>
     </row>
     <row r="348">
@@ -32168,9 +33212,12 @@
         <v>0.03819</v>
       </c>
       <c r="AB348" s="1" t="n">
+        <v>0.03844</v>
+      </c>
+      <c r="AC348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="AC348" s="1" t="n">
+      <c r="AD348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -32259,9 +33306,12 @@
         <v>0.305</v>
       </c>
       <c r="AB349" s="1" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="AC349" s="1" t="n">
         <v>0.3076</v>
       </c>
-      <c r="AC349" s="1" t="n">
+      <c r="AD349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -32350,10 +33400,13 @@
         <v>0.005052</v>
       </c>
       <c r="AB350" s="1" t="n">
+        <v>0.005023</v>
+      </c>
+      <c r="AC350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="AC350" s="1" t="n">
-        <v>0.005039</v>
+      <c r="AD350" s="1" t="n">
+        <v>0.005023</v>
       </c>
     </row>
     <row r="351">
@@ -32441,10 +33494,13 @@
         <v>0.005063</v>
       </c>
       <c r="AB351" s="1" t="n">
+        <v>0.005036</v>
+      </c>
+      <c r="AC351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="AC351" s="1" t="n">
-        <v>0.005054</v>
+      <c r="AD351" s="1" t="n">
+        <v>0.005036</v>
       </c>
     </row>
     <row r="352">
@@ -32532,10 +33588,13 @@
         <v>0.004381</v>
       </c>
       <c r="AB352" s="1" t="n">
+        <v>0.004362</v>
+      </c>
+      <c r="AC352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="AC352" s="1" t="n">
-        <v>0.004371</v>
+      <c r="AD352" s="1" t="n">
+        <v>0.004362</v>
       </c>
     </row>
     <row r="353">
@@ -32623,10 +33682,13 @@
         <v>0.08042000000000001</v>
       </c>
       <c r="AB353" s="1" t="n">
+        <v>0.08005</v>
+      </c>
+      <c r="AC353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="AC353" s="1" t="n">
-        <v>0.08008</v>
+      <c r="AD353" s="1" t="n">
+        <v>0.08005</v>
       </c>
     </row>
     <row r="354">
@@ -32714,10 +33776,13 @@
         <v>1.228</v>
       </c>
       <c r="AB354" s="1" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="AC354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="AC354" s="1" t="n">
-        <v>1.228</v>
+      <c r="AD354" s="1" t="n">
+        <v>1.201</v>
       </c>
     </row>
     <row r="355">
@@ -32805,9 +33870,12 @@
         <v>7.685</v>
       </c>
       <c r="AB355" s="1" t="n">
+        <v>7.671</v>
+      </c>
+      <c r="AC355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="AC355" s="1" t="n">
+      <c r="AD355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -32896,10 +33964,13 @@
         <v>0.00766</v>
       </c>
       <c r="AB356" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="AC356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="AC356" s="1" t="n">
-        <v>0.00766</v>
+      <c r="AD356" s="1" t="n">
+        <v>0.00765</v>
       </c>
     </row>
     <row r="357">
@@ -32987,10 +34058,13 @@
         <v>0.005631</v>
       </c>
       <c r="AB357" s="1" t="n">
+        <v>0.005603</v>
+      </c>
+      <c r="AC357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="AC357" s="1" t="n">
-        <v>0.005608</v>
+      <c r="AD357" s="1" t="n">
+        <v>0.005603</v>
       </c>
     </row>
     <row r="358">
@@ -33078,10 +34152,13 @@
         <v>0.01535</v>
       </c>
       <c r="AB358" s="1" t="n">
+        <v>0.01525</v>
+      </c>
+      <c r="AC358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="AC358" s="1" t="n">
-        <v>0.01533</v>
+      <c r="AD358" s="1" t="n">
+        <v>0.01525</v>
       </c>
     </row>
     <row r="359">
@@ -33169,10 +34246,13 @@
         <v>3.605</v>
       </c>
       <c r="AB359" s="1" t="n">
+        <v>3.593</v>
+      </c>
+      <c r="AC359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="AC359" s="1" t="n">
-        <v>3.597</v>
+      <c r="AD359" s="1" t="n">
+        <v>3.593</v>
       </c>
     </row>
     <row r="360">
@@ -33260,10 +34340,13 @@
         <v>0.1492</v>
       </c>
       <c r="AB360" s="1" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="AC360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="AC360" s="1" t="n">
-        <v>0.1492</v>
+      <c r="AD360" s="1" t="n">
+        <v>0.1483</v>
       </c>
     </row>
     <row r="361">
@@ -33351,9 +34434,12 @@
         <v>0.07009</v>
       </c>
       <c r="AB361" s="1" t="n">
+        <v>0.07011000000000001</v>
+      </c>
+      <c r="AC361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="AC361" s="1" t="n">
+      <c r="AD361" s="1" t="n">
         <v>0.07009</v>
       </c>
     </row>
@@ -33442,10 +34528,13 @@
         <v>0.01756</v>
       </c>
       <c r="AB362" s="1" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AC362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="AC362" s="1" t="n">
-        <v>0.01756</v>
+      <c r="AD362" s="1" t="n">
+        <v>0.01749</v>
       </c>
     </row>
     <row r="363">
@@ -33533,10 +34622,13 @@
         <v>0.02205</v>
       </c>
       <c r="AB363" s="1" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="AC363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="AC363" s="1" t="n">
-        <v>0.02205</v>
+      <c r="AD363" s="1" t="n">
+        <v>0.02203</v>
       </c>
     </row>
     <row r="364">
@@ -33624,10 +34716,13 @@
         <v>0.01243</v>
       </c>
       <c r="AB364" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="AC364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="AC364" s="1" t="n">
-        <v>0.01243</v>
+      <c r="AD364" s="1" t="n">
+        <v>0.01233</v>
       </c>
     </row>
     <row r="365">
@@ -33715,10 +34810,13 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="AB365" s="1" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="AC365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="AC365" s="1" t="n">
-        <v>0.08989999999999999</v>
+      <c r="AD365" s="1" t="n">
+        <v>0.0895</v>
       </c>
     </row>
     <row r="366">
@@ -33806,10 +34904,13 @@
         <v>0.04199</v>
       </c>
       <c r="AB366" s="1" t="n">
+        <v>0.04176</v>
+      </c>
+      <c r="AC366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="AC366" s="1" t="n">
-        <v>0.04199</v>
+      <c r="AD366" s="1" t="n">
+        <v>0.04176</v>
       </c>
     </row>
     <row r="367">
@@ -33897,9 +34998,12 @@
         <v>0.03081</v>
       </c>
       <c r="AB367" s="1" t="n">
+        <v>0.03082</v>
+      </c>
+      <c r="AC367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="AC367" s="1" t="n">
+      <c r="AD367" s="1" t="n">
         <v>0.03081</v>
       </c>
     </row>
@@ -33988,10 +35092,13 @@
         <v>0.02289</v>
       </c>
       <c r="AB368" s="1" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="AC368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="AC368" s="1" t="n">
-        <v>0.02289</v>
+      <c r="AD368" s="1" t="n">
+        <v>0.02273</v>
       </c>
     </row>
     <row r="369">
@@ -34079,10 +35186,13 @@
         <v>0.03066</v>
       </c>
       <c r="AB369" s="1" t="n">
+        <v>0.03054</v>
+      </c>
+      <c r="AC369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="AC369" s="1" t="n">
-        <v>0.03066</v>
+      <c r="AD369" s="1" t="n">
+        <v>0.03054</v>
       </c>
     </row>
     <row r="370">
@@ -34170,9 +35280,12 @@
         <v>0.0793</v>
       </c>
       <c r="AB370" s="1" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="AC370" s="1" t="n">
         <v>0.08017000000000001</v>
       </c>
-      <c r="AC370" s="1" t="n">
+      <c r="AD370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -34261,10 +35374,13 @@
         <v>0.1063</v>
       </c>
       <c r="AB371" s="1" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="AC371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="AC371" s="1" t="n">
-        <v>0.1063</v>
+      <c r="AD371" s="1" t="n">
+        <v>0.1059</v>
       </c>
     </row>
     <row r="372">
@@ -34352,10 +35468,13 @@
         <v>0.006926</v>
       </c>
       <c r="AB372" s="1" t="n">
+        <v>0.00688</v>
+      </c>
+      <c r="AC372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="AC372" s="1" t="n">
-        <v>0.006926</v>
+      <c r="AD372" s="1" t="n">
+        <v>0.00688</v>
       </c>
     </row>
     <row r="373">
@@ -34443,9 +35562,12 @@
         <v>0.0965</v>
       </c>
       <c r="AB373" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="AC373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="AC373" s="1" t="n">
+      <c r="AD373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -34534,10 +35656,13 @@
         <v>0.05683</v>
       </c>
       <c r="AB374" s="1" t="n">
+        <v>0.05633</v>
+      </c>
+      <c r="AC374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="AC374" s="1" t="n">
-        <v>0.05683</v>
+      <c r="AD374" s="1" t="n">
+        <v>0.05633</v>
       </c>
     </row>
     <row r="375">
@@ -34625,10 +35750,13 @@
         <v>0.3143</v>
       </c>
       <c r="AB375" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AC375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="AC375" s="1" t="n">
-        <v>0.3143</v>
+      <c r="AD375" s="1" t="n">
+        <v>0.312</v>
       </c>
     </row>
     <row r="376">
@@ -34716,10 +35844,13 @@
         <v>0.01923</v>
       </c>
       <c r="AB376" s="1" t="n">
+        <v>0.01914</v>
+      </c>
+      <c r="AC376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="AC376" s="1" t="n">
-        <v>0.01923</v>
+      <c r="AD376" s="1" t="n">
+        <v>0.01914</v>
       </c>
     </row>
     <row r="377">
@@ -34807,10 +35938,13 @@
         <v>0.06841999999999999</v>
       </c>
       <c r="AB377" s="1" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="AC377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="AC377" s="1" t="n">
-        <v>0.06818</v>
+      <c r="AD377" s="1" t="n">
+        <v>0.0679</v>
       </c>
     </row>
     <row r="378">
@@ -34898,9 +36032,12 @@
         <v>0.15749</v>
       </c>
       <c r="AB378" s="1" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AC378" s="1" t="n">
         <v>0.15872</v>
       </c>
-      <c r="AC378" s="1" t="n">
+      <c r="AD378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -34989,10 +36126,13 @@
         <v>0.0005909</v>
       </c>
       <c r="AB379" s="1" t="n">
+        <v>0.0005873</v>
+      </c>
+      <c r="AC379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="AC379" s="1" t="n">
-        <v>0.0005909</v>
+      <c r="AD379" s="1" t="n">
+        <v>0.0005873</v>
       </c>
     </row>
     <row r="380">
@@ -35080,10 +36220,13 @@
         <v>0.01008</v>
       </c>
       <c r="AB380" s="1" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="AC380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="AC380" s="1" t="n">
-        <v>0.01008</v>
+      <c r="AD380" s="1" t="n">
+        <v>0.01002</v>
       </c>
     </row>
     <row r="381">
@@ -35171,10 +36314,13 @@
         <v>0.02533</v>
       </c>
       <c r="AB381" s="1" t="n">
+        <v>0.02519</v>
+      </c>
+      <c r="AC381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="AC381" s="1" t="n">
-        <v>0.02533</v>
+      <c r="AD381" s="1" t="n">
+        <v>0.02519</v>
       </c>
     </row>
     <row r="382">
@@ -35262,9 +36408,12 @@
         <v>0.18387</v>
       </c>
       <c r="AB382" s="1" t="n">
+        <v>0.18425</v>
+      </c>
+      <c r="AC382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="AC382" s="1" t="n">
+      <c r="AD382" s="1" t="n">
         <v>0.18387</v>
       </c>
     </row>
@@ -35353,10 +36502,13 @@
         <v>0.09107999999999999</v>
       </c>
       <c r="AB383" s="1" t="n">
+        <v>0.09056</v>
+      </c>
+      <c r="AC383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="AC383" s="1" t="n">
-        <v>0.09107999999999999</v>
+      <c r="AD383" s="1" t="n">
+        <v>0.09056</v>
       </c>
     </row>
     <row r="384">
@@ -35444,10 +36596,13 @@
         <v>0.0316</v>
       </c>
       <c r="AB384" s="1" t="n">
+        <v>0.03141</v>
+      </c>
+      <c r="AC384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="AC384" s="1" t="n">
-        <v>0.0316</v>
+      <c r="AD384" s="1" t="n">
+        <v>0.03141</v>
       </c>
     </row>
     <row r="385">
@@ -35535,10 +36690,13 @@
         <v>0.0107</v>
       </c>
       <c r="AB385" s="1" t="n">
+        <v>0.01059</v>
+      </c>
+      <c r="AC385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="AC385" s="1" t="n">
-        <v>0.0107</v>
+      <c r="AD385" s="1" t="n">
+        <v>0.01059</v>
       </c>
     </row>
     <row r="386">
@@ -35626,10 +36784,13 @@
         <v>0.05022</v>
       </c>
       <c r="AB386" s="1" t="n">
+        <v>0.04982</v>
+      </c>
+      <c r="AC386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="AC386" s="1" t="n">
-        <v>0.05022</v>
+      <c r="AD386" s="1" t="n">
+        <v>0.04982</v>
       </c>
     </row>
     <row r="387">
@@ -35717,9 +36878,12 @@
         <v>0.02354</v>
       </c>
       <c r="AB387" s="1" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="AC387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="AC387" s="1" t="n">
+      <c r="AD387" s="1" t="n">
         <v>0.0235</v>
       </c>
     </row>
@@ -35808,9 +36972,12 @@
         <v>0.007297</v>
       </c>
       <c r="AB388" s="1" t="n">
+        <v>0.007255</v>
+      </c>
+      <c r="AC388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="AC388" s="1" t="n">
+      <c r="AD388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -35899,10 +37066,13 @@
         <v>0.01004</v>
       </c>
       <c r="AB389" s="1" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="AC389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="AC389" s="1" t="n">
-        <v>0.01004</v>
+      <c r="AD389" s="1" t="n">
+        <v>0.009990000000000001</v>
       </c>
     </row>
     <row r="390">
@@ -35990,10 +37160,13 @@
         <v>0.08146</v>
       </c>
       <c r="AB390" s="1" t="n">
+        <v>0.08108</v>
+      </c>
+      <c r="AC390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="AC390" s="1" t="n">
-        <v>0.08146</v>
+      <c r="AD390" s="1" t="n">
+        <v>0.08108</v>
       </c>
     </row>
     <row r="391">
@@ -36081,10 +37254,13 @@
         <v>0.4985</v>
       </c>
       <c r="AB391" s="1" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="AC391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="AC391" s="1" t="n">
-        <v>0.4985</v>
+      <c r="AD391" s="1" t="n">
+        <v>0.4965</v>
       </c>
     </row>
     <row r="392">
@@ -36172,10 +37348,13 @@
         <v>0.1158</v>
       </c>
       <c r="AB392" s="1" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="AC392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="AC392" s="1" t="n">
-        <v>0.1157</v>
+      <c r="AD392" s="1" t="n">
+        <v>0.1152</v>
       </c>
     </row>
     <row r="393">
@@ -36263,9 +37442,12 @@
         <v>0.00245</v>
       </c>
       <c r="AB393" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="AC393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="AC393" s="1" t="n">
+      <c r="AD393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -36354,9 +37536,12 @@
         <v>0.0217</v>
       </c>
       <c r="AB394" s="1" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="AC394" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="AC394" s="1" t="n">
+      <c r="AD394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -36445,9 +37630,12 @@
         <v>0.0163</v>
       </c>
       <c r="AB395" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AC395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="AC395" s="1" t="n">
+      <c r="AD395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -36536,10 +37724,13 @@
         <v>0.1345</v>
       </c>
       <c r="AB396" s="1" t="n">
+        <v>0.1339</v>
+      </c>
+      <c r="AC396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="AC396" s="1" t="n">
-        <v>0.1345</v>
+      <c r="AD396" s="1" t="n">
+        <v>0.1339</v>
       </c>
     </row>
     <row r="397">
@@ -36627,9 +37818,12 @@
         <v>0.01443</v>
       </c>
       <c r="AB397" s="1" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="AC397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="AC397" s="1" t="n">
+      <c r="AD397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -36718,9 +37912,12 @@
         <v>6.748</v>
       </c>
       <c r="AB398" s="1" t="n">
+        <v>6.715</v>
+      </c>
+      <c r="AC398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="AC398" s="1" t="n">
+      <c r="AD398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -36809,9 +38006,12 @@
         <v>0.009539000000000001</v>
       </c>
       <c r="AB399" s="1" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="AC399" s="1" t="n">
         <v>0.009542</v>
       </c>
-      <c r="AC399" s="1" t="n">
+      <c r="AD399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -36900,9 +38100,12 @@
         <v>0.001252</v>
       </c>
       <c r="AB400" s="1" t="n">
+        <v>0.001243</v>
+      </c>
+      <c r="AC400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="AC400" s="1" t="n">
+      <c r="AD400" s="1" t="n">
         <v>0.001241</v>
       </c>
     </row>
@@ -36991,10 +38194,13 @@
         <v>0.0184</v>
       </c>
       <c r="AB401" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="AC401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="AC401" s="1" t="n">
-        <v>0.0184</v>
+      <c r="AD401" s="1" t="n">
+        <v>0.0183</v>
       </c>
     </row>
     <row r="402">
@@ -37082,10 +38288,13 @@
         <v>0.08427999999999999</v>
       </c>
       <c r="AB402" s="1" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="AC402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AC402" s="1" t="n">
-        <v>0.08427999999999999</v>
+      <c r="AD402" s="1" t="n">
+        <v>0.0839</v>
       </c>
     </row>
     <row r="403">
@@ -37173,10 +38382,13 @@
         <v>0.00543</v>
       </c>
       <c r="AB403" s="1" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="AC403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="AC403" s="1" t="n">
-        <v>0.00543</v>
+      <c r="AD403" s="1" t="n">
+        <v>0.0054</v>
       </c>
     </row>
     <row r="404">
@@ -37264,9 +38476,12 @@
         <v>0.04277</v>
       </c>
       <c r="AB404" s="1" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AC404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="AC404" s="1" t="n">
+      <c r="AD404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -37355,10 +38570,13 @@
         <v>0.05802</v>
       </c>
       <c r="AB405" s="1" t="n">
+        <v>0.05785</v>
+      </c>
+      <c r="AC405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="AC405" s="1" t="n">
-        <v>0.05802</v>
+      <c r="AD405" s="1" t="n">
+        <v>0.05785</v>
       </c>
     </row>
     <row r="406">
@@ -37446,10 +38664,13 @@
         <v>0.01648</v>
       </c>
       <c r="AB406" s="1" t="n">
+        <v>0.01632</v>
+      </c>
+      <c r="AC406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="AC406" s="1" t="n">
-        <v>0.01647</v>
+      <c r="AD406" s="1" t="n">
+        <v>0.01632</v>
       </c>
     </row>
     <row r="407">
@@ -37537,10 +38758,13 @@
         <v>0.0421</v>
       </c>
       <c r="AB407" s="1" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AC407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="AC407" s="1" t="n">
-        <v>0.0421</v>
+      <c r="AD407" s="1" t="n">
+        <v>0.0418</v>
       </c>
     </row>
     <row r="408">
@@ -37628,10 +38852,13 @@
         <v>0.01918</v>
       </c>
       <c r="AB408" s="1" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="AC408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="AC408" s="1" t="n">
-        <v>0.01918</v>
+      <c r="AD408" s="1" t="n">
+        <v>0.01906</v>
       </c>
     </row>
     <row r="409">
@@ -37719,10 +38946,13 @@
         <v>0.4406</v>
       </c>
       <c r="AB409" s="1" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AC409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="AC409" s="1" t="n">
-        <v>0.4406</v>
+      <c r="AD409" s="1" t="n">
+        <v>0.438</v>
       </c>
     </row>
     <row r="410">
@@ -37810,10 +39040,13 @@
         <v>0.04322</v>
       </c>
       <c r="AB410" s="1" t="n">
+        <v>0.04302</v>
+      </c>
+      <c r="AC410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="AC410" s="1" t="n">
-        <v>0.04322</v>
+      <c r="AD410" s="1" t="n">
+        <v>0.04302</v>
       </c>
     </row>
     <row r="411">
@@ -37901,10 +39134,13 @@
         <v>26.93</v>
       </c>
       <c r="AB411" s="1" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="AC411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="AC411" s="1" t="n">
-        <v>26.78</v>
+      <c r="AD411" s="1" t="n">
+        <v>26.72</v>
       </c>
     </row>
     <row r="412">
@@ -37992,10 +39228,13 @@
         <v>0.0347</v>
       </c>
       <c r="AB412" s="1" t="n">
+        <v>0.03461</v>
+      </c>
+      <c r="AC412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="AC412" s="1" t="n">
-        <v>0.0347</v>
+      <c r="AD412" s="1" t="n">
+        <v>0.03461</v>
       </c>
     </row>
     <row r="413">
@@ -38083,10 +39322,13 @@
         <v>0.00339</v>
       </c>
       <c r="AB413" s="1" t="n">
+        <v>0.003377</v>
+      </c>
+      <c r="AC413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="AC413" s="1" t="n">
-        <v>0.003388</v>
+      <c r="AD413" s="1" t="n">
+        <v>0.003377</v>
       </c>
     </row>
     <row r="414">
@@ -38174,9 +39416,12 @@
         <v>0.1513</v>
       </c>
       <c r="AB414" s="1" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="AC414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="AC414" s="1" t="n">
+      <c r="AD414" s="1" t="n">
         <v>0.1513</v>
       </c>
     </row>
@@ -38265,10 +39510,13 @@
         <v>0.05222</v>
       </c>
       <c r="AB415" s="1" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="AC415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="AC415" s="1" t="n">
-        <v>0.05222</v>
+      <c r="AD415" s="1" t="n">
+        <v>0.05192</v>
       </c>
     </row>
     <row r="416">
@@ -38356,10 +39604,13 @@
         <v>0.00655</v>
       </c>
       <c r="AB416" s="1" t="n">
+        <v>0.00651</v>
+      </c>
+      <c r="AC416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="AC416" s="1" t="n">
-        <v>0.00654</v>
+      <c r="AD416" s="1" t="n">
+        <v>0.00651</v>
       </c>
     </row>
     <row r="417">
@@ -38447,10 +39698,13 @@
         <v>0.06026</v>
       </c>
       <c r="AB417" s="1" t="n">
+        <v>0.06015</v>
+      </c>
+      <c r="AC417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="AC417" s="1" t="n">
-        <v>0.06025</v>
+      <c r="AD417" s="1" t="n">
+        <v>0.06015</v>
       </c>
     </row>
     <row r="418">
@@ -38538,10 +39792,13 @@
         <v>0.008000999999999999</v>
       </c>
       <c r="AB418" s="1" t="n">
+        <v>0.007925</v>
+      </c>
+      <c r="AC418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="AC418" s="1" t="n">
-        <v>0.007979</v>
+      <c r="AD418" s="1" t="n">
+        <v>0.007925</v>
       </c>
     </row>
     <row r="419">
@@ -38629,10 +39886,13 @@
         <v>0.07319000000000001</v>
       </c>
       <c r="AB419" s="1" t="n">
+        <v>0.07278</v>
+      </c>
+      <c r="AC419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="AC419" s="1" t="n">
-        <v>0.07306</v>
+      <c r="AD419" s="1" t="n">
+        <v>0.07278</v>
       </c>
     </row>
     <row r="420">
@@ -38720,10 +39980,13 @@
         <v>0.02113</v>
       </c>
       <c r="AB420" s="1" t="n">
+        <v>0.02095</v>
+      </c>
+      <c r="AC420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="AC420" s="1" t="n">
-        <v>0.02105</v>
+      <c r="AD420" s="1" t="n">
+        <v>0.02095</v>
       </c>
     </row>
     <row r="421">
@@ -38811,10 +40074,13 @@
         <v>0.06843</v>
       </c>
       <c r="AB421" s="1" t="n">
+        <v>0.06793</v>
+      </c>
+      <c r="AC421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="AC421" s="1" t="n">
-        <v>0.06843</v>
+      <c r="AD421" s="1" t="n">
+        <v>0.06793</v>
       </c>
     </row>
     <row r="422">
@@ -38902,10 +40168,13 @@
         <v>0.01466</v>
       </c>
       <c r="AB422" s="1" t="n">
+        <v>0.01453</v>
+      </c>
+      <c r="AC422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="AC422" s="1" t="n">
-        <v>0.01466</v>
+      <c r="AD422" s="1" t="n">
+        <v>0.01453</v>
       </c>
     </row>
     <row r="423">
@@ -38993,10 +40262,13 @@
         <v>0.006597</v>
       </c>
       <c r="AB423" s="1" t="n">
+        <v>0.006564</v>
+      </c>
+      <c r="AC423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="AC423" s="1" t="n">
-        <v>0.00658</v>
+      <c r="AD423" s="1" t="n">
+        <v>0.006564</v>
       </c>
     </row>
     <row r="424">
@@ -39084,10 +40356,13 @@
         <v>0.901</v>
       </c>
       <c r="AB424" s="1" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AC424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="AC424" s="1" t="n">
-        <v>0.901</v>
+      <c r="AD424" s="1" t="n">
+        <v>0.897</v>
       </c>
     </row>
     <row r="425">
@@ -39175,10 +40450,13 @@
         <v>0.03507</v>
       </c>
       <c r="AB425" s="1" t="n">
+        <v>0.03491</v>
+      </c>
+      <c r="AC425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="AC425" s="1" t="n">
-        <v>0.03507</v>
+      <c r="AD425" s="1" t="n">
+        <v>0.03491</v>
       </c>
     </row>
     <row r="426">
@@ -39266,9 +40544,12 @@
         <v>1.792</v>
       </c>
       <c r="AB426" s="1" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="AC426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC426" s="1" t="n">
+      <c r="AD426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -39357,9 +40638,12 @@
         <v>0.12911</v>
       </c>
       <c r="AB427" s="1" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="AC427" s="1" t="n">
         <v>0.12936</v>
       </c>
-      <c r="AC427" s="1" t="n">
+      <c r="AD427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -39448,9 +40732,12 @@
         <v>0.05331</v>
       </c>
       <c r="AB428" s="1" t="n">
+        <v>0.05326</v>
+      </c>
+      <c r="AC428" s="1" t="n">
         <v>0.05391</v>
       </c>
-      <c r="AC428" s="1" t="n">
+      <c r="AD428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -39539,9 +40826,12 @@
         <v>1.297</v>
       </c>
       <c r="AB429" s="1" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="AC429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="AC429" s="1" t="n">
+      <c r="AD429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -39630,10 +40920,13 @@
         <v>0.07416</v>
       </c>
       <c r="AB430" s="1" t="n">
+        <v>0.07384</v>
+      </c>
+      <c r="AC430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="AC430" s="1" t="n">
-        <v>0.07416</v>
+      <c r="AD430" s="1" t="n">
+        <v>0.07384</v>
       </c>
     </row>
     <row r="431">
@@ -39721,10 +41014,13 @@
         <v>0.1547</v>
       </c>
       <c r="AB431" s="1" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="AC431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="AC431" s="1" t="n">
-        <v>0.1547</v>
+      <c r="AD431" s="1" t="n">
+        <v>0.1545</v>
       </c>
     </row>
     <row r="432">
@@ -39812,10 +41108,13 @@
         <v>1.441</v>
       </c>
       <c r="AB432" s="1" t="n">
+        <v>1.434</v>
+      </c>
+      <c r="AC432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="AC432" s="1" t="n">
-        <v>1.438</v>
+      <c r="AD432" s="1" t="n">
+        <v>1.434</v>
       </c>
     </row>
     <row r="433">
@@ -39903,10 +41202,13 @@
         <v>3.22</v>
       </c>
       <c r="AB433" s="1" t="n">
+        <v>3.197</v>
+      </c>
+      <c r="AC433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="AC433" s="1" t="n">
-        <v>3.22</v>
+      <c r="AD433" s="1" t="n">
+        <v>3.197</v>
       </c>
     </row>
     <row r="434">
@@ -39994,10 +41296,13 @@
         <v>0.1772</v>
       </c>
       <c r="AB434" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="AC434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="AC434" s="1" t="n">
-        <v>0.1772</v>
+      <c r="AD434" s="1" t="n">
+        <v>0.1765</v>
       </c>
     </row>
     <row r="435">
@@ -40085,10 +41390,13 @@
         <v>0.008536999999999999</v>
       </c>
       <c r="AB435" s="1" t="n">
+        <v>0.008494</v>
+      </c>
+      <c r="AC435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="AC435" s="1" t="n">
-        <v>0.008536999999999999</v>
+      <c r="AD435" s="1" t="n">
+        <v>0.008494</v>
       </c>
     </row>
     <row r="436">
@@ -40176,10 +41484,13 @@
         <v>0.2806</v>
       </c>
       <c r="AB436" s="1" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AC436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="AC436" s="1" t="n">
-        <v>0.2803</v>
+      <c r="AD436" s="1" t="n">
+        <v>0.2791</v>
       </c>
     </row>
     <row r="437">
@@ -40267,9 +41578,12 @@
         <v>0.03828</v>
       </c>
       <c r="AB437" s="1" t="n">
+        <v>0.03818</v>
+      </c>
+      <c r="AC437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="AC437" s="1" t="n">
+      <c r="AD437" s="1" t="n">
         <v>0.03802</v>
       </c>
     </row>
@@ -40358,10 +41672,13 @@
         <v>0.02416</v>
       </c>
       <c r="AB438" s="1" t="n">
+        <v>0.02344</v>
+      </c>
+      <c r="AC438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="AC438" s="1" t="n">
-        <v>0.02405</v>
+      <c r="AD438" s="1" t="n">
+        <v>0.02344</v>
       </c>
     </row>
     <row r="439">
@@ -40449,9 +41766,12 @@
         <v>0.04405</v>
       </c>
       <c r="AB439" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AC439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="AC439" s="1" t="n">
+      <c r="AD439" s="1" t="n">
         <v>0.044</v>
       </c>
     </row>
@@ -40540,9 +41860,12 @@
         <v>0.0005173000000000001</v>
       </c>
       <c r="AB440" s="1" t="n">
+        <v>0.0005177</v>
+      </c>
+      <c r="AC440" s="1" t="n">
         <v>0.0005312</v>
       </c>
-      <c r="AC440" s="1" t="n">
+      <c r="AD440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -40631,9 +41954,12 @@
         <v>0.04544</v>
       </c>
       <c r="AB441" s="1" t="n">
+        <v>0.04503</v>
+      </c>
+      <c r="AC441" s="1" t="n">
         <v>0.04581</v>
       </c>
-      <c r="AC441" s="1" t="n">
+      <c r="AD441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -40722,9 +42048,12 @@
         <v>0.000416</v>
       </c>
       <c r="AB442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="AC442" s="1" t="n">
         <v>0.000419</v>
       </c>
-      <c r="AC442" s="1" t="n">
+      <c r="AD442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -40813,9 +42142,12 @@
         <v>0.0945</v>
       </c>
       <c r="AB443" s="1" t="n">
+        <v>0.09395000000000001</v>
+      </c>
+      <c r="AC443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="AC443" s="1" t="n">
+      <c r="AD443" s="1" t="n">
         <v>0.09392</v>
       </c>
     </row>
@@ -40904,10 +42236,13 @@
         <v>2.268</v>
       </c>
       <c r="AB444" s="1" t="n">
+        <v>2.263</v>
+      </c>
+      <c r="AC444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="AC444" s="1" t="n">
-        <v>2.268</v>
+      <c r="AD444" s="1" t="n">
+        <v>2.263</v>
       </c>
     </row>
     <row r="445">
@@ -40995,10 +42330,13 @@
         <v>0.2659</v>
       </c>
       <c r="AB445" s="1" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AC445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="AC445" s="1" t="n">
-        <v>0.2659</v>
+      <c r="AD445" s="1" t="n">
+        <v>0.264</v>
       </c>
     </row>
     <row r="446">
@@ -41086,10 +42424,13 @@
         <v>0.0007421</v>
       </c>
       <c r="AB446" s="1" t="n">
+        <v>0.0007344</v>
+      </c>
+      <c r="AC446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="AC446" s="1" t="n">
-        <v>0.0007376</v>
+      <c r="AD446" s="1" t="n">
+        <v>0.0007344</v>
       </c>
     </row>
     <row r="447">
@@ -41177,9 +42518,12 @@
         <v>0.0386</v>
       </c>
       <c r="AB447" s="1" t="n">
+        <v>0.03843</v>
+      </c>
+      <c r="AC447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="AC447" s="1" t="n">
+      <c r="AD447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -41268,9 +42612,12 @@
         <v>0.1761</v>
       </c>
       <c r="AB448" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="AC448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="AC448" s="1" t="n">
+      <c r="AD448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -41359,9 +42706,12 @@
         <v>0.04282</v>
       </c>
       <c r="AB449" s="1" t="n">
+        <v>0.04273</v>
+      </c>
+      <c r="AC449" s="1" t="n">
         <v>0.04312</v>
       </c>
-      <c r="AC449" s="1" t="n">
+      <c r="AD449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -41450,10 +42800,13 @@
         <v>0.0001639</v>
       </c>
       <c r="AB450" s="1" t="n">
+        <v>0.0001624</v>
+      </c>
+      <c r="AC450" s="1" t="n">
         <v>0.0001657</v>
       </c>
-      <c r="AC450" s="1" t="n">
-        <v>0.0001632</v>
+      <c r="AD450" s="1" t="n">
+        <v>0.0001624</v>
       </c>
     </row>
     <row r="451">
@@ -41541,9 +42894,12 @@
         <v>0.03719</v>
       </c>
       <c r="AB451" s="1" t="n">
+        <v>0.03705</v>
+      </c>
+      <c r="AC451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="AC451" s="1" t="n">
+      <c r="AD451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -41632,10 +42988,13 @@
         <v>0.009310000000000001</v>
       </c>
       <c r="AB452" s="1" t="n">
+        <v>0.00916</v>
+      </c>
+      <c r="AC452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="AC452" s="1" t="n">
-        <v>0.009310000000000001</v>
+      <c r="AD452" s="1" t="n">
+        <v>0.00916</v>
       </c>
     </row>
     <row r="453">
@@ -41723,10 +43082,13 @@
         <v>0.06713</v>
       </c>
       <c r="AB453" s="1" t="n">
+        <v>0.06644</v>
+      </c>
+      <c r="AC453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="AC453" s="1" t="n">
-        <v>0.06713</v>
+      <c r="AD453" s="1" t="n">
+        <v>0.06644</v>
       </c>
     </row>
     <row r="454">
@@ -41814,10 +43176,13 @@
         <v>0.007453</v>
       </c>
       <c r="AB454" s="1" t="n">
+        <v>0.007433</v>
+      </c>
+      <c r="AC454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="AC454" s="1" t="n">
-        <v>0.007453</v>
+      <c r="AD454" s="1" t="n">
+        <v>0.007433</v>
       </c>
     </row>
     <row r="455">
@@ -41905,10 +43270,13 @@
         <v>0.003234</v>
       </c>
       <c r="AB455" s="1" t="n">
+        <v>0.003214</v>
+      </c>
+      <c r="AC455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="AC455" s="1" t="n">
-        <v>0.003234</v>
+      <c r="AD455" s="1" t="n">
+        <v>0.003214</v>
       </c>
     </row>
     <row r="456">
@@ -41996,10 +43364,13 @@
         <v>0.001826</v>
       </c>
       <c r="AB456" s="1" t="n">
+        <v>0.001814</v>
+      </c>
+      <c r="AC456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="AC456" s="1" t="n">
-        <v>0.001826</v>
+      <c r="AD456" s="1" t="n">
+        <v>0.001814</v>
       </c>
     </row>
     <row r="457">
@@ -42087,10 +43458,13 @@
         <v>0.0001737</v>
       </c>
       <c r="AB457" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="AC457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="AC457" s="1" t="n">
-        <v>0.0001737</v>
+      <c r="AD457" s="1" t="n">
+        <v>0.000173</v>
       </c>
     </row>
     <row r="458">
@@ -42178,10 +43552,13 @@
         <v>0.0003866</v>
       </c>
       <c r="AB458" s="1" t="n">
+        <v>0.0003858</v>
+      </c>
+      <c r="AC458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="AC458" s="1" t="n">
-        <v>0.0003866</v>
+      <c r="AD458" s="1" t="n">
+        <v>0.0003858</v>
       </c>
     </row>
     <row r="459">
@@ -42269,10 +43646,13 @@
         <v>0.01386</v>
       </c>
       <c r="AB459" s="1" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="AC459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="AC459" s="1" t="n">
-        <v>0.01386</v>
+      <c r="AD459" s="1" t="n">
+        <v>0.01375</v>
       </c>
     </row>
     <row r="460">
@@ -42360,10 +43740,13 @@
         <v>0.04524</v>
       </c>
       <c r="AB460" s="1" t="n">
+        <v>0.04513</v>
+      </c>
+      <c r="AC460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="AC460" s="1" t="n">
-        <v>0.04518</v>
+      <c r="AD460" s="1" t="n">
+        <v>0.04513</v>
       </c>
     </row>
     <row r="461">
@@ -42451,10 +43834,13 @@
         <v>0.2807</v>
       </c>
       <c r="AB461" s="1" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AC461" s="1" t="n">
         <v>0.2843</v>
       </c>
-      <c r="AC461" s="1" t="n">
-        <v>0.2807</v>
+      <c r="AD461" s="1" t="n">
+        <v>0.2796</v>
       </c>
     </row>
     <row r="462">
@@ -42542,10 +43928,13 @@
         <v>0.006184</v>
       </c>
       <c r="AB462" s="1" t="n">
+        <v>0.006151</v>
+      </c>
+      <c r="AC462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="AC462" s="1" t="n">
-        <v>0.006184</v>
+      <c r="AD462" s="1" t="n">
+        <v>0.006151</v>
       </c>
     </row>
     <row r="463">
@@ -42633,9 +44022,12 @@
         <v>0.00706</v>
       </c>
       <c r="AB463" s="1" t="n">
+        <v>0.007031</v>
+      </c>
+      <c r="AC463" s="1" t="n">
         <v>0.007153</v>
       </c>
-      <c r="AC463" s="1" t="n">
+      <c r="AD463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -42724,10 +44116,13 @@
         <v>0.287</v>
       </c>
       <c r="AB464" s="1" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="AC464" s="1" t="n">
         <v>0.2895</v>
       </c>
-      <c r="AC464" s="1" t="n">
-        <v>0.2853</v>
+      <c r="AD464" s="1" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="465">
@@ -42815,9 +44210,12 @@
         <v>0.08084</v>
       </c>
       <c r="AB465" s="1" t="n">
+        <v>0.08104</v>
+      </c>
+      <c r="AC465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="AC465" s="1" t="n">
+      <c r="AD465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -42906,10 +44304,13 @@
         <v>0.6288</v>
       </c>
       <c r="AB466" s="1" t="n">
+        <v>0.6242</v>
+      </c>
+      <c r="AC466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="AC466" s="1" t="n">
-        <v>0.6288</v>
+      <c r="AD466" s="1" t="n">
+        <v>0.6242</v>
       </c>
     </row>
     <row r="467">
@@ -42997,10 +44398,13 @@
         <v>0.0146</v>
       </c>
       <c r="AB467" s="1" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="AC467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="AC467" s="1" t="n">
-        <v>0.0146</v>
+      <c r="AD467" s="1" t="n">
+        <v>0.0145</v>
       </c>
     </row>
     <row r="468">
@@ -43088,9 +44492,12 @@
         <v>0.03457</v>
       </c>
       <c r="AB468" s="1" t="n">
+        <v>0.03454</v>
+      </c>
+      <c r="AC468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="AC468" s="1" t="n">
+      <c r="AD468" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -43179,10 +44586,13 @@
         <v>0.1604</v>
       </c>
       <c r="AB469" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AC469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="AC469" s="1" t="n">
-        <v>0.1604</v>
+      <c r="AD469" s="1" t="n">
+        <v>0.1598</v>
       </c>
     </row>
     <row r="470">
@@ -43270,10 +44680,13 @@
         <v>0.4058</v>
       </c>
       <c r="AB470" s="1" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="AC470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="AC470" s="1" t="n">
-        <v>0.4058</v>
+      <c r="AD470" s="1" t="n">
+        <v>0.4041</v>
       </c>
     </row>
     <row r="471">
@@ -43361,10 +44774,13 @@
         <v>0.06858</v>
       </c>
       <c r="AB471" s="1" t="n">
+        <v>0.06851</v>
+      </c>
+      <c r="AC471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="AC471" s="1" t="n">
-        <v>0.06854</v>
+      <c r="AD471" s="1" t="n">
+        <v>0.06851</v>
       </c>
     </row>
     <row r="472">
@@ -43452,10 +44868,13 @@
         <v>0.06469999999999999</v>
       </c>
       <c r="AB472" s="1" t="n">
+        <v>0.06446</v>
+      </c>
+      <c r="AC472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="AC472" s="1" t="n">
-        <v>0.06469999999999999</v>
+      <c r="AD472" s="1" t="n">
+        <v>0.06446</v>
       </c>
     </row>
     <row r="473">
@@ -43543,10 +44962,13 @@
         <v>0.01625</v>
       </c>
       <c r="AB473" s="1" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="AC473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="AC473" s="1" t="n">
-        <v>0.0162</v>
+      <c r="AD473" s="1" t="n">
+        <v>0.01615</v>
       </c>
     </row>
     <row r="474">
@@ -43634,10 +45056,13 @@
         <v>0.2037</v>
       </c>
       <c r="AB474" s="1" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="AC474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="AC474" s="1" t="n">
-        <v>0.2037</v>
+      <c r="AD474" s="1" t="n">
+        <v>0.2029</v>
       </c>
     </row>
     <row r="475">
@@ -43725,9 +45150,12 @@
         <v>0.0416</v>
       </c>
       <c r="AB475" s="1" t="n">
+        <v>0.04146</v>
+      </c>
+      <c r="AC475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="AC475" s="1" t="n">
+      <c r="AD475" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -43816,10 +45244,13 @@
         <v>1.554</v>
       </c>
       <c r="AB476" s="1" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="AC476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="AC476" s="1" t="n">
-        <v>1.554</v>
+      <c r="AD476" s="1" t="n">
+        <v>1.546</v>
       </c>
     </row>
     <row r="477">
@@ -43907,10 +45338,13 @@
         <v>0.1003</v>
       </c>
       <c r="AB477" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="AC477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="AC477" s="1" t="n">
-        <v>0.1002</v>
+      <c r="AD477" s="1" t="n">
+        <v>0.1001</v>
       </c>
     </row>
     <row r="478">
@@ -43998,10 +45432,13 @@
         <v>0.001151</v>
       </c>
       <c r="AB478" s="1" t="n">
+        <v>0.001146</v>
+      </c>
+      <c r="AC478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="AC478" s="1" t="n">
-        <v>0.00115</v>
+      <c r="AD478" s="1" t="n">
+        <v>0.001146</v>
       </c>
     </row>
     <row r="479">
@@ -44089,10 +45526,13 @@
         <v>0.1417</v>
       </c>
       <c r="AB479" s="1" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="AC479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="AC479" s="1" t="n">
-        <v>0.1417</v>
+      <c r="AD479" s="1" t="n">
+        <v>0.1408</v>
       </c>
     </row>
     <row r="480">
@@ -44180,9 +45620,12 @@
         <v>0.001886</v>
       </c>
       <c r="AB480" s="1" t="n">
+        <v>0.001867</v>
+      </c>
+      <c r="AC480" s="1" t="n">
         <v>0.001969</v>
       </c>
-      <c r="AC480" s="1" t="n">
+      <c r="AD480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -44271,10 +45714,13 @@
         <v>0.899</v>
       </c>
       <c r="AB481" s="1" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AC481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="AC481" s="1" t="n">
-        <v>0.899</v>
+      <c r="AD481" s="1" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="482">
@@ -44362,9 +45808,12 @@
         <v>0.13385</v>
       </c>
       <c r="AB482" s="1" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="AC482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="AC482" s="1" t="n">
+      <c r="AD482" s="1" t="n">
         <v>0.13233</v>
       </c>
     </row>
@@ -44453,10 +45902,13 @@
         <v>0.04004</v>
       </c>
       <c r="AB483" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="AC483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="AC483" s="1" t="n">
-        <v>0.04004</v>
+      <c r="AD483" s="1" t="n">
+        <v>0.03988</v>
       </c>
     </row>
     <row r="484">
@@ -44544,10 +45996,13 @@
         <v>0.3006</v>
       </c>
       <c r="AB484" s="1" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="AC484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="AC484" s="1" t="n">
-        <v>0.2999</v>
+      <c r="AD484" s="1" t="n">
+        <v>0.2984</v>
       </c>
     </row>
     <row r="485">
@@ -44635,10 +46090,13 @@
         <v>0.05601</v>
       </c>
       <c r="AB485" s="1" t="n">
+        <v>0.05583</v>
+      </c>
+      <c r="AC485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="AC485" s="1" t="n">
-        <v>0.05601</v>
+      <c r="AD485" s="1" t="n">
+        <v>0.05583</v>
       </c>
     </row>
     <row r="486">
@@ -44726,10 +46184,13 @@
         <v>0.001555</v>
       </c>
       <c r="AB486" s="1" t="n">
+        <v>0.001548</v>
+      </c>
+      <c r="AC486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="AC486" s="1" t="n">
-        <v>0.001555</v>
+      <c r="AD486" s="1" t="n">
+        <v>0.001548</v>
       </c>
     </row>
     <row r="487">
@@ -44817,10 +46278,13 @@
         <v>0.06635000000000001</v>
       </c>
       <c r="AB487" s="1" t="n">
+        <v>0.06615</v>
+      </c>
+      <c r="AC487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="AC487" s="1" t="n">
-        <v>0.06635000000000001</v>
+      <c r="AD487" s="1" t="n">
+        <v>0.06615</v>
       </c>
     </row>
     <row r="488">
@@ -44908,10 +46372,13 @@
         <v>0.1906</v>
       </c>
       <c r="AB488" s="1" t="n">
+        <v>0.1895</v>
+      </c>
+      <c r="AC488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="AC488" s="1" t="n">
-        <v>0.1906</v>
+      <c r="AD488" s="1" t="n">
+        <v>0.1895</v>
       </c>
     </row>
     <row r="489">
@@ -44999,10 +46466,13 @@
         <v>0.04745</v>
       </c>
       <c r="AB489" s="1" t="n">
+        <v>0.04708</v>
+      </c>
+      <c r="AC489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="AC489" s="1" t="n">
-        <v>0.04745</v>
+      <c r="AD489" s="1" t="n">
+        <v>0.04708</v>
       </c>
     </row>
     <row r="490">
@@ -45090,10 +46560,13 @@
         <v>0.138</v>
       </c>
       <c r="AB490" s="1" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="AC490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="AC490" s="1" t="n">
-        <v>0.138</v>
+      <c r="AD490" s="1" t="n">
+        <v>0.1378</v>
       </c>
     </row>
     <row r="491">
@@ -45181,9 +46654,12 @@
         <v>0.02252</v>
       </c>
       <c r="AB491" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="AC491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="AC491" s="1" t="n">
+      <c r="AD491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -45272,10 +46748,13 @@
         <v>0.007741</v>
       </c>
       <c r="AB492" s="1" t="n">
+        <v>0.007691</v>
+      </c>
+      <c r="AC492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="AC492" s="1" t="n">
-        <v>0.007706</v>
+      <c r="AD492" s="1" t="n">
+        <v>0.007691</v>
       </c>
     </row>
     <row r="493">
@@ -45363,10 +46842,13 @@
         <v>0.0005879</v>
       </c>
       <c r="AB493" s="1" t="n">
+        <v>0.0005865</v>
+      </c>
+      <c r="AC493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="AC493" s="1" t="n">
-        <v>0.0005879</v>
+      <c r="AD493" s="1" t="n">
+        <v>0.0005865</v>
       </c>
     </row>
     <row r="494">
@@ -45454,10 +46936,13 @@
         <v>2.993</v>
       </c>
       <c r="AB494" s="1" t="n">
+        <v>2.976</v>
+      </c>
+      <c r="AC494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="AC494" s="1" t="n">
-        <v>2.993</v>
+      <c r="AD494" s="1" t="n">
+        <v>2.976</v>
       </c>
     </row>
     <row r="495">
@@ -45545,10 +47030,13 @@
         <v>0.0504</v>
       </c>
       <c r="AB495" s="1" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="AC495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="AC495" s="1" t="n">
-        <v>0.0504</v>
+      <c r="AD495" s="1" t="n">
+        <v>0.05007</v>
       </c>
     </row>
     <row r="496">
@@ -45636,10 +47124,13 @@
         <v>0.006734</v>
       </c>
       <c r="AB496" s="1" t="n">
+        <v>0.006698</v>
+      </c>
+      <c r="AC496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="AC496" s="1" t="n">
-        <v>0.006734</v>
+      <c r="AD496" s="1" t="n">
+        <v>0.006698</v>
       </c>
     </row>
     <row r="497">
@@ -45727,10 +47218,13 @@
         <v>1.301</v>
       </c>
       <c r="AB497" s="1" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="AC497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="AC497" s="1" t="n">
-        <v>1.298</v>
+      <c r="AD497" s="1" t="n">
+        <v>1.297</v>
       </c>
     </row>
     <row r="498">
@@ -45818,10 +47312,13 @@
         <v>0.03906</v>
       </c>
       <c r="AB498" s="1" t="n">
+        <v>0.03881</v>
+      </c>
+      <c r="AC498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="AC498" s="1" t="n">
-        <v>0.03892</v>
+      <c r="AD498" s="1" t="n">
+        <v>0.03881</v>
       </c>
     </row>
     <row r="499">
@@ -45909,10 +47406,13 @@
         <v>0.04072</v>
       </c>
       <c r="AB499" s="1" t="n">
+        <v>0.04055</v>
+      </c>
+      <c r="AC499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="AC499" s="1" t="n">
-        <v>0.04072</v>
+      <c r="AD499" s="1" t="n">
+        <v>0.04055</v>
       </c>
     </row>
     <row r="500">
@@ -46000,9 +47500,12 @@
         <v>0.00541</v>
       </c>
       <c r="AB500" s="1" t="n">
+        <v>0.00538</v>
+      </c>
+      <c r="AC500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="AC500" s="1" t="n">
+      <c r="AD500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -46091,10 +47594,13 @@
         <v>0.03542</v>
       </c>
       <c r="AB501" s="1" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="AC501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="AC501" s="1" t="n">
-        <v>0.03542</v>
+      <c r="AD501" s="1" t="n">
+        <v>0.03527</v>
       </c>
     </row>
     <row r="502">
@@ -46182,10 +47688,13 @@
         <v>0.07174999999999999</v>
       </c>
       <c r="AB502" s="1" t="n">
+        <v>0.07155</v>
+      </c>
+      <c r="AC502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="AC502" s="1" t="n">
-        <v>0.07174999999999999</v>
+      <c r="AD502" s="1" t="n">
+        <v>0.07155</v>
       </c>
     </row>
     <row r="503">
@@ -46273,10 +47782,13 @@
         <v>0.000738</v>
       </c>
       <c r="AB503" s="1" t="n">
+        <v>0.0007356</v>
+      </c>
+      <c r="AC503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="AC503" s="1" t="n">
-        <v>0.000738</v>
+      <c r="AD503" s="1" t="n">
+        <v>0.0007356</v>
       </c>
     </row>
     <row r="504">
@@ -46364,9 +47876,12 @@
         <v>0.016062</v>
       </c>
       <c r="AB504" s="1" t="n">
+        <v>0.016063</v>
+      </c>
+      <c r="AC504" s="1" t="n">
         <v>0.01607</v>
       </c>
-      <c r="AC504" s="1" t="n">
+      <c r="AD504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -46455,10 +47970,13 @@
         <v>0.00698</v>
       </c>
       <c r="AB505" s="1" t="n">
+        <v>0.00694</v>
+      </c>
+      <c r="AC505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="AC505" s="1" t="n">
-        <v>0.00698</v>
+      <c r="AD505" s="1" t="n">
+        <v>0.00694</v>
       </c>
     </row>
     <row r="506">
@@ -46546,9 +48064,12 @@
         <v>0.0255</v>
       </c>
       <c r="AB506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="AC506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="AC506" s="1" t="n">
+      <c r="AD506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -46637,9 +48158,12 @@
         <v>0.001362</v>
       </c>
       <c r="AB507" s="1" t="n">
+        <v>0.001354</v>
+      </c>
+      <c r="AC507" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="AC507" s="1" t="n">
+      <c r="AD507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -46728,10 +48252,13 @@
         <v>0.2798</v>
       </c>
       <c r="AB508" s="1" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AC508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="AC508" s="1" t="n">
-        <v>0.2798</v>
+      <c r="AD508" s="1" t="n">
+        <v>0.278</v>
       </c>
     </row>
     <row r="509">
@@ -46819,10 +48346,13 @@
         <v>0.131</v>
       </c>
       <c r="AB509" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="AC509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="AC509" s="1" t="n">
-        <v>0.131</v>
+      <c r="AD509" s="1" t="n">
+        <v>0.1304</v>
       </c>
     </row>
     <row r="510">
@@ -46910,10 +48440,13 @@
         <v>0.04887</v>
       </c>
       <c r="AB510" s="1" t="n">
+        <v>0.04857</v>
+      </c>
+      <c r="AC510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="AC510" s="1" t="n">
-        <v>0.04883</v>
+      <c r="AD510" s="1" t="n">
+        <v>0.04857</v>
       </c>
     </row>
     <row r="511">
@@ -47001,10 +48534,13 @@
         <v>0.00267</v>
       </c>
       <c r="AB511" s="1" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="AC511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="AC511" s="1" t="n">
-        <v>0.00267</v>
+      <c r="AD511" s="1" t="n">
+        <v>0.00265</v>
       </c>
     </row>
     <row r="512">
@@ -47092,10 +48628,13 @@
         <v>0.014989</v>
       </c>
       <c r="AB512" s="1" t="n">
+        <v>0.014958</v>
+      </c>
+      <c r="AC512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="AC512" s="1" t="n">
-        <v>0.014989</v>
+      <c r="AD512" s="1" t="n">
+        <v>0.014958</v>
       </c>
     </row>
     <row r="513">
@@ -47183,10 +48722,13 @@
         <v>0.6899</v>
       </c>
       <c r="AB513" s="1" t="n">
+        <v>0.6867</v>
+      </c>
+      <c r="AC513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="AC513" s="1" t="n">
-        <v>0.6883</v>
+      <c r="AD513" s="1" t="n">
+        <v>0.6867</v>
       </c>
     </row>
     <row r="514">
@@ -47274,9 +48816,12 @@
         <v>0.004498</v>
       </c>
       <c r="AB514" s="1" t="n">
+        <v>0.004479</v>
+      </c>
+      <c r="AC514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="AC514" s="1" t="n">
+      <c r="AD514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -47365,9 +48910,12 @@
         <v>0.005064</v>
       </c>
       <c r="AB515" s="1" t="n">
+        <v>0.005026</v>
+      </c>
+      <c r="AC515" s="1" t="n">
         <v>0.005074</v>
       </c>
-      <c r="AC515" s="1" t="n">
+      <c r="AD515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -47456,10 +49004,13 @@
         <v>0.06283999999999999</v>
       </c>
       <c r="AB516" s="1" t="n">
+        <v>0.06256</v>
+      </c>
+      <c r="AC516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="AC516" s="1" t="n">
-        <v>0.06283999999999999</v>
+      <c r="AD516" s="1" t="n">
+        <v>0.06256</v>
       </c>
     </row>
     <row r="517">
@@ -47547,9 +49098,12 @@
         <v>0.06441</v>
       </c>
       <c r="AB517" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="AC517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="AC517" s="1" t="n">
+      <c r="AD517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -47638,10 +49192,13 @@
         <v>0.0119</v>
       </c>
       <c r="AB518" s="1" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="AC518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="AC518" s="1" t="n">
-        <v>0.0119</v>
+      <c r="AD518" s="1" t="n">
+        <v>0.01181</v>
       </c>
     </row>
     <row r="519">
@@ -47729,10 +49286,13 @@
         <v>0.0468</v>
       </c>
       <c r="AB519" s="1" t="n">
+        <v>0.04631</v>
+      </c>
+      <c r="AC519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="AC519" s="1" t="n">
-        <v>0.0468</v>
+      <c r="AD519" s="1" t="n">
+        <v>0.04631</v>
       </c>
     </row>
     <row r="520">
@@ -47820,10 +49380,13 @@
         <v>0.04356</v>
       </c>
       <c r="AB520" s="1" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="AC520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="AC520" s="1" t="n">
-        <v>0.04349</v>
+      <c r="AD520" s="1" t="n">
+        <v>0.04332</v>
       </c>
     </row>
     <row r="521">
@@ -47911,9 +49474,12 @@
         <v>0.008373</v>
       </c>
       <c r="AB521" s="1" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="AC521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="AC521" s="1" t="n">
+      <c r="AD521" s="1" t="n">
         <v>0.008288</v>
       </c>
     </row>
@@ -48002,9 +49568,12 @@
         <v>0.08749</v>
       </c>
       <c r="AB522" s="1" t="n">
+        <v>0.08839</v>
+      </c>
+      <c r="AC522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="AC522" s="1" t="n">
+      <c r="AD522" s="1" t="n">
         <v>0.08749</v>
       </c>
     </row>
@@ -48093,10 +49662,13 @@
         <v>0.006436</v>
       </c>
       <c r="AB523" s="1" t="n">
+        <v>0.006393</v>
+      </c>
+      <c r="AC523" s="1" t="n">
         <v>0.006503</v>
       </c>
-      <c r="AC523" s="1" t="n">
-        <v>0.006407</v>
+      <c r="AD523" s="1" t="n">
+        <v>0.006393</v>
       </c>
     </row>
     <row r="524">
@@ -48184,10 +49756,13 @@
         <v>0.01629</v>
       </c>
       <c r="AB524" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AC524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="AC524" s="1" t="n">
-        <v>0.01628</v>
+      <c r="AD524" s="1" t="n">
+        <v>0.0162</v>
       </c>
     </row>
     <row r="525">
@@ -48275,9 +49850,12 @@
         <v>0.01777</v>
       </c>
       <c r="AB525" s="1" t="n">
+        <v>0.01772</v>
+      </c>
+      <c r="AC525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="AC525" s="1" t="n">
+      <c r="AD525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -48366,10 +49944,13 @@
         <v>0.07820000000000001</v>
       </c>
       <c r="AB526" s="1" t="n">
+        <v>0.07794</v>
+      </c>
+      <c r="AC526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="AC526" s="1" t="n">
-        <v>0.07820000000000001</v>
+      <c r="AD526" s="1" t="n">
+        <v>0.07794</v>
       </c>
     </row>
     <row r="527">
@@ -48457,10 +50038,13 @@
         <v>0.01598</v>
       </c>
       <c r="AB527" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="AC527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="AC527" s="1" t="n">
-        <v>0.01594</v>
+      <c r="AD527" s="1" t="n">
+        <v>0.0159</v>
       </c>
     </row>
     <row r="528">
@@ -48548,10 +50132,13 @@
         <v>0.00409</v>
       </c>
       <c r="AB528" s="1" t="n">
+        <v>0.004062</v>
+      </c>
+      <c r="AC528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="AC528" s="1" t="n">
-        <v>0.00409</v>
+      <c r="AD528" s="1" t="n">
+        <v>0.004062</v>
       </c>
     </row>
     <row r="529">
@@ -48639,10 +50226,13 @@
         <v>0.003682</v>
       </c>
       <c r="AB529" s="1" t="n">
+        <v>0.003662</v>
+      </c>
+      <c r="AC529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="AC529" s="1" t="n">
-        <v>0.003665</v>
+      <c r="AD529" s="1" t="n">
+        <v>0.003662</v>
       </c>
     </row>
     <row r="530">
@@ -48730,10 +50320,13 @@
         <v>1.318</v>
       </c>
       <c r="AB530" s="1" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="AC530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="AC530" s="1" t="n">
-        <v>1.316</v>
+      <c r="AD530" s="1" t="n">
+        <v>1.313</v>
       </c>
     </row>
     <row r="531">
@@ -48821,10 +50414,13 @@
         <v>0.4858</v>
       </c>
       <c r="AB531" s="1" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="AC531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="AC531" s="1" t="n">
-        <v>0.4858</v>
+      <c r="AD531" s="1" t="n">
+        <v>0.4839</v>
       </c>
     </row>
     <row r="532">
@@ -48912,10 +50508,13 @@
         <v>0.03047</v>
       </c>
       <c r="AB532" s="1" t="n">
+        <v>0.03027</v>
+      </c>
+      <c r="AC532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="AC532" s="1" t="n">
-        <v>0.03041</v>
+      <c r="AD532" s="1" t="n">
+        <v>0.03027</v>
       </c>
     </row>
     <row r="533">
@@ -49003,10 +50602,13 @@
         <v>0.152</v>
       </c>
       <c r="AB533" s="1" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="AC533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="AC533" s="1" t="n">
-        <v>0.152</v>
+      <c r="AD533" s="1" t="n">
+        <v>0.1515</v>
       </c>
     </row>
     <row r="534">
@@ -49094,10 +50696,13 @@
         <v>0.05314</v>
       </c>
       <c r="AB534" s="1" t="n">
+        <v>0.05296</v>
+      </c>
+      <c r="AC534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="AC534" s="1" t="n">
-        <v>0.05314</v>
+      <c r="AD534" s="1" t="n">
+        <v>0.05296</v>
       </c>
     </row>
     <row r="535">
@@ -49185,10 +50790,13 @@
         <v>0.01471</v>
       </c>
       <c r="AB535" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="AC535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="AC535" s="1" t="n">
-        <v>0.01471</v>
+      <c r="AD535" s="1" t="n">
+        <v>0.01469</v>
       </c>
     </row>
     <row r="536">
@@ -49276,10 +50884,13 @@
         <v>0.0576</v>
       </c>
       <c r="AB536" s="1" t="n">
+        <v>0.05734</v>
+      </c>
+      <c r="AC536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="AC536" s="1" t="n">
-        <v>0.0576</v>
+      <c r="AD536" s="1" t="n">
+        <v>0.05734</v>
       </c>
     </row>
     <row r="537">
@@ -49367,10 +50978,13 @@
         <v>0.05459</v>
       </c>
       <c r="AB537" s="1" t="n">
+        <v>0.05452</v>
+      </c>
+      <c r="AC537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="AC537" s="1" t="n">
-        <v>0.05459</v>
+      <c r="AD537" s="1" t="n">
+        <v>0.05452</v>
       </c>
     </row>
     <row r="538">
@@ -49458,10 +51072,13 @@
         <v>0.1057</v>
       </c>
       <c r="AB538" s="1" t="n">
+        <v>0.1052</v>
+      </c>
+      <c r="AC538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="AC538" s="1" t="n">
-        <v>0.1057</v>
+      <c r="AD538" s="1" t="n">
+        <v>0.1052</v>
       </c>
     </row>
     <row r="539">
@@ -49549,10 +51166,13 @@
         <v>0.01265</v>
       </c>
       <c r="AB539" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AC539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="AC539" s="1" t="n">
-        <v>0.01265</v>
+      <c r="AD539" s="1" t="n">
+        <v>0.0126</v>
       </c>
     </row>
     <row r="540">
@@ -49640,10 +51260,13 @@
         <v>0.1719</v>
       </c>
       <c r="AB540" s="1" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="AC540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="AC540" s="1" t="n">
-        <v>0.1719</v>
+      <c r="AD540" s="1" t="n">
+        <v>0.1713</v>
       </c>
     </row>
     <row r="541">
@@ -49731,10 +51354,13 @@
         <v>0.1227</v>
       </c>
       <c r="AB541" s="1" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="AC541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="AC541" s="1" t="n">
-        <v>0.1225</v>
+      <c r="AD541" s="1" t="n">
+        <v>0.1222</v>
       </c>
     </row>
     <row r="542">
@@ -49822,10 +51448,13 @@
         <v>0.02474</v>
       </c>
       <c r="AB542" s="1" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="AC542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="AC542" s="1" t="n">
-        <v>0.02474</v>
+      <c r="AD542" s="1" t="n">
+        <v>0.02457</v>
       </c>
     </row>
     <row r="543">
@@ -49913,10 +51542,13 @@
         <v>0.05813</v>
       </c>
       <c r="AB543" s="1" t="n">
+        <v>0.05787</v>
+      </c>
+      <c r="AC543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="AC543" s="1" t="n">
-        <v>0.05813</v>
+      <c r="AD543" s="1" t="n">
+        <v>0.05787</v>
       </c>
     </row>
   </sheetData>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD543"/>
+  <dimension ref="A1:AE543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -447,8 +447,9 @@
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -594,10 +595,15 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>price_06:45</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -691,9 +697,12 @@
         <v>70636.60000000001</v>
       </c>
       <c r="AC2" s="1" t="n">
+        <v>70677.3</v>
+      </c>
+      <c r="AD2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="AD2" s="1" t="n">
+      <c r="AE2" s="1" t="n">
         <v>70636.60000000001</v>
       </c>
     </row>
@@ -785,9 +794,12 @@
         <v>2081.65</v>
       </c>
       <c r="AC3" s="1" t="n">
+        <v>2081.7</v>
+      </c>
+      <c r="AD3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="AD3" s="1" t="n">
+      <c r="AE3" s="1" t="n">
         <v>2081.65</v>
       </c>
     </row>
@@ -879,10 +891,13 @@
         <v>87.84</v>
       </c>
       <c r="AC4" s="1" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="AD4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="AD4" s="1" t="n">
-        <v>87.84</v>
+      <c r="AE4" s="1" t="n">
+        <v>87.79000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -973,9 +988,12 @@
         <v>3.791</v>
       </c>
       <c r="AC5" s="1" t="n">
+        <v>3.789</v>
+      </c>
+      <c r="AD5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AE5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -1067,9 +1085,12 @@
         <v>1.3913</v>
       </c>
       <c r="AC6" s="1" t="n">
+        <v>1.3915</v>
+      </c>
+      <c r="AD6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AE6" s="1" t="n">
         <v>1.3913</v>
       </c>
     </row>
@@ -1161,9 +1182,12 @@
         <v>0.09563000000000001</v>
       </c>
       <c r="AC7" s="1" t="n">
+        <v>0.09582</v>
+      </c>
+      <c r="AD7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AE7" s="1" t="n">
         <v>0.09563000000000001</v>
       </c>
     </row>
@@ -1255,9 +1279,12 @@
         <v>0.01259</v>
       </c>
       <c r="AC8" s="1" t="n">
+        <v>0.012917</v>
+      </c>
+      <c r="AD8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="AD8" s="1" t="n">
+      <c r="AE8" s="1" t="n">
         <v>0.01259</v>
       </c>
     </row>
@@ -1349,9 +1376,12 @@
         <v>654.74</v>
       </c>
       <c r="AC9" s="1" t="n">
+        <v>654.84</v>
+      </c>
+      <c r="AD9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="AD9" s="1" t="n">
+      <c r="AE9" s="1" t="n">
         <v>654.74</v>
       </c>
     </row>
@@ -1443,9 +1473,12 @@
         <v>20.014</v>
       </c>
       <c r="AC10" s="1" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="AD10" s="1" t="n">
         <v>20.464</v>
       </c>
-      <c r="AD10" s="1" t="n">
+      <c r="AE10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1537,10 +1570,13 @@
         <v>0.0033626</v>
       </c>
       <c r="AC11" s="1" t="n">
+        <v>0.0033624</v>
+      </c>
+      <c r="AD11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="AD11" s="1" t="n">
-        <v>0.0033626</v>
+      <c r="AE11" s="1" t="n">
+        <v>0.0033624</v>
       </c>
     </row>
     <row r="12">
@@ -1631,9 +1667,12 @@
         <v>36.098</v>
       </c>
       <c r="AC12" s="1" t="n">
+        <v>36.204</v>
+      </c>
+      <c r="AD12" s="1" t="n">
         <v>36.869</v>
       </c>
-      <c r="AD12" s="1" t="n">
+      <c r="AE12" s="1" t="n">
         <v>36.098</v>
       </c>
     </row>
@@ -1725,9 +1764,12 @@
         <v>206.94</v>
       </c>
       <c r="AC13" s="1" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AD13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="AD13" s="1" t="n">
+      <c r="AE13" s="1" t="n">
         <v>206.94</v>
       </c>
     </row>
@@ -1819,9 +1861,12 @@
         <v>0.0011368</v>
       </c>
       <c r="AC14" s="1" t="n">
+        <v>0.0011362</v>
+      </c>
+      <c r="AD14" s="1" t="n">
         <v>0.0011412</v>
       </c>
-      <c r="AD14" s="1" t="n">
+      <c r="AE14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1913,9 +1958,12 @@
         <v>0.3193</v>
       </c>
       <c r="AC15" s="1" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AD15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="AD15" s="1" t="n">
+      <c r="AE15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -2007,9 +2055,12 @@
         <v>230.49</v>
       </c>
       <c r="AC16" s="1" t="n">
+        <v>232.61</v>
+      </c>
+      <c r="AD16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="AD16" s="1" t="n">
+      <c r="AE16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -2101,9 +2152,12 @@
         <v>0.9883</v>
       </c>
       <c r="AC17" s="1" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="AD17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="AD17" s="1" t="n">
+      <c r="AE17" s="1" t="n">
         <v>0.9883</v>
       </c>
     </row>
@@ -2195,10 +2249,13 @@
         <v>0.2641</v>
       </c>
       <c r="AC18" s="1" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AD18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="AD18" s="1" t="n">
-        <v>0.2641</v>
+      <c r="AE18" s="1" t="n">
+        <v>0.264</v>
       </c>
     </row>
     <row r="19">
@@ -2289,10 +2346,13 @@
         <v>9.683999999999999</v>
       </c>
       <c r="AC19" s="1" t="n">
+        <v>9.682</v>
+      </c>
+      <c r="AD19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="AD19" s="1" t="n">
-        <v>9.683999999999999</v>
+      <c r="AE19" s="1" t="n">
+        <v>9.682</v>
       </c>
     </row>
     <row r="20">
@@ -2383,9 +2443,12 @@
         <v>5022.64</v>
       </c>
       <c r="AC20" s="1" t="n">
+        <v>5023.72</v>
+      </c>
+      <c r="AD20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="AD20" s="1" t="n">
+      <c r="AE20" s="1" t="n">
         <v>5012.13</v>
       </c>
     </row>
@@ -2477,10 +2540,13 @@
         <v>460.07</v>
       </c>
       <c r="AC21" s="1" t="n">
+        <v>459.74</v>
+      </c>
+      <c r="AD21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="AD21" s="1" t="n">
-        <v>460.07</v>
+      <c r="AE21" s="1" t="n">
+        <v>459.74</v>
       </c>
     </row>
     <row r="22">
@@ -2571,9 +2637,12 @@
         <v>1.3864</v>
       </c>
       <c r="AC22" s="1" t="n">
+        <v>1.3744</v>
+      </c>
+      <c r="AD22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="AD22" s="1" t="n">
+      <c r="AE22" s="1" t="n">
         <v>1.3686</v>
       </c>
     </row>
@@ -2665,9 +2734,12 @@
         <v>1.0386</v>
       </c>
       <c r="AC23" s="1" t="n">
+        <v>1.0653</v>
+      </c>
+      <c r="AD23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="AD23" s="1" t="n">
+      <c r="AE23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2759,9 +2831,12 @@
         <v>1.328</v>
       </c>
       <c r="AC24" s="1" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="AD24" s="1" t="n">
+      <c r="AE24" s="1" t="n">
         <v>1.328</v>
       </c>
     </row>
@@ -2853,10 +2928,13 @@
         <v>9.044</v>
       </c>
       <c r="AC25" s="1" t="n">
+        <v>9.034000000000001</v>
+      </c>
+      <c r="AD25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="AD25" s="1" t="n">
-        <v>9.044</v>
+      <c r="AE25" s="1" t="n">
+        <v>9.034000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2947,9 +3025,12 @@
         <v>0.3587</v>
       </c>
       <c r="AC26" s="1" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="AD26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="AD26" s="1" t="n">
+      <c r="AE26" s="1" t="n">
         <v>0.3578</v>
       </c>
     </row>
@@ -3041,9 +3122,12 @@
         <v>0.862</v>
       </c>
       <c r="AC27" s="1" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AD27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="AD27" s="1" t="n">
+      <c r="AE27" s="1" t="n">
         <v>0.862</v>
       </c>
     </row>
@@ -3135,10 +3219,13 @@
         <v>1.784</v>
       </c>
       <c r="AC28" s="1" t="n">
+        <v>1.782</v>
+      </c>
+      <c r="AD28" s="1" t="n">
         <v>1.863</v>
       </c>
-      <c r="AD28" s="1" t="n">
-        <v>1.784</v>
+      <c r="AE28" s="1" t="n">
+        <v>1.782</v>
       </c>
     </row>
     <row r="29">
@@ -3229,9 +3316,12 @@
         <v>0.1078</v>
       </c>
       <c r="AC29" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="AD29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="AD29" s="1" t="n">
+      <c r="AE29" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -3323,10 +3413,13 @@
         <v>0.001984</v>
       </c>
       <c r="AC30" s="1" t="n">
+        <v>0.001982</v>
+      </c>
+      <c r="AD30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="AD30" s="1" t="n">
-        <v>0.001984</v>
+      <c r="AE30" s="1" t="n">
+        <v>0.001982</v>
       </c>
     </row>
     <row r="31">
@@ -3417,9 +3510,12 @@
         <v>1.449</v>
       </c>
       <c r="AC31" s="1" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="AD31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="AD31" s="1" t="n">
+      <c r="AE31" s="1" t="n">
         <v>1.449</v>
       </c>
     </row>
@@ -3511,9 +3607,12 @@
         <v>0.176</v>
       </c>
       <c r="AC32" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="AD32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="AD32" s="1" t="n">
+      <c r="AE32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -3605,9 +3704,12 @@
         <v>0.1035</v>
       </c>
       <c r="AC33" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="AD33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="AD33" s="1" t="n">
+      <c r="AE33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -3699,9 +3801,12 @@
         <v>111.56</v>
       </c>
       <c r="AC34" s="1" t="n">
+        <v>111.59</v>
+      </c>
+      <c r="AD34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="AD34" s="1" t="n">
+      <c r="AE34" s="1" t="n">
         <v>111.56</v>
       </c>
     </row>
@@ -3793,10 +3898,13 @@
         <v>6.424</v>
       </c>
       <c r="AC35" s="1" t="n">
+        <v>6.376</v>
+      </c>
+      <c r="AD35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="AD35" s="1" t="n">
-        <v>6.424</v>
+      <c r="AE35" s="1" t="n">
+        <v>6.376</v>
       </c>
     </row>
     <row r="36">
@@ -3887,9 +3995,12 @@
         <v>0.018764</v>
       </c>
       <c r="AC36" s="1" t="n">
+        <v>0.018436</v>
+      </c>
+      <c r="AD36" s="1" t="n">
         <v>0.018773</v>
       </c>
-      <c r="AD36" s="1" t="n">
+      <c r="AE36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -3981,9 +4092,12 @@
         <v>0.3551</v>
       </c>
       <c r="AC37" s="1" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AD37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="AD37" s="1" t="n">
+      <c r="AE37" s="1" t="n">
         <v>0.3551</v>
       </c>
     </row>
@@ -4075,10 +4189,13 @@
         <v>55.17</v>
       </c>
       <c r="AC38" s="1" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="AD38" s="1" t="n">
         <v>55.92</v>
       </c>
-      <c r="AD38" s="1" t="n">
-        <v>55.17</v>
+      <c r="AE38" s="1" t="n">
+        <v>55.14</v>
       </c>
     </row>
     <row r="39">
@@ -4169,9 +4286,12 @@
         <v>0.59502</v>
       </c>
       <c r="AC39" s="1" t="n">
+        <v>0.5873699999999999</v>
+      </c>
+      <c r="AD39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="AD39" s="1" t="n">
+      <c r="AE39" s="1" t="n">
         <v>0.5717</v>
       </c>
     </row>
@@ -4263,9 +4383,12 @@
         <v>3.986</v>
       </c>
       <c r="AC40" s="1" t="n">
+        <v>3.989</v>
+      </c>
+      <c r="AD40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="AD40" s="1" t="n">
+      <c r="AE40" s="1" t="n">
         <v>3.986</v>
       </c>
     </row>
@@ -4357,10 +4480,13 @@
         <v>0.04676</v>
       </c>
       <c r="AC41" s="1" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="AD41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="AD41" s="1" t="n">
-        <v>0.04676</v>
+      <c r="AE41" s="1" t="n">
+        <v>0.04635</v>
       </c>
     </row>
     <row r="42">
@@ -4451,9 +4577,12 @@
         <v>0.6936</v>
       </c>
       <c r="AC42" s="1" t="n">
+        <v>0.6936</v>
+      </c>
+      <c r="AD42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="AD42" s="1" t="n">
+      <c r="AE42" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -4545,9 +4674,12 @@
         <v>0.22597</v>
       </c>
       <c r="AC43" s="1" t="n">
+        <v>0.22693</v>
+      </c>
+      <c r="AD43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="AD43" s="1" t="n">
+      <c r="AE43" s="1" t="n">
         <v>0.22597</v>
       </c>
     </row>
@@ -4639,9 +4771,12 @@
         <v>0.35953</v>
       </c>
       <c r="AC44" s="1" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AD44" s="1" t="n">
         <v>0.36291</v>
       </c>
-      <c r="AD44" s="1" t="n">
+      <c r="AE44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -4733,9 +4868,12 @@
         <v>0.1657</v>
       </c>
       <c r="AC45" s="1" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="AD45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="AD45" s="1" t="n">
+      <c r="AE45" s="1" t="n">
         <v>0.1657</v>
       </c>
     </row>
@@ -4827,10 +4965,13 @@
         <v>0.0255</v>
       </c>
       <c r="AC46" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="AD46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="AD46" s="1" t="n">
-        <v>0.0255</v>
+      <c r="AE46" s="1" t="n">
+        <v>0.0254</v>
       </c>
     </row>
     <row r="47">
@@ -4921,9 +5062,12 @@
         <v>0.005897</v>
       </c>
       <c r="AC47" s="1" t="n">
+        <v>0.005902</v>
+      </c>
+      <c r="AD47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="AD47" s="1" t="n">
+      <c r="AE47" s="1" t="n">
         <v>0.005897</v>
       </c>
     </row>
@@ -5015,9 +5159,12 @@
         <v>0.007228</v>
       </c>
       <c r="AC48" s="1" t="n">
+        <v>0.007232</v>
+      </c>
+      <c r="AD48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="AD48" s="1" t="n">
+      <c r="AE48" s="1" t="n">
         <v>0.007228</v>
       </c>
     </row>
@@ -5109,9 +5256,12 @@
         <v>0.108</v>
       </c>
       <c r="AC49" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="AD49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="AD49" s="1" t="n">
+      <c r="AE49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -5203,9 +5353,12 @@
         <v>0.04046</v>
       </c>
       <c r="AC50" s="1" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="AD50" s="1" t="n">
         <v>0.04222</v>
       </c>
-      <c r="AD50" s="1" t="n">
+      <c r="AE50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -5297,10 +5450,13 @@
         <v>0.1583</v>
       </c>
       <c r="AC51" s="1" t="n">
+        <v>0.1581</v>
+      </c>
+      <c r="AD51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="AD51" s="1" t="n">
-        <v>0.1583</v>
+      <c r="AE51" s="1" t="n">
+        <v>0.1581</v>
       </c>
     </row>
     <row r="52">
@@ -5391,9 +5547,12 @@
         <v>0.00349</v>
       </c>
       <c r="AC52" s="1" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="AD52" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="AD52" s="1" t="n">
+      <c r="AE52" s="1" t="n">
         <v>0.00349</v>
       </c>
     </row>
@@ -5485,10 +5644,13 @@
         <v>2.602</v>
       </c>
       <c r="AC53" s="1" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="AD53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="AD53" s="1" t="n">
-        <v>2.602</v>
+      <c r="AE53" s="1" t="n">
+        <v>2.594</v>
       </c>
     </row>
     <row r="54">
@@ -5579,9 +5741,12 @@
         <v>0.006086</v>
       </c>
       <c r="AC54" s="1" t="n">
+        <v>0.006102</v>
+      </c>
+      <c r="AD54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="AD54" s="1" t="n">
+      <c r="AE54" s="1" t="n">
         <v>0.006086</v>
       </c>
     </row>
@@ -5673,9 +5838,12 @@
         <v>0.02764</v>
       </c>
       <c r="AC55" s="1" t="n">
+        <v>0.02805</v>
+      </c>
+      <c r="AD55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="AD55" s="1" t="n">
+      <c r="AE55" s="1" t="n">
         <v>0.02738</v>
       </c>
     </row>
@@ -5767,9 +5935,12 @@
         <v>0.7159</v>
       </c>
       <c r="AC56" s="1" t="n">
+        <v>0.7191</v>
+      </c>
+      <c r="AD56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="AD56" s="1" t="n">
+      <c r="AE56" s="1" t="n">
         <v>0.7159</v>
       </c>
     </row>
@@ -5861,9 +6032,12 @@
         <v>0.1018</v>
       </c>
       <c r="AC57" s="1" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="AD57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="AD57" s="1" t="n">
+      <c r="AE57" s="1" t="n">
         <v>0.1018</v>
       </c>
     </row>
@@ -5955,9 +6129,12 @@
         <v>0.9211</v>
       </c>
       <c r="AC58" s="1" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="AD58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="AD58" s="1" t="n">
+      <c r="AE58" s="1" t="n">
         <v>0.9211</v>
       </c>
     </row>
@@ -6049,9 +6226,12 @@
         <v>0.08397</v>
       </c>
       <c r="AC59" s="1" t="n">
+        <v>0.08382000000000001</v>
+      </c>
+      <c r="AD59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="AD59" s="1" t="n">
+      <c r="AE59" s="1" t="n">
         <v>0.08294</v>
       </c>
     </row>
@@ -6143,10 +6323,13 @@
         <v>0.07053</v>
       </c>
       <c r="AC60" s="1" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="AD60" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="AD60" s="1" t="n">
-        <v>0.06900000000000001</v>
+      <c r="AE60" s="1" t="n">
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -6237,9 +6420,12 @@
         <v>0.05349</v>
       </c>
       <c r="AC61" s="1" t="n">
+        <v>0.05362</v>
+      </c>
+      <c r="AD61" s="1" t="n">
         <v>0.05539</v>
       </c>
-      <c r="AD61" s="1" t="n">
+      <c r="AE61" s="1" t="n">
         <v>0.05349</v>
       </c>
     </row>
@@ -6331,9 +6517,12 @@
         <v>0.01063</v>
       </c>
       <c r="AC62" s="1" t="n">
+        <v>0.010627</v>
+      </c>
+      <c r="AD62" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="AD62" s="1" t="n">
+      <c r="AE62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -6425,9 +6614,12 @@
         <v>0.2925</v>
       </c>
       <c r="AC63" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AD63" s="1" t="n">
         <v>0.29275</v>
       </c>
-      <c r="AD63" s="1" t="n">
+      <c r="AE63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -6519,10 +6711,13 @@
         <v>0.06677</v>
       </c>
       <c r="AC64" s="1" t="n">
+        <v>0.06598</v>
+      </c>
+      <c r="AD64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="AD64" s="1" t="n">
-        <v>0.06677</v>
+      <c r="AE64" s="1" t="n">
+        <v>0.06598</v>
       </c>
     </row>
     <row r="65">
@@ -6613,9 +6808,12 @@
         <v>0.3022</v>
       </c>
       <c r="AC65" s="1" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AD65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="AD65" s="1" t="n">
+      <c r="AE65" s="1" t="n">
         <v>0.3022</v>
       </c>
     </row>
@@ -6707,9 +6905,12 @@
         <v>0.164</v>
       </c>
       <c r="AC66" s="1" t="n">
+        <v>0.16315</v>
+      </c>
+      <c r="AD66" s="1" t="n">
         <v>0.16587</v>
       </c>
-      <c r="AD66" s="1" t="n">
+      <c r="AE66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -6801,9 +7002,12 @@
         <v>0.12027</v>
       </c>
       <c r="AC67" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="AD67" s="1" t="n">
         <v>0.12035</v>
       </c>
-      <c r="AD67" s="1" t="n">
+      <c r="AE67" s="1" t="n">
         <v>0.1191</v>
       </c>
     </row>
@@ -6895,10 +7099,13 @@
         <v>0.09465</v>
       </c>
       <c r="AC68" s="1" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="AD68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="AD68" s="1" t="n">
-        <v>0.09465</v>
+      <c r="AE68" s="1" t="n">
+        <v>0.0945</v>
       </c>
     </row>
     <row r="69">
@@ -6989,9 +7196,12 @@
         <v>0.1223</v>
       </c>
       <c r="AC69" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="AD69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="AD69" s="1" t="n">
+      <c r="AE69" s="1" t="n">
         <v>0.1223</v>
       </c>
     </row>
@@ -7083,10 +7293,13 @@
         <v>8.433</v>
       </c>
       <c r="AC70" s="1" t="n">
+        <v>8.423</v>
+      </c>
+      <c r="AD70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="AD70" s="1" t="n">
-        <v>8.433</v>
+      <c r="AE70" s="1" t="n">
+        <v>8.423</v>
       </c>
     </row>
     <row r="71">
@@ -7177,9 +7390,12 @@
         <v>0.234</v>
       </c>
       <c r="AC71" s="1" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AD71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="AD71" s="1" t="n">
+      <c r="AE71" s="1" t="n">
         <v>0.234</v>
       </c>
     </row>
@@ -7271,10 +7487,13 @@
         <v>0.04904</v>
       </c>
       <c r="AC72" s="1" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="AD72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="AD72" s="1" t="n">
-        <v>0.04904</v>
+      <c r="AE72" s="1" t="n">
+        <v>0.04899</v>
       </c>
     </row>
     <row r="73">
@@ -7365,9 +7584,12 @@
         <v>0.05019</v>
       </c>
       <c r="AC73" s="1" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="AD73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="AD73" s="1" t="n">
+      <c r="AE73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -7459,9 +7681,12 @@
         <v>0.1212</v>
       </c>
       <c r="AC74" s="1" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="AD74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="AD74" s="1" t="n">
+      <c r="AE74" s="1" t="n">
         <v>0.1212</v>
       </c>
     </row>
@@ -7553,9 +7778,12 @@
         <v>0.04658</v>
       </c>
       <c r="AC75" s="1" t="n">
+        <v>0.04658</v>
+      </c>
+      <c r="AD75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="AD75" s="1" t="n">
+      <c r="AE75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -7647,10 +7875,13 @@
         <v>0.06578000000000001</v>
       </c>
       <c r="AC76" s="1" t="n">
+        <v>0.06574000000000001</v>
+      </c>
+      <c r="AD76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="AD76" s="1" t="n">
-        <v>0.06578000000000001</v>
+      <c r="AE76" s="1" t="n">
+        <v>0.06574000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7741,9 +7972,12 @@
         <v>0.12686</v>
       </c>
       <c r="AC77" s="1" t="n">
+        <v>0.12951</v>
+      </c>
+      <c r="AD77" s="1" t="n">
         <v>0.13727</v>
       </c>
-      <c r="AD77" s="1" t="n">
+      <c r="AE77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -7835,9 +8069,12 @@
         <v>0.1587</v>
       </c>
       <c r="AC78" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AD78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="AD78" s="1" t="n">
+      <c r="AE78" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -7929,10 +8166,13 @@
         <v>0.02678</v>
       </c>
       <c r="AC79" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="AD79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="AD79" s="1" t="n">
-        <v>0.02678</v>
+      <c r="AE79" s="1" t="n">
+        <v>0.02677</v>
       </c>
     </row>
     <row r="80">
@@ -8023,9 +8263,12 @@
         <v>354.21</v>
       </c>
       <c r="AC80" s="1" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="AD80" s="1" t="n">
         <v>362.68</v>
       </c>
-      <c r="AD80" s="1" t="n">
+      <c r="AE80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -8117,9 +8360,12 @@
         <v>6.949e-05</v>
       </c>
       <c r="AC81" s="1" t="n">
+        <v>6.959e-05</v>
+      </c>
+      <c r="AD81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="AD81" s="1" t="n">
+      <c r="AE81" s="1" t="n">
         <v>6.949e-05</v>
       </c>
     </row>
@@ -8211,9 +8457,12 @@
         <v>0.2614</v>
       </c>
       <c r="AC82" s="1" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="AD82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="AD82" s="1" t="n">
+      <c r="AE82" s="1" t="n">
         <v>0.2614</v>
       </c>
     </row>
@@ -8305,10 +8554,13 @@
         <v>1.1058</v>
       </c>
       <c r="AC83" s="1" t="n">
+        <v>1.1031</v>
+      </c>
+      <c r="AD83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="AD83" s="1" t="n">
-        <v>1.1054</v>
+      <c r="AE83" s="1" t="n">
+        <v>1.1031</v>
       </c>
     </row>
     <row r="84">
@@ -8399,10 +8651,13 @@
         <v>0.3449</v>
       </c>
       <c r="AC84" s="1" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AD84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="AD84" s="1" t="n">
-        <v>0.3449</v>
+      <c r="AE84" s="1" t="n">
+        <v>0.3446</v>
       </c>
     </row>
     <row r="85">
@@ -8493,10 +8748,13 @@
         <v>1.9239</v>
       </c>
       <c r="AC85" s="1" t="n">
+        <v>1.9237</v>
+      </c>
+      <c r="AD85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="AD85" s="1" t="n">
-        <v>1.9239</v>
+      <c r="AE85" s="1" t="n">
+        <v>1.9237</v>
       </c>
     </row>
     <row r="86">
@@ -8587,9 +8845,12 @@
         <v>1.3065</v>
       </c>
       <c r="AC86" s="1" t="n">
+        <v>1.3084</v>
+      </c>
+      <c r="AD86" s="1" t="n">
         <v>1.3218</v>
       </c>
-      <c r="AD86" s="1" t="n">
+      <c r="AE86" s="1" t="n">
         <v>1.3065</v>
       </c>
     </row>
@@ -8681,10 +8942,13 @@
         <v>32.14</v>
       </c>
       <c r="AC87" s="1" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="AD87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="AD87" s="1" t="n">
-        <v>32.14</v>
+      <c r="AE87" s="1" t="n">
+        <v>32.12</v>
       </c>
     </row>
     <row r="88">
@@ -8775,9 +9039,12 @@
         <v>0.009429999999999999</v>
       </c>
       <c r="AC88" s="1" t="n">
+        <v>0.00949</v>
+      </c>
+      <c r="AD88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="AD88" s="1" t="n">
+      <c r="AE88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -8869,10 +9136,13 @@
         <v>0.01748</v>
       </c>
       <c r="AC89" s="1" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="AD89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="AD89" s="1" t="n">
-        <v>0.01748</v>
+      <c r="AE89" s="1" t="n">
+        <v>0.0174</v>
       </c>
     </row>
     <row r="90">
@@ -8963,10 +9233,13 @@
         <v>0.0333</v>
       </c>
       <c r="AC90" s="1" t="n">
+        <v>0.03299</v>
+      </c>
+      <c r="AD90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="AD90" s="1" t="n">
-        <v>0.0333</v>
+      <c r="AE90" s="1" t="n">
+        <v>0.03299</v>
       </c>
     </row>
     <row r="91">
@@ -9057,10 +9330,13 @@
         <v>0.01144</v>
       </c>
       <c r="AC91" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="AD91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AD91" s="1" t="n">
-        <v>0.01144</v>
+      <c r="AE91" s="1" t="n">
+        <v>0.0114</v>
       </c>
     </row>
     <row r="92">
@@ -9151,9 +9427,12 @@
         <v>3.069</v>
       </c>
       <c r="AC92" s="1" t="n">
+        <v>3.069</v>
+      </c>
+      <c r="AD92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="AD92" s="1" t="n">
+      <c r="AE92" s="1" t="n">
         <v>3.069</v>
       </c>
     </row>
@@ -9245,9 +9524,12 @@
         <v>0.005523</v>
       </c>
       <c r="AC93" s="1" t="n">
+        <v>0.005541</v>
+      </c>
+      <c r="AD93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="AD93" s="1" t="n">
+      <c r="AE93" s="1" t="n">
         <v>0.005523</v>
       </c>
     </row>
@@ -9339,9 +9621,12 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="AC94" s="1" t="n">
+        <v>0.0929</v>
+      </c>
+      <c r="AD94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="AD94" s="1" t="n">
+      <c r="AE94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -9433,9 +9718,12 @@
         <v>0.6528</v>
       </c>
       <c r="AC95" s="1" t="n">
-        <v>0.6528</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="AD95" s="1" t="n">
+        <v>0.6637999999999999</v>
+      </c>
+      <c r="AE95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -9527,9 +9815,12 @@
         <v>1.22e-05</v>
       </c>
       <c r="AC96" s="1" t="n">
+        <v>1.23e-05</v>
+      </c>
+      <c r="AD96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="AD96" s="1" t="n">
+      <c r="AE96" s="1" t="n">
         <v>1.22e-05</v>
       </c>
     </row>
@@ -9621,9 +9912,12 @@
         <v>1.097</v>
       </c>
       <c r="AC97" s="1" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="AD97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD97" s="1" t="n">
+      <c r="AE97" s="1" t="n">
         <v>1.097</v>
       </c>
     </row>
@@ -9715,9 +10009,12 @@
         <v>0.24367</v>
       </c>
       <c r="AC98" s="1" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="AD98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="AD98" s="1" t="n">
+      <c r="AE98" s="1" t="n">
         <v>0.24367</v>
       </c>
     </row>
@@ -9809,9 +10106,12 @@
         <v>1.142</v>
       </c>
       <c r="AC99" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="AD99" s="1" t="n">
         <v>1.157</v>
       </c>
-      <c r="AD99" s="1" t="n">
+      <c r="AE99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -9903,9 +10203,12 @@
         <v>1.843</v>
       </c>
       <c r="AC100" s="1" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="AD100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="AD100" s="1" t="n">
+      <c r="AE100" s="1" t="n">
         <v>1.843</v>
       </c>
     </row>
@@ -9997,10 +10300,13 @@
         <v>0.01551</v>
       </c>
       <c r="AC101" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="AD101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="AD101" s="1" t="n">
-        <v>0.01551</v>
+      <c r="AE101" s="1" t="n">
+        <v>0.01543</v>
       </c>
     </row>
     <row r="102">
@@ -10091,9 +10397,12 @@
         <v>0.10088</v>
       </c>
       <c r="AC102" s="1" t="n">
+        <v>0.10123</v>
+      </c>
+      <c r="AD102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="AD102" s="1" t="n">
+      <c r="AE102" s="1" t="n">
         <v>0.10062</v>
       </c>
     </row>
@@ -10185,10 +10494,13 @@
         <v>0.0005886</v>
       </c>
       <c r="AC103" s="1" t="n">
+        <v>0.000588</v>
+      </c>
+      <c r="AD103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="AD103" s="1" t="n">
-        <v>0.0005886</v>
+      <c r="AE103" s="1" t="n">
+        <v>0.000588</v>
       </c>
     </row>
     <row r="104">
@@ -10279,9 +10591,12 @@
         <v>0.0005729</v>
       </c>
       <c r="AC104" s="1" t="n">
+        <v>0.0005735</v>
+      </c>
+      <c r="AD104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="AD104" s="1" t="n">
+      <c r="AE104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -10373,9 +10688,12 @@
         <v>0.003178</v>
       </c>
       <c r="AC105" s="1" t="n">
+        <v>0.003181</v>
+      </c>
+      <c r="AD105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="AD105" s="1" t="n">
+      <c r="AE105" s="1" t="n">
         <v>0.003178</v>
       </c>
     </row>
@@ -10467,10 +10785,13 @@
         <v>2.509</v>
       </c>
       <c r="AC106" s="1" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="AD106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="AD106" s="1" t="n">
-        <v>2.509</v>
+      <c r="AE106" s="1" t="n">
+        <v>2.507</v>
       </c>
     </row>
     <row r="107">
@@ -10561,9 +10882,12 @@
         <v>0.1643</v>
       </c>
       <c r="AC107" s="1" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="AD107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="AD107" s="1" t="n">
+      <c r="AE107" s="1" t="n">
         <v>0.1643</v>
       </c>
     </row>
@@ -10655,10 +10979,13 @@
         <v>0.09492</v>
       </c>
       <c r="AC108" s="1" t="n">
+        <v>0.09481000000000001</v>
+      </c>
+      <c r="AD108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="AD108" s="1" t="n">
-        <v>0.09492</v>
+      <c r="AE108" s="1" t="n">
+        <v>0.09481000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -10749,10 +11076,13 @@
         <v>0.02205</v>
       </c>
       <c r="AC109" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="AD109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="AD109" s="1" t="n">
-        <v>0.02202</v>
+      <c r="AE109" s="1" t="n">
+        <v>0.02201</v>
       </c>
     </row>
     <row r="110">
@@ -10843,9 +11173,12 @@
         <v>0.2838</v>
       </c>
       <c r="AC110" s="1" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="AD110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="AD110" s="1" t="n">
+      <c r="AE110" s="1" t="n">
         <v>0.2838</v>
       </c>
     </row>
@@ -10937,10 +11270,13 @@
         <v>0.05629</v>
       </c>
       <c r="AC111" s="1" t="n">
+        <v>0.05614</v>
+      </c>
+      <c r="AD111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="AD111" s="1" t="n">
-        <v>0.05629</v>
+      <c r="AE111" s="1" t="n">
+        <v>0.05614</v>
       </c>
     </row>
     <row r="112">
@@ -11031,9 +11367,12 @@
         <v>0.2968</v>
       </c>
       <c r="AC112" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AD112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="AD112" s="1" t="n">
+      <c r="AE112" s="1" t="n">
         <v>0.2968</v>
       </c>
     </row>
@@ -11125,10 +11464,13 @@
         <v>18.43</v>
       </c>
       <c r="AC113" s="1" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AD113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="AD113" s="1" t="n">
-        <v>18.43</v>
+      <c r="AE113" s="1" t="n">
+        <v>18.41</v>
       </c>
     </row>
     <row r="114">
@@ -11219,9 +11561,12 @@
         <v>0.12683</v>
       </c>
       <c r="AC114" s="1" t="n">
+        <v>0.12712</v>
+      </c>
+      <c r="AD114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="AD114" s="1" t="n">
+      <c r="AE114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -11313,9 +11658,12 @@
         <v>0.01596</v>
       </c>
       <c r="AC115" s="1" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="AD115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="AD115" s="1" t="n">
+      <c r="AE115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -11407,9 +11755,12 @@
         <v>0.08352999999999999</v>
       </c>
       <c r="AC116" s="1" t="n">
+        <v>0.08357000000000001</v>
+      </c>
+      <c r="AD116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="AD116" s="1" t="n">
+      <c r="AE116" s="1" t="n">
         <v>0.08352999999999999</v>
       </c>
     </row>
@@ -11501,9 +11852,12 @@
         <v>0.046527</v>
       </c>
       <c r="AC117" s="1" t="n">
+        <v>0.046805</v>
+      </c>
+      <c r="AD117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="AD117" s="1" t="n">
+      <c r="AE117" s="1" t="n">
         <v>0.046106</v>
       </c>
     </row>
@@ -11595,10 +11949,13 @@
         <v>0.04651</v>
       </c>
       <c r="AC118" s="1" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="AD118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="AD118" s="1" t="n">
-        <v>0.04651</v>
+      <c r="AE118" s="1" t="n">
+        <v>0.0465</v>
       </c>
     </row>
     <row r="119">
@@ -11689,9 +12046,12 @@
         <v>0.04003</v>
       </c>
       <c r="AC119" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="AD119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="AD119" s="1" t="n">
+      <c r="AE119" s="1" t="n">
         <v>0.03993</v>
       </c>
     </row>
@@ -11783,9 +12143,12 @@
         <v>0.14564</v>
       </c>
       <c r="AC120" s="1" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="AD120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="AD120" s="1" t="n">
+      <c r="AE120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -11877,10 +12240,13 @@
         <v>0.1234</v>
       </c>
       <c r="AC121" s="1" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="AD121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="AD121" s="1" t="n">
-        <v>0.1234</v>
+      <c r="AE121" s="1" t="n">
+        <v>0.1232</v>
       </c>
     </row>
     <row r="122">
@@ -11971,9 +12337,12 @@
         <v>1.809</v>
       </c>
       <c r="AC122" s="1" t="n">
+        <v>1.813</v>
+      </c>
+      <c r="AD122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="AD122" s="1" t="n">
+      <c r="AE122" s="1" t="n">
         <v>1.809</v>
       </c>
     </row>
@@ -12065,9 +12434,12 @@
         <v>0.02973</v>
       </c>
       <c r="AC123" s="1" t="n">
+        <v>0.02978</v>
+      </c>
+      <c r="AD123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="AD123" s="1" t="n">
+      <c r="AE123" s="1" t="n">
         <v>0.02973</v>
       </c>
     </row>
@@ -12159,9 +12531,12 @@
         <v>0.13125</v>
       </c>
       <c r="AC124" s="1" t="n">
+        <v>0.13176</v>
+      </c>
+      <c r="AD124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="AD124" s="1" t="n">
+      <c r="AE124" s="1" t="n">
         <v>0.13125</v>
       </c>
     </row>
@@ -12253,9 +12628,12 @@
         <v>0.04036</v>
       </c>
       <c r="AC125" s="1" t="n">
+        <v>0.04047</v>
+      </c>
+      <c r="AD125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="AD125" s="1" t="n">
+      <c r="AE125" s="1" t="n">
         <v>0.04036</v>
       </c>
     </row>
@@ -12347,9 +12725,12 @@
         <v>0.1133</v>
       </c>
       <c r="AC126" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="AD126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="AD126" s="1" t="n">
+      <c r="AE126" s="1" t="n">
         <v>0.1133</v>
       </c>
     </row>
@@ -12441,9 +12822,12 @@
         <v>0.538</v>
       </c>
       <c r="AC127" s="1" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="AD127" s="1" t="n">
         <v>0.5446</v>
       </c>
-      <c r="AD127" s="1" t="n">
+      <c r="AE127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -12535,9 +12919,12 @@
         <v>0.03789</v>
       </c>
       <c r="AC128" s="1" t="n">
+        <v>0.03797</v>
+      </c>
+      <c r="AD128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="AD128" s="1" t="n">
+      <c r="AE128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -12629,9 +13016,12 @@
         <v>0.789</v>
       </c>
       <c r="AC129" s="1" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="AD129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="AD129" s="1" t="n">
+      <c r="AE129" s="1" t="n">
         <v>0.789</v>
       </c>
     </row>
@@ -12723,9 +13113,12 @@
         <v>0.03421</v>
       </c>
       <c r="AC130" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="AD130" s="1" t="n">
         <v>0.03463</v>
       </c>
-      <c r="AD130" s="1" t="n">
+      <c r="AE130" s="1" t="n">
         <v>0.03421</v>
       </c>
     </row>
@@ -12817,9 +13210,12 @@
         <v>0.421</v>
       </c>
       <c r="AC131" s="1" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="AD131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="AD131" s="1" t="n">
+      <c r="AE131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -12911,10 +13307,13 @@
         <v>0.04305</v>
       </c>
       <c r="AC132" s="1" t="n">
+        <v>0.04252</v>
+      </c>
+      <c r="AD132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="AD132" s="1" t="n">
-        <v>0.04296</v>
+      <c r="AE132" s="1" t="n">
+        <v>0.04252</v>
       </c>
     </row>
     <row r="133">
@@ -13005,10 +13404,13 @@
         <v>1.2712</v>
       </c>
       <c r="AC133" s="1" t="n">
+        <v>1.2698</v>
+      </c>
+      <c r="AD133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="AD133" s="1" t="n">
-        <v>1.2712</v>
+      <c r="AE133" s="1" t="n">
+        <v>1.2698</v>
       </c>
     </row>
     <row r="134">
@@ -13099,9 +13501,12 @@
         <v>0.02171</v>
       </c>
       <c r="AC134" s="1" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="AD134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="AD134" s="1" t="n">
+      <c r="AE134" s="1" t="n">
         <v>0.02171</v>
       </c>
     </row>
@@ -13193,9 +13598,12 @@
         <v>0.0004482</v>
       </c>
       <c r="AC135" s="1" t="n">
+        <v>0.0004492</v>
+      </c>
+      <c r="AD135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="AD135" s="1" t="n">
+      <c r="AE135" s="1" t="n">
         <v>0.0004482</v>
       </c>
     </row>
@@ -13287,10 +13695,13 @@
         <v>0.001892</v>
       </c>
       <c r="AC136" s="1" t="n">
+        <v>0.001877</v>
+      </c>
+      <c r="AD136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="AD136" s="1" t="n">
-        <v>0.001881</v>
+      <c r="AE136" s="1" t="n">
+        <v>0.001877</v>
       </c>
     </row>
     <row r="137">
@@ -13381,10 +13792,13 @@
         <v>0.3071</v>
       </c>
       <c r="AC137" s="1" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AD137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="AD137" s="1" t="n">
-        <v>0.3071</v>
+      <c r="AE137" s="1" t="n">
+        <v>0.3065</v>
       </c>
     </row>
     <row r="138">
@@ -13475,10 +13889,13 @@
         <v>0.5508</v>
       </c>
       <c r="AC138" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="AD138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="AD138" s="1" t="n">
-        <v>0.5508</v>
+      <c r="AE138" s="1" t="n">
+        <v>0.5501</v>
       </c>
     </row>
     <row r="139">
@@ -13569,9 +13986,12 @@
         <v>0.02118</v>
       </c>
       <c r="AC139" s="1" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="AD139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="AD139" s="1" t="n">
+      <c r="AE139" s="1" t="n">
         <v>0.02115</v>
       </c>
     </row>
@@ -13663,10 +14083,13 @@
         <v>0.07858</v>
       </c>
       <c r="AC140" s="1" t="n">
+        <v>0.07853</v>
+      </c>
+      <c r="AD140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="AD140" s="1" t="n">
-        <v>0.07858</v>
+      <c r="AE140" s="1" t="n">
+        <v>0.07853</v>
       </c>
     </row>
     <row r="141">
@@ -13757,9 +14180,12 @@
         <v>0.001525</v>
       </c>
       <c r="AC141" s="1" t="n">
+        <v>0.001521</v>
+      </c>
+      <c r="AD141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="AD141" s="1" t="n">
+      <c r="AE141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -13851,9 +14277,12 @@
         <v>0.4466</v>
       </c>
       <c r="AC142" s="1" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="AD142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="AD142" s="1" t="n">
+      <c r="AE142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -13945,9 +14374,12 @@
         <v>0.029604</v>
       </c>
       <c r="AC143" s="1" t="n">
+        <v>0.029755</v>
+      </c>
+      <c r="AD143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="AD143" s="1" t="n">
+      <c r="AE143" s="1" t="n">
         <v>0.029604</v>
       </c>
     </row>
@@ -14039,9 +14471,12 @@
         <v>0.000225</v>
       </c>
       <c r="AC144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="AD144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="AD144" s="1" t="n">
+      <c r="AE144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -14133,9 +14568,12 @@
         <v>0.03386</v>
       </c>
       <c r="AC145" s="1" t="n">
+        <v>0.03436</v>
+      </c>
+      <c r="AD145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="AD145" s="1" t="n">
+      <c r="AE145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -14227,9 +14665,12 @@
         <v>0.11787</v>
       </c>
       <c r="AC146" s="1" t="n">
+        <v>0.11785</v>
+      </c>
+      <c r="AD146" s="1" t="n">
         <v>0.11787</v>
       </c>
-      <c r="AD146" s="1" t="n">
+      <c r="AE146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -14321,9 +14762,12 @@
         <v>0.02192</v>
       </c>
       <c r="AC147" s="1" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="AD147" s="1" t="n">
         <v>0.02258</v>
       </c>
-      <c r="AD147" s="1" t="n">
+      <c r="AE147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -14415,9 +14859,12 @@
         <v>1.4029</v>
       </c>
       <c r="AC148" s="1" t="n">
+        <v>1.4036</v>
+      </c>
+      <c r="AD148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="AD148" s="1" t="n">
+      <c r="AE148" s="1" t="n">
         <v>1.4029</v>
       </c>
     </row>
@@ -14509,9 +14956,12 @@
         <v>1.8417</v>
       </c>
       <c r="AC149" s="1" t="n">
+        <v>1.8467</v>
+      </c>
+      <c r="AD149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="AD149" s="1" t="n">
+      <c r="AE149" s="1" t="n">
         <v>1.8417</v>
       </c>
     </row>
@@ -14603,9 +15053,12 @@
         <v>0.096</v>
       </c>
       <c r="AC150" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="AD150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="AD150" s="1" t="n">
+      <c r="AE150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -14697,9 +15150,12 @@
         <v>4.642</v>
       </c>
       <c r="AC151" s="1" t="n">
+        <v>4.627</v>
+      </c>
+      <c r="AD151" s="1" t="n">
         <v>4.731</v>
       </c>
-      <c r="AD151" s="1" t="n">
+      <c r="AE151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -14791,10 +15247,13 @@
         <v>5.519</v>
       </c>
       <c r="AC152" s="1" t="n">
+        <v>5.502</v>
+      </c>
+      <c r="AD152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="AD152" s="1" t="n">
-        <v>5.511</v>
+      <c r="AE152" s="1" t="n">
+        <v>5.502</v>
       </c>
     </row>
     <row r="153">
@@ -14885,9 +15344,12 @@
         <v>0.3174</v>
       </c>
       <c r="AC153" s="1" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AD153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="AD153" s="1" t="n">
+      <c r="AE153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -14979,9 +15441,12 @@
         <v>0.5807</v>
       </c>
       <c r="AC154" s="1" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="AD154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="AD154" s="1" t="n">
+      <c r="AE154" s="1" t="n">
         <v>0.5807</v>
       </c>
     </row>
@@ -15073,9 +15538,12 @@
         <v>0.0125</v>
       </c>
       <c r="AC155" s="1" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AD155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="AD155" s="1" t="n">
+      <c r="AE155" s="1" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -15167,9 +15635,12 @@
         <v>0.0956</v>
       </c>
       <c r="AC156" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="AD156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="AD156" s="1" t="n">
+      <c r="AE156" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -15261,10 +15732,13 @@
         <v>16.107</v>
       </c>
       <c r="AC157" s="1" t="n">
+        <v>16.101</v>
+      </c>
+      <c r="AD157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="AD157" s="1" t="n">
-        <v>16.107</v>
+      <c r="AE157" s="1" t="n">
+        <v>16.101</v>
       </c>
     </row>
     <row r="158">
@@ -15355,9 +15829,12 @@
         <v>0.05493</v>
       </c>
       <c r="AC158" s="1" t="n">
+        <v>0.05516</v>
+      </c>
+      <c r="AD158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="AD158" s="1" t="n">
+      <c r="AE158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -15449,10 +15926,13 @@
         <v>28.17</v>
       </c>
       <c r="AC159" s="1" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="AD159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="AD159" s="1" t="n">
-        <v>28.17</v>
+      <c r="AE159" s="1" t="n">
+        <v>28.14</v>
       </c>
     </row>
     <row r="160">
@@ -15543,9 +16023,12 @@
         <v>0.02126</v>
       </c>
       <c r="AC160" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="AD160" s="1" t="n">
         <v>0.0218</v>
       </c>
-      <c r="AD160" s="1" t="n">
+      <c r="AE160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -15637,10 +16120,13 @@
         <v>0.0006434</v>
       </c>
       <c r="AC161" s="1" t="n">
+        <v>0.0006426</v>
+      </c>
+      <c r="AD161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="AD161" s="1" t="n">
-        <v>0.0006434</v>
+      <c r="AE161" s="1" t="n">
+        <v>0.0006426</v>
       </c>
     </row>
     <row r="162">
@@ -15731,9 +16217,12 @@
         <v>0.3871</v>
       </c>
       <c r="AC162" s="1" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AD162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="AD162" s="1" t="n">
+      <c r="AE162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -15825,9 +16314,12 @@
         <v>0.1879</v>
       </c>
       <c r="AC163" s="1" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AD163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="AD163" s="1" t="n">
+      <c r="AE163" s="1" t="n">
         <v>0.1879</v>
       </c>
     </row>
@@ -15919,9 +16411,12 @@
         <v>0.312</v>
       </c>
       <c r="AC164" s="1" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AD164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="AD164" s="1" t="n">
+      <c r="AE164" s="1" t="n">
         <v>0.312</v>
       </c>
     </row>
@@ -16013,9 +16508,12 @@
         <v>0.372</v>
       </c>
       <c r="AC165" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AD165" s="1" t="n">
         <v>0.378</v>
       </c>
-      <c r="AD165" s="1" t="n">
+      <c r="AE165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -16107,9 +16605,12 @@
         <v>0.02223</v>
       </c>
       <c r="AC166" s="1" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="AD166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="AD166" s="1" t="n">
+      <c r="AE166" s="1" t="n">
         <v>0.02223</v>
       </c>
     </row>
@@ -16201,10 +16702,13 @@
         <v>0.007187</v>
       </c>
       <c r="AC167" s="1" t="n">
+        <v>0.007184</v>
+      </c>
+      <c r="AD167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="AD167" s="1" t="n">
-        <v>0.007187</v>
+      <c r="AE167" s="1" t="n">
+        <v>0.007184</v>
       </c>
     </row>
     <row r="168">
@@ -16295,9 +16799,12 @@
         <v>0.01312</v>
       </c>
       <c r="AC168" s="1" t="n">
+        <v>0.01315</v>
+      </c>
+      <c r="AD168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="AD168" s="1" t="n">
+      <c r="AE168" s="1" t="n">
         <v>0.01312</v>
       </c>
     </row>
@@ -16389,9 +16896,12 @@
         <v>0.2509</v>
       </c>
       <c r="AC169" s="1" t="n">
+        <v>0.25098</v>
+      </c>
+      <c r="AD169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="AD169" s="1" t="n">
+      <c r="AE169" s="1" t="n">
         <v>0.2509</v>
       </c>
     </row>
@@ -16483,9 +16993,12 @@
         <v>0.02219</v>
       </c>
       <c r="AC170" s="1" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="AD170" s="1" t="n">
         <v>0.02219</v>
       </c>
-      <c r="AD170" s="1" t="n">
+      <c r="AE170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -16577,10 +17090,13 @@
         <v>0.1708</v>
       </c>
       <c r="AC171" s="1" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="AD171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="AD171" s="1" t="n">
-        <v>0.1708</v>
+      <c r="AE171" s="1" t="n">
+        <v>0.1706</v>
       </c>
     </row>
     <row r="172">
@@ -16671,9 +17187,12 @@
         <v>0.089</v>
       </c>
       <c r="AC172" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AD172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="AD172" s="1" t="n">
+      <c r="AE172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -16765,10 +17284,13 @@
         <v>0.004642</v>
       </c>
       <c r="AC173" s="1" t="n">
+        <v>0.00464</v>
+      </c>
+      <c r="AD173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="AD173" s="1" t="n">
-        <v>0.004642</v>
+      <c r="AE173" s="1" t="n">
+        <v>0.00464</v>
       </c>
     </row>
     <row r="174">
@@ -16859,9 +17381,12 @@
         <v>0.439</v>
       </c>
       <c r="AC174" s="1" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="AD174" s="1" t="n">
         <v>0.4428</v>
       </c>
-      <c r="AD174" s="1" t="n">
+      <c r="AE174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -16953,9 +17478,12 @@
         <v>0.09166000000000001</v>
       </c>
       <c r="AC175" s="1" t="n">
+        <v>0.09199</v>
+      </c>
+      <c r="AD175" s="1" t="n">
         <v>0.09276</v>
       </c>
-      <c r="AD175" s="1" t="n">
+      <c r="AE175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -17047,10 +17575,13 @@
         <v>0.2401</v>
       </c>
       <c r="AC176" s="1" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="AD176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="AD176" s="1" t="n">
-        <v>0.2401</v>
+      <c r="AE176" s="1" t="n">
+        <v>0.2394</v>
       </c>
     </row>
     <row r="177">
@@ -17141,9 +17672,12 @@
         <v>0.01904</v>
       </c>
       <c r="AC177" s="1" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="AD177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="AD177" s="1" t="n">
+      <c r="AE177" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -17235,10 +17769,13 @@
         <v>6.021</v>
       </c>
       <c r="AC178" s="1" t="n">
+        <v>6.017</v>
+      </c>
+      <c r="AD178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="AD178" s="1" t="n">
-        <v>6.021</v>
+      <c r="AE178" s="1" t="n">
+        <v>6.017</v>
       </c>
     </row>
     <row r="179">
@@ -17329,9 +17866,12 @@
         <v>0.134</v>
       </c>
       <c r="AC179" s="1" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="AD179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="AD179" s="1" t="n">
+      <c r="AE179" s="1" t="n">
         <v>0.134</v>
       </c>
     </row>
@@ -17423,9 +17963,12 @@
         <v>0.004941</v>
       </c>
       <c r="AC180" s="1" t="n">
+        <v>0.004896</v>
+      </c>
+      <c r="AD180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="AD180" s="1" t="n">
+      <c r="AE180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -17517,9 +18060,12 @@
         <v>0.01179</v>
       </c>
       <c r="AC181" s="1" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="AD181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="AD181" s="1" t="n">
+      <c r="AE181" s="1" t="n">
         <v>0.01179</v>
       </c>
     </row>
@@ -17611,9 +18157,12 @@
         <v>0.007189</v>
       </c>
       <c r="AC182" s="1" t="n">
+        <v>0.007258</v>
+      </c>
+      <c r="AD182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="AD182" s="1" t="n">
+      <c r="AE182" s="1" t="n">
         <v>0.007168</v>
       </c>
     </row>
@@ -17705,9 +18254,12 @@
         <v>0.13202</v>
       </c>
       <c r="AC183" s="1" t="n">
+        <v>0.13148</v>
+      </c>
+      <c r="AD183" s="1" t="n">
         <v>0.13233</v>
       </c>
-      <c r="AD183" s="1" t="n">
+      <c r="AE183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -17799,9 +18351,12 @@
         <v>0.09608</v>
       </c>
       <c r="AC184" s="1" t="n">
+        <v>0.09629</v>
+      </c>
+      <c r="AD184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="AD184" s="1" t="n">
+      <c r="AE184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -17893,10 +18448,13 @@
         <v>0.00736</v>
       </c>
       <c r="AC185" s="1" t="n">
+        <v>0.00735</v>
+      </c>
+      <c r="AD185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="AD185" s="1" t="n">
-        <v>0.00736</v>
+      <c r="AE185" s="1" t="n">
+        <v>0.00735</v>
       </c>
     </row>
     <row r="186">
@@ -17987,9 +18545,12 @@
         <v>0.04797</v>
       </c>
       <c r="AC186" s="1" t="n">
+        <v>0.04798</v>
+      </c>
+      <c r="AD186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="AD186" s="1" t="n">
+      <c r="AE186" s="1" t="n">
         <v>0.04797</v>
       </c>
     </row>
@@ -18081,9 +18642,12 @@
         <v>0.02622</v>
       </c>
       <c r="AC187" s="1" t="n">
+        <v>0.02637</v>
+      </c>
+      <c r="AD187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="AD187" s="1" t="n">
+      <c r="AE187" s="1" t="n">
         <v>0.02622</v>
       </c>
     </row>
@@ -18175,9 +18739,12 @@
         <v>0.00322</v>
       </c>
       <c r="AC188" s="1" t="n">
+        <v>0.003228</v>
+      </c>
+      <c r="AD188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="AD188" s="1" t="n">
+      <c r="AE188" s="1" t="n">
         <v>0.00322</v>
       </c>
     </row>
@@ -18269,10 +18836,13 @@
         <v>0.2815</v>
       </c>
       <c r="AC189" s="1" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AD189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="AD189" s="1" t="n">
-        <v>0.2815</v>
+      <c r="AE189" s="1" t="n">
+        <v>0.2808</v>
       </c>
     </row>
     <row r="190">
@@ -18363,9 +18933,12 @@
         <v>0.01729</v>
       </c>
       <c r="AC190" s="1" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="AD190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="AD190" s="1" t="n">
+      <c r="AE190" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -18457,9 +19030,12 @@
         <v>0.254</v>
       </c>
       <c r="AC191" s="1" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="AD191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="AD191" s="1" t="n">
+      <c r="AE191" s="1" t="n">
         <v>0.254</v>
       </c>
     </row>
@@ -18551,10 +19127,13 @@
         <v>0.03695</v>
       </c>
       <c r="AC192" s="1" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="AD192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="AD192" s="1" t="n">
-        <v>0.03695</v>
+      <c r="AE192" s="1" t="n">
+        <v>0.03638</v>
       </c>
     </row>
     <row r="193">
@@ -18645,9 +19224,12 @@
         <v>0.0002179</v>
       </c>
       <c r="AC193" s="1" t="n">
+        <v>0.0002182</v>
+      </c>
+      <c r="AD193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="AD193" s="1" t="n">
+      <c r="AE193" s="1" t="n">
         <v>0.0002179</v>
       </c>
     </row>
@@ -18739,9 +19321,12 @@
         <v>4.02</v>
       </c>
       <c r="AC194" s="1" t="n">
+        <v>4.021</v>
+      </c>
+      <c r="AD194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="AD194" s="1" t="n">
+      <c r="AE194" s="1" t="n">
         <v>4.02</v>
       </c>
     </row>
@@ -18833,9 +19418,12 @@
         <v>0.999401</v>
       </c>
       <c r="AC195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="AD195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="AD195" s="1" t="n">
+      <c r="AE195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -18927,9 +19515,12 @@
         <v>4.304</v>
       </c>
       <c r="AC196" s="1" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="AD196" s="1" t="n">
         <v>4.368</v>
       </c>
-      <c r="AD196" s="1" t="n">
+      <c r="AE196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -19021,9 +19612,12 @@
         <v>0.15196</v>
       </c>
       <c r="AC197" s="1" t="n">
+        <v>0.15182</v>
+      </c>
+      <c r="AD197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="AD197" s="1" t="n">
+      <c r="AE197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -19115,9 +19709,12 @@
         <v>0.007744</v>
       </c>
       <c r="AC198" s="1" t="n">
+        <v>0.007826</v>
+      </c>
+      <c r="AD198" s="1" t="n">
         <v>0.007998999999999999</v>
       </c>
-      <c r="AD198" s="1" t="n">
+      <c r="AE198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -19209,9 +19806,12 @@
         <v>0.4502</v>
       </c>
       <c r="AC199" s="1" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AD199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="AD199" s="1" t="n">
+      <c r="AE199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -19303,10 +19903,13 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="AC200" s="1" t="n">
+        <v>0.5487</v>
+      </c>
+      <c r="AD200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="AD200" s="1" t="n">
-        <v>0.5649999999999999</v>
+      <c r="AE200" s="1" t="n">
+        <v>0.5487</v>
       </c>
     </row>
     <row r="201">
@@ -19397,10 +20000,13 @@
         <v>0.0915</v>
       </c>
       <c r="AC201" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="AD201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="AD201" s="1" t="n">
-        <v>0.0915</v>
+      <c r="AE201" s="1" t="n">
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -19491,9 +20097,12 @@
         <v>0.05966</v>
       </c>
       <c r="AC202" s="1" t="n">
+        <v>0.05966</v>
+      </c>
+      <c r="AD202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="AD202" s="1" t="n">
+      <c r="AE202" s="1" t="n">
         <v>0.05966</v>
       </c>
     </row>
@@ -19585,9 +20194,12 @@
         <v>0.008229999999999999</v>
       </c>
       <c r="AC203" s="1" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="AD203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="AD203" s="1" t="n">
+      <c r="AE203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -19679,9 +20291,12 @@
         <v>0.00409</v>
       </c>
       <c r="AC204" s="1" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="AD204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="AD204" s="1" t="n">
+      <c r="AE204" s="1" t="n">
         <v>0.00409</v>
       </c>
     </row>
@@ -19773,10 +20388,13 @@
         <v>0.008928</v>
       </c>
       <c r="AC205" s="1" t="n">
+        <v>0.008777999999999999</v>
+      </c>
+      <c r="AD205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="AD205" s="1" t="n">
-        <v>0.008928</v>
+      <c r="AE205" s="1" t="n">
+        <v>0.008777999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -19867,9 +20485,12 @@
         <v>0.2418</v>
       </c>
       <c r="AC206" s="1" t="n">
-        <v>0.2418</v>
+        <v>0.2423</v>
       </c>
       <c r="AD206" s="1" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="AE206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -19961,9 +20582,12 @@
         <v>0.02169</v>
       </c>
       <c r="AC207" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="AD207" s="1" t="n">
         <v>0.02169</v>
       </c>
-      <c r="AD207" s="1" t="n">
+      <c r="AE207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -20055,9 +20679,12 @@
         <v>0.2335</v>
       </c>
       <c r="AC208" s="1" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="AD208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="AD208" s="1" t="n">
+      <c r="AE208" s="1" t="n">
         <v>0.2335</v>
       </c>
     </row>
@@ -20149,10 +20776,13 @@
         <v>0.3524</v>
       </c>
       <c r="AC209" s="1" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AD209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="AD209" s="1" t="n">
-        <v>0.3524</v>
+      <c r="AE209" s="1" t="n">
+        <v>0.352</v>
       </c>
     </row>
     <row r="210">
@@ -20243,10 +20873,13 @@
         <v>0.04229</v>
       </c>
       <c r="AC210" s="1" t="n">
+        <v>0.04215</v>
+      </c>
+      <c r="AD210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="AD210" s="1" t="n">
-        <v>0.04229</v>
+      <c r="AE210" s="1" t="n">
+        <v>0.04215</v>
       </c>
     </row>
     <row r="211">
@@ -20337,9 +20970,12 @@
         <v>0.0004153</v>
       </c>
       <c r="AC211" s="1" t="n">
+        <v>0.0004166</v>
+      </c>
+      <c r="AD211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="AD211" s="1" t="n">
+      <c r="AE211" s="1" t="n">
         <v>0.0004153</v>
       </c>
     </row>
@@ -20431,9 +21067,12 @@
         <v>0.02103</v>
       </c>
       <c r="AC212" s="1" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="AD212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="AD212" s="1" t="n">
+      <c r="AE212" s="1" t="n">
         <v>0.02103</v>
       </c>
     </row>
@@ -20525,9 +21164,12 @@
         <v>0.1137</v>
       </c>
       <c r="AC213" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="AD213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="AD213" s="1" t="n">
+      <c r="AE213" s="1"